--- a/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
+++ b/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Path" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch Info" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_state" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News &amp; Sentiment" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_state" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +24,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="+0.00%;[Red]-0.00%;0.00%"/>
     <numFmt numFmtId="165" formatCode="₹#,##,##0;[Red]-₹#,##,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="168" formatCode="+0.00;-0.00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,6 +172,11 @@
       <b val="1"/>
       <color rgb="0064748B"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="002F4BD8"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="18">
@@ -376,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -595,6 +602,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1482,7 +1495,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 28-Sep-2026 13:27</t>
+          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2365,7 +2378,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 28-Sep-2026 13:27</t>
+          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10082,20 +10095,5698 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G158"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Positive News &amp; Sentiment</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Fetched 2026-09-29 02:53</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:36</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E5" s="80" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G5" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:19</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+        </is>
+      </c>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E6" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F6" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G6" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:10</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Nuclear Stocks With Earnings Growth Over 17%</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="E7" s="80" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F7" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G7" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:51</t>
+        </is>
+      </c>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>WION</t>
+        </is>
+      </c>
+      <c r="E8" s="80" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G8" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:36</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E9" s="80" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F9" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G9" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:42</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E10" s="80" t="n">
+        <v>-0.896</v>
+      </c>
+      <c r="F10" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G10" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:25</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E11" s="80" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="F11" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G11" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:16</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>hrtoday.in</t>
+        </is>
+      </c>
+      <c r="E12" s="80" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G12" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:48</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E13" s="80" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G13" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:56</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E14" s="80" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G14" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:46</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Falls 1,124 Points, Nifty Slips Below 22,800</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="E15" s="80" t="n">
+        <v>-0.318</v>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G15" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E16" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G16" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:06</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E17" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G17" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:20</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E18" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G18" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:15</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>Nifty, Sensex: History favours stock market comeback in October; stocks to watch</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="E19" s="80" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G19" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:03</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>Free Press Kashmir</t>
+        </is>
+      </c>
+      <c r="E20" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G20" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="E21" s="80" t="n">
+        <v>-0.8070000000000001</v>
+      </c>
+      <c r="F21" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G21" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:44</t>
+        </is>
+      </c>
+      <c r="C22" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="inlineStr">
+        <is>
+          <t>apacnewsnetwork.com</t>
+        </is>
+      </c>
+      <c r="E22" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G22" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B23" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:36</t>
+        </is>
+      </c>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E23" s="80" t="n">
+        <v>-0.806</v>
+      </c>
+      <c r="F23" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G23" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:06</t>
+        </is>
+      </c>
+      <c r="C24" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>CNBC TV18</t>
+        </is>
+      </c>
+      <c r="E24" s="80" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F24" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G24" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 06:47</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
+        </is>
+      </c>
+      <c r="D25" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E25" s="80" t="n">
+        <v>-0.791</v>
+      </c>
+      <c r="F25" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G25" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B26" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:52</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="inlineStr">
+        <is>
+          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E26" s="80" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F26" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G26" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:42</t>
+        </is>
+      </c>
+      <c r="C27" s="51" t="inlineStr">
+        <is>
+          <t>Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="inlineStr">
+        <is>
+          <t>India Infoline</t>
+        </is>
+      </c>
+      <c r="E27" s="80" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="F27" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G27" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:37</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E28" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G28" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:18</t>
+        </is>
+      </c>
+      <c r="C29" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E29" s="80" t="n">
+        <v>-0.6909999999999999</v>
+      </c>
+      <c r="F29" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G29" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:11</t>
+        </is>
+      </c>
+      <c r="C30" s="51" t="inlineStr">
+        <is>
+          <t>Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="E30" s="80" t="n">
+        <v>-0.852</v>
+      </c>
+      <c r="F30" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G30" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:45</t>
+        </is>
+      </c>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E31" s="80" t="n">
+        <v>-0.361</v>
+      </c>
+      <c r="F31" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G31" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:42</t>
+        </is>
+      </c>
+      <c r="C32" s="51" t="inlineStr">
+        <is>
+          <t>NSE stock slips below issue price of ₹1,785; down 2% on Monday</t>
+        </is>
+      </c>
+      <c r="D32" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E32" s="80" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F32" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G32" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B33" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:41</t>
+        </is>
+      </c>
+      <c r="C33" s="51" t="inlineStr">
+        <is>
+          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="E33" s="80" t="n">
+        <v>-0.758</v>
+      </c>
+      <c r="F33" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G33" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B34" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:29</t>
+        </is>
+      </c>
+      <c r="C34" s="51" t="inlineStr">
+        <is>
+          <t>Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%</t>
+        </is>
+      </c>
+      <c r="D34" s="51" t="inlineStr">
+        <is>
+          <t>newsdrum.in</t>
+        </is>
+      </c>
+      <c r="E34" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G34" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B35" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:25</t>
+        </is>
+      </c>
+      <c r="C35" s="51" t="inlineStr">
+        <is>
+          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
+        </is>
+      </c>
+      <c r="D35" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E35" s="80" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F35" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G35" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B36" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:17</t>
+        </is>
+      </c>
+      <c r="C36" s="51" t="inlineStr">
+        <is>
+          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
+        </is>
+      </c>
+      <c r="D36" s="51" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E36" s="80" t="n">
+        <v>-0.511</v>
+      </c>
+      <c r="F36" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G36" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:11</t>
+        </is>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
+        </is>
+      </c>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E37" s="80" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G37" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B38" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:08</t>
+        </is>
+      </c>
+      <c r="C38" s="51" t="inlineStr">
+        <is>
+          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="inlineStr">
+        <is>
+          <t>economictimes.com</t>
+        </is>
+      </c>
+      <c r="E38" s="80" t="n">
+        <v>-0.649</v>
+      </c>
+      <c r="F38" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G38" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B39" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:07</t>
+        </is>
+      </c>
+      <c r="C39" s="51" t="inlineStr">
+        <is>
+          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
+        </is>
+      </c>
+      <c r="D39" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E39" s="80" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F39" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G39" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B40" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:58</t>
+        </is>
+      </c>
+      <c r="C40" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
+        </is>
+      </c>
+      <c r="D40" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E40" s="80" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F40" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G40" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B41" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:54</t>
+        </is>
+      </c>
+      <c r="C41" s="51" t="inlineStr">
+        <is>
+          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
+        </is>
+      </c>
+      <c r="D41" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E41" s="80" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="F41" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G41" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:48</t>
+        </is>
+      </c>
+      <c r="C42" s="51" t="inlineStr">
+        <is>
+          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
+        </is>
+      </c>
+      <c r="D42" s="51" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E42" s="80" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F42" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G42" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B43" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:28</t>
+        </is>
+      </c>
+      <c r="C43" s="51" t="inlineStr">
+        <is>
+          <t>Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open</t>
+        </is>
+      </c>
+      <c r="D43" s="51" t="inlineStr">
+        <is>
+          <t>hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="E43" s="80" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="F43" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G43" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B44" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 02:19</t>
+        </is>
+      </c>
+      <c r="C44" s="51" t="inlineStr">
+        <is>
+          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
+        </is>
+      </c>
+      <c r="D44" s="51" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E44" s="80" t="n">
+        <v>-0.542</v>
+      </c>
+      <c r="F44" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G44" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B45" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:58</t>
+        </is>
+      </c>
+      <c r="C45" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices — Five Key Factors For Sensex, Nifty 50 On September 28</t>
+        </is>
+      </c>
+      <c r="D45" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E45" s="80" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F45" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G45" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B46" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:20</t>
+        </is>
+      </c>
+      <c r="C46" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
+        </is>
+      </c>
+      <c r="D46" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E46" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F46" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G46" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B47" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:30</t>
+        </is>
+      </c>
+      <c r="C47" s="51" t="inlineStr">
+        <is>
+          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
+        </is>
+      </c>
+      <c r="D47" s="51" t="inlineStr">
+        <is>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E47" s="80" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F47" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G47" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B48" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 17:20</t>
+        </is>
+      </c>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
+        </is>
+      </c>
+      <c r="D48" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E48" s="80" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F48" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G48" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B49" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:03</t>
+        </is>
+      </c>
+      <c r="C49" s="51" t="inlineStr">
+        <is>
+          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
+        </is>
+      </c>
+      <c r="D49" s="51" t="inlineStr">
+        <is>
+          <t>economictimes.com</t>
+        </is>
+      </c>
+      <c r="E49" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G49" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B50" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:48</t>
+        </is>
+      </c>
+      <c r="C50" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
+        </is>
+      </c>
+      <c r="D50" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E50" s="80" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F50" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G50" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="51" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B51" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 06:44</t>
+        </is>
+      </c>
+      <c r="C51" s="51" t="inlineStr">
+        <is>
+          <t>Acutaas shareholders reject ESOP scheme for subsidiary employees at AGM</t>
+        </is>
+      </c>
+      <c r="D51" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E51" s="80" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F51" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G51" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B52" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 04:22</t>
+        </is>
+      </c>
+      <c r="C52" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
+        </is>
+      </c>
+      <c r="D52" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E52" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F52" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G52" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 22:56</t>
+        </is>
+      </c>
+      <c r="C53" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
+        </is>
+      </c>
+      <c r="D53" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E53" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G53" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B54" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:51</t>
+        </is>
+      </c>
+      <c r="C54" s="51" t="inlineStr">
+        <is>
+          <t>🚦 Indian Markets Stuck In A Jam! But who's responsible for the traffic? 🤔 A Bernstein note argues that India’s large caps are stuck in a bygone economic era. But here's the BIG question: 🇮🇳 Is The Market’s Fate Really In India’s Hands? 🌍 Or are global cues pul</t>
+        </is>
+      </c>
+      <c r="D54" s="51" t="inlineStr">
+        <is>
+          <t>linkedin.com</t>
+        </is>
+      </c>
+      <c r="E54" s="80" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="F54" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G54" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B55" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:11</t>
+        </is>
+      </c>
+      <c r="C55" s="51" t="inlineStr">
+        <is>
+          <t>Share Market News: Nifty 50 Outlook &amp; Prediction</t>
+        </is>
+      </c>
+      <c r="D55" s="51" t="inlineStr">
+        <is>
+          <t>Liquide Blog</t>
+        </is>
+      </c>
+      <c r="E55" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F55" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G55" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B56" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 09:15</t>
+        </is>
+      </c>
+      <c r="C56" s="51" t="inlineStr">
+        <is>
+          <t>Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide</t>
+        </is>
+      </c>
+      <c r="D56" s="51" t="inlineStr">
+        <is>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="E56" s="80" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="F56" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G56" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="51" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B57" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:48</t>
+        </is>
+      </c>
+      <c r="C57" s="51" t="inlineStr">
+        <is>
+          <t>Thangamayil Jewellery Shuts Trading Window Ahead of September-Quarter Results</t>
+        </is>
+      </c>
+      <c r="D57" s="51" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="E57" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G57" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="51" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B58" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:30</t>
+        </is>
+      </c>
+      <c r="C58" s="51" t="inlineStr">
+        <is>
+          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
+        </is>
+      </c>
+      <c r="D58" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E58" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G58" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="51" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B59" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 00:50</t>
+        </is>
+      </c>
+      <c r="C59" s="51" t="inlineStr">
+        <is>
+          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
+        </is>
+      </c>
+      <c r="D59" s="51" t="inlineStr">
+        <is>
+          <t>Alice Blue</t>
+        </is>
+      </c>
+      <c r="E59" s="80" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F59" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G59" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B60" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:34</t>
+        </is>
+      </c>
+      <c r="C60" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
+        </is>
+      </c>
+      <c r="D60" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E60" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G60" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B61" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="C61" s="51" t="inlineStr">
+        <is>
+          <t>PERSISTENT Stock Price and Chart — NSE:PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D61" s="51" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="E61" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G61" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B62" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:04</t>
+        </is>
+      </c>
+      <c r="C62" s="51" t="inlineStr">
+        <is>
+          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
+        </is>
+      </c>
+      <c r="D62" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E62" s="80" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="F62" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G62" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:52</t>
+        </is>
+      </c>
+      <c r="C63" s="51" t="inlineStr">
+        <is>
+          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
+        </is>
+      </c>
+      <c r="D63" s="51" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E63" s="80" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F63" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G63" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="51" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:22</t>
+        </is>
+      </c>
+      <c r="C64" s="51" t="inlineStr">
+        <is>
+          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
+        </is>
+      </c>
+      <c r="D64" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E64" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G64" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:42</t>
+        </is>
+      </c>
+      <c r="C65" s="51" t="inlineStr">
+        <is>
+          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
+        </is>
+      </c>
+      <c r="D65" s="51" t="inlineStr">
+        <is>
+          <t>CNBC TV18</t>
+        </is>
+      </c>
+      <c r="E65" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G65" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B66" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:03</t>
+        </is>
+      </c>
+      <c r="C66" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%</t>
+        </is>
+      </c>
+      <c r="D66" s="51" t="inlineStr">
+        <is>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E66" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F66" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G66" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:01</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>Stock markets bounce back on value buying; Sensex rises 315 pts</t>
+        </is>
+      </c>
+      <c r="D67" s="51" t="inlineStr">
+        <is>
+          <t>DD India</t>
+        </is>
+      </c>
+      <c r="E67" s="80" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F67" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G67" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B68" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:48</t>
+        </is>
+      </c>
+      <c r="C68" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty Rebound on Value Buying After Sharp Losses</t>
+        </is>
+      </c>
+      <c r="D68" s="51" t="inlineStr">
+        <is>
+          <t>Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="E68" s="80" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F68" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G68" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B69" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:31</t>
+        </is>
+      </c>
+      <c r="C69" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses</t>
+        </is>
+      </c>
+      <c r="D69" s="51" t="inlineStr">
+        <is>
+          <t>apacnewsnetwork.com</t>
+        </is>
+      </c>
+      <c r="E69" s="80" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="F69" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G69" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B70" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:19</t>
+        </is>
+      </c>
+      <c r="C70" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today | Stock Market Live: Sensex rises 150 pts, Nifty eyes 23,100; realty gains, IT slips</t>
+        </is>
+      </c>
+      <c r="D70" s="51" t="inlineStr">
+        <is>
+          <t>IndiaIPO</t>
+        </is>
+      </c>
+      <c r="E70" s="80" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F70" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G70" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B71" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="C71" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX INDUSTRIES LTD Share Price</t>
+        </is>
+      </c>
+      <c r="D71" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E71" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G71" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B72" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="C72" s="51" t="inlineStr">
+        <is>
+          <t>Sah Polymers Share Price</t>
+        </is>
+      </c>
+      <c r="D72" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E72" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G72" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B73" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="C73" s="51" t="inlineStr">
+        <is>
+          <t>Laser Power &amp; Infra Ltd Share Price Today,, LASERPOWER Share Price NSE, BSE</t>
+        </is>
+      </c>
+      <c r="D73" s="51" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="E73" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G73" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B74" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="C74" s="51" t="inlineStr">
+        <is>
+          <t>Nifty Chemicals (NFTCHEMIC) Share Price</t>
+        </is>
+      </c>
+      <c r="D74" s="51" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="E74" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F74" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G74" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B75" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="C75" s="51" t="inlineStr">
+        <is>
+          <t>JSW Holdings Share Price Today, JSW Holdings Stock Price Live NSE/BSE Updates</t>
+        </is>
+      </c>
+      <c r="D75" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E75" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G75" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="51" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B76" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:49</t>
+        </is>
+      </c>
+      <c r="C76" s="51" t="inlineStr">
+        <is>
+          <t>Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today</t>
+        </is>
+      </c>
+      <c r="D76" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E76" s="80" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="F76" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G76" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B77" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:07</t>
+        </is>
+      </c>
+      <c r="C77" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty struggle for direction as oil, US yields weigh</t>
+        </is>
+      </c>
+      <c r="D77" s="51" t="inlineStr">
+        <is>
+          <t>PSU Watch</t>
+        </is>
+      </c>
+      <c r="E77" s="80" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="F77" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G77" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B78" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:52</t>
+        </is>
+      </c>
+      <c r="C78" s="51" t="inlineStr">
+        <is>
+          <t>Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons</t>
+        </is>
+      </c>
+      <c r="D78" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E78" s="80" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="F78" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G78" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B79" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:32</t>
+        </is>
+      </c>
+      <c r="C79" s="51" t="inlineStr">
+        <is>
+          <t>NSE shares dip on day 2 of listing, brokerages back long-term growth story</t>
+        </is>
+      </c>
+      <c r="D79" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E79" s="80" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="F79" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G79" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B80" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:09</t>
+        </is>
+      </c>
+      <c r="C80" s="51" t="inlineStr">
+        <is>
+          <t>Stock Markets Today: Sensex, Nifty up in Volatile Trade</t>
+        </is>
+      </c>
+      <c r="D80" s="51" t="inlineStr">
+        <is>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="E80" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F80" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G80" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B81" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:04</t>
+        </is>
+      </c>
+      <c r="C81" s="51" t="inlineStr">
+        <is>
+          <t>Stock markets turn volatile as oil prices, rising bond yields weigh on sentiments</t>
+        </is>
+      </c>
+      <c r="D81" s="51" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="E81" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G81" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B82" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:53</t>
+        </is>
+      </c>
+      <c r="C82" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty volatile after early rebound as crude, bond yields weigh</t>
+        </is>
+      </c>
+      <c r="D82" s="51" t="inlineStr">
+        <is>
+          <t>Telangana Today</t>
+        </is>
+      </c>
+      <c r="E82" s="80" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F82" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G82" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:52</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks vs ESDS: AI Cloud Business Models and Financials Compared</t>
+        </is>
+      </c>
+      <c r="D83" s="51" t="inlineStr">
+        <is>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="E83" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G83" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B84" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:45</t>
+        </is>
+      </c>
+      <c r="C84" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty Open Higher; IT Stocks Drag Market</t>
+        </is>
+      </c>
+      <c r="D84" s="51" t="inlineStr">
+        <is>
+          <t>hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="E84" s="80" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="F84" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G84" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B85" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:24</t>
+        </is>
+      </c>
+      <c r="C85" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty open cautiously today; IT stocks bleed as crude, yields bite</t>
+        </is>
+      </c>
+      <c r="D85" s="51" t="inlineStr">
+        <is>
+          <t>BusinessLine</t>
+        </is>
+      </c>
+      <c r="E85" s="80" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F85" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G85" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B86" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:11</t>
+        </is>
+      </c>
+      <c r="C86" s="51" t="inlineStr">
+        <is>
+          <t>Stock markets rebound in early trade: Sensex climbs 86 points, Nifty up 18.80 points</t>
+        </is>
+      </c>
+      <c r="D86" s="51" t="inlineStr">
+        <is>
+          <t>Telegraph India</t>
+        </is>
+      </c>
+      <c r="E86" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F86" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G86" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 03:51</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
+          <t>Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050</t>
+        </is>
+      </c>
+      <c r="D87" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E87" s="80" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="F87" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G87" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:58</t>
+        </is>
+      </c>
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty opening: Will the stock market fall again today?</t>
+        </is>
+      </c>
+      <c r="D88" s="51" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E88" s="80" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F88" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G88" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B89" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:18</t>
+        </is>
+      </c>
+      <c r="C89" s="51" t="inlineStr">
+        <is>
+          <t>Stock market today: Sensex, Nifty may open flat amid key headwinds</t>
+        </is>
+      </c>
+      <c r="D89" s="51" t="inlineStr">
+        <is>
+          <t>BusinessLine</t>
+        </is>
+      </c>
+      <c r="E89" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F89" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G89" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B90" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:06</t>
+        </is>
+      </c>
+      <c r="C90" s="51" t="inlineStr">
+        <is>
+          <t>Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...</t>
+        </is>
+      </c>
+      <c r="D90" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E90" s="80" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="F90" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G90" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B91" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 01:28</t>
+        </is>
+      </c>
+      <c r="C91" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, Bond Yields To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On September 25</t>
+        </is>
+      </c>
+      <c r="D91" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E91" s="80" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F91" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G91" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B92" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 01:15</t>
+        </is>
+      </c>
+      <c r="C92" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for 25 Sept 2026 | GIFT Nifty, Nikkei, Taiwan cues to watch</t>
+        </is>
+      </c>
+      <c r="D92" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E92" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F92" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G92" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B93" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:13</t>
+        </is>
+      </c>
+      <c r="C93" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Nuclear Stocks With Revenue Growth Up To 16%</t>
+        </is>
+      </c>
+      <c r="D93" s="51" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="E93" s="80" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="F93" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G93" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B94" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:46</t>
+        </is>
+      </c>
+      <c r="C94" s="51" t="inlineStr">
+        <is>
+          <t>R R Kabel acquires U M Cables business for Rs. 77 crores</t>
+        </is>
+      </c>
+      <c r="D94" s="51" t="inlineStr">
+        <is>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="E94" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G94" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B95" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:31</t>
+        </is>
+      </c>
+      <c r="C95" s="51" t="inlineStr">
+        <is>
+          <t>Usha Martin announces Rs. 77 crore slump sale of U M Cables to R R Kabel</t>
+        </is>
+      </c>
+      <c r="D95" s="51" t="inlineStr">
+        <is>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="E95" s="80" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="F95" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G95" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B96" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:21</t>
+        </is>
+      </c>
+      <c r="C96" s="51" t="inlineStr">
+        <is>
+          <t>R R Kabel acquires U M Cables business for ₹77 crore</t>
+        </is>
+      </c>
+      <c r="D96" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E96" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G96" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B97" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:04</t>
+        </is>
+      </c>
+      <c r="C97" s="51" t="inlineStr">
+        <is>
+          <t>Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets</t>
+        </is>
+      </c>
+      <c r="D97" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E97" s="80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F97" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G97" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="51" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B98" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:42</t>
+        </is>
+      </c>
+      <c r="C98" s="51" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics</t>
+        </is>
+      </c>
+      <c r="D98" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E98" s="80" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F98" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G98" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B99" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:49</t>
+        </is>
+      </c>
+      <c r="C99" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month</t>
+        </is>
+      </c>
+      <c r="D99" s="51" t="inlineStr">
+        <is>
+          <t>economictimes.com</t>
+        </is>
+      </c>
+      <c r="E99" s="80" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="F99" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G99" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B100" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:01</t>
+        </is>
+      </c>
+      <c r="C100" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Export Stocks That Could Benefit From A Weaker Rupee</t>
+        </is>
+      </c>
+      <c r="D100" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E100" s="80" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F100" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G100" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B101" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:51</t>
+        </is>
+      </c>
+      <c r="C101" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty slide on intense selloff, banking and financial stocks hit</t>
+        </is>
+      </c>
+      <c r="D101" s="51" t="inlineStr">
+        <is>
+          <t>The South First</t>
+        </is>
+      </c>
+      <c r="E101" s="80" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F101" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G101" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B102" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:36</t>
+        </is>
+      </c>
+      <c r="C102" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026</t>
+        </is>
+      </c>
+      <c r="D102" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E102" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F102" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G102" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B103" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:02</t>
+        </is>
+      </c>
+      <c r="C103" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty down over 1.6%: How crude oil, bond yields hit Indian markets</t>
+        </is>
+      </c>
+      <c r="D103" s="51" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="E103" s="80" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F103" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G103" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B104" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:51</t>
+        </is>
+      </c>
+      <c r="C104" s="51" t="inlineStr">
+        <is>
+          <t>Gift Nifty Signals Higher Opening After Sensex, Nifty Crash</t>
+        </is>
+      </c>
+      <c r="D104" s="51" t="inlineStr">
+        <is>
+          <t>hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="E104" s="80" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="F104" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G104" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B105" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:21</t>
+        </is>
+      </c>
+      <c r="C105" s="51" t="inlineStr">
+        <is>
+          <t>Sensex closes in red, Nifty settles below 23,100 on spike in crude oil</t>
+        </is>
+      </c>
+      <c r="D105" s="51" t="inlineStr">
+        <is>
+          <t>DD News</t>
+        </is>
+      </c>
+      <c r="E105" s="80" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F105" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G105" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:20</t>
+        </is>
+      </c>
+      <c r="C106" s="51" t="inlineStr">
+        <is>
+          <t>NSE shares end debut at ₹1,818, gain 1.85%; BSE slips nearly 3% amid broader market sell-off</t>
+        </is>
+      </c>
+      <c r="D106" s="51" t="inlineStr">
+        <is>
+          <t>fortuneindia.com</t>
+        </is>
+      </c>
+      <c r="E106" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G106" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B107" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:01</t>
+        </is>
+      </c>
+      <c r="C107" s="51" t="inlineStr">
+        <is>
+          <t>SENSEX Nifty Today: Nifty Settles at 23,063; Sensex Crashes1200 Points as Crude Oil Surges Above $105; India VIX Jumps 25%</t>
+        </is>
+      </c>
+      <c r="D107" s="51" t="inlineStr">
+        <is>
+          <t>India Infoline</t>
+        </is>
+      </c>
+      <c r="E107" s="80" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="F107" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G107" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B108" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:57</t>
+        </is>
+      </c>
+      <c r="C108" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty see worst day in weeks: Why was market down today? | Business News</t>
+        </is>
+      </c>
+      <c r="D108" s="51" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E108" s="80" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F108" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G108" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B109" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:44</t>
+        </is>
+      </c>
+      <c r="C109" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Sensex Crashes 1,200 Points, Nifty Falls</t>
+        </is>
+      </c>
+      <c r="D109" s="51" t="inlineStr">
+        <is>
+          <t>apacnewsnetwork.com</t>
+        </is>
+      </c>
+      <c r="E109" s="80" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F109" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G109" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B110" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:40</t>
+        </is>
+      </c>
+      <c r="C110" s="51" t="inlineStr">
+        <is>
+          <t>Sensex plunges 1,248 points, Nifty nosedives 1.64%; five factors behind market slump</t>
+        </is>
+      </c>
+      <c r="D110" s="51" t="inlineStr">
+        <is>
+          <t>fortuneindia.com</t>
+        </is>
+      </c>
+      <c r="E110" s="80" t="n">
+        <v>-0.612</v>
+      </c>
+      <c r="F110" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G110" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="51" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B111" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:15</t>
+        </is>
+      </c>
+      <c r="C111" s="51" t="inlineStr">
+        <is>
+          <t>TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026</t>
+        </is>
+      </c>
+      <c r="D111" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E111" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G111" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B112" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:06</t>
+        </is>
+      </c>
+      <c r="C112" s="51" t="inlineStr">
+        <is>
+          <t>Stock markets hit three-month low: Sensex drops over 1,200 points</t>
+        </is>
+      </c>
+      <c r="D112" s="51" t="inlineStr">
+        <is>
+          <t>Telegraph India</t>
+        </is>
+      </c>
+      <c r="E112" s="80" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F112" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G112" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B113" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="C113" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks</t>
+        </is>
+      </c>
+      <c r="D113" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E113" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G113" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B114" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:42</t>
+        </is>
+      </c>
+      <c r="C114" s="51" t="inlineStr">
+        <is>
+          <t>The battle between India’s stock exchanges is heating up again</t>
+        </is>
+      </c>
+      <c r="D114" s="51" t="inlineStr">
+        <is>
+          <t>The Economist</t>
+        </is>
+      </c>
+      <c r="E114" s="80" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F114" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G114" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B115" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:40</t>
+        </is>
+      </c>
+      <c r="C115" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss</t>
+        </is>
+      </c>
+      <c r="D115" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E115" s="80" t="n">
+        <v>-0.758</v>
+      </c>
+      <c r="F115" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G115" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B116" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:08</t>
+        </is>
+      </c>
+      <c r="C116" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday</t>
+        </is>
+      </c>
+      <c r="D116" s="51" t="inlineStr">
+        <is>
+          <t>CNBC TV18</t>
+        </is>
+      </c>
+      <c r="E116" s="80" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F116" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G116" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B117" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:04</t>
+        </is>
+      </c>
+      <c r="C117" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Tumbles 1,200 Points, Nifty Cracks Below 23,100 – Key Reasons Behind Sell-Off</t>
+        </is>
+      </c>
+      <c r="D117" s="51" t="inlineStr">
+        <is>
+          <t>Outlook Money</t>
+        </is>
+      </c>
+      <c r="E117" s="80" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="F117" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G117" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B118" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:02</t>
+        </is>
+      </c>
+      <c r="C118" s="51" t="inlineStr">
+        <is>
+          <t>Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today</t>
+        </is>
+      </c>
+      <c r="D118" s="51" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="E118" s="80" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F118" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G118" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B119" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:52</t>
+        </is>
+      </c>
+      <c r="C119" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall</t>
+        </is>
+      </c>
+      <c r="D119" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E119" s="80" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F119" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G119" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B120" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:50</t>
+        </is>
+      </c>
+      <c r="C120" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Investors Lose Rs 3.93 Lakh Crore As Sensex, Nifty Hit Three-Month Low</t>
+        </is>
+      </c>
+      <c r="D120" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E120" s="80" t="n">
+        <v>-0.758</v>
+      </c>
+      <c r="F120" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G120" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B121" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:46</t>
+        </is>
+      </c>
+      <c r="C121" s="51" t="inlineStr">
+        <is>
+          <t>Hero Motors Ltd leads gainers in 'B' group</t>
+        </is>
+      </c>
+      <c r="D121" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E121" s="80" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F121" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G121" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B122" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:35</t>
+        </is>
+      </c>
+      <c r="C122" s="51" t="inlineStr">
+        <is>
+          <t>TD Power Systems Share Price today: decline and analysis</t>
+        </is>
+      </c>
+      <c r="D122" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E122" s="80" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F122" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G122" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B123" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:21</t>
+        </is>
+      </c>
+      <c r="C123" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D123" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E123" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G123" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B124" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:35</t>
+        </is>
+      </c>
+      <c r="C124" s="51" t="inlineStr">
+        <is>
+          <t>Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices</t>
+        </is>
+      </c>
+      <c r="D124" s="51" t="inlineStr">
+        <is>
+          <t>theweek.in</t>
+        </is>
+      </c>
+      <c r="E124" s="80" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F124" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G124" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B125" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25</t>
+        </is>
+      </c>
+      <c r="C125" s="51" t="inlineStr">
+        <is>
+          <t>Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom — Ask Profit</t>
+        </is>
+      </c>
+      <c r="D125" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E125" s="80" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F125" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G125" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B126" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 06:33</t>
+        </is>
+      </c>
+      <c r="C126" s="51" t="inlineStr">
+        <is>
+          <t>NSE Share Price Rises 3.45%: IFCI, New India Assurance, GIC Re in Focus After NSE IPO Listing</t>
+        </is>
+      </c>
+      <c r="D126" s="51" t="inlineStr">
+        <is>
+          <t>India Infoline</t>
+        </is>
+      </c>
+      <c r="E126" s="80" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F126" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G126" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B127" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 06:20</t>
+        </is>
+      </c>
+      <c r="C127" s="51" t="inlineStr">
+        <is>
+          <t>Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest</t>
+        </is>
+      </c>
+      <c r="D127" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E127" s="80" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="F127" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G127" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B128" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 05:58</t>
+        </is>
+      </c>
+      <c r="C128" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Tomorrow: NSE, BSE Open on September 25</t>
+        </is>
+      </c>
+      <c r="D128" s="51" t="inlineStr">
+        <is>
+          <t>hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="E128" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G128" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B129" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 05:29</t>
+        </is>
+      </c>
+      <c r="C129" s="51" t="inlineStr">
+        <is>
+          <t>Stock Markets Today: Sensex, Nifty in Red; BSE tanked over 600 points</t>
+        </is>
+      </c>
+      <c r="D129" s="51" t="inlineStr">
+        <is>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="E129" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F129" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G129" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B130" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:55</t>
+        </is>
+      </c>
+      <c r="C130" s="51" t="inlineStr">
+        <is>
+          <t>Sensex opens in red, Nifty below 23,300 points</t>
+        </is>
+      </c>
+      <c r="D130" s="51" t="inlineStr">
+        <is>
+          <t>DD India</t>
+        </is>
+      </c>
+      <c r="E130" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F130" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G130" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B131" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:44</t>
+        </is>
+      </c>
+      <c r="C131" s="51" t="inlineStr">
+        <is>
+          <t>Sensex crashed over 1,200 points: Why stock market fell today?</t>
+        </is>
+      </c>
+      <c r="D131" s="51" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E131" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G131" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B132" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:31</t>
+        </is>
+      </c>
+      <c r="C132" s="51" t="inlineStr">
+        <is>
+          <t>NSE vs BSE: Which exchange should now be the preferred bet for investors?</t>
+        </is>
+      </c>
+      <c r="D132" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E132" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G132" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B133" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:12</t>
+        </is>
+      </c>
+      <c r="C133" s="51" t="inlineStr">
+        <is>
+          <t>Indian Stocks Slide At Open As Nifty, Sensex Extend Market Weakness</t>
+        </is>
+      </c>
+      <c r="D133" s="51" t="inlineStr">
+        <is>
+          <t>Investing.com India</t>
+        </is>
+      </c>
+      <c r="E133" s="80" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="F133" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G133" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B134" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:09</t>
+        </is>
+      </c>
+      <c r="C134" s="51" t="inlineStr">
+        <is>
+          <t>Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'</t>
+        </is>
+      </c>
+      <c r="D134" s="51" t="inlineStr">
+        <is>
+          <t>economictimes.com</t>
+        </is>
+      </c>
+      <c r="E134" s="80" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F134" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G134" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B135" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:02</t>
+        </is>
+      </c>
+      <c r="C135" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash: Nifty 50, Sensex fall 1% as crude tops $102; financial, insurance stocks slide on IRDAI proposal</t>
+        </is>
+      </c>
+      <c r="D135" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E135" s="80" t="n">
+        <v>-0.599</v>
+      </c>
+      <c r="F135" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G135" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B136" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 03:56</t>
+        </is>
+      </c>
+      <c r="C136" s="51" t="inlineStr">
+        <is>
+          <t>Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash</t>
+        </is>
+      </c>
+      <c r="D136" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E136" s="80" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F136" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G136" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B137" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:46</t>
+        </is>
+      </c>
+      <c r="C137" s="51" t="inlineStr">
+        <is>
+          <t>Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs</t>
+        </is>
+      </c>
+      <c r="D137" s="51" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E137" s="80" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="F137" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G137" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B138" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:44</t>
+        </is>
+      </c>
+      <c r="C138" s="51" t="inlineStr">
+        <is>
+          <t>US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact</t>
+        </is>
+      </c>
+      <c r="D138" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E138" s="80" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="F138" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G138" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B139" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:38</t>
+        </is>
+      </c>
+      <c r="C139" s="51" t="inlineStr">
+        <is>
+          <t>GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...</t>
+        </is>
+      </c>
+      <c r="D139" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E139" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F139" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G139" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B140" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 01:42</t>
+        </is>
+      </c>
+      <c r="C140" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields — Five Key Factors For Sensex, Nifty 50 On Sept 24</t>
+        </is>
+      </c>
+      <c r="D140" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E140" s="80" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F140" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G140" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B141" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 01:17</t>
+        </is>
+      </c>
+      <c r="C141" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals</t>
+        </is>
+      </c>
+      <c r="D141" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E141" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F141" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G141" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B142" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:57</t>
+        </is>
+      </c>
+      <c r="C142" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs stock gains 1.37 percent as profit jumps 126 percent</t>
+        </is>
+      </c>
+      <c r="D142" s="51" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="E142" s="80" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="F142" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G142" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B143" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:57</t>
+        </is>
+      </c>
+      <c r="C143" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month</t>
+        </is>
+      </c>
+      <c r="D143" s="51" t="inlineStr">
+        <is>
+          <t>economictimes.com</t>
+        </is>
+      </c>
+      <c r="E143" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G143" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="51" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B144" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:02</t>
+        </is>
+      </c>
+      <c r="C144" s="51" t="inlineStr">
+        <is>
+          <t>Diamond Power Infrastructure Share Price Rises 2.68% Today</t>
+        </is>
+      </c>
+      <c r="D144" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E144" s="80" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F144" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G144" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B145" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:19</t>
+        </is>
+      </c>
+      <c r="C145" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs Share Price: one-year high and valuation view</t>
+        </is>
+      </c>
+      <c r="D145" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E145" s="80" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="F145" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G145" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B146" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:59</t>
+        </is>
+      </c>
+      <c r="C146" s="51" t="inlineStr">
+        <is>
+          <t>NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details</t>
+        </is>
+      </c>
+      <c r="D146" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E146" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G146" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B147" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:26</t>
+        </is>
+      </c>
+      <c r="C147" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks Share Price news: price rise and valuation</t>
+        </is>
+      </c>
+      <c r="D147" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E147" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G147" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B148" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:24</t>
+        </is>
+      </c>
+      <c r="C148" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings</t>
+        </is>
+      </c>
+      <c r="D148" s="51" t="inlineStr">
+        <is>
+          <t>economictimes.com</t>
+        </is>
+      </c>
+      <c r="E148" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G148" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B149" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 05:56</t>
+        </is>
+      </c>
+      <c r="C149" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%</t>
+        </is>
+      </c>
+      <c r="D149" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E149" s="80" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F149" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G149" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B150" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 01:13</t>
+        </is>
+      </c>
+      <c r="C150" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal</t>
+        </is>
+      </c>
+      <c r="D150" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E150" s="80" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F150" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G150" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B151" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:46</t>
+        </is>
+      </c>
+      <c r="C151" s="51" t="inlineStr">
+        <is>
+          <t>Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors</t>
+        </is>
+      </c>
+      <c r="D151" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E151" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G151" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B152" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:04</t>
+        </is>
+      </c>
+      <c r="C152" s="51" t="inlineStr">
+        <is>
+          <t>Sensex drops 330 points, Nifty down to 23,329 dragged by IT stocks</t>
+        </is>
+      </c>
+      <c r="D152" s="51" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="E152" s="80" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="F152" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G152" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="51" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B153" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-22 08:51</t>
+        </is>
+      </c>
+      <c r="C153" s="51" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals to host investor meet at PL Capital conference on Sep 28</t>
+        </is>
+      </c>
+      <c r="D153" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E153" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G153" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="51" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B154" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:31</t>
+        </is>
+      </c>
+      <c r="C154" s="51" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals NSE:ACUTAAS Trading Window Closure Q2 FY27</t>
+        </is>
+      </c>
+      <c r="D154" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E154" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G154" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="51" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B155" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:22</t>
+        </is>
+      </c>
+      <c r="C155" s="51" t="inlineStr">
+        <is>
+          <t>Ather Energy Share Price News: Today’s Decline Explained</t>
+        </is>
+      </c>
+      <c r="D155" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E155" s="80" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="F155" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G155" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B156" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:19</t>
+        </is>
+      </c>
+      <c r="C156" s="51" t="inlineStr">
+        <is>
+          <t>RR Kabel Share Price Today: price rise and sector check</t>
+        </is>
+      </c>
+      <c r="D156" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E156" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G156" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B157" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:01</t>
+        </is>
+      </c>
+      <c r="C157" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines And 2 Indian Nuclear Power Stocks To Watch</t>
+        </is>
+      </c>
+      <c r="D157" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E157" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G157" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B158" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-22 03:51</t>
+        </is>
+      </c>
+      <c r="C158" s="51" t="inlineStr">
+        <is>
+          <t>Stock market today: Sensex, Nifty see positive start; NSE IPO receives 6x subscription on final day | Business News</t>
+        </is>
+      </c>
+      <c r="D158" s="51" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E158" s="80" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="F158" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G158" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E158">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="-1"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId154"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0094A3B8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"batch": {"batch_id": "2026-09-28", "title": "SwingScope batch 2026-09-28", "signal_date": "2026-09-28", "exit_date_est": "2026-10-27", "hold_sessions": 21, "universe": "liquidity top 400 of all NSE stocks", "capital": 139903.0, "est_costs": 859.0, "cost_pct": 0.6, "regime": "Down", "regime_note": "the signal's weakest regime historically", "warnings": "0 of 10", "evidence": ["Backtest, 2017\u20132026 | Replayed point in time on your survivorship-free archive. Not live results. | Signal strength | IC +0.041 | rank IC over 113 monthly dates, 2017-2026 (t 2.52); validated benchmark 0.026 | Top vs bottom decile | +1.89% | per 21-session hold, before costs (t 2.94) | Top-10 picks | +1.45% | per hold after 0.60% costs; Nifty 50 earned +1.02% before costs | Entry timing | Open wins | buying at the open beat all 30 support-entry rules (best -0.12% per hold) | Down markets | IC +0.009 | over 27 down-regime dates, against +0.050 over 86 up-regime dates", "Live record | No results yet | The first live result arrives when this system finishes its first batch. Live results are kept apart from the backtest and never mixed in."], "stocks": [{"rank": 1, "symbol": "TDPOWERSYS", "isin": "INE419M01035", "qty": 20, "last_close": 722.0, "amount": 14440.0, "spark_12m": "2.0,31.7 2.4,32.0 2.9,31.7 3.3,31.1 3.7,31.1 4.2,31.1 4.6,31.0 5.0,30.6 5.4,30.4 5.9,29.2 6.3,29.3 6.7,29.5 7.2,29.8 7.6,30.1 8.0,30.4 8.5,30.5 8.9,30.3 9.3,29.4 9.7,29.3 10.2,28.8 10.6,29.1 11.0,28.9 11.5,29.1 11.9,29.2 12.3,29.1 12.8,29.0 13.2,28.4 13.6,28.0 14.0,25.5 14.5,24.3 14.9,24.2 15.3,24.8 15.8,25.3 16.2,25.2 16.6,25.4 17.1,24.2 17.5,25.4 17.9,25.2 18.4,25.2 18.8,25.7 19.2,25.8 19.6,25.9 20.1,26.9 20.5,25.8 20.9,25.9 21.4,24.9 21.8,24.9 22.2,25.4 22.7,25.0 23.1,25.0 23.5,25.8 23.9,26.8 24.4,27.7 24.8,28.3 25.2,27.7 25.7,28.1 26.1,28.2 26.5,27.9 27.0,27.6 27.4,27.9 27.8,27.1 28.2,27.6 28.7,27.1 29.1,26.4 29.5,26.7 30.0,27.0 30.4,27.3 30.8,27.7 31.3,27.5 31.7,27.5 32.1,28.3 32.5,28.0 33.0,27.7 33.4,27.9 33.8,27.5 34.3,27.9 34.7,28.3 35.1,28.8 35.6,27.9 36.0,28.2 36.4,28.5 36.9,28.7 37.3,29.2 37.7,29.4 38.1,29.5 38.6,29.7 39.0,29.6 39.4,28.8 39.9,28.2 40.3,26.7 40.7,26.2 41.2,24.3 41.6,24.1 42.0,24.5 42.4,25.2 42.9,24.8 43.3,23.3 43.7,22.8 44.2,23.4 44.6,23.8 45.0,23.1 45.5,22.8 45.9,22.8 46.3,22.4 46.7,22.4 47.2,21.8 47.6,22.3 48.0,22.5 48.5,22.5 48.9,21.8 49.3,22.2 49.8,22.6 50.2,22.4 50.6,22.5 51.1,23.5 51.5,24.3 51.9,24.7 52.3,24.4 52.8,25.3 53.2,24.9 53.6,24.3 54.1,23.7 54.5,23.8 54.9,23.0 55.4,24.2 55.8,23.1 56.2,22.3 56.6,23.4 57.1,23.3 57.5,23.0 57.9,23.0 58.4,22.5 58.8,22.5 59.2,22.4 59.7,22.6 60.1,21.2 60.5,21.5 60.9,20.8 61.4,20.0 61.8,19.2 62.2,18.3 62.7,18.6 63.1,17.4 63.5,17.2 64.0,16.0 64.4,16.6 64.8,15.0 65.3,15.0 65.7,14.8 66.1,14.6 66.5,14.2 67.0,14.5 67.4,12.2 67.8,13.0 68.3,14.1 68.7,14.4 69.1,14.2 69.6,14.0 70.0,10.4 70.4,9.9 70.8,11.9 71.3,12.6 71.7,10.6 72.1,10.8 72.6,10.7 73.0,8.8 73.4,9.8 73.9,10.2 74.3,12.7 74.7,12.5 75.1,11.1 75.6,10.0 76.0,10.3 76.4,12.8 76.9,12.6 77.3,14.8 77.7,15.6 78.2,13.7 78.6,13.6 79.0,14.4 79.5,12.7 79.9,11.6 80.3,11.5 80.7,10.0 81.2,9.2 81.6,11.7 82.0,12.0 82.5,12.6 82.9,12.4 83.3,13.7 83.8,13.8 84.2,16.6 84.6,14.2 85.0,15.7 85.5,16.9 85.9,16.6 86.3,14.9 86.8,14.9 87.2,15.6 87.6,14.2 88.1,15.6 88.5,15.5 88.9,15.2 89.3,15.5 89.8,14.6 90.2,15.2 90.6,15.9 91.1,15.2 91.5,15.9 91.9,18.1 92.4,17.5 92.8,15.5 93.2,16.0 93.6,15.5 94.1,13.5 94.5,12.7 94.9,11.8 95.4,12.5 95.8,11.4 96.2,5.6 96.7,5.6 97.1,5.5 97.5,3.7 98.0,2.7 98.4,3.8 98.8,4.9 99.2,4.1 99.7,3.4 100.1,6.2 100.5,6.3 101.0,5.6 101.4,4.9 101.8,3.6 102.3,4.6 102.7,5.9 103.1,6.6 103.5,5.6 104.0,6.0 104.4,4.0 104.8,4.8 105.3,4.4 105.7,2.0 106.1,6.5 106.6,8.1 107.0,6.7 107.4,4.3 107.8,5.2 108.3,4.7 108.7,4.2 109.1,5.5 109.6,5.0 110.0,6.7", "ret_12_1": 177.0, "ret_6_1": 72.2, "ret_3_1": 19.6, "volatility": 60.1, "traded_daily_cr": 128.0, "watch": "Nothing flagged", "from_12m_high": -10.3, "signal_rank": 6, "data_quality": "Green"}, {"rank": 2, "symbol": "AEROFLEX", "isin": "INE024001021", "qty": 29, "last_close": 513.4, "amount": 14889.0, "spark_12m": "2.0,29.8 2.4,29.6 2.9,29.5 3.3,30.0 3.7,30.1 4.2,30.5 4.6,30.8 5.0,30.9 5.4,30.9 5.9,30.5 6.3,30.7 6.7,30.8 7.2,30.9 7.6,31.0 8.0,31.0 8.5,31.1 8.9,31.2 9.3,31.2 9.7,31.2 10.2,31.2 10.6,31.4 11.0,31.1 11.5,31.0 11.9,31.0 12.3,31.0 12.8,30.1 13.2,30.1 13.6,30.5 14.0,30.0 14.5,29.8 14.9,30.3 15.3,30.5 15.8,30.0 16.2,30.0 16.6,30.2 17.1,30.2 17.5,30.1 17.9,29.9 18.4,30.1 18.8,30.3 19.2,30.2 19.6,30.2 20.1,30.5 20.5,30.9 20.9,30.2 21.4,30.2 21.8,30.4 22.2,30.0 22.7,30.2 23.1,30.3 23.5,30.6 23.9,30.6 24.4,30.7 24.8,31.3 25.2,31.0 25.7,30.7 26.1,30.9 26.5,30.7 27.0,30.3 27.4,30.5 27.8,30.3 28.2,30.7 28.7,29.5 29.1,29.2 29.5,28.8 30.0,28.6 30.4,28.9 30.8,29.1 31.3,29.3 31.7,29.5 32.1,29.6 32.5,29.2 33.0,29.0 33.4,29.3 33.8,29.1 34.3,29.9 34.7,30.2 35.1,30.2 35.6,30.5 36.0,30.7 36.4,30.8 36.9,30.9 37.3,31.3 37.7,31.8 38.1,31.5 38.6,32.0 39.0,31.7 39.4,31.4 39.9,30.4 40.3,30.6 40.7,31.0 41.2,30.1 41.6,29.9 42.0,29.9 42.4,30.1 42.9,29.3 43.3,29.4 43.7,29.6 44.2,29.5 44.6,30.0 45.0,29.6 45.5,28.5 45.9,27.1 46.3,27.0 46.7,27.3 47.2,27.6 47.6,27.7 48.0,27.0 48.5,26.9 48.9,26.5 49.3,27.2 49.8,27.7 50.2,27.3 50.6,27.6 51.1,27.9 51.5,27.5 51.9,26.5 52.3,26.3 52.8,26.5 53.2,25.6 53.6,25.3 54.1,25.6 54.5,26.8 54.9,26.6 55.4,27.3 55.8,25.3 56.2,25.3 56.6,26.1 57.1,26.2 57.5,25.4 57.9,25.2 58.4,25.0 58.8,25.7 59.2,24.6 59.7,23.6 60.1,22.6 60.5,22.6 60.9,22.3 61.4,22.1 61.8,21.0 62.2,21.7 62.7,22.6 63.1,21.5 63.5,22.1 64.0,23.4 64.4,22.2 64.8,22.3 65.3,21.4 65.7,21.4 66.1,21.6 66.5,20.5 67.0,18.6 67.4,13.6 67.8,11.7 68.3,14.7 68.7,17.1 69.1,17.1 69.6,17.4 70.0,16.7 70.4,16.8 70.8,15.9 71.3,15.2 71.7,16.0 72.1,14.3 72.6,13.5 73.0,14.3 73.4,14.0 73.9,14.4 74.3,15.4 74.7,13.1 75.1,12.1 75.6,11.7 76.0,13.1 76.4,14.6 76.9,12.7 77.3,13.5 77.7,13.9 78.2,11.1 78.6,8.9 79.0,9.4 79.5,6.5 79.9,8.1 80.3,6.8 80.7,6.6 81.2,7.1 81.6,8.8 82.0,9.7 82.5,9.6 82.9,9.4 83.3,8.1 83.8,8.9 84.2,10.5 84.6,10.3 85.0,13.6 85.5,14.5 85.9,14.2 86.3,13.6 86.8,13.0 87.2,13.8 87.6,13.0 88.1,13.8 88.5,13.8 88.9,14.1 89.3,13.6 89.8,14.0 90.2,13.1 90.6,13.0 91.1,13.2 91.5,11.2 91.9,10.9 92.4,12.6 92.8,12.0 93.2,12.3 93.6,9.9 94.1,10.5 94.5,11.8 94.9,12.7 95.4,13.1 95.8,12.9 96.2,11.2 96.7,11.1 97.1,10.2 97.5,10.5 98.0,8.3 98.4,9.2 98.8,9.1 99.2,7.1 99.7,7.0 100.1,7.6 100.5,4.7 101.0,5.7 101.4,4.3 101.8,5.5 102.3,3.6 102.7,4.4 103.1,4.3 103.5,4.6 104.0,3.1 104.4,2.0 104.8,2.9 105.3,2.7 105.7,2.7 106.1,6.8 106.6,8.7 107.0,7.5 107.4,6.5 107.8,6.2 108.3,6.1 108.7,5.8 109.1,5.3 109.6,5.5 110.0,6.3", "ret_12_1": 175.0, "ret_6_1": 107.0, "ret_3_1": 10.7, "volatility": 67.3, "traded_daily_cr": 53.0, "watch": "Nothing flagged", "from_12m_high": -10.5, "signal_rank": 7, "data_quality": "Green"}, {"rank": 3, "symbol": "ATHERENERG", "isin": "INE0LEZ01016", "qty": 10, "last_close": 1454.9, "amount": 14549.0, "spark_12m": "2.0,30.9 2.4,30.7 2.9,31.2 3.3,30.9 3.7,31.6 4.2,32.0 4.6,31.0 5.0,31.4 5.4,30.8 5.9,30.7 6.3,30.0 6.7,29.7 7.2,29.5 7.6,29.9 8.0,30.6 8.5,30.2 8.9,30.1 9.3,29.6 9.7,28.2 10.2,28.1 10.6,27.4 11.0,26.3 11.5,27.1 11.9,27.8 12.3,27.1 12.8,27.0 13.2,27.8 13.6,27.8 14.0,28.2 14.5,28.2 14.9,28.8 15.3,29.6 15.8,29.1 16.2,29.8 16.6,29.0 17.1,29.8 17.5,29.5 17.9,29.2 18.4,29.3 18.8,28.7 19.2,28.3 19.6,28.0 20.1,28.1 20.5,28.6 20.9,28.3 21.4,28.1 21.8,27.7 22.2,27.5 22.7,27.7 23.1,28.3 23.5,28.4 23.9,28.7 24.4,28.6 24.8,28.5 25.2,29.2 25.7,29.3 26.1,29.3 26.5,29.3 27.0,28.3 27.4,28.6 27.8,28.9 28.2,28.9 28.7,27.9 29.1,28.0 29.5,27.8 30.0,27.4 30.4,27.7 30.8,27.5 31.3,27.1 31.7,26.6 32.1,27.0 32.5,26.9 33.0,28.3 33.4,28.1 33.8,28.1 34.3,28.6 34.7,29.6 35.1,29.5 35.6,29.1 36.0,29.3 36.4,30.0 36.9,29.8 37.3,30.3 37.7,30.1 38.1,29.7 38.6,29.9 39.0,30.0 39.4,30.3 39.9,30.4 40.3,29.9 40.7,30.3 41.2,28.6 41.6,28.0 42.0,27.6 42.4,27.8 42.9,27.3 43.3,27.3 43.7,27.5 44.2,27.3 44.6,27.7 45.0,27.7 45.5,27.3 45.9,27.2 46.3,27.1 46.7,27.7 47.2,27.5 47.6,28.0 48.0,27.8 48.5,27.9 48.9,27.7 49.3,27.8 49.8,27.9 50.2,28.3 50.6,28.6 51.1,28.4 51.5,28.1 51.9,27.9 52.3,27.7 52.8,27.8 53.2,27.6 53.6,27.3 54.1,26.7 54.5,26.6 54.9,25.9 55.4,26.7 55.8,26.5 56.2,26.0 56.6,25.5 57.1,26.6 57.5,26.2 57.9,26.4 58.4,25.8 58.8,26.4 59.2,26.2 59.7,24.9 60.1,23.8 60.5,22.7 60.9,23.6 61.4,23.7 61.8,24.1 62.2,23.2 62.7,23.0 63.1,22.7 63.5,22.9 64.0,23.3 64.4,21.8 64.8,22.1 65.3,21.9 65.7,22.0 66.1,22.0 66.5,21.9 67.0,23.0 67.4,22.7 67.8,22.5 68.3,21.1 68.7,22.3 69.1,21.6 69.6,21.9 70.0,21.9 70.4,22.6 70.8,22.6 71.3,22.7 71.7,23.2 72.1,23.3 72.6,22.3 73.0,21.6 73.4,21.5 73.9,21.3 74.3,21.9 74.7,21.4 75.1,19.8 75.6,20.7 76.0,19.5 76.4,20.3 76.9,19.5 77.3,19.3 77.7,19.7 78.2,19.6 78.6,19.7 79.0,20.4 79.5,20.6 79.9,21.1 80.3,21.1 80.7,21.4 81.2,20.2 81.6,20.6 82.0,20.4 82.5,18.2 82.9,16.8 83.3,17.1 83.8,16.7 84.2,17.1 84.6,17.2 85.0,16.8 85.5,15.3 85.9,14.8 86.3,14.6 86.8,15.7 87.2,15.3 87.6,12.9 88.1,13.6 88.5,13.2 88.9,12.9 89.3,13.1 89.8,13.6 90.2,14.5 90.6,15.1 91.1,14.9 91.5,15.2 91.9,14.1 92.4,14.3 92.8,13.8 93.2,13.5 93.6,9.0 94.1,8.4 94.5,8.9 94.9,8.2 95.4,8.6 95.8,7.1 96.2,6.0 96.7,7.0 97.1,7.4 97.5,8.1 98.0,8.6 98.4,9.3 98.8,9.0 99.2,8.7 99.7,8.9 100.1,9.2 100.5,7.8 101.0,7.8 101.4,4.8 101.8,2.2 102.3,2.0 102.7,3.0 103.1,4.2 103.5,5.6 104.0,5.2 104.4,5.7 104.8,5.7 105.3,3.7 105.7,3.8 106.1,6.0 106.6,6.0 107.0,6.4 107.4,4.2 107.8,5.4 108.3,6.6 108.7,7.7 109.1,7.7 109.6,7.8 110.0,8.8", "ret_12_1": 166.0, "ret_6_1": 97.5, "ret_3_1": 31.1, "volatility": 49.4, "traded_daily_cr": 493.0, "watch": "Nothing flagged", "from_12m_high": -15.7, "signal_rank": 9, "data_quality": "Green"}, {"rank": 4, "symbol": "THANGAMAYL", "isin": "INE085J01014", "qty": 2, "last_close": 5011.5, "amount": 10023.0, "spark_12m": "2.0,30.9 2.4,31.1 2.9,31.4 3.3,31.4 3.7,31.4 4.2,31.6 4.6,31.7 5.0,31.6 5.4,31.6 5.9,31.2 6.3,31.3 6.7,31.6 7.2,31.2 7.6,31.5 8.0,31.6 8.5,31.5 8.9,31.8 9.3,31.9 9.7,31.9 10.2,31.9 10.6,31.9 11.0,31.9 11.5,32.0 11.9,31.5 12.3,31.6 12.8,31.3 13.2,31.4 13.6,31.3 14.0,30.8 14.5,28.3 14.9,25.9 15.3,25.7 15.8,23.9 16.2,25.3 16.6,24.8 17.1,24.1 17.5,24.4 17.9,24.5 18.4,24.7 18.8,24.9 19.2,25.1 19.6,25.2 20.1,26.0 20.5,24.8 20.9,24.8 21.4,24.7 21.8,24.8 22.2,24.7 22.7,24.1 23.1,25.2 23.5,24.6 23.9,24.8 24.4,24.9 24.8,25.2 25.2,24.7 25.7,24.9 26.1,24.9 26.5,25.0 27.0,25.0 27.4,24.9 27.8,24.4 28.2,24.6 28.7,24.2 29.1,23.8 29.5,23.7 30.0,24.5 30.4,25.0 30.8,25.0 31.3,25.0 31.7,24.9 32.1,24.7 32.5,24.8 33.0,24.2 33.4,23.4 33.8,21.4 34.3,21.2 34.7,22.7 35.1,22.3 35.6,21.9 36.0,21.5 36.4,21.8 36.9,22.1 37.3,22.1 37.7,21.2 38.1,22.6 38.6,22.9 39.0,23.8 39.4,22.8 39.9,23.4 40.3,24.3 40.7,24.9 41.2,25.1 41.6,24.5 42.0,25.1 42.4,23.9 42.9,22.1 43.3,22.2 43.7,22.3 44.2,22.5 44.6,22.9 45.0,22.1 45.5,22.3 45.9,22.6 46.3,23.4 46.7,23.0 47.2,22.8 47.6,22.0 48.0,21.5 48.5,21.0 48.9,20.8 49.3,21.4 49.8,22.7 50.2,22.6 50.6,22.2 51.1,22.9 51.5,22.1 51.9,23.1 52.3,23.0 52.8,23.3 53.2,23.6 53.6,23.4 54.1,23.3 54.5,24.1 54.9,24.3 55.4,25.2 55.8,24.4 56.2,22.8 56.6,23.7 57.1,23.7 57.5,23.0 57.9,23.1 58.4,21.9 58.8,21.3 59.2,20.3 59.7,20.0 60.1,19.8 60.5,19.5 60.9,19.1 61.4,19.0 61.8,19.3 62.2,19.8 62.7,19.8 63.1,20.4 63.5,21.7 64.0,21.7 64.4,20.8 64.8,20.7 65.3,20.6 65.7,20.8 66.1,20.6 66.5,20.7 67.0,20.1 67.4,19.9 67.8,19.1 68.3,20.5 68.7,22.4 69.1,22.5 69.6,22.7 70.0,22.8 70.4,23.1 70.8,22.5 71.3,21.8 71.7,21.3 72.1,21.6 72.6,21.5 73.0,21.6 73.4,21.0 73.9,19.4 74.3,18.9 74.7,17.2 75.1,16.1 75.6,12.0 76.0,13.0 76.4,12.2 76.9,12.3 77.3,12.4 77.7,12.6 78.2,12.2 78.6,12.1 79.0,12.4 79.5,11.4 79.9,12.5 80.3,12.4 80.7,11.8 81.2,12.8 81.6,12.4 82.0,11.6 82.5,10.0 82.9,7.1 83.3,9.6 83.8,7.6 84.2,8.4 84.6,7.7 85.0,7.2 85.5,4.8 85.9,6.0 86.3,6.3 86.8,8.0 87.2,6.8 87.6,5.9 88.1,7.2 88.5,6.9 88.9,7.2 89.3,6.8 89.8,6.7 90.2,4.5 90.6,4.3 91.1,2.0 91.5,2.8 91.9,6.8 92.4,10.4 92.8,13.7 93.2,15.1 93.6,16.5 94.1,15.2 94.5,14.1 94.9,13.4 95.4,13.0 95.8,13.7 96.2,13.1 96.7,13.4 97.1,12.5 97.5,13.0 98.0,12.2 98.4,12.0 98.8,12.4 99.2,12.2 99.7,12.2 100.1,12.7 100.5,12.2 101.0,12.1 101.4,12.5 101.8,12.6 102.3,13.2 102.7,13.6 103.1,13.3 103.5,13.1 104.0,12.3 104.4,12.9 104.8,14.3 105.3,14.5 105.7,14.2 106.1,15.4 106.6,15.3 107.0,16.0 107.4,14.7 107.8,15.3 108.3,14.3 108.7,13.2 109.1,14.4 109.6,14.2 110.0,14.9", "ret_12_1": 154.0, "ret_6_1": 66.3, "ret_3_1": -14.0, "volatility": 59.8, "traded_daily_cr": 71.0, "watch": "Nothing flagged", "from_12m_high": -31.4, "signal_rank": 11, "data_quality": "Green"}, {"rank": 5, "symbol": "RRKABEL", "isin": "INE777K01022", "qty": 6, "last_close": 2459.8, "amount": 14759.0, "spark_12m": "2.0,31.3 2.4,31.1 2.9,30.7 3.3,31.2 3.7,31.2 4.2,32.0 4.6,31.8 5.0,31.2 5.4,31.1 5.9,31.4 6.3,31.1 6.7,31.1 7.2,31.3 7.6,31.4 8.0,31.0 8.5,31.2 8.9,31.3 9.3,31.3 9.7,31.0 10.2,31.2 10.6,31.4 11.0,31.2 11.5,31.4 11.9,31.5 12.3,30.1 12.8,28.7 13.2,28.4 13.6,28.6 14.0,28.6 14.5,29.0 14.9,28.4 15.3,28.8 15.8,29.2 16.2,29.8 16.6,29.6 17.1,28.8 17.5,29.3 17.9,29.3 18.4,29.1 18.8,29.7 19.2,29.5 19.6,29.4 20.1,29.7 20.5,29.7 20.9,29.5 21.4,29.0 21.8,29.1 22.2,28.8 22.7,28.8 23.1,28.8 23.5,29.0 23.9,28.9 24.4,29.4 24.8,29.5 25.2,29.1 25.7,28.6 26.1,28.7 26.5,28.4 27.0,27.8 27.4,28.1 27.8,28.3 28.2,28.3 28.7,27.3 29.1,26.5 29.5,26.6 30.0,27.1 30.4,27.5 30.8,28.1 31.3,28.2 31.7,27.9 32.1,27.6 32.5,26.9 33.0,26.4 33.4,26.3 33.8,26.4 34.3,26.7 34.7,26.9 35.1,27.3 35.6,27.0 36.0,27.1 36.4,27.5 36.9,28.0 37.3,28.6 37.7,28.6 38.1,28.4 38.6,29.7 39.0,30.0 39.4,29.7 39.9,30.3 40.3,29.3 40.7,29.6 41.2,28.4 41.6,27.8 42.0,27.5 42.4,27.7 42.9,27.6 43.3,28.5 43.7,28.2 44.2,28.3 44.6,28.7 45.0,28.7 45.5,28.4 45.9,28.5 46.3,28.4 46.7,28.1 47.2,27.9 47.6,27.0 48.0,26.9 48.5,26.7 48.9,26.0 49.3,26.5 49.8,27.3 50.2,27.1 50.6,26.6 51.1,27.2 51.5,27.8 51.9,28.4 52.3,28.2 52.8,29.8 53.2,29.3 53.6,28.9 54.1,28.1 54.5,28.9 54.9,29.0 55.4,30.3 55.8,29.7 56.2,29.7 56.6,30.3 57.1,30.7 57.5,30.0 57.9,30.0 58.4,30.0 58.8,30.2 59.2,28.8 59.7,29.1 60.1,28.9 60.5,29.3 60.9,29.0 61.4,27.8 61.8,27.5 62.2,27.6 62.7,27.8 63.1,27.7 63.5,28.3 64.0,28.1 64.4,26.9 64.8,25.1 65.3,24.8 65.7,25.8 66.1,22.2 66.5,22.1 67.0,21.8 67.4,19.6 67.8,19.3 68.3,19.7 68.7,19.4 69.1,19.0 69.6,17.6 70.0,19.1 70.4,19.2 70.8,19.7 71.3,18.9 71.7,19.2 72.1,19.2 72.6,18.5 73.0,18.7 73.4,19.1 73.9,17.3 74.3,17.8 74.7,17.9 75.1,15.6 75.6,14.4 76.0,14.4 76.4,15.6 76.9,15.2 77.3,15.3 77.7,16.0 78.2,15.3 78.6,15.0 79.0,14.8 79.5,14.6 79.9,13.1 80.3,12.7 80.7,12.1 81.2,11.8 81.6,10.6 82.0,9.7 82.5,9.5 82.9,11.4 83.3,11.6 83.8,11.4 84.2,12.3 84.6,13.1 85.0,14.9 85.5,15.0 85.9,14.7 86.3,14.3 86.8,11.7 87.2,12.2 87.6,13.2 88.1,11.2 88.5,13.1 88.9,12.4 89.3,12.2 89.8,10.7 90.2,11.7 90.6,9.6 91.1,9.1 91.5,8.2 91.9,8.5 92.4,8.4 92.8,7.7 93.2,7.2 93.6,7.0 94.1,4.4 94.5,4.9 94.9,5.0 95.4,5.0 95.8,4.0 96.2,4.4 96.7,3.7 97.1,4.5 97.5,5.2 98.0,4.5 98.4,2.5 98.8,2.6 99.2,2.2 99.7,3.0 100.1,4.2 100.5,4.1 101.0,3.7 101.4,2.4 101.8,2.0 102.3,3.0 102.7,7.2 103.1,7.5 103.5,10.3 104.0,11.5 104.4,10.4 104.8,10.9 105.3,10.6 105.7,10.8 106.1,11.6 106.6,11.3 107.0,11.4 107.4,10.4 107.8,11.1 108.3,10.0 108.7,9.9 109.1,9.0 109.6,9.0 110.0,10.2", "ret_12_1": 126.0, "ret_6_1": 110.0, "ret_3_1": 18.2, "volatility": 44.0, "traded_daily_cr": 93.0, "watch": "Nothing flagged", "from_12m_high": -16.0, "signal_rank": 15, "data_quality": "Green"}, {"rank": 6, "symbol": "ACUTAAS", "isin": "INE00FF01025", "qty": 4, "last_close": 3214.4, "amount": 12858.0, "spark_12m": "2.0,30.2 2.4,30.2 2.9,30.3 3.3,30.3 3.7,30.8 4.2,31.5 4.6,31.6 5.0,32.0 5.4,31.2 5.9,31.1 6.3,30.9 6.7,30.9 7.2,30.9 7.6,30.7 8.0,30.1 8.5,29.7 8.9,29.7 9.3,29.1 9.7,29.0 10.2,27.8 10.6,26.4 11.0,26.1 11.5,26.7 11.9,27.4 12.3,26.8 12.8,27.0 13.2,27.3 13.6,27.1 14.0,26.8 14.5,25.8 14.9,25.5 15.3,26.3 15.8,26.4 16.2,26.4 16.6,26.5 17.1,27.1 17.5,27.4 17.9,27.0 18.4,27.1 18.8,27.0 19.2,26.9 19.6,26.8 20.1,27.2 20.5,25.0 20.9,26.1 21.4,26.0 21.8,26.1 22.2,25.4 22.7,26.2 23.1,26.6 23.5,26.7 23.9,27.1 24.4,27.1 24.8,27.8 25.2,27.6 25.7,27.4 26.1,27.7 26.5,27.6 27.0,28.1 27.4,27.2 27.8,27.7 28.2,28.0 28.7,27.8 29.1,27.4 29.5,27.2 30.0,27.8 30.4,27.8 30.8,27.8 31.3,27.7 31.7,27.1 32.1,26.5 32.5,26.6 33.0,26.3 33.4,26.4 33.8,26.4 34.3,26.7 34.7,27.4 35.1,27.5 35.6,27.4 36.0,27.1 36.4,27.2 36.9,27.4 37.3,28.1 37.7,28.4 38.1,27.9 38.6,27.8 39.0,26.8 39.4,25.1 39.9,24.2 40.3,24.5 40.7,24.2 41.2,23.8 41.6,23.5 42.0,23.6 42.4,23.6 42.9,23.4 43.3,22.8 43.7,23.0 44.2,22.2 44.6,23.2 45.0,22.9 45.5,22.4 45.9,21.6 46.3,22.1 46.7,22.0 47.2,21.5 47.6,21.5 48.0,21.3 48.5,21.1 48.9,21.4 49.3,21.0 49.8,22.1 50.2,20.4 50.6,20.2 51.1,21.4 51.5,20.5 51.9,21.0 52.3,21.0 52.8,22.3 53.2,21.3 53.6,19.6 54.1,20.1 54.5,20.3 54.9,18.3 55.4,20.0 55.8,17.9 56.2,16.7 56.6,16.5 57.1,16.3 57.5,19.2 57.9,22.0 58.4,20.7 58.8,20.7 59.2,19.2 59.7,19.3 60.1,18.8 60.5,18.4 60.9,19.7 61.4,19.1 61.8,18.8 62.2,18.2 62.7,18.7 63.1,18.0 63.5,18.5 64.0,18.4 64.4,17.1 64.8,17.5 65.3,17.0 65.7,15.9 66.1,14.9 66.5,15.1 67.0,14.7 67.4,14.2 67.8,14.1 68.3,13.2 68.7,14.0 69.1,12.9 69.6,14.2 70.0,14.2 70.4,13.3 70.8,12.2 71.3,12.3 71.7,10.8 72.1,11.4 72.6,11.7 73.0,10.3 73.4,10.8 73.9,9.1 74.3,10.5 74.7,10.3 75.1,9.1 75.6,8.7 76.0,6.6 76.4,6.8 76.9,8.3 77.3,8.2 77.7,9.2 78.2,8.9 78.6,9.5 79.0,10.8 79.5,10.8 79.9,9.0 80.3,7.7 80.7,7.6 81.2,7.3 81.6,7.4 82.0,7.0 82.5,3.6 82.9,4.1 83.3,3.6 83.8,2.0 84.2,2.0 84.6,4.3 85.0,5.8 85.5,5.0 85.9,5.0 86.3,5.7 86.8,4.5 87.2,5.0 87.6,3.9 88.1,3.4 88.5,3.0 88.9,2.5 89.3,2.2 89.8,2.4 90.2,5.0 90.6,7.5 91.1,6.1 91.5,7.0 91.9,6.9 92.4,7.8 92.8,9.4 93.2,9.3 93.6,7.9 94.1,7.2 94.5,7.5 94.9,7.0 95.4,7.2 95.8,7.7 96.2,8.8 96.7,9.4 97.1,7.8 97.5,8.3 98.0,5.8 98.4,7.9 98.8,8.1 99.2,8.6 99.7,8.6 100.1,6.8 100.5,7.5 101.0,6.6 101.4,7.2 101.8,8.7 102.3,8.6 102.7,9.1 103.1,8.2 103.5,8.6 104.0,8.5 104.4,8.5 104.8,7.7 105.3,5.1 105.7,5.9 106.1,7.4 106.6,6.4 107.0,6.8 107.4,5.2 107.8,5.4 108.3,8.1 108.7,7.4 109.1,7.2 109.6,7.3 110.0,8.1", "ret_12_1": 126.0, "ret_6_1": 36.7, "ret_3_1": -5.6, "volatility": 46.7, "traded_daily_cr": 101.0, "watch": "Nothing flagged", "from_12m_high": -13.0, "signal_rank": 16, "data_quality": "Green"}, {"rank": 7, "symbol": "DIACABS", "isin": "INE989C01038", "qty": 44, "last_close": 339.25, "amount": 14927.0, "spark_12m": "2.0,27.2 2.4,27.3 2.9,27.2 3.3,27.4 3.7,28.0 4.2,28.4 4.6,28.2 5.0,28.6 5.4,28.5 5.9,28.3 6.3,28.7 6.7,29.2 7.2,29.3 7.6,29.4 8.0,29.4 8.5,29.6 8.9,29.5 9.3,29.2 9.7,29.3 10.2,29.4 10.6,29.2 11.0,29.1 11.5,29.1 11.9,29.3 12.3,28.1 12.8,28.5 13.2,28.1 13.6,28.2 14.0,28.2 14.5,28.1 14.9,27.9 15.3,28.6 15.8,28.3 16.2,28.8 16.6,28.9 17.1,28.8 17.5,28.4 17.9,28.4 18.4,28.4 18.8,28.7 19.2,28.3 19.6,28.7 20.1,29.1 20.5,29.5 20.9,29.6 21.4,29.4 21.8,29.4 22.2,28.5 22.7,28.6 23.1,28.9 23.5,29.2 23.9,29.3 24.4,29.1 24.8,29.4 25.2,29.4 25.7,29.7 26.1,29.7 26.5,29.5 27.0,29.4 27.4,29.6 27.8,29.6 28.2,29.5 28.7,29.5 29.1,29.2 29.5,29.3 30.0,29.5 30.4,29.6 30.8,29.8 31.3,29.8 31.7,29.8 32.1,29.8 32.5,29.9 33.0,29.3 33.4,29.3 33.8,29.1 34.3,29.7 34.7,30.2 35.1,30.1 35.6,30.5 36.0,30.7 36.4,30.6 36.9,30.4 37.3,31.0 37.7,30.9 38.1,30.8 38.6,31.4 39.0,31.4 39.4,31.1 39.9,31.4 40.3,31.5 40.7,31.7 41.2,31.2 41.6,30.8 42.0,31.3 42.4,31.3 42.9,30.9 43.3,30.4 43.7,30.2 44.2,30.3 44.6,30.5 45.0,29.5 45.5,29.8 45.9,29.8 46.3,30.2 46.7,30.1 47.2,30.2 47.6,30.4 48.0,30.0 48.5,29.6 48.9,29.9 49.3,29.9 49.8,30.4 50.2,29.9 50.6,30.1 51.1,30.2 51.5,29.7 51.9,29.9 52.3,30.0 52.8,30.8 53.2,31.0 53.6,31.2 54.1,30.7 54.5,31.4 54.9,31.0 55.4,32.0 55.8,31.7 56.2,30.9 56.6,31.5 57.1,31.9 57.5,31.2 57.9,31.2 58.4,30.8 58.8,30.9 59.2,30.3 59.7,30.4 60.1,29.9 60.5,29.8 60.9,29.5 61.4,28.7 61.8,28.6 62.2,27.4 62.7,27.2 63.1,27.5 63.5,27.5 64.0,27.3 64.4,26.8 64.8,27.1 65.3,27.3 65.7,27.7 66.1,26.8 66.5,26.6 67.0,25.6 67.4,26.4 67.8,26.0 68.3,25.8 68.7,26.4 69.1,25.9 69.6,24.0 70.0,23.5 70.4,24.0 70.8,24.2 71.3,23.6 71.7,23.8 72.1,23.8 72.6,23.5 73.0,22.4 73.4,23.3 73.9,23.7 74.3,25.0 74.7,23.7 75.1,24.3 75.6,23.9 76.0,22.7 76.4,23.3 76.9,22.8 77.3,23.4 77.7,23.8 78.2,22.9 78.6,21.4 79.0,22.4 79.5,22.6 79.9,22.9 80.3,22.1 80.7,22.3 81.2,22.9 81.6,22.6 82.0,22.4 82.5,22.2 82.9,22.1 83.3,22.2 83.8,22.0 84.2,23.2 84.6,21.1 85.0,20.4 85.5,19.7 85.9,18.9 86.3,20.0 86.8,20.1 87.2,20.4 87.6,20.2 88.1,20.4 88.5,20.7 88.9,18.3 89.3,15.6 89.8,15.6 90.2,15.1 90.6,12.8 91.1,11.5 91.5,10.0 91.9,8.2 92.4,9.2 92.8,9.7 93.2,9.8 93.6,10.5 94.1,8.8 94.5,7.0 94.9,5.3 95.4,5.7 95.8,5.5 96.2,4.9 96.7,5.0 97.1,4.8 97.5,5.8 98.0,4.9 98.4,5.8 98.8,6.4 99.2,6.2 99.7,6.5 100.1,8.0 100.5,8.1 101.0,8.1 101.4,6.9 101.8,7.1 102.3,7.9 102.7,8.9 103.1,9.8 103.5,8.8 104.0,8.7 104.4,8.3 104.8,8.5 105.3,6.7 105.7,4.8 106.1,2.8 106.6,2.0 107.0,4.0 107.4,5.0 107.8,4.0 108.3,4.6 108.7,3.8 109.1,5.7 109.6,6.4 110.0,8.0", "ret_12_1": 124.0, "ret_6_1": 180.0, "ret_3_1": 61.7, "volatility": 53.6, "traded_daily_cr": 51.0, "watch": "Nothing flagged", "from_12m_high": -14.1, "signal_rank": 17, "data_quality": "Green"}, {"rank": 8, "symbol": "KIRLOSENG", "isin": "INE146L01010", "qty": 7, "last_close": 2141.2, "amount": 14988.0, "spark_12m": "2.0,30.3 2.4,30.3 2.9,30.5 3.3,30.2 3.7,30.7 4.2,31.2 4.6,31.1 5.0,31.1 5.4,31.0 5.9,31.4 6.3,31.6 6.7,31.8 7.2,31.8 7.6,31.8 8.0,31.6 8.5,31.7 8.9,32.0 9.3,31.9 9.7,31.8 10.2,31.6 10.6,31.8 11.0,31.6 11.5,31.5 11.9,31.5 12.3,30.7 12.8,29.6 13.2,29.4 13.6,29.4 14.0,29.7 14.5,29.4 14.9,29.4 15.3,29.9 15.8,30.3 16.2,30.5 16.6,30.7 17.1,28.7 17.5,28.2 17.9,28.1 18.4,27.7 18.8,27.2 19.2,26.6 19.6,26.5 20.1,26.8 20.5,27.4 20.9,26.9 21.4,27.1 21.8,27.2 22.2,27.5 22.7,27.6 23.1,27.7 23.5,28.2 23.9,26.8 24.4,27.4 24.8,28.0 25.2,27.5 25.7,27.7 26.1,27.6 26.5,27.1 27.0,27.3 27.4,25.7 27.8,24.7 28.2,24.6 28.7,25.4 29.1,24.2 29.5,24.4 30.0,25.0 30.4,24.9 30.8,25.8 31.3,25.7 31.7,25.8 32.1,25.6 32.5,25.1 33.0,25.2 33.4,25.3 33.8,25.8 34.3,26.5 34.7,26.9 35.1,27.5 35.6,27.0 36.0,26.7 36.4,26.7 36.9,27.4 37.3,27.9 37.7,27.9 38.1,27.7 38.6,28.0 39.0,28.0 39.4,27.7 39.9,27.6 40.3,26.6 40.7,27.0 41.2,26.5 41.6,25.6 42.0,26.2 42.4,26.7 42.9,25.8 43.3,25.0 43.7,23.9 44.2,23.7 44.6,23.0 45.0,22.4 45.5,22.1 45.9,22.3 46.3,22.2 46.7,22.3 47.2,22.6 47.6,22.7 48.0,22.5 48.5,22.7 48.9,22.7 49.3,22.5 49.8,22.3 50.2,21.4 50.6,20.6 51.1,21.6 51.5,21.9 51.9,21.7 52.3,21.4 52.8,21.7 53.2,21.4 53.6,21.9 54.1,22.0 54.5,22.2 54.9,23.0 55.4,24.6 55.8,23.9 56.2,22.7 56.6,23.5 57.1,23.9 57.5,23.2 57.9,22.9 58.4,22.3 58.8,22.6 59.2,21.4 59.7,21.6 60.1,21.3 60.5,21.1 60.9,19.1 61.4,18.8 61.8,18.7 62.2,18.4 62.7,17.9 63.1,18.4 63.5,18.9 64.0,19.2 64.4,17.6 64.8,16.9 65.3,17.3 65.7,17.3 66.1,16.9 66.5,16.6 67.0,17.1 67.4,16.8 67.8,16.8 68.3,18.0 68.7,19.8 69.1,19.1 69.6,19.1 70.0,16.6 70.4,17.3 70.8,18.0 71.3,17.9 71.7,17.7 72.1,17.8 72.6,17.2 73.0,16.4 73.4,15.0 73.9,13.3 74.3,13.4 74.7,14.5 75.1,13.9 75.6,12.9 76.0,13.5 76.4,14.6 76.9,14.6 77.3,15.2 77.7,15.6 78.2,13.9 78.6,13.2 79.0,13.4 79.5,12.2 79.9,12.3 80.3,12.1 80.7,5.1 81.2,3.0 81.6,2.0 82.0,3.4 82.5,4.2 82.9,5.5 83.3,5.9 83.8,6.3 84.2,7.9 84.6,7.3 85.0,7.2 85.5,7.1 85.9,4.5 86.3,3.3 86.8,4.3 87.2,5.6 87.6,4.6 88.1,5.0 88.5,7.5 88.9,8.1 89.3,8.1 89.8,8.7 90.2,8.8 90.6,8.7 91.1,7.0 91.5,8.6 91.9,8.8 92.4,9.6 92.8,8.6 93.2,8.0 93.6,7.1 94.1,7.7 94.5,7.6 94.9,9.1 95.4,9.7 95.8,10.2 96.2,11.0 96.7,10.9 97.1,10.2 97.5,10.2 98.0,9.8 98.4,10.6 98.8,9.3 99.2,10.2 99.7,10.8 100.1,11.5 100.5,11.3 101.0,10.2 101.4,9.8 101.8,10.2 102.3,9.5 102.7,9.1 103.1,7.2 103.5,8.4 104.0,8.9 104.4,7.1 104.8,8.1 105.3,8.3 105.7,9.0 106.1,11.2 106.6,11.3 107.0,9.8 107.4,9.1 107.8,9.6 108.3,9.1 108.7,8.1 109.1,9.1 109.6,9.6 110.0,9.5", "ret_12_1": 123.0, "ret_6_1": 58.2, "ret_3_1": -11.2, "volatility": 49.9, "traded_daily_cr": 87.0, "watch": "Nothing flagged", "from_12m_high": -16.5, "signal_rank": 18, "data_quality": "Green"}, {"rank": 9, "symbol": "E2E", "isin": "INE255Z01027", "qty": 23, "last_close": 625.9, "amount": 14396.0, "spark_12m": "2.0,25.4 2.4,24.4 2.9,23.5 3.3,24.3 3.7,23.7 4.2,22.9 4.6,23.7 5.0,24.4 5.4,23.4 5.9,22.4 6.3,21.3 6.7,21.1 7.2,21.2 7.6,22.8 8.0,23.1 8.5,23.8 8.9,24.4 9.3,24.4 9.7,24.3 10.2,24.1 10.6,24.5 11.0,24.4 11.5,24.3 11.9,25.2 12.3,24.5 12.8,24.9 13.2,25.1 13.6,24.9 14.0,25.0 14.5,25.3 14.9,24.9 15.3,25.3 15.8,25.1 16.2,25.3 16.6,26.1 17.1,26.1 17.5,26.8 17.9,27.8 18.4,28.0 18.8,28.1 19.2,28.0 19.6,28.1 20.1,28.8 20.5,29.7 20.9,29.7 21.4,29.6 21.8,29.8 22.2,30.1 22.7,30.0 23.1,30.5 23.5,30.9 23.9,30.5 24.4,31.0 24.8,31.6 25.2,30.8 25.7,31.2 26.1,31.1 26.5,31.1 27.0,31.1 27.4,31.5 27.8,31.6 28.2,31.7 28.7,31.3 29.1,31.2 29.5,31.1 30.0,31.2 30.4,31.4 30.8,32.0 31.3,31.9 31.7,31.8 32.1,31.7 32.5,31.6 33.0,31.2 33.4,31.5 33.8,31.6 34.3,31.5 34.7,31.5 35.1,31.6 35.6,31.8 36.0,31.6 36.4,30.3 36.9,30.2 37.3,30.8 37.7,31.3 38.1,31.2 38.6,31.5 39.0,31.5 39.4,31.3 39.9,31.5 40.3,31.0 40.7,29.0 41.2,28.0 41.6,29.0 42.0,29.5 42.4,28.7 42.9,27.8 43.3,28.2 43.7,27.9 44.2,28.4 44.6,28.8 45.0,28.2 45.5,28.3 45.9,26.5 46.3,25.8 46.7,26.4 47.2,28.2 47.6,29.0 48.0,28.3 48.5,28.0 48.9,28.2 49.3,28.9 49.8,29.7 50.2,29.7 50.6,29.8 51.1,29.9 51.5,29.1 51.9,29.4 52.3,29.6 52.8,29.9 53.2,30.4 53.6,30.5 54.1,30.1 54.5,30.0 54.9,30.1 55.4,30.7 55.8,30.7 56.2,30.2 56.6,30.9 57.1,31.4 57.5,30.8 57.9,30.2 58.4,29.9 58.8,29.6 59.2,28.9 59.7,29.1 60.1,29.0 60.5,28.9 60.9,28.1 61.4,27.4 61.8,26.8 62.2,27.4 62.7,26.6 63.1,26.0 63.5,26.2 64.0,26.2 64.4,25.3 64.8,25.7 65.3,26.0 65.7,26.3 66.1,26.6 66.5,25.8 67.0,24.9 67.4,23.9 67.8,23.0 68.3,21.9 68.7,23.0 69.1,24.1 69.6,24.0 70.0,24.9 70.4,25.5 70.8,24.5 71.3,23.6 71.7,23.1 72.1,22.1 72.6,21.3 73.0,20.2 73.4,19.8 73.9,20.0 74.3,18.8 74.7,17.5 75.1,18.8 75.6,17.6 76.0,16.3 76.4,17.6 76.9,19.0 77.3,20.2 77.7,21.4 78.2,20.3 78.6,21.1 79.0,20.6 79.5,20.3 79.9,19.1 80.3,17.9 80.7,16.6 81.2,17.5 81.6,18.4 82.0,18.7 82.5,19.8 82.9,19.7 83.3,19.3 83.8,20.2 84.2,20.6 84.6,20.6 85.0,21.3 85.5,20.8 85.9,19.6 86.3,19.6 86.8,20.3 87.2,19.8 87.6,18.8 88.1,18.1 88.5,19.2 88.9,18.0 89.3,16.7 89.8,15.3 90.2,13.9 90.6,12.4 91.1,10.8 91.5,12.4 91.9,13.9 92.4,13.8 92.8,12.3 93.2,10.8 93.6,9.1 94.1,7.4 94.5,6.9 94.9,8.8 95.4,7.1 95.8,5.6 96.2,5.3 96.7,5.1 97.1,3.2 97.5,2.0 98.0,3.3 98.4,5.4 98.8,5.8 99.2,5.9 99.7,6.5 100.1,7.5 100.5,6.5 101.0,6.2 101.4,6.3 101.8,6.1 102.3,6.0 102.7,6.8 103.1,7.7 103.5,7.2 104.0,5.4 104.4,6.2 104.8,7.0 105.3,6.9 105.7,6.6 106.1,8.5 106.6,7.3 107.0,7.0 107.4,6.8 107.8,7.7 108.3,7.0 108.7,5.1 109.1,4.4 109.6,4.1 110.0,5.7", "ret_12_1": 109.0, "ret_6_1": 186.0, "ret_3_1": 56.0, "volatility": 56.2, "traded_daily_cr": 49.0, "watch": "Nothing flagged", "from_12m_high": -8.8, "signal_rank": 20, "data_quality": "Green"}, {"rank": 10, "symbol": "LAURUSLABS", "isin": "INE947Q01028", "qty": 7, "last_close": 2010.7, "amount": 14075.0, "spark_12m": "2.0,29.5 2.4,30.2 2.9,30.1 3.3,30.1 3.7,30.4 4.2,32.0 4.6,31.8 5.0,31.8 5.4,31.0 5.9,31.2 6.3,31.2 6.7,31.2 7.2,31.5 7.6,31.2 8.0,30.9 8.5,31.0 8.9,30.9 9.3,30.9 9.7,31.0 10.2,30.3 10.6,29.8 11.0,29.7 11.5,29.5 11.9,29.7 12.3,29.3 12.8,28.8 13.2,28.8 13.6,28.6 14.0,29.0 14.5,28.4 14.9,28.2 15.3,28.3 15.8,28.3 16.2,27.8 16.6,28.2 17.1,28.1 17.5,27.9 17.9,27.8 18.4,27.3 18.8,27.6 19.2,28.1 19.6,28.1 20.1,28.4 20.5,28.3 20.9,28.4 21.4,28.1 21.8,27.7 22.2,27.0 22.7,27.1 23.1,27.3 23.5,27.4 23.9,27.5 24.4,27.2 24.8,27.7 25.2,27.3 25.7,27.4 26.1,27.3 26.5,27.5 27.0,27.7 27.4,27.8 27.8,27.6 28.2,27.4 28.7,26.7 29.1,26.2 29.5,26.1 30.0,25.7 30.4,25.7 30.8,25.8 31.3,25.5 31.7,25.1 32.1,25.1 32.5,25.2 33.0,25.2 33.4,24.9 33.8,24.6 34.3,25.3 34.7,25.7 35.1,26.7 35.6,26.4 36.0,25.6 36.4,25.9 36.9,26.2 37.3,26.9 37.7,28.1 38.1,27.7 38.6,27.4 39.0,27.8 39.4,27.8 39.9,28.5 40.3,28.7 40.7,29.0 41.2,28.4 41.6,28.3 42.0,28.7 42.4,29.0 42.9,28.2 43.3,28.7 43.7,27.5 44.2,27.3 44.6,27.5 45.0,27.5 45.5,27.5 45.9,26.9 46.3,27.3 46.7,27.3 47.2,27.4 47.6,27.1 48.0,25.9 48.5,25.5 48.9,25.9 49.3,26.2 49.8,27.0 50.2,26.7 50.6,27.2 51.1,27.3 51.5,26.9 51.9,26.8 52.3,26.6 52.8,27.7 53.2,28.8 53.6,28.6 54.1,28.2 54.5,29.2 54.9,28.1 55.4,28.8 55.8,28.0 56.2,27.2 56.6,27.6 57.1,28.0 57.5,26.8 57.9,26.7 58.4,26.4 58.8,26.4 59.2,25.8 59.7,25.7 60.1,25.4 60.5,25.6 60.9,24.9 61.4,24.6 61.8,24.4 62.2,24.6 62.7,25.0 63.1,25.4 63.5,24.6 64.0,25.0 64.4,24.7 64.8,25.6 65.3,25.2 65.7,25.3 66.1,23.7 66.5,23.7 67.0,23.4 67.4,22.7 67.8,22.1 68.3,21.2 68.7,21.1 69.1,20.8 69.6,19.9 70.0,19.7 70.4,19.6 70.8,19.2 71.3,18.8 71.7,19.1 72.1,19.2 72.6,18.9 73.0,18.5 73.4,18.3 73.9,18.8 74.3,18.1 74.7,18.3 75.1,18.0 75.6,17.1 76.0,16.7 76.4,17.7 76.9,17.2 77.3,18.2 77.7,18.1 78.2,18.0 78.6,18.1 79.0,18.4 79.5,18.6 79.9,18.6 80.3,17.5 80.7,16.9 81.2,15.8 81.6,16.5 82.0,16.6 82.5,15.3 82.9,14.9 83.3,15.5 83.8,14.6 84.2,14.3 84.6,14.6 85.0,15.9 85.5,16.1 85.9,15.1 86.3,14.4 86.8,13.9 87.2,13.8 87.6,14.0 88.1,13.9 88.5,14.6 88.9,13.9 89.3,13.0 89.8,13.4 90.2,13.6 90.6,12.8 91.1,10.0 91.5,8.9 91.9,8.3 92.4,8.3 92.8,7.4 93.2,7.6 93.6,6.6 94.1,7.0 94.5,7.1 94.9,6.7 95.4,6.5 95.8,6.4 96.2,6.6 96.7,6.6 97.1,8.2 97.5,7.6 98.0,7.5 98.4,7.8 98.8,7.2 99.2,7.8 99.7,7.8 100.1,6.2 100.5,5.7 101.0,4.6 101.4,4.4 101.8,5.0 102.3,6.3 102.7,6.2 103.1,6.1 103.5,6.8 104.0,5.9 104.4,4.2 104.8,4.4 105.3,4.2 105.7,3.6 106.1,4.7 106.6,5.2 107.0,4.1 107.4,4.0 107.8,2.4 108.3,2.7 108.7,2.0 109.1,2.2 109.6,2.7 110.0,2.6", "ret_12_1": 109.0, "ret_6_1": 94.4, "ret_3_1": 27.2, "volatility": 28.1, "traded_daily_cr": 300.0, "watch": "Nothing flagged", "from_12m_high": -1.1, "signal_rank": 21, "data_quality": "Green"}]}, "prices": {}, "entry_override": {}, "news": null, "created": "2026-09-28T13:27:26", "last_updated": null, "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its </t>
+          <t>{"batch": {"batch_id": "2026-09-28", "title": "SwingScope batch 2026-09-28", "signal_date": "2026-09-28", "exit_date_est": "2026-10-27", "hold_sessions": 21, "universe": "liquidity top 400 of all NSE stocks", "capital": 139903.0, "est_costs": 859.0, "cost_pct": 0.6, "regime": "Down", "regime_note": "the signal's weakest regime historically", "warnings": "0 of 10", "evidence": ["Backtest, 2017\u20132026 | Replayed point in time on your survivorship-free archive. Not live results. | Signal strength | IC +0.041 | rank IC over 113 monthly dates, 2017-2026 (t 2.52); validated benchmark 0.026 | Top vs bottom decile | +1.89% | per 21-session hold, before costs (t 2.94) | Top-10 picks | +1.45% | per hold after 0.60% costs; Nifty 50 earned +1.02% before costs | Entry timing | Open wins | buying at the open beat all 30 support-entry rules (best -0.12% per hold) | Down markets | IC +0.009 | over 27 down-regime dates, against +0.050 over 86 up-regime dates", "Live record | No results yet | The first live result arrives when this system finishes its first batch. Live results are kept apart from the backtest and never mixed in."], "stocks": [{"rank": 1, "symbol": "TDPOWERSYS", "isin": "INE419M01035", "qty": 20, "last_close": 722.0, "amount": 14440.0, "spark_12m": "2.0,31.7 2.4,32.0 2.9,31.7 3.3,31.1 3.7,31.1 4.2,31.1 4.6,31.0 5.0,30.6 5.4,30.4 5.9,29.2 6.3,29.3 6.7,29.5 7.2,29.8 7.6,30.1 8.0,30.4 8.5,30.5 8.9,30.3 9.3,29.4 9.7,29.3 10.2,28.8 10.6,29.1 11.0,28.9 11.5,29.1 11.9,29.2 12.3,29.1 12.8,29.0 13.2,28.4 13.6,28.0 14.0,25.5 14.5,24.3 14.9,24.2 15.3,24.8 15.8,25.3 16.2,25.2 16.6,25.4 17.1,24.2 17.5,25.4 17.9,25.2 18.4,25.2 18.8,25.7 19.2,25.8 19.6,25.9 20.1,26.9 20.5,25.8 20.9,25.9 21.4,24.9 21.8,24.9 22.2,25.4 22.7,25.0 23.1,25.0 23.5,25.8 23.9,26.8 24.4,27.7 24.8,28.3 25.2,27.7 25.7,28.1 26.1,28.2 26.5,27.9 27.0,27.6 27.4,27.9 27.8,27.1 28.2,27.6 28.7,27.1 29.1,26.4 29.5,26.7 30.0,27.0 30.4,27.3 30.8,27.7 31.3,27.5 31.7,27.5 32.1,28.3 32.5,28.0 33.0,27.7 33.4,27.9 33.8,27.5 34.3,27.9 34.7,28.3 35.1,28.8 35.6,27.9 36.0,28.2 36.4,28.5 36.9,28.7 37.3,29.2 37.7,29.4 38.1,29.5 38.6,29.7 39.0,29.6 39.4,28.8 39.9,28.2 40.3,26.7 40.7,26.2 41.2,24.3 41.6,24.1 42.0,24.5 42.4,25.2 42.9,24.8 43.3,23.3 43.7,22.8 44.2,23.4 44.6,23.8 45.0,23.1 45.5,22.8 45.9,22.8 46.3,22.4 46.7,22.4 47.2,21.8 47.6,22.3 48.0,22.5 48.5,22.5 48.9,21.8 49.3,22.2 49.8,22.6 50.2,22.4 50.6,22.5 51.1,23.5 51.5,24.3 51.9,24.7 52.3,24.4 52.8,25.3 53.2,24.9 53.6,24.3 54.1,23.7 54.5,23.8 54.9,23.0 55.4,24.2 55.8,23.1 56.2,22.3 56.6,23.4 57.1,23.3 57.5,23.0 57.9,23.0 58.4,22.5 58.8,22.5 59.2,22.4 59.7,22.6 60.1,21.2 60.5,21.5 60.9,20.8 61.4,20.0 61.8,19.2 62.2,18.3 62.7,18.6 63.1,17.4 63.5,17.2 64.0,16.0 64.4,16.6 64.8,15.0 65.3,15.0 65.7,14.8 66.1,14.6 66.5,14.2 67.0,14.5 67.4,12.2 67.8,13.0 68.3,14.1 68.7,14.4 69.1,14.2 69.6,14.0 70.0,10.4 70.4,9.9 70.8,11.9 71.3,12.6 71.7,10.6 72.1,10.8 72.6,10.7 73.0,8.8 73.4,9.8 73.9,10.2 74.3,12.7 74.7,12.5 75.1,11.1 75.6,10.0 76.0,10.3 76.4,12.8 76.9,12.6 77.3,14.8 77.7,15.6 78.2,13.7 78.6,13.6 79.0,14.4 79.5,12.7 79.9,11.6 80.3,11.5 80.7,10.0 81.2,9.2 81.6,11.7 82.0,12.0 82.5,12.6 82.9,12.4 83.3,13.7 83.8,13.8 84.2,16.6 84.6,14.2 85.0,15.7 85.5,16.9 85.9,16.6 86.3,14.9 86.8,14.9 87.2,15.6 87.6,14.2 88.1,15.6 88.5,15.5 88.9,15.2 89.3,15.5 89.8,14.6 90.2,15.2 90.6,15.9 91.1,15.2 91.5,15.9 91.9,18.1 92.4,17.5 92.8,15.5 93.2,16.0 93.6,15.5 94.1,13.5 94.5,12.7 94.9,11.8 95.4,12.5 95.8,11.4 96.2,5.6 96.7,5.6 97.1,5.5 97.5,3.7 98.0,2.7 98.4,3.8 98.8,4.9 99.2,4.1 99.7,3.4 100.1,6.2 100.5,6.3 101.0,5.6 101.4,4.9 101.8,3.6 102.3,4.6 102.7,5.9 103.1,6.6 103.5,5.6 104.0,6.0 104.4,4.0 104.8,4.8 105.3,4.4 105.7,2.0 106.1,6.5 106.6,8.1 107.0,6.7 107.4,4.3 107.8,5.2 108.3,4.7 108.7,4.2 109.1,5.5 109.6,5.0 110.0,6.7", "ret_12_1": 177.0, "ret_6_1": 72.2, "ret_3_1": 19.6, "volatility": 60.1, "traded_daily_cr": 128.0, "watch": "Nothing flagged", "from_12m_high": -10.3, "signal_rank": 6, "data_quality": "Green"}, {"rank": 2, "symbol": "AEROFLEX", "isin": "INE024001021", "qty": 29, "last_close": 513.4, "amount": 14889.0, "spark_12m": "2.0,29.8 2.4,29.6 2.9,29.5 3.3,30.0 3.7,30.1 4.2,30.5 4.6,30.8 5.0,30.9 5.4,30.9 5.9,30.5 6.3,30.7 6.7,30.8 7.2,30.9 7.6,31.0 8.0,31.0 8.5,31.1 8.9,31.2 9.3,31.2 9.7,31.2 10.2,31.2 10.6,31.4 11.0,31.1 11.5,31.0 11.9,31.0 12.3,31.0 12.8,30.1 13.2,30.1 13.6,30.5 14.0,30.0 14.5,29.8 14.9,30.3 15.3,30.5 15.8,30.0 16.2,30.0 16.6,30.2 17.1,30.2 17.5,30.1 17.9,29.9 18.4,30.1 18.8,30.3 19.2,30.2 19.6,30.2 20.1,30.5 20.5,30.9 20.9,30.2 21.4,30.2 21.8,30.4 22.2,30.0 22.7,30.2 23.1,30.3 23.5,30.6 23.9,30.6 24.4,30.7 24.8,31.3 25.2,31.0 25.7,30.7 26.1,30.9 26.5,30.7 27.0,30.3 27.4,30.5 27.8,30.3 28.2,30.7 28.7,29.5 29.1,29.2 29.5,28.8 30.0,28.6 30.4,28.9 30.8,29.1 31.3,29.3 31.7,29.5 32.1,29.6 32.5,29.2 33.0,29.0 33.4,29.3 33.8,29.1 34.3,29.9 34.7,30.2 35.1,30.2 35.6,30.5 36.0,30.7 36.4,30.8 36.9,30.9 37.3,31.3 37.7,31.8 38.1,31.5 38.6,32.0 39.0,31.7 39.4,31.4 39.9,30.4 40.3,30.6 40.7,31.0 41.2,30.1 41.6,29.9 42.0,29.9 42.4,30.1 42.9,29.3 43.3,29.4 43.7,29.6 44.2,29.5 44.6,30.0 45.0,29.6 45.5,28.5 45.9,27.1 46.3,27.0 46.7,27.3 47.2,27.6 47.6,27.7 48.0,27.0 48.5,26.9 48.9,26.5 49.3,27.2 49.8,27.7 50.2,27.3 50.6,27.6 51.1,27.9 51.5,27.5 51.9,26.5 52.3,26.3 52.8,26.5 53.2,25.6 53.6,25.3 54.1,25.6 54.5,26.8 54.9,26.6 55.4,27.3 55.8,25.3 56.2,25.3 56.6,26.1 57.1,26.2 57.5,25.4 57.9,25.2 58.4,25.0 58.8,25.7 59.2,24.6 59.7,23.6 60.1,22.6 60.5,22.6 60.9,22.3 61.4,22.1 61.8,21.0 62.2,21.7 62.7,22.6 63.1,21.5 63.5,22.1 64.0,23.4 64.4,22.2 64.8,22.3 65.3,21.4 65.7,21.4 66.1,21.6 66.5,20.5 67.0,18.6 67.4,13.6 67.8,11.7 68.3,14.7 68.7,17.1 69.1,17.1 69.6,17.4 70.0,16.7 70.4,16.8 70.8,15.9 71.3,15.2 71.7,16.0 72.1,14.3 72.6,13.5 73.0,14.3 73.4,14.0 73.9,14.4 74.3,15.4 74.7,13.1 75.1,12.1 75.6,11.7 76.0,13.1 76.4,14.6 76.9,12.7 77.3,13.5 77.7,13.9 78.2,11.1 78.6,8.9 79.0,9.4 79.5,6.5 79.9,8.1 80.3,6.8 80.7,6.6 81.2,7.1 81.6,8.8 82.0,9.7 82.5,9.6 82.9,9.4 83.3,8.1 83.8,8.9 84.2,10.5 84.6,10.3 85.0,13.6 85.5,14.5 85.9,14.2 86.3,13.6 86.8,13.0 87.2,13.8 87.6,13.0 88.1,13.8 88.5,13.8 88.9,14.1 89.3,13.6 89.8,14.0 90.2,13.1 90.6,13.0 91.1,13.2 91.5,11.2 91.9,10.9 92.4,12.6 92.8,12.0 93.2,12.3 93.6,9.9 94.1,10.5 94.5,11.8 94.9,12.7 95.4,13.1 95.8,12.9 96.2,11.2 96.7,11.1 97.1,10.2 97.5,10.5 98.0,8.3 98.4,9.2 98.8,9.1 99.2,7.1 99.7,7.0 100.1,7.6 100.5,4.7 101.0,5.7 101.4,4.3 101.8,5.5 102.3,3.6 102.7,4.4 103.1,4.3 103.5,4.6 104.0,3.1 104.4,2.0 104.8,2.9 105.3,2.7 105.7,2.7 106.1,6.8 106.6,8.7 107.0,7.5 107.4,6.5 107.8,6.2 108.3,6.1 108.7,5.8 109.1,5.3 109.6,5.5 110.0,6.3", "ret_12_1": 175.0, "ret_6_1": 107.0, "ret_3_1": 10.7, "volatility": 67.3, "traded_daily_cr": 53.0, "watch": "Nothing flagged", "from_12m_high": -10.5, "signal_rank": 7, "data_quality": "Green"}, {"rank": 3, "symbol": "ATHERENERG", "isin": "INE0LEZ01016", "qty": 10, "last_close": 1454.9, "amount": 14549.0, "spark_12m": "2.0,30.9 2.4,30.7 2.9,31.2 3.3,30.9 3.7,31.6 4.2,32.0 4.6,31.0 5.0,31.4 5.4,30.8 5.9,30.7 6.3,30.0 6.7,29.7 7.2,29.5 7.6,29.9 8.0,30.6 8.5,30.2 8.9,30.1 9.3,29.6 9.7,28.2 10.2,28.1 10.6,27.4 11.0,26.3 11.5,27.1 11.9,27.8 12.3,27.1 12.8,27.0 13.2,27.8 13.6,27.8 14.0,28.2 14.5,28.2 14.9,28.8 15.3,29.6 15.8,29.1 16.2,29.8 16.6,29.0 17.1,29.8 17.5,29.5 17.9,29.2 18.4,29.3 18.8,28.7 19.2,28.3 19.6,28.0 20.1,28.1 20.5,28.6 20.9,28.3 21.4,28.1 21.8,27.7 22.2,27.5 22.7,27.7 23.1,28.3 23.5,28.4 23.9,28.7 24.4,28.6 24.8,28.5 25.2,29.2 25.7,29.3 26.1,29.3 26.5,29.3 27.0,28.3 27.4,28.6 27.8,28.9 28.2,28.9 28.7,27.9 29.1,28.0 29.5,27.8 30.0,27.4 30.4,27.7 30.8,27.5 31.3,27.1 31.7,26.6 32.1,27.0 32.5,26.9 33.0,28.3 33.4,28.1 33.8,28.1 34.3,28.6 34.7,29.6 35.1,29.5 35.6,29.1 36.0,29.3 36.4,30.0 36.9,29.8 37.3,30.3 37.7,30.1 38.1,29.7 38.6,29.9 39.0,30.0 39.4,30.3 39.9,30.4 40.3,29.9 40.7,30.3 41.2,28.6 41.6,28.0 42.0,27.6 42.4,27.8 42.9,27.3 43.3,27.3 43.7,27.5 44.2,27.3 44.6,27.7 45.0,27.7 45.5,27.3 45.9,27.2 46.3,27.1 46.7,27.7 47.2,27.5 47.6,28.0 48.0,27.8 48.5,27.9 48.9,27.7 49.3,27.8 49.8,27.9 50.2,28.3 50.6,28.6 51.1,28.4 51.5,28.1 51.9,27.9 52.3,27.7 52.8,27.8 53.2,27.6 53.6,27.3 54.1,26.7 54.5,26.6 54.9,25.9 55.4,26.7 55.8,26.5 56.2,26.0 56.6,25.5 57.1,26.6 57.5,26.2 57.9,26.4 58.4,25.8 58.8,26.4 59.2,26.2 59.7,24.9 60.1,23.8 60.5,22.7 60.9,23.6 61.4,23.7 61.8,24.1 62.2,23.2 62.7,23.0 63.1,22.7 63.5,22.9 64.0,23.3 64.4,21.8 64.8,22.1 65.3,21.9 65.7,22.0 66.1,22.0 66.5,21.9 67.0,23.0 67.4,22.7 67.8,22.5 68.3,21.1 68.7,22.3 69.1,21.6 69.6,21.9 70.0,21.9 70.4,22.6 70.8,22.6 71.3,22.7 71.7,23.2 72.1,23.3 72.6,22.3 73.0,21.6 73.4,21.5 73.9,21.3 74.3,21.9 74.7,21.4 75.1,19.8 75.6,20.7 76.0,19.5 76.4,20.3 76.9,19.5 77.3,19.3 77.7,19.7 78.2,19.6 78.6,19.7 79.0,20.4 79.5,20.6 79.9,21.1 80.3,21.1 80.7,21.4 81.2,20.2 81.6,20.6 82.0,20.4 82.5,18.2 82.9,16.8 83.3,17.1 83.8,16.7 84.2,17.1 84.6,17.2 85.0,16.8 85.5,15.3 85.9,14.8 86.3,14.6 86.8,15.7 87.2,15.3 87.6,12.9 88.1,13.6 88.5,13.2 88.9,12.9 89.3,13.1 89.8,13.6 90.2,14.5 90.6,15.1 91.1,14.9 91.5,15.2 91.9,14.1 92.4,14.3 92.8,13.8 93.2,13.5 93.6,9.0 94.1,8.4 94.5,8.9 94.9,8.2 95.4,8.6 95.8,7.1 96.2,6.0 96.7,7.0 97.1,7.4 97.5,8.1 98.0,8.6 98.4,9.3 98.8,9.0 99.2,8.7 99.7,8.9 100.1,9.2 100.5,7.8 101.0,7.8 101.4,4.8 101.8,2.2 102.3,2.0 102.7,3.0 103.1,4.2 103.5,5.6 104.0,5.2 104.4,5.7 104.8,5.7 105.3,3.7 105.7,3.8 106.1,6.0 106.6,6.0 107.0,6.4 107.4,4.2 107.8,5.4 108.3,6.6 108.7,7.7 109.1,7.7 109.6,7.8 110.0,8.8", "ret_12_1": 166.0, "ret_6_1": 97.5, "ret_3_1": 31.1, "volatility": 49.4, "traded_daily_cr": 493.0, "watch": "Nothing flagged", "from_12m_high": -15.7, "signal_rank": 9, "data_quality": "Green"}, {"rank": 4, "symbol": "THANGAMAYL", "isin": "INE085J01014", "qty": 2, "last_close": 5011.5, "amount": 10023.0, "spark_12m": "2.0,30.9 2.4,31.1 2.9,31.4 3.3,31.4 3.7,31.4 4.2,31.6 4.6,31.7 5.0,31.6 5.4,31.6 5.9,31.2 6.3,31.3 6.7,31.6 7.2,31.2 7.6,31.5 8.0,31.6 8.5,31.5 8.9,31.8 9.3,31.9 9.7,31.9 10.2,31.9 10.6,31.9 11.0,31.9 11.5,32.0 11.9,31.5 12.3,31.6 12.8,31.3 13.2,31.4 13.6,31.3 14.0,30.8 14.5,28.3 14.9,25.9 15.3,25.7 15.8,23.9 16.2,25.3 16.6,24.8 17.1,24.1 17.5,24.4 17.9,24.5 18.4,24.7 18.8,24.9 19.2,25.1 19.6,25.2 20.1,26.0 20.5,24.8 20.9,24.8 21.4,24.7 21.8,24.8 22.2,24.7 22.7,24.1 23.1,25.2 23.5,24.6 23.9,24.8 24.4,24.9 24.8,25.2 25.2,24.7 25.7,24.9 26.1,24.9 26.5,25.0 27.0,25.0 27.4,24.9 27.8,24.4 28.2,24.6 28.7,24.2 29.1,23.8 29.5,23.7 30.0,24.5 30.4,25.0 30.8,25.0 31.3,25.0 31.7,24.9 32.1,24.7 32.5,24.8 33.0,24.2 33.4,23.4 33.8,21.4 34.3,21.2 34.7,22.7 35.1,22.3 35.6,21.9 36.0,21.5 36.4,21.8 36.9,22.1 37.3,22.1 37.7,21.2 38.1,22.6 38.6,22.9 39.0,23.8 39.4,22.8 39.9,23.4 40.3,24.3 40.7,24.9 41.2,25.1 41.6,24.5 42.0,25.1 42.4,23.9 42.9,22.1 43.3,22.2 43.7,22.3 44.2,22.5 44.6,22.9 45.0,22.1 45.5,22.3 45.9,22.6 46.3,23.4 46.7,23.0 47.2,22.8 47.6,22.0 48.0,21.5 48.5,21.0 48.9,20.8 49.3,21.4 49.8,22.7 50.2,22.6 50.6,22.2 51.1,22.9 51.5,22.1 51.9,23.1 52.3,23.0 52.8,23.3 53.2,23.6 53.6,23.4 54.1,23.3 54.5,24.1 54.9,24.3 55.4,25.2 55.8,24.4 56.2,22.8 56.6,23.7 57.1,23.7 57.5,23.0 57.9,23.1 58.4,21.9 58.8,21.3 59.2,20.3 59.7,20.0 60.1,19.8 60.5,19.5 60.9,19.1 61.4,19.0 61.8,19.3 62.2,19.8 62.7,19.8 63.1,20.4 63.5,21.7 64.0,21.7 64.4,20.8 64.8,20.7 65.3,20.6 65.7,20.8 66.1,20.6 66.5,20.7 67.0,20.1 67.4,19.9 67.8,19.1 68.3,20.5 68.7,22.4 69.1,22.5 69.6,22.7 70.0,22.8 70.4,23.1 70.8,22.5 71.3,21.8 71.7,21.3 72.1,21.6 72.6,21.5 73.0,21.6 73.4,21.0 73.9,19.4 74.3,18.9 74.7,17.2 75.1,16.1 75.6,12.0 76.0,13.0 76.4,12.2 76.9,12.3 77.3,12.4 77.7,12.6 78.2,12.2 78.6,12.1 79.0,12.4 79.5,11.4 79.9,12.5 80.3,12.4 80.7,11.8 81.2,12.8 81.6,12.4 82.0,11.6 82.5,10.0 82.9,7.1 83.3,9.6 83.8,7.6 84.2,8.4 84.6,7.7 85.0,7.2 85.5,4.8 85.9,6.0 86.3,6.3 86.8,8.0 87.2,6.8 87.6,5.9 88.1,7.2 88.5,6.9 88.9,7.2 89.3,6.8 89.8,6.7 90.2,4.5 90.6,4.3 91.1,2.0 91.5,2.8 91.9,6.8 92.4,10.4 92.8,13.7 93.2,15.1 93.6,16.5 94.1,15.2 94.5,14.1 94.9,13.4 95.4,13.0 95.8,13.7 96.2,13.1 96.7,13.4 97.1,12.5 97.5,13.0 98.0,12.2 98.4,12.0 98.8,12.4 99.2,12.2 99.7,12.2 100.1,12.7 100.5,12.2 101.0,12.1 101.4,12.5 101.8,12.6 102.3,13.2 102.7,13.6 103.1,13.3 103.5,13.1 104.0,12.3 104.4,12.9 104.8,14.3 105.3,14.5 105.7,14.2 106.1,15.4 106.6,15.3 107.0,16.0 107.4,14.7 107.8,15.3 108.3,14.3 108.7,13.2 109.1,14.4 109.6,14.2 110.0,14.9", "ret_12_1": 154.0, "ret_6_1": 66.3, "ret_3_1": -14.0, "volatility": 59.8, "traded_daily_cr": 71.0, "watch": "Nothing flagged", "from_12m_high": -31.4, "signal_rank": 11, "data_quality": "Green"}, {"rank": 5, "symbol": "RRKABEL", "isin": "INE777K01022", "qty": 6, "last_close": 2459.8, "amount": 14759.0, "spark_12m": "2.0,31.3 2.4,31.1 2.9,30.7 3.3,31.2 3.7,31.2 4.2,32.0 4.6,31.8 5.0,31.2 5.4,31.1 5.9,31.4 6.3,31.1 6.7,31.1 7.2,31.3 7.6,31.4 8.0,31.0 8.5,31.2 8.9,31.3 9.3,31.3 9.7,31.0 10.2,31.2 10.6,31.4 11.0,31.2 11.5,31.4 11.9,31.5 12.3,30.1 12.8,28.7 13.2,28.4 13.6,28.6 14.0,28.6 14.5,29.0 14.9,28.4 15.3,28.8 15.8,29.2 16.2,29.8 16.6,29.6 17.1,28.8 17.5,29.3 17.9,29.3 18.4,29.1 18.8,29.7 19.2,29.5 19.6,29.4 20.1,29.7 20.5,29.7 20.9,29.5 21.4,29.0 21.8,29.1 22.2,28.8 22.7,28.8 23.1,28.8 23.5,29.0 23.9,28.9 24.4,29.4 24.8,29.5 25.2,29.1 25.7,28.6 26.1,28.7 26.5,28.4 27.0,27.8 27.4,28.1 27.8,28.3 28.2,28.3 28.7,27.3 29.1,26.5 29.5,26.6 30.0,27.1 30.4,27.5 30.8,28.1 31.3,28.2 31.7,27.9 32.1,27.6 32.5,26.9 33.0,26.4 33.4,26.3 33.8,26.4 34.3,26.7 34.7,26.9 35.1,27.3 35.6,27.0 36.0,27.1 36.4,27.5 36.9,28.0 37.3,28.6 37.7,28.6 38.1,28.4 38.6,29.7 39.0,30.0 39.4,29.7 39.9,30.3 40.3,29.3 40.7,29.6 41.2,28.4 41.6,27.8 42.0,27.5 42.4,27.7 42.9,27.6 43.3,28.5 43.7,28.2 44.2,28.3 44.6,28.7 45.0,28.7 45.5,28.4 45.9,28.5 46.3,28.4 46.7,28.1 47.2,27.9 47.6,27.0 48.0,26.9 48.5,26.7 48.9,26.0 49.3,26.5 49.8,27.3 50.2,27.1 50.6,26.6 51.1,27.2 51.5,27.8 51.9,28.4 52.3,28.2 52.8,29.8 53.2,29.3 53.6,28.9 54.1,28.1 54.5,28.9 54.9,29.0 55.4,30.3 55.8,29.7 56.2,29.7 56.6,30.3 57.1,30.7 57.5,30.0 57.9,30.0 58.4,30.0 58.8,30.2 59.2,28.8 59.7,29.1 60.1,28.9 60.5,29.3 60.9,29.0 61.4,27.8 61.8,27.5 62.2,27.6 62.7,27.8 63.1,27.7 63.5,28.3 64.0,28.1 64.4,26.9 64.8,25.1 65.3,24.8 65.7,25.8 66.1,22.2 66.5,22.1 67.0,21.8 67.4,19.6 67.8,19.3 68.3,19.7 68.7,19.4 69.1,19.0 69.6,17.6 70.0,19.1 70.4,19.2 70.8,19.7 71.3,18.9 71.7,19.2 72.1,19.2 72.6,18.5 73.0,18.7 73.4,19.1 73.9,17.3 74.3,17.8 74.7,17.9 75.1,15.6 75.6,14.4 76.0,14.4 76.4,15.6 76.9,15.2 77.3,15.3 77.7,16.0 78.2,15.3 78.6,15.0 79.0,14.8 79.5,14.6 79.9,13.1 80.3,12.7 80.7,12.1 81.2,11.8 81.6,10.6 82.0,9.7 82.5,9.5 82.9,11.4 83.3,11.6 83.8,11.4 84.2,12.3 84.6,13.1 85.0,14.9 85.5,15.0 85.9,14.7 86.3,14.3 86.8,11.7 87.2,12.2 87.6,13.2 88.1,11.2 88.5,13.1 88.9,12.4 89.3,12.2 89.8,10.7 90.2,11.7 90.6,9.6 91.1,9.1 91.5,8.2 91.9,8.5 92.4,8.4 92.8,7.7 93.2,7.2 93.6,7.0 94.1,4.4 94.5,4.9 94.9,5.0 95.4,5.0 95.8,4.0 96.2,4.4 96.7,3.7 97.1,4.5 97.5,5.2 98.0,4.5 98.4,2.5 98.8,2.6 99.2,2.2 99.7,3.0 100.1,4.2 100.5,4.1 101.0,3.7 101.4,2.4 101.8,2.0 102.3,3.0 102.7,7.2 103.1,7.5 103.5,10.3 104.0,11.5 104.4,10.4 104.8,10.9 105.3,10.6 105.7,10.8 106.1,11.6 106.6,11.3 107.0,11.4 107.4,10.4 107.8,11.1 108.3,10.0 108.7,9.9 109.1,9.0 109.6,9.0 110.0,10.2", "ret_12_1": 126.0, "ret_6_1": 110.0, "ret_3_1": 18.2, "volatility": 44.0, "traded_daily_cr": 93.0, "watch": "Nothing flagged", "from_12m_high": -16.0, "signal_rank": 15, "data_quality": "Green"}, {"rank": 6, "symbol": "ACUTAAS", "isin": "INE00FF01025", "qty": 4, "last_close": 3214.4, "amount": 12858.0, "spark_12m": "2.0,30.2 2.4,30.2 2.9,30.3 3.3,30.3 3.7,30.8 4.2,31.5 4.6,31.6 5.0,32.0 5.4,31.2 5.9,31.1 6.3,30.9 6.7,30.9 7.2,30.9 7.6,30.7 8.0,30.1 8.5,29.7 8.9,29.7 9.3,29.1 9.7,29.0 10.2,27.8 10.6,26.4 11.0,26.1 11.5,26.7 11.9,27.4 12.3,26.8 12.8,27.0 13.2,27.3 13.6,27.1 14.0,26.8 14.5,25.8 14.9,25.5 15.3,26.3 15.8,26.4 16.2,26.4 16.6,26.5 17.1,27.1 17.5,27.4 17.9,27.0 18.4,27.1 18.8,27.0 19.2,26.9 19.6,26.8 20.1,27.2 20.5,25.0 20.9,26.1 21.4,26.0 21.8,26.1 22.2,25.4 22.7,26.2 23.1,26.6 23.5,26.7 23.9,27.1 24.4,27.1 24.8,27.8 25.2,27.6 25.7,27.4 26.1,27.7 26.5,27.6 27.0,28.1 27.4,27.2 27.8,27.7 28.2,28.0 28.7,27.8 29.1,27.4 29.5,27.2 30.0,27.8 30.4,27.8 30.8,27.8 31.3,27.7 31.7,27.1 32.1,26.5 32.5,26.6 33.0,26.3 33.4,26.4 33.8,26.4 34.3,26.7 34.7,27.4 35.1,27.5 35.6,27.4 36.0,27.1 36.4,27.2 36.9,27.4 37.3,28.1 37.7,28.4 38.1,27.9 38.6,27.8 39.0,26.8 39.4,25.1 39.9,24.2 40.3,24.5 40.7,24.2 41.2,23.8 41.6,23.5 42.0,23.6 42.4,23.6 42.9,23.4 43.3,22.8 43.7,23.0 44.2,22.2 44.6,23.2 45.0,22.9 45.5,22.4 45.9,21.6 46.3,22.1 46.7,22.0 47.2,21.5 47.6,21.5 48.0,21.3 48.5,21.1 48.9,21.4 49.3,21.0 49.8,22.1 50.2,20.4 50.6,20.2 51.1,21.4 51.5,20.5 51.9,21.0 52.3,21.0 52.8,22.3 53.2,21.3 53.6,19.6 54.1,20.1 54.5,20.3 54.9,18.3 55.4,20.0 55.8,17.9 56.2,16.7 56.6,16.5 57.1,16.3 57.5,19.2 57.9,22.0 58.4,20.7 58.8,20.7 59.2,19.2 59.7,19.3 60.1,18.8 60.5,18.4 60.9,19.7 61.4,19.1 61.8,18.8 62.2,18.2 62.7,18.7 63.1,18.0 63.5,18.5 64.0,18.4 64.4,17.1 64.8,17.5 65.3,17.0 65.7,15.9 66.1,14.9 66.5,15.1 67.0,14.7 67.4,14.2 67.8,14.1 68.3,13.2 68.7,14.0 69.1,12.9 69.6,14.2 70.0,14.2 70.4,13.3 70.8,12.2 71.3,12.3 71.7,10.8 72.1,11.4 72.6,11.7 73.0,10.3 73.4,10.8 73.9,9.1 74.3,10.5 74.7,10.3 75.1,9.1 75.6,8.7 76.0,6.6 76.4,6.8 76.9,8.3 77.3,8.2 77.7,9.2 78.2,8.9 78.6,9.5 79.0,10.8 79.5,10.8 79.9,9.0 80.3,7.7 80.7,7.6 81.2,7.3 81.6,7.4 82.0,7.0 82.5,3.6 82.9,4.1 83.3,3.6 83.8,2.0 84.2,2.0 84.6,4.3 85.0,5.8 85.5,5.0 85.9,5.0 86.3,5.7 86.8,4.5 87.2,5.0 87.6,3.9 88.1,3.4 88.5,3.0 88.9,2.5 89.3,2.2 89.8,2.4 90.2,5.0 90.6,7.5 91.1,6.1 91.5,7.0 91.9,6.9 92.4,7.8 92.8,9.4 93.2,9.3 93.6,7.9 94.1,7.2 94.5,7.5 94.9,7.0 95.4,7.2 95.8,7.7 96.2,8.8 96.7,9.4 97.1,7.8 97.5,8.3 98.0,5.8 98.4,7.9 98.8,8.1 99.2,8.6 99.7,8.6 100.1,6.8 100.5,7.5 101.0,6.6 101.4,7.2 101.8,8.7 102.3,8.6 102.7,9.1 103.1,8.2 103.5,8.6 104.0,8.5 104.4,8.5 104.8,7.7 105.3,5.1 105.7,5.9 106.1,7.4 106.6,6.4 107.0,6.8 107.4,5.2 107.8,5.4 108.3,8.1 108.7,7.4 109.1,7.2 109.6,7.3 110.0,8.1", "ret_12_1": 126.0, "ret_6_1": 36.7, "ret_3_1": -5.6, "volatility": 46.7, "traded_daily_cr": 101.0, "watch": "Nothing flagged", "from_12m_high": -13.0, "signal_rank": 16, "data_quality": "Green"}, {"rank": 7, "symbol": "DIACABS", "isin": "INE989C01038", "qty": 44, "last_close": 339.25, "amount": 14927.0, "spark_12m": "2.0,27.2 2.4,27.3 2.9,27.2 3.3,27.4 3.7,28.0 4.2,28.4 4.6,28.2 5.0,28.6 5.4,28.5 5.9,28.3 6.3,28.7 6.7,29.2 7.2,29.3 7.6,29.4 8.0,29.4 8.5,29.6 8.9,29.5 9.3,29.2 9.7,29.3 10.2,29.4 10.6,29.2 11.0,29.1 11.5,29.1 11.9,29.3 12.3,28.1 12.8,28.5 13.2,28.1 13.6,28.2 14.0,28.2 14.5,28.1 14.9,27.9 15.3,28.6 15.8,28.3 16.2,28.8 16.6,28.9 17.1,28.8 17.5,28.4 17.9,28.4 18.4,28.4 18.8,28.7 19.2,28.3 19.6,28.7 20.1,29.1 20.5,29.5 20.9,29.6 21.4,29.4 21.8,29.4 22.2,28.5 22.7,28.6 23.1,28.9 23.5,29.2 23.9,29.3 24.4,29.1 24.8,29.4 25.2,29.4 25.7,29.7 26.1,29.7 26.5,29.5 27.0,29.4 27.4,29.6 27.8,29.6 28.2,29.5 28.7,29.5 29.1,29.2 29.5,29.3 30.0,29.5 30.4,29.6 30.8,29.8 31.3,29.8 31.7,29.8 32.1,29.8 32.5,29.9 33.0,29.3 33.4,29.3 33.8,29.1 34.3,29.7 34.7,30.2 35.1,30.1 35.6,30.5 36.0,30.7 36.4,30.6 36.9,30.4 37.3,31.0 37.7,30.9 38.1,30.8 38.6,31.4 39.0,31.4 39.4,31.1 39.9,31.4 40.3,31.5 40.7,31.7 41.2,31.2 41.6,30.8 42.0,31.3 42.4,31.3 42.9,30.9 43.3,30.4 43.7,30.2 44.2,30.3 44.6,30.5 45.0,29.5 45.5,29.8 45.9,29.8 46.3,30.2 46.7,30.1 47.2,30.2 47.6,30.4 48.0,30.0 48.5,29.6 48.9,29.9 49.3,29.9 49.8,30.4 50.2,29.9 50.6,30.1 51.1,30.2 51.5,29.7 51.9,29.9 52.3,30.0 52.8,30.8 53.2,31.0 53.6,31.2 54.1,30.7 54.5,31.4 54.9,31.0 55.4,32.0 55.8,31.7 56.2,30.9 56.6,31.5 57.1,31.9 57.5,31.2 57.9,31.2 58.4,30.8 58.8,30.9 59.2,30.3 59.7,30.4 60.1,29.9 60.5,29.8 60.9,29.5 61.4,28.7 61.8,28.6 62.2,27.4 62.7,27.2 63.1,27.5 63.5,27.5 64.0,27.3 64.4,26.8 64.8,27.1 65.3,27.3 65.7,27.7 66.1,26.8 66.5,26.6 67.0,25.6 67.4,26.4 67.8,26.0 68.3,25.8 68.7,26.4 69.1,25.9 69.6,24.0 70.0,23.5 70.4,24.0 70.8,24.2 71.3,23.6 71.7,23.8 72.1,23.8 72.6,23.5 73.0,22.4 73.4,23.3 73.9,23.7 74.3,25.0 74.7,23.7 75.1,24.3 75.6,23.9 76.0,22.7 76.4,23.3 76.9,22.8 77.3,23.4 77.7,23.8 78.2,22.9 78.6,21.4 79.0,22.4 79.5,22.6 79.9,22.9 80.3,22.1 80.7,22.3 81.2,22.9 81.6,22.6 82.0,22.4 82.5,22.2 82.9,22.1 83.3,22.2 83.8,22.0 84.2,23.2 84.6,21.1 85.0,20.4 85.5,19.7 85.9,18.9 86.3,20.0 86.8,20.1 87.2,20.4 87.6,20.2 88.1,20.4 88.5,20.7 88.9,18.3 89.3,15.6 89.8,15.6 90.2,15.1 90.6,12.8 91.1,11.5 91.5,10.0 91.9,8.2 92.4,9.2 92.8,9.7 93.2,9.8 93.6,10.5 94.1,8.8 94.5,7.0 94.9,5.3 95.4,5.7 95.8,5.5 96.2,4.9 96.7,5.0 97.1,4.8 97.5,5.8 98.0,4.9 98.4,5.8 98.8,6.4 99.2,6.2 99.7,6.5 100.1,8.0 100.5,8.1 101.0,8.1 101.4,6.9 101.8,7.1 102.3,7.9 102.7,8.9 103.1,9.8 103.5,8.8 104.0,8.7 104.4,8.3 104.8,8.5 105.3,6.7 105.7,4.8 106.1,2.8 106.6,2.0 107.0,4.0 107.4,5.0 107.8,4.0 108.3,4.6 108.7,3.8 109.1,5.7 109.6,6.4 110.0,8.0", "ret_12_1": 124.0, "ret_6_1": 180.0, "ret_3_1": 61.7, "volatility": 53.6, "traded_daily_cr": 51.0, "watch": "Nothing flagged", "from_12m_high": -14.1, "signal_rank": 17, "data_quality": "Green"}, {"rank": 8, "symbol": "KIRLOSENG", "isin": "INE146L01010", "qty": 7, "last_close": 2141.2, "amount": 14988.0, "spark_12m": "2.0,30.3 2.4,30.3 2.9,30.5 3.3,30.2 3.7,30.7 4.2,31.2 4.6,31.1 5.0,31.1 5.4,31.0 5.9,31.4 6.3,31.6 6.7,31.8 7.2,31.8 7.6,31.8 8.0,31.6 8.5,31.7 8.9,32.0 9.3,31.9 9.7,31.8 10.2,31.6 10.6,31.8 11.0,31.6 11.5,31.5 11.9,31.5 12.3,30.7 12.8,29.6 13.2,29.4 13.6,29.4 14.0,29.7 14.5,29.4 14.9,29.4 15.3,29.9 15.8,30.3 16.2,30.5 16.6,30.7 17.1,28.7 17.5,28.2 17.9,28.1 18.4,27.7 18.8,27.2 19.2,26.6 19.6,26.5 20.1,26.8 20.5,27.4 20.9,26.9 21.4,27.1 21.8,27.2 22.2,27.5 22.7,27.6 23.1,27.7 23.5,28.2 23.9,26.8 24.4,27.4 24.8,28.0 25.2,27.5 25.7,27.7 26.1,27.6 26.5,27.1 27.0,27.3 27.4,25.7 27.8,24.7 28.2,24.6 28.7,25.4 29.1,24.2 29.5,24.4 30.0,25.0 30.4,24.9 30.8,25.8 31.3,25.7 31.7,25.8 32.1,25.6 32.5,25.1 33.0,25.2 33.4,25.3 33.8,25.8 34.3,26.5 34.7,26.9 35.1,27.5 35.6,27.0 36.0,26.7 36.4,26.7 36.9,27.4 37.3,27.9 37.7,27.9 38.1,27.7 38.6,28.0 39.0,28.0 39.4,27.7 39.9,27.6 40.3,26.6 40.7,27.0 41.2,26.5 41.6,25.6 42.0,26.2 42.4,26.7 42.9,25.8 43.3,25.0 43.7,23.9 44.2,23.7 44.6,23.0 45.0,22.4 45.5,22.1 45.9,22.3 46.3,22.2 46.7,22.3 47.2,22.6 47.6,22.7 48.0,22.5 48.5,22.7 48.9,22.7 49.3,22.5 49.8,22.3 50.2,21.4 50.6,20.6 51.1,21.6 51.5,21.9 51.9,21.7 52.3,21.4 52.8,21.7 53.2,21.4 53.6,21.9 54.1,22.0 54.5,22.2 54.9,23.0 55.4,24.6 55.8,23.9 56.2,22.7 56.6,23.5 57.1,23.9 57.5,23.2 57.9,22.9 58.4,22.3 58.8,22.6 59.2,21.4 59.7,21.6 60.1,21.3 60.5,21.1 60.9,19.1 61.4,18.8 61.8,18.7 62.2,18.4 62.7,17.9 63.1,18.4 63.5,18.9 64.0,19.2 64.4,17.6 64.8,16.9 65.3,17.3 65.7,17.3 66.1,16.9 66.5,16.6 67.0,17.1 67.4,16.8 67.8,16.8 68.3,18.0 68.7,19.8 69.1,19.1 69.6,19.1 70.0,16.6 70.4,17.3 70.8,18.0 71.3,17.9 71.7,17.7 72.1,17.8 72.6,17.2 73.0,16.4 73.4,15.0 73.9,13.3 74.3,13.4 74.7,14.5 75.1,13.9 75.6,12.9 76.0,13.5 76.4,14.6 76.9,14.6 77.3,15.2 77.7,15.6 78.2,13.9 78.6,13.2 79.0,13.4 79.5,12.2 79.9,12.3 80.3,12.1 80.7,5.1 81.2,3.0 81.6,2.0 82.0,3.4 82.5,4.2 82.9,5.5 83.3,5.9 83.8,6.3 84.2,7.9 84.6,7.3 85.0,7.2 85.5,7.1 85.9,4.5 86.3,3.3 86.8,4.3 87.2,5.6 87.6,4.6 88.1,5.0 88.5,7.5 88.9,8.1 89.3,8.1 89.8,8.7 90.2,8.8 90.6,8.7 91.1,7.0 91.5,8.6 91.9,8.8 92.4,9.6 92.8,8.6 93.2,8.0 93.6,7.1 94.1,7.7 94.5,7.6 94.9,9.1 95.4,9.7 95.8,10.2 96.2,11.0 96.7,10.9 97.1,10.2 97.5,10.2 98.0,9.8 98.4,10.6 98.8,9.3 99.2,10.2 99.7,10.8 100.1,11.5 100.5,11.3 101.0,10.2 101.4,9.8 101.8,10.2 102.3,9.5 102.7,9.1 103.1,7.2 103.5,8.4 104.0,8.9 104.4,7.1 104.8,8.1 105.3,8.3 105.7,9.0 106.1,11.2 106.6,11.3 107.0,9.8 107.4,9.1 107.8,9.6 108.3,9.1 108.7,8.1 109.1,9.1 109.6,9.6 110.0,9.5", "ret_12_1": 123.0, "ret_6_1": 58.2, "ret_3_1": -11.2, "volatility": 49.9, "traded_daily_cr": 87.0, "watch": "Nothing flagged", "from_12m_high": -16.5, "signal_rank": 18, "data_quality": "Green"}, {"rank": 9, "symbol": "E2E", "isin": "INE255Z01027", "qty": 23, "last_close": 625.9, "amount": 14396.0, "spark_12m": "2.0,25.4 2.4,24.4 2.9,23.5 3.3,24.3 3.7,23.7 4.2,22.9 4.6,23.7 5.0,24.4 5.4,23.4 5.9,22.4 6.3,21.3 6.7,21.1 7.2,21.2 7.6,22.8 8.0,23.1 8.5,23.8 8.9,24.4 9.3,24.4 9.7,24.3 10.2,24.1 10.6,24.5 11.0,24.4 11.5,24.3 11.9,25.2 12.3,24.5 12.8,24.9 13.2,25.1 13.6,24.9 14.0,25.0 14.5,25.3 14.9,24.9 15.3,25.3 15.8,25.1 16.2,25.3 16.6,26.1 17.1,26.1 17.5,26.8 17.9,27.8 18.4,28.0 18.8,28.1 19.2,28.0 19.6,28.1 20.1,28.8 20.5,29.7 20.9,29.7 21.4,29.6 21.8,29.8 22.2,30.1 22.7,30.0 23.1,30.5 23.5,30.9 23.9,30.5 24.4,31.0 24.8,31.6 25.2,30.8 25.7,31.2 26.1,31.1 26.5,31.1 27.0,31.1 27.4,31.5 27.8,31.6 28.2,31.7 28.7,31.3 29.1,31.2 29.5,31.1 30.0,31.2 30.4,31.4 30.8,32.0 31.3,31.9 31.7,31.8 32.1,31.7 32.5,31.6 33.0,31.2 33.4,31.5 33.8,31.6 34.3,31.5 34.7,31.5 35.1,31.6 35.6,31.8 36.0,31.6 36.4,30.3 36.9,30.2 37.3,30.8 37.7,31.3 38.1,31.2 38.6,31.5 39.0,31.5 39.4,31.3 39.9,31.5 40.3,31.0 40.7,29.0 41.2,28.0 41.6,29.0 42.0,29.5 42.4,28.7 42.9,27.8 43.3,28.2 43.7,27.9 44.2,28.4 44.6,28.8 45.0,28.2 45.5,28.3 45.9,26.5 46.3,25.8 46.7,26.4 47.2,28.2 47.6,29.0 48.0,28.3 48.5,28.0 48.9,28.2 49.3,28.9 49.8,29.7 50.2,29.7 50.6,29.8 51.1,29.9 51.5,29.1 51.9,29.4 52.3,29.6 52.8,29.9 53.2,30.4 53.6,30.5 54.1,30.1 54.5,30.0 54.9,30.1 55.4,30.7 55.8,30.7 56.2,30.2 56.6,30.9 57.1,31.4 57.5,30.8 57.9,30.2 58.4,29.9 58.8,29.6 59.2,28.9 59.7,29.1 60.1,29.0 60.5,28.9 60.9,28.1 61.4,27.4 61.8,26.8 62.2,27.4 62.7,26.6 63.1,26.0 63.5,26.2 64.0,26.2 64.4,25.3 64.8,25.7 65.3,26.0 65.7,26.3 66.1,26.6 66.5,25.8 67.0,24.9 67.4,23.9 67.8,23.0 68.3,21.9 68.7,23.0 69.1,24.1 69.6,24.0 70.0,24.9 70.4,25.5 70.8,24.5 71.3,23.6 71.7,23.1 72.1,22.1 72.6,21.3 73.0,20.2 73.4,19.8 73.9,20.0 74.3,18.8 74.7,17.5 75.1,18.8 75.6,17.6 76.0,16.3 76.4,17.6 76.9,19.0 77.3,20.2 77.7,21.4 78.2,20.3 78.6,21.1 79.0,20.6 79.5,20.3 79.9,19.1 80.3,17.9 80.7,16.6 81.2,17.5 81.6,18.4 82.0,18.7 82.5,19.8 82.9,19.7 83.3,19.3 83.8,20.2 84.2,20.6 84.6,20.6 85.0,21.3 85.5,20.8 85.9,19.6 86.3,19.6 86.8,20.3 87.2,19.8 87.6,18.8 88.1,18.1 88.5,19.2 88.9,18.0 89.3,16.7 89.8,15.3 90.2,13.9 90.6,12.4 91.1,10.8 91.5,12.4 91.9,13.9 92.4,13.8 92.8,12.3 93.2,10.8 93.6,9.1 94.1,7.4 94.5,6.9 94.9,8.8 95.4,7.1 95.8,5.6 96.2,5.3 96.7,5.1 97.1,3.2 97.5,2.0 98.0,3.3 98.4,5.4 98.8,5.8 99.2,5.9 99.7,6.5 100.1,7.5 100.5,6.5 101.0,6.2 101.4,6.3 101.8,6.1 102.3,6.0 102.7,6.8 103.1,7.7 103.5,7.2 104.0,5.4 104.4,6.2 104.8,7.0 105.3,6.9 105.7,6.6 106.1,8.5 106.6,7.3 107.0,7.0 107.4,6.8 107.8,7.7 108.3,7.0 108.7,5.1 109.1,4.4 109.6,4.1 110.0,5.7", "ret_12_1": 109.0, "ret_6_1": 186.0, "ret_3_1": 56.0, "volatility": 56.2, "traded_daily_cr": 49.0, "watch": "Nothing flagged", "from_12m_high": -8.8, "signal_rank": 20, "data_quality": "Green"}, {"rank": 10, "symbol": "LAURUSLABS", "isin": "INE947Q01028", "qty": 7, "last_close": 2010.7, "amount": 14075.0, "spark_12m": "2.0,29.5 2.4,30.2 2.9,30.1 3.3,30.1 3.7,30.4 4.2,32.0 4.6,31.8 5.0,31.8 5.4,31.0 5.9,31.2 6.3,31.2 6.7,31.2 7.2,31.5 7.6,31.2 8.0,30.9 8.5,31.0 8.9,30.9 9.3,30.9 9.7,31.0 10.2,30.3 10.6,29.8 11.0,29.7 11.5,29.5 11.9,29.7 12.3,29.3 12.8,28.8 13.2,28.8 13.6,28.6 14.0,29.0 14.5,28.4 14.9,28.2 15.3,28.3 15.8,28.3 16.2,27.8 16.6,28.2 17.1,28.1 17.5,27.9 17.9,27.8 18.4,27.3 18.8,27.6 19.2,28.1 19.6,28.1 20.1,28.4 20.5,28.3 20.9,28.4 21.4,28.1 21.8,27.7 22.2,27.0 22.7,27.1 23.1,27.3 23.5,27.4 23.9,27.5 24.4,27.2 24.8,27.7 25.2,27.3 25.7,27.4 26.1,27.3 26.5,27.5 27.0,27.7 27.4,27.8 27.8,27.6 28.2,27.4 28.7,26.7 29.1,26.2 29.5,26.1 30.0,25.7 30.4,25.7 30.8,25.8 31.3,25.5 31.7,25.1 32.1,25.1 32.5,25.2 33.0,25.2 33.4,24.9 33.8,24.6 34.3,25.3 34.7,25.7 35.1,26.7 35.6,26.4 36.0,25.6 36.4,25.9 36.9,26.2 37.3,26.9 37.7,28.1 38.1,27.7 38.6,27.4 39.0,27.8 39.4,27.8 39.9,28.5 40.3,28.7 40.7,29.0 41.2,28.4 41.6,28.3 42.0,28.7 42.4,29.0 42.9,28.2 43.3,28.7 43.7,27.5 44.2,27.3 44.6,27.5 45.0,27.5 45.5,27.5 45.9,26.9 46.3,27.3 46.7,27.3 47.2,27.4 47.6,27.1 48.0,25.9 48.5,25.5 48.9,25.9 49.3,26.2 49.8,27.0 50.2,26.7 50.6,27.2 51.1,27.3 51.5,26.9 51.9,26.8 52.3,26.6 52.8,27.7 53.2,28.8 53.6,28.6 54.1,28.2 54.5,29.2 54.9,28.1 55.4,28.8 55.8,28.0 56.2,27.2 56.6,27.6 57.1,28.0 57.5,26.8 57.9,26.7 58.4,26.4 58.8,26.4 59.2,25.8 59.7,25.7 60.1,25.4 60.5,25.6 60.9,24.9 61.4,24.6 61.8,24.4 62.2,24.6 62.7,25.0 63.1,25.4 63.5,24.6 64.0,25.0 64.4,24.7 64.8,25.6 65.3,25.2 65.7,25.3 66.1,23.7 66.5,23.7 67.0,23.4 67.4,22.7 67.8,22.1 68.3,21.2 68.7,21.1 69.1,20.8 69.6,19.9 70.0,19.7 70.4,19.6 70.8,19.2 71.3,18.8 71.7,19.1 72.1,19.2 72.6,18.9 73.0,18.5 73.4,18.3 73.9,18.8 74.3,18.1 74.7,18.3 75.1,18.0 75.6,17.1 76.0,16.7 76.4,17.7 76.9,17.2 77.3,18.2 77.7,18.1 78.2,18.0 78.6,18.1 79.0,18.4 79.5,18.6 79.9,18.6 80.3,17.5 80.7,16.9 81.2,15.8 81.6,16.5 82.0,16.6 82.5,15.3 82.9,14.9 83.3,15.5 83.8,14.6 84.2,14.3 84.6,14.6 85.0,15.9 85.5,16.1 85.9,15.1 86.3,14.4 86.8,13.9 87.2,13.8 87.6,14.0 88.1,13.9 88.5,14.6 88.9,13.9 89.3,13.0 89.8,13.4 90.2,13.6 90.6,12.8 91.1,10.0 91.5,8.9 91.9,8.3 92.4,8.3 92.8,7.4 93.2,7.6 93.6,6.6 94.1,7.0 94.5,7.1 94.9,6.7 95.4,6.5 95.8,6.4 96.2,6.6 96.7,6.6 97.1,8.2 97.5,7.6 98.0,7.5 98.4,7.8 98.8,7.2 99.2,7.8 99.7,7.8 100.1,6.2 100.5,5.7 101.0,4.6 101.4,4.4 101.8,5.0 102.3,6.3 102.7,6.2 103.1,6.1 103.5,6.8 104.0,5.9 104.4,4.2 104.8,4.4 105.3,4.2 105.7,3.6 106.1,4.7 106.6,5.2 107.0,4.1 107.4,4.0 107.8,2.4 108.3,2.7 108.7,2.0 109.1,2.2 109.6,2.7 110.0,2.6", "ret_12_1": 109.0, "ret_6_1": 94.4, "ret_3_1": 27.2, "volatility": 28.1, "traded_daily_cr": 300.0, "watch": "Nothing flagged", "from_12m_high": -1.1, "signal_rank": 21, "data_quality": "Green"}]}, "prices": {"TDPOWERSYS": {"2026-09-28": {"open": 730.05, "close": 722.0, "src": "yahoo"}}, "AEROFLEX": {"2026-09-28": {"open": 524.25, "close": 513.4, "src": "yahoo"}}, "E2E": {"2026-09-28": {"open": 650.0, "close": 625.9, "src": "yahoo"}}, "LAURUSLABS": {"2026-09-28": {"open": 2000.0, "close": 2010.7, "src": "yahoo"}}, "NIFTY50": {"2026-09-28": {"open": 23064.9, "close": 22780.25, "src": "yahoo"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 02:53", "days": 7, "items": [{"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Gold Rate To Bond Yields \u2014 Five Key Factors For Sensex, Nifty 50 On September 29", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxPX2RZNUVYaGZnM0prSjZkblNWUDAyQkJnS3hOQVFsZVVzWWY3azFvYXFOekJUajR6R0Zla0NHN3NNSlZhbFI0NmhUUW1CaEdCckFrS3gxZGFUZDhVaEdqVzlwaDNIQV9mak</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n"}</t>
+          <t>8tTlNWVlZxU2J2OGUzemk1akNYb2k2MDREZGNNZFJ6UmxQcGQtblVyV2RKRnJ3cl96M0kzdmE5bmU1aktMcG9oZU5nUE52RnhuSGZSbnI1dU5udm9aNVpuQzVVanlZTWVHbHhGNDRDMlllS1F2ejFGcmxuNnhlOHloNE4yUdIB7gFBVV95cUxNYkFxX1BHMHZULVZmS05DY2N4cXJjaWdnX3RsWFFaWnJjTlF0dk1ySEtERGF5bzF1RFM2SjRZYzVlUUQ5LWswYUVvSHoyb3h0dC1jZ0ZZcnhkYXpFMzJvS25LNEk1SzFKTmdGVnN4MDdQN2FMaHhmZFdQVDc1TVZWTXlSSUtRYVlPVzBER004eFpRcFFhZFpXRVM4T0FWZFFVWFZQbjNnRk9tVFFtWVBNY1FEVmNBUzZPdFNJdWVZWGRsdzB2ZnRwZUI3YWdzUTk2Ym9lT2VtcXZFZVF0NUI0bmhKNHNUdzhMZnAzZDZn?oc=5", "source": "NDTV Profit", "published": "2026-09-29 01:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQWDNNbllRRzFSTkxtZmZHNmJ0ZnJPdDhyZFh0LUVuME1CYU9hdkZsR3NubDJXN2NQUXFnUER4RVhud1FsUENqWUhMdGdjT243VGZ1RGZJWGVMV2UwRl9HTTNQSk5wVU11djAzV05oalhsYzRrdG9mUF9ya2Q1ZUc5dFFUaUtNU0RqWExWMXVLSkVFSG9pUGp2VVZjWlJqdE9QbE9hRzIxYWJURXhwYm9faDk1S0Z3X18xd1J1d2duVXExemd6aDJyOEo2OW5RLVFUTWw3ZFFhU21oNGxZRnVfWXRPcjBDNzFUYVVrN0lfRzNoNDJJcktFa2FVR3lOSEVPSl9XN0dLQVNPaGfSAZACQVVfeXFMUEQ4OS1kTDJjTHlCVHp3dEFPZmJNdGxBQWlrdmN4dlhGSm45c1duQTM1WmFGRnRuTmNrRW5FaV9OQnBtc3dmVENWU1QzZG5yRGpyVFRTLTFnTlUySlNfSTFIR0RBSXpkQkhlWjNSZGFKTkFteVliTE1Zdmd4VWpCVkZ3MlQtTWxjZWdKR2VfdEM3ellKWlhua2lIVVZGaHB3bjlYQ0ptaWpmYUtid2dnLU0xdGlnMm9jYXlBSUJ5cV9ZbGZEUEUzMWd1czk4Q3Z3UHFWVWRyb3VxZy1EbnkxVXVmOVdmMVlHaEwteUllVkdCRThlQlc0S0xyblBKa2lUbWtwdzRJSGp0T0RfVE44cG0?oc=5", "source": "Livemint", "published": "2026-09-29 01:19", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks With Earnings Growth Over 17%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-earnings-001032785.html", "source": "Simply Wall St.", "published": "2026-09-29 00:10", "score": 0.888, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3ZwWkRNRjJrZ1RQN0tCaXBfTGZORVVIeFJ2d1FmTkJpZ3RFM2ZUNW52alVyTDVSLXNzN0hRWUE0YUZ1NXBJZWEzbWVuV2NDUFRxNmRmWXVSdnkzZ0MtLV9UMm9FeTVaM2VGckptZWt1Wnhpd2F6TmVjcEpXVEJhNXpKWkVFd0NCelczRTBidmMxam1zVjRfM1J0aDVHaVl5MWtkQ1RvS2xXNm9lMTlraE9IQXBqd9IBuwFBVV95cUxQdU1hSjhhcHpRbXBFRmlSLUVvakR5c3ZwYlpORGl2M1hiaEhqa2dDWTVIdHhmY2NsNkVUWFZKT1c4MHROTG1fbEtCYnZnM0VMOHFEXzB5cFotZEtGNHgyVDR6ZkpwM19JM1JaVmlFMElpSUw0OHRMUXNKVUlvSEswOFdQcXlLLVVZZWpDVlE5bHplYkZoNUp4bUVEV2VhaWFVZzNDN1dpRFVUMUROeGtLQ3VlZFJjUDZ5Rmd3?oc=5", "source": "WION", "published": "2026-09-28 19:51", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQWkFyUEVEYlc5ejlyTldhYVVvYml2c3N0YTlnSm9yZHEyMDNHUnNKVnRNeGl5NTZ0NkRpZFJJWURHUjdEczROQVpseThQbmlJdGRLa0R2X0Vid1VKM3FncW43TkVIU0hpVE5QY29VMklwNDRQa0FXNHpoRXhWSC1kaFQyVUtzc2RZYk9BMWhpTU5XTHZ4RHRMMU81azFLVFF4THZkTjJ6ZUl5NDNLcWFibmtqOUhjeEJYQW0zY24zT0lhZnMwZElXQXpB0gHPAUFVX3lxTE9jTkdQUlc5aXV2N0dtX0UzYWlfV2ZUSEhCUGp2OHFENzhsWnJQODNmemptdW9oQ2s3Si01ZnV0N3RlazVRS3YxZWJsNDZWZEx1MXdMcFFzZy11MnItN1pWQTdYS284QWJwd2hQZXdxdDc2VkR6emZGZFdsX1pDM1d2Rk1Ka25SVTRXcnAzT3dqekpRQnBKUXBwMGpHZjlQMXBtUi1pUEJac0RYSW9LcnBTUFkwbXoyQ2tDUkN4bEs5UGpoR3NBaldjekJVMFJ4MA?oc=5", "source": "Business Standard", "published": "2026-09-28 17:36", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr", "link": "https://news.google.com/rss/articles/CBMinAJBVV95cUxOOFgyakNMWTlmbmpOdjRVeTdlckZXNks0dmhfc21YME9FaUcxWjRFUG1XdTQwblI3MS1oUFN5eThST252YWpSdkhXbWZQY1V0ZWdVTGI5c2VXNXdFbzI3aUozMDh4RVMxLUxnb0tLX1NYU09yRGxGMWlvaDFlRzQyNkd2eUsxZ1lBTVNnMWI0VkMwejI1a0pWcm91NXFJSUVDZ1VhQ2JESWo2cnpDSHNHbGlhY19Za0pNQ0E3V045bjJMR09ueDZIdkNVUGthN3lRak53QWpiN1B0WkpRb3dRUTNaX1RYVXp0LUMyZG1EUWZPZlNXUGQ0WldOLWF6MFhQalU3YzA4WUttM0x6al9xS0xSVHdOajJJa2lacNIBogJBVV95cUxPanhKS0R3c2ZjbHJ5RlhHMmxmQUVLSFlUTEtBcWFTbS11YlNxdzZqNDVRSHBISmZfblhRcnhPbXVwN0NkclB6ZHNLYUk4bTZQU0x3YUs3NXdrUVE4RzJzY0VQVjZfazRmSmtudW9lNGtqcU1aMU5lMUVVS21lWm5pa2NxWlZxLTEwN0FlNGVJVS1lTzVvV1B6R0lsZGtDOUViTEFycFdFb3FmSm1KTjJZS3dEV3FUMEc4T0FVQXdBTFlCdk9sUlRyMDA5WHA0dmo2Q2lYcTFGTTJqYkI2R1JDLXZkbEdpYTBDU0NWZE1tTmd5SkFBNWxTM24yOERhN0x0SWkwY2RzZmZkRnFqNUJjdER2cFpqYmNBYVNfT2otZks5QQ?oc=5", "source": "The Times of India", "published": "2026-09-28 13:42", "score": -0.896, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNUkhaTEo2TVV5Q3h0cjBXLWVGX3EwakNwOXJxS1dmT0Fnc2p1eXByY2d4cFlIbE1HTER1QXFqWTB0bHNLR0lfWTdWT2RTTnJKRjYwLVhPU2t1dEdVMk5NMFZfemk3TFNhdk5GWDJGRVZUdV82aHJETlJWS051R0N6bU9pSktUWjR6SXY0d3g2ejhjeFRpdkszSFJzaw?oc=5", "source": "Equitymaster", "published": "2026-09-28 13:25", "score": 0.652, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxQeEMyTGpqalIydEJBcFVFWC12WDdUZVYwbkJPVk1RTGRrWlpwTnlnMWJPMk9TM21CWWxfWkpIRU1QRWNCcVcya2JHbEFRLUZLa0Vwb29SOWt0Q01nbmRfZUhrcDd1M0hsb1pHWWViTnRUNkNYek9KZDVEcUlnemU0SEozeGo0dDQxV3BJSkRlS3JQZU91YWEtUHBERUt1cWZ0T2VZY01yVVlWRlNUR3FpWlJNeFFHYlhiekdoa2htZzlJeWw3b3BhaXFnRy0?oc=5", "source": "hrtoday.in", "published": "2026-09-28 13:16", "score": 0.361, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOZGFILWIzX0lTNkh0Rm8zMGVUTWxEVGdYN1FXR2JPUTJDeVhiNHdwaVdGM0xCOHdUYTQ4MmZqLUtVTXk5NU5va01tSzN0b0lJWjFMcmY3M0N3OEhaa1NYLUF1WkxLUk8zaGZZT1RzYzd3MWpMQjFmdTgtYm5fWG5Xb3VWenYtZEVWQTJsZDd6elFSTWd2RWtMeURUdTgzTFgxSExQSW1rMFJLVkpnVG5TSGx3YUhtM01oUHpvRWNERDEwTmw3RzN1d0M3SlZ3dThNbEVnNnBtVmJXMGgyaWI0NVUzeFJ3LWFocVNyVnBqM1BxeEdlZXVQeUJZdXRKdWwxM2hDU9IBigJBVV95cUxQUWpCNDFiSU9RRGF5Rm5PYU9FZGp3c2JWVFRVSzFWTHdrdDZUczkxMVBnLV8yN0hmQkdhbXhYM3dLeHViT0Fjd0o1MkFpT2h4d0tkR2JjS29ZZWs3T25DRV95dDVtNWlFQ2ZkbGZ1WVgxRU43aEZBZEZjLVNnZ0JnZHd4TkJUbUVMaHdEUTZERnFvQ25RT3V5MmxrRk5UaG1oQWoyTUtPMG9oaktqczhZel9nTUN0eEpfRkdxWGZHRTNHUnVRQVlUdENBVFctUnRRS3lMRFBWMVk4Y1JhVFFHMGNMWDNrNjhiclVOOThFa1JrTkxZWjB6U09fRGRZLVhrbGx1OE9MZHFMUQ?oc=5", "source": "Livemint", "published": "2026-09-28 11:48", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPX21IU01KT20tUWlfRy1IMWJ2LVBfSXBlOFdWYUZid1ZJdDRncFozNEtSb3NRdnlUTUlOTHFBNkloNjROR2daRV9EQlRObWhYYm1uYkl1dGdDck5yRXM5b1pzU3podGhMc1UybjV6SGNnd2J0dW9xWjRaLWVMWjBLYXlqN2NCRk1fSndYX3lBUU9LUGRBMlg0VnBfYWtJcHhaZlYwVTBxMHBhMWtXY3NhRko4UmUyVDZOUUFVRWN1OWs5RUhyOGxzV0VMWl9sUG11RjdudmdVNHp5M0hFQ3N1aUpoN19LZ19vVmo1MGVBQQ?oc=5", "source": "Equitymaster", "published": "2026-09-28 10:56", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Falls 1,124 Points, Nifty Slips Below 22,800", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkNsYXBaNkxVbEJONXRoU2VUMDhmLVp5MjJ4bm9KZXJpWWp2TV9WQWhkYndIOWJOM3AxbHljM0Z4amc2NmVKS0p1SFk2REJiUVdxT3JEcG9tQ0VPMEJSa0kxNUlOS2dGTHFVN1M0T3JxbThwSkFVMHE2NzVYck1FUDR1bmM2bE1UbGJaZVFmR3hCVDJTbERmTzFnMVBoUlg3dmRkdno3b2lmZTVGNGhQbm9YOGl6SDlBSkt4M1ZoaUlsTkVf?oc=5", "source": "hdfcsky.com", "published": "2026-09-28 10:46", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPUU44cXhTejNjWEFmX3pOMEQ5YkhwR20yQUs4NGxnNks0d09rWnU2R2pxMWdmOGQ4N2s4Nm41WW9OR1lRRzU5X240Nnp4Zm44NFJ0b1N6a052VjJpXzlmR1VIXzlobHd2OVVJYnV4Q1BfMHNZUmZ0eWNqWUNqMzNGelN0Y3o5ZXRxY3hzby05M094NmZ4aWxpakRnZlZWYlRQMnhvVGRJcGlleVFpMHlNS0VRZllGQTktc1ZUWXM3MldYVkd3THVpOUh1TVVJVDJqd2tiU1N0al9oblNQajFGUDN6RlV6UGRQU2poMTV5dDRtTEVnZ2p4bzFITjQ4SVRoNVV5Z2dZbTFyUDDSAZACQVVfeXFMTl9adnRITUZ1VzVQX29ZOGpxVXpOZ24wcFluN2JGVjFsT056LU10RmMyQ3RnM3pkQlQzSV96TXZVT1ZWdmFNU1VSZmhpMWlCaWNtejhpNWwyZ05CM3c5NjJ0VnE3MUl5R19XWXphSU50eWRpd2RZemRtMzcyZTJMcWpOUUJEZ1BwZGdyXzl6ZW9MbkRoOXZjYWw2X0tURlRyTk13ajNhUXRBbWJpaFhQd2lUd1doVXRMU0VRQVRBTU1rM0xxMFN2alRHRWlWZ3pUUzd5dGJwQTJpdUlDUjJLMjBHNVVOVTJtMFFhdVlJb2dONjJjNzU1Y0p1ZE5Cbk9XcFFRT3ZYNHZaVFY1V1lIVjE?oc=5", "source": "Livemint", "published": "2026-09-28 10:15", "score": 0.402, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks shareholders approve fund raise and borrowing powers", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxNR1MxLTBoYmdoaG5EZlRjaXpBaS1ZNmkwbjBPV29xOUNGMlFQTjdFdG5ZS0JTRExGcm1XWTJCWERCMG9SRm5FcFBwSUZuVkZ1clJ3RDdRQWQxMENXTDA4UzdRUVBZeTJNN1RIZ281SG1sYkJ1TGZZeFBpN2FIRS1ieDJPcVNXY3ZuS3VHYTgyM1VuTzMyaFZkSTAwSzhrZWI2Mm1iVHlkOUlJelFUVnM4N0I3aVFwR3hvOHc?oc=5", "source": "scanx.trade", "published": "2026-09-28 10:06", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVkFmQXdEZjZITFVKV1BEOHlKXy1rajlNZ3NuN3N6UXdZa2lWWVFxNnhXOTJtYmZxOVpOcVVpLWE3VUhwZUhjVXBYV2VleEVpbVR4RTRsc05tTFBIcXNoME5VaVlJVFR2ZUx0Mmx6RXlHTFhKUUdFU1J2OUhXNERPU2xsa0FGTGFOcjJzQ0ZlQkIwY204X1Z3UUZTMEt6NDZRVDJMbUQzclRobkxrcFpWbGJTQXJnRFR0ZHBMdURjQjgxZw?oc=5", "source": "Kalkine India", "published": "2026-09-28 08:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Nifty, Sensex: History favours stock market comeback in October; stocks to watch", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZE5UeURMRWtrOUFNekVkT0ZOcFI1SkE4Q28tZDc1NkJvbmFaakNlQlBDWkt4RDd6b3FpazN4NjRzWGhMN0RaYXY0U05IVEY3bU1lN3RFaURJSjRUTnF5Y3o3LW1wT3RtSkx5LW5yaWpiemJ2Ym1lYjdtTmpKY2lPWk04aVhiR25wMVl5ME9HSmUtQ3RIaENZTC1pOHpOekZVUVNSSWlFaXl0N2NrS19MeVpJdUxLeEl2blBYSjNseU41V2NjTUxmeklyeTN2Y1B2eWNuQWFTS0FVX2hJNWfSAeMBQVVfeXFMUDhHbWlIakswUl8zYmdMcHhmcVlGQ1V4RkdsdHhqN19JMjZwT0dxMGtVeHBQX2gxZk8yVlFwamlzblJNbUZJZU84N0RRTWk0U1VJRmc4VUZyV2p5NnJLNjRYcExKb3NKWjg2NmlMbUhRVFNDZHdocnNsMl9RVTF3YjBkYzMzaTRqdFAzbE9jX2NKWlZWb3FGOEFPMkktYURRbUZLYTR3SUVTWG84cXo3TzItZGhlOTBoNFhfRTlXSnNfOHJPNVctVEFEcW5WSzg1bHNHR1c4MUoyODVYWnJqV3U2U3c?oc=5", "source": "Business Today", "published": "2026-09-28 08:15", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher", "link": "https://news.google.com/rss/articles/CBMiowFBVV95cUxOci1kRlliVGdLVkdiMUM4b1lqbEFvLUdDV0VITWp3NGlyb2w5N1Rmc2pZUi11cVhmNkxDUlkwZThkS1hOZ0lFaXdmYXJoa3FiT3hfeHhaNkFwdEg2b0V6NHZaZ094cG9RZGQxLTMySlZLX1J6SGRXcU1Sb2RuTng0RzFzc1lZMWNHNjY4b29HdWpzOFRWclh4S1JGUjlGelRRSzlv0gGjAUFVX3lxTE5yLWRGWWJUZ0tWR2IxQzhvWWpsQW8tR0NXRUhNanc0aXJvbDk3VGZzallSLXVxWGY2TENSWTBlOGRLWE5nSUVpd2ZhcmhrcWJPeF94eFo2QXB0SDZvRXo0dlpnT3hwb1FkZDEtMzJKVktfUnpIZFdxTVJvZG5OeDRHMXNzWVkxY0c2Njhvb0d1anM4VFZyWHhLUkZSOUZ6VFFLOW8?oc=5", "source": "Free Press Kashmir", "published": "2026-09-28 08:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHU1a2VYbkdKb1k1RENtVm56MHlVeE9EcW1DQWd4ZmRyY0g2b2JqZjkxVENveE5US2JvaWtoanpITFc5NzVFS3hzMWRxcmtPUFJ2a1NBX2xsVDJUWEZrekpKNWVLZzZ6TlRQUnVoVWZWTzZ3Q3VBWTM0WkxqRzVhM0FzWm5kNmtCa3JMUDRENUwyVU1iZDBNd1BMRkpWenlNUHpLTDFScU1rcW0zcnNBM3pWODVoMHV1WlhwNmVSSllWTHVWOW5hRE9B0gHPAUFVX3lxTE00UXRvMWNWTlhGMWphc2xibF9MLUtJQnFQRjR3UG5nbVh4M0NWMVg2MzdockRzaEdnWlpTcEtyM3dGWnRTbnFRQnRKV1JmZk9RdWY2UnpYY1VsWjRBSDVwTk10clJnNHlCSEs0a2g2TFA1alQyYUFWNXIzWDNfeXlOejBhVGJrQTJZRG13cG5XVEdVWExyM2Yyb1owX2pmUDNTWEZsenBGcUlYdWpWZ2NpSXh1dmt4blhQYUptLWFNNnBndk04NXhzdVc2ODNNVQ?oc=5", "source": "ETV Bharat", "published": "2026-09-28 07:56", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxQVWNmQ2tBRmd0NTdUbmZ2YW9kZW1wdDZrMXU4Y0gtTXZPYU9uc3JGRGJXQnhBaEY2YXk2TGhCWlhqZGU5OWs1eDlPOTJMcHp3ek5GUEYtcGQtYUdUVmpTZzVNZGlnS2UxVXhHZE9DcTYxSk9uWkFmaThOdUdzbnpmanpXUF9sSVVReXFLY29VeTg5QUZPNkszSmNGQQ?oc=5", "source": "apacnewsnetwork.com", "published": "2026-09-28 07:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxONU5xeDQyaGZ0M2JBemJwU0REcWJxYkZWN1hxM2d1VHZBOGh2X3gwR3plbk90RlZMLWtWZV9jek1KR2lsTDB4d09oQlJzRTNadHgyUEY4bHhFbGp6eVhOWDhqLUtQWkpIUldLLU1EbUoyU1VfYmNaOVdqWnJzREo0Mjh3bU5wTTZPN081MmVFY0liRzQzVEtZRWFVMURCaTJZX0twZzRZWVJHVV9KaEl2LUNFZzBpdmt0RFM1OXZoLXVKQmt3WmlDSGR6VHZFMWdiV2dWcklYVWxuTXdFbXc?oc=5", "source": "Upstox", "published": "2026-09-28 07:36", "score": -0.806, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxOMzZwenBCS1ZIMUJRRXVOZTBBME0xU0N0WGJsVEVfQkVhZ1NtMEplNUNXM1A0WGRZLUVOZWlTNi10QUVQQnJRSnZDZTh0SXVlQkN5eDZ3ZWstRVQ2TlctUE82ZmxJRG1BZkw1NjZGZGYyZWJiZlZ1YktSZU5OTk5MZ1A0Q2NyV0wzZEd6c3dHaUwxcUpZa3ZBQ0g0dGViQzhfTFF4RExTb2p4azg0WjhlVTBlSUZtSG80clVYa2p2MFBuZWIwVURXMGd5dG9wVE5sWUNLbGJCb1U5SjNBcHNXZnE2dGNkUlVhVUlrNndWVTVpOG1jWVZYeFppQUdRekXSAYQCQVVfeXFMTWsza1RTaVB1QndYVDNrWE1GWUo0QkJCd09tUGxGUkx2T3pVamh4d1VTUG9FYkxpUmpRV0RlaDhxeXVMMFN1Vk9sMVRIY2xaUjNXRlhYLWN0SXFuT2V4UktnYlRvVnZzUlFQbkJFZlNsMnBCR1JZeTVvRzVUa1duQm5hb2llbUlPNmZuQ2owWUFPbDRJWUV1ZHVoZWd2ODJMUFo1V3g5RzNfRnZ4MldzV0F3UGJfV3UzZ0lxWjdIS0hfZ2JXeXh5VFVtTm1JVnNtX0d2bjAySWZZU25TZGhiUjhkVERUenU0T1VJTld2WGM4QmVOckxtMk5QcThMbnR6bjg1cGs?oc=5", "source": "CNBC TV18", "published": "2026-09-28 07:06", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxPUkRFSHF1dXJEMUtBZUdNc0FqX0g2TjZqMV9MSFRVSXdDSHRobkFERnFiamUtMDVVcks2NDVkS3JYVzNYR0dCMnFlVDVobmpEWlduX2tCODBQMThWMm96RW1BTUlHbVlxbVMwNkpuWVphWFZJS1pTUHdwYWFJbEM2ZzNZTWhYS2luLWhYR1htelNSS3E1OHpXaV85Rm5iQWVIcHFnNkpiYzFFTHB5eXktdEplbUk3czJwV2dadzlBR3MtQmtlNnl3VDBhOGc1VGs1eENMWU54STdnREtoc2NOeGpJWXMxSnp1VGEtUVJWS2c3YWPSAfsBQVVfeXFMUFBfZ0J3ZVlJNGVQMHhXZTNvaU1wUzh3dHYzOU1sS3pFX2RIS01fSmpIMDRLOExqVmxMemRwRTZjbmxNcFRHbTlScFhKUHh4TXJzSTJyR0g1cVNwRmd3WDVWck1iaDB0b3FsVzNpYy1TZUU3RExUZjdfcl9ZTms2a2VnZUQ5NW11VEdGbFU1VmEwUjRPaGNHS01sVDVTMDNpVUltUFFUc2NKRDV6bmVyZWRMcDNXTzE0cEZLc3lNVDlpTmZMd2ttaVg0Ylo2d3BYY3BJa3dUcFM5UU9yLVpHSU16MXVUOUZ1dUhmSTdjVTRfTDZGZWUwd05zQjg?oc=5", "source": "NDTV Profit", "published": "2026-09-28 06:47", "score": -0.791, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: decline, valuation and peers", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE43Z0JKcUo3bkM2R2FfLWQ5TXNkQ2dpMnNldEZ1UHU3THMyeUkyTkc4TmN5V3NEUjFiNGVEQlBWd1pwQk5lZk54YWIyX0F3ZGNWQWJJc1NGY25WakxxMjQ3VWFfRHZhN291N1F6Wnd4YW55TjQ0eXJ5bXNuMA?oc=5", "source": "Univest", "published": "2026-09-28 05:52", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxOZFhpNERkTkx4Z2RRS1k2ejBhN1IyTzR6a2g5MjJ3bkNjeDZlOWRBSmlIek1xQk1GcVIweUZvcVFEcGwwSW90RThvU0J6cng2YVpLV0tZU1dQQlhGZUtieFVuZ3BmWXY5aFFkSlRuR2p2ZW8wZF9TQmZ2RnJoNFV2Q1lMT2JGMkxLUlp3OF81dlkyWHVmQ0xyNVg5R29GVXZkR1NLUkRqTzF2ZXA1cmtlcEptcmJNR3dwRi1R?oc=5", "source": "India Infoline", "published": "2026-09-28 05:42", "score": 0.103, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUdIB8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUQ?oc=5", "source": "simplywall.st", "published": "2026-09-28 05:37", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r", "link": "https://news.google.com/rss/articles/CBMiwgJBVV95cUxPQ3drbk9QbWRHcU9uVDJLU0EydWpPdVZRVE1rTEE5bFZadHZmUVJPeG9nUjVYWnVvSTkzNzFyNFo3TWhfN1lzX0ZScEVrSnZETUJ2MmtDaE1XYjc2TXo2a1p0UWZhcHprU1lwM3V3YUNUVzlTc3l4UXdCLVExX3dLQTdRaGh5Rk0xUDQtR2lkY3Mxd29QSHNPRU5fRDFYRVBSbC03X2pFaGpnWlJ6MFZDUGlicHlPUUpXeDh4ZU94UWR5ZHNCZ0pydDdFdHZNSjgyRThId0JfSlcxVzFibmR3clVwQzllekZnLUJ1LTdZcHpsRkt1YzN0b1FBT2FkZF9zblJkRlIxdmZfdzNFSXllSDM3b19zME9xaXhlWGk0Qjd5TWwxdDJaenFsOE5iOUNOU2VKRkxYazExZVAxYWJuVVVn0gHHAkFVX3lxTE1EMGdQdWlWbVp5aUpTbEJmb0M5dWQ5X0xJYmNpTFJJVERpUDZkcVo5V1ZGeTNyR3VmYjUyUDF0bG1HVlBGQ21nNDBfU1RZRTdYTEZFTy11OXExZmNOdzRwQTFQNlBRcFZ6NVdDSFFkeWdkV1ZGdm14cXpoTTc5eFc2WkZnVTQ1SlZ3NmxCOWk1b1BWU3doODZadUV0c0tkQ0VCeERINlczUmlYWmJ2MjNoblhPeWtqa0NvU3ZRcGw4NlQ3Mk5GcTFlZDIzQlN4SWxiNE5Md0ctQVBmMklselFGekszWTlFM2JFN244eVJtOHctcnFCc0RVM0Z4OUlqVmctZ25xTDVnTTV4djlfc2U3T2pkeC0tajA2ZnVKRDk3eEJ2ZkNWSmZicmVEOXN0UHpfRkJQdlZMLTVveENMYmdJenM0UFRfRQ?oc=5", "source": "The Times of India", "published": "2026-09-28 05:18", "score": -0.691, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeDRfUkctTnR5c0x3dEhXcmFSWWREQnhLUGMxbmFRT0RpWW1CbkVpN3dkcjJTSUZOd0ZpTjF2M3U5OW1vOEdHS3BKZG03d3BhenZtX21jTEh6VVc4ZC1oazJmSGJCZTBQTVZObmVYeEJFT2ZuaVd4OF9rbWNyUGo1T1ZMZFFtY1Zpd2dSYV94Yk5uS3FRVWFueWpYaTNyVjJVdnVoRzVFaGhvc1pOcmJOb1BWN2I1VXBTTnNNWURYZ18tRXFkZHR3Mks2TEk4X1lMb19NbVU1am5jd9IB4AFBVV95cUxNbVVHcVRveFpQaExzeVVnLXV2bTRTY0dTaTNSWDhoWEdCVkRCZjdZY0I2TElNdWxlb2RYVThZcXFFM1VDQVRxbmRETlVSTGJjX1R0MWpCQTFId3Iwb0hjUXF4bHhoNjNhZlBoeFptZHVHRWdwYTIxd0N4dmZtNHNFRXhvc0h4TVFXNl9ELUhkQ1VXS2FjV19NWWZpeGJTZmc4R0VWZldxNWVlOWlzVGRHX3cwaUd4UjVuMmlDVjlVelA5Umt3dVkwTDlhOEFSWGY5V1k0anMwOFNGbU5ZNmtZUg?oc=5", "source": "The Hindu", "published": "2026-09-28 05:11", "score": -0.852, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQeTNsTy1qVmtORm03dkJ0LVQwRUVQU3ZnT0RqMEI4NG5kVUxYeU0wcmp2N1hqaFVPdXhHNDV6cGRuZUcwclFTZ2NUV1NjdzQwYlhwWEMtcmFIVXZpMWxhWnpzOUFwaF9QUTVPQXVnTmZlUVVHNlNZQTVUOWxjdHZ6UHJuVDVtZkpPVWJqd1hlLXNlUVBEMmNuUFRCUFZZb25KNGpaNmJ4RjRuRDh5ZWFvS1JheXpLSzVQWkNSODVvaHh5ZUgyWjFPTTRnYlpxbUluek0xZHdaVU91cVRrYzFHWVJfRlJVemI0RW42Q19KSdIB9AFBVV95cUxPRWZEblJNRmlJNmdQMUpNa2FMYzNDRGZrTlp2RFh5MnZvSW5HMDhlVmNPODRlRkJTYkIySVFBWGZQLVh3Y1QzWXhValo3RkpjX0pidkhKQjJaTGFGOXhsZzBfeHBadVhGcjZKZXpuSkF1ZFB4RzVwVDIyeEtqamhHX09HR2FtY3ZRcGM3bzg5X25sU01NeW85LWQ0SG9pYjMzS2VfU0pncEJLc2QweG5wbFdZbEpDU3hvenI3V1BUU2FPclVvZGNCU1NEb0ZsZU9GdmQ3Smd6ZTZ3WTJtY3BTOElrdURuLVVsZFo3ZTVLalFBY0lD?oc=5", "source": "Hindustan Times", "published": "2026-09-28 04:45", "score": -0.361, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE stock slips below issue price of \u20b91,785; down 2% on Monday", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQSTM2eERXZ0NPUHpTR185VFYyNzFaR0lYZlMzeHB0Y2dGMjM4RlhXdWtnczBEblZtV2F3YVItUUpYbmhGTWI0YVpSdVlRejFmZUdyWmhLRUYzNFVCNkhsdWZoMlpTenVZSDBkVXNpY0Jwam9pTmtocUJhdzA1X1dyWTVJVWhVdzJZRWpiNzVFRzd1NUREdzd3bW1vQm4ydkVETWthRE1WVGpqUkZoSVZYbmtqdVNuWnhnM2ZaaHhORjRReXM50gHKAUFVX3lxTE9fUlRRS204UnpsenJGSWtxSnJiR19Dcmh2LXFMVWhQSzdDamQ4QlBSanluUDdfYUY5YkpXcURFZUZ3TU1TQVM1WFM3QnhoLWd0VFBXckt2R25razdOMEFvc0F1emhYVzIwZkY3OXc3Z2xJblJfTXo4SFZyekdPZDlHTDc5Ykp5VVlpaU9MblVhUlBhcW9Ta3h6SWpIeFZGOGs0bWh6NmNWT09yN3pjc0pzdXdqYlBjN25UajdLT3VvZEdNRlhxazh5ZWc?oc=5", "source": "Business Standard", "published": "2026-09-28 04:42", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOXdSQ1g3eFlqb0loV211WW1MSkhiWVlTNzBWd0M2a0ZFQUduVlI2bXk2eDBmYnBIZWlFeDRrbTh4TnNsM0hBSllPZTBHOTU2ZVZaQXhZOUFDczM2ZU1wdkZteFEyTXA1SFhGR1F5dGpDY3JGd0JyOEpnZEdmdWUzd3Fwczg0SzJyQ2tWaWxNSEJYSU5kdHpJbzlYQlAwWnd6bzBGaGpIS3Z3V3hlaVBWOU55X2Fyb3FLUE9DQ1pQcVlka1HSAcsBQVVfeXFMUGxERGozWEJnZFBKVXdKSTNKNUV1N2V0ODJPUEljV281NkFXYlpnWmtINFFlaUtfUDZwcUg5RHc5VlpRT3p3TlhzOHFKNkNIVXpfZi1SbXlTQV8xa25LU2FpTXJxNkRVNDJhQVRkWVFFaXFxQW1FcWVqUE1waDJKZDI1WDMtd05IQTlzdE9xNFFpdVRIRmJ3WGR5aS1Wb1Y5WWpMUTZmcWtqdnU1YnNPTUpTOHlvcmlPMkE0Ylp4Ql9idDVGcUxTZHRibnM?oc=5", "source": "NDTV", "published": "2026-09-28 04:41", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxQQl9VUVpCdDlvWEZ4OXE5V1pabEo4U0RPcVlBRXJuMVBQMzlWQ3Jidkxzc2drSUZPcEhOdG1jRmpqRXE3TDVIdEY5T3hCVXV4Ung2X19yRU1OcE8xUU1FZUwzR3ZTOVBCYWNvc1p1U0x3WF9kazVjV3h5Tk9PbElFSzN1V25BN0xDcU83cGZ1QVRTN2kwZWxjZW9VeFFZZTctcG5PWDdhbERNdzI4ZlZlLWJLYVdxUHZOQUJDWUc0MkbSAcABQVVfeXFMUEJfVVFaQnQ5b1hGeDlxOVdaWmxKOFNET3FZQUVybjFQUDM5VkNyYnZMc3Nna0lGT3BITnRtY0ZqakVxN0w1SHRGOU94QlV1eFJ4Nl9fckVNTnBPMVFNRWVMM0d2UzlQQmFjb3NadVNMd1hfZGs1Y1d4eU5PT2xJRUszdVduQTdMQ3FPN3BmdUFUUzdpMGVsY2VvVXhRWWU3LXBuT1g3YWxETXcyOGZWZS1iS2FXcVB2TkFCQ1lHNDJG?oc=5", "source": "newsdrum.in", "published": "2026-09-28 04:29", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb2JZRzNjNjBpV29mRkZobTRsNWJaVExQeWMxZmw0WjYzZnhCNktBQm5Hdmw0U3NrVGlrYm9abFZwRlZvendEZldPMlNlVGtqVFZ0ZC1rclZGci1yb3BjbVJ1YUlta1VYM3pBMl9kbXh1VjA4ZmtURl85S0Z4OTR0cDFyWXdkU1FiZ1JVdEZ4eVBPSUtJMk9RMnFJQUpxdjRiNmNHQzdmbnRwbGNjZUFJZkVXYV9yc3p3SlF2TDFkWk8tT3hnNkZPc1JTb3c1dkZ0MS12S09LWE9vaWV0SUhOOVpGUmRrZkJxbW9XQdIB8gFBVV95cUxNVVJKdDl3emc1ZEJXb2ROY3hadnZaaXlhZEtTZmZ1RjZFNFE1VVdJTnNxVFJFRWRlaTZaUGl3ckg2dzRfY2ZXTWxvS0dWVV9ibktOOGlsWjVmVDQ4YUN3aVlLaXA1anJ6YmdNRUM4UzRrZTJxWkE5UERZbmZJR2ZHQ3phMlg2bldoWDhBT2U4bVY4SnF2c1JiQkVHdXVVSGMwTVFJVG1GckhxdURSdkpMdUpfSUNQOWo5VjNxS3FEeGRNVzZiX0UzUVozR3JXMHduVzF0S2xnMVdhYVFaNEJmOHZvZGhfbkNmY2lMYlU2Y19wdw?oc=5", "source": "Livemint", "published": "2026-09-28 04:25", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?", "link": "https://news.google.com/rss/articles/CBMi7gFBVV95cUxNNDl1aHc2VHYtR3lHdGJnY2oxdXpXX0tNN29FU0dnYnZTX1hrRWFzOFBzSk5KTWc1RTFJOFdmT3VVMEFmOXNDcXhKbHdBMVUtR0kzclhZVDRLSDRHcnljSTF6UG40ak5SQmMtN2lzRG9QSkRNUzFidmRkSnc2aHRLanVnTURTNU9DcUZXU21kWVhoVUlacHhSa2lYT2tPMUJ6NUxkWjJ1V0xpYndCQU11S2djSjZ4aXpHdHpXRTZpRDlnZFZNNk9PU1hycldaa2w5Ylg1Ull2SXU2SlIwbDVrdG1RZUJaN1JpVjRUT0Jn0gHzAUFVX3lxTFBtcU5GS1BLNVRSQ1BWekxLUmhQaFFhMlZLV3RIcjk3M0RBVkpwU19mcmNLZ3I3UXQxdFY0WHBIMmw3SUtkeTdwN1RFa3RfbzB6bkNGSzJwZWtZN2dDS3E0a04zZEFid2pXVm9xejFDbUpLeG9hWGlfQ2p4NWZtakVWUmxLMEdteDBkVFFLLTlGWHVid2ZNYmh1cHdsS2R6UjFFUzlQNXdUX3VqSlRKY014bU1mcGlxZ2VGbGtxZWlDbHRZTnVZcm55NE5zaE1ra0lUVjlTNTZaQjhQbEJLOV9yWkxSSWwxZ2FacHBnaV85SzhfWQ?oc=5", "source": "India Today", "published": "2026-09-28 04:17", "score": -0.511, "label": "Negative"}, {"symbol": "MARKET", "title": "Mkt crash wipes off \u20b97.4 trn; Sensex down 1,180 pts intraday: 5 key factors", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNFNEZXdXeWxyUDZNNkJvYmhvM29nZ05JbUhkLWRmZ2VWME9TMFQyTWctZjhoeWVNQ3dGZ21NcmV2THVjUmt1TTBwTWNJTmVnRFVzVXlCekNMZnBqUDY5M3RWSWpQeVBYTXl4Zm1ndjhBcmZUV2ZVdHQ3VUFxQzN5c3NON3N3Zjh3UjZYSjR2VER1OXBWMkZOUExnTHF6OVBtTWxCM09ZVHhmdW9DZDZ2U2FxVEtGVHhIVlNsLWhkcnByMmdVaGl1OTFwQW5GZnZ1OVJvM9IB2gFBVV95cUxNWUItS2dqMFByNUlUcXdPMUdQSHZxX3VTYU1PcEdaWnFaOUo1MnhrQWQ4MTBmaWM2eDY5WURsaFpId1RnLVFJRTdadERxTDVKc0J0UkkwRDM4V0g2WDMtclZ4eEtxY3NCVTV5SV9tQnhEZUR2aHJ4N1Q3VzFLbF9Rb1ZadHN5Vk9tOEE3THlxQVViN0tfZnB1bl9aQU0xRjFZc1dqS3RKVWpLUVM3UkV4aUYzOVNaMDlBbEM3bS0ydnltemJ4TEFOZWt4OHNOcnNNdG5DaE5GVVRHUQ?oc=5", "source": "Business Standard", "published": "2026-09-28 04:11", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l", "link": "https://news.google.com/rss/articles/CBMilgJBVV95cUxQZi1NX0ZnR1pnWl9lLURWQW9uazJudU5adU43UVVWdG9BV1A5WTZaN2RPZ3NSWHl5bTlCZlA4ODkzcDRoc3JWVEtyRk1NbGx4MDQ5X3NGZ2ZHVW9MWnFTV0F4U3ZSWVA5S3BtbzdtZFRLT2JVOXJjZjUtNENidWtZai1JaTJPc0VQVE9mdDE2VGhBNXByZnZ3ZEtVdm5ZRkFvUXd4UGdfZjJTcFFRcHkwcmo3d0p0Vy0yZXNkV3RXV3ZFcTRLTlBUNGRrNXNGMGVpUXFKMDJzUndJWXpqWnpGSkFIRVJ4Q0MzQUJVOHMwT0Z6X3R3aHZ0YzU3TmN1RDZVQmNzWWNZbkF1YVJ3YlV2Tndac1N3Z9IBmwJBVV95cUxQcExWMGJPZG5EOW5QWXdrOGFGVWpSNnA2bjNYYnlRbGdhSG13ei1YYXExbjZPZlkweGtvRDJ4QmtZcFNJbmthU2xJNWxnV3hVYjh4SDRzU2k1cTQwcG9BS0VCOTlQcUpuS3FzREFhbXRIWVVYQVZRZEdHSE9HUVRWYTAtUFFWX2M1RmZXVXhKUzd5RmtuWjBhTi1wSXZfVXBWWHRCOTV3VGFRQ1NKeXQ1WU54dlBQZmpteFlFa3JrYlRkYnRoUWJsMVJZM1RlMnFWVVZGRmNUWExEUzZJUHRCcGpmMl8xU0Y3QmRBMTdESW85NTA3LVRGODFGakpiY2lIUlV2bVJLMWhaUVNqRl9HMmhsSEU0VFNGa3lR?oc=5", "source": "economictimes.com", "published": "2026-09-28 04:08", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi-gFBVV95cUxNd3FFLUl4RkRuRktMczNpNmU5VmotaWdaUENGMWExNHZJOERsVFNMQ2ZiX0tDSGFXYXhxSjVUM2p4QWUzZThrTkxDNXR6ZndFMXU2NEFTNG90Wm1JVnZpNDdaRU1vSnJOUno4VGN6dDhndTdDWDhhbGVjQ25nSDBWOXFGa2xUWlEtRDQ0dVNCZ0I2TWdQcmlZWkxLcllVUXBpa1NpdjItdDBhZlNLYUU5bWhwREZoSWV2dEMxMWJMNUZza0FpQ2dKM0JSdU9fajZEdmQzOXFnZUxqd09wcW9qd1V0alZ1TGtFYWs5d1k4eGc2NVZvbXFONkNB0gH_AUFVX3lxTE5yLU5FWTlXQmdqRWY5MS1MYXRPVHV3bjNkZWlEa25SVC1INTV0QjQzOXBxVzhFbEUxME1WbU9jbTZISE1fa19JS1dwRW9KOVplQ1A4QkNWWlE2YjM5NlBCNndyN2F4T2VfVmlOVnhEQzMtSENPZ2N2clVGNTdtVnQ4SU1idWI3eThwenZWRUZ4NzNwaHJvTllHUlBpYnQ4SEEtZFlRTmJuT3dGU2ZpRTdMLUFraWlfNjl5UWFZLTBlX2VMSTdXdWV6cXNOaGFzRU5QSjBOcHBPT081Z2R1d1JWQUt5TXFieXRCbGFLcGRkWVI4OG9oRk1YQXJuQmdrRQ?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 04:07", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 \u2014 Five Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNWmNXeUhrY0hPcXlaYnhxdEpqRTBKbWJadHhpVGFOX21Oc1FnTVM1UDNDOWZ3dU1jd2RjNTA5VTV1SnJHM1YyNC02dGlZYnhzeDZramF1NGpBTm0xcV9DS2ZIVURQSjlrT0M2bTJfY19qc0VmRHRBdWdZdXBmcC1pUHQzSzF4OThzSzFDV2sxbVVUQnBCWjhoemhmSEhyc01oeWJJeGlSbXlaX0xiUl9qXzdBaWhHSUt3eUdKMTh3djNuZlg3dVlqYUNjMkhpX0RoazhISVpBTnJFbmFVVGtZaFlKdGY3Rzd2SkxUTtIB9AFBVV95cUxOLV9xeHRCVnRiX1FUSENXSHZ3S3NqQkRRZFA4MzZPYkd6WENNM0NZQVpMU0FQUUJnWkVROVNSbTFrMkdJaHltbkUwTExjby0wVzViS0NkSVI1NDNORG5wNkFtSXBwMlRNbXhQbllkYnE3cGpVeVF2a1RrQTJqNG5oSnVsS2pyc0dUVEtlNnM3eHJ3bmJwbXBxZC1FSG1MbnRENzNmUFluMzJwMlJzelA3M3R5Y2V6SXZreFpGYTlZWXlITE5xS0NMdDZ3M244U0NUdWQ0R1N0TWE1bEJLM0hJYzlmYWJjcWJUUHhMVUZDZlJpMExI?oc=5", "source": "NDTV Profit", "published": "2026-09-28 03:58", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxNdFJQdUVBNmhGOF9naWYwc1VCWWozTGVwOWl1b082TGI2bmppQVQ5dmxfUWo0RGhBQ29IU29vaUJ1cDZCNEJoelpMc2g0eGhldHVGdy1WeWcxVEtZcDBDNDlfRkxNZnRFMURFLUVfY1U2UG1YTk1vampZZUozYjEzU3JGbDRWNkhhVU5qVy1qcVlhdWxFa2YzX19vSjZ4NEl0dk1reVhEMXlPb1RTTzdkNENIS2RraEdzTTlBXzFteWpPMkpkUk9MdEJqaG91ZTlUSll2UEVwcjNoM0FDdFJQVUJCM0JLQTZzS0xTVkNJQ3VIYUVyV2czYWxBLXRUNzlPUkwtTHFTNUs0cGE3VWdj0gGUAkFVX3lxTE55LTJyNkZRSldBTGdKNnM1THNXOEtPQ3FZaXdOWmhNMEVtby05Y0xaZV9QSlFuNDg3TFlfZlNpb1Z1eTI1S1ZaZDJVeGwxcktWMW9pbWxRZk83ZE1scnkxWGlVOGhDQUJJNWtnTS1MWV9BcDdKRmYybmZSVEJydVdzS1dTVGdvM0c0R09GdUEzd3Zfb3pmMXdSMGUwTk5uZ0xTTlRmV2NZWTV1M0FjWmlQZ1k3aW0wZE52QmlpeTI4bzFHTEtnbjRRZWtzb1NrTnE5dU1XX1ZQV2cxazdKZlRCNmZ6UkNSaVNnVGZVZVV4R21xZ2ZfOVBzcGZ2N3l2RkI3aGpqNnNJWjdTNnFwYnNQNEt0bw?oc=5", "source": "The Times of India", "published": "2026-09-28 03:54", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxNZ0dpRTVlRDlxc1RtOW81dTVmTTREN3MwakViZzNUakNFTDJkWkt2QkstemktQmhGZHBFWjRZYXhHcVZDcU83WWpLeXpBUDZyVzBINUVFalBwaDZ4YUhwOEdXN1E4TmVTX1ExY1U2MV83T25QZFhsa1NVcDRlWmtYSHlXdWFMTEIwcVdoS2tRWWZ6V2NIVFZMMHloczRjb0JvNHhmamx0SDEzZUxtLUJDeVgtWTNTWm50SktyR01HV0d1cXI2MmU1UWNseGFDRTVLbGx6b196aE5BMzJYV2lLYkEtZW9fcTRONVHSAe8BQVVfeXFMTVh3alpWbmYySWstWjFjN3NmVG5Sb1kyV0ZjSkYtc3MxN19pMDA3VkJwRGh0Z1FYZEU4X3BTVWkwRjlLdGQzTW9DMm5Nb05oel9SdVZrYmxRT2VIZk1nblpwMUZlWDR5ZlVnY25oU3BwaHVybk5ibEt1VXk5dS00QlBqV2ZLY01WWXN2TWNvWnc3YzRfNXBTVTJtR0w4MHRlNHBWbmcwS2tpWEkyRnlvRFFHSUtsdXdZZ010MVFsSXBEcEwyNTlNM3daV2l3Q2s2ZGVERFJNNGg5NE1iZzNJRnloY3FVYU1BRWUyaWNsRlE?oc=5", "source": "Hindustan Times", "published": "202</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6-09-28 03:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQU1VkYW85T1l4Mzh4SDJFZDBhZC1GczBiSUw3TmdJYUxvTW1TRXpUd3BTOVZwY1FzODlGUkxyNFlXSklFNzBRWUZ4WEpGdUZDWWRIZ21vM05wMHBnQ2N3UTk1VENDZTVYeHJsSEIwUG15RmpnRi0yOUdBaFRTdFg4Rkp6LXBSbzVmQjRQU0V1NXdCdVRmby13QXZqb2Zzb25Fd0FsR18yZW0yZlZBd1VibQ?oc=5", "source": "hdfcsky.com", "published": "2026-09-28 03:28", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxNQmUtcnhXbVNOQ0lacFk2Z1JXa0JON1VtZTRsYnZVMDlKdjh0dXhobk9tajVtRVdUbE5RV2MxUy1MbUpkNkc4UXNvalZoZXltbUNScGEyanBReERmbTRuQnB2d2M2dkU3NkJ0anMybXdHWV9QWElRVG9WcDhNSzE4eTV4VWs4WWluaGpYR1NZZTNuYVFPNWZwUk1YcXNOR0NrN0REb2V5eENFRjFaTVNpeWtJdw?oc=5", "source": "Reuters", "published": "2026-09-28 02:19", "score": -0.542, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices \u2014 Five Key Factors For Sensex, Nifty 50 On September 28", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQYTlhOERzdTdrb3FJNkRCaFpyd3p3dGE0QjFQNW5ndE9qQ0VTM3gwOURRS3hlYkxQOXh5UnUzYlVfMmxYZmtkcHVpZUpZZnhsNy05RWRKWi1FdHR2ZWVIa2F3MmxBTjBCeC1rNDBQQzhSYkVKSGdyV2pxa21xcnd3dk82Z2JOU3FMV3pKNzcyQjFreUdPZDlaNWh5WGVLUE1OSzV1VE9Qc3k1el9pOFdKYzBKVEMyRmZRMU9icTFpZTdQOFB5UEFCLXEybjl4MFFJam9tMFV4aXV5cjQ5bWR1Mnh3SUdXYzhtVUk5VU1uQWlMTHFwdlhr0gH_AUFVX3lxTE9yT1pHVWp1N19wOTVOLWdVWEloQV9BS0lKeDhwaWcwTGNqSnpxUVFIRkg3Y05tRUc4MUNDOF9CVm1EZjYzdnlsX0UwVkRDaEVKQ1ZNcVJteXhQQnpjR2JsMGh0QkhNcmt2eUxOdlRxTjVaMlFZWGtVSkU3Z2xfU1BLNjRrYzZ5eFE2V202Y2RKaVV4LXdqb2FNZHVDYlM5WmFyNWVSWnRKVDNab2h5VUhBaDlmbUVJWFNiOU9qYUNrVTJybWpyZkY3OHBiRUl0MTNBRjBNQ0lfYjljbkFCUE5oS3hDaEVILXd1TDNDRFVaOVR0enZ3VzBZZkJzQktabw?oc=5", "source": "NDTV Profit", "published": "2026-09-28 01:58", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOd3lLLTBUWlJpdVVESnptNXpwZnVmVk5zbTU4LWV3eTZyT1R0MzRfVFpFYzltdWhnSTI5Uko3M2dpSzY0NGJwZzFfbzZXM0ZOcV96T2hHaWQxR284Vi10dHRxeUVCQUJrV1lCclJZREI0NlpSdHp4Q0R2V1paVFlVWllhWkVCQWdaTlhiUjN4bENkS25yU0tJczFLVE9vUE1rY2hvc1FTSl9QZ1RkX1Q5ZVNfLUx2LWpmN2lQQ1pNMDNUS3NJenhycjRsNUNjbnZRMFNZNllsUU9WeU1xTk43NUY3OThtVFJadFJUSWhuNnZEMUh4VGdicDdNdFI5QkV4U20wY9IBigJBVV95cUxNVE84MHlqVDk1czZmeWtPckg1UUh1bF9OQU44MFlsSkdUeU14X2xZYXozODFYb0JtaGMwSDFVNzRpczZZb0MtY29aYTBsdl9fRFgzQkhhNG5Id2hYcE55WjhMYUU5N1hWRjg1RjJ6NGpuVmIyaURHQnI5d1RsVUxxRWZ2M0Q4NjlLQ1ZENVdyLWtSUkNrZG9MbVBwTnVENFc1UndfTzhlby1NdktITDZBbldMMlZua0xGbnVRTUFucy1GYVRaZUpPbEN4VlhTTGFlbElpVXBiZnNPeWpqQzVjbHhwYnFXUHBzWUM5WU1UVmh4ajlKbHpDRHdBR1F1bWNhNEhfZk1DNGRWZw?oc=5", "source": "Livemint", "published": "2026-09-28 01:20", "score": 0.842, "label": "Positive"}, {"symbol": "E2E", "title": "Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxORnluOHJzdFp4bmJaUl9hdWY5Ql9WeFd4cnF2ZnVZdkRIbGpTWlRzSlBxX1lBb3VEcFVTclJjQ0lVVkFKcGZTUFhLVDlDVkJkZDRnY3VQQkdlWFFOS2M1VVNNa1B1dmpueVBIRFNyRGhKVmRpd0IyV3NmTHNrdTZpZ3BKN3lSMjFnbGNyYnFtelZWWXgxWF9KYW5WSkoyQnA1R0dqTHBscWRHVVg2eDhveGtabHVVUjNoNTJCYjlsbGh4Mjk5cjgySUcwano1THJpbUY0X0swTG1POTA4a0ZSOEZFMVFJakg4RjI4aENIaVdZWWpSNWU5QnVDYkJyeTZlMXc?oc=5", "source": "Equitymaster", "published": "2026-09-28 00:30", "score": 0.557, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxQNmdxX3hPMzJrejF0R0pvaUNBbDFacW44MXRuLXZ1bF9yVnlwTXFwWGlOZUh0U19XOTJhYkZ1cHJ6VkJSMkk0QVAzcENpdkNJWVRWMDhkYXJ0NUdxRjVnaVhiS2VPWExCMWdaQlBmVzQ4a0lhNlNjNnV5Nk9xcV9zOWMyc24wTFdBY3lCbFdQdXlsaWFNdnVxblZYWVhBcm5wQW11NzdmV01JeVBsQV93eXJuU0ZaTmM?oc=5", "source": "scanx.trade", "published": "2026-09-27 17:20", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Ahead of Market: 10 things that will decide stock market action on Monday", "link": "https://news.google.com/rss/articles/CBMi3wFBVV95cUxOOHlGS3FhbzhQTUM5VG9rOXZjZXBTZ2Q2X1VJWjVOZXVEM1hET3BtSktCcmlhLXpIX3JUeWtBWlRNX1l4dWk0aGJiNFRuRVlzaDhfVUpzeF9jNzNUT0VpcFVSZWlGNkR5Mm5qeEU4ODR1RUpZcldoc2t3TkFweE8xLTF2YTROOGpkZ3lkWGRFQkpaY0xTRFB1akhkbG01QjZ1eXVBWlpjZHdnMGR2a0ZNODZuQWZ2cThKTG5nb3V1WUxxS3BCRHllVkhKM1hQTWVpQzd2WFU2b2x5TEdYcG5N0gHkAUFVX3lxTE9uUFVOSFVOazh5cm5jb1RDcVU5YzMwUjBJTV9yR1JmeHhaeTB1WmNIUS1faENuVTFJZEVxSEpheGpGcGMycjEwenhnekROSnR5OVI5V1l0TkJsTHp0V0g3MkF1TzNpMmZCUm54dXFiS3lJVWhGTkRnMklIT1pucDc1U0hrSkFoN1dkci1UM1UwVDdoNXNiZFNPWU9iUk1kSTV0RFBTTVl1UkJxc0t4OUIzcXRWWUJMbXcyZF9zZXp0c0ZEcUdBeXFKTFdxbzJWSzl6ZUFZTHI1aDZtdWFOOWhBbUQzbQ?oc=5", "source": "economictimes.com", "published": "2026-09-27 11:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show \u2014 3 reasons", "link": "https://news.google.com/rss/articles/CBMilAJBVV95cUxNekdIczJ6NEZleldrYUtRZ0pEMFlMaHFDcWdFeVVhVnJROWRBWTVFeURzYXM3NVY2eTUtZmNMOVg2VVF6eUZOZFpzcTd5S2ZqUmVJYkRaYnd2RF8xZjlDakRzUWFvaTlVb2REeWo4WUF2aTIxZUVncDVzY2o0Tmp3bVR5TmpRQmFSMDZzSTB1MFBCSWh5RmJ2b1d5QTNDdHlSN1hVcEJqUHdlOHZ3VENMVm8yWDMwV3N2M0phaDNFZzZGdE41OWVxbkdjU0tDNnFnTnM5Y2phV1pIYWN1RF9DNDhtd2JBd0I4WHRlMGFvZUtHdXNlWHJVYnN6eTFwVjVhODVsYW04ck9LRnJhb3NzTjEzVnfSAZoCQVVfeXFMUEV5VVRyZjl4LW9fV21rY0Y1SkJyYmluZTZHZlpld0cyakhLcHhKTXBNR1kwU0RET0VZeW1Ea2liT2JzSkNGenlOSzlkdVZwejU2X2FJVHFOUHZwRnM5YjRGUzJDM0VaMVlVR2M3N3FwZW83b3pBcnRwQjFTSy1UVVpDUWEwYTVDSmF0eExBWkdOQml5Zkp5aWtqU0hqNlloT2V0XzRPVml6dXV2WW5MVXlSMXZFYkQwMGNqZTBXNjBWTFVkd3pUblpDdHZ2RjlXRGlreDhvWXNnMV9KVGFySDFFNFBzUkpZUEh3OVFRVmFfSU1oU3V2bV9Pdm5hR21UWXBLYW9TUElFRExLRGdPTmJXQ2tSMjlFRV93?oc=5", "source": "Livemint", "published": "2026-09-27 09:48", "score": -0.44, "label": "Negative"}, {"symbol": "ACUTAAS", "title": "Acutaas shareholders reject ESOP scheme for subsidiary employees at AGM", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxPTUYtR2pST3JCR19XaXlmT3VmZ2JzQ0pWVWg2WC1mRDJDcjBtcmtEWU94YjZQb1hGZ0xvY2FjbmpEVVozQk9mb1M5YjVHSlJMNXNSRHVRenZXMjJUVmNQSzlhbG44SkRyaFFCT29xeDFqOFVUWUhvZjV3SHI4Snl6VngyZllRT2lGOEktdEIyZ1lRTFh3OEttcWR2SGd5N3JRaHZyZmw2Q1hQTy1tcWFjZ3ZSVUVlU3lmckFXQlp4Qm03NXVt?oc=5", "source": "scanx.trade", "published": "2026-09-27 06:44", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOT3N4b21hRzhJSXdJVzFVNWRNQ3RqT2l3aXFBN2RjN1JDX1Y2V2U5MXlDN2l1a1BGQ1hLcWktbEgwYU1UMUEtalJDYkc5RDZqX0FHdFVuMmpDVDhHdkhWSDVpMFpXLXpoa0ZTWDdGcTBxU1hJSUtIQzgwUXZvQTRPdUh6UnlXYUkxZTZHTmJFSnFQcVFSc0s4V2tGNUUwUTJVZktuRkUwY1c5eTI2NjA5VEgwMDExekhFYVhLRW4wRlduOU1wZ2JqV1F1emdiLVUwWHZwa3BmOXV3MmtLOVpzWlZOOXJ3b1MxY2pvR3VYRlFjYkxmNFdIWGFxNTJJYVVvcWhJRVVwb01UbU3SAZACQVVfeXFMUDJ0a2tkZUxvVXFoM0VZMW5YYm13NlNjNl9KY2l6X2NkS0VvMGw5eGhyWDRzU2ZsTlJmTVdTbmZ0Vzhqc1YyNGU2TWV2a0FLLU1vQmRRVktFOXhtcDRwVVVMbXZPNmo4Q0V4ZkNCU1M3TEZ3RzZwcVp6SlhoczYwY3NYNVN1c1BKSTJLYXBRbVh0bDN1ZWc4VnZNb1VZZERDOFlSXzFwNW1RX0d4LVVGRHUta0Q0cVR5dndQUGNYaTkxWFU4ZVloTzNfR01UMDJ5aVB2R0ptYjU5Q0RLRnBEZExqdEZJV1BDMHRiRTBBa19fa0djbno1blZZM1ZwUWx2VWREaHpQeS0yVFQtRFpQc2s?oc=5", "source": "Livemint", "published": "2026-09-27 04:22", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks To Own In September 2026", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWmN1VW9wZjRBZl96MHMzNnRmeS0tY28xWWZtR0hfa19FN2lyVjdtZUc0a0U3c1ZYNmZ3eTNiWFVIRElaRGV4VDFVYi1kYlN3ZjNNemNjVzFwWV9CQmxlR1B3X2kwVmphZGhMazZCVTE1a3E4clpQbU9GLVNXTWs5MjdNaldOQVBOOVpMWnNMUXA4VEtmc0drX3RWWk01aXVvd2xJS2JYeGppOElvRTFWbEJwdEJoYlBVaXFhTUNhMG14Y1FnSWROVk1qb241Sk1vOW1MWGJ3dXpuZ9IB3wFBVV95cUxPSXhqMzhnOGFvNkRfakZ0cUxHVkcycHlESmtYb2N6Vzc0MGVlSnNhLXUzOElWb1YwclgwRmY5MFhreTM0TkpzdjVjR3d1Qmd0Y1ZmRi1KM1dLeTU4QjRjOUdTNzlRNUR2b3FvaVNTbW5adHhMQk54YTR3YlRLclVfUmxKZmhRXzc4VG9PUVg4RFU5UWFOWmsyYWZHaFM4N1pxTHVLX3RVTVUwSzRtQzhCenRfa1REbS1CeXQ1Rm1GUXhvV3BxRndHZHRGVEV3VHM0S0Vidjk5bm1SSHJiVTFB?oc=5", "source": "simplywall.st", "published": "2026-09-26 22:56", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "\ud83d\udea6 Indian Markets Stuck In A Jam! But who's responsible for the traffic? \ud83e\udd14 A Bernstein note argues that India\u2019s large caps are stuck in a bygone economic era. But here's the BIG question: \ud83c\uddee\ud83c\uddf3 Is The Market\u2019s Fate Really In India\u2019s Hands? \ud83c\udf0d Or are global cues pul", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxORUdYckd5Y2pPQUg1MHZTaHlTT1ZXWTdmTGxwSWlMcE9NQm1vNE15dk9qS25VanFnTzk3c0FHTEpwaGcxXzhmekh2dUNLM2s5Zy1USHBjMHRfakhvYndNanZrV19NZVFMY1hjOHZsektLSVZoS2tTNkdzMEJTeExiS3ZVbDVRWTNWVjZ3MWVmSzhnZDVvT2d2YnEwZGJLRUp3QXhxTDVfSUc5TTdvTXIw?oc=5", "source": "linkedin.com", "published": "2026-09-26 13:51", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market News: Nifty 50 Outlook &amp; Prediction", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVJvTS1CRXVsT2ZzNUhBV0piRVV1UnZTeDVEcDJmRElmWHB5WkZsM2s5YzlYaXJuVU9vVjQ2dE5XVk93WTVVLUx2d19wRm9lc2YzWW9xX0F1YWJCTUJtMURwVzRxbC1vUlNDWEpLRUZibzdnbVdjdEJUeThfeHZLSXpwTktCQnlMM0tTNUhwWmplMHJKb2ptYmVn?oc=5", "source": "Liquide Blog", "published": "2026-09-26 12:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxPbm8wM0RSWWRXc1Bzc3daeEpaNnFwZW55Y1FBT19TQUdxYXdrZ2FJeDJGd1EwQk9BbFJTZ2xKNV9Gd1BadEFlZExtZWlxdUZEZHh1RkRIU1lMNEJVR3hkZ2VKWnNGWUVLa1Fha29hcWcyNVR6dEdydjluNGxlN1YybHFabnUzRWdzMTFSWThkNWRRX0NXQ055dWl2dXN3cGw2RUJxSHAyTTFWMnNOeXZ4S0xGQXFjRmhub1lHeVQyRUhUdEpFSGEwM2U1MEFnbExtV1JPRUVNRmV2dUNfZ1BiblROc2IzLVNPclpNRtIB-gFBVV95cUxOT2FRblV0ZG5vNUh2QTZGeldJa2FuRF8xSmRWYUQ4a1NLblFyUmtJNTRCdHB3NENTZUZhdi1Ha1g4aTV6cy1POUl0Njl3bzZNdE1ZRk43bWQwRXZvNGxncTdBaWg3cDNUMHcyRVp3d2ZKRmljNXZwQktjUTZnV3NpWldYMmNoV0ZJSjZONVJjNEQ3d2ZLWXlVREFsd1VFbFdob0xydFJ5dHpFdGIzeERrQU5kcXBubmVLd2RZODE2Skd0Yk92bFNnWG1qUjNnZWRSR2YwaWIxLU91ZHBzTlJVb0twSW5pUnYxb3E1WEJFTWdmQ0tzeVhaZjRR?oc=5", "source": "The New Indian Express", "published": "2026-09-26 09:15", "score": -0.128, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Shuts Trading Window Ahead of September-Quarter Results", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRG9haWQ2cXBQTXFHN2xLOGs5c3NtekhBM2g3ZV93blhnekIxenJUNEVyZFdYcTdwZnF4RHlrZ21Wcjh3RnFVaV9Oc01DSFd1RUIyRExqVUZHWkcteDlKWkQ1d3hEUC1OSTVGRzF4djdfMzZzR3gwd2QtSHJMZE5fU0JPQnFqanJ1TWFVd1pNTHhuczJoQWJudER1aW1pRGdHd1FQM1k0U1hVbHZwRnJyOWplYlBEUmFhRjktOHNvdGtQeXdGX190cQ?oc=5", "source": "TipRanks", "published": "2026-09-26 06:48", "score": 0.0, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQWm9DM0I5TUU2aWVIdHhCam9zXzFSUEI0RzhWaEFxWDFfbDFoeUFJUEZQbHk2OXJJdlpjeVBTVjd0RDdMSjdPMjl0eTN3NXZnRmR5bTM1Qi1KS3JsNFRrZlFCcmViSW5MTmdQdDItWTU4T3lUeFFkTEU5VHBEV2FmUjlqOWdvaDhNcGZlTk9jTjJQeVZ1Zkc4Q09fUGY4LVZiWk51d2U0ZGtxRFZ4cXpMV1V1UlJOdFN3RnZyTA?oc=5", "source": "Kalkine India", "published": "2026-09-26 06:30", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure \u0915\u0947 \u0936\u0947\u092f\u0930 \u092e\u0947\u0902 7% \u0915\u0940 \u092c\u0922\u093c\u0924; \u0915\u0902\u092a\u0928\u0940 \u0915\u094b \u092a\u093e\u0935\u0930 \u0915\u0947\u092c\u0932\u094d\u0938 \u0915\u0947 \u0932\u093f\u090f \u20b993 \u0915\u0930\u094b\u0921\u093c \u0915\u093e EPC \u0911\u0930\u094d\u0921\u0930 \u092e\u093f\u0932\u0928\u0947 \u0915\u0947 \u092c\u093e\u0926\u0964", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPVXU1bkFLVlVQVmhKWjdoVDlSNFQxTTlheVZFdGtDeEVEVzVtc3Y5Qk45R1RaOV93WlZrOXF3MzFKTlE5OGR1Xy1DcnFtUTV6YTYxYXlVMHlTWXFEbnlMaFliTC1uYTZOeVhCY2ZjQW5Qd0pzcEZWUmx5NHJHZ18tSDNHbTZrT29hbFNrWXFuQzFRTW5OQ3BMRERrUldoQUVMYmRTeTBfZEctVi1DUzF1bHphN2JnNV9lbWx3MGU5MlZRbHdZYnNrR1NHUVJVekRybmZtcWNFNGQ?oc=5", "source": "Alice Blue", "published": "2026-09-26 00:50", "score": 0.34, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxOTXpFTDNOdlg4R1lYS1FPU2VpM05pUUVGSHBvdWxqLXJ4SFpPTXZ6Q25FVjh0V1lvbnR3ODJsa1Q0ZDJlbWpRZFFiSmw2MUhwVF9lUVVyVWJTQ3lTMkJHNmtHMFNOMmwyRng2TlFUVlM0WGhOdU9KaTh4QWZ4bm81SUlqcEN0dm5FRHZVQ09UdTBIVWxZajM4alAwcjRrUURkMHFPSnNWVndUNjhjcjVUb0ROQVZJTFBCMmU1bFUyNUl5c0YzZDQ0bmVSNXB3Nm9pNUhnaW9RdEJYMU9WZkVqS3FHdGRaTnPSAewBQVVfeXFMTm9mRGRDb0NZSlU0UTM4c19nUEJhMERMSFc2ZlY4Ul96bUdPUFBlSEZQZ3c0NnFXX250RkQybjhjQkxoSVc2OGNlTnNoOWcweUdOVjlzdS1sZjZvUkM1T3FKWkxTSFczOHVHQ3pMbWlJbGxDX2Itd29DZU5iTzF1ZGlpSEk2dkNaZE0tNXA0Sms5SDdsZ3VuNjhQTGxYc0lYemowWmJzbFE2VUJjb0drM1NYNktGWTBieGFoOFJEbU05ekZtODl1UGsyM1UxbF9idTdCRlppbW05c1RYZXhVaFd3eXc0NU5PN3RGeWM?oc=5", "source": "simplywall.st", "published": "2026-09-25 14:34", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "PERSISTENT Stock Price and Chart \u2014 NSE:PERSISTENT", "link": "https://news.google.com/rss/articles/CBMiYEFVX3lxTE01VG4tR1ZHRnF6bF9CZzh6bHlySkh2MFd6bGJKUVhycUhNQkh2R2syeXEzOG9tLVpSTmNrcUEtOUVWZm45QUE1ZTB1VXFYSEc0LUI0akZJc3NQTDE5SHh0cg?oc=5", "source": "TradingView", "published": "2026-09-25 14:31", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "R R Kabel board approves proposal to acquire U M Cables\u2019 optical fibre cable business; shares rally 72% YTD", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcGpkYXl6WDhuYWFNMkVobGFYaHROYTR3R2NJcWhMcmptMEpqS09jeVBMRFNsQjkxSE9QVWVZQUVXeUFweWdVeEVTNzUycGFHMmxkekJSR2F2OFl0LV9CYUg3M0VvVnJEaUlEUFNrT2RqVkpNY21PeW53SThRUzMzSzhqYm93VkNPWjVSWUJUYnFicTdONEVQY1NwdTlqTTlSbWhxUGlZMEN5aUpyWjN5aUgxckhCampqdzhoQTYtZEpkSGljNWhhVUJoM2dqNUhSMGc?oc=5", "source": "Upstox", "published": "2026-09-25 14:04", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "India shares log longest weekly losing run since 2020 as oil prices bite", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRDlIOXFjNzhyRGVteU5DNTJCdVlRNUZEY3VObFdZNDI1MDU2SUo0NEM1N1JDTHpDMTk0YU9OM2V1eXRla1VaanBsTTlUM1lWR3VYU0g1eG5pM21hNzFWQTdabWphemRRMlc1U09MdWxVRVNLUWxjd3pIODVuY2UtcFE0dEhPTUM2MU1pbHNOQ1NnOUQtME1TTDJjSzJzOGljZTRmN0NBZ2Q0S1VodGZaSXFxZU1VTGNnanc3a0o0anM?oc=5", "source": "Reuters", "published": "2026-09-25 12:52", "score": -0.382, "label": "Negative"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxQbV84TnZBcDlZcGRjQ2YxN1Z3eC1lNHdhNTN1ZENIRnZsR21zVVQyQUFmNnpKbmQ1VWl6SEpGNi1XX01ZcXZuM09QZklRNUh3YTZwd1RJNDRpM01BRUJfS0VJSXRGVy12UllLVU5jZnd4UWMyQjlkZHJPRGsxX2RQZnY2c3RRRE0?oc=5", "source": "Univest", "published": "2026-09-25 12:22", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "RR Kabel enters optical fibre cable segment with \u20b977 crore U M Cables acquisition", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVHNrRVg1VDRadktqWU9TVnUtdlV0UGx2YVN1Wk9maFBKZkl6NXN1dEhmSGxFNVVaejRWQy05czFfT2twSjJxX1lDR2x5QTZycklWVWJBTDNGZ2lWYWFGYUN2dHUtRnEwUGxsVmw5UmhRandzdHdDUHZMUGZNbnhsUVdmbWJ5VTZ1NnlDdTM4UVJJNWlDU3QxRDJfeUZyMWF1Rl9fWmUyWmdyUHZpVXNRT0lkVjVUaHZpX25Na0RVa1lHRFh1ZFlQOUlhVUFJbmVLamVsdHZHVkt6bWJrRXY5UdIB5gFBVV95cUxONTd5ZUl2WG5FUzRqVGsyNGNWcHpEN0ItSkJvV2wweHhrVENsb1NFa3ppbm92bUFGdERMZWlva1YyMEl0dDYxcXg3clQwZ0xKRk1OY0c0cjZOYWFmamVwdnNsTm51TTIwV2lhNnFNX1pfS29Od0xQZXpWNWdFd1k5Y1Fmc2ZKRWJtRGlJUDdBM3NUS0RSMWJtdDlVaGM0NzVuZFZvTktxelNrd29GOFo2SjU5ZU1HR2VWUHZaUTBVa0l3TjZVOGZaWDZUTzRTSW52VnIyNThJb3p6b3lPU3RualRINlVGZw?oc=5", "source": "CNBC TV18", "published": "2026-09-25 11:42", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPbUR3cDZZTmx0T0FjVGdkU0ZOV21PRUFzdFNkR1FaT2hqcFQyZkVxS0ZKSVEydXF6OGlMbnUtakExc2NhTGI0WkE3NXVYYlpnR1NBV2l5SUxWUFhXX0VtemF1WG1pdUU3TnoyLVJCb3ZxM2ZrdjUzRW1wZFJ3M01WQmtaYnFWbUZxR1NGQ2Fwd2dJRTM1QndDMnlobXFVbjAtUnVscXUyZUtyMVZIaEdmSE9MQlFSTkpkYXhvQlBicjJTRjJ6V2VIRnM4RFNCSDNWVmFudGZNTQ?oc=5", "source": "Equitymaster", "published": "2026-09-25 11:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets bounce back on value buying; Sensex rises 315 pts", "link": "https://news.google.com/rss/articles/CBMimAFBVV95cUxNTXctaFR6eWUybzRBdVZHa1BueHV2ckVGVnJOQ1VKbnI1UXdLYXBocHhualBwZ1ZWOGVmTnkxelBSZFFUQnNRUG9BeWtsb1F4Z09tOElYb0FLclA2MmVDM3U1dldiUEd3MFlGQk0zTkZVV3JyUm1Iejd6dm15M0hBVGllcDhjUVFPUy1GUW80cERRbGU0TVdDaQ?oc=5", "source": "DD India", "published": "2026-09-25 11:01", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rebound on Value Buying After Sharp Losses", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSjR4N2QtaTVfdUc1bkpKY0JWcFZ6RzdlM21SN2M0eXNfT2hQVWt1eXZxYmlmUFVBSGhRdmxTalRGYlIyV3J2M2lmZk05WUpVcDQ3bk1IeFh5aTN5Mm1nVXFZOUJCenlPRzR6VVAtaW0zcjZMQno2QTh0MklYUFhvZW1Pa1JvRDNCS2JIa3U5Qk1SMjJRTm5zZjE4NGFIVlVFOHpwVWJHTlBtaGfSAbABQVVfeXFMTzMwT3V5UkdaUUpqeTRFOHBwOXhrSFdVNjV6QXlZc1lzN1AwUzU0RFNxYl9aWGdQSS10S1d4dnRZNlhQNjZzMW1hTmhBaFoxMmFIaWNIdjdDblFCanNIUjJXMHR2SEJyUnVUb1J4X2ZoS2FVLWh4N0tnZGJ0RGc4aXpPNnQxLXFrR3J1Z3FGczZjM181U3FTbnVySUducS1VNGUyaVByUVNyanFPdHRHSVQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-25 10:48", "score": 0.318, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE5hVC1JSXRqcHpiOC1BcW9STzVMX1E1Y2FuZThSci15UVN4VVBkU0syaVFzU01NaXVDZ21QSS03M0h2N0JoZFFOV1lZVlZna1YtRzRHdi03OHRLS3B0OGdGbzRKX01uc3BVbzZwTXVmVkFoMXU5Nk04aGhYZw?oc=5", "source": "apacnewsnetwork.com", "published": "2026-09-25 10:31", "score": -0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today | Stock Market Live: Sensex rises 150 pts, Nifty eyes 23,100; realty gains, IT slips", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxNNGZNa1lkSGVudThjR01EUWh3cTNHTVVPQ0NNcGRHZ1JmSndlS25UZTZXRWs2TjBqSnE1RzZxbTRfWWJMWEtSTUsyLWFoMUVvODMzdVVVSzl3WGRNeHZQYnFfazBWT1BJbmdjcFRVb09xTFh2Qkk2eEx4RFc4MzVFX2tzQXE2ODJvUTVkeXBqWGZScVlXaGRpZkJBaUNGZU82QUlzWVZRaVkza2dDa0dZbE4zcHB0S2FyYUVxZU9mQVZZVUdk?oc=5", "source": "IndiaIPO", "published": "2026-09-25 07:19", "score": 0.44, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "AEROFLEX INDUSTRIES LTD Share Price", "link": "https://news.google.com/rss/articles/CBMib0FVX3lxTFBha0hsSGJVRlJTaUd3OGkxdXEyMk5uZzA3QWlFS2twanVvZzZoVnZUUzlpOVo2dll5Z251ajFhU05sT2lhUGViMkRtWmx1aEtDLVNCM3NyaTlGTVk3amctYk96QXJMX0VheVpVcGZfRQ?oc=5", "source": "Upstox", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Sah Polymers Share Price", "link": "https://news.google.com/rss/articles/CBMia0FVX3lxTFAxM1NrSlNad3RNSzJKUGVISVgtY1lGZ3NYN3FyNTBJb0FBYlNGQjVCSTRBWXE0c1dHR1lvemdIOFFwLUQ4czVFaGplWHRnbWR4Wkc2N1pkTUlfQ29mQkFNdU9DZkg2akQ2LVRF?oc=5", "source": "Upstox", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Laser Power &amp; Infra Ltd Share Price Today,, LASERPOWER Share Price NSE, BSE", "link": "https://news.google.com/rss/articles/CBMikAFBVV95cUxNSlFTaGgxd29JS1hnbC02QWUyVkV1azhVUTRRZk52Y1h3Z0NRYU41WDhtYTg0M256bHF6QndKQU1VekVKbXN2ZTJlTnFFTVdfejBERXJueXFzQW11MG03OHNkVGY0S0J3MUNVV2xxZmUwc2g0SUltRzdlNXBSb1FhN2ZlWVhPQ3NKci03VFNXTzY?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "Nifty Chemicals (NFTCHEMIC) Share Price", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYURIakNOVnRybktpTUJSR0ZBR1Vla0tUNHQzQmY4clE5d0o4Q1pZM3BtaGhTcjk4UWtuR2tXbmJ1S3kxOGZ4SVhYSURHRkRCN3NwUUxzaDJ0dUZZWWZ0aWhlQkZtclZ6U0hIbTNJTlpNQk9Sblp6WW1WUTVyb3ZRRHJlV1BoUUE?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.402, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "JSW Holdings Share Price Today, JSW Holdings Stock Price Live NSE/BSE Updates", "link": "https://news.google.com/rss/articles/CBMikwFBVV95cUxQSk92TjRKUnJJUXluVlZFYWMyUVQ5T0g0RjBoSm1ROGJNSGc1UWxydTBxdTc5bUtmRjlQU1ZWUFhQVTUwXzJOMF9WaGVWblItaXFkSGpoZ2tzeHV1UWc3aFRlZzUyUWxjUW5sVHNwajl6aUJKc1MwTkpxZFJmNlcyZXJGUVNhTTdYVmc1TXl1WGF6Yzg?oc=5", "source": "The Economic Times", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today", "link": "https://news.google.com/rss/articles/CBMilgFBVV95cUxOSmhSUlhBeGVjR0VmV1paYzdJdDlLd045M2hLX1dPc0NQdkJXUmR5dUNCNGNYeGxBNnlrTVNtMkQya1JiamhQQTNfbU8zdmxndzB4TWlmSndSdmpzZ3RGU0VickFfeDg2U0x0ZmFkMWtxMndNU3FkdmMyTTE3R20wdnNpdUJoN1RNdlFKbXJHNXlqMU9KUUE?oc=5", "source": "Univest", "published": "2026-09-25 06:49", "score": -0.052, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty struggle for direction as oil, US yields weigh", "link": "https://news.google.com/rss/articles/CBMiqgFBVV95cUxQX1M4MzdlZVRMVGVUTXNrRTVQcUowb0k1Z2ZvSXp1MWgyQ0xLVE5JX2twRnhYOVBXYzRvYUoyMWI1a1ZFYTZFdEZOdmxvRVZlQllfcnA5OXRrWEhRVEdyNzIzVlNwWlJzdk5GcTUtc281VFFydy1tWmhCNHotVkQ4aUF2NHFFcTdrMEpvMVczMnNGZGVPelA4Q1luc3VoSGxZTVl2MlpILW52d9IBtwFBVV95cUxQMkQwb0hQcUdlOXAydktxZVlFc2JGMmM4RVM0d2o4MWFCbHhDdnc4VUxPUW1ka3l5YVFWRDBKT2xUaGMydWdfZjZUR1VsTFlBRUVPZnpWZEo1YnZZeThmZUN5akw0ZW14Q3owYzJXaGxLVURVVXJpNEt0UmpZTUFJUnY3amNXeEpjRDMtc0NRdFJteEdqeTJyc2M1WDZWMmN3STFCV3NaQ2hGWklQRWtCSmU4aXZOdGc?oc=5", "source": "PSU Watch", "published": "2026-09-25 06:07", "score": 0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxQTE9BdERYOTF4QjNsVFdOSUVsVjdickVLMkJHYld6YmRCdm5PRGloTnh2OHk5VmRRQjJiTDMyTUZNalZMQXk5eGt2OHd6RmllbVhWbUpEQjhnOVJvbmtVU2w2aEs1cTd4WWljRTkyc2dmT01xZVRnb3k2TGlvS0lCT3NVcS1yclo1TERWQWszM2l1dzhDdnBoSUpOVTRQNW10RFd6ODFidlM5QWttRnkyX1RWaWhWS3RzWURldTM4MDctTWR3d2ZWSWh1a2FJX29lV3Z5NnkxWUhVYzRzZmw3NGI0V1Q0R1o3TTVVZUl3REw4TFBtNTdUZVA3Q1VxanRQYVF5Yk8xc0g1YkVUZm1mTzFR0gGXAkFVX3lxTE9HLTI5ZmFma1R5UUFlREE1U052c1BXWndUTkY4ZlpnQi1hVGs0MFNNTS1SZU1qeUM3cXduelRYbzM2WENOQXNDVUprdkVfYnJDbE90cE9CQXZ6bUJEZkkxdE9wbW52akpFZTZwWGtQaTFQei14d2hFLWJMT2VpOVotMloyZ0U1UFFLeWZNZ3NzYVozQ0lwbE50S2pJN0REOVpaNWZXX0ZOTFVmZWVkbDI2RFA0OFRtUFZxc2ZEeF83emxxMHN2LVk2M2tNNUpmemRCR2lXeUtwYlVPdHFzNGh6Z1RJVmV2aUgtVkFzajM3R2VtOU9qNlAwY29sN09XSDRRR0FXTF9zVV8tNkY5YVpPbVYyb01icw?oc=5", "source": "Livemint", "published": "2026-09-25 05:52", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE shares dip on day 2 of listing, brokerages back long-term growth story", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNVmN3NGUwRl9DSWI4bV9GWXNDZk5fRV83NEJWVDc3RGVNQkh5ZWktVjdJRnJZcE9aZUxUQ3dyZWZodFFiZzljZmppdTJ1R0lPNUtPTjdLSVdfUXJ6VmNyN1FWVElaV094SGFJMlNOU2drVGlFdUlPSGpld1g4VGpoa0QyS21vUTE5QWViVl9ETWtJdHpKbDNvek9wOHZnR0ZRQTNvNGdPSmVaV1BvRmMyQmtPSWZpZmFwYklWOGpkS2dKdF9DUDg0LUU1QzZDUkhLNHdNR0RRd9IB3AFBVV95cUxPdk8wd0R3RW9FSW1lamlhT2tiT0phLWRyT0R5bDhEUVU2aVRjNVZwMGo0SHlfZVotNHZoTGxCR2ctcGxWNml2UWZCZ1FGOEJZNDRFNElqSUtKY3I4NjUyR1RsTEpZbWI2YkNudU9GRXJURUFfRjZfSlh3VHpsaWJ0VEhRdGhhcHVMVjMxMkg0Q3pEMWY1N0thZm5KTnRINTNwWE54NWNUc1REZFhzN0JCZnVxc0J0RndhMFZxTUJlOFZ0XzhnLUpGWDR2Y3Ftd2dwb2hRalRKSk1lS3M0?oc=5", "source": "Business Standard", "published": "2026-09-25 05:32", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty up in Volatile Trade", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNai04S3BOYlFIQUVwRlBMNDVOcXJDSkFJOFpuM1VLU1F2eno1VF8tSEQ4Wk0tNm1yMmE2NkJaRzRoSEVxOWpLM3BNWThjV2RNQ2hfOVhlWnlFb3hiSWZUUmJuckJZZko5UmFmeERYYlV6cVc4dm02MDlhaHliQzNOOFNvX0xyNlAyQzNfcVE5bHBRNF8xcEZvem1BWkRHd25BMndENC1GOW8tS095d21abDlMRzlFVExvSkN6ZDJ0eTlTeHdhcjJEU1h2QzFIT3I5X1hMc1k3cDNRZEHSAd4BQVVfeXFMT0pjQTFkYUp0UG10Sm5OOUJoWFhHZHNHNVZha25TOTJRdlE2aVZCNlVMcUFENFktUlFHOEloRVloMnhTbnU2UTY5bmRGSUlRLWNESnRzQV9TNWRlMzlVUFJlUV9XYmFIOGE2bDhkUEtjQlRjZHNPcm92d245Z20yZUdLaE1JRXc0aFZaQnI3bzJWUEhHNDBjdHNCX1pkUlZSY0E1aXExdHhBUmp0d3pncTJ1S0F5QkktekgySEc5UnZ4R0JiTUl0Sk0wYm5DWWdGZDFxLTBLMjkybUdUNGx3?oc=5", "source": "Rediff", "published": "2026-09-25 05:09", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets turn volatile as oil prices, rising bond yields weigh on sentiments", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNR1J5T0l1VEd5Ynk2RGZKaU5NN3Flelh5V0N3NjdsNEVoZnhFemVBMy1jWk91VGxXeUowQWRwaU5HQjhvTFBMTTRscnJQbjhyXzdkekkyNl9RaEJFV3cyRlhncEU3UWxocDJVVFdCd2VKSmJMb1pDdVNBZ1o4Ulo1U053ZGNobUViSHY0YmR3V1k0OUREc0ZRX3Fnc9IBogFBVV95cUxPcnZySGFNcF9nN1dRdzY1c3NybzN6X3B5UFRrZ1E0VGxCOWlfSjA4TEoySGpaWW0wVUhWWW9VcHZJMm0zRHRyTmpVUUw4RDlxVmtGSU9EODlhUGMwMHZRcnlJV1dhX1ZyYk9KN0lVWGVITHh1MUNKWlhVU1RHNjJoTkktVTZFS0ZyR0RVMWxPME5nRTZkY2tabWUwenVYRFdidVE?oc=5", "source": "The Hindu", "published": "2026-09-25 05:04", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty volatile after early rebound as crude, bond yields weigh", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxPU0xIaVI2TF9VODd0UXkzcWxSd2duY1NvSjhhQ1RxbDBTRkVwYW1nc1phbjh6ZnZmNmthOE45SGVDNHAtLUtmQ3VQZ3hXNF9iLVV0emwxMEMxampTa2NvRmpxWlp1Yl9BVlZJNThXMDVEYlJJYzg2T1FmZ09fUXluTEo1b01PbGs0S1dBb2NiTFE4b1k0dWtkYUlZWQ?oc=5", "source": "Telangana Today", "published": "2026-09-25 04:53", "score": -0.25, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks vs ESDS: AI Cloud Business Models and Financials Compared", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxOcldJYTMtdlhKcUxFVjJnaFZLX3k3ZVdnVDZDNmpVbnNXRklrcGdaWFpUZUEweUtXU3drUC1JUWwtVjJvd1BWYXNlVDVwd2V6Szd6R0YzQnJqR1JwUTJ2dFZYVlNXelJzeDZvbDZrOXF0VmxsamdPcTR4ZjJMUXBublJIVjhDcFhyQXNlLUdDdm9LQ2ZtV3paVUxSOHFEU3pNWEJ0amRtS1NjOWdfVWtaV3FJZF9Ma2kxaDJXWGt5QTFNWUREQlFmYXZNdko4T3FVNUJvUmxETEtjTnR6Q0E?oc=5", "source": "Business Upturn", "published": "2026-09-25 04:52", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Higher; IT Stocks Drag Market", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOa1g3WWJNZVo4UW5QcW1WUUJQSlh4RDRVWmV6SWJya2I0Vkt1OEZTQjJzRDFhcHlEdF9WOXhnNnVTMnpLbkxUeFNrY0F5RmMwWWNiSDI1LXBKdTc2LVh1VmJGUHg0VldSTHh5LUtpdXFNTUxXY3RyRW5LM1dGM1lZU2NuYTkzNkdCUkMxdzBFQ1ZPcmlic2xYVnQxT0NBbHhWbXRYUWlIZjRSWUtKeVZEMFpFdTE0T2Nfc3psUnFrOVgzaEpmQmVrVW1ISWhtU0c3YzBIMVhrek9BdlFubWwtTWt4aHJkRE1qcFE?oc=5", "source": "hdfcsky.com", "published": "2026-09-25 04:45", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty open cautiously today; IT stocks bleed as crude, yields bite", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbFllQWhOdXJ4WWowSWNVOWtJSVBGcDg5dTdhNEVmdFZGV01XUVA5RWdnemZYZDQ5QVRFeTdHbE9Od0F0dmlRZDJ4cnUyWFhaYTJVbmZKbG1CaEMwSjBCYmE4NDFiVEswM1VRSFR6MV83d0ZEcVR4VjUtWjJLN1BJdlotMFBSMTRaU1BDNmJlT2NmRmZEbktoY3hTS21fMDVEU2ZWTWpEM2h3SHktalAxZ1Z3dTNCVUZPOU9kVUFQaV84Znp3VmJUcGw5YzFLOXVidUtZRXBIUHN6Qm1s0gHjAUFVX3lxTE9jRjdpM01SdnNzdlMyYlRQMGx2clFUVEFrQUFCazhqYjZ5V2hWR3JrZjNMalZlR29zTTl4ckhzQU54b0hsUGNPNnMxR1pBY0hDSEcxNTJuYnVIT2tSanBBanVzWW05TFRZdUdwdXFTaFF1TXdvR25oUjdJM3hqVF9VaE5iUEpiTDUtelNEUzJuLWI2RVgzMXp2bzlvRnNmLUtyUTkyc2FYdUpxMkhSWFFKeEZ2SkxuS1MxbFlHejBOdGs0RUF1SWJScmxOZ1ByUGY0RkwzVjBuWlFDajhkRDhPSUIw?oc=5", "source": "BusinessLine", "published": "2026-09-25 04:24", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets rebound in early trade: Sensex climbs 86 points, Nifty up 18.80 points", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxPbl95eGhLbXl1M0hLVTVZYzU1UUs4dTlwRnBHWmJhUm5OVTVZbVNTMHR2T2NNbFFKSkxJcDBCSWhCN2phdDNCb1Z2STlBS0xFWnVlMHhDZU1wN1J5NXQ4WFRLMF82czhtUk9VVi15TGpCQk1OOEdLZUxMZFk2dDluT1UwcW5pOEotQW1Ed21reVhVQjd1RUJWbFZaTmJKOHhneHJaVmkxQllqX0dXdzVZTDEyNTBpSnVNOE1XRU1CbVlPVDdoRzhOUmwyWloza0XSAdQBQVVfeXFMTmhmcjZJWkw1Q0VaZnhWYldKVVQ1UlZ1SWd0QnhkeUc1aFhaekZpdjI1WUdjelh4WjRsRUpLcDI2aFcyanc0NVhXRnktY0RIS0pCdTdZWkZwX1N2SG5kaG4xSXczMDlPbldpMGpUUU9CT2VQc2ptamxtV1haeUd3N3h5NzlzMmxveUt4VVlWMlpqTlBfZm96Tk5GV2lOYkpXVjdaUVdEbWZzR1dTaTFNMVhoSHRVWEthdFRYVTRNUE5iX28tZnhOZG1EMTFzQnBPa2xVS1Y?oc=5", "source": "Telegraph India", "published": "2026-09-25 04:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNS2ZIYlJtSTJ2R0tUd041X2M0a2gyT0hxbktRNi1YSFpNcXlUZlBwcW9FMGl0RkRoUXJpLXFSYmI1SUlJTkFBNTl0dlExYi1LWm0xX1hUVVFqVjhxWlJwd1Mwb29fX1U0VVFhRE01d3IxSTNpNkkzQWY2TkpJSVVKLWtlM1dFWkFnaEFuZ2hCT2RYWktac2dQLUVmemdKeHlMMHYwbEtfaEI2d2w0MEdYVGx4T2R1ZktDV1RWQ2ZfUFBDZGRTWVdmSF92OS1kTnFNUTBXeHlZd3ctMF9wMk9lNHRoVEJTUTVYSV9rR0FvdG5jZVIxdzBJdnNSS1VzbXll0gGGAkFVX3lxTFBZX2J6TDljZ3haMlBoSFNpQWJ3XzE1aVhVTXVUNUkyYUZLY2N5Z1VuV19hbzZNNDhsb2RlTjZWRmpObFNlVFR1RmtRcVM3bXZGODZXUnhJcC11VXVDM2pKWVNfdXRjaENBQUZiRjZwZmZ2SmRmRTE1Nmxac1I4RlVla0U0LVdlNGdKS2RxOHhfRUFTaUtlcDNLTFVjY2JyZzBSWFEwVXR1R25rMjZmRldrRldOazUwRmRjTmhpVUl6Q1ViWFo4bS1GaEpuWkhUelYyd0ZBOGdIM0Fxa0p0U29jZEpnR1NWcGx6TEl6ckt5NUNhS0lTVU1QR043dEZvbC0zNmpHNmc?oc=5", "source": "The Times of India", "published": "2026-09-25 03:51", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty opening: Will the stock market fall again today?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>, "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxQTGdOWVNXLVlYOVZOaXJ0QS1ZVGhSX3V1c0RYN0VBTjBlWUxYOVY4VFkzQm5iMFVsVU5tVG50NnlXWmV2R20wQURmZ1J4RDN0TjJsbjk1anZfcGY5cVhIRkM4R0EtanpfbExSa1I2TzBidGV2djk1NVdNamZ5VjJVbnZQUjNaSnR5OWE1dVZGTXFDbW9kV19SN1FqT2lMRm1LcnZMQnp0YTF5OU5ZZDlxd1dsYkxRbzllUFh5aFFHclVkclNzaWx1emdoUWNfVm5zZ3Y5bVJxVElMRFNiSlZfYURKOHY5YlFpaEdyUVJvVlJINGdx0gH6AUFVX3lxTE5IYXFFYmhBbUpvcUdlb3ItY3ZNQUJta0Q4blRFTXBVbjdPZGNDb0pEYnQ4OTlRa3F4elN6NUdJNVAyWjZWa2Y1RkxFVzZyQ2dTMUVpM3FwWi1aQUtEdTl0em9OdGxxQnlUSXV6ZlVVVF81S21yOGlkWUU2X2VQbFBSektTR01TMll3cnFFUTZ3NkNEbDN1QVY4OVRDQ0lMYWlnaXRibXFxWXNOd1ZNeDFIY084dUY1aTRXcXg0SXQzN1hJT0VEdmE2eGxlQUV0bTY2Mmg5aVFWUjBfVmY0N2U4MF9KZkV0XzRGUzlYM2pRYVZGRFVxOFNGREE?oc=5", "source": "India Today", "published": "2026-09-25 02:58", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty may open flat amid key headwinds", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPUTZ0WFk4RmRvMGxLQ1NEcHdMTU5ZWWI5a2V4Uld4WVNIU3FsWmJpVXJXZFJaNnVXRTd3WjBKdDMwUmtoMktHVHlSekRoT1dsTjJTZjdrbDJYM3FGa1BTdVdIaUxOZ0o0U1NWaC1fZm4xbXJsWkJzZ3c3MTBtX1VhTjZkUHY0MmZQYWtMOEFrREZhTmstUUZ0eDdfRGx0aFZGNTRPU1VIcG8yTEVjNEF5NzJnUm82Q2hVYzNncS1qOEVDV0QyWG9mbW92elNEZ2tr0gHXAUFVX3lxTE5tQlVCbVlxQndqM1Zmd2ZtZWdldjZ6WXBqWjZiVEhjLTFKamtwNXhXbG9KWXZ1bUFuN19PMzFtdlNxS1N5UzRIckttOFBINUlKWnE1SmpYWHQ3MDlIUDRkVVR2eWwyQUMzMmNVSFM0UEZvTDR6Z0NBS2E1bzZoM3dDWlBJNkp6OGo5V2FZRHBzWVZBdUNYeTFPaGxyMkxpREF6enktNGFkbWRNVWZQVDNVVGo2WVhWTzd6YXM5MVA3YzlhM2RzMVJRTDM1emRDUVdPM0xObzRv?oc=5", "source": "BusinessLine", "published": "2026-09-25 02:18", "score": 0.402, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...", "link": "https://news.google.com/rss/articles/CBMiqAJBVV95cUxOQ0Z0MUFZM2ViTTdHaHJ5akJLdkNEbEVZeFFsZ25KVmN6UTE1X2xMTmtUckhBOUdZeE5OOHY5blA4WDhVZDVJbjZCeUJVWE5meUM0aWhoY01DRnRBRHJaVURNTWg2SVRPVkJhUjVUb3dkRDVQZ1B5ZzRhS1ZyUVA1NnNXOEJqbWh0TG5EWHAxZXIzcU5nYnIzQ2xZU2RWaHR1dE5KTE1sMUpTQUthdmdLbGpjcXZvY1JsWXNzcHp0b1F3c1I3ZHpmUTdqMUpmbTV3M0JNM3AzWDZETUFsOFpURk9oQlY3UXB2Rjh6cjNobFhYOTI4MXRUN3YxVXYwaXJnTklxOGU3NXNHSjl6c3RndGt4TmluUUROMVhIZ0pWc3hia3F6blRJSNIBrgJBVV95cUxOdWNfS1N2QVhiREVSTXpDajYwUE9RM1VycGxPNmRKaHU2N3N4Y2tiX2tKSlU1NEpYR0Y5Q2xOMFFhV0VRRE83WmNDUXFvUU5LNXFITElxRmNJSEFJT3dDcGNwT3Q5UHYzaFB4NHg4NlpKUXo3bGtOV1lPRllGMXUxdC13N2RoTl85V01LU3o3Yk5Oa2hzWVZxdGoweFJySlZDVXFPY3NFcXJwV0tpdkxOZDhhRXRpU3ZhOEZCMEZ5QWlBUnczdTRuMUxCcXdwb1Vtd3JWS1Q0aUxpbzhhLXh2bmRtZ05Cc2VyVWM2YjVJTzRXd18yNndmaklMQWdsWlEtdEkybzlJRng2WndzbnJWUGF2S0RBNnE2MlRCb1FGSVktd0g2TEdPdGEwMDRYZw?oc=5", "source": "Moneycontrol.com", "published": "2026-09-25 02:06", "score": 0.178, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Bond Yields To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On September 25", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxOdVk2NWY2YmFvVWRzUDF4anpscG54WjM1SVVVVldRT244LTh1aXVWbXFCWnQyQVZnbmQycU41N3JiV3p5ZTF6VlZMSUI3NUQtR0tsVDF6cS0zdjZiQ3lCM0VhTXFoSEt4aEh2YVF2cXFxY2ZfMkVZSjhuNDZyODRGQUNYRXNpeWdEZzRjd2ZaeThvb3BxdmpBdU1jZVhNWHAyUzR0eGhtTzRHYTVkdTdvYWhRcWhldEkxV3Z2bnZ2SjhqNVYzMWR4MTcxdWc4X0FkNzdjb1VhYUFFNFNOTnVMeGFtUkF5SC1ZRG4wM1Z3VUU1SE5ucnfSAf4BQVVfeXFMTzFDRFpfdFA3RTRhanpJaFljZTc3ams4V2FOMENpZWYtUC1uSEwtYWlNODhZSnhnVXBZUEc5REwtbjFDYkFtSjd3SlBwbHgzblJDQ2pyc2F2aHdwV1NnaTlxU2plcGhYNWg4cWZiZGNObUVPOENwTFRuS0dnbHdTbVNtQTZGUXlGTnVnaEhZYW0xVHhjVnpZdk1qMlQxWFNnRHM4NENlWDFtdFhQODYyNWFRb2haeThMUWdsZk55R1g4YzBWbkFGc2xvX0Q4REwxdHBjb2VidHFmMHNKRnZDXzBrQU5oZmJ5bVFuZ2dIVmhlMGJKNHhhQmFPdlNPVlE?oc=5", "source": "NDTV Profit", "published": "2026-09-25 01:28", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for 25 Sept 2026 | GIFT Nifty, Nikkei, Taiwan cues to watch", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxNWTM0dmdrRUdfSk9FUWpVejZ1SXQ0U2NjX0VxVFlzbzllSWhmVWtZMGdLODg2RnJGNkVSUzRFdGxzQUVsaEtfVk9lZ2ZVNmdaNDV1ZjlON3hBdllybjlOSWhWRkhKUjBGMnVPazJxRFBmdFRoOUZBQkFQZnNYZHdlUlRRV0lDbzFiZHM3Z2ZTNlJ5enBpc1Z6SnpOMkRpdzNYcXFkZTR3dG5neVZyLWI0NmJVOUM4Z2xQNlFoZTR5ZXFkN19kQTRtbkRLcW92ZHBGZGtnc09Md05XT014NXJDdzVOcHNJYWFOS3ZGM2JoSURuSDNPSGdvZDh5NGVaeDhta1hlZ05ZSmtseXPSAZACQVVfeXFMTTFlTERSSENCSkhwSzdDNExXMmdvNnVpUWRZWVZNWHFXdWdLNDdTb1JiNmVIbU5OM2ZhZE1Cc0RVMExmLUJvdVUyQ0RTLW8wM0xwRDI2YnRSMjJKVVl3di1ycnM0UjNQYmZMTWRuMU0yd1hxMDdaVWQwa3R3RF9scDJ2VU1GTWZ3cWYtU29uOGl4TjVBdDlpYlA1d1FDcUhqWjU4SEU4Nnk4VV82RlFxbVNZa2tsUVVMQ2NUZUNCZUl5V2RteEc2Qno4R0o0Z1FRTXh1eC1sVTRlbXBqQXRlcXRjZ0dHTUE2SDFlRlRxQng0QXpwbEJhNWlJQV9yc3JIQTN3bEFVT2x0RzEzalpsbXo?oc=5", "source": "Livemint", "published": "2026-09-25 01:15", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks With Revenue Growth Up To 16%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-revenue-171316164.html", "source": "Simply Wall St.", "published": "2026-09-24 17:13", "score": 0.932, "label": "Positive"}, {"symbol": "RRKABEL", "title": "R R Kabel acquires U M Cables business for Rs. 77 crores", "link": "https://news.google.com/rss/articles/CBMilwFBVV95cUxPQ0I0bk94a2s1NkRCd2ZFZC1ZWmNnNE9Fdy1Pb3JpZ1dMU0xTSVpVajRIOE44eHJkbW14OEY3bUxuWkNZOVoxaWxDUXByWFlaLXVJenBveVRGYUllb0RRRnlXeHhHOHB2OGNDeWViTFJSWmhDd3VtT2JTTGpKanZ4VjJYNWZVRHM5RW1CNjE5RHltRFZiRy1j?oc=5", "source": "Business Upturn", "published": "2026-09-24 16:46", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Usha Martin announces Rs. 77 crore slump sale of U M Cables to R R Kabel", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQRm9ZQzlMNHlOVTh4ZmRiSV9obWt0a1pEblBGRkZMakE4WUU2eUxYODJ4di1hcmNsRmFSWHRVa2NkOVBIVUQzaTRjcmRRblE3bzBGcG9VaXUtV05EbGVodkxCM0lPV3QwNS05Zlhhb3hsQ1RCbFFXMjZBVXVHMHFDU19uMVBxMG0xUFlJeEtNcXJ3S2tUek9hLXFBWFBvZjNsMUM2M0t5MWwyTVAx?oc=5", "source": "Business Upturn", "published": "2026-09-24 16:31", "score": -0.494, "label": "Negative"}, {"symbol": "RRKABEL", "title": "R R Kabel acquires U M Cables business for \u20b977 crore", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxOekdBdkJnQy1zc05YRUg5aFF1a0lwT04xNl9vZlhFaUhGVE0yeENFRkdPYWp5eW5qNGJPQ1Z5M0tIQWJTMmVBZ2NIcG13ZTFtc3FJaE9hOG1SQVk2UENVdGNWTXktTE10MGNUVmpvNkxodGg4TS1KdHFlZGprNUpZMkRsS2x6OW1LcGtSVnJPQnFvNlpOaHZZbFlnSlZ0MGtEdjdSdzVvSQ?oc=5", "source": "scanx.trade", "published": "2026-09-24 16:21", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets", "link": "https://news.google.com/rss/articles/CBMi-wFBVV95cUxNNDY4RnFxUWdPN3hFd2xaaFZRMERxSGpxN2Z1ZjF1LWVVZXFDUnZlQzFhNDRUYkdVWW14NDRCdXZ2LUQ0YzZpNWVUQmxtTEtHV1UzaUw1eWtXYm53a2JYSzdFQ3Z0clktdUNZY2J2dE9MU2lxM012czJpUDR1R2ZkN2h3QXNIWGkwX3pEM0xNakt5RUt3Y3hrQTZPNW9yUVhDQnRCaUs5RHdjRVM5Z2RMTGc2cG10WS0ycnl6ejY3YWFsYkUyVzJBYVc2UXlvaVNpRkFKZkZmWkE2RzBxcWFMNElnR19nMFN6cmRzRDBteVpQMjlDVHlaVi1VONIBgAJBVV95cUxQbEJYN0g0YUZETXczaUtkbUdMb1c4M2lQaUszdUtyTXZxMVVYWENrRm10czlDRHQ0alpzSjBhRXMwVzVYUUo0djJYXzBQWlM4S3NZZXZtZTM4TS1zd3BVbEtHeExGNHVVcTI1eDN1VWZHTUQwRllLU0VTenctSGtMT09DTFpSSG00UF81R2ZsdGxFMFlGVFB5aTZLWGVvQ3RwWTVVWTV3Rjg0N1RKbTROQjdaVjR0RTRuRUVtLTFUTDgxdUVMOWVhOV81ZEhMbHlxVmh5Qk5NMXNCdXo3anhfSTY1SlNaSi1zSEtvemVYdjY4R2YteVlTRG1qX2wzQXFy?oc=5", "source": "Livemint", "published": "2026-09-24 16:04", "score": 0.7, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxORWVLSFhyVy1XclJaTW9wUmtOTF84WGZkclJHbmtIdW5oUXNJS2J2V2xqUjNnVmEzRDJJRko2Y1UzaVVuYnFOUlRyYTFzNFB1dTlvMXp0U3BTRS1rUV9pWXotZG5FX2xZVnI0eHRaWDhlLVZwaThPXzdCNW0tT2ZEMFp1b0FrRFVsNnZSVzVCTTd4MWZEUm9ERnJ5bTJNaGRIYlhYcmRGOE1ub1c0THBORGt4d2h6SnlBWUhFeVdSUDg?oc=5", "source": "scanx.trade", "published": "2026-09-24 14:42", "score": 0.382, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQnJ1UkZncDJJcTRVNElLd1ZKN1Nnd053YjRobGxJUEdGYUdWS0lvb0dHS2MtemJ3SUppQmZ2c0NERjFpa2szSjhMZG5BcGZiT3NNa191ZHEtaGRCNUYyU3FhMHBnXzFBUkk1d09ZNWFnNXJvZHR2VU5LTWkwMFlWU19xVnZkUkk2aFd1N1FBZm5xVVlEQmx6dVhDcG83MGZveUFrMm9pMWgydUlPMDFZOTB2RFBBT3JPdDRVYmdKTUtzbVBMTDFIbGlzdkhVMklTNi1aeVFHNjNBUU9RclRiSmtXVjRlakw2S2UzVlhlRTZvWWs2RFNoVG0wUkhrZw?oc=5", "source": "economictimes.com", "published": "2026-09-24 13:49", "score": -0.153, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "3 Indian Export Stocks That Could Benefit From A Weaker Rupee", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQNUp4b2tjbFlmWklUVm5zT2NJRjVXMm53bE5DNjJvb2ZFd0tFZVRUWHVxbWozaEp4aVBQMGtxZkpfQ3FmYnZtbEppcGtXZ1hYYl9seFIwdlhpczRuUWg0dE05REgyUkRMdXJpaVZDc1BORHVteE1IcHptNnNRbkdTY0NEUTZKZk04cHEwWTlNTno4MjJKU05aVlVOZExfd3plejl1cUxiVXlVbVNibjctMlFyOWx3aEZmYk5VNElFYUM4WENySTZGcmFrWURmdElfRjhyTm4xelJnYWNjVGtmb1I2NmxXZnRPem56RDZ2b24xZ9IB9wFBVV95cUxNVGN5NWZ1TnFTNUt1elFVSE5Tam8xZi0zWVY4Um1SX3UyVE5xNDZPZmpWQ2VWXzBsaW1vcnVzX1NoZXk0aWJjeU5iaXpiT1dTejAwSUt6Z3FhTThnTlhsa1ZFdHpfTG1sNjIzQ3pkZ0duUXY5N3ZqZU1qckxKVlZneVRJVmxjU1VrckJtQWlBNWRsNGdZbnRxX253TU56dE9NdXA0RlRoR0dLS0VDWFQ3VXJILUlrcF9OTU1lVk1sODFsbmVIeG1ROEFLcUlhWmswVzVkUjgwRW85cUNQUXpOcS1VZnBLT2pMSlZ1c3lGQ3MyN0JKeGlB?oc=5", "source": "simplywall.st", "published": "2026-09-24 13:01", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty slide on intense selloff, banking and financial stocks hit", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFpGdEFRNW9Ca3dPWm9LMWk5T0R5T3BvbW84R3h1b1pJeXdlTFJ2VzlCOVotdkVCbGhya0lWdFpFOG5oNVJ3Z0hoNEhfOXlwdmFCby1RU3NkbnZPVllMd0N2MWRYeDJoYnhOUUNxVXh3bFV2RXR1bEFnUlZzX3RkNnJfYUlwSWVtMXNFb2FPUWF5RWR3Y3JReUhHTmVuZW9xcTM3ck05aE9vazJkenhF?oc=5", "source": "The South First", "published": "2026-09-24 12:51", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPTmEwdzJWdUtmS1lTeHJNaEFsLUVRRTNTSU0yMko0SUJCczVmU05rb2tDckFtclNUdEJzbmN4VUw0TUY0aWwtVVlEM19wTF9BZ0xyZmw4Z0ZTam4wMmphemF0SjRoWWZTaXZOOGJES2dTWWc4MXU2djFTZFQ2ZmtnTGgtNFBvMlpVbFJUeGVCQ242RGpic3ViMFl5QmlzbE9ZMFBIQktpRXRkSWhmWVh1WWJYZjRYQ3FkcEJtOTVNUmZseW02bXQ2cDlheEVZWnItWGFrOU5aTmdDVFQ5UDJMUEI5Y2VSREJGSmRGdFY1UGY0cUJTR0FFUDNSc014endZb3U2TUN0dFdXQdIBjwJBVV95cUxPX2xOWkM1Q0VWS2w1cGpsMXpBUFVpZHZOQ05TMTBkY3BMRHUzcjVIeEdpRHBhYXhKNXUxSzRjZkI1RHpXbkRQdlpBUkdPS0JIVG5jcjQ4cGxZUnZndUIwX1VMVWlwU2c3dUZTNHR4VjZrUzg2VXd6UHFaYzdTV2xMRXQyWmFQcFdIMEJUN2pqcFliNW1tRHU2a1VNNnUwekE5ZWRTYTF6Sy1FbnBhNEQ1Zkh3Uno3QTZuTXVRcHVlNm1LVE5oVEJHLWRiMWFUeEo2ams0QU1ocjRRREF3Vkd0dXQ3ZC14cWNLNE5oM3lPMXNKelVjbmxuQjA0dURockhtcDBQS2gweGZ5NERLYVRB?oc=5", "source": "Livemint", "published": "2026-09-24 12:36", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty down over 1.6%: How crude oil, bond yields hit Indian markets", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxPY2trdk9wVkNJdnNwUEgtZlI3bHRDMDBHREVDSXNDaHNiclptS2IyWlJsSXdwNGpiSzI2UU5JdXRUVTdNdzVtNWRWX2lkbWM2QjdPYVVKY2JRWWV5VFVJdDRMRkNWYWFISWtzZW9fZFpmZ185ZEVDcTJRSWVYMXNid2JuQ2pBVnlNUm93dUxydllsUkw1Rk52a2tHM01BRV9GUEw3ZE9ycUpDakRCZExSdUtpVURfVXdPRzVxdk5TOU5jZUg1aFFfMtIBzwFBVV95cUxQMXhUTEhvMEZjRVVvWWZFS1d0OWtHdDg5TndITDAzRWpsZklndU9LenJUV3ZzUXZwWVgyUHRtdlh0NndrWEN1RFhoeU00VUtTRVRIM2NBU0hJM2hTM3QyRWlmOFNJY2diZl9uXzZ5SlNObk45blNQVWs1VVRlN0NBSjFHR2pNdnE3VlJEcUZxTHhWSTR3NnA2c2xuQnlMQlJpcWJ1dzhqWjFRMG9fdFpXU3JyZER4RE1HdGV2VzUzcTlUTXlOTWhKN0pqX2Rtazg?oc=5", "source": "The Indian Express", "published": "2026-09-24 12:02", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Signals Higher Opening After Sensex, Nifty Crash", "link": "https://news.google.com/rss/articles/CBMinwFBVV95cUxQU0I0M0hsemxwc1F3ZjFyczZ3aXlPOTFWeF84OGFtM0JHUnhwYm5ncVFDY085cVZ4QW9RbWNyRDB5UWVMOXNOUkpxLWxTRTRjd0RWV2drX3dibzRkVFh5STZNRWFxWk9XVmRFWnJWYWtialVpR205R19YZF9vR3JsSHYyMzZFcEhLTWVUenBqRG03ME1yTEpMUDhXYm1uNE0?oc=5", "source": "hdfcsky.com", "published": "2026-09-24 11:51", "score": 0.542, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex closes in red, Nifty settles below 23,100 on spike in crude oil", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxNRlVKbFBuMkxHMWVDMkdLbkxzWUwtTDdWN0hqT2xXdHBBR1dhb1Z3M3pUcThKdTBQN2kzS3NVWFF5QmUtVXozWERsQ0pnTlhpZXE3WUt3enhReWljNy1JbkR2Mm95Z3BIYk00Zk05Wlg5RUJ6elBGZ1Z3dWNDQUE3V2VBam8wYzlCOHUxdVd3MDF5dXVUcWV3MzFn?oc=5", "source": "DD News", "published": "2026-09-24 11:21", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE shares end debut at \u20b91,818, gain 1.85%; BSE slips nearly 3% amid broader market sell-off", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxQUlk1a3F2cEpoWGRTeFlUVGFkVlYwR1BZWUR1d2tXTGFldGNFMnplOEVRWnFLMWpMeHkwZnBRQmdrLWJjN3dNUU9EMHNnUWF5NlRDdVJkVVdnbkF4NHowWHNXRWtzMHNNZHh0U2dobTEyZm9FcGNKMFlyb0QtVjFYbzYtTWlVRmY3bkU2TjRWZnBQcGhsOC1uVm5RdW5NemNKclNISlM5STBJUGxEYzNrZ05FV1BPQlJIWnRrcWRBRUxiaktvVUJ3WdIB1gFBVV95cUxOT0Z5cDJfanFuWnNKN09YVjA2ZUZWU1BiWV9MSEt2MFVhVjNOMGIwaWpBdUcyZHhydjRnb1g0LVc3S1NpSzBmZ203UGRRMDk0dHZlX3hOOFktNFliaWlacU1Fa1g5ekNBY3ZfMUFFVEpmOVRjT0dzQ2JlUElHQkx5STljMVdrWFBBeXNvbmYwNHhIaW5KbkpBU2RXUUVGcjYyNlJmRFh6Yl9uNFVOdEJqNFhGbFhjd1R2ckh0aTJ2OUdtaGxqczRTc1ZvTzZrcFVPV1dTR193?oc=5", "source": "fortuneindia.com", "published": "2026-09-24 11:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "SENSEX Nifty Today: Nifty Settles at 23,063; Sensex Crashes1200 Points as Crude Oil Surges Above $105; India VIX Jumps 25%", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxQV2Z0WGwxQTlqTU9rcExhRjRqRjlyUkZPcDVjSHZRWFdUcWNqOXBiaThCSU9oZGVCWG5lblpxLWRzc3B0emFldWI3UEQwb2h5SnFJT2NFSXZ4N092aWhiYzZtTWZRYnRJWjZDa3MxWjhVTzFhNUxYLXZuUUtIMW8zblNKcXl0V2FFSm4tUVhmOHRVanJXZDNtMHY5NFZuUGEwbEtsdFA2d2p5VFBzOGNDcElwVHkyQ2htd2F4SmlOOUxOU2QzYnJZTEVMZWxaNWh5dGhJVERiNzhsUDBEUExpcW9xeWltZW4wRlloN0xtQk0?oc=5", "source": "India Infoline", "published": "2026-09-24 11:01", "score": 0.784, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see worst day in weeks: Why was market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNTTMxLVltQWc5MkFQOUFYNlpYUTlLRnVtOWFTM19ETVhBaDduYk9pa3VKY2lIdGNGTkpIbVVKaDNkV2Z1NlBvdUVVeC1JbTNJem02eHlvdHRvMFFkR285ZjlFWk1fbXR2Z29HSnNVVklmYnhpOVlHdUFxeUFuNmtXeTZFY21KcGFraFdXRVBfNWZRLUU3WEhhd0x5OGxkRlRCbXR5T21JNDRpWE8tSU81VGtxUXFqUzl5T2FrS1dXd0s2QkdoTkRlSWJFR2lORk1JOWpnWHhvanB4bEdTaS1aZG1sbTJfUDFManBUNNIB8gFBVV95cUxQaVFGYUROS1ExTmNWWWI1RHNoTGZfWDd4U0hPeGVCdzM4eUtkZXVMaGZSTXp3NDZEcS1POXpFa01KQlNtY3U5QWgtdl9VV2hZY2VzZGp2U1pQbE5sT1JoQkZJeFFqT3VMOENGMjFXM3dRajdZdTVJMVpIWVVubzJhbjNyakljV1BrTl9vVDh1Nnhnd3VqdDJBbThXVDY5ZjBIZXFKZ0ZHUkt6eF81SHJEbEF0YkJnVDQ4clNuSFJONkZRRTkwZWxLaS1QcEVwVmRqQURkTlpSTm14R2Z4bDV0NEhMMzVJdWZ1TzhaRUlweVQ0UQ?oc=5", "source": "Hindustan Times", "published": "2026-09-24 10:57", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex Crashes 1,200 Points, Nifty Falls", "link": "https://news.google.com/rss/articles/CBMiiAFBVV95cUxNS2k0X084LWJ1bW81UDRhNWZrRkRQWG4wNWZ5UDhsU3d3dUg2NTc0c21RN1F0TmVuSzYyMzBYTHBwOVdIZVJEV0Q1RTFOaWF2Qy1vczJwOER2SEZBZUNHZmF4aC0zMGJrMEhrZVhlRUQ5N1ZBVV9TV1RFYVQ0c2l4eFNidnowaEhJ?oc=5", "source": "apacnewsnetwork.com", "published": "2026-09-24 10:44", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex plunges 1,248 points, Nifty nosedives 1.64%; five factors behind market slump", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNcE5taEEyeER5bklLZHdwdW8zRDJUR1U5MVc1NkNUc1hvV3doWnpCdU0yZUVINXhHS0szVElxd0swUFJqLVR5dGJodVFSUVVzdkd2ZWx4TGhjdnZVVGlXRzc4OUN4T3cydFhUb0xXSzd3b0RMMDFYS0FYbU1zeFFtaHpWQ0xXUGFJd3U2WG9CU0QzWklrdW9tQUphdXVkSXY5ZDNzRTJJaXBQcFdCT0x1Wmo3WkN0ckVSUnIzSlBqc1jSAc4BQVVfeXFMUG94Z3FNM3BuQ1V3ZDZhTm41WGUxZE5ua1lyRHVCMVJJZ1hiSjJuY1gxZXNoaUcwMWhfSXZ3ZlhrOHpXTlFHU0VDRTl3UUJQdE0tc0NtSmoyVTlNSGhOczVLREF5ZmVUbEpwV1VWaFlWYUNCTzdvUi1OLWN1eV9EYnFpOXNaSEtiVzBTMG1XMHF2Z25HeVpFQW1PVkxmNDYyMXZZTGRWaDJ3Y1pQWUVES0dyYWFTWnAxZS1XV1ZSb1pzaUUxdEJObTFlUzBmRHc?oc=5", "source": "fortuneindia.com", "published": "2026-09-24 10:40", "score": -0.612, "label": "Negative"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNb1U1UU5HdEFtaWZCRWdVRWxUc2pRMFZ2YXl2bUpYNE1xNzZBX01tTXNtQWc5d2ZCNTdzYUZwXzU5U2VOX19rRndvYkVDaUl3aGVqQ3lyU01qYkNtVENjRG41VW9IenA4V21EcDhLYWFrdHZPYU9yNGl2RDFSUEdRcEtObWtDS0doZlo1V3ZwOGcwcmRROTcweDNZeTZaRGdQZ084YzU0amppMUZaZERQamg3YUE3RF84TjFuLWx6T28?oc=5", "source": "Kalkine India", "published": "2026-09-24 10:15", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock markets hit three-month low: Sensex drops over 1,200 points", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxQbVQtWXNPU09LRktkUUs1eTNpTlNka181V1FzZXR2eFYwT2N5UlFwMGxoS0ZMVDhxaU1GUVpSaFlxZmF2R3RGME5oczZnSGVWVGhQVjdaU3Ffdl9GZWp6NktOa2RKUXY1Y29xZjUzVUNlM19yOWx0R3dhbHF0NUpGaDR0dHhidWpiYTNzLXJmY2pOMk5SNkFTekVweGgtdkFkN09wX3dFVkhoZVUxMGtvbDFnbDNvZ9IBuwFBVV95cUxQT2h1VGV3RW1Mcmh5Z09qcThNaENiZTlLVjNhYlYybDY0c0ZKY0lRZmRsSTktRzVfczlRSGZnV25kM0FHR2w4U1p3NmtMdy1BOHhTZjFlY3dVSmRudk9vR3cxdGFWNGFxQXNRYjRhOXk1OS1GUFhqb29GS1VMNmdSMGtrTXhfQlRnY1dRQk16QlUtQTJjcFZtbk5RSkZ5Ql9XeFYyQmdIemRkQjZOQU5vQkxGRHZkVEF4ZDZj?oc=5", "source": "Telegraph India", "published": "2026-09-24 10:06", "score": -0.402, "label": "Negative"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVTh5Q2ROa0YzRWp5NS1Kamp3NnMzYnBNRlJHcEZ1cVRnOG1aampUb2pFbERqcGNPZjN2WGZqNGd5dWNDN2R3bnhXQ016bjJoUXUxN2FqcVYxaDFrSTlwZGpSQmZIbGM3THdoMUFDX1hwZXo1OHNPTjVpNFhLWVZudVFHU2xxbmZ1aUFnWXZqM09tZzZ0TVlRWUwxakpaM3JIUkg4QlBBaG40QUQzTWxYYzNSZi1uVVZtWTJHVU1UQzhDWHB5OW9Fb2JHS3ExdVR3dExkMGJRRVRQVmZfZnM1THUyOTdWbWhDaWfSAe8BQVVfeXFMTUFnaWZmYkVLMzZkNk5ZRXF1ZF82LXluT0hoSlJNZ19kUVk4VHlzLXhabENVbTd5LThnUlJIc215aVY1T2ZwOThSS0dVNnJNTVBIdjgyQlBPQjJaTF9sQnZWeEw3Z3dVdFVMNnU4ZzBWOENQQ0dtZ1JQal84UmdMS3FvdEFJUFdMbVhXQm5tM3JYNUJhYTFFRnFtX2VIaDJMcWNPUFhpaUs1YjRSbG1lWWVTYng5VnNjbFF4Z3NqVWFHWEd3eEMxUjE5YUFQZ21qdVJJV240Q3dsYTdHQUhKTjVGcnk4UWRhd3lEdTJYeGs?oc=5", "source": "simplywall.st", "published": "2026-09-24 10:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "The battle between India\u2019s stock exchanges is heating up again", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQSllxZjNuQ0l0ZExkQlp2RmVURXBuMm5WRjUyUkZsOXNaeF90Zy1GWXMyZFAzYmlGMGFfTWlhSl9lT2JNMmVnclFGYlg3bjNZQTRUeERZRkFScXBYc0IxZnhEcUF4Q0tzcWhhQTZXaXR6NjA5Y1pTSWdDQXBPQS1HZWpMOWJHN0NzN0lLWkdiMlJWWjN3OC1Ha1VDQ1ViSE9QTmZmSHBYTVpFM1FiUEJtZ1B4Y01nd2dabTlwTw?oc=5", "source": "The Economist", "published": "2026-09-24 09:42", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPVWZGNDlpWFN6MFJFZVZMVWp4RnIxcTVXOTRMUS1oVnMyQkVmZkF4eDdQTGYxOXVKV253c2dWUVZrOFpQUEEzdUQ1Rm45bG1aX01RSzVBNjNIWEFIb0lLbFJsSWJNYzFzMVFaVFpXUnAtR2xtZEZ5YXhjdXRSOHI4ZkNVMlJvWUszcWJEdGFBWmpqZG9zaGJWRnZGMHFtM0J3OWluTEZMVE9xSkV0Q29QTnJFQzEza0ZQaERRWjNBaEN6QlpkSFdMcGRuWndIWE1RVU5uczhza2w2WndRYWlUVkg3Yi10bUJFLWRWTE1sT2I1NnhwVTdCa3ZBRmxpRklNbGtzbkQ3V1licnlmakQw0gGUAkFVX3lxTE5pNjM4R2ZHalBOWTl1aGVPaWxONlMyd2lmVERYa0RZeDlDMU1IbnZMWnhNQ2VuWXY2dGRTTlFrZVFrU3RmaUJtcjZxNnlVNXc0eU4wQjR5Z29zd2FWZVRoM2FVYl9BY0xldFp3SDNjYnNSdmRwdXFYTEpxcWM5WWFrbHZCeDhZZ1c4ODE2SWJpX1RvX0dkX1VHemI3dmpJem9uWWJsNU1Ia0JFWmxobTRWMjBFdktPS0dsZGhlVjdIaVh6dFRhU0FERjk4aE15ZmlNR19BbmlCei1FRHV2TXNwV1BJaVRHQmxSZnh5dGotNDRaUEpUZV9pMmR2STRRbkhLUHhPa2FMelZzX0VfdXJMOGVoeQ?oc=5", "source": "Livemint", "published": "2026-09-24 09:40", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZ3RITnlWRlVoLVRXRW9Pc1NnU042UFB5V1BVM0s0QkFvcnRjbElBRVd1ejJZQjdSTmNfM19uazFjYnZFbm9EMmhxVU0xYWtsd1dZNldfbEFJOE45dEVDMWw4TUVwSW5LdkVfSHZPVnZsRVI4eWhyVFpaQW1mRFM0UFUzZDhXaTB6anpwWDlSSk0yWjlpZ1Z4WEsxd3M3YklFREtEbi1TNXhEUmsxYUVyWXlPTHNxUXJVYUxpbV9ENkEtNURlYnlPcU5lTnBEbjRMVGE0SXdGRTd2VWvSAeABQVVfeXFMTVVqV1N6TXB3TXJhak1kUURlODRETFpFX1NBa1RRb1oyUlVNd0xRcXBHU2ozWVN4dlQ2N1Y2WUhpdTdZQk1NWWNYcDB4U2ZneFRVblBSajlpRmlzLXZWMTNCeHdIZG44a0ZMandxanFjTW5qTHpGM05QQ1Vxbnlsck51UjJhMkloS3dPaWstcTFoS3Q2NEQyRi0zQVhITkp3NzdWRnBkWG1vaVdWSll0SGlsdXRiaUxWc2FUVk9wMW1ZZ09tRlRCa3RoQjNONFhvQmdyN25tVWhBVTBEZmpuMnQ?oc=5", "source": "CNBC TV18", "published": "2026-09-24 09:08", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tumbles 1,200 Points, Nifty Cracks Below 23,100 \u2013 Key Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxOZDg4Rlc2Wll3UERfQk54T18wVjMtRkRwQmNBdk14N01wLVprZ2JKVUFKT3ZkZFMtVGxCbVJUOWJtNXNJX21XcW1pNENSeml0X2NHODBIT01aREJpUnRfZ1hfVU81UHJub1B0VUZUS2htOVJnQnFDMW1QbVFkRU5MQ2tnaHVxcV9qN1VzOHFWM3hiVzAwN3ZYRVVoSFVOMUttVWJuUHFHbnFyLWdkU01nOWp30gG_AUFVX3lxTE1SMGlha1duSXRtSDdZTmRfc3B6TVNsVHhOM245YktBZkdvNHdPWDJNUUpYQ2F5VFB6azB3YkdMSk1tMUppSlAtbllwQzdWWGNBSHcwSEpJc3QwNFlrMFZuLXhoZnMwSU00NzZrSnhYc3pqNG9WcDN1ck1CWG9ad1FXVU1tcm05dUNjVExQQ25oU1AwRDRUaWJ2dmNQT1R0eFBPTFNlUWR5NUVjX2xaa3paXzN5cUpsQVFkb1BLZHZF?oc=5", "source": "Outlook Money", "published": "2026-09-24 09:04", "score": -0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxNeEtEbWlBNTFIcHJzRV9zU0hnQUd4MVRma2VMWXpOdDl3SURrMGJPOXBnVnFOTm1MLVpMMFAzYUhUWDJVYnpYd1cyWG1xUjhxOVdkb0tVNkF2VnZfZktsRnRYTlNjMzBYblcyM0pHRUo4Ul8xVlFoci1JOXpSU2F2RlBkbFJaZGhTeE9yODV4aDlnSDdKbjd2c0ZKMzc0Y2JFbER0c2hDNW1pbURITlcw0gG3AUFVX3lxTE8xbVZoQm0xdm9CSmg5ZVBDMVluS0lTTUctTnpYYVU2S0RxcFhlaUY5Qndta09tY3VuZWI3MW1LRWlPNVl6QlY4OVBFcENPZEY4OU9jMThxdzM1cG56U1ZtN29HNGEtZmZ6eklRSXlNNERlUVF0dXNjVXV0dERKeFpyeHY4YUV3ZXdWYWhjcWsxM1d4TWtYOE1tUjRFQ0xKQm5aWHJhcnJfSHFha1FDeUJpSDdJaWhrNA?oc=5", "source": "NDTV", "published": "2026-09-24 09:02", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxNT1lNOEhqOHFBM0dUS21nbjEzUDVTOVY0YnkweVp1T1pQdy0zTG9LUmppQkhYTGtIZXBSTEtiVHdDNjZxWm5FM1VXYUl5Mk9WcklBS1p0NWlKY1FUWDNqUnlYcDRrTzI2dms1NVNjenlmQkJZdlIyQllHaEF5VVU5OWE1OFgzeE5jaVdSR0ZfNklZOGpsMGRyc3NXcEdsdFVGRl80QXRsZUhkSDVWbXN0TlRKNjJXSkRSc05IQnczMlpyYXJwYnV3NERXY3BQRjdJN0h6REx4LVo3S1dLQjNRQlpNOU9zX0RLaUlxNXUzRzFmTEdGakNJTHotX2cwX0hyb3lMVEZmR0PSAY4CQVVfeXFMTWdFZHhRbFpBMnQtazZaZUpQVk9Ramd2ajI4M296WDFaazhGZG1OV1RmeGRqcDJkeTNsWC1TYXNTbWtJa1RGRktmREpwbkpqNFYzUlFIYkR3ODg3RllZQTNWZ2h1ZzBLUlU0WXpYV2ZlQnN5WE9pN2JCV2sxbEZMdjcwQXcxRGE2c0lLSWdLVHJVYTRuX2gyYnV6MFlPZDhMUmpzVHpUUWk4WmJYNWtsMnRZSTdmNzBzdnhGRzNRUnN4aTdrakZ5QlJ0aHJsaGRGQlk5NFllakp1bHByRFpMbU05S2tqWFExY3lQYkVlUjlyX3hTUXpmRFQtVmdocWFJMG1aQ29LTHNvb200Rlh3?oc=5", "source": "The Times of India", "published": "2026-09-24 08:52", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 3.93 Lakh Crore As Sensex, Nifty Hit Three-Month Low", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxQNjFHX2Q3c08xMDdGUlpra0RVekh4Zy0waWJXT2cxdDIwOG1TYmJnSjAzMy1tVHowODJaQ2VRZTcxWmg3bjhLa3hrRHBEMktIc3VmNmFWSkVvLUhoM041UkM3WlNpV0NfM3pqT25YVzlvZjZDcE1FY2IxeXpscDBJVWVuUzNobzFPMktQbVFqdVhQdXlwY19DbUpnbUFweUFsZzdfZmxZemUyTUlZSkNLekJfT21oMW8yNjhuMzlTM1BLQ3RsWDlyWmxrQVlxc2stSTFSaG1DRU_SAeABQVVfeXFMTmlwcURVb0RtR0lWNC1MT1pvbUdtUDNMd3hHM25oUUpvNmNWcmdxNEpLR3VMYnVRU1dkSDg4ajN2a3NJMFppWVdkZ1R1LW1SVWxYa0ZWUnZkb05NeGNoZHZ4cFpVWmpwNGlLaWxxM2tFQnpvRXhaMWxIb0VkR2QxWjdTUkNOQTBqVG50Y0Nqb25ycWNTVEgyQkRHeG9hUkpPTUdPTjNLTWtiV2VlNFA5RUpWWllaY1dldUNWeGUxSmx1Y19Mbk1CeHhRNHpUYmZjaTlhR2VrS1RsbnZJS09pNDU?oc=5", "source": "NDTV Profit", "published": "2026-09-24 08:50", "score": -0.758, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "Hero Motors Ltd leads gainers in 'B' group", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQSDJtZTVDOFZES0ZIb3BKUnlmdkV5VTlSc2doTWJUZ1k3WEhzVDNxd0doUHI2aFBOUG9FRW1hbUw2bTBKb3FxYlNxZS1kM2VvaWtpcnp4ZEJpa1AxQ04yN3QySVkwS1dUZ3YzVUo3UVlIdzV2eE41ZUdJOWs4cTMtS2ZQNWdySzltWE5CVVFQZTZLdVZCaHVxTDVYTkJKLTE4ZWQ2SlpuVVAxNFFSVVJKYzlhT1FxMnYxZ0dKUDUwNNIBxAFBVV95cUxQS1NzWTc3QXZDVEZ2M1JsYlh1RFVzUjdVdHVWdVFrcWMyRS1zdVRJajBxXzdvSnVzWlZCQXRNbDJyenM5SDJwUnRMcW5BR3ZCMnlKbUY0dTdiVXZMalpuT1lsOHJoaFZtYkhkY2lIbVVXOVJ2MkRoRE1pa21xNU1LWUtYOGpEaVE4VFhqdElqLXVRZ1Q5SHNLVGJfN2VPNUtLT2F1ZnhMUU1hMjNXSTh1dzVZS1d2VE1fQ25BcmZEcVhTVGxf?oc=5", "source": "Business Standard", "published": "2026-09-24 08:46", "score": 0.557, "label": "Positive"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems Share Price today: decline and analysis", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxQcUhUNEJMQ3ZXeU5ZcFk0aUE1NndmWmVMR2E0MVJuM2RhTi1QRHhxT1lZRTZKeXp3NEkwak4yQ1RPVDBDRDlXUlJVUXQ1QjVIMURYTEtsZ2lXVW52SmR2VzZRS3FHanh2RklUTlNTWElScmtkaTdGMGx0SWIxdlF0YjlzVTZzQQ?oc=5", "source": "Univest", "published": "2026-09-24 08:35", "score": -0.382, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNYTRVYTVWR1lSdF95cG9QR1FLMk9SOTlCWVg0NzdVR21OeTdQQXJYc2UxbkUxa2I2blpPOVRYSmVCcWNaQnVxSnpvX0RGQnhZdmp6X1JXRGxXaVk0dXZnRDV0ZTJmdFNMTzUySWNXUjZ0OWN6Y2hwcHY2cWRxLS1hZVRpdHpISHpjMnl6b0s1M1J1bHR6LWNTd1otbHEzM0ZRV2RHeUNEdmY3X2t6ZnF3YkNyRHREUDA?oc=5", "source": "scanx.trade", "published": "2026-09-24 08:21", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices", "link": "https://news.google.com/rss/articles/CBMi6wFBVV95cUxNcnpYS1l4a05TYTZaQUM2enZTYmIxVThMMmd0UzZaSEczczdQSXhEU0tSSV9DdXFXdXE3SUNBem5BRV9BMUFlZF80U24xWHh1ZHM1SkRjU1p2a2NvM2NuRjdMQUswaWJkZUV6dVp1ZzVrZC1jZUdkX09JaWRSNWFOcEdOc1JFUVNRcEdfVXdYMVF4MHpnTl9zRDhLQWY2NVllQzkyMXN1Y0YzQzdSUTFoUC1nanVwcEhzNnc1NDNtbVZOSFhDVVpUM0F0ZG1VemZSZkF3eU5FSldzSEFLZGRBell3ZVA2Y01JWVhv0gHwAUFVX3lxTE1XVE1JUmZXOUd6YURZeGlua2c3dEZoZ3NQdWY4SnB2RFVOa0dnd012UlV5Mm16QmE1c1c1SHppQ2luZHZqU3lfb2llTkxTQmN3MUlpejNJOVVYb3BCaUQxZ1RSWEZBWWFwdjVlN2ZTZWVyTGZhdjVfWkNtUG50SkNhS3hNRFlFbHBhMG5DMjZXS1FGVWJnMmUtVzJueHhRa1IxdnZpaGVuU3ZJYmhUVXFGUWFNVW52ZGxYODBxWFVzMmRnNl9PMW53dGJ0Qi1EZmRaUGhzc0FLZWxnejdscjFjRDdUM0UtRWNpa1d5bm5JOA?oc=5", "source": "theweek.in", "published": "2026-09-24 07:35", "score": 0.077, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom \u2014 Ask Profit", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxPcjBhRnpQaFhkbGdfV3E0ZHlmUjFPQUlUQm9LTFU4UnFqSHduWnhNSEcwenhUQmM5LUxsdFNwUXN1S3gxZW9PN213QUx2TDhzUWpoNXJldnBQRmI4eTBIOE9JMGdqd3I3T2F1QVVYcVZSUF9jOEt6cnB3QWhmZ3F3Z202eHZkRXM4NHduSVVzLThxbTQ0aUJEeEJlTThhWHBFMkJ2OGJ5X0FXT3ZyWFR3MGlZeWEzWjJGU0hhejlZTFgxakpDdVVtbkV2VGJtOXU3aTh4Z0lPdmtneU5EQTNudGd30gHqAUFVX3lxTE5SeDJuQlhJbTcxaDUzbWNPNjNuZDFqLTNYYmEwR0o1QW43WVdkLW9FQUhpVExqaFluQjJwYWRVcG5NcE1ELTduTUxUVTJzQjhvVlN5YWJKa1AxaEFjYnIxempBeUNFbG1IeW94YVMwanoxOHAzNHlRSnFUbWJ3anJqQWVvb2xQeVRwZl9CQUwyUl9KSXhhTm16Qy00Uk5JdkhGU2Z5SGRzNkthQmRBN0J5WnE5bFNUREhuNC02SklqM01odWNqWjV1YTVsVUhXUUZMdlhkN09kWTdvbHhZUjFXV05sVTlGQkptQQ?oc=5", "source": "NDTV Profit", "published": "2026-09-24 07:25", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE Share Price Rises 3.45%: IFCI, New India Assurance, GIC Re in Focus After NSE IPO Listing", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxONVA1bWxGeWxFRDVpLUdnQzdZcTczTFdyQ0VNeWFZc1dUNzZTME81V0VYb3Q4eTc5a3I2MjE4aTNUSU93SWdIU1pXaHF2R2xZcjdoMDd5UEkxNnlZa2R0TlQwdkltYjY0VmhIT2xSa0xpcXp5bXhnbWJzcmZEUjJOMTQ1b3JYdmMzX1p4bEs1WlNGci1OTmY2czBMaGhmem1hVTRxcVJvd3EwU2tJY0F3c0ZscU9wTGZrdWZJN2FnQjNMc1I0eTAtSDZCbXBvNVk?oc=5", "source": "India Infoline", "published": "2026-09-24 06:33", "score": 0.34, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxOU0F5bUI3X2RaNWllcFpuSUpqZFp4Ui0xRVNpb2FSbVRfMjZieWxhWGV5R2N5MHpqeHBQcXIzT2dfTHBjZUt4Zk5aV2Y2SDNhM3VjamJBeTRhUjNjVklyZ3lWZDMxZ3hMMjNXaHFHWUFKV19ZaEp1WTBQekRXOU5ZdXc5UG1hQkIxRTJWdU9USDZqekc5QTh5VENqRW1ybVVCYUMwODlQRGJGVUZKV28tSVpXMFQ?oc=5", "source": "Kalkine India", "published": "2026-09-24 06:20", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Tomorrow: NSE, BSE Open on September 25", "link": "https://news.google.com/rss/articles/CBMikgFBVV95cUxQV1U2SUpTNjJGRW15cXVTOV8xLU5RUmRPRWtLWDJjQ0pSR2pLNkhXV1RGbE02MzNtZXRRVUo4c1ZjY1VrYy1xUXNEc1k5UGNIQlpxc2JsRVo0bHdmUmVfbEpyVTR3MHZneTBvYnlMX1dpandOWWs4bG1QMlhuOVBCT2d5dnVnVlJXU3ptYUVwQ2FKZw?oc=5", "source": "hdfcsky.com", "published": "2026-09-24 05:58", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty in Red; BSE tanked over 600 points", "link": "https://news.google.com/rss/articles/CBMizgFBVV95cUxQUk5oc0h1QzJkYXEwczVTMGwyc0labGN3T3RaY2Z1Sl84Y2xMbS1KQmxiYlFtWGpwTlNSM3ZMcUhCby1GaTNlc0RxTUNMeUJNT1ZIX2xUbnZGQTBUN1ctLW83RWhaZy1UY3JkWWJIb3d6WnNHTEVHZHZqcTUtRHZCWXZWcmtPV2xUMWVSM3hvamktNUxpY3FtU0RyUEE4bHpNcVlVdHJiSThtMzFfbnRFandGR2hvOTBrR3VscTU3clkzVHF5ZmFCRGF3el91d9IB0AFBVV95cUxNb3JKYVNUNnVBWmhCN285VmZjSXdYN2hwbDUx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ZnB4UmI0X3dWNzhLd1BCT01UY3FuaWNyR3FfaU5ITzZONkYtVDV5bFBORGtMTnFBLS1qWXRoUnhKWXNnOHUtUlRjUU1XZk5rd1RJWm0zR3p5dE0zOE8tdHloRm5lR1I3Z1pTenBTcTRvbExuLV8zajljWnd5TWpBdjNKY0ZiV09aQkRmRTZKRnNaNDk2NENidlVPZDdFd0VpTGVUa1pkdnlGWmtySXp1OGxNRWhN?oc=5", "source": "Rediff", "published": "2026-09-24 05:29", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex opens in red, Nifty below 23,300 points", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxONWRLMGNIYkVlWTZiZDZSeDY2ZGpFdjJZWVRaNGlkLXc2M3A2eHRmODhwLUFvZkVBS3NRQUJzNlIxQ1BkbjdtZTFWYV8wQ0JVdUdIcEVaeDR6STlfOVlqYXVwOVZPQkdhZUM3SnZ2dVhVLVlzeEhNQmhjcVpPNkM0OA?oc=5", "source": "DD India", "published": "2026-09-24 04:55", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex crashed over 1,200 points: Why stock market fell today?", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxQXzVxaEFRS2NOd2NZVUNtWHNQaTgwaVc1bGJhLTZVWVZFTjREMnJhVXllcllTYlZKTWM3TmVudWo3MXVfcnpTazhIX2RZWWZ5YjJ3XzMxNnZkemlkMjduaEExRXVRWjY3M2ZSNmo0c3BhRmZsSW82ampNRVBpVkJ3YWtvWVFSM0pPcl9tTGlKVDF0dUhNYmgzN2MtWTFGWHBpV1liRHFZVEYwdURaNkFiNnBaUHNoVW5aTjhOVG82Qm9tQXhIV2VqN0RWT2gyYW1yb0xEdEFpdG4ya0tFOVVtSTQ0aWdYQkQyS1liNWJOelMzdFXSAfgBQVVfeXFMTUFQcXZjUk93LXBGOGZqOHlmcXFNR2RoSkdCc2F2bVdPM0hGQ2lqQy04bG50MzZWY0JoUU1uRFFlME92NjFueGpyNFpBREFKTC1pMzZ1eGJlSWF5dGNjVXlFZ21JS0NjZmYtNWUzVG02ajRXbi1nWWtwSktpU3VxektCa3BpbTI2Sk9fZUFKbUIzYkM1V0tScExKMmgxM0l1SmhUTkpMYXVIMlZ2R1I2TkJ5emtlQ3BNXzBfWTRERkNLRW5tYWxnNjdqV29GUldwMExmU3pGaVJ5LWNaZHpnQ2Fsa2p3dE03QTZCU1c3Zkt1QzNLSWlyUk8?oc=5", "source": "India Today", "published": "2026-09-24 04:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "NSE vs BSE: Which exchange should now be the preferred bet for investors?", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSmpuTmdJXzZWT09uMUdJbE9vWlhudHJoOTluUlhlaFV4S0FnMExmQnNlSlp5b3hteTlQN09Td3hDRG9rUDVEaDNNNmFjcUxBVlZCUEpOdmtQNVU0blB5bnN0VFo3MHkwVjItQ0c3c3FIekxwd0N3R0xkU29WMFBfZzRkUE1KRWViTnU2TjItSlMxQ0hJVmFPdG5VYmVGUTFBQjJoY1A5MWxZS0N4MUdTemxmR3lfR0pfQmVuQ1ZCTi16T3h5ckVZS0dLU1VPeDlsN1BNZdIB2gFBVV95cUxNbEV4bVZySUQzYW9GWmJ4UzJQTE9NMU5zTGhnX3g2TU5tc3FiV1VkUEpTenZpblZfdFFOOWhNbFpzYU9yRTgwUGQ1LXFUSFZIR2VTYTZHVzVJWE91UGppYTJpSTZ0bV9jNW5iWjl5OUVxOTQybGlQREloMVdERXpnMDk1U1hCU3lxNG84bEY2V1N3M0MxNDJnMEd2YlJHNmJMbWxUcXRHMmg1N0tjVGthTGdmWFZ3Ykg0UE1TWXkwZmpjUXpyVFdxZ0YzWWREMWU4S1JSTWp6TnJUdw?oc=5", "source": "Business Standard", "published": "2026-09-24 04:31", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian Stocks Slide At Open As Nifty, Sensex Extend Market Weakness", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxOdFpaMjRkMHFmQl80MDZYRWhpSFRCbGtlcGRYbEZHV3ZmaTI2LXJoTHdGcVgwWVg1dWZXTUFaX3dFbUl5ZDlRVjl6QmNvOXAxeXM1Vk83UnpseUQ2Y01IdnhCeF9RZEV4bkV6LTB5N0VnVURTVUQtQkF0QnoyZEQ4djZ3VXZXREcxNzdvdi1JMGVMdXlfb3MzYWdSOW1qbUtlQ205NHBzWmdqWmJ2bmxxZF9WUmp1cXFHVlNoSWtNMA?oc=5", "source": "Investing.com India", "published": "2026-09-24 04:12", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'", "link": "https://news.google.com/rss/articles/CBMimwJBVV95cUxNblY5UUJKckZ0My1hbEZrdS1NbjFpR0Vyam1YUHcxd1BSMDdzWkpVZzVyN0ptcnZWZ0EwRElGTEdLV1pWNFd3a05HeEpBOC1UN0NCandyUjlzUVpsUXpKZElQajdHYUoyc2dvLXdMVkNQSW5lZHNFVG1aMzVJQ0tUcENOcmR3QWIyUFNWOFo1RENRX29SbEZLVmNGdVdjSVdkYVZyM1l6dUNtaE9KYjk1VmhIVTlWUlVZNUVFekwwRGZETkw1NTFzbWhSX2xVc2RTdzdCRExjMW5LZ05EbFZRODJvcXRnbmpKZGdPRGlpeGgza1BVNFA1V0xkR2ZJUEpCNWpPZnh5aXR2MW5aQ1EzTEJBdGY5Mi1UTkZF0gGgAkFVX3lxTE9GWEM2U2ttbzdkc05MdlJqN2tFU2pGUmxYbmVIeHktdHRhWVpuaWRnUE1RN01WREtsT2x1cTBBbExxTi1sRE93d3FvWDljRGJzWHNxMW9jek9KTklxUEdnbUk1a0t0YXdlMVZvbzc4Mnh0c3hUUXMzdV9VOWV3UXdqSnRQZFJNaVNRZ1RybmpKR19rS2dNdm5HVkNlUmRUTzJrbkRuYy1fR3pRLTFLUDBZcVAxMjRrdXg5ZVF2M2NDMjgwTXZ4bktqUXNidVU1dmJKWXEzUi1NLUwxUjliSG1vU2lQeWM2S1lRdkMxbW1qSGI4M1lpSHRVS1FVXzNja3B5Q3BYalFYLXV0T3d6VXlWVVdEWTdfUVRsWFV0RlVkdg?oc=5", "source": "economictimes.com", "published": "2026-09-24 04:09", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash: Nifty 50, Sensex fall 1% as crude tops $102; financial, insurance stocks slide on IRDAI proposal", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxOSkVkb0huSFhlbmNhN0psN1BPWVZOVThiUzlnRkx3RHZPc2plTl9CNDY3WDJoQUlNUUJ4Z0xXMHE3aU1Xb3k4Z1FUanJId3VYazRKZ3U5X1MzS0dUYTRlUXdTRDk3eWNiVUcyU2ttbXMzQ0JMSXYwZUFYMlBrQUZrRjNFT0V3enlTcVEzeGlGX3RORXVJTHdfUFhxQzdiYm5KWVJSdFp3Y3ZNSXhyTmZyekRESHdkc25NdkRybmpvVm1oRTdBWk9jdzRIVGlGdUNRZVNTMjhjQkliUE1zbklBMldjRVJ0a3QzN3hObHYtUXd6X3htQWozdWh1cE1DYVpvUDZBUnJvc3ltNnRC0gGSAkFVX3lxTFBPeHBSMFNDSEJ1UEVjaHNKbGlyd0lkY3c5cVYwT0M2OGFqREFwaEllMjFtanlXZG9iRFp2SnVOc0F1eXhka2tDek4xdXVQYWdsTGlQSjlsazJHcFVyZXN0eU9RVktPd1VhRXhGakFja3Q5amp5WUh3R2cyT3k5djdvU2pGRWk0Mk1FVVZPbTdIT0ZGcGdnR2hXbWdUaVEzdEU3bnZoMVpuQlVrUWIyQjBnMTZqMW1pTldyWDdPLWxYem4xbW1aeWNiTk9hTDRXMlVlLUM2cy1WOUVJTERGeU9zU0ZJa01oeHgzZklKSGRRcVZEbUlHZ1dIQjhkOUFNNjdIaW5fSk55eWd0bEdKX3Z5WFE?oc=5", "source": "Livemint", "published": "2026-09-24 04:02", "score": -0.599, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxNNmFnZnk5VzNtcVFkY1JFVlVCMFh6T3BlejFod0JXRWFjMng2alROdHU2YzRmcEVCV3VMZFdYM3hCbUFCa09PVmVkWTh1MWFaaUxhTndsdjlVb3pZZy1VZU1wWFl6WnNvUzUyZ243ZUQ2RUVIMEhVbm8tMWxWMzM0Y1N6aVlPenNvZkl5R0hmVG5JWlE2QkcxNlRDd0UwU2RSN3NscF9PR2NRVGVaRWYyVUpMeHFrYWNVcGdMNTM3MmpSVGdkc0laX1E5U2U4Q0pBM1N2cUNlQndvUGRvUHVhT2w3Qkh0UHZ4dkcwVTQwUkRMMHlY0gH6AUFVX3lxTE5jREhsTGtRRUVDMnRQMEhucHBndU15SnViUmVFb0ZxTUE1dmpUSlBMV01WYkZ6UXd4QkRncTdNZUh5VVRxNEQ1cmViQ2Z6WFViOVktS1hld09jM25FTHRYN0lJa3d2Q1NsWUxZR2VqUElmYXVFVk5wczFqMy13QUd4Ty1ER181WE5KaHE5SEhFdHZzTy15T0tnZ3pyZzhVMktvLUI2WDF2M3hTRThxVzZEeDRaU21jYUd4ZzZPbHlWRFVMN1lZVGRzcHd4bDUwTWc5d09MYks4c21iYlZKNUUyaC1GOXIzZ1ZzT3dXTWVaWm9KdVhHYzN4emc?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 03:56", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPRFR1dnlza0cxUU5PbXRVYmRRT19oaHZFS3NmTDZUdHhDUVpIaTJDVDFHYThvSXE3RzNWenBDSUlDUDVCdE51VkpDaXppUEl2M1htMGxsMkxPV3ZaS2d3YVhYVTlFUEphWm45cWVuYTZLYmJ2V0xwT2dtMFkwQXZ5bjVWOVh2UHczVnZUSFQ5NFBrUkJaQTJwRXFoSlY5ajhXaHJXOVd3enFaclR4QUpXODFjMWxjVVE?oc=5", "source": "Reuters", "published": "2026-09-24 02:46", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPUXhSRW9fbndZUTd4Q3FFZjhsaThCbS1jNzk4Z1N2TUdiU0lpcHNQcEZ0WmpqdGZHUUlIUUhNdlNseThhQ0hkVDVNazBSQTV1SmRVNTJ6SnUyVTBEQ3pfWTBubFpaREdzcjI0VTFacmFUZzI4ajJfZXZLcU0yQ05NcG9BN1ZkYWQ4M3pJVkFmRllNRXJXeU8zWXRMRkVoQ2o5aGJOamlGaXlfYll4WDBEdGdpY21SN1o4UENfRGNSZ1E5elpxVjJ1aGVWZ1BnZGpfUFMwM0VYM0t4eHpnM3BTTlBKaFZoQkFTT3M2bWhSNlExcEZkcmRUUHZMVmNzSzlPc2fSAYcCQVVfeXFMTnBRN0FXeEh4U2V5eEYydmZXb19IdldaZk5tYU8zbVV2TFV5ZjgxOGg5cGZfdHVScXprR3dCeEQ4czVEOF9zSWpoM3MzdWVrNFphaTdJZWg3SHVac0VnOVc0Si04cUdma2xrRFRLRlJSakp5N1FobmtwdUNqRVRFNWxsYnJrbVpjRHI2RTI5dmJ0Qml3eVBLa2NTXzNhUHZzckNXVHJxVGs1clVveXhUYlk1MjdQOTE3SDZTelVJb1JpSF9wWkpjMno4X0lDdkt2TzFIVE0zVEVRaUFxNG5IVFRhTGRwVURPZlBOcTZtUmlNTTJYS0gxU2RWTkh4T2RZOHB3SFQ4RHc?oc=5", "source": "Livemint", "published": "2026-09-24 02:44", "score": 0.758, "label": "Positive"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxOT0tVTzVLRFhsRHJ6QVB0WV85ZGh4RHFXTEdKY1R3Snp4T1VIcXVyQmNMOGpKeDF2aVdfckZKRGVqMzVpaDlTMDU0Q0lVemMzLUxFblYwQkIxcFFvalhLYng4bVdZbUhqTnFDSDFweU93akx6V3ViVXF5cEtCbk9QSFJQTjNobXRLQUpPTGNuSlc3UkVfNGdnQ0hWbXJldU11M3hadi1FU1o5azNRZ3pIUldvMkV3b1FQYVktMldOcWZkVFhPcHI2QUdMOXQxOEY1aGN6TG13WW1yMjlQWHNYd0p5LTFkRGZqOHhHNlJIcW9pWU1VQ1k0Yy01VDRPQdIBgwJBVV95cUxOdVk4MlI1LWY0aGw5azFlQ3UtdkF1V2lVYjJBaC1UYUtRNi1FT1lTeWpTbG1jZ2dPeGtBVnFYcTdISXFqaUxJcnpuZ29EWml0UkJEN0VfeHRONWRtcGo5dG9ZTDhOWGlvemZrUWZHRWtxUVBwcFRaRno4UmpWSDIwdHh6Si1LbFFDS1E3R3hvTTRGSFA4T256enl3RjBfb1hWNEFaTEkyOHJNRXBMVng1YnJMd01TMW51ZGhta1dRRmNnc3p4TC0xa2lsMDVOQ3VoZFZzUzRGV2IzYTVzajR1Mm11ZXZ6NkNfNjJjSG5iOVNmSkVXaWozaDNwaHVTNS1MNjRF?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 02:38", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields \u2014 Five Key Factors For Sensex, Nifty 50 On Sept 24", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxNMHRUa21iWVZtelA2Um13ZTJ6ZDhOSGNJMlcyandCLUFTT0w0V3R5eWd5SEdCZ1pyOEMwSlY3ak42dHRhUjdnREc5UzdaNmI3QnFkd2RsLUk0SmhaRGNqOS1QdWp0ZVdnOExERTduSHhXZlpFb2ZHaHVneDFmaGdpVTAwa3I4RWxTT3NxUHp5ekV2YTlVd3ltNS1FLTdKN19nUzBFaHB2a1Etd0xVb0NMVDJMaG5RcGlDMDhhLUJqOWFoTmFEdXFCbDZ0SlAwTmlheHZuWEZ5dGJJdW1LQ2dGeTVtNS15Z0tmR1B2YXZ0eDR6YlFBUFRIUlRVLTZ2ZTjSAYcCQVVfeXFMTVJoelZ4TXkyUmNUWkk2RThDUWRtT1RrS0dqQUtzTHJTM1RZX0w5ZHl3b0xicjN6Z1IxS2dQUV94YWdwRGpyME1rZmVaZnZ6SGE1bW5sUlM3N2ZBYl9lajJub1AwcjJLYUc1d3pHUG5HLWUtc1VFVlc3Z0FVNXI1anMwNzA5MkZvd1YzdTRUNHpRZTBBSWpqcm05bUp0ZmxNZklyNU9LS0l0NG9uSWZCRkhYenIzaktxa3Bic25SYzVfVVdPcko2ZG95YWhraURGZ212MDJBVHBCVWxXUWVQVzZZLTFIZmVGdkdsNHF3aTNOclNEMUEtSjNsUHFCZU5JSlA5bE1aZGs?oc=5", "source": "NDTV Profit", "published": "2026-09-24 01:42", "score": 0.844, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQTDl3ZlJyNW5xZXBBLUtBLXRfSU5kbEdSOXFWM3V2RU51eVdlanIzclZnczhweGRBR1lmWkVUNWI0SlBsbW5tWmd4SzBzNXA0Ty15d21DNVJkQ0piMXpzMDYxYkNndEtmV19UQnV6NVBKZlgzU1ltZEpEakJ5dVl3WU8xQS1DRVQxN0pxV1NuU19RaGZhTWNqSHFhRHFGUVROWDhEMkxhODZ2bmZFX1piMDl0ZzVJSVRhUU5KUC1pV0NCclR5dGxXXzR1VUNvbHMweU1xaHRIQWNIRG5HN1o4NWNlRlBlRjhRVFc2SElTNklUNEtMSXBZVmQ1YkxBOFg2eWtOOFZiMUTSAY4CQVVfeXFMTUdPNHFyRDVseGxVX1p5RDdOWFBabmJQdm1ZNmVZOVB0RGZMeERCSnFfZUMxV3FrMXBJT1liYmFZekEzWGR4cUs4eDlKOUhiNURta2xDLTM0dUFkRTJrOHNaa0djNnlJWFpQcE43OGt0SkFJNEgxSm9hd0puemtzNVgyX3dHdUtGa1VIRHJBdFllRUFmYlYwQ3Y4elV1djY2ZUo5R204dmZyZ3RwaGdZSHZrbERxQWZfRlhCUEhrZjdaelZGLXZmY2lTWm84ek9wWHYzdGRKQVFOR3pYWU94RUVERlBYOXFEeDJaUVI1and2N1hCenc4anc0NVVaRG50TF9Pa1o2di0xc3k3SDdn?oc=5", "source": "Livemint", "published": "2026-09-24 01:17", "score": 0.842, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs stock gains 1.37 percent as profit jumps 126 percent", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRGZMMkVQZFBodEJ4cHVqbng0YWJyNHJjbndja3pLdkJzamNORjlNUGNab3A1MDczV2piSTRpUG5yeklwV2ZvMWlFMGp2OVota2lsTHJoZlB6dG10UlBHeXRYNTk5NlRLVVduSzZJM0dLdFlTN2hkM29mWnhNU3lHVUlaTmlGQ25fUFo0dXhGT2cyNWlhQmllc3hiRFU3Z1RIN01VV0xHOFBTMUtoWUQxTDZUY2J0VTNxRXYyb2xhQ3c?oc=5", "source": "AD HOC NEWS", "published": "2026-09-23 22:57", "score": 0.791, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUE9BMFBTZkQ0bmQwWjZyUG4tSWp1VU1ERG50V2ptaVRoamFQX21HUDNBVmdwOG81TjVLeU1GSUZoNGIzUU5Vc0drSzhsMlZkOFl4MmstUEMyZWdYTTNING9fVnZrR0ZvS3VCYmJaVEk5aFdJRUJNWTZMMlV5Sy1iaU5ieC05WjZtaFJaQmMyaU5jTW9Oc1pmZHFsaUl3aVJ6TUJTR0s3SjYtdnE4c0NDejFJOFprT0Z0Zm1RTGFsTFlFVTVvUHo3d0lpZk16R1NmVGczYlUzZGNXb0Mwd3RQUmxKR0pRcklfUl9XRVNyMEZBZ1Fxa2FsSWtGSllrV2QwSmRSVnBOMmQ?oc=5", "source": "economictimes.com", "published": "2026-09-23 12:57", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure Share Price Rises 2.68% Today", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNbjd5UVZ4d3N3ZUtybnEyZW1MZ1R4T0NrS1JsMEhETFc5d2tyclFHRnV4bzQ1RVQyUkZvNnIwOURYdjdBUzZldEpRN0FBV29YLVZOTjlFalZfemVpUzBVZ3BZSDJxSVFqSmdCMDVfNVNVXy1ZZVJpZUZORHdmNUFzazBrdGVsOGVPN1ZMRmdyQ0U1X3kzS1ZNZU1mQQ?oc=5", "source": "Univest", "published": "2026-09-23 10:02", "score": 0.34, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs Share Price: one-year high and valuation view", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYU9VS2psbTA2SEFlWWF6NVFFbVRManpTcU0wUjJIbWRQdEU2S1JUeWVXWVUtSW1RNGp3VmdEZjRGYkdVYmFtV2tZd1BQLWJfT2ZHYzhXcFhMTVgwaDlmNmZkOHhaY0JiOEVaQmZmTk5FS1luRmcxeE9ZbGV3VDlqOWR4VFhCZEE?oc=5", "source": "Univest", "published": "2026-09-23 09:19", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQa2ZFOFYwaEJuQTl6N3NjWFFvMWUyUGdxNXlZNFJHVWxtcFNEenVuTlNieHRNX3RpY0dfNnNCUk1hMU9Ndk5Sckl3TVg1Z2lJYnFORjgtY0UySTc0WW5qVmV0bU5hd0UzTVM3OVdKUFNUUHdzbEhaTTNERlV0WTdFWTBYSnpadUhucV9mejJxMnNlZ2V2UzJaOVY0dHdfNWtMVWN3U0tkVVFuSUVSMnV5NjhTUUE5a2Zrc2xieTVkZEphNmVqSEQ1MmRqMEFKM2xwU1FCVkxkZ0VsdFZYazRiMDhKcEhsejFNOXgtSGo0bFRJWThyZkZaXzJVQWpwbklBNno4NE1QSzRfT001NktmddIBlgJBVV95cUxOdy1fS2JiOHZGWTlaelh4ak5fQTR6TU9lek4tN0tIODhtWjRtRkJmS2hhZHVLTmpSMkQ2T0dXNnk1VFlTdFRjcmE1b1dCQWYtSnVQRFh0Z1hsUUljNkZVeF9GQ2pSZmplX082cHlVWEx2aVQ0dWpyZndmREdSOUJmcHBfczhYU0ZjUVVWYU96N1J0SENVQV8tR243REJnYzZwcnNzTlFnakJWcmV6eU9yTUs3NC1FWVpwRnFiZTRrUVVtM1UxQy01YnNsN1BweXNTbGpkb1l1UTNTRzNDUDEtWjBOeVJsa2QtejEtRElXcy1LNXc5bW5FY0Q4TGhXQXNWWlgxRjlXQlNEQ1R0V1B2OVZqWHluUQ?oc=5", "source": "The Times of India", "published": "2026-09-23 07:59", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks Share Price news: price rise and valuation", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNS3pobG5zQUpFLU53cFlCQWxZTFQ5S0E1dDNmbTU3V2daQUx1ZTMxMjctRHphNW5OSWVoYk9UY09CU2NxbF9GWjVCZDJzeF9OTXVTX3NUYVRjZ1U3ekZnLVFxZ01Sc3dVWlZIcnZOdXdvTzVlNTdoMlhYaVZZaWNaTEpZTkxpZw?oc=5", "source": "Univest", "published": "2026-09-23 07:26", "score": 0.0, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQThVQlhqMHhQX1dCbzk5aTVLRzAzLVhTQ0kzajBZMXRVTTNTazhRNTM3Y2d5SE1fbUhYVkJkT0hDeDlCZFhGRHEtWUxEcEhISzA4bkNGUlQ2RW44NEdPa1k5VFF5MGktRHhhZHJMRjAyeUVCVmEwWkVIQ2ROQmlhdTZTY255RFg2Rkp4NWtCTk1vaGxrUFc1VTRFSkJFY1Nnakd4VXpMNGxRVkpvMkl5VnpmakQtMWgwcV90RFpwM3BwaFFfNzhsR3IzQWhRNmpCWVVjdVM1ZExSSkxZR1N1bEpNaUp0eGV5bGIyTDQzZTZjdw?oc=5", "source": "economictimes.com", "published": "2026-09-23 06:24", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPa2tacGJLRFdET1pPVlhxQlRodHp4ZVZkREJLUU8yQlFiSmdib0hReElVbW5Qc2QtMnFqZWVDREFveHlPbDB5MHhGQjlBcTVfMS12Q1hyNGRFUjZrOHY0Ym9jSGhaSnV4YlZYZDZGV25jb1NtRV9admFLQWN1N1NETF9pUU1GbFFadFVXdzJ0dUxJelU3SFlaQUR0MlZxTWxHaDQ2SnpjRl9LczRSQ1BiX2h6SWl3ckJiek5mSDVwNm84cVVBYnRCSnFPYWRHLUlhUUlwb2cyN0tGdHRGU2lNdnVkdlNQZGJS0gHuAUFVX3lxTFBtQmV3OHlXVURIb1VpaGFmZnYtYjJnSFVyVjEtM2pvajJYV3BZQlZDOGtuOEZ4dG9hMDNkQmJVaXJPODNLdFdBMHJVdmRoTkRkR1NERk5DaWRlNXgyMUJmNDkzYXZzWVUwSzlIZ29CX3BueG8ySTU4Ymlod19HTFVJM1k2X1FDMmFpLXJPa3YtVjlSdi0tdjJ4UVc3MHZGR1ljSTJHdENmV0MwOHhJdmgyTEZBV0ZUN1JVR2gxOFhXSXBHdXlWTVYxT2RMdkhnY3UtN3FXOGd1UUtZYWRaWXVIR193bmsydVZRVnJNV0E?oc=5", "source": "simplywall.st", "published": "2026-09-23 05:56", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxNNi1kLW5uekpsdjNub29Fa3NDaWEzNU91MUMxNGZMS1ZVeEZPZ2tiLWZWY1M4MW84dTRYRl93QjFISTVtSG9oUHRpLUZZcE9welgydkFGTDZPRWtBbXVkaC1xOVgtWnhuNVZNVklETHgyNFdOMEo3UWFjUWx4dzI0ZlZDbXJ3cEdKMTFWZkNoeVo1OXlpUG1iLXhIUkREVElXLWozbkxtUWtmWXFxc043VHB2R0NpU2dQVVVGZlNWeXNkbVItSGk0VGZ5M202QUVzckd5bFliQUtMbE5SZ2NURVNsZW50aFZnd1RsQkJoRGVHUklpNF9iRGxCbE5XamlvWnZyVUNIM3NrdkZiYjI1MjFB0gGXAkFVX3lxTE1waWJFallWREMwLVdIUXFpMDlzd1loMmViNEdDbzVfbTJoSUxubGpLVy1NZjU1c2taUzdsczJIaG9OSmpIVFc5bUlyRjZQdzZkWVZKeVlwMG9GTTI1N0dHV09ucTJJX0hQUS1rUGtMLXhVTkNXQjNpNDVYVTQ1TmxtMmVWWGx0UVhpTDhmSGdCNlNma19TQTZadDlPa0RjZ2RfQ1dLaXFHMVZtdjNPRzFhdGVnMFYydnNJR3VGWEJiTHVvNW11dV9SbzNiaU1fSEJLeUpVY0R3UnBZbWp3NTNZN2NwU3ZFMzVhME9XVjI0cWdvdW1DZno2ZHVkTWFwMkRDUUkwdVRsYW5XQkx6M0gwX2tJYWJacw?oc=5", "source": "Livemint", "published": "2026-09-23 01:13", "score": 0.557, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPeE5EWjI1ZEd2aG02OThzbUpNSXdERzVpYkNmNXRCdEFNLU1JUEk2RG9IanhndHM2N1oxMDAwblVrcXpSaVFfcmc0WEF6UUJqd09acWZQYXdzM2cwZFJkUVZVSkE5Tk9WWnhJV0ZXR19HN18tRFhCU2hqWXR5a3lBazR6UWN4UDJ0VEh3NGFxNE1oX3M2Sjhib0h5N0RvMGdUcU9zVm91ODRoaGl2dVJXc18xTnJObk9pS3BfX1lQWS1HWGUzR0lEbDZ1ZTZ1b1FlY0h6SnBCRdIB3AFBVV95cUxQbHN0Tmw0M3l2RFNtTzBTaEtMbzJ5WmE3cWRraUhSRTc3ejR4SUE2NDBvTEhqMTZPQmktdXJ5N3VwM2ZudzBPTU8zZU1tLUVIUFlVVDdCbGFaZGllcHA5UmEzLUpOU2RlU2c0YzlrTUk4ejU3UUxQM2hXTWlsU0p5eVh0blVNMmdpcERxXzFnZ1d2R3lzUzE2c21vOGxBWGlIMnR1Z25MQTlITTI4S3JIcU56YU5VVHVyUXVSU3JHZ3ZiVnZFLWVFbmR0S0dHTHVqOGw2QlZrZzg5bDFT?oc=5", "source": "simplywall.st", "published": "2026-09-23 00:46", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex drops 330 points, Nifty down to 23,329 dragged by IT stocks", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxPNFJTNFB5dk9wRmoxYUFueUhJcHRhRVhXNUwwb05HRm5xeHpOSUdVVUdmd010X1lTMVRmekwzbURob0Q0VU1kOXpLZERFSVdIamc0cU1vQUJUOGdMWGxBTHJTUzF5cV9WVFJwX2J1eU9faU5PMml0TW9XMEw4MmRYbzdtWk14U0JjVkZnaVJ2VzEwRnFhRWtoTmtsOE5EY1RDa01qZWhMSnNNQzhKc1l0UEtCbVdHd9IBvAFBVV95cUxQWDhBbHBnUVp1Nm5VbW5zbXZQTjJWR2pwdjMzTWk0Z3hHZzFQVnNpb1VTcWt0ZlZfWlQzQTNvYXhSZEcwSjFKWmIwbm85YlZ0UUJhdHJrZkdZRHRpdDNhOXJXM1pETVFUSGFXZ3g5N19FYnhqV3M2WEppNmZYMHVnZmYyTHVvQnhNYnRSUDJrN2pJNHMwM2ZNaVBQS1RLNHYxUUdMWHh1UzJxN2ltcURlMWUxQVkzTllaU2xjZA?oc=5", "source": "The Hindu", "published": "2026-09-22 11:04", "score": 0.361, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals to host investor meet at PL Capital conference on Sep 28", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxOemZyUExJOUpZeW9vRDRtRmI4LUFZOXNDY3ZBNjJ6ZXJqSVAzQkhtMk5xSmpaVGxCQ21GVFoyODFYSGdMYngyLWVQZ0lVT3JnUE9sZEJNUzI4eV9wcW9UY3VsdG5VemUwUmFPaWhJbTlScWJCV25OYkc5XzBKaXNSMFZZWlE3cUhsblRqSXp4SWpvS2Z4bmpRcWJiN1JCRmhrTTJuQ1VjbFUwS2hOSEhCcmxHdjI0ekRhV1RZQlFrRQ?oc=5", "source": "scanx.trade", "published": "2026-09-22 08:51", "score": 0.0, "label": "Neutral"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals NSE:ACUTAAS Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOYnY1bG13T0VMaGh4bVVwcWg4VXZydnVVa0hQTEZlQVlVRnJZdEdxRGZ1Zy1CSFQ5NTVqQkxjUUplU1NmaDRuWWliSlZaWUtPTXJSUGN5c2VZRUpUeFFfdmw4Zy1sNE5qdGt4Qy02OVQ0MXFaUUZZcE80el9BVEQ4SjdTWWE1M2NNbERjNEgzMDd2Mjd2UE5xQ0c4a2tmMnZoX2FnMHdlRmNkSG82LVExUjgxdVBpZw?oc=5", "source": "Kalkine India", "published": "2026-09-22 07:31", "score": 0.0, "label": "Neutral"}, {"symbol": "ATHERENERG", "title": "Ather Energy Share Price News: Today\u2019s Decline Explained", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxONjFLdmNlWldKcVdBQWxtakF5dmI4cFdXODhVWkpqTElHcTUzZWhoN3R3OV8wdjVOSU9aVGZ3dGNzN3RDTm5XdEtHZmc0T0twMURva1ZPVk1zaDZhZFBLY0tuamtkUmZGZy02YllXMklOSzhiQXdPYm5yYktSRmtnZw?oc=5", "source": "Univest", "published": "2026-09-22 07:22", "score": -0.128, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: price rise and sector check", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxQbjk1eVNKTElsd0tEcEVPeVRzZ0VJMk9KV3lyaUViUEVvQ3U4VG9uc0t0czlWSkVMLVF6WWRORkJSTUlDOTRFVU5jOVR1UEQ1OTNUa3dpTDRGNDdXLXl0NGlYUjFLS2RBYjVLVFIyMWtTRkNKTWtsNE41MF9pcEtvSA?oc=5", "source": "Univest", "published": "2026-09-22 07:19", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxQSUdyXzNaTFpFQktnX2tJNVotaGRyUXdzUF84LWxwdkdiX3VfTnBWRHJpak1VdkhpVVQ5MVJGRHQ4bjVLQXlDRzlyUENyRE83MXlwT0lLaEZEd0JKbHV4RWVtX194MkFJc3AxeXFGOEFMT0NmbDZqMVFVVEhrNUZWNGRrRXpZY0xzbDcwWjBQc2dpbFQ2blFKV2RiVWdSenlDUUlfMDloc1I4S2lBaGVUQVBzNGdwbXBESVgyYTZ5Z052YzZMdTJFYm5iTlUzV19aSVJDUnlkd1VRdEhiR1Q3T3JMTElyc1dlaGfSAe8BQVVfeXFMTnBPVmlmNEtYY0Z3WEdMNWZ3Y1dLSnVEcXhSVUJ5YkNnUXhxYWtnX3dHRWZyY0hlMnEtTkZWWXlMSW1CcjRLMjlQeUNWS0d5NERGZE5DaU1VaW1LcE5FLUw1bGdKZTFmdFQtTUlpTjNXN1Q2WkJpTDUycmtNM0ExVWw0eFlnei1SODB2UWNQcGtOR3FWcDFFcVN6ZnhOSDdoS2EyQS1Pa3ljS1llZloyblNzUGlBb2RDWGFiZkV5dm5kb3BXSjlYLXU2Z0VQNTNpMld3MVZGeW8zc0JGZ19Wa3QwRHRUZFVQenJ0NnRJUDg?oc=5", "source": "simplywall.st", "published": "2026-09-22 05:01", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty see positive start; NSE IPO receives 6x subscription on final day | Business News", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQTkFFZlczeUxrZGxNZXpkWDdpYVhxdDdXNy1Yems4cTdtV3pkQUEtX1pQWFRKWUh0cUJFSVUwMDFTVjZiaEotVzdxV0Q4MUFIZkRJd0FKT3VodVJlazVIbXNnRnZaVkR1d2xzLUVNVlNaM0x2ODNaNjlEaDlDNjFFT1dCR0FUV0pZcDZkR3V2cmhLT0VHelZ5aEFoT0p0UGkxLS0zdXJZYlFhZFFLWmhfV25jTjNFUUlLMjBsWWhkbi16ZmVpcVpfUTVQWlhrR1gwMGx6bEp5bnhqM1HSAeABQVVfeXFMT1M5bV93ZEdtOUtUbks4OEtBSEdkaWJxWlp0TDNsQUlqblVkUGFyQ2hHM0pwb0Q4U0lhcVM5dFlYYlJUMU5QeUFvbV9EOGx0cGVsR2xfdFZ0THNXMVBkY21wYklLRVZUcVIwbldIaVFsSXlpdDJtbXlVa0lMNzQyVzdjVUVITXZ3cVdPUnByeFN5REpBcVlNM0FoUjZ5V2gxRUE2UFQ0RjF4UmtLcEJOSkZaT0FaekQ0SGFDZFhmRnZNdWNVeXZiekhHWGJ1SjkwdVBkdjl2VlBvSzVvMnowN3Q?oc=5", "source": "Hindustan Times", "published": "2026-09-22 03:51", "score": 0.743, "label": "Positive"}], "errors": []}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T02:53:52", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}}</t>
         </is>
       </c>
     </row>

--- a/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
+++ b/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
@@ -1495,7 +1495,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 02:53</t>
+          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 03:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2378,7 +2378,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 02:53</t>
+          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 03:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10095,7 +10095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10123,7 +10123,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fetched 2026-09-29 02:53</t>
+          <t>Fetched 2026-09-29 03:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10173,26 +10173,26 @@
     <row r="5">
       <c r="A5" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B5" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:36</t>
+          <t>2026-09-29 00:10</t>
         </is>
       </c>
       <c r="C5" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
+          <t>3 Indian Nuclear Stocks With Earnings Growth Over 17%</t>
         </is>
       </c>
       <c r="D5" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Simply Wall St.</t>
         </is>
       </c>
       <c r="E5" s="80" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.888</v>
       </c>
       <c r="F5" s="51" t="inlineStr">
         <is>
@@ -10208,26 +10208,26 @@
     <row r="6">
       <c r="A6" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B6" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:19</t>
+          <t>2026-09-24 17:13</t>
         </is>
       </c>
       <c r="C6" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>3 Indian Nuclear Stocks With Revenue Growth Up To 16%</t>
         </is>
       </c>
       <c r="D6" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Simply Wall St.</t>
         </is>
       </c>
       <c r="E6" s="80" t="n">
-        <v>0.842</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F6" s="51" t="inlineStr">
         <is>
@@ -10235,5326 +10235,6 @@
         </is>
       </c>
       <c r="G6" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B7" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-29 00:10</t>
-        </is>
-      </c>
-      <c r="C7" s="51" t="inlineStr">
-        <is>
-          <t>3 Indian Nuclear Stocks With Earnings Growth Over 17%</t>
-        </is>
-      </c>
-      <c r="D7" s="51" t="inlineStr">
-        <is>
-          <t>Simply Wall St.</t>
-        </is>
-      </c>
-      <c r="E7" s="80" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="F7" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G7" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B8" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 19:51</t>
-        </is>
-      </c>
-      <c r="C8" s="51" t="inlineStr">
-        <is>
-          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
-        </is>
-      </c>
-      <c r="D8" s="51" t="inlineStr">
-        <is>
-          <t>WION</t>
-        </is>
-      </c>
-      <c r="E8" s="80" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="F8" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G8" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B9" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:36</t>
-        </is>
-      </c>
-      <c r="C9" s="51" t="inlineStr">
-        <is>
-          <t>Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens</t>
-        </is>
-      </c>
-      <c r="D9" s="51" t="inlineStr">
-        <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E9" s="80" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F9" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G9" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B10" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:42</t>
-        </is>
-      </c>
-      <c r="C10" s="51" t="inlineStr">
-        <is>
-          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
-        </is>
-      </c>
-      <c r="D10" s="51" t="inlineStr">
-        <is>
-          <t>The Times of India</t>
-        </is>
-      </c>
-      <c r="E10" s="80" t="n">
-        <v>-0.896</v>
-      </c>
-      <c r="F10" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G10" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="51" t="inlineStr">
-        <is>
-          <t>AEROFLEX</t>
-        </is>
-      </c>
-      <c r="B11" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:25</t>
-        </is>
-      </c>
-      <c r="C11" s="51" t="inlineStr">
-        <is>
-          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
-        </is>
-      </c>
-      <c r="D11" s="51" t="inlineStr">
-        <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E11" s="80" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="F11" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G11" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B12" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:16</t>
-        </is>
-      </c>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
-        </is>
-      </c>
-      <c r="D12" s="51" t="inlineStr">
-        <is>
-          <t>hrtoday.in</t>
-        </is>
-      </c>
-      <c r="E12" s="80" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="F12" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G12" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B13" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 11:48</t>
-        </is>
-      </c>
-      <c r="C13" s="51" t="inlineStr">
-        <is>
-          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
-        </is>
-      </c>
-      <c r="D13" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E13" s="80" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="F13" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G13" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B14" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 10:56</t>
-        </is>
-      </c>
-      <c r="C14" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
-        </is>
-      </c>
-      <c r="D14" s="51" t="inlineStr">
-        <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E14" s="80" t="n">
-        <v>-0.273</v>
-      </c>
-      <c r="F14" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G14" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B15" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 10:46</t>
-        </is>
-      </c>
-      <c r="C15" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Falls 1,124 Points, Nifty Slips Below 22,800</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="inlineStr">
-        <is>
-          <t>hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="E15" s="80" t="n">
-        <v>-0.318</v>
-      </c>
-      <c r="F15" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G15" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B16" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 10:15</t>
-        </is>
-      </c>
-      <c r="C16" s="51" t="inlineStr">
-        <is>
-          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E16" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G16" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B17" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 10:06</t>
-        </is>
-      </c>
-      <c r="C17" s="51" t="inlineStr">
-        <is>
-          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
-        </is>
-      </c>
-      <c r="D17" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E17" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G17" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B18" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 08:20</t>
-        </is>
-      </c>
-      <c r="C18" s="51" t="inlineStr">
-        <is>
-          <t>E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?</t>
-        </is>
-      </c>
-      <c r="D18" s="51" t="inlineStr">
-        <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E18" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G18" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B19" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 08:15</t>
-        </is>
-      </c>
-      <c r="C19" s="51" t="inlineStr">
-        <is>
-          <t>Nifty, Sensex: History favours stock market comeback in October; stocks to watch</t>
-        </is>
-      </c>
-      <c r="D19" s="51" t="inlineStr">
-        <is>
-          <t>Business Today</t>
-        </is>
-      </c>
-      <c r="E19" s="80" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F19" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G19" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B20" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 08:03</t>
-        </is>
-      </c>
-      <c r="C20" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
-        </is>
-      </c>
-      <c r="D20" s="51" t="inlineStr">
-        <is>
-          <t>Free Press Kashmir</t>
-        </is>
-      </c>
-      <c r="E20" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G20" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B21" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 07:56</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?</t>
-        </is>
-      </c>
-      <c r="D21" s="51" t="inlineStr">
-        <is>
-          <t>ETV Bharat</t>
-        </is>
-      </c>
-      <c r="E21" s="80" t="n">
-        <v>-0.8070000000000001</v>
-      </c>
-      <c r="F21" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G21" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B22" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 07:44</t>
-        </is>
-      </c>
-      <c r="C22" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts</t>
-        </is>
-      </c>
-      <c r="D22" s="51" t="inlineStr">
-        <is>
-          <t>apacnewsnetwork.com</t>
-        </is>
-      </c>
-      <c r="E22" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G22" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B23" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 07:36</t>
-        </is>
-      </c>
-      <c r="C23" s="51" t="inlineStr">
-        <is>
-          <t>September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets</t>
-        </is>
-      </c>
-      <c r="D23" s="51" t="inlineStr">
-        <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E23" s="80" t="n">
-        <v>-0.806</v>
-      </c>
-      <c r="F23" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G23" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B24" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 07:06</t>
-        </is>
-      </c>
-      <c r="C24" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800</t>
-        </is>
-      </c>
-      <c r="D24" s="51" t="inlineStr">
-        <is>
-          <t>CNBC TV18</t>
-        </is>
-      </c>
-      <c r="E24" s="80" t="n">
-        <v>-0.402</v>
-      </c>
-      <c r="F24" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G24" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B25" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 06:47</t>
-        </is>
-      </c>
-      <c r="C25" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
-        </is>
-      </c>
-      <c r="D25" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E25" s="80" t="n">
-        <v>-0.791</v>
-      </c>
-      <c r="F25" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G25" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B26" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 05:52</t>
-        </is>
-      </c>
-      <c r="C26" s="51" t="inlineStr">
-        <is>
-          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
-        </is>
-      </c>
-      <c r="D26" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E26" s="80" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="F26" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G26" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B27" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 05:42</t>
-        </is>
-      </c>
-      <c r="C27" s="51" t="inlineStr">
-        <is>
-          <t>Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern</t>
-        </is>
-      </c>
-      <c r="D27" s="51" t="inlineStr">
-        <is>
-          <t>India Infoline</t>
-        </is>
-      </c>
-      <c r="E27" s="80" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="F27" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G27" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B28" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 05:37</t>
-        </is>
-      </c>
-      <c r="C28" s="51" t="inlineStr">
-        <is>
-          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
-        </is>
-      </c>
-      <c r="D28" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E28" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G28" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B29" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 05:18</t>
-        </is>
-      </c>
-      <c r="C29" s="51" t="inlineStr">
-        <is>
-          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
-        </is>
-      </c>
-      <c r="D29" s="51" t="inlineStr">
-        <is>
-          <t>The Times of India</t>
-        </is>
-      </c>
-      <c r="E29" s="80" t="n">
-        <v>-0.6909999999999999</v>
-      </c>
-      <c r="F29" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G29" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B30" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 05:11</t>
-        </is>
-      </c>
-      <c r="C30" s="51" t="inlineStr">
-        <is>
-          <t>Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties</t>
-        </is>
-      </c>
-      <c r="D30" s="51" t="inlineStr">
-        <is>
-          <t>The Hindu</t>
-        </is>
-      </c>
-      <c r="E30" s="80" t="n">
-        <v>-0.852</v>
-      </c>
-      <c r="F30" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G30" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B31" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:45</t>
-        </is>
-      </c>
-      <c r="C31" s="51" t="inlineStr">
-        <is>
-          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
-        </is>
-      </c>
-      <c r="D31" s="51" t="inlineStr">
-        <is>
-          <t>Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E31" s="80" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="F31" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G31" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B32" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:42</t>
-        </is>
-      </c>
-      <c r="C32" s="51" t="inlineStr">
-        <is>
-          <t>NSE stock slips below issue price of ₹1,785; down 2% on Monday</t>
-        </is>
-      </c>
-      <c r="D32" s="51" t="inlineStr">
-        <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E32" s="80" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="F32" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G32" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B33" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:41</t>
-        </is>
-      </c>
-      <c r="C33" s="51" t="inlineStr">
-        <is>
-          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
-        </is>
-      </c>
-      <c r="D33" s="51" t="inlineStr">
-        <is>
-          <t>NDTV</t>
-        </is>
-      </c>
-      <c r="E33" s="80" t="n">
-        <v>-0.758</v>
-      </c>
-      <c r="F33" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G33" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B34" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:29</t>
-        </is>
-      </c>
-      <c r="C34" s="51" t="inlineStr">
-        <is>
-          <t>Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%</t>
-        </is>
-      </c>
-      <c r="D34" s="51" t="inlineStr">
-        <is>
-          <t>newsdrum.in</t>
-        </is>
-      </c>
-      <c r="E34" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G34" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B35" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:25</t>
-        </is>
-      </c>
-      <c r="C35" s="51" t="inlineStr">
-        <is>
-          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
-        </is>
-      </c>
-      <c r="D35" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E35" s="80" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="F35" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G35" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B36" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:17</t>
-        </is>
-      </c>
-      <c r="C36" s="51" t="inlineStr">
-        <is>
-          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
-        </is>
-      </c>
-      <c r="D36" s="51" t="inlineStr">
-        <is>
-          <t>India Today</t>
-        </is>
-      </c>
-      <c r="E36" s="80" t="n">
-        <v>-0.511</v>
-      </c>
-      <c r="F36" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G36" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B37" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:11</t>
-        </is>
-      </c>
-      <c r="C37" s="51" t="inlineStr">
-        <is>
-          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
-        </is>
-      </c>
-      <c r="D37" s="51" t="inlineStr">
-        <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E37" s="80" t="n">
-        <v>-0.586</v>
-      </c>
-      <c r="F37" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G37" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B38" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:08</t>
-        </is>
-      </c>
-      <c r="C38" s="51" t="inlineStr">
-        <is>
-          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l</t>
-        </is>
-      </c>
-      <c r="D38" s="51" t="inlineStr">
-        <is>
-          <t>economictimes.com</t>
-        </is>
-      </c>
-      <c r="E38" s="80" t="n">
-        <v>-0.649</v>
-      </c>
-      <c r="F38" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G38" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B39" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 04:07</t>
-        </is>
-      </c>
-      <c r="C39" s="51" t="inlineStr">
-        <is>
-          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
-        </is>
-      </c>
-      <c r="D39" s="51" t="inlineStr">
-        <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E39" s="80" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F39" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G39" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B40" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 03:58</t>
-        </is>
-      </c>
-      <c r="C40" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
-        </is>
-      </c>
-      <c r="D40" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E40" s="80" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="F40" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G40" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B41" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 03:54</t>
-        </is>
-      </c>
-      <c r="C41" s="51" t="inlineStr">
-        <is>
-          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
-        </is>
-      </c>
-      <c r="D41" s="51" t="inlineStr">
-        <is>
-          <t>The Times of India</t>
-        </is>
-      </c>
-      <c r="E41" s="80" t="n">
-        <v>-0.494</v>
-      </c>
-      <c r="F41" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G41" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B42" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 03:48</t>
-        </is>
-      </c>
-      <c r="C42" s="51" t="inlineStr">
-        <is>
-          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
-        </is>
-      </c>
-      <c r="D42" s="51" t="inlineStr">
-        <is>
-          <t>Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E42" s="80" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F42" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G42" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B43" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 03:28</t>
-        </is>
-      </c>
-      <c r="C43" s="51" t="inlineStr">
-        <is>
-          <t>Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open</t>
-        </is>
-      </c>
-      <c r="D43" s="51" t="inlineStr">
-        <is>
-          <t>hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="E43" s="80" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="F43" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G43" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B44" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 02:19</t>
-        </is>
-      </c>
-      <c r="C44" s="51" t="inlineStr">
-        <is>
-          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
-        </is>
-      </c>
-      <c r="D44" s="51" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="E44" s="80" t="n">
-        <v>-0.542</v>
-      </c>
-      <c r="F44" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G44" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B45" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 01:58</t>
-        </is>
-      </c>
-      <c r="C45" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices — Five Key Factors For Sensex, Nifty 50 On September 28</t>
-        </is>
-      </c>
-      <c r="D45" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E45" s="80" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="F45" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G45" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B46" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 01:20</t>
-        </is>
-      </c>
-      <c r="C46" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
-        </is>
-      </c>
-      <c r="D46" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E46" s="80" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="F46" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G46" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B47" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:30</t>
-        </is>
-      </c>
-      <c r="C47" s="51" t="inlineStr">
-        <is>
-          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
-        </is>
-      </c>
-      <c r="D47" s="51" t="inlineStr">
-        <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E47" s="80" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="F47" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G47" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="51" t="inlineStr">
-        <is>
-          <t>ACUTAAS</t>
-        </is>
-      </c>
-      <c r="B48" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-27 17:20</t>
-        </is>
-      </c>
-      <c r="C48" s="51" t="inlineStr">
-        <is>
-          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
-        </is>
-      </c>
-      <c r="D48" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E48" s="80" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="F48" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G48" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B49" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-27 11:03</t>
-        </is>
-      </c>
-      <c r="C49" s="51" t="inlineStr">
-        <is>
-          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
-        </is>
-      </c>
-      <c r="D49" s="51" t="inlineStr">
-        <is>
-          <t>economictimes.com</t>
-        </is>
-      </c>
-      <c r="E49" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G49" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B50" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-27 09:48</t>
-        </is>
-      </c>
-      <c r="C50" s="51" t="inlineStr">
-        <is>
-          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
-        </is>
-      </c>
-      <c r="D50" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E50" s="80" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F50" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G50" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="51" t="inlineStr">
-        <is>
-          <t>ACUTAAS</t>
-        </is>
-      </c>
-      <c r="B51" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-27 06:44</t>
-        </is>
-      </c>
-      <c r="C51" s="51" t="inlineStr">
-        <is>
-          <t>Acutaas shareholders reject ESOP scheme for subsidiary employees at AGM</t>
-        </is>
-      </c>
-      <c r="D51" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E51" s="80" t="n">
-        <v>-0.402</v>
-      </c>
-      <c r="F51" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G51" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B52" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-27 04:22</t>
-        </is>
-      </c>
-      <c r="C52" s="51" t="inlineStr">
-        <is>
-          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
-        </is>
-      </c>
-      <c r="D52" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E52" s="80" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="F52" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G52" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B53" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-26 22:56</t>
-        </is>
-      </c>
-      <c r="C53" s="51" t="inlineStr">
-        <is>
-          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
-        </is>
-      </c>
-      <c r="D53" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E53" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G53" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B54" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-26 13:51</t>
-        </is>
-      </c>
-      <c r="C54" s="51" t="inlineStr">
-        <is>
-          <t>🚦 Indian Markets Stuck In A Jam! But who's responsible for the traffic? 🤔 A Bernstein note argues that India’s large caps are stuck in a bygone economic era. But here's the BIG question: 🇮🇳 Is The Market’s Fate Really In India’s Hands? 🌍 Or are global cues pul</t>
-        </is>
-      </c>
-      <c r="D54" s="51" t="inlineStr">
-        <is>
-          <t>linkedin.com</t>
-        </is>
-      </c>
-      <c r="E54" s="80" t="n">
-        <v>-0.625</v>
-      </c>
-      <c r="F54" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G54" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B55" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-26 12:11</t>
-        </is>
-      </c>
-      <c r="C55" s="51" t="inlineStr">
-        <is>
-          <t>Share Market News: Nifty 50 Outlook &amp; Prediction</t>
-        </is>
-      </c>
-      <c r="D55" s="51" t="inlineStr">
-        <is>
-          <t>Liquide Blog</t>
-        </is>
-      </c>
-      <c r="E55" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F55" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G55" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B56" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-26 09:15</t>
-        </is>
-      </c>
-      <c r="C56" s="51" t="inlineStr">
-        <is>
-          <t>Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide</t>
-        </is>
-      </c>
-      <c r="D56" s="51" t="inlineStr">
-        <is>
-          <t>The New Indian Express</t>
-        </is>
-      </c>
-      <c r="E56" s="80" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="F56" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G56" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="51" t="inlineStr">
-        <is>
-          <t>THANGAMAYL</t>
-        </is>
-      </c>
-      <c r="B57" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-26 06:48</t>
-        </is>
-      </c>
-      <c r="C57" s="51" t="inlineStr">
-        <is>
-          <t>Thangamayil Jewellery Shuts Trading Window Ahead of September-Quarter Results</t>
-        </is>
-      </c>
-      <c r="D57" s="51" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="E57" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G57" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="51" t="inlineStr">
-        <is>
-          <t>THANGAMAYL</t>
-        </is>
-      </c>
-      <c r="B58" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-26 06:30</t>
-        </is>
-      </c>
-      <c r="C58" s="51" t="inlineStr">
-        <is>
-          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
-        </is>
-      </c>
-      <c r="D58" s="51" t="inlineStr">
-        <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E58" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G58" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="51" t="inlineStr">
-        <is>
-          <t>DIACABS</t>
-        </is>
-      </c>
-      <c r="B59" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-26 00:50</t>
-        </is>
-      </c>
-      <c r="C59" s="51" t="inlineStr">
-        <is>
-          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
-        </is>
-      </c>
-      <c r="D59" s="51" t="inlineStr">
-        <is>
-          <t>Alice Blue</t>
-        </is>
-      </c>
-      <c r="E59" s="80" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F59" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G59" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B60" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:34</t>
-        </is>
-      </c>
-      <c r="C60" s="51" t="inlineStr">
-        <is>
-          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
-        </is>
-      </c>
-      <c r="D60" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E60" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G60" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B61" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:31</t>
-        </is>
-      </c>
-      <c r="C61" s="51" t="inlineStr">
-        <is>
-          <t>PERSISTENT Stock Price and Chart — NSE:PERSISTENT</t>
-        </is>
-      </c>
-      <c r="D61" s="51" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="E61" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G61" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B62" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:04</t>
-        </is>
-      </c>
-      <c r="C62" s="51" t="inlineStr">
-        <is>
-          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
-        </is>
-      </c>
-      <c r="D62" s="51" t="inlineStr">
-        <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E62" s="80" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="F62" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G62" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B63" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 12:52</t>
-        </is>
-      </c>
-      <c r="C63" s="51" t="inlineStr">
-        <is>
-          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
-        </is>
-      </c>
-      <c r="D63" s="51" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="E63" s="80" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="F63" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G63" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="51" t="inlineStr">
-        <is>
-          <t>THANGAMAYL</t>
-        </is>
-      </c>
-      <c r="B64" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 12:22</t>
-        </is>
-      </c>
-      <c r="C64" s="51" t="inlineStr">
-        <is>
-          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
-        </is>
-      </c>
-      <c r="D64" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E64" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G64" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B65" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 11:42</t>
-        </is>
-      </c>
-      <c r="C65" s="51" t="inlineStr">
-        <is>
-          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
-        </is>
-      </c>
-      <c r="D65" s="51" t="inlineStr">
-        <is>
-          <t>CNBC TV18</t>
-        </is>
-      </c>
-      <c r="E65" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G65" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B66" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 11:03</t>
-        </is>
-      </c>
-      <c r="C66" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%</t>
-        </is>
-      </c>
-      <c r="D66" s="51" t="inlineStr">
-        <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E66" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F66" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G66" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B67" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 11:01</t>
-        </is>
-      </c>
-      <c r="C67" s="51" t="inlineStr">
-        <is>
-          <t>Stock markets bounce back on value buying; Sensex rises 315 pts</t>
-        </is>
-      </c>
-      <c r="D67" s="51" t="inlineStr">
-        <is>
-          <t>DD India</t>
-        </is>
-      </c>
-      <c r="E67" s="80" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F67" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G67" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B68" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 10:48</t>
-        </is>
-      </c>
-      <c r="C68" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty Rebound on Value Buying After Sharp Losses</t>
-        </is>
-      </c>
-      <c r="D68" s="51" t="inlineStr">
-        <is>
-          <t>Rediff MoneyWiz</t>
-        </is>
-      </c>
-      <c r="E68" s="80" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="F68" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G68" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B69" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 10:31</t>
-        </is>
-      </c>
-      <c r="C69" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses</t>
-        </is>
-      </c>
-      <c r="D69" s="51" t="inlineStr">
-        <is>
-          <t>apacnewsnetwork.com</t>
-        </is>
-      </c>
-      <c r="E69" s="80" t="n">
-        <v>-0.026</v>
-      </c>
-      <c r="F69" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G69" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B70" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 07:19</t>
-        </is>
-      </c>
-      <c r="C70" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Today | Stock Market Live: Sensex rises 150 pts, Nifty eyes 23,100; realty gains, IT slips</t>
-        </is>
-      </c>
-      <c r="D70" s="51" t="inlineStr">
-        <is>
-          <t>IndiaIPO</t>
-        </is>
-      </c>
-      <c r="E70" s="80" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F70" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G70" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="51" t="inlineStr">
-        <is>
-          <t>AEROFLEX</t>
-        </is>
-      </c>
-      <c r="B71" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 07:00</t>
-        </is>
-      </c>
-      <c r="C71" s="51" t="inlineStr">
-        <is>
-          <t>AEROFLEX INDUSTRIES LTD Share Price</t>
-        </is>
-      </c>
-      <c r="D71" s="51" t="inlineStr">
-        <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E71" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G71" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="51" t="inlineStr">
-        <is>
-          <t>AEROFLEX</t>
-        </is>
-      </c>
-      <c r="B72" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 07:00</t>
-        </is>
-      </c>
-      <c r="C72" s="51" t="inlineStr">
-        <is>
-          <t>Sah Polymers Share Price</t>
-        </is>
-      </c>
-      <c r="D72" s="51" t="inlineStr">
-        <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E72" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G72" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B73" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 07:00</t>
-        </is>
-      </c>
-      <c r="C73" s="51" t="inlineStr">
-        <is>
-          <t>Laser Power &amp; Infra Ltd Share Price Today,, LASERPOWER Share Price NSE, BSE</t>
-        </is>
-      </c>
-      <c r="D73" s="51" t="inlineStr">
-        <is>
-          <t>Business Today</t>
-        </is>
-      </c>
-      <c r="E73" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G73" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B74" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 07:00</t>
-        </is>
-      </c>
-      <c r="C74" s="51" t="inlineStr">
-        <is>
-          <t>Nifty Chemicals (NFTCHEMIC) Share Price</t>
-        </is>
-      </c>
-      <c r="D74" s="51" t="inlineStr">
-        <is>
-          <t>Business Today</t>
-        </is>
-      </c>
-      <c r="E74" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F74" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G74" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B75" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 07:00</t>
-        </is>
-      </c>
-      <c r="C75" s="51" t="inlineStr">
-        <is>
-          <t>JSW Holdings Share Price Today, JSW Holdings Stock Price Live NSE/BSE Updates</t>
-        </is>
-      </c>
-      <c r="D75" s="51" t="inlineStr">
-        <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E75" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G75" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="51" t="inlineStr">
-        <is>
-          <t>DIACABS</t>
-        </is>
-      </c>
-      <c r="B76" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 06:49</t>
-        </is>
-      </c>
-      <c r="C76" s="51" t="inlineStr">
-        <is>
-          <t>Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today</t>
-        </is>
-      </c>
-      <c r="D76" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E76" s="80" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="F76" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G76" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B77" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 06:07</t>
-        </is>
-      </c>
-      <c r="C77" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty struggle for direction as oil, US yields weigh</t>
-        </is>
-      </c>
-      <c r="D77" s="51" t="inlineStr">
-        <is>
-          <t>PSU Watch</t>
-        </is>
-      </c>
-      <c r="E77" s="80" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="F77" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G77" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B78" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 05:52</t>
-        </is>
-      </c>
-      <c r="C78" s="51" t="inlineStr">
-        <is>
-          <t>Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons</t>
-        </is>
-      </c>
-      <c r="D78" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E78" s="80" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="F78" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G78" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B79" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 05:32</t>
-        </is>
-      </c>
-      <c r="C79" s="51" t="inlineStr">
-        <is>
-          <t>NSE shares dip on day 2 of listing, brokerages back long-term growth story</t>
-        </is>
-      </c>
-      <c r="D79" s="51" t="inlineStr">
-        <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E79" s="80" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="F79" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G79" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B80" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 05:09</t>
-        </is>
-      </c>
-      <c r="C80" s="51" t="inlineStr">
-        <is>
-          <t>Stock Markets Today: Sensex, Nifty up in Volatile Trade</t>
-        </is>
-      </c>
-      <c r="D80" s="51" t="inlineStr">
-        <is>
-          <t>Rediff</t>
-        </is>
-      </c>
-      <c r="E80" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F80" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G80" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B81" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 05:04</t>
-        </is>
-      </c>
-      <c r="C81" s="51" t="inlineStr">
-        <is>
-          <t>Stock markets turn volatile as oil prices, rising bond yields weigh on sentiments</t>
-        </is>
-      </c>
-      <c r="D81" s="51" t="inlineStr">
-        <is>
-          <t>The Hindu</t>
-        </is>
-      </c>
-      <c r="E81" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G81" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B82" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 04:53</t>
-        </is>
-      </c>
-      <c r="C82" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty volatile after early rebound as crude, bond yields weigh</t>
-        </is>
-      </c>
-      <c r="D82" s="51" t="inlineStr">
-        <is>
-          <t>Telangana Today</t>
-        </is>
-      </c>
-      <c r="E82" s="80" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F82" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G82" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B83" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 04:52</t>
-        </is>
-      </c>
-      <c r="C83" s="51" t="inlineStr">
-        <is>
-          <t>E2E Networks vs ESDS: AI Cloud Business Models and Financials Compared</t>
-        </is>
-      </c>
-      <c r="D83" s="51" t="inlineStr">
-        <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="E83" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G83" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B84" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 04:45</t>
-        </is>
-      </c>
-      <c r="C84" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty Open Higher; IT Stocks Drag Market</t>
-        </is>
-      </c>
-      <c r="D84" s="51" t="inlineStr">
-        <is>
-          <t>hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="E84" s="80" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="F84" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G84" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B85" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 04:24</t>
-        </is>
-      </c>
-      <c r="C85" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty open cautiously today; IT stocks bleed as crude, yields bite</t>
-        </is>
-      </c>
-      <c r="D85" s="51" t="inlineStr">
-        <is>
-          <t>BusinessLine</t>
-        </is>
-      </c>
-      <c r="E85" s="80" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F85" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G85" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B86" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 04:11</t>
-        </is>
-      </c>
-      <c r="C86" s="51" t="inlineStr">
-        <is>
-          <t>Stock markets rebound in early trade: Sensex climbs 86 points, Nifty up 18.80 points</t>
-        </is>
-      </c>
-      <c r="D86" s="51" t="inlineStr">
-        <is>
-          <t>Telegraph India</t>
-        </is>
-      </c>
-      <c r="E86" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F86" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G86" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B87" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 03:51</t>
-        </is>
-      </c>
-      <c r="C87" s="51" t="inlineStr">
-        <is>
-          <t>Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050</t>
-        </is>
-      </c>
-      <c r="D87" s="51" t="inlineStr">
-        <is>
-          <t>The Times of India</t>
-        </is>
-      </c>
-      <c r="E87" s="80" t="n">
-        <v>-0.494</v>
-      </c>
-      <c r="F87" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G87" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B88" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 02:58</t>
-        </is>
-      </c>
-      <c r="C88" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty opening: Will the stock market fall again today?</t>
-        </is>
-      </c>
-      <c r="D88" s="51" t="inlineStr">
-        <is>
-          <t>India Today</t>
-        </is>
-      </c>
-      <c r="E88" s="80" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F88" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G88" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B89" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 02:18</t>
-        </is>
-      </c>
-      <c r="C89" s="51" t="inlineStr">
-        <is>
-          <t>Stock market today: Sensex, Nifty may open flat amid key headwinds</t>
-        </is>
-      </c>
-      <c r="D89" s="51" t="inlineStr">
-        <is>
-          <t>BusinessLine</t>
-        </is>
-      </c>
-      <c r="E89" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F89" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G89" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B90" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 02:06</t>
-        </is>
-      </c>
-      <c r="C90" s="51" t="inlineStr">
-        <is>
-          <t>Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...</t>
-        </is>
-      </c>
-      <c r="D90" s="51" t="inlineStr">
-        <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E90" s="80" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="F90" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G90" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B91" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 01:28</t>
-        </is>
-      </c>
-      <c r="C91" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Today: Gift Nifty, Bond Yields To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On September 25</t>
-        </is>
-      </c>
-      <c r="D91" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E91" s="80" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="F91" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G91" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B92" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-25 01:15</t>
-        </is>
-      </c>
-      <c r="C92" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for 25 Sept 2026 | GIFT Nifty, Nikkei, Taiwan cues to watch</t>
-        </is>
-      </c>
-      <c r="D92" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E92" s="80" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="F92" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G92" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B93" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 17:13</t>
-        </is>
-      </c>
-      <c r="C93" s="51" t="inlineStr">
-        <is>
-          <t>3 Indian Nuclear Stocks With Revenue Growth Up To 16%</t>
-        </is>
-      </c>
-      <c r="D93" s="51" t="inlineStr">
-        <is>
-          <t>Simply Wall St.</t>
-        </is>
-      </c>
-      <c r="E93" s="80" t="n">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="F93" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G93" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B94" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 16:46</t>
-        </is>
-      </c>
-      <c r="C94" s="51" t="inlineStr">
-        <is>
-          <t>R R Kabel acquires U M Cables business for Rs. 77 crores</t>
-        </is>
-      </c>
-      <c r="D94" s="51" t="inlineStr">
-        <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="E94" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G94" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B95" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 16:31</t>
-        </is>
-      </c>
-      <c r="C95" s="51" t="inlineStr">
-        <is>
-          <t>Usha Martin announces Rs. 77 crore slump sale of U M Cables to R R Kabel</t>
-        </is>
-      </c>
-      <c r="D95" s="51" t="inlineStr">
-        <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="E95" s="80" t="n">
-        <v>-0.494</v>
-      </c>
-      <c r="F95" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G95" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B96" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 16:21</t>
-        </is>
-      </c>
-      <c r="C96" s="51" t="inlineStr">
-        <is>
-          <t>R R Kabel acquires U M Cables business for ₹77 crore</t>
-        </is>
-      </c>
-      <c r="D96" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E96" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G96" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B97" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 16:04</t>
-        </is>
-      </c>
-      <c r="C97" s="51" t="inlineStr">
-        <is>
-          <t>Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets</t>
-        </is>
-      </c>
-      <c r="D97" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E97" s="80" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F97" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G97" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="51" t="inlineStr">
-        <is>
-          <t>ACUTAAS</t>
-        </is>
-      </c>
-      <c r="B98" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 14:42</t>
-        </is>
-      </c>
-      <c r="C98" s="51" t="inlineStr">
-        <is>
-          <t>Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics</t>
-        </is>
-      </c>
-      <c r="D98" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E98" s="80" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="F98" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G98" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B99" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:49</t>
-        </is>
-      </c>
-      <c r="C99" s="51" t="inlineStr">
-        <is>
-          <t>Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month</t>
-        </is>
-      </c>
-      <c r="D99" s="51" t="inlineStr">
-        <is>
-          <t>economictimes.com</t>
-        </is>
-      </c>
-      <c r="E99" s="80" t="n">
-        <v>-0.153</v>
-      </c>
-      <c r="F99" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G99" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B100" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:01</t>
-        </is>
-      </c>
-      <c r="C100" s="51" t="inlineStr">
-        <is>
-          <t>3 Indian Export Stocks That Could Benefit From A Weaker Rupee</t>
-        </is>
-      </c>
-      <c r="D100" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E100" s="80" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F100" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G100" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B101" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 12:51</t>
-        </is>
-      </c>
-      <c r="C101" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty slide on intense selloff, banking and financial stocks hit</t>
-        </is>
-      </c>
-      <c r="D101" s="51" t="inlineStr">
-        <is>
-          <t>The South First</t>
-        </is>
-      </c>
-      <c r="E101" s="80" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F101" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G101" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B102" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 12:36</t>
-        </is>
-      </c>
-      <c r="C102" s="51" t="inlineStr">
-        <is>
-          <t>Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026</t>
-        </is>
-      </c>
-      <c r="D102" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E102" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F102" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G102" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B103" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 12:02</t>
-        </is>
-      </c>
-      <c r="C103" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty down over 1.6%: How crude oil, bond yields hit Indian markets</t>
-        </is>
-      </c>
-      <c r="D103" s="51" t="inlineStr">
-        <is>
-          <t>The Indian Express</t>
-        </is>
-      </c>
-      <c r="E103" s="80" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="F103" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G103" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B104" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 11:51</t>
-        </is>
-      </c>
-      <c r="C104" s="51" t="inlineStr">
-        <is>
-          <t>Gift Nifty Signals Higher Opening After Sensex, Nifty Crash</t>
-        </is>
-      </c>
-      <c r="D104" s="51" t="inlineStr">
-        <is>
-          <t>hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="E104" s="80" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="F104" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G104" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B105" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 11:21</t>
-        </is>
-      </c>
-      <c r="C105" s="51" t="inlineStr">
-        <is>
-          <t>Sensex closes in red, Nifty settles below 23,100 on spike in crude oil</t>
-        </is>
-      </c>
-      <c r="D105" s="51" t="inlineStr">
-        <is>
-          <t>DD News</t>
-        </is>
-      </c>
-      <c r="E105" s="80" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F105" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G105" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B106" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 11:20</t>
-        </is>
-      </c>
-      <c r="C106" s="51" t="inlineStr">
-        <is>
-          <t>NSE shares end debut at ₹1,818, gain 1.85%; BSE slips nearly 3% amid broader market sell-off</t>
-        </is>
-      </c>
-      <c r="D106" s="51" t="inlineStr">
-        <is>
-          <t>fortuneindia.com</t>
-        </is>
-      </c>
-      <c r="E106" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G106" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B107" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 11:01</t>
-        </is>
-      </c>
-      <c r="C107" s="51" t="inlineStr">
-        <is>
-          <t>SENSEX Nifty Today: Nifty Settles at 23,063; Sensex Crashes1200 Points as Crude Oil Surges Above $105; India VIX Jumps 25%</t>
-        </is>
-      </c>
-      <c r="D107" s="51" t="inlineStr">
-        <is>
-          <t>India Infoline</t>
-        </is>
-      </c>
-      <c r="E107" s="80" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="F107" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G107" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B108" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:57</t>
-        </is>
-      </c>
-      <c r="C108" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty see worst day in weeks: Why was market down today? | Business News</t>
-        </is>
-      </c>
-      <c r="D108" s="51" t="inlineStr">
-        <is>
-          <t>Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E108" s="80" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="F108" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G108" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B109" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:44</t>
-        </is>
-      </c>
-      <c r="C109" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Today: Sensex Crashes 1,200 Points, Nifty Falls</t>
-        </is>
-      </c>
-      <c r="D109" s="51" t="inlineStr">
-        <is>
-          <t>apacnewsnetwork.com</t>
-        </is>
-      </c>
-      <c r="E109" s="80" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F109" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G109" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B110" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:40</t>
-        </is>
-      </c>
-      <c r="C110" s="51" t="inlineStr">
-        <is>
-          <t>Sensex plunges 1,248 points, Nifty nosedives 1.64%; five factors behind market slump</t>
-        </is>
-      </c>
-      <c r="D110" s="51" t="inlineStr">
-        <is>
-          <t>fortuneindia.com</t>
-        </is>
-      </c>
-      <c r="E110" s="80" t="n">
-        <v>-0.612</v>
-      </c>
-      <c r="F110" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G110" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="51" t="inlineStr">
-        <is>
-          <t>TDPOWERSYS</t>
-        </is>
-      </c>
-      <c r="B111" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:15</t>
-        </is>
-      </c>
-      <c r="C111" s="51" t="inlineStr">
-        <is>
-          <t>TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026</t>
-        </is>
-      </c>
-      <c r="D111" s="51" t="inlineStr">
-        <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E111" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G111" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B112" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:06</t>
-        </is>
-      </c>
-      <c r="C112" s="51" t="inlineStr">
-        <is>
-          <t>Stock markets hit three-month low: Sensex drops over 1,200 points</t>
-        </is>
-      </c>
-      <c r="D112" s="51" t="inlineStr">
-        <is>
-          <t>Telegraph India</t>
-        </is>
-      </c>
-      <c r="E112" s="80" t="n">
-        <v>-0.402</v>
-      </c>
-      <c r="F112" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G112" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B113" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:00</t>
-        </is>
-      </c>
-      <c r="C113" s="51" t="inlineStr">
-        <is>
-          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks</t>
-        </is>
-      </c>
-      <c r="D113" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E113" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G113" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B114" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:42</t>
-        </is>
-      </c>
-      <c r="C114" s="51" t="inlineStr">
-        <is>
-          <t>The battle between India’s stock exchanges is heating up again</t>
-        </is>
-      </c>
-      <c r="D114" s="51" t="inlineStr">
-        <is>
-          <t>The Economist</t>
-        </is>
-      </c>
-      <c r="E114" s="80" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="F114" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G114" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B115" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:40</t>
-        </is>
-      </c>
-      <c r="C115" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss</t>
-        </is>
-      </c>
-      <c r="D115" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E115" s="80" t="n">
-        <v>-0.758</v>
-      </c>
-      <c r="F115" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G115" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B116" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:08</t>
-        </is>
-      </c>
-      <c r="C116" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday</t>
-        </is>
-      </c>
-      <c r="D116" s="51" t="inlineStr">
-        <is>
-          <t>CNBC TV18</t>
-        </is>
-      </c>
-      <c r="E116" s="80" t="n">
-        <v>-0.273</v>
-      </c>
-      <c r="F116" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G116" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B117" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:04</t>
-        </is>
-      </c>
-      <c r="C117" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Tumbles 1,200 Points, Nifty Cracks Below 23,100 – Key Reasons Behind Sell-Off</t>
-        </is>
-      </c>
-      <c r="D117" s="51" t="inlineStr">
-        <is>
-          <t>Outlook Money</t>
-        </is>
-      </c>
-      <c r="E117" s="80" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="F117" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G117" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B118" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:02</t>
-        </is>
-      </c>
-      <c r="C118" s="51" t="inlineStr">
-        <is>
-          <t>Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today</t>
-        </is>
-      </c>
-      <c r="D118" s="51" t="inlineStr">
-        <is>
-          <t>NDTV</t>
-        </is>
-      </c>
-      <c r="E118" s="80" t="n">
-        <v>-0.402</v>
-      </c>
-      <c r="F118" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G118" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B119" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 08:52</t>
-        </is>
-      </c>
-      <c r="C119" s="51" t="inlineStr">
-        <is>
-          <t>Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall</t>
-        </is>
-      </c>
-      <c r="D119" s="51" t="inlineStr">
-        <is>
-          <t>The Times of India</t>
-        </is>
-      </c>
-      <c r="E119" s="80" t="n">
-        <v>-0.402</v>
-      </c>
-      <c r="F119" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G119" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B120" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 08:50</t>
-        </is>
-      </c>
-      <c r="C120" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Crash: Investors Lose Rs 3.93 Lakh Crore As Sensex, Nifty Hit Three-Month Low</t>
-        </is>
-      </c>
-      <c r="D120" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E120" s="80" t="n">
-        <v>-0.758</v>
-      </c>
-      <c r="F120" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G120" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="51" t="inlineStr">
-        <is>
-          <t>AEROFLEX</t>
-        </is>
-      </c>
-      <c r="B121" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 08:46</t>
-        </is>
-      </c>
-      <c r="C121" s="51" t="inlineStr">
-        <is>
-          <t>Hero Motors Ltd leads gainers in 'B' group</t>
-        </is>
-      </c>
-      <c r="D121" s="51" t="inlineStr">
-        <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E121" s="80" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="F121" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G121" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="51" t="inlineStr">
-        <is>
-          <t>TDPOWERSYS</t>
-        </is>
-      </c>
-      <c r="B122" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 08:35</t>
-        </is>
-      </c>
-      <c r="C122" s="51" t="inlineStr">
-        <is>
-          <t>TD Power Systems Share Price today: decline and analysis</t>
-        </is>
-      </c>
-      <c r="D122" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E122" s="80" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="F122" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G122" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B123" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 08:21</t>
-        </is>
-      </c>
-      <c r="C123" s="51" t="inlineStr">
-        <is>
-          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer</t>
-        </is>
-      </c>
-      <c r="D123" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E123" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G123" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B124" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 07:35</t>
-        </is>
-      </c>
-      <c r="C124" s="51" t="inlineStr">
-        <is>
-          <t>Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices</t>
-        </is>
-      </c>
-      <c r="D124" s="51" t="inlineStr">
-        <is>
-          <t>theweek.in</t>
-        </is>
-      </c>
-      <c r="E124" s="80" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F124" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G124" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B125" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 07:25</t>
-        </is>
-      </c>
-      <c r="C125" s="51" t="inlineStr">
-        <is>
-          <t>Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom — Ask Profit</t>
-        </is>
-      </c>
-      <c r="D125" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E125" s="80" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="F125" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G125" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B126" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 06:33</t>
-        </is>
-      </c>
-      <c r="C126" s="51" t="inlineStr">
-        <is>
-          <t>NSE Share Price Rises 3.45%: IFCI, New India Assurance, GIC Re in Focus After NSE IPO Listing</t>
-        </is>
-      </c>
-      <c r="D126" s="51" t="inlineStr">
-        <is>
-          <t>India Infoline</t>
-        </is>
-      </c>
-      <c r="E126" s="80" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F126" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G126" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="51" t="inlineStr">
-        <is>
-          <t>AEROFLEX</t>
-        </is>
-      </c>
-      <c r="B127" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 06:20</t>
-        </is>
-      </c>
-      <c r="C127" s="51" t="inlineStr">
-        <is>
-          <t>Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest</t>
-        </is>
-      </c>
-      <c r="D127" s="51" t="inlineStr">
-        <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E127" s="80" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="F127" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G127" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B128" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 05:58</t>
-        </is>
-      </c>
-      <c r="C128" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Tomorrow: NSE, BSE Open on September 25</t>
-        </is>
-      </c>
-      <c r="D128" s="51" t="inlineStr">
-        <is>
-          <t>hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="E128" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G128" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B129" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 05:29</t>
-        </is>
-      </c>
-      <c r="C129" s="51" t="inlineStr">
-        <is>
-          <t>Stock Markets Today: Sensex, Nifty in Red; BSE tanked over 600 points</t>
-        </is>
-      </c>
-      <c r="D129" s="51" t="inlineStr">
-        <is>
-          <t>Rediff</t>
-        </is>
-      </c>
-      <c r="E129" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F129" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G129" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B130" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 04:55</t>
-        </is>
-      </c>
-      <c r="C130" s="51" t="inlineStr">
-        <is>
-          <t>Sensex opens in red, Nifty below 23,300 points</t>
-        </is>
-      </c>
-      <c r="D130" s="51" t="inlineStr">
-        <is>
-          <t>DD India</t>
-        </is>
-      </c>
-      <c r="E130" s="80" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F130" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G130" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B131" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 04:44</t>
-        </is>
-      </c>
-      <c r="C131" s="51" t="inlineStr">
-        <is>
-          <t>Sensex crashed over 1,200 points: Why stock market fell today?</t>
-        </is>
-      </c>
-      <c r="D131" s="51" t="inlineStr">
-        <is>
-          <t>India Today</t>
-        </is>
-      </c>
-      <c r="E131" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G131" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B132" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 04:31</t>
-        </is>
-      </c>
-      <c r="C132" s="51" t="inlineStr">
-        <is>
-          <t>NSE vs BSE: Which exchange should now be the preferred bet for investors?</t>
-        </is>
-      </c>
-      <c r="D132" s="51" t="inlineStr">
-        <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E132" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G132" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B133" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 04:12</t>
-        </is>
-      </c>
-      <c r="C133" s="51" t="inlineStr">
-        <is>
-          <t>Indian Stocks Slide At Open As Nifty, Sensex Extend Market Weakness</t>
-        </is>
-      </c>
-      <c r="D133" s="51" t="inlineStr">
-        <is>
-          <t>Investing.com India</t>
-        </is>
-      </c>
-      <c r="E133" s="80" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="F133" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G133" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B134" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 04:09</t>
-        </is>
-      </c>
-      <c r="C134" s="51" t="inlineStr">
-        <is>
-          <t>Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'</t>
-        </is>
-      </c>
-      <c r="D134" s="51" t="inlineStr">
-        <is>
-          <t>economictimes.com</t>
-        </is>
-      </c>
-      <c r="E134" s="80" t="n">
-        <v>-0.273</v>
-      </c>
-      <c r="F134" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G134" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B135" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 04:02</t>
-        </is>
-      </c>
-      <c r="C135" s="51" t="inlineStr">
-        <is>
-          <t>Stock market crash: Nifty 50, Sensex fall 1% as crude tops $102; financial, insurance stocks slide on IRDAI proposal</t>
-        </is>
-      </c>
-      <c r="D135" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E135" s="80" t="n">
-        <v>-0.599</v>
-      </c>
-      <c r="F135" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G135" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B136" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 03:56</t>
-        </is>
-      </c>
-      <c r="C136" s="51" t="inlineStr">
-        <is>
-          <t>Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash</t>
-        </is>
-      </c>
-      <c r="D136" s="51" t="inlineStr">
-        <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E136" s="80" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F136" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G136" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B137" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 02:46</t>
-        </is>
-      </c>
-      <c r="C137" s="51" t="inlineStr">
-        <is>
-          <t>Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs</t>
-        </is>
-      </c>
-      <c r="D137" s="51" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="E137" s="80" t="n">
-        <v>-0.625</v>
-      </c>
-      <c r="F137" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G137" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B138" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 02:44</t>
-        </is>
-      </c>
-      <c r="C138" s="51" t="inlineStr">
-        <is>
-          <t>US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact</t>
-        </is>
-      </c>
-      <c r="D138" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E138" s="80" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="F138" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G138" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B139" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 02:38</t>
-        </is>
-      </c>
-      <c r="C139" s="51" t="inlineStr">
-        <is>
-          <t>GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...</t>
-        </is>
-      </c>
-      <c r="D139" s="51" t="inlineStr">
-        <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E139" s="80" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="F139" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G139" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B140" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 01:42</t>
-        </is>
-      </c>
-      <c r="C140" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields — Five Key Factors For Sensex, Nifty 50 On Sept 24</t>
-        </is>
-      </c>
-      <c r="D140" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E140" s="80" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="F140" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G140" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B141" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 01:17</t>
-        </is>
-      </c>
-      <c r="C141" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals</t>
-        </is>
-      </c>
-      <c r="D141" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E141" s="80" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="F141" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G141" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B142" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 22:57</t>
-        </is>
-      </c>
-      <c r="C142" s="51" t="inlineStr">
-        <is>
-          <t>Laurus Labs stock gains 1.37 percent as profit jumps 126 percent</t>
-        </is>
-      </c>
-      <c r="D142" s="51" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="E142" s="80" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="F142" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G142" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B143" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 12:57</t>
-        </is>
-      </c>
-      <c r="C143" s="51" t="inlineStr">
-        <is>
-          <t>Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month</t>
-        </is>
-      </c>
-      <c r="D143" s="51" t="inlineStr">
-        <is>
-          <t>economictimes.com</t>
-        </is>
-      </c>
-      <c r="E143" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G143" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="51" t="inlineStr">
-        <is>
-          <t>DIACABS</t>
-        </is>
-      </c>
-      <c r="B144" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 10:02</t>
-        </is>
-      </c>
-      <c r="C144" s="51" t="inlineStr">
-        <is>
-          <t>Diamond Power Infrastructure Share Price Rises 2.68% Today</t>
-        </is>
-      </c>
-      <c r="D144" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E144" s="80" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F144" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G144" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B145" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 09:19</t>
-        </is>
-      </c>
-      <c r="C145" s="51" t="inlineStr">
-        <is>
-          <t>Laurus Labs Share Price: one-year high and valuation view</t>
-        </is>
-      </c>
-      <c r="D145" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E145" s="80" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="F145" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G145" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B146" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 07:59</t>
-        </is>
-      </c>
-      <c r="C146" s="51" t="inlineStr">
-        <is>
-          <t>NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details</t>
-        </is>
-      </c>
-      <c r="D146" s="51" t="inlineStr">
-        <is>
-          <t>The Times of India</t>
-        </is>
-      </c>
-      <c r="E146" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G146" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="51" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="B147" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 07:26</t>
-        </is>
-      </c>
-      <c r="C147" s="51" t="inlineStr">
-        <is>
-          <t>E2E Networks Share Price news: price rise and valuation</t>
-        </is>
-      </c>
-      <c r="D147" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E147" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G147" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="51" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B148" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 06:24</t>
-        </is>
-      </c>
-      <c r="C148" s="51" t="inlineStr">
-        <is>
-          <t>Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings</t>
-        </is>
-      </c>
-      <c r="D148" s="51" t="inlineStr">
-        <is>
-          <t>economictimes.com</t>
-        </is>
-      </c>
-      <c r="E148" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G148" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B149" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 05:56</t>
-        </is>
-      </c>
-      <c r="C149" s="51" t="inlineStr">
-        <is>
-          <t>3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%</t>
-        </is>
-      </c>
-      <c r="D149" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E149" s="80" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="F149" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G149" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B150" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 01:13</t>
-        </is>
-      </c>
-      <c r="C150" s="51" t="inlineStr">
-        <is>
-          <t>Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal</t>
-        </is>
-      </c>
-      <c r="D150" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E150" s="80" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="F150" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G150" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B151" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-23 00:46</t>
-        </is>
-      </c>
-      <c r="C151" s="51" t="inlineStr">
-        <is>
-          <t>Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors</t>
-        </is>
-      </c>
-      <c r="D151" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E151" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G151" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B152" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:04</t>
-        </is>
-      </c>
-      <c r="C152" s="51" t="inlineStr">
-        <is>
-          <t>Sensex drops 330 points, Nifty down to 23,329 dragged by IT stocks</t>
-        </is>
-      </c>
-      <c r="D152" s="51" t="inlineStr">
-        <is>
-          <t>The Hindu</t>
-        </is>
-      </c>
-      <c r="E152" s="80" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="F152" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G152" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="51" t="inlineStr">
-        <is>
-          <t>ACUTAAS</t>
-        </is>
-      </c>
-      <c r="B153" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-22 08:51</t>
-        </is>
-      </c>
-      <c r="C153" s="51" t="inlineStr">
-        <is>
-          <t>Acutaas Chemicals to host investor meet at PL Capital conference on Sep 28</t>
-        </is>
-      </c>
-      <c r="D153" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E153" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G153" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="51" t="inlineStr">
-        <is>
-          <t>ACUTAAS</t>
-        </is>
-      </c>
-      <c r="B154" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-22 07:31</t>
-        </is>
-      </c>
-      <c r="C154" s="51" t="inlineStr">
-        <is>
-          <t>Acutaas Chemicals NSE:ACUTAAS Trading Window Closure Q2 FY27</t>
-        </is>
-      </c>
-      <c r="D154" s="51" t="inlineStr">
-        <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E154" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G154" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="51" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="B155" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-22 07:22</t>
-        </is>
-      </c>
-      <c r="C155" s="51" t="inlineStr">
-        <is>
-          <t>Ather Energy Share Price News: Today’s Decline Explained</t>
-        </is>
-      </c>
-      <c r="D155" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E155" s="80" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="F155" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G155" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="51" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B156" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-22 07:19</t>
-        </is>
-      </c>
-      <c r="C156" s="51" t="inlineStr">
-        <is>
-          <t>RR Kabel Share Price Today: price rise and sector check</t>
-        </is>
-      </c>
-      <c r="D156" s="51" t="inlineStr">
-        <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E156" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G156" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="51" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B157" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-22 05:01</t>
-        </is>
-      </c>
-      <c r="C157" s="51" t="inlineStr">
-        <is>
-          <t>Kirloskar Oil Engines And 2 Indian Nuclear Power Stocks To Watch</t>
-        </is>
-      </c>
-      <c r="D157" s="51" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="E157" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G157" s="81" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B158" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-22 03:51</t>
-        </is>
-      </c>
-      <c r="C158" s="51" t="inlineStr">
-        <is>
-          <t>Stock market today: Sensex, Nifty see positive start; NSE IPO receives 6x subscription on final day | Business News</t>
-        </is>
-      </c>
-      <c r="D158" s="51" t="inlineStr">
-        <is>
-          <t>Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E158" s="80" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="F158" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G158" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -15565,7 +10245,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E158">
+  <conditionalFormatting sqref="E5:E6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1"/>
@@ -15580,158 +10260,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -15745,48 +10273,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"batch": {"batch_id": "2026-09-28", "title": "SwingScope batch 2026-09-28", "signal_date": "2026-09-28", "exit_date_est": "2026-10-27", "hold_sessions": 21, "universe": "liquidity top 400 of all NSE stocks", "capital": 139903.0, "est_costs": 859.0, "cost_pct": 0.6, "regime": "Down", "regime_note": "the signal's weakest regime historically", "warnings": "0 of 10", "evidence": ["Backtest, 2017\u20132026 | Replayed point in time on your survivorship-free archive. Not live results. | Signal strength | IC +0.041 | rank IC over 113 monthly dates, 2017-2026 (t 2.52); validated benchmark 0.026 | Top vs bottom decile | +1.89% | per 21-session hold, before costs (t 2.94) | Top-10 picks | +1.45% | per hold after 0.60% costs; Nifty 50 earned +1.02% before costs | Entry timing | Open wins | buying at the open beat all 30 support-entry rules (best -0.12% per hold) | Down markets | IC +0.009 | over 27 down-regime dates, against +0.050 over 86 up-regime dates", "Live record | No results yet | The first live result arrives when this system finishes its first batch. Live results are kept apart from the backtest and never mixed in."], "stocks": [{"rank": 1, "symbol": "TDPOWERSYS", "isin": "INE419M01035", "qty": 20, "last_close": 722.0, "amount": 14440.0, "spark_12m": "2.0,31.7 2.4,32.0 2.9,31.7 3.3,31.1 3.7,31.1 4.2,31.1 4.6,31.0 5.0,30.6 5.4,30.4 5.9,29.2 6.3,29.3 6.7,29.5 7.2,29.8 7.6,30.1 8.0,30.4 8.5,30.5 8.9,30.3 9.3,29.4 9.7,29.3 10.2,28.8 10.6,29.1 11.0,28.9 11.5,29.1 11.9,29.2 12.3,29.1 12.8,29.0 13.2,28.4 13.6,28.0 14.0,25.5 14.5,24.3 14.9,24.2 15.3,24.8 15.8,25.3 16.2,25.2 16.6,25.4 17.1,24.2 17.5,25.4 17.9,25.2 18.4,25.2 18.8,25.7 19.2,25.8 19.6,25.9 20.1,26.9 20.5,25.8 20.9,25.9 21.4,24.9 21.8,24.9 22.2,25.4 22.7,25.0 23.1,25.0 23.5,25.8 23.9,26.8 24.4,27.7 24.8,28.3 25.2,27.7 25.7,28.1 26.1,28.2 26.5,27.9 27.0,27.6 27.4,27.9 27.8,27.1 28.2,27.6 28.7,27.1 29.1,26.4 29.5,26.7 30.0,27.0 30.4,27.3 30.8,27.7 31.3,27.5 31.7,27.5 32.1,28.3 32.5,28.0 33.0,27.7 33.4,27.9 33.8,27.5 34.3,27.9 34.7,28.3 35.1,28.8 35.6,27.9 36.0,28.2 36.4,28.5 36.9,28.7 37.3,29.2 37.7,29.4 38.1,29.5 38.6,29.7 39.0,29.6 39.4,28.8 39.9,28.2 40.3,26.7 40.7,26.2 41.2,24.3 41.6,24.1 42.0,24.5 42.4,25.2 42.9,24.8 43.3,23.3 43.7,22.8 44.2,23.4 44.6,23.8 45.0,23.1 45.5,22.8 45.9,22.8 46.3,22.4 46.7,22.4 47.2,21.8 47.6,22.3 48.0,22.5 48.5,22.5 48.9,21.8 49.3,22.2 49.8,22.6 50.2,22.4 50.6,22.5 51.1,23.5 51.5,24.3 51.9,24.7 52.3,24.4 52.8,25.3 53.2,24.9 53.6,24.3 54.1,23.7 54.5,23.8 54.9,23.0 55.4,24.2 55.8,23.1 56.2,22.3 56.6,23.4 57.1,23.3 57.5,23.0 57.9,23.0 58.4,22.5 58.8,22.5 59.2,22.4 59.7,22.6 60.1,21.2 60.5,21.5 60.9,20.8 61.4,20.0 61.8,19.2 62.2,18.3 62.7,18.6 63.1,17.4 63.5,17.2 64.0,16.0 64.4,16.6 64.8,15.0 65.3,15.0 65.7,14.8 66.1,14.6 66.5,14.2 67.0,14.5 67.4,12.2 67.8,13.0 68.3,14.1 68.7,14.4 69.1,14.2 69.6,14.0 70.0,10.4 70.4,9.9 70.8,11.9 71.3,12.6 71.7,10.6 72.1,10.8 72.6,10.7 73.0,8.8 73.4,9.8 73.9,10.2 74.3,12.7 74.7,12.5 75.1,11.1 75.6,10.0 76.0,10.3 76.4,12.8 76.9,12.6 77.3,14.8 77.7,15.6 78.2,13.7 78.6,13.6 79.0,14.4 79.5,12.7 79.9,11.6 80.3,11.5 80.7,10.0 81.2,9.2 81.6,11.7 82.0,12.0 82.5,12.6 82.9,12.4 83.3,13.7 83.8,13.8 84.2,16.6 84.6,14.2 85.0,15.7 85.5,16.9 85.9,16.6 86.3,14.9 86.8,14.9 87.2,15.6 87.6,14.2 88.1,15.6 88.5,15.5 88.9,15.2 89.3,15.5 89.8,14.6 90.2,15.2 90.6,15.9 91.1,15.2 91.5,15.9 91.9,18.1 92.4,17.5 92.8,15.5 93.2,16.0 93.6,15.5 94.1,13.5 94.5,12.7 94.9,11.8 95.4,12.5 95.8,11.4 96.2,5.6 96.7,5.6 97.1,5.5 97.5,3.7 98.0,2.7 98.4,3.8 98.8,4.9 99.2,4.1 99.7,3.4 100.1,6.2 100.5,6.3 101.0,5.6 101.4,4.9 101.8,3.6 102.3,4.6 102.7,5.9 103.1,6.6 103.5,5.6 104.0,6.0 104.4,4.0 104.8,4.8 105.3,4.4 105.7,2.0 106.1,6.5 106.6,8.1 107.0,6.7 107.4,4.3 107.8,5.2 108.3,4.7 108.7,4.2 109.1,5.5 109.6,5.0 110.0,6.7", "ret_12_1": 177.0, "ret_6_1": 72.2, "ret_3_1": 19.6, "volatility": 60.1, "traded_daily_cr": 128.0, "watch": "Nothing flagged", "from_12m_high": -10.3, "signal_rank": 6, "data_quality": "Green"}, {"rank": 2, "symbol": "AEROFLEX", "isin": "INE024001021", "qty": 29, "last_close": 513.4, "amount": 14889.0, "spark_12m": "2.0,29.8 2.4,29.6 2.9,29.5 3.3,30.0 3.7,30.1 4.2,30.5 4.6,30.8 5.0,30.9 5.4,30.9 5.9,30.5 6.3,30.7 6.7,30.8 7.2,30.9 7.6,31.0 8.0,31.0 8.5,31.1 8.9,31.2 9.3,31.2 9.7,31.2 10.2,31.2 10.6,31.4 11.0,31.1 11.5,31.0 11.9,31.0 12.3,31.0 12.8,30.1 13.2,30.1 13.6,30.5 14.0,30.0 14.5,29.8 14.9,30.3 15.3,30.5 15.8,30.0 16.2,30.0 16.6,30.2 17.1,30.2 17.5,30.1 17.9,29.9 18.4,30.1 18.8,30.3 19.2,30.2 19.6,30.2 20.1,30.5 20.5,30.9 20.9,30.2 21.4,30.2 21.8,30.4 22.2,30.0 22.7,30.2 23.1,30.3 23.5,30.6 23.9,30.6 24.4,30.7 24.8,31.3 25.2,31.0 25.7,30.7 26.1,30.9 26.5,30.7 27.0,30.3 27.4,30.5 27.8,30.3 28.2,30.7 28.7,29.5 29.1,29.2 29.5,28.8 30.0,28.6 30.4,28.9 30.8,29.1 31.3,29.3 31.7,29.5 32.1,29.6 32.5,29.2 33.0,29.0 33.4,29.3 33.8,29.1 34.3,29.9 34.7,30.2 35.1,30.2 35.6,30.5 36.0,30.7 36.4,30.8 36.9,30.9 37.3,31.3 37.7,31.8 38.1,31.5 38.6,32.0 39.0,31.7 39.4,31.4 39.9,30.4 40.3,30.6 40.7,31.0 41.2,30.1 41.6,29.9 42.0,29.9 42.4,30.1 42.9,29.3 43.3,29.4 43.7,29.6 44.2,29.5 44.6,30.0 45.0,29.6 45.5,28.5 45.9,27.1 46.3,27.0 46.7,27.3 47.2,27.6 47.6,27.7 48.0,27.0 48.5,26.9 48.9,26.5 49.3,27.2 49.8,27.7 50.2,27.3 50.6,27.6 51.1,27.9 51.5,27.5 51.9,26.5 52.3,26.3 52.8,26.5 53.2,25.6 53.6,25.3 54.1,25.6 54.5,26.8 54.9,26.6 55.4,27.3 55.8,25.3 56.2,25.3 56.6,26.1 57.1,26.2 57.5,25.4 57.9,25.2 58.4,25.0 58.8,25.7 59.2,24.6 59.7,23.6 60.1,22.6 60.5,22.6 60.9,22.3 61.4,22.1 61.8,21.0 62.2,21.7 62.7,22.6 63.1,21.5 63.5,22.1 64.0,23.4 64.4,22.2 64.8,22.3 65.3,21.4 65.7,21.4 66.1,21.6 66.5,20.5 67.0,18.6 67.4,13.6 67.8,11.7 68.3,14.7 68.7,17.1 69.1,17.1 69.6,17.4 70.0,16.7 70.4,16.8 70.8,15.9 71.3,15.2 71.7,16.0 72.1,14.3 72.6,13.5 73.0,14.3 73.4,14.0 73.9,14.4 74.3,15.4 74.7,13.1 75.1,12.1 75.6,11.7 76.0,13.1 76.4,14.6 76.9,12.7 77.3,13.5 77.7,13.9 78.2,11.1 78.6,8.9 79.0,9.4 79.5,6.5 79.9,8.1 80.3,6.8 80.7,6.6 81.2,7.1 81.6,8.8 82.0,9.7 82.5,9.6 82.9,9.4 83.3,8.1 83.8,8.9 84.2,10.5 84.6,10.3 85.0,13.6 85.5,14.5 85.9,14.2 86.3,13.6 86.8,13.0 87.2,13.8 87.6,13.0 88.1,13.8 88.5,13.8 88.9,14.1 89.3,13.6 89.8,14.0 90.2,13.1 90.6,13.0 91.1,13.2 91.5,11.2 91.9,10.9 92.4,12.6 92.8,12.0 93.2,12.3 93.6,9.9 94.1,10.5 94.5,11.8 94.9,12.7 95.4,13.1 95.8,12.9 96.2,11.2 96.7,11.1 97.1,10.2 97.5,10.5 98.0,8.3 98.4,9.2 98.8,9.1 99.2,7.1 99.7,7.0 100.1,7.6 100.5,4.7 101.0,5.7 101.4,4.3 101.8,5.5 102.3,3.6 102.7,4.4 103.1,4.3 103.5,4.6 104.0,3.1 104.4,2.0 104.8,2.9 105.3,2.7 105.7,2.7 106.1,6.8 106.6,8.7 107.0,7.5 107.4,6.5 107.8,6.2 108.3,6.1 108.7,5.8 109.1,5.3 109.6,5.5 110.0,6.3", "ret_12_1": 175.0, "ret_6_1": 107.0, "ret_3_1": 10.7, "volatility": 67.3, "traded_daily_cr": 53.0, "watch": "Nothing flagged", "from_12m_high": -10.5, "signal_rank": 7, "data_quality": "Green"}, {"rank": 3, "symbol": "ATHERENERG", "isin": "INE0LEZ01016", "qty": 10, "last_close": 1454.9, "amount": 14549.0, "spark_12m": "2.0,30.9 2.4,30.7 2.9,31.2 3.3,30.9 3.7,31.6 4.2,32.0 4.6,31.0 5.0,31.4 5.4,30.8 5.9,30.7 6.3,30.0 6.7,29.7 7.2,29.5 7.6,29.9 8.0,30.6 8.5,30.2 8.9,30.1 9.3,29.6 9.7,28.2 10.2,28.1 10.6,27.4 11.0,26.3 11.5,27.1 11.9,27.8 12.3,27.1 12.8,27.0 13.2,27.8 13.6,27.8 14.0,28.2 14.5,28.2 14.9,28.8 15.3,29.6 15.8,29.1 16.2,29.8 16.6,29.0 17.1,29.8 17.5,29.5 17.9,29.2 18.4,29.3 18.8,28.7 19.2,28.3 19.6,28.0 20.1,28.1 20.5,28.6 20.9,28.3 21.4,28.1 21.8,27.7 22.2,27.5 22.7,27.7 23.1,28.3 23.5,28.4 23.9,28.7 24.4,28.6 24.8,28.5 25.2,29.2 25.7,29.3 26.1,29.3 26.5,29.3 27.0,28.3 27.4,28.6 27.8,28.9 28.2,28.9 28.7,27.9 29.1,28.0 29.5,27.8 30.0,27.4 30.4,27.7 30.8,27.5 31.3,27.1 31.7,26.6 32.1,27.0 32.5,26.9 33.0,28.3 33.4,28.1 33.8,28.1 34.3,28.6 34.7,29.6 35.1,29.5 35.6,29.1 36.0,29.3 36.4,30.0 36.9,29.8 37.3,30.3 37.7,30.1 38.1,29.7 38.6,29.9 39.0,30.0 39.4,30.3 39.9,30.4 40.3,29.9 40.7,30.3 41.2,28.6 41.6,28.0 42.0,27.6 42.4,27.8 42.9,27.3 43.3,27.3 43.7,27.5 44.2,27.3 44.6,27.7 45.0,27.7 45.5,27.3 45.9,27.2 46.3,27.1 46.7,27.7 47.2,27.5 47.6,28.0 48.0,27.8 48.5,27.9 48.9,27.7 49.3,27.8 49.8,27.9 50.2,28.3 50.6,28.6 51.1,28.4 51.5,28.1 51.9,27.9 52.3,27.7 52.8,27.8 53.2,27.6 53.6,27.3 54.1,26.7 54.5,26.6 54.9,25.9 55.4,26.7 55.8,26.5 56.2,26.0 56.6,25.5 57.1,26.6 57.5,26.2 57.9,26.4 58.4,25.8 58.8,26.4 59.2,26.2 59.7,24.9 60.1,23.8 60.5,22.7 60.9,23.6 61.4,23.7 61.8,24.1 62.2,23.2 62.7,23.0 63.1,22.7 63.5,22.9 64.0,23.3 64.4,21.8 64.8,22.1 65.3,21.9 65.7,22.0 66.1,22.0 66.5,21.9 67.0,23.0 67.4,22.7 67.8,22.5 68.3,21.1 68.7,22.3 69.1,21.6 69.6,21.9 70.0,21.9 70.4,22.6 70.8,22.6 71.3,22.7 71.7,23.2 72.1,23.3 72.6,22.3 73.0,21.6 73.4,21.5 73.9,21.3 74.3,21.9 74.7,21.4 75.1,19.8 75.6,20.7 76.0,19.5 76.4,20.3 76.9,19.5 77.3,19.3 77.7,19.7 78.2,19.6 78.6,19.7 79.0,20.4 79.5,20.6 79.9,21.1 80.3,21.1 80.7,21.4 81.2,20.2 81.6,20.6 82.0,20.4 82.5,18.2 82.9,16.8 83.3,17.1 83.8,16.7 84.2,17.1 84.6,17.2 85.0,16.8 85.5,15.3 85.9,14.8 86.3,14.6 86.8,15.7 87.2,15.3 87.6,12.9 88.1,13.6 88.5,13.2 88.9,12.9 89.3,13.1 89.8,13.6 90.2,14.5 90.6,15.1 91.1,14.9 91.5,15.2 91.9,14.1 92.4,14.3 92.8,13.8 93.2,13.5 93.6,9.0 94.1,8.4 94.5,8.9 94.9,8.2 95.4,8.6 95.8,7.1 96.2,6.0 96.7,7.0 97.1,7.4 97.5,8.1 98.0,8.6 98.4,9.3 98.8,9.0 99.2,8.7 99.7,8.9 100.1,9.2 100.5,7.8 101.0,7.8 101.4,4.8 101.8,2.2 102.3,2.0 102.7,3.0 103.1,4.2 103.5,5.6 104.0,5.2 104.4,5.7 104.8,5.7 105.3,3.7 105.7,3.8 106.1,6.0 106.6,6.0 107.0,6.4 107.4,4.2 107.8,5.4 108.3,6.6 108.7,7.7 109.1,7.7 109.6,7.8 110.0,8.8", "ret_12_1": 166.0, "ret_6_1": 97.5, "ret_3_1": 31.1, "volatility": 49.4, "traded_daily_cr": 493.0, "watch": "Nothing flagged", "from_12m_high": -15.7, "signal_rank": 9, "data_quality": "Green"}, {"rank": 4, "symbol": "THANGAMAYL", "isin": "INE085J01014", "qty": 2, "last_close": 5011.5, "amount": 10023.0, "spark_12m": "2.0,30.9 2.4,31.1 2.9,31.4 3.3,31.4 3.7,31.4 4.2,31.6 4.6,31.7 5.0,31.6 5.4,31.6 5.9,31.2 6.3,31.3 6.7,31.6 7.2,31.2 7.6,31.5 8.0,31.6 8.5,31.5 8.9,31.8 9.3,31.9 9.7,31.9 10.2,31.9 10.6,31.9 11.0,31.9 11.5,32.0 11.9,31.5 12.3,31.6 12.8,31.3 13.2,31.4 13.6,31.3 14.0,30.8 14.5,28.3 14.9,25.9 15.3,25.7 15.8,23.9 16.2,25.3 16.6,24.8 17.1,24.1 17.5,24.4 17.9,24.5 18.4,24.7 18.8,24.9 19.2,25.1 19.6,25.2 20.1,26.0 20.5,24.8 20.9,24.8 21.4,24.7 21.8,24.8 22.2,24.7 22.7,24.1 23.1,25.2 23.5,24.6 23.9,24.8 24.4,24.9 24.8,25.2 25.2,24.7 25.7,24.9 26.1,24.9 26.5,25.0 27.0,25.0 27.4,24.9 27.8,24.4 28.2,24.6 28.7,24.2 29.1,23.8 29.5,23.7 30.0,24.5 30.4,25.0 30.8,25.0 31.3,25.0 31.7,24.9 32.1,24.7 32.5,24.8 33.0,24.2 33.4,23.4 33.8,21.4 34.3,21.2 34.7,22.7 35.1,22.3 35.6,21.9 36.0,21.5 36.4,21.8 36.9,22.1 37.3,22.1 37.7,21.2 38.1,22.6 38.6,22.9 39.0,23.8 39.4,22.8 39.9,23.4 40.3,24.3 40.7,24.9 41.2,25.1 41.6,24.5 42.0,25.1 42.4,23.9 42.9,22.1 43.3,22.2 43.7,22.3 44.2,22.5 44.6,22.9 45.0,22.1 45.5,22.3 45.9,22.6 46.3,23.4 46.7,23.0 47.2,22.8 47.6,22.0 48.0,21.5 48.5,21.0 48.9,20.8 49.3,21.4 49.8,22.7 50.2,22.6 50.6,22.2 51.1,22.9 51.5,22.1 51.9,23.1 52.3,23.0 52.8,23.3 53.2,23.6 53.6,23.4 54.1,23.3 54.5,24.1 54.9,24.3 55.4,25.2 55.8,24.4 56.2,22.8 56.6,23.7 57.1,23.7 57.5,23.0 57.9,23.1 58.4,21.9 58.8,21.3 59.2,20.3 59.7,20.0 60.1,19.8 60.5,19.5 60.9,19.1 61.4,19.0 61.8,19.3 62.2,19.8 62.7,19.8 63.1,20.4 63.5,21.7 64.0,21.7 64.4,20.8 64.8,20.7 65.3,20.6 65.7,20.8 66.1,20.6 66.5,20.7 67.0,20.1 67.4,19.9 67.8,19.1 68.3,20.5 68.7,22.4 69.1,22.5 69.6,22.7 70.0,22.8 70.4,23.1 70.8,22.5 71.3,21.8 71.7,21.3 72.1,21.6 72.6,21.5 73.0,21.6 73.4,21.0 73.9,19.4 74.3,18.9 74.7,17.2 75.1,16.1 75.6,12.0 76.0,13.0 76.4,12.2 76.9,12.3 77.3,12.4 77.7,12.6 78.2,12.2 78.6,12.1 79.0,12.4 79.5,11.4 79.9,12.5 80.3,12.4 80.7,11.8 81.2,12.8 81.6,12.4 82.0,11.6 82.5,10.0 82.9,7.1 83.3,9.6 83.8,7.6 84.2,8.4 84.6,7.7 85.0,7.2 85.5,4.8 85.9,6.0 86.3,6.3 86.8,8.0 87.2,6.8 87.6,5.9 88.1,7.2 88.5,6.9 88.9,7.2 89.3,6.8 89.8,6.7 90.2,4.5 90.6,4.3 91.1,2.0 91.5,2.8 91.9,6.8 92.4,10.4 92.8,13.7 93.2,15.1 93.6,16.5 94.1,15.2 94.5,14.1 94.9,13.4 95.4,13.0 95.8,13.7 96.2,13.1 96.7,13.4 97.1,12.5 97.5,13.0 98.0,12.2 98.4,12.0 98.8,12.4 99.2,12.2 99.7,12.2 100.1,12.7 100.5,12.2 101.0,12.1 101.4,12.5 101.8,12.6 102.3,13.2 102.7,13.6 103.1,13.3 103.5,13.1 104.0,12.3 104.4,12.9 104.8,14.3 105.3,14.5 105.7,14.2 106.1,15.4 106.6,15.3 107.0,16.0 107.4,14.7 107.8,15.3 108.3,14.3 108.7,13.2 109.1,14.4 109.6,14.2 110.0,14.9", "ret_12_1": 154.0, "ret_6_1": 66.3, "ret_3_1": -14.0, "volatility": 59.8, "traded_daily_cr": 71.0, "watch": "Nothing flagged", "from_12m_high": -31.4, "signal_rank": 11, "data_quality": "Green"}, {"rank": 5, "symbol": "RRKABEL", "isin": "INE777K01022", "qty": 6, "last_close": 2459.8, "amount": 14759.0, "spark_12m": "2.0,31.3 2.4,31.1 2.9,30.7 3.3,31.2 3.7,31.2 4.2,32.0 4.6,31.8 5.0,31.2 5.4,31.1 5.9,31.4 6.3,31.1 6.7,31.1 7.2,31.3 7.6,31.4 8.0,31.0 8.5,31.2 8.9,31.3 9.3,31.3 9.7,31.0 10.2,31.2 10.6,31.4 11.0,31.2 11.5,31.4 11.9,31.5 12.3,30.1 12.8,28.7 13.2,28.4 13.6,28.6 14.0,28.6 14.5,29.0 14.9,28.4 15.3,28.8 15.8,29.2 16.2,29.8 16.6,29.6 17.1,28.8 17.5,29.3 17.9,29.3 18.4,29.1 18.8,29.7 19.2,29.5 19.6,29.4 20.1,29.7 20.5,29.7 20.9,29.5 21.4,29.0 21.8,29.1 22.2,28.8 22.7,28.8 23.1,28.8 23.5,29.0 23.9,28.9 24.4,29.4 24.8,29.5 25.2,29.1 25.7,28.6 26.1,28.7 26.5,28.4 27.0,27.8 27.4,28.1 27.8,28.3 28.2,28.3 28.7,27.3 29.1,26.5 29.5,26.6 30.0,27.1 30.4,27.5 30.8,28.1 31.3,28.2 31.7,27.9 32.1,27.6 32.5,26.9 33.0,26.4 33.4,26.3 33.8,26.4 34.3,26.7 34.7,26.9 35.1,27.3 35.6,27.0 36.0,27.1 36.4,27.5 36.9,28.0 37.3,28.6 37.7,28.6 38.1,28.4 38.6,29.7 39.0,30.0 39.4,29.7 39.9,30.3 40.3,29.3 40.7,29.6 41.2,28.4 41.6,27.8 42.0,27.5 42.4,27.7 42.9,27.6 43.3,28.5 43.7,28.2 44.2,28.3 44.6,28.7 45.0,28.7 45.5,28.4 45.9,28.5 46.3,28.4 46.7,28.1 47.2,27.9 47.6,27.0 48.0,26.9 48.5,26.7 48.9,26.0 49.3,26.5 49.8,27.3 50.2,27.1 50.6,26.6 51.1,27.2 51.5,27.8 51.9,28.4 52.3,28.2 52.8,29.8 53.2,29.3 53.6,28.9 54.1,28.1 54.5,28.9 54.9,29.0 55.4,30.3 55.8,29.7 56.2,29.7 56.6,30.3 57.1,30.7 57.5,30.0 57.9,30.0 58.4,30.0 58.8,30.2 59.2,28.8 59.7,29.1 60.1,28.9 60.5,29.3 60.9,29.0 61.4,27.8 61.8,27.5 62.2,27.6 62.7,27.8 63.1,27.7 63.5,28.3 64.0,28.1 64.4,26.9 64.8,25.1 65.3,24.8 65.7,25.8 66.1,22.2 66.5,22.1 67.0,21.8 67.4,19.6 67.8,19.3 68.3,19.7 68.7,19.4 69.1,19.0 69.6,17.6 70.0,19.1 70.4,19.2 70.8,19.7 71.3,18.9 71.7,19.2 72.1,19.2 72.6,18.5 73.0,18.7 73.4,19.1 73.9,17.3 74.3,17.8 74.7,17.9 75.1,15.6 75.6,14.4 76.0,14.4 76.4,15.6 76.9,15.2 77.3,15.3 77.7,16.0 78.2,15.3 78.6,15.0 79.0,14.8 79.5,14.6 79.9,13.1 80.3,12.7 80.7,12.1 81.2,11.8 81.6,10.6 82.0,9.7 82.5,9.5 82.9,11.4 83.3,11.6 83.8,11.4 84.2,12.3 84.6,13.1 85.0,14.9 85.5,15.0 85.9,14.7 86.3,14.3 86.8,11.7 87.2,12.2 87.6,13.2 88.1,11.2 88.5,13.1 88.9,12.4 89.3,12.2 89.8,10.7 90.2,11.7 90.6,9.6 91.1,9.1 91.5,8.2 91.9,8.5 92.4,8.4 92.8,7.7 93.2,7.2 93.6,7.0 94.1,4.4 94.5,4.9 94.9,5.0 95.4,5.0 95.8,4.0 96.2,4.4 96.7,3.7 97.1,4.5 97.5,5.2 98.0,4.5 98.4,2.5 98.8,2.6 99.2,2.2 99.7,3.0 100.1,4.2 100.5,4.1 101.0,3.7 101.4,2.4 101.8,2.0 102.3,3.0 102.7,7.2 103.1,7.5 103.5,10.3 104.0,11.5 104.4,10.4 104.8,10.9 105.3,10.6 105.7,10.8 106.1,11.6 106.6,11.3 107.0,11.4 107.4,10.4 107.8,11.1 108.3,10.0 108.7,9.9 109.1,9.0 109.6,9.0 110.0,10.2", "ret_12_1": 126.0, "ret_6_1": 110.0, "ret_3_1": 18.2, "volatility": 44.0, "traded_daily_cr": 93.0, "watch": "Nothing flagged", "from_12m_high": -16.0, "signal_rank": 15, "data_quality": "Green"}, {"rank": 6, "symbol": "ACUTAAS", "isin": "INE00FF01025", "qty": 4, "last_close": 3214.4, "amount": 12858.0, "spark_12m": "2.0,30.2 2.4,30.2 2.9,30.3 3.3,30.3 3.7,30.8 4.2,31.5 4.6,31.6 5.0,32.0 5.4,31.2 5.9,31.1 6.3,30.9 6.7,30.9 7.2,30.9 7.6,30.7 8.0,30.1 8.5,29.7 8.9,29.7 9.3,29.1 9.7,29.0 10.2,27.8 10.6,26.4 11.0,26.1 11.5,26.7 11.9,27.4 12.3,26.8 12.8,27.0 13.2,27.3 13.6,27.1 14.0,26.8 14.5,25.8 14.9,25.5 15.3,26.3 15.8,26.4 16.2,26.4 16.6,26.5 17.1,27.1 17.5,27.4 17.9,27.0 18.4,27.1 18.8,27.0 19.2,26.9 19.6,26.8 20.1,27.2 20.5,25.0 20.9,26.1 21.4,26.0 21.8,26.1 22.2,25.4 22.7,26.2 23.1,26.6 23.5,26.7 23.9,27.1 24.4,27.1 24.8,27.8 25.2,27.6 25.7,27.4 26.1,27.7 26.5,27.6 27.0,28.1 27.4,27.2 27.8,27.7 28.2,28.0 28.7,27.8 29.1,27.4 29.5,27.2 30.0,27.8 30.4,27.8 30.8,27.8 31.3,27.7 31.7,27.1 32.1,26.5 32.5,26.6 33.0,26.3 33.4,26.4 33.8,26.4 34.3,26.7 34.7,27.4 35.1,27.5 35.6,27.4 36.0,27.1 36.4,27.2 36.9,27.4 37.3,28.1 37.7,28.4 38.1,27.9 38.6,27.8 39.0,26.8 39.4,25.1 39.9,24.2 40.3,24.5 40.7,24.2 41.2,23.8 41.6,23.5 42.0,23.6 42.4,23.6 42.9,23.4 43.3,22.8 43.7,23.0 44.2,22.2 44.6,23.2 45.0,22.9 45.5,22.4 45.9,21.6 46.3,22.1 46.7,22.0 47.2,21.5 47.6,21.5 48.0,21.3 48.5,21.1 48.9,21.4 49.3,21.0 49.8,22.1 50.2,20.4 50.6,20.2 51.1,21.4 51.5,20.5 51.9,21.0 52.3,21.0 52.8,22.3 53.2,21.3 53.6,19.6 54.1,20.1 54.5,20.3 54.9,18.3 55.4,20.0 55.8,17.9 56.2,16.7 56.6,16.5 57.1,16.3 57.5,19.2 57.9,22.0 58.4,20.7 58.8,20.7 59.2,19.2 59.7,19.3 60.1,18.8 60.5,18.4 60.9,19.7 61.4,19.1 61.8,18.8 62.2,18.2 62.7,18.7 63.1,18.0 63.5,18.5 64.0,18.4 64.4,17.1 64.8,17.5 65.3,17.0 65.7,15.9 66.1,14.9 66.5,15.1 67.0,14.7 67.4,14.2 67.8,14.1 68.3,13.2 68.7,14.0 69.1,12.9 69.6,14.2 70.0,14.2 70.4,13.3 70.8,12.2 71.3,12.3 71.7,10.8 72.1,11.4 72.6,11.7 73.0,10.3 73.4,10.8 73.9,9.1 74.3,10.5 74.7,10.3 75.1,9.1 75.6,8.7 76.0,6.6 76.4,6.8 76.9,8.3 77.3,8.2 77.7,9.2 78.2,8.9 78.6,9.5 79.0,10.8 79.5,10.8 79.9,9.0 80.3,7.7 80.7,7.6 81.2,7.3 81.6,7.4 82.0,7.0 82.5,3.6 82.9,4.1 83.3,3.6 83.8,2.0 84.2,2.0 84.6,4.3 85.0,5.8 85.5,5.0 85.9,5.0 86.3,5.7 86.8,4.5 87.2,5.0 87.6,3.9 88.1,3.4 88.5,3.0 88.9,2.5 89.3,2.2 89.8,2.4 90.2,5.0 90.6,7.5 91.1,6.1 91.5,7.0 91.9,6.9 92.4,7.8 92.8,9.4 93.2,9.3 93.6,7.9 94.1,7.2 94.5,7.5 94.9,7.0 95.4,7.2 95.8,7.7 96.2,8.8 96.7,9.4 97.1,7.8 97.5,8.3 98.0,5.8 98.4,7.9 98.8,8.1 99.2,8.6 99.7,8.6 100.1,6.8 100.5,7.5 101.0,6.6 101.4,7.2 101.8,8.7 102.3,8.6 102.7,9.1 103.1,8.2 103.5,8.6 104.0,8.5 104.4,8.5 104.8,7.7 105.3,5.1 105.7,5.9 106.1,7.4 106.6,6.4 107.0,6.8 107.4,5.2 107.8,5.4 108.3,8.1 108.7,7.4 109.1,7.2 109.6,7.3 110.0,8.1", "ret_12_1": 126.0, "ret_6_1": 36.7, "ret_3_1": -5.6, "volatility": 46.7, "traded_daily_cr": 101.0, "watch": "Nothing flagged", "from_12m_high": -13.0, "signal_rank": 16, "data_quality": "Green"}, {"rank": 7, "symbol": "DIACABS", "isin": "INE989C01038", "qty": 44, "last_close": 339.25, "amount": 14927.0, "spark_12m": "2.0,27.2 2.4,27.3 2.9,27.2 3.3,27.4 3.7,28.0 4.2,28.4 4.6,28.2 5.0,28.6 5.4,28.5 5.9,28.3 6.3,28.7 6.7,29.2 7.2,29.3 7.6,29.4 8.0,29.4 8.5,29.6 8.9,29.5 9.3,29.2 9.7,29.3 10.2,29.4 10.6,29.2 11.0,29.1 11.5,29.1 11.9,29.3 12.3,28.1 12.8,28.5 13.2,28.1 13.6,28.2 14.0,28.2 14.5,28.1 14.9,27.9 15.3,28.6 15.8,28.3 16.2,28.8 16.6,28.9 17.1,28.8 17.5,28.4 17.9,28.4 18.4,28.4 18.8,28.7 19.2,28.3 19.6,28.7 20.1,29.1 20.5,29.5 20.9,29.6 21.4,29.4 21.8,29.4 22.2,28.5 22.7,28.6 23.1,28.9 23.5,29.2 23.9,29.3 24.4,29.1 24.8,29.4 25.2,29.4 25.7,29.7 26.1,29.7 26.5,29.5 27.0,29.4 27.4,29.6 27.8,29.6 28.2,29.5 28.7,29.5 29.1,29.2 29.5,29.3 30.0,29.5 30.4,29.6 30.8,29.8 31.3,29.8 31.7,29.8 32.1,29.8 32.5,29.9 33.0,29.3 33.4,29.3 33.8,29.1 34.3,29.7 34.7,30.2 35.1,30.1 35.6,30.5 36.0,30.7 36.4,30.6 36.9,30.4 37.3,31.0 37.7,30.9 38.1,30.8 38.6,31.4 39.0,31.4 39.4,31.1 39.9,31.4 40.3,31.5 40.7,31.7 41.2,31.2 41.6,30.8 42.0,31.3 42.4,31.3 42.9,30.9 43.3,30.4 43.7,30.2 44.2,30.3 44.6,30.5 45.0,29.5 45.5,29.8 45.9,29.8 46.3,30.2 46.7,30.1 47.2,30.2 47.6,30.4 48.0,30.0 48.5,29.6 48.9,29.9 49.3,29.9 49.8,30.4 50.2,29.9 50.6,30.1 51.1,30.2 51.5,29.7 51.9,29.9 52.3,30.0 52.8,30.8 53.2,31.0 53.6,31.2 54.1,30.7 54.5,31.4 54.9,31.0 55.4,32.0 55.8,31.7 56.2,30.9 56.6,31.5 57.1,31.9 57.5,31.2 57.9,31.2 58.4,30.8 58.8,30.9 59.2,30.3 59.7,30.4 60.1,29.9 60.5,29.8 60.9,29.5 61.4,28.7 61.8,28.6 62.2,27.4 62.7,27.2 63.1,27.5 63.5,27.5 64.0,27.3 64.4,26.8 64.8,27.1 65.3,27.3 65.7,27.7 66.1,26.8 66.5,26.6 67.0,25.6 67.4,26.4 67.8,26.0 68.3,25.8 68.7,26.4 69.1,25.9 69.6,24.0 70.0,23.5 70.4,24.0 70.8,24.2 71.3,23.6 71.7,23.8 72.1,23.8 72.6,23.5 73.0,22.4 73.4,23.3 73.9,23.7 74.3,25.0 74.7,23.7 75.1,24.3 75.6,23.9 76.0,22.7 76.4,23.3 76.9,22.8 77.3,23.4 77.7,23.8 78.2,22.9 78.6,21.4 79.0,22.4 79.5,22.6 79.9,22.9 80.3,22.1 80.7,22.3 81.2,22.9 81.6,22.6 82.0,22.4 82.5,22.2 82.9,22.1 83.3,22.2 83.8,22.0 84.2,23.2 84.6,21.1 85.0,20.4 85.5,19.7 85.9,18.9 86.3,20.0 86.8,20.1 87.2,20.4 87.6,20.2 88.1,20.4 88.5,20.7 88.9,18.3 89.3,15.6 89.8,15.6 90.2,15.1 90.6,12.8 91.1,11.5 91.5,10.0 91.9,8.2 92.4,9.2 92.8,9.7 93.2,9.8 93.6,10.5 94.1,8.8 94.5,7.0 94.9,5.3 95.4,5.7 95.8,5.5 96.2,4.9 96.7,5.0 97.1,4.8 97.5,5.8 98.0,4.9 98.4,5.8 98.8,6.4 99.2,6.2 99.7,6.5 100.1,8.0 100.5,8.1 101.0,8.1 101.4,6.9 101.8,7.1 102.3,7.9 102.7,8.9 103.1,9.8 103.5,8.8 104.0,8.7 104.4,8.3 104.8,8.5 105.3,6.7 105.7,4.8 106.1,2.8 106.6,2.0 107.0,4.0 107.4,5.0 107.8,4.0 108.3,4.6 108.7,3.8 109.1,5.7 109.6,6.4 110.0,8.0", "ret_12_1": 124.0, "ret_6_1": 180.0, "ret_3_1": 61.7, "volatility": 53.6, "traded_daily_cr": 51.0, "watch": "Nothing flagged", "from_12m_high": -14.1, "signal_rank": 17, "data_quality": "Green"}, {"rank": 8, "symbol": "KIRLOSENG", "isin": "INE146L01010", "qty": 7, "last_close": 2141.2, "amount": 14988.0, "spark_12m": "2.0,30.3 2.4,30.3 2.9,30.5 3.3,30.2 3.7,30.7 4.2,31.2 4.6,31.1 5.0,31.1 5.4,31.0 5.9,31.4 6.3,31.6 6.7,31.8 7.2,31.8 7.6,31.8 8.0,31.6 8.5,31.7 8.9,32.0 9.3,31.9 9.7,31.8 10.2,31.6 10.6,31.8 11.0,31.6 11.5,31.5 11.9,31.5 12.3,30.7 12.8,29.6 13.2,29.4 13.6,29.4 14.0,29.7 14.5,29.4 14.9,29.4 15.3,29.9 15.8,30.3 16.2,30.5 16.6,30.7 17.1,28.7 17.5,28.2 17.9,28.1 18.4,27.7 18.8,27.2 19.2,26.6 19.6,26.5 20.1,26.8 20.5,27.4 20.9,26.9 21.4,27.1 21.8,27.2 22.2,27.5 22.7,27.6 23.1,27.7 23.5,28.2 23.9,26.8 24.4,27.4 24.8,28.0 25.2,27.5 25.7,27.7 26.1,27.6 26.5,27.1 27.0,27.3 27.4,25.7 27.8,24.7 28.2,24.6 28.7,25.4 29.1,24.2 29.5,24.4 30.0,25.0 30.4,24.9 30.8,25.8 31.3,25.7 31.7,25.8 32.1,25.6 32.5,25.1 33.0,25.2 33.4,25.3 33.8,25.8 34.3,26.5 34.7,26.9 35.1,27.5 35.6,27.0 36.0,26.7 36.4,26.7 36.9,27.4 37.3,27.9 37.7,27.9 38.1,27.7 38.6,28.0 39.0,28.0 39.4,27.7 39.9,27.6 40.3,26.6 40.7,27.0 41.2,26.5 41.6,25.6 42.0,26.2 42.4,26.7 42.9,25.8 43.3,25.0 43.7,23.9 44.2,23.7 44.6,23.0 45.0,22.4 45.5,22.1 45.9,22.3 46.3,22.2 46.7,22.3 47.2,22.6 47.6,22.7 48.0,22.5 48.5,22.7 48.9,22.7 49.3,22.5 49.8,22.3 50.2,21.4 50.6,20.6 51.1,21.6 51.5,21.9 51.9,21.7 52.3,21.4 52.8,21.7 53.2,21.4 53.6,21.9 54.1,22.0 54.5,22.2 54.9,23.0 55.4,24.6 55.8,23.9 56.2,22.7 56.6,23.5 57.1,23.9 57.5,23.2 57.9,22.9 58.4,22.3 58.8,22.6 59.2,21.4 59.7,21.6 60.1,21.3 60.5,21.1 60.9,19.1 61.4,18.8 61.8,18.7 62.2,18.4 62.7,17.9 63.1,18.4 63.5,18.9 64.0,19.2 64.4,17.6 64.8,16.9 65.3,17.3 65.7,17.3 66.1,16.9 66.5,16.6 67.0,17.1 67.4,16.8 67.8,16.8 68.3,18.0 68.7,19.8 69.1,19.1 69.6,19.1 70.0,16.6 70.4,17.3 70.8,18.0 71.3,17.9 71.7,17.7 72.1,17.8 72.6,17.2 73.0,16.4 73.4,15.0 73.9,13.3 74.3,13.4 74.7,14.5 75.1,13.9 75.6,12.9 76.0,13.5 76.4,14.6 76.9,14.6 77.3,15.2 77.7,15.6 78.2,13.9 78.6,13.2 79.0,13.4 79.5,12.2 79.9,12.3 80.3,12.1 80.7,5.1 81.2,3.0 81.6,2.0 82.0,3.4 82.5,4.2 82.9,5.5 83.3,5.9 83.8,6.3 84.2,7.9 84.6,7.3 85.0,7.2 85.5,7.1 85.9,4.5 86.3,3.3 86.8,4.3 87.2,5.6 87.6,4.6 88.1,5.0 88.5,7.5 88.9,8.1 89.3,8.1 89.8,8.7 90.2,8.8 90.6,8.7 91.1,7.0 91.5,8.6 91.9,8.8 92.4,9.6 92.8,8.6 93.2,8.0 93.6,7.1 94.1,7.7 94.5,7.6 94.9,9.1 95.4,9.7 95.8,10.2 96.2,11.0 96.7,10.9 97.1,10.2 97.5,10.2 98.0,9.8 98.4,10.6 98.8,9.3 99.2,10.2 99.7,10.8 100.1,11.5 100.5,11.3 101.0,10.2 101.4,9.8 101.8,10.2 102.3,9.5 102.7,9.1 103.1,7.2 103.5,8.4 104.0,8.9 104.4,7.1 104.8,8.1 105.3,8.3 105.7,9.0 106.1,11.2 106.6,11.3 107.0,9.8 107.4,9.1 107.8,9.6 108.3,9.1 108.7,8.1 109.1,9.1 109.6,9.6 110.0,9.5", "ret_12_1": 123.0, "ret_6_1": 58.2, "ret_3_1": -11.2, "volatility": 49.9, "traded_daily_cr": 87.0, "watch": "Nothing flagged", "from_12m_high": -16.5, "signal_rank": 18, "data_quality": "Green"}, {"rank": 9, "symbol": "E2E", "isin": "INE255Z01027", "qty": 23, "last_close": 625.9, "amount": 14396.0, "spark_12m": "2.0,25.4 2.4,24.4 2.9,23.5 3.3,24.3 3.7,23.7 4.2,22.9 4.6,23.7 5.0,24.4 5.4,23.4 5.9,22.4 6.3,21.3 6.7,21.1 7.2,21.2 7.6,22.8 8.0,23.1 8.5,23.8 8.9,24.4 9.3,24.4 9.7,24.3 10.2,24.1 10.6,24.5 11.0,24.4 11.5,24.3 11.9,25.2 12.3,24.5 12.8,24.9 13.2,25.1 13.6,24.9 14.0,25.0 14.5,25.3 14.9,24.9 15.3,25.3 15.8,25.1 16.2,25.3 16.6,26.1 17.1,26.1 17.5,26.8 17.9,27.8 18.4,28.0 18.8,28.1 19.2,28.0 19.6,28.1 20.1,28.8 20.5,29.7 20.9,29.7 21.4,29.6 21.8,29.8 22.2,30.1 22.7,30.0 23.1,30.5 23.5,30.9 23.9,30.5 24.4,31.0 24.8,31.6 25.2,30.8 25.7,31.2 26.1,31.1 26.5,31.1 27.0,31.1 27.4,31.5 27.8,31.6 28.2,31.7 28.7,31.3 29.1,31.2 29.5,31.1 30.0,31.2 30.4,31.4 30.8,32.0 31.3,31.9 31.7,31.8 32.1,31.7 32.5,31.6 33.0,31.2 33.4,31.5 33.8,31.6 34.3,31.5 34.7,31.5 35.1,31.6 35.6,31.8 36.0,31.6 36.4,30.3 36.9,30.2 37.3,30.8 37.7,31.3 38.1,31.2 38.6,31.5 39.0,31.5 39.4,31.3 39.9,31.5 40.3,31.0 40.7,29.0 41.2,28.0 41.6,29.0 42.0,29.5 42.4,28.7 42.9,27.8 43.3,28.2 43.7,27.9 44.2,28.4 44.6,28.8 45.0,28.2 45.5,28.3 45.9,26.5 46.3,25.8 46.7,26.4 47.2,28.2 47.6,29.0 48.0,28.3 48.5,28.0 48.9,28.2 49.3,28.9 49.8,29.7 50.2,29.7 50.6,29.8 51.1,29.9 51.5,29.1 51.9,29.4 52.3,29.6 52.8,29.9 53.2,30.4 53.6,30.5 54.1,30.1 54.5,30.0 54.9,30.1 55.4,30.7 55.8,30.7 56.2,30.2 56.6,30.9 57.1,31.4 57.5,30.8 57.9,30.2 58.4,29.9 58.8,29.6 59.2,28.9 59.7,29.1 60.1,29.0 60.5,28.9 60.9,28.1 61.4,27.4 61.8,26.8 62.2,27.4 62.7,26.6 63.1,26.0 63.5,26.2 64.0,26.2 64.4,25.3 64.8,25.7 65.3,26.0 65.7,26.3 66.1,26.6 66.5,25.8 67.0,24.9 67.4,23.9 67.8,23.0 68.3,21.9 68.7,23.0 69.1,24.1 69.6,24.0 70.0,24.9 70.4,25.5 70.8,24.5 71.3,23.6 71.7,23.1 72.1,22.1 72.6,21.3 73.0,20.2 73.4,19.8 73.9,20.0 74.3,18.8 74.7,17.5 75.1,18.8 75.6,17.6 76.0,16.3 76.4,17.6 76.9,19.0 77.3,20.2 77.7,21.4 78.2,20.3 78.6,21.1 79.0,20.6 79.5,20.3 79.9,19.1 80.3,17.9 80.7,16.6 81.2,17.5 81.6,18.4 82.0,18.7 82.5,19.8 82.9,19.7 83.3,19.3 83.8,20.2 84.2,20.6 84.6,20.6 85.0,21.3 85.5,20.8 85.9,19.6 86.3,19.6 86.8,20.3 87.2,19.8 87.6,18.8 88.1,18.1 88.5,19.2 88.9,18.0 89.3,16.7 89.8,15.3 90.2,13.9 90.6,12.4 91.1,10.8 91.5,12.4 91.9,13.9 92.4,13.8 92.8,12.3 93.2,10.8 93.6,9.1 94.1,7.4 94.5,6.9 94.9,8.8 95.4,7.1 95.8,5.6 96.2,5.3 96.7,5.1 97.1,3.2 97.5,2.0 98.0,3.3 98.4,5.4 98.8,5.8 99.2,5.9 99.7,6.5 100.1,7.5 100.5,6.5 101.0,6.2 101.4,6.3 101.8,6.1 102.3,6.0 102.7,6.8 103.1,7.7 103.5,7.2 104.0,5.4 104.4,6.2 104.8,7.0 105.3,6.9 105.7,6.6 106.1,8.5 106.6,7.3 107.0,7.0 107.4,6.8 107.8,7.7 108.3,7.0 108.7,5.1 109.1,4.4 109.6,4.1 110.0,5.7", "ret_12_1": 109.0, "ret_6_1": 186.0, "ret_3_1": 56.0, "volatility": 56.2, "traded_daily_cr": 49.0, "watch": "Nothing flagged", "from_12m_high": -8.8, "signal_rank": 20, "data_quality": "Green"}, {"rank": 10, "symbol": "LAURUSLABS", "isin": "INE947Q01028", "qty": 7, "last_close": 2010.7, "amount": 14075.0, "spark_12m": "2.0,29.5 2.4,30.2 2.9,30.1 3.3,30.1 3.7,30.4 4.2,32.0 4.6,31.8 5.0,31.8 5.4,31.0 5.9,31.2 6.3,31.2 6.7,31.2 7.2,31.5 7.6,31.2 8.0,30.9 8.5,31.0 8.9,30.9 9.3,30.9 9.7,31.0 10.2,30.3 10.6,29.8 11.0,29.7 11.5,29.5 11.9,29.7 12.3,29.3 12.8,28.8 13.2,28.8 13.6,28.6 14.0,29.0 14.5,28.4 14.9,28.2 15.3,28.3 15.8,28.3 16.2,27.8 16.6,28.2 17.1,28.1 17.5,27.9 17.9,27.8 18.4,27.3 18.8,27.6 19.2,28.1 19.6,28.1 20.1,28.4 20.5,28.3 20.9,28.4 21.4,28.1 21.8,27.7 22.2,27.0 22.7,27.1 23.1,27.3 23.5,27.4 23.9,27.5 24.4,27.2 24.8,27.7 25.2,27.3 25.7,27.4 26.1,27.3 26.5,27.5 27.0,27.7 27.4,27.8 27.8,27.6 28.2,27.4 28.7,26.7 29.1,26.2 29.5,26.1 30.0,25.7 30.4,25.7 30.8,25.8 31.3,25.5 31.7,25.1 32.1,25.1 32.5,25.2 33.0,25.2 33.4,24.9 33.8,24.6 34.3,25.3 34.7,25.7 35.1,26.7 35.6,26.4 36.0,25.6 36.4,25.9 36.9,26.2 37.3,26.9 37.7,28.1 38.1,27.7 38.6,27.4 39.0,27.8 39.4,27.8 39.9,28.5 40.3,28.7 40.7,29.0 41.2,28.4 41.6,28.3 42.0,28.7 42.4,29.0 42.9,28.2 43.3,28.7 43.7,27.5 44.2,27.3 44.6,27.5 45.0,27.5 45.5,27.5 45.9,26.9 46.3,27.3 46.7,27.3 47.2,27.4 47.6,27.1 48.0,25.9 48.5,25.5 48.9,25.9 49.3,26.2 49.8,27.0 50.2,26.7 50.6,27.2 51.1,27.3 51.5,26.9 51.9,26.8 52.3,26.6 52.8,27.7 53.2,28.8 53.6,28.6 54.1,28.2 54.5,29.2 54.9,28.1 55.4,28.8 55.8,28.0 56.2,27.2 56.6,27.6 57.1,28.0 57.5,26.8 57.9,26.7 58.4,26.4 58.8,26.4 59.2,25.8 59.7,25.7 60.1,25.4 60.5,25.6 60.9,24.9 61.4,24.6 61.8,24.4 62.2,24.6 62.7,25.0 63.1,25.4 63.5,24.6 64.0,25.0 64.4,24.7 64.8,25.6 65.3,25.2 65.7,25.3 66.1,23.7 66.5,23.7 67.0,23.4 67.4,22.7 67.8,22.1 68.3,21.2 68.7,21.1 69.1,20.8 69.6,19.9 70.0,19.7 70.4,19.6 70.8,19.2 71.3,18.8 71.7,19.1 72.1,19.2 72.6,18.9 73.0,18.5 73.4,18.3 73.9,18.8 74.3,18.1 74.7,18.3 75.1,18.0 75.6,17.1 76.0,16.7 76.4,17.7 76.9,17.2 77.3,18.2 77.7,18.1 78.2,18.0 78.6,18.1 79.0,18.4 79.5,18.6 79.9,18.6 80.3,17.5 80.7,16.9 81.2,15.8 81.6,16.5 82.0,16.6 82.5,15.3 82.9,14.9 83.3,15.5 83.8,14.6 84.2,14.3 84.6,14.6 85.0,15.9 85.5,16.1 85.9,15.1 86.3,14.4 86.8,13.9 87.2,13.8 87.6,14.0 88.1,13.9 88.5,14.6 88.9,13.9 89.3,13.0 89.8,13.4 90.2,13.6 90.6,12.8 91.1,10.0 91.5,8.9 91.9,8.3 92.4,8.3 92.8,7.4 93.2,7.6 93.6,6.6 94.1,7.0 94.5,7.1 94.9,6.7 95.4,6.5 95.8,6.4 96.2,6.6 96.7,6.6 97.1,8.2 97.5,7.6 98.0,7.5 98.4,7.8 98.8,7.2 99.2,7.8 99.7,7.8 100.1,6.2 100.5,5.7 101.0,4.6 101.4,4.4 101.8,5.0 102.3,6.3 102.7,6.2 103.1,6.1 103.5,6.8 104.0,5.9 104.4,4.2 104.8,4.4 105.3,4.2 105.7,3.6 106.1,4.7 106.6,5.2 107.0,4.1 107.4,4.0 107.8,2.4 108.3,2.7 108.7,2.0 109.1,2.2 109.6,2.7 110.0,2.6", "ret_12_1": 109.0, "ret_6_1": 94.4, "ret_3_1": 27.2, "volatility": 28.1, "traded_daily_cr": 300.0, "watch": "Nothing flagged", "from_12m_high": -1.1, "signal_rank": 21, "data_quality": "Green"}]}, "prices": {"TDPOWERSYS": {"2026-09-28": {"open": 730.05, "close": 722.0, "src": "yahoo"}}, "AEROFLEX": {"2026-09-28": {"open": 524.25, "close": 513.4, "src": "yahoo"}}, "E2E": {"2026-09-28": {"open": 650.0, "close": 625.9, "src": "yahoo"}}, "LAURUSLABS": {"2026-09-28": {"open": 2000.0, "close": 2010.7, "src": "yahoo"}}, "NIFTY50": {"2026-09-28": {"open": 23064.9, "close": 22780.25, "src": "yahoo"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 02:53", "days": 7, "items": [{"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Gold Rate To Bond Yields \u2014 Five Key Factors For Sensex, Nifty 50 On September 29", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxPX2RZNUVYaGZnM0prSjZkblNWUDAyQkJnS3hOQVFsZVVzWWY3azFvYXFOekJUajR6R0Zla0NHN3NNSlZhbFI0NmhUUW1CaEdCckFrS3gxZGFUZDhVaEdqVzlwaDNIQV9mak</t>
+          <t>{"batch": {"batch_id": "2026-09-28", "title": "SwingScope batch 2026-09-28", "signal_date": "2026-09-28", "exit_date_est": "2026-10-27", "hold_sessions": 21, "universe": "liquidity top 400 of all NSE stocks", "capital": 139903.0, "est_costs": 859.0, "cost_pct": 0.6, "regime": "Down", "regime_note": "the signal's weakest regime historically", "warnings": "0 of 10", "evidence": ["Backtest, 2017\u20132026 | Replayed point in time on your survivorship-free archive. Not live results. | Signal strength | IC +0.041 | rank IC over 113 monthly dates, 2017-2026 (t 2.52); validated benchmark 0.026 | Top vs bottom decile | +1.89% | per 21-session hold, before costs (t 2.94) | Top-10 picks | +1.45% | per hold after 0.60% costs; Nifty 50 earned +1.02% before costs | Entry timing | Open wins | buying at the open beat all 30 support-entry rules (best -0.12% per hold) | Down markets | IC +0.009 | over 27 down-regime dates, against +0.050 over 86 up-regime dates", "Live record | No results yet | The first live result arrives when this system finishes its first batch. Live results are kept apart from the backtest and never mixed in."], "stocks": [{"rank": 1, "symbol": "TDPOWERSYS", "isin": "INE419M01035", "qty": 20, "last_close": 722.0, "amount": 14440.0, "spark_12m": "2.0,31.7 2.4,32.0 2.9,31.7 3.3,31.1 3.7,31.1 4.2,31.1 4.6,31.0 5.0,30.6 5.4,30.4 5.9,29.2 6.3,29.3 6.7,29.5 7.2,29.8 7.6,30.1 8.0,30.4 8.5,30.5 8.9,30.3 9.3,29.4 9.7,29.3 10.2,28.8 10.6,29.1 11.0,28.9 11.5,29.1 11.9,29.2 12.3,29.1 12.8,29.0 13.2,28.4 13.6,28.0 14.0,25.5 14.5,24.3 14.9,24.2 15.3,24.8 15.8,25.3 16.2,25.2 16.6,25.4 17.1,24.2 17.5,25.4 17.9,25.2 18.4,25.2 18.8,25.7 19.2,25.8 19.6,25.9 20.1,26.9 20.5,25.8 20.9,25.9 21.4,24.9 21.8,24.9 22.2,25.4 22.7,25.0 23.1,25.0 23.5,25.8 23.9,26.8 24.4,27.7 24.8,28.3 25.2,27.7 25.7,28.1 26.1,28.2 26.5,27.9 27.0,27.6 27.4,27.9 27.8,27.1 28.2,27.6 28.7,27.1 29.1,26.4 29.5,26.7 30.0,27.0 30.4,27.3 30.8,27.7 31.3,27.5 31.7,27.5 32.1,28.3 32.5,28.0 33.0,27.7 33.4,27.9 33.8,27.5 34.3,27.9 34.7,28.3 35.1,28.8 35.6,27.9 36.0,28.2 36.4,28.5 36.9,28.7 37.3,29.2 37.7,29.4 38.1,29.5 38.6,29.7 39.0,29.6 39.4,28.8 39.9,28.2 40.3,26.7 40.7,26.2 41.2,24.3 41.6,24.1 42.0,24.5 42.4,25.2 42.9,24.8 43.3,23.3 43.7,22.8 44.2,23.4 44.6,23.8 45.0,23.1 45.5,22.8 45.9,22.8 46.3,22.4 46.7,22.4 47.2,21.8 47.6,22.3 48.0,22.5 48.5,22.5 48.9,21.8 49.3,22.2 49.8,22.6 50.2,22.4 50.6,22.5 51.1,23.5 51.5,24.3 51.9,24.7 52.3,24.4 52.8,25.3 53.2,24.9 53.6,24.3 54.1,23.7 54.5,23.8 54.9,23.0 55.4,24.2 55.8,23.1 56.2,22.3 56.6,23.4 57.1,23.3 57.5,23.0 57.9,23.0 58.4,22.5 58.8,22.5 59.2,22.4 59.7,22.6 60.1,21.2 60.5,21.5 60.9,20.8 61.4,20.0 61.8,19.2 62.2,18.3 62.7,18.6 63.1,17.4 63.5,17.2 64.0,16.0 64.4,16.6 64.8,15.0 65.3,15.0 65.7,14.8 66.1,14.6 66.5,14.2 67.0,14.5 67.4,12.2 67.8,13.0 68.3,14.1 68.7,14.4 69.1,14.2 69.6,14.0 70.0,10.4 70.4,9.9 70.8,11.9 71.3,12.6 71.7,10.6 72.1,10.8 72.6,10.7 73.0,8.8 73.4,9.8 73.9,10.2 74.3,12.7 74.7,12.5 75.1,11.1 75.6,10.0 76.0,10.3 76.4,12.8 76.9,12.6 77.3,14.8 77.7,15.6 78.2,13.7 78.6,13.6 79.0,14.4 79.5,12.7 79.9,11.6 80.3,11.5 80.7,10.0 81.2,9.2 81.6,11.7 82.0,12.0 82.5,12.6 82.9,12.4 83.3,13.7 83.8,13.8 84.2,16.6 84.6,14.2 85.0,15.7 85.5,16.9 85.9,16.6 86.3,14.9 86.8,14.9 87.2,15.6 87.6,14.2 88.1,15.6 88.5,15.5 88.9,15.2 89.3,15.5 89.8,14.6 90.2,15.2 90.6,15.9 91.1,15.2 91.5,15.9 91.9,18.1 92.4,17.5 92.8,15.5 93.2,16.0 93.6,15.5 94.1,13.5 94.5,12.7 94.9,11.8 95.4,12.5 95.8,11.4 96.2,5.6 96.7,5.6 97.1,5.5 97.5,3.7 98.0,2.7 98.4,3.8 98.8,4.9 99.2,4.1 99.7,3.4 100.1,6.2 100.5,6.3 101.0,5.6 101.4,4.9 101.8,3.6 102.3,4.6 102.7,5.9 103.1,6.6 103.5,5.6 104.0,6.0 104.4,4.0 104.8,4.8 105.3,4.4 105.7,2.0 106.1,6.5 106.6,8.1 107.0,6.7 107.4,4.3 107.8,5.2 108.3,4.7 108.7,4.2 109.1,5.5 109.6,5.0 110.0,6.7", "ret_12_1": 177.0, "ret_6_1": 72.2, "ret_3_1": 19.6, "volatility": 60.1, "traded_daily_cr": 128.0, "watch": "Nothing flagged", "from_12m_high": -10.3, "signal_rank": 6, "data_quality": "Green"}, {"rank": 2, "symbol": "AEROFLEX", "isin": "INE024001021", "qty": 29, "last_close": 513.4, "amount": 14889.0, "spark_12m": "2.0,29.8 2.4,29.6 2.9,29.5 3.3,30.0 3.7,30.1 4.2,30.5 4.6,30.8 5.0,30.9 5.4,30.9 5.9,30.5 6.3,30.7 6.7,30.8 7.2,30.9 7.6,31.0 8.0,31.0 8.5,31.1 8.9,31.2 9.3,31.2 9.7,31.2 10.2,31.2 10.6,31.4 11.0,31.1 11.5,31.0 11.9,31.0 12.3,31.0 12.8,30.1 13.2,30.1 13.6,30.5 14.0,30.0 14.5,29.8 14.9,30.3 15.3,30.5 15.8,30.0 16.2,30.0 16.6,30.2 17.1,30.2 17.5,30.1 17.9,29.9 18.4,30.1 18.8,30.3 19.2,30.2 19.6,30.2 20.1,30.5 20.5,30.9 20.9,30.2 21.4,30.2 21.8,30.4 22.2,30.0 22.7,30.2 23.1,30.3 23.5,30.6 23.9,30.6 24.4,30.7 24.8,31.3 25.2,31.0 25.7,30.7 26.1,30.9 26.5,30.7 27.0,30.3 27.4,30.5 27.8,30.3 28.2,30.7 28.7,29.5 29.1,29.2 29.5,28.8 30.0,28.6 30.4,28.9 30.8,29.1 31.3,29.3 31.7,29.5 32.1,29.6 32.5,29.2 33.0,29.0 33.4,29.3 33.8,29.1 34.3,29.9 34.7,30.2 35.1,30.2 35.6,30.5 36.0,30.7 36.4,30.8 36.9,30.9 37.3,31.3 37.7,31.8 38.1,31.5 38.6,32.0 39.0,31.7 39.4,31.4 39.9,30.4 40.3,30.6 40.7,31.0 41.2,30.1 41.6,29.9 42.0,29.9 42.4,30.1 42.9,29.3 43.3,29.4 43.7,29.6 44.2,29.5 44.6,30.0 45.0,29.6 45.5,28.5 45.9,27.1 46.3,27.0 46.7,27.3 47.2,27.6 47.6,27.7 48.0,27.0 48.5,26.9 48.9,26.5 49.3,27.2 49.8,27.7 50.2,27.3 50.6,27.6 51.1,27.9 51.5,27.5 51.9,26.5 52.3,26.3 52.8,26.5 53.2,25.6 53.6,25.3 54.1,25.6 54.5,26.8 54.9,26.6 55.4,27.3 55.8,25.3 56.2,25.3 56.6,26.1 57.1,26.2 57.5,25.4 57.9,25.2 58.4,25.0 58.8,25.7 59.2,24.6 59.7,23.6 60.1,22.6 60.5,22.6 60.9,22.3 61.4,22.1 61.8,21.0 62.2,21.7 62.7,22.6 63.1,21.5 63.5,22.1 64.0,23.4 64.4,22.2 64.8,22.3 65.3,21.4 65.7,21.4 66.1,21.6 66.5,20.5 67.0,18.6 67.4,13.6 67.8,11.7 68.3,14.7 68.7,17.1 69.1,17.1 69.6,17.4 70.0,16.7 70.4,16.8 70.8,15.9 71.3,15.2 71.7,16.0 72.1,14.3 72.6,13.5 73.0,14.3 73.4,14.0 73.9,14.4 74.3,15.4 74.7,13.1 75.1,12.1 75.6,11.7 76.0,13.1 76.4,14.6 76.9,12.7 77.3,13.5 77.7,13.9 78.2,11.1 78.6,8.9 79.0,9.4 79.5,6.5 79.9,8.1 80.3,6.8 80.7,6.6 81.2,7.1 81.6,8.8 82.0,9.7 82.5,9.6 82.9,9.4 83.3,8.1 83.8,8.9 84.2,10.5 84.6,10.3 85.0,13.6 85.5,14.5 85.9,14.2 86.3,13.6 86.8,13.0 87.2,13.8 87.6,13.0 88.1,13.8 88.5,13.8 88.9,14.1 89.3,13.6 89.8,14.0 90.2,13.1 90.6,13.0 91.1,13.2 91.5,11.2 91.9,10.9 92.4,12.6 92.8,12.0 93.2,12.3 93.6,9.9 94.1,10.5 94.5,11.8 94.9,12.7 95.4,13.1 95.8,12.9 96.2,11.2 96.7,11.1 97.1,10.2 97.5,10.5 98.0,8.3 98.4,9.2 98.8,9.1 99.2,7.1 99.7,7.0 100.1,7.6 100.5,4.7 101.0,5.7 101.4,4.3 101.8,5.5 102.3,3.6 102.7,4.4 103.1,4.3 103.5,4.6 104.0,3.1 104.4,2.0 104.8,2.9 105.3,2.7 105.7,2.7 106.1,6.8 106.6,8.7 107.0,7.5 107.4,6.5 107.8,6.2 108.3,6.1 108.7,5.8 109.1,5.3 109.6,5.5 110.0,6.3", "ret_12_1": 175.0, "ret_6_1": 107.0, "ret_3_1": 10.7, "volatility": 67.3, "traded_daily_cr": 53.0, "watch": "Nothing flagged", "from_12m_high": -10.5, "signal_rank": 7, "data_quality": "Green"}, {"rank": 3, "symbol": "ATHERENERG", "isin": "INE0LEZ01016", "qty": 10, "last_close": 1454.9, "amount": 14549.0, "spark_12m": "2.0,30.9 2.4,30.7 2.9,31.2 3.3,30.9 3.7,31.6 4.2,32.0 4.6,31.0 5.0,31.4 5.4,30.8 5.9,30.7 6.3,30.0 6.7,29.7 7.2,29.5 7.6,29.9 8.0,30.6 8.5,30.2 8.9,30.1 9.3,29.6 9.7,28.2 10.2,28.1 10.6,27.4 11.0,26.3 11.5,27.1 11.9,27.8 12.3,27.1 12.8,27.0 13.2,27.8 13.6,27.8 14.0,28.2 14.5,28.2 14.9,28.8 15.3,29.6 15.8,29.1 16.2,29.8 16.6,29.0 17.1,29.8 17.5,29.5 17.9,29.2 18.4,29.3 18.8,28.7 19.2,28.3 19.6,28.0 20.1,28.1 20.5,28.6 20.9,28.3 21.4,28.1 21.8,27.7 22.2,27.5 22.7,27.7 23.1,28.3 23.5,28.4 23.9,28.7 24.4,28.6 24.8,28.5 25.2,29.2 25.7,29.3 26.1,29.3 26.5,29.3 27.0,28.3 27.4,28.6 27.8,28.9 28.2,28.9 28.7,27.9 29.1,28.0 29.5,27.8 30.0,27.4 30.4,27.7 30.8,27.5 31.3,27.1 31.7,26.6 32.1,27.0 32.5,26.9 33.0,28.3 33.4,28.1 33.8,28.1 34.3,28.6 34.7,29.6 35.1,29.5 35.6,29.1 36.0,29.3 36.4,30.0 36.9,29.8 37.3,30.3 37.7,30.1 38.1,29.7 38.6,29.9 39.0,30.0 39.4,30.3 39.9,30.4 40.3,29.9 40.7,30.3 41.2,28.6 41.6,28.0 42.0,27.6 42.4,27.8 42.9,27.3 43.3,27.3 43.7,27.5 44.2,27.3 44.6,27.7 45.0,27.7 45.5,27.3 45.9,27.2 46.3,27.1 46.7,27.7 47.2,27.5 47.6,28.0 48.0,27.8 48.5,27.9 48.9,27.7 49.3,27.8 49.8,27.9 50.2,28.3 50.6,28.6 51.1,28.4 51.5,28.1 51.9,27.9 52.3,27.7 52.8,27.8 53.2,27.6 53.6,27.3 54.1,26.7 54.5,26.6 54.9,25.9 55.4,26.7 55.8,26.5 56.2,26.0 56.6,25.5 57.1,26.6 57.5,26.2 57.9,26.4 58.4,25.8 58.8,26.4 59.2,26.2 59.7,24.9 60.1,23.8 60.5,22.7 60.9,23.6 61.4,23.7 61.8,24.1 62.2,23.2 62.7,23.0 63.1,22.7 63.5,22.9 64.0,23.3 64.4,21.8 64.8,22.1 65.3,21.9 65.7,22.0 66.1,22.0 66.5,21.9 67.0,23.0 67.4,22.7 67.8,22.5 68.3,21.1 68.7,22.3 69.1,21.6 69.6,21.9 70.0,21.9 70.4,22.6 70.8,22.6 71.3,22.7 71.7,23.2 72.1,23.3 72.6,22.3 73.0,21.6 73.4,21.5 73.9,21.3 74.3,21.9 74.7,21.4 75.1,19.8 75.6,20.7 76.0,19.5 76.4,20.3 76.9,19.5 77.3,19.3 77.7,19.7 78.2,19.6 78.6,19.7 79.0,20.4 79.5,20.6 79.9,21.1 80.3,21.1 80.7,21.4 81.2,20.2 81.6,20.6 82.0,20.4 82.5,18.2 82.9,16.8 83.3,17.1 83.8,16.7 84.2,17.1 84.6,17.2 85.0,16.8 85.5,15.3 85.9,14.8 86.3,14.6 86.8,15.7 87.2,15.3 87.6,12.9 88.1,13.6 88.5,13.2 88.9,12.9 89.3,13.1 89.8,13.6 90.2,14.5 90.6,15.1 91.1,14.9 91.5,15.2 91.9,14.1 92.4,14.3 92.8,13.8 93.2,13.5 93.6,9.0 94.1,8.4 94.5,8.9 94.9,8.2 95.4,8.6 95.8,7.1 96.2,6.0 96.7,7.0 97.1,7.4 97.5,8.1 98.0,8.6 98.4,9.3 98.8,9.0 99.2,8.7 99.7,8.9 100.1,9.2 100.5,7.8 101.0,7.8 101.4,4.8 101.8,2.2 102.3,2.0 102.7,3.0 103.1,4.2 103.5,5.6 104.0,5.2 104.4,5.7 104.8,5.7 105.3,3.7 105.7,3.8 106.1,6.0 106.6,6.0 107.0,6.4 107.4,4.2 107.8,5.4 108.3,6.6 108.7,7.7 109.1,7.7 109.6,7.8 110.0,8.8", "ret_12_1": 166.0, "ret_6_1": 97.5, "ret_3_1": 31.1, "volatility": 49.4, "traded_daily_cr": 493.0, "watch": "Nothing flagged", "from_12m_high": -15.7, "signal_rank": 9, "data_quality": "Green"}, {"rank": 4, "symbol": "THANGAMAYL", "isin": "INE085J01014", "qty": 2, "last_close": 5011.5, "amount": 10023.0, "spark_12m": "2.0,30.9 2.4,31.1 2.9,31.4 3.3,31.4 3.7,31.4 4.2,31.6 4.6,31.7 5.0,31.6 5.4,31.6 5.9,31.2 6.3,31.3 6.7,31.6 7.2,31.2 7.6,31.5 8.0,31.6 8.5,31.5 8.9,31.8 9.3,31.9 9.7,31.9 10.2,31.9 10.6,31.9 11.0,31.9 11.5,32.0 11.9,31.5 12.3,31.6 12.8,31.3 13.2,31.4 13.6,31.3 14.0,30.8 14.5,28.3 14.9,25.9 15.3,25.7 15.8,23.9 16.2,25.3 16.6,24.8 17.1,24.1 17.5,24.4 17.9,24.5 18.4,24.7 18.8,24.9 19.2,25.1 19.6,25.2 20.1,26.0 20.5,24.8 20.9,24.8 21.4,24.7 21.8,24.8 22.2,24.7 22.7,24.1 23.1,25.2 23.5,24.6 23.9,24.8 24.4,24.9 24.8,25.2 25.2,24.7 25.7,24.9 26.1,24.9 26.5,25.0 27.0,25.0 27.4,24.9 27.8,24.4 28.2,24.6 28.7,24.2 29.1,23.8 29.5,23.7 30.0,24.5 30.4,25.0 30.8,25.0 31.3,25.0 31.7,24.9 32.1,24.7 32.5,24.8 33.0,24.2 33.4,23.4 33.8,21.4 34.3,21.2 34.7,22.7 35.1,22.3 35.6,21.9 36.0,21.5 36.4,21.8 36.9,22.1 37.3,22.1 37.7,21.2 38.1,22.6 38.6,22.9 39.0,23.8 39.4,22.8 39.9,23.4 40.3,24.3 40.7,24.9 41.2,25.1 41.6,24.5 42.0,25.1 42.4,23.9 42.9,22.1 43.3,22.2 43.7,22.3 44.2,22.5 44.6,22.9 45.0,22.1 45.5,22.3 45.9,22.6 46.3,23.4 46.7,23.0 47.2,22.8 47.6,22.0 48.0,21.5 48.5,21.0 48.9,20.8 49.3,21.4 49.8,22.7 50.2,22.6 50.6,22.2 51.1,22.9 51.5,22.1 51.9,23.1 52.3,23.0 52.8,23.3 53.2,23.6 53.6,23.4 54.1,23.3 54.5,24.1 54.9,24.3 55.4,25.2 55.8,24.4 56.2,22.8 56.6,23.7 57.1,23.7 57.5,23.0 57.9,23.1 58.4,21.9 58.8,21.3 59.2,20.3 59.7,20.0 60.1,19.8 60.5,19.5 60.9,19.1 61.4,19.0 61.8,19.3 62.2,19.8 62.7,19.8 63.1,20.4 63.5,21.7 64.0,21.7 64.4,20.8 64.8,20.7 65.3,20.6 65.7,20.8 66.1,20.6 66.5,20.7 67.0,20.1 67.4,19.9 67.8,19.1 68.3,20.5 68.7,22.4 69.1,22.5 69.6,22.7 70.0,22.8 70.4,23.1 70.8,22.5 71.3,21.8 71.7,21.3 72.1,21.6 72.6,21.5 73.0,21.6 73.4,21.0 73.9,19.4 74.3,18.9 74.7,17.2 75.1,16.1 75.6,12.0 76.0,13.0 76.4,12.2 76.9,12.3 77.3,12.4 77.7,12.6 78.2,12.2 78.6,12.1 79.0,12.4 79.5,11.4 79.9,12.5 80.3,12.4 80.7,11.8 81.2,12.8 81.6,12.4 82.0,11.6 82.5,10.0 82.9,7.1 83.3,9.6 83.8,7.6 84.2,8.4 84.6,7.7 85.0,7.2 85.5,4.8 85.9,6.0 86.3,6.3 86.8,8.0 87.2,6.8 87.6,5.9 88.1,7.2 88.5,6.9 88.9,7.2 89.3,6.8 89.8,6.7 90.2,4.5 90.6,4.3 91.1,2.0 91.5,2.8 91.9,6.8 92.4,10.4 92.8,13.7 93.2,15.1 93.6,16.5 94.1,15.2 94.5,14.1 94.9,13.4 95.4,13.0 95.8,13.7 96.2,13.1 96.7,13.4 97.1,12.5 97.5,13.0 98.0,12.2 98.4,12.0 98.8,12.4 99.2,12.2 99.7,12.2 100.1,12.7 100.5,12.2 101.0,12.1 101.4,12.5 101.8,12.6 102.3,13.2 102.7,13.6 103.1,13.3 103.5,13.1 104.0,12.3 104.4,12.9 104.8,14.3 105.3,14.5 105.7,14.2 106.1,15.4 106.6,15.3 107.0,16.0 107.4,14.7 107.8,15.3 108.3,14.3 108.7,13.2 109.1,14.4 109.6,14.2 110.0,14.9", "ret_12_1": 154.0, "ret_6_1": 66.3, "ret_3_1": -14.0, "volatility": 59.8, "traded_daily_cr": 71.0, "watch": "Nothing flagged", "from_12m_high": -31.4, "signal_rank": 11, "data_quality": "Green"}, {"rank": 5, "symbol": "RRKABEL", "isin": "INE777K01022", "qty": 6, "last_close": 2459.8, "amount": 14759.0, "spark_12m": "2.0,31.3 2.4,31.1 2.9,30.7 3.3,31.2 3.7,31.2 4.2,32.0 4.6,31.8 5.0,31.2 5.4,31.1 5.9,31.4 6.3,31.1 6.7,31.1 7.2,31.3 7.6,31.4 8.0,31.0 8.5,31.2 8.9,31.3 9.3,31.3 9.7,31.0 10.2,31.2 10.6,31.4 11.0,31.2 11.5,31.4 11.9,31.5 12.3,30.1 12.8,28.7 13.2,28.4 13.6,28.6 14.0,28.6 14.5,29.0 14.9,28.4 15.3,28.8 15.8,29.2 16.2,29.8 16.6,29.6 17.1,28.8 17.5,29.3 17.9,29.3 18.4,29.1 18.8,29.7 19.2,29.5 19.6,29.4 20.1,29.7 20.5,29.7 20.9,29.5 21.4,29.0 21.8,29.1 22.2,28.8 22.7,28.8 23.1,28.8 23.5,29.0 23.9,28.9 24.4,29.4 24.8,29.5 25.2,29.1 25.7,28.6 26.1,28.7 26.5,28.4 27.0,27.8 27.4,28.1 27.8,28.3 28.2,28.3 28.7,27.3 29.1,26.5 29.5,26.6 30.0,27.1 30.4,27.5 30.8,28.1 31.3,28.2 31.7,27.9 32.1,27.6 32.5,26.9 33.0,26.4 33.4,26.3 33.8,26.4 34.3,26.7 34.7,26.9 35.1,27.3 35.6,27.0 36.0,27.1 36.4,27.5 36.9,28.0 37.3,28.6 37.7,28.6 38.1,28.4 38.6,29.7 39.0,30.0 39.4,29.7 39.9,30.3 40.3,29.3 40.7,29.6 41.2,28.4 41.6,27.8 42.0,27.5 42.4,27.7 42.9,27.6 43.3,28.5 43.7,28.2 44.2,28.3 44.6,28.7 45.0,28.7 45.5,28.4 45.9,28.5 46.3,28.4 46.7,28.1 47.2,27.9 47.6,27.0 48.0,26.9 48.5,26.7 48.9,26.0 49.3,26.5 49.8,27.3 50.2,27.1 50.6,26.6 51.1,27.2 51.5,27.8 51.9,28.4 52.3,28.2 52.8,29.8 53.2,29.3 53.6,28.9 54.1,28.1 54.5,28.9 54.9,29.0 55.4,30.3 55.8,29.7 56.2,29.7 56.6,30.3 57.1,30.7 57.5,30.0 57.9,30.0 58.4,30.0 58.8,30.2 59.2,28.8 59.7,29.1 60.1,28.9 60.5,29.3 60.9,29.0 61.4,27.8 61.8,27.5 62.2,27.6 62.7,27.8 63.1,27.7 63.5,28.3 64.0,28.1 64.4,26.9 64.8,25.1 65.3,24.8 65.7,25.8 66.1,22.2 66.5,22.1 67.0,21.8 67.4,19.6 67.8,19.3 68.3,19.7 68.7,19.4 69.1,19.0 69.6,17.6 70.0,19.1 70.4,19.2 70.8,19.7 71.3,18.9 71.7,19.2 72.1,19.2 72.6,18.5 73.0,18.7 73.4,19.1 73.9,17.3 74.3,17.8 74.7,17.9 75.1,15.6 75.6,14.4 76.0,14.4 76.4,15.6 76.9,15.2 77.3,15.3 77.7,16.0 78.2,15.3 78.6,15.0 79.0,14.8 79.5,14.6 79.9,13.1 80.3,12.7 80.7,12.1 81.2,11.8 81.6,10.6 82.0,9.7 82.5,9.5 82.9,11.4 83.3,11.6 83.8,11.4 84.2,12.3 84.6,13.1 85.0,14.9 85.5,15.0 85.9,14.7 86.3,14.3 86.8,11.7 87.2,12.2 87.6,13.2 88.1,11.2 88.5,13.1 88.9,12.4 89.3,12.2 89.8,10.7 90.2,11.7 90.6,9.6 91.1,9.1 91.5,8.2 91.9,8.5 92.4,8.4 92.8,7.7 93.2,7.2 93.6,7.0 94.1,4.4 94.5,4.9 94.9,5.0 95.4,5.0 95.8,4.0 96.2,4.4 96.7,3.7 97.1,4.5 97.5,5.2 98.0,4.5 98.4,2.5 98.8,2.6 99.2,2.2 99.7,3.0 100.1,4.2 100.5,4.1 101.0,3.7 101.4,2.4 101.8,2.0 102.3,3.0 102.7,7.2 103.1,7.5 103.5,10.3 104.0,11.5 104.4,10.4 104.8,10.9 105.3,10.6 105.7,10.8 106.1,11.6 106.6,11.3 107.0,11.4 107.4,10.4 107.8,11.1 108.3,10.0 108.7,9.9 109.1,9.0 109.6,9.0 110.0,10.2", "ret_12_1": 126.0, "ret_6_1": 110.0, "ret_3_1": 18.2, "volatility": 44.0, "traded_daily_cr": 93.0, "watch": "Nothing flagged", "from_12m_high": -16.0, "signal_rank": 15, "data_quality": "Green"}, {"rank": 6, "symbol": "ACUTAAS", "isin": "INE00FF01025", "qty": 4, "last_close": 3214.4, "amount": 12858.0, "spark_12m": "2.0,30.2 2.4,30.2 2.9,30.3 3.3,30.3 3.7,30.8 4.2,31.5 4.6,31.6 5.0,32.0 5.4,31.2 5.9,31.1 6.3,30.9 6.7,30.9 7.2,30.9 7.6,30.7 8.0,30.1 8.5,29.7 8.9,29.7 9.3,29.1 9.7,29.0 10.2,27.8 10.6,26.4 11.0,26.1 11.5,26.7 11.9,27.4 12.3,26.8 12.8,27.0 13.2,27.3 13.6,27.1 14.0,26.8 14.5,25.8 14.9,25.5 15.3,26.3 15.8,26.4 16.2,26.4 16.6,26.5 17.1,27.1 17.5,27.4 17.9,27.0 18.4,27.1 18.8,27.0 19.2,26.9 19.6,26.8 20.1,27.2 20.5,25.0 20.9,26.1 21.4,26.0 21.8,26.1 22.2,25.4 22.7,26.2 23.1,26.6 23.5,26.7 23.9,27.1 24.4,27.1 24.8,27.8 25.2,27.6 25.7,27.4 26.1,27.7 26.5,27.6 27.0,28.1 27.4,27.2 27.8,27.7 28.2,28.0 28.7,27.8 29.1,27.4 29.5,27.2 30.0,27.8 30.4,27.8 30.8,27.8 31.3,27.7 31.7,27.1 32.1,26.5 32.5,26.6 33.0,26.3 33.4,26.4 33.8,26.4 34.3,26.7 34.7,27.4 35.1,27.5 35.6,27.4 36.0,27.1 36.4,27.2 36.9,27.4 37.3,28.1 37.7,28.4 38.1,27.9 38.6,27.8 39.0,26.8 39.4,25.1 39.9,24.2 40.3,24.5 40.7,24.2 41.2,23.8 41.6,23.5 42.0,23.6 42.4,23.6 42.9,23.4 43.3,22.8 43.7,23.0 44.2,22.2 44.6,23.2 45.0,22.9 45.5,22.4 45.9,21.6 46.3,22.1 46.7,22.0 47.2,21.5 47.6,21.5 48.0,21.3 48.5,21.1 48.9,21.4 49.3,21.0 49.8,22.1 50.2,20.4 50.6,20.2 51.1,21.4 51.5,20.5 51.9,21.0 52.3,21.0 52.8,22.3 53.2,21.3 53.6,19.6 54.1,20.1 54.5,20.3 54.9,18.3 55.4,20.0 55.8,17.9 56.2,16.7 56.6,16.5 57.1,16.3 57.5,19.2 57.9,22.0 58.4,20.7 58.8,20.7 59.2,19.2 59.7,19.3 60.1,18.8 60.5,18.4 60.9,19.7 61.4,19.1 61.8,18.8 62.2,18.2 62.7,18.7 63.1,18.0 63.5,18.5 64.0,18.4 64.4,17.1 64.8,17.5 65.3,17.0 65.7,15.9 66.1,14.9 66.5,15.1 67.0,14.7 67.4,14.2 67.8,14.1 68.3,13.2 68.7,14.0 69.1,12.9 69.6,14.2 70.0,14.2 70.4,13.3 70.8,12.2 71.3,12.3 71.7,10.8 72.1,11.4 72.6,11.7 73.0,10.3 73.4,10.8 73.9,9.1 74.3,10.5 74.7,10.3 75.1,9.1 75.6,8.7 76.0,6.6 76.4,6.8 76.9,8.3 77.3,8.2 77.7,9.2 78.2,8.9 78.6,9.5 79.0,10.8 79.5,10.8 79.9,9.0 80.3,7.7 80.7,7.6 81.2,7.3 81.6,7.4 82.0,7.0 82.5,3.6 82.9,4.1 83.3,3.6 83.8,2.0 84.2,2.0 84.6,4.3 85.0,5.8 85.5,5.0 85.9,5.0 86.3,5.7 86.8,4.5 87.2,5.0 87.6,3.9 88.1,3.4 88.5,3.0 88.9,2.5 89.3,2.2 89.8,2.4 90.2,5.0 90.6,7.5 91.1,6.1 91.5,7.0 91.9,6.9 92.4,7.8 92.8,9.4 93.2,9.3 93.6,7.9 94.1,7.2 94.5,7.5 94.9,7.0 95.4,7.2 95.8,7.7 96.2,8.8 96.7,9.4 97.1,7.8 97.5,8.3 98.0,5.8 98.4,7.9 98.8,8.1 99.2,8.6 99.7,8.6 100.1,6.8 100.5,7.5 101.0,6.6 101.4,7.2 101.8,8.7 102.3,8.6 102.7,9.1 103.1,8.2 103.5,8.6 104.0,8.5 104.4,8.5 104.8,7.7 105.3,5.1 105.7,5.9 106.1,7.4 106.6,6.4 107.0,6.8 107.4,5.2 107.8,5.4 108.3,8.1 108.7,7.4 109.1,7.2 109.6,7.3 110.0,8.1", "ret_12_1": 126.0, "ret_6_1": 36.7, "ret_3_1": -5.6, "volatility": 46.7, "traded_daily_cr": 101.0, "watch": "Nothing flagged", "from_12m_high": -13.0, "signal_rank": 16, "data_quality": "Green"}, {"rank": 7, "symbol": "DIACABS", "isin": "INE989C01038", "qty": 44, "last_close": 339.25, "amount": 14927.0, "spark_12m": "2.0,27.2 2.4,27.3 2.9,27.2 3.3,27.4 3.7,28.0 4.2,28.4 4.6,28.2 5.0,28.6 5.4,28.5 5.9,28.3 6.3,28.7 6.7,29.2 7.2,29.3 7.6,29.4 8.0,29.4 8.5,29.6 8.9,29.5 9.3,29.2 9.7,29.3 10.2,29.4 10.6,29.2 11.0,29.1 11.5,29.1 11.9,29.3 12.3,28.1 12.8,28.5 13.2,28.1 13.6,28.2 14.0,28.2 14.5,28.1 14.9,27.9 15.3,28.6 15.8,28.3 16.2,28.8 16.6,28.9 17.1,28.8 17.5,28.4 17.9,28.4 18.4,28.4 18.8,28.7 19.2,28.3 19.6,28.7 20.1,29.1 20.5,29.5 20.9,29.6 21.4,29.4 21.8,29.4 22.2,28.5 22.7,28.6 23.1,28.9 23.5,29.2 23.9,29.3 24.4,29.1 24.8,29.4 25.2,29.4 25.7,29.7 26.1,29.7 26.5,29.5 27.0,29.4 27.4,29.6 27.8,29.6 28.2,29.5 28.7,29.5 29.1,29.2 29.5,29.3 30.0,29.5 30.4,29.6 30.8,29.8 31.3,29.8 31.7,29.8 32.1,29.8 32.5,29.9 33.0,29.3 33.4,29.3 33.8,29.1 34.3,29.7 34.7,30.2 35.1,30.1 35.6,30.5 36.0,30.7 36.4,30.6 36.9,30.4 37.3,31.0 37.7,30.9 38.1,30.8 38.6,31.4 39.0,31.4 39.4,31.1 39.9,31.4 40.3,31.5 40.7,31.7 41.2,31.2 41.6,30.8 42.0,31.3 42.4,31.3 42.9,30.9 43.3,30.4 43.7,30.2 44.2,30.3 44.6,30.5 45.0,29.5 45.5,29.8 45.9,29.8 46.3,30.2 46.7,30.1 47.2,30.2 47.6,30.4 48.0,30.0 48.5,29.6 48.9,29.9 49.3,29.9 49.8,30.4 50.2,29.9 50.6,30.1 51.1,30.2 51.5,29.7 51.9,29.9 52.3,30.0 52.8,30.8 53.2,31.0 53.6,31.2 54.1,30.7 54.5,31.4 54.9,31.0 55.4,32.0 55.8,31.7 56.2,30.9 56.6,31.5 57.1,31.9 57.5,31.2 57.9,31.2 58.4,30.8 58.8,30.9 59.2,30.3 59.7,30.4 60.1,29.9 60.5,29.8 60.9,29.5 61.4,28.7 61.8,28.6 62.2,27.4 62.7,27.2 63.1,27.5 63.5,27.5 64.0,27.3 64.4,26.8 64.8,27.1 65.3,27.3 65.7,27.7 66.1,26.8 66.5,26.6 67.0,25.6 67.4,26.4 67.8,26.0 68.3,25.8 68.7,26.4 69.1,25.9 69.6,24.0 70.0,23.5 70.4,24.0 70.8,24.2 71.3,23.6 71.7,23.8 72.1,23.8 72.6,23.5 73.0,22.4 73.4,23.3 73.9,23.7 74.3,25.0 74.7,23.7 75.1,24.3 75.6,23.9 76.0,22.7 76.4,23.3 76.9,22.8 77.3,23.4 77.7,23.8 78.2,22.9 78.6,21.4 79.0,22.4 79.5,22.6 79.9,22.9 80.3,22.1 80.7,22.3 81.2,22.9 81.6,22.6 82.0,22.4 82.5,22.2 82.9,22.1 83.3,22.2 83.8,22.0 84.2,23.2 84.6,21.1 85.0,20.4 85.5,19.7 85.9,18.9 86.3,20.0 86.8,20.1 87.2,20.4 87.6,20.2 88.1,20.4 88.5,20.7 88.9,18.3 89.3,15.6 89.8,15.6 90.2,15.1 90.6,12.8 91.1,11.5 91.5,10.0 91.9,8.2 92.4,9.2 92.8,9.7 93.2,9.8 93.6,10.5 94.1,8.8 94.5,7.0 94.9,5.3 95.4,5.7 95.8,5.5 96.2,4.9 96.7,5.0 97.1,4.8 97.5,5.8 98.0,4.9 98.4,5.8 98.8,6.4 99.2,6.2 99.7,6.5 100.1,8.0 100.5,8.1 101.0,8.1 101.4,6.9 101.8,7.1 102.3,7.9 102.7,8.9 103.1,9.8 103.5,8.8 104.0,8.7 104.4,8.3 104.8,8.5 105.3,6.7 105.7,4.8 106.1,2.8 106.6,2.0 107.0,4.0 107.4,5.0 107.8,4.0 108.3,4.6 108.7,3.8 109.1,5.7 109.6,6.4 110.0,8.0", "ret_12_1": 124.0, "ret_6_1": 180.0, "ret_3_1": 61.7, "volatility": 53.6, "traded_daily_cr": 51.0, "watch": "Nothing flagged", "from_12m_high": -14.1, "signal_rank": 17, "data_quality": "Green"}, {"rank": 8, "symbol": "KIRLOSENG", "isin": "INE146L01010", "qty": 7, "last_close": 2141.2, "amount": 14988.0, "spark_12m": "2.0,30.3 2.4,30.3 2.9,30.5 3.3,30.2 3.7,30.7 4.2,31.2 4.6,31.1 5.0,31.1 5.4,31.0 5.9,31.4 6.3,31.6 6.7,31.8 7.2,31.8 7.6,31.8 8.0,31.6 8.5,31.7 8.9,32.0 9.3,31.9 9.7,31.8 10.2,31.6 10.6,31.8 11.0,31.6 11.5,31.5 11.9,31.5 12.3,30.7 12.8,29.6 13.2,29.4 13.6,29.4 14.0,29.7 14.5,29.4 14.9,29.4 15.3,29.9 15.8,30.3 16.2,30.5 16.6,30.7 17.1,28.7 17.5,28.2 17.9,28.1 18.4,27.7 18.8,27.2 19.2,26.6 19.6,26.5 20.1,26.8 20.5,27.4 20.9,26.9 21.4,27.1 21.8,27.2 22.2,27.5 22.7,27.6 23.1,27.7 23.5,28.2 23.9,26.8 24.4,27.4 24.8,28.0 25.2,27.5 25.7,27.7 26.1,27.6 26.5,27.1 27.0,27.3 27.4,25.7 27.8,24.7 28.2,24.6 28.7,25.4 29.1,24.2 29.5,24.4 30.0,25.0 30.4,24.9 30.8,25.8 31.3,25.7 31.7,25.8 32.1,25.6 32.5,25.1 33.0,25.2 33.4,25.3 33.8,25.8 34.3,26.5 34.7,26.9 35.1,27.5 35.6,27.0 36.0,26.7 36.4,26.7 36.9,27.4 37.3,27.9 37.7,27.9 38.1,27.7 38.6,28.0 39.0,28.0 39.4,27.7 39.9,27.6 40.3,26.6 40.7,27.0 41.2,26.5 41.6,25.6 42.0,26.2 42.4,26.7 42.9,25.8 43.3,25.0 43.7,23.9 44.2,23.7 44.6,23.0 45.0,22.4 45.5,22.1 45.9,22.3 46.3,22.2 46.7,22.3 47.2,22.6 47.6,22.7 48.0,22.5 48.5,22.7 48.9,22.7 49.3,22.5 49.8,22.3 50.2,21.4 50.6,20.6 51.1,21.6 51.5,21.9 51.9,21.7 52.3,21.4 52.8,21.7 53.2,21.4 53.6,21.9 54.1,22.0 54.5,22.2 54.9,23.0 55.4,24.6 55.8,23.9 56.2,22.7 56.6,23.5 57.1,23.9 57.5,23.2 57.9,22.9 58.4,22.3 58.8,22.6 59.2,21.4 59.7,21.6 60.1,21.3 60.5,21.1 60.9,19.1 61.4,18.8 61.8,18.7 62.2,18.4 62.7,17.9 63.1,18.4 63.5,18.9 64.0,19.2 64.4,17.6 64.8,16.9 65.3,17.3 65.7,17.3 66.1,16.9 66.5,16.6 67.0,17.1 67.4,16.8 67.8,16.8 68.3,18.0 68.7,19.8 69.1,19.1 69.6,19.1 70.0,16.6 70.4,17.3 70.8,18.0 71.3,17.9 71.7,17.7 72.1,17.8 72.6,17.2 73.0,16.4 73.4,15.0 73.9,13.3 74.3,13.4 74.7,14.5 75.1,13.9 75.6,12.9 76.0,13.5 76.4,14.6 76.9,14.6 77.3,15.2 77.7,15.6 78.2,13.9 78.6,13.2 79.0,13.4 79.5,12.2 79.9,12.3 80.3,12.1 80.7,5.1 81.2,3.0 81.6,2.0 82.0,3.4 82.5,4.2 82.9,5.5 83.3,5.9 83.8,6.3 84.2,7.9 84.6,7.3 85.0,7.2 85.5,7.1 85.9,4.5 86.3,3.3 86.8,4.3 87.2,5.6 87.6,4.6 88.1,5.0 88.5,7.5 88.9,8.1 89.3,8.1 89.8,8.7 90.2,8.8 90.6,8.7 91.1,7.0 91.5,8.6 91.9,8.8 92.4,9.6 92.8,8.6 93.2,8.0 93.6,7.1 94.1,7.7 94.5,7.6 94.9,9.1 95.4,9.7 95.8,10.2 96.2,11.0 96.7,10.9 97.1,10.2 97.5,10.2 98.0,9.8 98.4,10.6 98.8,9.3 99.2,10.2 99.7,10.8 100.1,11.5 100.5,11.3 101.0,10.2 101.4,9.8 101.8,10.2 102.3,9.5 102.7,9.1 103.1,7.2 103.5,8.4 104.0,8.9 104.4,7.1 104.8,8.1 105.3,8.3 105.7,9.0 106.1,11.2 106.6,11.3 107.0,9.8 107.4,9.1 107.8,9.6 108.3,9.1 108.7,8.1 109.1,9.1 109.6,9.6 110.0,9.5", "ret_12_1": 123.0, "ret_6_1": 58.2, "ret_3_1": -11.2, "volatility": 49.9, "traded_daily_cr": 87.0, "watch": "Nothing flagged", "from_12m_high": -16.5, "signal_rank": 18, "data_quality": "Green"}, {"rank": 9, "symbol": "E2E", "isin": "INE255Z01027", "qty": 23, "last_close": 625.9, "amount": 14396.0, "spark_12m": "2.0,25.4 2.4,24.4 2.9,23.5 3.3,24.3 3.7,23.7 4.2,22.9 4.6,23.7 5.0,24.4 5.4,23.4 5.9,22.4 6.3,21.3 6.7,21.1 7.2,21.2 7.6,22.8 8.0,23.1 8.5,23.8 8.9,24.4 9.3,24.4 9.7,24.3 10.2,24.1 10.6,24.5 11.0,24.4 11.5,24.3 11.9,25.2 12.3,24.5 12.8,24.9 13.2,25.1 13.6,24.9 14.0,25.0 14.5,25.3 14.9,24.9 15.3,25.3 15.8,25.1 16.2,25.3 16.6,26.1 17.1,26.1 17.5,26.8 17.9,27.8 18.4,28.0 18.8,28.1 19.2,28.0 19.6,28.1 20.1,28.8 20.5,29.7 20.9,29.7 21.4,29.6 21.8,29.8 22.2,30.1 22.7,30.0 23.1,30.5 23.5,30.9 23.9,30.5 24.4,31.0 24.8,31.6 25.2,30.8 25.7,31.2 26.1,31.1 26.5,31.1 27.0,31.1 27.4,31.5 27.8,31.6 28.2,31.7 28.7,31.3 29.1,31.2 29.5,31.1 30.0,31.2 30.4,31.4 30.8,32.0 31.3,31.9 31.7,31.8 32.1,31.7 32.5,31.6 33.0,31.2 33.4,31.5 33.8,31.6 34.3,31.5 34.7,31.5 35.1,31.6 35.6,31.8 36.0,31.6 36.4,30.3 36.9,30.2 37.3,30.8 37.7,31.3 38.1,31.2 38.6,31.5 39.0,31.5 39.4,31.3 39.9,31.5 40.3,31.0 40.7,29.0 41.2,28.0 41.6,29.0 42.0,29.5 42.4,28.7 42.9,27.8 43.3,28.2 43.7,27.9 44.2,28.4 44.6,28.8 45.0,28.2 45.5,28.3 45.9,26.5 46.3,25.8 46.7,26.4 47.2,28.2 47.6,29.0 48.0,28.3 48.5,28.0 48.9,28.2 49.3,28.9 49.8,29.7 50.2,29.7 50.6,29.8 51.1,29.9 51.5,29.1 51.9,29.4 52.3,29.6 52.8,29.9 53.2,30.4 53.6,30.5 54.1,30.1 54.5,30.0 54.9,30.1 55.4,30.7 55.8,30.7 56.2,30.2 56.6,30.9 57.1,31.4 57.5,30.8 57.9,30.2 58.4,29.9 58.8,29.6 59.2,28.9 59.7,29.1 60.1,29.0 60.5,28.9 60.9,28.1 61.4,27.4 61.8,26.8 62.2,27.4 62.7,26.6 63.1,26.0 63.5,26.2 64.0,26.2 64.4,25.3 64.8,25.7 65.3,26.0 65.7,26.3 66.1,26.6 66.5,25.8 67.0,24.9 67.4,23.9 67.8,23.0 68.3,21.9 68.7,23.0 69.1,24.1 69.6,24.0 70.0,24.9 70.4,25.5 70.8,24.5 71.3,23.6 71.7,23.1 72.1,22.1 72.6,21.3 73.0,20.2 73.4,19.8 73.9,20.0 74.3,18.8 74.7,17.5 75.1,18.8 75.6,17.6 76.0,16.3 76.4,17.6 76.9,19.0 77.3,20.2 77.7,21.4 78.2,20.3 78.6,21.1 79.0,20.6 79.5,20.3 79.9,19.1 80.3,17.9 80.7,16.6 81.2,17.5 81.6,18.4 82.0,18.7 82.5,19.8 82.9,19.7 83.3,19.3 83.8,20.2 84.2,20.6 84.6,20.6 85.0,21.3 85.5,20.8 85.9,19.6 86.3,19.6 86.8,20.3 87.2,19.8 87.6,18.8 88.1,18.1 88.5,19.2 88.9,18.0 89.3,16.7 89.8,15.3 90.2,13.9 90.6,12.4 91.1,10.8 91.5,12.4 91.9,13.9 92.4,13.8 92.8,12.3 93.2,10.8 93.6,9.1 94.1,7.4 94.5,6.9 94.9,8.8 95.4,7.1 95.8,5.6 96.2,5.3 96.7,5.1 97.1,3.2 97.5,2.0 98.0,3.3 98.4,5.4 98.8,5.8 99.2,5.9 99.7,6.5 100.1,7.5 100.5,6.5 101.0,6.2 101.4,6.3 101.8,6.1 102.3,6.0 102.7,6.8 103.1,7.7 103.5,7.2 104.0,5.4 104.4,6.2 104.8,7.0 105.3,6.9 105.7,6.6 106.1,8.5 106.6,7.3 107.0,7.0 107.4,6.8 107.8,7.7 108.3,7.0 108.7,5.1 109.1,4.4 109.6,4.1 110.0,5.7", "ret_12_1": 109.0, "ret_6_1": 186.0, "ret_3_1": 56.0, "volatility": 56.2, "traded_daily_cr": 49.0, "watch": "Nothing flagged", "from_12m_high": -8.8, "signal_rank": 20, "data_quality": "Green"}, {"rank": 10, "symbol": "LAURUSLABS", "isin": "INE947Q01028", "qty": 7, "last_close": 2010.7, "amount": 14075.0, "spark_12m": "2.0,29.5 2.4,30.2 2.9,30.1 3.3,30.1 3.7,30.4 4.2,32.0 4.6,31.8 5.0,31.8 5.4,31.0 5.9,31.2 6.3,31.2 6.7,31.2 7.2,31.5 7.6,31.2 8.0,30.9 8.5,31.0 8.9,30.9 9.3,30.9 9.7,31.0 10.2,30.3 10.6,29.8 11.0,29.7 11.5,29.5 11.9,29.7 12.3,29.3 12.8,28.8 13.2,28.8 13.6,28.6 14.0,29.0 14.5,28.4 14.9,28.2 15.3,28.3 15.8,28.3 16.2,27.8 16.6,28.2 17.1,28.1 17.5,27.9 17.9,27.8 18.4,27.3 18.8,27.6 19.2,28.1 19.6,28.1 20.1,28.4 20.5,28.3 20.9,28.4 21.4,28.1 21.8,27.7 22.2,27.0 22.7,27.1 23.1,27.3 23.5,27.4 23.9,27.5 24.4,27.2 24.8,27.7 25.2,27.3 25.7,27.4 26.1,27.3 26.5,27.5 27.0,27.7 27.4,27.8 27.8,27.6 28.2,27.4 28.7,26.7 29.1,26.2 29.5,26.1 30.0,25.7 30.4,25.7 30.8,25.8 31.3,25.5 31.7,25.1 32.1,25.1 32.5,25.2 33.0,25.2 33.4,24.9 33.8,24.6 34.3,25.3 34.7,25.7 35.1,26.7 35.6,26.4 36.0,25.6 36.4,25.9 36.9,26.2 37.3,26.9 37.7,28.1 38.1,27.7 38.6,27.4 39.0,27.8 39.4,27.8 39.9,28.5 40.3,28.7 40.7,29.0 41.2,28.4 41.6,28.3 42.0,28.7 42.4,29.0 42.9,28.2 43.3,28.7 43.7,27.5 44.2,27.3 44.6,27.5 45.0,27.5 45.5,27.5 45.9,26.9 46.3,27.3 46.7,27.3 47.2,27.4 47.6,27.1 48.0,25.9 48.5,25.5 48.9,25.9 49.3,26.2 49.8,27.0 50.2,26.7 50.6,27.2 51.1,27.3 51.5,26.9 51.9,26.8 52.3,26.6 52.8,27.7 53.2,28.8 53.6,28.6 54.1,28.2 54.5,29.2 54.9,28.1 55.4,28.8 55.8,28.0 56.2,27.2 56.6,27.6 57.1,28.0 57.5,26.8 57.9,26.7 58.4,26.4 58.8,26.4 59.2,25.8 59.7,25.7 60.1,25.4 60.5,25.6 60.9,24.9 61.4,24.6 61.8,24.4 62.2,24.6 62.7,25.0 63.1,25.4 63.5,24.6 64.0,25.0 64.4,24.7 64.8,25.6 65.3,25.2 65.7,25.3 66.1,23.7 66.5,23.7 67.0,23.4 67.4,22.7 67.8,22.1 68.3,21.2 68.7,21.1 69.1,20.8 69.6,19.9 70.0,19.7 70.4,19.6 70.8,19.2 71.3,18.8 71.7,19.1 72.1,19.2 72.6,18.9 73.0,18.5 73.4,18.3 73.9,18.8 74.3,18.1 74.7,18.3 75.1,18.0 75.6,17.1 76.0,16.7 76.4,17.7 76.9,17.2 77.3,18.2 77.7,18.1 78.2,18.0 78.6,18.1 79.0,18.4 79.5,18.6 79.9,18.6 80.3,17.5 80.7,16.9 81.2,15.8 81.6,16.5 82.0,16.6 82.5,15.3 82.9,14.9 83.3,15.5 83.8,14.6 84.2,14.3 84.6,14.6 85.0,15.9 85.5,16.1 85.9,15.1 86.3,14.4 86.8,13.9 87.2,13.8 87.6,14.0 88.1,13.9 88.5,14.6 88.9,13.9 89.3,13.0 89.8,13.4 90.2,13.6 90.6,12.8 91.1,10.0 91.5,8.9 91.9,8.3 92.4,8.3 92.8,7.4 93.2,7.6 93.6,6.6 94.1,7.0 94.5,7.1 94.9,6.7 95.4,6.5 95.8,6.4 96.2,6.6 96.7,6.6 97.1,8.2 97.5,7.6 98.0,7.5 98.4,7.8 98.8,7.2 99.2,7.8 99.7,7.8 100.1,6.2 100.5,5.7 101.0,4.6 101.4,4.4 101.8,5.0 102.3,6.3 102.7,6.2 103.1,6.1 103.5,6.8 104.0,5.9 104.4,4.2 104.8,4.4 105.3,4.2 105.7,3.6 106.1,4.7 106.6,5.2 107.0,4.1 107.4,4.0 107.8,2.4 108.3,2.7 108.7,2.0 109.1,2.2 109.6,2.7 110.0,2.6", "ret_12_1": 109.0, "ret_6_1": 94.4, "ret_3_1": 27.2, "volatility": 28.1, "traded_daily_cr": 300.0, "watch": "Nothing flagged", "from_12m_high": -1.1, "signal_rank": 21, "data_quality": "Green"}]}, "prices": {"TDPOWERSYS": {"2026-09-28": {"open": 730.05, "close": 722.0, "src": "yahoo"}}, "AEROFLEX": {"2026-09-28": {"open": 524.25, "close": 513.4, "src": "yahoo"}}, "E2E": {"2026-09-28": {"open": 650.0, "close": 625.9, "src": "yahoo"}}, "LAURUSLABS": {"2026-09-28": {"open": 2000.0, "close": 2010.7, "src": "yahoo"}}, "NIFTY50": {"2026-09-28": {"open": 23064.9, "close": 22780.25, "src": "yahoo"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 03:09", "days": 7, "items": [{"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks With Earnings Growth Over 17%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-earnings-001032785.html", "source": "Simply Wall St.", "published": "2026-09-29 00:10", "score": 0.888, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear S</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8tTlNWVlZxU2J2OGUzemk1akNYb2k2MDREZGNNZFJ6UmxQcGQtblVyV2RKRnJ3cl96M0kzdmE5bmU1aktMcG9oZU5nUE52RnhuSGZSbnI1dU5udm9aNVpuQzVVanlZTWVHbHhGNDRDMlllS1F2ejFGcmxuNnhlOHloNE4yUdIB7gFBVV95cUxNYkFxX1BHMHZULVZmS05DY2N4cXJjaWdnX3RsWFFaWnJjTlF0dk1ySEtERGF5bzF1RFM2SjRZYzVlUUQ5LWswYUVvSHoyb3h0dC1jZ0ZZcnhkYXpFMzJvS25LNEk1SzFKTmdGVnN4MDdQN2FMaHhmZFdQVDc1TVZWTXlSSUtRYVlPVzBER004eFpRcFFhZFpXRVM4T0FWZFFVWFZQbjNnRk9tVFFtWVBNY1FEVmNBUzZPdFNJdWVZWGRsdzB2ZnRwZUI3YWdzUTk2Ym9lT2VtcXZFZVF0NUI0bmhKNHNUdzhMZnAzZDZn?oc=5", "source": "NDTV Profit", "published": "2026-09-29 01:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQWDNNbllRRzFSTkxtZmZHNmJ0ZnJPdDhyZFh0LUVuME1CYU9hdkZsR3NubDJXN2NQUXFnUER4RVhud1FsUENqWUhMdGdjT243VGZ1RGZJWGVMV2UwRl9HTTNQSk5wVU11djAzV05oalhsYzRrdG9mUF9ya2Q1ZUc5dFFUaUtNU0RqWExWMXVLSkVFSG9pUGp2VVZjWlJqdE9QbE9hRzIxYWJURXhwYm9faDk1S0Z3X18xd1J1d2duVXExemd6aDJyOEo2OW5RLVFUTWw3ZFFhU21oNGxZRnVfWXRPcjBDNzFUYVVrN0lfRzNoNDJJcktFa2FVR3lOSEVPSl9XN0dLQVNPaGfSAZACQVVfeXFMUEQ4OS1kTDJjTHlCVHp3dEFPZmJNdGxBQWlrdmN4dlhGSm45c1duQTM1WmFGRnRuTmNrRW5FaV9OQnBtc3dmVENWU1QzZG5yRGpyVFRTLTFnTlUySlNfSTFIR0RBSXpkQkhlWjNSZGFKTkFteVliTE1Zdmd4VWpCVkZ3MlQtTWxjZWdKR2VfdEM3ellKWlhua2lIVVZGaHB3bjlYQ0ptaWpmYUtid2dnLU0xdGlnMm9jYXlBSUJ5cV9ZbGZEUEUzMWd1czk4Q3Z3UHFWVWRyb3VxZy1EbnkxVXVmOVdmMVlHaEwteUllVkdCRThlQlc0S0xyblBKa2lUbWtwdzRJSGp0T0RfVE44cG0?oc=5", "source": "Livemint", "published": "2026-09-29 01:19", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks With Earnings Growth Over 17%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-earnings-001032785.html", "source": "Simply Wall St.", "published": "2026-09-29 00:10", "score": 0.888, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3ZwWkRNRjJrZ1RQN0tCaXBfTGZORVVIeFJ2d1FmTkJpZ3RFM2ZUNW52alVyTDVSLXNzN0hRWUE0YUZ1NXBJZWEzbWVuV2NDUFRxNmRmWXVSdnkzZ0MtLV9UMm9FeTVaM2VGckptZWt1Wnhpd2F6TmVjcEpXVEJhNXpKWkVFd0NCelczRTBidmMxam1zVjRfM1J0aDVHaVl5MWtkQ1RvS2xXNm9lMTlraE9IQXBqd9IBuwFBVV95cUxQdU1hSjhhcHpRbXBFRmlSLUVvakR5c3ZwYlpORGl2M1hiaEhqa2dDWTVIdHhmY2NsNkVUWFZKT1c4MHROTG1fbEtCYnZnM0VMOHFEXzB5cFotZEtGNHgyVDR6ZkpwM19JM1JaVmlFMElpSUw0OHRMUXNKVUlvSEswOFdQcXlLLVVZZWpDVlE5bHplYkZoNUp4bUVEV2VhaWFVZzNDN1dpRFVUMUROeGtLQ3VlZFJjUDZ5Rmd3?oc=5", "source": "WION", "published": "2026-09-28 19:51", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQWkFyUEVEYlc5ejlyTldhYVVvYml2c3N0YTlnSm9yZHEyMDNHUnNKVnRNeGl5NTZ0NkRpZFJJWURHUjdEczROQVpseThQbmlJdGRLa0R2X0Vid1VKM3FncW43TkVIU0hpVE5QY29VMklwNDRQa0FXNHpoRXhWSC1kaFQyVUtzc2RZYk9BMWhpTU5XTHZ4RHRMMU81azFLVFF4THZkTjJ6ZUl5NDNLcWFibmtqOUhjeEJYQW0zY24zT0lhZnMwZElXQXpB0gHPAUFVX3lxTE9jTkdQUlc5aXV2N0dtX0UzYWlfV2ZUSEhCUGp2OHFENzhsWnJQODNmemptdW9oQ2s3Si01ZnV0N3RlazVRS3YxZWJsNDZWZEx1MXdMcFFzZy11MnItN1pWQTdYS284QWJwd2hQZXdxdDc2VkR6emZGZFdsX1pDM1d2Rk1Ka25SVTRXcnAzT3dqekpRQnBKUXBwMGpHZjlQMXBtUi1pUEJac0RYSW9LcnBTUFkwbXoyQ2tDUkN4bEs5UGpoR3NBaldjekJVMFJ4MA?oc=5", "source": "Business Standard", "published": "2026-09-28 17:36", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr", "link": "https://news.google.com/rss/articles/CBMinAJBVV95cUxOOFgyakNMWTlmbmpOdjRVeTdlckZXNks0dmhfc21YME9FaUcxWjRFUG1XdTQwblI3MS1oUFN5eThST252YWpSdkhXbWZQY1V0ZWdVTGI5c2VXNXdFbzI3aUozMDh4RVMxLUxnb0tLX1NYU09yRGxGMWlvaDFlRzQyNkd2eUsxZ1lBTVNnMWI0VkMwejI1a0pWcm91NXFJSUVDZ1VhQ2JESWo2cnpDSHNHbGlhY19Za0pNQ0E3V045bjJMR09ueDZIdkNVUGthN3lRak53QWpiN1B0WkpRb3dRUTNaX1RYVXp0LUMyZG1EUWZPZlNXUGQ0WldOLWF6MFhQalU3YzA4WUttM0x6al9xS0xSVHdOajJJa2lacNIBogJBVV95cUxPanhKS0R3c2ZjbHJ5RlhHMmxmQUVLSFlUTEtBcWFTbS11YlNxdzZqNDVRSHBISmZfblhRcnhPbXVwN0NkclB6ZHNLYUk4bTZQU0x3YUs3NXdrUVE4RzJzY0VQVjZfazRmSmtudW9lNGtqcU1aMU5lMUVVS21lWm5pa2NxWlZxLTEwN0FlNGVJVS1lTzVvV1B6R0lsZGtDOUViTEFycFdFb3FmSm1KTjJZS3dEV3FUMEc4T0FVQXdBTFlCdk9sUlRyMDA5WHA0dmo2Q2lYcTFGTTJqYkI2R1JDLXZkbEdpYTBDU0NWZE1tTmd5SkFBNWxTM24yOERhN0x0SWkwY2RzZmZkRnFqNUJjdER2cFpqYmNBYVNfT2otZks5QQ?oc=5", "source": "The Times of India", "published": "2026-09-28 13:42", "score": -0.896, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNUkhaTEo2TVV5Q3h0cjBXLWVGX3EwakNwOXJxS1dmT0Fnc2p1eXByY2d4cFlIbE1HTER1QXFqWTB0bHNLR0lfWTdWT2RTTnJKRjYwLVhPU2t1dEdVMk5NMFZfemk3TFNhdk5GWDJGRVZUdV82aHJETlJWS051R0N6bU9pSktUWjR6SXY0d3g2ejhjeFRpdkszSFJzaw?oc=5", "source": "Equitymaster", "published": "2026-09-28 13:25", "score": 0.652, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxQeEMyTGpqalIydEJBcFVFWC12WDdUZVYwbkJPVk1RTGRrWlpwTnlnMWJPMk9TM21CWWxfWkpIRU1QRWNCcVcya2JHbEFRLUZLa0Vwb29SOWt0Q01nbmRfZUhrcDd1M0hsb1pHWWViTnRUNkNYek9KZDVEcUlnemU0SEozeGo0dDQxV3BJSkRlS3JQZU91YWEtUHBERUt1cWZ0T2VZY01yVVlWRlNUR3FpWlJNeFFHYlhiekdoa2htZzlJeWw3b3BhaXFnRy0?oc=5", "source": "hrtoday.in", "published": "2026-09-28 13:16", "score": 0.361, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOZGFILWIzX0lTNkh0Rm8zMGVUTWxEVGdYN1FXR2JPUTJDeVhiNHdwaVdGM0xCOHdUYTQ4MmZqLUtVTXk5NU5va01tSzN0b0lJWjFMcmY3M0N3OEhaa1NYLUF1WkxLUk8zaGZZT1RzYzd3MWpMQjFmdTgtYm5fWG5Xb3VWenYtZEVWQTJsZDd6elFSTWd2RWtMeURUdTgzTFgxSExQSW1rMFJLVkpnVG5TSGx3YUhtM01oUHpvRWNERDEwTmw3RzN1d0M3SlZ3dThNbEVnNnBtVmJXMGgyaWI0NVUzeFJ3LWFocVNyVnBqM1BxeEdlZXVQeUJZdXRKdWwxM2hDU9IBigJBVV95cUxQUWpCNDFiSU9RRGF5Rm5PYU9FZGp3c2JWVFRVSzFWTHdrdDZUczkxMVBnLV8yN0hmQkdhbXhYM3dLeHViT0Fjd0o1MkFpT2h4d0tkR2JjS29ZZWs3T25DRV95dDVtNWlFQ2ZkbGZ1WVgxRU43aEZBZEZjLVNnZ0JnZHd4TkJUbUVMaHdEUTZERnFvQ25RT3V5MmxrRk5UaG1oQWoyTUtPMG9oaktqczhZel9nTUN0eEpfRkdxWGZHRTNHUnVRQVlUdENBVFctUnRRS3lMRFBWMVk4Y1JhVFFHMGNMWDNrNjhiclVOOThFa1JrTkxZWjB6U09fRGRZLVhrbGx1OE9MZHFMUQ?oc=5", "source": "Livemint", "published": "2026-09-28 11:48", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPX21IU01KT20tUWlfRy1IMWJ2LVBfSXBlOFdWYUZid1ZJdDRncFozNEtSb3NRdnlUTUlOTHFBNkloNjROR2daRV9EQlRObWhYYm1uYkl1dGdDck5yRXM5b1pzU3podGhMc1UybjV6SGNnd2J0dW9xWjRaLWVMWjBLYXlqN2NCRk1fSndYX3lBUU9LUGRBMlg0VnBfYWtJcHhaZlYwVTBxMHBhMWtXY3NhRko4UmUyVDZOUUFVRWN1OWs5RUhyOGxzV0VMWl9sUG11RjdudmdVNHp5M0hFQ3N1aUpoN19LZ19vVmo1MGVBQQ?oc=5", "source": "Equitymaster", "published": "2026-09-28 10:56", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Falls 1,124 Points, Nifty Slips Below 22,800", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkNsYXBaNkxVbEJONXRoU2VUMDhmLVp5MjJ4bm9KZXJpWWp2TV9WQWhkYndIOWJOM3AxbHljM0Z4amc2NmVKS0p1SFk2REJiUVdxT3JEcG9tQ0VPMEJSa0kxNUlOS2dGTHFVN1M0T3JxbThwSkFVMHE2NzVYck1FUDR1bmM2bE1UbGJaZVFmR3hCVDJTbERmTzFnMVBoUlg3dmRkdno3b2lmZTVGNGhQbm9YOGl6SDlBSkt4M1ZoaUlsTkVf?oc=5", "source": "hdfcsky.com", "published": "2026-09-28 10:46", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPUU44cXhTejNjWEFmX3pOMEQ5YkhwR20yQUs4NGxnNks0d09rWnU2R2pxMWdmOGQ4N2s4Nm41WW9OR1lRRzU5X240Nnp4Zm44NFJ0b1N6a052VjJpXzlmR1VIXzlobHd2OVVJYnV4Q1BfMHNZUmZ0eWNqWUNqMzNGelN0Y3o5ZXRxY3hzby05M094NmZ4aWxpakRnZlZWYlRQMnhvVGRJcGlleVFpMHlNS0VRZllGQTktc1ZUWXM3MldYVkd3THVpOUh1TVVJVDJqd2tiU1N0al9oblNQajFGUDN6RlV6UGRQU2poMTV5dDRtTEVnZ2p4bzFITjQ4SVRoNVV5Z2dZbTFyUDDSAZACQVVfeXFMTl9adnRITUZ1VzVQX29ZOGpxVXpOZ24wcFluN2JGVjFsT056LU10RmMyQ3RnM3pkQlQzSV96TXZVT1ZWdmFNU1VSZmhpMWlCaWNtejhpNWwyZ05CM3c5NjJ0VnE3MUl5R19XWXphSU50eWRpd2RZemRtMzcyZTJMcWpOUUJEZ1BwZGdyXzl6ZW9MbkRoOXZjYWw2X0tURlRyTk13ajNhUXRBbWJpaFhQd2lUd1doVXRMU0VRQVRBTU1rM0xxMFN2alRHRWlWZ3pUUzd5dGJwQTJpdUlDUjJLMjBHNVVOVTJtMFFhdVlJb2dONjJjNzU1Y0p1ZE5Cbk9XcFFRT3ZYNHZaVFY1V1lIVjE?oc=5", "source": "Livemint", "published": "2026-09-28 10:15", "score": 0.402, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks shareholders approve fund raise and borrowing powers", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxNR1MxLTBoYmdoaG5EZlRjaXpBaS1ZNmkwbjBPV29xOUNGMlFQTjdFdG5ZS0JTRExGcm1XWTJCWERCMG9SRm5FcFBwSUZuVkZ1clJ3RDdRQWQxMENXTDA4UzdRUVBZeTJNN1RIZ281SG1sYkJ1TGZZeFBpN2FIRS1ieDJPcVNXY3ZuS3VHYTgyM1VuTzMyaFZkSTAwSzhrZWI2Mm1iVHlkOUlJelFUVnM4N0I3aVFwR3hvOHc?oc=5", "source": "scanx.trade", "published": "2026-09-28 10:06", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVkFmQXdEZjZITFVKV1BEOHlKXy1rajlNZ3NuN3N6UXdZa2lWWVFxNnhXOTJtYmZxOVpOcVVpLWE3VUhwZUhjVXBYV2VleEVpbVR4RTRsc05tTFBIcXNoME5VaVlJVFR2ZUx0Mmx6RXlHTFhKUUdFU1J2OUhXNERPU2xsa0FGTGFOcjJzQ0ZlQkIwY204X1Z3UUZTMEt6NDZRVDJMbUQzclRobkxrcFpWbGJTQXJnRFR0ZHBMdURjQjgxZw?oc=5", "source": "Kalkine India", "published": "2026-09-28 08:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Nifty, Sensex: History favours stock market comeback in October; stocks to watch", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZE5UeURMRWtrOUFNekVkT0ZOcFI1SkE4Q28tZDc1NkJvbmFaakNlQlBDWkt4RDd6b3FpazN4NjRzWGhMN0RaYXY0U05IVEY3bU1lN3RFaURJSjRUTnF5Y3o3LW1wT3RtSkx5LW5yaWpiemJ2Ym1lYjdtTmpKY2lPWk04aVhiR25wMVl5ME9HSmUtQ3RIaENZTC1pOHpOekZVUVNSSWlFaXl0N2NrS19MeVpJdUxLeEl2blBYSjNseU41V2NjTUxmeklyeTN2Y1B2eWNuQWFTS0FVX2hJNWfSAeMBQVVfeXFMUDhHbWlIakswUl8zYmdMcHhmcVlGQ1V4RkdsdHhqN19JMjZwT0dxMGtVeHBQX2gxZk8yVlFwamlzblJNbUZJZU84N0RRTWk0U1VJRmc4VUZyV2p5NnJLNjRYcExKb3NKWjg2NmlMbUhRVFNDZHdocnNsMl9RVTF3YjBkYzMzaTRqdFAzbE9jX2NKWlZWb3FGOEFPMkktYURRbUZLYTR3SUVTWG84cXo3TzItZGhlOTBoNFhfRTlXSnNfOHJPNVctVEFEcW5WSzg1bHNHR1c4MUoyODVYWnJqV3U2U3c?oc=5", "source": "Business Today", "published": "2026-09-28 08:15", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher", "link": "https://news.google.com/rss/articles/CBMiowFBVV95cUxOci1kRlliVGdLVkdiMUM4b1lqbEFvLUdDV0VITWp3NGlyb2w5N1Rmc2pZUi11cVhmNkxDUlkwZThkS1hOZ0lFaXdmYXJoa3FiT3hfeHhaNkFwdEg2b0V6NHZaZ094cG9RZGQxLTMySlZLX1J6SGRXcU1Sb2RuTng0RzFzc1lZMWNHNjY4b29HdWpzOFRWclh4S1JGUjlGelRRSzlv0gGjAUFVX3lxTE5yLWRGWWJUZ0tWR2IxQzhvWWpsQW8tR0NXRUhNanc0aXJvbDk3VGZzallSLXVxWGY2TENSWTBlOGRLWE5nSUVpd2ZhcmhrcWJPeF94eFo2QXB0SDZvRXo0dlpnT3hwb1FkZDEtMzJKVktfUnpIZFdxTVJvZG5OeDRHMXNzWVkxY0c2Njhvb0d1anM4VFZyWHhLUkZSOUZ6VFFLOW8?oc=5", "source": "Free Press Kashmir", "published": "2026-09-28 08:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHU1a2VYbkdKb1k1RENtVm56MHlVeE9EcW1DQWd4ZmRyY0g2b2JqZjkxVENveE5US2JvaWtoanpITFc5NzVFS3hzMWRxcmtPUFJ2a1NBX2xsVDJUWEZrekpKNWVLZzZ6TlRQUnVoVWZWTzZ3Q3VBWTM0WkxqRzVhM0FzWm5kNmtCa3JMUDRENUwyVU1iZDBNd1BMRkpWenlNUHpLTDFScU1rcW0zcnNBM3pWODVoMHV1WlhwNmVSSllWTHVWOW5hRE9B0gHPAUFVX3lxTE00UXRvMWNWTlhGMWphc2xibF9MLUtJQnFQRjR3UG5nbVh4M0NWMVg2MzdockRzaEdnWlpTcEtyM3dGWnRTbnFRQnRKV1JmZk9RdWY2UnpYY1VsWjRBSDVwTk10clJnNHlCSEs0a2g2TFA1alQyYUFWNXIzWDNfeXlOejBhVGJrQTJZRG13cG5XVEdVWExyM2Yyb1owX2pmUDNTWEZsenBGcUlYdWpWZ2NpSXh1dmt4blhQYUptLWFNNnBndk04NXhzdVc2ODNNVQ?oc=5", "source": "ETV Bharat", "published": "2026-09-28 07:56", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxQVWNmQ2tBRmd0NTdUbmZ2YW9kZW1wdDZrMXU4Y0gtTXZPYU9uc3JGRGJXQnhBaEY2YXk2TGhCWlhqZGU5OWs1eDlPOTJMcHp3ek5GUEYtcGQtYUdUVmpTZzVNZGlnS2UxVXhHZE9DcTYxSk9uWkFmaThOdUdzbnpmanpXUF9sSVVReXFLY29VeTg5QUZPNkszSmNGQQ?oc=5", "source": "apacnewsnetwork.com", "published": "2026-09-28 07:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxONU5xeDQyaGZ0M2JBemJwU0REcWJxYkZWN1hxM2d1VHZBOGh2X3gwR3plbk90RlZMLWtWZV9jek1KR2lsTDB4d09oQlJzRTNadHgyUEY4bHhFbGp6eVhOWDhqLUtQWkpIUldLLU1EbUoyU1VfYmNaOVdqWnJzREo0Mjh3bU5wTTZPN081MmVFY0liRzQzVEtZRWFVMURCaTJZX0twZzRZWVJHVV9KaEl2LUNFZzBpdmt0RFM1OXZoLXVKQmt3WmlDSGR6VHZFMWdiV2dWcklYVWxuTXdFbXc?oc=5", "source": "Upstox", "published": "2026-09-28 07:36", "score": -0.806, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxOMzZwenBCS1ZIMUJRRXVOZTBBME0xU0N0WGJsVEVfQkVhZ1NtMEplNUNXM1A0WGRZLUVOZWlTNi10QUVQQnJRSnZDZTh0SXVlQkN5eDZ3ZWstRVQ2TlctUE82ZmxJRG1BZkw1NjZGZGYyZWJiZlZ1YktSZU5OTk5MZ1A0Q2NyV0wzZEd6c3dHaUwxcUpZa3ZBQ0g0dGViQzhfTFF4RExTb2p4azg0WjhlVTBlSUZtSG80clVYa2p2MFBuZWIwVURXMGd5dG9wVE5sWUNLbGJCb1U5SjNBcHNXZnE2dGNkUlVhVUlrNndWVTVpOG1jWVZYeFppQUdRekXSAYQCQVVfeXFMTWsza1RTaVB1QndYVDNrWE1GWUo0QkJCd09tUGxGUkx2T3pVamh4d1VTUG9FYkxpUmpRV0RlaDhxeXVMMFN1Vk9sMVRIY2xaUjNXRlhYLWN0SXFuT2V4UktnYlRvVnZzUlFQbkJFZlNsMnBCR1JZeTVvRzVUa1duQm5hb2llbUlPNmZuQ2owWUFPbDRJWUV1ZHVoZWd2ODJMUFo1V3g5RzNfRnZ4MldzV0F3UGJfV3UzZ0lxWjdIS0hfZ2JXeXh5VFVtTm1JVnNtX0d2bjAySWZZU25TZGhiUjhkVERUenU0T1VJTld2WGM4QmVOckxtMk5QcThMbnR6bjg1cGs?oc=5", "source": "CNBC TV18", "published": "2026-09-28 07:06", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxPUkRFSHF1dXJEMUtBZUdNc0FqX0g2TjZqMV9MSFRVSXdDSHRobkFERnFiamUtMDVVcks2NDVkS3JYVzNYR0dCMnFlVDVobmpEWlduX2tCODBQMThWMm96RW1BTUlHbVlxbVMwNkpuWVphWFZJS1pTUHdwYWFJbEM2ZzNZTWhYS2luLWhYR1htelNSS3E1OHpXaV85Rm5iQWVIcHFnNkpiYzFFTHB5eXktdEplbUk3czJwV2dadzlBR3MtQmtlNnl3VDBhOGc1VGs1eENMWU54STdnREtoc2NOeGpJWXMxSnp1VGEtUVJWS2c3YWPSAfsBQVVfeXFMUFBfZ0J3ZVlJNGVQMHhXZTNvaU1wUzh3dHYzOU1sS3pFX2RIS01fSmpIMDRLOExqVmxMemRwRTZjbmxNcFRHbTlScFhKUHh4TXJzSTJyR0g1cVNwRmd3WDVWck1iaDB0b3FsVzNpYy1TZUU3RExUZjdfcl9ZTms2a2VnZUQ5NW11VEdGbFU1VmEwUjRPaGNHS01sVDVTMDNpVUltUFFUc2NKRDV6bmVyZWRMcDNXTzE0cEZLc3lNVDlpTmZMd2ttaVg0Ylo2d3BYY3BJa3dUcFM5UU9yLVpHSU16MXVUOUZ1dUhmSTdjVTRfTDZGZWUwd05zQjg?oc=5", "source": "NDTV Profit", "published": "2026-09-28 06:47", "score": -0.791, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: decline, valuation and peers", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE43Z0JKcUo3bkM2R2FfLWQ5TXNkQ2dpMnNldEZ1UHU3THMyeUkyTkc4TmN5V3NEUjFiNGVEQlBWd1pwQk5lZk54YWIyX0F3ZGNWQWJJc1NGY25WakxxMjQ3VWFfRHZhN291N1F6Wnd4YW55TjQ0eXJ5bXNuMA?oc=5", "source": "Univest", "published": "2026-09-28 05:52", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxOZFhpNERkTkx4Z2RRS1k2ejBhN1IyTzR6a2g5MjJ3bkNjeDZlOWRBSmlIek1xQk1GcVIweUZvcVFEcGwwSW90RThvU0J6cng2YVpLV0tZU1dQQlhGZUtieFVuZ3BmWXY5aFFkSlRuR2p2ZW8wZF9TQmZ2RnJoNFV2Q1lMT2JGMkxLUlp3OF81dlkyWHVmQ0xyNVg5R29GVXZkR1NLUkRqTzF2ZXA1cmtlcEptcmJNR3dwRi1R?oc=5", "source": "India Infoline", "published": "2026-09-28 05:42", "score": 0.103, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUdIB8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUQ?oc=5", "source": "simplywall.st", "published": "2026-09-28 05:37", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r", "link": "https://news.google.com/rss/articles/CBMiwgJBVV95cUxPQ3drbk9QbWRHcU9uVDJLU0EydWpPdVZRVE1rTEE5bFZadHZmUVJPeG9nUjVYWnVvSTkzNzFyNFo3TWhfN1lzX0ZScEVrSnZETUJ2MmtDaE1XYjc2TXo2a1p0UWZhcHprU1lwM3V3YUNUVzlTc3l4UXdCLVExX3dLQTdRaGh5Rk0xUDQtR2lkY3Mxd29QSHNPRU5fRDFYRVBSbC03X2pFaGpnWlJ6MFZDUGlicHlPUUpXeDh4ZU94UWR5ZHNCZ0pydDdFdHZNSjgyRThId0JfSlcxVzFibmR3clVwQzllekZnLUJ1LTdZcHpsRkt1YzN0b1FBT2FkZF9zblJkRlIxdmZfdzNFSXllSDM3b19zME9xaXhlWGk0Qjd5TWwxdDJaenFsOE5iOUNOU2VKRkxYazExZVAxYWJuVVVn0gHHAkFVX3lxTE1EMGdQdWlWbVp5aUpTbEJmb0M5dWQ5X0xJYmNpTFJJVERpUDZkcVo5V1ZGeTNyR3VmYjUyUDF0bG1HVlBGQ21nNDBfU1RZRTdYTEZFTy11OXExZmNOdzRwQTFQNlBRcFZ6NVdDSFFkeWdkV1ZGdm14cXpoTTc5eFc2WkZnVTQ1SlZ3NmxCOWk1b1BWU3doODZadUV0c0tkQ0VCeERINlczUmlYWmJ2MjNoblhPeWtqa0NvU3ZRcGw4NlQ3Mk5GcTFlZDIzQlN4SWxiNE5Md0ctQVBmMklselFGekszWTlFM2JFN244eVJtOHctcnFCc0RVM0Z4OUlqVmctZ25xTDVnTTV4djlfc2U3T2pkeC0tajA2ZnVKRDk3eEJ2ZkNWSmZicmVEOXN0UHpfRkJQdlZMLTVveENMYmdJenM0UFRfRQ?oc=5", "source": "The Times of India", "published": "2026-09-28 05:18", "score": -0.691, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeDRfUkctTnR5c0x3dEhXcmFSWWREQnhLUGMxbmFRT0RpWW1CbkVpN3dkcjJTSUZOd0ZpTjF2M3U5OW1vOEdHS3BKZG03d3BhenZtX21jTEh6VVc4ZC1oazJmSGJCZTBQTVZObmVYeEJFT2ZuaVd4OF9rbWNyUGo1T1ZMZFFtY1Zpd2dSYV94Yk5uS3FRVWFueWpYaTNyVjJVdnVoRzVFaGhvc1pOcmJOb1BWN2I1VXBTTnNNWURYZ18tRXFkZHR3Mks2TEk4X1lMb19NbVU1am5jd9IB4AFBVV95cUxNbVVHcVRveFpQaExzeVVnLXV2bTRTY0dTaTNSWDhoWEdCVkRCZjdZY0I2TElNdWxlb2RYVThZcXFFM1VDQVRxbmRETlVSTGJjX1R0MWpCQTFId3Iwb0hjUXF4bHhoNjNhZlBoeFptZHVHRWdwYTIxd0N4dmZtNHNFRXhvc0h4TVFXNl9ELUhkQ1VXS2FjV19NWWZpeGJTZmc4R0VWZldxNWVlOWlzVGRHX3cwaUd4UjVuMmlDVjlVelA5Umt3dVkwTDlhOEFSWGY5V1k0anMwOFNGbU5ZNmtZUg?oc=5", "source": "The Hindu", "published": "2026-09-28 05:11", "score": -0.852, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQeTNsTy1qVmtORm03dkJ0LVQwRUVQU3ZnT0RqMEI4NG5kVUxYeU0wcmp2N1hqaFVPdXhHNDV6cGRuZUcwclFTZ2NUV1NjdzQwYlhwWEMtcmFIVXZpMWxhWnpzOUFwaF9QUTVPQXVnTmZlUVVHNlNZQTVUOWxjdHZ6UHJuVDVtZkpPVWJqd1hlLXNlUVBEMmNuUFRCUFZZb25KNGpaNmJ4RjRuRDh5ZWFvS1JheXpLSzVQWkNSODVvaHh5ZUgyWjFPTTRnYlpxbUluek0xZHdaVU91cVRrYzFHWVJfRlJVemI0RW42Q19KSdIB9AFBVV95cUxPRWZEblJNRmlJNmdQMUpNa2FMYzNDRGZrTlp2RFh5MnZvSW5HMDhlVmNPODRlRkJTYkIySVFBWGZQLVh3Y1QzWXhValo3RkpjX0pidkhKQjJaTGFGOXhsZzBfeHBadVhGcjZKZXpuSkF1ZFB4RzVwVDIyeEtqamhHX09HR2FtY3ZRcGM3bzg5X25sU01NeW85LWQ0SG9pYjMzS2VfU0pncEJLc2QweG5wbFdZbEpDU3hvenI3V1BUU2FPclVvZGNCU1NEb0ZsZU9GdmQ3Smd6ZTZ3WTJtY3BTOElrdURuLVVsZFo3ZTVLalFBY0lD?oc=5", "source": "Hindustan Times", "published": "2026-09-28 04:45", "score": -0.361, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE stock slips below issue price of \u20b91,785; down 2% on Monday", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQSTM2eERXZ0NPUHpTR185VFYyNzFaR0lYZlMzeHB0Y2dGMjM4RlhXdWtnczBEblZtV2F3YVItUUpYbmhGTWI0YVpSdVlRejFmZUdyWmhLRUYzNFVCNkhsdWZoMlpTenVZSDBkVXNpY0Jwam9pTmtocUJhdzA1X1dyWTVJVWhVdzJZRWpiNzVFRzd1NUREdzd3bW1vQm4ydkVETWthRE1WVGpqUkZoSVZYbmtqdVNuWnhnM2ZaaHhORjRReXM50gHKAUFVX3lxTE9fUlRRS204UnpsenJGSWtxSnJiR19Dcmh2LXFMVWhQSzdDamQ4QlBSanluUDdfYUY5YkpXcURFZUZ3TU1TQVM1WFM3QnhoLWd0VFBXckt2R25razdOMEFvc0F1emhYVzIwZkY3OXc3Z2xJblJfTXo4SFZyekdPZDlHTDc5Ykp5VVlpaU9MblVhUlBhcW9Ta3h6SWpIeFZGOGs0bWh6NmNWT09yN3pjc0pzdXdqYlBjN25UajdLT3VvZEdNRlhxazh5ZWc?oc=5", "source": "Business Standard", "published": "2026-09-28 04:42", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOXdSQ1g3eFlqb0loV211WW1MSkhiWVlTNzBWd0M2a0ZFQUduVlI2bXk2eDBmYnBIZWlFeDRrbTh4TnNsM0hBSllPZTBHOTU2ZVZaQXhZOUFDczM2ZU1wdkZteFEyTXA1SFhGR1F5dGpDY3JGd0JyOEpnZEdmdWUzd3Fwczg0SzJyQ2tWaWxNSEJYSU5kdHpJbzlYQlAwWnd6bzBGaGpIS3Z3V3hlaVBWOU55X2Fyb3FLUE9DQ1pQcVlka1HSAcsBQVVfeXFMUGxERGozWEJnZFBKVXdKSTNKNUV1N2V0ODJPUEljV281NkFXYlpnWmtINFFlaUtfUDZwcUg5RHc5VlpRT3p3TlhzOHFKNkNIVXpfZi1SbXlTQV8xa25LU2FpTXJxNkRVNDJhQVRkWVFFaXFxQW1FcWVqUE1waDJKZDI1WDMtd05IQTlzdE9xNFFpdVRIRmJ3WGR5aS1Wb1Y5WWpMUTZmcWtqdnU1YnNPTUpTOHlvcmlPMkE0Ylp4Ql9idDVGcUxTZHRibnM?oc=5", "source": "NDTV", "published": "2026-09-28 04:41", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxQQl9VUVpCdDlvWEZ4OXE5V1pabEo4U0RPcVlBRXJuMVBQMzlWQ3Jidkxzc2drSUZPcEhOdG1jRmpqRXE3TDVIdEY5T3hCVXV4Ung2X19yRU1OcE8xUU1FZUwzR3ZTOVBCYWNvc1p1U0x3WF9kazVjV3h5Tk9PbElFSzN1V25BN0xDcU83cGZ1QVRTN2kwZWxjZW9VeFFZZTctcG5PWDdhbERNdzI4ZlZlLWJLYVdxUHZOQUJDWUc0MkbSAcABQVVfeXFMUEJfVVFaQnQ5b1hGeDlxOVdaWmxKOFNET3FZQUVybjFQUDM5VkNyYnZMc3Nna0lGT3BITnRtY0ZqakVxN0w1SHRGOU94QlV1eFJ4Nl9fckVNTnBPMVFNRWVMM0d2UzlQQmFjb3NadVNMd1hfZGs1Y1d4eU5PT2xJRUszdVduQTdMQ3FPN3BmdUFUUzdpMGVsY2VvVXhRWWU3LXBuT1g3YWxETXcyOGZWZS1iS2FXcVB2TkFCQ1lHNDJG?oc=5", "source": "newsdrum.in", "published": "2026-09-28 04:29", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb2JZRzNjNjBpV29mRkZobTRsNWJaVExQeWMxZmw0WjYzZnhCNktBQm5Hdmw0U3NrVGlrYm9abFZwRlZvendEZldPMlNlVGtqVFZ0ZC1rclZGci1yb3BjbVJ1YUlta1VYM3pBMl9kbXh1VjA4ZmtURl85S0Z4OTR0cDFyWXdkU1FiZ1JVdEZ4eVBPSUtJMk9RMnFJQUpxdjRiNmNHQzdmbnRwbGNjZUFJZkVXYV9yc3p3SlF2TDFkWk8tT3hnNkZPc1JTb3c1dkZ0MS12S09LWE9vaWV0SUhOOVpGUmRrZkJxbW9XQdIB8gFBVV95cUxNVVJKdDl3emc1ZEJXb2ROY3hadnZaaXlhZEtTZmZ1RjZFNFE1VVdJTnNxVFJFRWRlaTZaUGl3ckg2dzRfY2ZXTWxvS0dWVV9ibktOOGlsWjVmVDQ4YUN3aVlLaXA1anJ6YmdNRUM4UzRrZTJxWkE5UERZbmZJR2ZHQ3phMlg2bldoWDhBT2U4bVY4SnF2c1JiQkVHdXVVSGMwTVFJVG1GckhxdURSdkpMdUpfSUNQOWo5VjNxS3FEeGRNVzZiX0UzUVozR3JXMHduVzF0S2xnMVdhYVFaNEJmOHZvZGhfbkNmY2lMYlU2Y19wdw?oc=5", "source": "Livemint", "published": "2026-09-28 04:25", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?", "link": "https://news.google.com/rss/articles/CBMi7gFBVV95cUxNNDl1aHc2VHYtR3lHdGJnY2oxdXpXX0tNN29FU0dnYnZTX1hrRWFzOFBzSk5KTWc1RTFJOFdmT3VVMEFmOXNDcXhKbHdBMVUtR0kzclhZVDRLSDRHcnljSTF6UG40ak5SQmMtN2lzRG9QSkRNUzFidmRkSnc2aHRLanVnTURTNU9DcUZXU21kWVhoVUlacHhSa2lYT2tPMUJ6NUxkWjJ1V0xpYndCQU11S2djSjZ4aXpHdHpXRTZpRDlnZFZNNk9PU1hycldaa2w5Ylg1Ull2SXU2SlIwbDVrdG1RZUJaN1JpVjRUT0Jn0gHzAUFVX3lxTFBtcU5GS1BLNVRSQ1BWekxLUmhQaFFhMlZLV3RIcjk3M0RBVkpwU19mcmNLZ3I3UXQxdFY0WHBIMmw3SUtkeTdwN1RFa3RfbzB6bkNGSzJwZWtZN2dDS3E0a04zZEFid2pXVm9xejFDbUpLeG9hWGlfQ2p4NWZtakVWUmxLMEdteDBkVFFLLTlGWHVid2ZNYmh1cHdsS2R6UjFFUzlQNXdUX3VqSlRKY014bU1mcGlxZ2VGbGtxZWlDbHRZTnVZcm55NE5zaE1ra0lUVjlTNTZaQjhQbEJLOV9yWkxSSWwxZ2FacHBnaV85SzhfWQ?oc=5", "source": "India Today", "published": "2026-09-28 04:17", "score": -0.511, "label": "Negative"}, {"symbol": "MARKET", "title": "Mkt crash wipes off \u20b97.4 trn; Sensex down 1,180 pts intraday: 5 key factors", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNFNEZXdXeWxyUDZNNkJvYmhvM29nZ05JbUhkLWRmZ2VWME9TMFQyTWctZjhoeWVNQ3dGZ21NcmV2THVjUmt1TTBwTWNJTmVnRFVzVXlCekNMZnBqUDY5M3RWSWpQeVBYTXl4Zm1ndjhBcmZUV2ZVdHQ3VUFxQzN5c3NON3N3Zjh3UjZYSjR2VER1OXBWMkZOUExnTHF6OVBtTWxCM09ZVHhmdW9DZDZ2U2FxVEtGVHhIVlNsLWhkcnByMmdVaGl1OTFwQW5GZnZ1OVJvM9IB2gFBVV95cUxNWUItS2dqMFByNUlUcXdPMUdQSHZxX3VTYU1PcEdaWnFaOUo1MnhrQWQ4MTBmaWM2eDY5WURsaFpId1RnLVFJRTdadERxTDVKc0J0UkkwRDM4V0g2WDMtclZ4eEtxY3NCVTV5SV9tQnhEZUR2aHJ4N1Q3VzFLbF9Rb1ZadHN5Vk9tOEE3THlxQVViN0tfZnB1bl9aQU0xRjFZc1dqS3RKVWpLUVM3UkV4aUYzOVNaMDlBbEM3bS0ydnltemJ4TEFOZWt4OHNOcnNNdG5DaE5GVVRHUQ?oc=5", "source": "Business Standard", "published": "2026-09-28 04:11", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l", "link": "https://news.google.com/rss/articles/CBMilgJBVV95cUxQZi1NX0ZnR1pnWl9lLURWQW9uazJudU5adU43UVVWdG9BV1A5WTZaN2RPZ3NSWHl5bTlCZlA4ODkzcDRoc3JWVEtyRk1NbGx4MDQ5X3NGZ2ZHVW9MWnFTV0F4U3ZSWVA5S3BtbzdtZFRLT2JVOXJjZjUtNENidWtZai1JaTJPc0VQVE9mdDE2VGhBNXByZnZ3ZEtVdm5ZRkFvUXd4UGdfZjJTcFFRcHkwcmo3d0p0Vy0yZXNkV3RXV3ZFcTRLTlBUNGRrNXNGMGVpUXFKMDJzUndJWXpqWnpGSkFIRVJ4Q0MzQUJVOHMwT0Z6X3R3aHZ0YzU3TmN1RDZVQmNzWWNZbkF1YVJ3YlV2Tndac1N3Z9IBmwJBVV95cUxQcExWMGJPZG5EOW5QWXdrOGFGVWpSNnA2bjNYYnlRbGdhSG13ei1YYXExbjZPZlkweGtvRDJ4QmtZcFNJbmthU2xJNWxnV3hVYjh4SDRzU2k1cTQwcG9BS0VCOTlQcUpuS3FzREFhbXRIWVVYQVZRZEdHSE9HUVRWYTAtUFFWX2M1RmZXVXhKUzd5RmtuWjBhTi1wSXZfVXBWWHRCOTV3VGFRQ1NKeXQ1WU54dlBQZmpteFlFa3JrYlRkYnRoUWJsMVJZM1RlMnFWVVZGRmNUWExEUzZJUHRCcGpmMl8xU0Y3QmRBMTdESW85NTA3LVRGODFGakpiY2lIUlV2bVJLMWhaUVNqRl9HMmhsSEU0VFNGa3lR?oc=5", "source": "economictimes.com", "published": "2026-09-28 04:08", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi-gFBVV95cUxNd3FFLUl4RkRuRktMczNpNmU5VmotaWdaUENGMWExNHZJOERsVFNMQ2ZiX0tDSGFXYXhxSjVUM2p4QWUzZThrTkxDNXR6ZndFMXU2NEFTNG90Wm1JVnZpNDdaRU1vSnJOUno4VGN6dDhndTdDWDhhbGVjQ25nSDBWOXFGa2xUWlEtRDQ0dVNCZ0I2TWdQcmlZWkxLcllVUXBpa1NpdjItdDBhZlNLYUU5bWhwREZoSWV2dEMxMWJMNUZza0FpQ2dKM0JSdU9fajZEdmQzOXFnZUxqd09wcW9qd1V0alZ1TGtFYWs5d1k4eGc2NVZvbXFONkNB0gH_AUFVX3lxTE5yLU5FWTlXQmdqRWY5MS1MYXRPVHV3bjNkZWlEa25SVC1INTV0QjQzOXBxVzhFbEUxME1WbU9jbTZISE1fa19JS1dwRW9KOVplQ1A4QkNWWlE2YjM5NlBCNndyN2F4T2VfVmlOVnhEQzMtSENPZ2N2clVGNTdtVnQ4SU1idWI3eThwenZWRUZ4NzNwaHJvTllHUlBpYnQ4SEEtZFlRTmJuT3dGU2ZpRTdMLUFraWlfNjl5UWFZLTBlX2VMSTdXdWV6cXNOaGFzRU5QSjBOcHBPT081Z2R1d1JWQUt5TXFieXRCbGFLcGRkWVI4OG9oRk1YQXJuQmdrRQ?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 04:07", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 \u2014 Five Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNWmNXeUhrY0hPcXlaYnhxdEpqRTBKbWJadHhpVGFOX21Oc1FnTVM1UDNDOWZ3dU1jd2RjNTA5VTV1SnJHM1YyNC02dGlZYnhzeDZramF1NGpBTm0xcV9DS2ZIVURQSjlrT0M2bTJfY19qc0VmRHRBdWdZdXBmcC1pUHQzSzF4OThzSzFDV2sxbVVUQnBCWjhoemhmSEhyc01oeWJJeGlSbXlaX0xiUl9qXzdBaWhHSUt3eUdKMTh3djNuZlg3dVlqYUNjMkhpX0RoazhISVpBTnJFbmFVVGtZaFlKdGY3Rzd2SkxUTtIB9AFBVV95cUxOLV9xeHRCVnRiX1FUSENXSHZ3S3NqQkRRZFA4MzZPYkd6WENNM0NZQVpMU0FQUUJnWkVROVNSbTFrMkdJaHltbkUwTExjby0wVzViS0NkSVI1NDNORG5wNkFtSXBwMlRNbXhQbllkYnE3cGpVeVF2a1RrQTJqNG5oSnVsS2pyc0dUVEtlNnM3eHJ3bmJwbXBxZC1FSG1MbnRENzNmUFluMzJwMlJzelA3M3R5Y2V6SXZreFpGYTlZWXlITE5xS0NMdDZ3M244U0NUdWQ0R1N0TWE1bEJLM0hJYzlmYWJjcWJUUHhMVUZDZlJpMExI?oc=5", "source": "NDTV Profit", "published": "2026-09-28 03:58", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxNdFJQdUVBNmhGOF9naWYwc1VCWWozTGVwOWl1b082TGI2bmppQVQ5dmxfUWo0RGhBQ29IU29vaUJ1cDZCNEJoelpMc2g0eGhldHVGdy1WeWcxVEtZcDBDNDlfRkxNZnRFMURFLUVfY1U2UG1YTk1vampZZUozYjEzU3JGbDRWNkhhVU5qVy1qcVlhdWxFa2YzX19vSjZ4NEl0dk1reVhEMXlPb1RTTzdkNENIS2RraEdzTTlBXzFteWpPMkpkUk9MdEJqaG91ZTlUSll2UEVwcjNoM0FDdFJQVUJCM0JLQTZzS0xTVkNJQ3VIYUVyV2czYWxBLXRUNzlPUkwtTHFTNUs0cGE3VWdj0gGUAkFVX3lxTE55LTJyNkZRSldBTGdKNnM1THNXOEtPQ3FZaXdOWmhNMEVtby05Y0xaZV9QSlFuNDg3TFlfZlNpb1Z1eTI1S1ZaZDJVeGwxcktWMW9pbWxRZk83ZE1scnkxWGlVOGhDQUJJNWtnTS1MWV9BcDdKRmYybmZSVEJydVdzS1dTVGdvM0c0R09GdUEzd3Zfb3pmMXdSMGUwTk5uZ0xTTlRmV2NZWTV1M0FjWmlQZ1k3aW0wZE52QmlpeTI4bzFHTEtnbjRRZWtzb1NrTnE5dU1XX1ZQV2cxazdKZlRCNmZ6UkNSaVNnVGZVZVV4R21xZ2ZfOVBzcGZ2N3l2RkI3aGpqNnNJWjdTNnFwYnNQNEt0bw?oc=5", "source": "The Times of India", "published": "2026-09-28 03:54", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxNZ0dpRTVlRDlxc1RtOW81dTVmTTREN3MwakViZzNUakNFTDJkWkt2QkstemktQmhGZHBFWjRZYXhHcVZDcU83WWpLeXpBUDZyVzBINUVFalBwaDZ4YUhwOEdXN1E4TmVTX1ExY1U2MV83T25QZFhsa1NVcDRlWmtYSHlXdWFMTEIwcVdoS2tRWWZ6V2NIVFZMMHloczRjb0JvNHhmamx0SDEzZUxtLUJDeVgtWTNTWm50SktyR01HV0d1cXI2MmU1UWNseGFDRTVLbGx6b196aE5BMzJYV2lLYkEtZW9fcTRONVHSAe8BQVVfeXFMTVh3alpWbmYySWstWjFjN3NmVG5Sb1kyV0ZjSkYtc3MxN19pMDA3VkJwRGh0Z1FYZEU4X3BTVWkwRjlLdGQzTW9DMm5Nb05oel9SdVZrYmxRT2VIZk1nblpwMUZlWDR5ZlVnY25oU3BwaHVybk5ibEt1VXk5dS00QlBqV2ZLY01WWXN2TWNvWnc3YzRfNXBTVTJtR0w4MHRlNHBWbmcwS2tpWEkyRnlvRFFHSUtsdXdZZ010MVFsSXBEcEwyNTlNM3daV2l3Q2s2ZGVERFJNNGg5NE1iZzNJRnloY3FVYU1BRWUyaWNsRlE?oc=5", "source": "Hindustan Times", "published": "202</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>6-09-28 03:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQU1VkYW85T1l4Mzh4SDJFZDBhZC1GczBiSUw3TmdJYUxvTW1TRXpUd3BTOVZwY1FzODlGUkxyNFlXSklFNzBRWUZ4WEpGdUZDWWRIZ21vM05wMHBnQ2N3UTk1VENDZTVYeHJsSEIwUG15RmpnRi0yOUdBaFRTdFg4Rkp6LXBSbzVmQjRQU0V1NXdCdVRmby13QXZqb2Zzb25Fd0FsR18yZW0yZlZBd1VibQ?oc=5", "source": "hdfcsky.com", "published": "2026-09-28 03:28", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxNQmUtcnhXbVNOQ0lacFk2Z1JXa0JON1VtZTRsYnZVMDlKdjh0dXhobk9tajVtRVdUbE5RV2MxUy1MbUpkNkc4UXNvalZoZXltbUNScGEyanBReERmbTRuQnB2d2M2dkU3NkJ0anMybXdHWV9QWElRVG9WcDhNSzE4eTV4VWs4WWluaGpYR1NZZTNuYVFPNWZwUk1YcXNOR0NrN0REb2V5eENFRjFaTVNpeWtJdw?oc=5", "source": "Reuters", "published": "2026-09-28 02:19", "score": -0.542, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices \u2014 Five Key Factors For Sensex, Nifty 50 On September 28", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQYTlhOERzdTdrb3FJNkRCaFpyd3p3dGE0QjFQNW5ndE9qQ0VTM3gwOURRS3hlYkxQOXh5UnUzYlVfMmxYZmtkcHVpZUpZZnhsNy05RWRKWi1FdHR2ZWVIa2F3MmxBTjBCeC1rNDBQQzhSYkVKSGdyV2pxa21xcnd3dk82Z2JOU3FMV3pKNzcyQjFreUdPZDlaNWh5WGVLUE1OSzV1VE9Qc3k1el9pOFdKYzBKVEMyRmZRMU9icTFpZTdQOFB5UEFCLXEybjl4MFFJam9tMFV4aXV5cjQ5bWR1Mnh3SUdXYzhtVUk5VU1uQWlMTHFwdlhr0gH_AUFVX3lxTE9yT1pHVWp1N19wOTVOLWdVWEloQV9BS0lKeDhwaWcwTGNqSnpxUVFIRkg3Y05tRUc4MUNDOF9CVm1EZjYzdnlsX0UwVkRDaEVKQ1ZNcVJteXhQQnpjR2JsMGh0QkhNcmt2eUxOdlRxTjVaMlFZWGtVSkU3Z2xfU1BLNjRrYzZ5eFE2V202Y2RKaVV4LXdqb2FNZHVDYlM5WmFyNWVSWnRKVDNab2h5VUhBaDlmbUVJWFNiOU9qYUNrVTJybWpyZkY3OHBiRUl0MTNBRjBNQ0lfYjljbkFCUE5oS3hDaEVILXd1TDNDRFVaOVR0enZ3VzBZZkJzQktabw?oc=5", "source": "NDTV Profit", "published": "2026-09-28 01:58", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOd3lLLTBUWlJpdVVESnptNXpwZnVmVk5zbTU4LWV3eTZyT1R0MzRfVFpFYzltdWhnSTI5Uko3M2dpSzY0NGJwZzFfbzZXM0ZOcV96T2hHaWQxR284Vi10dHRxeUVCQUJrV1lCclJZREI0NlpSdHp4Q0R2V1paVFlVWllhWkVCQWdaTlhiUjN4bENkS25yU0tJczFLVE9vUE1rY2hvc1FTSl9QZ1RkX1Q5ZVNfLUx2LWpmN2lQQ1pNMDNUS3NJenhycjRsNUNjbnZRMFNZNllsUU9WeU1xTk43NUY3OThtVFJadFJUSWhuNnZEMUh4VGdicDdNdFI5QkV4U20wY9IBigJBVV95cUxNVE84MHlqVDk1czZmeWtPckg1UUh1bF9OQU44MFlsSkdUeU14X2xZYXozODFYb0JtaGMwSDFVNzRpczZZb0MtY29aYTBsdl9fRFgzQkhhNG5Id2hYcE55WjhMYUU5N1hWRjg1RjJ6NGpuVmIyaURHQnI5d1RsVUxxRWZ2M0Q4NjlLQ1ZENVdyLWtSUkNrZG9MbVBwTnVENFc1UndfTzhlby1NdktITDZBbldMMlZua0xGbnVRTUFucy1GYVRaZUpPbEN4VlhTTGFlbElpVXBiZnNPeWpqQzVjbHhwYnFXUHBzWUM5WU1UVmh4ajlKbHpDRHdBR1F1bWNhNEhfZk1DNGRWZw?oc=5", "source": "Livemint", "published": "2026-09-28 01:20", "score": 0.842, "label": "Positive"}, {"symbol": "E2E", "title": "Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxORnluOHJzdFp4bmJaUl9hdWY5Ql9WeFd4cnF2ZnVZdkRIbGpTWlRzSlBxX1lBb3VEcFVTclJjQ0lVVkFKcGZTUFhLVDlDVkJkZDRnY3VQQkdlWFFOS2M1VVNNa1B1dmpueVBIRFNyRGhKVmRpd0IyV3NmTHNrdTZpZ3BKN3lSMjFnbGNyYnFtelZWWXgxWF9KYW5WSkoyQnA1R0dqTHBscWRHVVg2eDhveGtabHVVUjNoNTJCYjlsbGh4Mjk5cjgySUcwano1THJpbUY0X0swTG1POTA4a0ZSOEZFMVFJakg4RjI4aENIaVdZWWpSNWU5QnVDYkJyeTZlMXc?oc=5", "source": "Equitymaster", "published": "2026-09-28 00:30", "score": 0.557, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxQNmdxX3hPMzJrejF0R0pvaUNBbDFacW44MXRuLXZ1bF9yVnlwTXFwWGlOZUh0U19XOTJhYkZ1cHJ6VkJSMkk0QVAzcENpdkNJWVRWMDhkYXJ0NUdxRjVnaVhiS2VPWExCMWdaQlBmVzQ4a0lhNlNjNnV5Nk9xcV9zOWMyc24wTFdBY3lCbFdQdXlsaWFNdnVxblZYWVhBcm5wQW11NzdmV01JeVBsQV93eXJuU0ZaTmM?oc=5", "source": "scanx.trade", "published": "2026-09-27 17:20", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Ahead of Market: 10 things that will decide stock market action on Monday", "link": "https://news.google.com/rss/articles/CBMi3wFBVV95cUxOOHlGS3FhbzhQTUM5VG9rOXZjZXBTZ2Q2X1VJWjVOZXVEM1hET3BtSktCcmlhLXpIX3JUeWtBWlRNX1l4dWk0aGJiNFRuRVlzaDhfVUpzeF9jNzNUT0VpcFVSZWlGNkR5Mm5qeEU4ODR1RUpZcldoc2t3TkFweE8xLTF2YTROOGpkZ3lkWGRFQkpaY0xTRFB1akhkbG01QjZ1eXVBWlpjZHdnMGR2a0ZNODZuQWZ2cThKTG5nb3V1WUxxS3BCRHllVkhKM1hQTWVpQzd2WFU2b2x5TEdYcG5N0gHkAUFVX3lxTE9uUFVOSFVOazh5cm5jb1RDcVU5YzMwUjBJTV9yR1JmeHhaeTB1WmNIUS1faENuVTFJZEVxSEpheGpGcGMycjEwenhnekROSnR5OVI5V1l0TkJsTHp0V0g3MkF1TzNpMmZCUm54dXFiS3lJVWhGTkRnMklIT1pucDc1U0hrSkFoN1dkci1UM1UwVDdoNXNiZFNPWU9iUk1kSTV0RFBTTVl1UkJxc0t4OUIzcXRWWUJMbXcyZF9zZXp0c0ZEcUdBeXFKTFdxbzJWSzl6ZUFZTHI1aDZtdWFOOWhBbUQzbQ?oc=5", "source": "economictimes.com", "published": "2026-09-27 11:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show \u2014 3 reasons", "link": "https://news.google.com/rss/articles/CBMilAJBVV95cUxNekdIczJ6NEZleldrYUtRZ0pEMFlMaHFDcWdFeVVhVnJROWRBWTVFeURzYXM3NVY2eTUtZmNMOVg2VVF6eUZOZFpzcTd5S2ZqUmVJYkRaYnd2RF8xZjlDakRzUWFvaTlVb2REeWo4WUF2aTIxZUVncDVzY2o0Tmp3bVR5TmpRQmFSMDZzSTB1MFBCSWh5RmJ2b1d5QTNDdHlSN1hVcEJqUHdlOHZ3VENMVm8yWDMwV3N2M0phaDNFZzZGdE41OWVxbkdjU0tDNnFnTnM5Y2phV1pIYWN1RF9DNDhtd2JBd0I4WHRlMGFvZUtHdXNlWHJVYnN6eTFwVjVhODVsYW04ck9LRnJhb3NzTjEzVnfSAZoCQVVfeXFMUEV5VVRyZjl4LW9fV21rY0Y1SkJyYmluZTZHZlpld0cyakhLcHhKTXBNR1kwU0RET0VZeW1Ea2liT2JzSkNGenlOSzlkdVZwejU2X2FJVHFOUHZwRnM5YjRGUzJDM0VaMVlVR2M3N3FwZW83b3pBcnRwQjFTSy1UVVpDUWEwYTVDSmF0eExBWkdOQml5Zkp5aWtqU0hqNlloT2V0XzRPVml6dXV2WW5MVXlSMXZFYkQwMGNqZTBXNjBWTFVkd3pUblpDdHZ2RjlXRGlreDhvWXNnMV9KVGFySDFFNFBzUkpZUEh3OVFRVmFfSU1oU3V2bV9Pdm5hR21UWXBLYW9TUElFRExLRGdPTmJXQ2tSMjlFRV93?oc=5", "source": "Livemint", "published": "2026-09-27 09:48", "score": -0.44, "label": "Negative"}, {"symbol": "ACUTAAS", "title": "Acutaas shareholders reject ESOP scheme for subsidiary employees at AGM", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxPTUYtR2pST3JCR19XaXlmT3VmZ2JzQ0pWVWg2WC1mRDJDcjBtcmtEWU94YjZQb1hGZ0xvY2FjbmpEVVozQk9mb1M5YjVHSlJMNXNSRHVRenZXMjJUVmNQSzlhbG44SkRyaFFCT29xeDFqOFVUWUhvZjV3SHI4Snl6VngyZllRT2lGOEktdEIyZ1lRTFh3OEttcWR2SGd5N3JRaHZyZmw2Q1hQTy1tcWFjZ3ZSVUVlU3lmckFXQlp4Qm03NXVt?oc=5", "source": "scanx.trade", "published": "2026-09-27 06:44", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOT3N4b21hRzhJSXdJVzFVNWRNQ3RqT2l3aXFBN2RjN1JDX1Y2V2U5MXlDN2l1a1BGQ1hLcWktbEgwYU1UMUEtalJDYkc5RDZqX0FHdFVuMmpDVDhHdkhWSDVpMFpXLXpoa0ZTWDdGcTBxU1hJSUtIQzgwUXZvQTRPdUh6UnlXYUkxZTZHTmJFSnFQcVFSc0s4V2tGNUUwUTJVZktuRkUwY1c5eTI2NjA5VEgwMDExekhFYVhLRW4wRlduOU1wZ2JqV1F1emdiLVUwWHZwa3BmOXV3MmtLOVpzWlZOOXJ3b1MxY2pvR3VYRlFjYkxmNFdIWGFxNTJJYVVvcWhJRVVwb01UbU3SAZACQVVfeXFMUDJ0a2tkZUxvVXFoM0VZMW5YYm13NlNjNl9KY2l6X2NkS0VvMGw5eGhyWDRzU2ZsTlJmTVdTbmZ0Vzhqc1YyNGU2TWV2a0FLLU1vQmRRVktFOXhtcDRwVVVMbXZPNmo4Q0V4ZkNCU1M3TEZ3RzZwcVp6SlhoczYwY3NYNVN1c1BKSTJLYXBRbVh0bDN1ZWc4VnZNb1VZZERDOFlSXzFwNW1RX0d4LVVGRHUta0Q0cVR5dndQUGNYaTkxWFU4ZVloTzNfR01UMDJ5aVB2R0ptYjU5Q0RLRnBEZExqdEZJV1BDMHRiRTBBa19fa0djbno1blZZM1ZwUWx2VWREaHpQeS0yVFQtRFpQc2s?oc=5", "source": "Livemint", "published": "2026-09-27 04:22", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks To Own In September 2026", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWmN1VW9wZjRBZl96MHMzNnRmeS0tY28xWWZtR0hfa19FN2lyVjdtZUc0a0U3c1ZYNmZ3eTNiWFVIRElaRGV4VDFVYi1kYlN3ZjNNemNjVzFwWV9CQmxlR1B3X2kwVmphZGhMazZCVTE1a3E4clpQbU9GLVNXTWs5MjdNaldOQVBOOVpMWnNMUXA4VEtmc0drX3RWWk01aXVvd2xJS2JYeGppOElvRTFWbEJwdEJoYlBVaXFhTUNhMG14Y1FnSWROVk1qb241Sk1vOW1MWGJ3dXpuZ9IB3wFBVV95cUxPSXhqMzhnOGFvNkRfakZ0cUxHVkcycHlESmtYb2N6Vzc0MGVlSnNhLXUzOElWb1YwclgwRmY5MFhreTM0TkpzdjVjR3d1Qmd0Y1ZmRi1KM1dLeTU4QjRjOUdTNzlRNUR2b3FvaVNTbW5adHhMQk54YTR3YlRLclVfUmxKZmhRXzc4VG9PUVg4RFU5UWFOWmsyYWZHaFM4N1pxTHVLX3RVTVUwSzRtQzhCenRfa1REbS1CeXQ1Rm1GUXhvV3BxRndHZHRGVEV3VHM0S0Vidjk5bm1SSHJiVTFB?oc=5", "source": "simplywall.st", "published": "2026-09-26 22:56", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "\ud83d\udea6 Indian Markets Stuck In A Jam! But who's responsible for the traffic? \ud83e\udd14 A Bernstein note argues that India\u2019s large caps are stuck in a bygone economic era. But here's the BIG question: \ud83c\uddee\ud83c\uddf3 Is The Market\u2019s Fate Really In India\u2019s Hands? \ud83c\udf0d Or are global cues pul", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxORUdYckd5Y2pPQUg1MHZTaHlTT1ZXWTdmTGxwSWlMcE9NQm1vNE15dk9qS25VanFnTzk3c0FHTEpwaGcxXzhmekh2dUNLM2s5Zy1USHBjMHRfakhvYndNanZrV19NZVFMY1hjOHZsektLSVZoS2tTNkdzMEJTeExiS3ZVbDVRWTNWVjZ3MWVmSzhnZDVvT2d2YnEwZGJLRUp3QXhxTDVfSUc5TTdvTXIw?oc=5", "source": "linkedin.com", "published": "2026-09-26 13:51", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market News: Nifty 50 Outlook &amp; Prediction", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVJvTS1CRXVsT2ZzNUhBV0piRVV1UnZTeDVEcDJmRElmWHB5WkZsM2s5YzlYaXJuVU9vVjQ2dE5XVk93WTVVLUx2d19wRm9lc2YzWW9xX0F1YWJCTUJtMURwVzRxbC1vUlNDWEpLRUZibzdnbVdjdEJUeThfeHZLSXpwTktCQnlMM0tTNUhwWmplMHJKb2ptYmVn?oc=5", "source": "Liquide Blog", "published": "2026-09-26 12:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxPbm8wM0RSWWRXc1Bzc3daeEpaNnFwZW55Y1FBT19TQUdxYXdrZ2FJeDJGd1EwQk9BbFJTZ2xKNV9Gd1BadEFlZExtZWlxdUZEZHh1RkRIU1lMNEJVR3hkZ2VKWnNGWUVLa1Fha29hcWcyNVR6dEdydjluNGxlN1YybHFabnUzRWdzMTFSWThkNWRRX0NXQ055dWl2dXN3cGw2RUJxSHAyTTFWMnNOeXZ4S0xGQXFjRmhub1lHeVQyRUhUdEpFSGEwM2U1MEFnbExtV1JPRUVNRmV2dUNfZ1BiblROc2IzLVNPclpNRtIB-gFBVV95cUxOT2FRblV0ZG5vNUh2QTZGeldJa2FuRF8xSmRWYUQ4a1NLblFyUmtJNTRCdHB3NENTZUZhdi1Ha1g4aTV6cy1POUl0Njl3bzZNdE1ZRk43bWQwRXZvNGxncTdBaWg3cDNUMHcyRVp3d2ZKRmljNXZwQktjUTZnV3NpWldYMmNoV0ZJSjZONVJjNEQ3d2ZLWXlVREFsd1VFbFdob0xydFJ5dHpFdGIzeERrQU5kcXBubmVLd2RZODE2Skd0Yk92bFNnWG1qUjNnZWRSR2YwaWIxLU91ZHBzTlJVb0twSW5pUnYxb3E1WEJFTWdmQ0tzeVhaZjRR?oc=5", "source": "The New Indian Express", "published": "2026-09-26 09:15", "score": -0.128, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Shuts Trading Window Ahead of September-Quarter Results", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRG9haWQ2cXBQTXFHN2xLOGs5c3NtekhBM2g3ZV93blhnekIxenJUNEVyZFdYcTdwZnF4RHlrZ21Wcjh3RnFVaV9Oc01DSFd1RUIyRExqVUZHWkcteDlKWkQ1d3hEUC1OSTVGRzF4djdfMzZzR3gwd2QtSHJMZE5fU0JPQnFqanJ1TWFVd1pNTHhuczJoQWJudER1aW1pRGdHd1FQM1k0U1hVbHZwRnJyOWplYlBEUmFhRjktOHNvdGtQeXdGX190cQ?oc=5", "source": "TipRanks", "published": "2026-09-26 06:48", "score": 0.0, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQWm9DM0I5TUU2aWVIdHhCam9zXzFSUEI0RzhWaEFxWDFfbDFoeUFJUEZQbHk2OXJJdlpjeVBTVjd0RDdMSjdPMjl0eTN3NXZnRmR5bTM1Qi1KS3JsNFRrZlFCcmViSW5MTmdQdDItWTU4T3lUeFFkTEU5VHBEV2FmUjlqOWdvaDhNcGZlTk9jTjJQeVZ1Zkc4Q09fUGY4LVZiWk51d2U0ZGtxRFZ4cXpMV1V1UlJOdFN3RnZyTA?oc=5", "source": "Kalkine India", "published": "2026-09-26 06:30", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure \u0915\u0947 \u0936\u0947\u092f\u0930 \u092e\u0947\u0902 7% \u0915\u0940 \u092c\u0922\u093c\u0924; \u0915\u0902\u092a\u0928\u0940 \u0915\u094b \u092a\u093e\u0935\u0930 \u0915\u0947\u092c\u0932\u094d\u0938 \u0915\u0947 \u0932\u093f\u090f \u20b993 \u0915\u0930\u094b\u0921\u093c \u0915\u093e EPC \u0911\u0930\u094d\u0921\u0930 \u092e\u093f\u0932\u0928\u0947 \u0915\u0947 \u092c\u093e\u0926\u0964", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPVXU1bkFLVlVQVmhKWjdoVDlSNFQxTTlheVZFdGtDeEVEVzVtc3Y5Qk45R1RaOV93WlZrOXF3MzFKTlE5OGR1Xy1DcnFtUTV6YTYxYXlVMHlTWXFEbnlMaFliTC1uYTZOeVhCY2ZjQW5Qd0pzcEZWUmx5NHJHZ18tSDNHbTZrT29hbFNrWXFuQzFRTW5OQ3BMRERrUldoQUVMYmRTeTBfZEctVi1DUzF1bHphN2JnNV9lbWx3MGU5MlZRbHdZYnNrR1NHUVJVekRybmZtcWNFNGQ?oc=5", "source": "Alice Blue", "published": "2026-09-26 00:50", "score": 0.34, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxOTXpFTDNOdlg4R1lYS1FPU2VpM05pUUVGSHBvdWxqLXJ4SFpPTXZ6Q25FVjh0V1lvbnR3ODJsa1Q0ZDJlbWpRZFFiSmw2MUhwVF9lUVVyVWJTQ3lTMkJHNmtHMFNOMmwyRng2TlFUVlM0WGhOdU9KaTh4QWZ4bm81SUlqcEN0dm5FRHZVQ09UdTBIVWxZajM4alAwcjRrUURkMHFPSnNWVndUNjhjcjVUb0ROQVZJTFBCMmU1bFUyNUl5c0YzZDQ0bmVSNXB3Nm9pNUhnaW9RdEJYMU9WZkVqS3FHdGRaTnPSAewBQVVfeXFMTm9mRGRDb0NZSlU0UTM4c19nUEJhMERMSFc2ZlY4Ul96bUdPUFBlSEZQZ3c0NnFXX250RkQybjhjQkxoSVc2OGNlTnNoOWcweUdOVjlzdS1sZjZvUkM1T3FKWkxTSFczOHVHQ3pMbWlJbGxDX2Itd29DZU5iTzF1ZGlpSEk2dkNaZE0tNXA0Sms5SDdsZ3VuNjhQTGxYc0lYemowWmJzbFE2VUJjb0drM1NYNktGWTBieGFoOFJEbU05ekZtODl1UGsyM1UxbF9idTdCRlppbW05c1RYZXhVaFd3eXc0NU5PN3RGeWM?oc=5", "source": "simplywall.st", "published": "2026-09-25 14:34", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "PERSISTENT Stock Price and Chart \u2014 NSE:PERSISTENT", "link": "https://news.google.com/rss/articles/CBMiYEFVX3lxTE01VG4tR1ZHRnF6bF9CZzh6bHlySkh2MFd6bGJKUVhycUhNQkh2R2syeXEzOG9tLVpSTmNrcUEtOUVWZm45QUE1ZTB1VXFYSEc0LUI0akZJc3NQTDE5SHh0cg?oc=5", "source": "TradingView", "published": "2026-09-25 14:31", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "R R Kabel board approves proposal to acquire U M Cables\u2019 optical fibre cable business; shares rally 72% YTD", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcGpkYXl6WDhuYWFNMkVobGFYaHROYTR3R2NJcWhMcmptMEpqS09jeVBMRFNsQjkxSE9QVWVZQUVXeUFweWdVeEVTNzUycGFHMmxkekJSR2F2OFl0LV9CYUg3M0VvVnJEaUlEUFNrT2RqVkpNY21PeW53SThRUzMzSzhqYm93VkNPWjVSWUJUYnFicTdONEVQY1NwdTlqTTlSbWhxUGlZMEN5aUpyWjN5aUgxckhCampqdzhoQTYtZEpkSGljNWhhVUJoM2dqNUhSMGc?oc=5", "source": "Upstox", "published": "2026-09-25 14:04", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "India shares log longest weekly losing run since 2020 as oil prices bite", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRDlIOXFjNzhyRGVteU5DNTJCdVlRNUZEY3VObFdZNDI1MDU2SUo0NEM1N1JDTHpDMTk0YU9OM2V1eXRla1VaanBsTTlUM1lWR3VYU0g1eG5pM21hNzFWQTdabWphemRRMlc1U09MdWxVRVNLUWxjd3pIODVuY2UtcFE0dEhPTUM2MU1pbHNOQ1NnOUQtME1TTDJjSzJzOGljZTRmN0NBZ2Q0S1VodGZaSXFxZU1VTGNnanc3a0o0anM?oc=5", "source": "Reuters", "published": "2026-09-25 12:52", "score": -0.382, "label": "Negative"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxQbV84TnZBcDlZcGRjQ2YxN1Z3eC1lNHdhNTN1ZENIRnZsR21zVVQyQUFmNnpKbmQ1VWl6SEpGNi1XX01ZcXZuM09QZklRNUh3YTZwd1RJNDRpM01BRUJfS0VJSXRGVy12UllLVU5jZnd4UWMyQjlkZHJPRGsxX2RQZnY2c3RRRE0?oc=5", "source": "Univest", "published": "2026-09-25 12:22", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "RR Kabel enters optical fibre cable segment with \u20b977 crore U M Cables acquisition", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVHNrRVg1VDRadktqWU9TVnUtdlV0UGx2YVN1Wk9maFBKZkl6NXN1dEhmSGxFNVVaejRWQy05czFfT2twSjJxX1lDR2x5QTZycklWVWJBTDNGZ2lWYWFGYUN2dHUtRnEwUGxsVmw5UmhRandzdHdDUHZMUGZNbnhsUVdmbWJ5VTZ1NnlDdTM4UVJJNWlDU3QxRDJfeUZyMWF1Rl9fWmUyWmdyUHZpVXNRT0lkVjVUaHZpX25Na0RVa1lHRFh1ZFlQOUlhVUFJbmVLamVsdHZHVkt6bWJrRXY5UdIB5gFBVV95cUxONTd5ZUl2WG5FUzRqVGsyNGNWcHpEN0ItSkJvV2wweHhrVENsb1NFa3ppbm92bUFGdERMZWlva1YyMEl0dDYxcXg3clQwZ0xKRk1OY0c0cjZOYWFmamVwdnNsTm51TTIwV2lhNnFNX1pfS29Od0xQZXpWNWdFd1k5Y1Fmc2ZKRWJtRGlJUDdBM3NUS0RSMWJtdDlVaGM0NzVuZFZvTktxelNrd29GOFo2SjU5ZU1HR2VWUHZaUTBVa0l3TjZVOGZaWDZUTzRTSW52VnIyNThJb3p6b3lPU3RualRINlVGZw?oc=5", "source": "CNBC TV18", "published": "2026-09-25 11:42", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPbUR3cDZZTmx0T0FjVGdkU0ZOV21PRUFzdFNkR1FaT2hqcFQyZkVxS0ZKSVEydXF6OGlMbnUtakExc2NhTGI0WkE3NXVYYlpnR1NBV2l5SUxWUFhXX0VtemF1WG1pdUU3TnoyLVJCb3ZxM2ZrdjUzRW1wZFJ3M01WQmtaYnFWbUZxR1NGQ2Fwd2dJRTM1QndDMnlobXFVbjAtUnVscXUyZUtyMVZIaEdmSE9MQlFSTkpkYXhvQlBicjJTRjJ6V2VIRnM4RFNCSDNWVmFudGZNTQ?oc=5", "source": "Equitymaster", "published": "2026-09-25 11:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets bounce back on value buying; Sensex rises 315 pts", "link": "https://news.google.com/rss/articles/CBMimAFBVV95cUxNTXctaFR6eWUybzRBdVZHa1BueHV2ckVGVnJOQ1VKbnI1UXdLYXBocHhualBwZ1ZWOGVmTnkxelBSZFFUQnNRUG9BeWtsb1F4Z09tOElYb0FLclA2MmVDM3U1dldiUEd3MFlGQk0zTkZVV3JyUm1Iejd6dm15M0hBVGllcDhjUVFPUy1GUW80cERRbGU0TVdDaQ?oc=5", "source": "DD India", "published": "2026-09-25 11:01", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rebound on Value Buying After Sharp Losses", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSjR4N2QtaTVfdUc1bkpKY0JWcFZ6RzdlM21SN2M0eXNfT2hQVWt1eXZxYmlmUFVBSGhRdmxTalRGYlIyV3J2M2lmZk05WUpVcDQ3bk1IeFh5aTN5Mm1nVXFZOUJCenlPRzR6VVAtaW0zcjZMQno2QTh0MklYUFhvZW1Pa1JvRDNCS2JIa3U5Qk1SMjJRTm5zZjE4NGFIVlVFOHpwVWJHTlBtaGfSAbABQVVfeXFMTzMwT3V5UkdaUUpqeTRFOHBwOXhrSFdVNjV6QXlZc1lzN1AwUzU0RFNxYl9aWGdQSS10S1d4dnRZNlhQNjZzMW1hTmhBaFoxMmFIaWNIdjdDblFCanNIUjJXMHR2SEJyUnVUb1J4X2ZoS2FVLWh4N0tnZGJ0RGc4aXpPNnQxLXFrR3J1Z3FGczZjM181U3FTbnVySUducS1VNGUyaVByUVNyanFPdHRHSVQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-25 10:48", "score": 0.318, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE5hVC1JSXRqcHpiOC1BcW9STzVMX1E1Y2FuZThSci15UVN4VVBkU0syaVFzU01NaXVDZ21QSS03M0h2N0JoZFFOV1lZVlZna1YtRzRHdi03OHRLS3B0OGdGbzRKX01uc3BVbzZwTXVmVkFoMXU5Nk04aGhYZw?oc=5", "source": "apacnewsnetwork.com", "published": "2026-09-25 10:31", "score": -0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today | Stock Market Live: Sensex rises 150 pts, Nifty eyes 23,100; realty gains, IT slips", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxNNGZNa1lkSGVudThjR01EUWh3cTNHTVVPQ0NNcGRHZ1JmSndlS25UZTZXRWs2TjBqSnE1RzZxbTRfWWJMWEtSTUsyLWFoMUVvODMzdVVVSzl3WGRNeHZQYnFfazBWT1BJbmdjcFRVb09xTFh2Qkk2eEx4RFc4MzVFX2tzQXE2ODJvUTVkeXBqWGZScVlXaGRpZkJBaUNGZU82QUlzWVZRaVkza2dDa0dZbE4zcHB0S2FyYUVxZU9mQVZZVUdk?oc=5", "source": "IndiaIPO", "published": "2026-09-25 07:19", "score": 0.44, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "AEROFLEX INDUSTRIES LTD Share Price", "link": "https://news.google.com/rss/articles/CBMib0FVX3lxTFBha0hsSGJVRlJTaUd3OGkxdXEyMk5uZzA3QWlFS2twanVvZzZoVnZUUzlpOVo2dll5Z251ajFhU05sT2lhUGViMkRtWmx1aEtDLVNCM3NyaTlGTVk3amctYk96QXJMX0VheVpVcGZfRQ?oc=5", "source": "Upstox", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Sah Polymers Share Price", "link": "https://news.google.com/rss/articles/CBMia0FVX3lxTFAxM1NrSlNad3RNSzJKUGVISVgtY1lGZ3NYN3FyNTBJb0FBYlNGQjVCSTRBWXE0c1dHR1lvemdIOFFwLUQ4czVFaGplWHRnbWR4Wkc2N1pkTUlfQ29mQkFNdU9DZkg2akQ2LVRF?oc=5", "source": "Upstox", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Laser Power &amp; Infra Ltd Share Price Today,, LASERPOWER Share Price NSE, BSE", "link": "https://news.google.com/rss/articles/CBMikAFBVV95cUxNSlFTaGgxd29JS1hnbC02QWUyVkV1azhVUTRRZk52Y1h3Z0NRYU41WDhtYTg0M256bHF6QndKQU1VekVKbXN2ZTJlTnFFTVdfejBERXJueXFzQW11MG03OHNkVGY0S0J3MUNVV2xxZmUwc2g0SUltRzdlNXBSb1FhN2ZlWVhPQ3NKci03VFNXTzY?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "Nifty Chemicals (NFTCHEMIC) Share Price", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYURIakNOVnRybktpTUJSR0ZBR1Vla0tUNHQzQmY4clE5d0o4Q1pZM3BtaGhTcjk4UWtuR2tXbmJ1S3kxOGZ4SVhYSURHRkRCN3NwUUxzaDJ0dUZZWWZ0aWhlQkZtclZ6U0hIbTNJTlpNQk9Sblp6WW1WUTVyb3ZRRHJlV1BoUUE?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.402, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "JSW Holdings Share Price Today, JSW Holdings Stock Price Live NSE/BSE Updates", "link": "https://news.google.com/rss/articles/CBMikwFBVV95cUxQSk92TjRKUnJJUXluVlZFYWMyUVQ5T0g0RjBoSm1ROGJNSGc1UWxydTBxdTc5bUtmRjlQU1ZWUFhQVTUwXzJOMF9WaGVWblItaXFkSGpoZ2tzeHV1UWc3aFRlZzUyUWxjUW5sVHNwajl6aUJKc1MwTkpxZFJmNlcyZXJGUVNhTTdYVmc1TXl1WGF6Yzg?oc=5", "source": "The Economic Times", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today", "link": "https://news.google.com/rss/articles/CBMilgFBVV95cUxOSmhSUlhBeGVjR0VmV1paYzdJdDlLd045M2hLX1dPc0NQdkJXUmR5dUNCNGNYeGxBNnlrTVNtMkQya1JiamhQQTNfbU8zdmxndzB4TWlmSndSdmpzZ3RGU0VickFfeDg2U0x0ZmFkMWtxMndNU3FkdmMyTTE3R20wdnNpdUJoN1RNdlFKbXJHNXlqMU9KUUE?oc=5", "source": "Univest", "published": "2026-09-25 06:49", "score": -0.052, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty struggle for direction as oil, US yields weigh", "link": "https://news.google.com/rss/articles/CBMiqgFBVV95cUxQX1M4MzdlZVRMVGVUTXNrRTVQcUowb0k1Z2ZvSXp1MWgyQ0xLVE5JX2twRnhYOVBXYzRvYUoyMWI1a1ZFYTZFdEZOdmxvRVZlQllfcnA5OXRrWEhRVEdyNzIzVlNwWlJzdk5GcTUtc281VFFydy1tWmhCNHotVkQ4aUF2NHFFcTdrMEpvMVczMnNGZGVPelA4Q1luc3VoSGxZTVl2MlpILW52d9IBtwFBVV95cUxQMkQwb0hQcUdlOXAydktxZVlFc2JGMmM4RVM0d2o4MWFCbHhDdnc4VUxPUW1ka3l5YVFWRDBKT2xUaGMydWdfZjZUR1VsTFlBRUVPZnpWZEo1YnZZeThmZUN5akw0ZW14Q3owYzJXaGxLVURVVXJpNEt0UmpZTUFJUnY3amNXeEpjRDMtc0NRdFJteEdqeTJyc2M1WDZWMmN3STFCV3NaQ2hGWklQRWtCSmU4aXZOdGc?oc=5", "source": "PSU Watch", "published": "2026-09-25 06:07", "score": 0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxQTE9BdERYOTF4QjNsVFdOSUVsVjdickVLMkJHYld6YmRCdm5PRGloTnh2OHk5VmRRQjJiTDMyTUZNalZMQXk5eGt2OHd6RmllbVhWbUpEQjhnOVJvbmtVU2w2aEs1cTd4WWljRTkyc2dmT01xZVRnb3k2TGlvS0lCT3NVcS1yclo1TERWQWszM2l1dzhDdnBoSUpOVTRQNW10RFd6ODFidlM5QWttRnkyX1RWaWhWS3RzWURldTM4MDctTWR3d2ZWSWh1a2FJX29lV3Z5NnkxWUhVYzRzZmw3NGI0V1Q0R1o3TTVVZUl3REw4TFBtNTdUZVA3Q1VxanRQYVF5Yk8xc0g1YkVUZm1mTzFR0gGXAkFVX3lxTE9HLTI5ZmFma1R5UUFlREE1U052c1BXWndUTkY4ZlpnQi1hVGs0MFNNTS1SZU1qeUM3cXduelRYbzM2WENOQXNDVUprdkVfYnJDbE90cE9CQXZ6bUJEZkkxdE9wbW52akpFZTZwWGtQaTFQei14d2hFLWJMT2VpOVotMloyZ0U1UFFLeWZNZ3NzYVozQ0lwbE50S2pJN0REOVpaNWZXX0ZOTFVmZWVkbDI2RFA0OFRtUFZxc2ZEeF83emxxMHN2LVk2M2tNNUpmemRCR2lXeUtwYlVPdHFzNGh6Z1RJVmV2aUgtVkFzajM3R2VtOU9qNlAwY29sN09XSDRRR0FXTF9zVV8tNkY5YVpPbVYyb01icw?oc=5", "source": "Livemint", "published": "2026-09-25 05:52", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE shares dip on day 2 of listing, brokerages back long-term growth story", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNVmN3NGUwRl9DSWI4bV9GWXNDZk5fRV83NEJWVDc3RGVNQkh5ZWktVjdJRnJZcE9aZUxUQ3dyZWZodFFiZzljZmppdTJ1R0lPNUtPTjdLSVdfUXJ6VmNyN1FWVElaV094SGFJMlNOU2drVGlFdUlPSGpld1g4VGpoa0QyS21vUTE5QWViVl9ETWtJdHpKbDNvek9wOHZnR0ZRQTNvNGdPSmVaV1BvRmMyQmtPSWZpZmFwYklWOGpkS2dKdF9DUDg0LUU1QzZDUkhLNHdNR0RRd9IB3AFBVV95cUxPdk8wd0R3RW9FSW1lamlhT2tiT0phLWRyT0R5bDhEUVU2aVRjNVZwMGo0SHlfZVotNHZoTGxCR2ctcGxWNml2UWZCZ1FGOEJZNDRFNElqSUtKY3I4NjUyR1RsTEpZbWI2YkNudU9GRXJURUFfRjZfSlh3VHpsaWJ0VEhRdGhhcHVMVjMxMkg0Q3pEMWY1N0thZm5KTnRINTNwWE54NWNUc1REZFhzN0JCZnVxc0J0RndhMFZxTUJlOFZ0XzhnLUpGWDR2Y3Ftd2dwb2hRalRKSk1lS3M0?oc=5", "source": "Business Standard", "published": "2026-09-25 05:32", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty up in Volatile Trade", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNai04S3BOYlFIQUVwRlBMNDVOcXJDSkFJOFpuM1VLU1F2eno1VF8tSEQ4Wk0tNm1yMmE2NkJaRzRoSEVxOWpLM3BNWThjV2RNQ2hfOVhlWnlFb3hiSWZUUmJuckJZZko5UmFmeERYYlV6cVc4dm02MDlhaHliQzNOOFNvX0xyNlAyQzNfcVE5bHBRNF8xcEZvem1BWkRHd25BMndENC1GOW8tS095d21abDlMRzlFVExvSkN6ZDJ0eTlTeHdhcjJEU1h2QzFIT3I5X1hMc1k3cDNRZEHSAd4BQVVfeXFMT0pjQTFkYUp0UG10Sm5OOUJoWFhHZHNHNVZha25TOTJRdlE2aVZCNlVMcUFENFktUlFHOEloRVloMnhTbnU2UTY5bmRGSUlRLWNESnRzQV9TNWRlMzlVUFJlUV9XYmFIOGE2bDhkUEtjQlRjZHNPcm92d245Z20yZUdLaE1JRXc0aFZaQnI3bzJWUEhHNDBjdHNCX1pkUlZSY0E1aXExdHhBUmp0d3pncTJ1S0F5QkktekgySEc5UnZ4R0JiTUl0Sk0wYm5DWWdGZDFxLTBLMjkybUdUNGx3?oc=5", "source": "Rediff", "published": "2026-09-25 05:09", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets turn volatile as oil prices, rising bond yields weigh on sentiments", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNR1J5T0l1VEd5Ynk2RGZKaU5NN3Flelh5V0N3NjdsNEVoZnhFemVBMy1jWk91VGxXeUowQWRwaU5HQjhvTFBMTTRscnJQbjhyXzdkekkyNl9RaEJFV3cyRlhncEU3UWxocDJVVFdCd2VKSmJMb1pDdVNBZ1o4Ulo1U053ZGNobUViSHY0YmR3V1k0OUREc0ZRX3Fnc9IBogFBVV95cUxPcnZySGFNcF9nN1dRdzY1c3NybzN6X3B5UFRrZ1E0VGxCOWlfSjA4TEoySGpaWW0wVUhWWW9VcHZJMm0zRHRyTmpVUUw4RDlxVmtGSU9EODlhUGMwMHZRcnlJV1dhX1ZyYk9KN0lVWGVITHh1MUNKWlhVU1RHNjJoTkktVTZFS0ZyR0RVMWxPME5nRTZkY2tabWUwenVYRFdidVE?oc=5", "source": "The Hindu", "published": "2026-09-25 05:04", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty volatile after early rebound as crude, bond yields weigh", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxPU0xIaVI2TF9VODd0UXkzcWxSd2duY1NvSjhhQ1RxbDBTRkVwYW1nc1phbjh6ZnZmNmthOE45SGVDNHAtLUtmQ3VQZ3hXNF9iLVV0emwxMEMxampTa2NvRmpxWlp1Yl9BVlZJNThXMDVEYlJJYzg2T1FmZ09fUXluTEo1b01PbGs0S1dBb2NiTFE4b1k0dWtkYUlZWQ?oc=5", "source": "Telangana Today", "published": "2026-09-25 04:53", "score": -0.25, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks vs ESDS: AI Cloud Business Models and Financials Compared", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxOcldJYTMtdlhKcUxFVjJnaFZLX3k3ZVdnVDZDNmpVbnNXRklrcGdaWFpUZUEweUtXU3drUC1JUWwtVjJvd1BWYXNlVDVwd2V6Szd6R0YzQnJqR1JwUTJ2dFZYVlNXelJzeDZvbDZrOXF0VmxsamdPcTR4ZjJMUXBublJIVjhDcFhyQXNlLUdDdm9LQ2ZtV3paVUxSOHFEU3pNWEJ0amRtS1NjOWdfVWtaV3FJZF9Ma2kxaDJXWGt5QTFNWUREQlFmYXZNdko4T3FVNUJvUmxETEtjTnR6Q0E?oc=5", "source": "Business Upturn", "published": "2026-09-25 04:52", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Higher; IT Stocks Drag Market", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOa1g3WWJNZVo4UW5QcW1WUUJQSlh4RDRVWmV6SWJya2I0Vkt1OEZTQjJzRDFhcHlEdF9WOXhnNnVTMnpLbkxUeFNrY0F5RmMwWWNiSDI1LXBKdTc2LVh1VmJGUHg0VldSTHh5LUtpdXFNTUxXY3RyRW5LM1dGM1lZU2NuYTkzNkdCUkMxdzBFQ1ZPcmlic2xYVnQxT0NBbHhWbXRYUWlIZjRSWUtKeVZEMFpFdTE0T2Nfc3psUnFrOVgzaEpmQmVrVW1ISWhtU0c3YzBIMVhrek9BdlFubWwtTWt4aHJkRE1qcFE?oc=5", "source": "hdfcsky.com", "published": "2026-09-25 04:45", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty open cautiously today; IT stocks bleed as crude, yields bite", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbFllQWhOdXJ4WWowSWNVOWtJSVBGcDg5dTdhNEVmdFZGV01XUVA5RWdnemZYZDQ5QVRFeTdHbE9Od0F0dmlRZDJ4cnUyWFhaYTJVbmZKbG1CaEMwSjBCYmE4NDFiVEswM1VRSFR6MV83d0ZEcVR4VjUtWjJLN1BJdlotMFBSMTRaU1BDNmJlT2NmRmZEbktoY3hTS21fMDVEU2ZWTWpEM2h3SHktalAxZ1Z3dTNCVUZPOU9kVUFQaV84Znp3VmJUcGw5YzFLOXVidUtZRXBIUHN6Qm1s0gHjAUFVX3lxTE9jRjdpM01SdnNzdlMyYlRQMGx2clFUVEFrQUFCazhqYjZ5V2hWR3JrZjNMalZlR29zTTl4ckhzQU54b0hsUGNPNnMxR1pBY0hDSEcxNTJuYnVIT2tSanBBanVzWW05TFRZdUdwdXFTaFF1TXdvR25oUjdJM3hqVF9VaE5iUEpiTDUtelNEUzJuLWI2RVgzMXp2bzlvRnNmLUtyUTkyc2FYdUpxMkhSWFFKeEZ2SkxuS1MxbFlHejBOdGs0RUF1SWJScmxOZ1ByUGY0RkwzVjBuWlFDajhkRDhPSUIw?oc=5", "source": "BusinessLine", "published": "2026-09-25 04:24", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets rebound in early trade: Sensex climbs 86 points, Nifty up 18.80 points", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxPbl95eGhLbXl1M0hLVTVZYzU1UUs4dTlwRnBHWmJhUm5OVTVZbVNTMHR2T2NNbFFKSkxJcDBCSWhCN2phdDNCb1Z2STlBS0xFWnVlMHhDZU1wN1J5NXQ4WFRLMF82czhtUk9VVi15TGpCQk1OOEdLZUxMZFk2dDluT1UwcW5pOEotQW1Ed21reVhVQjd1RUJWbFZaTmJKOHhneHJaVmkxQllqX0dXdzVZTDEyNTBpSnVNOE1XRU1CbVlPVDdoRzhOUmwyWloza0XSAdQBQVVfeXFMTmhmcjZJWkw1Q0VaZnhWYldKVVQ1UlZ1SWd0QnhkeUc1aFhaekZpdjI1WUdjelh4WjRsRUpLcDI2aFcyanc0NVhXRnktY0RIS0pCdTdZWkZwX1N2SG5kaG4xSXczMDlPbldpMGpUUU9CT2VQc2ptamxtV1haeUd3N3h5NzlzMmxveUt4VVlWMlpqTlBfZm96Tk5GV2lOYkpXVjdaUVdEbWZzR1dTaTFNMVhoSHRVWEthdFRYVTRNUE5iX28tZnhOZG1EMTFzQnBPa2xVS1Y?oc=5", "source": "Telegraph India", "published": "2026-09-25 04:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNS2ZIYlJtSTJ2R0tUd041X2M0a2gyT0hxbktRNi1YSFpNcXlUZlBwcW9FMGl0RkRoUXJpLXFSYmI1SUlJTkFBNTl0dlExYi1LWm0xX1hUVVFqVjhxWlJwd1Mwb29fX1U0VVFhRE01d3IxSTNpNkkzQWY2TkpJSVVKLWtlM1dFWkFnaEFuZ2hCT2RYWktac2dQLUVmemdKeHlMMHYwbEtfaEI2d2w0MEdYVGx4T2R1ZktDV1RWQ2ZfUFBDZGRTWVdmSF92OS1kTnFNUTBXeHlZd3ctMF9wMk9lNHRoVEJTUTVYSV9rR0FvdG5jZVIxdzBJdnNSS1VzbXll0gGGAkFVX3lxTFBZX2J6TDljZ3haMlBoSFNpQWJ3XzE1aVhVTXVUNUkyYUZLY2N5Z1VuV19hbzZNNDhsb2RlTjZWRmpObFNlVFR1RmtRcVM3bXZGODZXUnhJcC11VXVDM2pKWVNfdXRjaENBQUZiRjZwZmZ2SmRmRTE1Nmxac1I4RlVla0U0LVdlNGdKS2RxOHhfRUFTaUtlcDNLTFVjY2JyZzBSWFEwVXR1R25rMjZmRldrRldOazUwRmRjTmhpVUl6Q1ViWFo4bS1GaEpuWkhUelYyd0ZBOGdIM0Fxa0p0U29jZEpnR1NWcGx6TEl6ckt5NUNhS0lTVU1QR043dEZvbC0zNmpHNmc?oc=5", "source": "The Times of India", "published": "2026-09-25 03:51", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty opening: Will the stock market fall again today?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>, "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxQTGdOWVNXLVlYOVZOaXJ0QS1ZVGhSX3V1c0RYN0VBTjBlWUxYOVY4VFkzQm5iMFVsVU5tVG50NnlXWmV2R20wQURmZ1J4RDN0TjJsbjk1anZfcGY5cVhIRkM4R0EtanpfbExSa1I2TzBidGV2djk1NVdNamZ5VjJVbnZQUjNaSnR5OWE1dVZGTXFDbW9kV19SN1FqT2lMRm1LcnZMQnp0YTF5OU5ZZDlxd1dsYkxRbzllUFh5aFFHclVkclNzaWx1emdoUWNfVm5zZ3Y5bVJxVElMRFNiSlZfYURKOHY5YlFpaEdyUVJvVlJINGdx0gH6AUFVX3lxTE5IYXFFYmhBbUpvcUdlb3ItY3ZNQUJta0Q4blRFTXBVbjdPZGNDb0pEYnQ4OTlRa3F4elN6NUdJNVAyWjZWa2Y1RkxFVzZyQ2dTMUVpM3FwWi1aQUtEdTl0em9OdGxxQnlUSXV6ZlVVVF81S21yOGlkWUU2X2VQbFBSektTR01TMll3cnFFUTZ3NkNEbDN1QVY4OVRDQ0lMYWlnaXRibXFxWXNOd1ZNeDFIY084dUY1aTRXcXg0SXQzN1hJT0VEdmE2eGxlQUV0bTY2Mmg5aVFWUjBfVmY0N2U4MF9KZkV0XzRGUzlYM2pRYVZGRFVxOFNGREE?oc=5", "source": "India Today", "published": "2026-09-25 02:58", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty may open flat amid key headwinds", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPUTZ0WFk4RmRvMGxLQ1NEcHdMTU5ZWWI5a2V4Uld4WVNIU3FsWmJpVXJXZFJaNnVXRTd3WjBKdDMwUmtoMktHVHlSekRoT1dsTjJTZjdrbDJYM3FGa1BTdVdIaUxOZ0o0U1NWaC1fZm4xbXJsWkJzZ3c3MTBtX1VhTjZkUHY0MmZQYWtMOEFrREZhTmstUUZ0eDdfRGx0aFZGNTRPU1VIcG8yTEVjNEF5NzJnUm82Q2hVYzNncS1qOEVDV0QyWG9mbW92elNEZ2tr0gHXAUFVX3lxTE5tQlVCbVlxQndqM1Zmd2ZtZWdldjZ6WXBqWjZiVEhjLTFKamtwNXhXbG9KWXZ1bUFuN19PMzFtdlNxS1N5UzRIckttOFBINUlKWnE1SmpYWHQ3MDlIUDRkVVR2eWwyQUMzMmNVSFM0UEZvTDR6Z0NBS2E1bzZoM3dDWlBJNkp6OGo5V2FZRHBzWVZBdUNYeTFPaGxyMkxpREF6enktNGFkbWRNVWZQVDNVVGo2WVhWTzd6YXM5MVA3YzlhM2RzMVJRTDM1emRDUVdPM0xObzRv?oc=5", "source": "BusinessLine", "published": "2026-09-25 02:18", "score": 0.402, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...", "link": "https://news.google.com/rss/articles/CBMiqAJBVV95cUxOQ0Z0MUFZM2ViTTdHaHJ5akJLdkNEbEVZeFFsZ25KVmN6UTE1X2xMTmtUckhBOUdZeE5OOHY5blA4WDhVZDVJbjZCeUJVWE5meUM0aWhoY01DRnRBRHJaVURNTWg2SVRPVkJhUjVUb3dkRDVQZ1B5ZzRhS1ZyUVA1NnNXOEJqbWh0TG5EWHAxZXIzcU5nYnIzQ2xZU2RWaHR1dE5KTE1sMUpTQUthdmdLbGpjcXZvY1JsWXNzcHp0b1F3c1I3ZHpmUTdqMUpmbTV3M0JNM3AzWDZETUFsOFpURk9oQlY3UXB2Rjh6cjNobFhYOTI4MXRUN3YxVXYwaXJnTklxOGU3NXNHSjl6c3RndGt4TmluUUROMVhIZ0pWc3hia3F6blRJSNIBrgJBVV95cUxOdWNfS1N2QVhiREVSTXpDajYwUE9RM1VycGxPNmRKaHU2N3N4Y2tiX2tKSlU1NEpYR0Y5Q2xOMFFhV0VRRE83WmNDUXFvUU5LNXFITElxRmNJSEFJT3dDcGNwT3Q5UHYzaFB4NHg4NlpKUXo3bGtOV1lPRllGMXUxdC13N2RoTl85V01LU3o3Yk5Oa2hzWVZxdGoweFJySlZDVXFPY3NFcXJwV0tpdkxOZDhhRXRpU3ZhOEZCMEZ5QWlBUnczdTRuMUxCcXdwb1Vtd3JWS1Q0aUxpbzhhLXh2bmRtZ05Cc2VyVWM2YjVJTzRXd18yNndmaklMQWdsWlEtdEkybzlJRng2WndzbnJWUGF2S0RBNnE2MlRCb1FGSVktd0g2TEdPdGEwMDRYZw?oc=5", "source": "Moneycontrol.com", "published": "2026-09-25 02:06", "score": 0.178, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Bond Yields To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On September 25", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxOdVk2NWY2YmFvVWRzUDF4anpscG54WjM1SVVVVldRT244LTh1aXVWbXFCWnQyQVZnbmQycU41N3JiV3p5ZTF6VlZMSUI3NUQtR0tsVDF6cS0zdjZiQ3lCM0VhTXFoSEt4aEh2YVF2cXFxY2ZfMkVZSjhuNDZyODRGQUNYRXNpeWdEZzRjd2ZaeThvb3BxdmpBdU1jZVhNWHAyUzR0eGhtTzRHYTVkdTdvYWhRcWhldEkxV3Z2bnZ2SjhqNVYzMWR4MTcxdWc4X0FkNzdjb1VhYUFFNFNOTnVMeGFtUkF5SC1ZRG4wM1Z3VUU1SE5ucnfSAf4BQVVfeXFMTzFDRFpfdFA3RTRhanpJaFljZTc3ams4V2FOMENpZWYtUC1uSEwtYWlNODhZSnhnVXBZUEc5REwtbjFDYkFtSjd3SlBwbHgzblJDQ2pyc2F2aHdwV1NnaTlxU2plcGhYNWg4cWZiZGNObUVPOENwTFRuS0dnbHdTbVNtQTZGUXlGTnVnaEhZYW0xVHhjVnpZdk1qMlQxWFNnRHM4NENlWDFtdFhQODYyNWFRb2haeThMUWdsZk55R1g4YzBWbkFGc2xvX0Q4REwxdHBjb2VidHFmMHNKRnZDXzBrQU5oZmJ5bVFuZ2dIVmhlMGJKNHhhQmFPdlNPVlE?oc=5", "source": "NDTV Profit", "published": "2026-09-25 01:28", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for 25 Sept 2026 | GIFT Nifty, Nikkei, Taiwan cues to watch", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxNWTM0dmdrRUdfSk9FUWpVejZ1SXQ0U2NjX0VxVFlzbzllSWhmVWtZMGdLODg2RnJGNkVSUzRFdGxzQUVsaEtfVk9lZ2ZVNmdaNDV1ZjlON3hBdllybjlOSWhWRkhKUjBGMnVPazJxRFBmdFRoOUZBQkFQZnNYZHdlUlRRV0lDbzFiZHM3Z2ZTNlJ5enBpc1Z6SnpOMkRpdzNYcXFkZTR3dG5neVZyLWI0NmJVOUM4Z2xQNlFoZTR5ZXFkN19kQTRtbkRLcW92ZHBGZGtnc09Md05XT014NXJDdzVOcHNJYWFOS3ZGM2JoSURuSDNPSGdvZDh5NGVaeDhta1hlZ05ZSmtseXPSAZACQVVfeXFMTTFlTERSSENCSkhwSzdDNExXMmdvNnVpUWRZWVZNWHFXdWdLNDdTb1JiNmVIbU5OM2ZhZE1Cc0RVMExmLUJvdVUyQ0RTLW8wM0xwRDI2YnRSMjJKVVl3di1ycnM0UjNQYmZMTWRuMU0yd1hxMDdaVWQwa3R3RF9scDJ2VU1GTWZ3cWYtU29uOGl4TjVBdDlpYlA1d1FDcUhqWjU4SEU4Nnk4VV82RlFxbVNZa2tsUVVMQ2NUZUNCZUl5V2RteEc2Qno4R0o0Z1FRTXh1eC1sVTRlbXBqQXRlcXRjZ0dHTUE2SDFlRlRxQng0QXpwbEJhNWlJQV9yc3JIQTN3bEFVT2x0RzEzalpsbXo?oc=5", "source": "Livemint", "published": "2026-09-25 01:15", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks With Revenue Growth Up To 16%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-revenue-171316164.html", "source": "Simply Wall St.", "published": "2026-09-24 17:13", "score": 0.932, "label": "Positive"}, {"symbol": "RRKABEL", "title": "R R Kabel acquires U M Cables business for Rs. 77 crores", "link": "https://news.google.com/rss/articles/CBMilwFBVV95cUxPQ0I0bk94a2s1NkRCd2ZFZC1ZWmNnNE9Fdy1Pb3JpZ1dMU0xTSVpVajRIOE44eHJkbW14OEY3bUxuWkNZOVoxaWxDUXByWFlaLXVJenBveVRGYUllb0RRRnlXeHhHOHB2OGNDeWViTFJSWmhDd3VtT2JTTGpKanZ4VjJYNWZVRHM5RW1CNjE5RHltRFZiRy1j?oc=5", "source": "Business Upturn", "published": "2026-09-24 16:46", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Usha Martin announces Rs. 77 crore slump sale of U M Cables to R R Kabel", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQRm9ZQzlMNHlOVTh4ZmRiSV9obWt0a1pEblBGRkZMakE4WUU2eUxYODJ4di1hcmNsRmFSWHRVa2NkOVBIVUQzaTRjcmRRblE3bzBGcG9VaXUtV05EbGVodkxCM0lPV3QwNS05Zlhhb3hsQ1RCbFFXMjZBVXVHMHFDU19uMVBxMG0xUFlJeEtNcXJ3S2tUek9hLXFBWFBvZjNsMUM2M0t5MWwyTVAx?oc=5", "source": "Business Upturn", "published": "2026-09-24 16:31", "score": -0.494, "label": "Negative"}, {"symbol": "RRKABEL", "title": "R R Kabel acquires U M Cables business for \u20b977 crore", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxOekdBdkJnQy1zc05YRUg5aFF1a0lwT04xNl9vZlhFaUhGVE0yeENFRkdPYWp5eW5qNGJPQ1Z5M0tIQWJTMmVBZ2NIcG13ZTFtc3FJaE9hOG1SQVk2UENVdGNWTXktTE10MGNUVmpvNkxodGg4TS1KdHFlZGprNUpZMkRsS2x6OW1LcGtSVnJPQnFvNlpOaHZZbFlnSlZ0MGtEdjdSdzVvSQ?oc=5", "source": "scanx.trade", "published": "2026-09-24 16:21", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets", "link": "https://news.google.com/rss/articles/CBMi-wFBVV95cUxNNDY4RnFxUWdPN3hFd2xaaFZRMERxSGpxN2Z1ZjF1LWVVZXFDUnZlQzFhNDRUYkdVWW14NDRCdXZ2LUQ0YzZpNWVUQmxtTEtHV1UzaUw1eWtXYm53a2JYSzdFQ3Z0clktdUNZY2J2dE9MU2lxM012czJpUDR1R2ZkN2h3QXNIWGkwX3pEM0xNakt5RUt3Y3hrQTZPNW9yUVhDQnRCaUs5RHdjRVM5Z2RMTGc2cG10WS0ycnl6ejY3YWFsYkUyVzJBYVc2UXlvaVNpRkFKZkZmWkE2RzBxcWFMNElnR19nMFN6cmRzRDBteVpQMjlDVHlaVi1VONIBgAJBVV95cUxQbEJYN0g0YUZETXczaUtkbUdMb1c4M2lQaUszdUtyTXZxMVVYWENrRm10czlDRHQ0alpzSjBhRXMwVzVYUUo0djJYXzBQWlM4S3NZZXZtZTM4TS1zd3BVbEtHeExGNHVVcTI1eDN1VWZHTUQwRllLU0VTenctSGtMT09DTFpSSG00UF81R2ZsdGxFMFlGVFB5aTZLWGVvQ3RwWTVVWTV3Rjg0N1RKbTROQjdaVjR0RTRuRUVtLTFUTDgxdUVMOWVhOV81ZEhMbHlxVmh5Qk5NMXNCdXo3anhfSTY1SlNaSi1zSEtvemVYdjY4R2YteVlTRG1qX2wzQXFy?oc=5", "source": "Livemint", "published": "2026-09-24 16:04", "score": 0.7, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxORWVLSFhyVy1XclJaTW9wUmtOTF84WGZkclJHbmtIdW5oUXNJS2J2V2xqUjNnVmEzRDJJRko2Y1UzaVVuYnFOUlRyYTFzNFB1dTlvMXp0U3BTRS1rUV9pWXotZG5FX2xZVnI0eHRaWDhlLVZwaThPXzdCNW0tT2ZEMFp1b0FrRFVsNnZSVzVCTTd4MWZEUm9ERnJ5bTJNaGRIYlhYcmRGOE1ub1c0THBORGt4d2h6SnlBWUhFeVdSUDg?oc=5", "source": "scanx.trade", "published": "2026-09-24 14:42", "score": 0.382, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQnJ1UkZncDJJcTRVNElLd1ZKN1Nnd053YjRobGxJUEdGYUdWS0lvb0dHS2MtemJ3SUppQmZ2c0NERjFpa2szSjhMZG5BcGZiT3NNa191ZHEtaGRCNUYyU3FhMHBnXzFBUkk1d09ZNWFnNXJvZHR2VU5LTWkwMFlWU19xVnZkUkk2aFd1N1FBZm5xVVlEQmx6dVhDcG83MGZveUFrMm9pMWgydUlPMDFZOTB2RFBBT3JPdDRVYmdKTUtzbVBMTDFIbGlzdkhVMklTNi1aeVFHNjNBUU9RclRiSmtXVjRlakw2S2UzVlhlRTZvWWs2RFNoVG0wUkhrZw?oc=5", "source": "economictimes.com", "published": "2026-09-24 13:49", "score": -0.153, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "3 Indian Export Stocks That Could Benefit From A Weaker Rupee", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQNUp4b2tjbFlmWklUVm5zT2NJRjVXMm53bE5DNjJvb2ZFd0tFZVRUWHVxbWozaEp4aVBQMGtxZkpfQ3FmYnZtbEppcGtXZ1hYYl9seFIwdlhpczRuUWg0dE05REgyUkRMdXJpaVZDc1BORHVteE1IcHptNnNRbkdTY0NEUTZKZk04cHEwWTlNTno4MjJKU05aVlVOZExfd3plejl1cUxiVXlVbVNibjctMlFyOWx3aEZmYk5VNElFYUM4WENySTZGcmFrWURmdElfRjhyTm4xelJnYWNjVGtmb1I2NmxXZnRPem56RDZ2b24xZ9IB9wFBVV95cUxNVGN5NWZ1TnFTNUt1elFVSE5Tam8xZi0zWVY4Um1SX3UyVE5xNDZPZmpWQ2VWXzBsaW1vcnVzX1NoZXk0aWJjeU5iaXpiT1dTejAwSUt6Z3FhTThnTlhsa1ZFdHpfTG1sNjIzQ3pkZ0duUXY5N3ZqZU1qckxKVlZneVRJVmxjU1VrckJtQWlBNWRsNGdZbnRxX253TU56dE9NdXA0RlRoR0dLS0VDWFQ3VXJILUlrcF9OTU1lVk1sODFsbmVIeG1ROEFLcUlhWmswVzVkUjgwRW85cUNQUXpOcS1VZnBLT2pMSlZ1c3lGQ3MyN0JKeGlB?oc=5", "source": "simplywall.st", "published": "2026-09-24 13:01", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty slide on intense selloff, banking and financial stocks hit", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFpGdEFRNW9Ca3dPWm9LMWk5T0R5T3BvbW84R3h1b1pJeXdlTFJ2VzlCOVotdkVCbGhya0lWdFpFOG5oNVJ3Z0hoNEhfOXlwdmFCby1RU3NkbnZPVllMd0N2MWRYeDJoYnhOUUNxVXh3bFV2RXR1bEFnUlZzX3RkNnJfYUlwSWVtMXNFb2FPUWF5RWR3Y3JReUhHTmVuZW9xcTM3ck05aE9vazJkenhF?oc=5", "source": "The South First", "published": "2026-09-24 12:51", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPTmEwdzJWdUtmS1lTeHJNaEFsLUVRRTNTSU0yMko0SUJCczVmU05rb2tDckFtclNUdEJzbmN4VUw0TUY0aWwtVVlEM19wTF9BZ0xyZmw4Z0ZTam4wMmphemF0SjRoWWZTaXZOOGJES2dTWWc4MXU2djFTZFQ2ZmtnTGgtNFBvMlpVbFJUeGVCQ242RGpic3ViMFl5QmlzbE9ZMFBIQktpRXRkSWhmWVh1WWJYZjRYQ3FkcEJtOTVNUmZseW02bXQ2cDlheEVZWnItWGFrOU5aTmdDVFQ5UDJMUEI5Y2VSREJGSmRGdFY1UGY0cUJTR0FFUDNSc014endZb3U2TUN0dFdXQdIBjwJBVV95cUxPX2xOWkM1Q0VWS2w1cGpsMXpBUFVpZHZOQ05TMTBkY3BMRHUzcjVIeEdpRHBhYXhKNXUxSzRjZkI1RHpXbkRQdlpBUkdPS0JIVG5jcjQ4cGxZUnZndUIwX1VMVWlwU2c3dUZTNHR4VjZrUzg2VXd6UHFaYzdTV2xMRXQyWmFQcFdIMEJUN2pqcFliNW1tRHU2a1VNNnUwekE5ZWRTYTF6Sy1FbnBhNEQ1Zkh3Uno3QTZuTXVRcHVlNm1LVE5oVEJHLWRiMWFUeEo2ams0QU1ocjRRREF3Vkd0dXQ3ZC14cWNLNE5oM3lPMXNKelVjbmxuQjA0dURockhtcDBQS2gweGZ5NERLYVRB?oc=5", "source": "Livemint", "published": "2026-09-24 12:36", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty down over 1.6%: How crude oil, bond yields hit Indian markets", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxPY2trdk9wVkNJdnNwUEgtZlI3bHRDMDBHREVDSXNDaHNiclptS2IyWlJsSXdwNGpiSzI2UU5JdXRUVTdNdzVtNWRWX2lkbWM2QjdPYVVKY2JRWWV5VFVJdDRMRkNWYWFISWtzZW9fZFpmZ185ZEVDcTJRSWVYMXNid2JuQ2pBVnlNUm93dUxydllsUkw1Rk52a2tHM01BRV9GUEw3ZE9ycUpDakRCZExSdUtpVURfVXdPRzVxdk5TOU5jZUg1aFFfMtIBzwFBVV95cUxQMXhUTEhvMEZjRVVvWWZFS1d0OWtHdDg5TndITDAzRWpsZklndU9LenJUV3ZzUXZwWVgyUHRtdlh0NndrWEN1RFhoeU00VUtTRVRIM2NBU0hJM2hTM3QyRWlmOFNJY2diZl9uXzZ5SlNObk45blNQVWs1VVRlN0NBSjFHR2pNdnE3VlJEcUZxTHhWSTR3NnA2c2xuQnlMQlJpcWJ1dzhqWjFRMG9fdFpXU3JyZER4RE1HdGV2VzUzcTlUTXlOTWhKN0pqX2Rtazg?oc=5", "source": "The Indian Express", "published": "2026-09-24 12:02", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Signals Higher Opening After Sensex, Nifty Crash", "link": "https://news.google.com/rss/articles/CBMinwFBVV95cUxQU0I0M0hsemxwc1F3ZjFyczZ3aXlPOTFWeF84OGFtM0JHUnhwYm5ncVFDY085cVZ4QW9RbWNyRDB5UWVMOXNOUkpxLWxTRTRjd0RWV2drX3dibzRkVFh5STZNRWFxWk9XVmRFWnJWYWtialVpR205R19YZF9vR3JsSHYyMzZFcEhLTWVUenBqRG03ME1yTEpMUDhXYm1uNE0?oc=5", "source": "hdfcsky.com", "published": "2026-09-24 11:51", "score": 0.542, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex closes in red, Nifty settles below 23,100 on spike in crude oil", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxNRlVKbFBuMkxHMWVDMkdLbkxzWUwtTDdWN0hqT2xXdHBBR1dhb1Z3M3pUcThKdTBQN2kzS3NVWFF5QmUtVXozWERsQ0pnTlhpZXE3WUt3enhReWljNy1JbkR2Mm95Z3BIYk00Zk05Wlg5RUJ6elBGZ1Z3dWNDQUE3V2VBam8wYzlCOHUxdVd3MDF5dXVUcWV3MzFn?oc=5", "source": "DD News", "published": "2026-09-24 11:21", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE shares end debut at \u20b91,818, gain 1.85%; BSE slips nearly 3% amid broader market sell-off", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxQUlk1a3F2cEpoWGRTeFlUVGFkVlYwR1BZWUR1d2tXTGFldGNFMnplOEVRWnFLMWpMeHkwZnBRQmdrLWJjN3dNUU9EMHNnUWF5NlRDdVJkVVdnbkF4NHowWHNXRWtzMHNNZHh0U2dobTEyZm9FcGNKMFlyb0QtVjFYbzYtTWlVRmY3bkU2TjRWZnBQcGhsOC1uVm5RdW5NemNKclNISlM5STBJUGxEYzNrZ05FV1BPQlJIWnRrcWRBRUxiaktvVUJ3WdIB1gFBVV95cUxOT0Z5cDJfanFuWnNKN09YVjA2ZUZWU1BiWV9MSEt2MFVhVjNOMGIwaWpBdUcyZHhydjRnb1g0LVc3S1NpSzBmZ203UGRRMDk0dHZlX3hOOFktNFliaWlacU1Fa1g5ekNBY3ZfMUFFVEpmOVRjT0dzQ2JlUElHQkx5STljMVdrWFBBeXNvbmYwNHhIaW5KbkpBU2RXUUVGcjYyNlJmRFh6Yl9uNFVOdEJqNFhGbFhjd1R2ckh0aTJ2OUdtaGxqczRTc1ZvTzZrcFVPV1dTR193?oc=5", "source": "fortuneindia.com", "published": "2026-09-24 11:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "SENSEX Nifty Today: Nifty Settles at 23,063; Sensex Crashes1200 Points as Crude Oil Surges Above $105; India VIX Jumps 25%", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxQV2Z0WGwxQTlqTU9rcExhRjRqRjlyUkZPcDVjSHZRWFdUcWNqOXBiaThCSU9oZGVCWG5lblpxLWRzc3B0emFldWI3UEQwb2h5SnFJT2NFSXZ4N092aWhiYzZtTWZRYnRJWjZDa3MxWjhVTzFhNUxYLXZuUUtIMW8zblNKcXl0V2FFSm4tUVhmOHRVanJXZDNtMHY5NFZuUGEwbEtsdFA2d2p5VFBzOGNDcElwVHkyQ2htd2F4SmlOOUxOU2QzYnJZTEVMZWxaNWh5dGhJVERiNzhsUDBEUExpcW9xeWltZW4wRlloN0xtQk0?oc=5", "source": "India Infoline", "published": "2026-09-24 11:01", "score": 0.784, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see worst day in weeks: Why was market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNTTMxLVltQWc5MkFQOUFYNlpYUTlLRnVtOWFTM19ETVhBaDduYk9pa3VKY2lIdGNGTkpIbVVKaDNkV2Z1NlBvdUVVeC1JbTNJem02eHlvdHRvMFFkR285ZjlFWk1fbXR2Z29HSnNVVklmYnhpOVlHdUFxeUFuNmtXeTZFY21KcGFraFdXRVBfNWZRLUU3WEhhd0x5OGxkRlRCbXR5T21JNDRpWE8tSU81VGtxUXFqUzl5T2FrS1dXd0s2QkdoTkRlSWJFR2lORk1JOWpnWHhvanB4bEdTaS1aZG1sbTJfUDFManBUNNIB8gFBVV95cUxQaVFGYUROS1ExTmNWWWI1RHNoTGZfWDd4U0hPeGVCdzM4eUtkZXVMaGZSTXp3NDZEcS1POXpFa01KQlNtY3U5QWgtdl9VV2hZY2VzZGp2U1pQbE5sT1JoQkZJeFFqT3VMOENGMjFXM3dRajdZdTVJMVpIWVVubzJhbjNyakljV1BrTl9vVDh1Nnhnd3VqdDJBbThXVDY5ZjBIZXFKZ0ZHUkt6eF81SHJEbEF0YkJnVDQ4clNuSFJONkZRRTkwZWxLaS1QcEVwVmRqQURkTlpSTm14R2Z4bDV0NEhMMzVJdWZ1TzhaRUlweVQ0UQ?oc=5", "source": "Hindustan Times", "published": "2026-09-24 10:57", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex Crashes 1,200 Points, Nifty Falls", "link": "https://news.google.com/rss/articles/CBMiiAFBVV95cUxNS2k0X084LWJ1bW81UDRhNWZrRkRQWG4wNWZ5UDhsU3d3dUg2NTc0c21RN1F0TmVuSzYyMzBYTHBwOVdIZVJEV0Q1RTFOaWF2Qy1vczJwOER2SEZBZUNHZmF4aC0zMGJrMEhrZVhlRUQ5N1ZBVV9TV1RFYVQ0c2l4eFNidnowaEhJ?oc=5", "source": "apacnewsnetwork.com", "published": "2026-09-24 10:44", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex plunges 1,248 points, Nifty nosedives 1.64%; five factors behind market slump", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNcE5taEEyeER5bklLZHdwdW8zRDJUR1U5MVc1NkNUc1hvV3doWnpCdU0yZUVINXhHS0szVElxd0swUFJqLVR5dGJodVFSUVVzdkd2ZWx4TGhjdnZVVGlXRzc4OUN4T3cydFhUb0xXSzd3b0RMMDFYS0FYbU1zeFFtaHpWQ0xXUGFJd3U2WG9CU0QzWklrdW9tQUphdXVkSXY5ZDNzRTJJaXBQcFdCT0x1Wmo3WkN0ckVSUnIzSlBqc1jSAc4BQVVfeXFMUG94Z3FNM3BuQ1V3ZDZhTm41WGUxZE5ua1lyRHVCMVJJZ1hiSjJuY1gxZXNoaUcwMWhfSXZ3ZlhrOHpXTlFHU0VDRTl3UUJQdE0tc0NtSmoyVTlNSGhOczVLREF5ZmVUbEpwV1VWaFlWYUNCTzdvUi1OLWN1eV9EYnFpOXNaSEtiVzBTMG1XMHF2Z25HeVpFQW1PVkxmNDYyMXZZTGRWaDJ3Y1pQWUVES0dyYWFTWnAxZS1XV1ZSb1pzaUUxdEJObTFlUzBmRHc?oc=5", "source": "fortuneindia.com", "published": "2026-09-24 10:40", "score": -0.612, "label": "Negative"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNb1U1UU5HdEFtaWZCRWdVRWxUc2pRMFZ2YXl2bUpYNE1xNzZBX01tTXNtQWc5d2ZCNTdzYUZwXzU5U2VOX19rRndvYkVDaUl3aGVqQ3lyU01qYkNtVENjRG41VW9IenA4V21EcDhLYWFrdHZPYU9yNGl2RDFSUEdRcEtObWtDS0doZlo1V3ZwOGcwcmRROTcweDNZeTZaRGdQZ084YzU0amppMUZaZERQamg3YUE3RF84TjFuLWx6T28?oc=5", "source": "Kalkine India", "published": "2026-09-24 10:15", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock markets hit three-month low: Sensex drops over 1,200 points", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxQbVQtWXNPU09LRktkUUs1eTNpTlNka181V1FzZXR2eFYwT2N5UlFwMGxoS0ZMVDhxaU1GUVpSaFlxZmF2R3RGME5oczZnSGVWVGhQVjdaU3Ffdl9GZWp6NktOa2RKUXY1Y29xZjUzVUNlM19yOWx0R3dhbHF0NUpGaDR0dHhidWpiYTNzLXJmY2pOMk5SNkFTekVweGgtdkFkN09wX3dFVkhoZVUxMGtvbDFnbDNvZ9IBuwFBVV95cUxQT2h1VGV3RW1Mcmh5Z09qcThNaENiZTlLVjNhYlYybDY0c0ZKY0lRZmRsSTktRzVfczlRSGZnV25kM0FHR2w4U1p3NmtMdy1BOHhTZjFlY3dVSmRudk9vR3cxdGFWNGFxQXNRYjRhOXk1OS1GUFhqb29GS1VMNmdSMGtrTXhfQlRnY1dRQk16QlUtQTJjcFZtbk5RSkZ5Ql9XeFYyQmdIemRkQjZOQU5vQkxGRHZkVEF4ZDZj?oc=5", "source": "Telegraph India", "published": "2026-09-24 10:06", "score": -0.402, "label": "Negative"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVTh5Q2ROa0YzRWp5NS1Kamp3NnMzYnBNRlJHcEZ1cVRnOG1aampUb2pFbERqcGNPZjN2WGZqNGd5dWNDN2R3bnhXQ016bjJoUXUxN2FqcVYxaDFrSTlwZGpSQmZIbGM3THdoMUFDX1hwZXo1OHNPTjVpNFhLWVZudVFHU2xxbmZ1aUFnWXZqM09tZzZ0TVlRWUwxakpaM3JIUkg4QlBBaG40QUQzTWxYYzNSZi1uVVZtWTJHVU1UQzhDWHB5OW9Fb2JHS3ExdVR3dExkMGJRRVRQVmZfZnM1THUyOTdWbWhDaWfSAe8BQVVfeXFMTUFnaWZmYkVLMzZkNk5ZRXF1ZF82LXluT0hoSlJNZ19kUVk4VHlzLXhabENVbTd5LThnUlJIc215aVY1T2ZwOThSS0dVNnJNTVBIdjgyQlBPQjJaTF9sQnZWeEw3Z3dVdFVMNnU4ZzBWOENQQ0dtZ1JQal84UmdMS3FvdEFJUFdMbVhXQm5tM3JYNUJhYTFFRnFtX2VIaDJMcWNPUFhpaUs1YjRSbG1lWWVTYng5VnNjbFF4Z3NqVWFHWEd3eEMxUjE5YUFQZ21qdVJJV240Q3dsYTdHQUhKTjVGcnk4UWRhd3lEdTJYeGs?oc=5", "source": "simplywall.st", "published": "2026-09-24 10:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "The battle between India\u2019s stock exchanges is heating up again", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQSllxZjNuQ0l0ZExkQlp2RmVURXBuMm5WRjUyUkZsOXNaeF90Zy1GWXMyZFAzYmlGMGFfTWlhSl9lT2JNMmVnclFGYlg3bjNZQTRUeERZRkFScXBYc0IxZnhEcUF4Q0tzcWhhQTZXaXR6NjA5Y1pTSWdDQXBPQS1HZWpMOWJHN0NzN0lLWkdiMlJWWjN3OC1Ha1VDQ1ViSE9QTmZmSHBYTVpFM1FiUEJtZ1B4Y01nd2dabTlwTw?oc=5", "source": "The Economist", "published": "2026-09-24 09:42", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPVWZGNDlpWFN6MFJFZVZMVWp4RnIxcTVXOTRMUS1oVnMyQkVmZkF4eDdQTGYxOXVKV253c2dWUVZrOFpQUEEzdUQ1Rm45bG1aX01RSzVBNjNIWEFIb0lLbFJsSWJNYzFzMVFaVFpXUnAtR2xtZEZ5YXhjdXRSOHI4ZkNVMlJvWUszcWJEdGFBWmpqZG9zaGJWRnZGMHFtM0J3OWluTEZMVE9xSkV0Q29QTnJFQzEza0ZQaERRWjNBaEN6QlpkSFdMcGRuWndIWE1RVU5uczhza2w2WndRYWlUVkg3Yi10bUJFLWRWTE1sT2I1NnhwVTdCa3ZBRmxpRklNbGtzbkQ3V1licnlmakQw0gGUAkFVX3lxTE5pNjM4R2ZHalBOWTl1aGVPaWxONlMyd2lmVERYa0RZeDlDMU1IbnZMWnhNQ2VuWXY2dGRTTlFrZVFrU3RmaUJtcjZxNnlVNXc0eU4wQjR5Z29zd2FWZVRoM2FVYl9BY0xldFp3SDNjYnNSdmRwdXFYTEpxcWM5WWFrbHZCeDhZZ1c4ODE2SWJpX1RvX0dkX1VHemI3dmpJem9uWWJsNU1Ia0JFWmxobTRWMjBFdktPS0dsZGhlVjdIaVh6dFRhU0FERjk4aE15ZmlNR19BbmlCei1FRHV2TXNwV1BJaVRHQmxSZnh5dGotNDRaUEpUZV9pMmR2STRRbkhLUHhPa2FMelZzX0VfdXJMOGVoeQ?oc=5", "source": "Livemint", "published": "2026-09-24 09:40", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZ3RITnlWRlVoLVRXRW9Pc1NnU042UFB5V1BVM0s0QkFvcnRjbElBRVd1ejJZQjdSTmNfM19uazFjYnZFbm9EMmhxVU0xYWtsd1dZNldfbEFJOE45dEVDMWw4TUVwSW5LdkVfSHZPVnZsRVI4eWhyVFpaQW1mRFM0UFUzZDhXaTB6anpwWDlSSk0yWjlpZ1Z4WEsxd3M3YklFREtEbi1TNXhEUmsxYUVyWXlPTHNxUXJVYUxpbV9ENkEtNURlYnlPcU5lTnBEbjRMVGE0SXdGRTd2VWvSAeABQVVfeXFMTVVqV1N6TXB3TXJhak1kUURlODRETFpFX1NBa1RRb1oyUlVNd0xRcXBHU2ozWVN4dlQ2N1Y2WUhpdTdZQk1NWWNYcDB4U2ZneFRVblBSajlpRmlzLXZWMTNCeHdIZG44a0ZMandxanFjTW5qTHpGM05QQ1Vxbnlsck51UjJhMkloS3dPaWstcTFoS3Q2NEQyRi0zQVhITkp3NzdWRnBkWG1vaVdWSll0SGlsdXRiaUxWc2FUVk9wMW1ZZ09tRlRCa3RoQjNONFhvQmdyN25tVWhBVTBEZmpuMnQ?oc=5", "source": "CNBC TV18", "published": "2026-09-24 09:08", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tumbles 1,200 Points, Nifty Cracks Below 23,100 \u2013 Key Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxOZDg4Rlc2Wll3UERfQk54T18wVjMtRkRwQmNBdk14N01wLVprZ2JKVUFKT3ZkZFMtVGxCbVJUOWJtNXNJX21XcW1pNENSeml0X2NHODBIT01aREJpUnRfZ1hfVU81UHJub1B0VUZUS2htOVJnQnFDMW1QbVFkRU5MQ2tnaHVxcV9qN1VzOHFWM3hiVzAwN3ZYRVVoSFVOMUttVWJuUHFHbnFyLWdkU01nOWp30gG_AUFVX3lxTE1SMGlha1duSXRtSDdZTmRfc3B6TVNsVHhOM245YktBZkdvNHdPWDJNUUpYQ2F5VFB6azB3YkdMSk1tMUppSlAtbllwQzdWWGNBSHcwSEpJc3QwNFlrMFZuLXhoZnMwSU00NzZrSnhYc3pqNG9WcDN1ck1CWG9ad1FXVU1tcm05dUNjVExQQ25oU1AwRDRUaWJ2dmNQT1R0eFBPTFNlUWR5NUVjX2xaa3paXzN5cUpsQVFkb1BLZHZF?oc=5", "source": "Outlook Money", "published": "2026-09-24 09:04", "score": -0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxNeEtEbWlBNTFIcHJzRV9zU0hnQUd4MVRma2VMWXpOdDl3SURrMGJPOXBnVnFOTm1MLVpMMFAzYUhUWDJVYnpYd1cyWG1xUjhxOVdkb0tVNkF2VnZfZktsRnRYTlNjMzBYblcyM0pHRUo4Ul8xVlFoci1JOXpSU2F2RlBkbFJaZGhTeE9yODV4aDlnSDdKbjd2c0ZKMzc0Y2JFbER0c2hDNW1pbURITlcw0gG3AUFVX3lxTE8xbVZoQm0xdm9CSmg5ZVBDMVluS0lTTUctTnpYYVU2S0RxcFhlaUY5Qndta09tY3VuZWI3MW1LRWlPNVl6QlY4OVBFcENPZEY4OU9jMThxdzM1cG56U1ZtN29HNGEtZmZ6eklRSXlNNERlUVF0dXNjVXV0dERKeFpyeHY4YUV3ZXdWYWhjcWsxM1d4TWtYOE1tUjRFQ0xKQm5aWHJhcnJfSHFha1FDeUJpSDdJaWhrNA?oc=5", "source": "NDTV", "published": "2026-09-24 09:02", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxNT1lNOEhqOHFBM0dUS21nbjEzUDVTOVY0YnkweVp1T1pQdy0zTG9LUmppQkhYTGtIZXBSTEtiVHdDNjZxWm5FM1VXYUl5Mk9WcklBS1p0NWlKY1FUWDNqUnlYcDRrTzI2dms1NVNjenlmQkJZdlIyQllHaEF5VVU5OWE1OFgzeE5jaVdSR0ZfNklZOGpsMGRyc3NXcEdsdFVGRl80QXRsZUhkSDVWbXN0TlRKNjJXSkRSc05IQnczMlpyYXJwYnV3NERXY3BQRjdJN0h6REx4LVo3S1dLQjNRQlpNOU9zX0RLaUlxNXUzRzFmTEdGakNJTHotX2cwX0hyb3lMVEZmR0PSAY4CQVVfeXFMTWdFZHhRbFpBMnQtazZaZUpQVk9Ramd2ajI4M296WDFaazhGZG1OV1RmeGRqcDJkeTNsWC1TYXNTbWtJa1RGRktmREpwbkpqNFYzUlFIYkR3ODg3RllZQTNWZ2h1ZzBLUlU0WXpYV2ZlQnN5WE9pN2JCV2sxbEZMdjcwQXcxRGE2c0lLSWdLVHJVYTRuX2gyYnV6MFlPZDhMUmpzVHpUUWk4WmJYNWtsMnRZSTdmNzBzdnhGRzNRUnN4aTdrakZ5QlJ0aHJsaGRGQlk5NFllakp1bHByRFpMbU05S2tqWFExY3lQYkVlUjlyX3hTUXpmRFQtVmdocWFJMG1aQ29LTHNvb200Rlh3?oc=5", "source": "The Times of India", "published": "2026-09-24 08:52", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 3.93 Lakh Crore As Sensex, Nifty Hit Three-Month Low", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxQNjFHX2Q3c08xMDdGUlpra0RVekh4Zy0waWJXT2cxdDIwOG1TYmJnSjAzMy1tVHowODJaQ2VRZTcxWmg3bjhLa3hrRHBEMktIc3VmNmFWSkVvLUhoM041UkM3WlNpV0NfM3pqT25YVzlvZjZDcE1FY2IxeXpscDBJVWVuUzNobzFPMktQbVFqdVhQdXlwY19DbUpnbUFweUFsZzdfZmxZemUyTUlZSkNLekJfT21oMW8yNjhuMzlTM1BLQ3RsWDlyWmxrQVlxc2stSTFSaG1DRU_SAeABQVVfeXFMTmlwcURVb0RtR0lWNC1MT1pvbUdtUDNMd3hHM25oUUpvNmNWcmdxNEpLR3VMYnVRU1dkSDg4ajN2a3NJMFppWVdkZ1R1LW1SVWxYa0ZWUnZkb05NeGNoZHZ4cFpVWmpwNGlLaWxxM2tFQnpvRXhaMWxIb0VkR2QxWjdTUkNOQTBqVG50Y0Nqb25ycWNTVEgyQkRHeG9hUkpPTUdPTjNLTWtiV2VlNFA5RUpWWllaY1dldUNWeGUxSmx1Y19Mbk1CeHhRNHpUYmZjaTlhR2VrS1RsbnZJS09pNDU?oc=5", "source": "NDTV Profit", "published": "2026-09-24 08:50", "score": -0.758, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "Hero Motors Ltd leads gainers in 'B' group", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQSDJtZTVDOFZES0ZIb3BKUnlmdkV5VTlSc2doTWJUZ1k3WEhzVDNxd0doUHI2aFBOUG9FRW1hbUw2bTBKb3FxYlNxZS1kM2VvaWtpcnp4ZEJpa1AxQ04yN3QySVkwS1dUZ3YzVUo3UVlIdzV2eE41ZUdJOWs4cTMtS2ZQNWdySzltWE5CVVFQZTZLdVZCaHVxTDVYTkJKLTE4ZWQ2SlpuVVAxNFFSVVJKYzlhT1FxMnYxZ0dKUDUwNNIBxAFBVV95cUxQS1NzWTc3QXZDVEZ2M1JsYlh1RFVzUjdVdHVWdVFrcWMyRS1zdVRJajBxXzdvSnVzWlZCQXRNbDJyenM5SDJwUnRMcW5BR3ZCMnlKbUY0dTdiVXZMalpuT1lsOHJoaFZtYkhkY2lIbVVXOVJ2MkRoRE1pa21xNU1LWUtYOGpEaVE4VFhqdElqLXVRZ1Q5SHNLVGJfN2VPNUtLT2F1ZnhMUU1hMjNXSTh1dzVZS1d2VE1fQ25BcmZEcVhTVGxf?oc=5", "source": "Business Standard", "published": "2026-09-24 08:46", "score": 0.557, "label": "Positive"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems Share Price today: decline and analysis", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxQcUhUNEJMQ3ZXeU5ZcFk0aUE1NndmWmVMR2E0MVJuM2RhTi1QRHhxT1lZRTZKeXp3NEkwak4yQ1RPVDBDRDlXUlJVUXQ1QjVIMURYTEtsZ2lXVW52SmR2VzZRS3FHanh2RklUTlNTWElScmtkaTdGMGx0SWIxdlF0YjlzVTZzQQ?oc=5", "source": "Univest", "published": "2026-09-24 08:35", "score": -0.382, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNYTRVYTVWR1lSdF95cG9QR1FLMk9SOTlCWVg0NzdVR21OeTdQQXJYc2UxbkUxa2I2blpPOVRYSmVCcWNaQnVxSnpvX0RGQnhZdmp6X1JXRGxXaVk0dXZnRDV0ZTJmdFNMTzUySWNXUjZ0OWN6Y2hwcHY2cWRxLS1hZVRpdHpISHpjMnl6b0s1M1J1bHR6LWNTd1otbHEzM0ZRV2RHeUNEdmY3X2t6ZnF3YkNyRHREUDA?oc=5", "source": "scanx.trade", "published": "2026-09-24 08:21", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices", "link": "https://news.google.com/rss/articles/CBMi6wFBVV95cUxNcnpYS1l4a05TYTZaQUM2enZTYmIxVThMMmd0UzZaSEczczdQSXhEU0tSSV9DdXFXdXE3SUNBem5BRV9BMUFlZF80U24xWHh1ZHM1SkRjU1p2a2NvM2NuRjdMQUswaWJkZUV6dVp1ZzVrZC1jZUdkX09JaWRSNWFOcEdOc1JFUVNRcEdfVXdYMVF4MHpnTl9zRDhLQWY2NVllQzkyMXN1Y0YzQzdSUTFoUC1nanVwcEhzNnc1NDNtbVZOSFhDVVpUM0F0ZG1VemZSZkF3eU5FSldzSEFLZGRBell3ZVA2Y01JWVhv0gHwAUFVX3lxTE1XVE1JUmZXOUd6YURZeGlua2c3dEZoZ3NQdWY4SnB2RFVOa0dnd012UlV5Mm16QmE1c1c1SHppQ2luZHZqU3lfb2llTkxTQmN3MUlpejNJOVVYb3BCaUQxZ1RSWEZBWWFwdjVlN2ZTZWVyTGZhdjVfWkNtUG50SkNhS3hNRFlFbHBhMG5DMjZXS1FGVWJnMmUtVzJueHhRa1IxdnZpaGVuU3ZJYmhUVXFGUWFNVW52ZGxYODBxWFVzMmRnNl9PMW53dGJ0Qi1EZmRaUGhzc0FLZWxnejdscjFjRDdUM0UtRWNpa1d5bm5JOA?oc=5", "source": "theweek.in", "published": "2026-09-24 07:35", "score": 0.077, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom \u2014 Ask Profit", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxPcjBhRnpQaFhkbGdfV3E0ZHlmUjFPQUlUQm9LTFU4UnFqSHduWnhNSEcwenhUQmM5LUxsdFNwUXN1S3gxZW9PN213QUx2TDhzUWpoNXJldnBQRmI4eTBIOE9JMGdqd3I3T2F1QVVYcVZSUF9jOEt6cnB3QWhmZ3F3Z202eHZkRXM4NHduSVVzLThxbTQ0aUJEeEJlTThhWHBFMkJ2OGJ5X0FXT3ZyWFR3MGlZeWEzWjJGU0hhejlZTFgxakpDdVVtbkV2VGJtOXU3aTh4Z0lPdmtneU5EQTNudGd30gHqAUFVX3lxTE5SeDJuQlhJbTcxaDUzbWNPNjNuZDFqLTNYYmEwR0o1QW43WVdkLW9FQUhpVExqaFluQjJwYWRVcG5NcE1ELTduTUxUVTJzQjhvVlN5YWJKa1AxaEFjYnIxempBeUNFbG1IeW94YVMwanoxOHAzNHlRSnFUbWJ3anJqQWVvb2xQeVRwZl9CQUwyUl9KSXhhTm16Qy00Uk5JdkhGU2Z5SGRzNkthQmRBN0J5WnE5bFNUREhuNC02SklqM01odWNqWjV1YTVsVUhXUUZMdlhkN09kWTdvbHhZUjFXV05sVTlGQkptQQ?oc=5", "source": "NDTV Profit", "published": "2026-09-24 07:25", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE Share Price Rises 3.45%: IFCI, New India Assurance, GIC Re in Focus After NSE IPO Listing", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxONVA1bWxGeWxFRDVpLUdnQzdZcTczTFdyQ0VNeWFZc1dUNzZTME81V0VYb3Q4eTc5a3I2MjE4aTNUSU93SWdIU1pXaHF2R2xZcjdoMDd5UEkxNnlZa2R0TlQwdkltYjY0VmhIT2xSa0xpcXp5bXhnbWJzcmZEUjJOMTQ1b3JYdmMzX1p4bEs1WlNGci1OTmY2czBMaGhmem1hVTRxcVJvd3EwU2tJY0F3c0ZscU9wTGZrdWZJN2FnQjNMc1I0eTAtSDZCbXBvNVk?oc=5", "source": "India Infoline", "published": "2026-09-24 06:33", "score": 0.34, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxOU0F5bUI3X2RaNWllcFpuSUpqZFp4Ui0xRVNpb2FSbVRfMjZieWxhWGV5R2N5MHpqeHBQcXIzT2dfTHBjZUt4Zk5aV2Y2SDNhM3VjamJBeTRhUjNjVklyZ3lWZDMxZ3hMMjNXaHFHWUFKV19ZaEp1WTBQekRXOU5ZdXc5UG1hQkIxRTJWdU9USDZqekc5QTh5VENqRW1ybVVCYUMwODlQRGJGVUZKV28tSVpXMFQ?oc=5", "source": "Kalkine India", "published": "2026-09-24 06:20", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Tomorrow: NSE, BSE Open on September 25", "link": "https://news.google.com/rss/articles/CBMikgFBVV95cUxQV1U2SUpTNjJGRW15cXVTOV8xLU5RUmRPRWtLWDJjQ0pSR2pLNkhXV1RGbE02MzNtZXRRVUo4c1ZjY1VrYy1xUXNEc1k5UGNIQlpxc2JsRVo0bHdmUmVfbEpyVTR3MHZneTBvYnlMX1dpandOWWs4bG1QMlhuOVBCT2d5dnVnVlJXU3ptYUVwQ2FKZw?oc=5", "source": "hdfcsky.com", "published": "2026-09-24 05:58", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty in Red; BSE tanked over 600 points", "link": "https://news.google.com/rss/articles/CBMizgFBVV95cUxQUk5oc0h1QzJkYXEwczVTMGwyc0labGN3T3RaY2Z1Sl84Y2xMbS1KQmxiYlFtWGpwTlNSM3ZMcUhCby1GaTNlc0RxTUNMeUJNT1ZIX2xUbnZGQTBUN1ctLW83RWhaZy1UY3JkWWJIb3d6WnNHTEVHZHZqcTUtRHZCWXZWcmtPV2xUMWVSM3hvamktNUxpY3FtU0RyUEE4bHpNcVlVdHJiSThtMzFfbnRFandGR2hvOTBrR3VscTU3clkzVHF5ZmFCRGF3el91d9IB0AFBVV95cUxNb3JKYVNUNnVBWmhCN285VmZjSXdYN2hwbDUx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ZnB4UmI0X3dWNzhLd1BCT01UY3FuaWNyR3FfaU5ITzZONkYtVDV5bFBORGtMTnFBLS1qWXRoUnhKWXNnOHUtUlRjUU1XZk5rd1RJWm0zR3p5dE0zOE8tdHloRm5lR1I3Z1pTenBTcTRvbExuLV8zajljWnd5TWpBdjNKY0ZiV09aQkRmRTZKRnNaNDk2NENidlVPZDdFd0VpTGVUa1pkdnlGWmtySXp1OGxNRWhN?oc=5", "source": "Rediff", "published": "2026-09-24 05:29", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex opens in red, Nifty below 23,300 points", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxONWRLMGNIYkVlWTZiZDZSeDY2ZGpFdjJZWVRaNGlkLXc2M3A2eHRmODhwLUFvZkVBS3NRQUJzNlIxQ1BkbjdtZTFWYV8wQ0JVdUdIcEVaeDR6STlfOVlqYXVwOVZPQkdhZUM3SnZ2dVhVLVlzeEhNQmhjcVpPNkM0OA?oc=5", "source": "DD India", "published": "2026-09-24 04:55", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex crashed over 1,200 points: Why stock market fell today?", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxQXzVxaEFRS2NOd2NZVUNtWHNQaTgwaVc1bGJhLTZVWVZFTjREMnJhVXllcllTYlZKTWM3TmVudWo3MXVfcnpTazhIX2RZWWZ5YjJ3XzMxNnZkemlkMjduaEExRXVRWjY3M2ZSNmo0c3BhRmZsSW82ampNRVBpVkJ3YWtvWVFSM0pPcl9tTGlKVDF0dUhNYmgzN2MtWTFGWHBpV1liRHFZVEYwdURaNkFiNnBaUHNoVW5aTjhOVG82Qm9tQXhIV2VqN0RWT2gyYW1yb0xEdEFpdG4ya0tFOVVtSTQ0aWdYQkQyS1liNWJOelMzdFXSAfgBQVVfeXFMTUFQcXZjUk93LXBGOGZqOHlmcXFNR2RoSkdCc2F2bVdPM0hGQ2lqQy04bG50MzZWY0JoUU1uRFFlME92NjFueGpyNFpBREFKTC1pMzZ1eGJlSWF5dGNjVXlFZ21JS0NjZmYtNWUzVG02ajRXbi1nWWtwSktpU3VxektCa3BpbTI2Sk9fZUFKbUIzYkM1V0tScExKMmgxM0l1SmhUTkpMYXVIMlZ2R1I2TkJ5emtlQ3BNXzBfWTRERkNLRW5tYWxnNjdqV29GUldwMExmU3pGaVJ5LWNaZHpnQ2Fsa2p3dE03QTZCU1c3Zkt1QzNLSWlyUk8?oc=5", "source": "India Today", "published": "2026-09-24 04:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "NSE vs BSE: Which exchange should now be the preferred bet for investors?", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSmpuTmdJXzZWT09uMUdJbE9vWlhudHJoOTluUlhlaFV4S0FnMExmQnNlSlp5b3hteTlQN09Td3hDRG9rUDVEaDNNNmFjcUxBVlZCUEpOdmtQNVU0blB5bnN0VFo3MHkwVjItQ0c3c3FIekxwd0N3R0xkU29WMFBfZzRkUE1KRWViTnU2TjItSlMxQ0hJVmFPdG5VYmVGUTFBQjJoY1A5MWxZS0N4MUdTemxmR3lfR0pfQmVuQ1ZCTi16T3h5ckVZS0dLU1VPeDlsN1BNZdIB2gFBVV95cUxNbEV4bVZySUQzYW9GWmJ4UzJQTE9NMU5zTGhnX3g2TU5tc3FiV1VkUEpTenZpblZfdFFOOWhNbFpzYU9yRTgwUGQ1LXFUSFZIR2VTYTZHVzVJWE91UGppYTJpSTZ0bV9jNW5iWjl5OUVxOTQybGlQREloMVdERXpnMDk1U1hCU3lxNG84bEY2V1N3M0MxNDJnMEd2YlJHNmJMbWxUcXRHMmg1N0tjVGthTGdmWFZ3Ykg0UE1TWXkwZmpjUXpyVFdxZ0YzWWREMWU4S1JSTWp6TnJUdw?oc=5", "source": "Business Standard", "published": "2026-09-24 04:31", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian Stocks Slide At Open As Nifty, Sensex Extend Market Weakness", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxOdFpaMjRkMHFmQl80MDZYRWhpSFRCbGtlcGRYbEZHV3ZmaTI2LXJoTHdGcVgwWVg1dWZXTUFaX3dFbUl5ZDlRVjl6QmNvOXAxeXM1Vk83UnpseUQ2Y01IdnhCeF9RZEV4bkV6LTB5N0VnVURTVUQtQkF0QnoyZEQ4djZ3VXZXREcxNzdvdi1JMGVMdXlfb3MzYWdSOW1qbUtlQ205NHBzWmdqWmJ2bmxxZF9WUmp1cXFHVlNoSWtNMA?oc=5", "source": "Investing.com India", "published": "2026-09-24 04:12", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'", "link": "https://news.google.com/rss/articles/CBMimwJBVV95cUxNblY5UUJKckZ0My1hbEZrdS1NbjFpR0Vyam1YUHcxd1BSMDdzWkpVZzVyN0ptcnZWZ0EwRElGTEdLV1pWNFd3a05HeEpBOC1UN0NCandyUjlzUVpsUXpKZElQajdHYUoyc2dvLXdMVkNQSW5lZHNFVG1aMzVJQ0tUcENOcmR3QWIyUFNWOFo1RENRX29SbEZLVmNGdVdjSVdkYVZyM1l6dUNtaE9KYjk1VmhIVTlWUlVZNUVFekwwRGZETkw1NTFzbWhSX2xVc2RTdzdCRExjMW5LZ05EbFZRODJvcXRnbmpKZGdPRGlpeGgza1BVNFA1V0xkR2ZJUEpCNWpPZnh5aXR2MW5aQ1EzTEJBdGY5Mi1UTkZF0gGgAkFVX3lxTE9GWEM2U2ttbzdkc05MdlJqN2tFU2pGUmxYbmVIeHktdHRhWVpuaWRnUE1RN01WREtsT2x1cTBBbExxTi1sRE93d3FvWDljRGJzWHNxMW9jek9KTklxUEdnbUk1a0t0YXdlMVZvbzc4Mnh0c3hUUXMzdV9VOWV3UXdqSnRQZFJNaVNRZ1RybmpKR19rS2dNdm5HVkNlUmRUTzJrbkRuYy1fR3pRLTFLUDBZcVAxMjRrdXg5ZVF2M2NDMjgwTXZ4bktqUXNidVU1dmJKWXEzUi1NLUwxUjliSG1vU2lQeWM2S1lRdkMxbW1qSGI4M1lpSHRVS1FVXzNja3B5Q3BYalFYLXV0T3d6VXlWVVdEWTdfUVRsWFV0RlVkdg?oc=5", "source": "economictimes.com", "published": "2026-09-24 04:09", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash: Nifty 50, Sensex fall 1% as crude tops $102; financial, insurance stocks slide on IRDAI proposal", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxOSkVkb0huSFhlbmNhN0psN1BPWVZOVThiUzlnRkx3RHZPc2plTl9CNDY3WDJoQUlNUUJ4Z0xXMHE3aU1Xb3k4Z1FUanJId3VYazRKZ3U5X1MzS0dUYTRlUXdTRDk3eWNiVUcyU2ttbXMzQ0JMSXYwZUFYMlBrQUZrRjNFT0V3enlTcVEzeGlGX3RORXVJTHdfUFhxQzdiYm5KWVJSdFp3Y3ZNSXhyTmZyekRESHdkc25NdkRybmpvVm1oRTdBWk9jdzRIVGlGdUNRZVNTMjhjQkliUE1zbklBMldjRVJ0a3QzN3hObHYtUXd6X3htQWozdWh1cE1DYVpvUDZBUnJvc3ltNnRC0gGSAkFVX3lxTFBPeHBSMFNDSEJ1UEVjaHNKbGlyd0lkY3c5cVYwT0M2OGFqREFwaEllMjFtanlXZG9iRFp2SnVOc0F1eXhka2tDek4xdXVQYWdsTGlQSjlsazJHcFVyZXN0eU9RVktPd1VhRXhGakFja3Q5amp5WUh3R2cyT3k5djdvU2pGRWk0Mk1FVVZPbTdIT0ZGcGdnR2hXbWdUaVEzdEU3bnZoMVpuQlVrUWIyQjBnMTZqMW1pTldyWDdPLWxYem4xbW1aeWNiTk9hTDRXMlVlLUM2cy1WOUVJTERGeU9zU0ZJa01oeHgzZklKSGRRcVZEbUlHZ1dIQjhkOUFNNjdIaW5fSk55eWd0bEdKX3Z5WFE?oc=5", "source": "Livemint", "published": "2026-09-24 04:02", "score": -0.599, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxNNmFnZnk5VzNtcVFkY1JFVlVCMFh6T3BlejFod0JXRWFjMng2alROdHU2YzRmcEVCV3VMZFdYM3hCbUFCa09PVmVkWTh1MWFaaUxhTndsdjlVb3pZZy1VZU1wWFl6WnNvUzUyZ243ZUQ2RUVIMEhVbm8tMWxWMzM0Y1N6aVlPenNvZkl5R0hmVG5JWlE2QkcxNlRDd0UwU2RSN3NscF9PR2NRVGVaRWYyVUpMeHFrYWNVcGdMNTM3MmpSVGdkc0laX1E5U2U4Q0pBM1N2cUNlQndvUGRvUHVhT2w3Qkh0UHZ4dkcwVTQwUkRMMHlY0gH6AUFVX3lxTE5jREhsTGtRRUVDMnRQMEhucHBndU15SnViUmVFb0ZxTUE1dmpUSlBMV01WYkZ6UXd4QkRncTdNZUh5VVRxNEQ1cmViQ2Z6WFViOVktS1hld09jM25FTHRYN0lJa3d2Q1NsWUxZR2VqUElmYXVFVk5wczFqMy13QUd4Ty1ER181WE5KaHE5SEhFdHZzTy15T0tnZ3pyZzhVMktvLUI2WDF2M3hTRThxVzZEeDRaU21jYUd4ZzZPbHlWRFVMN1lZVGRzcHd4bDUwTWc5d09MYks4c21iYlZKNUUyaC1GOXIzZ1ZzT3dXTWVaWm9KdVhHYzN4emc?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 03:56", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPRFR1dnlza0cxUU5PbXRVYmRRT19oaHZFS3NmTDZUdHhDUVpIaTJDVDFHYThvSXE3RzNWenBDSUlDUDVCdE51VkpDaXppUEl2M1htMGxsMkxPV3ZaS2d3YVhYVTlFUEphWm45cWVuYTZLYmJ2V0xwT2dtMFkwQXZ5bjVWOVh2UHczVnZUSFQ5NFBrUkJaQTJwRXFoSlY5ajhXaHJXOVd3enFaclR4QUpXODFjMWxjVVE?oc=5", "source": "Reuters", "published": "2026-09-24 02:46", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPUXhSRW9fbndZUTd4Q3FFZjhsaThCbS1jNzk4Z1N2TUdiU0lpcHNQcEZ0WmpqdGZHUUlIUUhNdlNseThhQ0hkVDVNazBSQTV1SmRVNTJ6SnUyVTBEQ3pfWTBubFpaREdzcjI0VTFacmFUZzI4ajJfZXZLcU0yQ05NcG9BN1ZkYWQ4M3pJVkFmRllNRXJXeU8zWXRMRkVoQ2o5aGJOamlGaXlfYll4WDBEdGdpY21SN1o4UENfRGNSZ1E5elpxVjJ1aGVWZ1BnZGpfUFMwM0VYM0t4eHpnM3BTTlBKaFZoQkFTT3M2bWhSNlExcEZkcmRUUHZMVmNzSzlPc2fSAYcCQVVfeXFMTnBRN0FXeEh4U2V5eEYydmZXb19IdldaZk5tYU8zbVV2TFV5ZjgxOGg5cGZfdHVScXprR3dCeEQ4czVEOF9zSWpoM3MzdWVrNFphaTdJZWg3SHVac0VnOVc0Si04cUdma2xrRFRLRlJSakp5N1FobmtwdUNqRVRFNWxsYnJrbVpjRHI2RTI5dmJ0Qml3eVBLa2NTXzNhUHZzckNXVHJxVGs1clVveXhUYlk1MjdQOTE3SDZTelVJb1JpSF9wWkpjMno4X0lDdkt2TzFIVE0zVEVRaUFxNG5IVFRhTGRwVURPZlBOcTZtUmlNTTJYS0gxU2RWTkh4T2RZOHB3SFQ4RHc?oc=5", "source": "Livemint", "published": "2026-09-24 02:44", "score": 0.758, "label": "Positive"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxOT0tVTzVLRFhsRHJ6QVB0WV85ZGh4RHFXTEdKY1R3Snp4T1VIcXVyQmNMOGpKeDF2aVdfckZKRGVqMzVpaDlTMDU0Q0lVemMzLUxFblYwQkIxcFFvalhLYng4bVdZbUhqTnFDSDFweU93akx6V3ViVXF5cEtCbk9QSFJQTjNobXRLQUpPTGNuSlc3UkVfNGdnQ0hWbXJldU11M3hadi1FU1o5azNRZ3pIUldvMkV3b1FQYVktMldOcWZkVFhPcHI2QUdMOXQxOEY1aGN6TG13WW1yMjlQWHNYd0p5LTFkRGZqOHhHNlJIcW9pWU1VQ1k0Yy01VDRPQdIBgwJBVV95cUxOdVk4MlI1LWY0aGw5azFlQ3UtdkF1V2lVYjJBaC1UYUtRNi1FT1lTeWpTbG1jZ2dPeGtBVnFYcTdISXFqaUxJcnpuZ29EWml0UkJEN0VfeHRONWRtcGo5dG9ZTDhOWGlvemZrUWZHRWtxUVBwcFRaRno4UmpWSDIwdHh6Si1LbFFDS1E3R3hvTTRGSFA4T256enl3RjBfb1hWNEFaTEkyOHJNRXBMVng1YnJMd01TMW51ZGhta1dRRmNnc3p4TC0xa2lsMDVOQ3VoZFZzUzRGV2IzYTVzajR1Mm11ZXZ6NkNfNjJjSG5iOVNmSkVXaWozaDNwaHVTNS1MNjRF?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 02:38", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields \u2014 Five Key Factors For Sensex, Nifty 50 On Sept 24", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxNMHRUa21iWVZtelA2Um13ZTJ6ZDhOSGNJMlcyandCLUFTT0w0V3R5eWd5SEdCZ1pyOEMwSlY3ak42dHRhUjdnREc5UzdaNmI3QnFkd2RsLUk0SmhaRGNqOS1QdWp0ZVdnOExERTduSHhXZlpFb2ZHaHVneDFmaGdpVTAwa3I4RWxTT3NxUHp5ekV2YTlVd3ltNS1FLTdKN19nUzBFaHB2a1Etd0xVb0NMVDJMaG5RcGlDMDhhLUJqOWFoTmFEdXFCbDZ0SlAwTmlheHZuWEZ5dGJJdW1LQ2dGeTVtNS15Z0tmR1B2YXZ0eDR6YlFBUFRIUlRVLTZ2ZTjSAYcCQVVfeXFMTVJoelZ4TXkyUmNUWkk2RThDUWRtT1RrS0dqQUtzTHJTM1RZX0w5ZHl3b0xicjN6Z1IxS2dQUV94YWdwRGpyME1rZmVaZnZ6SGE1bW5sUlM3N2ZBYl9lajJub1AwcjJLYUc1d3pHUG5HLWUtc1VFVlc3Z0FVNXI1anMwNzA5MkZvd1YzdTRUNHpRZTBBSWpqcm05bUp0ZmxNZklyNU9LS0l0NG9uSWZCRkhYenIzaktxa3Bic25SYzVfVVdPcko2ZG95YWhraURGZ212MDJBVHBCVWxXUWVQVzZZLTFIZmVGdkdsNHF3aTNOclNEMUEtSjNsUHFCZU5JSlA5bE1aZGs?oc=5", "source": "NDTV Profit", "published": "2026-09-24 01:42", "score": 0.844, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQTDl3ZlJyNW5xZXBBLUtBLXRfSU5kbEdSOXFWM3V2RU51eVdlanIzclZnczhweGRBR1lmWkVUNWI0SlBsbW5tWmd4SzBzNXA0Ty15d21DNVJkQ0piMXpzMDYxYkNndEtmV19UQnV6NVBKZlgzU1ltZEpEakJ5dVl3WU8xQS1DRVQxN0pxV1NuU19RaGZhTWNqSHFhRHFGUVROWDhEMkxhODZ2bmZFX1piMDl0ZzVJSVRhUU5KUC1pV0NCclR5dGxXXzR1VUNvbHMweU1xaHRIQWNIRG5HN1o4NWNlRlBlRjhRVFc2SElTNklUNEtMSXBZVmQ1YkxBOFg2eWtOOFZiMUTSAY4CQVVfeXFMTUdPNHFyRDVseGxVX1p5RDdOWFBabmJQdm1ZNmVZOVB0RGZMeERCSnFfZUMxV3FrMXBJT1liYmFZekEzWGR4cUs4eDlKOUhiNURta2xDLTM0dUFkRTJrOHNaa0djNnlJWFpQcE43OGt0SkFJNEgxSm9hd0puemtzNVgyX3dHdUtGa1VIRHJBdFllRUFmYlYwQ3Y4elV1djY2ZUo5R204dmZyZ3RwaGdZSHZrbERxQWZfRlhCUEhrZjdaelZGLXZmY2lTWm84ek9wWHYzdGRKQVFOR3pYWU94RUVERlBYOXFEeDJaUVI1and2N1hCenc4anc0NVVaRG50TF9Pa1o2di0xc3k3SDdn?oc=5", "source": "Livemint", "published": "2026-09-24 01:17", "score": 0.842, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs stock gains 1.37 percent as profit jumps 126 percent", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRGZMMkVQZFBodEJ4cHVqbng0YWJyNHJjbndja3pLdkJzamNORjlNUGNab3A1MDczV2piSTRpUG5yeklwV2ZvMWlFMGp2OVota2lsTHJoZlB6dG10UlBHeXRYNTk5NlRLVVduSzZJM0dLdFlTN2hkM29mWnhNU3lHVUlaTmlGQ25fUFo0dXhGT2cyNWlhQmllc3hiRFU3Z1RIN01VV0xHOFBTMUtoWUQxTDZUY2J0VTNxRXYyb2xhQ3c?oc=5", "source": "AD HOC NEWS", "published": "2026-09-23 22:57", "score": 0.791, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUE9BMFBTZkQ0bmQwWjZyUG4tSWp1VU1ERG50V2ptaVRoamFQX21HUDNBVmdwOG81TjVLeU1GSUZoNGIzUU5Vc0drSzhsMlZkOFl4MmstUEMyZWdYTTNING9fVnZrR0ZvS3VCYmJaVEk5aFdJRUJNWTZMMlV5Sy1iaU5ieC05WjZtaFJaQmMyaU5jTW9Oc1pmZHFsaUl3aVJ6TUJTR0s3SjYtdnE4c0NDejFJOFprT0Z0Zm1RTGFsTFlFVTVvUHo3d0lpZk16R1NmVGczYlUzZGNXb0Mwd3RQUmxKR0pRcklfUl9XRVNyMEZBZ1Fxa2FsSWtGSllrV2QwSmRSVnBOMmQ?oc=5", "source": "economictimes.com", "published": "2026-09-23 12:57", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure Share Price Rises 2.68% Today", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNbjd5UVZ4d3N3ZUtybnEyZW1MZ1R4T0NrS1JsMEhETFc5d2tyclFHRnV4bzQ1RVQyUkZvNnIwOURYdjdBUzZldEpRN0FBV29YLVZOTjlFalZfemVpUzBVZ3BZSDJxSVFqSmdCMDVfNVNVXy1ZZVJpZUZORHdmNUFzazBrdGVsOGVPN1ZMRmdyQ0U1X3kzS1ZNZU1mQQ?oc=5", "source": "Univest", "published": "2026-09-23 10:02", "score": 0.34, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs Share Price: one-year high and valuation view", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYU9VS2psbTA2SEFlWWF6NVFFbVRManpTcU0wUjJIbWRQdEU2S1JUeWVXWVUtSW1RNGp3VmdEZjRGYkdVYmFtV2tZd1BQLWJfT2ZHYzhXcFhMTVgwaDlmNmZkOHhaY0JiOEVaQmZmTk5FS1luRmcxeE9ZbGV3VDlqOWR4VFhCZEE?oc=5", "source": "Univest", "published": "2026-09-23 09:19", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQa2ZFOFYwaEJuQTl6N3NjWFFvMWUyUGdxNXlZNFJHVWxtcFNEenVuTlNieHRNX3RpY0dfNnNCUk1hMU9Ndk5Sckl3TVg1Z2lJYnFORjgtY0UySTc0WW5qVmV0bU5hd0UzTVM3OVdKUFNUUHdzbEhaTTNERlV0WTdFWTBYSnpadUhucV9mejJxMnNlZ2V2UzJaOVY0dHdfNWtMVWN3U0tkVVFuSUVSMnV5NjhTUUE5a2Zrc2xieTVkZEphNmVqSEQ1MmRqMEFKM2xwU1FCVkxkZ0VsdFZYazRiMDhKcEhsejFNOXgtSGo0bFRJWThyZkZaXzJVQWpwbklBNno4NE1QSzRfT001NktmddIBlgJBVV95cUxOdy1fS2JiOHZGWTlaelh4ak5fQTR6TU9lek4tN0tIODhtWjRtRkJmS2hhZHVLTmpSMkQ2T0dXNnk1VFlTdFRjcmE1b1dCQWYtSnVQRFh0Z1hsUUljNkZVeF9GQ2pSZmplX082cHlVWEx2aVQ0dWpyZndmREdSOUJmcHBfczhYU0ZjUVVWYU96N1J0SENVQV8tR243REJnYzZwcnNzTlFnakJWcmV6eU9yTUs3NC1FWVpwRnFiZTRrUVVtM1UxQy01YnNsN1BweXNTbGpkb1l1UTNTRzNDUDEtWjBOeVJsa2QtejEtRElXcy1LNXc5bW5FY0Q4TGhXQXNWWlgxRjlXQlNEQ1R0V1B2OVZqWHluUQ?oc=5", "source": "The Times of India", "published": "2026-09-23 07:59", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks Share Price news: price rise and valuation", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNS3pobG5zQUpFLU53cFlCQWxZTFQ5S0E1dDNmbTU3V2daQUx1ZTMxMjctRHphNW5OSWVoYk9UY09CU2NxbF9GWjVCZDJzeF9OTXVTX3NUYVRjZ1U3ekZnLVFxZ01Sc3dVWlZIcnZOdXdvTzVlNTdoMlhYaVZZaWNaTEpZTkxpZw?oc=5", "source": "Univest", "published": "2026-09-23 07:26", "score": 0.0, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQThVQlhqMHhQX1dCbzk5aTVLRzAzLVhTQ0kzajBZMXRVTTNTazhRNTM3Y2d5SE1fbUhYVkJkT0hDeDlCZFhGRHEtWUxEcEhISzA4bkNGUlQ2RW44NEdPa1k5VFF5MGktRHhhZHJMRjAyeUVCVmEwWkVIQ2ROQmlhdTZTY255RFg2Rkp4NWtCTk1vaGxrUFc1VTRFSkJFY1Nnakd4VXpMNGxRVkpvMkl5VnpmakQtMWgwcV90RFpwM3BwaFFfNzhsR3IzQWhRNmpCWVVjdVM1ZExSSkxZR1N1bEpNaUp0eGV5bGIyTDQzZTZjdw?oc=5", "source": "economictimes.com", "published": "2026-09-23 06:24", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPa2tacGJLRFdET1pPVlhxQlRodHp4ZVZkREJLUU8yQlFiSmdib0hReElVbW5Qc2QtMnFqZWVDREFveHlPbDB5MHhGQjlBcTVfMS12Q1hyNGRFUjZrOHY0Ym9jSGhaSnV4YlZYZDZGV25jb1NtRV9admFLQWN1N1NETF9pUU1GbFFadFVXdzJ0dUxJelU3SFlaQUR0MlZxTWxHaDQ2SnpjRl9LczRSQ1BiX2h6SWl3ckJiek5mSDVwNm84cVVBYnRCSnFPYWRHLUlhUUlwb2cyN0tGdHRGU2lNdnVkdlNQZGJS0gHuAUFVX3lxTFBtQmV3OHlXVURIb1VpaGFmZnYtYjJnSFVyVjEtM2pvajJYV3BZQlZDOGtuOEZ4dG9hMDNkQmJVaXJPODNLdFdBMHJVdmRoTkRkR1NERk5DaWRlNXgyMUJmNDkzYXZzWVUwSzlIZ29CX3BueG8ySTU4Ymlod19HTFVJM1k2X1FDMmFpLXJPa3YtVjlSdi0tdjJ4UVc3MHZGR1ljSTJHdENmV0MwOHhJdmgyTEZBV0ZUN1JVR2gxOFhXSXBHdXlWTVYxT2RMdkhnY3UtN3FXOGd1UUtZYWRaWXVIR193bmsydVZRVnJNV0E?oc=5", "source": "simplywall.st", "published": "2026-09-23 05:56", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxNNi1kLW5uekpsdjNub29Fa3NDaWEzNU91MUMxNGZMS1ZVeEZPZ2tiLWZWY1M4MW84dTRYRl93QjFISTVtSG9oUHRpLUZZcE9welgydkFGTDZPRWtBbXVkaC1xOVgtWnhuNVZNVklETHgyNFdOMEo3UWFjUWx4dzI0ZlZDbXJ3cEdKMTFWZkNoeVo1OXlpUG1iLXhIUkREVElXLWozbkxtUWtmWXFxc043VHB2R0NpU2dQVVVGZlNWeXNkbVItSGk0VGZ5M202QUVzckd5bFliQUtMbE5SZ2NURVNsZW50aFZnd1RsQkJoRGVHUklpNF9iRGxCbE5XamlvWnZyVUNIM3NrdkZiYjI1MjFB0gGXAkFVX3lxTE1waWJFallWREMwLVdIUXFpMDlzd1loMmViNEdDbzVfbTJoSUxubGpLVy1NZjU1c2taUzdsczJIaG9OSmpIVFc5bUlyRjZQdzZkWVZKeVlwMG9GTTI1N0dHV09ucTJJX0hQUS1rUGtMLXhVTkNXQjNpNDVYVTQ1TmxtMmVWWGx0UVhpTDhmSGdCNlNma19TQTZadDlPa0RjZ2RfQ1dLaXFHMVZtdjNPRzFhdGVnMFYydnNJR3VGWEJiTHVvNW11dV9SbzNiaU1fSEJLeUpVY0R3UnBZbWp3NTNZN2NwU3ZFMzVhME9XVjI0cWdvdW1DZno2ZHVkTWFwMkRDUUkwdVRsYW5XQkx6M0gwX2tJYWJacw?oc=5", "source": "Livemint", "published": "2026-09-23 01:13", "score": 0.557, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPeE5EWjI1ZEd2aG02OThzbUpNSXdERzVpYkNmNXRCdEFNLU1JUEk2RG9IanhndHM2N1oxMDAwblVrcXpSaVFfcmc0WEF6UUJqd09acWZQYXdzM2cwZFJkUVZVSkE5Tk9WWnhJV0ZXR19HN18tRFhCU2hqWXR5a3lBazR6UWN4UDJ0VEh3NGFxNE1oX3M2Sjhib0h5N0RvMGdUcU9zVm91ODRoaGl2dVJXc18xTnJObk9pS3BfX1lQWS1HWGUzR0lEbDZ1ZTZ1b1FlY0h6SnBCRdIB3AFBVV95cUxQbHN0Tmw0M3l2RFNtTzBTaEtMbzJ5WmE3cWRraUhSRTc3ejR4SUE2NDBvTEhqMTZPQmktdXJ5N3VwM2ZudzBPTU8zZU1tLUVIUFlVVDdCbGFaZGllcHA5UmEzLUpOU2RlU2c0YzlrTUk4ejU3UUxQM2hXTWlsU0p5eVh0blVNMmdpcERxXzFnZ1d2R3lzUzE2c21vOGxBWGlIMnR1Z25MQTlITTI4S3JIcU56YU5VVHVyUXVSU3JHZ3ZiVnZFLWVFbmR0S0dHTHVqOGw2QlZrZzg5bDFT?oc=5", "source": "simplywall.st", "published": "2026-09-23 00:46", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex drops 330 points, Nifty down to 23,329 dragged by IT stocks", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxPNFJTNFB5dk9wRmoxYUFueUhJcHRhRVhXNUwwb05HRm5xeHpOSUdVVUdmd010X1lTMVRmekwzbURob0Q0VU1kOXpLZERFSVdIamc0cU1vQUJUOGdMWGxBTHJTUzF5cV9WVFJwX2J1eU9faU5PMml0TW9XMEw4MmRYbzdtWk14U0JjVkZnaVJ2VzEwRnFhRWtoTmtsOE5EY1RDa01qZWhMSnNNQzhKc1l0UEtCbVdHd9IBvAFBVV95cUxQWDhBbHBnUVp1Nm5VbW5zbXZQTjJWR2pwdjMzTWk0Z3hHZzFQVnNpb1VTcWt0ZlZfWlQzQTNvYXhSZEcwSjFKWmIwbm85YlZ0UUJhdHJrZkdZRHRpdDNhOXJXM1pETVFUSGFXZ3g5N19FYnhqV3M2WEppNmZYMHVnZmYyTHVvQnhNYnRSUDJrN2pJNHMwM2ZNaVBQS1RLNHYxUUdMWHh1UzJxN2ltcURlMWUxQVkzTllaU2xjZA?oc=5", "source": "The Hindu", "published": "2026-09-22 11:04", "score": 0.361, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals to host investor meet at PL Capital conference on Sep 28", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxOemZyUExJOUpZeW9vRDRtRmI4LUFZOXNDY3ZBNjJ6ZXJqSVAzQkhtMk5xSmpaVGxCQ21GVFoyODFYSGdMYngyLWVQZ0lVT3JnUE9sZEJNUzI4eV9wcW9UY3VsdG5VemUwUmFPaWhJbTlScWJCV25OYkc5XzBKaXNSMFZZWlE3cUhsblRqSXp4SWpvS2Z4bmpRcWJiN1JCRmhrTTJuQ1VjbFUwS2hOSEhCcmxHdjI0ekRhV1RZQlFrRQ?oc=5", "source": "scanx.trade", "published": "2026-09-22 08:51", "score": 0.0, "label": "Neutral"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals NSE:ACUTAAS Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOYnY1bG13T0VMaGh4bVVwcWg4VXZydnVVa0hQTEZlQVlVRnJZdEdxRGZ1Zy1CSFQ5NTVqQkxjUUplU1NmaDRuWWliSlZaWUtPTXJSUGN5c2VZRUpUeFFfdmw4Zy1sNE5qdGt4Qy02OVQ0MXFaUUZZcE80el9BVEQ4SjdTWWE1M2NNbERjNEgzMDd2Mjd2UE5xQ0c4a2tmMnZoX2FnMHdlRmNkSG82LVExUjgxdVBpZw?oc=5", "source": "Kalkine India", "published": "2026-09-22 07:31", "score": 0.0, "label": "Neutral"}, {"symbol": "ATHERENERG", "title": "Ather Energy Share Price News: Today\u2019s Decline Explained", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxONjFLdmNlWldKcVdBQWxtakF5dmI4cFdXODhVWkpqTElHcTUzZWhoN3R3OV8wdjVOSU9aVGZ3dGNzN3RDTm5XdEtHZmc0T0twMURva1ZPVk1zaDZhZFBLY0tuamtkUmZGZy02YllXMklOSzhiQXdPYm5yYktSRmtnZw?oc=5", "source": "Univest", "published": "2026-09-22 07:22", "score": -0.128, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: price rise and sector check", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxQbjk1eVNKTElsd0tEcEVPeVRzZ0VJMk9KV3lyaUViUEVvQ3U4VG9uc0t0czlWSkVMLVF6WWRORkJSTUlDOTRFVU5jOVR1UEQ1OTNUa3dpTDRGNDdXLXl0NGlYUjFLS2RBYjVLVFIyMWtTRkNKTWtsNE41MF9pcEtvSA?oc=5", "source": "Univest", "published": "2026-09-22 07:19", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxQSUdyXzNaTFpFQktnX2tJNVotaGRyUXdzUF84LWxwdkdiX3VfTnBWRHJpak1VdkhpVVQ5MVJGRHQ4bjVLQXlDRzlyUENyRE83MXlwT0lLaEZEd0JKbHV4RWVtX194MkFJc3AxeXFGOEFMT0NmbDZqMVFVVEhrNUZWNGRrRXpZY0xzbDcwWjBQc2dpbFQ2blFKV2RiVWdSenlDUUlfMDloc1I4S2lBaGVUQVBzNGdwbXBESVgyYTZ5Z052YzZMdTJFYm5iTlUzV19aSVJDUnlkd1VRdEhiR1Q3T3JMTElyc1dlaGfSAe8BQVVfeXFMTnBPVmlmNEtYY0Z3WEdMNWZ3Y1dLSnVEcXhSVUJ5YkNnUXhxYWtnX3dHRWZyY0hlMnEtTkZWWXlMSW1CcjRLMjlQeUNWS0d5NERGZE5DaU1VaW1LcE5FLUw1bGdKZTFmdFQtTUlpTjNXN1Q2WkJpTDUycmtNM0ExVWw0eFlnei1SODB2UWNQcGtOR3FWcDFFcVN6ZnhOSDdoS2EyQS1Pa3ljS1llZloyblNzUGlBb2RDWGFiZkV5dm5kb3BXSjlYLXU2Z0VQNTNpMld3MVZGeW8zc0JGZ19Wa3QwRHRUZFVQenJ0NnRJUDg?oc=5", "source": "simplywall.st", "published": "2026-09-22 05:01", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty see positive start; NSE IPO receives 6x subscription on final day | Business News", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQTkFFZlczeUxrZGxNZXpkWDdpYVhxdDdXNy1Yems4cTdtV3pkQUEtX1pQWFRKWUh0cUJFSVUwMDFTVjZiaEotVzdxV0Q4MUFIZkRJd0FKT3VodVJlazVIbXNnRnZaVkR1d2xzLUVNVlNaM0x2ODNaNjlEaDlDNjFFT1dCR0FUV0pZcDZkR3V2cmhLT0VHelZ5aEFoT0p0UGkxLS0zdXJZYlFhZFFLWmhfV25jTjNFUUlLMjBsWWhkbi16ZmVpcVpfUTVQWlhrR1gwMGx6bEp5bnhqM1HSAeABQVVfeXFMT1M5bV93ZEdtOUtUbks4OEtBSEdkaWJxWlp0TDNsQUlqblVkUGFyQ2hHM0pwb0Q4U0lhcVM5dFlYYlJUMU5QeUFvbV9EOGx0cGVsR2xfdFZ0THNXMVBkY21wYklLRVZUcVIwbldIaVFsSXlpdDJtbXlVa0lMNzQyVzdjVUVITXZ3cVdPUnByeFN5REpBcVlNM0FoUjZ5V2gxRUE2UFQ0RjF4UmtLcEJOSkZaT0FaekQ0SGFDZFhmRnZNdWNVeXZiekhHWGJ1SjkwdVBkdjl2VlBvSzVvMnowN3Q?oc=5", "source": "Hindustan Times", "published": "2026-09-22 03:51", "score": 0.743, "label": "Positive"}], "errors": []}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T02:53:52", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}}</t>
+          <t>tocks With Revenue Growth Up To 16%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-revenue-171316164.html", "source": "Simply Wall St.", "published": "2026-09-24 17:13", "score": 0.932, "label": "Positive"}], "errors": ["TDPOWERSYS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=TDPOWERSYS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "AEROFLEX Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=AEROFLEX%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "ATHERENERG Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=ATHERENERG%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "THANGAMAYL Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=THANGAMAYL%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "RRKABEL Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=RRKABEL%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "ACUTAAS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=ACUTAAS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "DIACABS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=DIACABS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "KIRLOSENG Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=KIRLOSENG%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "E2E Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=E2E%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "LAURUSLABS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=LAURUSLABS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "MARKET Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=Sensex%20Nifty%20stock%20market%20India%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en"]}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T03:08:34", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}}</t>
         </is>
       </c>
     </row>

--- a/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
+++ b/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
@@ -198,7 +198,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C9860A"/>
+        <fgColor rgb="000E7C86"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,7 +208,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7C86"/>
+        <fgColor rgb="00C9860A"/>
       </patternFill>
     </fill>
     <fill>
@@ -383,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -525,6 +525,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -870,12 +873,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Portfolio Path'!$A$5</f>
+              <f>'Portfolio Path'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Portfolio Path'!$D$5</f>
+              <f>'Portfolio Path'!$D$5:$D$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1495,7 +1498,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 03:09</t>
+          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 17:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1513,7 +1516,7 @@
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS  Day 0/21</t>
+          <t>PROGRESS  Day 1/21</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1533,7 @@
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -1563,13 +1566,13 @@
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Day 0 / 21</t>
+          <t>Day 1 / 21</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F8" s="9" t="n"/>
@@ -1587,7 +1590,7 @@
     <row r="9">
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Signal day — buy at next open</t>
+          <t>Entry day (bought at open)</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -1711,13 +1714,17 @@
       <c r="L15" s="7" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="12" t="n"/>
+      <c r="B16" s="12" t="n">
+        <v>-0.002811646053050287</v>
+      </c>
       <c r="C16" s="9" t="n"/>
-      <c r="E16" s="12" t="n"/>
+      <c r="E16" s="12" t="n">
+        <v>0.04013470084814344</v>
+      </c>
       <c r="F16" s="9" t="n"/>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>0 / 0</t>
+          <t>8 / 2</t>
         </is>
       </c>
       <c r="I16" s="9" t="n"/>
@@ -1814,341 +1821,341 @@
     <row r="21">
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>722</v>
+        <v>2141.2</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>722</v>
+        <v>2402</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>0</v>
+        <v>0.121801</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0</v>
+        <v>1825.6</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0</v>
+        <v>0.121801</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>0</v>
+        <v>0.121801</v>
       </c>
       <c r="J21" s="20" t="n">
-        <v>0.103214</v>
+        <v>0.107094</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>0</v>
+        <v>0.013044</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>513.4</v>
+        <v>719</v>
       </c>
       <c r="E22" s="23" t="n">
-        <v>513.4</v>
+        <v>777.35</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>0</v>
+        <v>0.081154</v>
       </c>
       <c r="G22" s="25" t="n">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0</v>
+        <v>0.081154</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0</v>
+        <v>0.081154</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>0.106421</v>
+        <v>0.102747</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0</v>
+        <v>0.008338</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>1454.9</v>
+        <v>511.3</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>1454.9</v>
+        <v>539.6</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0</v>
+        <v>0.055349</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0</v>
+        <v>820.7</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0</v>
+        <v>0.055349</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>0</v>
+        <v>0.055349</v>
       </c>
       <c r="J23" s="20" t="n">
-        <v>0.103993</v>
+        <v>0.105946</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>0</v>
+        <v>0.005864</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>5011.5</v>
+        <v>619.55</v>
       </c>
       <c r="E24" s="23" t="n">
-        <v>5011.5</v>
+        <v>651.8</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>0</v>
+        <v>0.052054</v>
       </c>
       <c r="G24" s="25" t="n">
-        <v>0</v>
+        <v>741.75</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0</v>
+        <v>0.052054</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0</v>
+        <v>0.052054</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>0.071642</v>
+        <v>0.101816</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>2459.8</v>
+        <v>336.9</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>2459.8</v>
+        <v>352.05</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>0</v>
+        <v>0.044969</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>0</v>
+        <v>666.6</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0</v>
+        <v>0.044969</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>0</v>
+        <v>0.044969</v>
       </c>
       <c r="J25" s="20" t="n">
-        <v>0.105493</v>
+        <v>0.105917</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>0</v>
+        <v>0.004763</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="C26" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>3214.4</v>
+        <v>5010</v>
       </c>
       <c r="E26" s="23" t="n">
-        <v>3214.4</v>
+        <v>5204.5</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>0</v>
+        <v>0.038822</v>
       </c>
       <c r="G26" s="25" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0</v>
+        <v>0.038822</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0</v>
+        <v>0.038822</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0.091904</v>
+        <v>0.071594</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0</v>
+        <v>0.002779</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D27" s="17" t="n">
-        <v>339.25</v>
+        <v>2459.8</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>339.25</v>
+        <v>2523.2</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>0</v>
+        <v>0.025774</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0</v>
+        <v>380.4</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>0</v>
+        <v>0.025774</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>0</v>
+        <v>0.025774</v>
       </c>
       <c r="J27" s="20" t="n">
-        <v>0.106695</v>
+        <v>0.105454</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>0</v>
+        <v>0.002718</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>2141.2</v>
+        <v>3290</v>
       </c>
       <c r="E28" s="23" t="n">
-        <v>2141.2</v>
+        <v>3304.1</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>0</v>
+        <v>0.004286</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>0</v>
+        <v>0.004286</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>0</v>
+        <v>0.004286</v>
       </c>
       <c r="J28" s="26" t="n">
-        <v>0.107134</v>
+        <v>0.09403</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0</v>
+        <v>0.000403</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D29" s="17" t="n">
-        <v>625.9</v>
+        <v>2020.7</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>625.9</v>
+        <v>1979</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>0</v>
+        <v>-0.020636</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0</v>
+        <v>-291.9</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0</v>
+        <v>-0.020636</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>0</v>
+        <v>-0.020636</v>
       </c>
       <c r="J29" s="20" t="n">
-        <v>0.102898</v>
+        <v>0.101067</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>0</v>
+        <v>-0.002086</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C30" s="22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>2010.7</v>
+        <v>1460.2</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>2010.7</v>
+        <v>1407</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>0</v>
+        <v>-0.036433</v>
       </c>
       <c r="G30" s="25" t="n">
-        <v>0</v>
+        <v>-532</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0</v>
+        <v>-0.036433</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>0</v>
+        <v>-0.036433</v>
       </c>
       <c r="J30" s="26" t="n">
-        <v>0.100605</v>
+        <v>0.104333</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0</v>
+        <v>-0.003801</v>
       </c>
     </row>
   </sheetData>
@@ -2378,7 +2385,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 0 of 21  •  Signal day — buy at next open  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 03:09</t>
+          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 17:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2551,7 +2558,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="AA4" s="29" t="inlineStr">
+      <c r="AA4" s="28" t="inlineStr">
         <is>
           <t>Day 21</t>
         </is>
@@ -2593,9 +2600,9 @@
           <t>28-Sep</t>
         </is>
       </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>29-Sep (p)</t>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="H5" s="33" t="inlineStr">
@@ -2722,12 +2729,14 @@
         <v>20</v>
       </c>
       <c r="E6" s="36" t="n">
+        <v>719</v>
+      </c>
+      <c r="F6" s="17" t="n">
         <v>722</v>
       </c>
-      <c r="F6" s="37" t="n">
-        <v>722</v>
-      </c>
-      <c r="G6" s="38" t="n"/>
+      <c r="G6" s="37" t="n">
+        <v>777.35</v>
+      </c>
       <c r="H6" s="38" t="n"/>
       <c r="I6" s="38" t="n"/>
       <c r="J6" s="38" t="n"/>
@@ -2761,7 +2770,7 @@
         <v/>
       </c>
       <c r="AE6" s="18">
-        <f>IFERROR(F6/F6-1,0)</f>
+        <f>IFERROR(G6/F6-1,0)</f>
         <v/>
       </c>
       <c r="AF6" s="34">
@@ -2787,12 +2796,14 @@
         <v>29</v>
       </c>
       <c r="E7" s="43" t="n">
+        <v>511.3</v>
+      </c>
+      <c r="F7" s="23" t="n">
         <v>513.4</v>
       </c>
-      <c r="F7" s="37" t="n">
-        <v>513.4</v>
-      </c>
-      <c r="G7" s="38" t="n"/>
+      <c r="G7" s="37" t="n">
+        <v>539.6</v>
+      </c>
       <c r="H7" s="38" t="n"/>
       <c r="I7" s="38" t="n"/>
       <c r="J7" s="38" t="n"/>
@@ -2826,7 +2837,7 @@
         <v/>
       </c>
       <c r="AE7" s="18">
-        <f>IFERROR(F7/F7-1,0)</f>
+        <f>IFERROR(G7/F7-1,0)</f>
         <v/>
       </c>
       <c r="AF7" s="34">
@@ -2852,12 +2863,14 @@
         <v>10</v>
       </c>
       <c r="E8" s="36" t="n">
+        <v>1460.2</v>
+      </c>
+      <c r="F8" s="17" t="n">
         <v>1454.9</v>
       </c>
-      <c r="F8" s="37" t="n">
-        <v>1454.9</v>
-      </c>
-      <c r="G8" s="38" t="n"/>
+      <c r="G8" s="37" t="n">
+        <v>1407</v>
+      </c>
       <c r="H8" s="38" t="n"/>
       <c r="I8" s="38" t="n"/>
       <c r="J8" s="38" t="n"/>
@@ -2891,7 +2904,7 @@
         <v/>
       </c>
       <c r="AE8" s="18">
-        <f>IFERROR(F8/F8-1,0)</f>
+        <f>IFERROR(G8/F8-1,0)</f>
         <v/>
       </c>
       <c r="AF8" s="34">
@@ -2917,12 +2930,14 @@
         <v>2</v>
       </c>
       <c r="E9" s="43" t="n">
+        <v>5010</v>
+      </c>
+      <c r="F9" s="23" t="n">
         <v>5011.5</v>
       </c>
-      <c r="F9" s="37" t="n">
-        <v>5011.5</v>
-      </c>
-      <c r="G9" s="38" t="n"/>
+      <c r="G9" s="37" t="n">
+        <v>5204.5</v>
+      </c>
       <c r="H9" s="38" t="n"/>
       <c r="I9" s="38" t="n"/>
       <c r="J9" s="38" t="n"/>
@@ -2956,7 +2971,7 @@
         <v/>
       </c>
       <c r="AE9" s="18">
-        <f>IFERROR(F9/F9-1,0)</f>
+        <f>IFERROR(G9/F9-1,0)</f>
         <v/>
       </c>
       <c r="AF9" s="34">
@@ -2984,10 +2999,12 @@
       <c r="E10" s="36" t="n">
         <v>2459.8</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="17" t="n">
         <v>2459.8</v>
       </c>
-      <c r="G10" s="38" t="n"/>
+      <c r="G10" s="37" t="n">
+        <v>2523.2</v>
+      </c>
       <c r="H10" s="38" t="n"/>
       <c r="I10" s="38" t="n"/>
       <c r="J10" s="38" t="n"/>
@@ -3021,7 +3038,7 @@
         <v/>
       </c>
       <c r="AE10" s="18">
-        <f>IFERROR(F10/F10-1,0)</f>
+        <f>IFERROR(G10/F10-1,0)</f>
         <v/>
       </c>
       <c r="AF10" s="34">
@@ -3047,12 +3064,14 @@
         <v>4</v>
       </c>
       <c r="E11" s="43" t="n">
+        <v>3290</v>
+      </c>
+      <c r="F11" s="23" t="n">
         <v>3214.4</v>
       </c>
-      <c r="F11" s="37" t="n">
-        <v>3214.4</v>
-      </c>
-      <c r="G11" s="38" t="n"/>
+      <c r="G11" s="37" t="n">
+        <v>3304.1</v>
+      </c>
       <c r="H11" s="38" t="n"/>
       <c r="I11" s="38" t="n"/>
       <c r="J11" s="38" t="n"/>
@@ -3086,7 +3105,7 @@
         <v/>
       </c>
       <c r="AE11" s="18">
-        <f>IFERROR(F11/F11-1,0)</f>
+        <f>IFERROR(G11/F11-1,0)</f>
         <v/>
       </c>
       <c r="AF11" s="34">
@@ -3112,12 +3131,14 @@
         <v>44</v>
       </c>
       <c r="E12" s="36" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="F12" s="17" t="n">
         <v>339.25</v>
       </c>
-      <c r="F12" s="37" t="n">
-        <v>339.25</v>
-      </c>
-      <c r="G12" s="38" t="n"/>
+      <c r="G12" s="37" t="n">
+        <v>352.05</v>
+      </c>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="38" t="n"/>
       <c r="J12" s="38" t="n"/>
@@ -3151,7 +3172,7 @@
         <v/>
       </c>
       <c r="AE12" s="18">
-        <f>IFERROR(F12/F12-1,0)</f>
+        <f>IFERROR(G12/F12-1,0)</f>
         <v/>
       </c>
       <c r="AF12" s="34">
@@ -3179,10 +3200,12 @@
       <c r="E13" s="43" t="n">
         <v>2141.2</v>
       </c>
-      <c r="F13" s="37" t="n">
+      <c r="F13" s="23" t="n">
         <v>2141.2</v>
       </c>
-      <c r="G13" s="38" t="n"/>
+      <c r="G13" s="37" t="n">
+        <v>2402</v>
+      </c>
       <c r="H13" s="38" t="n"/>
       <c r="I13" s="38" t="n"/>
       <c r="J13" s="38" t="n"/>
@@ -3216,7 +3239,7 @@
         <v/>
       </c>
       <c r="AE13" s="18">
-        <f>IFERROR(F13/F13-1,0)</f>
+        <f>IFERROR(G13/F13-1,0)</f>
         <v/>
       </c>
       <c r="AF13" s="34">
@@ -3242,12 +3265,14 @@
         <v>23</v>
       </c>
       <c r="E14" s="36" t="n">
+        <v>619.55</v>
+      </c>
+      <c r="F14" s="17" t="n">
         <v>625.9</v>
       </c>
-      <c r="F14" s="37" t="n">
-        <v>625.9</v>
-      </c>
-      <c r="G14" s="38" t="n"/>
+      <c r="G14" s="37" t="n">
+        <v>651.8</v>
+      </c>
       <c r="H14" s="38" t="n"/>
       <c r="I14" s="38" t="n"/>
       <c r="J14" s="38" t="n"/>
@@ -3281,7 +3306,7 @@
         <v/>
       </c>
       <c r="AE14" s="18">
-        <f>IFERROR(F14/F14-1,0)</f>
+        <f>IFERROR(G14/F14-1,0)</f>
         <v/>
       </c>
       <c r="AF14" s="34">
@@ -3307,12 +3332,14 @@
         <v>7</v>
       </c>
       <c r="E15" s="43" t="n">
+        <v>2020.7</v>
+      </c>
+      <c r="F15" s="23" t="n">
         <v>2010.7</v>
       </c>
-      <c r="F15" s="37" t="n">
-        <v>2010.7</v>
-      </c>
-      <c r="G15" s="38" t="n"/>
+      <c r="G15" s="37" t="n">
+        <v>1979</v>
+      </c>
       <c r="H15" s="38" t="n"/>
       <c r="I15" s="38" t="n"/>
       <c r="J15" s="38" t="n"/>
@@ -3346,7 +3373,7 @@
         <v/>
       </c>
       <c r="AE15" s="18">
-        <f>IFERROR(F15/F15-1,0)</f>
+        <f>IFERROR(G15/F15-1,0)</f>
         <v/>
       </c>
       <c r="AF15" s="34">
@@ -3656,12 +3683,12 @@
           <t>Entry ₹</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Day 0</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>Day 1</t>
         </is>
@@ -5211,12 +5238,12 @@
           <t>Entry ₹</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Day 0</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>Day 1</t>
         </is>
@@ -6643,469 +6670,481 @@
       <c r="A5" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="53" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D5" s="55" t="n">
+      <c r="D5" s="19" t="n">
         <v>139903</v>
       </c>
-      <c r="E5" s="55" t="n">
+      <c r="E5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="56" t="n">
+      <c r="F5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="56" t="n"/>
-      <c r="H5" s="56" t="n"/>
-      <c r="I5" s="56" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="57" t="n">
+      <c r="A6" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
-        <is>
-          <t>Entry (upcoming)</t>
-        </is>
-      </c>
-      <c r="D6" s="60" t="n"/>
-      <c r="E6" s="60" t="n"/>
-      <c r="F6" s="61" t="n"/>
-      <c r="G6" s="61" t="n"/>
-      <c r="H6" s="61" t="n"/>
-      <c r="I6" s="61" t="n"/>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="n">
+        <v>145178.6</v>
+      </c>
+      <c r="E6" s="56" t="n">
+        <v>5223.55</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>0.037323</v>
+      </c>
+      <c r="G6" s="57" t="n"/>
+      <c r="H6" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="57" t="n">
+        <v>-0.002812</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="n">
+      <c r="A7" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D7" s="60" t="n"/>
-      <c r="E7" s="60" t="n"/>
-      <c r="F7" s="61" t="n"/>
-      <c r="G7" s="61" t="n"/>
-      <c r="H7" s="61" t="n"/>
-      <c r="I7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="61" t="n"/>
+      <c r="F7" s="62" t="n"/>
+      <c r="G7" s="62" t="n"/>
+      <c r="H7" s="62" t="n"/>
+      <c r="I7" s="62" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="57" t="n">
+      <c r="A8" s="58" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="61" t="n"/>
-      <c r="G8" s="61" t="n"/>
-      <c r="H8" s="61" t="n"/>
-      <c r="I8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="62" t="n"/>
+      <c r="G8" s="62" t="n"/>
+      <c r="H8" s="62" t="n"/>
+      <c r="I8" s="62" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="57" t="n">
+      <c r="A9" s="58" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D9" s="60" t="n"/>
-      <c r="E9" s="60" t="n"/>
-      <c r="F9" s="61" t="n"/>
-      <c r="G9" s="61" t="n"/>
-      <c r="H9" s="61" t="n"/>
-      <c r="I9" s="61" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="61" t="n"/>
+      <c r="F9" s="62" t="n"/>
+      <c r="G9" s="62" t="n"/>
+      <c r="H9" s="62" t="n"/>
+      <c r="I9" s="62" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="57" t="n">
+      <c r="A10" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D10" s="60" t="n"/>
-      <c r="E10" s="60" t="n"/>
-      <c r="F10" s="61" t="n"/>
-      <c r="G10" s="61" t="n"/>
-      <c r="H10" s="61" t="n"/>
-      <c r="I10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="62" t="n"/>
+      <c r="G10" s="62" t="n"/>
+      <c r="H10" s="62" t="n"/>
+      <c r="I10" s="62" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="57" t="n">
+      <c r="A11" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="58" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D11" s="60" t="n"/>
-      <c r="E11" s="60" t="n"/>
-      <c r="F11" s="61" t="n"/>
-      <c r="G11" s="61" t="n"/>
-      <c r="H11" s="61" t="n"/>
-      <c r="I11" s="61" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="E11" s="61" t="n"/>
+      <c r="F11" s="62" t="n"/>
+      <c r="G11" s="62" t="n"/>
+      <c r="H11" s="62" t="n"/>
+      <c r="I11" s="62" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="n">
+      <c r="A12" s="58" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D12" s="60" t="n"/>
-      <c r="E12" s="60" t="n"/>
-      <c r="F12" s="61" t="n"/>
-      <c r="G12" s="61" t="n"/>
-      <c r="H12" s="61" t="n"/>
-      <c r="I12" s="61" t="n"/>
+      <c r="D12" s="61" t="n"/>
+      <c r="E12" s="61" t="n"/>
+      <c r="F12" s="62" t="n"/>
+      <c r="G12" s="62" t="n"/>
+      <c r="H12" s="62" t="n"/>
+      <c r="I12" s="62" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="57" t="n">
+      <c r="A13" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D13" s="60" t="n"/>
-      <c r="E13" s="60" t="n"/>
-      <c r="F13" s="61" t="n"/>
-      <c r="G13" s="61" t="n"/>
-      <c r="H13" s="61" t="n"/>
-      <c r="I13" s="61" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="62" t="n"/>
+      <c r="G13" s="62" t="n"/>
+      <c r="H13" s="62" t="n"/>
+      <c r="I13" s="62" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="57" t="n">
+      <c r="A14" s="58" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D14" s="60" t="n"/>
-      <c r="E14" s="60" t="n"/>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="61" t="n"/>
-      <c r="H14" s="61" t="n"/>
-      <c r="I14" s="61" t="n"/>
+      <c r="D14" s="61" t="n"/>
+      <c r="E14" s="61" t="n"/>
+      <c r="F14" s="62" t="n"/>
+      <c r="G14" s="62" t="n"/>
+      <c r="H14" s="62" t="n"/>
+      <c r="I14" s="62" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="57" t="n">
+      <c r="A15" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D15" s="60" t="n"/>
-      <c r="E15" s="60" t="n"/>
-      <c r="F15" s="61" t="n"/>
-      <c r="G15" s="61" t="n"/>
-      <c r="H15" s="61" t="n"/>
-      <c r="I15" s="61" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="E15" s="61" t="n"/>
+      <c r="F15" s="62" t="n"/>
+      <c r="G15" s="62" t="n"/>
+      <c r="H15" s="62" t="n"/>
+      <c r="I15" s="62" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="57" t="n">
+      <c r="A16" s="58" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D16" s="60" t="n"/>
-      <c r="E16" s="60" t="n"/>
-      <c r="F16" s="61" t="n"/>
-      <c r="G16" s="61" t="n"/>
-      <c r="H16" s="61" t="n"/>
-      <c r="I16" s="61" t="n"/>
+      <c r="D16" s="61" t="n"/>
+      <c r="E16" s="61" t="n"/>
+      <c r="F16" s="62" t="n"/>
+      <c r="G16" s="62" t="n"/>
+      <c r="H16" s="62" t="n"/>
+      <c r="I16" s="62" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="57" t="n">
+      <c r="A17" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="58" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D17" s="60" t="n"/>
-      <c r="E17" s="60" t="n"/>
-      <c r="F17" s="61" t="n"/>
-      <c r="G17" s="61" t="n"/>
-      <c r="H17" s="61" t="n"/>
-      <c r="I17" s="61" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="61" t="n"/>
+      <c r="F17" s="62" t="n"/>
+      <c r="G17" s="62" t="n"/>
+      <c r="H17" s="62" t="n"/>
+      <c r="I17" s="62" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="n">
+      <c r="A18" s="58" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D18" s="60" t="n"/>
-      <c r="E18" s="60" t="n"/>
-      <c r="F18" s="61" t="n"/>
-      <c r="G18" s="61" t="n"/>
-      <c r="H18" s="61" t="n"/>
-      <c r="I18" s="61" t="n"/>
+      <c r="D18" s="61" t="n"/>
+      <c r="E18" s="61" t="n"/>
+      <c r="F18" s="62" t="n"/>
+      <c r="G18" s="62" t="n"/>
+      <c r="H18" s="62" t="n"/>
+      <c r="I18" s="62" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="57" t="n">
+      <c r="A19" s="58" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D19" s="60" t="n"/>
-      <c r="E19" s="60" t="n"/>
-      <c r="F19" s="61" t="n"/>
-      <c r="G19" s="61" t="n"/>
-      <c r="H19" s="61" t="n"/>
-      <c r="I19" s="61" t="n"/>
+      <c r="D19" s="61" t="n"/>
+      <c r="E19" s="61" t="n"/>
+      <c r="F19" s="62" t="n"/>
+      <c r="G19" s="62" t="n"/>
+      <c r="H19" s="62" t="n"/>
+      <c r="I19" s="62" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="57" t="n">
+      <c r="A20" s="58" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D20" s="60" t="n"/>
-      <c r="E20" s="60" t="n"/>
-      <c r="F20" s="61" t="n"/>
-      <c r="G20" s="61" t="n"/>
-      <c r="H20" s="61" t="n"/>
-      <c r="I20" s="61" t="n"/>
+      <c r="D20" s="61" t="n"/>
+      <c r="E20" s="61" t="n"/>
+      <c r="F20" s="62" t="n"/>
+      <c r="G20" s="62" t="n"/>
+      <c r="H20" s="62" t="n"/>
+      <c r="I20" s="62" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="57" t="n">
+      <c r="A21" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="58" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C21" s="59" t="inlineStr">
+      <c r="C21" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D21" s="60" t="n"/>
-      <c r="E21" s="60" t="n"/>
-      <c r="F21" s="61" t="n"/>
-      <c r="G21" s="61" t="n"/>
-      <c r="H21" s="61" t="n"/>
-      <c r="I21" s="61" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="61" t="n"/>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="62" t="n"/>
+      <c r="H21" s="62" t="n"/>
+      <c r="I21" s="62" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="57" t="n">
+      <c r="A22" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="58" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C22" s="59" t="inlineStr">
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D22" s="60" t="n"/>
-      <c r="E22" s="60" t="n"/>
-      <c r="F22" s="61" t="n"/>
-      <c r="G22" s="61" t="n"/>
-      <c r="H22" s="61" t="n"/>
-      <c r="I22" s="61" t="n"/>
+      <c r="D22" s="61" t="n"/>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="62" t="n"/>
+      <c r="G22" s="62" t="n"/>
+      <c r="H22" s="62" t="n"/>
+      <c r="I22" s="62" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="57" t="n">
+      <c r="A23" s="58" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="58" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C23" s="59" t="inlineStr">
+      <c r="C23" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D23" s="60" t="n"/>
-      <c r="E23" s="60" t="n"/>
-      <c r="F23" s="61" t="n"/>
-      <c r="G23" s="61" t="n"/>
-      <c r="H23" s="61" t="n"/>
-      <c r="I23" s="61" t="n"/>
+      <c r="D23" s="61" t="n"/>
+      <c r="E23" s="61" t="n"/>
+      <c r="F23" s="62" t="n"/>
+      <c r="G23" s="62" t="n"/>
+      <c r="H23" s="62" t="n"/>
+      <c r="I23" s="62" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="57" t="n">
+      <c r="A24" s="58" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="58" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="C24" s="59" t="inlineStr">
+      <c r="C24" s="60" t="inlineStr">
         <is>
           <t>Hold (upcoming)</t>
         </is>
       </c>
-      <c r="D24" s="60" t="n"/>
-      <c r="E24" s="60" t="n"/>
-      <c r="F24" s="61" t="n"/>
-      <c r="G24" s="61" t="n"/>
-      <c r="H24" s="61" t="n"/>
-      <c r="I24" s="61" t="n"/>
+      <c r="D24" s="61" t="n"/>
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="62" t="n"/>
+      <c r="G24" s="62" t="n"/>
+      <c r="H24" s="62" t="n"/>
+      <c r="I24" s="62" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="57" t="n">
+      <c r="A25" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="58" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="C25" s="59" t="inlineStr">
+      <c r="C25" s="60" t="inlineStr">
         <is>
           <t>Exit reminder (upcoming)</t>
         </is>
       </c>
-      <c r="D25" s="60" t="n"/>
-      <c r="E25" s="60" t="n"/>
-      <c r="F25" s="61" t="n"/>
-      <c r="G25" s="61" t="n"/>
-      <c r="H25" s="61" t="n"/>
-      <c r="I25" s="61" t="n"/>
+      <c r="D25" s="61" t="n"/>
+      <c r="E25" s="61" t="n"/>
+      <c r="F25" s="62" t="n"/>
+      <c r="G25" s="62" t="n"/>
+      <c r="H25" s="62" t="n"/>
+      <c r="I25" s="62" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="57" t="n">
+      <c r="A26" s="58" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="58" t="inlineStr">
+      <c r="B26" s="59" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="C26" s="59" t="inlineStr">
+      <c r="C26" s="60" t="inlineStr">
         <is>
           <t>Exit (upcoming)</t>
         </is>
       </c>
-      <c r="D26" s="60" t="n"/>
-      <c r="E26" s="60" t="n"/>
-      <c r="F26" s="61" t="n"/>
-      <c r="G26" s="61" t="n"/>
-      <c r="H26" s="61" t="n"/>
-      <c r="I26" s="61" t="n"/>
+      <c r="D26" s="61" t="n"/>
+      <c r="E26" s="61" t="n"/>
+      <c r="F26" s="62" t="n"/>
+      <c r="G26" s="62" t="n"/>
+      <c r="H26" s="62" t="n"/>
+      <c r="I26" s="62" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7133,7 +7172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7193,11 +7232,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="D4" s="62" t="n"/>
-      <c r="E4" s="62" t="n"/>
-      <c r="F4" s="62" t="n"/>
-      <c r="G4" s="62" t="n"/>
-      <c r="H4" s="63" t="n"/>
+      <c r="D4" s="63" t="n"/>
+      <c r="E4" s="63" t="n"/>
+      <c r="F4" s="63" t="n"/>
+      <c r="G4" s="63" t="n"/>
+      <c r="H4" s="64" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="21" t="inlineStr">
@@ -7210,11 +7249,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="D5" s="62" t="n"/>
-      <c r="E5" s="62" t="n"/>
-      <c r="F5" s="62" t="n"/>
-      <c r="G5" s="62" t="n"/>
-      <c r="H5" s="63" t="n"/>
+      <c r="D5" s="63" t="n"/>
+      <c r="E5" s="63" t="n"/>
+      <c r="F5" s="63" t="n"/>
+      <c r="G5" s="63" t="n"/>
+      <c r="H5" s="64" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="21" t="inlineStr">
@@ -7227,11 +7266,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D6" s="62" t="n"/>
-      <c r="E6" s="62" t="n"/>
-      <c r="F6" s="62" t="n"/>
-      <c r="G6" s="62" t="n"/>
-      <c r="H6" s="63" t="n"/>
+      <c r="D6" s="63" t="n"/>
+      <c r="E6" s="63" t="n"/>
+      <c r="F6" s="63" t="n"/>
+      <c r="G6" s="63" t="n"/>
+      <c r="H6" s="64" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="21" t="inlineStr">
@@ -7244,11 +7283,11 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="D7" s="62" t="n"/>
-      <c r="E7" s="62" t="n"/>
-      <c r="F7" s="62" t="n"/>
-      <c r="G7" s="62" t="n"/>
-      <c r="H7" s="63" t="n"/>
+      <c r="D7" s="63" t="n"/>
+      <c r="E7" s="63" t="n"/>
+      <c r="F7" s="63" t="n"/>
+      <c r="G7" s="63" t="n"/>
+      <c r="H7" s="64" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="21" t="inlineStr">
@@ -7261,11 +7300,11 @@
           <t>21 sessions — no stop, no target</t>
         </is>
       </c>
-      <c r="D8" s="62" t="n"/>
-      <c r="E8" s="62" t="n"/>
-      <c r="F8" s="62" t="n"/>
-      <c r="G8" s="62" t="n"/>
-      <c r="H8" s="63" t="n"/>
+      <c r="D8" s="63" t="n"/>
+      <c r="E8" s="63" t="n"/>
+      <c r="F8" s="63" t="n"/>
+      <c r="G8" s="63" t="n"/>
+      <c r="H8" s="64" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="21" t="inlineStr">
@@ -7278,11 +7317,11 @@
           <t>liquidity top 400 of all NSE stocks</t>
         </is>
       </c>
-      <c r="D9" s="62" t="n"/>
-      <c r="E9" s="62" t="n"/>
-      <c r="F9" s="62" t="n"/>
-      <c r="G9" s="62" t="n"/>
-      <c r="H9" s="63" t="n"/>
+      <c r="D9" s="63" t="n"/>
+      <c r="E9" s="63" t="n"/>
+      <c r="F9" s="63" t="n"/>
+      <c r="G9" s="63" t="n"/>
+      <c r="H9" s="64" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="21" t="inlineStr">
@@ -7290,14 +7329,14 @@
           <t>Capital committed (at signal close)</t>
         </is>
       </c>
-      <c r="C10" s="64" t="n">
+      <c r="C10" s="65" t="n">
         <v>139903</v>
       </c>
-      <c r="D10" s="62" t="n"/>
-      <c r="E10" s="62" t="n"/>
-      <c r="F10" s="62" t="n"/>
-      <c r="G10" s="62" t="n"/>
-      <c r="H10" s="63" t="n"/>
+      <c r="D10" s="63" t="n"/>
+      <c r="E10" s="63" t="n"/>
+      <c r="F10" s="63" t="n"/>
+      <c r="G10" s="63" t="n"/>
+      <c r="H10" s="64" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="21" t="inlineStr">
@@ -7305,14 +7344,14 @@
           <t>Estimated costs</t>
         </is>
       </c>
-      <c r="C11" s="64" t="n">
+      <c r="C11" s="65" t="n">
         <v>859</v>
       </c>
-      <c r="D11" s="62" t="n"/>
-      <c r="E11" s="62" t="n"/>
-      <c r="F11" s="62" t="n"/>
-      <c r="G11" s="62" t="n"/>
-      <c r="H11" s="63" t="n"/>
+      <c r="D11" s="63" t="n"/>
+      <c r="E11" s="63" t="n"/>
+      <c r="F11" s="63" t="n"/>
+      <c r="G11" s="63" t="n"/>
+      <c r="H11" s="64" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="21" t="inlineStr">
@@ -7325,11 +7364,11 @@
           <t>0.6%</t>
         </is>
       </c>
-      <c r="D12" s="62" t="n"/>
-      <c r="E12" s="62" t="n"/>
-      <c r="F12" s="62" t="n"/>
-      <c r="G12" s="62" t="n"/>
-      <c r="H12" s="63" t="n"/>
+      <c r="D12" s="63" t="n"/>
+      <c r="E12" s="63" t="n"/>
+      <c r="F12" s="63" t="n"/>
+      <c r="G12" s="63" t="n"/>
+      <c r="H12" s="64" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="21" t="inlineStr">
@@ -7342,11 +7381,11 @@
           <t>Down — the signal's weakest regime historically</t>
         </is>
       </c>
-      <c r="D13" s="62" t="n"/>
-      <c r="E13" s="62" t="n"/>
-      <c r="F13" s="62" t="n"/>
-      <c r="G13" s="62" t="n"/>
-      <c r="H13" s="63" t="n"/>
+      <c r="D13" s="63" t="n"/>
+      <c r="E13" s="63" t="n"/>
+      <c r="F13" s="63" t="n"/>
+      <c r="G13" s="63" t="n"/>
+      <c r="H13" s="64" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="21" t="inlineStr">
@@ -7359,11 +7398,11 @@
           <t>0 of 10</t>
         </is>
       </c>
-      <c r="D14" s="62" t="n"/>
-      <c r="E14" s="62" t="n"/>
-      <c r="F14" s="62" t="n"/>
-      <c r="G14" s="62" t="n"/>
-      <c r="H14" s="63" t="n"/>
+      <c r="D14" s="63" t="n"/>
+      <c r="E14" s="63" t="n"/>
+      <c r="F14" s="63" t="n"/>
+      <c r="G14" s="63" t="n"/>
+      <c r="H14" s="64" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="14" t="inlineStr">
@@ -8000,16 +8039,30 @@
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
-      <c r="B31" s="65" t="inlineStr">
+      <c r="B31" s="66" t="inlineStr">
         <is>
           <t>Backtest, 2017–2026 | Replayed point in time on your survivorship-free archive. Not live results. | Signal strength | IC +0.041 | rank IC over 113 monthly dates, 2017-2026 (t 2.52); validated benchmark 0.026 | Top vs bottom decile | +1.89% | per 21-session hold, before costs (t 2.94) | Top-10 picks | +1.45% | per hold after 0.60% costs; Nifty 50 earned +1.02% before costs | Entry timing | Open wins | buying at the open beat all 30 support-entry rules (best -0.12% per hold) | Down markets | IC +0.009 | over 27 down-regime dates, against +0.050 over 86 up-regime dates</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1">
-      <c r="B32" s="65" t="inlineStr">
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>Live record | No results yet | The first live result arrives when this system finishes its first batch. Live results are kept apart from the backtest and never mixed in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Corporate actions (splits, bonuses, dividends)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>None recorded during this hold.</t>
         </is>
       </c>
     </row>
@@ -8142,23 +8195,25 @@
           <t>Laurus Labs</t>
         </is>
       </c>
-      <c r="D5" s="66" t="inlineStr">
+      <c r="D5" s="67" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="E5" s="67" t="n">
+      <c r="E5" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="68" t="inlineStr">
+      <c r="F5" s="69" t="inlineStr">
         <is>
           <t>Relative strength near highs, lowest volatility, defensive sector</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n"/>
+      <c r="G5" s="18" t="n">
+        <v>-0.02063641312416487</v>
+      </c>
       <c r="H5" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✗ Off track</t>
         </is>
       </c>
     </row>
@@ -8176,23 +8231,25 @@
           <t>TD Power Systems</t>
         </is>
       </c>
-      <c r="D6" s="69" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="E6" s="67" t="n">
+      <c r="E6" s="68" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="68" t="inlineStr">
+      <c r="F6" s="69" t="inlineStr">
         <is>
           <t>Guidance raised, shallow pullback. Check for a fundraise.</t>
         </is>
       </c>
-      <c r="G6" s="18" t="n"/>
+      <c r="G6" s="18" t="n">
+        <v>0.08115438108484006</v>
+      </c>
       <c r="H6" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✓ On track</t>
         </is>
       </c>
     </row>
@@ -8210,23 +8267,25 @@
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="D7" s="70" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="E7" s="67" t="n">
+      <c r="E7" s="68" t="n">
         <v>1.25</v>
       </c>
-      <c r="F7" s="68" t="inlineStr">
+      <c r="F7" s="69" t="inlineStr">
         <is>
           <t>Strong catalysts and brokers, but still pulling back</t>
         </is>
       </c>
-      <c r="G7" s="18" t="n"/>
+      <c r="G7" s="18" t="n">
+        <v>-0.03643336529242569</v>
+      </c>
       <c r="H7" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✗ Off track</t>
         </is>
       </c>
     </row>
@@ -8244,23 +8303,25 @@
           <t>RR Kabel</t>
         </is>
       </c>
-      <c r="D8" s="70" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>Moderately bullish</t>
         </is>
       </c>
-      <c r="E8" s="67" t="n">
+      <c r="E8" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="68" t="inlineStr">
+      <c r="F8" s="69" t="inlineStr">
         <is>
           <t>Strong Q1, moderate volatility</t>
         </is>
       </c>
-      <c r="G8" s="18" t="n"/>
+      <c r="G8" s="18" t="n">
+        <v>0.02577445320757765</v>
+      </c>
       <c r="H8" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✓ On track</t>
         </is>
       </c>
     </row>
@@ -8278,23 +8339,25 @@
           <t>Aeroflex Industries</t>
         </is>
       </c>
-      <c r="D9" s="69" t="inlineStr">
+      <c r="D9" s="70" t="inlineStr">
         <is>
           <t>Bullish, risky</t>
         </is>
       </c>
-      <c r="E9" s="67" t="n">
+      <c r="E9" s="68" t="n">
         <v>1.25</v>
       </c>
-      <c r="F9" s="68" t="inlineStr">
+      <c r="F9" s="69" t="inlineStr">
         <is>
           <t>Strong growth, expensive, volatile, thin liquidity</t>
         </is>
       </c>
-      <c r="G9" s="18" t="n"/>
+      <c r="G9" s="18" t="n">
+        <v>0.05534911011148047</v>
+      </c>
       <c r="H9" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✓ On track</t>
         </is>
       </c>
     </row>
@@ -8312,23 +8375,25 @@
           <t>E2E Networks</t>
         </is>
       </c>
-      <c r="D10" s="71" t="inlineStr">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>Speculative</t>
         </is>
       </c>
-      <c r="E10" s="67" t="n">
+      <c r="E10" s="68" t="n">
         <v>0.5</v>
       </c>
-      <c r="F10" s="68" t="inlineStr">
+      <c r="F10" s="69" t="inlineStr">
         <is>
           <t>Big revenue jump, P/E near 400</t>
         </is>
       </c>
-      <c r="G10" s="18" t="n"/>
+      <c r="G10" s="18" t="n">
+        <v>0.05205391009603755</v>
+      </c>
       <c r="H10" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>↑ Beat call</t>
         </is>
       </c>
     </row>
@@ -8346,23 +8411,25 @@
           <t>Acutaas Chemicals</t>
         </is>
       </c>
-      <c r="D11" s="72" t="inlineStr">
+      <c r="D11" s="73" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="E11" s="67" t="n">
+      <c r="E11" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="68" t="inlineStr">
+      <c r="F11" s="69" t="inlineStr">
         <is>
           <t>No catalyst, sideways trend</t>
         </is>
       </c>
-      <c r="G11" s="18" t="n"/>
+      <c r="G11" s="18" t="n">
+        <v>0.004285714285714226</v>
+      </c>
       <c r="H11" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>• Neutral call</t>
         </is>
       </c>
     </row>
@@ -8380,23 +8447,25 @@
           <t>Diamond Power Infra</t>
         </is>
       </c>
-      <c r="D12" s="73" t="inlineStr">
+      <c r="D12" s="74" t="inlineStr">
         <is>
           <t>Neutral to bearish</t>
         </is>
       </c>
-      <c r="E12" s="67" t="n">
+      <c r="E12" s="68" t="n">
         <v>-1</v>
       </c>
-      <c r="F12" s="68" t="inlineStr">
+      <c r="F12" s="69" t="inlineStr">
         <is>
           <t>Extended, weak balance sheet</t>
         </is>
       </c>
-      <c r="G12" s="18" t="n"/>
+      <c r="G12" s="18" t="n">
+        <v>0.04496883348174552</v>
+      </c>
       <c r="H12" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✗ Off track</t>
         </is>
       </c>
     </row>
@@ -8414,23 +8483,25 @@
           <t>Kirloskar Oil Engines</t>
         </is>
       </c>
-      <c r="D13" s="73" t="inlineStr">
+      <c r="D13" s="74" t="inlineStr">
         <is>
           <t>Neutral to bearish</t>
         </is>
       </c>
-      <c r="E13" s="67" t="n">
+      <c r="E13" s="68" t="n">
         <v>-1</v>
       </c>
-      <c r="F13" s="68" t="inlineStr">
+      <c r="F13" s="69" t="inlineStr">
         <is>
           <t>Margins and momentum fading</t>
         </is>
       </c>
-      <c r="G13" s="18" t="n"/>
+      <c r="G13" s="18" t="n">
+        <v>0.1218008593312163</v>
+      </c>
       <c r="H13" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✗ Off track</t>
         </is>
       </c>
     </row>
@@ -8448,28 +8519,30 @@
           <t>Thangamayil Jewellery</t>
         </is>
       </c>
-      <c r="D14" s="74" t="inlineStr">
+      <c r="D14" s="75" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="E14" s="67" t="n">
+      <c r="E14" s="68" t="n">
         <v>-2</v>
       </c>
-      <c r="F14" s="68" t="inlineStr">
+      <c r="F14" s="69" t="inlineStr">
         <is>
           <t>Downtrend, avoid</t>
         </is>
       </c>
-      <c r="G14" s="18" t="n"/>
+      <c r="G14" s="18" t="n">
+        <v>0.03882235528942113</v>
+      </c>
       <c r="H14" s="51" t="inlineStr">
         <is>
-          <t>awaiting Day 1</t>
+          <t>✗ Off track</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="75" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr">
         <is>
           <t>STOCK BY STOCK — catalysts, risks and sources</t>
         </is>
@@ -8527,17 +8600,17 @@
           <t>Laurus Labs</t>
         </is>
       </c>
-      <c r="D18" s="76" t="inlineStr">
+      <c r="D18" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E18" s="68" t="inlineStr">
+      <c r="E18" s="69" t="inlineStr">
         <is>
           <t>Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).</t>
         </is>
       </c>
-      <c r="F18" s="63" t="n"/>
+      <c r="F18" s="64" t="n"/>
       <c r="G18" s="51" t="inlineStr"/>
       <c r="H18" s="51" t="n"/>
     </row>
@@ -8555,23 +8628,23 @@
           <t>Laurus Labs</t>
         </is>
       </c>
-      <c r="D19" s="76" t="inlineStr">
+      <c r="D19" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E19" s="68" t="inlineStr">
+      <c r="E19" s="69" t="inlineStr">
         <is>
           <t>FY26 profit after tax was ₹740 crore vs ₹380 crore the year before.</t>
         </is>
       </c>
-      <c r="F19" s="63" t="n"/>
+      <c r="F19" s="64" t="n"/>
       <c r="G19" s="51" t="inlineStr">
         <is>
           <t>torusdigital</t>
         </is>
       </c>
-      <c r="H19" s="77" t="inlineStr">
+      <c r="H19" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8591,23 +8664,23 @@
           <t>Laurus Labs</t>
         </is>
       </c>
-      <c r="D20" s="76" t="inlineStr">
+      <c r="D20" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E20" s="68" t="inlineStr">
+      <c r="E20" s="69" t="inlineStr">
         <is>
           <t>It is up about 94% in six months and holding near highs while the index falls.</t>
         </is>
       </c>
-      <c r="F20" s="63" t="n"/>
+      <c r="F20" s="64" t="n"/>
       <c r="G20" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H20" s="77" t="inlineStr">
+      <c r="H20" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8627,23 +8700,23 @@
           <t>Laurus Labs</t>
         </is>
       </c>
-      <c r="D21" s="76" t="inlineStr">
+      <c r="D21" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E21" s="68" t="inlineStr">
+      <c r="E21" s="69" t="inlineStr">
         <is>
           <t>Pharma is also defensive in a risk-off tape.</t>
         </is>
       </c>
-      <c r="F21" s="63" t="n"/>
+      <c r="F21" s="64" t="n"/>
       <c r="G21" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H21" s="77" t="inlineStr">
+      <c r="H21" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8663,23 +8736,23 @@
           <t>Laurus Labs</t>
         </is>
       </c>
-      <c r="D22" s="78" t="inlineStr">
+      <c r="D22" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E22" s="68" t="inlineStr">
+      <c r="E22" s="69" t="inlineStr">
         <is>
           <t>P/E is high, so it can still pull back.</t>
         </is>
       </c>
-      <c r="F22" s="63" t="n"/>
+      <c r="F22" s="64" t="n"/>
       <c r="G22" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H22" s="77" t="inlineStr">
+      <c r="H22" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8699,17 +8772,17 @@
           <t>TD Power Systems</t>
         </is>
       </c>
-      <c r="D23" s="79" t="inlineStr">
+      <c r="D23" s="80" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="E23" s="68" t="inlineStr">
+      <c r="E23" s="69" t="inlineStr">
         <is>
           <t>The stock is 10% below its high, a shallow pullback within a strong uptrend.</t>
         </is>
       </c>
-      <c r="F23" s="63" t="n"/>
+      <c r="F23" s="64" t="n"/>
       <c r="G23" s="51" t="inlineStr"/>
       <c r="H23" s="51" t="n"/>
     </row>
@@ -8727,23 +8800,23 @@
           <t>TD Power Systems</t>
         </is>
       </c>
-      <c r="D24" s="76" t="inlineStr">
+      <c r="D24" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E24" s="68" t="inlineStr">
+      <c r="E24" s="69" t="inlineStr">
         <is>
           <t>Q1 FY27 revenue rose about 72% YoY.</t>
         </is>
       </c>
-      <c r="F24" s="63" t="n"/>
+      <c r="F24" s="64" t="n"/>
       <c r="G24" s="51" t="inlineStr">
         <is>
           <t>5paisa</t>
         </is>
       </c>
-      <c r="H24" s="77" t="inlineStr">
+      <c r="H24" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8763,23 +8836,23 @@
           <t>TD Power Systems</t>
         </is>
       </c>
-      <c r="D25" s="76" t="inlineStr">
+      <c r="D25" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E25" s="68" t="inlineStr">
+      <c r="E25" s="69" t="inlineStr">
         <is>
           <t>It raised its FY27 revenue guidance to ₹2,600 crore.</t>
         </is>
       </c>
-      <c r="F25" s="63" t="n"/>
+      <c r="F25" s="64" t="n"/>
       <c r="G25" s="51" t="inlineStr">
         <is>
           <t>fyers</t>
         </is>
       </c>
-      <c r="H25" s="77" t="inlineStr">
+      <c r="H25" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8799,23 +8872,23 @@
           <t>TD Power Systems</t>
         </is>
       </c>
-      <c r="D26" s="78" t="inlineStr">
+      <c r="D26" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E26" s="68" t="inlineStr">
+      <c r="E26" s="69" t="inlineStr">
         <is>
           <t>A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.</t>
         </is>
       </c>
-      <c r="F26" s="63" t="n"/>
+      <c r="F26" s="64" t="n"/>
       <c r="G26" s="51" t="inlineStr">
         <is>
           <t>5paisa</t>
         </is>
       </c>
-      <c r="H26" s="77" t="inlineStr">
+      <c r="H26" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8835,23 +8908,23 @@
           <t>TD Power Systems</t>
         </is>
       </c>
-      <c r="D27" s="78" t="inlineStr">
+      <c r="D27" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E27" s="68" t="inlineStr">
+      <c r="E27" s="69" t="inlineStr">
         <is>
           <t>Valuation is stretched (P/E around 70).</t>
         </is>
       </c>
-      <c r="F27" s="63" t="n"/>
+      <c r="F27" s="64" t="n"/>
       <c r="G27" s="51" t="inlineStr">
         <is>
           <t>5paisa</t>
         </is>
       </c>
-      <c r="H27" s="77" t="inlineStr">
+      <c r="H27" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8871,23 +8944,23 @@
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="D28" s="76" t="inlineStr">
+      <c r="D28" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E28" s="68" t="inlineStr">
+      <c r="E28" s="69" t="inlineStr">
         <is>
           <t>Q1 revenue grew 89% and the loss narrowed 71%.</t>
         </is>
       </c>
-      <c r="F28" s="63" t="n"/>
+      <c r="F28" s="64" t="n"/>
       <c r="G28" s="51" t="inlineStr">
         <is>
           <t>indmoney</t>
         </is>
       </c>
-      <c r="H28" s="77" t="inlineStr">
+      <c r="H28" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8907,23 +8980,23 @@
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="D29" s="76" t="inlineStr">
+      <c r="D29" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E29" s="68" t="inlineStr">
+      <c r="E29" s="69" t="inlineStr">
         <is>
           <t>It was also added to the MSCI India Domestic Small Cap Index.</t>
         </is>
       </c>
-      <c r="F29" s="63" t="n"/>
+      <c r="F29" s="64" t="n"/>
       <c r="G29" s="51" t="inlineStr">
         <is>
           <t>indmoney</t>
         </is>
       </c>
-      <c r="H29" s="77" t="inlineStr">
+      <c r="H29" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8943,23 +9016,23 @@
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="D30" s="76" t="inlineStr">
+      <c r="D30" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E30" s="68" t="inlineStr">
+      <c r="E30" s="69" t="inlineStr">
         <is>
           <t>Hero MotoCorp is lifting its stake to about 32.8%.</t>
         </is>
       </c>
-      <c r="F30" s="63" t="n"/>
+      <c r="F30" s="64" t="n"/>
       <c r="G30" s="51" t="inlineStr">
         <is>
           <t>freepressjournal</t>
         </is>
       </c>
-      <c r="H30" s="77" t="inlineStr">
+      <c r="H30" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8979,23 +9052,23 @@
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="D31" s="76" t="inlineStr">
+      <c r="D31" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E31" s="68" t="inlineStr">
+      <c r="E31" s="69" t="inlineStr">
         <is>
           <t>A global broker raised its target to ₹1,926.</t>
         </is>
       </c>
-      <c r="F31" s="63" t="n"/>
+      <c r="F31" s="64" t="n"/>
       <c r="G31" s="51" t="inlineStr">
         <is>
           <t>hdfcsky</t>
         </is>
       </c>
-      <c r="H31" s="77" t="inlineStr">
+      <c r="H31" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9015,17 +9088,17 @@
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="D32" s="79" t="inlineStr">
+      <c r="D32" s="80" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="E32" s="68" t="inlineStr">
+      <c r="E32" s="69" t="inlineStr">
         <is>
           <t>The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.</t>
         </is>
       </c>
-      <c r="F32" s="63" t="n"/>
+      <c r="F32" s="64" t="n"/>
       <c r="G32" s="51" t="inlineStr"/>
       <c r="H32" s="51" t="n"/>
     </row>
@@ -9043,17 +9116,17 @@
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="D33" s="76" t="inlineStr">
+      <c r="D33" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E33" s="68" t="inlineStr">
+      <c r="E33" s="69" t="inlineStr">
         <is>
           <t>High oil prices are a tailwind for the EV theme.</t>
         </is>
       </c>
-      <c r="F33" s="63" t="n"/>
+      <c r="F33" s="64" t="n"/>
       <c r="G33" s="51" t="inlineStr"/>
       <c r="H33" s="51" t="n"/>
     </row>
@@ -9071,23 +9144,23 @@
           <t>RR Kabel</t>
         </is>
       </c>
-      <c r="D34" s="76" t="inlineStr">
+      <c r="D34" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E34" s="68" t="inlineStr">
+      <c r="E34" s="69" t="inlineStr">
         <is>
           <t>Q1 PAT jumped 129% and EBITDA doubled.</t>
         </is>
       </c>
-      <c r="F34" s="63" t="n"/>
+      <c r="F34" s="64" t="n"/>
       <c r="G34" s="51" t="inlineStr">
         <is>
           <t>5paisa</t>
         </is>
       </c>
-      <c r="H34" s="77" t="inlineStr">
+      <c r="H34" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9107,23 +9180,23 @@
           <t>RR Kabel</t>
         </is>
       </c>
-      <c r="D35" s="76" t="inlineStr">
+      <c r="D35" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E35" s="68" t="inlineStr">
+      <c r="E35" s="69" t="inlineStr">
         <is>
           <t>CLSA initiated at Outperform with a ₹2,850 target.</t>
         </is>
       </c>
-      <c r="F35" s="63" t="n"/>
+      <c r="F35" s="64" t="n"/>
       <c r="G35" s="51" t="inlineStr">
         <is>
           <t>fyers</t>
         </is>
       </c>
-      <c r="H35" s="77" t="inlineStr">
+      <c r="H35" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9143,17 +9216,17 @@
           <t>RR Kabel</t>
         </is>
       </c>
-      <c r="D36" s="79" t="inlineStr">
+      <c r="D36" s="80" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="E36" s="68" t="inlineStr">
+      <c r="E36" s="69" t="inlineStr">
         <is>
           <t>The stock is 16% off its high, so it is consolidating.</t>
         </is>
       </c>
-      <c r="F36" s="63" t="n"/>
+      <c r="F36" s="64" t="n"/>
       <c r="G36" s="51" t="inlineStr"/>
       <c r="H36" s="51" t="n"/>
     </row>
@@ -9171,17 +9244,17 @@
           <t>RR Kabel</t>
         </is>
       </c>
-      <c r="D37" s="76" t="inlineStr">
+      <c r="D37" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E37" s="68" t="inlineStr">
+      <c r="E37" s="69" t="inlineStr">
         <is>
           <t>Volatility is moderate (44%), which is better than most here.</t>
         </is>
       </c>
-      <c r="F37" s="63" t="n"/>
+      <c r="F37" s="64" t="n"/>
       <c r="G37" s="51" t="inlineStr"/>
       <c r="H37" s="51" t="n"/>
     </row>
@@ -9199,23 +9272,23 @@
           <t>Aeroflex Industries</t>
         </is>
       </c>
-      <c r="D38" s="76" t="inlineStr">
+      <c r="D38" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E38" s="68" t="inlineStr">
+      <c r="E38" s="69" t="inlineStr">
         <is>
           <t>Q1 FY27 revenue grew 72.4% and PAT rose 162%.</t>
         </is>
       </c>
-      <c r="F38" s="63" t="n"/>
+      <c r="F38" s="64" t="n"/>
       <c r="G38" s="51" t="inlineStr">
         <is>
           <t>sahi</t>
         </is>
       </c>
-      <c r="H38" s="77" t="inlineStr">
+      <c r="H38" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9235,23 +9308,23 @@
           <t>Aeroflex Industries</t>
         </is>
       </c>
-      <c r="D39" s="76" t="inlineStr">
+      <c r="D39" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E39" s="68" t="inlineStr">
+      <c r="E39" s="69" t="inlineStr">
         <is>
           <t>Liquid-cooling skid capacity was raised 50%, with further expansion planned.</t>
         </is>
       </c>
-      <c r="F39" s="63" t="n"/>
+      <c r="F39" s="64" t="n"/>
       <c r="G39" s="51" t="inlineStr">
         <is>
           <t>sahi</t>
         </is>
       </c>
-      <c r="H39" s="77" t="inlineStr">
+      <c r="H39" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9271,23 +9344,23 @@
           <t>Aeroflex Industries</t>
         </is>
       </c>
-      <c r="D40" s="78" t="inlineStr">
+      <c r="D40" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E40" s="68" t="inlineStr">
+      <c r="E40" s="69" t="inlineStr">
         <is>
           <t>P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (₹53 cr/day).</t>
         </is>
       </c>
-      <c r="F40" s="63" t="n"/>
+      <c r="F40" s="64" t="n"/>
       <c r="G40" s="51" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="H40" s="77" t="inlineStr">
+      <c r="H40" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9307,23 +9380,23 @@
           <t>Aeroflex Industries</t>
         </is>
       </c>
-      <c r="D41" s="78" t="inlineStr">
+      <c r="D41" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E41" s="68" t="inlineStr">
+      <c r="E41" s="69" t="inlineStr">
         <is>
           <t>That makes it the most fragile in a falling market.</t>
         </is>
       </c>
-      <c r="F41" s="63" t="n"/>
+      <c r="F41" s="64" t="n"/>
       <c r="G41" s="51" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="H41" s="77" t="inlineStr">
+      <c r="H41" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9343,23 +9416,23 @@
           <t>E2E Networks</t>
         </is>
       </c>
-      <c r="D42" s="76" t="inlineStr">
+      <c r="D42" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E42" s="68" t="inlineStr">
+      <c r="E42" s="69" t="inlineStr">
         <is>
           <t>Q1 revenue was ₹156.76 crore vs ₹36.11 crore a year earlier, with a profit of ₹43.88 crore, on GPU cluster expansion.</t>
         </is>
       </c>
-      <c r="F42" s="63" t="n"/>
+      <c r="F42" s="64" t="n"/>
       <c r="G42" s="51" t="inlineStr">
         <is>
           <t>angelone</t>
         </is>
       </c>
-      <c r="H42" s="77" t="inlineStr">
+      <c r="H42" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9379,23 +9452,23 @@
           <t>E2E Networks</t>
         </is>
       </c>
-      <c r="D43" s="78" t="inlineStr">
+      <c r="D43" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E43" s="68" t="inlineStr">
+      <c r="E43" s="69" t="inlineStr">
         <is>
           <t>P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.</t>
         </is>
       </c>
-      <c r="F43" s="63" t="n"/>
+      <c r="F43" s="64" t="n"/>
       <c r="G43" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H43" s="77" t="inlineStr">
+      <c r="H43" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9415,23 +9488,23 @@
           <t>E2E Networks</t>
         </is>
       </c>
-      <c r="D44" s="79" t="inlineStr">
+      <c r="D44" s="80" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="E44" s="68" t="inlineStr">
+      <c r="E44" s="69" t="inlineStr">
         <is>
           <t>It has bounced since.</t>
         </is>
       </c>
-      <c r="F44" s="63" t="n"/>
+      <c r="F44" s="64" t="n"/>
       <c r="G44" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H44" s="77" t="inlineStr">
+      <c r="H44" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9451,17 +9524,17 @@
           <t>E2E Networks</t>
         </is>
       </c>
-      <c r="D45" s="78" t="inlineStr">
+      <c r="D45" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E45" s="68" t="inlineStr">
+      <c r="E45" s="69" t="inlineStr">
         <is>
           <t>It is an AI-theme stock with thin liquidity and gap risk in both directions.</t>
         </is>
       </c>
-      <c r="F45" s="63" t="n"/>
+      <c r="F45" s="64" t="n"/>
       <c r="G45" s="51" t="inlineStr"/>
       <c r="H45" s="51" t="n"/>
     </row>
@@ -9479,23 +9552,23 @@
           <t>Acutaas Chemicals</t>
         </is>
       </c>
-      <c r="D46" s="76" t="inlineStr">
+      <c r="D46" s="77" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="E46" s="68" t="inlineStr">
+      <c r="E46" s="69" t="inlineStr">
         <is>
           <t>It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.</t>
         </is>
       </c>
-      <c r="F46" s="63" t="n"/>
+      <c r="F46" s="64" t="n"/>
       <c r="G46" s="51" t="inlineStr">
         <is>
           <t>fyers</t>
         </is>
       </c>
-      <c r="H46" s="77" t="inlineStr">
+      <c r="H46" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9515,23 +9588,23 @@
           <t>Acutaas Chemicals</t>
         </is>
       </c>
-      <c r="D47" s="78" t="inlineStr">
+      <c r="D47" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E47" s="68" t="inlineStr">
+      <c r="E47" s="69" t="inlineStr">
         <is>
           <t>Quarterly revenue and profit were lower sequentially (₹327 cr and ₹76 cr in Jun vs ₹436 cr and ₹137 cr in Mar).</t>
         </is>
       </c>
-      <c r="F47" s="63" t="n"/>
+      <c r="F47" s="64" t="n"/>
       <c r="G47" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H47" s="77" t="inlineStr">
+      <c r="H47" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9551,23 +9624,23 @@
           <t>Acutaas Chemicals</t>
         </is>
       </c>
-      <c r="D48" s="78" t="inlineStr">
+      <c r="D48" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E48" s="68" t="inlineStr">
+      <c r="E48" s="69" t="inlineStr">
         <is>
           <t>The 6-1 return is negative.</t>
         </is>
       </c>
-      <c r="F48" s="63" t="n"/>
+      <c r="F48" s="64" t="n"/>
       <c r="G48" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H48" s="77" t="inlineStr">
+      <c r="H48" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9587,17 +9660,17 @@
           <t>Acutaas Chemicals</t>
         </is>
       </c>
-      <c r="D49" s="78" t="inlineStr">
+      <c r="D49" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E49" s="68" t="inlineStr">
+      <c r="E49" s="69" t="inlineStr">
         <is>
           <t>The price has moved sideways since June.</t>
         </is>
       </c>
-      <c r="F49" s="63" t="n"/>
+      <c r="F49" s="64" t="n"/>
       <c r="G49" s="51" t="inlineStr"/>
       <c r="H49" s="51" t="n"/>
     </row>
@@ -9615,17 +9688,17 @@
           <t>Acutaas Chemicals</t>
         </is>
       </c>
-      <c r="D50" s="78" t="inlineStr">
+      <c r="D50" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E50" s="68" t="inlineStr">
+      <c r="E50" s="69" t="inlineStr">
         <is>
           <t>There is no clear trigger for a 21-day move.</t>
         </is>
       </c>
-      <c r="F50" s="63" t="n"/>
+      <c r="F50" s="64" t="n"/>
       <c r="G50" s="51" t="inlineStr"/>
       <c r="H50" s="51" t="n"/>
     </row>
@@ -9643,23 +9716,23 @@
           <t>Diamond Power Infra</t>
         </is>
       </c>
-      <c r="D51" s="78" t="inlineStr">
+      <c r="D51" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E51" s="68" t="inlineStr">
+      <c r="E51" s="69" t="inlineStr">
         <is>
           <t>It hit a 52-week high of about ₹395 on 17 Sep, up 202% in six months, with a P/E near 128.</t>
         </is>
       </c>
-      <c r="F51" s="63" t="n"/>
+      <c r="F51" s="64" t="n"/>
       <c r="G51" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H51" s="77" t="inlineStr">
+      <c r="H51" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9679,23 +9752,23 @@
           <t>Diamond Power Infra</t>
         </is>
       </c>
-      <c r="D52" s="78" t="inlineStr">
+      <c r="D52" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E52" s="68" t="inlineStr">
+      <c r="E52" s="69" t="inlineStr">
         <is>
           <t>Book value per share was negative in the July data.</t>
         </is>
       </c>
-      <c r="F52" s="63" t="n"/>
+      <c r="F52" s="64" t="n"/>
       <c r="G52" s="51" t="inlineStr">
         <is>
           <t>bajajfinserv</t>
         </is>
       </c>
-      <c r="H52" s="77" t="inlineStr">
+      <c r="H52" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9715,17 +9788,17 @@
           <t>Diamond Power Infra</t>
         </is>
       </c>
-      <c r="D53" s="78" t="inlineStr">
+      <c r="D53" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E53" s="68" t="inlineStr">
+      <c r="E53" s="69" t="inlineStr">
         <is>
           <t>It is now 14% off that high.</t>
         </is>
       </c>
-      <c r="F53" s="63" t="n"/>
+      <c r="F53" s="64" t="n"/>
       <c r="G53" s="51" t="inlineStr"/>
       <c r="H53" s="51" t="n"/>
     </row>
@@ -9743,17 +9816,17 @@
           <t>Diamond Power Infra</t>
         </is>
       </c>
-      <c r="D54" s="79" t="inlineStr">
+      <c r="D54" s="80" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="E54" s="68" t="inlineStr">
+      <c r="E54" s="69" t="inlineStr">
         <is>
           <t>The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.</t>
         </is>
       </c>
-      <c r="F54" s="63" t="n"/>
+      <c r="F54" s="64" t="n"/>
       <c r="G54" s="51" t="inlineStr"/>
       <c r="H54" s="51" t="n"/>
     </row>
@@ -9771,23 +9844,23 @@
           <t>Kirloskar Oil Engines</t>
         </is>
       </c>
-      <c r="D55" s="78" t="inlineStr">
+      <c r="D55" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E55" s="68" t="inlineStr">
+      <c r="E55" s="69" t="inlineStr">
         <is>
           <t>June-quarter revenue was ₹1,482 cr vs ₹1,284 cr a year ago, but EBITDA slipped to ₹176 cr from ₹184 cr, so margins are compressing.</t>
         </is>
       </c>
-      <c r="F55" s="63" t="n"/>
+      <c r="F55" s="64" t="n"/>
       <c r="G55" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H55" s="77" t="inlineStr">
+      <c r="H55" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9807,17 +9880,17 @@
           <t>Kirloskar Oil Engines</t>
         </is>
       </c>
-      <c r="D56" s="78" t="inlineStr">
+      <c r="D56" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E56" s="68" t="inlineStr">
+      <c r="E56" s="69" t="inlineStr">
         <is>
           <t>The 6-1 return is −11% and the stock is 16.5% below its high.</t>
         </is>
       </c>
-      <c r="F56" s="63" t="n"/>
+      <c r="F56" s="64" t="n"/>
       <c r="G56" s="51" t="inlineStr"/>
       <c r="H56" s="51" t="n"/>
     </row>
@@ -9835,17 +9908,17 @@
           <t>Kirloskar Oil Engines</t>
         </is>
       </c>
-      <c r="D57" s="78" t="inlineStr">
+      <c r="D57" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E57" s="68" t="inlineStr">
+      <c r="E57" s="69" t="inlineStr">
         <is>
           <t>Momentum is fading.</t>
         </is>
       </c>
-      <c r="F57" s="63" t="n"/>
+      <c r="F57" s="64" t="n"/>
       <c r="G57" s="51" t="inlineStr"/>
       <c r="H57" s="51" t="n"/>
     </row>
@@ -9863,23 +9936,23 @@
           <t>Thangamayil Jewellery</t>
         </is>
       </c>
-      <c r="D58" s="79" t="inlineStr">
+      <c r="D58" s="80" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="E58" s="68" t="inlineStr">
+      <c r="E58" s="69" t="inlineStr">
         <is>
           <t>It hit a high of ₹7,429 and traded near ₹5,085 on 22 Sep.</t>
         </is>
       </c>
-      <c r="F58" s="63" t="n"/>
+      <c r="F58" s="64" t="n"/>
       <c r="G58" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H58" s="77" t="inlineStr">
+      <c r="H58" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9899,23 +9972,23 @@
           <t>Thangamayil Jewellery</t>
         </is>
       </c>
-      <c r="D59" s="78" t="inlineStr">
+      <c r="D59" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E59" s="68" t="inlineStr">
+      <c r="E59" s="69" t="inlineStr">
         <is>
           <t>It is now about 31% below the peak.</t>
         </is>
       </c>
-      <c r="F59" s="63" t="n"/>
+      <c r="F59" s="64" t="n"/>
       <c r="G59" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H59" s="77" t="inlineStr">
+      <c r="H59" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9935,23 +10008,23 @@
           <t>Thangamayil Jewellery</t>
         </is>
       </c>
-      <c r="D60" s="78" t="inlineStr">
+      <c r="D60" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E60" s="68" t="inlineStr">
+      <c r="E60" s="69" t="inlineStr">
         <is>
           <t>Q1 EBITDA (₹145 cr) fell from ₹214 cr in the March quarter.</t>
         </is>
       </c>
-      <c r="F60" s="63" t="n"/>
+      <c r="F60" s="64" t="n"/>
       <c r="G60" s="51" t="inlineStr">
         <is>
           <t>anandrathi</t>
         </is>
       </c>
-      <c r="H60" s="77" t="inlineStr">
+      <c r="H60" s="78" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9971,17 +10044,17 @@
           <t>Thangamayil Jewellery</t>
         </is>
       </c>
-      <c r="D61" s="78" t="inlineStr">
+      <c r="D61" s="79" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E61" s="68" t="inlineStr">
+      <c r="E61" s="69" t="inlineStr">
         <is>
           <t>It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.</t>
         </is>
       </c>
-      <c r="F61" s="63" t="n"/>
+      <c r="F61" s="64" t="n"/>
       <c r="G61" s="51" t="inlineStr"/>
       <c r="H61" s="51" t="n"/>
     </row>
@@ -10095,7 +10168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10123,7 +10196,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fetched 2026-09-29 03:09</t>
+          <t>Fetched 2026-09-29 17:07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10173,33 +10246,33 @@
     <row r="5">
       <c r="A5" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B5" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:10</t>
+          <t>2026-09-29 15:41</t>
         </is>
       </c>
       <c r="C5" s="51" t="inlineStr">
         <is>
-          <t>3 Indian Nuclear Stocks With Earnings Growth Over 17%</t>
+          <t>Sensex, Nifty End Lower for Second Day; Global Tensions, FII Selling Hurt Investor Mood</t>
         </is>
       </c>
       <c r="D5" s="51" t="inlineStr">
         <is>
-          <t>Simply Wall St.</t>
-        </is>
-      </c>
-      <c r="E5" s="80" t="n">
-        <v>0.888</v>
+          <t>The Indian Awaaz</t>
+        </is>
+      </c>
+      <c r="E5" s="81" t="n">
+        <v>-0.637</v>
       </c>
       <c r="F5" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G5" s="81" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G5" s="82" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10208,33 +10281,5073 @@
     <row r="6">
       <c r="A6" s="51" t="inlineStr">
         <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:34</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>Markets ride expiry-day seesaw as derivatives swings jolt Nifty</t>
+        </is>
+      </c>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E6" s="81" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F6" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G6" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:51</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>The Federal</t>
+        </is>
+      </c>
+      <c r="E7" s="81" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="F7" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G7" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:14</t>
+        </is>
+      </c>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>APAC Media</t>
+        </is>
+      </c>
+      <c r="E8" s="81" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G8" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:48</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>DD India</t>
+        </is>
+      </c>
+      <c r="E9" s="81" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F9" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G9" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:19</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>equitymaster.com</t>
+        </is>
+      </c>
+      <c r="E10" s="81" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="F10" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G10" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:11</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F11" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G11" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 06:14</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty rebound from near six-month lows amid crude shock</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E12" s="81" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G12" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:26</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="E13" s="81" t="n">
+        <v>-0.599</v>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G13" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:23</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G14" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:09</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E15" s="81" t="n">
+        <v>-0.791</v>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G15" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:06</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E16" s="81" t="n">
+        <v>-0.459</v>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G16" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:38</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>BusinessLine</t>
+        </is>
+      </c>
+      <c r="E17" s="81" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G17" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:35</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Falls 400 Points; Nifty Slips Below 22,700</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E18" s="81" t="n">
+        <v>-0.318</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G18" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:35</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>equitymaster.com</t>
+        </is>
+      </c>
+      <c r="E19" s="81" t="n">
+        <v>-0.477</v>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G19" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:23</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>Ather Energy Share Price News: Today’s Decline Analyzed</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E20" s="81" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G20" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:23</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>Oil rise, bond yields: Top factors behind Tuesday's stock market fall</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E21" s="81" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="F21" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G21" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:21</t>
+        </is>
+      </c>
+      <c r="C22" s="51" t="inlineStr">
+        <is>
+          <t>No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what’s dragging the market?</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="inlineStr">
+        <is>
+          <t>fortuneindia.com</t>
+        </is>
+      </c>
+      <c r="E22" s="81" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G22" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B23" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:21</t>
+        </is>
+      </c>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty sink further; What is keeping the market under pressure?</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="inlineStr">
+        <is>
+          <t>newsdrum.in</t>
+        </is>
+      </c>
+      <c r="E23" s="81" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F23" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G23" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:14</t>
+        </is>
+      </c>
+      <c r="C24" s="51" t="inlineStr">
+        <is>
+          <t>Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E24" s="81" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F24" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G24" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:02</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="inlineStr">
+        <is>
+          <t>Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...</t>
+        </is>
+      </c>
+      <c r="D25" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="n">
+        <v>-0.421</v>
+      </c>
+      <c r="F25" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G25" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B26" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:01</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="inlineStr">
+        <is>
+          <t>Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="E26" s="81" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F26" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G26" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 02:57</t>
+        </is>
+      </c>
+      <c r="C27" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty opening: Will stock market crash or open higher today?</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F27" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G27" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:36</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E28" s="81" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F28" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G28" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:19</t>
+        </is>
+      </c>
+      <c r="C29" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E29" s="81" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F29" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G29" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:51</t>
+        </is>
+      </c>
+      <c r="C30" s="51" t="inlineStr">
+        <is>
+          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="inlineStr">
+        <is>
+          <t>wionews.com</t>
+        </is>
+      </c>
+      <c r="E30" s="81" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F30" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G30" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:36</t>
+        </is>
+      </c>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E31" s="81" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F31" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G31" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:42</t>
+        </is>
+      </c>
+      <c r="C32" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
+        </is>
+      </c>
+      <c r="D32" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E32" s="81" t="n">
+        <v>-0.896</v>
+      </c>
+      <c r="F32" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G32" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B33" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:25</t>
+        </is>
+      </c>
+      <c r="C33" s="51" t="inlineStr">
+        <is>
+          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="inlineStr">
+        <is>
+          <t>equitymaster.com</t>
+        </is>
+      </c>
+      <c r="E33" s="81" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="F33" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G33" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B34" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:16</t>
+        </is>
+      </c>
+      <c r="C34" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
+        </is>
+      </c>
+      <c r="D34" s="51" t="inlineStr">
+        <is>
+          <t>hrtoday.in</t>
+        </is>
+      </c>
+      <c r="E34" s="81" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="F34" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G34" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B35" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:48</t>
+        </is>
+      </c>
+      <c r="C35" s="51" t="inlineStr">
+        <is>
+          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
+        </is>
+      </c>
+      <c r="D35" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E35" s="81" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="F35" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G35" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B36" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:56</t>
+        </is>
+      </c>
+      <c r="C36" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
+        </is>
+      </c>
+      <c r="D36" s="51" t="inlineStr">
+        <is>
+          <t>equitymaster.com</t>
+        </is>
+      </c>
+      <c r="E36" s="81" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F36" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G36" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:48</t>
+        </is>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge</t>
+        </is>
+      </c>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="E37" s="81" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G37" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B38" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:46</t>
+        </is>
+      </c>
+      <c r="C38" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Falls 1,124 Points, Nifty Slips Below 22,800</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="inlineStr">
+        <is>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E38" s="81" t="n">
+        <v>-0.318</v>
+      </c>
+      <c r="F38" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G38" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B39" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:26</t>
+        </is>
+      </c>
+      <c r="C39" s="51" t="inlineStr">
+        <is>
+          <t>Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low</t>
+        </is>
+      </c>
+      <c r="D39" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E39" s="81" t="n">
+        <v>-0.612</v>
+      </c>
+      <c r="F39" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G39" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B40" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="C40" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
+        </is>
+      </c>
+      <c r="D40" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E40" s="81" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F40" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G40" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B41" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:06</t>
+        </is>
+      </c>
+      <c r="C41" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
+        </is>
+      </c>
+      <c r="D41" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E41" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G41" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:05</t>
+        </is>
+      </c>
+      <c r="C42" s="51" t="inlineStr">
+        <is>
+          <t>Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top losers</t>
+        </is>
+      </c>
+      <c r="D42" s="51" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E42" s="81" t="n">
+        <v>-0.178</v>
+      </c>
+      <c r="F42" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G42" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B43" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:20</t>
+        </is>
+      </c>
+      <c r="C43" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?</t>
+        </is>
+      </c>
+      <c r="D43" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E43" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G43" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B44" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:15</t>
+        </is>
+      </c>
+      <c r="C44" s="51" t="inlineStr">
+        <is>
+          <t>Nifty, Sensex: History favours stock market comeback in October; stocks to watch</t>
+        </is>
+      </c>
+      <c r="D44" s="51" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="E44" s="81" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F44" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G44" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B45" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:03</t>
+        </is>
+      </c>
+      <c r="C45" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
+        </is>
+      </c>
+      <c r="D45" s="51" t="inlineStr">
+        <is>
+          <t>Free Press Kashmir</t>
+        </is>
+      </c>
+      <c r="E45" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G45" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B46" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C46" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?</t>
+        </is>
+      </c>
+      <c r="D46" s="51" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="E46" s="81" t="n">
+        <v>-0.8070000000000001</v>
+      </c>
+      <c r="F46" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G46" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B47" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:44</t>
+        </is>
+      </c>
+      <c r="C47" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts</t>
+        </is>
+      </c>
+      <c r="D47" s="51" t="inlineStr">
+        <is>
+          <t>APAC Media</t>
+        </is>
+      </c>
+      <c r="E47" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G47" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B48" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:36</t>
+        </is>
+      </c>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets</t>
+        </is>
+      </c>
+      <c r="D48" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E48" s="81" t="n">
+        <v>-0.806</v>
+      </c>
+      <c r="F48" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G48" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B49" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:06</t>
+        </is>
+      </c>
+      <c r="C49" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800</t>
+        </is>
+      </c>
+      <c r="D49" s="51" t="inlineStr">
+        <is>
+          <t>CNBC TV18</t>
+        </is>
+      </c>
+      <c r="E49" s="81" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F49" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G49" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B50" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 06:47</t>
+        </is>
+      </c>
+      <c r="C50" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
+        </is>
+      </c>
+      <c r="D50" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E50" s="81" t="n">
+        <v>-0.791</v>
+      </c>
+      <c r="F50" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G50" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B51" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 06:40</t>
+        </is>
+      </c>
+      <c r="C51" s="51" t="inlineStr">
+        <is>
+          <t>SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday’s market crash</t>
+        </is>
+      </c>
+      <c r="D51" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E51" s="81" t="n">
+        <v>-0.595</v>
+      </c>
+      <c r="F51" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G51" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B52" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:52</t>
+        </is>
+      </c>
+      <c r="C52" s="51" t="inlineStr">
+        <is>
+          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
+        </is>
+      </c>
+      <c r="D52" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E52" s="81" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F52" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G52" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:52</t>
+        </is>
+      </c>
+      <c r="C53" s="51" t="inlineStr">
+        <is>
+          <t>India VIX spikes 14% as oil, geopolitical risks trigger market sell-off</t>
+        </is>
+      </c>
+      <c r="D53" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E53" s="81" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F53" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G53" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B54" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:42</t>
+        </is>
+      </c>
+      <c r="C54" s="51" t="inlineStr">
+        <is>
+          <t>Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern</t>
+        </is>
+      </c>
+      <c r="D54" s="51" t="inlineStr">
+        <is>
+          <t>India Infoline</t>
+        </is>
+      </c>
+      <c r="E54" s="81" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="F54" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G54" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="51" t="inlineStr">
+        <is>
           <t>KIRLOSENG</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
-        <is>
-          <t>2026-09-24 17:13</t>
-        </is>
-      </c>
-      <c r="C6" s="51" t="inlineStr">
-        <is>
-          <t>3 Indian Nuclear Stocks With Revenue Growth Up To 16%</t>
-        </is>
-      </c>
-      <c r="D6" s="51" t="inlineStr">
-        <is>
-          <t>Simply Wall St.</t>
-        </is>
-      </c>
-      <c r="E6" s="80" t="n">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="F6" s="51" t="inlineStr">
+      <c r="B55" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:37</t>
+        </is>
+      </c>
+      <c r="C55" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
+        </is>
+      </c>
+      <c r="D55" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E55" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G55" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B56" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:18</t>
+        </is>
+      </c>
+      <c r="C56" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
+        </is>
+      </c>
+      <c r="D56" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E56" s="81" t="n">
+        <v>-0.6909999999999999</v>
+      </c>
+      <c r="F56" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G56" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B57" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:11</t>
+        </is>
+      </c>
+      <c r="C57" s="51" t="inlineStr">
+        <is>
+          <t>Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties</t>
+        </is>
+      </c>
+      <c r="D57" s="51" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="E57" s="81" t="n">
+        <v>-0.852</v>
+      </c>
+      <c r="F57" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G57" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B58" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:56</t>
+        </is>
+      </c>
+      <c r="C58" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+        </is>
+      </c>
+      <c r="D58" s="51" t="inlineStr">
+        <is>
+          <t>equitymaster.com</t>
+        </is>
+      </c>
+      <c r="E58" s="81" t="n">
+        <v>-0.477</v>
+      </c>
+      <c r="F58" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G58" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B59" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:51</t>
+        </is>
+      </c>
+      <c r="C59" s="51" t="inlineStr">
+        <is>
+          <t>Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil</t>
+        </is>
+      </c>
+      <c r="D59" s="51" t="inlineStr">
+        <is>
+          <t>rediff.com</t>
+        </is>
+      </c>
+      <c r="E59" s="81" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="F59" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G59" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B60" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:45</t>
+        </is>
+      </c>
+      <c r="C60" s="51" t="inlineStr">
+        <is>
+          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
+        </is>
+      </c>
+      <c r="D60" s="51" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E60" s="81" t="n">
+        <v>-0.361</v>
+      </c>
+      <c r="F60" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G60" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B61" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:42</t>
+        </is>
+      </c>
+      <c r="C61" s="51" t="inlineStr">
+        <is>
+          <t>NSE stock slips below issue price of ₹1,785; down 2% on Monday</t>
+        </is>
+      </c>
+      <c r="D61" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E61" s="81" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F61" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G61" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B62" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:41</t>
+        </is>
+      </c>
+      <c r="C62" s="51" t="inlineStr">
+        <is>
+          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
+        </is>
+      </c>
+      <c r="D62" s="51" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="E62" s="81" t="n">
+        <v>-0.758</v>
+      </c>
+      <c r="F62" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G62" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:29</t>
+        </is>
+      </c>
+      <c r="C63" s="51" t="inlineStr">
+        <is>
+          <t>Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%</t>
+        </is>
+      </c>
+      <c r="D63" s="51" t="inlineStr">
+        <is>
+          <t>newsdrum.in</t>
+        </is>
+      </c>
+      <c r="E63" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G63" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:25</t>
+        </is>
+      </c>
+      <c r="C64" s="51" t="inlineStr">
+        <is>
+          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
+        </is>
+      </c>
+      <c r="D64" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E64" s="81" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F64" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G64" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:17</t>
+        </is>
+      </c>
+      <c r="C65" s="51" t="inlineStr">
+        <is>
+          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
+        </is>
+      </c>
+      <c r="D65" s="51" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E65" s="81" t="n">
+        <v>-0.511</v>
+      </c>
+      <c r="F65" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G65" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B66" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:11</t>
+        </is>
+      </c>
+      <c r="C66" s="51" t="inlineStr">
+        <is>
+          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
+        </is>
+      </c>
+      <c r="D66" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E66" s="81" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="F66" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G66" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:08</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l</t>
+        </is>
+      </c>
+      <c r="D67" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E67" s="81" t="n">
+        <v>-0.649</v>
+      </c>
+      <c r="F67" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G67" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B68" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:07</t>
+        </is>
+      </c>
+      <c r="C68" s="51" t="inlineStr">
+        <is>
+          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
+        </is>
+      </c>
+      <c r="D68" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E68" s="81" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F68" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G68" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B69" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:01</t>
+        </is>
+      </c>
+      <c r="C69" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines ESOP 2019 Share Allotment Explained</t>
+        </is>
+      </c>
+      <c r="D69" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E69" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G69" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B70" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:58</t>
+        </is>
+      </c>
+      <c r="C70" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
+        </is>
+      </c>
+      <c r="D70" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E70" s="81" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F70" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G6" s="81" t="inlineStr">
+      <c r="G70" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B71" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:54</t>
+        </is>
+      </c>
+      <c r="C71" s="51" t="inlineStr">
+        <is>
+          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
+        </is>
+      </c>
+      <c r="D71" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E71" s="81" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="F71" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G71" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B72" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:48</t>
+        </is>
+      </c>
+      <c r="C72" s="51" t="inlineStr">
+        <is>
+          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
+        </is>
+      </c>
+      <c r="D72" s="51" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E72" s="81" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F72" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G72" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B73" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:28</t>
+        </is>
+      </c>
+      <c r="C73" s="51" t="inlineStr">
+        <is>
+          <t>Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open</t>
+        </is>
+      </c>
+      <c r="D73" s="51" t="inlineStr">
+        <is>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E73" s="81" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="F73" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G73" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B74" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 02:19</t>
+        </is>
+      </c>
+      <c r="C74" s="51" t="inlineStr">
+        <is>
+          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
+        </is>
+      </c>
+      <c r="D74" s="51" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E74" s="81" t="n">
+        <v>-0.542</v>
+      </c>
+      <c r="F74" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G74" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B75" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:58</t>
+        </is>
+      </c>
+      <c r="C75" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices — Five Key Factors For Sensex, Nifty 50 On September 28</t>
+        </is>
+      </c>
+      <c r="D75" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E75" s="81" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F75" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G75" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B76" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:20</t>
+        </is>
+      </c>
+      <c r="C76" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
+        </is>
+      </c>
+      <c r="D76" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E76" s="81" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F76" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G76" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B77" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:30</t>
+        </is>
+      </c>
+      <c r="C77" s="51" t="inlineStr">
+        <is>
+          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
+        </is>
+      </c>
+      <c r="D77" s="51" t="inlineStr">
+        <is>
+          <t>equitymaster.com</t>
+        </is>
+      </c>
+      <c r="E77" s="81" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F77" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G77" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="51" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B78" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 17:20</t>
+        </is>
+      </c>
+      <c r="C78" s="51" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
+        </is>
+      </c>
+      <c r="D78" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E78" s="81" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F78" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G78" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B79" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:03</t>
+        </is>
+      </c>
+      <c r="C79" s="51" t="inlineStr">
+        <is>
+          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
+        </is>
+      </c>
+      <c r="D79" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E79" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G79" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B80" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:48</t>
+        </is>
+      </c>
+      <c r="C80" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
+        </is>
+      </c>
+      <c r="D80" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E80" s="81" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F80" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G80" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B81" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-27 04:22</t>
+        </is>
+      </c>
+      <c r="C81" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
+        </is>
+      </c>
+      <c r="D81" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E81" s="81" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F81" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G81" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B82" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 22:56</t>
+        </is>
+      </c>
+      <c r="C82" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
+        </is>
+      </c>
+      <c r="D82" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E82" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G82" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:51</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>🚦 Indian Markets Stuck In A Jam! But who's responsible for the traffic? 🤔 A Bernstein note argues that India’s large caps are stuck in a bygone economic era. But here's the BIG question: 🇮🇳 Is The Market’s Fate Really In India’s Hands? 🌍 Or are global cues pul</t>
+        </is>
+      </c>
+      <c r="D83" s="51" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E83" s="81" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="F83" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G83" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B84" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:11</t>
+        </is>
+      </c>
+      <c r="C84" s="51" t="inlineStr">
+        <is>
+          <t>Share Market News: Nifty 50 Outlook &amp; Prediction</t>
+        </is>
+      </c>
+      <c r="D84" s="51" t="inlineStr">
+        <is>
+          <t>Liquide Blog</t>
+        </is>
+      </c>
+      <c r="E84" s="81" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F84" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G84" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B85" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 09:15</t>
+        </is>
+      </c>
+      <c r="C85" s="51" t="inlineStr">
+        <is>
+          <t>Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide</t>
+        </is>
+      </c>
+      <c r="D85" s="51" t="inlineStr">
+        <is>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="E85" s="81" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="F85" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G85" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="51" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B86" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:30</t>
+        </is>
+      </c>
+      <c r="C86" s="51" t="inlineStr">
+        <is>
+          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
+        </is>
+      </c>
+      <c r="D86" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E86" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G86" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="51" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-26 00:50</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
+          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
+        </is>
+      </c>
+      <c r="D87" s="51" t="inlineStr">
+        <is>
+          <t>Alice Blue</t>
+        </is>
+      </c>
+      <c r="E87" s="81" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F87" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G87" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:34</t>
+        </is>
+      </c>
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
+        </is>
+      </c>
+      <c r="D88" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E88" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G88" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B89" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="C89" s="51" t="inlineStr">
+        <is>
+          <t>PERSISTENT Stock Price and Chart — NSE:PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D89" s="51" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="E89" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G89" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B90" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:04</t>
+        </is>
+      </c>
+      <c r="C90" s="51" t="inlineStr">
+        <is>
+          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
+        </is>
+      </c>
+      <c r="D90" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E90" s="81" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="F90" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G90" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B91" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:52</t>
+        </is>
+      </c>
+      <c r="C91" s="51" t="inlineStr">
+        <is>
+          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
+        </is>
+      </c>
+      <c r="D91" s="51" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E91" s="81" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F91" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G91" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="51" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B92" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:22</t>
+        </is>
+      </c>
+      <c r="C92" s="51" t="inlineStr">
+        <is>
+          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
+        </is>
+      </c>
+      <c r="D92" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E92" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G92" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B93" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:56</t>
+        </is>
+      </c>
+      <c r="C93" s="51" t="inlineStr">
+        <is>
+          <t>Two years ago Sensex hit lifetime high: What went wrong after that &amp; what’s the road ahead?</t>
+        </is>
+      </c>
+      <c r="D93" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E93" s="81" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F93" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G93" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B94" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:42</t>
+        </is>
+      </c>
+      <c r="C94" s="51" t="inlineStr">
+        <is>
+          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
+        </is>
+      </c>
+      <c r="D94" s="51" t="inlineStr">
+        <is>
+          <t>CNBC TV18</t>
+        </is>
+      </c>
+      <c r="E94" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G94" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B95" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:22</t>
+        </is>
+      </c>
+      <c r="C95" s="51" t="inlineStr">
+        <is>
+          <t>Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points</t>
+        </is>
+      </c>
+      <c r="D95" s="51" t="inlineStr">
+        <is>
+          <t>rediff.com</t>
+        </is>
+      </c>
+      <c r="E95" s="81" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="F95" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G95" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B96" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:03</t>
+        </is>
+      </c>
+      <c r="C96" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%</t>
+        </is>
+      </c>
+      <c r="D96" s="51" t="inlineStr">
+        <is>
+          <t>equitymaster.com</t>
+        </is>
+      </c>
+      <c r="E96" s="81" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F96" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G96" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B97" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:48</t>
+        </is>
+      </c>
+      <c r="C97" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty Rebound on Value Buying After Sharp Losses</t>
+        </is>
+      </c>
+      <c r="D97" s="51" t="inlineStr">
+        <is>
+          <t>Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="E97" s="81" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F97" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G97" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="51" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B98" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:31</t>
+        </is>
+      </c>
+      <c r="C98" s="51" t="inlineStr">
+        <is>
+          <t>Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date</t>
+        </is>
+      </c>
+      <c r="D98" s="51" t="inlineStr">
+        <is>
+          <t>INDmoney</t>
+        </is>
+      </c>
+      <c r="E98" s="81" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="F98" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G98" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B99" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:31</t>
+        </is>
+      </c>
+      <c r="C99" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses</t>
+        </is>
+      </c>
+      <c r="D99" s="51" t="inlineStr">
+        <is>
+          <t>APAC Media</t>
+        </is>
+      </c>
+      <c r="E99" s="81" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="F99" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G99" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B100" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="C100" s="51" t="inlineStr">
+        <is>
+          <t>Sah Polymers Share Price</t>
+        </is>
+      </c>
+      <c r="D100" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E100" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G100" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B101" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="C101" s="51" t="inlineStr">
+        <is>
+          <t>Nifty Chemicals (NFTCHEMIC) Share Price</t>
+        </is>
+      </c>
+      <c r="D101" s="51" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="E101" s="81" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F101" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G101" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B102" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:49</t>
+        </is>
+      </c>
+      <c r="C102" s="51" t="inlineStr">
+        <is>
+          <t>Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today</t>
+        </is>
+      </c>
+      <c r="D102" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E102" s="81" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="F102" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G102" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B103" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:34</t>
+        </is>
+      </c>
+      <c r="C103" s="51" t="inlineStr">
+        <is>
+          <t>Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore</t>
+        </is>
+      </c>
+      <c r="D103" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E103" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G103" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B104" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:52</t>
+        </is>
+      </c>
+      <c r="C104" s="51" t="inlineStr">
+        <is>
+          <t>Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons</t>
+        </is>
+      </c>
+      <c r="D104" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E104" s="81" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="F104" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G104" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B105" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:32</t>
+        </is>
+      </c>
+      <c r="C105" s="51" t="inlineStr">
+        <is>
+          <t>NSE shares dip on day 2 of listing, brokerages back long-term growth story</t>
+        </is>
+      </c>
+      <c r="D105" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E105" s="81" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="F105" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G105" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 03:51</t>
+        </is>
+      </c>
+      <c r="C106" s="51" t="inlineStr">
+        <is>
+          <t>Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050</t>
+        </is>
+      </c>
+      <c r="D106" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E106" s="81" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="F106" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G106" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B107" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:49</t>
+        </is>
+      </c>
+      <c r="C107" s="51" t="inlineStr">
+        <is>
+          <t>Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others</t>
+        </is>
+      </c>
+      <c r="D107" s="51" t="inlineStr">
+        <is>
+          <t>ET Now</t>
+        </is>
+      </c>
+      <c r="E107" s="81" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="F107" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G107" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B108" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:06</t>
+        </is>
+      </c>
+      <c r="C108" s="51" t="inlineStr">
+        <is>
+          <t>Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...</t>
+        </is>
+      </c>
+      <c r="D108" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E108" s="81" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="F108" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G108" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B109" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-25 01:28</t>
+        </is>
+      </c>
+      <c r="C109" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, Bond Yields To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On September 25</t>
+        </is>
+      </c>
+      <c r="D109" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E109" s="81" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F109" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G109" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B110" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:21</t>
+        </is>
+      </c>
+      <c r="C110" s="51" t="inlineStr">
+        <is>
+          <t>R R Kabel executes BTA to acquire U M Cables business for ₹77 crore</t>
+        </is>
+      </c>
+      <c r="D110" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E110" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G110" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B111" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:04</t>
+        </is>
+      </c>
+      <c r="C111" s="51" t="inlineStr">
+        <is>
+          <t>Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets</t>
+        </is>
+      </c>
+      <c r="D111" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E111" s="81" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F111" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G111" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="51" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B112" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:42</t>
+        </is>
+      </c>
+      <c r="C112" s="51" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics</t>
+        </is>
+      </c>
+      <c r="D112" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E112" s="81" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F112" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G112" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B113" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:49</t>
+        </is>
+      </c>
+      <c r="C113" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month</t>
+        </is>
+      </c>
+      <c r="D113" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E113" s="81" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="F113" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G113" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B114" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:15</t>
+        </is>
+      </c>
+      <c r="C114" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team</t>
+        </is>
+      </c>
+      <c r="D114" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E114" s="81" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F114" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G114" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B115" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:01</t>
+        </is>
+      </c>
+      <c r="C115" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Export Stocks That Could Benefit From A Weaker Rupee</t>
+        </is>
+      </c>
+      <c r="D115" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E115" s="81" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F115" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G115" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B116" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:36</t>
+        </is>
+      </c>
+      <c r="C116" s="51" t="inlineStr">
+        <is>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026</t>
+        </is>
+      </c>
+      <c r="D116" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E116" s="81" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F116" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G116" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B117" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:57</t>
+        </is>
+      </c>
+      <c r="C117" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty see worst day in weeks: Why was market down today? | Business News</t>
+        </is>
+      </c>
+      <c r="D117" s="51" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E117" s="81" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F117" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G117" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="51" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B118" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:15</t>
+        </is>
+      </c>
+      <c r="C118" s="51" t="inlineStr">
+        <is>
+          <t>TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026</t>
+        </is>
+      </c>
+      <c r="D118" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E118" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G118" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B119" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="C119" s="51" t="inlineStr">
+        <is>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks</t>
+        </is>
+      </c>
+      <c r="D119" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E119" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G119" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B120" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:42</t>
+        </is>
+      </c>
+      <c r="C120" s="51" t="inlineStr">
+        <is>
+          <t>The battle between India’s stock exchanges is heating up again</t>
+        </is>
+      </c>
+      <c r="D120" s="51" t="inlineStr">
+        <is>
+          <t>The Economist</t>
+        </is>
+      </c>
+      <c r="E120" s="81" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F120" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G120" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B121" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:40</t>
+        </is>
+      </c>
+      <c r="C121" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss</t>
+        </is>
+      </c>
+      <c r="D121" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E121" s="81" t="n">
+        <v>-0.758</v>
+      </c>
+      <c r="F121" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G121" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B122" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:08</t>
+        </is>
+      </c>
+      <c r="C122" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday</t>
+        </is>
+      </c>
+      <c r="D122" s="51" t="inlineStr">
+        <is>
+          <t>CNBC TV18</t>
+        </is>
+      </c>
+      <c r="E122" s="81" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F122" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G122" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B123" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:02</t>
+        </is>
+      </c>
+      <c r="C123" s="51" t="inlineStr">
+        <is>
+          <t>Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today</t>
+        </is>
+      </c>
+      <c r="D123" s="51" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="E123" s="81" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F123" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G123" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B124" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:52</t>
+        </is>
+      </c>
+      <c r="C124" s="51" t="inlineStr">
+        <is>
+          <t>Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall</t>
+        </is>
+      </c>
+      <c r="D124" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E124" s="81" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="F124" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G124" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B125" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:46</t>
+        </is>
+      </c>
+      <c r="C125" s="51" t="inlineStr">
+        <is>
+          <t>Hero Motors Ltd leads gainers in 'B' group</t>
+        </is>
+      </c>
+      <c r="D125" s="51" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E125" s="81" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F125" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G125" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B126" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:35</t>
+        </is>
+      </c>
+      <c r="C126" s="51" t="inlineStr">
+        <is>
+          <t>TD Power Systems Share Price today: decline and analysis</t>
+        </is>
+      </c>
+      <c r="D126" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E126" s="81" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="F126" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G126" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B127" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:21</t>
+        </is>
+      </c>
+      <c r="C127" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D127" s="51" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E127" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G127" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B128" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:35</t>
+        </is>
+      </c>
+      <c r="C128" s="51" t="inlineStr">
+        <is>
+          <t>Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices</t>
+        </is>
+      </c>
+      <c r="D128" s="51" t="inlineStr">
+        <is>
+          <t>theweek.in</t>
+        </is>
+      </c>
+      <c r="E128" s="81" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F128" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G128" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B129" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25</t>
+        </is>
+      </c>
+      <c r="C129" s="51" t="inlineStr">
+        <is>
+          <t>Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom — Ask Profit</t>
+        </is>
+      </c>
+      <c r="D129" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E129" s="81" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F129" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G129" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="51" t="inlineStr">
+        <is>
+          <t>AEROFLEX</t>
+        </is>
+      </c>
+      <c r="B130" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 06:20</t>
+        </is>
+      </c>
+      <c r="C130" s="51" t="inlineStr">
+        <is>
+          <t>Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest</t>
+        </is>
+      </c>
+      <c r="D130" s="51" t="inlineStr">
+        <is>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E130" s="81" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="F130" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G130" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B131" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:09</t>
+        </is>
+      </c>
+      <c r="C131" s="51" t="inlineStr">
+        <is>
+          <t>Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'</t>
+        </is>
+      </c>
+      <c r="D131" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E131" s="81" t="n">
+        <v>-0.273</v>
+      </c>
+      <c r="F131" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G131" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B132" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 03:56</t>
+        </is>
+      </c>
+      <c r="C132" s="51" t="inlineStr">
+        <is>
+          <t>Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash</t>
+        </is>
+      </c>
+      <c r="D132" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E132" s="81" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F132" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G132" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B133" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:46</t>
+        </is>
+      </c>
+      <c r="C133" s="51" t="inlineStr">
+        <is>
+          <t>Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs</t>
+        </is>
+      </c>
+      <c r="D133" s="51" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E133" s="81" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="F133" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G133" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B134" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:44</t>
+        </is>
+      </c>
+      <c r="C134" s="51" t="inlineStr">
+        <is>
+          <t>US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact</t>
+        </is>
+      </c>
+      <c r="D134" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E134" s="81" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="F134" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G134" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B135" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:38</t>
+        </is>
+      </c>
+      <c r="C135" s="51" t="inlineStr">
+        <is>
+          <t>GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...</t>
+        </is>
+      </c>
+      <c r="D135" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E135" s="81" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F135" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G135" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B136" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 01:42</t>
+        </is>
+      </c>
+      <c r="C136" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields — Five Key Factors For Sensex, Nifty 50 On Sept 24</t>
+        </is>
+      </c>
+      <c r="D136" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E136" s="81" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F136" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G136" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B137" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-24 01:17</t>
+        </is>
+      </c>
+      <c r="C137" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals</t>
+        </is>
+      </c>
+      <c r="D137" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E137" s="81" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F137" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G137" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B138" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:57</t>
+        </is>
+      </c>
+      <c r="C138" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs stock gains 1.37 percent as profit jumps 126 percent</t>
+        </is>
+      </c>
+      <c r="D138" s="51" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="E138" s="81" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="F138" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G138" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B139" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:57</t>
+        </is>
+      </c>
+      <c r="C139" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month</t>
+        </is>
+      </c>
+      <c r="D139" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E139" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G139" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B140" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:16</t>
+        </is>
+      </c>
+      <c r="C140" s="51" t="inlineStr">
+        <is>
+          <t>Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market</t>
+        </is>
+      </c>
+      <c r="D140" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E140" s="81" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="F140" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G140" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B141" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:15</t>
+        </is>
+      </c>
+      <c r="C141" s="51" t="inlineStr">
+        <is>
+          <t>Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers</t>
+        </is>
+      </c>
+      <c r="D141" s="51" t="inlineStr">
+        <is>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E141" s="81" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="F141" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G141" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="51" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B142" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:02</t>
+        </is>
+      </c>
+      <c r="C142" s="51" t="inlineStr">
+        <is>
+          <t>Diamond Power Infrastructure Share Price Rises 2.68% Today</t>
+        </is>
+      </c>
+      <c r="D142" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E142" s="81" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F142" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G142" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B143" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:19</t>
+        </is>
+      </c>
+      <c r="C143" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs Share Price: one-year high and valuation view</t>
+        </is>
+      </c>
+      <c r="D143" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E143" s="81" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="F143" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G143" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B144" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:59</t>
+        </is>
+      </c>
+      <c r="C144" s="51" t="inlineStr">
+        <is>
+          <t>NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details</t>
+        </is>
+      </c>
+      <c r="D144" s="51" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E144" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G144" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="51" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B145" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:26</t>
+        </is>
+      </c>
+      <c r="C145" s="51" t="inlineStr">
+        <is>
+          <t>E2E Networks Share Price news: price rise and valuation</t>
+        </is>
+      </c>
+      <c r="D145" s="51" t="inlineStr">
+        <is>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E145" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G145" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="51" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B146" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:24</t>
+        </is>
+      </c>
+      <c r="C146" s="51" t="inlineStr">
+        <is>
+          <t>Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings</t>
+        </is>
+      </c>
+      <c r="D146" s="51" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E146" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G146" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="51" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B147" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 05:56</t>
+        </is>
+      </c>
+      <c r="C147" s="51" t="inlineStr">
+        <is>
+          <t>3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%</t>
+        </is>
+      </c>
+      <c r="D147" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E147" s="81" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F147" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G147" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B148" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 01:42</t>
+        </is>
+      </c>
+      <c r="C148" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23</t>
+        </is>
+      </c>
+      <c r="D148" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E148" s="81" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F148" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G148" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B149" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 01:13</t>
+        </is>
+      </c>
+      <c r="C149" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal</t>
+        </is>
+      </c>
+      <c r="D149" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E149" s="81" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F149" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G149" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="51" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B150" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:46</t>
+        </is>
+      </c>
+      <c r="C150" s="51" t="inlineStr">
+        <is>
+          <t>Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors</t>
+        </is>
+      </c>
+      <c r="D150" s="51" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="E150" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G150" s="82" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10245,7 +15358,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E6">
+  <conditionalFormatting sqref="E5:E150">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1"/>
@@ -10260,6 +15373,150 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId146"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -10273,20 +15530,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"batch": {"batch_id": "2026-09-28", "title": "SwingScope batch 2026-09-28", "signal_date": "2026-09-28", "exit_date_est": "2026-10-27", "hold_sessions": 21, "universe": "liquidity top 400 of all NSE stocks", "capital": 139903.0, "est_costs": 859.0, "cost_pct": 0.6, "regime": "Down", "regime_note": "the signal's weakest regime historically", "warnings": "0 of 10", "evidence": ["Backtest, 2017\u20132026 | Replayed point in time on your survivorship-free archive. Not live results. | Signal strength | IC +0.041 | rank IC over 113 monthly dates, 2017-2026 (t 2.52); validated benchmark 0.026 | Top vs bottom decile | +1.89% | per 21-session hold, before costs (t 2.94) | Top-10 picks | +1.45% | per hold after 0.60% costs; Nifty 50 earned +1.02% before costs | Entry timing | Open wins | buying at the open beat all 30 support-entry rules (best -0.12% per hold) | Down markets | IC +0.009 | over 27 down-regime dates, against +0.050 over 86 up-regime dates", "Live record | No results yet | The first live result arrives when this system finishes its first batch. Live results are kept apart from the backtest and never mixed in."], "stocks": [{"rank": 1, "symbol": "TDPOWERSYS", "isin": "INE419M01035", "qty": 20, "last_close": 722.0, "amount": 14440.0, "spark_12m": "2.0,31.7 2.4,32.0 2.9,31.7 3.3,31.1 3.7,31.1 4.2,31.1 4.6,31.0 5.0,30.6 5.4,30.4 5.9,29.2 6.3,29.3 6.7,29.5 7.2,29.8 7.6,30.1 8.0,30.4 8.5,30.5 8.9,30.3 9.3,29.4 9.7,29.3 10.2,28.8 10.6,29.1 11.0,28.9 11.5,29.1 11.9,29.2 12.3,29.1 12.8,29.0 13.2,28.4 13.6,28.0 14.0,25.5 14.5,24.3 14.9,24.2 15.3,24.8 15.8,25.3 16.2,25.2 16.6,25.4 17.1,24.2 17.5,25.4 17.9,25.2 18.4,25.2 18.8,25.7 19.2,25.8 19.6,25.9 20.1,26.9 20.5,25.8 20.9,25.9 21.4,24.9 21.8,24.9 22.2,25.4 22.7,25.0 23.1,25.0 23.5,25.8 23.9,26.8 24.4,27.7 24.8,28.3 25.2,27.7 25.7,28.1 26.1,28.2 26.5,27.9 27.0,27.6 27.4,27.9 27.8,27.1 28.2,27.6 28.7,27.1 29.1,26.4 29.5,26.7 30.0,27.0 30.4,27.3 30.8,27.7 31.3,27.5 31.7,27.5 32.1,28.3 32.5,28.0 33.0,27.7 33.4,27.9 33.8,27.5 34.3,27.9 34.7,28.3 35.1,28.8 35.6,27.9 36.0,28.2 36.4,28.5 36.9,28.7 37.3,29.2 37.7,29.4 38.1,29.5 38.6,29.7 39.0,29.6 39.4,28.8 39.9,28.2 40.3,26.7 40.7,26.2 41.2,24.3 41.6,24.1 42.0,24.5 42.4,25.2 42.9,24.8 43.3,23.3 43.7,22.8 44.2,23.4 44.6,23.8 45.0,23.1 45.5,22.8 45.9,22.8 46.3,22.4 46.7,22.4 47.2,21.8 47.6,22.3 48.0,22.5 48.5,22.5 48.9,21.8 49.3,22.2 49.8,22.6 50.2,22.4 50.6,22.5 51.1,23.5 51.5,24.3 51.9,24.7 52.3,24.4 52.8,25.3 53.2,24.9 53.6,24.3 54.1,23.7 54.5,23.8 54.9,23.0 55.4,24.2 55.8,23.1 56.2,22.3 56.6,23.4 57.1,23.3 57.5,23.0 57.9,23.0 58.4,22.5 58.8,22.5 59.2,22.4 59.7,22.6 60.1,21.2 60.5,21.5 60.9,20.8 61.4,20.0 61.8,19.2 62.2,18.3 62.7,18.6 63.1,17.4 63.5,17.2 64.0,16.0 64.4,16.6 64.8,15.0 65.3,15.0 65.7,14.8 66.1,14.6 66.5,14.2 67.0,14.5 67.4,12.2 67.8,13.0 68.3,14.1 68.7,14.4 69.1,14.2 69.6,14.0 70.0,10.4 70.4,9.9 70.8,11.9 71.3,12.6 71.7,10.6 72.1,10.8 72.6,10.7 73.0,8.8 73.4,9.8 73.9,10.2 74.3,12.7 74.7,12.5 75.1,11.1 75.6,10.0 76.0,10.3 76.4,12.8 76.9,12.6 77.3,14.8 77.7,15.6 78.2,13.7 78.6,13.6 79.0,14.4 79.5,12.7 79.9,11.6 80.3,11.5 80.7,10.0 81.2,9.2 81.6,11.7 82.0,12.0 82.5,12.6 82.9,12.4 83.3,13.7 83.8,13.8 84.2,16.6 84.6,14.2 85.0,15.7 85.5,16.9 85.9,16.6 86.3,14.9 86.8,14.9 87.2,15.6 87.6,14.2 88.1,15.6 88.5,15.5 88.9,15.2 89.3,15.5 89.8,14.6 90.2,15.2 90.6,15.9 91.1,15.2 91.5,15.9 91.9,18.1 92.4,17.5 92.8,15.5 93.2,16.0 93.6,15.5 94.1,13.5 94.5,12.7 94.9,11.8 95.4,12.5 95.8,11.4 96.2,5.6 96.7,5.6 97.1,5.5 97.5,3.7 98.0,2.7 98.4,3.8 98.8,4.9 99.2,4.1 99.7,3.4 100.1,6.2 100.5,6.3 101.0,5.6 101.4,4.9 101.8,3.6 102.3,4.6 102.7,5.9 103.1,6.6 103.5,5.6 104.0,6.0 104.4,4.0 104.8,4.8 105.3,4.4 105.7,2.0 106.1,6.5 106.6,8.1 107.0,6.7 107.4,4.3 107.8,5.2 108.3,4.7 108.7,4.2 109.1,5.5 109.6,5.0 110.0,6.7", "ret_12_1": 177.0, "ret_6_1": 72.2, "ret_3_1": 19.6, "volatility": 60.1, "traded_daily_cr": 128.0, "watch": "Nothing flagged", "from_12m_high": -10.3, "signal_rank": 6, "data_quality": "Green"}, {"rank": 2, "symbol": "AEROFLEX", "isin": "INE024001021", "qty": 29, "last_close": 513.4, "amount": 14889.0, "spark_12m": "2.0,29.8 2.4,29.6 2.9,29.5 3.3,30.0 3.7,30.1 4.2,30.5 4.6,30.8 5.0,30.9 5.4,30.9 5.9,30.5 6.3,30.7 6.7,30.8 7.2,30.9 7.6,31.0 8.0,31.0 8.5,31.1 8.9,31.2 9.3,31.2 9.7,31.2 10.2,31.2 10.6,31.4 11.0,31.1 11.5,31.0 11.9,31.0 12.3,31.0 12.8,30.1 13.2,30.1 13.6,30.5 14.0,30.0 14.5,29.8 14.9,30.3 15.3,30.5 15.8,30.0 16.2,30.0 16.6,30.2 17.1,30.2 17.5,30.1 17.9,29.9 18.4,30.1 18.8,30.3 19.2,30.2 19.6,30.2 20.1,30.5 20.5,30.9 20.9,30.2 21.4,30.2 21.8,30.4 22.2,30.0 22.7,30.2 23.1,30.3 23.5,30.6 23.9,30.6 24.4,30.7 24.8,31.3 25.2,31.0 25.7,30.7 26.1,30.9 26.5,30.7 27.0,30.3 27.4,30.5 27.8,30.3 28.2,30.7 28.7,29.5 29.1,29.2 29.5,28.8 30.0,28.6 30.4,28.9 30.8,29.1 31.3,29.3 31.7,29.5 32.1,29.6 32.5,29.2 33.0,29.0 33.4,29.3 33.8,29.1 34.3,29.9 34.7,30.2 35.1,30.2 35.6,30.5 36.0,30.7 36.4,30.8 36.9,30.9 37.3,31.3 37.7,31.8 38.1,31.5 38.6,32.0 39.0,31.7 39.4,31.4 39.9,30.4 40.3,30.6 40.7,31.0 41.2,30.1 41.6,29.9 42.0,29.9 42.4,30.1 42.9,29.3 43.3,29.4 43.7,29.6 44.2,29.5 44.6,30.0 45.0,29.6 45.5,28.5 45.9,27.1 46.3,27.0 46.7,27.3 47.2,27.6 47.6,27.7 48.0,27.0 48.5,26.9 48.9,26.5 49.3,27.2 49.8,27.7 50.2,27.3 50.6,27.6 51.1,27.9 51.5,27.5 51.9,26.5 52.3,26.3 52.8,26.5 53.2,25.6 53.6,25.3 54.1,25.6 54.5,26.8 54.9,26.6 55.4,27.3 55.8,25.3 56.2,25.3 56.6,26.1 57.1,26.2 57.5,25.4 57.9,25.2 58.4,25.0 58.8,25.7 59.2,24.6 59.7,23.6 60.1,22.6 60.5,22.6 60.9,22.3 61.4,22.1 61.8,21.0 62.2,21.7 62.7,22.6 63.1,21.5 63.5,22.1 64.0,23.4 64.4,22.2 64.8,22.3 65.3,21.4 65.7,21.4 66.1,21.6 66.5,20.5 67.0,18.6 67.4,13.6 67.8,11.7 68.3,14.7 68.7,17.1 69.1,17.1 69.6,17.4 70.0,16.7 70.4,16.8 70.8,15.9 71.3,15.2 71.7,16.0 72.1,14.3 72.6,13.5 73.0,14.3 73.4,14.0 73.9,14.4 74.3,15.4 74.7,13.1 75.1,12.1 75.6,11.7 76.0,13.1 76.4,14.6 76.9,12.7 77.3,13.5 77.7,13.9 78.2,11.1 78.6,8.9 79.0,9.4 79.5,6.5 79.9,8.1 80.3,6.8 80.7,6.6 81.2,7.1 81.6,8.8 82.0,9.7 82.5,9.6 82.9,9.4 83.3,8.1 83.8,8.9 84.2,10.5 84.6,10.3 85.0,13.6 85.5,14.5 85.9,14.2 86.3,13.6 86.8,13.0 87.2,13.8 87.6,13.0 88.1,13.8 88.5,13.8 88.9,14.1 89.3,13.6 89.8,14.0 90.2,13.1 90.6,13.0 91.1,13.2 91.5,11.2 91.9,10.9 92.4,12.6 92.8,12.0 93.2,12.3 93.6,9.9 94.1,10.5 94.5,11.8 94.9,12.7 95.4,13.1 95.8,12.9 96.2,11.2 96.7,11.1 97.1,10.2 97.5,10.5 98.0,8.3 98.4,9.2 98.8,9.1 99.2,7.1 99.7,7.0 100.1,7.6 100.5,4.7 101.0,5.7 101.4,4.3 101.8,5.5 102.3,3.6 102.7,4.4 103.1,4.3 103.5,4.6 104.0,3.1 104.4,2.0 104.8,2.9 105.3,2.7 105.7,2.7 106.1,6.8 106.6,8.7 107.0,7.5 107.4,6.5 107.8,6.2 108.3,6.1 108.7,5.8 109.1,5.3 109.6,5.5 110.0,6.3", "ret_12_1": 175.0, "ret_6_1": 107.0, "ret_3_1": 10.7, "volatility": 67.3, "traded_daily_cr": 53.0, "watch": "Nothing flagged", "from_12m_high": -10.5, "signal_rank": 7, "data_quality": "Green"}, {"rank": 3, "symbol": "ATHERENERG", "isin": "INE0LEZ01016", "qty": 10, "last_close": 1454.9, "amount": 14549.0, "spark_12m": "2.0,30.9 2.4,30.7 2.9,31.2 3.3,30.9 3.7,31.6 4.2,32.0 4.6,31.0 5.0,31.4 5.4,30.8 5.9,30.7 6.3,30.0 6.7,29.7 7.2,29.5 7.6,29.9 8.0,30.6 8.5,30.2 8.9,30.1 9.3,29.6 9.7,28.2 10.2,28.1 10.6,27.4 11.0,26.3 11.5,27.1 11.9,27.8 12.3,27.1 12.8,27.0 13.2,27.8 13.6,27.8 14.0,28.2 14.5,28.2 14.9,28.8 15.3,29.6 15.8,29.1 16.2,29.8 16.6,29.0 17.1,29.8 17.5,29.5 17.9,29.2 18.4,29.3 18.8,28.7 19.2,28.3 19.6,28.0 20.1,28.1 20.5,28.6 20.9,28.3 21.4,28.1 21.8,27.7 22.2,27.5 22.7,27.7 23.1,28.3 23.5,28.4 23.9,28.7 24.4,28.6 24.8,28.5 25.2,29.2 25.7,29.3 26.1,29.3 26.5,29.3 27.0,28.3 27.4,28.6 27.8,28.9 28.2,28.9 28.7,27.9 29.1,28.0 29.5,27.8 30.0,27.4 30.4,27.7 30.8,27.5 31.3,27.1 31.7,26.6 32.1,27.0 32.5,26.9 33.0,28.3 33.4,28.1 33.8,28.1 34.3,28.6 34.7,29.6 35.1,29.5 35.6,29.1 36.0,29.3 36.4,30.0 36.9,29.8 37.3,30.3 37.7,30.1 38.1,29.7 38.6,29.9 39.0,30.0 39.4,30.3 39.9,30.4 40.3,29.9 40.7,30.3 41.2,28.6 41.6,28.0 42.0,27.6 42.4,27.8 42.9,27.3 43.3,27.3 43.7,27.5 44.2,27.3 44.6,27.7 45.0,27.7 45.5,27.3 45.9,27.2 46.3,27.1 46.7,27.7 47.2,27.5 47.6,28.0 48.0,27.8 48.5,27.9 48.9,27.7 49.3,27.8 49.8,27.9 50.2,28.3 50.6,28.6 51.1,28.4 51.5,28.1 51.9,27.9 52.3,27.7 52.8,27.8 53.2,27.6 53.6,27.3 54.1,26.7 54.5,26.6 54.9,25.9 55.4,26.7 55.8,26.5 56.2,26.0 56.6,25.5 57.1,26.6 57.5,26.2 57.9,26.4 58.4,25.8 58.8,26.4 59.2,26.2 59.7,24.9 60.1,23.8 60.5,22.7 60.9,23.6 61.4,23.7 61.8,24.1 62.2,23.2 62.7,23.0 63.1,22.7 63.5,22.9 64.0,23.3 64.4,21.8 64.8,22.1 65.3,21.9 65.7,22.0 66.1,22.0 66.5,21.9 67.0,23.0 67.4,22.7 67.8,22.5 68.3,21.1 68.7,22.3 69.1,21.6 69.6,21.9 70.0,21.9 70.4,22.6 70.8,22.6 71.3,22.7 71.7,23.2 72.1,23.3 72.6,22.3 73.0,21.6 73.4,21.5 73.9,21.3 74.3,21.9 74.7,21.4 75.1,19.8 75.6,20.7 76.0,19.5 76.4,20.3 76.9,19.5 77.3,19.3 77.7,19.7 78.2,19.6 78.6,19.7 79.0,20.4 79.5,20.6 79.9,21.1 80.3,21.1 80.7,21.4 81.2,20.2 81.6,20.6 82.0,20.4 82.5,18.2 82.9,16.8 83.3,17.1 83.8,16.7 84.2,17.1 84.6,17.2 85.0,16.8 85.5,15.3 85.9,14.8 86.3,14.6 86.8,15.7 87.2,15.3 87.6,12.9 88.1,13.6 88.5,13.2 88.9,12.9 89.3,13.1 89.8,13.6 90.2,14.5 90.6,15.1 91.1,14.9 91.5,15.2 91.9,14.1 92.4,14.3 92.8,13.8 93.2,13.5 93.6,9.0 94.1,8.4 94.5,8.9 94.9,8.2 95.4,8.6 95.8,7.1 96.2,6.0 96.7,7.0 97.1,7.4 97.5,8.1 98.0,8.6 98.4,9.3 98.8,9.0 99.2,8.7 99.7,8.9 100.1,9.2 100.5,7.8 101.0,7.8 101.4,4.8 101.8,2.2 102.3,2.0 102.7,3.0 103.1,4.2 103.5,5.6 104.0,5.2 104.4,5.7 104.8,5.7 105.3,3.7 105.7,3.8 106.1,6.0 106.6,6.0 107.0,6.4 107.4,4.2 107.8,5.4 108.3,6.6 108.7,7.7 109.1,7.7 109.6,7.8 110.0,8.8", "ret_12_1": 166.0, "ret_6_1": 97.5, "ret_3_1": 31.1, "volatility": 49.4, "traded_daily_cr": 493.0, "watch": "Nothing flagged", "from_12m_high": -15.7, "signal_rank": 9, "data_quality": "Green"}, {"rank": 4, "symbol": "THANGAMAYL", "isin": "INE085J01014", "qty": 2, "last_close": 5011.5, "amount": 10023.0, "spark_12m": "2.0,30.9 2.4,31.1 2.9,31.4 3.3,31.4 3.7,31.4 4.2,31.6 4.6,31.7 5.0,31.6 5.4,31.6 5.9,31.2 6.3,31.3 6.7,31.6 7.2,31.2 7.6,31.5 8.0,31.6 8.5,31.5 8.9,31.8 9.3,31.9 9.7,31.9 10.2,31.9 10.6,31.9 11.0,31.9 11.5,32.0 11.9,31.5 12.3,31.6 12.8,31.3 13.2,31.4 13.6,31.3 14.0,30.8 14.5,28.3 14.9,25.9 15.3,25.7 15.8,23.9 16.2,25.3 16.6,24.8 17.1,24.1 17.5,24.4 17.9,24.5 18.4,24.7 18.8,24.9 19.2,25.1 19.6,25.2 20.1,26.0 20.5,24.8 20.9,24.8 21.4,24.7 21.8,24.8 22.2,24.7 22.7,24.1 23.1,25.2 23.5,24.6 23.9,24.8 24.4,24.9 24.8,25.2 25.2,24.7 25.7,24.9 26.1,24.9 26.5,25.0 27.0,25.0 27.4,24.9 27.8,24.4 28.2,24.6 28.7,24.2 29.1,23.8 29.5,23.7 30.0,24.5 30.4,25.0 30.8,25.0 31.3,25.0 31.7,24.9 32.1,24.7 32.5,24.8 33.0,24.2 33.4,23.4 33.8,21.4 34.3,21.2 34.7,22.7 35.1,22.3 35.6,21.9 36.0,21.5 36.4,21.8 36.9,22.1 37.3,22.1 37.7,21.2 38.1,22.6 38.6,22.9 39.0,23.8 39.4,22.8 39.9,23.4 40.3,24.3 40.7,24.9 41.2,25.1 41.6,24.5 42.0,25.1 42.4,23.9 42.9,22.1 43.3,22.2 43.7,22.3 44.2,22.5 44.6,22.9 45.0,22.1 45.5,22.3 45.9,22.6 46.3,23.4 46.7,23.0 47.2,22.8 47.6,22.0 48.0,21.5 48.5,21.0 48.9,20.8 49.3,21.4 49.8,22.7 50.2,22.6 50.6,22.2 51.1,22.9 51.5,22.1 51.9,23.1 52.3,23.0 52.8,23.3 53.2,23.6 53.6,23.4 54.1,23.3 54.5,24.1 54.9,24.3 55.4,25.2 55.8,24.4 56.2,22.8 56.6,23.7 57.1,23.7 57.5,23.0 57.9,23.1 58.4,21.9 58.8,21.3 59.2,20.3 59.7,20.0 60.1,19.8 60.5,19.5 60.9,19.1 61.4,19.0 61.8,19.3 62.2,19.8 62.7,19.8 63.1,20.4 63.5,21.7 64.0,21.7 64.4,20.8 64.8,20.7 65.3,20.6 65.7,20.8 66.1,20.6 66.5,20.7 67.0,20.1 67.4,19.9 67.8,19.1 68.3,20.5 68.7,22.4 69.1,22.5 69.6,22.7 70.0,22.8 70.4,23.1 70.8,22.5 71.3,21.8 71.7,21.3 72.1,21.6 72.6,21.5 73.0,21.6 73.4,21.0 73.9,19.4 74.3,18.9 74.7,17.2 75.1,16.1 75.6,12.0 76.0,13.0 76.4,12.2 76.9,12.3 77.3,12.4 77.7,12.6 78.2,12.2 78.6,12.1 79.0,12.4 79.5,11.4 79.9,12.5 80.3,12.4 80.7,11.8 81.2,12.8 81.6,12.4 82.0,11.6 82.5,10.0 82.9,7.1 83.3,9.6 83.8,7.6 84.2,8.4 84.6,7.7 85.0,7.2 85.5,4.8 85.9,6.0 86.3,6.3 86.8,8.0 87.2,6.8 87.6,5.9 88.1,7.2 88.5,6.9 88.9,7.2 89.3,6.8 89.8,6.7 90.2,4.5 90.6,4.3 91.1,2.0 91.5,2.8 91.9,6.8 92.4,10.4 92.8,13.7 93.2,15.1 93.6,16.5 94.1,15.2 94.5,14.1 94.9,13.4 95.4,13.0 95.8,13.7 96.2,13.1 96.7,13.4 97.1,12.5 97.5,13.0 98.0,12.2 98.4,12.0 98.8,12.4 99.2,12.2 99.7,12.2 100.1,12.7 100.5,12.2 101.0,12.1 101.4,12.5 101.8,12.6 102.3,13.2 102.7,13.6 103.1,13.3 103.5,13.1 104.0,12.3 104.4,12.9 104.8,14.3 105.3,14.5 105.7,14.2 106.1,15.4 106.6,15.3 107.0,16.0 107.4,14.7 107.8,15.3 108.3,14.3 108.7,13.2 109.1,14.4 109.6,14.2 110.0,14.9", "ret_12_1": 154.0, "ret_6_1": 66.3, "ret_3_1": -14.0, "volatility": 59.8, "traded_daily_cr": 71.0, "watch": "Nothing flagged", "from_12m_high": -31.4, "signal_rank": 11, "data_quality": "Green"}, {"rank": 5, "symbol": "RRKABEL", "isin": "INE777K01022", "qty": 6, "last_close": 2459.8, "amount": 14759.0, "spark_12m": "2.0,31.3 2.4,31.1 2.9,30.7 3.3,31.2 3.7,31.2 4.2,32.0 4.6,31.8 5.0,31.2 5.4,31.1 5.9,31.4 6.3,31.1 6.7,31.1 7.2,31.3 7.6,31.4 8.0,31.0 8.5,31.2 8.9,31.3 9.3,31.3 9.7,31.0 10.2,31.2 10.6,31.4 11.0,31.2 11.5,31.4 11.9,31.5 12.3,30.1 12.8,28.7 13.2,28.4 13.6,28.6 14.0,28.6 14.5,29.0 14.9,28.4 15.3,28.8 15.8,29.2 16.2,29.8 16.6,29.6 17.1,28.8 17.5,29.3 17.9,29.3 18.4,29.1 18.8,29.7 19.2,29.5 19.6,29.4 20.1,29.7 20.5,29.7 20.9,29.5 21.4,29.0 21.8,29.1 22.2,28.8 22.7,28.8 23.1,28.8 23.5,29.0 23.9,28.9 24.4,29.4 24.8,29.5 25.2,29.1 25.7,28.6 26.1,28.7 26.5,28.4 27.0,27.8 27.4,28.1 27.8,28.3 28.2,28.3 28.7,27.3 29.1,26.5 29.5,26.6 30.0,27.1 30.4,27.5 30.8,28.1 31.3,28.2 31.7,27.9 32.1,27.6 32.5,26.9 33.0,26.4 33.4,26.3 33.8,26.4 34.3,26.7 34.7,26.9 35.1,27.3 35.6,27.0 36.0,27.1 36.4,27.5 36.9,28.0 37.3,28.6 37.7,28.6 38.1,28.4 38.6,29.7 39.0,30.0 39.4,29.7 39.9,30.3 40.3,29.3 40.7,29.6 41.2,28.4 41.6,27.8 42.0,27.5 42.4,27.7 42.9,27.6 43.3,28.5 43.7,28.2 44.2,28.3 44.6,28.7 45.0,28.7 45.5,28.4 45.9,28.5 46.3,28.4 46.7,28.1 47.2,27.9 47.6,27.0 48.0,26.9 48.5,26.7 48.9,26.0 49.3,26.5 49.8,27.3 50.2,27.1 50.6,26.6 51.1,27.2 51.5,27.8 51.9,28.4 52.3,28.2 52.8,29.8 53.2,29.3 53.6,28.9 54.1,28.1 54.5,28.9 54.9,29.0 55.4,30.3 55.8,29.7 56.2,29.7 56.6,30.3 57.1,30.7 57.5,30.0 57.9,30.0 58.4,30.0 58.8,30.2 59.2,28.8 59.7,29.1 60.1,28.9 60.5,29.3 60.9,29.0 61.4,27.8 61.8,27.5 62.2,27.6 62.7,27.8 63.1,27.7 63.5,28.3 64.0,28.1 64.4,26.9 64.8,25.1 65.3,24.8 65.7,25.8 66.1,22.2 66.5,22.1 67.0,21.8 67.4,19.6 67.8,19.3 68.3,19.7 68.7,19.4 69.1,19.0 69.6,17.6 70.0,19.1 70.4,19.2 70.8,19.7 71.3,18.9 71.7,19.2 72.1,19.2 72.6,18.5 73.0,18.7 73.4,19.1 73.9,17.3 74.3,17.8 74.7,17.9 75.1,15.6 75.6,14.4 76.0,14.4 76.4,15.6 76.9,15.2 77.3,15.3 77.7,16.0 78.2,15.3 78.6,15.0 79.0,14.8 79.5,14.6 79.9,13.1 80.3,12.7 80.7,12.1 81.2,11.8 81.6,10.6 82.0,9.7 82.5,9.5 82.9,11.4 83.3,11.6 83.8,11.4 84.2,12.3 84.6,13.1 85.0,14.9 85.5,15.0 85.9,14.7 86.3,14.3 86.8,11.7 87.2,12.2 87.6,13.2 88.1,11.2 88.5,13.1 88.9,12.4 89.3,12.2 89.8,10.7 90.2,11.7 90.6,9.6 91.1,9.1 91.5,8.2 91.9,8.5 92.4,8.4 92.8,7.7 93.2,7.2 93.6,7.0 94.1,4.4 94.5,4.9 94.9,5.0 95.4,5.0 95.8,4.0 96.2,4.4 96.7,3.7 97.1,4.5 97.5,5.2 98.0,4.5 98.4,2.5 98.8,2.6 99.2,2.2 99.7,3.0 100.1,4.2 100.5,4.1 101.0,3.7 101.4,2.4 101.8,2.0 102.3,3.0 102.7,7.2 103.1,7.5 103.5,10.3 104.0,11.5 104.4,10.4 104.8,10.9 105.3,10.6 105.7,10.8 106.1,11.6 106.6,11.3 107.0,11.4 107.4,10.4 107.8,11.1 108.3,10.0 108.7,9.9 109.1,9.0 109.6,9.0 110.0,10.2", "ret_12_1": 126.0, "ret_6_1": 110.0, "ret_3_1": 18.2, "volatility": 44.0, "traded_daily_cr": 93.0, "watch": "Nothing flagged", "from_12m_high": -16.0, "signal_rank": 15, "data_quality": "Green"}, {"rank": 6, "symbol": "ACUTAAS", "isin": "INE00FF01025", "qty": 4, "last_close": 3214.4, "amount": 12858.0, "spark_12m": "2.0,30.2 2.4,30.2 2.9,30.3 3.3,30.3 3.7,30.8 4.2,31.5 4.6,31.6 5.0,32.0 5.4,31.2 5.9,31.1 6.3,30.9 6.7,30.9 7.2,30.9 7.6,30.7 8.0,30.1 8.5,29.7 8.9,29.7 9.3,29.1 9.7,29.0 10.2,27.8 10.6,26.4 11.0,26.1 11.5,26.7 11.9,27.4 12.3,26.8 12.8,27.0 13.2,27.3 13.6,27.1 14.0,26.8 14.5,25.8 14.9,25.5 15.3,26.3 15.8,26.4 16.2,26.4 16.6,26.5 17.1,27.1 17.5,27.4 17.9,27.0 18.4,27.1 18.8,27.0 19.2,26.9 19.6,26.8 20.1,27.2 20.5,25.0 20.9,26.1 21.4,26.0 21.8,26.1 22.2,25.4 22.7,26.2 23.1,26.6 23.5,26.7 23.9,27.1 24.4,27.1 24.8,27.8 25.2,27.6 25.7,27.4 26.1,27.7 26.5,27.6 27.0,28.1 27.4,27.2 27.8,27.7 28.2,28.0 28.7,27.8 29.1,27.4 29.5,27.2 30.0,27.8 30.4,27.8 30.8,27.8 31.3,27.7 31.7,27.1 32.1,26.5 32.5,26.6 33.0,26.3 33.4,26.4 33.8,26.4 34.3,26.7 34.7,27.4 35.1,27.5 35.6,27.4 36.0,27.1 36.4,27.2 36.9,27.4 37.3,28.1 37.7,28.4 38.1,27.9 38.6,27.8 39.0,26.8 39.4,25.1 39.9,24.2 40.3,24.5 40.7,24.2 41.2,23.8 41.6,23.5 42.0,23.6 42.4,23.6 42.9,23.4 43.3,22.8 43.7,23.0 44.2,22.2 44.6,23.2 45.0,22.9 45.5,22.4 45.9,21.6 46.3,22.1 46.7,22.0 47.2,21.5 47.6,21.5 48.0,21.3 48.5,21.1 48.9,21.4 49.3,21.0 49.8,22.1 50.2,20.4 50.6,20.2 51.1,21.4 51.5,20.5 51.9,21.0 52.3,21.0 52.8,22.3 53.2,21.3 53.6,19.6 54.1,20.1 54.5,20.3 54.9,18.3 55.4,20.0 55.8,17.9 56.2,16.7 56.6,16.5 57.1,16.3 57.5,19.2 57.9,22.0 58.4,20.7 58.8,20.7 59.2,19.2 59.7,19.3 60.1,18.8 60.5,18.4 60.9,19.7 61.4,19.1 61.8,18.8 62.2,18.2 62.7,18.7 63.1,18.0 63.5,18.5 64.0,18.4 64.4,17.1 64.8,17.5 65.3,17.0 65.7,15.9 66.1,14.9 66.5,15.1 67.0,14.7 67.4,14.2 67.8,14.1 68.3,13.2 68.7,14.0 69.1,12.9 69.6,14.2 70.0,14.2 70.4,13.3 70.8,12.2 71.3,12.3 71.7,10.8 72.1,11.4 72.6,11.7 73.0,10.3 73.4,10.8 73.9,9.1 74.3,10.5 74.7,10.3 75.1,9.1 75.6,8.7 76.0,6.6 76.4,6.8 76.9,8.3 77.3,8.2 77.7,9.2 78.2,8.9 78.6,9.5 79.0,10.8 79.5,10.8 79.9,9.0 80.3,7.7 80.7,7.6 81.2,7.3 81.6,7.4 82.0,7.0 82.5,3.6 82.9,4.1 83.3,3.6 83.8,2.0 84.2,2.0 84.6,4.3 85.0,5.8 85.5,5.0 85.9,5.0 86.3,5.7 86.8,4.5 87.2,5.0 87.6,3.9 88.1,3.4 88.5,3.0 88.9,2.5 89.3,2.2 89.8,2.4 90.2,5.0 90.6,7.5 91.1,6.1 91.5,7.0 91.9,6.9 92.4,7.8 92.8,9.4 93.2,9.3 93.6,7.9 94.1,7.2 94.5,7.5 94.9,7.0 95.4,7.2 95.8,7.7 96.2,8.8 96.7,9.4 97.1,7.8 97.5,8.3 98.0,5.8 98.4,7.9 98.8,8.1 99.2,8.6 99.7,8.6 100.1,6.8 100.5,7.5 101.0,6.6 101.4,7.2 101.8,8.7 102.3,8.6 102.7,9.1 103.1,8.2 103.5,8.6 104.0,8.5 104.4,8.5 104.8,7.7 105.3,5.1 105.7,5.9 106.1,7.4 106.6,6.4 107.0,6.8 107.4,5.2 107.8,5.4 108.3,8.1 108.7,7.4 109.1,7.2 109.6,7.3 110.0,8.1", "ret_12_1": 126.0, "ret_6_1": 36.7, "ret_3_1": -5.6, "volatility": 46.7, "traded_daily_cr": 101.0, "watch": "Nothing flagged", "from_12m_high": -13.0, "signal_rank": 16, "data_quality": "Green"}, {"rank": 7, "symbol": "DIACABS", "isin": "INE989C01038", "qty": 44, "last_close": 339.25, "amount": 14927.0, "spark_12m": "2.0,27.2 2.4,27.3 2.9,27.2 3.3,27.4 3.7,28.0 4.2,28.4 4.6,28.2 5.0,28.6 5.4,28.5 5.9,28.3 6.3,28.7 6.7,29.2 7.2,29.3 7.6,29.4 8.0,29.4 8.5,29.6 8.9,29.5 9.3,29.2 9.7,29.3 10.2,29.4 10.6,29.2 11.0,29.1 11.5,29.1 11.9,29.3 12.3,28.1 12.8,28.5 13.2,28.1 13.6,28.2 14.0,28.2 14.5,28.1 14.9,27.9 15.3,28.6 15.8,28.3 16.2,28.8 16.6,28.9 17.1,28.8 17.5,28.4 17.9,28.4 18.4,28.4 18.8,28.7 19.2,28.3 19.6,28.7 20.1,29.1 20.5,29.5 20.9,29.6 21.4,29.4 21.8,29.4 22.2,28.5 22.7,28.6 23.1,28.9 23.5,29.2 23.9,29.3 24.4,29.1 24.8,29.4 25.2,29.4 25.7,29.7 26.1,29.7 26.5,29.5 27.0,29.4 27.4,29.6 27.8,29.6 28.2,29.5 28.7,29.5 29.1,29.2 29.5,29.3 30.0,29.5 30.4,29.6 30.8,29.8 31.3,29.8 31.7,29.8 32.1,29.8 32.5,29.9 33.0,29.3 33.4,29.3 33.8,29.1 34.3,29.7 34.7,30.2 35.1,30.1 35.6,30.5 36.0,30.7 36.4,30.6 36.9,30.4 37.3,31.0 37.7,30.9 38.1,30.8 38.6,31.4 39.0,31.4 39.4,31.1 39.9,31.4 40.3,31.5 40.7,31.7 41.2,31.2 41.6,30.8 42.0,31.3 42.4,31.3 42.9,30.9 43.3,30.4 43.7,30.2 44.2,30.3 44.6,30.5 45.0,29.5 45.5,29.8 45.9,29.8 46.3,30.2 46.7,30.1 47.2,30.2 47.6,30.4 48.0,30.0 48.5,29.6 48.9,29.9 49.3,29.9 49.8,30.4 50.2,29.9 50.6,30.1 51.1,30.2 51.5,29.7 51.9,29.9 52.3,30.0 52.8,30.8 53.2,31.0 53.6,31.2 54.1,30.7 54.5,31.4 54.9,31.0 55.4,32.0 55.8,31.7 56.2,30.9 56.6,31.5 57.1,31.9 57.5,31.2 57.9,31.2 58.4,30.8 58.8,30.9 59.2,30.3 59.7,30.4 60.1,29.9 60.5,29.8 60.9,29.5 61.4,28.7 61.8,28.6 62.2,27.4 62.7,27.2 63.1,27.5 63.5,27.5 64.0,27.3 64.4,26.8 64.8,27.1 65.3,27.3 65.7,27.7 66.1,26.8 66.5,26.6 67.0,25.6 67.4,26.4 67.8,26.0 68.3,25.8 68.7,26.4 69.1,25.9 69.6,24.0 70.0,23.5 70.4,24.0 70.8,24.2 71.3,23.6 71.7,23.8 72.1,23.8 72.6,23.5 73.0,22.4 73.4,23.3 73.9,23.7 74.3,25.0 74.7,23.7 75.1,24.3 75.6,23.9 76.0,22.7 76.4,23.3 76.9,22.8 77.3,23.4 77.7,23.8 78.2,22.9 78.6,21.4 79.0,22.4 79.5,22.6 79.9,22.9 80.3,22.1 80.7,22.3 81.2,22.9 81.6,22.6 82.0,22.4 82.5,22.2 82.9,22.1 83.3,22.2 83.8,22.0 84.2,23.2 84.6,21.1 85.0,20.4 85.5,19.7 85.9,18.9 86.3,20.0 86.8,20.1 87.2,20.4 87.6,20.2 88.1,20.4 88.5,20.7 88.9,18.3 89.3,15.6 89.8,15.6 90.2,15.1 90.6,12.8 91.1,11.5 91.5,10.0 91.9,8.2 92.4,9.2 92.8,9.7 93.2,9.8 93.6,10.5 94.1,8.8 94.5,7.0 94.9,5.3 95.4,5.7 95.8,5.5 96.2,4.9 96.7,5.0 97.1,4.8 97.5,5.8 98.0,4.9 98.4,5.8 98.8,6.4 99.2,6.2 99.7,6.5 100.1,8.0 100.5,8.1 101.0,8.1 101.4,6.9 101.8,7.1 102.3,7.9 102.7,8.9 103.1,9.8 103.5,8.8 104.0,8.7 104.4,8.3 104.8,8.5 105.3,6.7 105.7,4.8 106.1,2.8 106.6,2.0 107.0,4.0 107.4,5.0 107.8,4.0 108.3,4.6 108.7,3.8 109.1,5.7 109.6,6.4 110.0,8.0", "ret_12_1": 124.0, "ret_6_1": 180.0, "ret_3_1": 61.7, "volatility": 53.6, "traded_daily_cr": 51.0, "watch": "Nothing flagged", "from_12m_high": -14.1, "signal_rank": 17, "data_quality": "Green"}, {"rank": 8, "symbol": "KIRLOSENG", "isin": "INE146L01010", "qty": 7, "last_close": 2141.2, "amount": 14988.0, "spark_12m": "2.0,30.3 2.4,30.3 2.9,30.5 3.3,30.2 3.7,30.7 4.2,31.2 4.6,31.1 5.0,31.1 5.4,31.0 5.9,31.4 6.3,31.6 6.7,31.8 7.2,31.8 7.6,31.8 8.0,31.6 8.5,31.7 8.9,32.0 9.3,31.9 9.7,31.8 10.2,31.6 10.6,31.8 11.0,31.6 11.5,31.5 11.9,31.5 12.3,30.7 12.8,29.6 13.2,29.4 13.6,29.4 14.0,29.7 14.5,29.4 14.9,29.4 15.3,29.9 15.8,30.3 16.2,30.5 16.6,30.7 17.1,28.7 17.5,28.2 17.9,28.1 18.4,27.7 18.8,27.2 19.2,26.6 19.6,26.5 20.1,26.8 20.5,27.4 20.9,26.9 21.4,27.1 21.8,27.2 22.2,27.5 22.7,27.6 23.1,27.7 23.5,28.2 23.9,26.8 24.4,27.4 24.8,28.0 25.2,27.5 25.7,27.7 26.1,27.6 26.5,27.1 27.0,27.3 27.4,25.7 27.8,24.7 28.2,24.6 28.7,25.4 29.1,24.2 29.5,24.4 30.0,25.0 30.4,24.9 30.8,25.8 31.3,25.7 31.7,25.8 32.1,25.6 32.5,25.1 33.0,25.2 33.4,25.3 33.8,25.8 34.3,26.5 34.7,26.9 35.1,27.5 35.6,27.0 36.0,26.7 36.4,26.7 36.9,27.4 37.3,27.9 37.7,27.9 38.1,27.7 38.6,28.0 39.0,28.0 39.4,27.7 39.9,27.6 40.3,26.6 40.7,27.0 41.2,26.5 41.6,25.6 42.0,26.2 42.4,26.7 42.9,25.8 43.3,25.0 43.7,23.9 44.2,23.7 44.6,23.0 45.0,22.4 45.5,22.1 45.9,22.3 46.3,22.2 46.7,22.3 47.2,22.6 47.6,22.7 48.0,22.5 48.5,22.7 48.9,22.7 49.3,22.5 49.8,22.3 50.2,21.4 50.6,20.6 51.1,21.6 51.5,21.9 51.9,21.7 52.3,21.4 52.8,21.7 53.2,21.4 53.6,21.9 54.1,22.0 54.5,22.2 54.9,23.0 55.4,24.6 55.8,23.9 56.2,22.7 56.6,23.5 57.1,23.9 57.5,23.2 57.9,22.9 58.4,22.3 58.8,22.6 59.2,21.4 59.7,21.6 60.1,21.3 60.5,21.1 60.9,19.1 61.4,18.8 61.8,18.7 62.2,18.4 62.7,17.9 63.1,18.4 63.5,18.9 64.0,19.2 64.4,17.6 64.8,16.9 65.3,17.3 65.7,17.3 66.1,16.9 66.5,16.6 67.0,17.1 67.4,16.8 67.8,16.8 68.3,18.0 68.7,19.8 69.1,19.1 69.6,19.1 70.0,16.6 70.4,17.3 70.8,18.0 71.3,17.9 71.7,17.7 72.1,17.8 72.6,17.2 73.0,16.4 73.4,15.0 73.9,13.3 74.3,13.4 74.7,14.5 75.1,13.9 75.6,12.9 76.0,13.5 76.4,14.6 76.9,14.6 77.3,15.2 77.7,15.6 78.2,13.9 78.6,13.2 79.0,13.4 79.5,12.2 79.9,12.3 80.3,12.1 80.7,5.1 81.2,3.0 81.6,2.0 82.0,3.4 82.5,4.2 82.9,5.5 83.3,5.9 83.8,6.3 84.2,7.9 84.6,7.3 85.0,7.2 85.5,7.1 85.9,4.5 86.3,3.3 86.8,4.3 87.2,5.6 87.6,4.6 88.1,5.0 88.5,7.5 88.9,8.1 89.3,8.1 89.8,8.7 90.2,8.8 90.6,8.7 91.1,7.0 91.5,8.6 91.9,8.8 92.4,9.6 92.8,8.6 93.2,8.0 93.6,7.1 94.1,7.7 94.5,7.6 94.9,9.1 95.4,9.7 95.8,10.2 96.2,11.0 96.7,10.9 97.1,10.2 97.5,10.2 98.0,9.8 98.4,10.6 98.8,9.3 99.2,10.2 99.7,10.8 100.1,11.5 100.5,11.3 101.0,10.2 101.4,9.8 101.8,10.2 102.3,9.5 102.7,9.1 103.1,7.2 103.5,8.4 104.0,8.9 104.4,7.1 104.8,8.1 105.3,8.3 105.7,9.0 106.1,11.2 106.6,11.3 107.0,9.8 107.4,9.1 107.8,9.6 108.3,9.1 108.7,8.1 109.1,9.1 109.6,9.6 110.0,9.5", "ret_12_1": 123.0, "ret_6_1": 58.2, "ret_3_1": -11.2, "volatility": 49.9, "traded_daily_cr": 87.0, "watch": "Nothing flagged", "from_12m_high": -16.5, "signal_rank": 18, "data_quality": "Green"}, {"rank": 9, "symbol": "E2E", "isin": "INE255Z01027", "qty": 23, "last_close": 625.9, "amount": 14396.0, "spark_12m": "2.0,25.4 2.4,24.4 2.9,23.5 3.3,24.3 3.7,23.7 4.2,22.9 4.6,23.7 5.0,24.4 5.4,23.4 5.9,22.4 6.3,21.3 6.7,21.1 7.2,21.2 7.6,22.8 8.0,23.1 8.5,23.8 8.9,24.4 9.3,24.4 9.7,24.3 10.2,24.1 10.6,24.5 11.0,24.4 11.5,24.3 11.9,25.2 12.3,24.5 12.8,24.9 13.2,25.1 13.6,24.9 14.0,25.0 14.5,25.3 14.9,24.9 15.3,25.3 15.8,25.1 16.2,25.3 16.6,26.1 17.1,26.1 17.5,26.8 17.9,27.8 18.4,28.0 18.8,28.1 19.2,28.0 19.6,28.1 20.1,28.8 20.5,29.7 20.9,29.7 21.4,29.6 21.8,29.8 22.2,30.1 22.7,30.0 23.1,30.5 23.5,30.9 23.9,30.5 24.4,31.0 24.8,31.6 25.2,30.8 25.7,31.2 26.1,31.1 26.5,31.1 27.0,31.1 27.4,31.5 27.8,31.6 28.2,31.7 28.7,31.3 29.1,31.2 29.5,31.1 30.0,31.2 30.4,31.4 30.8,32.0 31.3,31.9 31.7,31.8 32.1,31.7 32.5,31.6 33.0,31.2 33.4,31.5 33.8,31.6 34.3,31.5 34.7,31.5 35.1,31.6 35.6,31.8 36.0,31.6 36.4,30.3 36.9,30.2 37.3,30.8 37.7,31.3 38.1,31.2 38.6,31.5 39.0,31.5 39.4,31.3 39.9,31.5 40.3,31.0 40.7,29.0 41.2,28.0 41.6,29.0 42.0,29.5 42.4,28.7 42.9,27.8 43.3,28.2 43.7,27.9 44.2,28.4 44.6,28.8 45.0,28.2 45.5,28.3 45.9,26.5 46.3,25.8 46.7,26.4 47.2,28.2 47.6,29.0 48.0,28.3 48.5,28.0 48.9,28.2 49.3,28.9 49.8,29.7 50.2,29.7 50.6,29.8 51.1,29.9 51.5,29.1 51.9,29.4 52.3,29.6 52.8,29.9 53.2,30.4 53.6,30.5 54.1,30.1 54.5,30.0 54.9,30.1 55.4,30.7 55.8,30.7 56.2,30.2 56.6,30.9 57.1,31.4 57.5,30.8 57.9,30.2 58.4,29.9 58.8,29.6 59.2,28.9 59.7,29.1 60.1,29.0 60.5,28.9 60.9,28.1 61.4,27.4 61.8,26.8 62.2,27.4 62.7,26.6 63.1,26.0 63.5,26.2 64.0,26.2 64.4,25.3 64.8,25.7 65.3,26.0 65.7,26.3 66.1,26.6 66.5,25.8 67.0,24.9 67.4,23.9 67.8,23.0 68.3,21.9 68.7,23.0 69.1,24.1 69.6,24.0 70.0,24.9 70.4,25.5 70.8,24.5 71.3,23.6 71.7,23.1 72.1,22.1 72.6,21.3 73.0,20.2 73.4,19.8 73.9,20.0 74.3,18.8 74.7,17.5 75.1,18.8 75.6,17.6 76.0,16.3 76.4,17.6 76.9,19.0 77.3,20.2 77.7,21.4 78.2,20.3 78.6,21.1 79.0,20.6 79.5,20.3 79.9,19.1 80.3,17.9 80.7,16.6 81.2,17.5 81.6,18.4 82.0,18.7 82.5,19.8 82.9,19.7 83.3,19.3 83.8,20.2 84.2,20.6 84.6,20.6 85.0,21.3 85.5,20.8 85.9,19.6 86.3,19.6 86.8,20.3 87.2,19.8 87.6,18.8 88.1,18.1 88.5,19.2 88.9,18.0 89.3,16.7 89.8,15.3 90.2,13.9 90.6,12.4 91.1,10.8 91.5,12.4 91.9,13.9 92.4,13.8 92.8,12.3 93.2,10.8 93.6,9.1 94.1,7.4 94.5,6.9 94.9,8.8 95.4,7.1 95.8,5.6 96.2,5.3 96.7,5.1 97.1,3.2 97.5,2.0 98.0,3.3 98.4,5.4 98.8,5.8 99.2,5.9 99.7,6.5 100.1,7.5 100.5,6.5 101.0,6.2 101.4,6.3 101.8,6.1 102.3,6.0 102.7,6.8 103.1,7.7 103.5,7.2 104.0,5.4 104.4,6.2 104.8,7.0 105.3,6.9 105.7,6.6 106.1,8.5 106.6,7.3 107.0,7.0 107.4,6.8 107.8,7.7 108.3,7.0 108.7,5.1 109.1,4.4 109.6,4.1 110.0,5.7", "ret_12_1": 109.0, "ret_6_1": 186.0, "ret_3_1": 56.0, "volatility": 56.2, "traded_daily_cr": 49.0, "watch": "Nothing flagged", "from_12m_high": -8.8, "signal_rank": 20, "data_quality": "Green"}, {"rank": 10, "symbol": "LAURUSLABS", "isin": "INE947Q01028", "qty": 7, "last_close": 2010.7, "amount": 14075.0, "spark_12m": "2.0,29.5 2.4,30.2 2.9,30.1 3.3,30.1 3.7,30.4 4.2,32.0 4.6,31.8 5.0,31.8 5.4,31.0 5.9,31.2 6.3,31.2 6.7,31.2 7.2,31.5 7.6,31.2 8.0,30.9 8.5,31.0 8.9,30.9 9.3,30.9 9.7,31.0 10.2,30.3 10.6,29.8 11.0,29.7 11.5,29.5 11.9,29.7 12.3,29.3 12.8,28.8 13.2,28.8 13.6,28.6 14.0,29.0 14.5,28.4 14.9,28.2 15.3,28.3 15.8,28.3 16.2,27.8 16.6,28.2 17.1,28.1 17.5,27.9 17.9,27.8 18.4,27.3 18.8,27.6 19.2,28.1 19.6,28.1 20.1,28.4 20.5,28.3 20.9,28.4 21.4,28.1 21.8,27.7 22.2,27.0 22.7,27.1 23.1,27.3 23.5,27.4 23.9,27.5 24.4,27.2 24.8,27.7 25.2,27.3 25.7,27.4 26.1,27.3 26.5,27.5 27.0,27.7 27.4,27.8 27.8,27.6 28.2,27.4 28.7,26.7 29.1,26.2 29.5,26.1 30.0,25.7 30.4,25.7 30.8,25.8 31.3,25.5 31.7,25.1 32.1,25.1 32.5,25.2 33.0,25.2 33.4,24.9 33.8,24.6 34.3,25.3 34.7,25.7 35.1,26.7 35.6,26.4 36.0,25.6 36.4,25.9 36.9,26.2 37.3,26.9 37.7,28.1 38.1,27.7 38.6,27.4 39.0,27.8 39.4,27.8 39.9,28.5 40.3,28.7 40.7,29.0 41.2,28.4 41.6,28.3 42.0,28.7 42.4,29.0 42.9,28.2 43.3,28.7 43.7,27.5 44.2,27.3 44.6,27.5 45.0,27.5 45.5,27.5 45.9,26.9 46.3,27.3 46.7,27.3 47.2,27.4 47.6,27.1 48.0,25.9 48.5,25.5 48.9,25.9 49.3,26.2 49.8,27.0 50.2,26.7 50.6,27.2 51.1,27.3 51.5,26.9 51.9,26.8 52.3,26.6 52.8,27.7 53.2,28.8 53.6,28.6 54.1,28.2 54.5,29.2 54.9,28.1 55.4,28.8 55.8,28.0 56.2,27.2 56.6,27.6 57.1,28.0 57.5,26.8 57.9,26.7 58.4,26.4 58.8,26.4 59.2,25.8 59.7,25.7 60.1,25.4 60.5,25.6 60.9,24.9 61.4,24.6 61.8,24.4 62.2,24.6 62.7,25.0 63.1,25.4 63.5,24.6 64.0,25.0 64.4,24.7 64.8,25.6 65.3,25.2 65.7,25.3 66.1,23.7 66.5,23.7 67.0,23.4 67.4,22.7 67.8,22.1 68.3,21.2 68.7,21.1 69.1,20.8 69.6,19.9 70.0,19.7 70.4,19.6 70.8,19.2 71.3,18.8 71.7,19.1 72.1,19.2 72.6,18.9 73.0,18.5 73.4,18.3 73.9,18.8 74.3,18.1 74.7,18.3 75.1,18.0 75.6,17.1 76.0,16.7 76.4,17.7 76.9,17.2 77.3,18.2 77.7,18.1 78.2,18.0 78.6,18.1 79.0,18.4 79.5,18.6 79.9,18.6 80.3,17.5 80.7,16.9 81.2,15.8 81.6,16.5 82.0,16.6 82.5,15.3 82.9,14.9 83.3,15.5 83.8,14.6 84.2,14.3 84.6,14.6 85.0,15.9 85.5,16.1 85.9,15.1 86.3,14.4 86.8,13.9 87.2,13.8 87.6,14.0 88.1,13.9 88.5,14.6 88.9,13.9 89.3,13.0 89.8,13.4 90.2,13.6 90.6,12.8 91.1,10.0 91.5,8.9 91.9,8.3 92.4,8.3 92.8,7.4 93.2,7.6 93.6,6.6 94.1,7.0 94.5,7.1 94.9,6.7 95.4,6.5 95.8,6.4 96.2,6.6 96.7,6.6 97.1,8.2 97.5,7.6 98.0,7.5 98.4,7.8 98.8,7.2 99.2,7.8 99.7,7.8 100.1,6.2 100.5,5.7 101.0,4.6 101.4,4.4 101.8,5.0 102.3,6.3 102.7,6.2 103.1,6.1 103.5,6.8 104.0,5.9 104.4,4.2 104.8,4.4 105.3,4.2 105.7,3.6 106.1,4.7 106.6,5.2 107.0,4.1 107.4,4.0 107.8,2.4 108.3,2.7 108.7,2.0 109.1,2.2 109.6,2.7 110.0,2.6", "ret_12_1": 109.0, "ret_6_1": 94.4, "ret_3_1": 27.2, "volatility": 28.1, "traded_daily_cr": 300.0, "watch": "Nothing flagged", "from_12m_high": -1.1, "signal_rank": 21, "data_quality": "Green"}]}, "prices": {"TDPOWERSYS": {"2026-09-28": {"open": 730.05, "close": 722.0, "src": "yahoo"}}, "AEROFLEX": {"2026-09-28": {"open": 524.25, "close": 513.4, "src": "yahoo"}}, "E2E": {"2026-09-28": {"open": 650.0, "close": 625.9, "src": "yahoo"}}, "LAURUSLABS": {"2026-09-28": {"open": 2000.0, "close": 2010.7, "src": "yahoo"}}, "NIFTY50": {"2026-09-28": {"open": 23064.9, "close": 22780.25, "src": "yahoo"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 03:09", "days": 7, "items": [{"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks With Earnings Growth Over 17%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-earnings-001032785.html", "source": "Simply Wall St.", "published": "2026-09-29 00:10", "score": 0.888, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear S</t>
+          <t>{"batch": {"batch_id": "2026-09-28", "title": "SwingScope batch 2026-09-28", "signal_date": "2026-09-28", "exit_date_est": "2026-10-27", "hold_sessions": 21, "universe": "liquidity top 400 of all NSE stocks", "capital": 139903.0, "est_costs": 859.0, "cost_pct": 0.6, "regime": "Down", "regime_note": "the signal's weakest regime historically", "warnings": "0 of 10", "evidence": ["Backtest, 2017\u20132026 | Replayed point in time on your survivorship-free archive. Not live results. | Signal strength | IC +0.041 | rank IC over 113 monthly dates, 2017-2026 (t 2.52); validated benchmark 0.026 | Top vs bottom decile | +1.89% | per 21-session hold, before costs (t 2.94) | Top-10 picks | +1.45% | per hold after 0.60% costs; Nifty 50 earned +1.02% before costs | Entry timing | Open wins | buying at the open beat all 30 support-entry rules (best -0.12% per hold) | Down markets | IC +0.009 | over 27 down-regime dates, against +0.050 over 86 up-regime dates", "Live record | No results yet | The first live result arrives when this system finishes its first batch. Live results are kept apart from the backtest and never mixed in."], "stocks": [{"rank": 1, "symbol": "TDPOWERSYS", "isin": "INE419M01035", "qty": 20, "last_close": 722.0, "amount": 14440.0, "spark_12m": "2.0,31.7 2.4,32.0 2.9,31.7 3.3,31.1 3.7,31.1 4.2,31.1 4.6,31.0 5.0,30.6 5.4,30.4 5.9,29.2 6.3,29.3 6.7,29.5 7.2,29.8 7.6,30.1 8.0,30.4 8.5,30.5 8.9,30.3 9.3,29.4 9.7,29.3 10.2,28.8 10.6,29.1 11.0,28.9 11.5,29.1 11.9,29.2 12.3,29.1 12.8,29.0 13.2,28.4 13.6,28.0 14.0,25.5 14.5,24.3 14.9,24.2 15.3,24.8 15.8,25.3 16.2,25.2 16.6,25.4 17.1,24.2 17.5,25.4 17.9,25.2 18.4,25.2 18.8,25.7 19.2,25.8 19.6,25.9 20.1,26.9 20.5,25.8 20.9,25.9 21.4,24.9 21.8,24.9 22.2,25.4 22.7,25.0 23.1,25.0 23.5,25.8 23.9,26.8 24.4,27.7 24.8,28.3 25.2,27.7 25.7,28.1 26.1,28.2 26.5,27.9 27.0,27.6 27.4,27.9 27.8,27.1 28.2,27.6 28.7,27.1 29.1,26.4 29.5,26.7 30.0,27.0 30.4,27.3 30.8,27.7 31.3,27.5 31.7,27.5 32.1,28.3 32.5,28.0 33.0,27.7 33.4,27.9 33.8,27.5 34.3,27.9 34.7,28.3 35.1,28.8 35.6,27.9 36.0,28.2 36.4,28.5 36.9,28.7 37.3,29.2 37.7,29.4 38.1,29.5 38.6,29.7 39.0,29.6 39.4,28.8 39.9,28.2 40.3,26.7 40.7,26.2 41.2,24.3 41.6,24.1 42.0,24.5 42.4,25.2 42.9,24.8 43.3,23.3 43.7,22.8 44.2,23.4 44.6,23.8 45.0,23.1 45.5,22.8 45.9,22.8 46.3,22.4 46.7,22.4 47.2,21.8 47.6,22.3 48.0,22.5 48.5,22.5 48.9,21.8 49.3,22.2 49.8,22.6 50.2,22.4 50.6,22.5 51.1,23.5 51.5,24.3 51.9,24.7 52.3,24.4 52.8,25.3 53.2,24.9 53.6,24.3 54.1,23.7 54.5,23.8 54.9,23.0 55.4,24.2 55.8,23.1 56.2,22.3 56.6,23.4 57.1,23.3 57.5,23.0 57.9,23.0 58.4,22.5 58.8,22.5 59.2,22.4 59.7,22.6 60.1,21.2 60.5,21.5 60.9,20.8 61.4,20.0 61.8,19.2 62.2,18.3 62.7,18.6 63.1,17.4 63.5,17.2 64.0,16.0 64.4,16.6 64.8,15.0 65.3,15.0 65.7,14.8 66.1,14.6 66.5,14.2 67.0,14.5 67.4,12.2 67.8,13.0 68.3,14.1 68.7,14.4 69.1,14.2 69.6,14.0 70.0,10.4 70.4,9.9 70.8,11.9 71.3,12.6 71.7,10.6 72.1,10.8 72.6,10.7 73.0,8.8 73.4,9.8 73.9,10.2 74.3,12.7 74.7,12.5 75.1,11.1 75.6,10.0 76.0,10.3 76.4,12.8 76.9,12.6 77.3,14.8 77.7,15.6 78.2,13.7 78.6,13.6 79.0,14.4 79.5,12.7 79.9,11.6 80.3,11.5 80.7,10.0 81.2,9.2 81.6,11.7 82.0,12.0 82.5,12.6 82.9,12.4 83.3,13.7 83.8,13.8 84.2,16.6 84.6,14.2 85.0,15.7 85.5,16.9 85.9,16.6 86.3,14.9 86.8,14.9 87.2,15.6 87.6,14.2 88.1,15.6 88.5,15.5 88.9,15.2 89.3,15.5 89.8,14.6 90.2,15.2 90.6,15.9 91.1,15.2 91.5,15.9 91.9,18.1 92.4,17.5 92.8,15.5 93.2,16.0 93.6,15.5 94.1,13.5 94.5,12.7 94.9,11.8 95.4,12.5 95.8,11.4 96.2,5.6 96.7,5.6 97.1,5.5 97.5,3.7 98.0,2.7 98.4,3.8 98.8,4.9 99.2,4.1 99.7,3.4 100.1,6.2 100.5,6.3 101.0,5.6 101.4,4.9 101.8,3.6 102.3,4.6 102.7,5.9 103.1,6.6 103.5,5.6 104.0,6.0 104.4,4.0 104.8,4.8 105.3,4.4 105.7,2.0 106.1,6.5 106.6,8.1 107.0,6.7 107.4,4.3 107.8,5.2 108.3,4.7 108.7,4.2 109.1,5.5 109.6,5.0 110.0,6.7", "ret_12_1": 177.0, "ret_6_1": 72.2, "ret_3_1": 19.6, "volatility": 60.1, "traded_daily_cr": 128.0, "watch": "Nothing flagged", "from_12m_high": -10.3, "signal_rank": 6, "data_quality": "Green"}, {"rank": 2, "symbol": "AEROFLEX", "isin": "INE024001021", "qty": 29, "last_close": 513.4, "amount": 14889.0, "spark_12m": "2.0,29.8 2.4,29.6 2.9,29.5 3.3,30.0 3.7,30.1 4.2,30.5 4.6,30.8 5.0,30.9 5.4,30.9 5.9,30.5 6.3,30.7 6.7,30.8 7.2,30.9 7.6,31.0 8.0,31.0 8.5,31.1 8.9,31.2 9.3,31.2 9.7,31.2 10.2,31.2 10.6,31.4 11.0,31.1 11.5,31.0 11.9,31.0 12.3,31.0 12.8,30.1 13.2,30.1 13.6,30.5 14.0,30.0 14.5,29.8 14.9,30.3 15.3,30.5 15.8,30.0 16.2,30.0 16.6,30.2 17.1,30.2 17.5,30.1 17.9,29.9 18.4,30.1 18.8,30.3 19.2,30.2 19.6,30.2 20.1,30.5 20.5,30.9 20.9,30.2 21.4,30.2 21.8,30.4 22.2,30.0 22.7,30.2 23.1,30.3 23.5,30.6 23.9,30.6 24.4,30.7 24.8,31.3 25.2,31.0 25.7,30.7 26.1,30.9 26.5,30.7 27.0,30.3 27.4,30.5 27.8,30.3 28.2,30.7 28.7,29.5 29.1,29.2 29.5,28.8 30.0,28.6 30.4,28.9 30.8,29.1 31.3,29.3 31.7,29.5 32.1,29.6 32.5,29.2 33.0,29.0 33.4,29.3 33.8,29.1 34.3,29.9 34.7,30.2 35.1,30.2 35.6,30.5 36.0,30.7 36.4,30.8 36.9,30.9 37.3,31.3 37.7,31.8 38.1,31.5 38.6,32.0 39.0,31.7 39.4,31.4 39.9,30.4 40.3,30.6 40.7,31.0 41.2,30.1 41.6,29.9 42.0,29.9 42.4,30.1 42.9,29.3 43.3,29.4 43.7,29.6 44.2,29.5 44.6,30.0 45.0,29.6 45.5,28.5 45.9,27.1 46.3,27.0 46.7,27.3 47.2,27.6 47.6,27.7 48.0,27.0 48.5,26.9 48.9,26.5 49.3,27.2 49.8,27.7 50.2,27.3 50.6,27.6 51.1,27.9 51.5,27.5 51.9,26.5 52.3,26.3 52.8,26.5 53.2,25.6 53.6,25.3 54.1,25.6 54.5,26.8 54.9,26.6 55.4,27.3 55.8,25.3 56.2,25.3 56.6,26.1 57.1,26.2 57.5,25.4 57.9,25.2 58.4,25.0 58.8,25.7 59.2,24.6 59.7,23.6 60.1,22.6 60.5,22.6 60.9,22.3 61.4,22.1 61.8,21.0 62.2,21.7 62.7,22.6 63.1,21.5 63.5,22.1 64.0,23.4 64.4,22.2 64.8,22.3 65.3,21.4 65.7,21.4 66.1,21.6 66.5,20.5 67.0,18.6 67.4,13.6 67.8,11.7 68.3,14.7 68.7,17.1 69.1,17.1 69.6,17.4 70.0,16.7 70.4,16.8 70.8,15.9 71.3,15.2 71.7,16.0 72.1,14.3 72.6,13.5 73.0,14.3 73.4,14.0 73.9,14.4 74.3,15.4 74.7,13.1 75.1,12.1 75.6,11.7 76.0,13.1 76.4,14.6 76.9,12.7 77.3,13.5 77.7,13.9 78.2,11.1 78.6,8.9 79.0,9.4 79.5,6.5 79.9,8.1 80.3,6.8 80.7,6.6 81.2,7.1 81.6,8.8 82.0,9.7 82.5,9.6 82.9,9.4 83.3,8.1 83.8,8.9 84.2,10.5 84.6,10.3 85.0,13.6 85.5,14.5 85.9,14.2 86.3,13.6 86.8,13.0 87.2,13.8 87.6,13.0 88.1,13.8 88.5,13.8 88.9,14.1 89.3,13.6 89.8,14.0 90.2,13.1 90.6,13.0 91.1,13.2 91.5,11.2 91.9,10.9 92.4,12.6 92.8,12.0 93.2,12.3 93.6,9.9 94.1,10.5 94.5,11.8 94.9,12.7 95.4,13.1 95.8,12.9 96.2,11.2 96.7,11.1 97.1,10.2 97.5,10.5 98.0,8.3 98.4,9.2 98.8,9.1 99.2,7.1 99.7,7.0 100.1,7.6 100.5,4.7 101.0,5.7 101.4,4.3 101.8,5.5 102.3,3.6 102.7,4.4 103.1,4.3 103.5,4.6 104.0,3.1 104.4,2.0 104.8,2.9 105.3,2.7 105.7,2.7 106.1,6.8 106.6,8.7 107.0,7.5 107.4,6.5 107.8,6.2 108.3,6.1 108.7,5.8 109.1,5.3 109.6,5.5 110.0,6.3", "ret_12_1": 175.0, "ret_6_1": 107.0, "ret_3_1": 10.7, "volatility": 67.3, "traded_daily_cr": 53.0, "watch": "Nothing flagged", "from_12m_high": -10.5, "signal_rank": 7, "data_quality": "Green"}, {"rank": 3, "symbol": "ATHERENERG", "isin": "INE0LEZ01016", "qty": 10, "last_close": 1454.9, "amount": 14549.0, "spark_12m": "2.0,30.9 2.4,30.7 2.9,31.2 3.3,30.9 3.7,31.6 4.2,32.0 4.6,31.0 5.0,31.4 5.4,30.8 5.9,30.7 6.3,30.0 6.7,29.7 7.2,29.5 7.6,29.9 8.0,30.6 8.5,30.2 8.9,30.1 9.3,29.6 9.7,28.2 10.2,28.1 10.6,27.4 11.0,26.3 11.5,27.1 11.9,27.8 12.3,27.1 12.8,27.0 13.2,27.8 13.6,27.8 14.0,28.2 14.5,28.2 14.9,28.8 15.3,29.6 15.8,29.1 16.2,29.8 16.6,29.0 17.1,29.8 17.5,29.5 17.9,29.2 18.4,29.3 18.8,28.7 19.2,28.3 19.6,28.0 20.1,28.1 20.5,28.6 20.9,28.3 21.4,28.1 21.8,27.7 22.2,27.5 22.7,27.7 23.1,28.3 23.5,28.4 23.9,28.7 24.4,28.6 24.8,28.5 25.2,29.2 25.7,29.3 26.1,29.3 26.5,29.3 27.0,28.3 27.4,28.6 27.8,28.9 28.2,28.9 28.7,27.9 29.1,28.0 29.5,27.8 30.0,27.4 30.4,27.7 30.8,27.5 31.3,27.1 31.7,26.6 32.1,27.0 32.5,26.9 33.0,28.3 33.4,28.1 33.8,28.1 34.3,28.6 34.7,29.6 35.1,29.5 35.6,29.1 36.0,29.3 36.4,30.0 36.9,29.8 37.3,30.3 37.7,30.1 38.1,29.7 38.6,29.9 39.0,30.0 39.4,30.3 39.9,30.4 40.3,29.9 40.7,30.3 41.2,28.6 41.6,28.0 42.0,27.6 42.4,27.8 42.9,27.3 43.3,27.3 43.7,27.5 44.2,27.3 44.6,27.7 45.0,27.7 45.5,27.3 45.9,27.2 46.3,27.1 46.7,27.7 47.2,27.5 47.6,28.0 48.0,27.8 48.5,27.9 48.9,27.7 49.3,27.8 49.8,27.9 50.2,28.3 50.6,28.6 51.1,28.4 51.5,28.1 51.9,27.9 52.3,27.7 52.8,27.8 53.2,27.6 53.6,27.3 54.1,26.7 54.5,26.6 54.9,25.9 55.4,26.7 55.8,26.5 56.2,26.0 56.6,25.5 57.1,26.6 57.5,26.2 57.9,26.4 58.4,25.8 58.8,26.4 59.2,26.2 59.7,24.9 60.1,23.8 60.5,22.7 60.9,23.6 61.4,23.7 61.8,24.1 62.2,23.2 62.7,23.0 63.1,22.7 63.5,22.9 64.0,23.3 64.4,21.8 64.8,22.1 65.3,21.9 65.7,22.0 66.1,22.0 66.5,21.9 67.0,23.0 67.4,22.7 67.8,22.5 68.3,21.1 68.7,22.3 69.1,21.6 69.6,21.9 70.0,21.9 70.4,22.6 70.8,22.6 71.3,22.7 71.7,23.2 72.1,23.3 72.6,22.3 73.0,21.6 73.4,21.5 73.9,21.3 74.3,21.9 74.7,21.4 75.1,19.8 75.6,20.7 76.0,19.5 76.4,20.3 76.9,19.5 77.3,19.3 77.7,19.7 78.2,19.6 78.6,19.7 79.0,20.4 79.5,20.6 79.9,21.1 80.3,21.1 80.7,21.4 81.2,20.2 81.6,20.6 82.0,20.4 82.5,18.2 82.9,16.8 83.3,17.1 83.8,16.7 84.2,17.1 84.6,17.2 85.0,16.8 85.5,15.3 85.9,14.8 86.3,14.6 86.8,15.7 87.2,15.3 87.6,12.9 88.1,13.6 88.5,13.2 88.9,12.9 89.3,13.1 89.8,13.6 90.2,14.5 90.6,15.1 91.1,14.9 91.5,15.2 91.9,14.1 92.4,14.3 92.8,13.8 93.2,13.5 93.6,9.0 94.1,8.4 94.5,8.9 94.9,8.2 95.4,8.6 95.8,7.1 96.2,6.0 96.7,7.0 97.1,7.4 97.5,8.1 98.0,8.6 98.4,9.3 98.8,9.0 99.2,8.7 99.7,8.9 100.1,9.2 100.5,7.8 101.0,7.8 101.4,4.8 101.8,2.2 102.3,2.0 102.7,3.0 103.1,4.2 103.5,5.6 104.0,5.2 104.4,5.7 104.8,5.7 105.3,3.7 105.7,3.8 106.1,6.0 106.6,6.0 107.0,6.4 107.4,4.2 107.8,5.4 108.3,6.6 108.7,7.7 109.1,7.7 109.6,7.8 110.0,8.8", "ret_12_1": 166.0, "ret_6_1": 97.5, "ret_3_1": 31.1, "volatility": 49.4, "traded_daily_cr": 493.0, "watch": "Nothing flagged", "from_12m_high": -15.7, "signal_rank": 9, "data_quality": "Green"}, {"rank": 4, "symbol": "THANGAMAYL", "isin": "INE085J01014", "qty": 2, "last_close": 5011.5, "amount": 10023.0, "spark_12m": "2.0,30.9 2.4,31.1 2.9,31.4 3.3,31.4 3.7,31.4 4.2,31.6 4.6,31.7 5.0,31.6 5.4,31.6 5.9,31.2 6.3,31.3 6.7,31.6 7.2,31.2 7.6,31.5 8.0,31.6 8.5,31.5 8.9,31.8 9.3,31.9 9.7,31.9 10.2,31.9 10.6,31.9 11.0,31.9 11.5,32.0 11.9,31.5 12.3,31.6 12.8,31.3 13.2,31.4 13.6,31.3 14.0,30.8 14.5,28.3 14.9,25.9 15.3,25.7 15.8,23.9 16.2,25.3 16.6,24.8 17.1,24.1 17.5,24.4 17.9,24.5 18.4,24.7 18.8,24.9 19.2,25.1 19.6,25.2 20.1,26.0 20.5,24.8 20.9,24.8 21.4,24.7 21.8,24.8 22.2,24.7 22.7,24.1 23.1,25.2 23.5,24.6 23.9,24.8 24.4,24.9 24.8,25.2 25.2,24.7 25.7,24.9 26.1,24.9 26.5,25.0 27.0,25.0 27.4,24.9 27.8,24.4 28.2,24.6 28.7,24.2 29.1,23.8 29.5,23.7 30.0,24.5 30.4,25.0 30.8,25.0 31.3,25.0 31.7,24.9 32.1,24.7 32.5,24.8 33.0,24.2 33.4,23.4 33.8,21.4 34.3,21.2 34.7,22.7 35.1,22.3 35.6,21.9 36.0,21.5 36.4,21.8 36.9,22.1 37.3,22.1 37.7,21.2 38.1,22.6 38.6,22.9 39.0,23.8 39.4,22.8 39.9,23.4 40.3,24.3 40.7,24.9 41.2,25.1 41.6,24.5 42.0,25.1 42.4,23.9 42.9,22.1 43.3,22.2 43.7,22.3 44.2,22.5 44.6,22.9 45.0,22.1 45.5,22.3 45.9,22.6 46.3,23.4 46.7,23.0 47.2,22.8 47.6,22.0 48.0,21.5 48.5,21.0 48.9,20.8 49.3,21.4 49.8,22.7 50.2,22.6 50.6,22.2 51.1,22.9 51.5,22.1 51.9,23.1 52.3,23.0 52.8,23.3 53.2,23.6 53.6,23.4 54.1,23.3 54.5,24.1 54.9,24.3 55.4,25.2 55.8,24.4 56.2,22.8 56.6,23.7 57.1,23.7 57.5,23.0 57.9,23.1 58.4,21.9 58.8,21.3 59.2,20.3 59.7,20.0 60.1,19.8 60.5,19.5 60.9,19.1 61.4,19.0 61.8,19.3 62.2,19.8 62.7,19.8 63.1,20.4 63.5,21.7 64.0,21.7 64.4,20.8 64.8,20.7 65.3,20.6 65.7,20.8 66.1,20.6 66.5,20.7 67.0,20.1 67.4,19.9 67.8,19.1 68.3,20.5 68.7,22.4 69.1,22.5 69.6,22.7 70.0,22.8 70.4,23.1 70.8,22.5 71.3,21.8 71.7,21.3 72.1,21.6 72.6,21.5 73.0,21.6 73.4,21.0 73.9,19.4 74.3,18.9 74.7,17.2 75.1,16.1 75.6,12.0 76.0,13.0 76.4,12.2 76.9,12.3 77.3,12.4 77.7,12.6 78.2,12.2 78.6,12.1 79.0,12.4 79.5,11.4 79.9,12.5 80.3,12.4 80.7,11.8 81.2,12.8 81.6,12.4 82.0,11.6 82.5,10.0 82.9,7.1 83.3,9.6 83.8,7.6 84.2,8.4 84.6,7.7 85.0,7.2 85.5,4.8 85.9,6.0 86.3,6.3 86.8,8.0 87.2,6.8 87.6,5.9 88.1,7.2 88.5,6.9 88.9,7.2 89.3,6.8 89.8,6.7 90.2,4.5 90.6,4.3 91.1,2.0 91.5,2.8 91.9,6.8 92.4,10.4 92.8,13.7 93.2,15.1 93.6,16.5 94.1,15.2 94.5,14.1 94.9,13.4 95.4,13.0 95.8,13.7 96.2,13.1 96.7,13.4 97.1,12.5 97.5,13.0 98.0,12.2 98.4,12.0 98.8,12.4 99.2,12.2 99.7,12.2 100.1,12.7 100.5,12.2 101.0,12.1 101.4,12.5 101.8,12.6 102.3,13.2 102.7,13.6 103.1,13.3 103.5,13.1 104.0,12.3 104.4,12.9 104.8,14.3 105.3,14.5 105.7,14.2 106.1,15.4 106.6,15.3 107.0,16.0 107.4,14.7 107.8,15.3 108.3,14.3 108.7,13.2 109.1,14.4 109.6,14.2 110.0,14.9", "ret_12_1": 154.0, "ret_6_1": 66.3, "ret_3_1": -14.0, "volatility": 59.8, "traded_daily_cr": 71.0, "watch": "Nothing flagged", "from_12m_high": -31.4, "signal_rank": 11, "data_quality": "Green"}, {"rank": 5, "symbol": "RRKABEL", "isin": "INE777K01022", "qty": 6, "last_close": 2459.8, "amount": 14759.0, "spark_12m": "2.0,31.3 2.4,31.1 2.9,30.7 3.3,31.2 3.7,31.2 4.2,32.0 4.6,31.8 5.0,31.2 5.4,31.1 5.9,31.4 6.3,31.1 6.7,31.1 7.2,31.3 7.6,31.4 8.0,31.0 8.5,31.2 8.9,31.3 9.3,31.3 9.7,31.0 10.2,31.2 10.6,31.4 11.0,31.2 11.5,31.4 11.9,31.5 12.3,30.1 12.8,28.7 13.2,28.4 13.6,28.6 14.0,28.6 14.5,29.0 14.9,28.4 15.3,28.8 15.8,29.2 16.2,29.8 16.6,29.6 17.1,28.8 17.5,29.3 17.9,29.3 18.4,29.1 18.8,29.7 19.2,29.5 19.6,29.4 20.1,29.7 20.5,29.7 20.9,29.5 21.4,29.0 21.8,29.1 22.2,28.8 22.7,28.8 23.1,28.8 23.5,29.0 23.9,28.9 24.4,29.4 24.8,29.5 25.2,29.1 25.7,28.6 26.1,28.7 26.5,28.4 27.0,27.8 27.4,28.1 27.8,28.3 28.2,28.3 28.7,27.3 29.1,26.5 29.5,26.6 30.0,27.1 30.4,27.5 30.8,28.1 31.3,28.2 31.7,27.9 32.1,27.6 32.5,26.9 33.0,26.4 33.4,26.3 33.8,26.4 34.3,26.7 34.7,26.9 35.1,27.3 35.6,27.0 36.0,27.1 36.4,27.5 36.9,28.0 37.3,28.6 37.7,28.6 38.1,28.4 38.6,29.7 39.0,30.0 39.4,29.7 39.9,30.3 40.3,29.3 40.7,29.6 41.2,28.4 41.6,27.8 42.0,27.5 42.4,27.7 42.9,27.6 43.3,28.5 43.7,28.2 44.2,28.3 44.6,28.7 45.0,28.7 45.5,28.4 45.9,28.5 46.3,28.4 46.7,28.1 47.2,27.9 47.6,27.0 48.0,26.9 48.5,26.7 48.9,26.0 49.3,26.5 49.8,27.3 50.2,27.1 50.6,26.6 51.1,27.2 51.5,27.8 51.9,28.4 52.3,28.2 52.8,29.8 53.2,29.3 53.6,28.9 54.1,28.1 54.5,28.9 54.9,29.0 55.4,30.3 55.8,29.7 56.2,29.7 56.6,30.3 57.1,30.7 57.5,30.0 57.9,30.0 58.4,30.0 58.8,30.2 59.2,28.8 59.7,29.1 60.1,28.9 60.5,29.3 60.9,29.0 61.4,27.8 61.8,27.5 62.2,27.6 62.7,27.8 63.1,27.7 63.5,28.3 64.0,28.1 64.4,26.9 64.8,25.1 65.3,24.8 65.7,25.8 66.1,22.2 66.5,22.1 67.0,21.8 67.4,19.6 67.8,19.3 68.3,19.7 68.7,19.4 69.1,19.0 69.6,17.6 70.0,19.1 70.4,19.2 70.8,19.7 71.3,18.9 71.7,19.2 72.1,19.2 72.6,18.5 73.0,18.7 73.4,19.1 73.9,17.3 74.3,17.8 74.7,17.9 75.1,15.6 75.6,14.4 76.0,14.4 76.4,15.6 76.9,15.2 77.3,15.3 77.7,16.0 78.2,15.3 78.6,15.0 79.0,14.8 79.5,14.6 79.9,13.1 80.3,12.7 80.7,12.1 81.2,11.8 81.6,10.6 82.0,9.7 82.5,9.5 82.9,11.4 83.3,11.6 83.8,11.4 84.2,12.3 84.6,13.1 85.0,14.9 85.5,15.0 85.9,14.7 86.3,14.3 86.8,11.7 87.2,12.2 87.6,13.2 88.1,11.2 88.5,13.1 88.9,12.4 89.3,12.2 89.8,10.7 90.2,11.7 90.6,9.6 91.1,9.1 91.5,8.2 91.9,8.5 92.4,8.4 92.8,7.7 93.2,7.2 93.6,7.0 94.1,4.4 94.5,4.9 94.9,5.0 95.4,5.0 95.8,4.0 96.2,4.4 96.7,3.7 97.1,4.5 97.5,5.2 98.0,4.5 98.4,2.5 98.8,2.6 99.2,2.2 99.7,3.0 100.1,4.2 100.5,4.1 101.0,3.7 101.4,2.4 101.8,2.0 102.3,3.0 102.7,7.2 103.1,7.5 103.5,10.3 104.0,11.5 104.4,10.4 104.8,10.9 105.3,10.6 105.7,10.8 106.1,11.6 106.6,11.3 107.0,11.4 107.4,10.4 107.8,11.1 108.3,10.0 108.7,9.9 109.1,9.0 109.6,9.0 110.0,10.2", "ret_12_1": 126.0, "ret_6_1": 110.0, "ret_3_1": 18.2, "volatility": 44.0, "traded_daily_cr": 93.0, "watch": "Nothing flagged", "from_12m_high": -16.0, "signal_rank": 15, "data_quality": "Green"}, {"rank": 6, "symbol": "ACUTAAS", "isin": "INE00FF01025", "qty": 4, "last_close": 3214.4, "amount": 12858.0, "spark_12m": "2.0,30.2 2.4,30.2 2.9,30.3 3.3,30.3 3.7,30.8 4.2,31.5 4.6,31.6 5.0,32.0 5.4,31.2 5.9,31.1 6.3,30.9 6.7,30.9 7.2,30.9 7.6,30.7 8.0,30.1 8.5,29.7 8.9,29.7 9.3,29.1 9.7,29.0 10.2,27.8 10.6,26.4 11.0,26.1 11.5,26.7 11.9,27.4 12.3,26.8 12.8,27.0 13.2,27.3 13.6,27.1 14.0,26.8 14.5,25.8 14.9,25.5 15.3,26.3 15.8,26.4 16.2,26.4 16.6,26.5 17.1,27.1 17.5,27.4 17.9,27.0 18.4,27.1 18.8,27.0 19.2,26.9 19.6,26.8 20.1,27.2 20.5,25.0 20.9,26.1 21.4,26.0 21.8,26.1 22.2,25.4 22.7,26.2 23.1,26.6 23.5,26.7 23.9,27.1 24.4,27.1 24.8,27.8 25.2,27.6 25.7,27.4 26.1,27.7 26.5,27.6 27.0,28.1 27.4,27.2 27.8,27.7 28.2,28.0 28.7,27.8 29.1,27.4 29.5,27.2 30.0,27.8 30.4,27.8 30.8,27.8 31.3,27.7 31.7,27.1 32.1,26.5 32.5,26.6 33.0,26.3 33.4,26.4 33.8,26.4 34.3,26.7 34.7,27.4 35.1,27.5 35.6,27.4 36.0,27.1 36.4,27.2 36.9,27.4 37.3,28.1 37.7,28.4 38.1,27.9 38.6,27.8 39.0,26.8 39.4,25.1 39.9,24.2 40.3,24.5 40.7,24.2 41.2,23.8 41.6,23.5 42.0,23.6 42.4,23.6 42.9,23.4 43.3,22.8 43.7,23.0 44.2,22.2 44.6,23.2 45.0,22.9 45.5,22.4 45.9,21.6 46.3,22.1 46.7,22.0 47.2,21.5 47.6,21.5 48.0,21.3 48.5,21.1 48.9,21.4 49.3,21.0 49.8,22.1 50.2,20.4 50.6,20.2 51.1,21.4 51.5,20.5 51.9,21.0 52.3,21.0 52.8,22.3 53.2,21.3 53.6,19.6 54.1,20.1 54.5,20.3 54.9,18.3 55.4,20.0 55.8,17.9 56.2,16.7 56.6,16.5 57.1,16.3 57.5,19.2 57.9,22.0 58.4,20.7 58.8,20.7 59.2,19.2 59.7,19.3 60.1,18.8 60.5,18.4 60.9,19.7 61.4,19.1 61.8,18.8 62.2,18.2 62.7,18.7 63.1,18.0 63.5,18.5 64.0,18.4 64.4,17.1 64.8,17.5 65.3,17.0 65.7,15.9 66.1,14.9 66.5,15.1 67.0,14.7 67.4,14.2 67.8,14.1 68.3,13.2 68.7,14.0 69.1,12.9 69.6,14.2 70.0,14.2 70.4,13.3 70.8,12.2 71.3,12.3 71.7,10.8 72.1,11.4 72.6,11.7 73.0,10.3 73.4,10.8 73.9,9.1 74.3,10.5 74.7,10.3 75.1,9.1 75.6,8.7 76.0,6.6 76.4,6.8 76.9,8.3 77.3,8.2 77.7,9.2 78.2,8.9 78.6,9.5 79.0,10.8 79.5,10.8 79.9,9.0 80.3,7.7 80.7,7.6 81.2,7.3 81.6,7.4 82.0,7.0 82.5,3.6 82.9,4.1 83.3,3.6 83.8,2.0 84.2,2.0 84.6,4.3 85.0,5.8 85.5,5.0 85.9,5.0 86.3,5.7 86.8,4.5 87.2,5.0 87.6,3.9 88.1,3.4 88.5,3.0 88.9,2.5 89.3,2.2 89.8,2.4 90.2,5.0 90.6,7.5 91.1,6.1 91.5,7.0 91.9,6.9 92.4,7.8 92.8,9.4 93.2,9.3 93.6,7.9 94.1,7.2 94.5,7.5 94.9,7.0 95.4,7.2 95.8,7.7 96.2,8.8 96.7,9.4 97.1,7.8 97.5,8.3 98.0,5.8 98.4,7.9 98.8,8.1 99.2,8.6 99.7,8.6 100.1,6.8 100.5,7.5 101.0,6.6 101.4,7.2 101.8,8.7 102.3,8.6 102.7,9.1 103.1,8.2 103.5,8.6 104.0,8.5 104.4,8.5 104.8,7.7 105.3,5.1 105.7,5.9 106.1,7.4 106.6,6.4 107.0,6.8 107.4,5.2 107.8,5.4 108.3,8.1 108.7,7.4 109.1,7.2 109.6,7.3 110.0,8.1", "ret_12_1": 126.0, "ret_6_1": 36.7, "ret_3_1": -5.6, "volatility": 46.7, "traded_daily_cr": 101.0, "watch": "Nothing flagged", "from_12m_high": -13.0, "signal_rank": 16, "data_quality": "Green"}, {"rank": 7, "symbol": "DIACABS", "isin": "INE989C01038", "qty": 44, "last_close": 339.25, "amount": 14927.0, "spark_12m": "2.0,27.2 2.4,27.3 2.9,27.2 3.3,27.4 3.7,28.0 4.2,28.4 4.6,28.2 5.0,28.6 5.4,28.5 5.9,28.3 6.3,28.7 6.7,29.2 7.2,29.3 7.6,29.4 8.0,29.4 8.5,29.6 8.9,29.5 9.3,29.2 9.7,29.3 10.2,29.4 10.6,29.2 11.0,29.1 11.5,29.1 11.9,29.3 12.3,28.1 12.8,28.5 13.2,28.1 13.6,28.2 14.0,28.2 14.5,28.1 14.9,27.9 15.3,28.6 15.8,28.3 16.2,28.8 16.6,28.9 17.1,28.8 17.5,28.4 17.9,28.4 18.4,28.4 18.8,28.7 19.2,28.3 19.6,28.7 20.1,29.1 20.5,29.5 20.9,29.6 21.4,29.4 21.8,29.4 22.2,28.5 22.7,28.6 23.1,28.9 23.5,29.2 23.9,29.3 24.4,29.1 24.8,29.4 25.2,29.4 25.7,29.7 26.1,29.7 26.5,29.5 27.0,29.4 27.4,29.6 27.8,29.6 28.2,29.5 28.7,29.5 29.1,29.2 29.5,29.3 30.0,29.5 30.4,29.6 30.8,29.8 31.3,29.8 31.7,29.8 32.1,29.8 32.5,29.9 33.0,29.3 33.4,29.3 33.8,29.1 34.3,29.7 34.7,30.2 35.1,30.1 35.6,30.5 36.0,30.7 36.4,30.6 36.9,30.4 37.3,31.0 37.7,30.9 38.1,30.8 38.6,31.4 39.0,31.4 39.4,31.1 39.9,31.4 40.3,31.5 40.7,31.7 41.2,31.2 41.6,30.8 42.0,31.3 42.4,31.3 42.9,30.9 43.3,30.4 43.7,30.2 44.2,30.3 44.6,30.5 45.0,29.5 45.5,29.8 45.9,29.8 46.3,30.2 46.7,30.1 47.2,30.2 47.6,30.4 48.0,30.0 48.5,29.6 48.9,29.9 49.3,29.9 49.8,30.4 50.2,29.9 50.6,30.1 51.1,30.2 51.5,29.7 51.9,29.9 52.3,30.0 52.8,30.8 53.2,31.0 53.6,31.2 54.1,30.7 54.5,31.4 54.9,31.0 55.4,32.0 55.8,31.7 56.2,30.9 56.6,31.5 57.1,31.9 57.5,31.2 57.9,31.2 58.4,30.8 58.8,30.9 59.2,30.3 59.7,30.4 60.1,29.9 60.5,29.8 60.9,29.5 61.4,28.7 61.8,28.6 62.2,27.4 62.7,27.2 63.1,27.5 63.5,27.5 64.0,27.3 64.4,26.8 64.8,27.1 65.3,27.3 65.7,27.7 66.1,26.8 66.5,26.6 67.0,25.6 67.4,26.4 67.8,26.0 68.3,25.8 68.7,26.4 69.1,25.9 69.6,24.0 70.0,23.5 70.4,24.0 70.8,24.2 71.3,23.6 71.7,23.8 72.1,23.8 72.6,23.5 73.0,22.4 73.4,23.3 73.9,23.7 74.3,25.0 74.7,23.7 75.1,24.3 75.6,23.9 76.0,22.7 76.4,23.3 76.9,22.8 77.3,23.4 77.7,23.8 78.2,22.9 78.6,21.4 79.0,22.4 79.5,22.6 79.9,22.9 80.3,22.1 80.7,22.3 81.2,22.9 81.6,22.6 82.0,22.4 82.5,22.2 82.9,22.1 83.3,22.2 83.8,22.0 84.2,23.2 84.6,21.1 85.0,20.4 85.5,19.7 85.9,18.9 86.3,20.0 86.8,20.1 87.2,20.4 87.6,20.2 88.1,20.4 88.5,20.7 88.9,18.3 89.3,15.6 89.8,15.6 90.2,15.1 90.6,12.8 91.1,11.5 91.5,10.0 91.9,8.2 92.4,9.2 92.8,9.7 93.2,9.8 93.6,10.5 94.1,8.8 94.5,7.0 94.9,5.3 95.4,5.7 95.8,5.5 96.2,4.9 96.7,5.0 97.1,4.8 97.5,5.8 98.0,4.9 98.4,5.8 98.8,6.4 99.2,6.2 99.7,6.5 100.1,8.0 100.5,8.1 101.0,8.1 101.4,6.9 101.8,7.1 102.3,7.9 102.7,8.9 103.1,9.8 103.5,8.8 104.0,8.7 104.4,8.3 104.8,8.5 105.3,6.7 105.7,4.8 106.1,2.8 106.6,2.0 107.0,4.0 107.4,5.0 107.8,4.0 108.3,4.6 108.7,3.8 109.1,5.7 109.6,6.4 110.0,8.0", "ret_12_1": 124.0, "ret_6_1": 180.0, "ret_3_1": 61.7, "volatility": 53.6, "traded_daily_cr": 51.0, "watch": "Nothing flagged", "from_12m_high": -14.1, "signal_rank": 17, "data_quality": "Green"}, {"rank": 8, "symbol": "KIRLOSENG", "isin": "INE146L01010", "qty": 7, "last_close": 2141.2, "amount": 14988.0, "spark_12m": "2.0,30.3 2.4,30.3 2.9,30.5 3.3,30.2 3.7,30.7 4.2,31.2 4.6,31.1 5.0,31.1 5.4,31.0 5.9,31.4 6.3,31.6 6.7,31.8 7.2,31.8 7.6,31.8 8.0,31.6 8.5,31.7 8.9,32.0 9.3,31.9 9.7,31.8 10.2,31.6 10.6,31.8 11.0,31.6 11.5,31.5 11.9,31.5 12.3,30.7 12.8,29.6 13.2,29.4 13.6,29.4 14.0,29.7 14.5,29.4 14.9,29.4 15.3,29.9 15.8,30.3 16.2,30.5 16.6,30.7 17.1,28.7 17.5,28.2 17.9,28.1 18.4,27.7 18.8,27.2 19.2,26.6 19.6,26.5 20.1,26.8 20.5,27.4 20.9,26.9 21.4,27.1 21.8,27.2 22.2,27.5 22.7,27.6 23.1,27.7 23.5,28.2 23.9,26.8 24.4,27.4 24.8,28.0 25.2,27.5 25.7,27.7 26.1,27.6 26.5,27.1 27.0,27.3 27.4,25.7 27.8,24.7 28.2,24.6 28.7,25.4 29.1,24.2 29.5,24.4 30.0,25.0 30.4,24.9 30.8,25.8 31.3,25.7 31.7,25.8 32.1,25.6 32.5,25.1 33.0,25.2 33.4,25.3 33.8,25.8 34.3,26.5 34.7,26.9 35.1,27.5 35.6,27.0 36.0,26.7 36.4,26.7 36.9,27.4 37.3,27.9 37.7,27.9 38.1,27.7 38.6,28.0 39.0,28.0 39.4,27.7 39.9,27.6 40.3,26.6 40.7,27.0 41.2,26.5 41.6,25.6 42.0,26.2 42.4,26.7 42.9,25.8 43.3,25.0 43.7,23.9 44.2,23.7 44.6,23.0 45.0,22.4 45.5,22.1 45.9,22.3 46.3,22.2 46.7,22.3 47.2,22.6 47.6,22.7 48.0,22.5 48.5,22.7 48.9,22.7 49.3,22.5 49.8,22.3 50.2,21.4 50.6,20.6 51.1,21.6 51.5,21.9 51.9,21.7 52.3,21.4 52.8,21.7 53.2,21.4 53.6,21.9 54.1,22.0 54.5,22.2 54.9,23.0 55.4,24.6 55.8,23.9 56.2,22.7 56.6,23.5 57.1,23.9 57.5,23.2 57.9,22.9 58.4,22.3 58.8,22.6 59.2,21.4 59.7,21.6 60.1,21.3 60.5,21.1 60.9,19.1 61.4,18.8 61.8,18.7 62.2,18.4 62.7,17.9 63.1,18.4 63.5,18.9 64.0,19.2 64.4,17.6 64.8,16.9 65.3,17.3 65.7,17.3 66.1,16.9 66.5,16.6 67.0,17.1 67.4,16.8 67.8,16.8 68.3,18.0 68.7,19.8 69.1,19.1 69.6,19.1 70.0,16.6 70.4,17.3 70.8,18.0 71.3,17.9 71.7,17.7 72.1,17.8 72.6,17.2 73.0,16.4 73.4,15.0 73.9,13.3 74.3,13.4 74.7,14.5 75.1,13.9 75.6,12.9 76.0,13.5 76.4,14.6 76.9,14.6 77.3,15.2 77.7,15.6 78.2,13.9 78.6,13.2 79.0,13.4 79.5,12.2 79.9,12.3 80.3,12.1 80.7,5.1 81.2,3.0 81.6,2.0 82.0,3.4 82.5,4.2 82.9,5.5 83.3,5.9 83.8,6.3 84.2,7.9 84.6,7.3 85.0,7.2 85.5,7.1 85.9,4.5 86.3,3.3 86.8,4.3 87.2,5.6 87.6,4.6 88.1,5.0 88.5,7.5 88.9,8.1 89.3,8.1 89.8,8.7 90.2,8.8 90.6,8.7 91.1,7.0 91.5,8.6 91.9,8.8 92.4,9.6 92.8,8.6 93.2,8.0 93.6,7.1 94.1,7.7 94.5,7.6 94.9,9.1 95.4,9.7 95.8,10.2 96.2,11.0 96.7,10.9 97.1,10.2 97.5,10.2 98.0,9.8 98.4,10.6 98.8,9.3 99.2,10.2 99.7,10.8 100.1,11.5 100.5,11.3 101.0,10.2 101.4,9.8 101.8,10.2 102.3,9.5 102.7,9.1 103.1,7.2 103.5,8.4 104.0,8.9 104.4,7.1 104.8,8.1 105.3,8.3 105.7,9.0 106.1,11.2 106.6,11.3 107.0,9.8 107.4,9.1 107.8,9.6 108.3,9.1 108.7,8.1 109.1,9.1 109.6,9.6 110.0,9.5", "ret_12_1": 123.0, "ret_6_1": 58.2, "ret_3_1": -11.2, "volatility": 49.9, "traded_daily_cr": 87.0, "watch": "Nothing flagged", "from_12m_high": -16.5, "signal_rank": 18, "data_quality": "Green"}, {"rank": 9, "symbol": "E2E", "isin": "INE255Z01027", "qty": 23, "last_close": 625.9, "amount": 14396.0, "spark_12m": "2.0,25.4 2.4,24.4 2.9,23.5 3.3,24.3 3.7,23.7 4.2,22.9 4.6,23.7 5.0,24.4 5.4,23.4 5.9,22.4 6.3,21.3 6.7,21.1 7.2,21.2 7.6,22.8 8.0,23.1 8.5,23.8 8.9,24.4 9.3,24.4 9.7,24.3 10.2,24.1 10.6,24.5 11.0,24.4 11.5,24.3 11.9,25.2 12.3,24.5 12.8,24.9 13.2,25.1 13.6,24.9 14.0,25.0 14.5,25.3 14.9,24.9 15.3,25.3 15.8,25.1 16.2,25.3 16.6,26.1 17.1,26.1 17.5,26.8 17.9,27.8 18.4,28.0 18.8,28.1 19.2,28.0 19.6,28.1 20.1,28.8 20.5,29.7 20.9,29.7 21.4,29.6 21.8,29.8 22.2,30.1 22.7,30.0 23.1,30.5 23.5,30.9 23.9,30.5 24.4,31.0 24.8,31.6 25.2,30.8 25.7,31.2 26.1,31.1 26.5,31.1 27.0,31.1 27.4,31.5 27.8,31.6 28.2,31.7 28.7,31.3 29.1,31.2 29.5,31.1 30.0,31.2 30.4,31.4 30.8,32.0 31.3,31.9 31.7,31.8 32.1,31.7 32.5,31.6 33.0,31.2 33.4,31.5 33.8,31.6 34.3,31.5 34.7,31.5 35.1,31.6 35.6,31.8 36.0,31.6 36.4,30.3 36.9,30.2 37.3,30.8 37.7,31.3 38.1,31.2 38.6,31.5 39.0,31.5 39.4,31.3 39.9,31.5 40.3,31.0 40.7,29.0 41.2,28.0 41.6,29.0 42.0,29.5 42.4,28.7 42.9,27.8 43.3,28.2 43.7,27.9 44.2,28.4 44.6,28.8 45.0,28.2 45.5,28.3 45.9,26.5 46.3,25.8 46.7,26.4 47.2,28.2 47.6,29.0 48.0,28.3 48.5,28.0 48.9,28.2 49.3,28.9 49.8,29.7 50.2,29.7 50.6,29.8 51.1,29.9 51.5,29.1 51.9,29.4 52.3,29.6 52.8,29.9 53.2,30.4 53.6,30.5 54.1,30.1 54.5,30.0 54.9,30.1 55.4,30.7 55.8,30.7 56.2,30.2 56.6,30.9 57.1,31.4 57.5,30.8 57.9,30.2 58.4,29.9 58.8,29.6 59.2,28.9 59.7,29.1 60.1,29.0 60.5,28.9 60.9,28.1 61.4,27.4 61.8,26.8 62.2,27.4 62.7,26.6 63.1,26.0 63.5,26.2 64.0,26.2 64.4,25.3 64.8,25.7 65.3,26.0 65.7,26.3 66.1,26.6 66.5,25.8 67.0,24.9 67.4,23.9 67.8,23.0 68.3,21.9 68.7,23.0 69.1,24.1 69.6,24.0 70.0,24.9 70.4,25.5 70.8,24.5 71.3,23.6 71.7,23.1 72.1,22.1 72.6,21.3 73.0,20.2 73.4,19.8 73.9,20.0 74.3,18.8 74.7,17.5 75.1,18.8 75.6,17.6 76.0,16.3 76.4,17.6 76.9,19.0 77.3,20.2 77.7,21.4 78.2,20.3 78.6,21.1 79.0,20.6 79.5,20.3 79.9,19.1 80.3,17.9 80.7,16.6 81.2,17.5 81.6,18.4 82.0,18.7 82.5,19.8 82.9,19.7 83.3,19.3 83.8,20.2 84.2,20.6 84.6,20.6 85.0,21.3 85.5,20.8 85.9,19.6 86.3,19.6 86.8,20.3 87.2,19.8 87.6,18.8 88.1,18.1 88.5,19.2 88.9,18.0 89.3,16.7 89.8,15.3 90.2,13.9 90.6,12.4 91.1,10.8 91.5,12.4 91.9,13.9 92.4,13.8 92.8,12.3 93.2,10.8 93.6,9.1 94.1,7.4 94.5,6.9 94.9,8.8 95.4,7.1 95.8,5.6 96.2,5.3 96.7,5.1 97.1,3.2 97.5,2.0 98.0,3.3 98.4,5.4 98.8,5.8 99.2,5.9 99.7,6.5 100.1,7.5 100.5,6.5 101.0,6.2 101.4,6.3 101.8,6.1 102.3,6.0 102.7,6.8 103.1,7.7 103.5,7.2 104.0,5.4 104.4,6.2 104.8,7.0 105.3,6.9 105.7,6.6 106.1,8.5 106.6,7.3 107.0,7.0 107.4,6.8 107.8,7.7 108.3,7.0 108.7,5.1 109.1,4.4 109.6,4.1 110.0,5.7", "ret_12_1": 109.0, "ret_6_1": 186.0, "ret_3_1": 56.0, "volatility": 56.2, "traded_daily_cr": 49.0, "watch": "Nothing flagged", "from_12m_high": -8.8, "signal_rank": 20, "data_quality": "Green"}, {"rank": 10, "symbol": "LAURUSLABS", "isin": "INE947Q01028", "qty": 7, "last_close": 2010.7, "amount": 14075.0, "spark_12m": "2.0,29.5 2.4,30.2 2.9,30.1 3.3,30.1 3.7,30.4 4.2,32.0 4.6,31.8 5.0,31.8 5.4,31.0 5.9,31.2 6.3,31.2 6.7,31.2 7.2,31.5 7.6,31.2 8.0,30.9 8.5,31.0 8.9,30.9 9.3,30.9 9.7,31.0 10.2,30.3 10.6,29.8 11.0,29.7 11.5,29.5 11.9,29.7 12.3,29.3 12.8,28.8 13.2,28.8 13.6,28.6 14.0,29.0 14.5,28.4 14.9,28.2 15.3,28.3 15.8,28.3 16.2,27.8 16.6,28.2 17.1,28.1 17.5,27.9 17.9,27.8 18.4,27.3 18.8,27.6 19.2,28.1 19.6,28.1 20.1,28.4 20.5,28.3 20.9,28.4 21.4,28.1 21.8,27.7 22.2,27.0 22.7,27.1 23.1,27.3 23.5,27.4 23.9,27.5 24.4,27.2 24.8,27.7 25.2,27.3 25.7,27.4 26.1,27.3 26.5,27.5 27.0,27.7 27.4,27.8 27.8,27.6 28.2,27.4 28.7,26.7 29.1,26.2 29.5,26.1 30.0,25.7 30.4,25.7 30.8,25.8 31.3,25.5 31.7,25.1 32.1,25.1 32.5,25.2 33.0,25.2 33.4,24.9 33.8,24.6 34.3,25.3 34.7,25.7 35.1,26.7 35.6,26.4 36.0,25.6 36.4,25.9 36.9,26.2 37.3,26.9 37.7,28.1 38.1,27.7 38.6,27.4 39.0,27.8 39.4,27.8 39.9,28.5 40.3,28.7 40.7,29.0 41.2,28.4 41.6,28.3 42.0,28.7 42.4,29.0 42.9,28.2 43.3,28.7 43.7,27.5 44.2,27.3 44.6,27.5 45.0,27.5 45.5,27.5 45.9,26.9 46.3,27.3 46.7,27.3 47.2,27.4 47.6,27.1 48.0,25.9 48.5,25.5 48.9,25.9 49.3,26.2 49.8,27.0 50.2,26.7 50.6,27.2 51.1,27.3 51.5,26.9 51.9,26.8 52.3,26.6 52.8,27.7 53.2,28.8 53.6,28.6 54.1,28.2 54.5,29.2 54.9,28.1 55.4,28.8 55.8,28.0 56.2,27.2 56.6,27.6 57.1,28.0 57.5,26.8 57.9,26.7 58.4,26.4 58.8,26.4 59.2,25.8 59.7,25.7 60.1,25.4 60.5,25.6 60.9,24.9 61.4,24.6 61.8,24.4 62.2,24.6 62.7,25.0 63.1,25.4 63.5,24.6 64.0,25.0 64.4,24.7 64.8,25.6 65.3,25.2 65.7,25.3 66.1,23.7 66.5,23.7 67.0,23.4 67.4,22.7 67.8,22.1 68.3,21.2 68.7,21.1 69.1,20.8 69.6,19.9 70.0,19.7 70.4,19.6 70.8,19.2 71.3,18.8 71.7,19.1 72.1,19.2 72.6,18.9 73.0,18.5 73.4,18.3 73.9,18.8 74.3,18.1 74.7,18.3 75.1,18.0 75.6,17.1 76.0,16.7 76.4,17.7 76.9,17.2 77.3,18.2 77.7,18.1 78.2,18.0 78.6,18.1 79.0,18.4 79.5,18.6 79.9,18.6 80.3,17.5 80.7,16.9 81.2,15.8 81.6,16.5 82.0,16.6 82.5,15.3 82.9,14.9 83.3,15.5 83.8,14.6 84.2,14.3 84.6,14.6 85.0,15.9 85.5,16.1 85.9,15.1 86.3,14.4 86.8,13.9 87.2,13.8 87.6,14.0 88.1,13.9 88.5,14.6 88.9,13.9 89.3,13.0 89.8,13.4 90.2,13.6 90.6,12.8 91.1,10.0 91.5,8.9 91.9,8.3 92.4,8.3 92.8,7.4 93.2,7.6 93.6,6.6 94.1,7.0 94.5,7.1 94.9,6.7 95.4,6.5 95.8,6.4 96.2,6.6 96.7,6.6 97.1,8.2 97.5,7.6 98.0,7.5 98.4,7.8 98.8,7.2 99.2,7.8 99.7,7.8 100.1,6.2 100.5,5.7 101.0,4.6 101.4,4.4 101.8,5.0 102.3,6.3 102.7,6.2 103.1,6.1 103.5,6.8 104.0,5.9 104.4,4.2 104.8,4.4 105.3,4.2 105.7,3.6 106.1,4.7 106.6,5.2 107.0,4.1 107.4,4.0 107.8,2.4 108.3,2.7 108.7,2.0 109.1,2.2 109.6,2.7 110.0,2.6", "ret_12_1": 109.0, "ret_6_1": 94.4, "ret_3_1": 27.2, "volatility": 28.1, "traded_daily_cr": 300.0, "watch": "Nothing flagged", "from_12m_high": -1.1, "signal_rank": 21, "data_quality": "Green"}]}, "prices": {"TDPOWERSYS": {"2026-09-28": {"open": 730.05, "close": 722.0, "src": "yahoo"}, "2026-09-29": {"open": 719.0, "close": 777.35, "src": "bhavcopy"}}, "AEROFLEX": {"2026-09-28": {"open": 524.25, "close": 513.4, "src": "yahoo"}, "2026-09-29": {"open": 511.3, "close": 539.6, "src": "bhavcopy"}}, "E2E": {"2026-09-28": {"open": 650.0, "close": 625.9, "src": "yahoo"}, "2026-09-29": {"open": 619.55, "close": 651.8, "src": "bhavcopy"}}, "LAURUSLABS": {"2026-09-28": {"open": 2000.0, "close": 2010.7, "src": "yahoo"}, "2026-09-29": {"open": 2020.7, "close": 1979.0, "src": "bhavcopy"}}, "NIFTY50": {"2026-09-28": {"open": 23064.9, "close": 22780.25, "src": "yahoo"}, "2026-09-29": {"open": 22732.45, "close": 22716.2, "src": "bhavcopy"}}, "ATHERENERG": {"2026-09-28": {"open": 1495.0, "close": 1454.9, "src": "yahoo"}, "2026-09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tocks With Revenue Growth Up To 16%", "link": "https://finance.yahoo.com/energy/articles/3-indian-nuclear-stocks-revenue-171316164.html", "source": "Simply Wall St.", "published": "2026-09-24 17:13", "score": 0.932, "label": "Positive"}], "errors": ["TDPOWERSYS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=TDPOWERSYS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "AEROFLEX Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=AEROFLEX%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "ATHERENERG Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=ATHERENERG%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "THANGAMAYL Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=THANGAMAYL%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "RRKABEL Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=RRKABEL%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "ACUTAAS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=ACUTAAS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "DIACABS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=DIACABS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "KIRLOSENG Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=KIRLOSENG%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "E2E Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=E2E%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "LAURUSLABS Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=LAURUSLABS%20NSE%20share%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en", "MARKET Google News: 503 Server Error: Service Unavailable for url: https://news.google.com/rss/search?q=Sensex%20Nifty%20stock%20market%20India%20when%3A7d&amp;hl=en-IN&amp;gl=IN&amp;ceid=IN:en"]}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T03:08:34", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}}</t>
+          <t>-29": {"open": 1460.2, "close": 1407.0, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-09-28": {"open": 5100.0, "close": 5011.5, "src": "yahoo"}, "2026-09-29": {"open": 5010.0, "close": 5204.5, "src": "bhavcopy"}}, "RRKABEL": {"2026-09-28": {"open": 2530.4, "close": 2459.8, "src": "yahoo"}, "2026-09-29": {"open": 2459.8, "close": 2523.2, "src": "bhavcopy"}}, "ACUTAAS": {"2026-09-28": {"open": 3272.5, "close": 3214.4, "src": "yahoo"}, "2026-09-29": {"open": 3290.0, "close": 3304.1, "src": "bhavcopy"}}, "DIACABS": {"2026-09-28": {"open": 353.0, "close": 339.25, "src": "yahoo"}, "2026-09-29": {"open": 336.9, "close": 352.05, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-09-28": {"open": 2138.1, "close": 2141.2, "src": "yahoo"}, "2026-09-29": {"open": 2141.2, "close": 2402.0, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 17:07", "days": 7, "items": [{"symbol": "MARKET", "title": "Sensex, Nifty End Lower for Second Day; Global Tensions, FII Selling Hurt Investor Mood", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxNOC0wWWx3dmhaeFRrNDNBUU8zLUxRMDdKSXNURGVXT09GdFJQbGlOR2pOeXdmTHlVMzViVWpVcFJrSmtGbktLUWlESkNzWGJwTlNERW00Y0hWVmR5dUxIV1AzNl9YeXFIZTR1WGRRZlp3RTVyMUR5Wmw0d0xWYWg2ME9Yc2Z3NlBibjR0S1NiV1l5d080TWxvQmpPVVVRMHA2VlNUM1oycTlZcG5CSlh4amFn?oc=5", "source": "The Indian Awaaz", "published": "2026-09-29 15:41", "score": -0.637, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets ride expiry-day seesaw as derivatives swings jolt Nifty", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxOX2lHWmtSZUZtUnhORjFzUGQweW5Ca1F2VDdRdVhDaHd3OF83Q1hvY09NMU5NY1JzQ1Z3MU1hRmVHVkppOHJxTXBYeE1aOFh2MUZEejFaNV9yWVNmNFRtRDJXN0xic1JiVGtaY25JTWZVTFh0bzRCZnVud29LQ1pkR2tIeVF1amxrZElwZTNNdW5IV0drNjBXU2RvUGZNNzgxaVRrTVlHcjdRcnBjLXNkMmlXQTV0N1F3LXI3TzU1a29UTmpMQ2p2OGxR0gHPAUFVX3lxTE0wYlo3VkFBcjJTdjdPWGJiVnY5SjRFb2tSRl9iVzVmTkNDSTNQSVRrVWF3SmhfVTlwWE1UQXkzZDludUdlbnhOUHlLZmI2M19OTGprTHVFLXV0N3BBczlFV1VqemhMT1NhOHhVVGNVY0pRQ21RSGJ4eVJBTUF6NktiOWkzd19kYkF5QVd3WEU5SlNydGFqTXNiM1RDZ0l1d1BHV2tnSGdQREFUdzUyWlZVTkRqR19VRXQ1emJMVFZ5ZjZsbGhBSUtOOEhZSUl1RQ?oc=5", "source": "Business Standard", "published": "2026-09-29 14:34", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZExVZU95MGlua1BLV2ZFTG9YR0dpLXI5czY0TTVJYTV1UU5PeWFJdGtTTjV4VmdnUFJoNGJ1Tl9BYS1LR0FGY0pkNmpWOG00RzZvMTFkZXFsZWVHdjNhMXBGWFJYOC1BR0NkdkNsSnU5TzAzaU9ka2VBZV93Yk95TVhlUFJBbmpxa3dEYnlqT3g3STBOZmN6eXJJVVVuTk9PdXZ0NWNHVXJhUE83R1JuelFPSGdjOTFO?oc=5", "source": "The Federal", "published": "2026-09-29 12:51", "score": -0.226, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMiiwFBVV95cUxOSzJsdnF0SDkzMmFPNTNaZ05vaGU2STJGWFdWNEprdEJSWV9JeUZpaW1XTWs3eGJsVGJUTVctVlFLOHpScGZEaF9wWkxEWms0TG1aOHdKY0F2Q2hmSXlMMS1XOTNtX2lLQmVFTlN1ZzFOVzhMemtQV0NJMExuR3ZObDZadHhUOUxkeTQ4?oc=5", "source": "APAC Media", "published": "2026-09-29 11:14", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjE0RnktVUk3N3FQdTJJOHFVOUhKQ01LNGVXUm4tZVNyRnJOY0JhaXNnMkliMUtRdmxZakl1ZTN2VERkdjNxVVRLUXhSV19zY2ZnOE1icGVtSVRXOHNtM3Zwa0ZmTWNPejZwdkhmd0puNzlqeTRZcjRsNTdMcjFhLUxBb1VFWjg3OExMRGFycUt6YUZXbTlsUVUzNGhhSi1HdVFDRjlfOHJjbXMwNXhTckhpa041QQ?oc=5", "source": "DD India", "published": "2026-09-29 10:48", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOd0ZfSDFRbVZ0dEJpMlltNlF3Uy1wdlRBOGpYWGdJc3k3TFNNSkJKOGxnUExZNjZ5SlNQMnVzNU1jSm1EQzVXdHJDdkx1YmdrMzBQS2oxXy1veUY5V2xnNl9KR0Q0akNFYmVnb2MtcFBMMjlFR2FvM3JNYU1YV1dvcDFIVGJaWndpTUJEc1Z5V2dQWGxKSzVsbFA0RlhyeVNtMTkwWl9qdFJHTVVnT2FxaEZDVktKdUd2TUtZS2tyWGVQNGtjSmdadVVWQTlHRUplQl96cA?oc=5", "source": "equitymaster.com", "published": "2026-09-29 10:19", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026", "link": "https://news.google.com/rss/articles/CBMijgJBVV95cUxQUlR6X25LUHNTc0Z0WHFMTkd6QTFmWWYxU3NHa0lFLXI4SFpHWXRMQVpMTHFGeE5lM2ktZTloaDZYMXozNWMxY25Rdk9sZ240YlhaeENTNmRraUFDTW9IbHdEdGxuOV8tR0J4bDlIeDdCZGlEYU9jem9qOEVBWjk3YU1oNVdrZGE5NmxKWG5jSWludXFEV3Y5aENySDBaQXJmRDNtalNPVU04NXF3VUNGS0xzUFFDMko1TDE3d0F2ckFwVzlhMG95M0h5QWdSSkpnTzBqbVpPYmhIMXhlVURMM3Rwb1R6ZUdjOUExX1I5Vl8yWl84dUZiNTFRU2dFbVMxUTM4X0ZXaGhBYlpHQ0HSAZMCQVVfeXFMTlppcXBnR2F2R1p4Z1hXNjZlRUtaeU9sa3VLeHV5NXFfQWFGd08wRE5mWDN5TFJiMEU1Y29JY1BNVzdDRTRaUE1NYkp1SEFycmtIVkE5dW51Ym1WUVZYS1ZFVW5ZY0puSm9kUFlxZ0t6YnFyY2x0M0dWNFQyYW9LeUtlZk4tYXltODh1ZzI3bWJMTFRRdWFUSzNyMllQOVd1RjJHcWFab2JrWkxJMmtLNUV4OHNRcWdrS2lpZHVFVzVfMEtwWkl5OTY5WVBrMmJFSmVTZEdKZmlDbzJSd1NlUC1wQTZYR1l0d3NpU1JzX1BybEllN091c3dwOXVNaU5LYTBxLWpxOVE0MFYycC1nbjNlZ1U?oc=5", "source": "Livemint", "published": "2026-09-29 10:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rebound from near six-month lows amid crude shock", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxPbnlwRUxnX0Mtc0I1MHBlVmo5dlptQ2NnUm5ib1lSUk5EU1o4TjhNNUgtY2k3TENnYlpQSkptbEZRU1JXaFcydWNEY0F2c2FjcjZhajBmQllqU2dIckQyZDlMcWo2emcxajVEN0xjaWQtSy1NVlBaa2x0QzFlV3cyblVHemQ2X2xSWjVCZVJUNkdjak5SQ0h5NEVqSGZsZUlIQTdCUUZxR1hpUmMtYVZxeHRaRUZpWVcw0gG-AUFVX3lxTE5ySzVLbHhfdWYzTWpxYm1zLWNSUEZ4QVE3c1BhZ1ktWDM0aENCZ0Qtal85VVhCVFFFeVJqbFVwNkRxOEJaTVdyZWZPZTR0bTNDT0xyNndFS0ZlTUtwTDFzNnpQZFprT3pEazRHX0xFbFczaGhoemc1OWNkeWFqQUk0UVUtYnNiUWV6WC1iZHpJQ3U5ZWRSZnh6eWlKNlR2MTkwUmwzSE1pZzh5NzREOUtkRy1Tb2ZvY0Fpa0RickE?oc=5", "source": "Livemint", "published": "2026-09-29 06:14", "score": -0.66, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows", "link": "https://news.google.com/rss/articles/CBMingFBVV95cUxOOTVLQWt4QUFvUzdlVURzbTFiZElZQTJ4ZGxERVdHZElrLUJKRVg1cHZKNVFLY0JjckVPSVdaOU9jVlZ0U2p0RWM5RjZOOVRLN25ncUdtSEhCZWZyYlFWbDVnTEJQbndBV2ZqQWktRFdQQ1djOVlaTmhfNFBaUE9kNDVnelNwdGxtVU1OczBva1ByODZGVkFfTE9HcHlJUdIBpAFBVV95cUxQdUIxRFphQzJqZ0Jqa0kxVmpvbFBMN19SVzhCY3RPMGR4TmgtOEhLN2FNZFN0bDJxUklqbG5pTDdQcUNTRjdnRk8zZmoxUEUtaXNXRFBrWldLMHh4VlpaOWdJQ1kyMDNUU0ZmWG9qQWlLUlQ2TEFNZHZLbHdoVWFzRDB1N1V0ejN5VXlGazByTG5JeXRVeWE3Y2tOd3lpMERISm05Rw?oc=5", "source": "The Hindu", "published": "2026-09-29 05:26", "score": -0.599, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxOYXhNdG9wbEpyV1JrT2ZVSG1veDJCakIwTVJDTGNZY1RuRDlYZFlTMHpWcjBRN0lwQ1I0WnBxWWJveEJvZzkySFZ5NG1JODR2OHlFQlMwR0FEZGY1cFRCcFRobUR1RjJoeEtxdXlCd3Fac2otQXpSTFEyLTVUTktTLTBfb3c3MVl5NExiUm5aN1pOQkR2bDBWLUJJQTVBdE0xQ3BLR3l2NG1hemFCb0VuNjJiMDlkZmpvZFNUSHZBMGhSbm41OTJpT1VWY1J3aTlrMGw2QldJTDA1RndGM2ZpLXR5dFdFYUpYcUxFd3paUU1kRmZEdGhYSNIB_gFBVV95cUxNUGZ4U1VBSU1YUGdsOTVHb0dyVkNoT1lGSjBucl9LR24yUnRKajNCSHFLWWFFbDg2b05iN0pNR05KdG5ZQWo0dzFDRUp3N0hCamVpbWdMeTZMSVQ1bU1GRmY2X3hjMTRTMFFMZVJKOExiZFF5dFhkbUZkcUVjWHNma2YzcFVQZF9LT1hJaVgxYTZXSFBoTDBkT25jNDdIMzI4YldxdjJ5TmtINF8wa2tnb3d2eWtsX3FVamNKV2RmZG5KdzBKd292V0pYd3dQcDVFTGg4QjNLWWxLZ3o3MVNvS3FnT0ZJQnR3REYxSTd4TUdtenFheXQzb3FLMmZzdw?oc=5", "source": "Livemint", "published": "2026-09-29 05:23", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNYi1rRVNYUG1VMmF2VjVva1lnTmNXSGdCbU5SeG1yMkhWUkVjUUl5WjljdGhWNU1wcUhDakVQU3FsQjh5bmlRV08wX3pxMXV0U0Q0VDAweWUzQ0tNZnVsd19FLVVyb3daaTVGY2FZcGtXM25qYkxCaUk2NFB2NXc4dThpTld2ZDh6TFNzanJlYmx3OXVDNTctSW5haEtqWHBrcjJSOWROYmwxQUVEejlnUm0zYVFhTUQ4VXFSbFptWDA3LVBVVER2NzEyaFdLUkljcUltVTdhci1JejFSSEpiQ053RWtjQ2dWaTJ2blJuY3ZYVnFiN1NnT1RxYkpoNTh0Z2tLTTRR0gGOAkFVX3lxTFBSSFVsVGFrRGxxQmZjSF9Lbi14XzVaa0tIRFh0MzhJS21ONkxBTWNkUkJDXzNnRnFjMmk2dTlwNzRoem9INy1sYk12YVNkLVJ0VTUySkJnNTM1QzV6ZFFFQVlhd3c5cUlUZVpUc1hha184X2pGSE5JTEkwWW84LWlwNV9HMkNVamNaWGo0Mlp0M1N3cmRxSmZJUUw5UzN6aTd5MUlHLTRlM25uM2VScXljRXlVcjFlZk4yajZwZkxYSkx1VFp1LWtLX2dWdW51V2NSVFhxUUlUZ3lQT3pkNDctM1hldGtrX2NJQ3hkN0xXQmM3MmFkeXdweXA0M3VsdjhZbWN6ZjREclA0eFdHdw?oc=5", "source": "NDTV Profit", "published": "2026-09-29 05:09", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxORm9sbGt4LWI0Qnc2ZTIyNm5MMVFFT0FXelZ0aTQta2ExTkZxbUZ0bW55RjFMVG9yNmZVczZSWFluQmpxNkxKRnpMdmJPUFNfRDFQSk1vVUVpMGpLdkp0V1c1RDd6Q1NEZUFjQTJzT1VWaTNZTGYyOU45T0cxRWV4UUs0NER0Qm5ucWJxV0xyY2diTFJ5a2N0eWVWRElHZ081bFlNckRUNEpRbmZVYXRZaTA5TWxpUUltR3dsdEQ3VEMxMUkzZWNLZmlsTlRPWWV0dHBwQ2Q5MUlOcDNqVWhNS1RoSlhfYlg0X0hVR0k5R3VER3JjS2JBejJrWFJ0TFhYLTFLX2RBQkpaVDhtd2RJOFRn0gGXAkFVX3lxTE9YUFdsMTlDTl9lbkdfTE1VY0toUk10QmlBcWM0blRhdTBjU0RxV3Q4eWNyNDhpNmhFTGZvSFY2bHU2RVpMM0JzMGdsWFRKQWdPVTNpSkl2WXZHVHNuTXo5c2VDOHBuVXltMnVKT2c4UVprUHdodmd6QUF0ODN5MnQ4UW5sS3RCWjVTMGhZNVNNRjViWFkxek51M3hqUHd3SWJtVzVwMGx3LUNnV2xfLU5WLWk0UXZDYVFLWGtxdlprQl8xNVF0SmR5ZmZiLXFBNDd1YnBuRkJabWZNSDY4SVpseDZKZEZQV1JsbHdFdHJVMW43T0JmRGR1THNMcjVxbVFyUGZpdVN3X0lSTzRLVkE0UDBZeHlFbw?oc=5", "source": "The Times of India", "published": "2026-09-29 05:06", "score": -0.459, "label": "Negative"}, {"symbol": "MARKET", "title": "BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWFYxc2FLNFJkeU5VQ0dWdFVETE9Sb1JzT2tuVnNEWTdRaU9JNWQzX0x0VjNmZlNuem9FdGRUelVPeUhNMUpTUWlmbF9nUGJJU1NndEl4eGxYaU5IWjdzSVlpOE9TQlhmakNHbTZlRmMxbGkya1JTYmJpM3FWNnhLM0FSeDhYRndHcDJzaW50dEE4WkVyb1MtcTZvN2pyeV9sTlZ5NVBLc3M4Wl9hQ3JmUF9CSWp2N2NEVk1rWld2Zm5BbXNXdFBZ0gHOAUFVX3lxTE5YV0ZiOEdkcDVUc2tDU1Myb0RnY1VRYkFHUERHLWdyM205dmdzWUoyekhSd2FIaVltYUZVa3ZUNG1qdktXNEpPTkVxdTduMmhGNGFlckQ3UkNrS0lqYkU0dVFqRmtSVS1nUkdNVXlnN1RIdmlaNUhMVGlFWHdrMERaVFo2bnlla2w0eklGTEFzSUdCeVNmYW0wZThzQ2N0WF9wNnhIZy0tZmxwREprRUFLMFk4eDN0eWhPV0x2YmZ5WXhzVU55aExVaFJtMnNR?oc=5", "source": "BusinessLine", "published": "2026-09-29 04:38", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Falls 400 Points; Nifty Slips Below 22,700", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWW5nZzl6c0Rqemg0cG1reGtZa3NMMTJEb2xNczJsMS1xbnJscHczcXpwSnJVOFVVQTJQZ2w1T0RNZ1pXb3hoWHFFMkhTdGIxYWgtNGZvQUE1X2dzNS1LMmF5dUZnZVJDbUhqdURGTlhpMTd0NERLVl9wZnNTUEx1dTJXeXY1ZVZnOWgtZGhLUEQxMzM3bmgzWTVxVXA0TWlwbDdTdXFRRVpLQ3p6NjI2ZU5SMTZIU1hsbFhXYU4wUDZpbW1fQUtZ?oc=5", "source": "HDFC Sky", "published": "2026-09-29 04:35", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxQNjN4TURGTmhtN2ctbmhRZ0NIMUVodFU1RzZNQlB0UkxGemdVQjZiYWh4WDJGakxkN290TjNzY0JEV3RsZkEtLXlxTW0xNFRzbksyQjRtSW9nSFlCSHF5Z1JMMHJjblJLbFJhX1VjRVE2WTZ2YV9wbnhNM1ZCMG5hekNoQU5uVEpscFdaczk1c1BPcWt1VXRzbWs4WFAtYUZIQVFMbWZNcmxWNE9zN3dkanZUdDhOb3dFckZGWXZfc21sMVc1Q0pOeDRQejVMR2Ztck1hTFFwSW9qM21kYWxqM3BoXzRGZw?oc=5", "source": "equitymaster.com", "published": "2026-09-29 04:35", "score": -0.477, "label": "Negative"}, {"symbol": "ATHERENERG", "title": "Ather Energy Share Price News: Today\u2019s Decline Analyzed", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxNSlI3d1lGdTBUQ1NsMmhvSDh5UVZMVndVcjQtLUJBX2VLOFhIT1hoZFFhaEZWaVhKSm85eUw5SFY3NTBrMlJ0SThWYU1Ib1R5Y0NyUGlSQzk4UDloNlhPVmRyR1JWR0hZUDdfeGZXT2toVDVseWxuZVBKVFVKdW1RNg?oc=5", "source": "Univest", "published": "2026-09-29 04:23", "score": -0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Oil rise, bond yields: Top factors behind Tuesday's stock market fall", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxNQWN6aWtsVWFkYzZta0ppZDBKT3V2WEIyYy1nWWJNMWNEYUl1T09nLXRyeTFlNWF6NTZUQ2dxQmZfYWxuTkxKbFRkQm9RUWZfMVA2R0lVMFlubHFyTi1BV0NGWnBuNGtobzJmZURPa1IwbjlGU1VwUkZNQUlOWEt1U2Y2SW40MV9ncTAySWd1bjVJMWRJTVhZczlVczRQZWMyekNLTThSXzFDM3pwR0NONHVidWVEbUhzN2h0bklZMkNEYTJqSU13bF9uUi1ISVAwemU5RGRFTi1EZkowSWE4emRB0gHnAUFVX3lxTE1aRkM0ZnlvVmp3MHNlaklqcFR1dTFSeUFtbHBBbjdMV0tkY3lTbUpPQ280dkFZUXoyaDEyT3gwVHRrRW9CVm9PanNSb1k3RGtSZlFTeWtBWWotMGwxUzBOUzNVZ19lZHA3RHdwRTlfbTMzekNDR0trRXdrZzZWUmJFVmFWdmhaTnRzWkZYdDBmZXhnMmlEcjBiN0k3Tl9yWnJLMHBPZ2lHYWhGMXMtWEtCQXFfMmpxVkYwYTc0UmFIX01WVXFoZVFncHNybGktUkxhZzRLTFJGdEE5d05KWnVaUy01ZmRmZw?oc=5", "source": "Business Standard", "published": "2026-09-29 04:23", "score": -0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what\u2019s dragging the market?", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUmk0WlNhUWFKM2hkY0tydWR0QV9jUVFvV0lQclJYVFlpcXd1Q2xYWjV6aDQ3SGZKWjdkdE9nWTFNNWFsT3NwNXpnVlNtQVowZDhOTmF5eHJkbmdZZ0R5eWh2RHlhZmlXNE03ODdxWnJtYWE0NzlLdmZCNXBVMUNLRW1Hem5EYjUwMXdvcjN5alZJbUdLSTN2RDhvamt1cm8yNWNzOURJZUctaExtNk1ocHRONWswa2ZRc2pjYnRtMXJQcV93MEtTc05yZkJIa1phUnFSSjlSaXpGZ9IB5wFBVV95cUxQUXJua0JCWWl3dVNjWmdUNFdmYTNrYjh1ZDNMS0tVRUhNSTJ6c3RRRjZaRmJnNnMya2MxbmpId0djX3QzQ29LS2EweVFmSFNjZTVfVFIxUEZlbUFEX0F6djZvMnZhUW1oUWlHV29yMno5V0ZzZjJwYnhOSkhuT1BMc1FDdTFwcGtiTTYyT3ktdnVaSjFnU1hkZVhrSE82N1c5NDJjR2Z3LUlNQ0Q5N29rVnVPRTJwUjY5NlNoVkVRMlFQRFVzUnFtYmh0NHhManBaYm5HOEYwckcyR25KR3NiZXFFbVRVZDA?oc=5", "source": "fortuneindia.com", "published": "2026-09-29 04:21", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty sink further; What is keeping the market under pressure?", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxPT2hTUks4TnNPVTAzVG1rd2xFajdvVU5QX2VTZWplSk9zXzBWc0ZOdGVzOHlrTmVOOC1hYXV1MnZxQmdnUFUwcHZPbTVMenVma0hOOVc3ZDVwWnZScEpoQUp1d2I5XzRyMmktMHZIYWhvZVVtZ2xzakx4ekpES1h6RzlfbHFxTGRUakRTbU9yeDZFT3JLUFZPMVBLdXQ1SW90Umc3S3hIMWFTeVlReWfSAa4BQVVfeXFMT09oU1JLOE5zT1UwM1Rta3dsRWo3b1VOUF9lU2VqZUpPc18wVnNGTnRlczh5a05lTjgtYWF1dTJ2cUJnZ1BVMHB2T201THp1ZmtITjlXN2Q1cFp2UnBKaEFKdXdiOV80cjJpLTB2SGFob2VVbWdsc2pMeHpKREtYekc5X2xxcUxkVGpEU21Pcng2RU9yS1BWTzFQS3V0NUlvdFJnN0t4SDFhU3lZUXln?oc=5", "source": "newsdrum.in", "published": "2026-09-29 04:21", "score": 0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street", "link": "https://news.google.com/rss/articles/CBMihwJBVV95cUxPSUtnaHFiYjg4Q204R0luSEhzcmdiaE4ycm9QNW93XzVKMGFOVlpkLUhhbXJDeXhqWWVTWW9FTGw3N2ExV1JFaTg0YjJhV0FrMUQ0Q2lOY3RtekpOUHpHWGJsU2tJTWhzSWdrU1pxNWpaZDVCclRGWWJrSi1HX2k2WmdEREJtd0RBeUdBSlNqekVYTHVqZnBNT2s2UDhYYXBBNmh3cE9kN29vbFlvRjU1OFVaemROVDFEMTgtbnRDVE5HeGRRSUkzY1ZScTlhM1ZqTVBSRThJXzhTb1QwX0R3YnR0b2twZEtsYmJJWHAwTzE2MFR1eWlsUDhNMHpvOW1BeG1pOE92NNIBjAJBVV95cUxOQTI5THdETFZZTFQwUFpsMktSVFhjeDZZWjhqcWdldDVwa2YzOXEtRzBrMWp4UW1QU3dqSzlqeGR5UGJpYUo4MXJMVndFdHpVd1MwOF9vWEFjQ0haZEwzNHB0RWZBRDVCdFZWUmhKdnM1bHRLbkp6cHNTUC1hNVIxdGRlVEtsczRRSXZtVlhyYWpQTUVXelJyeHFOZkREMUx3dnQxTXhCdFd3RGdraUd5NGFUU3NCM2hQY0tLaEU1Ym14WDM4UmZNdFppUWVNYWJtY2c4VjhFRTd0Zm4zczBtSGxJcXBPM2FCVXI1akRfU1VGWWd5UmlGV3Z4dkZHc0hjU0VsZ2p0Ny0wUndQ?oc=5", "source": "The Economic Times", "published": "2026-09-29 04:14", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxQYUFDem9SaEJWdjhyclFJQ0NyNENLejUtdThtMHpzZlREc1dxWVNucG95Mnc5QjE4WGNZc1dMRnFUZkxmanN1T1FmTEw0ZUE4bDhCQ2lXeFU1X2FlVERFS3BEcEVncG5Ya3BGQlRrQmI1WHJkRUcya1F6bV9XU0tvaXZGXzVwN0tEMGFONklKRTV5MVc0bkN4UUYySm50SmZGZms2UHptNTVPMDZnTlJvXzNFNEUxcWRKbTlTZlNLT29rcHBWaWd6RGZLTVV0NjNJSG1kTXBpSW1SZjRJcWRCb3FhWURJTFc3ck45WURndnRTZjNTYlHSAfsBQVVfeXFMTXItZGlfbXJYZnI0OFZ2V0c1VnNhMFB6Z0Y3ZjFrckJPTVZLajJBaXRmS2JjNnJyR1RfMXNoTy1ZQUViZk9tay1yQl8tbDVIQU5TSDJBdF8za3FjMGVZbWZZcV9NdDdILV9MZTFybHRtNlpDeFlPdVh4cmd5d01McXlQVEN1N1M2VlB4ZnJFdERpbUtJX3FlMXJlQmdzcDFnekRROExiRk9RTFBncFpwbzJQanZGZThMZWx5UWlIM2g0cVY0d0tLTi1kWnU1WW8xMHBNQU1qc01GcGl2ZXRHLVN6SXk5djFxZ0J6akJVSF9MZ2RVY3BYYUtoVGM?oc=5", "source": "Moneycontrol.com", "published": "2026-09-29 04:02", "score": -0.421, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxPM0JpdnpnZHlIYlVQUnRNYVVFYUlUZFJ3YkdJWXpXSzRQaktqaTN3LTdPYXU1SkRibHhTd0dOTTJkeV9NM1FZU1JWbFVPTmVBOGwzRFNwLTZ2V0lldi1kNXR3RWpjZzNmaUJOSGlIamdJcWY5TTlvRzdIZE9xZ0NiMFRpTTRnWHJZS2JaR0FOd3M1TmltbXBhb2RZU1dXUHhPdGp0MlNVbEEwV0cybVc3cEhxclU0azJyVzV3dNIBxAFBVV95cUxNS3psTE9IOFpFRVFkLU11bGZMbjA5VFNIN04xWDZJYkxIX0RscVpJTWJ0Z1N3Sjlsb3lCNTl2RURseHQ0ZVZTeHZSQnVjOFJCUjBZLUl4OUhSN0NLTm9kUmlLbU5BaTFLSzVYSVNXNExPb0VQRm9FSTVodDkzaEVLeThKSUl4b3IzcEhwbE1vSFJESGxRRnU4SDNaVkI0N05VTmtpX3F4S0VaZnBfekd4YWk5YXF2LXRycHVlOGVGTUVmX0hJ?oc=5", "source": "NDTV", "published": "2026-09-29 04:01", "score": 0.214, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty opening: Will stock market crash or open higher today?", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOUDZsU21wOWJFXzhjakg3OUQxaHREd05uWF95VTJlS05aOXQ0Vjdqam9UcjAycERGamJKcVdrYVJ6WEt4QUhHeWJaaVlJY09vQWxqUU5FVFVjcVBheEhubUkwMWdfSV8wSFNxOXpGWWN5WGwtZHk5VjlwTGw5TEVUdmNDUk4tMmZTdVlwOVpwX1IwaEVnNjNSeW9abHNFUThiS2I1RG13YS1pVjRWYkduWXk2YXh1STNNWUdEUWpKZXpVMUs0Sm9aOUs1Vm5vWFFiLWR0TmNTNmx1bXlkd2h4b2JocnN0RkpqRUHSAe8BQVVfeXFMT0JkeUl1MmI5TEZGbmM2bGFKWnl3LWdpQk8xVlVnNXhhbHg0VTI4WUUybUxNRjdKZHBVem5GbWVqZWZsSzhacWNOa3NpaUQwa0tQV0pMSGg1cDJVRGJHNVl1UWF3YjllaDJ5WnU4NjA0dFVTRkprekFzTHBGYlkyb1VmZXd2czlibnoyRm1Scy0tcGR4TXU0aGVDZjdua3JrcXJDUXRUZENMY0pTc1ZpUEk3UFl2andIckNfZ2tNZlZBXzEtMVF0Y1YwYmhkRTNOVmp2Q0ZMd01jQWR1SVJQMVlJQk5SRVpzbHpveVQyazg?oc=5", "source": "India Today", "published": "2026-09-29 02:57", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Gold Rate To Bond Yields \u2014 Five Key Factors For Sensex, Nifty 50 On September 29", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxPX2RZNUVYaGZnM0prSjZkblNWUDAyQkJnS3hOQVFsZVVzWWY3azFvYXFOekJUajR6R0Zla0NHN3NNSlZhbFI0NmhUUW1CaEdCckFrS3gxZGFUZDhVaEdqVzlwaDNIQV9mak8tTlNWVlZxU2J2OGUzemk1akNYb2k2MDREZGNNZFJ6UmxQcGQtblVyV2RKRnJ3cl96M0kzdmE5bmU1aktMcG9oZU5nUE52RnhuSGZSbnI1dU5udm9aNVpuQzVVanlZTWVHbHhGNDRDMlllS1F2ejFGcmxuNnhlOHloNE4yUdIB7gFBVV95cUxNYkFxX1BHMHZULVZmS05DY2N4cXJjaWdnX3RsWFFaWnJjTlF0dk1ySEtERGF5bzF1RFM2SjRZYzVlUUQ5LWswYUVvSHoyb3h0dC1jZ0ZZcnhkYXpFMzJvS25LNEk1SzFKTmdGVnN4MDdQN2FMaHhmZFdQVDc1TVZWTXlSSUtRYVlPVzBER004eFpRcFFhZFpXRVM4T0FWZFFVWFZQbjNnRk9tVFFtWVBNY1FEVmNBUzZPdFNJdWVZWGRsdzB2ZnRwZUI3YWdzUTk2Ym9lT2VtcXZFZVF0NUI0bmhKNHNUdzhMZnAzZDZn?oc=5", "source": "NDTV Profit", "published": "2026-09-29 01:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQWDNNbllRRzFSTkxtZmZHNmJ0ZnJPdDhyZFh0LUVuME1CYU9hdkZsR3NubDJXN2NQUXFnUER4RVhud1FsUENqWUhMdGdjT243VGZ1RGZJWGVMV2UwRl9HTTNQSk5wVU11djAzV05oalhsYzRrdG9mUF9ya2Q1ZUc5dFFUaUtNU0RqWExWMXVLSkVFSG9pUGp2VVZjWlJqdE9QbE9hRzIxYWJURXhwYm9faDk1S0Z3X18xd1J1d2duVXExemd6aDJyOEo2OW5RLVFUTWw3ZFFhU21oNGxZRnVfWXRPcjBDNzFUYVVrN0lfRzNoNDJJcktFa2FVR3lOSEVPSl9XN0dLQVNPaGfSAZACQVVfeXFMUEQ4OS1kTDJjTHlCVHp3dEFPZmJNdGxBQWlrdmN4dlhGSm45c1duQTM1WmFGRnRuTmNrRW5FaV9OQnBtc3dmVENWU1QzZG5yRGpyVFRTLTFnTlUySlNfSTFIR0RBSXpkQkhlWjNSZGFKTkFteVliTE1Zdmd4VWpCVkZ3MlQtTWxjZWdKR2VfdEM3ellKWlhua2lIVVZGaHB3bjlYQ0ptaWpmYUtid2dnLU0xdGlnMm9jYXlBSUJ5cV9ZbGZEUEUzMWd1czk4Q3Z3UHFWVWRyb3VxZy1EbnkxVXVmOVdmMVlHaEwteUllVkdCRThlQlc0S0xyblBKa2lUbWtwdzRJSGp0T0RfVE44cG0?oc=5", "source": "Livemint", "published": "2026-09-29 01:19", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3ZwWkRNRjJrZ1RQN0tCaXBfTGZORVVIeFJ2d1FmTkJpZ3RFM2ZUNW52alVyTDVSLXNzN0hRWUE0YUZ1NXBJZWEzbWVuV2NDUFRxNmRmWXVSdnkzZ0MtLV9UMm9FeTVaM2VGckptZWt1Wnhpd2F6TmVjcEpXVEJhNXpKWkVFd0NCelczRTBidmMxam1zVjRfM1J0aDVHaVl5MWtkQ1RvS2xXNm9lMTlraE9IQXBqd9IBuwFBVV95cUxQdU1hSjhhcHpRbXBFRmlSLUVvakR5c3ZwYlpORGl2M1hiaEhqa2dDWTVIdHhmY2NsNkVUWFZKT1c4MHROTG1fbEtCYnZnM0VMOHFEXzB5cFotZEtGNHgyVDR6ZkpwM19JM1JaVmlFMElpSUw0OHRMUXNKVUlvSEswOFdQcXlLLVVZZWpDVlE5bHplYkZoNUp4bUVEV2VhaWFVZzNDN1dpRFVUMUROeGtLQ3VlZFJjUDZ5Rmd3?oc=5", "source": "wionews.com", "published": "2026-09-28 19:51", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQWkFyUEVEYlc5ejlyTldhYVVvYml2c3N0YTlnSm9yZHEyMDNHUnNKVnRNeGl5NTZ0NkRpZFJJWURHUjdEczROQVpseThQbmlJdGRLa0R2X0Vid1VKM3FncW43TkVIU0hpVE5QY29VMklwNDRQa0FXNHpoRXhWSC1kaFQyVUtzc2RZYk9BMWhpTU5XTHZ4RHRMMU81azFLVFF4THZkTjJ6ZUl5NDNLcWFibmtqOUhjeEJYQW0zY24zT0lhZnMwZElXQXpB0gHPAUFVX3lxTE9jTkdQUlc5aXV2N0dtX0UzYWlfV2ZUSEhCUGp2OHFENzhsWnJQODNmemptdW9oQ2s3Si01ZnV0N3RlazVRS3YxZWJsNDZWZEx1MXdMcFFzZy11MnItN1pWQTdYS284QWJwd2hQZXdxdDc2VkR6emZGZFdsX1pDM1d2Rk1Ka25SVTRXcnAzT3dqekpRQnBKUXBwMGpHZjlQMXBtUi1pUEJac0RYSW9LcnBTUFkwbXoyQ2tDUkN4bEs5UGpoR3NBaldjekJVMFJ4MA?oc=5", "source": "Business Standard", "published": "2026-09-28 17:36", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr", "link": "https://news.google.com/rss/articles/CBMinAJBVV95cUxOOFgyakNMWTlmbmpOdjRVeTdlckZXNks0dmhfc21YME9FaUcxWjRFUG1XdTQwblI3MS1oUFN5eThST252YWpSdkhXbWZQY1V0ZWdVTGI5c2VXNXdFbzI3aUozMDh4RVMxLUxnb0tLX1NYU09yRGxGMWlvaDFlRzQyNkd2eUsxZ1lBTVNnMWI0VkMwejI1a0pWcm91NXFJSUVDZ1VhQ2JESWo2cnpDSHNHbGlhY19Za0pNQ0E3V045bjJMR09ueDZIdkNVUGthN3lRak53QWpiN1B0WkpRb3dRUTNaX1RYVXp0LUMyZG1EUWZPZlNXUGQ0WldOLWF6MFhQalU3YzA4WUttM0x6al9xS0xSVHdOajJJa2lacNIBogJBVV95cUxPanhKS0R3c2ZjbHJ5RlhHMmxmQUVLSFlUTEtBcWFTbS11YlNxdzZqNDVRSHBISmZfblhRcnhPbXVwN0NkclB6ZHNLYUk4bTZQU0x3YUs3NXdrUVE4RzJzY0VQVjZfazRmSmtudW9lNGtqcU1aMU5lMUVVS21lWm5pa2NxWlZxLTEwN0FlNGVJVS1lTzVvV1B6R0lsZGtDOUViTEFycFdFb3FmSm1KTjJZS3dEV3FUMEc4T0FVQXdBTFlCdk9sUlRyMDA5WHA0dmo2Q2lYcTFGTTJqYkI2R1JDLXZkbEdpYTBDU0NWZE1tTmd5SkFBNWxTM24yOERhN0x0SWkwY2RzZmZkRnFqNUJjdER2cFpqYmNBYVNfT2otZks5QQ?oc=5", "source": "The Times of India", "published": "2026-09-28 13:42", "score": -0.896, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNUkhaTEo2TVV5Q3h0cjBXLWVGX3EwakNwOXJxS1dmT0Fnc2p1eXByY2d4cFlIbE1HTER1QXFqWTB0bHNLR0lfWTdWT2RTTnJKRjYwLVhPU2t1dEdVMk5NMFZfemk3TFNhdk5GWDJGRVZUdV82aHJETlJWS051R0N6bU9pSktUWjR6SXY0d3g2ejhjeFRpdkszSFJzaw?oc=5", "source": "equitymaster.com", "published": "2026-09-28 13:25", "score": 0.652, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxQeEMyTGpqalIydEJBcFVFWC12WDdUZVYwbkJPVk1RTGRrWlpwTnlnMWJPMk9TM21CWWxfWkpIRU1QRWNCcVcya2JHbEFRLUZLa0Vwb29SOWt0Q01nbmRfZUhrcDd1M0hsb1pHWWViTnRUNkNYek9KZDVEcUlnemU0SEozeGo0dDQxV3BJSkRlS3JQZU91YWEtUHBERUt1cWZ0T2VZY01yVVlWRlNUR3FpWlJNeFFHYlhiekdoa2htZzlJeWw3b3BhaXFnRy0?oc=5", "source": "hrtoday.in", "published": "2026-09-28 13:16", "score": 0.361, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOZGFILWIzX0lTNkh0Rm8zMGVUTWxEVGdYN1FXR2JPUTJDeVhiNHdwaVdGM0xCOHdUYTQ4MmZqLUtVTXk5NU5va01tSzN0b0lJWjFMcmY3M0N3OEhaa1NYLUF1WkxLUk8zaGZZT1RzYzd3MWpMQjFmdTgtYm5fWG5Xb3VWenYtZEVWQTJsZDd6elFSTWd2RWtMeURUdTgzTFgxSExQSW1rMFJLVkpnVG5TSGx3YUhtM01oUHpvRWNERDEwTmw3RzN1d0M3SlZ3dThNbEVnNnBtVmJXMGgyaWI0NVUzeFJ3LWFocVNyVnBqM1BxeEdlZXVQeUJZdXRKdWwxM2hDU9IBigJBVV95cUxQUWpCNDFiSU9RRGF5Rm5PYU9FZGp3c2JWVFRVSzFWTHdrdDZUczkxMVBnLV8yN0hmQkdhbXhYM3dLeHViT0Fjd0o1MkFpT2h4d0tkR2JjS29ZZWs3T25DRV95dDVtNWlFQ2ZkbGZ1WVgxRU43aEZBZEZjLVNnZ0JnZHd4TkJUbUVMaHdEUTZERnFvQ25RT3V5MmxrRk5UaG1oQWoyTUtPMG9oaktqczhZel9nTUN0eEpfRkdxWGZHRTNHUnVRQVlUdENBVFctUnRRS3lMRFBWMVk4Y1JhVFFHMGNMWDNrNjhiclVOOThFa1JrTkxZWjB6U09fRGRZLVhrbGx1OE9MZHFMUQ?oc=5", "source": "Livemint", "published": "2026-09-28 11:48", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPX21IU01KT20tUWlfRy1IMWJ2LVBfSXBlOFdWYUZid1ZJdDRncFozNEtSb3NRdnlUTUlOTHFBNkloNjROR2daRV9EQlRObWhYYm1uYkl1dGdDck5yRXM5b1pzU3podGhMc1UybjV6SGNnd2J0dW9xWjRaLWVMWjBLYXlqN2NCRk1fSndYX3lBUU9LUGRBMlg0VnBfYWtJcHhaZlYwVTBxMHBhMWtXY3NhRko4UmUyVDZOUUFVRWN1OWs5RUhyOGxzV0VMWl9sUG11RjdudmdVNHp5M0hFQ3N1aUpoN19LZ19vVmo1MGVBQQ?oc=5", "source": "equitymaster.com", "published": "2026-09-28 10:56", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxPSmh5R1BHajZwb2tLTkNjdWctZ2g4d1RVU2FVaXdvU2Q4RlYzWmhia2RFWVlCbDBQdUd1NkQ1bWJUbkQtTWQ4Rk9zYkVMTVFKSGZINVFtSkVKMzhRU19ueHF3SUszbkdSOThBNFQwa0lhN1c3LVdJajZqV01uZENnWHV5UzlqbDVfSGpVdm80WlM2STJRQ3RBN2NSc1Fqc1h2amk5aFlyRExGQjh30gGyAUFVX3lxTFBSM1VWX25QMlNMcVR3N1ZFR21rX0JhZy1FVlJ3UFF1cS1PekRTcVhTOEU0Q0VGenl6Ujl1VzUtbEFvaDNiTGVpT0lHakNiQkpOX1lYRktta2stajUxT3NqSmZzRnBzVlUxNUlvdHFlRUJIN2ZKLWJfRjJ4R0ZaZVpOazYtTFlnakVCSWFINDdfcXE4cGJUYmJXcFhWbHhZUHczOHFrb0x2QV9wa0ZtTkJzb2c?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-28 10:48", "score": -0.7, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Falls 1,124 Points, Nifty Slips Below 22,800", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkNsYXBaNkxVbEJONXRoU2VUMDhmLVp5MjJ4bm9KZXJpWWp2TV9WQWhkYndIOWJOM3AxbHljM0Z4amc2NmVKS0p1SFk2REJiUVdxT3JEcG9tQ0VPMEJSa0kxNUlOS2dGTHFVN1M0T3JxbThwSkFVMHE2NzVYck1FUDR1bmM2bE1UbGJaZVFmR3hCVDJTbERmTzFnMVBoUlg3dmRkdno3b2lmZTVGNGhQbm9YOGl6SDlBSkt4M1ZoaUlsTkVf?oc=5", "source": "HDFC Sky", "published": "2026-09-28 10:46", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaFhnckpab0xJQWs2Q0lFM2ZfamY0ZklMM19qbWRQLTFXY053NHJjdkRkMWJIWUI5aU1OVl9YNEhRWGNCU0syb0RZcXUzRE1rbDBSZGE3WWVxZmJGN2poT0VJYl9VTThlQVZVYmcwS0tyal9kcFVkRmVpT0FRODZRdFZCTzE4bjhOVXctRTR0ODBvdC1DWGVEdVY3a185cEJQdUdxRmxXbFpJQlVUdHpYNlVXS3VIdmJXQl83VFgtRnNJRHJXX3BpZkhqN0hlOXFjZ1l5ekpJTdIB3AFBVV95cUxPYTNqWi1LYzdqcXJ2c2FtWEJGUVdUd3k1YXRDTnNWVWlyUFo3am13UmVSaHd1c1FqcDFHQ0pNSXlvaVZKYnVYWGZBRzJXOTgzdkdpbHVfWjlHbnBVV3Mwcnc5eE56S0hwaFlRREl0WVIwS0Q4WjRsOGMxVm1XUWQ5YnY0dzcxOUVPbUxrUFYzcEx2T0JPZ3Z6X2tkazNjRXc3ci04MHZGZnJUalk4c0M1OG1UZ1VDQ3E1UFJ5eVVaLXdqSWs3eWVnMnRPV2ZWcHE0YUw0cGVROG03aXV0?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 10:26", "score": -0.612, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPUU44cXhTejNjWEFmX3pOMEQ5YkhwR20yQUs4NGxnNks0d09rWnU2R2pxMWdmOGQ4N2s4Nm41WW9OR1lRRzU5X240Nnp4Zm44NFJ0b1N6a052VjJpXzlmR1VIXzlobHd2OVVJYnV4Q1BfMHNZUmZ0eWNqWUNqMzNGelN0Y3o5ZXRxY3hzby05M094NmZ4aWxpakRnZlZWYlRQMnhvVGRJcGlleVFpMHlNS0VRZllGQTktc1ZUWXM3MldYVkd3THVpOUh1TVVJVDJqd2tiU1N0al9oblNQajFGUDN6RlV6UGRQU2poMTV5dDRtTEVnZ2p4bzFITjQ4SVRoNVV5Z2dZbTFyUDDSAZACQVVfeXFMTl9adnRITUZ1VzVQX29ZOGpxVXpOZ24wcFluN2JGVjFsT056LU10RmMyQ3RnM3pkQlQzSV96TXZVT1ZWdmFNU1VSZmhpMWlCaWNtejhpNWwyZ05CM3c5NjJ0VnE3MUl5R19XWXphSU50eWRpd2RZemRtMzcyZTJMcWpOUUJEZ1BwZGdyXzl6ZW9MbkRoOXZjYWw2X0tURlRyTk13ajNhUXRBbWJpaFhQd2lUd1doVXRMU0VRQVRBTU1rM0xxMFN2alRHRWlWZ3pUUzd5dGJwQTJpdUlDUjJLMjBHNVVOVTJtMFFhdVlJb2dONjJjNzU1Y0p1ZE5Cbk9XcFFRT3ZYNHZaVFY1V1lIVjE?oc=5", "source": "Livemint", "published": "2026-09-28 10:15", "score": 0.402, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks shareholders approve fund raise and borrowing powers", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxNR1MxLTBoYmdoaG5EZlRjaXpBaS1ZNmkwbjBPV29xOUNGMlFQTjdFdG5ZS0JTRExGcm1XWTJCWERCMG9SRm5FcFBwSUZuVkZ1clJ3RDdRQWQxMENXTDA4UzdRUVBZeTJNN1RIZ281SG1sYkJ1TGZZeFBpN2FIRS1ieDJPcVNXY3ZuS3VHYTgyM1VuTzMyaFZkSTAwSzhrZWI2Mm1iVHlkOUlJelFUVnM4N0I3aVFwR3hvOHc?oc=5", "source": "scanx.trade", "published": "2026-09-28 10:06", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top losers", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNMmZlbEQ0Z0pQZ3FTUXJfQ3E0YkxMTFZlY3pIRjROZTIxeXE3T05xbW1iTUpkV3QwTGlqUnplMUtNZHF0Y0ZzSXBnS1luZG5UZ2h0NkpxNzhPZW52NGUyMjZPaHpveHVHZmpHM21TNmRtS3FldUdGeFRyMEk3MzhLRVkzMWI0RVhKbHFqa2JCUGh3U09IckU2bTEwbkxwenhaSC02X2NVTVBlT0FWN0hPWGFleXdzR1FwZWhBYW1kUmVMdHdha0s2REl2LWxjczAtOTBIQjMtZ3N2SnZHNDdRY3VydlJCM0XSAewBQVVfeXFMUHQ2MUh1aFVLaDBFTVZuR05mVGlpR2V2QVkzMnJFSC1DRXROZDNRSENDMHk2blF4TGR2WllXRk13YlhFRTJJT0UxN1BPbnRBcEpJZWRSc1VTU2tfcWwtNk5vTHZYdjlRZ0FjOG1OYlVuNHFyQjN5MGRicU14eEpadzRkMjVYdmNWbG1Zbmh3ZkJicGV6c3ppMlMtLWhqazd0VkpsVHEwNFlfVFlOTDd0Zjg0OWJLeFBXMGxGWlBzS3Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>heDYwdDN0UWNXdl9BUGFnTnRMamNnTWJYUVNmRWJWTzJhN0U3YzU0YS1PSDI?oc=5", "source": "India Today", "published": "2026-09-28 10:05", "score": -0.178, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVkFmQXdEZjZITFVKV1BEOHlKXy1rajlNZ3NuN3N6UXdZa2lWWVFxNnhXOTJtYmZxOVpOcVVpLWE3VUhwZUhjVXBYV2VleEVpbVR4RTRsc05tTFBIcXNoME5VaVlJVFR2ZUx0Mmx6RXlHTFhKUUdFU1J2OUhXNERPU2xsa0FGTGFOcjJzQ0ZlQkIwY204X1Z3UUZTMEt6NDZRVDJMbUQzclRobkxrcFpWbGJTQXJnRFR0ZHBMdURjQjgxZw?oc=5", "source": "Kalkine India", "published": "2026-09-28 08:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Nifty, Sensex: History favours stock market comeback in October; stocks to watch", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZE5UeURMRWtrOUFNekVkT0ZOcFI1SkE4Q28tZDc1NkJvbmFaakNlQlBDWkt4RDd6b3FpazN4NjRzWGhMN0RaYXY0U05IVEY3bU1lN3RFaURJSjRUTnF5Y3o3LW1wT3RtSkx5LW5yaWpiemJ2Ym1lYjdtTmpKY2lPWk04aVhiR25wMVl5ME9HSmUtQ3RIaENZTC1pOHpOekZVUVNSSWlFaXl0N2NrS19MeVpJdUxLeEl2blBYSjNseU41V2NjTUxmeklyeTN2Y1B2eWNuQWFTS0FVX2hJNWfSAeMBQVVfeXFMUDhHbWlIakswUl8zYmdMcHhmcVlGQ1V4RkdsdHhqN19JMjZwT0dxMGtVeHBQX2gxZk8yVlFwamlzblJNbUZJZU84N0RRTWk0U1VJRmc4VUZyV2p5NnJLNjRYcExKb3NKWjg2NmlMbUhRVFNDZHdocnNsMl9RVTF3YjBkYzMzaTRqdFAzbE9jX2NKWlZWb3FGOEFPMkktYURRbUZLYTR3SUVTWG84cXo3TzItZGhlOTBoNFhfRTlXSnNfOHJPNVctVEFEcW5WSzg1bHNHR1c4MUoyODVYWnJqV3U2U3c?oc=5", "source": "Business Today", "published": "2026-09-28 08:15", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher", "link": "https://news.google.com/rss/articles/CBMiowFBVV95cUxOci1kRlliVGdLVkdiMUM4b1lqbEFvLUdDV0VITWp3NGlyb2w5N1Rmc2pZUi11cVhmNkxDUlkwZThkS1hOZ0lFaXdmYXJoa3FiT3hfeHhaNkFwdEg2b0V6NHZaZ094cG9RZGQxLTMySlZLX1J6SGRXcU1Sb2RuTng0RzFzc1lZMWNHNjY4b29HdWpzOFRWclh4S1JGUjlGelRRSzlv0gGjAUFVX3lxTE5yLWRGWWJUZ0tWR2IxQzhvWWpsQW8tR0NXRUhNanc0aXJvbDk3VGZzallSLXVxWGY2TENSWTBlOGRLWE5nSUVpd2ZhcmhrcWJPeF94eFo2QXB0SDZvRXo0dlpnT3hwb1FkZDEtMzJKVktfUnpIZFdxTVJvZG5OeDRHMXNzWVkxY0c2Njhvb0d1anM4VFZyWHhLUkZSOUZ6VFFLOW8?oc=5", "source": "Free Press Kashmir", "published": "2026-09-28 08:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHU1a2VYbkdKb1k1RENtVm56MHlVeE9EcW1DQWd4ZmRyY0g2b2JqZjkxVENveE5US2JvaWtoanpITFc5NzVFS3hzMWRxcmtPUFJ2a1NBX2xsVDJUWEZrekpKNWVLZzZ6TlRQUnVoVWZWTzZ3Q3VBWTM0WkxqRzVhM0FzWm5kNmtCa3JMUDRENUwyVU1iZDBNd1BMRkpWenlNUHpLTDFScU1rcW0zcnNBM3pWODVoMHV1WlhwNmVSSllWTHVWOW5hRE9B0gHPAUFVX3lxTE00UXRvMWNWTlhGMWphc2xibF9MLUtJQnFQRjR3UG5nbVh4M0NWMVg2MzdockRzaEdnWlpTcEtyM3dGWnRTbnFRQnRKV1JmZk9RdWY2UnpYY1VsWjRBSDVwTk10clJnNHlCSEs0a2g2TFA1alQyYUFWNXIzWDNfeXlOejBhVGJrQTJZRG13cG5XVEdVWExyM2Yyb1owX2pmUDNTWEZsenBGcUlYdWpWZ2NpSXh1dmt4blhQYUptLWFNNnBndk04NXhzdVc2ODNNVQ?oc=5", "source": "ETV Bharat", "published": "2026-09-28 07:56", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxQVWNmQ2tBRmd0NTdUbmZ2YW9kZW1wdDZrMXU4Y0gtTXZPYU9uc3JGRGJXQnhBaEY2YXk2TGhCWlhqZGU5OWs1eDlPOTJMcHp3ek5GUEYtcGQtYUdUVmpTZzVNZGlnS2UxVXhHZE9DcTYxSk9uWkFmaThOdUdzbnpmanpXUF9sSVVReXFLY29VeTg5QUZPNkszSmNGQQ?oc=5", "source": "APAC Media", "published": "2026-09-28 07:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxONU5xeDQyaGZ0M2JBemJwU0REcWJxYkZWN1hxM2d1VHZBOGh2X3gwR3plbk90RlZMLWtWZV9jek1KR2lsTDB4d09oQlJzRTNadHgyUEY4bHhFbGp6eVhOWDhqLUtQWkpIUldLLU1EbUoyU1VfYmNaOVdqWnJzREo0Mjh3bU5wTTZPN081MmVFY0liRzQzVEtZRWFVMURCaTJZX0twZzRZWVJHVV9KaEl2LUNFZzBpdmt0RFM1OXZoLXVKQmt3WmlDSGR6VHZFMWdiV2dWcklYVWxuTXdFbXc?oc=5", "source": "Upstox", "published": "2026-09-28 07:36", "score": -0.806, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxOMzZwenBCS1ZIMUJRRXVOZTBBME0xU0N0WGJsVEVfQkVhZ1NtMEplNUNXM1A0WGRZLUVOZWlTNi10QUVQQnJRSnZDZTh0SXVlQkN5eDZ3ZWstRVQ2TlctUE82ZmxJRG1BZkw1NjZGZGYyZWJiZlZ1YktSZU5OTk5MZ1A0Q2NyV0wzZEd6c3dHaUwxcUpZa3ZBQ0g0dGViQzhfTFF4RExTb2p4azg0WjhlVTBlSUZtSG80clVYa2p2MFBuZWIwVURXMGd5dG9wVE5sWUNLbGJCb1U5SjNBcHNXZnE2dGNkUlVhVUlrNndWVTVpOG1jWVZYeFppQUdRekXSAYQCQVVfeXFMTWsza1RTaVB1QndYVDNrWE1GWUo0QkJCd09tUGxGUkx2T3pVamh4d1VTUG9FYkxpUmpRV0RlaDhxeXVMMFN1Vk9sMVRIY2xaUjNXRlhYLWN0SXFuT2V4UktnYlRvVnZzUlFQbkJFZlNsMnBCR1JZeTVvRzVUa1duQm5hb2llbUlPNmZuQ2owWUFPbDRJWUV1ZHVoZWd2ODJMUFo1V3g5RzNfRnZ4MldzV0F3UGJfV3UzZ0lxWjdIS0hfZ2JXeXh5VFVtTm1JVnNtX0d2bjAySWZZU25TZGhiUjhkVERUenU0T1VJTld2WGM4QmVOckxtMk5QcThMbnR6bjg1cGs?oc=5", "source": "CNBC TV18", "published": "2026-09-28 07:06", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxPUkRFSHF1dXJEMUtBZUdNc0FqX0g2TjZqMV9MSFRVSXdDSHRobkFERnFiamUtMDVVcks2NDVkS3JYVzNYR0dCMnFlVDVobmpEWlduX2tCODBQMThWMm96RW1BTUlHbVlxbVMwNkpuWVphWFZJS1pTUHdwYWFJbEM2ZzNZTWhYS2luLWhYR1htelNSS3E1OHpXaV85Rm5iQWVIcHFnNkpiYzFFTHB5eXktdEplbUk3czJwV2dadzlBR3MtQmtlNnl3VDBhOGc1VGs1eENMWU54STdnREtoc2NOeGpJWXMxSnp1VGEtUVJWS2c3YWPSAfsBQVVfeXFMUFBfZ0J3ZVlJNGVQMHhXZTNvaU1wUzh3dHYzOU1sS3pFX2RIS01fSmpIMDRLOExqVmxMemRwRTZjbmxNcFRHbTlScFhKUHh4TXJzSTJyR0g1cVNwRmd3WDVWck1iaDB0b3FsVzNpYy1TZUU3RExUZjdfcl9ZTms2a2VnZUQ5NW11VEdGbFU1VmEwUjRPaGNHS01sVDVTMDNpVUltUFFUc2NKRDV6bmVyZWRMcDNXTzE0cEZLc3lNVDlpTmZMd2ttaVg0Ylo2d3BYY3BJa3dUcFM5UU9yLVpHSU16MXVUOUZ1dUhmSTdjVTRfTDZGZWUwd05zQjg?oc=5", "source": "NDTV Profit", "published": "2026-09-28 06:47", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday\u2019s market crash", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNeDY4VXlDMWttUXVoM1pMNFhYeks3ZVJpaUI1eDVJZklkME5QbmdzcFpRbFMyT3JYUEV5REM1V1hPSE9JckhRcE5EU0xpOWFfZmtTdVVqM3h2TDdwLWJDWUpMb09XOHdkVURHaUx1Y1BYNW1qbWh2cUpTazhOREdqa0lmMkl5d2pSV0RqSDhUOXlmT2VCWUdxdlZMV0lOeDc4ZFJIWHk1ZXhhbUhjUlpVSmVZNEY2cVpTQUxXdjVpOFJEWDU3RGZOemRCVEJiLUVSMXNhSWE3N25TQVV1eUoxMjJjcHh3YlU?oc=5", "source": "Upstox", "published": "2026-09-28 06:40", "score": -0.595, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: decline, valuation and peers", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE43Z0JKcUo3bkM2R2FfLWQ5TXNkQ2dpMnNldEZ1UHU3THMyeUkyTkc4TmN5V3NEUjFiNGVEQlBWd1pwQk5lZk54YWIyX0F3ZGNWQWJJc1NGY25WakxxMjQ3VWFfRHZhN291N1F6Wnd4YW55TjQ0eXJ5bXNuMA?oc=5", "source": "Univest", "published": "2026-09-28 05:52", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "India VIX spikes 14% as oil, geopolitical risks trigger market sell-off", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQc3R2Z25xanJ3ZVVqYmk4THp6a0pjWnc2UFg5VUNQLUZOaEowZW9WREszOXhBNURRYzh4ZkZNNWJaUmx2TGZjZDBVUUsyQ2VRczJUa0lvNzBLVzFZX1ZhdlV4R1Z4T3pIaWZOdWVvaDcxLXJ0Q1hxQzNaaDBURkRVN3VYT3ZUd3ZjNFNCNzJkZWtnZHgwQ2ViSWxHa1p0TUVlRXpROXVQaTNnbGtHM1dOOHkzUkJtSnBXS0YwU3JEd2J0VmdpQng2bENyOVFfTHhiTXfSAdcBQVVfeXFMUEE2WUJINWNtZDJCUTRSY1RsRHJsWUVSZi16N1F6YjBwVU1keTJZRFpUaE9rZ2FYZ2lKdU1KaldxM1ZFZkRMelphRi0xTnBxRWczdUNlU1FQTExxUE1qSnBzQkxlVGFNZUwwdExoVG91NFlEcHdOOUtJZ0xmZ0wyMnh1QjJrZzVUSWMwX0JYbHNBVVBNNXJLbkx4UG1GdmxKNExxWVdpWFVYUkoxSWRHQWRmTWh0QlNzSTVrMHlRaGVjSFowbUtkdF9GR2FUN0wtaEJWd0t5SWM?oc=5", "source": "Business Standard", "published": "2026-09-28 05:52", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxOZFhpNERkTkx4Z2RRS1k2ejBhN1IyTzR6a2g5MjJ3bkNjeDZlOWRBSmlIek1xQk1GcVIweUZvcVFEcGwwSW90RThvU0J6cng2YVpLV0tZU1dQQlhGZUtieFVuZ3BmWXY5aFFkSlRuR2p2ZW8wZF9TQmZ2RnJoNFV2Q1lMT2JGMkxLUlp3OF81dlkyWHVmQ0xyNVg5R29GVXZkR1NLUkRqTzF2ZXA1cmtlcEptcmJNR3dwRi1R?oc=5", "source": "India Infoline", "published": "2026-09-28 05:42", "score": 0.103, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUdIB8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUQ?oc=5", "source": "simplywall.st", "published": "2026-09-28 05:37", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r", "link": "https://news.google.com/rss/articles/CBMiwgJBVV95cUxPQ3drbk9QbWRHcU9uVDJLU0EydWpPdVZRVE1rTEE5bFZadHZmUVJPeG9nUjVYWnVvSTkzNzFyNFo3TWhfN1lzX0ZScEVrSnZETUJ2MmtDaE1XYjc2TXo2a1p0UWZhcHprU1lwM3V3YUNUVzlTc3l4UXdCLVExX3dLQTdRaGh5Rk0xUDQtR2lkY3Mxd29QSHNPRU5fRDFYRVBSbC03X2pFaGpnWlJ6MFZDUGlicHlPUUpXeDh4ZU94UWR5ZHNCZ0pydDdFdHZNSjgyRThId0JfSlcxVzFibmR3clVwQzllekZnLUJ1LTdZcHpsRkt1YzN0b1FBT2FkZF9zblJkRlIxdmZfdzNFSXllSDM3b19zME9xaXhlWGk0Qjd5TWwxdDJaenFsOE5iOUNOU2VKRkxYazExZVAxYWJuVVVn0gHHAkFVX3lxTE1EMGdQdWlWbVp5aUpTbEJmb0M5dWQ5X0xJYmNpTFJJVERpUDZkcVo5V1ZGeTNyR3VmYjUyUDF0bG1HVlBGQ21nNDBfU1RZRTdYTEZFTy11OXExZmNOdzRwQTFQNlBRcFZ6NVdDSFFkeWdkV1ZGdm14cXpoTTc5eFc2WkZnVTQ1SlZ3NmxCOWk1b1BWU3doODZadUV0c0tkQ0VCeERINlczUmlYWmJ2MjNoblhPeWtqa0NvU3ZRcGw4NlQ3Mk5GcTFlZDIzQlN4SWxiNE5Md0ctQVBmMklselFGekszWTlFM2JFN244eVJtOHctcnFCc0RVM0Z4OUlqVmctZ25xTDVnTTV4djlfc2U3T2pkeC0tajA2ZnVKRDk3eEJ2ZkNWSmZicmVEOXN0UHpfRkJQdlZMLTVveENMYmdJenM0UFRfRQ?oc=5", "source": "The Times of India", "published": "2026-09-28 05:18", "score": -0.691, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeDRfUkctTnR5c0x3dEhXcmFSWWREQnhLUGMxbmFRT0RpWW1CbkVpN3dkcjJTSUZOd0ZpTjF2M3U5OW1vOEdHS3BKZG03d3BhenZtX21jTEh6VVc4ZC1oazJmSGJCZTBQTVZObmVYeEJFT2ZuaVd4OF9rbWNyUGo1T1ZMZFFtY1Zpd2dSYV94Yk5uS3FRVWFueWpYaTNyVjJVdnVoRzVFaGhvc1pOcmJOb1BWN2I1VXBTTnNNWURYZ18tRXFkZHR3Mks2TEk4X1lMb19NbVU1am5jd9IB4AFBVV95cUxNbVVHcVRveFpQaExzeVVnLXV2bTRTY0dTaTNSWDhoWEdCVkRCZjdZY0I2TElNdWxlb2RYVThZcXFFM1VDQVRxbmRETlVSTGJjX1R0MWpCQTFId3Iwb0hjUXF4bHhoNjNhZlBoeFptZHVHRWdwYTIxd0N4dmZtNHNFRXhvc0h4TVFXNl9ELUhkQ1VXS2FjV19NWWZpeGJTZmc4R0VWZldxNWVlOWlzVGRHX3cwaUd4UjVuMmlDVjlVelA5Umt3dVkwTDlhOEFSWGY5V1k0anMwOFNGbU5ZNmtZUg?oc=5", "source": "The Hindu", "published": "2026-09-28 05:11", "score": -0.852, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxObFRUUjZrRFpjTE1NcXBPb2NicXQtS3RtU0wtNHVjVHV4VHRlWWtMc1RtMzYwbXN2dnl3SVRBcjJxWFphN0hXMm0yZFNFNVduQ2dDdnVweVhTR24xNW5qemFXaTl2dkxsMkFYTlNCbGM1Si1IcmZIN3ZBTmF2ajBCcERjU1RPNXlIRHdlanZ1T0VxWWlWZkZ2eEYyZFBJWUJiSUp6b2gtcEtUQjJMaHNuWHNrRkNYek0tZlRITmkteDFreTNVb2VvcmhWZnJNa3FzTnZiUy1aXzVMMzg0cGNZR3pvMUFRQQ?oc=5", "source": "equitymaster.com", "published": "2026-09-28 04:56", "score": -0.477, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil", "link": "https://news.google.com/rss/articles/CBMi5AFBVV95cUxOMEwwTHh2ZHV6TVZtbjNDSEprS000QlNTUjh4X09yNWFTUmpHcW12aERXVXNSOUlSNWVrMlM1eG94ckljVXRpdDUzVHFtWUJ1M1p2TncyUDdBUWItZnppY0dSV2VZQjZiTDNLNzRBYVZnZUpIQzBPQk1BbjNEckUtdUxuU0oxMmRLYmw1cnhOV2FpUkMwNHhqazg4MGs0VTQySklGWTJwUGl5U09GS0t4alJNajVvc2lMdi1nMTJxQkNLeTg1OWUyYWlwbVJoR3F0b2NWU1pOVDFiOVhBZk9Nbk5TQUTSAecBQVVfeXFMTkhYdHl3d2FCU3RHT2JTZzJfcmhZbzNWWFZqMXFObDVBVHNsNnZsX29kak5jdG1BLUowT0REU2xTQWt0RmdoVVg5LXpzSEJobHl0U2hnNUJ6ZDU5MHlIaVVpTG1YeG5VQThDa05fTm1IczQwR3o2TjdQa2NEOVZ6dVZuU1lXN1dEN3dZWTV6ZkgxX0tYWXJNZXJLSU1nYXh2aGtrQTJJQUl1VnRJVGhjbmZpRmp5QnBjcThMTlJrbGFvb2tjUnkyT3B3MXo4VkdEdERQM3hKSmMwWWdoWk9uZGphb0M2a1Q4?oc=5", "source": "rediff.com", "published": "2026-09-28 04:51", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQeTNsTy1qVmtORm03dkJ0LVQwRUVQU3ZnT0RqMEI4NG5kVUxYeU0wcmp2N1hqaFVPdXhHNDV6cGRuZUcwclFTZ2NUV1NjdzQwYlhwWEMtcmFIVXZpMWxhWnpzOUFwaF9QUTVPQXVnTmZlUVVHNlNZQTVUOWxjdHZ6UHJuVDVtZkpPVWJqd1hlLXNlUVBEMmNuUFRCUFZZb25KNGpaNmJ4RjRuRDh5ZWFvS1JheXpLSzVQWkNSODVvaHh5ZUgyWjFPTTRnYlpxbUluek0xZHdaVU91cVRrYzFHWVJfRlJVemI0RW42Q19KSdIB9AFBVV95cUxPRWZEblJNRmlJNmdQMUpNa2FMYzNDRGZrTlp2RFh5MnZvSW5HMDhlVmNPODRlRkJTYkIySVFBWGZQLVh3Y1QzWXhValo3RkpjX0pidkhKQjJaTGFGOXhsZzBfeHBadVhGcjZKZXpuSkF1ZFB4RzVwVDIyeEtqamhHX09HR2FtY3ZRcGM3bzg5X25sU01NeW85LWQ0SG9pYjMzS2VfU0pncEJLc2QweG5wbFdZbEpDU3hvenI3V1BUU2FPclVvZGNCU1NEb0ZsZU9GdmQ3Smd6ZTZ3WTJtY3BTOElrdURuLVVsZFo3ZTVLalFBY0lD?oc=5", "source": "Hindustan Times", "published": "2026-09-28 04:45", "score": -0.361, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE stock slips below issue price of \u20b91,785; down 2% on Monday", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQSTM2eERXZ0NPUHpTR185VFYyNzFaR0lYZlMzeHB0Y2dGMjM4RlhXdWtnczBEblZtV2F3YVItUUpYbmhGTWI0YVpSdVlRejFmZUdyWmhLRUYzNFVCNkhsdWZoMlpTenVZSDBkVXNpY0Jwam9pTmtocUJhdzA1X1dyWTVJVWhVdzJZRWpiNzVFRzd1NUREdzd3bW1vQm4ydkVETWthRE1WVGpqUkZoSVZYbmtqdVNuWnhnM2ZaaHhORjRReXM50gHKAUFVX3lxTE9fUlRRS204UnpsenJGSWtxSnJiR19Dcmh2LXFMVWhQSzdDamQ4QlBSanluUDdfYUY5YkpXcURFZUZ3TU1TQVM1WFM3QnhoLWd0VFBXckt2R25razdOMEFvc0F1emhYVzIwZkY3OXc3Z2xJblJfTXo4SFZyekdPZDlHTDc5Ykp5VVlpaU9MblVhUlBhcW9Ta3h6SWpIeFZGOGs0bWh6NmNWT09yN3pjc0pzdXdqYlBjN25UajdLT3VvZEdNRlhxazh5ZWc?oc=5", "source": "Business Standard", "published": "2026-09-28 04:42", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOXdSQ1g3eFlqb0loV211WW1MSkhiWVlTNzBWd0M2a0ZFQUduVlI2bXk2eDBmYnBIZWlFeDRrbTh4TnNsM0hBSllPZTBHOTU2ZVZaQXhZOUFDczM2ZU1wdkZteFEyTXA1SFhGR1F5dGpDY3JGd0JyOEpnZEdmdWUzd3Fwczg0SzJyQ2tWaWxNSEJYSU5kdHpJbzlYQlAwWnd6bzBGaGpIS3Z3V3hlaVBWOU55X2Fyb3FLUE9DQ1pQcVlka1HSAcsBQVVfeXFMUGxERGozWEJnZFBKVXdKSTNKNUV1N2V0ODJPUEljV281NkFXYlpnWmtINFFlaUtfUDZwcUg5RHc5VlpRT3p3TlhzOHFKNkNIVXpfZi1SbXlTQV8xa25LU2FpTXJxNkRVNDJhQVRkWVFFaXFxQW1FcWVqUE1waDJKZDI1WDMtd05IQTlzdE9xNFFpdVRIRmJ3WGR5aS1Wb1Y5WWpMUTZmcWtqdnU1YnNPTUpTOHlvcmlPMkE0Ylp4Ql9idDVGcUxTZHRibnM?oc=5", "source": "NDTV", "published": "2026-09-28 04:41", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxQQl9VUVpCdDlvWEZ4OXE5V1pabEo4U0RPcVlBRXJuMVBQMzlWQ3Jidkxzc2drSUZPcEhOdG1jRmpqRXE3TDVIdEY5T3hCVXV4Ung2X19yRU1OcE8xUU1FZUwzR3ZTOVBCYWNvc1p1U0x3WF9kazVjV3h5Tk9PbElFSzN1V25BN0xDcU83cGZ1QVRTN2kwZWxjZW9VeFFZZTctcG5PWDdhbERNdzI4ZlZlLWJLYVdxUHZOQUJDWUc0MkbSAcABQVVfeXFMUEJfVVFaQnQ5b1hGeDlxOVdaWmxKOFNET3FZQUVybjFQUDM5VkNyYnZMc3Nna0lGT3BITnRtY0ZqakVxN0w1SHRGOU94QlV1eFJ4Nl9fckVNTnBPMVFNRWVMM0d2UzlQQmFjb3NadVNMd1hfZGs1Y1d4eU5PT2xJRUszdVduQTdMQ3FPN3BmdUFUUzdpMGVsY2VvVXhRWWU3LXBuT1g3YWxETXcyOGZWZS1iS2FXcVB2TkFCQ1lHNDJG?oc=5", "source": "newsdrum.in", "published": "2026-09-28 04:29", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb2JZRzNjNjBpV29mRkZobTRsNWJaVExQeWMxZmw0WjYzZnhCNktBQm5Hdmw0U3NrVGlrYm9abFZwRlZvendEZldPMlNlVGtqVFZ0ZC1rclZGci1yb3BjbVJ1YUlta1VYM3pBMl9kbXh1VjA4ZmtURl85S0Z4OTR0cDFyWXdkU1FiZ1JVdEZ4eVBPSUtJMk9RMnFJQUpxdjRiNmNHQzdmbnRwbGNjZUFJZkVXYV9yc3p3SlF2TDFkWk8tT3hnNkZPc1JTb3c1dkZ0MS12S09LWE9vaWV0SUhOOVpGUmRrZkJxbW9XQdIB8gFBVV95cUxNVVJKdDl3emc1ZEJXb2ROY3hadnZaaXlhZEtTZmZ1RjZFNFE1VVdJTnNxVFJFRWRlaTZaUGl3ckg2dzRfY2ZXTWxvS0dWVV9ibktOOGlsWjVmVDQ4YUN3aVlLaXA1anJ6YmdNRUM4UzRrZTJxWkE5UERZbmZJR2ZHQ3phMlg2bldoWDhBT2U4bVY4SnF2c1JiQkVHdXVVSGMwTVFJVG1GckhxdURSdkpMdUpfSUNQOWo5VjNxS3FEeGRNVzZiX0UzUVozR3JXMHduVzF0S2xnMVdhYVFaNEJmOHZvZGhfbkNmY2lMYlU2Y19wdw?oc=5", "source": "Livemint", "published": "2026-09-28 04:25", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?", "link": "https://news.google.com/rss/articles/CBMi7gFBVV95cUxNNDl1aHc2VHYtR3lHdGJnY2oxdXpXX0tNN29FU0dnYnZTX1hrRWFzOFBzSk5KTWc1RTFJOFdmT3VVMEFmOXNDcXhKbHdBMVUtR0kzclhZVDRLSDRHcnljSTF6UG40ak5SQmMtN2lzRG9QSkRNUzFidmRkSnc2aHRLanVnTURTNU9DcUZXU21kWVhoVUlacHhSa2lYT2tPMUJ6NUxkWjJ1V0xpYndCQU11S2djSjZ4aXpHdHpXRTZpRDlnZFZNNk9PU1hycldaa2w5Ylg1Ull2SXU2SlIwbDVrdG1RZUJaN1JpVjRUT0Jn0gHzAUFVX3lxTFBtcU5GS1BLNVRSQ1BWekxLUmhQaFFhMlZLV3RIcjk3M0RBVkpwU19mcmNLZ3I3UXQxdFY0WHBIMmw3SUtkeTdwN1RFa3RfbzB6bkNGSzJwZWtZN2dDS3E0a04zZEFid2pXVm9xejFDbUpLeG9hWGlfQ2p4NWZtakVWUmxLMEdteDBkVFFLLTlGWHVid2ZNYmh1cHdsS2R6UjFFUzlQNXdUX3VqSlRKY014bU1mcGlxZ2VGbGtxZWlDbHRZTnVZcm55NE5zaE1ra0lUVjlTNTZaQjhQbEJLOV9yWkxSSWwxZ2FacHBnaV85SzhfWQ?oc=5", "source": "India Today", "published": "2026-09-28 04:17", "score": -0.511, "label": "Negative"}, {"symbol": "MARKET", "title": "Mkt crash wipes off \u20b97.4 trn; Sensex down 1,180 pts intraday: 5 key factors", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNFNEZXdXeWxyUDZNNkJvYmhvM29nZ05JbUhkLWRmZ2VWME9TMFQyTWctZjhoeWVNQ3dGZ21NcmV2THVjUmt1TTBwTWNJTmVnRFVzVXlCekNMZnBqUDY5M3RWSWpQeVBYTXl4Zm1ndjhBcmZUV2ZVdHQ3VUFxQzN5c3NON3N3Zjh3UjZYSjR2VER1OXBWMkZOUExnTHF6OVBtTWxCM09ZVHhmdW9DZDZ2U2FxVEtGVHhIVlNsLWhkcnByMmdVaGl1OTFwQW5GZnZ1OVJvM9IB2gFBVV95cUxNWUItS2dqMFByNUlUcXdPMUdQSHZxX3VTYU1PcEdaWnFaOUo1MnhrQWQ4MTBmaWM2eDY5WURsaFpId1RnLVFJRTdadERxTDVKc0J0UkkwRDM4V0g2WDMtclZ4eEtxY3NCVTV5SV9tQnhEZUR2aHJ4N1Q3VzFLbF9Rb1ZadHN5Vk9tOEE3THlxQVViN0tfZnB1bl9aQU0xRjFZc1dqS3RKVWpLUVM3UkV4aUYzOVNaMDlBbEM3bS0ydnltemJ4TEFOZWt4OHNOcnNNdG5DaE5GVVRHUQ?oc=5", "source": "Business Standard", "published": "2026-09-28 04:11", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l", "link": "https://news.google.com/rss/articles/CBMilgJBVV95cUxQZi1NX0ZnR1pnWl9lLURWQW9uazJudU5adU43UVVWdG9BV1A5WTZaN2RPZ3NSWHl5bTlCZlA4ODkzcDRoc3JWVEtyRk1NbGx4MDQ5X3NGZ2ZHVW9MWnFTV0F4U3ZSWVA5S3BtbzdtZFRLT2JVOXJjZjUtNENidWtZai1JaTJPc0VQVE9mdDE2VGhBNXByZnZ3ZEtVdm5ZRkFvUXd4UGdfZjJTcFFRcHkwcmo3d0p0Vy0yZXNkV3RXV3ZFcTRLTlBUNGRrNXNGMGVpUXFKMDJzUndJWXpqWnpGSkFIRVJ4Q0MzQUJVOHMwT0Z6X3R3aHZ0YzU3TmN1RDZVQmNzWWNZbkF1YVJ3YlV2Tndac1N3Z9IBmwJBVV95cUxQcExWMGJPZG5EOW5QWXdrOGFGVWpSNnA2bjNYYnlRbGdhSG13ei1YYXExbjZPZlkweGtvRDJ4QmtZcFNJbmthU2xJNWxnV3hVYjh4SDRzU2k1cTQwcG9BS0VCOTlQcUpuS3FzREFhbXRIWVVYQVZRZEdHSE9HUVRWYTAtUFFWX2M1RmZXVXhKUzd5RmtuWjBhTi1wSXZfVXBWWHRCOTV3VGFRQ1NKeXQ1WU54dlBQZmpteFlFa3JrYlRkYnRoUWJsMVJZM1RlMnFWVVZGRmNUWExEUzZJUHRCcGpmMl8xU0Y3QmRBMTdESW85NTA3LVRGODFGakpiY2lIUlV2bVJLMWhaUVNqRl9HMmhsSEU0VFNGa3lR?oc=5", "source": "The Economic Times", "published": "2026-09-28 04:08", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi-gFBVV95cUxNd3FFLUl4RkRuRktMczNpNmU5VmotaWdaUENGMWExNHZJOERsVFNMQ2ZiX0tDSGFXYXhxSjVUM2p4QWUzZThrTkxDNXR6ZndFMXU2NEFTNG90Wm1JVnZpNDdaRU1vSnJOUno4VGN6dDhndTdDWDhhbGVjQ25nSDBWOXFGa2xUWlEtRDQ0dVNCZ0I2TWdQcmlZWkxLcllVUXBpa1NpdjItdDBhZlNLYUU5bWhwREZoSWV2dEMxMWJMNUZza0FpQ2dKM0JSdU9fajZEdmQzOXFnZUxqd09wcW9qd1V0alZ1TGtFYWs5d1k4eGc2NVZvbXFONkNB0gH_AUFVX3lxTE5yLU5FWTlXQmdqRWY5MS1MYXRPVHV3bjNkZWlEa25SVC1INTV0QjQzOXBxVzhFbEUxME1WbU9jbTZISE1fa19JS1dwRW9KOVplQ1A4QkNWWlE2YjM5NlBCNndyN2F4T2VfVmlOVnhEQzMtSENPZ2N2clVGNTdtVnQ4SU1idWI3eThwenZWRUZ4NzNwaHJvTllHUlBpYnQ4SEEtZFlRTmJuT3dGU2ZpRTdMLUFraWlfNjl5UWFZLTBlX2VMSTdXdWV6cXNOaGFzRU5QSjBOcHBPT081Z2R1d1JWQUt5TXFieXRCbGFLcGRkWVI4OG9oRk1YQXJuQmdrRQ?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 04:07", "score": -0.44, "label": "Negative"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines ESOP 2019 Share Allotment Explained", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxPUWZWQWFhUXl0MHliZTNDMXZuOTFtUXB4UTgxU1hJTlotLVRrSjdSMXBGWU9vaXk4ZC1vaTVzbTJMb3djcjZfZi1xYkR4clBmdE42NC05V1BWbmxfZTRXN3pDS1pKNmF0UWJ5dlE0Ry1qczcwdUQ2VHM3V0hzQ196M0ZxeVBuMkNXUXR6X01mVm9HNWgtVW5XamJNcVlTdW5MVklzZlRWdFM1MG1VNDdJbFZLcUkzVENpVVRrWkk5NTJJWG5hbWtCWmJmWTNtUDB0VWhEV0xnZEExUWxxOVhjejZ2b3BwRFk4QlE?oc=5", "source": "Kalkine India", "published": "2026-09-28 04:01", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 \u2014 Five Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNWmNXeUhrY0hPcXlaYnhxdEpqRTBKbWJadHhpVGFOX21Oc1FnTVM1UDNDOWZ3dU1jd2RjNTA5VTV1SnJHM1YyNC02dGlZYnhzeDZramF1NGpBTm0xcV9DS2ZIVURQSjlrT0M2bTJfY19qc0VmRHRBdWdZdXBmcC1pUHQzSzF4OThzSzFDV2sxbVVUQnBCWjhoemhmSEhyc01oeWJJeGlSbXlaX0xiUl9qXzdBaWhHSUt3eUdKMTh3djNuZlg3dVlqYUNjMkhpX0RoazhISVpBTnJFbmFVVGtZaFlKdGY3Rzd2SkxUTtIB9AFBVV95cUxOLV9xeHRCVnRiX1FUSENXSHZ3S3NqQkRRZFA4MzZPYkd6WENNM0NZQVpMU0FQUUJnWkVROVNSbTFrMkdJaHltbkUwTExjby0wVzViS0NkSVI1NDNORG5wNkFtSXBwMlRNbXhQbllkYnE3cGpVeVF2a1RrQTJqNG5oSnVsS2pyc0dUVEtlNnM3eHJ3bmJwbXBxZC1FSG1MbnRENzNmUFluMzJwMlJzelA3M3R5Y2V6SXZreFpGYTlZWXlITE5xS0NMdDZ3M244U0NUdWQ0R1N0TWE1bEJLM0hJYzlmYWJjcWJUUHhMVUZDZlJpMExI?oc=5", "source": "NDTV Profit", "published": "2026-09-28 03:58", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxNdFJQdUVBNmhGOF9naWYwc1VCWWozTGVwOWl1b082TGI2bmppQVQ5dmxfUWo0RGhBQ29IU29vaUJ1cDZCNEJoelpMc2g0eGhldHVGdy1WeWcxVEtZcDBDNDlfRkxNZnRFMURFLUVfY1U2UG1YTk1vampZZUozYjEzU3JGbDRWNkhhVU5qVy1qcVlhdWxFa2YzX19vSjZ4NEl0dk1reVhEMXlPb1RTTzdkNENIS2RraEdzTTlBXzFteWpPMkpkUk9MdEJqaG91ZTlUSll2UEVwcjNoM0FDdFJQVUJCM0JLQTZzS0xTVkNJQ3VIYUVyV2czYWxBLXRUNzlPUkwtTHFTNUs0cGE3VWdj0gGUAkFVX3lxTE55LTJyNkZRSldBTGdKNnM1THNXOEtPQ3FZaXdOWmhNMEVtby05Y0xaZV9QSlFuNDg3TFlfZlNpb1Z1eTI1S1ZaZDJVeGwxcktWMW9pbWxRZk83ZE1scnkxWGlVOGhDQUJJNWtnTS1MWV9BcDdKRmYybmZSVEJydVdzS1dTVGdvM0c0R09GdUEzd3Zfb3pmMXdSMGUwTk5uZ0xTTlRmV2NZWTV1M0FjWmlQZ1k3aW0wZE52QmlpeTI4bzFHTEtnbjRRZWtzb1NrTnE5dU1XX1ZQV2cxazdKZlRCNmZ6UkNSaVNnVGZVZVV4R21xZ2ZfOVBzcGZ2N3l2RkI3aGpqNnNJWjdTNnFwYnNQNEt0bw?oc=5", "source": "The Times of India", "published": "2026-09-28 03:54", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxNZ0dpRTVlRDlxc1RtOW81dTVmTTREN3MwakViZzNUakNFTDJkWkt2QkstemktQmhGZHBFWjRZYXhHcVZDcU83WWpLeXpBUDZyVzBINUVFalBwaDZ4YUhwOEdXN1E4TmVTX1ExY1U2MV83T25QZFhsa1NVcDRlWmtYSHlXdWFMTEIwcVdoS2tRWWZ6V2NIVFZMMHloczRjb0JvNHhmamx0SDEzZUxtLUJDeVgtWTNTWm50SktyR01HV0d1cXI2MmU1UWNseGFDRTVLbGx6b196aE5BMzJYV2lLYkEtZW9fcTRONVHSAe8BQVVfeXFMTVh3alpWbmYySWstWjFjN3NmVG5Sb1kyV0ZjSkYtc3MxN19pMDA3VkJwRGh0Z1FYZEU4X3BTVWkwRjlLdGQzTW9DMm5Nb05oel9SdVZrYmxRT2VIZk1nblpwMUZlWDR5ZlVnY25oU3BwaHVybk5ibEt1VXk5dS00QlBqV2ZLY01WWXN2TWNvWnc3YzRfNXBTVTJtR0w4MHRlNHBWbmcwS2tpWEkyRnlvRFFHSUtsdXdZZ010MVFsSXBEcEwyNTlNM3daV2l3Q2s2ZGVERFJNNGg5NE1iZzNJRnloY3FVYU1BRWUyaWNsRlE?oc=5", "source": "Hindustan Times", "published": "2026-09-28 03:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQU1VkYW85T1l4Mzh4SDJFZDBhZC1GczBiSUw3TmdJYUxvTW1TRXpUd3BTOVZwY1FzODlGUkxyNFlXSklFNzBRWUZ4WEpGdUZDWWRIZ21vM05wMHBnQ2N3UTk1VENDZTVYeHJsSEIwUG15RmpnRi0yOUdBaFRTdFg4Rkp6LXBSbzVmQjRQU0V1NXdCdVRmby13QXZqb2Zzb25Fd0FsR18yZW0yZlZBd1VibQ?oc=5", "source": "HDFC Sky", "published": "2026-09-28 03:28", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxNQmUtcnhXbVNOQ0lacFk2Z1JXa0JON1VtZTRsYnZVMDlKdjh0dXhobk9tajVtRVdUbE5RV2MxUy1MbUpkNkc4UXNvalZoZXltbUNScGEyanBReERmbTRuQnB2d2M2dkU3NkJ0anMybXdHWV9QWElRVG9WcDhNSzE4eTV4VWs4WWluaGpYR1NZZTNuYVFPNWZwUk1YcXNOR0NrN0REb2V5eENFRjFaTVNpeWtJdw?oc=5", "source": "Reuters", "published": "2026-09-28 02:19", "score": -0.542, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices \u2014 Five Key Factors For Sensex, Nifty 50 On September 28", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQYTlhOERzdTdrb3FJNkRCaFpyd3p3dGE0QjFQNW5ndE9qQ0VTM3gwOURRS3hlYkxQOXh5UnUzYlVfMmxYZmtkcHVpZUpZZnhsNy05RWRKWi1FdHR2ZWVIa2F3MmxBTjBCeC1rNDBQQzhSYkVKSGdyV2pxa21xcnd3dk82Z2JOU3FMV3pKNzcyQjFreUdPZDlaNWh5WGVLUE1OSzV1VE9Qc3k1el9pOFdKYzBKVEMyRmZRMU9icTFpZTdQOFB5UEFCLXEybjl4MFFJam9tMFV4aXV5cjQ5bWR1Mnh3SUdXYzhtVUk5VU1uQWlMTHFwdlhr0gH_AUFVX3lxTE9yT1pHVWp1N19wOTVOLWdVWEloQV9BS0lKeDhwaWcwTGNqSnpxUVFIRkg3Y05tRUc4MUNDOF9CVm1EZjYzdnlsX0UwVkRDaEVKQ1ZNcVJteXhQQnpjR2JsMGh0QkhNcmt2eUxOdlRxTjVaMlFZWGtVSkU3Z2xfU1BLNjRrYzZ5eFE2V202Y2RKaVV4LXdqb2FNZHVDYlM5WmFyNWVSWnRKVDNab2h5VUhBaDlmbUVJWFNiOU9qYUNrVTJybWpyZkY3OHBiRUl0MTNBRjBNQ0lfYjljbkFCUE5oS3hDaEVILXd1TDNDRFVaOVR0enZ3VzBZZkJzQktabw?oc=5", "source": "NDTV Profit", "published": "2026-09-28 01:58", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOd3lLLTBUWlJpdVVESnptNXpwZnVmVk5zbTU4LWV3eTZyT1R0MzRfVFpFYzltdWhnSTI5Uko3M2dpSzY0NGJwZzFfbzZXM0ZOcV96T2hHaWQxR284Vi10dHRxeUVCQUJrV1lCclJZREI0NlpSdHp4Q0R2V1paVFlVWllhWkVCQWdaTlhiUjN4bENkS25yU0tJczFLVE9vUE1rY2hvc1FTSl9QZ1RkX1Q5ZVNfLUx2LWpmN2lQQ1pNMDNUS3NJenhycjRsNUNjbnZRMFNZNllsUU9WeU1xTk43NUY3OThtVFJadFJUSWhuNnZEMUh4VGdicDdNdFI5QkV4U20wY9IBigJBVV95cUxNVE84MHlqVDk1czZmeWtPckg1UUh1bF9OQU44MFlsSkdUeU14X2xZYXozODFYb0JtaGMwSDFVNzRpczZZb0MtY29aYTBsdl9fRFgzQkhhNG5Id2hYcE55WjhMYUU5N1hWRjg1RjJ6NGpuVmIyaURHQnI5d1RsVUxxRWZ2M0Q4NjlLQ1ZENVdyLWtSUkNrZG9MbVBwTnVENFc1UndfTzhlby1NdktITDZBbldMMlZua0xGbnVRTUFucy1GYVRaZUpPbEN4VlhTTGFlbElpVXBiZnNPeWpqQzVjbHhwYnFXUHBzWUM5WU1UVmh4ajlKbHpDRHdBR1F1bWNhNEhfZk1DNGRWZw?oc=5", "source": "Livemint", "published": "2026-09-28 01:20", "score": 0.842, "label": "Positive"}, {"symbol": "E2E", "title": "Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxORnluOHJzdFp4bmJaUl9hdWY5Ql9WeFd4cnF2ZnVZdkRIbGpTWlRzSlBxX1lBb3VEcFVTclJjQ0lVVkFKcGZTUFhLVDlDVkJkZDRnY3VQQkdlWFFOS2M1VVNNa1B1dmpueVBIRFNyRGhKVmRpd0IyV3NmTHNrdTZpZ3BKN3lSMjFnbGNyYnFtelZWWXgxWF9KYW5WSkoyQnA1R0dqTHBscWRHVVg2eDhveGtabHVVUjNoNTJCYjlsbGh4Mjk5cjgySUcwano1THJpbUY0X0swTG1POTA4a0ZSOEZFMVFJakg4RjI4aENIaVdZWWpSNWU5QnVDYkJyeTZlMXc?oc=5", "source": "equitymaster.com", "published": "2026-09-28 00:30", "score": 0.557, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxQNmdxX3hPMzJrejF0R0pvaUNBbDFacW44MXRuLXZ1bF9yVnlwTXFwWGlOZUh0U19XOTJhYkZ1cHJ6VkJSMkk0QVAzcENpdkNJWVRWMDhkYXJ0NUdxRjVnaVhiS2VPWExCMWdaQlBmVzQ4a0lhNlNjNnV5Nk9xcV9zOWMyc24wTFdBY3lCbFdQdXlsaWFNdnVxblZYWVhBcm5wQW11NzdmV01JeVBsQV93eXJuU0ZaTmM?oc=5", "source": "scanx.trade", "published": "2026-09-27 17:20", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Ahead of Market: 10 things that will decide stock market action on Monday", "link": "https://news.google.com/rss/articles/CBMi3wFBVV95cUxOOHlGS3FhbzhQTUM5VG9rOXZjZXBTZ2Q2X1VJWjVOZXVEM1hET3BtSktCcmlhLXpIX3JUeWtBWlRNX1l4dWk0aGJiNFRuRVlzaDhfVUpzeF9jNzNUT0VpcFVSZWlGNkR5Mm5qeEU4ODR1RUpZcldoc2t3TkFweE8xLTF2YTROOGpkZ3lkWGRFQkpaY0xTRFB1akhkbG01QjZ1eXVBWlpjZHdnMGR2a0ZNODZuQWZ2cThKTG5nb3V1WUxxS3BCRHllVkhKM1hQTWVpQzd2WFU2b2x5TEdYcG5N0gHkAUFVX3lxTE9uUFVOSFVOazh5cm5jb1RDcVU5YzMwUjBJTV9yR1JmeHhaeTB1WmNIUS1faENuVTFJZEVxSEpheGpGcGMycjEwenhnekROSnR5OVI5V1l0TkJsTHp0V0g3MkF1TzNpMmZCUm54dXFiS3lJVWhGTkRnMklIT1pucDc1U0hrSkFoN1dkci1UM1UwVDdoNXNiZFNPWU9iUk1kSTV0RFBTTVl1UkJxc0t4OUIzcXRWWUJMbXcyZF9zZXp0c0ZEcUdBeXFKTFdxbzJWSzl6ZUFZTHI1aDZtdWFOOWhBbUQzbQ?oc=5", "source": "The Economic Times", "published": "2026-09-27 11:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show \u2014 3 reasons", "link": "https://news.google.com/rss/articles/CBMilAJBVV95cUxNekdIczJ6NEZleldrYUtRZ0pEMFlMaHFDcWdFeVVhVnJROWRBWTVFeURzYXM3NVY2eTUtZmNMOVg2VVF6eUZOZFpzcTd5S2ZqUmVJYkRaYnd2RF8xZjlDakRzUWFvaTlVb2REeWo4WUF2aTIxZUVncDVzY2o0Tmp3bVR5TmpRQmFSMDZzSTB1MFBCSWh5RmJ2b1d5QTNDdHlSN1hVcEJqUHdlOHZ3VENMVm8yWDMwV3N2M0phaDNFZzZGdE41OWVxbkdjU0tDNnFnTnM5Y2phV1pIYWN1RF9DNDhtd2JBd0I4WHRlMGFvZUtHdXNlWHJVYnN6eTFwVjVhODVsYW04ck9LRnJhb3NzT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>jEzVnfSAZoCQVVfeXFMUEV5VVRyZjl4LW9fV21rY0Y1SkJyYmluZTZHZlpld0cyakhLcHhKTXBNR1kwU0RET0VZeW1Ea2liT2JzSkNGenlOSzlkdVZwejU2X2FJVHFOUHZwRnM5YjRGUzJDM0VaMVlVR2M3N3FwZW83b3pBcnRwQjFTSy1UVVpDUWEwYTVDSmF0eExBWkdOQml5Zkp5aWtqU0hqNlloT2V0XzRPVml6dXV2WW5MVXlSMXZFYkQwMGNqZTBXNjBWTFVkd3pUblpDdHZ2RjlXRGlreDhvWXNnMV9KVGFySDFFNFBzUkpZUEh3OVFRVmFfSU1oU3V2bV9Pdm5hR21UWXBLYW9TUElFRExLRGdPTmJXQ2tSMjlFRV93?oc=5", "source": "Livemint", "published": "2026-09-27 09:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOT3N4b21hRzhJSXdJVzFVNWRNQ3RqT2l3aXFBN2RjN1JDX1Y2V2U5MXlDN2l1a1BGQ1hLcWktbEgwYU1UMUEtalJDYkc5RDZqX0FHdFVuMmpDVDhHdkhWSDVpMFpXLXpoa0ZTWDdGcTBxU1hJSUtIQzgwUXZvQTRPdUh6UnlXYUkxZTZHTmJFSnFQcVFSc0s4V2tGNUUwUTJVZktuRkUwY1c5eTI2NjA5VEgwMDExekhFYVhLRW4wRlduOU1wZ2JqV1F1emdiLVUwWHZwa3BmOXV3MmtLOVpzWlZOOXJ3b1MxY2pvR3VYRlFjYkxmNFdIWGFxNTJJYVVvcWhJRVVwb01UbU3SAZACQVVfeXFMUDJ0a2tkZUxvVXFoM0VZMW5YYm13NlNjNl9KY2l6X2NkS0VvMGw5eGhyWDRzU2ZsTlJmTVdTbmZ0Vzhqc1YyNGU2TWV2a0FLLU1vQmRRVktFOXhtcDRwVVVMbXZPNmo4Q0V4ZkNCU1M3TEZ3RzZwcVp6SlhoczYwY3NYNVN1c1BKSTJLYXBRbVh0bDN1ZWc4VnZNb1VZZERDOFlSXzFwNW1RX0d4LVVGRHUta0Q0cVR5dndQUGNYaTkxWFU4ZVloTzNfR01UMDJ5aVB2R0ptYjU5Q0RLRnBEZExqdEZJV1BDMHRiRTBBa19fa0djbno1blZZM1ZwUWx2VWREaHpQeS0yVFQtRFpQc2s?oc=5", "source": "Livemint", "published": "2026-09-27 04:22", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks To Own In September 2026", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWmN1VW9wZjRBZl96MHMzNnRmeS0tY28xWWZtR0hfa19FN2lyVjdtZUc0a0U3c1ZYNmZ3eTNiWFVIRElaRGV4VDFVYi1kYlN3ZjNNemNjVzFwWV9CQmxlR1B3X2kwVmphZGhMazZCVTE1a3E4clpQbU9GLVNXTWs5MjdNaldOQVBOOVpMWnNMUXA4VEtmc0drX3RWWk01aXVvd2xJS2JYeGppOElvRTFWbEJwdEJoYlBVaXFhTUNhMG14Y1FnSWROVk1qb241Sk1vOW1MWGJ3dXpuZ9IB3wFBVV95cUxPSXhqMzhnOGFvNkRfakZ0cUxHVkcycHlESmtYb2N6Vzc0MGVlSnNhLXUzOElWb1YwclgwRmY5MFhreTM0TkpzdjVjR3d1Qmd0Y1ZmRi1KM1dLeTU4QjRjOUdTNzlRNUR2b3FvaVNTbW5adHhMQk54YTR3YlRLclVfUmxKZmhRXzc4VG9PUVg4RFU5UWFOWmsyYWZHaFM4N1pxTHVLX3RVTVUwSzRtQzhCenRfa1REbS1CeXQ1Rm1GUXhvV3BxRndHZHRGVEV3VHM0S0Vidjk5bm1SSHJiVTFB?oc=5", "source": "simplywall.st", "published": "2026-09-26 22:56", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "\ud83d\udea6 Indian Markets Stuck In A Jam! But who's responsible for the traffic? \ud83e\udd14 A Bernstein note argues that India\u2019s large caps are stuck in a bygone economic era. But here's the BIG question: \ud83c\uddee\ud83c\uddf3 Is The Market\u2019s Fate Really In India\u2019s Hands? \ud83c\udf0d Or are global cues pul", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxORUdYckd5Y2pPQUg1MHZTaHlTT1ZXWTdmTGxwSWlMcE9NQm1vNE15dk9qS25VanFnTzk3c0FHTEpwaGcxXzhmekh2dUNLM2s5Zy1USHBjMHRfakhvYndNanZrV19NZVFMY1hjOHZsektLSVZoS2tTNkdzMEJTeExiS3ZVbDVRWTNWVjZ3MWVmSzhnZDVvT2d2YnEwZGJLRUp3QXhxTDVfSUc5TTdvTXIw?oc=5", "source": "LinkedIn", "published": "2026-09-26 13:51", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market News: Nifty 50 Outlook &amp; Prediction", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVJvTS1CRXVsT2ZzNUhBV0piRVV1UnZTeDVEcDJmRElmWHB5WkZsM2s5YzlYaXJuVU9vVjQ2dE5XVk93WTVVLUx2d19wRm9lc2YzWW9xX0F1YWJCTUJtMURwVzRxbC1vUlNDWEpLRUZibzdnbVdjdEJUeThfeHZLSXpwTktCQnlMM0tTNUhwWmplMHJKb2ptYmVn?oc=5", "source": "Liquide Blog", "published": "2026-09-26 12:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxPbm8wM0RSWWRXc1Bzc3daeEpaNnFwZW55Y1FBT19TQUdxYXdrZ2FJeDJGd1EwQk9BbFJTZ2xKNV9Gd1BadEFlZExtZWlxdUZEZHh1RkRIU1lMNEJVR3hkZ2VKWnNGWUVLa1Fha29hcWcyNVR6dEdydjluNGxlN1YybHFabnUzRWdzMTFSWThkNWRRX0NXQ055dWl2dXN3cGw2RUJxSHAyTTFWMnNOeXZ4S0xGQXFjRmhub1lHeVQyRUhUdEpFSGEwM2U1MEFnbExtV1JPRUVNRmV2dUNfZ1BiblROc2IzLVNPclpNRtIB-gFBVV95cUxOT2FRblV0ZG5vNUh2QTZGeldJa2FuRF8xSmRWYUQ4a1NLblFyUmtJNTRCdHB3NENTZUZhdi1Ha1g4aTV6cy1POUl0Njl3bzZNdE1ZRk43bWQwRXZvNGxncTdBaWg3cDNUMHcyRVp3d2ZKRmljNXZwQktjUTZnV3NpWldYMmNoV0ZJSjZONVJjNEQ3d2ZLWXlVREFsd1VFbFdob0xydFJ5dHpFdGIzeERrQU5kcXBubmVLd2RZODE2Skd0Yk92bFNnWG1qUjNnZWRSR2YwaWIxLU91ZHBzTlJVb0twSW5pUnYxb3E1WEJFTWdmQ0tzeVhaZjRR?oc=5", "source": "The New Indian Express", "published": "2026-09-26 09:15", "score": -0.128, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQWm9DM0I5TUU2aWVIdHhCam9zXzFSUEI0RzhWaEFxWDFfbDFoeUFJUEZQbHk2OXJJdlpjeVBTVjd0RDdMSjdPMjl0eTN3NXZnRmR5bTM1Qi1KS3JsNFRrZlFCcmViSW5MTmdQdDItWTU4T3lUeFFkTEU5VHBEV2FmUjlqOWdvaDhNcGZlTk9jTjJQeVZ1Zkc4Q09fUGY4LVZiWk51d2U0ZGtxRFZ4cXpMV1V1UlJOdFN3RnZyTA?oc=5", "source": "Kalkine India", "published": "2026-09-26 06:30", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure \u0915\u0947 \u0936\u0947\u092f\u0930 \u092e\u0947\u0902 7% \u0915\u0940 \u092c\u0922\u093c\u0924; \u0915\u0902\u092a\u0928\u0940 \u0915\u094b \u092a\u093e\u0935\u0930 \u0915\u0947\u092c\u0932\u094d\u0938 \u0915\u0947 \u0932\u093f\u090f \u20b993 \u0915\u0930\u094b\u0921\u093c \u0915\u093e EPC \u0911\u0930\u094d\u0921\u0930 \u092e\u093f\u0932\u0928\u0947 \u0915\u0947 \u092c\u093e\u0926\u0964", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPVXU1bkFLVlVQVmhKWjdoVDlSNFQxTTlheVZFdGtDeEVEVzVtc3Y5Qk45R1RaOV93WlZrOXF3MzFKTlE5OGR1Xy1DcnFtUTV6YTYxYXlVMHlTWXFEbnlMaFliTC1uYTZOeVhCY2ZjQW5Qd0pzcEZWUmx5NHJHZ18tSDNHbTZrT29hbFNrWXFuQzFRTW5OQ3BMRERrUldoQUVMYmRTeTBfZEctVi1DUzF1bHphN2JnNV9lbWx3MGU5MlZRbHdZYnNrR1NHUVJVekRybmZtcWNFNGQ?oc=5", "source": "Alice Blue", "published": "2026-09-26 00:50", "score": 0.34, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxOTXpFTDNOdlg4R1lYS1FPU2VpM05pUUVGSHBvdWxqLXJ4SFpPTXZ6Q25FVjh0V1lvbnR3ODJsa1Q0ZDJlbWpRZFFiSmw2MUhwVF9lUVVyVWJTQ3lTMkJHNmtHMFNOMmwyRng2TlFUVlM0WGhOdU9KaTh4QWZ4bm81SUlqcEN0dm5FRHZVQ09UdTBIVWxZajM4alAwcjRrUURkMHFPSnNWVndUNjhjcjVUb0ROQVZJTFBCMmU1bFUyNUl5c0YzZDQ0bmVSNXB3Nm9pNUhnaW9RdEJYMU9WZkVqS3FHdGRaTnPSAewBQVVfeXFMTm9mRGRDb0NZSlU0UTM4c19nUEJhMERMSFc2ZlY4Ul96bUdPUFBlSEZQZ3c0NnFXX250RkQybjhjQkxoSVc2OGNlTnNoOWcweUdOVjlzdS1sZjZvUkM1T3FKWkxTSFczOHVHQ3pMbWlJbGxDX2Itd29DZU5iTzF1ZGlpSEk2dkNaZE0tNXA0Sms5SDdsZ3VuNjhQTGxYc0lYemowWmJzbFE2VUJjb0drM1NYNktGWTBieGFoOFJEbU05ekZtODl1UGsyM1UxbF9idTdCRlppbW05c1RYZXhVaFd3eXc0NU5PN3RGeWM?oc=5", "source": "simplywall.st", "published": "2026-09-25 14:34", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "PERSISTENT Stock Price and Chart \u2014 NSE:PERSISTENT", "link": "https://news.google.com/rss/articles/CBMiYEFVX3lxTE01VG4tR1ZHRnF6bF9CZzh6bHlySkh2MFd6bGJKUVhycUhNQkh2R2syeXEzOG9tLVpSTmNrcUEtOUVWZm45QUE1ZTB1VXFYSEc0LUI0akZJc3NQTDE5SHh0cg?oc=5", "source": "TradingView", "published": "2026-09-25 14:31", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "R R Kabel board approves proposal to acquire U M Cables\u2019 optical fibre cable business; shares rally 72% YTD", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcGpkYXl6WDhuYWFNMkVobGFYaHROYTR3R2NJcWhMcmptMEpqS09jeVBMRFNsQjkxSE9QVWVZQUVXeUFweWdVeEVTNzUycGFHMmxkekJSR2F2OFl0LV9CYUg3M0VvVnJEaUlEUFNrT2RqVkpNY21PeW53SThRUzMzSzhqYm93VkNPWjVSWUJUYnFicTdONEVQY1NwdTlqTTlSbWhxUGlZMEN5aUpyWjN5aUgxckhCampqdzhoQTYtZEpkSGljNWhhVUJoM2dqNUhSMGc?oc=5", "source": "Upstox", "published": "2026-09-25 14:04", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "India shares log longest weekly losing run since 2020 as oil prices bite", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRDlIOXFjNzhyRGVteU5DNTJCdVlRNUZEY3VObFdZNDI1MDU2SUo0NEM1N1JDTHpDMTk0YU9OM2V1eXRla1VaanBsTTlUM1lWR3VYU0g1eG5pM21hNzFWQTdabWphemRRMlc1U09MdWxVRVNLUWxjd3pIODVuY2UtcFE0dEhPTUM2MU1pbHNOQ1NnOUQtME1TTDJjSzJzOGljZTRmN0NBZ2Q0S1VodGZaSXFxZU1VTGNnanc3a0o0anM?oc=5", "source": "Reuters", "published": "2026-09-25 12:52", "score": -0.382, "label": "Negative"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxQbV84TnZBcDlZcGRjQ2YxN1Z3eC1lNHdhNTN1ZENIRnZsR21zVVQyQUFmNnpKbmQ1VWl6SEpGNi1XX01ZcXZuM09QZklRNUh3YTZwd1RJNDRpM01BRUJfS0VJSXRGVy12UllLVU5jZnd4UWMyQjlkZHJPRGsxX2RQZnY2c3RRRE0?oc=5", "source": "Univest", "published": "2026-09-25 12:22", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Two years ago Sensex hit lifetime high: What went wrong after that &amp; what\u2019s the road ahead?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPNjg3MGJpYWo0SHZZNlZLX09hOHJTTU1CZm9FYzZTejdsbWl1bmZfY2t4SVEyNTFLM01ZcVZueHJhZlVtRC1zdWo5ZXZaRkhWOUtJc193NnZOZVhXUDcxcWpzcXQ0eHlmdG1TWEQ1R3NfaElGZjc3eldBcmtIbmphT3F4VFZoMWFwOFZQZ1ctWjAzRlZNTlZOOVVrVFVGcVJkSHo2WVBleXNYWi1VU3VaMk1teVJnVGgtN3BKdXY4U1cwTXYyUXJ6Q21YWmhZbTI5QkdCUG5xaDdyUVFvMi13SGVteFl5a2lSNUhYSTN1ZFo2Vkk1X2lURTB4QXpmc253Zmc?oc=5", "source": "The Times of India", "published": "2026-09-25 11:56", "score": -0.44, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel enters optical fibre cable segment with \u20b977 crore U M Cables acquisition", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVHNrRVg1VDRadktqWU9TVnUtdlV0UGx2YVN1Wk9maFBKZkl6NXN1dEhmSGxFNVVaejRWQy05czFfT2twSjJxX1lDR2x5QTZycklWVWJBTDNGZ2lWYWFGYUN2dHUtRnEwUGxsVmw5UmhRandzdHdDUHZMUGZNbnhsUVdmbWJ5VTZ1NnlDdTM4UVJJNWlDU3QxRDJfeUZyMWF1Rl9fWmUyWmdyUHZpVXNRT0lkVjVUaHZpX25Na0RVa1lHRFh1ZFlQOUlhVUFJbmVLamVsdHZHVkt6bWJrRXY5UdIB5gFBVV95cUxONTd5ZUl2WG5FUzRqVGsyNGNWcHpEN0ItSkJvV2wweHhrVENsb1NFa3ppbm92bUFGdERMZWlva1YyMEl0dDYxcXg3clQwZ0xKRk1OY0c0cjZOYWFmamVwdnNsTm51TTIwV2lhNnFNX1pfS29Od0xQZXpWNWdFd1k5Y1Fmc2ZKRWJtRGlJUDdBM3NUS0RSMWJtdDlVaGM0NzVuZFZvTktxelNrd29GOFo2SjU5ZU1HR2VWUHZaUTBVa0l3TjZVOGZaWDZUTzRTSW52VnIyNThJb3p6b3lPU3RualRINlVGZw?oc=5", "source": "CNBC TV18", "published": "2026-09-25 11:42", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPMGh4UXhKOTVzdW1BeE5LNGFFR2Jwbzd3T3ZvV0NTYU4wekJVZmE1U0FuZ3FsTXlTakZ1Y09lZTFJRXVIOVl2Z1R2ZmJsUUFHaEZXREJUZEtCdFNjWjRKWHhZWDNBMGpMOTJnZHhIa3ZLdHpvQ0tmMEdOTy1BN1hBcm5WcFZpYUdVZmdXZkVFYUkwdnA1VFhQWlNDc2xGNzY1eGlPdjhvZGR2MlRYbnVoTVFjakVVeTd5SWxEbnc2RjlxcHdkcTRYb2tDaXhocjVD0gHTAUFVX3lxTFBiSHlyQWowSl9jdW9fNEZsWnBKV0VjVkFTcV9kNkNoNDQxUHhiZHZiREtiMjkzMGplU19TNjNqVXlVTFRTd1kzeTBwSlFCS2VDdEt2VmlOb1ZvY3ZhMW11aFZWd3Y0bWxUWUQ5WmhGN21xeE9XcnNHWUpvQ05iRER2R1NoaXIwMDJ2dm84a2NpRzRVZ1N5NWk4Tk9XOGxKb0R3aHZlNFdfTzU2MFBMQjBBeEFVSUV5cDQ5eTVWSWgwRGY2dGs3X1BoWDdQQWRhUzJiRXM?oc=5", "source": "rediff.com", "published": "2026-09-25 11:22", "score": 0.612, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPbUR3cDZZTmx0T0FjVGdkU0ZOV21PRUFzdFNkR1FaT2hqcFQyZkVxS0ZKSVEydXF6OGlMbnUtakExc2NhTGI0WkE3NXVYYlpnR1NBV2l5SUxWUFhXX0VtemF1WG1pdUU3TnoyLVJCb3ZxM2ZrdjUzRW1wZFJ3M01WQmtaYnFWbUZxR1NGQ2Fwd2dJRTM1QndDMnlobXFVbjAtUnVscXUyZUtyMVZIaEdmSE9MQlFSTkpkYXhvQlBicjJTRjJ6V2VIRnM4RFNCSDNWVmFudGZNTQ?oc=5", "source": "equitymaster.com", "published": "2026-09-25 11:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rebound on Value Buying After Sharp Losses", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSjR4N2QtaTVfdUc1bkpKY0JWcFZ6RzdlM21SN2M0eXNfT2hQVWt1eXZxYmlmUFVBSGhRdmxTalRGYlIyV3J2M2lmZk05WUpVcDQ3bk1IeFh5aTN5Mm1nVXFZOUJCenlPRzR6VVAtaW0zcjZMQno2QTh0MklYUFhvZW1Pa1JvRDNCS2JIa3U5Qk1SMjJRTm5zZjE4NGFIVlVFOHpwVWJHTlBtaGfSAbABQVVfeXFMTzMwT3V5UkdaUUpqeTRFOHBwOXhrSFdVNjV6QXlZc1lzN1AwUzU0RFNxYl9aWGdQSS10S1d4dnRZNlhQNjZzMW1hTmhBaFoxMmFIaWNIdjdDblFCanNIUjJXMHR2SEJyUnVUb1J4X2ZoS2FVLWh4N0tnZGJ0RGc4aXpPNnQxLXFrR3J1Z3FGczZjM181U3FTbnVySUducS1VNGUyaVByUVNyanFPdHRHSVQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-25 10:48", "score": 0.318, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxPQUxBSWtnLWFqMkRfMks5NTlUcF9sTm1lNEtSdFZDaEstMWw3ejZUX2czMHFwS3k5MEFOWHNBb2w5VElVd011VTdpZ3V4OE94Q3ZGUVhJYTJhXzlKQnRicGVnc25ZNDZDdzhmN09xTzJCNDhLM0JQOHdRZlFKTXlXLQ?oc=5", "source": "INDmoney", "published": "2026-09-25 10:31", "score": 0.572, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE5hVC1JSXRqcHpiOC1BcW9STzVMX1E1Y2FuZThSci15UVN4VVBkU0syaVFzU01NaXVDZ21QSS03M0h2N0JoZFFOV1lZVlZna1YtRzRHdi03OHRLS3B0OGdGbzRKX01uc3BVbzZwTXVmVkFoMXU5Nk04aGhYZw?oc=5", "source": "APAC Media", "published": "2026-09-25 10:31", "score": -0.026, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Sah Polymers Share Price", "link": "https://news.google.com/rss/articles/CBMia0FVX3lxTFAxM1NrSlNad3RNSzJKUGVISVgtY1lGZ3NYN3FyNTBJb0FBYlNGQjVCSTRBWXE0c1dHR1lvemdIOFFwLUQ4czVFaGplWHRnbWR4Wkc2N1pkTUlfQ29mQkFNdU9DZkg2akQ2LVRF?oc=5", "source": "Upstox", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "Nifty Chemicals (NFTCHEMIC) Share Price", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYURIakNOVnRybktpTUJSR0ZBR1Vla0tUNHQzQmY4clE5d0o4Q1pZM3BtaGhTcjk4UWtuR2tXbmJ1S3kxOGZ4SVhYSURHRkRCN3NwUUxzaDJ0dUZZWWZ0aWhlQkZtclZ6U0hIbTNJTlpNQk9Sblp6WW1WUTVyb3ZRRHJlV1BoUUE?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.402, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today", "link": "https://news.google.com/rss/articles/CBMilgFBVV95cUxOSmhSUlhBeGVjR0VmV1paYzdJdDlLd045M2hLX1dPc0NQdkJXUmR5dUNCNGNYeGxBNnlrTVNtMkQya1JiamhQQTNfbU8zdmxndzB4TWlmSndSdmpzZ3RGU0VickFfeDg2U0x0ZmFkMWtxMndNU3FkdmMyTTE3R20wdnNpdUJoN1RNdlFKbXJHNXlqMU9KUUE?oc=5", "source": "Univest", "published": "2026-09-25 06:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNU2lpQ2pNTWhOZFRyMzhsc25Pd1Z2VjI5SkFZa2d3VDhmQVNmT2JuNjBoNWczYU5QaDZZLVhRdVc5WkNZR3RzcGhTN3JpdEJRcWllYlNWQjd3aDBwM0Z3RnNVeG45SUllbmQzX3RtTlZVVmFyRllRTHZwcmZVcFpybi16QVlYeEZoU1Q4Z3o4ZXMxekZ4UWdWYjV1b1Njc3g0dVJlVk5sbEFmRkp5VFNvb1BXeU40RFhHZV9jOXdhU2tIeXV1Sk5mYTdUaHVRamxZTHlqbkwtLVA4MW93SDVJbk5HT0hrbVYwdEZJQVJfSDJSanFzQl9lZtIB_gFBVV95cUxQZ3hlSUszOFFSZW8zSkdBSm0wY3ZNblIxRS1HRnBLVG91VVZ4blFjb2xzakhtMjNBblRzU09WR2NZeWdGT0x3ZHBiSkNKNkJoTmFGanNzX3owUE5sb0szNFhhVEpjV1I3NVFKMGU4VnRCTFBON0doMmhmUUtnZDVYTWpiNV9CZWdkZnlEWXdZVlpBRFRCdUNLVU4xQjJ2dHdJM21Va21pbGppWDBGUkpYbi1VTjVVTEEwM0Jza3ZzbEFHQnFybUJJTUVTc3lsbVNVbF93VzdqV3BWdHR6THZEYXpBeGRZbHZ5Z1hUOUFWeDVJWTRFS3htSFB0N2Jadw?oc=5", "source": "Business Standard", "published": "2026-09-25 06:34", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxQTE9BdERYOTF4QjNsVFdOSUVsVjdickVLMkJHYld6YmRCdm5PRGloTnh2OHk5VmRRQjJiTDMyTUZNalZMQXk5eGt2OHd6RmllbVhWbUpEQjhnOVJvbmtVU2w2aEs1cTd4WWljRTkyc2dmT01xZVRnb3k2TGlvS0lCT3NVcS1yclo1TERWQWszM2l1dzhDdnBoSUpOVTRQNW10RFd6ODFidlM5QWttRnkyX1RWaWhWS3RzWURldTM4MDctTWR3d2ZWSWh1a2FJX29lV3Z5NnkxWUhVYzRzZmw3NGI0V1Q0R1o3TTVVZUl3REw4TFBtNTdUZVA3Q1VxanRQYVF5Yk8xc0g1YkVUZm1mTzFR0gGXAkFVX3lxTE9HLTI5ZmFma1R5UUFlREE1U052c1BXWndUTkY4ZlpnQi1hVGs0MFNNTS1SZU1qeUM3cXduelRYbzM2WENOQXNDVUprdkVfYnJDbE90cE9CQXZ6bUJEZkkxdE9wbW52akpFZTZwWGtQaTFQei14d2hFLWJMT2VpOVotMloyZ0U1UFFLeWZNZ3NzYVozQ0lwbE50S2pJN0REOVpaNWZXX0ZOTFVmZWVkbDI2RFA0OFRtUFZxc2ZEeF83emxxMHN2LVk2M2tNNUpmemRCR2lXeUtwYlVPdHFzNGh6Z1RJVmV2aUgtVkFzajM3R2VtOU9qNlAwY29sN09XSDRRR0FXTF9zVV8tNkY5YVpPbVYyb01icw?oc=5", "source": "Livemint", "published": "2026-09-25 05:52", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE shares dip on day 2 of listing, brokerages back long-term growth story", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNVmN3NGUwRl9DSWI4bV9GWXNDZk5fRV83NEJWVDc3RGVNQkh5ZWktVjdJRnJZcE9aZUxUQ3dyZWZodFFiZzljZmppdTJ1R0lPNUtPTjdLSVdfUXJ6VmNyN1FWVElaV094SGFJMlNOU2drVGlFdUlPSGpld1g4VGpoa0QyS21vUTE5QWViVl9ETWtJdHpKbDNvek9wOHZnR0ZRQTNvNGdPSmVaV1BvRmMyQmtPSWZpZmFwYklWOGpkS2dKdF9DUDg0LUU1QzZDUkhLNHdNR0RRd9IB3AFBVV95cUxPdk8wd0R3RW9FSW1lamlhT2tiT0phLWRyT0R5bDhEUVU2aVRjNVZwMGo0SHlfZVotNHZoTGxCR2ctcGxWNml2UWZCZ1FGOEJZNDRFNElqSUtKY3I4NjUyR1RsTEpZbWI2YkNudU9GRXJURUFfRjZfSlh3VHpsaWJ0VEhRdGhhcHVMVjMxMkg0Q3pEMWY1N0thZm5KTnRINTNwWE54NWNUc1REZFhzN0JCZnVxc0J0RndhMFZxTUJlOFZ0XzhnLUpGWDR2Y3Ftd2dwb2hRalRKSk1lS3M0?oc=5", "source": "Business Standard", "published": "2026-09-25 05:32", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNS2ZIYlJtSTJ2R0tUd041X2M0a2gyT0hxbktRNi1YSFpNcXlUZlBwcW9FMGl0RkRoUXJpLXFSYmI1SUlJTkFBNTl0dlExYi1LWm0xX1hUVVFqVjhxWlJwd1Mwb29fX1U0VVFhRE01d3IxSTNpNkkzQWY2TkpJSVVKLWtlM1dFWkFnaEFuZ2hCT2RYWktac2dQLUVmemdKeHlMMHYwbEtfaEI2d2w0MEdYVGx4T2R1ZktDV1RWQ2ZfUFBDZGRTWVdmSF92OS1kTnFNUTBXeHlZd3ctMF9wMk9lNHRoVEJTUTVYSV9rR0FvdG5jZVIxdzBJdnNSS1VzbXll0gGGAkFVX3lxTFBZX2J6TDljZ3haMlBoSFNpQWJ3XzE1aVhVTXVUNUkyYUZLY2N5Z1VuV19hbzZNNDhsb2RlTjZWRmpObFNlVFR1RmtRcVM3bXZGODZXUnhJcC11VXVDM2pKWVNfdXRjaENBQUZiRjZwZmZ2SmRmRTE1Nmxac1I4RlVla0U0LVdlNGdKS2RxOHhfRUFTaUtlcDNLTFVjY2JyZzBSWFEwVXR1R25rMjZmRldrRldOazUwRmRjTmhpVUl6Q1ViWFo4bS1GaEpuWkhUelYyd0ZBOGdIM0Fxa0p0U29jZEpnR1NWcGx6TEl6ckt5NUNhS0lTVU1QR043dEZvbC0zNmpHNmc?oc=5", "source": "The Times of India", "published": "2026-09-25 03:51", "score": -0.494, "label": "Negative"}, {"symbol": "LAURUSLABS", "title": "Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSUFqNDJicXN5c19sQXd2WXNJb1BWb2UtNUpOZTI3d2JudFdlNkZmTzVQUzFKM3VXTHJlZGZKUlhCZTR6MUZob0p6Y0hERlZkcDBzYmp6OGJaMTBKRFcySjNlblpkZXNabW1kZFZLRzdkT2N2Wnl0TWtJcU54Skk2MTJMUTVFQmJnbXlzeE9jSDgxRlhQaUd1X0xibGxDWks3Y01hZkViMTdVNVJYZ3RJald5TGVvUW5sMkV2M2dxbXBiWUNDT2ZXV0xONFBVa1lPOWN0aW1ZY3JVZ9IB3wFBVV95cUxQOGJWak1PMG9YdEpvYzc3S1VhNXI1bDBheUl0TVdJMTBCdmJoM2M5NUFhQzdYb0VFM2dsRmZLOER4U3k1eFUwQmg2QTdlRGNYZ3Fod1F3RW52bWVGUU02NlpaUkVhWTBXUXd3SERZblFDR2JVR3ZZZ1FkcTVTcGU2ZWZQUEVaWlFTMmJRWDR5WHVoYWtQejV5YjRjNXQtSHBKOFdaM1Y0UVBTNTZENWU1elFHYTZmVkUzSFkwUkM2TGw4Sno0SU00WXNUMjZUenpEMXdqQ3AxdmFOeE9HNnI4?oc=5", "source": "ET Now", "published": "2026-09-25 02:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...", "link": "https://news.google.com/rss/articles/CBMiqAJBVV95cUxOQ0Z0MUFZM2ViTTdHaHJ5akJLdkNEbEVZeFFsZ25KVmN6UTE1X2xMTmtUckhBOUdZeE5OOHY5blA4WDhVZDVJbjZCeUJVWE5meUM0aWhoY01DRnRBRHJaVURNTWg2SVRPVkJhUjVUb3dkRDVQZ1B5ZzRhS1ZyUVA1NnNXOEJqbWh0TG5EWHAxZXIzcU5nYnIzQ2xZU2RWaHR1dE5KTE1sMUpTQUthdmdLbGpjcXZvY1JsWXNzcHp0b1F3c1I3ZHpmUTdqMUpmbTV3M0JNM3AzWDZETUFsOFpURk9oQlY3UXB2Rjh6cjNobFhYOTI4MXRUN3YxVXYwaXJnTklxOGU3NXNHSjl6c3RndGt4TmluUUROMVhIZ0pWc3hia3F6blRJSNIBrgJBVV95cUxOdWNfS1N2QVhiREVSTXpDajYwUE9RM1VycGxPNmRKaHU2N3N4Y2tiX2tKSlU1NEpYR0Y5Q2xOMFFhV0VRRE83WmNDUXFvUU5LNXFITElxRmNJSEFJT3dDcGNwT3Q5UHYzaFB4NHg4NlpKUXo3bGtOV1lPRllGMXUxdC13N2RoTl85V01LU3o3Yk5Oa2hzWVZxdGoweFJySlZDVXFPY3NFcXJwV0tpdkxOZDhhRXRpU3ZhOEZCMEZ5QWlBUnczdTRuMUxCcXdwb1Vtd3JWS1Q0aUxpbzhhLXh2bmRtZ05Cc2VyVWM2YjVJTzRXd18yNndmaklMQWdsWlEtdEkybzlJRng2WndzbnJWUGF2S0RBNnE2MlRCb1FGSVktd0g2TEdPdGEwMDRYZw?oc=5", "source": "Moneycontrol.com", "published": "2026-09-25 02:06", "score": 0.178, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Bond Yields To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On September 25", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxOdVk2NWY2YmFvVWRzUDF4anpscG54WjM1SVVVVldRT244LTh1aXVWbXFCWnQyQVZnbmQycU41N3JiV3p5ZTF6VlZMSUI3NUQtR0tsVDF6cS0zdjZiQ3lCM0VhTXFoSEt4aEh2YVF2cXFxY2ZfMkVZSjhuNDZyODRGQUNYRXNpeWdEZzRjd2ZaeThvb3BxdmpBdU1jZVhNWHAyUzR0eGhtTzRHYTVkdTdvYWhRcWhldEkxV3Z2bnZ2SjhqNVYzMWR4MTcxdWc4X0FkNzdjb1VhYUFFNFNOTnVMeGFtUkF5SC1ZRG4wM1Z3VUU1SE5ucnfSAf4BQVVfeXFMTzFDRFpfdFA3RTRhanpJaFljZTc3ams4V2FOMENpZWYtUC1uSEwtYWlNODhZSnhnVXBZUEc5REwtbjFDYkFtSjd3SlBwbHgzblJDQ2pyc2F2aHdwV1NnaTlxU2plcGhYNWg4cWZiZGNObUVPOENwTFRuS0dnbHdTbVNtQTZGUXlGTnVnaEhZYW0xVHhjVnpZdk1qMlQxWFNnRHM4NENlWDFtdFhQODYyNWFRb2haeThMUWdsZk55R1g4YzBWbkFGc2xvX0Q4REwxdHBjb2VidHFmMHNKRnZDXzBrQU5oZmJ5bVFuZ2dIVmhlMGJKNHhhQmFPdlNPVlE?oc=5", "source": "NDTV Profit", "published": "2026-09-25 01:28", "score": 0.807, "label": "Positive"}, {"symbol": "RRKABEL", "title": "R R Kabel executes BTA to acquire U M Cables business for \u20b977 crore", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxOekdBdkJnQy1zc05YRUg5aFF1a0lwT04xNl9vZlhFaUhGVE0yeENFRkdPYWp5eW5qNGJPQ1Z5M0tIQWJTMmVBZ2NIcG13ZTFtc3FJaE9hOG1SQVk2UENVdGNWTXktTE10MGNUVmpvNkxodGg4TS1KdHFlZGprNUpZMkRsS2x6OW1LcGtSVnJPQnFvNlpOaHZZbFlnSlZ0MGtEdjdSdzVvSQ?oc=5", "source": "scanx.trade", "published": "2026-09-24 16:21", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets", "link": "https://news.google.com/rss/articles/CBMi-wFBVV95cUxNNDY4RnFxUWdPN3hFd2xaaFZRMERxSGpxN2Z1ZjF1LWVVZXFDUnZlQzFhNDRUYkdVWW14NDRCdXZ2LUQ0YzZpNWVUQmxtTEtHV1UzaUw1eWtXYm53a2JYSzdFQ3Z0clktdUNZY2J2dE9MU2lxM012czJpUDR1R2ZkN2h3QXNIWGkwX3pEM0xNakt5RUt3Y3hrQTZPNW9yUVhDQnRCaUs5RHdjRVM5Z2RMTGc2cG10WS0ycnl6ejY3YWFsYkUyVzJBYVc2UXlvaVNpRkFKZkZmWkE2RzBxcWFMNElnR19nMFN6cmRzRDBteVpQMjlDVHlaVi1VONIBgAJBVV95cUxQbEJYN0g0YUZETXczaUtkbUdMb1c4M2lQaUszdUtyTXZxMVVYWENrRm10czlDRHQ0alpzSjBhRXMwVzVYUUo0djJYXzBQWlM4S3NZZXZtZTM4TS1zd3BVbEtHeExGNHVVcTI1eDN1VWZHTUQwRllLU0VTenctSGtMT09DTFpSSG00UF81R2ZsdGxFMFlGVFB5aTZLWGVvQ3RwWTVVWTV3Rjg0N1RKbTROQjdaVjR0RTRuRUVtLTFUTDgxdUVMOWVhOV81ZEhMbHlxVmh5Qk5NMXNCdXo3anhfSTY1SlNaSi1zSEtvemVYdjY4R2YteVlTRG1qX2wzQXFy?oc=5", "source": "Livemint", "published": "2026-09-24 16:04", "score": 0.7, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxORWVLSFhyVy1XclJaTW9wUmtOTF84WGZkclJHbmtIdW5oUXNJS2J2V2xqUjNnVmEzRDJJRko2Y1UzaVVuYnFOUlRyYTFzNFB1dTlvMXp0U3BTRS1rUV9pWXotZG5FX2xZVnI0eHRaWDhlLVZwaThPXzdCNW0tT2ZEMFp1b0FrRFVsNnZSVzVCTTd4MWZEUm9ERnJ5bTJNaGRIYlhYcmRGOE1ub1c0THBORGt4d2h6SnlBWUhFeVdSUDg?oc=5", "source": "scanx.trade", "published": "2026-09-24 14:42", "score": 0.382, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQnJ1UkZncDJJcTRVNElLd1ZKN1Nnd053YjRobGxJUEdGYUdWS0lvb0dHS2MtemJ3SUppQmZ2c0NERjFpa2szSjhMZG5BcGZiT3NNa191ZHEtaGRCNUYyU3FhMHBnXzFBUkk1d09ZNWFnNXJvZHR2VU5LTWkwMFlWU19xVnZkUkk2aFd1N1FBZm5xVVlEQmx6dVhDcG83MGZveUFrMm9pMWgydUlPMDFZOTB2RFBBT3JPdDRVYmdKTUtzbVBMTDFIbGlzdkhVMklTNi1aeVFHNjNBUU9RclRiSmtXVjRlakw2S2UzVlhlRTZvWWs2RFNoVG0wUkhrZw?oc=5", "source": "The Economic Times", "published": "2026-09-24 13:49", "score": -0.153, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxPSmdZMUhhTERFclM4bzZicU5pWTdPX3lDUFQ3NU5qcU5hNWVHU3Jrem1lS3FuYjhUcXBVOGJFLXVKc3hCSFlvZ0E4QzNJYjQtNGRHNldTU0pyWS00ci1qNUNTNFpXd2lJLTZnRnQzVGNraVBUUGNhSkJzWWRjVVNqWm9Qa004SHQ0bXIwUV9SNm4tLWxtUHl6eHFoZVpPUHQ3UXZxdUxZTHZrdnpYY3JrTHhFTUxuQ24wd1lBR092aDNFV0lPcXJWMkxITnFFZkdNTkJqRzZqeVFIZmYx?oc=5", "source": "Kalkine India", "published": "2026-09-24 13:15", "score": 0.318, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "3 Indian Export Stocks That Could Benefit From A Weaker Rupee", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQNUp4b2tjbFlmWklUVm5zT2NJRjVXMm53bE5DNjJvb2ZFd0tFZVRUWHVxbWozaEp4aVBQMGtxZkpfQ3FmYnZtbEppcGtXZ1hYYl9seFIwdlhpczRuUWg0dE05REgyUkRMdXJpaVZDc1BORHVteE1IcHptNnNRbkdTY0NEUTZKZk04cHEwWTlNTno4MjJKU05aVlVOZExfd3plejl1cUxiVXlVbVNibjctMlFyOWx3aEZmYk5VNElFYUM4WENySTZGcmFrWURmdElfRjhyTm4xelJnYWNjVGtmb1I2NmxXZnRPem56RDZ2b24xZ9IB9wFBVV95cUxNVGN5NWZ1TnFTNUt1elFVSE5Tam8xZi0zWVY4Um1SX3UyVE5xNDZPZmpWQ2VWXzBsaW1vcnVzX1NoZXk0aWJjeU5iaXpiT1dTejAwSUt6Z3FhTThnTlhsa1ZFdHpfTG1sNjIzQ3pkZ0duUXY5N3ZqZU1qckxKVlZneVRJVmxjU1VrckJtQWlBNWRsNGdZbnRxX253TU56dE9NdXA0RlRoR0dLS0VDWFQ3VXJILUlrcF9OTU1lVk1sODFsbmVIeG1ROEFLcUlhWmswVzVkUjgwRW85cUNQUXpOcS1VZnBLT2pMSlZ1c3lGQ3MyN0JKeGlB?oc=5", "source": "simplywall.st", "published": "2026-09-24 13:01", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPTmEwdzJWdUtmS1lTeHJNaEFsLUVRRTNTSU0yMko0SUJCczVmU05rb2tDckFtclNUdEJzbmN4VUw0TUY0aWwtVVlEM19wTF9BZ0xyZmw4Z0ZTam4wMmphemF0SjRoWWZTaXZOOGJES2dTWWc4MXU2djFTZFQ2ZmtnTGgtNFBvMlpVbFJUeGVCQ242RGpic3ViMFl5QmlzbE9ZMFBIQktpRXRkSWhmWVh1WWJYZjRYQ3FkcEJtOTVNUmZseW02bXQ2cDlheEVZWnItWGFrOU5aTmdDVFQ5UDJMUEI5Y2VSREJGSmRGdFY1UGY0cUJTR0FFUDNSc014endZb3U2TUN0dFdXQdIBjwJBVV95cUxPX2xOWkM1Q0VWS2w1cGpsMXpBUFVpZHZOQ05TMTBkY3BMRHUzcjVIeEdpRHBhYXhKNXUxSzRjZkI1RHpXbkRQdlpBUkdPS0JIVG5jcjQ4cGxZUnZndUIwX1VMVWlwU2c3dUZTNHR4VjZrUzg2VXd6UHFaYzdTV2xMRXQyWmFQcFdIMEJUN2pqcFliNW1tRHU2a1VNNnUwekE5ZWRTYTF6Sy1FbnBhNEQ1Zkh3Uno3QTZuTXVRcHVlNm1LVE5oVEJHLWRiMWFUeEo2ams0QU1ocjRRREF3Vkd0dXQ3ZC14cWNLNE5oM3lPMXNKelVjbmxuQjA0dURockhtcDBQS2gweGZ5NERLYVRB?oc=5", "source": "Livemint", "published": "2026-09-24 12:36", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see worst day in weeks: Why was market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNTTMxLVltQWc5MkFQOUFYNlpYUTlLRnVtOWFTM19ETVhBaDduYk9pa3VKY2lIdGNGTkpIbVVKaDNkV2Z1NlBvdUVVeC1JbTNJem02eHlvdHRvMFFkR285ZjlFWk1fbXR2Z29HSnNVVklmYnhpOVlHdUFxeUFuNmtXeTZFY21KcGFraFdXRVBfNWZRLUU3WEhhd0x5OGxkRlRCbXR5T21JNDRpWE8tSU81VGtxUXFqUzl5T2FrS1dXd0s2QkdoTkRlSWJFR2lORk1JOWpnWHhvanB4bEdTaS1aZG1sbTJfUDFManBUNNIB8gFBVV95cUxQaVFGYUROS1ExTmNWWWI1RHNoTGZfWDd4U0hPeGVCdzM4eUtkZXVMaGZSTXp3NDZEcS1POXpFa01KQlNtY3U5QWgtdl9VV2hZY2VzZGp2U1pQbE5sT1JoQkZJeFFqT3VMOENGMjFXM3dRajdZdTVJMVpIWVVubzJhbjNyakljV1BrTl9vVDh1Nnhnd3VqdDJBbThXVDY5ZjBIZXFKZ0ZHUkt6eF81SHJEbEF0YkJnVDQ4clNuSFJONkZRRTkwZWxLaS1QcEVwVmRqQURkTlpSTm14R2Z4bDV0NEhMMzVJdWZ1TzhaRUlweVQ0UQ?oc=5", "source": "Hindustan Times", "published": "2026-09-24 10:57", "score": -0.34, "label": "Negative"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNb1U1UU5HdEFtaWZCRWdVRWxUc2pRMFZ2YXl2bUpYNE1xNzZBX01tTXNtQWc5d2ZCNTdzYUZwXzU5U2VOX19rRndvYkVDaUl3aGVqQ3lyU01qYkNtVENjRG41VW9IenA4V21EcDhLYWFrdHZPYU9yNGl2RDFSUEdRcEtObWtDS0doZlo1V3ZwOGcwcmRROTcweDNZeTZaRGdQZ084YzU0amppMUZaZERQamg3YUE3RF84TjFuLWx6T28?oc=5", "source": "Kalkine India", "published": "2026-09-24 10:15", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVTh5Q2ROa0YzRWp5NS1Kamp3NnMzYnBNRlJHcEZ1cVRnOG1aampUb2pFbERqcGNPZjN2WGZqNGd5dWNDN2R3bnhXQ016bjJoUXUxN2FqcVYxaDFrSTlwZGpSQmZIbGM3THdoMUFDX1hwZXo1OHNPTjVpNFhLWVZudVFHU2xxbmZ1aUFnWXZqM09tZzZ0TVlRWUwxakpaM3JIUkg4QlBBaG40QUQzTWxYYzNSZi1uVVZtWTJHVU1UQzhDWHB5OW9Fb2JHS3ExdVR3dExkMGJRRVRQVmZfZnM1THUyOTdWbWhDaWfSAe8BQVVfeXFMTUFnaWZmYkVLMzZkNk5ZRXF1ZF82LXluT0hoSlJNZ19kUVk4VHlzLXhabENVbTd5LThnUlJIc215aVY1T2ZwOThSS0dVNnJNTVBIdjgyQlBPQjJaTF9sQnZWeEw3Z3dVdFVMNnU4ZzBWOENQQ0dtZ1JQal84UmdMS3FvdEFJUFdMbVhXQm5tM3JYNUJhYTFFRnFtX2VIaDJMcWNPUFhpaUs1YjRSbG1lWWVTYng5VnNjbFF4Z3NqVWFHWEd3eEMxUjE5YUFQZ21qdVJJV240Q3dsYTdHQUhKTjVGcnk4UWRhd3lEdTJYeGs?oc=5", "source": "simplywall.st", "published": "2026-09-24 10:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "The battle between India\u2019s stock exchanges is heating up again", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQSllxZjNuQ0l0ZExkQlp2RmVURXBuMm5WRjUyUkZsOXNaeF90Zy1GWXMyZFAzYmlGMGFfTWlhSl9lT2JNMmVnclFGYlg3bjNZQTRUeERZRkFScXBYc0IxZnhEcUF4Q0tzcWhhQTZXaXR6NjA5Y1pTSWdDQXBPQS1HZWpMOWJHN0NzN0lLWkdiMlJWWjN3OC1Ha1VDQ1ViSE9QTmZmSHBYTVpFM1FiUEJtZ1B4Y01nd2dabTlwTw?oc=5", "source": "The Economist", "published": "2026-09-24 09:42", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPVWZGNDlpWFN6MFJFZVZMVWp4RnIxcTVXOTRMUS1oVnMyQkVmZkF4eDdQTGYxOXVKV253c2dWUVZrOFpQUEEzdUQ1Rm45bG1aX01RSzVBNjNIWEFIb0lLbFJsSWJNYzFzMVFaVFpXUnAtR2xtZEZ5YXhjdXRSOHI4ZkNVMlJvWUszcWJEdGFBWmpqZG9zaGJWRnZGMHFtM0J3OWluTEZMVE9xSkV0Q29QTnJFQzEza0ZQaERRWjNBaEN6QlpkSFdMcGRuWndIWE1RVU5uczhza2w2WndRYWlUVkg3Yi10bUJFLWRWTE1sT2I1NnhwVTdCa3ZBRmxpRklNbGtzbkQ3V1licnlmakQw0gGUAkFVX3lxTE5pNjM4R2ZHalBOWTl1aGVPaWxONlMyd2lmVERYa0RZeDlDMU1IbnZMWnhNQ2VuWXY2dGRTTlFrZVFrU3RmaUJtcjZxNnlVNXc0eU4wQjR5Z29zd2FWZVRoM2FVYl9BY0xldFp3SDNjYnNSdmRwdXFYTEpxcWM5WWFrbHZCeDhZZ1c4ODE2SWJpX1RvX0dkX1VHemI3dmpJem9uWWJsNU1Ia0JFWmxobTRWMjBFdktPS0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sZGhlVjdIaVh6dFRhU0FERjk4aE15ZmlNR19BbmlCei1FRHV2TXNwV1BJaVRHQmxSZnh5dGotNDRaUEpUZV9pMmR2STRRbkhLUHhPa2FMelZzX0VfdXJMOGVoeQ?oc=5", "source": "Livemint", "published": "2026-09-24 09:40", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZ3RITnlWRlVoLVRXRW9Pc1NnU042UFB5V1BVM0s0QkFvcnRjbElBRVd1ejJZQjdSTmNfM19uazFjYnZFbm9EMmhxVU0xYWtsd1dZNldfbEFJOE45dEVDMWw4TUVwSW5LdkVfSHZPVnZsRVI4eWhyVFpaQW1mRFM0UFUzZDhXaTB6anpwWDlSSk0yWjlpZ1Z4WEsxd3M3YklFREtEbi1TNXhEUmsxYUVyWXlPTHNxUXJVYUxpbV9ENkEtNURlYnlPcU5lTnBEbjRMVGE0SXdGRTd2VWvSAeABQVVfeXFMTVVqV1N6TXB3TXJhak1kUURlODRETFpFX1NBa1RRb1oyUlVNd0xRcXBHU2ozWVN4dlQ2N1Y2WUhpdTdZQk1NWWNYcDB4U2ZneFRVblBSajlpRmlzLXZWMTNCeHdIZG44a0ZMandxanFjTW5qTHpGM05QQ1Vxbnlsck51UjJhMkloS3dPaWstcTFoS3Q2NEQyRi0zQVhITkp3NzdWRnBkWG1vaVdWSll0SGlsdXRiaUxWc2FUVk9wMW1ZZ09tRlRCa3RoQjNONFhvQmdyN25tVWhBVTBEZmpuMnQ?oc=5", "source": "CNBC TV18", "published": "2026-09-24 09:08", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxNeEtEbWlBNTFIcHJzRV9zU0hnQUd4MVRma2VMWXpOdDl3SURrMGJPOXBnVnFOTm1MLVpMMFAzYUhUWDJVYnpYd1cyWG1xUjhxOVdkb0tVNkF2VnZfZktsRnRYTlNjMzBYblcyM0pHRUo4Ul8xVlFoci1JOXpSU2F2RlBkbFJaZGhTeE9yODV4aDlnSDdKbjd2c0ZKMzc0Y2JFbER0c2hDNW1pbURITlcw0gG3AUFVX3lxTE8xbVZoQm0xdm9CSmg5ZVBDMVluS0lTTUctTnpYYVU2S0RxcFhlaUY5Qndta09tY3VuZWI3MW1LRWlPNVl6QlY4OVBFcENPZEY4OU9jMThxdzM1cG56U1ZtN29HNGEtZmZ6eklRSXlNNERlUVF0dXNjVXV0dERKeFpyeHY4YUV3ZXdWYWhjcWsxM1d4TWtYOE1tUjRFQ0xKQm5aWHJhcnJfSHFha1FDeUJpSDdJaWhrNA?oc=5", "source": "NDTV", "published": "2026-09-24 09:02", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxNT1lNOEhqOHFBM0dUS21nbjEzUDVTOVY0YnkweVp1T1pQdy0zTG9LUmppQkhYTGtIZXBSTEtiVHdDNjZxWm5FM1VXYUl5Mk9WcklBS1p0NWlKY1FUWDNqUnlYcDRrTzI2dms1NVNjenlmQkJZdlIyQllHaEF5VVU5OWE1OFgzeE5jaVdSR0ZfNklZOGpsMGRyc3NXcEdsdFVGRl80QXRsZUhkSDVWbXN0TlRKNjJXSkRSc05IQnczMlpyYXJwYnV3NERXY3BQRjdJN0h6REx4LVo3S1dLQjNRQlpNOU9zX0RLaUlxNXUzRzFmTEdGakNJTHotX2cwX0hyb3lMVEZmR0PSAY4CQVVfeXFMTWdFZHhRbFpBMnQtazZaZUpQVk9Ramd2ajI4M296WDFaazhGZG1OV1RmeGRqcDJkeTNsWC1TYXNTbWtJa1RGRktmREpwbkpqNFYzUlFIYkR3ODg3RllZQTNWZ2h1ZzBLUlU0WXpYV2ZlQnN5WE9pN2JCV2sxbEZMdjcwQXcxRGE2c0lLSWdLVHJVYTRuX2gyYnV6MFlPZDhMUmpzVHpUUWk4WmJYNWtsMnRZSTdmNzBzdnhGRzNRUnN4aTdrakZ5QlJ0aHJsaGRGQlk5NFllakp1bHByRFpMbU05S2tqWFExY3lQYkVlUjlyX3hTUXpmRFQtVmdocWFJMG1aQ29LTHNvb200Rlh3?oc=5", "source": "The Times of India", "published": "2026-09-24 08:52", "score": -0.402, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "Hero Motors Ltd leads gainers in 'B' group", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQSDJtZTVDOFZES0ZIb3BKUnlmdkV5VTlSc2doTWJUZ1k3WEhzVDNxd0doUHI2aFBOUG9FRW1hbUw2bTBKb3FxYlNxZS1kM2VvaWtpcnp4ZEJpa1AxQ04yN3QySVkwS1dUZ3YzVUo3UVlIdzV2eE41ZUdJOWs4cTMtS2ZQNWdySzltWE5CVVFQZTZLdVZCaHVxTDVYTkJKLTE4ZWQ2SlpuVVAxNFFSVVJKYzlhT1FxMnYxZ0dKUDUwNNIBxAFBVV95cUxQS1NzWTc3QXZDVEZ2M1JsYlh1RFVzUjdVdHVWdVFrcWMyRS1zdVRJajBxXzdvSnVzWlZCQXRNbDJyenM5SDJwUnRMcW5BR3ZCMnlKbUY0dTdiVXZMalpuT1lsOHJoaFZtYkhkY2lIbVVXOVJ2MkRoRE1pa21xNU1LWUtYOGpEaVE4VFhqdElqLXVRZ1Q5SHNLVGJfN2VPNUtLT2F1ZnhMUU1hMjNXSTh1dzVZS1d2VE1fQ25BcmZEcVhTVGxf?oc=5", "source": "Business Standard", "published": "2026-09-24 08:46", "score": 0.557, "label": "Positive"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems Share Price today: decline and analysis", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxQcUhUNEJMQ3ZXeU5ZcFk0aUE1NndmWmVMR2E0MVJuM2RhTi1QRHhxT1lZRTZKeXp3NEkwak4yQ1RPVDBDRDlXUlJVUXQ1QjVIMURYTEtsZ2lXVW52SmR2VzZRS3FHanh2RklUTlNTWElScmtkaTdGMGx0SWIxdlF0YjlzVTZzQQ?oc=5", "source": "Univest", "published": "2026-09-24 08:35", "score": -0.382, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNYTRVYTVWR1lSdF95cG9QR1FLMk9SOTlCWVg0NzdVR21OeTdQQXJYc2UxbkUxa2I2blpPOVRYSmVCcWNaQnVxSnpvX0RGQnhZdmp6X1JXRGxXaVk0dXZnRDV0ZTJmdFNMTzUySWNXUjZ0OWN6Y2hwcHY2cWRxLS1hZVRpdHpISHpjMnl6b0s1M1J1bHR6LWNTd1otbHEzM0ZRV2RHeUNEdmY3X2t6ZnF3YkNyRHREUDA?oc=5", "source": "scanx.trade", "published": "2026-09-24 08:21", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices", "link": "https://news.google.com/rss/articles/CBMi6wFBVV95cUxNcnpYS1l4a05TYTZaQUM2enZTYmIxVThMMmd0UzZaSEczczdQSXhEU0tSSV9DdXFXdXE3SUNBem5BRV9BMUFlZF80U24xWHh1ZHM1SkRjU1p2a2NvM2NuRjdMQUswaWJkZUV6dVp1ZzVrZC1jZUdkX09JaWRSNWFOcEdOc1JFUVNRcEdfVXdYMVF4MHpnTl9zRDhLQWY2NVllQzkyMXN1Y0YzQzdSUTFoUC1nanVwcEhzNnc1NDNtbVZOSFhDVVpUM0F0ZG1VemZSZkF3eU5FSldzSEFLZGRBell3ZVA2Y01JWVhv0gHwAUFVX3lxTE1XVE1JUmZXOUd6YURZeGlua2c3dEZoZ3NQdWY4SnB2RFVOa0dnd012UlV5Mm16QmE1c1c1SHppQ2luZHZqU3lfb2llTkxTQmN3MUlpejNJOVVYb3BCaUQxZ1RSWEZBWWFwdjVlN2ZTZWVyTGZhdjVfWkNtUG50SkNhS3hNRFlFbHBhMG5DMjZXS1FGVWJnMmUtVzJueHhRa1IxdnZpaGVuU3ZJYmhUVXFGUWFNVW52ZGxYODBxWFVzMmRnNl9PMW53dGJ0Qi1EZmRaUGhzc0FLZWxnejdscjFjRDdUM0UtRWNpa1d5bm5JOA?oc=5", "source": "theweek.in", "published": "2026-09-24 07:35", "score": 0.077, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom \u2014 Ask Profit", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxPcjBhRnpQaFhkbGdfV3E0ZHlmUjFPQUlUQm9LTFU4UnFqSHduWnhNSEcwenhUQmM5LUxsdFNwUXN1S3gxZW9PN213QUx2TDhzUWpoNXJldnBQRmI4eTBIOE9JMGdqd3I3T2F1QVVYcVZSUF9jOEt6cnB3QWhmZ3F3Z202eHZkRXM4NHduSVVzLThxbTQ0aUJEeEJlTThhWHBFMkJ2OGJ5X0FXT3ZyWFR3MGlZeWEzWjJGU0hhejlZTFgxakpDdVVtbkV2VGJtOXU3aTh4Z0lPdmtneU5EQTNudGd30gHqAUFVX3lxTE5SeDJuQlhJbTcxaDUzbWNPNjNuZDFqLTNYYmEwR0o1QW43WVdkLW9FQUhpVExqaFluQjJwYWRVcG5NcE1ELTduTUxUVTJzQjhvVlN5YWJKa1AxaEFjYnIxempBeUNFbG1IeW94YVMwanoxOHAzNHlRSnFUbWJ3anJqQWVvb2xQeVRwZl9CQUwyUl9KSXhhTm16Qy00Uk5JdkhGU2Z5SGRzNkthQmRBN0J5WnE5bFNUREhuNC02SklqM01odWNqWjV1YTVsVUhXUUZMdlhkN09kWTdvbHhZUjFXV05sVTlGQkptQQ?oc=5", "source": "NDTV Profit", "published": "2026-09-24 07:25", "score": 0.296, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxOU0F5bUI3X2RaNWllcFpuSUpqZFp4Ui0xRVNpb2FSbVRfMjZieWxhWGV5R2N5MHpqeHBQcXIzT2dfTHBjZUt4Zk5aV2Y2SDNhM3VjamJBeTRhUjNjVklyZ3lWZDMxZ3hMMjNXaHFHWUFKV19ZaEp1WTBQekRXOU5ZdXc5UG1hQkIxRTJWdU9USDZqekc5QTh5VENqRW1ybVVCYUMwODlQRGJGVUZKV28tSVpXMFQ?oc=5", "source": "Kalkine India", "published": "2026-09-24 06:20", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'", "link": "https://news.google.com/rss/articles/CBMimwJBVV95cUxNblY5UUJKckZ0My1hbEZrdS1NbjFpR0Vyam1YUHcxd1BSMDdzWkpVZzVyN0ptcnZWZ0EwRElGTEdLV1pWNFd3a05HeEpBOC1UN0NCandyUjlzUVpsUXpKZElQajdHYUoyc2dvLXdMVkNQSW5lZHNFVG1aMzVJQ0tUcENOcmR3QWIyUFNWOFo1RENRX29SbEZLVmNGdVdjSVdkYVZyM1l6dUNtaE9KYjk1VmhIVTlWUlVZNUVFekwwRGZETkw1NTFzbWhSX2xVc2RTdzdCRExjMW5LZ05EbFZRODJvcXRnbmpKZGdPRGlpeGgza1BVNFA1V0xkR2ZJUEpCNWpPZnh5aXR2MW5aQ1EzTEJBdGY5Mi1UTkZF0gGgAkFVX3lxTE9GWEM2U2ttbzdkc05MdlJqN2tFU2pGUmxYbmVIeHktdHRhWVpuaWRnUE1RN01WREtsT2x1cTBBbExxTi1sRE93d3FvWDljRGJzWHNxMW9jek9KTklxUEdnbUk1a0t0YXdlMVZvbzc4Mnh0c3hUUXMzdV9VOWV3UXdqSnRQZFJNaVNRZ1RybmpKR19rS2dNdm5HVkNlUmRUTzJrbkRuYy1fR3pRLTFLUDBZcVAxMjRrdXg5ZVF2M2NDMjgwTXZ4bktqUXNidVU1dmJKWXEzUi1NLUwxUjliSG1vU2lQeWM2S1lRdkMxbW1qSGI4M1lpSHRVS1FVXzNja3B5Q3BYalFYLXV0T3d6VXlWVVdEWTdfUVRsWFV0RlVkdg?oc=5", "source": "The Economic Times", "published": "2026-09-24 04:09", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxNNmFnZnk5VzNtcVFkY1JFVlVCMFh6T3BlejFod0JXRWFjMng2alROdHU2YzRmcEVCV3VMZFdYM3hCbUFCa09PVmVkWTh1MWFaaUxhTndsdjlVb3pZZy1VZU1wWFl6WnNvUzUyZ243ZUQ2RUVIMEhVbm8tMWxWMzM0Y1N6aVlPenNvZkl5R0hmVG5JWlE2QkcxNlRDd0UwU2RSN3NscF9PR2NRVGVaRWYyVUpMeHFrYWNVcGdMNTM3MmpSVGdkc0laX1E5U2U4Q0pBM1N2cUNlQndvUGRvUHVhT2w3Qkh0UHZ4dkcwVTQwUkRMMHlY0gH6AUFVX3lxTE5jREhsTGtRRUVDMnRQMEhucHBndU15SnViUmVFb0ZxTUE1dmpUSlBMV01WYkZ6UXd4QkRncTdNZUh5VVRxNEQ1cmViQ2Z6WFViOVktS1hld09jM25FTHRYN0lJa3d2Q1NsWUxZR2VqUElmYXVFVk5wczFqMy13QUd4Ty1ER181WE5KaHE5SEhFdHZzTy15T0tnZ3pyZzhVMktvLUI2WDF2M3hTRThxVzZEeDRaU21jYUd4ZzZPbHlWRFVMN1lZVGRzcHd4bDUwTWc5d09MYks4c21iYlZKNUUyaC1GOXIzZ1ZzT3dXTWVaWm9KdVhHYzN4emc?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 03:56", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPRFR1dnlza0cxUU5PbXRVYmRRT19oaHZFS3NmTDZUdHhDUVpIaTJDVDFHYThvSXE3RzNWenBDSUlDUDVCdE51VkpDaXppUEl2M1htMGxsMkxPV3ZaS2d3YVhYVTlFUEphWm45cWVuYTZLYmJ2V0xwT2dtMFkwQXZ5bjVWOVh2UHczVnZUSFQ5NFBrUkJaQTJwRXFoSlY5ajhXaHJXOVd3enFaclR4QUpXODFjMWxjVVE?oc=5", "source": "Reuters", "published": "2026-09-24 02:46", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPUXhSRW9fbndZUTd4Q3FFZjhsaThCbS1jNzk4Z1N2TUdiU0lpcHNQcEZ0WmpqdGZHUUlIUUhNdlNseThhQ0hkVDVNazBSQTV1SmRVNTJ6SnUyVTBEQ3pfWTBubFpaREdzcjI0VTFacmFUZzI4ajJfZXZLcU0yQ05NcG9BN1ZkYWQ4M3pJVkFmRllNRXJXeU8zWXRMRkVoQ2o5aGJOamlGaXlfYll4WDBEdGdpY21SN1o4UENfRGNSZ1E5elpxVjJ1aGVWZ1BnZGpfUFMwM0VYM0t4eHpnM3BTTlBKaFZoQkFTT3M2bWhSNlExcEZkcmRUUHZMVmNzSzlPc2fSAYcCQVVfeXFMTnBRN0FXeEh4U2V5eEYydmZXb19IdldaZk5tYU8zbVV2TFV5ZjgxOGg5cGZfdHVScXprR3dCeEQ4czVEOF9zSWpoM3MzdWVrNFphaTdJZWg3SHVac0VnOVc0Si04cUdma2xrRFRLRlJSakp5N1FobmtwdUNqRVRFNWxsYnJrbVpjRHI2RTI5dmJ0Qml3eVBLa2NTXzNhUHZzckNXVHJxVGs1clVveXhUYlk1MjdQOTE3SDZTelVJb1JpSF9wWkpjMno4X0lDdkt2TzFIVE0zVEVRaUFxNG5IVFRhTGRwVURPZlBOcTZtUmlNTTJYS0gxU2RWTkh4T2RZOHB3SFQ4RHc?oc=5", "source": "Livemint", "published": "2026-09-24 02:44", "score": 0.758, "label": "Positive"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxOT0tVTzVLRFhsRHJ6QVB0WV85ZGh4RHFXTEdKY1R3Snp4T1VIcXVyQmNMOGpKeDF2aVdfckZKRGVqMzVpaDlTMDU0Q0lVemMzLUxFblYwQkIxcFFvalhLYng4bVdZbUhqTnFDSDFweU93akx6V3ViVXF5cEtCbk9QSFJQTjNobXRLQUpPTGNuSlc3UkVfNGdnQ0hWbXJldU11M3hadi1FU1o5azNRZ3pIUldvMkV3b1FQYVktMldOcWZkVFhPcHI2QUdMOXQxOEY1aGN6TG13WW1yMjlQWHNYd0p5LTFkRGZqOHhHNlJIcW9pWU1VQ1k0Yy01VDRPQdIBgwJBVV95cUxOdVk4MlI1LWY0aGw5azFlQ3UtdkF1V2lVYjJBaC1UYUtRNi1FT1lTeWpTbG1jZ2dPeGtBVnFYcTdISXFqaUxJcnpuZ29EWml0UkJEN0VfeHRONWRtcGo5dG9ZTDhOWGlvemZrUWZHRWtxUVBwcFRaRno4UmpWSDIwdHh6Si1LbFFDS1E3R3hvTTRGSFA4T256enl3RjBfb1hWNEFaTEkyOHJNRXBMVng1YnJMd01TMW51ZGhta1dRRmNnc3p4TC0xa2lsMDVOQ3VoZFZzUzRGV2IzYTVzajR1Mm11ZXZ6NkNfNjJjSG5iOVNmSkVXaWozaDNwaHVTNS1MNjRF?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 02:38", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields \u2014 Five Key Factors For Sensex, Nifty 50 On Sept 24", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxNMHRUa21iWVZtelA2Um13ZTJ6ZDhOSGNJMlcyandCLUFTT0w0V3R5eWd5SEdCZ1pyOEMwSlY3ak42dHRhUjdnREc5UzdaNmI3QnFkd2RsLUk0SmhaRGNqOS1QdWp0ZVdnOExERTduSHhXZlpFb2ZHaHVneDFmaGdpVTAwa3I4RWxTT3NxUHp5ekV2YTlVd3ltNS1FLTdKN19nUzBFaHB2a1Etd0xVb0NMVDJMaG5RcGlDMDhhLUJqOWFoTmFEdXFCbDZ0SlAwTmlheHZuWEZ5dGJJdW1LQ2dGeTVtNS15Z0tmR1B2YXZ0eDR6YlFBUFRIUlRVLTZ2ZTjSAYcCQVVfeXFMTVJoelZ4TXkyUmNUWkk2RThDUWRtT1RrS0dqQUtzTHJTM1RZX0w5ZHl3b0xicjN6Z1IxS2dQUV94YWdwRGpyME1rZmVaZnZ6SGE1bW5sUlM3N2ZBYl9lajJub1AwcjJLYUc1d3pHUG5HLWUtc1VFVlc3Z0FVNXI1anMwNzA5MkZvd1YzdTRUNHpRZTBBSWpqcm05bUp0ZmxNZklyNU9LS0l0NG9uSWZCRkhYenIzaktxa3Bic25SYzVfVVdPcko2ZG95YWhraURGZ212MDJBVHBCVWxXUWVQVzZZLTFIZmVGdkdsNHF3aTNOclNEMUEtSjNsUHFCZU5JSlA5bE1aZGs?oc=5", "source": "NDTV Profit", "published": "2026-09-24 01:42", "score": 0.844, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQTDl3ZlJyNW5xZXBBLUtBLXRfSU5kbEdSOXFWM3V2RU51eVdlanIzclZnczhweGRBR1lmWkVUNWI0SlBsbW5tWmd4SzBzNXA0Ty15d21DNVJkQ0piMXpzMDYxYkNndEtmV19UQnV6NVBKZlgzU1ltZEpEakJ5dVl3WU8xQS1DRVQxN0pxV1NuU19RaGZhTWNqSHFhRHFGUVROWDhEMkxhODZ2bmZFX1piMDl0ZzVJSVRhUU5KUC1pV0NCclR5dGxXXzR1VUNvbHMweU1xaHRIQWNIRG5HN1o4NWNlRlBlRjhRVFc2SElTNklUNEtMSXBZVmQ1YkxBOFg2eWtOOFZiMUTSAY4CQVVfeXFMTUdPNHFyRDVseGxVX1p5RDdOWFBabmJQdm1ZNmVZOVB0RGZMeERCSnFfZUMxV3FrMXBJT1liYmFZekEzWGR4cUs4eDlKOUhiNURta2xDLTM0dUFkRTJrOHNaa0djNnlJWFpQcE43OGt0SkFJNEgxSm9hd0puemtzNVgyX3dHdUtGa1VIRHJBdFllRUFmYlYwQ3Y4elV1djY2ZUo5R204dmZyZ3RwaGdZSHZrbERxQWZfRlhCUEhrZjdaelZGLXZmY2lTWm84ek9wWHYzdGRKQVFOR3pYWU94RUVERlBYOXFEeDJaUVI1and2N1hCenc4anc0NVVaRG50TF9Pa1o2di0xc3k3SDdn?oc=5", "source": "Livemint", "published": "2026-09-24 01:17", "score": 0.842, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs stock gains 1.37 percent as profit jumps 126 percent", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRGZMMkVQZFBodEJ4cHVqbng0YWJyNHJjbndja3pLdkJzamNORjlNUGNab3A1MDczV2piSTRpUG5yeklwV2ZvMWlFMGp2OVota2lsTHJoZlB6dG10UlBHeXRYNTk5NlRLVVduSzZJM0dLdFlTN2hkM29mWnhNU3lHVUlaTmlGQ25fUFo0dXhGT2cyNWlhQmllc3hiRFU3Z1RIN01VV0xHOFBTMUtoWUQxTDZUY2J0VTNxRXYyb2xhQ3c?oc=5", "source": "AD HOC NEWS", "published": "2026-09-23 22:57", "score": 0.791, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUE9BMFBTZkQ0bmQwWjZyUG4tSWp1VU1ERG50V2ptaVRoamFQX21HUDNBVmdwOG81TjVLeU1GSUZoNGIzUU5Vc0drSzhsMlZkOFl4MmstUEMyZWdYTTNING9fVnZrR0ZvS3VCYmJaVEk5aFdJRUJNWTZMMlV5Sy1iaU5ieC05WjZtaFJaQmMyaU5jTW9Oc1pmZHFsaUl3aVJ6TUJTR0s3SjYtdnE4c0NDejFJOFprT0Z0Zm1RTGFsTFlFVTVvUHo3d0lpZk16R1NmVGczYlUzZGNXb0Mwd3RQUmxKR0pRcklfUl9XRVNyMEZBZ1Fxa2FsSWtGSllrV2QwSmRSVnBOMmQ?oc=5", "source": "The Economic Times", "published": "2026-09-23 12:57", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxOUExzY0ZPTTBDblhZUWV1SjVUZWd0amE1STlQN1N6bm9VajdoT2NVb1ZvVjJrcHg2WTNBYlI1SGkwMlVOU3o4NDY2ZVpRMHRkRUhVUWVaS0N5QUdNbzRLa1I4UkRhNkVwOWpaVVNxOHhFV0NxZFhGOUx4anFCRDlDb0ptMHlzWFhvTmhMTEFvSk1ybFBSTzA1SG1KQnczZVdTX1NmUktxYURuVTBFbk0ydGhjNVBNN1d0Q1lUWkZlQVBJWWJLd0NhVml5amI0STBVcEs5WW4tN1pTajJSbU1wYm5ydUdIUjdvSW04MWVkdl85NmpZVmVVVFl1YmxZaWxBTVB5bkhUSFVaMXFu0gGSAkFVX3lxTE5LZmlZbUxuSjFGRzllWHk1R0RmZ0tla0huTUZYM25TUGxFMXpWLU5rTXc0WXdXM3lTWW1nYUNmNTI2elJWcEhZOTRhZ3A2X2JOUHZ1XzBuSmRRX2ZsNGZrQVBkVDlFSExzbHc3Z0VPYjRTekszODB5QndnS1Q3NmVvRmpfdmc4QzhRcGZScWlZZ01KUE1ZVWZmSFQ0UnpKVFllOFZxY3ZIME1LX2xaZ2o5bUxoYkR6Q0JQTlN0b3ZWU19IRHRCaTRmdFZLVXo1dG1oODdLOWJhSkQ4akVrODVaQTUxZnZtLWxUNDhyTGdxMDBkS3ExQXJwbnRPQlpxTFdReTZxNEtLWGRwNnIwTEhCcGc?oc=5", "source": "Livemint", "published": "2026-09-23 11:16", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPaHBTQzhTRUdZS2tNRmJlTDU1UXJ4bnYzUXZNY1RzZWhub0dSbFFIZDM3aGZCNFJ2V2F1QmJRX3lVelpSd2ZsTkZVTF9ncUZCZ1NYblZYUjBYNi13Z19fOVhDN19taGt4MGV1Q1NtWEY4U0lrdnVXaUtFQm9TZTFUMGlzNWdoTUdBYWZxOUtWcG1idGJwOE10NTloS1hrdV9HN3lhLXZXWUh3dzA2TVVLcHRuRFJDVXdmUC1nV084LTVEV2N4OFRVQjU1Smg4Q2ktSTBKWmRCRGtRdWdWOEc5UGh0YWpOTUlNWmVyV2l0RC10T3d1YndQalotU0NWWDBqTDhn?oc=5", "source": "Upstox", "published": "2026-09-23 10:15", "score": 0.612, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure Share Price Rises 2.68% Today", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNbjd5UVZ4d3N3ZUtybnEyZW1MZ1R4T0NrS1JsMEhETFc5d2tyclFHRnV4bzQ1RVQyUkZvNnIwOURYdjdBUzZldEpRN0FBV29YLVZOTjlFalZfemVpUzBVZ3BZSDJxSVFqSmdCMDVfNVNVXy1ZZVJpZUZORHdmNUFzazBrdGVsOGVPN1ZMRmdyQ0U1X3kzS1ZNZU1mQQ?oc=5", "source": "Univest", "published": "2026-09-23 10:02", "score": 0.34, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs Share Price: one-year high and valuation view", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYU9VS2psbTA2SEFlWWF6NVFFbVRManpTcU0wUjJIbWRQdEU2S1JUeWVXWVUtSW1RNGp3VmdEZjRGYkdVYmFtV2tZd1BQLWJfT2ZHYzhXcFhMTVgwaDlmNmZkOHhaY0JiOEVaQmZmTk5FS1luRmcxeE9ZbGV3VDlqOWR4VFhCZEE?oc=5", "source": "Univest", "published": "2026-09-23 09:19", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQa2ZFOFYwaEJuQTl6N3NjWFFvMWUyUGdxNXlZNFJHVWxtcFNEenVuTlNieHRNX3RpY0dfNnNCUk1hMU9Ndk5Sckl3TVg1Z2lJYnFORjgtY0UySTc0WW5qVmV0bU5hd0UzTVM3OVdKUFNUUHdzbEhaTTNERlV0WTdFWTBYSnpadUhucV9mejJxMnNlZ2V2UzJaOVY0dHdfNWtMVWN3U0tkVVFuSUVSMnV5NjhTUUE5a2Zrc2xieTVkZEphNmVqSEQ1MmRqMEFKM2xwU1FCVkxkZ0VsdFZYazRiMDhKcEhsejFNOXgtSGo0bFRJWThyZkZaXzJVQWpwbklBNno4NE1QSzRfT001NktmddIBlgJBVV95cUxOdy1fS2JiOHZGWTlaelh4ak5fQTR6TU9lek4tN0tIODhtWjRtRkJmS2hhZHVLTmpSMkQ2T0dXNnk1VFlTdFRjcmE1b1dCQWYtSnVQRFh0Z1hsUUljNkZVeF9GQ2pSZmplX082cHlVWEx2aVQ0dWpyZndmREdSOUJmcHBfczhYU0ZjUVVWYU96N1J0SENVQV8tR243REJnYzZwcnNzTlFnakJWcmV6eU9yTUs3NC1FWVpwRnFiZTRrUVVtM1UxQy01YnNsN1BweXNTbGpkb1l1UTNTRzNDUDEtWjBOeVJsa2QtejEtRElXcy1LNXc5bW5FY0Q4TGhXQXNWWlgxRjlXQlNEQ1R0V1B2OVZqWHluUQ?oc=5", "source": "The Times of India", "published": "2026-09-23 07:59", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks Share Price news: price rise and valuation", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNS3pobG5zQUpFLU53cFlCQWxZTFQ5S0E1dDNmbTU3V2daQUx1ZTMxMjctRHphNW5OSWVoYk9UY09CU2NxbF9GWjVCZDJzeF9OTXVTX3NUYVRjZ1U3ekZnLVFxZ01Sc3dVWlZIcnZOdXdvTzVlNTdoMlhYaVZZaWNaTEpZTkxpZw?oc=5", "source": "Univest", "published": "2026-09-23 07:26", "score": 0.0, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQThVQlhqMHhQX1dCbzk5aTVLRzAzLVhTQ0kzajBZMXRVTTNTazhRNTM3Y2d5SE1fbUhYVkJkT0hDeDlCZFhGRHEtWUxEcEhISzA4bkNGUlQ2RW44NEdPa1k5VFF5MGktRHhhZHJMRjAyeUVCVmEwWkVIQ2ROQmlhdTZTY255RFg2Rkp4NWtCTk1vaGxrUFc1VTRFSkJFY1Nnakd4VXpMNGxRVkpvMkl5VnpmakQtMWgwcV90RFpwM3BwaFFfNzhsR3IzQWhRNmpCWVVjdVM1ZExSSkxZR1N1bEpNaUp0eGV5bGIyTDQzZTZjdw?oc=5", "source": "The Economic Times", "published": "2026-09-23 06:24", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPa2tacGJLRFdET1pPVlhxQlRodHp4ZVZkREJLUU8yQlFiSmdib0hReElVbW5Qc2QtMnFqZWVDREFveHlPbDB5MHhGQjlBcTVfMS12Q1hyNGRFUjZrOHY0Ym9jSGhaSnV4YlZYZDZGV25jb1NtRV9admFLQWN1N1NETF9pUU1GbFFadFVXdzJ0dUxJelU3SFlaQUR0MlZxTWxHaDQ2SnpjRl9LczRSQ1BiX2h6SWl3ckJiek5mSDVwNm84cVVBYnRCSnFPYWRHLUlhUUlwb2cyN0tGdHRGU2lNdnVkdlNQZGJS0gHuAUFVX3lxTFBtQmV3OHlXVURIb1VpaGFmZnYtYjJnSFVyVjEtM2pvajJYV3BZQlZDOGtuOEZ4dG9hMDNkQmJVaXJPODNLdFdBMHJVdmRoTkRkR1NERk5DaWRlNXgyMUJmNDkzYXZzWVUwSzlIZ29CX3BueG8ySTU4Ymlod19HTFVJM1k2X1FDMmFpLXJPa3YtVjlSdi0tdjJ4UVc3MHZGR1ljSTJHdENmV0MwOHhJdmgyTEZBV0ZUN1JVR2gxOFhXSXBHdXlWTVYxT2RMdkhnY3UtN3FXOGd1UUtZYWRaWXVIR193bmsydVZRVnJNV0E?oc=5", "source": "simplywall.st", "published": "2026-09-23 05:56", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNUnltRmdqM0NYQ2wzZWItS3BOdjdlU1pUcFJ6aEtPV1Zub1hfcVR0MERkbjZzTWpuc3pFdFVxUFBSY3U5WEhLVjdOLV9tX2lSWG1yNjJzUzVWR2xhRFJ1NUctcDN6VlJtMGlZaGlpQWx3T3RBYWs0ZExick04cTBYd0tYY1dBcTV2MjFVTUtsWFdtY3NZMFFiVjYyM0JpSmpNUWVzSVJqRGpUMzUyRHc2dm1yZEgyRmNnQmpjbDFYaXZkV3NPaXgxM2ZFWGtoemxNWU9STmpkUVlSa3oydXk5bjJpMWFRWlNqM2J5Y2lCMTB4d0FoTGFNNdIBgAJBVV95cUxQYm1wblRHcjNRcnF0MG5Uel9qVFEycDNoSzNfQWx4WWoweVQzX3d3Ym5UTTM3cjVzUG9STkdXYmlzc1psbE10cUNKYTBGVlZPaTh4bEFkN0szUHJmS2wzYzRmazBKT2MxY29WZUxaWVhmdjVEbS1TU0NyeFlRVGFEbXk3R2R3OFJYc0s1bTZmbzJGZ1hDRWE4Z05Wa2lPT0FiWWRvaFlRWFFkaDNoYnBmazJfYVlhblBVMF8yMDlfVllVdk9BeVZKUzRVSXUwNUlxOE9LUVZENWw2LW8yNGhWX3VnaUxSZC04bDljRXJGZUE0RlgycFlabTVrRDVoYy1W?oc=5", "source": "NDTV Profit", "published": "2026-09-23 01:42", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxNNi1kLW5uekpsdjNub29Fa3NDaWEzNU91MUMxNGZMS1ZVeEZPZ2tiLWZWY1M4MW84dTRYRl93QjFISTVtSG9oUHRpLUZZcE9welgydkFGTDZPRWtBbXVkaC1xOVgtWnhuNVZNVklETHgyNFdOMEo3UWFjUWx4dzI0ZlZDbXJ3cEdKMTFWZkNoeVo1OXlpUG1iLXhIUkREVElXLWozbkxtUWtmWXFxc043VHB2R0NpU2dQVVVGZlNWeXNkbVItSGk0VGZ5M202QUVzckd5bFliQUtMbE5SZ2NURVNsZW50aFZnd1RsQkJoRGVHUklpNF9iRGxCbE5XamlvWnZyVUNIM3NrdkZiYjI1MjFB0gGXAkFVX3lxTE1waWJFallWREMwLVdIUXFpMDlzd1loMmViNEdDbzVfbTJoSUxubGpLVy1NZjU1c2taUzdsczJIaG9OSmpIVFc5bUlyRjZQdzZkWVZKeVlwMG9GTTI1N0dHV09ucTJJX0hQUS1rUGtMLXhVTkNXQjNpNDVYVTQ1TmxtMmVWWGx0UVhpTDhmSGdCNlNma19TQTZadDlPa0RjZ2RfQ1dLaXFHMVZtdjNPRzFhdGVnMFYydnNJR3VGWEJiTHVvNW11dV9SbzNiaU1fSEJLeUpVY0R3UnBZbWp3NTNZN2NwU3ZFMzVhME9XVjI0cWdvdW1DZno2ZHVkTWFwMkRDUUkwdVRsYW5XQkx6M0gwX2tJYWJacw?oc=5", "source": "Livemint", "published": "2026-09-23 01:13", "score": 0.557, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPeE5EWjI1ZEd2aG02OThzbUpNSXdERzVpYkNmNXRCdEFNLU1JUEk2RG9IanhndHM2N1oxMDAwblVrcXpSaVFfcmc0WEF6UUJqd09acWZQYXdzM2cwZFJkUVZVSkE5Tk9WWnhJV0ZXR19HN18tRFhCU2hqWXR5a3lBazR6UWN4UDJ0VEh3NGFxNE1oX3M2Sjhib0h5N0RvMGdUcU9zVm91ODRoaGl2dVJXc18xTnJObk9pS3BfX1lQWS1HWGUzR0lEbDZ1ZTZ1b1FlY0h6SnBCRdIB3AFBVV95cUxQbHN0Tmw0M3l2RFNtTzBTaEtMbzJ5WmE3cWRraUhSRTc3ejR4SUE2NDBvTEhqMTZPQmktdXJ5N3VwM2ZudzBPTU8zZU1tLUVIUFlVVDdCbGFaZGllcHA5UmEzLUpOU2RlU2c0YzlrTUk4ejU3UUxQM2hXTWlsU0p5eVh0blVNMmdpcERxXzFnZ1d2R3lzUzE2c21vOGxBWGlIMnR1Z25MQTlITTI4S3JIcU56YU5VVHVyUXVSU3JHZ3ZiVnZFLWVFbmR0S0dHTHVqOGw2QlZrZzg5bDFT?oc=5", "source": "simplywall.st", "published": "2026-09-23 00:46", "score": 0.0, "label": "Neutral"}], "errors": []}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T17:07:39", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view":</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}, "telegram_sent": "2026-09-28", "corp_actions": []}</t>
         </is>
       </c>
     </row>

--- a/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
+++ b/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
@@ -1498,7 +1498,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 17:07</t>
+          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 18:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 17:07</t>
+          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 18:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10196,7 +10196,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fetched 2026-09-29 17:07</t>
+          <t>Fetched 2026-09-29 18:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10356,25 +10356,25 @@
       </c>
       <c r="B8" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 11:14</t>
+          <t>2026-09-29 11:26</t>
         </is>
       </c>
       <c r="C8" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%</t>
+          <t>Stock market today, Sept 29: 227 securities hit 52-week low on NSE; Waaree Energies, Canara Bank, Britannia on list</t>
         </is>
       </c>
       <c r="D8" s="51" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>upstox.com</t>
         </is>
       </c>
       <c r="E8" s="81" t="n">
-        <v>0.226</v>
+        <v>0.103</v>
       </c>
       <c r="F8" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G8" s="82" t="inlineStr">
@@ -10391,25 +10391,25 @@
       </c>
       <c r="B9" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 10:48</t>
+          <t>2026-09-29 11:14</t>
         </is>
       </c>
       <c r="C9" s="51" t="inlineStr">
         <is>
-          <t>Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh</t>
+          <t>Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%</t>
         </is>
       </c>
       <c r="D9" s="51" t="inlineStr">
         <is>
-          <t>DD India</t>
+          <t>APAC Media</t>
         </is>
       </c>
       <c r="E9" s="81" t="n">
-        <v>-0.34</v>
+        <v>0.226</v>
       </c>
       <c r="F9" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G9" s="82" t="inlineStr">
@@ -10426,25 +10426,25 @@
       </c>
       <c r="B10" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 10:19</t>
+          <t>2026-09-29 10:48</t>
         </is>
       </c>
       <c r="C10" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%</t>
+          <t>Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh</t>
         </is>
       </c>
       <c r="D10" s="51" t="inlineStr">
         <is>
-          <t>equitymaster.com</t>
+          <t>DD India</t>
         </is>
       </c>
       <c r="E10" s="81" t="n">
-        <v>0.226</v>
+        <v>-0.34</v>
       </c>
       <c r="F10" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G10" s="82" t="inlineStr">
@@ -10461,21 +10461,21 @@
       </c>
       <c r="B11" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 10:11</t>
+          <t>2026-09-29 10:19</t>
         </is>
       </c>
       <c r="C11" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026</t>
+          <t>Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E11" s="81" t="n">
-        <v>0.402</v>
+        <v>0.226</v>
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
@@ -10496,12 +10496,12 @@
       </c>
       <c r="B12" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 06:14</t>
+          <t>2026-09-29 10:11</t>
         </is>
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty rebound from near six-month lows amid crude shock</t>
+          <t>Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026</t>
         </is>
       </c>
       <c r="D12" s="51" t="inlineStr">
@@ -10510,11 +10510,11 @@
         </is>
       </c>
       <c r="E12" s="81" t="n">
-        <v>-0.66</v>
+        <v>0.402</v>
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G12" s="82" t="inlineStr">
@@ -10531,21 +10531,21 @@
       </c>
       <c r="B13" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 05:26</t>
+          <t>2026-09-29 06:14</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
         <is>
-          <t>Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows</t>
+          <t>Sensex, Nifty rebound from near six-month lows amid crude shock</t>
         </is>
       </c>
       <c r="D13" s="51" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E13" s="81" t="n">
-        <v>-0.599</v>
+        <v>-0.66</v>
       </c>
       <c r="F13" s="51" t="inlineStr">
         <is>
@@ -10566,21 +10566,21 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 05:23</t>
+          <t>2026-09-29 05:26</t>
         </is>
       </c>
       <c r="C14" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons</t>
+          <t>Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows</t>
         </is>
       </c>
       <c r="D14" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E14" s="81" t="n">
-        <v>-0.382</v>
+        <v>-0.599</v>
       </c>
       <c r="F14" s="51" t="inlineStr">
         <is>
@@ -10601,21 +10601,21 @@
       </c>
       <c r="B15" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 05:09</t>
+          <t>2026-09-29 05:23</t>
         </is>
       </c>
       <c r="C15" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600</t>
+          <t>Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E15" s="81" t="n">
-        <v>-0.791</v>
+        <v>-0.382</v>
       </c>
       <c r="F15" s="51" t="inlineStr">
         <is>
@@ -10636,21 +10636,21 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 05:06</t>
+          <t>2026-09-29 05:09</t>
         </is>
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for</t>
+          <t>Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E16" s="81" t="n">
-        <v>-0.459</v>
+        <v>-0.791</v>
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
@@ -10671,25 +10671,25 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:38</t>
+          <t>2026-09-29 05:06</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle</t>
+          <t>Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E17" s="81" t="n">
-        <v>0.71</v>
+        <v>-0.459</v>
       </c>
       <c r="F17" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G17" s="82" t="inlineStr">
@@ -10706,25 +10706,25 @@
       </c>
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:35</t>
+          <t>2026-09-29 04:38</t>
         </is>
       </c>
       <c r="C18" s="51" t="inlineStr">
         <is>
-          <t>Sensex Falls 400 Points; Nifty Slips Below 22,700</t>
+          <t>BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle</t>
         </is>
       </c>
       <c r="D18" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="E18" s="81" t="n">
-        <v>-0.318</v>
+        <v>0.71</v>
       </c>
       <c r="F18" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G18" s="82" t="inlineStr">
@@ -10746,16 +10746,16 @@
       </c>
       <c r="C19" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+          <t>Sensex Falls 400 Points; Nifty Slips Below 22,700</t>
         </is>
       </c>
       <c r="D19" s="51" t="inlineStr">
         <is>
-          <t>equitymaster.com</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E19" s="81" t="n">
-        <v>-0.477</v>
+        <v>-0.318</v>
       </c>
       <c r="F19" s="51" t="inlineStr">
         <is>
@@ -10771,30 +10771,30 @@
     <row r="20">
       <c r="A20" s="51" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B20" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:23</t>
+          <t>2026-09-29 04:35</t>
         </is>
       </c>
       <c r="C20" s="51" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price News: Today’s Decline Analyzed</t>
+          <t>Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
         </is>
       </c>
       <c r="D20" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E20" s="81" t="n">
-        <v>-0.128</v>
+        <v>-0.477</v>
       </c>
       <c r="F20" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G20" s="82" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="21">
       <c r="A21" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B21" s="51" t="inlineStr">
@@ -10816,16 +10816,16 @@
       </c>
       <c r="C21" s="51" t="inlineStr">
         <is>
-          <t>Oil rise, bond yields: Top factors behind Tuesday's stock market fall</t>
+          <t>Ather Energy Share Price News: Today’s Decline Analyzed</t>
         </is>
       </c>
       <c r="D21" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E21" s="81" t="n">
-        <v>-0.153</v>
+        <v>-0.128</v>
       </c>
       <c r="F21" s="51" t="inlineStr">
         <is>
@@ -10846,25 +10846,25 @@
       </c>
       <c r="B22" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:21</t>
+          <t>2026-09-29 04:23</t>
         </is>
       </c>
       <c r="C22" s="51" t="inlineStr">
         <is>
-          <t>No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what’s dragging the market?</t>
+          <t>Oil rise, bond yields: Top factors behind Tuesday's stock market fall</t>
         </is>
       </c>
       <c r="D22" s="51" t="inlineStr">
         <is>
-          <t>fortuneindia.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E22" s="81" t="n">
-        <v>-0.402</v>
+        <v>-0.153</v>
       </c>
       <c r="F22" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G22" s="82" t="inlineStr">
@@ -10886,20 +10886,20 @@
       </c>
       <c r="C23" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty sink further; What is keeping the market under pressure?</t>
+          <t>No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what’s dragging the market?</t>
         </is>
       </c>
       <c r="D23" s="51" t="inlineStr">
         <is>
-          <t>newsdrum.in</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="E23" s="81" t="n">
-        <v>0.128</v>
+        <v>-0.402</v>
       </c>
       <c r="F23" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G23" s="82" t="inlineStr">
@@ -10916,25 +10916,25 @@
       </c>
       <c r="B24" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:14</t>
+          <t>2026-09-29 04:21</t>
         </is>
       </c>
       <c r="C24" s="51" t="inlineStr">
         <is>
-          <t>Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street</t>
+          <t>Sensex, Nifty sink further; What is keeping the market under pressure?</t>
         </is>
       </c>
       <c r="D24" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>newsdrum.in</t>
         </is>
       </c>
       <c r="E24" s="81" t="n">
-        <v>-0.273</v>
+        <v>0.128</v>
       </c>
       <c r="F24" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G24" s="82" t="inlineStr">
@@ -10951,21 +10951,21 @@
       </c>
       <c r="B25" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:02</t>
+          <t>2026-09-29 04:14</t>
         </is>
       </c>
       <c r="C25" s="51" t="inlineStr">
         <is>
-          <t>Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...</t>
+          <t>Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street</t>
         </is>
       </c>
       <c r="D25" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E25" s="81" t="n">
-        <v>-0.421</v>
+        <v>-0.273</v>
       </c>
       <c r="F25" s="51" t="inlineStr">
         <is>
@@ -10986,25 +10986,25 @@
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:01</t>
+          <t>2026-09-29 04:02</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr">
         <is>
-          <t>Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How</t>
+          <t>Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...</t>
         </is>
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E26" s="81" t="n">
-        <v>0.214</v>
+        <v>-0.421</v>
       </c>
       <c r="F26" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G26" s="82" t="inlineStr">
@@ -11021,25 +11021,25 @@
       </c>
       <c r="B27" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 02:57</t>
+          <t>2026-09-29 04:01</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty opening: Will stock market crash or open higher today?</t>
+          <t>Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How</t>
         </is>
       </c>
       <c r="D27" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="E27" s="81" t="n">
-        <v>-0.273</v>
+        <v>0.214</v>
       </c>
       <c r="F27" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G27" s="82" t="inlineStr">
@@ -11056,25 +11056,25 @@
       </c>
       <c r="B28" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:36</t>
+          <t>2026-09-29 02:57</t>
         </is>
       </c>
       <c r="C28" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
+          <t>Sensex, Nifty opening: Will stock market crash or open higher today?</t>
         </is>
       </c>
       <c r="D28" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E28" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.273</v>
       </c>
       <c r="F28" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G28" s="82" t="inlineStr">
@@ -11091,21 +11091,21 @@
       </c>
       <c r="B29" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:19</t>
+          <t>2026-09-29 01:36</t>
         </is>
       </c>
       <c r="C29" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
         </is>
       </c>
       <c r="D29" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E29" s="81" t="n">
-        <v>0.842</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F29" s="51" t="inlineStr">
         <is>
@@ -11126,25 +11126,25 @@
       </c>
       <c r="B30" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 19:51</t>
+          <t>2026-09-29 01:19</t>
         </is>
       </c>
       <c r="C30" s="51" t="inlineStr">
         <is>
-          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D30" s="51" t="inlineStr">
         <is>
-          <t>wionews.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E30" s="81" t="n">
-        <v>-0.34</v>
+        <v>0.842</v>
       </c>
       <c r="F30" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G30" s="82" t="inlineStr">
@@ -11161,25 +11161,25 @@
       </c>
       <c r="B31" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 17:36</t>
+          <t>2026-09-28 19:51</t>
         </is>
       </c>
       <c r="C31" s="51" t="inlineStr">
         <is>
-          <t>Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens</t>
+          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
         </is>
       </c>
       <c r="D31" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>wionews.com</t>
         </is>
       </c>
       <c r="E31" s="81" t="n">
-        <v>0.026</v>
+        <v>-0.34</v>
       </c>
       <c r="F31" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G31" s="82" t="inlineStr">
@@ -11196,25 +11196,25 @@
       </c>
       <c r="B32" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42</t>
+          <t>2026-09-28 17:36</t>
         </is>
       </c>
       <c r="C32" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
+          <t>Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens</t>
         </is>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E32" s="81" t="n">
-        <v>-0.896</v>
+        <v>0.026</v>
       </c>
       <c r="F32" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G32" s="82" t="inlineStr">
@@ -11226,30 +11226,30 @@
     <row r="33">
       <c r="A33" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B33" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 13:25</t>
+          <t>2026-09-28 13:42</t>
         </is>
       </c>
       <c r="C33" s="51" t="inlineStr">
         <is>
-          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
+          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
         </is>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>equitymaster.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E33" s="81" t="n">
-        <v>0.652</v>
+        <v>-0.896</v>
       </c>
       <c r="F33" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G33" s="82" t="inlineStr">
@@ -11261,26 +11261,26 @@
     <row r="34">
       <c r="A34" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B34" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 13:16</t>
+          <t>2026-09-28 13:25</t>
         </is>
       </c>
       <c r="C34" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
+          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
         </is>
       </c>
       <c r="D34" s="51" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E34" s="81" t="n">
-        <v>0.361</v>
+        <v>0.652</v>
       </c>
       <c r="F34" s="51" t="inlineStr">
         <is>
@@ -11296,30 +11296,30 @@
     <row r="35">
       <c r="A35" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B35" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 11:48</t>
+          <t>2026-09-28 13:16</t>
         </is>
       </c>
       <c r="C35" s="51" t="inlineStr">
         <is>
-          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
         </is>
       </c>
       <c r="D35" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="E35" s="81" t="n">
-        <v>0.153</v>
+        <v>0.361</v>
       </c>
       <c r="F35" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G35" s="82" t="inlineStr">
@@ -11331,30 +11331,30 @@
     <row r="36">
       <c r="A36" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B36" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:56</t>
+          <t>2026-09-28 11:48</t>
         </is>
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
+          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>equitymaster.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E36" s="81" t="n">
-        <v>-0.273</v>
+        <v>0.153</v>
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G36" s="82" t="inlineStr">
@@ -11371,21 +11371,21 @@
       </c>
       <c r="B37" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:48</t>
+          <t>2026-09-28 10:56</t>
         </is>
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge</t>
+          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
         </is>
       </c>
       <c r="D37" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E37" s="81" t="n">
-        <v>-0.7</v>
+        <v>-0.273</v>
       </c>
       <c r="F37" s="51" t="inlineStr">
         <is>
@@ -11406,21 +11406,21 @@
       </c>
       <c r="B38" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:46</t>
+          <t>2026-09-28 10:48</t>
         </is>
       </c>
       <c r="C38" s="51" t="inlineStr">
         <is>
-          <t>Sensex Falls 1,124 Points, Nifty Slips Below 22,800</t>
+          <t>Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge</t>
         </is>
       </c>
       <c r="D38" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="E38" s="81" t="n">
-        <v>-0.318</v>
+        <v>-0.7</v>
       </c>
       <c r="F38" s="51" t="inlineStr">
         <is>
@@ -11441,21 +11441,21 @@
       </c>
       <c r="B39" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:26</t>
+          <t>2026-09-28 10:46</t>
         </is>
       </c>
       <c r="C39" s="51" t="inlineStr">
         <is>
-          <t>Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low</t>
+          <t>Sensex Falls 1,124 Points, Nifty Slips Below 22,800</t>
         </is>
       </c>
       <c r="D39" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E39" s="81" t="n">
-        <v>-0.612</v>
+        <v>-0.318</v>
       </c>
       <c r="F39" s="51" t="inlineStr">
         <is>
@@ -11476,25 +11476,25 @@
       </c>
       <c r="B40" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:15</t>
+          <t>2026-09-28 10:26</t>
         </is>
       </c>
       <c r="C40" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
+          <t>Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E40" s="81" t="n">
-        <v>0.402</v>
+        <v>-0.612</v>
       </c>
       <c r="F40" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G40" s="82" t="inlineStr">
@@ -11506,30 +11506,30 @@
     <row r="41">
       <c r="A41" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B41" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:06</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="C41" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
         </is>
       </c>
       <c r="D41" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E41" s="81" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F41" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G41" s="82" t="inlineStr">
@@ -11541,26 +11541,26 @@
     <row r="42">
       <c r="A42" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B42" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:05</t>
+          <t>2026-09-28 10:06</t>
         </is>
       </c>
       <c r="C42" s="51" t="inlineStr">
         <is>
-          <t>Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top losers</t>
+          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
         </is>
       </c>
       <c r="D42" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E42" s="81" t="n">
-        <v>-0.178</v>
+        <v>0</v>
       </c>
       <c r="F42" s="51" t="inlineStr">
         <is>
@@ -11576,26 +11576,26 @@
     <row r="43">
       <c r="A43" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B43" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 08:20</t>
+          <t>2026-09-28 10:05</t>
         </is>
       </c>
       <c r="C43" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?</t>
+          <t>Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top losers</t>
         </is>
       </c>
       <c r="D43" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E43" s="81" t="n">
-        <v>0</v>
+        <v>-0.178</v>
       </c>
       <c r="F43" s="51" t="inlineStr">
         <is>
@@ -11611,30 +11611,30 @@
     <row r="44">
       <c r="A44" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B44" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 08:15</t>
+          <t>2026-09-28 08:20</t>
         </is>
       </c>
       <c r="C44" s="51" t="inlineStr">
         <is>
-          <t>Nifty, Sensex: History favours stock market comeback in October; stocks to watch</t>
+          <t>E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?</t>
         </is>
       </c>
       <c r="D44" s="51" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E44" s="81" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="F44" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G44" s="82" t="inlineStr">
@@ -11651,25 +11651,25 @@
       </c>
       <c r="B45" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 08:03</t>
+          <t>2026-09-28 08:15</t>
         </is>
       </c>
       <c r="C45" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
+          <t>Nifty, Sensex: History favours stock market comeback in October; stocks to watch</t>
         </is>
       </c>
       <c r="D45" s="51" t="inlineStr">
         <is>
-          <t>Free Press Kashmir</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="E45" s="81" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="F45" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G45" s="82" t="inlineStr">
@@ -11686,25 +11686,25 @@
       </c>
       <c r="B46" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 08:03</t>
         </is>
       </c>
       <c r="C46" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?</t>
+          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
         </is>
       </c>
       <c r="D46" s="51" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>Free Press Kashmir</t>
         </is>
       </c>
       <c r="E46" s="81" t="n">
-        <v>-0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G46" s="82" t="inlineStr">
@@ -11721,25 +11721,25 @@
       </c>
       <c r="B47" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:44</t>
+          <t>2026-09-28 07:56</t>
         </is>
       </c>
       <c r="C47" s="51" t="inlineStr">
         <is>
-          <t>Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts</t>
+          <t>Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?</t>
         </is>
       </c>
       <c r="D47" s="51" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="E47" s="81" t="n">
-        <v>0</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="F47" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G47" s="82" t="inlineStr">
@@ -11756,25 +11756,25 @@
       </c>
       <c r="B48" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:36</t>
+          <t>2026-09-28 07:44</t>
         </is>
       </c>
       <c r="C48" s="51" t="inlineStr">
         <is>
-          <t>September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets</t>
+          <t>Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts</t>
         </is>
       </c>
       <c r="D48" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>APAC Media</t>
         </is>
       </c>
       <c r="E48" s="81" t="n">
-        <v>-0.806</v>
+        <v>0</v>
       </c>
       <c r="F48" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G48" s="82" t="inlineStr">
@@ -11791,21 +11791,21 @@
       </c>
       <c r="B49" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:06</t>
+          <t>2026-09-28 07:36</t>
         </is>
       </c>
       <c r="C49" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800</t>
+          <t>September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets</t>
         </is>
       </c>
       <c r="D49" s="51" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>upstox.com</t>
         </is>
       </c>
       <c r="E49" s="81" t="n">
-        <v>-0.402</v>
+        <v>-0.806</v>
       </c>
       <c r="F49" s="51" t="inlineStr">
         <is>
@@ -11826,21 +11826,21 @@
       </c>
       <c r="B50" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 06:47</t>
+          <t>2026-09-28 07:06</t>
         </is>
       </c>
       <c r="C50" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
+          <t>Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800</t>
         </is>
       </c>
       <c r="D50" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="E50" s="81" t="n">
-        <v>-0.791</v>
+        <v>-0.402</v>
       </c>
       <c r="F50" s="51" t="inlineStr">
         <is>
@@ -11861,21 +11861,21 @@
       </c>
       <c r="B51" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 06:40</t>
+          <t>2026-09-28 06:47</t>
         </is>
       </c>
       <c r="C51" s="51" t="inlineStr">
         <is>
-          <t>SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday’s market crash</t>
+          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
         </is>
       </c>
       <c r="D51" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E51" s="81" t="n">
-        <v>-0.595</v>
+        <v>-0.791</v>
       </c>
       <c r="F51" s="51" t="inlineStr">
         <is>
@@ -11891,26 +11891,26 @@
     <row r="52">
       <c r="A52" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B52" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:52</t>
+          <t>2026-09-28 06:40</t>
         </is>
       </c>
       <c r="C52" s="51" t="inlineStr">
         <is>
-          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
+          <t>SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday’s market crash</t>
         </is>
       </c>
       <c r="D52" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>upstox.com</t>
         </is>
       </c>
       <c r="E52" s="81" t="n">
-        <v>-0.382</v>
+        <v>-0.595</v>
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
     <row r="53">
       <c r="A53" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B53" s="51" t="inlineStr">
@@ -11936,16 +11936,16 @@
       </c>
       <c r="C53" s="51" t="inlineStr">
         <is>
-          <t>India VIX spikes 14% as oil, geopolitical risks trigger market sell-off</t>
+          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
         </is>
       </c>
       <c r="D53" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E53" s="81" t="n">
-        <v>-0.273</v>
+        <v>-0.382</v>
       </c>
       <c r="F53" s="51" t="inlineStr">
         <is>
@@ -11966,25 +11966,25 @@
       </c>
       <c r="B54" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:42</t>
+          <t>2026-09-28 05:52</t>
         </is>
       </c>
       <c r="C54" s="51" t="inlineStr">
         <is>
-          <t>Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern</t>
+          <t>India VIX spikes 14% as oil, geopolitical risks trigger market sell-off</t>
         </is>
       </c>
       <c r="D54" s="51" t="inlineStr">
         <is>
-          <t>India Infoline</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E54" s="81" t="n">
-        <v>0.103</v>
+        <v>-0.273</v>
       </c>
       <c r="F54" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G54" s="82" t="inlineStr">
@@ -11996,26 +11996,26 @@
     <row r="55">
       <c r="A55" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B55" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:37</t>
+          <t>2026-09-28 05:42</t>
         </is>
       </c>
       <c r="C55" s="51" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
+          <t>Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern</t>
         </is>
       </c>
       <c r="D55" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>India Infoline</t>
         </is>
       </c>
       <c r="E55" s="81" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="F55" s="51" t="inlineStr">
         <is>
@@ -12031,30 +12031,30 @@
     <row r="56">
       <c r="A56" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B56" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:18</t>
+          <t>2026-09-28 05:37</t>
         </is>
       </c>
       <c r="C56" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
         </is>
       </c>
       <c r="D56" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E56" s="81" t="n">
-        <v>-0.6909999999999999</v>
+        <v>0</v>
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G56" s="82" t="inlineStr">
@@ -12071,21 +12071,21 @@
       </c>
       <c r="B57" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:11</t>
+          <t>2026-09-28 05:18</t>
         </is>
       </c>
       <c r="C57" s="51" t="inlineStr">
         <is>
-          <t>Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties</t>
+          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
         </is>
       </c>
       <c r="D57" s="51" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E57" s="81" t="n">
-        <v>-0.852</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="F57" s="51" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:56</t>
+          <t>2026-09-28 05:11</t>
         </is>
       </c>
       <c r="C58" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+          <t>Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties</t>
         </is>
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>equitymaster.com</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E58" s="81" t="n">
-        <v>-0.477</v>
+        <v>-0.852</v>
       </c>
       <c r="F58" s="51" t="inlineStr">
         <is>
@@ -12141,21 +12141,21 @@
       </c>
       <c r="B59" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:51</t>
+          <t>2026-09-28 04:56</t>
         </is>
       </c>
       <c r="C59" s="51" t="inlineStr">
         <is>
-          <t>Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil</t>
+          <t>Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
         </is>
       </c>
       <c r="D59" s="51" t="inlineStr">
         <is>
-          <t>rediff.com</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E59" s="81" t="n">
-        <v>-0.586</v>
+        <v>-0.477</v>
       </c>
       <c r="F59" s="51" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:45</t>
+          <t>2026-09-28 04:51</t>
         </is>
       </c>
       <c r="C60" s="51" t="inlineStr">
         <is>
-          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
+          <t>Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil</t>
         </is>
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="E60" s="81" t="n">
-        <v>-0.361</v>
+        <v>-0.586</v>
       </c>
       <c r="F60" s="51" t="inlineStr">
         <is>
@@ -12211,21 +12211,21 @@
       </c>
       <c r="B61" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:42</t>
+          <t>2026-09-28 04:45</t>
         </is>
       </c>
       <c r="C61" s="51" t="inlineStr">
         <is>
-          <t>NSE stock slips below issue price of ₹1,785; down 2% on Monday</t>
+          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
         </is>
       </c>
       <c r="D61" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>hindustantimes.com</t>
         </is>
       </c>
       <c r="E61" s="81" t="n">
-        <v>-0.34</v>
+        <v>-0.361</v>
       </c>
       <c r="F61" s="51" t="inlineStr">
         <is>
@@ -12246,21 +12246,21 @@
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:41</t>
+          <t>2026-09-28 04:42</t>
         </is>
       </c>
       <c r="C62" s="51" t="inlineStr">
         <is>
-          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
+          <t>NSE stock slips below issue price of ₹1,785; down 2% on Monday</t>
         </is>
       </c>
       <c r="D62" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E62" s="81" t="n">
-        <v>-0.758</v>
+        <v>-0.34</v>
       </c>
       <c r="F62" s="51" t="inlineStr">
         <is>
@@ -12281,25 +12281,25 @@
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:29</t>
+          <t>2026-09-28 04:41</t>
         </is>
       </c>
       <c r="C63" s="51" t="inlineStr">
         <is>
-          <t>Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%</t>
+          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
         </is>
       </c>
       <c r="D63" s="51" t="inlineStr">
         <is>
-          <t>newsdrum.in</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="E63" s="81" t="n">
-        <v>0</v>
+        <v>-0.758</v>
       </c>
       <c r="F63" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G63" s="82" t="inlineStr">
@@ -12316,25 +12316,25 @@
       </c>
       <c r="B64" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:25</t>
+          <t>2026-09-28 04:29</t>
         </is>
       </c>
       <c r="C64" s="51" t="inlineStr">
         <is>
-          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
+          <t>Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%</t>
         </is>
       </c>
       <c r="D64" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>newsdrum.in</t>
         </is>
       </c>
       <c r="E64" s="81" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="F64" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G64" s="82" t="inlineStr">
@@ -12351,21 +12351,21 @@
       </c>
       <c r="B65" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:17</t>
+          <t>2026-09-28 04:25</t>
         </is>
       </c>
       <c r="C65" s="51" t="inlineStr">
         <is>
-          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
+          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
         </is>
       </c>
       <c r="D65" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E65" s="81" t="n">
-        <v>-0.511</v>
+        <v>-0.34</v>
       </c>
       <c r="F65" s="51" t="inlineStr">
         <is>
@@ -12386,21 +12386,21 @@
       </c>
       <c r="B66" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:11</t>
+          <t>2026-09-28 04:17</t>
         </is>
       </c>
       <c r="C66" s="51" t="inlineStr">
         <is>
-          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
+          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
         </is>
       </c>
       <c r="D66" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E66" s="81" t="n">
-        <v>-0.586</v>
+        <v>-0.511</v>
       </c>
       <c r="F66" s="51" t="inlineStr">
         <is>
@@ -12421,21 +12421,21 @@
       </c>
       <c r="B67" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:08</t>
+          <t>2026-09-28 04:11</t>
         </is>
       </c>
       <c r="C67" s="51" t="inlineStr">
         <is>
-          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l</t>
+          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
         </is>
       </c>
       <c r="D67" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E67" s="81" t="n">
-        <v>-0.649</v>
+        <v>-0.586</v>
       </c>
       <c r="F67" s="51" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
       </c>
       <c r="B68" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:07</t>
+          <t>2026-09-28 04:08</t>
         </is>
       </c>
       <c r="C68" s="51" t="inlineStr">
         <is>
-          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
+          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 lakh crore rout</t>
         </is>
       </c>
       <c r="D68" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E68" s="81" t="n">
-        <v>-0.44</v>
+        <v>-0.649</v>
       </c>
       <c r="F68" s="51" t="inlineStr">
         <is>
@@ -12486,30 +12486,30 @@
     <row r="69">
       <c r="A69" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B69" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:01</t>
+          <t>2026-09-28 04:07</t>
         </is>
       </c>
       <c r="C69" s="51" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines ESOP 2019 Share Allotment Explained</t>
+          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
         </is>
       </c>
       <c r="D69" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E69" s="81" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="F69" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G69" s="82" t="inlineStr">
@@ -12521,30 +12521,30 @@
     <row r="70">
       <c r="A70" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B70" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:58</t>
+          <t>2026-09-28 04:01</t>
         </is>
       </c>
       <c r="C70" s="51" t="inlineStr">
         <is>
-          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
+          <t>Kirloskar Oil Engines ESOP 2019 Share Allotment Explained</t>
         </is>
       </c>
       <c r="D70" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E70" s="81" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="F70" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G70" s="82" t="inlineStr">
@@ -12561,25 +12561,25 @@
       </c>
       <c r="B71" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:54</t>
+          <t>2026-09-28 03:58</t>
         </is>
       </c>
       <c r="C71" s="51" t="inlineStr">
         <is>
-          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
+          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
         </is>
       </c>
       <c r="D71" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E71" s="81" t="n">
-        <v>-0.494</v>
+        <v>0.296</v>
       </c>
       <c r="F71" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G71" s="82" t="inlineStr">
@@ -12596,21 +12596,21 @@
       </c>
       <c r="B72" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:48</t>
+          <t>2026-09-28 03:54</t>
         </is>
       </c>
       <c r="C72" s="51" t="inlineStr">
         <is>
-          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
+          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
         </is>
       </c>
       <c r="D72" s="51" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E72" s="81" t="n">
-        <v>-0.44</v>
+        <v>-0.494</v>
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
@@ -12631,25 +12631,25 @@
       </c>
       <c r="B73" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:28</t>
+          <t>2026-09-28 03:48</t>
         </is>
       </c>
       <c r="C73" s="51" t="inlineStr">
         <is>
-          <t>Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open</t>
+          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
         </is>
       </c>
       <c r="D73" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>hindustantimes.com</t>
         </is>
       </c>
       <c r="E73" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.44</v>
       </c>
       <c r="F73" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G73" s="82" t="inlineStr">
@@ -12666,25 +12666,25 @@
       </c>
       <c r="B74" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 02:19</t>
+          <t>2026-09-28 03:28</t>
         </is>
       </c>
       <c r="C74" s="51" t="inlineStr">
         <is>
-          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
+          <t>Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open</t>
         </is>
       </c>
       <c r="D74" s="51" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E74" s="81" t="n">
-        <v>-0.542</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G74" s="82" t="inlineStr">
@@ -12701,25 +12701,25 @@
       </c>
       <c r="B75" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 01:58</t>
+          <t>2026-09-28 02:19</t>
         </is>
       </c>
       <c r="C75" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices — Five Key Factors For Sensex, Nifty 50 On September 28</t>
+          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
         </is>
       </c>
       <c r="D75" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E75" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.542</v>
       </c>
       <c r="F75" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G75" s="82" t="inlineStr">
@@ -12736,21 +12736,21 @@
       </c>
       <c r="B76" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 01:20</t>
+          <t>2026-09-28 01:58</t>
         </is>
       </c>
       <c r="C76" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
+          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices — Five Key Factors For Sensex, Nifty 50 On September 28</t>
         </is>
       </c>
       <c r="D76" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E76" s="81" t="n">
-        <v>0.842</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F76" s="51" t="inlineStr">
         <is>
@@ -12766,26 +12766,26 @@
     <row r="77">
       <c r="A77" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B77" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 00:30</t>
+          <t>2026-09-28 01:20</t>
         </is>
       </c>
       <c r="C77" s="51" t="inlineStr">
         <is>
-          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
         </is>
       </c>
       <c r="D77" s="51" t="inlineStr">
         <is>
-          <t>equitymaster.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E77" s="81" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.842</v>
       </c>
       <c r="F77" s="51" t="inlineStr">
         <is>
@@ -12801,26 +12801,26 @@
     <row r="78">
       <c r="A78" s="51" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B78" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 17:20</t>
+          <t>2026-09-28 00:30</t>
         </is>
       </c>
       <c r="C78" s="51" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
+          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
         </is>
       </c>
       <c r="D78" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E78" s="81" t="n">
-        <v>0.625</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F78" s="51" t="inlineStr">
         <is>
@@ -12836,30 +12836,30 @@
     <row r="79">
       <c r="A79" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B79" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 11:03</t>
+          <t>2026-09-27 17:20</t>
         </is>
       </c>
       <c r="C79" s="51" t="inlineStr">
         <is>
-          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
+          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
         </is>
       </c>
       <c r="D79" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E79" s="81" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="F79" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G79" s="82" t="inlineStr">
@@ -12876,25 +12876,25 @@
       </c>
       <c r="B80" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 09:48</t>
+          <t>2026-09-27 11:03</t>
         </is>
       </c>
       <c r="C80" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
+          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
         </is>
       </c>
       <c r="D80" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E80" s="81" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="F80" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G80" s="82" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="B81" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 04:22</t>
+          <t>2026-09-27 09:48</t>
         </is>
       </c>
       <c r="C81" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
+          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
         </is>
       </c>
       <c r="D81" s="51" t="inlineStr">
@@ -12925,11 +12925,11 @@
         </is>
       </c>
       <c r="E81" s="81" t="n">
-        <v>0.842</v>
+        <v>-0.44</v>
       </c>
       <c r="F81" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G81" s="82" t="inlineStr">
@@ -12941,30 +12941,30 @@
     <row r="82">
       <c r="A82" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B82" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 22:56</t>
+          <t>2026-09-27 04:22</t>
         </is>
       </c>
       <c r="C82" s="51" t="inlineStr">
         <is>
-          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
+          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
         </is>
       </c>
       <c r="D82" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E82" s="81" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="F82" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G82" s="82" t="inlineStr">
@@ -12976,30 +12976,30 @@
     <row r="83">
       <c r="A83" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B83" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 13:51</t>
+          <t>2026-09-26 22:56</t>
         </is>
       </c>
       <c r="C83" s="51" t="inlineStr">
         <is>
-          <t>🚦 Indian Markets Stuck In A Jam! But who's responsible for the traffic? 🤔 A Bernstein note argues that India’s large caps are stuck in a bygone economic era. But here's the BIG question: 🇮🇳 Is The Market’s Fate Really In India’s Hands? 🌍 Or are global cues pul</t>
+          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
         </is>
       </c>
       <c r="D83" s="51" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E83" s="81" t="n">
-        <v>-0.625</v>
+        <v>0</v>
       </c>
       <c r="F83" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G83" s="82" t="inlineStr">
@@ -13016,25 +13016,25 @@
       </c>
       <c r="B84" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 12:11</t>
+          <t>2026-09-26 13:51</t>
         </is>
       </c>
       <c r="C84" s="51" t="inlineStr">
         <is>
-          <t>Share Market News: Nifty 50 Outlook &amp; Prediction</t>
+          <t>🚦 Indian Markets Stuck In A Jam! But who's responsible for the traffic? 🤔 A Bernstein note argues that India’s large caps are stuck in a bygone economic era. But here's the BIG question: 🇮🇳 Is The Market’s Fate Really In India’s Hands? 🌍 Or are global cues pul</t>
         </is>
       </c>
       <c r="D84" s="51" t="inlineStr">
         <is>
-          <t>Liquide Blog</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E84" s="81" t="n">
-        <v>0.402</v>
+        <v>-0.625</v>
       </c>
       <c r="F84" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G84" s="82" t="inlineStr">
@@ -13051,25 +13051,25 @@
       </c>
       <c r="B85" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 09:15</t>
+          <t>2026-09-26 12:11</t>
         </is>
       </c>
       <c r="C85" s="51" t="inlineStr">
         <is>
-          <t>Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide</t>
+          <t>Share Market News: Nifty 50 Outlook &amp; Prediction</t>
         </is>
       </c>
       <c r="D85" s="51" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>Liquide Blog</t>
         </is>
       </c>
       <c r="E85" s="81" t="n">
-        <v>-0.128</v>
+        <v>0.402</v>
       </c>
       <c r="F85" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G85" s="82" t="inlineStr">
@@ -13081,26 +13081,26 @@
     <row r="86">
       <c r="A86" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 06:30</t>
+          <t>2026-09-26 09:15</t>
         </is>
       </c>
       <c r="C86" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
+          <t>Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide</t>
         </is>
       </c>
       <c r="D86" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="E86" s="81" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="F86" s="51" t="inlineStr">
         <is>
@@ -13116,30 +13116,30 @@
     <row r="87">
       <c r="A87" s="51" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B87" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 00:50</t>
+          <t>2026-09-26 06:30</t>
         </is>
       </c>
       <c r="C87" s="51" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
+          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
         </is>
       </c>
       <c r="D87" s="51" t="inlineStr">
         <is>
-          <t>Alice Blue</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E87" s="81" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="F87" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G87" s="82" t="inlineStr">
@@ -13151,30 +13151,30 @@
     <row r="88">
       <c r="A88" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B88" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 14:34</t>
+          <t>2026-09-26 00:50</t>
         </is>
       </c>
       <c r="C88" s="51" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
+          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
         </is>
       </c>
       <c r="D88" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Alice Blue</t>
         </is>
       </c>
       <c r="E88" s="81" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="F88" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G88" s="82" t="inlineStr">
@@ -13186,22 +13186,22 @@
     <row r="89">
       <c r="A89" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B89" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 14:31</t>
+          <t>2026-09-25 14:34</t>
         </is>
       </c>
       <c r="C89" s="51" t="inlineStr">
         <is>
-          <t>PERSISTENT Stock Price and Chart — NSE:PERSISTENT</t>
+          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
         </is>
       </c>
       <c r="D89" s="51" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E89" s="81" t="n">
@@ -13221,30 +13221,30 @@
     <row r="90">
       <c r="A90" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B90" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 14:04</t>
+          <t>2026-09-25 14:31</t>
         </is>
       </c>
       <c r="C90" s="51" t="inlineStr">
         <is>
-          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
+          <t>PERSISTENT Stock Price and Chart — NSE:PERSISTENT</t>
         </is>
       </c>
       <c r="D90" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="E90" s="81" t="n">
-        <v>0.681</v>
+        <v>0</v>
       </c>
       <c r="F90" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G90" s="82" t="inlineStr">
@@ -13256,30 +13256,30 @@
     <row r="91">
       <c r="A91" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B91" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 12:52</t>
+          <t>2026-09-25 14:04</t>
         </is>
       </c>
       <c r="C91" s="51" t="inlineStr">
         <is>
-          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
+          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
         </is>
       </c>
       <c r="D91" s="51" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>upstox.com</t>
         </is>
       </c>
       <c r="E91" s="81" t="n">
-        <v>-0.382</v>
+        <v>0.681</v>
       </c>
       <c r="F91" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G91" s="82" t="inlineStr">
@@ -13291,30 +13291,30 @@
     <row r="92">
       <c r="A92" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B92" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 12:22</t>
+          <t>2026-09-25 12:52</t>
         </is>
       </c>
       <c r="C92" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
+          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
         </is>
       </c>
       <c r="D92" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E92" s="81" t="n">
-        <v>0</v>
+        <v>-0.382</v>
       </c>
       <c r="F92" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G92" s="82" t="inlineStr">
@@ -13326,30 +13326,30 @@
     <row r="93">
       <c r="A93" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B93" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:56</t>
+          <t>2026-09-25 12:22</t>
         </is>
       </c>
       <c r="C93" s="51" t="inlineStr">
         <is>
-          <t>Two years ago Sensex hit lifetime high: What went wrong after that &amp; what’s the road ahead?</t>
+          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
         </is>
       </c>
       <c r="D93" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E93" s="81" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="F93" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G93" s="82" t="inlineStr">
@@ -13361,30 +13361,30 @@
     <row r="94">
       <c r="A94" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B94" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:42</t>
+          <t>2026-09-25 11:56</t>
         </is>
       </c>
       <c r="C94" s="51" t="inlineStr">
         <is>
-          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
+          <t>Two years ago Sensex hit lifetime high: What went wrong after that &amp; what’s the road ahead?</t>
         </is>
       </c>
       <c r="D94" s="51" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E94" s="81" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="F94" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G94" s="82" t="inlineStr">
@@ -13396,30 +13396,30 @@
     <row r="95">
       <c r="A95" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B95" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:22</t>
+          <t>2026-09-25 11:42</t>
         </is>
       </c>
       <c r="C95" s="51" t="inlineStr">
         <is>
-          <t>Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points</t>
+          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
         </is>
       </c>
       <c r="D95" s="51" t="inlineStr">
         <is>
-          <t>rediff.com</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="E95" s="81" t="n">
-        <v>0.612</v>
+        <v>0</v>
       </c>
       <c r="F95" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G95" s="82" t="inlineStr">
@@ -13436,21 +13436,21 @@
       </c>
       <c r="B96" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:03</t>
+          <t>2026-09-25 11:22</t>
         </is>
       </c>
       <c r="C96" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%</t>
+          <t>Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points</t>
         </is>
       </c>
       <c r="D96" s="51" t="inlineStr">
         <is>
-          <t>equitymaster.com</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="E96" s="81" t="n">
-        <v>0.402</v>
+        <v>0.612</v>
       </c>
       <c r="F96" s="51" t="inlineStr">
         <is>
@@ -13471,21 +13471,21 @@
       </c>
       <c r="B97" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 10:48</t>
+          <t>2026-09-25 11:03</t>
         </is>
       </c>
       <c r="C97" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rebound on Value Buying After Sharp Losses</t>
+          <t>Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%</t>
         </is>
       </c>
       <c r="D97" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E97" s="81" t="n">
-        <v>0.318</v>
+        <v>0.402</v>
       </c>
       <c r="F97" s="51" t="inlineStr">
         <is>
@@ -13501,26 +13501,26 @@
     <row r="98">
       <c r="A98" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B98" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 10:31</t>
+          <t>2026-09-25 10:48</t>
         </is>
       </c>
       <c r="C98" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date</t>
+          <t>Sensex, Nifty Rebound on Value Buying After Sharp Losses</t>
         </is>
       </c>
       <c r="D98" s="51" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="E98" s="81" t="n">
-        <v>0.572</v>
+        <v>0.318</v>
       </c>
       <c r="F98" s="51" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
     <row r="99">
       <c r="A99" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B99" s="51" t="inlineStr">
@@ -13546,20 +13546,20 @@
       </c>
       <c r="C99" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses</t>
+          <t>Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date</t>
         </is>
       </c>
       <c r="D99" s="51" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>INDmoney</t>
         </is>
       </c>
       <c r="E99" s="81" t="n">
-        <v>-0.026</v>
+        <v>0.572</v>
       </c>
       <c r="F99" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G99" s="82" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="D100" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>upstox.com</t>
         </is>
       </c>
       <c r="E100" s="81" t="n">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="D117" s="51" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>hindustantimes.com</t>
         </is>
       </c>
       <c r="E117" s="81" t="n">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="D141" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>upstox.com</t>
         </is>
       </c>
       <c r="E141" s="81" t="n">
@@ -15543,35 +15543,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-29": {"open": 1460.2, "close": 1407.0, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-09-28": {"open": 5100.0, "close": 5011.5, "src": "yahoo"}, "2026-09-29": {"open": 5010.0, "close": 5204.5, "src": "bhavcopy"}}, "RRKABEL": {"2026-09-28": {"open": 2530.4, "close": 2459.8, "src": "yahoo"}, "2026-09-29": {"open": 2459.8, "close": 2523.2, "src": "bhavcopy"}}, "ACUTAAS": {"2026-09-28": {"open": 3272.5, "close": 3214.4, "src": "yahoo"}, "2026-09-29": {"open": 3290.0, "close": 3304.1, "src": "bhavcopy"}}, "DIACABS": {"2026-09-28": {"open": 353.0, "close": 339.25, "src": "yahoo"}, "2026-09-29": {"open": 336.9, "close": 352.05, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-09-28": {"open": 2138.1, "close": 2141.2, "src": "yahoo"}, "2026-09-29": {"open": 2141.2, "close": 2402.0, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 17:07", "days": 7, "items": [{"symbol": "MARKET", "title": "Sensex, Nifty End Lower for Second Day; Global Tensions, FII Selling Hurt Investor Mood", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxNOC0wWWx3dmhaeFRrNDNBUU8zLUxRMDdKSXNURGVXT09GdFJQbGlOR2pOeXdmTHlVMzViVWpVcFJrSmtGbktLUWlESkNzWGJwTlNERW00Y0hWVmR5dUxIV1AzNl9YeXFIZTR1WGRRZlp3RTVyMUR5Wmw0d0xWYWg2ME9Yc2Z3NlBibjR0S1NiV1l5d080TWxvQmpPVVVRMHA2VlNUM1oycTlZcG5CSlh4amFn?oc=5", "source": "The Indian Awaaz", "published": "2026-09-29 15:41", "score": -0.637, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets ride expiry-day seesaw as derivatives swings jolt Nifty", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxOX2lHWmtSZUZtUnhORjFzUGQweW5Ca1F2VDdRdVhDaHd3OF83Q1hvY09NMU5NY1JzQ1Z3MU1hRmVHVkppOHJxTXBYeE1aOFh2MUZEejFaNV9yWVNmNFRtRDJXN0xic1JiVGtaY25JTWZVTFh0bzRCZnVud29LQ1pkR2tIeVF1amxrZElwZTNNdW5IV0drNjBXU2RvUGZNNzgxaVRrTVlHcjdRcnBjLXNkMmlXQTV0N1F3LXI3TzU1a29UTmpMQ2p2OGxR0gHPAUFVX3lxTE0wYlo3VkFBcjJTdjdPWGJiVnY5SjRFb2tSRl9iVzVmTkNDSTNQSVRrVWF3SmhfVTlwWE1UQXkzZDludUdlbnhOUHlLZmI2M19OTGprTHVFLXV0N3BBczlFV1VqemhMT1NhOHhVVGNVY0pRQ21RSGJ4eVJBTUF6NktiOWkzd19kYkF5QVd3WEU5SlNydGFqTXNiM1RDZ0l1d1BHV2tnSGdQREFUdzUyWlZVTkRqR19VRXQ1emJMVFZ5ZjZsbGhBSUtOOEhZSUl1RQ?oc=5", "source": "Business Standard", "published": "2026-09-29 14:34", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZExVZU95MGlua1BLV2ZFTG9YR0dpLXI5czY0TTVJYTV1UU5PeWFJdGtTTjV4VmdnUFJoNGJ1Tl9BYS1LR0FGY0pkNmpWOG00RzZvMTFkZXFsZWVHdjNhMXBGWFJYOC1BR0NkdkNsSnU5TzAzaU9ka2VBZV93Yk95TVhlUFJBbmpxa3dEYnlqT3g3STBOZmN6eXJJVVVuTk9PdXZ0NWNHVXJhUE83R1JuelFPSGdjOTFO?oc=5", "source": "The Federal", "published": "2026-09-29 12:51", "score": -0.226, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMiiwFBVV95cUxOSzJsdnF0SDkzMmFPNTNaZ05vaGU2STJGWFdWNEprdEJSWV9JeUZpaW1XTWs3eGJsVGJUTVctVlFLOHpScGZEaF9wWkxEWms0TG1aOHdKY0F2Q2hmSXlMMS1XOTNtX2lLQmVFTlN1ZzFOVzhMemtQV0NJMExuR3ZObDZadHhUOUxkeTQ4?oc=5", "source": "APAC Media", "published": "2026-09-29 11:14", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjE0RnktVUk3N3FQdTJJOHFVOUhKQ01LNGVXUm4tZVNyRnJOY0JhaXNnMkliMUtRdmxZakl1ZTN2VERkdjNxVVRLUXhSV19zY2ZnOE1icGVtSVRXOHNtM3Zwa0ZmTWNPejZwdkhmd0puNzlqeTRZcjRsNTdMcjFhLUxBb1VFWjg3OExMRGFycUt6YUZXbTlsUVUzNGhhSi1HdVFDRjlfOHJjbXMwNXhTckhpa041QQ?oc=5", "source": "DD India", "published": "2026-09-29 10:48", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOd0ZfSDFRbVZ0dEJpMlltNlF3Uy1wdlRBOGpYWGdJc3k3TFNNSkJKOGxnUExZNjZ5SlNQMnVzNU1jSm1EQzVXdHJDdkx1YmdrMzBQS2oxXy1veUY5V2xnNl9KR0Q0akNFYmVnb2MtcFBMMjlFR2FvM3JNYU1YV1dvcDFIVGJaWndpTUJEc1Z5V2dQWGxKSzVsbFA0RlhyeVNtMTkwWl9qdFJHTVVnT2FxaEZDVktKdUd2TUtZS2tyWGVQNGtjSmdadVVWQTlHRUplQl96cA?oc=5", "source": "equitymaster.com", "published": "2026-09-29 10:19", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026", "link": "https://news.google.com/rss/articles/CBMijgJBVV95cUxQUlR6X25LUHNTc0Z0WHFMTkd6QTFmWWYxU3NHa0lFLXI4SFpHWXRMQVpMTHFGeE5lM2ktZTloaDZYMXozNWMxY25Rdk9sZ240YlhaeENTNmRraUFDTW9IbHdEdGxuOV8tR0J4bDlIeDdCZGlEYU9jem9qOEVBWjk3YU1oNVdrZGE5NmxKWG5jSWludXFEV3Y5aENySDBaQXJmRDNtalNPVU04NXF3VUNGS0xzUFFDMko1TDE3d0F2ckFwVzlhMG95M0h5QWdSSkpnTzBqbVpPYmhIMXhlVURMM3Rwb1R6ZUdjOUExX1I5Vl8yWl84dUZiNTFRU2dFbVMxUTM4X0ZXaGhBYlpHQ0HSAZMCQVVfeXFMTlppcXBnR2F2R1p4Z1hXNjZlRUtaeU9sa3VLeHV5NXFfQWFGd08wRE5mWDN5TFJiMEU1Y29JY1BNVzdDRTRaUE1NYkp1SEFycmtIVkE5dW51Ym1WUVZYS1ZFVW5ZY0puSm9kUFlxZ0t6YnFyY2x0M0dWNFQyYW9LeUtlZk4tYXltODh1ZzI3bWJMTFRRdWFUSzNyMllQOVd1RjJHcWFab2JrWkxJMmtLNUV4OHNRcWdrS2lpZHVFVzVfMEtwWkl5OTY5WVBrMmJFSmVTZEdKZmlDbzJSd1NlUC1wQTZYR1l0d3NpU1JzX1BybEllN091c3dwOXVNaU5LYTBxLWpxOVE0MFYycC1nbjNlZ1U?oc=5", "source": "Livemint", "published": "2026-09-29 10:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rebound from near six-month lows amid crude shock", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxPbnlwRUxnX0Mtc0I1MHBlVmo5dlptQ2NnUm5ib1lSUk5EU1o4TjhNNUgtY2k3TENnYlpQSkptbEZRU1JXaFcydWNEY0F2c2FjcjZhajBmQllqU2dIckQyZDlMcWo2emcxajVEN0xjaWQtSy1NVlBaa2x0QzFlV3cyblVHemQ2X2xSWjVCZVJUNkdjak5SQ0h5NEVqSGZsZUlIQTdCUUZxR1hpUmMtYVZxeHRaRUZpWVcw0gG-AUFVX3lxTE5ySzVLbHhfdWYzTWpxYm1zLWNSUEZ4QVE3c1BhZ1ktWDM0aENCZ0Qtal85VVhCVFFFeVJqbFVwNkRxOEJaTVdyZWZPZTR0bTNDT0xyNndFS0ZlTUtwTDFzNnpQZFprT3pEazRHX0xFbFczaGhoemc1OWNkeWFqQUk0UVUtYnNiUWV6WC1iZHpJQ3U5ZWRSZnh6eWlKNlR2MTkwUmwzSE1pZzh5NzREOUtkRy1Tb2ZvY0Fpa0RickE?oc=5", "source": "Livemint", "published": "2026-09-29 06:14", "score": -0.66, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows", "link": "https://news.google.com/rss/articles/CBMingFBVV95cUxOOTVLQWt4QUFvUzdlVURzbTFiZElZQTJ4ZGxERVdHZElrLUJKRVg1cHZKNVFLY0JjckVPSVdaOU9jVlZ0U2p0RWM5RjZOOVRLN25ncUdtSEhCZWZyYlFWbDVnTEJQbndBV2ZqQWktRFdQQ1djOVlaTmhfNFBaUE9kNDVnelNwdGxtVU1OczBva1ByODZGVkFfTE9HcHlJUdIBpAFBVV95cUxQdUIxRFphQzJqZ0Jqa0kxVmpvbFBMN19SVzhCY3RPMGR4TmgtOEhLN2FNZFN0bDJxUklqbG5pTDdQcUNTRjdnRk8zZmoxUEUtaXNXRFBrWldLMHh4VlpaOWdJQ1kyMDNUU0ZmWG9qQWlLUlQ2TEFNZHZLbHdoVWFzRDB1N1V0ejN5VXlGazByTG5JeXRVeWE3Y2tOd3lpMERISm05Rw?oc=5", "source": "The Hindu", "published": "2026-09-29 05:26", "score": -0.599, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxOYXhNdG9wbEpyV1JrT2ZVSG1veDJCakIwTVJDTGNZY1RuRDlYZFlTMHpWcjBRN0lwQ1I0WnBxWWJveEJvZzkySFZ5NG1JODR2OHlFQlMwR0FEZGY1cFRCcFRobUR1RjJoeEtxdXlCd3Fac2otQXpSTFEyLTVUTktTLTBfb3c3MVl5NExiUm5aN1pOQkR2bDBWLUJJQTVBdE0xQ3BLR3l2NG1hemFCb0VuNjJiMDlkZmpvZFNUSHZBMGhSbm41OTJpT1VWY1J3aTlrMGw2QldJTDA1RndGM2ZpLXR5dFdFYUpYcUxFd3paUU1kRmZEdGhYSNIB_gFBVV95cUxNUGZ4U1VBSU1YUGdsOTVHb0dyVkNoT1lGSjBucl9LR24yUnRKajNCSHFLWWFFbDg2b05iN0pNR05KdG5ZQWo0dzFDRUp3N0hCamVpbWdMeTZMSVQ1bU1GRmY2X3hjMTRTMFFMZVJKOExiZFF5dFhkbUZkcUVjWHNma2YzcFVQZF9LT1hJaVgxYTZXSFBoTDBkT25jNDdIMzI4YldxdjJ5TmtINF8wa2tnb3d2eWtsX3FVamNKV2RmZG5KdzBKd292V0pYd3dQcDVFTGg4QjNLWWxLZ3o3MVNvS3FnT0ZJQnR3REYxSTd4TUdtenFheXQzb3FLMmZzdw?oc=5", "source": "Livemint", "published": "2026-09-29 05:23", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNYi1rRVNYUG1VMmF2VjVva1lnTmNXSGdCbU5SeG1yMkhWUkVjUUl5WjljdGhWNU1wcUhDakVQU3FsQjh5bmlRV08wX3pxMXV0U0Q0VDAweWUzQ0tNZnVsd19FLVVyb3daaTVGY2FZcGtXM25qYkxCaUk2NFB2NXc4dThpTld2ZDh6TFNzanJlYmx3OXVDNTctSW5haEtqWHBrcjJSOWROYmwxQUVEejlnUm0zYVFhTUQ4VXFSbFptWDA3LVBVVER2NzEyaFdLUkljcUltVTdhci1JejFSSEpiQ053RWtjQ2dWaTJ2blJuY3ZYVnFiN1NnT1RxYkpoNTh0Z2tLTTRR0gGOAkFVX3lxTFBSSFVsVGFrRGxxQmZjSF9Lbi14XzVaa0tIRFh0MzhJS21ONkxBTWNkUkJDXzNnRnFjMmk2dTlwNzRoem9INy1sYk12YVNkLVJ0VTUySkJnNTM1QzV6ZFFFQVlhd3c5cUlUZVpUc1hha184X2pGSE5JTEkwWW84LWlwNV9HMkNVamNaWGo0Mlp0M1N3cmRxSmZJUUw5UzN6aTd5MUlHLTRlM25uM2VScXljRXlVcjFlZk4yajZwZkxYSkx1VFp1LWtLX2dWdW51V2NSVFhxUUlUZ3lQT3pkNDctM1hldGtrX2NJQ3hkN0xXQmM3MmFkeXdweXA0M3VsdjhZbWN6ZjREclA0eFdHdw?oc=5", "source": "NDTV Profit", "published": "2026-09-29 05:09", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxORm9sbGt4LWI0Qnc2ZTIyNm5MMVFFT0FXelZ0aTQta2ExTkZxbUZ0bW55RjFMVG9yNmZVczZSWFluQmpxNkxKRnpMdmJPUFNfRDFQSk1vVUVpMGpLdkp0V1c1RDd6Q1NEZUFjQTJzT1VWaTNZTGYyOU45T0cxRWV4UUs0NER0Qm5ucWJxV0xyY2diTFJ5a2N0eWVWRElHZ081bFlNckRUNEpRbmZVYXRZaTA5TWxpUUltR3dsdEQ3VEMxMUkzZWNLZmlsTlRPWWV0dHBwQ2Q5MUlOcDNqVWhNS1RoSlhfYlg0X0hVR0k5R3VER3JjS2JBejJrWFJ0TFhYLTFLX2RBQkpaVDhtd2RJOFRn0gGXAkFVX3lxTE9YUFdsMTlDTl9lbkdfTE1VY0toUk10QmlBcWM0blRhdTBjU0RxV3Q4eWNyNDhpNmhFTGZvSFY2bHU2RVpMM0JzMGdsWFRKQWdPVTNpSkl2WXZHVHNuTXo5c2VDOHBuVXltMnVKT2c4UVprUHdodmd6QUF0ODN5MnQ4UW5sS3RCWjVTMGhZNVNNRjViWFkxek51M3hqUHd3SWJtVzVwMGx3LUNnV2xfLU5WLWk0UXZDYVFLWGtxdlprQl8xNVF0SmR5ZmZiLXFBNDd1YnBuRkJabWZNSDY4SVpseDZKZEZQV1JsbHdFdHJVMW43T0JmRGR1THNMcjVxbVFyUGZpdVN3X0lSTzRLVkE0UDBZeHlFbw?oc=5", "source": "The Times of India", "published": "2026-09-29 05:06", "score": -0.459, "label": "Negative"}, {"symbol": "MARKET", "title": "BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWFYxc2FLNFJkeU5VQ0dWdFVETE9Sb1JzT2tuVnNEWTdRaU9JNWQzX0x0VjNmZlNuem9FdGRUelVPeUhNMUpTUWlmbF9nUGJJU1NndEl4eGxYaU5IWjdzSVlpOE9TQlhmakNHbTZlRmMxbGkya1JTYmJpM3FWNnhLM0FSeDhYRndHcDJzaW50dEE4WkVyb1MtcTZvN2pyeV9sTlZ5NVBLc3M4Wl9hQ3JmUF9CSWp2N2NEVk1rWld2Zm5BbXNXdFBZ0gHOAUFVX3lxTE5YV0ZiOEdkcDVUc2tDU1Myb0RnY1VRYkFHUERHLWdyM205dmdzWUoyekhSd2FIaVltYUZVa3ZUNG1qdktXNEpPTkVxdTduMmhGNGFlckQ3UkNrS0lqYkU0dVFqRmtSVS1nUkdNVXlnN1RIdmlaNUhMVGlFWHdrMERaVFo2bnlla2w0eklGTEFzSUdCeVNmYW0wZThzQ2N0WF9wNnhIZy0tZmxwREprRUFLMFk4eDN0eWhPV0x2YmZ5WXhzVU55aExVaFJtMnNR?oc=5", "source": "BusinessLine", "published": "2026-09-29 04:38", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Falls 400 Points; Nifty Slips Below 22,700", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWW5nZzl6c0Rqemg0cG1reGtZa3NMMTJEb2xNczJsMS1xbnJscHczcXpwSnJVOFVVQTJQZ2w1T0RNZ1pXb3hoWHFFMkhTdGIxYWgtNGZvQUE1X2dzNS1LMmF5dUZnZVJDbUhqdURGTlhpMTd0NERLVl9wZnNTUEx1dTJXeXY1ZVZnOWgtZGhLUEQxMzM3bmgzWTVxVXA0TWlwbDdTdXFRRVpLQ3p6NjI2ZU5SMTZIU1hsbFhXYU4wUDZpbW1fQUtZ?oc=5", "source": "HDFC Sky", "published": "2026-09-29 04:35", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxQNjN4TURGTmhtN2ctbmhRZ0NIMUVodFU1RzZNQlB0UkxGemdVQjZiYWh4WDJGakxkN290TjNzY0JEV3RsZkEtLXlxTW0xNFRzbksyQjRtSW9nSFlCSHF5Z1JMMHJjblJLbFJhX1VjRVE2WTZ2YV9wbnhNM1ZCMG5hekNoQU5uVEpscFdaczk1c1BPcWt1VXRzbWs4WFAtYUZIQVFMbWZNcmxWNE9zN3dkanZUdDhOb3dFckZGWXZfc21sMVc1Q0pOeDRQejVMR2Ztck1hTFFwSW9qM21kYWxqM3BoXzRGZw?oc=5", "source": "equitymaster.com", "published": "2026-09-29 04:35", "score": -0.477, "label": "Negative"}, {"symbol": "ATHERENERG", "title": "Ather Energy Share Price News: Today\u2019s Decline Analyzed", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxNSlI3d1lGdTBUQ1NsMmhvSDh5UVZMVndVcjQtLUJBX2VLOFhIT1hoZFFhaEZWaVhKSm85eUw5SFY3NTBrMlJ0SThWYU1Ib1R5Y0NyUGlSQzk4UDloNlhPVmRyR1JWR0hZUDdfeGZXT2toVDVseWxuZVBKVFVKdW1RNg?oc=5", "source": "Univest", "published": "2026-09-29 04:23", "score": -0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Oil rise, bond yields: Top factors behind Tuesday's stock market fall", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxNQWN6aWtsVWFkYzZta0ppZDBKT3V2WEIyYy1nWWJNMWNEYUl1T09nLXRyeTFlNWF6NTZUQ2dxQmZfYWxuTkxKbFRkQm9RUWZfMVA2R0lVMFlubHFyTi1BV0NGWnBuNGtobzJmZURPa1IwbjlGU1VwUkZNQUlOWEt1U2Y2SW40MV9ncTAySWd1bjVJMWRJTVhZczlVczRQZWMyekNLTThSXzFDM3pwR0NONHVidWVEbUhzN2h0bklZMkNEYTJqSU13bF9uUi1ISVAwemU5RGRFTi1EZkowSWE4emRB0gHnAUFVX3lxTE1aRkM0ZnlvVmp3MHNlaklqcFR1dTFSeUFtbHBBbjdMV0tkY3lTbUpPQ280dkFZUXoyaDEyT3gwVHRrRW9CVm9PanNSb1k3RGtSZlFTeWtBWWotMGwxUzBOUzNVZ19lZHA3RHdwRTlfbTMzekNDR0trRXdrZzZWUmJFVmFWdmhaTnRzWkZYdDBmZXhnMmlEcjBiN0k3Tl9yWnJLMHBPZ2lHYWhGMXMtWEtCQXFfMmpxVkYwYTc0UmFIX01WVXFoZVFncHNybGktUkxhZzRLTFJGdEE5d05KWnVaUy01ZmRmZw?oc=5", "source": "Business Standard", "published": "2026-09-29 04:23", "score": -0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what\u2019s dragging the market?", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUmk0WlNhUWFKM2hkY0tydWR0QV9jUVFvV0lQclJYVFlpcXd1Q2xYWjV6aDQ3SGZKWjdkdE9nWTFNNWFsT3NwNXpnVlNtQVowZDhOTmF5eHJkbmdZZ0R5eWh2RHlhZmlXNE03ODdxWnJtYWE0NzlLdmZCNXBVMUNLRW1Hem5EYjUwMXdvcjN5alZJbUdLSTN2RDhvamt1cm8yNWNzOURJZUctaExtNk1ocHRONWswa2ZRc2pjYnRtMXJQcV93MEtTc05yZkJIa1phUnFSSjlSaXpGZ9IB5wFBVV95cUxQUXJua0JCWWl3dVNjWmdUNFdmYTNrYjh1ZDNMS0tVRUhNSTJ6c3RRRjZaRmJnNnMya2MxbmpId0djX3QzQ29LS2EweVFmSFNjZTVfVFIxUEZlbUFEX0F6djZvMnZhUW1oUWlHV29yMno5V0ZzZjJwYnhOSkhuT1BMc1FDdTFwcGtiTTYyT3ktdnVaSjFnU1hkZVhrSE82N1c5NDJjR2Z3LUlNQ0Q5N29rVnVPRTJwUjY5NlNoVkVRMlFQRFVzUnFtYmh0NHhManBaYm5HOEYwckcyR25KR3NiZXFFbVRVZDA?oc=5", "source": "fortuneindia.com", "published": "2026-09-29 04:21", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty sink further; What is keeping the market under pressure?", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxPT2hTUks4TnNPVTAzVG1rd2xFajdvVU5QX2VTZWplSk9zXzBWc0ZOdGVzOHlrTmVOOC1hYXV1MnZxQmdnUFUwcHZPbTVMenVma0hOOVc3ZDVwWnZScEpoQUp1d2I5XzRyMmktMHZIYWhvZVVtZ2xzakx4ekpES1h6RzlfbHFxTGRUakRTbU9yeDZFT3JLUFZPMVBLdXQ1SW90Umc3S3hIMWFTeVlReWfSAa4BQVVfeXFMT09oU1JLOE5zT1UwM1Rta3dsRWo3b1VOUF9lU2VqZUpPc18wVnNGTnRlczh5a05lTjgtYWF1dTJ2cUJnZ1BVMHB2T201THp1ZmtITjlXN2Q1cFp2UnBKaEFKdXdiOV80cjJpLTB2SGFob2VVbWdsc2pMeHpKREtYekc5X2xxcUxkVGpEU21Pcng2RU9yS1BWTzFQS3V0NUlvdFJnN0t4SDFhU3lZUXln?oc=5", "source": "newsdrum.in", "published": "2026-09-29 04:21", "score": 0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street", "link": "https://news.google.com/rss/articles/CBMihwJBVV95cUxPSUtnaHFiYjg4Q204R0luSEhzcmdiaE4ycm9QNW93XzVKMGFOVlpkLUhhbXJDeXhqWWVTWW9FTGw3N2ExV1JFaTg0YjJhV0FrMUQ0Q2lOY3RtekpOUHpHWGJsU2tJTWhzSWdrU1pxNWpaZDVCclRGWWJrSi1HX2k2WmdEREJtd0RBeUdBSlNqekVYTHVqZnBNT2s2UDhYYXBBNmh3cE9kN29vbFlvRjU1OFVaemROVDFEMTgtbnRDVE5HeGRRSUkzY1ZScTlhM1ZqTVBSRThJXzhTb1QwX0R3YnR0b2twZEtsYmJJWHAwTzE2MFR1eWlsUDhNMHpvOW1BeG1pOE92NNIBjAJBVV95cUxOQTI5THdETFZZTFQwUFpsMktSVFhjeDZZWjhqcWdldDVwa2YzOXEtRzBrMWp4UW1QU3dqSzlqeGR5UGJpYUo4MXJMVndFdHpVd1MwOF9vWEFjQ0haZEwzNHB0RWZBRDVCdFZWUmhKdnM1bHRLbkp6cHNTUC1hNVIxdGRlVEtsczRRSXZtVlhyYWpQTUVXelJyeHFOZkREMUx3dnQxTXhCdFd3RGdraUd5NGFUU3NCM2hQY0tLaEU1Ym14WDM4UmZNdFppUWVNYWJtY2c4VjhFRTd0Zm4zczBtSGxJcXBPM2FCVXI1akRfU1VGWWd5UmlGV3Z4dkZHc0hjU0VsZ2p0Ny0wUndQ?oc=5", "source": "The Economic Times", "published": "2026-09-29 04:14", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxQYUFDem9SaEJWdjhyclFJQ0NyNENLejUtdThtMHpzZlREc1dxWVNucG95Mnc5QjE4WGNZc1dMRnFUZkxmanN1T1FmTEw0ZUE4bDhCQ2lXeFU1X2FlVERFS3BEcEVncG5Ya3BGQlRrQmI1WHJkRUcya1F6bV9XU0tvaXZGXzVwN0tEMGFONklKRTV5MVc0bkN4UUYySm50SmZGZms2UHptNTVPMDZnTlJvXzNFNEUxcWRKbTlTZlNLT29rcHBWaWd6RGZLTVV0NjNJSG1kTXBpSW1SZjRJcWRCb3FhWURJTFc3ck45WURndnRTZjNTYlHSAfsBQVVfeXFMTXItZGlfbXJYZnI0OFZ2V0c1VnNhMFB6Z0Y3ZjFrckJPTVZLajJBaXRmS2JjNnJyR1RfMXNoTy1ZQUViZk9tay1yQl8tbDVIQU5TSDJBdF8za3FjMGVZbWZZcV9NdDdILV9MZTFybHRtNlpDeFlPdVh4cmd5d01McXlQVEN1N1M2VlB4ZnJFdERpbUtJX3FlMXJlQmdzcDFnekRROExiRk9RTFBncFpwbzJQanZGZThMZWx5UWlIM2g0cVY0d0tLTi1kWnU1WW8xMHBNQU1qc01GcGl2ZXRHLVN6SXk5djFxZ0J6akJVSF9MZ2RVY3BYYUtoVGM?oc=5", "source": "Moneycontrol.com", "published": "2026-09-29 04:02", "score": -0.421, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxPM0JpdnpnZHlIYlVQUnRNYVVFYUlUZFJ3YkdJWXpXSzRQaktqaTN3LTdPYXU1SkRibHhTd0dOTTJkeV9NM1FZU1JWbFVPTmVBOGwzRFNwLTZ2V0lldi1kNXR3RWpjZzNmaUJOSGlIamdJcWY5TTlvRzdIZE9xZ0NiMFRpTTRnWHJZS2JaR0FOd3M1TmltbXBhb2RZU1dXUHhPdGp0MlNVbEEwV0cybVc3cEhxclU0azJyVzV3dNIBxAFBVV95cUxNS3psTE9IOFpFRVFkLU11bGZMbjA5VFNIN04xWDZJYkxIX0RscVpJTWJ0Z1N3Sjlsb3lCNTl2RURseHQ0ZVZTeHZSQnVjOFJCUjBZLUl4OUhSN0NLTm9kUmlLbU5BaTFLSzVYSVNXNExPb0VQRm9FSTVodDkzaEVLeThKSUl4b3IzcEhwbE1vSFJESGxRRnU4SDNaVkI0N05VTmtpX3F4S0VaZnBfekd4YWk5YXF2LXRycHVlOGVGTUVmX0hJ?oc=5", "source": "NDTV", "published": "2026-09-29 04:01", "score": 0.214, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty opening: Will stock market crash or open higher today?", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOUDZsU21wOWJFXzhjakg3OUQxaHREd05uWF95VTJlS05aOXQ0Vjdqam9UcjAycERGamJKcVdrYVJ6WEt4QUhHeWJaaVlJY09vQWxqUU5FVFVjcVBheEhubUkwMWdfSV8wSFNxOXpGWWN5WGwtZHk5VjlwTGw5TEVUdmNDUk4tMmZTdVlwOVpwX1IwaEVnNjNSeW9abHNFUThiS2I1RG13YS1pVjRWYkduWXk2YXh1STNNWUdEUWpKZXpVMUs0Sm9aOUs1Vm5vWFFiLWR0TmNTNmx1bXlkd2h4b2JocnN0RkpqRUHSAe8BQVVfeXFMT0JkeUl1MmI5TEZGbmM2bGFKWnl3LWdpQk8xVlVnNXhhbHg0VTI4WUUybUxNRjdKZHBVem5GbWVqZWZsSzhacWNOa3NpaUQwa0tQV0pMSGg1cDJVRGJHNVl1UWF3YjllaDJ5WnU4NjA0dFVTRkprekFzTHBGYlkyb1VmZXd2czlibnoyRm1Scy0tcGR4TXU0aGVDZjdua3JrcXJDUXRUZENMY0pTc1ZpUEk3UFl2andIckNfZ2tNZlZBXzEtMVF0Y1YwYmhkRTNOVmp2Q0ZMd01jQWR1SVJQMVlJQk5SRVpzbHpveVQyazg?oc=5", "source": "India Today", "published": "2026-09-29 02:57", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Gold Rate To Bond Yields \u2014 Five Key Factors For Sensex, Nifty 50 On September 29", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxPX2RZNUVYaGZnM0prSjZkblNWUDAyQkJnS3hOQVFsZVVzWWY3azFvYXFOekJUajR6R0Zla0NHN3NNSlZhbFI0NmhUUW1CaEdCckFrS3gxZGFUZDhVaEdqVzlwaDNIQV9mak8tTlNWVlZxU2J2OGUzemk1akNYb2k2MDREZGNNZFJ6UmxQcGQtblVyV2RKRnJ3cl96M0kzdmE5bmU1aktMcG9oZU5nUE52RnhuSGZSbnI1dU5udm9aNVpuQzVVanlZTWVHbHhGNDRDMlllS1F2ejFGcmxuNnhlOHloNE4yUdIB7gFBVV95cUxNYkFxX1BHMHZULVZmS05DY2N4cXJjaWdnX3RsWFFaWnJjTlF0dk1ySEtERGF5bzF1RFM2SjRZYzVlUUQ5LWswYUVvSHoyb3h0dC1jZ0ZZcnhkYXpFMzJvS25LNEk1SzFKTmdGVnN4MDdQN2FMaHhmZFdQVDc1TVZWTXlSSUtRYVlPVzBER004eFpRcFFhZFpXRVM4T0FWZFFVWFZQbjNnRk9tVFFtWVBNY1FEVmNBUzZPdFNJdWVZWGRsdzB2ZnRwZUI3YWdzUTk2Ym9lT2VtcXZFZVF0NUI0bmhKNHNUdzhMZnAzZDZn?oc=5", "source": "NDTV Profit", "published": "2026-09-29 01:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQWDNNbllRRzFSTkxtZmZHNmJ0ZnJPdDhyZFh0LUVuME1CYU9hdkZsR3NubDJXN2NQUXFnUER4RVhud1FsUENqWUhMdGdjT243VGZ1RGZJWGVMV2UwRl9HTTNQSk5wVU11djAzV05oalhsYzRrdG9mUF9ya2Q1ZUc5dFFUaUtNU0RqWExWMXVLSkVFSG9pUGp2VVZjWlJqdE9QbE9hRzIxYWJURXhwYm9faDk1S0Z3X18xd1J1d2duVXExemd6aDJyOEo2OW5RLVFUTWw3ZFFhU21oNGxZRnVfWXRPcjBDNzFUYVVrN0lfRzNoNDJJcktFa2FVR3lOSEVPSl9XN0dLQVNPaGfSAZACQVVfeXFMUEQ4OS1kTDJjTHlCVHp3dEFPZmJNdGxBQWlrdmN4dlhGSm45c1duQTM1WmFGRnRuTmNrRW5FaV9OQnBtc3dmVENWU1QzZG5yRGpyVFRTLTFnTlUySlNfSTFIR0RBSXpkQkhlWjNSZGFKTkFteVliTE1Zdmd4VWpCVkZ3MlQtTWxjZWdKR2VfdEM3ellKWlhua2lIVVZGaHB3bjlYQ0ptaWpmYUtid2dnLU0xdGlnMm9jYXlBSUJ5cV9ZbGZEUEUzMWd1czk4Q3Z3UHFWVWRyb3VxZy1EbnkxVXVmOVdmMVlHaEwteUllVkdCRThlQlc0S0xyblBKa2lUbWtwdzRJSGp0T0RfVE44cG0?oc=5", "source": "Livemint", "published": "2026-09-29 01:19", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3ZwWkRNRjJrZ1RQN0tCaXBfTGZORVVIeFJ2d1FmTkJpZ3RFM2ZUNW52alVyTDVSLXNzN0hRWUE0YUZ1NXBJZWEzbWVuV2NDUFRxNmRmWXVSdnkzZ0MtLV9UMm9FeTVaM2VGckptZWt1Wnhpd2F6TmVjcEpXVEJhNXpKWkVFd0NCelczRTBidmMxam1zVjRfM1J0aDVHaVl5MWtkQ1RvS2xXNm9lMTlraE9IQXBqd9IBuwFBVV95cUxQdU1hSjhhcHpRbXBFRmlSLUVvakR5c3ZwYlpORGl2M1hiaEhqa2dDWTVIdHhmY2NsNkVUWFZKT1c4MHROTG1fbEtCYnZnM0VMOHFEXzB5cFotZEtGNHgyVDR6ZkpwM19JM1JaVmlFMElpSUw0OHRMUXNKVUlvSEswOFdQcXlLLVVZZWpDVlE5bHplYkZoNUp4bUVEV2VhaWFVZzNDN1dpRFVUMUROeGtLQ3VlZFJjUDZ5Rmd3?oc=5", "source": "wionews.com", "published": "2026-09-28 19:51", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQWkFyUEVEYlc5ejlyTldhYVVvYml2c3N0YTlnSm9yZHEyMDNHUnNKVnRNeGl5NTZ0NkRpZFJJWURHUjdEczROQVpseThQbmlJdGRLa0R2X0Vid1VKM3FncW43TkVIU0hpVE5QY29VMklwNDRQa0FXNHpoRXhWSC1kaFQyVUtzc2RZYk9BMWhpTU5XTHZ4RHRMMU81azFLVFF4THZkTjJ6ZUl5NDNLcWFibmtqOUhjeEJYQW0zY24zT0lhZnMwZElXQXpB0gHPAUFVX3lxTE9jTkdQUlc5aXV2N0dtX0UzYWlfV2ZUSEhCUGp2OHFENzhsWnJQODNmemptdW9oQ2s3Si01ZnV0N3RlazVRS3YxZWJsNDZWZEx1MXdMcFFzZy11MnItN1pWQTdYS284QWJwd2hQZXdxdDc2VkR6emZGZFdsX1pDM1d2Rk1Ka25SVTRXcnAzT3dqekpRQnBKUXBwMGpHZjlQMXBtUi1pUEJac0RYSW9LcnBTUFkwbXoyQ2tDUkN4bEs5UGpoR3NBaldjekJVMFJ4MA?oc=5", "source": "Business Standard", "published": "2026-09-28 17:36", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr", "link": "https://news.google.com/rss/articles/CBMinAJBVV95cUxOOFgyakNMWTlmbmpOdjRVeTdlckZXNks0dmhfc21YME9FaUcxWjRFUG1XdTQwblI3MS1oUFN5eThST252YWpSdkhXbWZQY1V0ZWdVTGI5c2VXNXdFbzI3aUozMDh4RVMxLUxnb0tLX1NYU09yRGxGMWlvaDFlRzQyNkd2eUsxZ1lBTVNnMWI0VkMwejI1a0pWcm91NXFJSUVDZ1VhQ2JESWo2cnpDSHNHbGlhY19Za0pNQ0E3V045bjJMR09ueDZIdkNVUGthN3lRak53QWpiN1B0WkpRb3dRUTNaX1RYVXp0LUMyZG1EUWZPZlNXUGQ0WldOLWF6MFhQalU3YzA4WUttM0x6al9xS0xSVHdOajJJa2lacNIBogJBVV95cUxPanhKS0R3c2ZjbHJ5RlhHMmxmQUVLSFlUTEtBcWFTbS11YlNxdzZqNDVRSHBISmZfblhRcnhPbXVwN0NkclB6ZHNLYUk4bTZQU0x3YUs3NXdrUVE4RzJzY0VQVjZfazRmSmtudW9lNGtqcU1aMU5lMUVVS21lWm5pa2NxWlZxLTEwN0FlNGVJVS1lTzVvV1B6R0lsZGtDOUViTEFycFdFb3FmSm1KTjJZS3dEV3FUMEc4T0FVQXdBTFlCdk9sUlRyMDA5WHA0dmo2Q2lYcTFGTTJqYkI2R1JDLXZkbEdpYTBDU0NWZE1tTmd5SkFBNWxTM24yOERhN0x0SWkwY2RzZmZkRnFqNUJjdER2cFpqYmNBYVNfT2otZks5QQ?oc=5", "source": "The Times of India", "published": "2026-09-28 13:42", "score": -0.896, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNUkhaTEo2TVV5Q3h0cjBXLWVGX3EwakNwOXJxS1dmT0Fnc2p1eXByY2d4cFlIbE1HTER1QXFqWTB0bHNLR0lfWTdWT2RTTnJKRjYwLVhPU2t1dEdVMk5NMFZfemk3TFNhdk5GWDJGRVZUdV82aHJETlJWS051R0N6bU9pSktUWjR6SXY0d3g2ejhjeFRpdkszSFJzaw?oc=5", "source": "equitymaster.com", "published": "2026-09-28 13:25", "score": 0.652, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxQeEMyTGpqalIydEJBcFVFWC12WDdUZVYwbkJPVk1RTGRrWlpwTnlnMWJPMk9TM21CWWxfWkpIRU1QRWNCcVcya2JHbEFRLUZLa0Vwb29SOWt0Q01nbmRfZUhrcDd1M0hsb1pHWWViTnRUNkNYek9KZDVEcUlnemU0SEozeGo0dDQxV3BJSkRlS3JQZU91YWEtUHBERUt1cWZ0T2VZY01yVVlWRlNUR3FpWlJNeFFHYlhiekdoa2htZzlJeWw3b3BhaXFnRy0?oc=5", "source": "hrtoday.in", "published": "2026-09-28 13:16", "score": 0.361, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOZGFILWIzX0lTNkh0Rm8zMGVUTWxEVGdYN1FXR2JPUTJDeVhiNHdwaVdGM0xCOHdUYTQ4MmZqLUtVTXk5NU5va01tSzN0b0lJWjFMcmY3M0N3OEhaa1NYLUF1WkxLUk8zaGZZT1RzYzd3MWpMQjFmdTgtYm5fWG5Xb3VWenYtZEVWQTJsZDd6elFSTWd2RWtMeURUdTgzTFgxSExQSW1rMFJLVkpnVG5TSGx3YUhtM01oUHpvRWNERDEwTmw3RzN1d0M3SlZ3dThNbEVnNnBtVmJXMGgyaWI0NVUzeFJ3LWFocVNyVnBqM1BxeEdlZXVQeUJZdXRKdWwxM2hDU9IBigJBVV95cUxQUWpCNDFiSU9RRGF5Rm5PYU9FZGp3c2JWVFRVSzFWTHdrdDZUczkxMVBnLV8yN0hmQkdhbXhYM3dLeHViT0Fjd0o1MkFpT2h4d0tkR2JjS29ZZWs3T25DRV95dDVtNWlFQ2ZkbGZ1WVgxRU43aEZBZEZjLVNnZ0JnZHd4TkJUbUVMaHdEUTZERnFvQ25RT3V5MmxrRk5UaG1oQWoyTUtPMG9oaktqczhZel9nTUN0eEpfRkdxWGZHRTNHUnVRQVlUdENBVFctUnRRS3lMRFBWMVk4Y1JhVFFHMGNMWDNrNjhiclVOOThFa1JrTkxZWjB6U09fRGRZLVhrbGx1OE9MZHFMUQ?oc=5", "source": "Livemint", "published": "2026-09-28 11:48", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPX21IU01KT20tUWlfRy1IMWJ2LVBfSXBlOFdWYUZid1ZJdDRncFozNEtSb3NRdnlUTUlOTHFBNkloNjROR2daRV9EQlRObWhYYm1uYkl1dGdDck5yRXM5b1pzU3podGhMc1UybjV6SGNnd2J0dW9xWjRaLWVMWjBLYXlqN2NCRk1fSndYX3lBUU9LUGRBMlg0VnBfYWtJcHhaZlYwVTBxMHBhMWtXY3NhRko4UmUyVDZOUUFVRWN1OWs5RUhyOGxzV0VMWl9sUG11RjdudmdVNHp5M0hFQ3N1aUpoN19LZ19vVmo1MGVBQQ?oc=5", "source": "equitymaster.com", "published": "2026-09-28 10:56", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxPSmh5R1BHajZwb2tLTkNjdWctZ2g4d1RVU2FVaXdvU2Q4RlYzWmhia2RFWVlCbDBQdUd1NkQ1bWJUbkQtTWQ4Rk9zYkVMTVFKSGZINVFtSkVKMzhRU19ueHF3SUszbkdSOThBNFQwa0lhN1c3LVdJajZqV01uZENnWHV5UzlqbDVfSGpVdm80WlM2STJRQ3RBN2NSc1Fqc1h2amk5aFlyRExGQjh30gGyAUFVX3lxTFBSM1VWX25QMlNMcVR3N1ZFR21rX0JhZy1FVlJ3UFF1cS1PekRTcVhTOEU0Q0VGenl6Ujl1VzUtbEFvaDNiTGVpT0lHakNiQkpOX1lYRktta2stajUxT3NqSmZzRnBzVlUxNUlvdHFlRUJIN2ZKLWJfRjJ4R0ZaZVpOazYtTFlnakVCSWFINDdfcXE4cGJUYmJXcFhWbHhZUHczOHFrb0x2QV9wa0ZtTkJzb2c?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-28 10:48", "score": -0.7, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Falls 1,124 Points, Nifty Slips Below 22,800", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkNsYXBaNkxVbEJONXRoU2VUMDhmLVp5MjJ4bm9KZXJpWWp2TV9WQWhkYndIOWJOM3AxbHljM0Z4amc2NmVKS0p1SFk2REJiUVdxT3JEcG9tQ0VPMEJSa0kxNUlOS2dGTHFVN1M0T3JxbThwSkFVMHE2NzVYck1FUDR1bmM2bE1UbGJaZVFmR3hCVDJTbERmTzFnMVBoUlg3dmRkdno3b2lmZTVGNGhQbm9YOGl6SDlBSkt4M1ZoaUlsTkVf?oc=5", "source": "HDFC Sky", "published": "2026-09-28 10:46", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaFhnckpab0xJQWs2Q0lFM2ZfamY0ZklMM19qbWRQLTFXY053NHJjdkRkMWJIWUI5aU1OVl9YNEhRWGNCU0syb0RZcXUzRE1rbDBSZGE3WWVxZmJGN2poT0VJYl9VTThlQVZVYmcwS0tyal9kcFVkRmVpT0FRODZRdFZCTzE4bjhOVXctRTR0ODBvdC1DWGVEdVY3a185cEJQdUdxRmxXbFpJQlVUdHpYNlVXS3VIdmJXQl83VFgtRnNJRHJXX3BpZkhqN0hlOXFjZ1l5ekpJTdIB3AFBVV95cUxPYTNqWi1LYzdqcXJ2c2FtWEJGUVdUd3k1YXRDTnNWVWlyUFo3am13UmVSaHd1c1FqcDFHQ0pNSXlvaVZKYnVYWGZBRzJXOTgzdkdpbHVfWjlHbnBVV3Mwcnc5eE56S0hwaFlRREl0WVIwS0Q4WjRsOGMxVm1XUWQ5YnY0dzcxOUVPbUxrUFYzcEx2T0JPZ3Z6X2tkazNjRXc3ci04MHZGZnJUalk4c0M1OG1UZ1VDQ3E1UFJ5eVVaLXdqSWs3eWVnMnRPV2ZWcHE0YUw0cGVROG03aXV0?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 10:26", "score": -0.612, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPUU44cXhTejNjWEFmX3pOMEQ5YkhwR20yQUs4NGxnNks0d09rWnU2R2pxMWdmOGQ4N2s4Nm41WW9OR1lRRzU5X240Nnp4Zm44NFJ0b1N6a052VjJpXzlmR1VIXzlobHd2OVVJYnV4Q1BfMHNZUmZ0eWNqWUNqMzNGelN0Y3o5ZXRxY3hzby05M094NmZ4aWxpakRnZlZWYlRQMnhvVGRJcGlleVFpMHlNS0VRZllGQTktc1ZUWXM3MldYVkd3THVpOUh1TVVJVDJqd2tiU1N0al9oblNQajFGUDN6RlV6UGRQU2poMTV5dDRtTEVnZ2p4bzFITjQ4SVRoNVV5Z2dZbTFyUDDSAZACQVVfeXFMTl9adnRITUZ1VzVQX29ZOGpxVXpOZ24wcFluN2JGVjFsT056LU10RmMyQ3RnM3pkQlQzSV96TXZVT1ZWdmFNU1VSZmhpMWlCaWNtejhpNWwyZ05CM3c5NjJ0VnE3MUl5R19XWXphSU50eWRpd2RZemRtMzcyZTJMcWpOUUJEZ1BwZGdyXzl6ZW9MbkRoOXZjYWw2X0tURlRyTk13ajNhUXRBbWJpaFhQd2lUd1doVXRMU0VRQVRBTU1rM0xxMFN2alRHRWlWZ3pUUzd5dGJwQTJpdUlDUjJLMjBHNVVOVTJtMFFhdVlJb2dONjJjNzU1Y0p1ZE5Cbk9XcFFRT3ZYNHZaVFY1V1lIVjE?oc=5", "source": "Livemint", "published": "2026-09-28 10:15", "score": 0.402, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks shareholders approve fund raise and borrowing powers", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxNR1MxLTBoYmdoaG5EZlRjaXpBaS1ZNmkwbjBPV29xOUNGMlFQTjdFdG5ZS0JTRExGcm1XWTJCWERCMG9SRm5FcFBwSUZuVkZ1clJ3RDdRQWQxMENXTDA4UzdRUVBZeTJNN1RIZ281SG1sYkJ1TGZZeFBpN2FIRS1ieDJPcVNXY3ZuS3VHYTgyM1VuTzMyaFZkSTAwSzhrZWI2Mm1iVHlkOUlJelFUVnM4N0I3aVFwR3hvOHc?oc=5", "source": "scanx.trade", "published": "2026-09-28 10:06", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top losers", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNMmZlbEQ0Z0pQZ3FTUXJfQ3E0YkxMTFZlY3pIRjROZTIxeXE3T05xbW1iTUpkV3QwTGlqUnplMUtNZHF0Y0ZzSXBnS1luZG5UZ2h0NkpxNzhPZW52NGUyMjZPaHpveHVHZmpHM21TNmRtS3FldUdGeFRyMEk3MzhLRVkzMWI0RVhKbHFqa2JCUGh3U09IckU2bTEwbkxwenhaSC02X2NVTVBlT0FWN0hPWGFleXdzR1FwZWhBYW1kUmVMdHdha0s2REl2LWxjczAtOTBIQjMtZ3N2SnZHNDdRY3VydlJCM0XSAewBQVVfeXFMUHQ2MUh1aFVLaDBFTVZuR05mVGlpR2V2QVkzMnJFSC1DRXROZDNRSENDMHk2blF4TGR2WllXRk13YlhFRTJJT0UxN1BPbnRBcEpJZWRSc1VTU2tfcWwtNk5vTHZYdjlRZ0FjOG1OYlVuNHFyQjN5MGRicU14eEpadzRkMjVYdmNWbG1Zbmh3ZkJicGV6c3ppMlMtLWhqazd0VkpsVHEwNFlfVFlOTDd0Zjg0OWJLeFBXMGxGWlBzS3Z</t>
+          <t xml:space="preserve">-29": {"open": 1460.2, "close": 1407.0, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-09-28": {"open": 5100.0, "close": 5011.5, "src": "yahoo"}, "2026-09-29": {"open": 5010.0, "close": 5204.5, "src": "bhavcopy"}}, "RRKABEL": {"2026-09-28": {"open": 2530.4, "close": 2459.8, "src": "yahoo"}, "2026-09-29": {"open": 2459.8, "close": 2523.2, "src": "bhavcopy"}}, "ACUTAAS": {"2026-09-28": {"open": 3272.5, "close": 3214.4, "src": "yahoo"}, "2026-09-29": {"open": 3290.0, "close": 3304.1, "src": "bhavcopy"}}, "DIACABS": {"2026-09-28": {"open": 353.0, "close": 339.25, "src": "yahoo"}, "2026-09-29": {"open": 336.9, "close": 352.05, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-09-28": {"open": 2138.1, "close": 2141.2, "src": "yahoo"}, "2026-09-29": {"open": 2141.2, "close": 2402.0, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 18:13", "days": 7, "items": [{"symbol": "MARKET", "title": "Sensex, Nifty End Lower for Second Day; Global Tensions, FII Selling Hurt Investor Mood", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxNOC0wWWx3dmhaeFRrNDNBUU8zLUxRMDdKSXNURGVXT09GdFJQbGlOR2pOeXdmTHlVMzViVWpVcFJrSmtGbktLUWlESkNzWGJwTlNERW00Y0hWVmR5dUxIV1AzNl9YeXFIZTR1WGRRZlp3RTVyMUR5Wmw0d0xWYWg2ME9Yc2Z3NlBibjR0S1NiV1l5d080TWxvQmpPVVVRMHA2VlNUM1oycTlZcG5CSlh4amFn?oc=5", "source": "The Indian Awaaz", "published": "2026-09-29 15:41", "score": -0.637, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets ride expiry-day seesaw as derivatives swings jolt Nifty", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxOX2lHWmtSZUZtUnhORjFzUGQweW5Ca1F2VDdRdVhDaHd3OF83Q1hvY09NMU5NY1JzQ1Z3MU1hRmVHVkppOHJxTXBYeE1aOFh2MUZEejFaNV9yWVNmNFRtRDJXN0xic1JiVGtaY25JTWZVTFh0bzRCZnVud29LQ1pkR2tIeVF1amxrZElwZTNNdW5IV0drNjBXU2RvUGZNNzgxaVRrTVlHcjdRcnBjLXNkMmlXQTV0N1F3LXI3TzU1a29UTmpMQ2p2OGxR0gHPAUFVX3lxTE0wYlo3VkFBcjJTdjdPWGJiVnY5SjRFb2tSRl9iVzVmTkNDSTNQSVRrVWF3SmhfVTlwWE1UQXkzZDludUdlbnhOUHlLZmI2M19OTGprTHVFLXV0N3BBczlFV1VqemhMT1NhOHhVVGNVY0pRQ21RSGJ4eVJBTUF6NktiOWkzd19kYkF5QVd3WEU5SlNydGFqTXNiM1RDZ0l1d1BHV2tnSGdQREFUdzUyWlZVTkRqR19VRXQ1emJMVFZ5ZjZsbGhBSUtOOEhZSUl1RQ?oc=5", "source": "Business Standard", "published": "2026-09-29 14:34", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZExVZU95MGlua1BLV2ZFTG9YR0dpLXI5czY0TTVJYTV1UU5PeWFJdGtTTjV4VmdnUFJoNGJ1Tl9BYS1LR0FGY0pkNmpWOG00RzZvMTFkZXFsZWVHdjNhMXBGWFJYOC1BR0NkdkNsSnU5TzAzaU9ka2VBZV93Yk95TVhlUFJBbmpxa3dEYnlqT3g3STBOZmN6eXJJVVVuTk9PdXZ0NWNHVXJhUE83R1JuelFPSGdjOTFO?oc=5", "source": "The Federal", "published": "2026-09-29 12:51", "score": -0.226, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market today, Sept 29: 227 securities hit 52-week low on NSE; Waaree Energies, Canara Bank, Britannia on list", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPelRLOXBfN3VzSWJZNVlQM2h6enZDQmF6TnZ2Z3RUT0FsUklwX0NiUC1GaWRUYTNzLU9Kc3d0V1M5U1NPck95OFpUZE9aTnRTLUJEcGc1Y2FsVHNyZXFUS1JEWkhjRnkwS19IMWxZTXZ3QnB6WWZncXVXcEpXNjBkN3Q2cmFBZmJ1Rk5mME9jbnFzTEFWOFgtNXNETGZmekR2X2xWZlA2RUZKdnN0MXdVazNFM1hnbnVxTGR6M012NmUxN3Aza2tRVUV5dThNWjFROUtybFQxYXI4RW53VzFjS1prZzRCOXVGbHFqUHEtRVJPQ2RUZW9neERnZUw2TVJhQ1U4?oc=5", "source": "upstox.com", "published": "2026-09-29 11:26", "score": 0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMiiwFBVV95cUxOSzJsdnF0SDkzMmFPNTNaZ05vaGU2STJGWFdWNEprdEJSWV9JeUZpaW1XTWs3eGJsVGJUTVctVlFLOHpScGZEaF9wWkxEWms0TG1aOHdKY0F2Q2hmSXlMMS1XOTNtX2lLQmVFTlN1ZzFOVzhMemtQV0NJMExuR3ZObDZadHhUOUxkeTQ4?oc=5", "source": "APAC Media", "published": "2026-09-29 11:14", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjE0RnktVUk3N3FQdTJJOHFVOUhKQ01LNGVXUm4tZVNyRnJOY0JhaXNnMkliMUtRdmxZakl1ZTN2VERkdjNxVVRLUXhSV19zY2ZnOE1icGVtSVRXOHNtM3Zwa0ZmTWNPejZwdkhmd0puNzlqeTRZcjRsNTdMcjFhLUxBb1VFWjg3OExMRGFycUt6YUZXbTlsUVUzNGhhSi1HdVFDRjlfOHJjbXMwNXhTckhpa041QQ?oc=5", "source": "DD India", "published": "2026-09-29 10:48", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOd0ZfSDFRbVZ0dEJpMlltNlF3Uy1wdlRBOGpYWGdJc3k3TFNNSkJKOGxnUExZNjZ5SlNQMnVzNU1jSm1EQzVXdHJDdkx1YmdrMzBQS2oxXy1veUY5V2xnNl9KR0Q0akNFYmVnb2MtcFBMMjlFR2FvM3JNYU1YV1dvcDFIVGJaWndpTUJEc1Z5V2dQWGxKSzVsbFA0RlhyeVNtMTkwWl9qdFJHTVVnT2FxaEZDVktKdUd2TUtZS2tyWGVQNGtjSmdadVVWQTlHRUplQl96cA?oc=5", "source": "Equitymaster", "published": "2026-09-29 10:19", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026", "link": "https://news.google.com/rss/articles/CBMijgJBVV95cUxQUlR6X25LUHNTc0Z0WHFMTkd6QTFmWWYxU3NHa0lFLXI4SFpHWXRMQVpMTHFGeE5lM2ktZTloaDZYMXozNWMxY25Rdk9sZ240YlhaeENTNmRraUFDTW9IbHdEdGxuOV8tR0J4bDlIeDdCZGlEYU9jem9qOEVBWjk3YU1oNVdrZGE5NmxKWG5jSWludXFEV3Y5aENySDBaQXJmRDNtalNPVU04NXF3VUNGS0xzUFFDMko1TDE3d0F2ckFwVzlhMG95M0h5QWdSSkpnTzBqbVpPYmhIMXhlVURMM3Rwb1R6ZUdjOUExX1I5Vl8yWl84dUZiNTFRU2dFbVMxUTM4X0ZXaGhBYlpHQ0HSAZMCQVVfeXFMTlppcXBnR2F2R1p4Z1hXNjZlRUtaeU9sa3VLeHV5NXFfQWFGd08wRE5mWDN5TFJiMEU1Y29JY1BNVzdDRTRaUE1NYkp1SEFycmtIVkE5dW51Ym1WUVZYS1ZFVW5ZY0puSm9kUFlxZ0t6YnFyY2x0M0dWNFQyYW9LeUtlZk4tYXltODh1ZzI3bWJMTFRRdWFUSzNyMllQOVd1RjJHcWFab2JrWkxJMmtLNUV4OHNRcWdrS2lpZHVFVzVfMEtwWkl5OTY5WVBrMmJFSmVTZEdKZmlDbzJSd1NlUC1wQTZYR1l0d3NpU1JzX1BybEllN091c3dwOXVNaU5LYTBxLWpxOVE0MFYycC1nbjNlZ1U?oc=5", "source": "Livemint", "published": "2026-09-29 10:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rebound from near six-month lows amid crude shock", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxPbnlwRUxnX0Mtc0I1MHBlVmo5dlptQ2NnUm5ib1lSUk5EU1o4TjhNNUgtY2k3TENnYlpQSkptbEZRU1JXaFcydWNEY0F2c2FjcjZhajBmQllqU2dIckQyZDlMcWo2emcxajVEN0xjaWQtSy1NVlBaa2x0QzFlV3cyblVHemQ2X2xSWjVCZVJUNkdjak5SQ0h5NEVqSGZsZUlIQTdCUUZxR1hpUmMtYVZxeHRaRUZpWVcw0gG-AUFVX3lxTE5ySzVLbHhfdWYzTWpxYm1zLWNSUEZ4QVE3c1BhZ1ktWDM0aENCZ0Qtal85VVhCVFFFeVJqbFVwNkRxOEJaTVdyZWZPZTR0bTNDT0xyNndFS0ZlTUtwTDFzNnpQZFprT3pEazRHX0xFbFczaGhoemc1OWNkeWFqQUk0UVUtYnNiUWV6WC1iZHpJQ3U5ZWRSZnh6eWlKNlR2MTkwUmwzSE1pZzh5NzREOUtkRy1Tb2ZvY0Fpa0RickE?oc=5", "source": "Livemint", "published": "2026-09-29 06:14", "score": -0.66, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows", "link": "https://news.google.com/rss/articles/CBMingFBVV95cUxOOTVLQWt4QUFvUzdlVURzbTFiZElZQTJ4ZGxERVdHZElrLUJKRVg1cHZKNVFLY0JjckVPSVdaOU9jVlZ0U2p0RWM5RjZOOVRLN25ncUdtSEhCZWZyYlFWbDVnTEJQbndBV2ZqQWktRFdQQ1djOVlaTmhfNFBaUE9kNDVnelNwdGxtVU1OczBva1ByODZGVkFfTE9HcHlJUdIBpAFBVV95cUxQdUIxRFphQzJqZ0Jqa0kxVmpvbFBMN19SVzhCY3RPMGR4TmgtOEhLN2FNZFN0bDJxUklqbG5pTDdQcUNTRjdnRk8zZmoxUEUtaXNXRFBrWldLMHh4VlpaOWdJQ1kyMDNUU0ZmWG9qQWlLUlQ2TEFNZHZLbHdoVWFzRDB1N1V0ejN5VXlGazByTG5JeXRVeWE3Y2tOd3lpMERISm05Rw?oc=5", "source": "The Hindu", "published": "2026-09-29 05:26", "score": -0.599, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxOYXhNdG9wbEpyV1JrT2ZVSG1veDJCakIwTVJDTGNZY1RuRDlYZFlTMHpWcjBRN0lwQ1I0WnBxWWJveEJvZzkySFZ5NG1JODR2OHlFQlMwR0FEZGY1cFRCcFRobUR1RjJoeEtxdXlCd3Fac2otQXpSTFEyLTVUTktTLTBfb3c3MVl5NExiUm5aN1pOQkR2bDBWLUJJQTVBdE0xQ3BLR3l2NG1hemFCb0VuNjJiMDlkZmpvZFNUSHZBMGhSbm41OTJpT1VWY1J3aTlrMGw2QldJTDA1RndGM2ZpLXR5dFdFYUpYcUxFd3paUU1kRmZEdGhYSNIB_gFBVV95cUxNUGZ4U1VBSU1YUGdsOTVHb0dyVkNoT1lGSjBucl9LR24yUnRKajNCSHFLWWFFbDg2b05iN0pNR05KdG5ZQWo0dzFDRUp3N0hCamVpbWdMeTZMSVQ1bU1GRmY2X3hjMTRTMFFMZVJKOExiZFF5dFhkbUZkcUVjWHNma2YzcFVQZF9LT1hJaVgxYTZXSFBoTDBkT25jNDdIMzI4YldxdjJ5TmtINF8wa2tnb3d2eWtsX3FVamNKV2RmZG5KdzBKd292V0pYd3dQcDVFTGg4QjNLWWxLZ3o3MVNvS3FnT0ZJQnR3REYxSTd4TUdtenFheXQzb3FLMmZzdw?oc=5", "source": "Livemint", "published": "2026-09-29 05:23", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNYi1rRVNYUG1VMmF2VjVva1lnTmNXSGdCbU5SeG1yMkhWUkVjUUl5WjljdGhWNU1wcUhDakVQU3FsQjh5bmlRV08wX3pxMXV0U0Q0VDAweWUzQ0tNZnVsd19FLVVyb3daaTVGY2FZcGtXM25qYkxCaUk2NFB2NXc4dThpTld2ZDh6TFNzanJlYmx3OXVDNTctSW5haEtqWHBrcjJSOWROYmwxQUVEejlnUm0zYVFhTUQ4VXFSbFptWDA3LVBVVER2NzEyaFdLUkljcUltVTdhci1JejFSSEpiQ053RWtjQ2dWaTJ2blJuY3ZYVnFiN1NnT1RxYkpoNTh0Z2tLTTRR0gGOAkFVX3lxTFBSSFVsVGFrRGxxQmZjSF9Lbi14XzVaa0tIRFh0MzhJS21ONkxBTWNkUkJDXzNnRnFjMmk2dTlwNzRoem9INy1sYk12YVNkLVJ0VTUySkJnNTM1QzV6ZFFFQVlhd3c5cUlUZVpUc1hha184X2pGSE5JTEkwWW84LWlwNV9HMkNVamNaWGo0Mlp0M1N3cmRxSmZJUUw5UzN6aTd5MUlHLTRlM25uM2VScXljRXlVcjFlZk4yajZwZkxYSkx1VFp1LWtLX2dWdW51V2NSVFhxUUlUZ3lQT3pkNDctM1hldGtrX2NJQ3hkN0xXQmM3MmFkeXdweXA0M3VsdjhZbWN6ZjREclA0eFdHdw?oc=5", "source": "NDTV Profit", "published": "2026-09-29 05:09", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxORm9sbGt4LWI0Qnc2ZTIyNm5MMVFFT0FXelZ0aTQta2ExTkZxbUZ0bW55RjFMVG9yNmZVczZSWFluQmpxNkxKRnpMdmJPUFNfRDFQSk1vVUVpMGpLdkp0V1c1RDd6Q1NEZUFjQTJzT1VWaTNZTGYyOU45T0cxRWV4UUs0NER0Qm5ucWJxV0xyY2diTFJ5a2N0eWVWRElHZ081bFlNckRUNEpRbmZVYXRZaTA5TWxpUUltR3dsdEQ3VEMxMUkzZWNLZmlsTlRPWWV0dHBwQ2Q5MUlOcDNqVWhNS1RoSlhfYlg0X0hVR0k5R3VER3JjS2JBejJrWFJ0TFhYLTFLX2RBQkpaVDhtd2RJOFRn0gGXAkFVX3lxTE9YUFdsMTlDTl9lbkdfTE1VY0toUk10QmlBcWM0blRhdTBjU0RxV3Q4eWNyNDhpNmhFTGZvSFY2bHU2RVpMM0JzMGdsWFRKQWdPVTNpSkl2WXZHVHNuTXo5c2VDOHBuVXltMnVKT2c4UVprUHdodmd6QUF0ODN5MnQ4UW5sS3RCWjVTMGhZNVNNRjViWFkxek51M3hqUHd3SWJtVzVwMGx3LUNnV2xfLU5WLWk0UXZDYVFLWGtxdlprQl8xNVF0SmR5ZmZiLXFBNDd1YnBuRkJabWZNSDY4SVpseDZKZEZQV1JsbHdFdHJVMW43T0JmRGR1THNMcjVxbVFyUGZpdVN3X0lSTzRLVkE0UDBZeHlFbw?oc=5", "source": "The Times of India", "published": "2026-09-29 05:06", "score": -0.459, "label": "Negative"}, {"symbol": "MARKET", "title": "BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWFYxc2FLNFJkeU5VQ0dWdFVETE9Sb1JzT2tuVnNEWTdRaU9JNWQzX0x0VjNmZlNuem9FdGRUelVPeUhNMUpTUWlmbF9nUGJJU1NndEl4eGxYaU5IWjdzSVlpOE9TQlhmakNHbTZlRmMxbGkya1JTYmJpM3FWNnhLM0FSeDhYRndHcDJzaW50dEE4WkVyb1MtcTZvN2pyeV9sTlZ5NVBLc3M4Wl9hQ3JmUF9CSWp2N2NEVk1rWld2Zm5BbXNXdFBZ0gHOAUFVX3lxTE5YV0ZiOEdkcDVUc2tDU1Myb0RnY1VRYkFHUERHLWdyM205dmdzWUoyekhSd2FIaVltYUZVa3ZUNG1qdktXNEpPTkVxdTduMmhGNGFlckQ3UkNrS0lqYkU0dVFqRmtSVS1nUkdNVXlnN1RIdmlaNUhMVGlFWHdrMERaVFo2bnlla2w0eklGTEFzSUdCeVNmYW0wZThzQ2N0WF9wNnhIZy0tZmxwREprRUFLMFk4eDN0eWhPV0x2YmZ5WXhzVU55aExVaFJtMnNR?oc=5", "source": "BusinessLine", "published": "2026-09-29 04:38", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Falls 400 Points; Nifty Slips Below 22,700", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWW5nZzl6c0Rqemg0cG1reGtZa3NMMTJEb2xNczJsMS1xbnJscHczcXpwSnJVOFVVQTJQZ2w1T0RNZ1pXb3hoWHFFMkhTdGIxYWgtNGZvQUE1X2dzNS1LMmF5dUZnZVJDbUhqdURGTlhpMTd0NERLVl9wZnNTUEx1dTJXeXY1ZVZnOWgtZGhLUEQxMzM3bmgzWTVxVXA0TWlwbDdTdXFRRVpLQ3p6NjI2ZU5SMTZIU1hsbFhXYU4wUDZpbW1fQUtZ?oc=5", "source": "HDFC Sky", "published": "2026-09-29 04:35", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxQNjN4TURGTmhtN2ctbmhRZ0NIMUVodFU1RzZNQlB0UkxGemdVQjZiYWh4WDJGakxkN290TjNzY0JEV3RsZkEtLXlxTW0xNFRzbksyQjRtSW9nSFlCSHF5Z1JMMHJjblJLbFJhX1VjRVE2WTZ2YV9wbnhNM1ZCMG5hekNoQU5uVEpscFdaczk1c1BPcWt1VXRzbWs4WFAtYUZIQVFMbWZNcmxWNE9zN3dkanZUdDhOb3dFckZGWXZfc21sMVc1Q0pOeDRQejVMR2Ztck1hTFFwSW9qM21kYWxqM3BoXzRGZw?oc=5", "source": "Equitymaster", "published": "2026-09-29 04:35", "score": -0.477, "label": "Negative"}, {"symbol": "ATHERENERG", "title": "Ather Energy Share Price News: Today\u2019s Decline Analyzed", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxNSlI3d1lGdTBUQ1NsMmhvSDh5UVZMVndVcjQtLUJBX2VLOFhIT1hoZFFhaEZWaVhKSm85eUw5SFY3NTBrMlJ0SThWYU1Ib1R5Y0NyUGlSQzk4UDloNlhPVmRyR1JWR0hZUDdfeGZXT2toVDVseWxuZVBKVFVKdW1RNg?oc=5", "source": "Univest", "published": "2026-09-29 04:23", "score": -0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Oil rise, bond yields: Top factors behind Tuesday's stock market fall", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxNQWN6aWtsVWFkYzZta0ppZDBKT3V2WEIyYy1nWWJNMWNEYUl1T09nLXRyeTFlNWF6NTZUQ2dxQmZfYWxuTkxKbFRkQm9RUWZfMVA2R0lVMFlubHFyTi1BV0NGWnBuNGtobzJmZURPa1IwbjlGU1VwUkZNQUlOWEt1U2Y2SW40MV9ncTAySWd1bjVJMWRJTVhZczlVczRQZWMyekNLTThSXzFDM3pwR0NONHVidWVEbUhzN2h0bklZMkNEYTJqSU13bF9uUi1ISVAwemU5RGRFTi1EZkowSWE4emRB0gHnAUFVX3lxTE1aRkM0ZnlvVmp3MHNlaklqcFR1dTFSeUFtbHBBbjdMV0tkY3lTbUpPQ280dkFZUXoyaDEyT3gwVHRrRW9CVm9PanNSb1k3RGtSZlFTeWtBWWotMGwxUzBOUzNVZ19lZHA3RHdwRTlfbTMzekNDR0trRXdrZzZWUmJFVmFWdmhaTnRzWkZYdDBmZXhnMmlEcjBiN0k3Tl9yWnJLMHBPZ2lHYWhGMXMtWEtCQXFfMmpxVkYwYTc0UmFIX01WVXFoZVFncHNybGktUkxhZzRLTFJGdEE5d05KWnVaUy01ZmRmZw?oc=5", "source": "Business Standard", "published": "2026-09-29 04:23", "score": -0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what\u2019s dragging the market?", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUmk0WlNhUWFKM2hkY0tydWR0QV9jUVFvV0lQclJYVFlpcXd1Q2xYWjV6aDQ3SGZKWjdkdE9nWTFNNWFsT3NwNXpnVlNtQVowZDhOTmF5eHJkbmdZZ0R5eWh2RHlhZmlXNE03ODdxWnJtYWE0NzlLdmZCNXBVMUNLRW1Hem5EYjUwMXdvcjN5alZJbUdLSTN2RDhvamt1cm8yNWNzOURJZUctaExtNk1ocHRONWswa2ZRc2pjYnRtMXJQcV93MEtTc05yZkJIa1phUnFSSjlSaXpGZ9IB5wFBVV95cUxQUXJua0JCWWl3dVNjWmdUNFdmYTNrYjh1ZDNMS0tVRUhNSTJ6c3RRRjZaRmJnNnMya2MxbmpId0djX3QzQ29LS2EweVFmSFNjZTVfVFIxUEZlbUFEX0F6djZvMnZhUW1oUWlHV29yMno5V0ZzZjJwYnhOSkhuT1BMc1FDdTFwcGtiTTYyT3ktdnVaSjFnU1hkZVhrSE82N1c5NDJjR2Z3LUlNQ0Q5N29rVnVPRTJwUjY5NlNoVkVRMlFQRFVzUnFtYmh0NHhManBaYm5HOEYwckcyR25KR3NiZXFFbVRVZDA?oc=5", "source": "Fortune India", "published": "2026-09-29 04:21", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty sink further; What is keeping the market under pressure?", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxPT2hTUks4TnNPVTAzVG1rd2xFajdvVU5QX2VTZWplSk9zXzBWc0ZOdGVzOHlrTmVOOC1hYXV1MnZxQmdnUFUwcHZPbTVMenVma0hOOVc3ZDVwWnZScEpoQUp1d2I5XzRyMmktMHZIYWhvZVVtZ2xzakx4ekpES1h6RzlfbHFxTGRUakRTbU9yeDZFT3JLUFZPMVBLdXQ1SW90Umc3S3hIMWFTeVlReWfSAa4BQVVfeXFMT09oU1JLOE5zT1UwM1Rta3dsRWo3b1VOUF9lU2VqZUpPc18wVnNGTnRlczh5a05lTjgtYWF1dTJ2cUJnZ1BVMHB2T201THp1ZmtITjlXN2Q1cFp2UnBKaEFKdXdiOV80cjJpLTB2SGFob2VVbWdsc2pMeHpKREtYekc5X2xxcUxkVGpEU21Pcng2RU9yS1BWTzFQS3V0NUlvdFJnN0t4SDFhU3lZUXln?oc=5", "source": "newsdrum.in", "published": "2026-09-29 04:21", "score": 0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street", "link": "https://news.google.com/rss/articles/CBMihwJBVV95cUxPSUtnaHFiYjg4Q204R0luSEhzcmdiaE4ycm9QNW93XzVKMGFOVlpkLUhhbXJDeXhqWWVTWW9FTGw3N2ExV1JFaTg0YjJhV0FrMUQ0Q2lOY3RtekpOUHpHWGJsU2tJTWhzSWdrU1pxNWpaZDVCclRGWWJrSi1HX2k2WmdEREJtd0RBeUdBSlNqekVYTHVqZnBNT2s2UDhYYXBBNmh3cE9kN29vbFlvRjU1OFVaemROVDFEMTgtbnRDVE5HeGRRSUkzY1ZScTlhM1ZqTVBSRThJXzhTb1QwX0R3YnR0b2twZEtsYmJJWHAwTzE2MFR1eWlsUDhNMHpvOW1BeG1pOE92NNIBjAJBVV95cUxOQTI5THdETFZZTFQwUFpsMktSVFhjeDZZWjhqcWdldDVwa2YzOXEtRzBrMWp4UW1QU3dqSzlqeGR5UGJpYUo4MXJMVndFdHpVd1MwOF9vWEFjQ0haZEwzNHB0RWZBRDVCdFZWUmhKdnM1bHRLbkp6cHNTUC1hNVIxdGRlVEtsczRRSXZtVlhyYWpQTUVXelJyeHFOZkREMUx3dnQxTXhCdFd3RGdraUd5NGFUU3NCM2hQY0tLaEU1Ym14WDM4UmZNdFppUWVNYWJtY2c4VjhFRTd0Zm4zczBtSGxJcXBPM2FCVXI1akRfU1VGWWd5UmlGV3Z4dkZHc0hjU0VsZ2p0Ny0wUndQ?oc=5", "source": "The Economic Times", "published": "2026-09-29 04:14", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxQYUFDem9SaEJWdjhyclFJQ0NyNENLejUtdThtMHpzZlREc1dxWVNucG95Mnc5QjE4WGNZc1dMRnFUZkxmanN1T1FmTEw0ZUE4bDhCQ2lXeFU1X2FlVERFS3BEcEVncG5Ya3BGQlRrQmI1WHJkRUcya1F6bV9XU0tvaXZGXzVwN0tEMGFONklKRTV5MVc0bkN4UUYySm50SmZGZms2UHptNTVPMDZnTlJvXzNFNEUxcWRKbTlTZlNLT29rcHBWaWd6RGZLTVV0NjNJSG1kTXBpSW1SZjRJcWRCb3FhWURJTFc3ck45WURndnRTZjNTYlHSAfsBQVVfeXFMTXItZGlfbXJYZnI0OFZ2V0c1VnNhMFB6Z0Y3ZjFrckJPTVZLajJBaXRmS2JjNnJyR1RfMXNoTy1ZQUViZk9tay1yQl8tbDVIQU5TSDJBdF8za3FjMGVZbWZZcV9NdDdILV9MZTFybHRtNlpDeFlPdVh4cmd5d01McXlQVEN1N1M2VlB4ZnJFdERpbUtJX3FlMXJlQmdzcDFnekRROExiRk9RTFBncFpwbzJQanZGZThMZWx5UWlIM2g0cVY0d0tLTi1kWnU1WW8xMHBNQU1qc01GcGl2ZXRHLVN6SXk5djFxZ0J6akJVSF9MZ2RVY3BYYUtoVGM?oc=5", "source": "Moneycontrol.com", "published": "2026-09-29 04:02", "score": -0.421, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxPM0JpdnpnZHlIYlVQUnRNYVVFYUlUZFJ3YkdJWXpXSzRQaktqaTN3LTdPYXU1SkRibHhTd0dOTTJkeV9NM1FZU1JWbFVPTmVBOGwzRFNwLTZ2V0lldi1kNXR3RWpjZzNmaUJOSGlIamdJcWY5TTlvRzdIZE9xZ0NiMFRpTTRnWHJZS2JaR0FOd3M1TmltbXBhb2RZU1dXUHhPdGp0MlNVbEEwV0cybVc3cEhxclU0azJyVzV3dNIBxAFBVV95cUxNS3psTE9IOFpFRVFkLU11bGZMbjA5VFNIN04xWDZJYkxIX0RscVpJTWJ0Z1N3Sjlsb3lCNTl2RURseHQ0ZVZTeHZSQnVjOFJCUjBZLUl4OUhSN0NLTm9kUmlLbU5BaTFLSzVYSVNXNExPb0VQRm9FSTVodDkzaEVLeThKSUl4b3IzcEhwbE1vSFJESGxRRnU4SDNaVkI0N05VTmtpX3F4S0VaZnBfekd4YWk5YXF2LXRycHVlOGVGTUVmX0hJ?oc=5", "source": "NDTV", "published": "2026-09-29 04:01", "score": 0.214, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty opening: Will stock market crash or open higher today?", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOUDZsU21wOWJFXzhjakg3OUQxaHREd05uWF95VTJlS05aOXQ0Vjdqam9UcjAycERGamJKcVdrYVJ6WEt4QUhHeWJaaVlJY09vQWxqUU5FVFVjcVBheEhubUkwMWdfSV8wSFNxOXpGWWN5WGwtZHk5VjlwTGw5TEVUdmNDUk4tMmZTdVlwOVpwX1IwaEVnNjNSeW9abHNFUThiS2I1RG13YS1pVjRWYkduWXk2YXh1STNNWUdEUWpKZXpVMUs0Sm9aOUs1Vm5vWFFiLWR0TmNTNmx1bXlkd2h4b2JocnN0RkpqRUHSAe8BQVVfeXFMT0JkeUl1MmI5TEZGbmM2bGFKWnl3LWdpQk8xVlVnNXhhbHg0VTI4WUUybUxNRjdKZHBVem5GbWVqZWZsSzhacWNOa3NpaUQwa0tQV0pMSGg1cDJVRGJHNVl1UWF3YjllaDJ5WnU4NjA0dFVTRkprekFzTHBGYlkyb1VmZXd2czlibnoyRm1Scy0tcGR4TXU0aGVDZjdua3JrcXJDUXRUZENMY0pTc1ZpUEk3UFl2andIckNfZ2tNZlZBXzEtMVF0Y1YwYmhkRTNOVmp2Q0ZMd01jQWR1SVJQMVlJQk5SRVpzbHpveVQyazg?oc=5", "source": "India Today", "published": "2026-09-29 02:57", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Gold Rate To Bond Yields \u2014 Five Key Factors For Sensex, Nifty 50 On September 29", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxPX2RZNUVYaGZnM0prSjZkblNWUDAyQkJnS3hOQVFsZVVzWWY3azFvYXFOekJUajR6R0Zla0NHN3NNSlZhbFI0NmhUUW1CaEdCckFrS3gxZGFUZDhVaEdqVzlwaDNIQV9mak8tTlNWVlZxU2J2OGUzemk1akNYb2k2MDREZGNNZFJ6UmxQcGQtblVyV2RKRnJ3cl96M0kzdmE5bmU1aktMcG9oZU5nUE52RnhuSGZSbnI1dU5udm9aNVpuQzVVanlZTWVHbHhGNDRDMlllS1F2ejFGcmxuNnhlOHloNE4yUdIB7gFBVV95cUxNYkFxX1BHMHZULVZmS05DY2N4cXJjaWdnX3RsWFFaWnJjTlF0dk1ySEtERGF5bzF1RFM2SjRZYzVlUUQ5LWswYUVvSHoyb3h0dC1jZ0ZZcnhkYXpFMzJvS25LNEk1SzFKTmdGVnN4MDdQN2FMaHhmZFdQVDc1TVZWTXlSSUtRYVlPVzBER004eFpRcFFhZFpXRVM4T0FWZFFVWFZQbjNnRk9tVFFtWVBNY1FEVmNBUzZPdFNJdWVZWGRsdzB2ZnRwZUI3YWdzUTk2Ym9lT2VtcXZFZVF0NUI0bmhKNHNUdzhMZnAzZDZn?oc=5", "source": "NDTV Profit", "published": "2026-09-29 01:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQWDNNbllRRzFSTkxtZmZHNmJ0ZnJPdDhyZFh0LUVuME1CYU9hdkZsR3NubDJXN2NQUXFnUER4RVhud1FsUENqWUhMdGdjT243VGZ1RGZJWGVMV2UwRl9HTTNQSk5wVU11djAzV05oalhsYzRrdG9mUF9ya2Q1ZUc5dFFUaUtNU0RqWExWMXVLSkVFSG9pUGp2VVZjWlJqdE9QbE9hRzIxYWJURXhwYm9faDk1S0Z3X18xd1J1d2duVXExemd6aDJyOEo2OW5RLVFUTWw3ZFFhU21oNGxZRnVfWXRPcjBDNzFUYVVrN0lfRzNoNDJJcktFa2FVR3lOSEVPSl9XN0dLQVNPaGfSAZACQVVfeXFMUEQ4OS1kTDJjTHlCVHp3dEFPZmJNdGxBQWlrdmN4dlhGSm45c1duQTM1WmFGRnRuTmNrRW5FaV9OQnBtc3dmVENWU1QzZG5yRGpyVFRTLTFnTlUySlNfSTFIR0RBSXpkQkhlWjNSZGFKTkFteVliTE1Zdmd4VWpCVkZ3MlQtTWxjZWdKR2VfdEM3ellKWlhua2lIVVZGaHB3bjlYQ0ptaWpmYUtid2dnLU0xdGlnMm9jYXlBSUJ5cV9ZbGZEUEUzMWd1czk4Q3Z3UHFWVWRyb3VxZy1EbnkxVXVmOVdmMVlHaEwteUllVkdCRThlQlc0S0xyblBKa2lUbWtwdzRJSGp0T0RfVE44cG0?oc=5", "source": "Livemint", "published": "2026-09-29 01:19", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3ZwWkRNRjJrZ1RQN0tCaXBfTGZORVVIeFJ2d1FmTkJpZ3RFM2ZUNW52alVyTDVSLXNzN0hRWUE0YUZ1NXBJZWEzbWVuV2NDUFRxNmRmWXVSdnkzZ0MtLV9UMm9FeTVaM2VGckptZWt1Wnhpd2F6TmVjcEpXVEJhNXpKWkVFd0NCelczRTBidmMxam1zVjRfM1J0aDVHaVl5MWtkQ1RvS2xXNm9lMTlraE9IQXBqd9IBuwFBVV95cUxQdU1hSjhhcHpRbXBFRmlSLUVvakR5c3ZwYlpORGl2M1hiaEhqa2dDWTVIdHhmY2NsNkVUWFZKT1c4MHROTG1fbEtCYnZnM0VMOHFEXzB5cFotZEtGNHgyVDR6ZkpwM19JM1JaVmlFMElpSUw0OHRMUXNKVUlvSEswOFdQcXlLLVVZZWpDVlE5bHplYkZoNUp4bUVEV2VhaWFVZzNDN1dpRFVUMUROeGtLQ3VlZFJjUDZ5Rmd3?oc=5", "source": "wionews.com", "published": "2026-09-28 19:51", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQWkFyUEVEYlc5ejlyTldhYVVvYml2c3N0YTlnSm9yZHEyMDNHUnNKVnRNeGl5NTZ0NkRpZFJJWURHUjdEczROQVpseThQbmlJdGRLa0R2X0Vid1VKM3FncW43TkVIU0hpVE5QY29VMklwNDRQa0FXNHpoRXhWSC1kaFQyVUtzc2RZYk9BMWhpTU5XTHZ4RHRMMU81azFLVFF4THZkTjJ6ZUl5NDNLcWFibmtqOUhjeEJYQW0zY24zT0lhZnMwZElXQXpB0gHPAUFVX3lxTE9jTkdQUlc5aXV2N0dtX0UzYWlfV2ZUSEhCUGp2OHFENzhsWnJQODNmemptdW9oQ2s3Si01ZnV0N3RlazVRS3YxZWJsNDZWZEx1MXdMcFFzZy11MnItN1pWQTdYS284QWJwd2hQZXdxdDc2VkR6emZGZFdsX1pDM1d2Rk1Ka25SVTRXcnAzT3dqekpRQnBKUXBwMGpHZjlQMXBtUi1pUEJac0RYSW9LcnBTUFkwbXoyQ2tDUkN4bEs5UGpoR3NBaldjekJVMFJ4MA?oc=5", "source": "Business Standard", "published": "2026-09-28 17:36", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr", "link": "https://news.google.com/rss/articles/CBMinAJBVV95cUxOOFgyakNMWTlmbmpOdjRVeTdlckZXNks0dmhfc21YME9FaUcxWjRFUG1XdTQwblI3MS1oUFN5eThST252YWpSdkhXbWZQY1V0ZWdVTGI5c2VXNXdFbzI3aUozMDh4RVMxLUxnb0tLX1NYU09yRGxGMWlvaDFlRzQyNkd2eUsxZ1lBTVNnMWI0VkMwejI1a0pWcm91NXFJSUVDZ1VhQ2JESWo2cnpDSHNHbGlhY19Za0pNQ0E3V045bjJMR09ueDZIdkNVUGthN3lRak53QWpiN1B0WkpRb3dRUTNaX1RYVXp0LUMyZG1EUWZPZlNXUGQ0WldOLWF6MFhQalU3YzA4WUttM0x6al9xS0xSVHdOajJJa2lacNIBogJBVV95cUxPanhKS0R3c2ZjbHJ5RlhHMmxmQUVLSFlUTEtBcWFTbS11YlNxdzZqNDVRSHBISmZfblhRcnhPbXVwN0NkclB6ZHNLYUk4bTZQU0x3YUs3NXdrUVE4RzJzY0VQVjZfazRmSmtudW9lNGtqcU1aMU5lMUVVS21lWm5pa2NxWlZxLTEwN0FlNGVJVS1lTzVvV1B6R0lsZGtDOUViTEFycFdFb3FmSm1KTjJZS3dEV3FUMEc4T0FVQXdBTFlCdk9sUlRyMDA5WHA0dmo2Q2lYcTFGTTJqYkI2R1JDLXZkbEdpYTBDU0NWZE1tTmd5SkFBNWxTM24yOERhN0x0SWkwY2RzZmZkRnFqNUJjdER2cFpqYmNBYVNfT2otZks5QQ?oc=5", "source": "The Times of India", "published": "2026-09-28 13:42", "score": -0.896, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNUkhaTEo2TVV5Q3h0cjBXLWVGX3EwakNwOXJxS1dmT0Fnc2p1eXByY2d4cFlIbE1HTER1QXFqWTB0bHNLR0lfWTdWT2RTTnJKRjYwLVhPU2t1dEdVMk5NMFZfemk3TFNhdk5GWDJGRVZUdV82aHJETlJWS051R0N6bU9pSktUWjR6SXY0d3g2ejhjeFRpdkszSFJzaw?oc=5", "source": "Equitymaster", "published": "2026-09-28 13:25", "score": 0.652, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxQeEMyTGpqalIydEJBcFVFWC12WDdUZVYwbkJPVk1RTGRrWlpwTnlnMWJPMk9TM21CWWxfWkpIRU1QRWNCcVcya2JHbEFRLUZLa0Vwb29SOWt0Q01nbmRfZUhrcDd1M0hsb1pHWWViTnRUNkNYek9KZDVEcUlnemU0SEozeGo0dDQxV3BJSkRlS3JQZU91YWEtUHBERUt1cWZ0T2VZY01yVVlWRlNUR3FpWlJNeFFHYlhiekdoa2htZzlJeWw3b3BhaXFnRy0?oc=5", "source": "hrtoday.in", "published": "2026-09-28 13:16", "score": 0.361, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOZGFILWIzX0lTNkh0Rm8zMGVUTWxEVGdYN1FXR2JPUTJDeVhiNHdwaVdGM0xCOHdUYTQ4MmZqLUtVTXk5NU5va01tSzN0b0lJWjFMcmY3M0N3OEhaa1NYLUF1WkxLUk8zaGZZT1RzYzd3MWpMQjFmdTgtYm5fWG5Xb3VWenYtZEVWQTJsZDd6elFSTWd2RWtMeURUdTgzTFgxSExQSW1rMFJLVkpnVG5TSGx3YUhtM01oUHpvRWNERDEwTmw3RzN1d0M3SlZ3dThNbEVnNnBtVmJXMGgyaWI0NVUzeFJ3LWFocVNyVnBqM1BxeEdlZXVQeUJZdXRKdWwxM2hDU9IBigJBVV95cUxQUWpCNDFiSU9RRGF5Rm5PYU9FZGp3c2JWVFRVSzFWTHdrdDZUczkxMVBnLV8yN0hmQkdhbXhYM3dLeHViT0Fjd0o1MkFpT2h4d0tkR2JjS29ZZWs3T25DRV95dDVtNWlFQ2ZkbGZ1WVgxRU43aEZBZEZjLVNnZ0JnZHd4TkJUbUVMaHdEUTZERnFvQ25RT3V5MmxrRk5UaG1oQWoyTUtPMG9oaktqczhZel9nTUN0eEpfRkdxWGZHRTNHUnVRQVlUdENBVFctUnRRS3lMRFBWMVk4Y1JhVFFHMGNMWDNrNjhiclVOOThFa1JrTkxZWjB6U09fRGRZLVhrbGx1OE9MZHFMUQ?oc=5", "source": "Livemint", "published": "2026-09-28 11:48", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPX21IU01KT20tUWlfRy1IMWJ2LVBfSXBlOFdWYUZid1ZJdDRncFozNEtSb3NRdnlUTUlOTHFBNkloNjROR2daRV9EQlRObWhYYm1uYkl1dGdDck5yRXM5b1pzU3podGhMc1UybjV6SGNnd2J0dW9xWjRaLWVMWjBLYXlqN2NCRk1fSndYX3lBUU9LUGRBMlg0VnBfYWtJcHhaZlYwVTBxMHBhMWtXY3NhRko4UmUyVDZOUUFVRWN1OWs5RUhyOGxzV0VMWl9sUG11RjdudmdVNHp5M0hFQ3N1aUpoN19LZ19vVmo1MGVBQQ?oc=5", "source": "Equitymaster", "published": "2026-09-28 10:56", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxPSmh5R1BHajZwb2tLTkNjdWctZ2g4d1RVU2FVaXdvU2Q4RlYzWmhia2RFWVlCbDBQdUd1NkQ1bWJUbkQtTWQ4Rk9zYkVMTVFKSGZINVFtSkVKMzhRU19ueHF3SUszbkdSOThBNFQwa0lhN1c3LVdJajZqV01uZENnWHV5UzlqbDVfSGpVdm80WlM2STJRQ3RBN2NSc1Fqc1h2amk5aFlyRExGQjh30gGyAUFVX3lxTFBSM1VWX25QMlNMcVR3N1ZFR21rX0JhZy1FVlJ3UFF1cS1PekRTcVhTOEU0Q0VGenl6Ujl1VzUtbEFvaDNiTGVpT0lHakNiQkpOX1lYRktta2stajUxT3NqSmZzRnBzVlUxNUlvdHFlRUJIN2ZKLWJfRjJ4R0ZaZVpOazYtTFlnakVCSWFINDdfcXE4cGJUYmJXcFhWbHhZUHczOHFrb0x2QV9wa0ZtTkJzb2c?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-28 10:48", "score": -0.7, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Falls 1,124 Points, Nifty Slips Below 22,800", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkNsYXBaNkxVbEJONXRoU2VUMDhmLVp5MjJ4bm9KZXJpWWp2TV9WQWhkYndIOWJOM3AxbHljM0Z4amc2NmVKS0p1SFk2REJiUVdxT3JEcG9tQ0VPMEJSa0kxNUlOS2dGTHFVN1M0T3JxbThwSkFVMHE2NzVYck1FUDR1bmM2bE1UbGJaZVFmR3hCVDJTbERmTzFnMVBoUlg3dmRkdno3b2lmZTVGNGhQbm9YOGl6SDlBSkt4M1ZoaUlsTkVf?oc=5", "source": "HDFC Sky", "published": "2026-09-28 10:46", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaFhnckpab0xJQWs2Q0lFM2ZfamY0ZklMM19qbWRQLTFXY053NHJjdkRkMWJIWUI5aU1OVl9YNEhRWGNCU0syb0RZcXUzRE1rbDBSZGE3WWVxZmJGN2poT0VJYl9VTThlQVZVYmcwS0tyal9kcFVkRmVpT0FRODZRdFZCTzE4bjhOVXctRTR0ODBvdC1DWGVEdVY3a185cEJQdUdxRmxXbFpJQlVUdHpYNlVXS3VIdmJXQl83VFgtRnNJRHJXX3BpZkhqN0hlOXFjZ1l5ekpJTdIB3AFBVV95cUxPYTNqWi1LYzdqcXJ2c2FtWEJGUVdUd3k1YXRDTnNWVWlyUFo3am13UmVSaHd1c1FqcDFHQ0pNSXlvaVZKYnVYWGZBRzJXOTgzdkdpbHVfWjlHbnBVV3Mwcnc5eE56S0hwaFlRREl0WVIwS0Q4WjRsOGMxVm1XUWQ5YnY0dzcxOUVPbUxrUFYzcEx2T0JPZ3Z6X2tkazNjRXc3ci04MHZGZnJUalk4c0M1OG1UZ1VDQ3E1UFJ5eVVaLXdqSWs3eWVnMnRPV2ZWcHE0YUw0cGVROG03aXV0?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 10:26", "score": -0.612, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPUU44cXhTejNjWEFmX3pOMEQ5YkhwR20yQUs4NGxnNks0d09rWnU2R2pxMWdmOGQ4N2s4Nm41WW9OR1lRRzU5X240Nnp4Zm44NFJ0b1N6a052VjJpXzlmR1VIXzlobHd2OVVJYnV4Q1BfMHNZUmZ0eWNqWUNqMzNGelN0Y3o5ZXRxY3hzby05M094NmZ4aWxpakRnZlZWYlRQMnhvVGRJcGlleVFpMHlNS0VRZllGQTktc1ZUWXM3MldYVkd3THVpOUh1TVVJVDJqd2tiU1N0al9oblNQajFGUDN6RlV6UGRQU2poMTV5dDRtTEVnZ2p4bzFITjQ4SVRoNVV5Z2dZbTFyUDDSAZACQVVfeXFMTl9adnRITUZ1VzVQX29ZOGpxVXpOZ24wcFluN2JGVjFsT056LU10RmMyQ3RnM3pkQlQzSV96TXZVT1ZWdmFNU1VSZmhpMWlCaWNtejhpNWwyZ05CM3c5NjJ0VnE3MUl5R19XWXphSU50eWRpd2RZemRtMzcyZTJMcWpOUUJEZ1BwZGdyXzl6ZW9MbkRoOXZjYWw2X0tURlRyTk13ajNhUXRBbWJpaFhQd2lUd1doVXRMU0VRQVRBTU1rM0xxMFN2alRHRWlWZ3pUUzd5dGJwQTJpdUlDUjJLMjBHNVVOVTJtMFFhdVlJb2dONjJjNzU1Y0p1ZE5Cbk9XcFFRT3ZYNHZaVFY1V1lIVjE?oc=5", "source": "Livemint", "published": "2026-09-28 10:15", "score": 0.402, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks shareholders approve fund raise and borrowing powers", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxNR1MxLTBoYmdoaG5EZlRjaXpBaS1ZNmkwbjBPV29xOUNGMlFQTjdFdG5ZS0JTRExGcm1XWTJCWERCMG9SRm5FcFBwSUZuVkZ1clJ3RDdRQWQxMENXTDA4UzdRUVBZeTJNN1RIZ281SG1sYkJ1TGZZeFBpN2FIRS1ieDJPcVNXY3ZuS3VHYTgyM1VuTzMyaFZkSTAwSzhrZWI2Mm1iVHlkOUlJelFUVnM4N0I3aVFwR3hvOHc?oc=5", "source": "scanx.trade", "published": "2026-09-28 10:06", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>heDYwdDN0UWNXdl9BUGFnTnRMamNnTWJYUVNmRWJWTzJhN0U3YzU0YS1PSDI?oc=5", "source": "India Today", "published": "2026-09-28 10:05", "score": -0.178, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVkFmQXdEZjZITFVKV1BEOHlKXy1rajlNZ3NuN3N6UXdZa2lWWVFxNnhXOTJtYmZxOVpOcVVpLWE3VUhwZUhjVXBYV2VleEVpbVR4RTRsc05tTFBIcXNoME5VaVlJVFR2ZUx0Mmx6RXlHTFhKUUdFU1J2OUhXNERPU2xsa0FGTGFOcjJzQ0ZlQkIwY204X1Z3UUZTMEt6NDZRVDJMbUQzclRobkxrcFpWbGJTQXJnRFR0ZHBMdURjQjgxZw?oc=5", "source": "Kalkine India", "published": "2026-09-28 08:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Nifty, Sensex: History favours stock market comeback in October; stocks to watch", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZE5UeURMRWtrOUFNekVkT0ZOcFI1SkE4Q28tZDc1NkJvbmFaakNlQlBDWkt4RDd6b3FpazN4NjRzWGhMN0RaYXY0U05IVEY3bU1lN3RFaURJSjRUTnF5Y3o3LW1wT3RtSkx5LW5yaWpiemJ2Ym1lYjdtTmpKY2lPWk04aVhiR25wMVl5ME9HSmUtQ3RIaENZTC1pOHpOekZVUVNSSWlFaXl0N2NrS19MeVpJdUxLeEl2blBYSjNseU41V2NjTUxmeklyeTN2Y1B2eWNuQWFTS0FVX2hJNWfSAeMBQVVfeXFMUDhHbWlIakswUl8zYmdMcHhmcVlGQ1V4RkdsdHhqN19JMjZwT0dxMGtVeHBQX2gxZk8yVlFwamlzblJNbUZJZU84N0RRTWk0U1VJRmc4VUZyV2p5NnJLNjRYcExKb3NKWjg2NmlMbUhRVFNDZHdocnNsMl9RVTF3YjBkYzMzaTRqdFAzbE9jX2NKWlZWb3FGOEFPMkktYURRbUZLYTR3SUVTWG84cXo3TzItZGhlOTBoNFhfRTlXSnNfOHJPNVctVEFEcW5WSzg1bHNHR1c4MUoyODVYWnJqV3U2U3c?oc=5", "source": "Business Today", "published": "2026-09-28 08:15", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher", "link": "https://news.google.com/rss/articles/CBMiowFBVV95cUxOci1kRlliVGdLVkdiMUM4b1lqbEFvLUdDV0VITWp3NGlyb2w5N1Rmc2pZUi11cVhmNkxDUlkwZThkS1hOZ0lFaXdmYXJoa3FiT3hfeHhaNkFwdEg2b0V6NHZaZ094cG9RZGQxLTMySlZLX1J6SGRXcU1Sb2RuTng0RzFzc1lZMWNHNjY4b29HdWpzOFRWclh4S1JGUjlGelRRSzlv0gGjAUFVX3lxTE5yLWRGWWJUZ0tWR2IxQzhvWWpsQW8tR0NXRUhNanc0aXJvbDk3VGZzallSLXVxWGY2TENSWTBlOGRLWE5nSUVpd2ZhcmhrcWJPeF94eFo2QXB0SDZvRXo0dlpnT3hwb1FkZDEtMzJKVktfUnpIZFdxTVJvZG5OeDRHMXNzWVkxY0c2Njhvb0d1anM4VFZyWHhLUkZSOUZ6VFFLOW8?oc=5", "source": "Free Press Kashmir", "published": "2026-09-28 08:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHU1a2VYbkdKb1k1RENtVm56MHlVeE9EcW1DQWd4ZmRyY0g2b2JqZjkxVENveE5US2JvaWtoanpITFc5NzVFS3hzMWRxcmtPUFJ2a1NBX2xsVDJUWEZrekpKNWVLZzZ6TlRQUnVoVWZWTzZ3Q3VBWTM0WkxqRzVhM0FzWm5kNmtCa3JMUDRENUwyVU1iZDBNd1BMRkpWenlNUHpLTDFScU1rcW0zcnNBM3pWODVoMHV1WlhwNmVSSllWTHVWOW5hRE9B0gHPAUFVX3lxTE00UXRvMWNWTlhGMWphc2xibF9MLUtJQnFQRjR3UG5nbVh4M0NWMVg2MzdockRzaEdnWlpTcEtyM3dGWnRTbnFRQnRKV1JmZk9RdWY2UnpYY1VsWjRBSDVwTk10clJnNHlCSEs0a2g2TFA1alQyYUFWNXIzWDNfeXlOejBhVGJrQTJZRG13cG5XVEdVWExyM2Yyb1owX2pmUDNTWEZsenBGcUlYdWpWZ2NpSXh1dmt4blhQYUptLWFNNnBndk04NXhzdVc2ODNNVQ?oc=5", "source": "ETV Bharat", "published": "2026-09-28 07:56", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxQVWNmQ2tBRmd0NTdUbmZ2YW9kZW1wdDZrMXU4Y0gtTXZPYU9uc3JGRGJXQnhBaEY2YXk2TGhCWlhqZGU5OWs1eDlPOTJMcHp3ek5GUEYtcGQtYUdUVmpTZzVNZGlnS2UxVXhHZE9DcTYxSk9uWkFmaThOdUdzbnpmanpXUF9sSVVReXFLY29VeTg5QUZPNkszSmNGQQ?oc=5", "source": "APAC Media", "published": "2026-09-28 07:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxONU5xeDQyaGZ0M2JBemJwU0REcWJxYkZWN1hxM2d1VHZBOGh2X3gwR3plbk90RlZMLWtWZV9jek1KR2lsTDB4d09oQlJzRTNadHgyUEY4bHhFbGp6eVhOWDhqLUtQWkpIUldLLU1EbUoyU1VfYmNaOVdqWnJzREo0Mjh3bU5wTTZPN081MmVFY0liRzQzVEtZRWFVMURCaTJZX0twZzRZWVJHVV9KaEl2LUNFZzBpdmt0RFM1OXZoLXVKQmt3WmlDSGR6VHZFMWdiV2dWcklYVWxuTXdFbXc?oc=5", "source": "Upstox", "published": "2026-09-28 07:36", "score": -0.806, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxOMzZwenBCS1ZIMUJRRXVOZTBBME0xU0N0WGJsVEVfQkVhZ1NtMEplNUNXM1A0WGRZLUVOZWlTNi10QUVQQnJRSnZDZTh0SXVlQkN5eDZ3ZWstRVQ2TlctUE82ZmxJRG1BZkw1NjZGZGYyZWJiZlZ1YktSZU5OTk5MZ1A0Q2NyV0wzZEd6c3dHaUwxcUpZa3ZBQ0g0dGViQzhfTFF4RExTb2p4azg0WjhlVTBlSUZtSG80clVYa2p2MFBuZWIwVURXMGd5dG9wVE5sWUNLbGJCb1U5SjNBcHNXZnE2dGNkUlVhVUlrNndWVTVpOG1jWVZYeFppQUdRekXSAYQCQVVfeXFMTWsza1RTaVB1QndYVDNrWE1GWUo0QkJCd09tUGxGUkx2T3pVamh4d1VTUG9FYkxpUmpRV0RlaDhxeXVMMFN1Vk9sMVRIY2xaUjNXRlhYLWN0SXFuT2V4UktnYlRvVnZzUlFQbkJFZlNsMnBCR1JZeTVvRzVUa1duQm5hb2llbUlPNmZuQ2owWUFPbDRJWUV1ZHVoZWd2ODJMUFo1V3g5RzNfRnZ4MldzV0F3UGJfV3UzZ0lxWjdIS0hfZ2JXeXh5VFVtTm1JVnNtX0d2bjAySWZZU25TZGhiUjhkVERUenU0T1VJTld2WGM4QmVOckxtMk5QcThMbnR6bjg1cGs?oc=5", "source": "CNBC TV18", "published": "2026-09-28 07:06", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxPUkRFSHF1dXJEMUtBZUdNc0FqX0g2TjZqMV9MSFRVSXdDSHRobkFERnFiamUtMDVVcks2NDVkS3JYVzNYR0dCMnFlVDVobmpEWlduX2tCODBQMThWMm96RW1BTUlHbVlxbVMwNkpuWVphWFZJS1pTUHdwYWFJbEM2ZzNZTWhYS2luLWhYR1htelNSS3E1OHpXaV85Rm5iQWVIcHFnNkpiYzFFTHB5eXktdEplbUk3czJwV2dadzlBR3MtQmtlNnl3VDBhOGc1VGs1eENMWU54STdnREtoc2NOeGpJWXMxSnp1VGEtUVJWS2c3YWPSAfsBQVVfeXFMUFBfZ0J3ZVlJNGVQMHhXZTNvaU1wUzh3dHYzOU1sS3pFX2RIS01fSmpIMDRLOExqVmxMemRwRTZjbmxNcFRHbTlScFhKUHh4TXJzSTJyR0g1cVNwRmd3WDVWck1iaDB0b3FsVzNpYy1TZUU3RExUZjdfcl9ZTms2a2VnZUQ5NW11VEdGbFU1VmEwUjRPaGNHS01sVDVTMDNpVUltUFFUc2NKRDV6bmVyZWRMcDNXTzE0cEZLc3lNVDlpTmZMd2ttaVg0Ylo2d3BYY3BJa3dUcFM5UU9yLVpHSU16MXVUOUZ1dUhmSTdjVTRfTDZGZWUwd05zQjg?oc=5", "source": "NDTV Profit", "published": "2026-09-28 06:47", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday\u2019s market crash", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNeDY4VXlDMWttUXVoM1pMNFhYeks3ZVJpaUI1eDVJZklkME5QbmdzcFpRbFMyT3JYUEV5REM1V1hPSE9JckhRcE5EU0xpOWFfZmtTdVVqM3h2TDdwLWJDWUpMb09XOHdkVURHaUx1Y1BYNW1qbWh2cUpTazhOREdqa0lmMkl5d2pSV0RqSDhUOXlmT2VCWUdxdlZMV0lOeDc4ZFJIWHk1ZXhhbUhjUlpVSmVZNEY2cVpTQUxXdjVpOFJEWDU3RGZOemRCVEJiLUVSMXNhSWE3N25TQVV1eUoxMjJjcHh3YlU?oc=5", "source": "Upstox", "published": "2026-09-28 06:40", "score": -0.595, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: decline, valuation and peers", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE43Z0JKcUo3bkM2R2FfLWQ5TXNkQ2dpMnNldEZ1UHU3THMyeUkyTkc4TmN5V3NEUjFiNGVEQlBWd1pwQk5lZk54YWIyX0F3ZGNWQWJJc1NGY25WakxxMjQ3VWFfRHZhN291N1F6Wnd4YW55TjQ0eXJ5bXNuMA?oc=5", "source": "Univest", "published": "2026-09-28 05:52", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "India VIX spikes 14% as oil, geopolitical risks trigger market sell-off", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQc3R2Z25xanJ3ZVVqYmk4THp6a0pjWnc2UFg5VUNQLUZOaEowZW9WREszOXhBNURRYzh4ZkZNNWJaUmx2TGZjZDBVUUsyQ2VRczJUa0lvNzBLVzFZX1ZhdlV4R1Z4T3pIaWZOdWVvaDcxLXJ0Q1hxQzNaaDBURkRVN3VYT3ZUd3ZjNFNCNzJkZWtnZHgwQ2ViSWxHa1p0TUVlRXpROXVQaTNnbGtHM1dOOHkzUkJtSnBXS0YwU3JEd2J0VmdpQng2bENyOVFfTHhiTXfSAdcBQVVfeXFMUEE2WUJINWNtZDJCUTRSY1RsRHJsWUVSZi16N1F6YjBwVU1keTJZRFpUaE9rZ2FYZ2lKdU1KaldxM1ZFZkRMelphRi0xTnBxRWczdUNlU1FQTExxUE1qSnBzQkxlVGFNZUwwdExoVG91NFlEcHdOOUtJZ0xmZ0wyMnh1QjJrZzVUSWMwX0JYbHNBVVBNNXJLbkx4UG1GdmxKNExxWVdpWFVYUkoxSWRHQWRmTWh0QlNzSTVrMHlRaGVjSFowbUtkdF9GR2FUN0wtaEJWd0t5SWM?oc=5", "source": "Business Standard", "published": "2026-09-28 05:52", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxOZFhpNERkTkx4Z2RRS1k2ejBhN1IyTzR6a2g5MjJ3bkNjeDZlOWRBSmlIek1xQk1GcVIweUZvcVFEcGwwSW90RThvU0J6cng2YVpLV0tZU1dQQlhGZUtieFVuZ3BmWXY5aFFkSlRuR2p2ZW8wZF9TQmZ2RnJoNFV2Q1lMT2JGMkxLUlp3OF81dlkyWHVmQ0xyNVg5R29GVXZkR1NLUkRqTzF2ZXA1cmtlcEptcmJNR3dwRi1R?oc=5", "source": "India Infoline", "published": "2026-09-28 05:42", "score": 0.103, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUdIB8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUQ?oc=5", "source": "simplywall.st", "published": "2026-09-28 05:37", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r", "link": "https://news.google.com/rss/articles/CBMiwgJBVV95cUxPQ3drbk9QbWRHcU9uVDJLU0EydWpPdVZRVE1rTEE5bFZadHZmUVJPeG9nUjVYWnVvSTkzNzFyNFo3TWhfN1lzX0ZScEVrSnZETUJ2MmtDaE1XYjc2TXo2a1p0UWZhcHprU1lwM3V3YUNUVzlTc3l4UXdCLVExX3dLQTdRaGh5Rk0xUDQtR2lkY3Mxd29QSHNPRU5fRDFYRVBSbC03X2pFaGpnWlJ6MFZDUGlicHlPUUpXeDh4ZU94UWR5ZHNCZ0pydDdFdHZNSjgyRThId0JfSlcxVzFibmR3clVwQzllekZnLUJ1LTdZcHpsRkt1YzN0b1FBT2FkZF9zblJkRlIxdmZfdzNFSXllSDM3b19zME9xaXhlWGk0Qjd5TWwxdDJaenFsOE5iOUNOU2VKRkxYazExZVAxYWJuVVVn0gHHAkFVX3lxTE1EMGdQdWlWbVp5aUpTbEJmb0M5dWQ5X0xJYmNpTFJJVERpUDZkcVo5V1ZGeTNyR3VmYjUyUDF0bG1HVlBGQ21nNDBfU1RZRTdYTEZFTy11OXExZmNOdzRwQTFQNlBRcFZ6NVdDSFFkeWdkV1ZGdm14cXpoTTc5eFc2WkZnVTQ1SlZ3NmxCOWk1b1BWU3doODZadUV0c0tkQ0VCeERINlczUmlYWmJ2MjNoblhPeWtqa0NvU3ZRcGw4NlQ3Mk5GcTFlZDIzQlN4SWxiNE5Md0ctQVBmMklselFGekszWTlFM2JFN244eVJtOHctcnFCc0RVM0Z4OUlqVmctZ25xTDVnTTV4djlfc2U3T2pkeC0tajA2ZnVKRDk3eEJ2ZkNWSmZicmVEOXN0UHpfRkJQdlZMLTVveENMYmdJenM0UFRfRQ?oc=5", "source": "The Times of India", "published": "2026-09-28 05:18", "score": -0.691, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeDRfUkctTnR5c0x3dEhXcmFSWWREQnhLUGMxbmFRT0RpWW1CbkVpN3dkcjJTSUZOd0ZpTjF2M3U5OW1vOEdHS3BKZG03d3BhenZtX21jTEh6VVc4ZC1oazJmSGJCZTBQTVZObmVYeEJFT2ZuaVd4OF9rbWNyUGo1T1ZMZFFtY1Zpd2dSYV94Yk5uS3FRVWFueWpYaTNyVjJVdnVoRzVFaGhvc1pOcmJOb1BWN2I1VXBTTnNNWURYZ18tRXFkZHR3Mks2TEk4X1lMb19NbVU1am5jd9IB4AFBVV95cUxNbVVHcVRveFpQaExzeVVnLXV2bTRTY0dTaTNSWDhoWEdCVkRCZjdZY0I2TElNdWxlb2RYVThZcXFFM1VDQVRxbmRETlVSTGJjX1R0MWpCQTFId3Iwb0hjUXF4bHhoNjNhZlBoeFptZHVHRWdwYTIxd0N4dmZtNHNFRXhvc0h4TVFXNl9ELUhkQ1VXS2FjV19NWWZpeGJTZmc4R0VWZldxNWVlOWlzVGRHX3cwaUd4UjVuMmlDVjlVelA5Umt3dVkwTDlhOEFSWGY5V1k0anMwOFNGbU5ZNmtZUg?oc=5", "source": "The Hindu", "published": "2026-09-28 05:11", "score": -0.852, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxObFRUUjZrRFpjTE1NcXBPb2NicXQtS3RtU0wtNHVjVHV4VHRlWWtMc1RtMzYwbXN2dnl3SVRBcjJxWFphN0hXMm0yZFNFNVduQ2dDdnVweVhTR24xNW5qemFXaTl2dkxsMkFYTlNCbGM1Si1IcmZIN3ZBTmF2ajBCcERjU1RPNXlIRHdlanZ1T0VxWWlWZkZ2eEYyZFBJWUJiSUp6b2gtcEtUQjJMaHNuWHNrRkNYek0tZlRITmkteDFreTNVb2VvcmhWZnJNa3FzTnZiUy1aXzVMMzg0cGNZR3pvMUFRQQ?oc=5", "source": "equitymaster.com", "published": "2026-09-28 04:56", "score": -0.477, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil", "link": "https://news.google.com/rss/articles/CBMi5AFBVV95cUxOMEwwTHh2ZHV6TVZtbjNDSEprS000QlNTUjh4X09yNWFTUmpHcW12aERXVXNSOUlSNWVrMlM1eG94ckljVXRpdDUzVHFtWUJ1M1p2TncyUDdBUWItZnppY0dSV2VZQjZiTDNLNzRBYVZnZUpIQzBPQk1BbjNEckUtdUxuU0oxMmRLYmw1cnhOV2FpUkMwNHhqazg4MGs0VTQySklGWTJwUGl5U09GS0t4alJNajVvc2lMdi1nMTJxQkNLeTg1OWUyYWlwbVJoR3F0b2NWU1pOVDFiOVhBZk9Nbk5TQUTSAecBQVVfeXFMTkhYdHl3d2FCU3RHT2JTZzJfcmhZbzNWWFZqMXFObDVBVHNsNnZsX29kak5jdG1BLUowT0REU2xTQWt0RmdoVVg5LXpzSEJobHl0U2hnNUJ6ZDU5MHlIaVVpTG1YeG5VQThDa05fTm1IczQwR3o2TjdQa2NEOVZ6dVZuU1lXN1dEN3dZWTV6ZkgxX0tYWXJNZXJLSU1nYXh2aGtrQTJJQUl1VnRJVGhjbmZpRmp5QnBjcThMTlJrbGFvb2tjUnkyT3B3MXo4VkdEdERQM3hKSmMwWWdoWk9uZGphb0M2a1Q4?oc=5", "source": "rediff.com", "published": "2026-09-28 04:51", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQeTNsTy1qVmtORm03dkJ0LVQwRUVQU3ZnT0RqMEI4NG5kVUxYeU0wcmp2N1hqaFVPdXhHNDV6cGRuZUcwclFTZ2NUV1NjdzQwYlhwWEMtcmFIVXZpMWxhWnpzOUFwaF9QUTVPQXVnTmZlUVVHNlNZQTVUOWxjdHZ6UHJuVDVtZkpPVWJqd1hlLXNlUVBEMmNuUFRCUFZZb25KNGpaNmJ4RjRuRDh5ZWFvS1JheXpLSzVQWkNSODVvaHh5ZUgyWjFPTTRnYlpxbUluek0xZHdaVU91cVRrYzFHWVJfRlJVemI0RW42Q19KSdIB9AFBVV95cUxPRWZEblJNRmlJNmdQMUpNa2FMYzNDRGZrTlp2RFh5MnZvSW5HMDhlVmNPODRlRkJTYkIySVFBWGZQLVh3Y1QzWXhValo3RkpjX0pidkhKQjJaTGFGOXhsZzBfeHBadVhGcjZKZXpuSkF1ZFB4RzVwVDIyeEtqamhHX09HR2FtY3ZRcGM3bzg5X25sU01NeW85LWQ0SG9pYjMzS2VfU0pncEJLc2QweG5wbFdZbEpDU3hvenI3V1BUU2FPclVvZGNCU1NEb0ZsZU9GdmQ3Smd6ZTZ3WTJtY3BTOElrdURuLVVsZFo3ZTVLalFBY0lD?oc=5", "source": "Hindustan Times", "published": "2026-09-28 04:45", "score": -0.361, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE stock slips below issue price of \u20b91,785; down 2% on Monday", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQSTM2eERXZ0NPUHpTR185VFYyNzFaR0lYZlMzeHB0Y2dGMjM4RlhXdWtnczBEblZtV2F3YVItUUpYbmhGTWI0YVpSdVlRejFmZUdyWmhLRUYzNFVCNkhsdWZoMlpTenVZSDBkVXNpY0Jwam9pTmtocUJhdzA1X1dyWTVJVWhVdzJZRWpiNzVFRzd1NUREdzd3bW1vQm4ydkVETWthRE1WVGpqUkZoSVZYbmtqdVNuWnhnM2ZaaHhORjRReXM50gHKAUFVX3lxTE9fUlRRS204UnpsenJGSWtxSnJiR19Dcmh2LXFMVWhQSzdDamQ4QlBSanluUDdfYUY5YkpXcURFZUZ3TU1TQVM1WFM3QnhoLWd0VFBXckt2R25razdOMEFvc0F1emhYVzIwZkY3OXc3Z2xJblJfTXo4SFZyekdPZDlHTDc5Ykp5VVlpaU9MblVhUlBhcW9Ta3h6SWpIeFZGOGs0bWh6NmNWT09yN3pjc0pzdXdqYlBjN25UajdLT3VvZEdNRlhxazh5ZWc?oc=5", "source": "Business Standard", "published": "2026-09-28 04:42", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOXdSQ1g3eFlqb0loV211WW1MSkhiWVlTNzBWd0M2a0ZFQUduVlI2bXk2eDBmYnBIZWlFeDRrbTh4TnNsM0hBSllPZTBHOTU2ZVZaQXhZOUFDczM2ZU1wdkZteFEyTXA1SFhGR1F5dGpDY3JGd0JyOEpnZEdmdWUzd3Fwczg0SzJyQ2tWaWxNSEJYSU5kdHpJbzlYQlAwWnd6bzBGaGpIS3Z3V3hlaVBWOU55X2Fyb3FLUE9DQ1pQcVlka1HSAcsBQVVfeXFMUGxERGozWEJnZFBKVXdKSTNKNUV1N2V0ODJPUEljV281NkFXYlpnWmtINFFlaUtfUDZwcUg5RHc5VlpRT3p3TlhzOHFKNkNIVXpfZi1SbXlTQV8xa25LU2FpTXJxNkRVNDJhQVRkWVFFaXFxQW1FcWVqUE1waDJKZDI1WDMtd05IQTlzdE9xNFFpdVRIRmJ3WGR5aS1Wb1Y5WWpMUTZmcWtqdnU1YnNPTUpTOHlvcmlPMkE0Ylp4Ql9idDVGcUxTZHRibnM?oc=5", "source": "NDTV", "published": "2026-09-28 04:41", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxQQl9VUVpCdDlvWEZ4OXE5V1pabEo4U0RPcVlBRXJuMVBQMzlWQ3Jidkxzc2drSUZPcEhOdG1jRmpqRXE3TDVIdEY5T3hCVXV4Ung2X19yRU1OcE8xUU1FZUwzR3ZTOVBCYWNvc1p1U0x3WF9kazVjV3h5Tk9PbElFSzN1V25BN0xDcU83cGZ1QVRTN2kwZWxjZW9VeFFZZTctcG5PWDdhbERNdzI4ZlZlLWJLYVdxUHZOQUJDWUc0MkbSAcABQVVfeXFMUEJfVVFaQnQ5b1hGeDlxOVdaWmxKOFNET3FZQUVybjFQUDM5VkNyYnZMc3Nna0lGT3BITnRtY0ZqakVxN0w1SHRGOU94QlV1eFJ4Nl9fckVNTnBPMVFNRWVMM0d2UzlQQmFjb3NadVNMd1hfZGs1Y1d4eU5PT2xJRUszdVduQTdMQ3FPN3BmdUFUUzdpMGVsY2VvVXhRWWU3LXBuT1g3YWxETXcyOGZWZS1iS2FXcVB2TkFCQ1lHNDJG?oc=5", "source": "newsdrum.in", "published": "2026-09-28 04:29", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb2JZRzNjNjBpV29mRkZobTRsNWJaVExQeWMxZmw0WjYzZnhCNktBQm5Hdmw0U3NrVGlrYm9abFZwRlZvendEZldPMlNlVGtqVFZ0ZC1rclZGci1yb3BjbVJ1YUlta1VYM3pBMl9kbXh1VjA4ZmtURl85S0Z4OTR0cDFyWXdkU1FiZ1JVdEZ4eVBPSUtJMk9RMnFJQUpxdjRiNmNHQzdmbnRwbGNjZUFJZkVXYV9yc3p3SlF2TDFkWk8tT3hnNkZPc1JTb3c1dkZ0MS12S09LWE9vaWV0SUhOOVpGUmRrZkJxbW9XQdIB8gFBVV95cUxNVVJKdDl3emc1ZEJXb2ROY3hadnZaaXlhZEtTZmZ1RjZFNFE1VVdJTnNxVFJFRWRlaTZaUGl3ckg2dzRfY2ZXTWxvS0dWVV9ibktOOGlsWjVmVDQ4YUN3aVlLaXA1anJ6YmdNRUM4UzRrZTJxWkE5UERZbmZJR2ZHQ3phMlg2bldoWDhBT2U4bVY4SnF2c1JiQkVHdXVVSGMwTVFJVG1GckhxdURSdkpMdUpfSUNQOWo5VjNxS3FEeGRNVzZiX0UzUVozR3JXMHduVzF0S2xnMVdhYVFaNEJmOHZvZGhfbkNmY2lMYlU2Y19wdw?oc=5", "source": "Livemint", "published": "2026-09-28 04:25", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?", "link": "https://news.google.com/rss/articles/CBMi7gFBVV95cUxNNDl1aHc2VHYtR3lHdGJnY2oxdXpXX0tNN29FU0dnYnZTX1hrRWFzOFBzSk5KTWc1RTFJOFdmT3VVMEFmOXNDcXhKbHdBMVUtR0kzclhZVDRLSDRHcnljSTF6UG40ak5SQmMtN2lzRG9QSkRNUzFidmRkSnc2aHRLanVnTURTNU9DcUZXU21kWVhoVUlacHhSa2lYT2tPMUJ6NUxkWjJ1V0xpYndCQU11S2djSjZ4aXpHdHpXRTZpRDlnZFZNNk9PU1hycldaa2w5Ylg1Ull2SXU2SlIwbDVrdG1RZUJaN1JpVjRUT0Jn0gHzAUFVX3lxTFBtcU5GS1BLNVRSQ1BWekxLUmhQaFFhMlZLV3RIcjk3M0RBVkpwU19mcmNLZ3I3UXQxdFY0WHBIMmw3SUtkeTdwN1RFa3RfbzB6bkNGSzJwZWtZN2dDS3E0a04zZEFid2pXVm9xejFDbUpLeG9hWGlfQ2p4NWZtakVWUmxLMEdteDBkVFFLLTlGWHVid2ZNYmh1cHdsS2R6UjFFUzlQNXdUX3VqSlRKY014bU1mcGlxZ2VGbGtxZWlDbHRZTnVZcm55NE5zaE1ra0lUVjlTNTZaQjhQbEJLOV9yWkxSSWwxZ2FacHBnaV85SzhfWQ?oc=5", "source": "India Today", "published": "2026-09-28 04:17", "score": -0.511, "label": "Negative"}, {"symbol": "MARKET", "title": "Mkt crash wipes off \u20b97.4 trn; Sensex down 1,180 pts intraday: 5 key factors", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNFNEZXdXeWxyUDZNNkJvYmhvM29nZ05JbUhkLWRmZ2VWME9TMFQyTWctZjhoeWVNQ3dGZ21NcmV2THVjUmt1TTBwTWNJTmVnRFVzVXlCekNMZnBqUDY5M3RWSWpQeVBYTXl4Zm1ndjhBcmZUV2ZVdHQ3VUFxQzN5c3NON3N3Zjh3UjZYSjR2VER1OXBWMkZOUExnTHF6OVBtTWxCM09ZVHhmdW9DZDZ2U2FxVEtGVHhIVlNsLWhkcnByMmdVaGl1OTFwQW5GZnZ1OVJvM9IB2gFBVV95cUxNWUItS2dqMFByNUlUcXdPMUdQSHZxX3VTYU1PcEdaWnFaOUo1MnhrQWQ4MTBmaWM2eDY5WURsaFpId1RnLVFJRTdadERxTDVKc0J0UkkwRDM4V0g2WDMtclZ4eEtxY3NCVTV5SV9tQnhEZUR2aHJ4N1Q3VzFLbF9Rb1ZadHN5Vk9tOEE3THlxQVViN0tfZnB1bl9aQU0xRjFZc1dqS3RKVWpLUVM3UkV4aUYzOVNaMDlBbEM3bS0ydnltemJ4TEFOZWt4OHNOcnNNdG5DaE5GVVRHUQ?oc=5", "source": "Business Standard", "published": "2026-09-28 04:11", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l", "link": "https://news.google.com/rss/articles/CBMilgJBVV95cUxQZi1NX0ZnR1pnWl9lLURWQW9uazJudU5adU43UVVWdG9BV1A5WTZaN2RPZ3NSWHl5bTlCZlA4ODkzcDRoc3JWVEtyRk1NbGx4MDQ5X3NGZ2ZHVW9MWnFTV0F4U3ZSWVA5S3BtbzdtZFRLT2JVOXJjZjUtNENidWtZai1JaTJPc0VQVE9mdDE2VGhBNXByZnZ3ZEtVdm5ZRkFvUXd4UGdfZjJTcFFRcHkwcmo3d0p0Vy0yZXNkV3RXV3ZFcTRLTlBUNGRrNXNGMGVpUXFKMDJzUndJWXpqWnpGSkFIRVJ4Q0MzQUJVOHMwT0Z6X3R3aHZ0YzU3TmN1RDZVQmNzWWNZbkF1YVJ3YlV2Tndac1N3Z9IBmwJBVV95cUxQcExWMGJPZG5EOW5QWXdrOGFGVWpSNnA2bjNYYnlRbGdhSG13ei1YYXExbjZPZlkweGtvRDJ4QmtZcFNJbmthU2xJNWxnV3hVYjh4SDRzU2k1cTQwcG9BS0VCOTlQcUpuS3FzREFhbXRIWVVYQVZRZEdHSE9HUVRWYTAtUFFWX2M1RmZXVXhKUzd5RmtuWjBhTi1wSXZfVXBWWHRCOTV3VGFRQ1NKeXQ1WU54dlBQZmpteFlFa3JrYlRkYnRoUWJsMVJZM1RlMnFWVVZGRmNUWExEUzZJUHRCcGpmMl8xU0Y3QmRBMTdESW85NTA3LVRGODFGakpiY2lIUlV2bVJLMWhaUVNqRl9HMmhsSEU0VFNGa3lR?oc=5", "source": "The Economic Times", "published": "2026-09-28 04:08", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi-gFBVV95cUxNd3FFLUl4RkRuRktMczNpNmU5VmotaWdaUENGMWExNHZJOERsVFNMQ2ZiX0tDSGFXYXhxSjVUM2p4QWUzZThrTkxDNXR6ZndFMXU2NEFTNG90Wm1JVnZpNDdaRU1vSnJOUno4VGN6dDhndTdDWDhhbGVjQ25nSDBWOXFGa2xUWlEtRDQ0dVNCZ0I2TWdQcmlZWkxLcllVUXBpa1NpdjItdDBhZlNLYUU5bWhwREZoSWV2dEMxMWJMNUZza0FpQ2dKM0JSdU9fajZEdmQzOXFnZUxqd09wcW9qd1V0alZ1TGtFYWs5d1k4eGc2NVZvbXFONkNB0gH_AUFVX3lxTE5yLU5FWTlXQmdqRWY5MS1MYXRPVHV3bjNkZWlEa25SVC1INTV0QjQzOXBxVzhFbEUxME1WbU9jbTZISE1fa19JS1dwRW9KOVplQ1A4QkNWWlE2YjM5NlBCNndyN2F4T2VfVmlOVnhEQzMtSENPZ2N2clVGNTdtVnQ4SU1idWI3eThwenZWRUZ4NzNwaHJvTllHUlBpYnQ4SEEtZFlRTmJuT3dGU2ZpRTdMLUFraWlfNjl5UWFZLTBlX2VMSTdXdWV6cXNOaGFzRU5QSjBOcHBPT081Z2R1d1JWQUt5TXFieXRCbGFLcGRkWVI4OG9oRk1YQXJuQmdrRQ?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 04:07", "score": -0.44, "label": "Negative"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines ESOP 2019 Share Allotment Explained", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxPUWZWQWFhUXl0MHliZTNDMXZuOTFtUXB4UTgxU1hJTlotLVRrSjdSMXBGWU9vaXk4ZC1vaTVzbTJMb3djcjZfZi1xYkR4clBmdE42NC05V1BWbmxfZTRXN3pDS1pKNmF0UWJ5dlE0Ry1qczcwdUQ2VHM3V0hzQ196M0ZxeVBuMkNXUXR6X01mVm9HNWgtVW5XamJNcVlTdW5MVklzZlRWdFM1MG1VNDdJbFZLcUkzVENpVVRrWkk5NTJJWG5hbWtCWmJmWTNtUDB0VWhEV0xnZEExUWxxOVhjejZ2b3BwRFk4QlE?oc=5", "source": "Kalkine India", "published": "2026-09-28 04:01", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 \u2014 Five Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNWmNXeUhrY0hPcXlaYnhxdEpqRTBKbWJadHhpVGFOX21Oc1FnTVM1UDNDOWZ3dU1jd2RjNTA5VTV1SnJHM1YyNC02dGlZYnhzeDZramF1NGpBTm0xcV9DS2ZIVURQSjlrT0M2bTJfY19qc0VmRHRBdWdZdXBmcC1pUHQzSzF4OThzSzFDV2sxbVVUQnBCWjhoemhmSEhyc01oeWJJeGlSbXlaX0xiUl9qXzdBaWhHSUt3eUdKMTh3djNuZlg3dVlqYUNjMkhpX0RoazhISVpBTnJFbmFVVGtZaFlKdGY3Rzd2SkxUTtIB9AFBVV95cUxOLV9xeHRCVnRiX1FUSENXSHZ3S3NqQkRRZFA4MzZPYkd6WENNM0NZQVpMU0FQUUJnWkVROVNSbTFrMkdJaHltbkUwTExjby0wVzViS0NkSVI1NDNORG5wNkFtSXBwMlRNbXhQbllkYnE3cGpVeVF2a1RrQTJqNG5oSnVsS2pyc0dUVEtlNnM3eHJ3bmJwbXBxZC1FSG1MbnRENzNmUFluMzJwMlJzelA3M3R5Y2V6SXZreFpGYTlZWXlITE5xS0NMdDZ3M244U0NUdWQ0R1N0TWE1bEJLM0hJYzlmYWJjcWJUUHhMVUZDZlJpMExI?oc=5", "source": "NDTV Profit", "published": "2026-09-28 03:58", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxNdFJQdUVBNmhGOF9naWYwc1VCWWozTGVwOWl1b082TGI2bmppQVQ5dmxfUWo0RGhBQ29IU29vaUJ1cDZCNEJoelpMc2g0eGhldHVGdy1WeWcxVEtZcDBDNDlfRkxNZnRFMURFLUVfY1U2UG1YTk1vampZZUozYjEzU3JGbDRWNkhhVU5qVy1qcVlhdWxFa2YzX19vSjZ4NEl0dk1reVhEMXlPb1RTTzdkNENIS2RraEdzTTlBXzFteWpPMkpkUk9MdEJqaG91ZTlUSll2UEVwcjNoM0FDdFJQVUJCM0JLQTZzS0xTVkNJQ3VIYUVyV2czYWxBLXRUNzlPUkwtTHFTNUs0cGE3VWdj0gGUAkFVX3lxTE55LTJyNkZRSldBTGdKNnM1THNXOEtPQ3FZaXdOWmhNMEVtby05Y0xaZV9QSlFuNDg3TFlfZlNpb1Z1eTI1S1ZaZDJVeGwxcktWMW9pbWxRZk83ZE1scnkxWGlVOGhDQUJJNWtnTS1MWV9BcDdKRmYybmZSVEJydVdzS1dTVGdvM0c0R09GdUEzd3Zfb3pmMXdSMGUwTk5uZ0xTTlRmV2NZWTV1M0FjWmlQZ1k3aW0wZE52QmlpeTI4bzFHTEtnbjRRZWtzb1NrTnE5dU1XX1ZQV2cxazdKZlRCNmZ6UkNSaVNnVGZVZVV4R21xZ2ZfOVBzcGZ2N3l2RkI3aGpqNnNJWjdTNnFwYnNQNEt0bw?oc=5", "source": "The Times of India", "published": "2026-09-28 03:54", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxNZ0dpRTVlRDlxc1RtOW81dTVmTTREN3MwakViZzNUakNFTDJkWkt2QkstemktQmhGZHBFWjRZYXhHcVZDcU83WWpLeXpBUDZyVzBINUVFalBwaDZ4YUhwOEdXN1E4TmVTX1ExY1U2MV83T25QZFhsa1NVcDRlWmtYSHlXdWFMTEIwcVdoS2tRWWZ6V2NIVFZMMHloczRjb0JvNHhmamx0SDEzZUxtLUJDeVgtWTNTWm50SktyR01HV0d1cXI2MmU1UWNseGFDRTVLbGx6b196aE5BMzJYV2lLYkEtZW9fcTRONVHSAe8BQVVfeXFMTVh3alpWbmYySWstWjFjN3NmVG5Sb1kyV0ZjSkYtc3MxN19pMDA3VkJwRGh0Z1FYZEU4X3BTVWkwRjlLdGQzTW9DMm5Nb05oel9SdVZrYmxRT2VIZk1nblpwMUZlWDR5ZlVnY25oU3BwaHVybk5ibEt1VXk5dS00QlBqV2ZLY01WWXN2TWNvWnc3YzRfNXBTVTJtR0w4MHRlNHBWbmcwS2tpWEkyRnlvRFFHSUtsdXdZZ010MVFsSXBEcEwyNTlNM3daV2l3Q2s2ZGVERFJNNGg5NE1iZzNJRnloY3FVYU1BRWUyaWNsRlE?oc=5", "source": "Hindustan Times", "published": "2026-09-28 03:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQU1VkYW85T1l4Mzh4SDJFZDBhZC1GczBiSUw3TmdJYUxvTW1TRXpUd3BTOVZwY1FzODlGUkxyNFlXSklFNzBRWUZ4WEpGdUZDWWRIZ21vM05wMHBnQ2N3UTk1VENDZTVYeHJsSEIwUG15RmpnRi0yOUdBaFRTdFg4Rkp6LXBSbzVmQjRQU0V1NXdCdVRmby13QXZqb2Zzb25Fd0FsR18yZW0yZlZBd1VibQ?oc=5", "source": "HDFC Sky", "published": "2026-09-28 03:28", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxNQmUtcnhXbVNOQ0lacFk2Z1JXa0JON1VtZTRsYnZVMDlKdjh0dXhobk9tajVtRVdUbE5RV2MxUy1MbUpkNkc4UXNvalZoZXltbUNScGEyanBReERmbTRuQnB2d2M2dkU3NkJ0anMybXdHWV9QWElRVG9WcDhNSzE4eTV4VWs4WWluaGpYR1NZZTNuYVFPNWZwUk1YcXNOR0NrN0REb2V5eENFRjFaTVNpeWtJdw?oc=5", "source": "Reuters", "published": "2026-09-28 02:19", "score": -0.542, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices \u2014 Five Key Factors For Sensex, Nifty 50 On September 28", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQYTlhOERzdTdrb3FJNkRCaFpyd3p3dGE0QjFQNW5ndE9qQ0VTM3gwOURRS3hlYkxQOXh5UnUzYlVfMmxYZmtkcHVpZUpZZnhsNy05RWRKWi1FdHR2ZWVIa2F3MmxBTjBCeC1rNDBQQzhSYkVKSGdyV2pxa21xcnd3dk82Z2JOU3FMV3pKNzcyQjFreUdPZDlaNWh5WGVLUE1OSzV1VE9Qc3k1el9pOFdKYzBKVEMyRmZRMU9icTFpZTdQOFB5UEFCLXEybjl4MFFJam9tMFV4aXV5cjQ5bWR1Mnh3SUdXYzhtVUk5VU1uQWlMTHFwdlhr0gH_AUFVX3lxTE9yT1pHVWp1N19wOTVOLWdVWEloQV9BS0lKeDhwaWcwTGNqSnpxUVFIRkg3Y05tRUc4MUNDOF9CVm1EZjYzdnlsX0UwVkRDaEVKQ1ZNcVJteXhQQnpjR2JsMGh0QkhNcmt2eUxOdlRxTjVaMlFZWGtVSkU3Z2xfU1BLNjRrYzZ5eFE2V202Y2RKaVV4LXdqb2FNZHVDYlM5WmFyNWVSWnRKVDNab2h5VUhBaDlmbUVJWFNiOU9qYUNrVTJybWpyZkY3OHBiRUl0MTNBRjBNQ0lfYjljbkFCUE5oS3hDaEVILXd1TDNDRFVaOVR0enZ3VzBZZkJzQktabw?oc=5", "source": "NDTV Profit", "published": "2026-09-28 01:58", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOd3lLLTBUWlJpdVVESnptNXpwZnVmVk5zbTU4LWV3eTZyT1R0MzRfVFpFYzltdWhnSTI5Uko3M2dpSzY0NGJwZzFfbzZXM0ZOcV96T2hHaWQxR284Vi10dHRxeUVCQUJrV1lCclJZREI0NlpSdHp4Q0R2V1paVFlVWllhWkVCQWdaTlhiUjN4bENkS25yU0tJczFLVE9vUE1rY2hvc1FTSl9QZ1RkX1Q5ZVNfLUx2LWpmN2lQQ1pNMDNUS3NJenhycjRsNUNjbnZRMFNZNllsUU9WeU1xTk43NUY3OThtVFJadFJUSWhuNnZEMUh4VGdicDdNdFI5QkV4U20wY9IBigJBVV95cUxNVE84MHlqVDk1czZmeWtPckg1UUh1bF9OQU44MFlsSkdUeU14X2xZYXozODFYb0JtaGMwSDFVNzRpczZZb0MtY29aYTBsdl9fRFgzQkhhNG5Id2hYcE55WjhMYUU5N1hWRjg1RjJ6NGpuVmIyaURHQnI5d1RsVUxxRWZ2M0Q4NjlLQ1ZENVdyLWtSUkNrZG9MbVBwTnVENFc1UndfTzhlby1NdktITDZBbldMMlZua0xGbnVRTUFucy1GYVRaZUpPbEN4VlhTTGFlbElpVXBiZnNPeWpqQzVjbHhwYnFXUHBzWUM5WU1UVmh4ajlKbHpDRHdBR1F1bWNhNEhfZk1DNGRWZw?oc=5", "source": "Livemint", "published": "2026-09-28 01:20", "score": 0.842, "label": "Positive"}, {"symbol": "E2E", "title": "Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxORnluOHJzdFp4bmJaUl9hdWY5Ql9WeFd4cnF2ZnVZdkRIbGpTWlRzSlBxX1lBb3VEcFVTclJjQ0lVVkFKcGZTUFhLVDlDVkJkZDRnY3VQQkdlWFFOS2M1VVNNa1B1dmpueVBIRFNyRGhKVmRpd0IyV3NmTHNrdTZpZ3BKN3lSMjFnbGNyYnFtelZWWXgxWF9KYW5WSkoyQnA1R0dqTHBscWRHVVg2eDhveGtabHVVUjNoNTJCYjlsbGh4Mjk5cjgySUcwano1THJpbUY0X0swTG1POTA4a0ZSOEZFMVFJakg4RjI4aENIaVdZWWpSNWU5QnVDYkJyeTZlMXc?oc=5", "source": "equitymaster.com", "published": "2026-09-28 00:30", "score": 0.557, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxQNmdxX3hPMzJrejF0R0pvaUNBbDFacW44MXRuLXZ1bF9yVnlwTXFwWGlOZUh0U19XOTJhYkZ1cHJ6VkJSMkk0QVAzcENpdkNJWVRWMDhkYXJ0NUdxRjVnaVhiS2VPWExCMWdaQlBmVzQ4a0lhNlNjNnV5Nk9xcV9zOWMyc24wTFdBY3lCbFdQdXlsaWFNdnVxblZYWVhBcm5wQW11NzdmV01JeVBsQV93eXJuU0ZaTmM?oc=5", "source": "scanx.trade", "published": "2026-09-27 17:20", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Ahead of Market: 10 things that will decide stock market action on Monday", "link": "https://news.google.com/rss/articles/CBMi3wFBVV95cUxOOHlGS3FhbzhQTUM5VG9rOXZjZXBTZ2Q2X1VJWjVOZXVEM1hET3BtSktCcmlhLXpIX3JUeWtBWlRNX1l4dWk0aGJiNFRuRVlzaDhfVUpzeF9jNzNUT0VpcFVSZWlGNkR5Mm5qeEU4ODR1RUpZcldoc2t3TkFweE8xLTF2YTROOGpkZ3lkWGRFQkpaY0xTRFB1akhkbG01QjZ1eXVBWlpjZHdnMGR2a0ZNODZuQWZ2cThKTG5nb3V1WUxxS3BCRHllVkhKM1hQTWVpQzd2WFU2b2x5TEdYcG5N0gHkAUFVX3lxTE9uUFVOSFVOazh5cm5jb1RDcVU5YzMwUjBJTV9yR1JmeHhaeTB1WmNIUS1faENuVTFJZEVxSEpheGpGcGMycjEwenhnekROSnR5OVI5V1l0TkJsTHp0V0g3MkF1TzNpMmZCUm54dXFiS3lJVWhGTkRnMklIT1pucDc1U0hrSkFoN1dkci1UM1UwVDdoNXNiZFNPWU9iUk1kSTV0RFBTTVl1UkJxc0t4OUIzcXRWWUJMbXcyZF9zZXp0c0ZEcUdBeXFKTFdxbzJWSzl6ZUFZTHI1aDZtdWFOOWhBbUQzbQ?oc=5", "source": "The Economic Times", "published": "2026-09-27 11:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show \u2014 3 reasons", "link": "https://news.google.com/rss/articles/CBMilAJBVV95cUxNekdIczJ6NEZleldrYUtRZ0pEMFlMaHFDcWdFeVVhVnJROWRBWTVFeURzYXM3NVY2eTUtZmNMOVg2VVF6eUZOZFpzcTd5S2ZqUmVJYkRaYnd2RF8xZjlDakRzUWFvaTlVb2REeWo4WUF2aTIxZUVncDVzY2o0Tmp3bVR5TmpRQmFSMDZzSTB1MFBCSWh5RmJ2b1d5QTNDdHlSN1hVcEJqUHdlOHZ3VENMVm8yWDMwV3N2M0phaDNFZzZGdE41OWVxbkdjU0tDNnFnTnM5Y2phV1pIYWN1RF9DNDhtd2JBd0I4WHRlMGFvZUtHdXNlWHJVYnN6eTFwVjVhODVsYW04ck9LRnJhb3NzT</t>
+          <t>losers", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNMmZlbEQ0Z0pQZ3FTUXJfQ3E0YkxMTFZlY3pIRjROZTIxeXE3T05xbW1iTUpkV3QwTGlqUnplMUtNZHF0Y0ZzSXBnS1luZG5UZ2h0NkpxNzhPZW52NGUyMjZPaHpveHVHZmpHM21TNmRtS3FldUdGeFRyMEk3MzhLRVkzMWI0RVhKbHFqa2JCUGh3U09IckU2bTEwbkxwenhaSC02X2NVTVBlT0FWN0hPWGFleXdzR1FwZWhBYW1kUmVMdHdha0s2REl2LWxjczAtOTBIQjMtZ3N2SnZHNDdRY3VydlJCM0XSAewBQVVfeXFMUHQ2MUh1aFVLaDBFTVZuR05mVGlpR2V2QVkzMnJFSC1DRXROZDNRSENDMHk2blF4TGR2WllXRk13YlhFRTJJT0UxN1BPbnRBcEpJZWRSc1VTU2tfcWwtNk5vTHZYdjlRZ0FjOG1OYlVuNHFyQjN5MGRicU14eEpadzRkMjVYdmNWbG1Zbmh3ZkJicGV6c3ppMlMtLWhqazd0VkpsVHEwNFlfVFlOTDd0Zjg0OWJLeFBXMGxGWlBzS3ZheDYwdDN0UWNXdl9BUGFnTnRMamNnTWJYUVNmRWJWTzJhN0U3YzU0YS1PSDI?oc=5", "source": "India Today", "published": "2026-09-28 10:05", "score": -0.178, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVkFmQXdEZjZITFVKV1BEOHlKXy1rajlNZ3NuN3N6UXdZa2lWWVFxNnhXOTJtYmZxOVpOcVVpLWE3VUhwZUhjVXBYV2VleEVpbVR4RTRsc05tTFBIcXNoME5VaVlJVFR2ZUx0Mmx6RXlHTFhKUUdFU1J2OUhXNERPU2xsa0FGTGFOcjJzQ0ZlQkIwY204X1Z3UUZTMEt6NDZRVDJMbUQzclRobkxrcFpWbGJTQXJnRFR0ZHBMdURjQjgxZw?oc=5", "source": "Kalkine India", "published": "2026-09-28 08:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Nifty, Sensex: History favours stock market comeback in October; stocks to watch", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZE5UeURMRWtrOUFNekVkT0ZOcFI1SkE4Q28tZDc1NkJvbmFaakNlQlBDWkt4RDd6b3FpazN4NjRzWGhMN0RaYXY0U05IVEY3bU1lN3RFaURJSjRUTnF5Y3o3LW1wT3RtSkx5LW5yaWpiemJ2Ym1lYjdtTmpKY2lPWk04aVhiR25wMVl5ME9HSmUtQ3RIaENZTC1pOHpOekZVUVNSSWlFaXl0N2NrS19MeVpJdUxLeEl2blBYSjNseU41V2NjTUxmeklyeTN2Y1B2eWNuQWFTS0FVX2hJNWfSAeMBQVVfeXFMUDhHbWlIakswUl8zYmdMcHhmcVlGQ1V4RkdsdHhqN19JMjZwT0dxMGtVeHBQX2gxZk8yVlFwamlzblJNbUZJZU84N0RRTWk0U1VJRmc4VUZyV2p5NnJLNjRYcExKb3NKWjg2NmlMbUhRVFNDZHdocnNsMl9RVTF3YjBkYzMzaTRqdFAzbE9jX2NKWlZWb3FGOEFPMkktYURRbUZLYTR3SUVTWG84cXo3TzItZGhlOTBoNFhfRTlXSnNfOHJPNVctVEFEcW5WSzg1bHNHR1c4MUoyODVYWnJqV3U2U3c?oc=5", "source": "Business Today", "published": "2026-09-28 08:15", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher", "link": "https://news.google.com/rss/articles/CBMiowFBVV95cUxOci1kRlliVGdLVkdiMUM4b1lqbEFvLUdDV0VITWp3NGlyb2w5N1Rmc2pZUi11cVhmNkxDUlkwZThkS1hOZ0lFaXdmYXJoa3FiT3hfeHhaNkFwdEg2b0V6NHZaZ094cG9RZGQxLTMySlZLX1J6SGRXcU1Sb2RuTng0RzFzc1lZMWNHNjY4b29HdWpzOFRWclh4S1JGUjlGelRRSzlv0gGjAUFVX3lxTE5yLWRGWWJUZ0tWR2IxQzhvWWpsQW8tR0NXRUhNanc0aXJvbDk3VGZzallSLXVxWGY2TENSWTBlOGRLWE5nSUVpd2ZhcmhrcWJPeF94eFo2QXB0SDZvRXo0dlpnT3hwb1FkZDEtMzJKVktfUnpIZFdxTVJvZG5OeDRHMXNzWVkxY0c2Njhvb0d1anM4VFZyWHhLUkZSOUZ6VFFLOW8?oc=5", "source": "Free Press Kashmir", "published": "2026-09-28 08:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHU1a2VYbkdKb1k1RENtVm56MHlVeE9EcW1DQWd4ZmRyY0g2b2JqZjkxVENveE5US2JvaWtoanpITFc5NzVFS3hzMWRxcmtPUFJ2a1NBX2xsVDJUWEZrekpKNWVLZzZ6TlRQUnVoVWZWTzZ3Q3VBWTM0WkxqRzVhM0FzWm5kNmtCa3JMUDRENUwyVU1iZDBNd1BMRkpWenlNUHpLTDFScU1rcW0zcnNBM3pWODVoMHV1WlhwNmVSSllWTHVWOW5hRE9B0gHPAUFVX3lxTE00UXRvMWNWTlhGMWphc2xibF9MLUtJQnFQRjR3UG5nbVh4M0NWMVg2MzdockRzaEdnWlpTcEtyM3dGWnRTbnFRQnRKV1JmZk9RdWY2UnpYY1VsWjRBSDVwTk10clJnNHlCSEs0a2g2TFA1alQyYUFWNXIzWDNfeXlOejBhVGJrQTJZRG13cG5XVEdVWExyM2Yyb1owX2pmUDNTWEZsenBGcUlYdWpWZ2NpSXh1dmt4blhQYUptLWFNNnBndk04NXhzdVc2ODNNVQ?oc=5", "source": "ETV Bharat", "published": "2026-09-28 07:56", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxQVWNmQ2tBRmd0NTdUbmZ2YW9kZW1wdDZrMXU4Y0gtTXZPYU9uc3JGRGJXQnhBaEY2YXk2TGhCWlhqZGU5OWs1eDlPOTJMcHp3ek5GUEYtcGQtYUdUVmpTZzVNZGlnS2UxVXhHZE9DcTYxSk9uWkFmaThOdUdzbnpmanpXUF9sSVVReXFLY29VeTg5QUZPNkszSmNGQQ?oc=5", "source": "APAC Media", "published": "2026-09-28 07:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxONU5xeDQyaGZ0M2JBemJwU0REcWJxYkZWN1hxM2d1VHZBOGh2X3gwR3plbk90RlZMLWtWZV9jek1KR2lsTDB4d09oQlJzRTNadHgyUEY4bHhFbGp6eVhOWDhqLUtQWkpIUldLLU1EbUoyU1VfYmNaOVdqWnJzREo0Mjh3bU5wTTZPN081MmVFY0liRzQzVEtZRWFVMURCaTJZX0twZzRZWVJHVV9KaEl2LUNFZzBpdmt0RFM1OXZoLXVKQmt3WmlDSGR6VHZFMWdiV2dWcklYVWxuTXdFbXc?oc=5", "source": "upstox.com", "published": "2026-09-28 07:36", "score": -0.806, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxOMzZwenBCS1ZIMUJRRXVOZTBBME0xU0N0WGJsVEVfQkVhZ1NtMEplNUNXM1A0WGRZLUVOZWlTNi10QUVQQnJRSnZDZTh0SXVlQkN5eDZ3ZWstRVQ2TlctUE82ZmxJRG1BZkw1NjZGZGYyZWJiZlZ1YktSZU5OTk5MZ1A0Q2NyV0wzZEd6c3dHaUwxcUpZa3ZBQ0g0dGViQzhfTFF4RExTb2p4azg0WjhlVTBlSUZtSG80clVYa2p2MFBuZWIwVURXMGd5dG9wVE5sWUNLbGJCb1U5SjNBcHNXZnE2dGNkUlVhVUlrNndWVTVpOG1jWVZYeFppQUdRekXSAYQCQVVfeXFMTWsza1RTaVB1QndYVDNrWE1GWUo0QkJCd09tUGxGUkx2T3pVamh4d1VTUG9FYkxpUmpRV0RlaDhxeXVMMFN1Vk9sMVRIY2xaUjNXRlhYLWN0SXFuT2V4UktnYlRvVnZzUlFQbkJFZlNsMnBCR1JZeTVvRzVUa1duQm5hb2llbUlPNmZuQ2owWUFPbDRJWUV1ZHVoZWd2ODJMUFo1V3g5RzNfRnZ4MldzV0F3UGJfV3UzZ0lxWjdIS0hfZ2JXeXh5VFVtTm1JVnNtX0d2bjAySWZZU25TZGhiUjhkVERUenU0T1VJTld2WGM4QmVOckxtMk5QcThMbnR6bjg1cGs?oc=5", "source": "CNBC TV18", "published": "2026-09-28 07:06", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxPUkRFSHF1dXJEMUtBZUdNc0FqX0g2TjZqMV9MSFRVSXdDSHRobkFERnFiamUtMDVVcks2NDVkS3JYVzNYR0dCMnFlVDVobmpEWlduX2tCODBQMThWMm96RW1BTUlHbVlxbVMwNkpuWVphWFZJS1pTUHdwYWFJbEM2ZzNZTWhYS2luLWhYR1htelNSS3E1OHpXaV85Rm5iQWVIcHFnNkpiYzFFTHB5eXktdEplbUk3czJwV2dadzlBR3MtQmtlNnl3VDBhOGc1VGs1eENMWU54STdnREtoc2NOeGpJWXMxSnp1VGEtUVJWS2c3YWPSAfsBQVVfeXFMUFBfZ0J3ZVlJNGVQMHhXZTNvaU1wUzh3dHYzOU1sS3pFX2RIS01fSmpIMDRLOExqVmxMemRwRTZjbmxNcFRHbTlScFhKUHh4TXJzSTJyR0g1cVNwRmd3WDVWck1iaDB0b3FsVzNpYy1TZUU3RExUZjdfcl9ZTms2a2VnZUQ5NW11VEdGbFU1VmEwUjRPaGNHS01sVDVTMDNpVUltUFFUc2NKRDV6bmVyZWRMcDNXTzE0cEZLc3lNVDlpTmZMd2ttaVg0Ylo2d3BYY3BJa3dUcFM5UU9yLVpHSU16MXVUOUZ1dUhmSTdjVTRfTDZGZWUwd05zQjg?oc=5", "source": "NDTV Profit", "published": "2026-09-28 06:47", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday\u2019s market crash", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNeDY4VXlDMWttUXVoM1pMNFhYeks3ZVJpaUI1eDVJZklkME5QbmdzcFpRbFMyT3JYUEV5REM1V1hPSE9JckhRcE5EU0xpOWFfZmtTdVVqM3h2TDdwLWJDWUpMb09XOHdkVURHaUx1Y1BYNW1qbWh2cUpTazhOREdqa0lmMkl5d2pSV0RqSDhUOXlmT2VCWUdxdlZMV0lOeDc4ZFJIWHk1ZXhhbUhjUlpVSmVZNEY2cVpTQUxXdjVpOFJEWDU3RGZOemRCVEJiLUVSMXNhSWE3N25TQVV1eUoxMjJjcHh3YlU?oc=5", "source": "upstox.com", "published": "2026-09-28 06:40", "score": -0.595, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: decline, valuation and peers", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE43Z0JKcUo3bkM2R2FfLWQ5TXNkQ2dpMnNldEZ1UHU3THMyeUkyTkc4TmN5V3NEUjFiNGVEQlBWd1pwQk5lZk54YWIyX0F3ZGNWQWJJc1NGY25WakxxMjQ3VWFfRHZhN291N1F6Wnd4YW55TjQ0eXJ5bXNuMA?oc=5", "source": "Univest", "published": "2026-09-28 05:52", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "India VIX spikes 14% as oil, geopolitical risks trigger market sell-off", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQc3R2Z25xanJ3ZVVqYmk4THp6a0pjWnc2UFg5VUNQLUZOaEowZW9WREszOXhBNURRYzh4ZkZNNWJaUmx2TGZjZDBVUUsyQ2VRczJUa0lvNzBLVzFZX1ZhdlV4R1Z4T3pIaWZOdWVvaDcxLXJ0Q1hxQzNaaDBURkRVN3VYT3ZUd3ZjNFNCNzJkZWtnZHgwQ2ViSWxHa1p0TUVlRXpROXVQaTNnbGtHM1dOOHkzUkJtSnBXS0YwU3JEd2J0VmdpQng2bENyOVFfTHhiTXfSAdcBQVVfeXFMUEE2WUJINWNtZDJCUTRSY1RsRHJsWUVSZi16N1F6YjBwVU1keTJZRFpUaE9rZ2FYZ2lKdU1KaldxM1ZFZkRMelphRi0xTnBxRWczdUNlU1FQTExxUE1qSnBzQkxlVGFNZUwwdExoVG91NFlEcHdOOUtJZ0xmZ0wyMnh1QjJrZzVUSWMwX0JYbHNBVVBNNXJLbkx4UG1GdmxKNExxWVdpWFVYUkoxSWRHQWRmTWh0QlNzSTVrMHlRaGVjSFowbUtkdF9GR2FUN0wtaEJWd0t5SWM?oc=5", "source": "Business Standard", "published": "2026-09-28 05:52", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxOZFhpNERkTkx4Z2RRS1k2ejBhN1IyTzR6a2g5MjJ3bkNjeDZlOWRBSmlIek1xQk1GcVIweUZvcVFEcGwwSW90RThvU0J6cng2YVpLV0tZU1dQQlhGZUtieFVuZ3BmWXY5aFFkSlRuR2p2ZW8wZF9TQmZ2RnJoNFV2Q1lMT2JGMkxLUlp3OF81dlkyWHVmQ0xyNVg5R29GVXZkR1NLUkRqTzF2ZXA1cmtlcEptcmJNR3dwRi1R?oc=5", "source": "India Infoline", "published": "2026-09-28 05:42", "score": 0.103, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUdIB8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUQ?oc=5", "source": "simplywall.st", "published": "2026-09-28 05:37", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r", "link": "https://news.google.com/rss/articles/CBMiwgJBVV95cUxPQ3drbk9QbWRHcU9uVDJLU0EydWpPdVZRVE1rTEE5bFZadHZmUVJPeG9nUjVYWnVvSTkzNzFyNFo3TWhfN1lzX0ZScEVrSnZETUJ2MmtDaE1XYjc2TXo2a1p0UWZhcHprU1lwM3V3YUNUVzlTc3l4UXdCLVExX3dLQTdRaGh5Rk0xUDQtR2lkY3Mxd29QSHNPRU5fRDFYRVBSbC03X2pFaGpnWlJ6MFZDUGlicHlPUUpXeDh4ZU94UWR5ZHNCZ0pydDdFdHZNSjgyRThId0JfSlcxVzFibmR3clVwQzllekZnLUJ1LTdZcHpsRkt1YzN0b1FBT2FkZF9zblJkRlIxdmZfdzNFSXllSDM3b19zME9xaXhlWGk0Qjd5TWwxdDJaenFsOE5iOUNOU2VKRkxYazExZVAxYWJuVVVn0gHHAkFVX3lxTE1EMGdQdWlWbVp5aUpTbEJmb0M5dWQ5X0xJYmNpTFJJVERpUDZkcVo5V1ZGeTNyR3VmYjUyUDF0bG1HVlBGQ21nNDBfU1RZRTdYTEZFTy11OXExZmNOdzRwQTFQNlBRcFZ6NVdDSFFkeWdkV1ZGdm14cXpoTTc5eFc2WkZnVTQ1SlZ3NmxCOWk1b1BWU3doODZadUV0c0tkQ0VCeERINlczUmlYWmJ2MjNoblhPeWtqa0NvU3ZRcGw4NlQ3Mk5GcTFlZDIzQlN4SWxiNE5Md0ctQVBmMklselFGekszWTlFM2JFN244eVJtOHctcnFCc0RVM0Z4OUlqVmctZ25xTDVnTTV4djlfc2U3T2pkeC0tajA2ZnVKRDk3eEJ2ZkNWSmZicmVEOXN0UHpfRkJQdlZMLTVveENMYmdJenM0UFRfRQ?oc=5", "source": "The Times of India", "published": "2026-09-28 05:18", "score": -0.691, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeDRfUkctTnR5c0x3dEhXcmFSWWREQnhLUGMxbmFRT0RpWW1CbkVpN3dkcjJTSUZOd0ZpTjF2M3U5OW1vOEdHS3BKZG03d3BhenZtX21jTEh6VVc4ZC1oazJmSGJCZTBQTVZObmVYeEJFT2ZuaVd4OF9rbWNyUGo1T1ZMZFFtY1Zpd2dSYV94Yk5uS3FRVWFueWpYaTNyVjJVdnVoRzVFaGhvc1pOcmJOb1BWN2I1VXBTTnNNWURYZ18tRXFkZHR3Mks2TEk4X1lMb19NbVU1am5jd9IB4AFBVV95cUxNbVVHcVRveFpQaExzeVVnLXV2bTRTY0dTaTNSWDhoWEdCVkRCZjdZY0I2TElNdWxlb2RYVThZcXFFM1VDQVRxbmRETlVSTGJjX1R0MWpCQTFId3Iwb0hjUXF4bHhoNjNhZlBoeFptZHVHRWdwYTIxd0N4dmZtNHNFRXhvc0h4TVFXNl9ELUhkQ1VXS2FjV19NWWZpeGJTZmc4R0VWZldxNWVlOWlzVGRHX3cwaUd4UjVuMmlDVjlVelA5Umt3dVkwTDlhOEFSWGY5V1k0anMwOFNGbU5ZNmtZUg?oc=5", "source": "The Hindu", "published": "2026-09-28 05:11", "score": -0.852, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxObFRUUjZrRFpjTE1NcXBPb2NicXQtS3RtU0wtNHVjVHV4VHRlWWtMc1RtMzYwbXN2dnl3SVRBcjJxWFphN0hXMm0yZFNFNVduQ2dDdnVweVhTR24xNW5qemFXaTl2dkxsMkFYTlNCbGM1Si1IcmZIN3ZBTmF2ajBCcERjU1RPNXlIRHdlanZ1T0VxWWlWZkZ2eEYyZFBJWUJiSUp6b2gtcEtUQjJMaHNuWHNrRkNYek0tZlRITmkteDFreTNVb2VvcmhWZnJNa3FzTnZiUy1aXzVMMzg0cGNZR3pvMUFRQQ?oc=5", "source": "Equitymaster", "published": "2026-09-28 04:56", "score": -0.477, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil", "link": "https://news.google.com/rss/articles/CBMi5AFBVV95cUxOMEwwTHh2ZHV6TVZtbjNDSEprS000QlNTUjh4X09yNWFTUmpHcW12aERXVXNSOUlSNWVrMlM1eG94ckljVXRpdDUzVHFtWUJ1M1p2TncyUDdBUWItZnppY0dSV2VZQjZiTDNLNzRBYVZnZUpIQzBPQk1BbjNEckUtdUxuU0oxMmRLYmw1cnhOV2FpUkMwNHhqazg4MGs0VTQySklGWTJwUGl5U09GS0t4alJNajVvc2lMdi1nMTJxQkNLeTg1OWUyYWlwbVJoR3F0b2NWU1pOVDFiOVhBZk9Nbk5TQUTSAecBQVVfeXFMTkhYdHl3d2FCU3RHT2JTZzJfcmhZbzNWWFZqMXFObDVBVHNsNnZsX29kak5jdG1BLUowT0REU2xTQWt0RmdoVVg5LXpzSEJobHl0U2hnNUJ6ZDU5MHlIaVVpTG1YeG5VQThDa05fTm1IczQwR3o2TjdQa2NEOVZ6dVZuU1lXN1dEN3dZWTV6ZkgxX0tYWXJNZXJLSU1nYXh2aGtrQTJJQUl1VnRJVGhjbmZpRmp5QnBjcThMTlJrbGFvb2tjUnkyT3B3MXo4VkdEdERQM3hKSmMwWWdoWk9uZGphb0M2a1Q4?oc=5", "source": "Rediff", "published": "2026-09-28 04:51", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQeTNsTy1qVmtORm03dkJ0LVQwRUVQU3ZnT0RqMEI4NG5kVUxYeU0wcmp2N1hqaFVPdXhHNDV6cGRuZUcwclFTZ2NUV1NjdzQwYlhwWEMtcmFIVXZpMWxhWnpzOUFwaF9QUTVPQXVnTmZlUVVHNlNZQTVUOWxjdHZ6UHJuVDVtZkpPVWJqd1hlLXNlUVBEMmNuUFRCUFZZb25KNGpaNmJ4RjRuRDh5ZWFvS1JheXpLSzVQWkNSODVvaHh5ZUgyWjFPTTRnYlpxbUluek0xZHdaVU91cVRrYzFHWVJfRlJVemI0RW42Q19KSdIB9AFBVV95cUxPRWZEblJNRmlJNmdQMUpNa2FMYzNDRGZrTlp2RFh5MnZvSW5HMDhlVmNPODRlRkJTYkIySVFBWGZQLVh3Y1QzWXhValo3RkpjX0pidkhKQjJaTGFGOXhsZzBfeHBadVhGcjZKZXpuSkF1ZFB4RzVwVDIyeEtqamhHX09HR2FtY3ZRcGM3bzg5X25sU01NeW85LWQ0SG9pYjMzS2VfU0pncEJLc2QweG5wbFdZbEpDU3hvenI3V1BUU2FPclVvZGNCU1NEb0ZsZU9GdmQ3Smd6ZTZ3WTJtY3BTOElrdURuLVVsZFo3ZTVLalFBY0lD?oc=5", "source": "hindustantimes.com", "published": "2026-09-28 04:45", "score": -0.361, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE stock slips below issue price of \u20b91,785; down 2% on Monday", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQSTM2eERXZ0NPUHpTR185VFYyNzFaR0lYZlMzeHB0Y2dGMjM4RlhXdWtnczBEblZtV2F3YVItUUpYbmhGTWI0YVpSdVlRejFmZUdyWmhLRUYzNFVCNkhsdWZoMlpTenVZSDBkVXNpY0Jwam9pTmtocUJhdzA1X1dyWTVJVWhVdzJZRWpiNzVFRzd1NUREdzd3bW1vQm4ydkVETWthRE1WVGpqUkZoSVZYbmtqdVNuWnhnM2ZaaHhORjRReXM50gHKAUFVX3lxTE9fUlRRS204UnpsenJGSWtxSnJiR19Dcmh2LXFMVWhQSzdDamQ4QlBSanluUDdfYUY5YkpXcURFZUZ3TU1TQVM1WFM3QnhoLWd0VFBXckt2R25razdOMEFvc0F1emhYVzIwZkY3OXc3Z2xJblJfTXo4SFZyekdPZDlHTDc5Ykp5VVlpaU9MblVhUlBhcW9Ta3h6SWpIeFZGOGs0bWh6NmNWT09yN3pjc0pzdXdqYlBjN25UajdLT3VvZEdNRlhxazh5ZWc?oc=5", "source": "Business Standard", "published": "2026-09-28 04:42", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOXdSQ1g3eFlqb0loV211WW1MSkhiWVlTNzBWd0M2a0ZFQUduVlI2bXk2eDBmYnBIZWlFeDRrbTh4TnNsM0hBSllPZTBHOTU2ZVZaQXhZOUFDczM2ZU1wdkZteFEyTXA1SFhGR1F5dGpDY3JGd0JyOEpnZEdmdWUzd3Fwczg0SzJyQ2tWaWxNSEJYSU5kdHpJbzlYQlAwWnd6bzBGaGpIS3Z3V3hlaVBWOU55X2Fyb3FLUE9DQ1pQcVlka1HSAcsBQVVfeXFMUGxERGozWEJnZFBKVXdKSTNKNUV1N2V0ODJPUEljV281NkFXYlpnWmtINFFlaUtfUDZwcUg5RHc5VlpRT3p3TlhzOHFKNkNIVXpfZi1SbXlTQV8xa25LU2FpTXJxNkRVNDJhQVRkWVFFaXFxQW1FcWVqUE1waDJKZDI1WDMtd05IQTlzdE9xNFFpdVRIRmJ3WGR5aS1Wb1Y5WWpMUTZmcWtqdnU1YnNPTUpTOHlvcmlPMkE0Ylp4Ql9idDVGcUxTZHRibnM?oc=5", "source": "NDTV", "published": "2026-09-28 04:41", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxQQl9VUVpCdDlvWEZ4OXE5V1pabEo4U0RPcVlBRXJuMVBQMzlWQ3Jidkxzc2drSUZPcEhOdG1jRmpqRXE3TDVIdEY5T3hCVXV4Ung2X19yRU1OcE8xUU1FZUwzR3ZTOVBCYWNvc1p1U0x3WF9kazVjV3h5Tk9PbElFSzN1V25BN0xDcU83cGZ1QVRTN2kwZWxjZW9VeFFZZTctcG5PWDdhbERNdzI4ZlZlLWJLYVdxUHZOQUJDWUc0MkbSAcABQVVfeXFMUEJfVVFaQnQ5b1hGeDlxOVdaWmxKOFNET3FZQUVybjFQUDM5VkNyYnZMc3Nna0lGT3BITnRtY0ZqakVxN0w1SHRGOU94QlV1eFJ4Nl9fckVNTnBPMVFNRWVMM0d2UzlQQmFjb3NadVNMd1hfZGs1Y1d4eU5PT2xJRUszdVduQTdMQ3FPN3BmdUFUUzdpMGVsY2VvVXhRWWU3LXBuT1g3YWxETXcyOGZWZS1iS2FXcVB2TkFCQ1lHNDJG?oc=5", "source": "newsdrum.in", "published": "2026-09-28 04:29", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb2JZRzNjNjBpV29mRkZobTRsNWJaVExQeWMxZmw0WjYzZnhCNktBQm5Hdmw0U3NrVGlrYm9abFZwRlZvendEZldPMlNlVGtqVFZ0ZC1rclZGci1yb3BjbVJ1YUlta1VYM3pBMl9kbXh1VjA4ZmtURl85S0Z4OTR0cDFyWXdkU1FiZ1JVdEZ4eVBPSUtJMk9RMnFJQUpxdjRiNmNHQzdmbnRwbGNjZUFJZkVXYV9yc3p3SlF2TDFkWk8tT3hnNkZPc1JTb3c1dkZ0MS12S09LWE9vaWV0SUhOOVpGUmRrZkJxbW9XQdIB8gFBVV95cUxNVVJKdDl3emc1ZEJXb2ROY3hadnZaaXlhZEtTZmZ1RjZFNFE1VVdJTnNxVFJFRWRlaTZaUGl3ckg2dzRfY2ZXTWxvS0dWVV9ibktOOGlsWjVmVDQ4YUN3aVlLaXA1anJ6YmdNRUM4UzRrZTJxWkE5UERZbmZJR2ZHQ3phMlg2bldoWDhBT2U4bVY4SnF2c1JiQkVHdXVVSGMwTVFJVG1GckhxdURSdkpMdUpfSUNQOWo5VjNxS3FEeGRNVzZiX0UzUVozR3JXMHduVzF0S2xnMVdhYVFaNEJmOHZvZGhfbkNmY2lMYlU2Y19wdw?oc=5", "source": "Livemint", "published": "2026-09-28 04:25", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?", "link": "https://news.google.com/rss/articles/CBMi7gFBVV95cUxNNDl1aHc2VHYtR3lHdGJnY2oxdXpXX0tNN29FU0dnYnZTX1hrRWFzOFBzSk5KTWc1RTFJOFdmT3VVMEFmOXNDcXhKbHdBMVUtR0kzclhZVDRLSDRHcnljSTF6UG40ak5SQmMtN2lzRG9QSkRNUzFidmRkSnc2aHRLanVnTURTNU9DcUZXU21kWVhoVUlacHhSa2lYT2tPMUJ6NUxkWjJ1V0xpYndCQU11S2djSjZ4aXpHdHpXRTZpRDlnZFZNNk9PU1hycldaa2w5Ylg1Ull2SXU2SlIwbDVrdG1RZUJaN1JpVjRUT0Jn0gHzAUFVX3lxTFBtcU5GS1BLNVRSQ1BWekxLUmhQaFFhMlZLV3RIcjk3M0RBVkpwU19mcmNLZ3I3UXQxdFY0WHBIMmw3SUtkeTdwN1RFa3RfbzB6bkNGSzJwZWtZN2dDS3E0a04zZEFid2pXVm9xejFDbUpLeG9hWGlfQ2p4NWZtakVWUmxLMEdteDBkVFFLLTlGWHVid2ZNYmh1cHdsS2R6UjFFUzlQNXdUX3VqSlRKY014bU1mcGlxZ2VGbGtxZWlDbHRZTnVZcm55NE5zaE1ra0lUVjlTNTZaQjhQbEJLOV9yWkxSSWwxZ2FacHBnaV85SzhfWQ?oc=5", "source": "India Today", "published": "2026-09-28 04:17", "score": -0.511, "label": "Negative"}, {"symbol": "MARKET", "title": "Mkt crash wipes off \u20b97.4 trn; Sensex down 1,180 pts intraday: 5 key factors", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNFNEZXdXeWxyUDZNNkJvYmhvM29nZ05JbUhkLWRmZ2VWME9TMFQyTWctZjhoeWVNQ3dGZ21NcmV2THVjUmt1TTBwTWNJTmVnRFVzVXlCekNMZnBqUDY5M3RWSWpQeVBYTXl4Zm1ndjhBcmZUV2ZVdHQ3VUFxQzN5c3NON3N3Zjh3UjZYSjR2VER1OXBWMkZOUExnTHF6OVBtTWxCM09ZVHhmdW9DZDZ2U2FxVEtGVHhIVlNsLWhkcnByMmdVaGl1OTFwQW5GZnZ1OVJvM9IB2gFBVV95cUxNWUItS2dqMFByNUlUcXdPMUdQSHZxX3VTYU1PcEdaWnFaOUo1MnhrQWQ4MTBmaWM2eDY5WURsaFpId1RnLVFJRTdadERxTDVKc0J0UkkwRDM4V0g2WDMtclZ4eEtxY3NCVTV5SV9tQnhEZUR2aHJ4N1Q3VzFLbF9Rb1ZadHN5Vk9tOEE3THlxQVViN0tfZnB1bl9aQU0xRjFZc1dqS3RKVWpLUVM3UkV4aUYzOVNaMDlBbEM3bS0ydnltemJ4TEFOZWt4OHNOcnNNdG5DaE5GVVRHUQ?oc=5", "source": "Business Standard", "published": "2026-09-28 04:11", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 lakh crore rout", "link": "https://news.google.com/rss/articles/CBMilgJBVV95cUxQZi1NX0ZnR1pnWl9lLURWQW9uazJudU5adU43UVVWdG9BV1A5WTZaN2RPZ3NSWHl5bTlCZlA4ODkzcDRoc3JWVEtyRk1NbGx4MDQ5X3NGZ2ZHVW9MWnFTV0F4U3ZSWVA5S3BtbzdtZFRLT2JVOXJjZjUtNENidWtZai1JaTJPc0VQVE9mdDE2VGhBNXByZnZ3ZEtVdm5ZRkFvUXd4UGdfZjJTcFFRcHkwcmo3d0p0Vy0yZXNkV3RXV3ZFcTRLTlBUNGRrNXNGMGVpUXFKMDJzUndJWXpqWnpGSkFIRVJ4Q0MzQUJVOHMwT0Z6X3R3aHZ0YzU3TmN1RDZVQmNzWWNZbkF1YVJ3YlV2Tndac1N3Zw?oc=5", "source": "The Economic Times", "published": "2026-09-28 04:08", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi-gFBVV95cUxNd3FFLUl4RkRuRktMczNpNmU5VmotaWdaUENGMWExNHZJOERsVFNMQ2ZiX0tDSGFXYXhxSjVUM2p4QWUzZThrTkxDNXR6ZndFMXU2NEFTNG90Wm1JVnZpNDdaRU1vSnJOUno4VGN6dDhndTdDWDhhbGVjQ25nSDBWOXFGa2xUWlEtRDQ0dVNCZ0I2TWdQcmlZWkxLcllVUXBpa1NpdjItdDBhZlNLYUU5bWhwREZoSWV2dEMxMWJMNUZza0FpQ2dKM0JSdU9fajZEdmQzOXFnZUxqd09wcW9qd1V0alZ1TGtFYWs5d1k4eGc2NVZvbXFONkNB0gH_AUFVX3lxTE5yLU5FWTlXQmdqRWY5MS1MYXRPVHV3bjNkZWlEa25SVC1INTV0QjQzOXBxVzhFbEUxME1WbU9jbTZISE1fa19JS1dwRW9KOVplQ1A4QkNWWlE2YjM5NlBCNndyN2F4T2VfVmlOVnhEQzMtSENPZ2N2clVGNTdtVnQ4SU1idWI3eThwenZWRUZ4NzNwaHJvTllHUlBpYnQ4SEEtZFlRTmJuT3dGU2ZpRTdMLUFraWlfNjl5UWFZLTBlX2VMSTdXdWV6cXNOaGFzRU5QSjBOcHBPT081Z2R1d1JWQUt5TXFieXRCbGFLcGRkWVI4OG9oRk1YQXJuQmdrRQ?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 04:07", "score": -0.44, "label": "Negative"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines ESOP 2019 Share Allotment Explained", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxPUWZWQWFhUXl0MHliZTNDMXZuOTFtUXB4UTgxU1hJTlotLVRrSjdSMXBGWU9vaXk4ZC1vaTVzbTJMb3djcjZfZi1xYkR4clBmdE42NC05V1BWbmxfZTRXN3pDS1pKNmF0UWJ5dlE0Ry1qczcwdUQ2VHM3V0hzQ196M0ZxeVBuMkNXUXR6X01mVm9HNWgtVW5XamJNcVlTdW5MVklzZlRWdFM1MG1VNDdJbFZLcUkzVENpVVRrWkk5NTJJWG5hbWtCWmJmWTNtUDB0VWhEV0xnZEExUWxxOVhjejZ2b3BwRFk4QlE?oc=5", "source": "Kalkine India", "published": "2026-09-28 04:01", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 \u2014 Five Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNWmNXeUhrY0hPcXlaYnhxdEpqRTBKbWJadHhpVGFOX21Oc1FnTVM1UDNDOWZ3dU1jd2RjNTA5VTV1SnJHM1YyNC02dGlZYnhzeDZramF1NGpBTm0xcV9DS2ZIVURQSjlrT0M2bTJfY19qc0VmRHRBdWdZdXBmcC1pUHQzSzF4OThzSzFDV2sxbVVUQnBCWjhoemhmSEhyc01oeWJJeGlSbXlaX0xiUl9qXzdBaWhHSUt3eUdKMTh3djNuZlg3dVlqYUNjMkhpX0RoazhISVpBTnJFbmFVVGtZaFlKdGY3Rzd2SkxUTtIB9AFBVV95cUxOLV9xeHRCVnRiX1FUSENXSHZ3S3NqQkRRZFA4MzZPYkd6WENNM0NZQVpMU0FQUUJnWkVROVNSbTFrMkdJaHltbkUwTExjby0wVzViS0NkSVI1NDNORG5wNkFtSXBwMlRNbXhQbllkYnE3cGpVeVF2a1RrQTJqNG5oSnVsS2pyc0dUVEtlNnM3eHJ3bmJwbXBxZC1FSG1MbnRENzNmUFluMzJwMlJzelA3M3R5Y2V6SXZreFpGYTlZWXlITE5xS0NMdDZ3M244U0NUdWQ0R1N0TWE1bEJLM0hJYzlmYWJjcWJUUHhMVUZDZlJpMExI?oc=5", "source": "NDTV Profit", "published": "2026-09-28 03:58", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxNdFJQdUVBNmhGOF9naWYwc1VCWWozTGVwOWl1b082TGI2bmppQVQ5dmxfUWo0RGhBQ29IU29vaUJ1cDZCNEJoelpMc2g0eGhldHVGdy1WeWcxVEtZcDBDNDlfRkxNZnRFMURFLUVfY1U2UG1YTk1vampZZUozYjEzU3JGbDRWNkhhVU5qVy1qcVlhdWxFa2YzX19vSjZ4NEl0dk1reVhEMXlPb1RTTzdkNENIS2RraEdzTTlBXzFteWpPMkpkUk9MdEJqaG91ZTlUSll2UEVwcjNoM0FDdFJQVUJCM0JLQTZzS0xTVkNJQ3VIYUVyV2czYWxBLXRUNzlPUkwtTHFTNUs0cGE3VWdj0gGUAkFVX3lxTE55LTJyNkZRSldBTGdKNnM1THNXOEtPQ3FZaXdOWmhNMEVtby05Y0xaZV9QSlFuNDg3TFlfZlNpb1Z1eTI1S1ZaZDJVeGwxcktWMW9pbWxRZk83ZE1scnkxWGlVOGhDQUJJNWtnTS1MWV9BcDdKRmYybmZSVEJydVdzS1dTVGdvM0c0R09GdUEzd3Zfb3pmMXdSMGUwTk5uZ0xTTlRmV2NZWTV1M0FjWmlQZ1k3aW0wZE52QmlpeTI4bzFHTEtnbjRRZWtzb1NrTnE5dU1XX1ZQV2cxazdKZlRCNmZ6UkNSaVNnVGZVZVV4R21xZ2ZfOVBzcGZ2N3l2RkI3aGpqNnNJWjdTNnFwYnNQNEt0bw?oc=5", "source": "The Times of India", "published": "2026-09-28 03:54", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxNZ0dpRTVlRDlxc1RtOW81dTVmTTREN3MwakViZzNUakNFTDJkWkt2QkstemktQmhGZHBFWjRZYXhHcVZDcU83WWpLeXpBUDZyVzBINUVFalBwaDZ4YUhwOEdXN1E4TmVTX1ExY1U2MV83T25QZFhsa1NVcDRlWmtYSHlXdWFMTEIwcVdoS2tRWWZ6V2NIVFZMMHloczRjb0JvNHhmamx0SDEzZUxtLUJDeVgtWTNTWm50SktyR01HV0d1cXI2MmU1UWNseGFDRTVLbGx6b196aE5BMzJYV2lLYkEtZW9fcTRONVHSAe8BQVVfeXFMTVh3alpWbmYySWstWjFjN3NmVG5Sb1kyV0ZjSkYtc3MxN19pMDA3VkJwRGh0Z1FYZEU4X3BTVWkwRjlLdGQzTW9DMm5Nb05oel9SdVZrYmxRT2VIZk1nblpwMUZlWDR5ZlVnY25oU3BwaHVybk5ibEt1VXk5dS00QlBqV2ZLY01WWXN2TWNvWnc3YzRfNXBTVTJtR0w4MHRlNHBWbmcwS2tpWEkyRnlvRFFHSUtsdXdZZ010MVFsSXBEcEwyNTlNM3daV2l3Q2s2ZGVERFJNNGg5NE1iZzNJRnloY3FVYU1BRWUyaWNsRlE?oc=5", "source": "hindustantimes.com", "published": "2026-09-28 03:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQU1VkYW85T1l4Mzh4SDJFZDBhZC1GczBiSUw3TmdJYUxvTW1TRXpUd3BTOVZwY1FzODlGUkxyNFlXSklFNzBRWUZ4WEpGdUZDWWRIZ21vM05wMHBnQ2N3UTk1VENDZTVYeHJsSEIwUG15RmpnRi0yOUdBaFRTdFg4Rkp6LXBSbzVmQjRQU0V1NXdCdVRmby13QXZqb2Zzb25Fd0FsR18yZW0yZlZBd1VibQ?oc=5", "source": "HDFC Sky", "published": "2026-09-28 03:28", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxNQmUtcnhXbVNOQ0lacFk2Z1JXa0JON1VtZTRsYnZVMDlKdjh0dXhobk9tajVtRVdUbE5RV2MxUy1MbUpkNkc4UXNvalZoZXltbUNScGEyanBReERmbTRuQnB2d2M2dkU3NkJ0anMybXdHWV9QWElRVG9WcDhNSzE4eTV4VWs4WWluaGpYR1NZZTNuYVFPNWZwUk1YcXNOR0NrN0REb2V5eENFRjFaTVNpeWtJdw?oc=5", "source": "Reuters", "published": "2026-09-28 02:19", "score": -0.542, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices \u2014 Five Key Factors For Sensex, Nifty 50 On September 28", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQYTlhOERzdTdrb3FJNkRCaFpyd3p3dGE0QjFQNW5ndE9qQ0VTM3gwOURRS3hlYkxQOXh5UnUzYlVfMmxYZmtkcHVpZUpZZnhsNy05RWRKWi1FdHR2ZWVIa2F3MmxBTjBCeC1rNDBQQzhSYkVKSGdyV2pxa21xcnd3dk82Z2JOU3FMV3pKNzcyQjFreUdPZDlaNWh5WGVLUE1OSzV1VE9Qc3k1el9pOFdKYzBKVEMyRmZRMU9icTFpZTdQOFB5UEFCLXEybjl4MFFJam9tMFV4aXV5cjQ5bWR1Mnh3SUdXYzhtVUk5VU1uQWlMTHFwdlhr0gH_AUFVX3lxTE9yT1pHVWp1N19wOTVOLWdVWEloQV9BS0lKeDhwaWcwTGNqSnpxUVFIRkg3Y05tRUc4MUNDOF9CVm1EZjYzdnlsX0UwVkRDaEVKQ1ZNcVJteXhQQnpjR2JsMGh0QkhNcmt2eUxOdlRxTjVaMlFZWGtVSkU3Z2xfU1BLNjRrYzZ5eFE2V202Y2RKaVV4LXdqb2FNZHVDYlM5WmFyNWVSWnRKVDNab2h5VUhBaDlmbUVJWFNiOU9qYUNrVTJybWpyZkY3OHBiRUl0MTNBRjBNQ0lfYjljbkFCUE5oS3hDaEVILXd1TDNDRFVaOVR0enZ3VzBZZkJzQktabw?oc=5", "source": "NDTV Profit", "published": "2026-09-28 01:58", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOd3lLLTBUWlJpdVVESnptNXpwZnVmVk5zbTU4LWV3eTZyT1R0MzRfVFpFYzltdWhnSTI5Uko3M2dpSzY0NGJwZzFfbzZXM0ZOcV96T2hHaWQxR284Vi10dHRxeUVCQUJrV1lCclJZREI0NlpSdHp4Q0R2V1paVFlVWllhWkVCQWdaTlhiUjN4bENkS25yU0tJczFLVE9vUE1rY2hvc1FTSl9QZ1RkX1Q5ZVNfLUx2LWpmN2lQQ1pNMDNUS3NJenhycjRsNUNjbnZRMFNZNllsUU9WeU1xTk43NUY3OThtVFJadFJUSWhuNnZEMUh4VGdicDdNdFI5QkV4U20wY9IBigJBVV95cUxNVE84MHlqVDk1czZmeWtPckg1UUh1bF9OQU44MFlsSkdUeU14X2xZYXozODFYb0JtaGMwSDFVNzRpczZZb0MtY29aYTBsdl9fRFgzQkhhNG5Id2hYcE55WjhMYUU5N1hWRjg1RjJ6NGpuVmIyaURHQnI5d1RsVUxxRWZ2M0Q4NjlLQ1ZENVdyLWtSUkNrZG9MbVBwTnVENFc1UndfTzhlby1NdktITDZBbldMMlZua0xGbnVRTUFucy1GYVRaZUpPbEN4VlhTTGFlbElpVXBiZnNPeWpqQzVjbHhwYnFXUHBzWUM5WU1UVmh4ajlKbHpDRHdBR1F1bWNhNEhfZk1DNGRWZw?oc=5", "source": "Livemint", "published": "2026-09-28 01:20", "score": 0.842, "label": "Positive"}, {"symbol": "E2E", "title": "Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxORnluOHJzdFp4bmJaUl9hdWY5Ql9WeFd4cnF2ZnVZdkRIbGpTWlRzSlBxX1lBb3VEcFVTclJjQ0lVVkFKcGZTUFhLVDlDVkJkZDRnY3VQQkdlWFFOS2M1VVNNa1B1dmpueVBIRFNyRGhKVmRpd0IyV3NmTHNrdTZpZ3BKN3lSMjFnbGNyYnFtelZWWXgxWF9KYW5WSkoyQnA1R0dqTHBscWRHVVg2eDhveGtabHVVUjNoNTJCYjlsbGh4Mjk5cjgySUcwano1THJpbUY0X0swTG1POTA4a0ZSOEZFMVFJakg4RjI4aENIaVdZWWpSNWU5QnVDYkJyeTZlMXc?oc=5", "source": "Equitymaster", "published": "2026-09-28 00:30", "score": 0.557, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxQNmdxX3hPMzJrejF0R0pvaUNBbDFacW44MXRuLXZ1bF9yVnlwTXFwWGlOZUh0U19XOTJhYkZ1cHJ6VkJSMkk0QVAzcENpdkNJWVRWMDhkYXJ0NUdxRjVnaVhiS2VPWExCMWdaQlBmVzQ4a0lhNlNjNnV5Nk9xcV9zOWMyc24wTFdBY3lCbFdQdXlsaWFNdnVxblZYWVhBcm5wQW11NzdmV01JeVBsQV93eXJuU0ZaTmM?oc=5", "source": "scanx.trade", "published": "2026-09-27 17:20", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Ahead of Market: 10 things that will decide stock market action on Monday", "link": "https://news.google.com/rss/articles/CBMi3wFBVV95cUxOOHlGS3FhbzhQTUM5VG9rOXZjZXBTZ2Q2X1VJWjVOZXVEM1hET3BtSktCcmlhLXpIX3JUeWtBWlRNX1l4dWk0aGJiNFRuRVlzaDhfVUpzeF9jNzNUT0VpcFVSZWlGNkR5Mm5qeEU4ODR1RUpZcldoc2t3TkFweE8xLTF2YTROOGpkZ3lkWGRFQkpaY0xTRFB1akhkbG01QjZ1eXVBWlpjZHdnMGR2a0ZNODZuQWZ2cThKTG5nb3V1WUxxS3BCRHllVkhKM1hQTWVpQzd2WFU2b2x5TEdYcG5N0gHkAUFVX3lxTE9uUFVOSFVOazh5cm5jb1RDcVU5YzMwUjBJTV9yR1JmeHhaeTB1WmNIUS1faENuVTFJZEVxSEpheGpGcGMycjEwenhnekROSnR5OVI5V1l0TkJsTHp0V0g3MkF1TzNpMmZCUm54dXFiS3lJVWhGTkRnMklIT1pucDc1U0hrSkFoN1dkci1UM1UwVDdoNXNiZFNPWU9iUk1kSTV0RFBTTVl1UkJxc0t4OUIzcXRWWUJMbXcyZF9zZXp0c0ZEcUdBeXFKTFdxbzJWSzl6ZUFZTHI1aDZtdWFOOWhBbUQzbQ?oc=5", "source": "The Economic Times", "published": "2026-09-27 11:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show \u2014 3 reasons", "link": "https://news.google.com/rss/articles/CBMilAJBVV95cUxNekdIczJ6NEZleldrYUtRZ0pEMFlMaHFDcWdFeVVhVnJROWRBWTVFeURzYXM3NVY2eTUtZmNMOVg2VVF6eUZOZFpzc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jEzVnfSAZoCQVVfeXFMUEV5VVRyZjl4LW9fV21rY0Y1SkJyYmluZTZHZlpld0cyakhLcHhKTXBNR1kwU0RET0VZeW1Ea2liT2JzSkNGenlOSzlkdVZwejU2X2FJVHFOUHZwRnM5YjRGUzJDM0VaMVlVR2M3N3FwZW83b3pBcnRwQjFTSy1UVVpDUWEwYTVDSmF0eExBWkdOQml5Zkp5aWtqU0hqNlloT2V0XzRPVml6dXV2WW5MVXlSMXZFYkQwMGNqZTBXNjBWTFVkd3pUblpDdHZ2RjlXRGlreDhvWXNnMV9KVGFySDFFNFBzUkpZUEh3OVFRVmFfSU1oU3V2bV9Pdm5hR21UWXBLYW9TUElFRExLRGdPTmJXQ2tSMjlFRV93?oc=5", "source": "Livemint", "published": "2026-09-27 09:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOT3N4b21hRzhJSXdJVzFVNWRNQ3RqT2l3aXFBN2RjN1JDX1Y2V2U5MXlDN2l1a1BGQ1hLcWktbEgwYU1UMUEtalJDYkc5RDZqX0FHdFVuMmpDVDhHdkhWSDVpMFpXLXpoa0ZTWDdGcTBxU1hJSUtIQzgwUXZvQTRPdUh6UnlXYUkxZTZHTmJFSnFQcVFSc0s4V2tGNUUwUTJVZktuRkUwY1c5eTI2NjA5VEgwMDExekhFYVhLRW4wRlduOU1wZ2JqV1F1emdiLVUwWHZwa3BmOXV3MmtLOVpzWlZOOXJ3b1MxY2pvR3VYRlFjYkxmNFdIWGFxNTJJYVVvcWhJRVVwb01UbU3SAZACQVVfeXFMUDJ0a2tkZUxvVXFoM0VZMW5YYm13NlNjNl9KY2l6X2NkS0VvMGw5eGhyWDRzU2ZsTlJmTVdTbmZ0Vzhqc1YyNGU2TWV2a0FLLU1vQmRRVktFOXhtcDRwVVVMbXZPNmo4Q0V4ZkNCU1M3TEZ3RzZwcVp6SlhoczYwY3NYNVN1c1BKSTJLYXBRbVh0bDN1ZWc4VnZNb1VZZERDOFlSXzFwNW1RX0d4LVVGRHUta0Q0cVR5dndQUGNYaTkxWFU4ZVloTzNfR01UMDJ5aVB2R0ptYjU5Q0RLRnBEZExqdEZJV1BDMHRiRTBBa19fa0djbno1blZZM1ZwUWx2VWREaHpQeS0yVFQtRFpQc2s?oc=5", "source": "Livemint", "published": "2026-09-27 04:22", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks To Own In September 2026", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWmN1VW9wZjRBZl96MHMzNnRmeS0tY28xWWZtR0hfa19FN2lyVjdtZUc0a0U3c1ZYNmZ3eTNiWFVIRElaRGV4VDFVYi1kYlN3ZjNNemNjVzFwWV9CQmxlR1B3X2kwVmphZGhMazZCVTE1a3E4clpQbU9GLVNXTWs5MjdNaldOQVBOOVpMWnNMUXA4VEtmc0drX3RWWk01aXVvd2xJS2JYeGppOElvRTFWbEJwdEJoYlBVaXFhTUNhMG14Y1FnSWROVk1qb241Sk1vOW1MWGJ3dXpuZ9IB3wFBVV95cUxPSXhqMzhnOGFvNkRfakZ0cUxHVkcycHlESmtYb2N6Vzc0MGVlSnNhLXUzOElWb1YwclgwRmY5MFhreTM0TkpzdjVjR3d1Qmd0Y1ZmRi1KM1dLeTU4QjRjOUdTNzlRNUR2b3FvaVNTbW5adHhMQk54YTR3YlRLclVfUmxKZmhRXzc4VG9PUVg4RFU5UWFOWmsyYWZHaFM4N1pxTHVLX3RVTVUwSzRtQzhCenRfa1REbS1CeXQ1Rm1GUXhvV3BxRndHZHRGVEV3VHM0S0Vidjk5bm1SSHJiVTFB?oc=5", "source": "simplywall.st", "published": "2026-09-26 22:56", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "\ud83d\udea6 Indian Markets Stuck In A Jam! But who's responsible for the traffic? \ud83e\udd14 A Bernstein note argues that India\u2019s large caps are stuck in a bygone economic era. But here's the BIG question: \ud83c\uddee\ud83c\uddf3 Is The Market\u2019s Fate Really In India\u2019s Hands? \ud83c\udf0d Or are global cues pul", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxORUdYckd5Y2pPQUg1MHZTaHlTT1ZXWTdmTGxwSWlMcE9NQm1vNE15dk9qS25VanFnTzk3c0FHTEpwaGcxXzhmekh2dUNLM2s5Zy1USHBjMHRfakhvYndNanZrV19NZVFMY1hjOHZsektLSVZoS2tTNkdzMEJTeExiS3ZVbDVRWTNWVjZ3MWVmSzhnZDVvT2d2YnEwZGJLRUp3QXhxTDVfSUc5TTdvTXIw?oc=5", "source": "LinkedIn", "published": "2026-09-26 13:51", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market News: Nifty 50 Outlook &amp; Prediction", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVJvTS1CRXVsT2ZzNUhBV0piRVV1UnZTeDVEcDJmRElmWHB5WkZsM2s5YzlYaXJuVU9vVjQ2dE5XVk93WTVVLUx2d19wRm9lc2YzWW9xX0F1YWJCTUJtMURwVzRxbC1vUlNDWEpLRUZibzdnbVdjdEJUeThfeHZLSXpwTktCQnlMM0tTNUhwWmplMHJKb2ptYmVn?oc=5", "source": "Liquide Blog", "published": "2026-09-26 12:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxPbm8wM0RSWWRXc1Bzc3daeEpaNnFwZW55Y1FBT19TQUdxYXdrZ2FJeDJGd1EwQk9BbFJTZ2xKNV9Gd1BadEFlZExtZWlxdUZEZHh1RkRIU1lMNEJVR3hkZ2VKWnNGWUVLa1Fha29hcWcyNVR6dEdydjluNGxlN1YybHFabnUzRWdzMTFSWThkNWRRX0NXQ055dWl2dXN3cGw2RUJxSHAyTTFWMnNOeXZ4S0xGQXFjRmhub1lHeVQyRUhUdEpFSGEwM2U1MEFnbExtV1JPRUVNRmV2dUNfZ1BiblROc2IzLVNPclpNRtIB-gFBVV95cUxOT2FRblV0ZG5vNUh2QTZGeldJa2FuRF8xSmRWYUQ4a1NLblFyUmtJNTRCdHB3NENTZUZhdi1Ha1g4aTV6cy1POUl0Njl3bzZNdE1ZRk43bWQwRXZvNGxncTdBaWg3cDNUMHcyRVp3d2ZKRmljNXZwQktjUTZnV3NpWldYMmNoV0ZJSjZONVJjNEQ3d2ZLWXlVREFsd1VFbFdob0xydFJ5dHpFdGIzeERrQU5kcXBubmVLd2RZODE2Skd0Yk92bFNnWG1qUjNnZWRSR2YwaWIxLU91ZHBzTlJVb0twSW5pUnYxb3E1WEJFTWdmQ0tzeVhaZjRR?oc=5", "source": "The New Indian Express", "published": "2026-09-26 09:15", "score": -0.128, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQWm9DM0I5TUU2aWVIdHhCam9zXzFSUEI0RzhWaEFxWDFfbDFoeUFJUEZQbHk2OXJJdlpjeVBTVjd0RDdMSjdPMjl0eTN3NXZnRmR5bTM1Qi1KS3JsNFRrZlFCcmViSW5MTmdQdDItWTU4T3lUeFFkTEU5VHBEV2FmUjlqOWdvaDhNcGZlTk9jTjJQeVZ1Zkc4Q09fUGY4LVZiWk51d2U0ZGtxRFZ4cXpMV1V1UlJOdFN3RnZyTA?oc=5", "source": "Kalkine India", "published": "2026-09-26 06:30", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure \u0915\u0947 \u0936\u0947\u092f\u0930 \u092e\u0947\u0902 7% \u0915\u0940 \u092c\u0922\u093c\u0924; \u0915\u0902\u092a\u0928\u0940 \u0915\u094b \u092a\u093e\u0935\u0930 \u0915\u0947\u092c\u0932\u094d\u0938 \u0915\u0947 \u0932\u093f\u090f \u20b993 \u0915\u0930\u094b\u0921\u093c \u0915\u093e EPC \u0911\u0930\u094d\u0921\u0930 \u092e\u093f\u0932\u0928\u0947 \u0915\u0947 \u092c\u093e\u0926\u0964", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPVXU1bkFLVlVQVmhKWjdoVDlSNFQxTTlheVZFdGtDeEVEVzVtc3Y5Qk45R1RaOV93WlZrOXF3MzFKTlE5OGR1Xy1DcnFtUTV6YTYxYXlVMHlTWXFEbnlMaFliTC1uYTZOeVhCY2ZjQW5Qd0pzcEZWUmx5NHJHZ18tSDNHbTZrT29hbFNrWXFuQzFRTW5OQ3BMRERrUldoQUVMYmRTeTBfZEctVi1DUzF1bHphN2JnNV9lbWx3MGU5MlZRbHdZYnNrR1NHUVJVekRybmZtcWNFNGQ?oc=5", "source": "Alice Blue", "published": "2026-09-26 00:50", "score": 0.34, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxOTXpFTDNOdlg4R1lYS1FPU2VpM05pUUVGSHBvdWxqLXJ4SFpPTXZ6Q25FVjh0V1lvbnR3ODJsa1Q0ZDJlbWpRZFFiSmw2MUhwVF9lUVVyVWJTQ3lTMkJHNmtHMFNOMmwyRng2TlFUVlM0WGhOdU9KaTh4QWZ4bm81SUlqcEN0dm5FRHZVQ09UdTBIVWxZajM4alAwcjRrUURkMHFPSnNWVndUNjhjcjVUb0ROQVZJTFBCMmU1bFUyNUl5c0YzZDQ0bmVSNXB3Nm9pNUhnaW9RdEJYMU9WZkVqS3FHdGRaTnPSAewBQVVfeXFMTm9mRGRDb0NZSlU0UTM4c19nUEJhMERMSFc2ZlY4Ul96bUdPUFBlSEZQZ3c0NnFXX250RkQybjhjQkxoSVc2OGNlTnNoOWcweUdOVjlzdS1sZjZvUkM1T3FKWkxTSFczOHVHQ3pMbWlJbGxDX2Itd29DZU5iTzF1ZGlpSEk2dkNaZE0tNXA0Sms5SDdsZ3VuNjhQTGxYc0lYemowWmJzbFE2VUJjb0drM1NYNktGWTBieGFoOFJEbU05ekZtODl1UGsyM1UxbF9idTdCRlppbW05c1RYZXhVaFd3eXc0NU5PN3RGeWM?oc=5", "source": "simplywall.st", "published": "2026-09-25 14:34", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "PERSISTENT Stock Price and Chart \u2014 NSE:PERSISTENT", "link": "https://news.google.com/rss/articles/CBMiYEFVX3lxTE01VG4tR1ZHRnF6bF9CZzh6bHlySkh2MFd6bGJKUVhycUhNQkh2R2syeXEzOG9tLVpSTmNrcUEtOUVWZm45QUE1ZTB1VXFYSEc0LUI0akZJc3NQTDE5SHh0cg?oc=5", "source": "TradingView", "published": "2026-09-25 14:31", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "R R Kabel board approves proposal to acquire U M Cables\u2019 optical fibre cable business; shares rally 72% YTD", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcGpkYXl6WDhuYWFNMkVobGFYaHROYTR3R2NJcWhMcmptMEpqS09jeVBMRFNsQjkxSE9QVWVZQUVXeUFweWdVeEVTNzUycGFHMmxkekJSR2F2OFl0LV9CYUg3M0VvVnJEaUlEUFNrT2RqVkpNY21PeW53SThRUzMzSzhqYm93VkNPWjVSWUJUYnFicTdONEVQY1NwdTlqTTlSbWhxUGlZMEN5aUpyWjN5aUgxckhCampqdzhoQTYtZEpkSGljNWhhVUJoM2dqNUhSMGc?oc=5", "source": "Upstox", "published": "2026-09-25 14:04", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "India shares log longest weekly losing run since 2020 as oil prices bite", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRDlIOXFjNzhyRGVteU5DNTJCdVlRNUZEY3VObFdZNDI1MDU2SUo0NEM1N1JDTHpDMTk0YU9OM2V1eXRla1VaanBsTTlUM1lWR3VYU0g1eG5pM21hNzFWQTdabWphemRRMlc1U09MdWxVRVNLUWxjd3pIODVuY2UtcFE0dEhPTUM2MU1pbHNOQ1NnOUQtME1TTDJjSzJzOGljZTRmN0NBZ2Q0S1VodGZaSXFxZU1VTGNnanc3a0o0anM?oc=5", "source": "Reuters", "published": "2026-09-25 12:52", "score": -0.382, "label": "Negative"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxQbV84TnZBcDlZcGRjQ2YxN1Z3eC1lNHdhNTN1ZENIRnZsR21zVVQyQUFmNnpKbmQ1VWl6SEpGNi1XX01ZcXZuM09QZklRNUh3YTZwd1RJNDRpM01BRUJfS0VJSXRGVy12UllLVU5jZnd4UWMyQjlkZHJPRGsxX2RQZnY2c3RRRE0?oc=5", "source": "Univest", "published": "2026-09-25 12:22", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Two years ago Sensex hit lifetime high: What went wrong after that &amp; what\u2019s the road ahead?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPNjg3MGJpYWo0SHZZNlZLX09hOHJTTU1CZm9FYzZTejdsbWl1bmZfY2t4SVEyNTFLM01ZcVZueHJhZlVtRC1zdWo5ZXZaRkhWOUtJc193NnZOZVhXUDcxcWpzcXQ0eHlmdG1TWEQ1R3NfaElGZjc3eldBcmtIbmphT3F4VFZoMWFwOFZQZ1ctWjAzRlZNTlZOOVVrVFVGcVJkSHo2WVBleXNYWi1VU3VaMk1teVJnVGgtN3BKdXY4U1cwTXYyUXJ6Q21YWmhZbTI5QkdCUG5xaDdyUVFvMi13SGVteFl5a2lSNUhYSTN1ZFo2Vkk1X2lURTB4QXpmc253Zmc?oc=5", "source": "The Times of India", "published": "2026-09-25 11:56", "score": -0.44, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel enters optical fibre cable segment with \u20b977 crore U M Cables acquisition", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVHNrRVg1VDRadktqWU9TVnUtdlV0UGx2YVN1Wk9maFBKZkl6NXN1dEhmSGxFNVVaejRWQy05czFfT2twSjJxX1lDR2x5QTZycklWVWJBTDNGZ2lWYWFGYUN2dHUtRnEwUGxsVmw5UmhRandzdHdDUHZMUGZNbnhsUVdmbWJ5VTZ1NnlDdTM4UVJJNWlDU3QxRDJfeUZyMWF1Rl9fWmUyWmdyUHZpVXNRT0lkVjVUaHZpX25Na0RVa1lHRFh1ZFlQOUlhVUFJbmVLamVsdHZHVkt6bWJrRXY5UdIB5gFBVV95cUxONTd5ZUl2WG5FUzRqVGsyNGNWcHpEN0ItSkJvV2wweHhrVENsb1NFa3ppbm92bUFGdERMZWlva1YyMEl0dDYxcXg3clQwZ0xKRk1OY0c0cjZOYWFmamVwdnNsTm51TTIwV2lhNnFNX1pfS29Od0xQZXpWNWdFd1k5Y1Fmc2ZKRWJtRGlJUDdBM3NUS0RSMWJtdDlVaGM0NzVuZFZvTktxelNrd29GOFo2SjU5ZU1HR2VWUHZaUTBVa0l3TjZVOGZaWDZUTzRTSW52VnIyNThJb3p6b3lPU3RualRINlVGZw?oc=5", "source": "CNBC TV18", "published": "2026-09-25 11:42", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPMGh4UXhKOTVzdW1BeE5LNGFFR2Jwbzd3T3ZvV0NTYU4wekJVZmE1U0FuZ3FsTXlTakZ1Y09lZTFJRXVIOVl2Z1R2ZmJsUUFHaEZXREJUZEtCdFNjWjRKWHhZWDNBMGpMOTJnZHhIa3ZLdHpvQ0tmMEdOTy1BN1hBcm5WcFZpYUdVZmdXZkVFYUkwdnA1VFhQWlNDc2xGNzY1eGlPdjhvZGR2MlRYbnVoTVFjakVVeTd5SWxEbnc2RjlxcHdkcTRYb2tDaXhocjVD0gHTAUFVX3lxTFBiSHlyQWowSl9jdW9fNEZsWnBKV0VjVkFTcV9kNkNoNDQxUHhiZHZiREtiMjkzMGplU19TNjNqVXlVTFRTd1kzeTBwSlFCS2VDdEt2VmlOb1ZvY3ZhMW11aFZWd3Y0bWxUWUQ5WmhGN21xeE9XcnNHWUpvQ05iRER2R1NoaXIwMDJ2dm84a2NpRzRVZ1N5NWk4Tk9XOGxKb0R3aHZlNFdfTzU2MFBMQjBBeEFVSUV5cDQ5eTVWSWgwRGY2dGs3X1BoWDdQQWRhUzJiRXM?oc=5", "source": "rediff.com", "published": "2026-09-25 11:22", "score": 0.612, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPbUR3cDZZTmx0T0FjVGdkU0ZOV21PRUFzdFNkR1FaT2hqcFQyZkVxS0ZKSVEydXF6OGlMbnUtakExc2NhTGI0WkE3NXVYYlpnR1NBV2l5SUxWUFhXX0VtemF1WG1pdUU3TnoyLVJCb3ZxM2ZrdjUzRW1wZFJ3M01WQmtaYnFWbUZxR1NGQ2Fwd2dJRTM1QndDMnlobXFVbjAtUnVscXUyZUtyMVZIaEdmSE9MQlFSTkpkYXhvQlBicjJTRjJ6V2VIRnM4RFNCSDNWVmFudGZNTQ?oc=5", "source": "equitymaster.com", "published": "2026-09-25 11:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rebound on Value Buying After Sharp Losses", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSjR4N2QtaTVfdUc1bkpKY0JWcFZ6RzdlM21SN2M0eXNfT2hQVWt1eXZxYmlmUFVBSGhRdmxTalRGYlIyV3J2M2lmZk05WUpVcDQ3bk1IeFh5aTN5Mm1nVXFZOUJCenlPRzR6VVAtaW0zcjZMQno2QTh0MklYUFhvZW1Pa1JvRDNCS2JIa3U5Qk1SMjJRTm5zZjE4NGFIVlVFOHpwVWJHTlBtaGfSAbABQVVfeXFMTzMwT3V5UkdaUUpqeTRFOHBwOXhrSFdVNjV6QXlZc1lzN1AwUzU0RFNxYl9aWGdQSS10S1d4dnRZNlhQNjZzMW1hTmhBaFoxMmFIaWNIdjdDblFCanNIUjJXMHR2SEJyUnVUb1J4X2ZoS2FVLWh4N0tnZGJ0RGc4aXpPNnQxLXFrR3J1Z3FGczZjM181U3FTbnVySUducS1VNGUyaVByUVNyanFPdHRHSVQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-25 10:48", "score": 0.318, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxPQUxBSWtnLWFqMkRfMks5NTlUcF9sTm1lNEtSdFZDaEstMWw3ejZUX2czMHFwS3k5MEFOWHNBb2w5VElVd011VTdpZ3V4OE94Q3ZGUVhJYTJhXzlKQnRicGVnc25ZNDZDdzhmN09xTzJCNDhLM0JQOHdRZlFKTXlXLQ?oc=5", "source": "INDmoney", "published": "2026-09-25 10:31", "score": 0.572, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Today: Indian Markets Recover After Heavy Thursday Losses", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE5hVC1JSXRqcHpiOC1BcW9STzVMX1E1Y2FuZThSci15UVN4VVBkU0syaVFzU01NaXVDZ21QSS03M0h2N0JoZFFOV1lZVlZna1YtRzRHdi03OHRLS3B0OGdGbzRKX01uc3BVbzZwTXVmVkFoMXU5Nk04aGhYZw?oc=5", "source": "APAC Media", "published": "2026-09-25 10:31", "score": -0.026, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Sah Polymers Share Price", "link": "https://news.google.com/rss/articles/CBMia0FVX3lxTFAxM1NrSlNad3RNSzJKUGVISVgtY1lGZ3NYN3FyNTBJb0FBYlNGQjVCSTRBWXE0c1dHR1lvemdIOFFwLUQ4czVFaGplWHRnbWR4Wkc2N1pkTUlfQ29mQkFNdU9DZkg2akQ2LVRF?oc=5", "source": "Upstox", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "Nifty Chemicals (NFTCHEMIC) Share Price", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYURIakNOVnRybktpTUJSR0ZBR1Vla0tUNHQzQmY4clE5d0o4Q1pZM3BtaGhTcjk4UWtuR2tXbmJ1S3kxOGZ4SVhYSURHRkRCN3NwUUxzaDJ0dUZZWWZ0aWhlQkZtclZ6U0hIbTNJTlpNQk9Sblp6WW1WUTVyb3ZRRHJlV1BoUUE?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.402, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today", "link": "https://news.google.com/rss/articles/CBMilgFBVV95cUxOSmhSUlhBeGVjR0VmV1paYzdJdDlLd045M2hLX1dPc0NQdkJXUmR5dUNCNGNYeGxBNnlrTVNtMkQya1JiamhQQTNfbU8zdmxndzB4TWlmSndSdmpzZ3RGU0VickFfeDg2U0x0ZmFkMWtxMndNU3FkdmMyTTE3R20wdnNpdUJoN1RNdlFKbXJHNXlqMU9KUUE?oc=5", "source": "Univest", "published": "2026-09-25 06:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNU2lpQ2pNTWhOZFRyMzhsc25Pd1Z2VjI5SkFZa2d3VDhmQVNmT2JuNjBoNWczYU5QaDZZLVhRdVc5WkNZR3RzcGhTN3JpdEJRcWllYlNWQjd3aDBwM0Z3RnNVeG45SUllbmQzX3RtTlZVVmFyRllRTHZwcmZVcFpybi16QVlYeEZoU1Q4Z3o4ZXMxekZ4UWdWYjV1b1Njc3g0dVJlVk5sbEFmRkp5VFNvb1BXeU40RFhHZV9jOXdhU2tIeXV1Sk5mYTdUaHVRamxZTHlqbkwtLVA4MW93SDVJbk5HT0hrbVYwdEZJQVJfSDJSanFzQl9lZtIB_gFBVV95cUxQZ3hlSUszOFFSZW8zSkdBSm0wY3ZNblIxRS1HRnBLVG91VVZ4blFjb2xzakhtMjNBblRzU09WR2NZeWdGT0x3ZHBiSkNKNkJoTmFGanNzX3owUE5sb0szNFhhVEpjV1I3NVFKMGU4VnRCTFBON0doMmhmUUtnZDVYTWpiNV9CZWdkZnlEWXdZVlpBRFRCdUNLVU4xQjJ2dHdJM21Va21pbGppWDBGUkpYbi1VTjVVTEEwM0Jza3ZzbEFHQnFybUJJTUVTc3lsbVNVbF93VzdqV3BWdHR6THZEYXpBeGRZbHZ5Z1hUOUFWeDVJWTRFS3htSFB0N2Jadw?oc=5", "source": "Business Standard", "published": "2026-09-25 06:34", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxQTE9BdERYOTF4QjNsVFdOSUVsVjdickVLMkJHYld6YmRCdm5PRGloTnh2OHk5VmRRQjJiTDMyTUZNalZMQXk5eGt2OHd6RmllbVhWbUpEQjhnOVJvbmtVU2w2aEs1cTd4WWljRTkyc2dmT01xZVRnb3k2TGlvS0lCT3NVcS1yclo1TERWQWszM2l1dzhDdnBoSUpOVTRQNW10RFd6ODFidlM5QWttRnkyX1RWaWhWS3RzWURldTM4MDctTWR3d2ZWSWh1a2FJX29lV3Z5NnkxWUhVYzRzZmw3NGI0V1Q0R1o3TTVVZUl3REw4TFBtNTdUZVA3Q1VxanRQYVF5Yk8xc0g1YkVUZm1mTzFR0gGXAkFVX3lxTE9HLTI5ZmFma1R5UUFlREE1U052c1BXWndUTkY4ZlpnQi1hVGs0MFNNTS1SZU1qeUM3cXduelRYbzM2WENOQXNDVUprdkVfYnJDbE90cE9CQXZ6bUJEZkkxdE9wbW52akpFZTZwWGtQaTFQei14d2hFLWJMT2VpOVotMloyZ0U1UFFLeWZNZ3NzYVozQ0lwbE50S2pJN0REOVpaNWZXX0ZOTFVmZWVkbDI2RFA0OFRtUFZxc2ZEeF83emxxMHN2LVk2M2tNNUpmemRCR2lXeUtwYlVPdHFzNGh6Z1RJVmV2aUgtVkFzajM3R2VtOU9qNlAwY29sN09XSDRRR0FXTF9zVV8tNkY5YVpPbVYyb01icw?oc=5", "source": "Livemint", "published": "2026-09-25 05:52", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE shares dip on day 2 of listing, brokerages back long-term growth story", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNVmN3NGUwRl9DSWI4bV9GWXNDZk5fRV83NEJWVDc3RGVNQkh5ZWktVjdJRnJZcE9aZUxUQ3dyZWZodFFiZzljZmppdTJ1R0lPNUtPTjdLSVdfUXJ6VmNyN1FWVElaV094SGFJMlNOU2drVGlFdUlPSGpld1g4VGpoa0QyS21vUTE5QWViVl9ETWtJdHpKbDNvek9wOHZnR0ZRQTNvNGdPSmVaV1BvRmMyQmtPSWZpZmFwYklWOGpkS2dKdF9DUDg0LUU1QzZDUkhLNHdNR0RRd9IB3AFBVV95cUxPdk8wd0R3RW9FSW1lamlhT2tiT0phLWRyT0R5bDhEUVU2aVRjNVZwMGo0SHlfZVotNHZoTGxCR2ctcGxWNml2UWZCZ1FGOEJZNDRFNElqSUtKY3I4NjUyR1RsTEpZbWI2YkNudU9GRXJURUFfRjZfSlh3VHpsaWJ0VEhRdGhhcHVMVjMxMkg0Q3pEMWY1N0thZm5KTnRINTNwWE54NWNUc1REZFhzN0JCZnVxc0J0RndhMFZxTUJlOFZ0XzhnLUpGWDR2Y3Ftd2dwb2hRalRKSk1lS3M0?oc=5", "source": "Business Standard", "published": "2026-09-25 05:32", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNS2ZIYlJtSTJ2R0tUd041X2M0a2gyT0hxbktRNi1YSFpNcXlUZlBwcW9FMGl0RkRoUXJpLXFSYmI1SUlJTkFBNTl0dlExYi1LWm0xX1hUVVFqVjhxWlJwd1Mwb29fX1U0VVFhRE01d3IxSTNpNkkzQWY2TkpJSVVKLWtlM1dFWkFnaEFuZ2hCT2RYWktac2dQLUVmemdKeHlMMHYwbEtfaEI2d2w0MEdYVGx4T2R1ZktDV1RWQ2ZfUFBDZGRTWVdmSF92OS1kTnFNUTBXeHlZd3ctMF9wMk9lNHRoVEJTUTVYSV9rR0FvdG5jZVIxdzBJdnNSS1VzbXll0gGGAkFVX3lxTFBZX2J6TDljZ3haMlBoSFNpQWJ3XzE1aVhVTXVUNUkyYUZLY2N5Z1VuV19hbzZNNDhsb2RlTjZWRmpObFNlVFR1RmtRcVM3bXZGODZXUnhJcC11VXVDM2pKWVNfdXRjaENBQUZiRjZwZmZ2SmRmRTE1Nmxac1I4RlVla0U0LVdlNGdKS2RxOHhfRUFTaUtlcDNLTFVjY2JyZzBSWFEwVXR1R25rMjZmRldrRldOazUwRmRjTmhpVUl6Q1ViWFo4bS1GaEpuWkhUelYyd0ZBOGdIM0Fxa0p0U29jZEpnR1NWcGx6TEl6ckt5NUNhS0lTVU1QR043dEZvbC0zNmpHNmc?oc=5", "source": "The Times of India", "published": "2026-09-25 03:51", "score": -0.494, "label": "Negative"}, {"symbol": "LAURUSLABS", "title": "Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSUFqNDJicXN5c19sQXd2WXNJb1BWb2UtNUpOZTI3d2JudFdlNkZmTzVQUzFKM3VXTHJlZGZKUlhCZTR6MUZob0p6Y0hERlZkcDBzYmp6OGJaMTBKRFcySjNlblpkZXNabW1kZFZLRzdkT2N2Wnl0TWtJcU54Skk2MTJMUTVFQmJnbXlzeE9jSDgxRlhQaUd1X0xibGxDWks3Y01hZkViMTdVNVJYZ3RJald5TGVvUW5sMkV2M2dxbXBiWUNDT2ZXV0xONFBVa1lPOWN0aW1ZY3JVZ9IB3wFBVV95cUxQOGJWak1PMG9YdEpvYzc3S1VhNXI1bDBheUl0TVdJMTBCdmJoM2M5NUFhQzdYb0VFM2dsRmZLOER4U3k1eFUwQmg2QTdlRGNYZ3Fod1F3RW52bWVGUU02NlpaUkVhWTBXUXd3SERZblFDR2JVR3ZZZ1FkcTVTcGU2ZWZQUEVaWlFTMmJRWDR5WHVoYWtQejV5YjRjNXQtSHBKOFdaM1Y0UVBTNTZENWU1elFHYTZmVkUzSFkwUkM2TGw4Sno0SU00WXNUMjZUenpEMXdqQ3AxdmFOeE9HNnI4?oc=5", "source": "ET Now", "published": "2026-09-25 02:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...", "link": "https://news.google.com/rss/articles/CBMiqAJBVV95cUxOQ0Z0MUFZM2ViTTdHaHJ5akJLdkNEbEVZeFFsZ25KVmN6UTE1X2xMTmtUckhBOUdZeE5OOHY5blA4WDhVZDVJbjZCeUJVWE5meUM0aWhoY01DRnRBRHJaVURNTWg2SVRPVkJhUjVUb3dkRDVQZ1B5ZzRhS1ZyUVA1NnNXOEJqbWh0TG5EWHAxZXIzcU5nYnIzQ2xZU2RWaHR1dE5KTE1sMUpTQUthdmdLbGpjcXZvY1JsWXNzcHp0b1F3c1I3ZHpmUTdqMUpmbTV3M0JNM3AzWDZETUFsOFpURk9oQlY3UXB2Rjh6cjNobFhYOTI4MXRUN3YxVXYwaXJnTklxOGU3NXNHSjl6c3RndGt4TmluUUROMVhIZ0pWc3hia3F6blRJSNIBrgJBVV95cUxOdWNfS1N2QVhiREVSTXpDajYwUE9RM1VycGxPNmRKaHU2N3N4Y2tiX2tKSlU1NEpYR0Y5Q2xOMFFhV0VRRE83WmNDUXFvUU5LNXFITElxRmNJSEFJT3dDcGNwT3Q5UHYzaFB4NHg4NlpKUXo3bGtOV1lPRllGMXUxdC13N2RoTl85V01LU3o3Yk5Oa2hzWVZxdGoweFJySlZDVXFPY3NFcXJwV0tpdkxOZDhhRXRpU3ZhOEZCMEZ5QWlBUnczdTRuMUxCcXdwb1Vtd3JWS1Q0aUxpbzhhLXh2bmRtZ05Cc2VyVWM2YjVJTzRXd18yNndmaklMQWdsWlEtdEkybzlJRng2WndzbnJWUGF2S0RBNnE2MlRCb1FGSVktd0g2TEdPdGEwMDRYZw?oc=5", "source": "Moneycontrol.com", "published": "2026-09-25 02:06", "score": 0.178, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Bond Yields To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On September 25", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxOdVk2NWY2YmFvVWRzUDF4anpscG54WjM1SVVVVldRT244LTh1aXVWbXFCWnQyQVZnbmQycU41N3JiV3p5ZTF6VlZMSUI3NUQtR0tsVDF6cS0zdjZiQ3lCM0VhTXFoSEt4aEh2YVF2cXFxY2ZfMkVZSjhuNDZyODRGQUNYRXNpeWdEZzRjd2ZaeThvb3BxdmpBdU1jZVhNWHAyUzR0eGhtTzRHYTVkdTdvYWhRcWhldEkxV3Z2bnZ2SjhqNVYzMWR4MTcxdWc4X0FkNzdjb1VhYUFFNFNOTnVMeGFtUkF5SC1ZRG4wM1Z3VUU1SE5ucnfSAf4BQVVfeXFMTzFDRFpfdFA3RTRhanpJaFljZTc3ams4V2FOMENpZWYtUC1uSEwtYWlNODhZSnhnVXBZUEc5REwtbjFDYkFtSjd3SlBwbHgzblJDQ2pyc2F2aHdwV1NnaTlxU2plcGhYNWg4cWZiZGNObUVPOENwTFRuS0dnbHdTbVNtQTZGUXlGTnVnaEhZYW0xVHhjVnpZdk1qMlQxWFNnRHM4NENlWDFtdFhQODYyNWFRb2haeThMUWdsZk55R1g4YzBWbkFGc2xvX0Q4REwxdHBjb2VidHFmMHNKRnZDXzBrQU5oZmJ5bVFuZ2dIVmhlMGJKNHhhQmFPdlNPVlE?oc=5", "source": "NDTV Profit", "published": "2026-09-25 01:28", "score": 0.807, "label": "Positive"}, {"symbol": "RRKABEL", "title": "R R Kabel executes BTA to acquire U M Cables business for \u20b977 crore", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxOekdBdkJnQy1zc05YRUg5aFF1a0lwT04xNl9vZlhFaUhGVE0yeENFRkdPYWp5eW5qNGJPQ1Z5M0tIQWJTMmVBZ2NIcG13ZTFtc3FJaE9hOG1SQVk2UENVdGNWTXktTE10MGNUVmpvNkxodGg4TS1KdHFlZGprNUpZMkRsS2x6OW1LcGtSVnJPQnFvNlpOaHZZbFlnSlZ0MGtEdjdSdzVvSQ?oc=5", "source": "scanx.trade", "published": "2026-09-24 16:21", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets", "link": "https://news.google.com/rss/articles/CBMi-wFBVV95cUxNNDY4RnFxUWdPN3hFd2xaaFZRMERxSGpxN2Z1ZjF1LWVVZXFDUnZlQzFhNDRUYkdVWW14NDRCdXZ2LUQ0YzZpNWVUQmxtTEtHV1UzaUw1eWtXYm53a2JYSzdFQ3Z0clktdUNZY2J2dE9MU2lxM012czJpUDR1R2ZkN2h3QXNIWGkwX3pEM0xNakt5RUt3Y3hrQTZPNW9yUVhDQnRCaUs5RHdjRVM5Z2RMTGc2cG10WS0ycnl6ejY3YWFsYkUyVzJBYVc2UXlvaVNpRkFKZkZmWkE2RzBxcWFMNElnR19nMFN6cmRzRDBteVpQMjlDVHlaVi1VONIBgAJBVV95cUxQbEJYN0g0YUZETXczaUtkbUdMb1c4M2lQaUszdUtyTXZxMVVYWENrRm10czlDRHQ0alpzSjBhRXMwVzVYUUo0djJYXzBQWlM4S3NZZXZtZTM4TS1zd3BVbEtHeExGNHVVcTI1eDN1VWZHTUQwRllLU0VTenctSGtMT09DTFpSSG00UF81R2ZsdGxFMFlGVFB5aTZLWGVvQ3RwWTVVWTV3Rjg0N1RKbTROQjdaVjR0RTRuRUVtLTFUTDgxdUVMOWVhOV81ZEhMbHlxVmh5Qk5NMXNCdXo3anhfSTY1SlNaSi1zSEtvemVYdjY4R2YteVlTRG1qX2wzQXFy?oc=5", "source": "Livemint", "published": "2026-09-24 16:04", "score": 0.7, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxORWVLSFhyVy1XclJaTW9wUmtOTF84WGZkclJHbmtIdW5oUXNJS2J2V2xqUjNnVmEzRDJJRko2Y1UzaVVuYnFOUlRyYTFzNFB1dTlvMXp0U3BTRS1rUV9pWXotZG5FX2xZVnI0eHRaWDhlLVZwaThPXzdCNW0tT2ZEMFp1b0FrRFVsNnZSVzVCTTd4MWZEUm9ERnJ5bTJNaGRIYlhYcmRGOE1ub1c0THBORGt4d2h6SnlBWUhFeVdSUDg?oc=5", "source": "scanx.trade", "published": "2026-09-24 14:42", "score": 0.382, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQnJ1UkZncDJJcTRVNElLd1ZKN1Nnd053YjRobGxJUEdGYUdWS0lvb0dHS2MtemJ3SUppQmZ2c0NERjFpa2szSjhMZG5BcGZiT3NNa191ZHEtaGRCNUYyU3FhMHBnXzFBUkk1d09ZNWFnNXJvZHR2VU5LTWkwMFlWU19xVnZkUkk2aFd1N1FBZm5xVVlEQmx6dVhDcG83MGZveUFrMm9pMWgydUlPMDFZOTB2RFBBT3JPdDRVYmdKTUtzbVBMTDFIbGlzdkhVMklTNi1aeVFHNjNBUU9RclRiSmtXVjRlakw2S2UzVlhlRTZvWWs2RFNoVG0wUkhrZw?oc=5", "source": "The Economic Times", "published": "2026-09-24 13:49", "score": -0.153, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxPSmdZMUhhTERFclM4bzZicU5pWTdPX3lDUFQ3NU5qcU5hNWVHU3Jrem1lS3FuYjhUcXBVOGJFLXVKc3hCSFlvZ0E4QzNJYjQtNGRHNldTU0pyWS00ci1qNUNTNFpXd2lJLTZnRnQzVGNraVBUUGNhSkJzWWRjVVNqWm9Qa004SHQ0bXIwUV9SNm4tLWxtUHl6eHFoZVpPUHQ3UXZxdUxZTHZrdnpYY3JrTHhFTUxuQ24wd1lBR092aDNFV0lPcXJWMkxITnFFZkdNTkJqRzZqeVFIZmYx?oc=5", "source": "Kalkine India", "published": "2026-09-24 13:15", "score": 0.318, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "3 Indian Export Stocks That Could Benefit From A Weaker Rupee", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQNUp4b2tjbFlmWklUVm5zT2NJRjVXMm53bE5DNjJvb2ZFd0tFZVRUWHVxbWozaEp4aVBQMGtxZkpfQ3FmYnZtbEppcGtXZ1hYYl9seFIwdlhpczRuUWg0dE05REgyUkRMdXJpaVZDc1BORHVteE1IcHptNnNRbkdTY0NEUTZKZk04cHEwWTlNTno4MjJKU05aVlVOZExfd3plejl1cUxiVXlVbVNibjctMlFyOWx3aEZmYk5VNElFYUM4WENySTZGcmFrWURmdElfRjhyTm4xelJnYWNjVGtmb1I2NmxXZnRPem56RDZ2b24xZ9IB9wFBVV95cUxNVGN5NWZ1TnFTNUt1elFVSE5Tam8xZi0zWVY4Um1SX3UyVE5xNDZPZmpWQ2VWXzBsaW1vcnVzX1NoZXk0aWJjeU5iaXpiT1dTejAwSUt6Z3FhTThnTlhsa1ZFdHpfTG1sNjIzQ3pkZ0duUXY5N3ZqZU1qckxKVlZneVRJVmxjU1VrckJtQWlBNWRsNGdZbnRxX253TU56dE9NdXA0RlRoR0dLS0VDWFQ3VXJILUlrcF9OTU1lVk1sODFsbmVIeG1ROEFLcUlhWmswVzVkUjgwRW85cUNQUXpOcS1VZnBLT2pMSlZ1c3lGQ3MyN0JKeGlB?oc=5", "source": "simplywall.st", "published": "2026-09-24 13:01", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPTmEwdzJWdUtmS1lTeHJNaEFsLUVRRTNTSU0yMko0SUJCczVmU05rb2tDckFtclNUdEJzbmN4VUw0TUY0aWwtVVlEM19wTF9BZ0xyZmw4Z0ZTam4wMmphemF0SjRoWWZTaXZOOGJES2dTWWc4MXU2djFTZFQ2ZmtnTGgtNFBvMlpVbFJUeGVCQ242RGpic3ViMFl5QmlzbE9ZMFBIQktpRXRkSWhmWVh1WWJYZjRYQ3FkcEJtOTVNUmZseW02bXQ2cDlheEVZWnItWGFrOU5aTmdDVFQ5UDJMUEI5Y2VSREJGSmRGdFY1UGY0cUJTR0FFUDNSc014endZb3U2TUN0dFdXQdIBjwJBVV95cUxPX2xOWkM1Q0VWS2w1cGpsMXpBUFVpZHZOQ05TMTBkY3BMRHUzcjVIeEdpRHBhYXhKNXUxSzRjZkI1RHpXbkRQdlpBUkdPS0JIVG5jcjQ4cGxZUnZndUIwX1VMVWlwU2c3dUZTNHR4VjZrUzg2VXd6UHFaYzdTV2xMRXQyWmFQcFdIMEJUN2pqcFliNW1tRHU2a1VNNnUwekE5ZWRTYTF6Sy1FbnBhNEQ1Zkh3Uno3QTZuTXVRcHVlNm1LVE5oVEJHLWRiMWFUeEo2ams0QU1ocjRRREF3Vkd0dXQ3ZC14cWNLNE5oM3lPMXNKelVjbmxuQjA0dURockhtcDBQS2gweGZ5NERLYVRB?oc=5", "source": "Livemint", "published": "2026-09-24 12:36", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see worst day in weeks: Why was market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNTTMxLVltQWc5MkFQOUFYNlpYUTlLRnVtOWFTM19ETVhBaDduYk9pa3VKY2lIdGNGTkpIbVVKaDNkV2Z1NlBvdUVVeC1JbTNJem02eHlvdHRvMFFkR285ZjlFWk1fbXR2Z29HSnNVVklmYnhpOVlHdUFxeUFuNmtXeTZFY21KcGFraFdXRVBfNWZRLUU3WEhhd0x5OGxkRlRCbXR5T21JNDRpWE8tSU81VGtxUXFqUzl5T2FrS1dXd0s2QkdoTkRlSWJFR2lORk1JOWpnWHhvanB4bEdTaS1aZG1sbTJfUDFManBUNNIB8gFBVV95cUxQaVFGYUROS1ExTmNWWWI1RHNoTGZfWDd4U0hPeGVCdzM4eUtkZXVMaGZSTXp3NDZEcS1POXpFa01KQlNtY3U5QWgtdl9VV2hZY2VzZGp2U1pQbE5sT1JoQkZJeFFqT3VMOENGMjFXM3dRajdZdTVJMVpIWVVubzJhbjNyakljV1BrTl9vVDh1Nnhnd3VqdDJBbThXVDY5ZjBIZXFKZ0ZHUkt6eF81SHJEbEF0YkJnVDQ4clNuSFJONkZRRTkwZWxLaS1QcEVwVmRqQURkTlpSTm14R2Z4bDV0NEhMMzVJdWZ1TzhaRUlweVQ0UQ?oc=5", "source": "Hindustan Times", "published": "2026-09-24 10:57", "score": -0.34, "label": "Negative"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNb1U1UU5HdEFtaWZCRWdVRWxUc2pRMFZ2YXl2bUpYNE1xNzZBX01tTXNtQWc5d2ZCNTdzYUZwXzU5U2VOX19rRndvYkVDaUl3aGVqQ3lyU01qYkNtVENjRG41VW9IenA4V21EcDhLYWFrdHZPYU9yNGl2RDFSUEdRcEtObWtDS0doZlo1V3ZwOGcwcmRROTcweDNZeTZaRGdQZ084YzU0amppMUZaZERQamg3YUE3RF84TjFuLWx6T28?oc=5", "source": "Kalkine India", "published": "2026-09-24 10:15", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVTh5Q2ROa0YzRWp5NS1Kamp3NnMzYnBNRlJHcEZ1cVRnOG1aampUb2pFbERqcGNPZjN2WGZqNGd5dWNDN2R3bnhXQ016bjJoUXUxN2FqcVYxaDFrSTlwZGpSQmZIbGM3THdoMUFDX1hwZXo1OHNPTjVpNFhLWVZudVFHU2xxbmZ1aUFnWXZqM09tZzZ0TVlRWUwxakpaM3JIUkg4QlBBaG40QUQzTWxYYzNSZi1uVVZtWTJHVU1UQzhDWHB5OW9Fb2JHS3ExdVR3dExkMGJRRVRQVmZfZnM1THUyOTdWbWhDaWfSAe8BQVVfeXFMTUFnaWZmYkVLMzZkNk5ZRXF1ZF82LXluT0hoSlJNZ19kUVk4VHlzLXhabENVbTd5LThnUlJIc215aVY1T2ZwOThSS0dVNnJNTVBIdjgyQlBPQjJaTF9sQnZWeEw3Z3dVdFVMNnU4ZzBWOENQQ0dtZ1JQal84UmdMS3FvdEFJUFdMbVhXQm5tM3JYNUJhYTFFRnFtX2VIaDJMcWNPUFhpaUs1YjRSbG1lWWVTYng5VnNjbFF4Z3NqVWFHWEd3eEMxUjE5YUFQZ21qdVJJV240Q3dsYTdHQUhKTjVGcnk4UWRhd3lEdTJYeGs?oc=5", "source": "simplywall.st", "published": "2026-09-24 10:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "The battle between India\u2019s stock exchanges is heating up again", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQSllxZjNuQ0l0ZExkQlp2RmVURXBuMm5WRjUyUkZsOXNaeF90Zy1GWXMyZFAzYmlGMGFfTWlhSl9lT2JNMmVnclFGYlg3bjNZQTRUeERZRkFScXBYc0IxZnhEcUF4Q0tzcWhhQTZXaXR6NjA5Y1pTSWdDQXBPQS1HZWpMOWJHN0NzN0lLWkdiMlJWWjN3OC1Ha1VDQ1ViSE9QTmZmSHBYTVpFM1FiUEJtZ1B4Y01nd2dabTlwTw?oc=5", "source": "The Economist", "published": "2026-09-24 09:42", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPVWZGNDlpWFN6MFJFZVZMVWp4RnIxcTVXOTRMUS1oVnMyQkVmZkF4eDdQTGYxOXVKV253c2dWUVZrOFpQUEEzdUQ1Rm45bG1aX01RSzVBNjNIWEFIb0lLbFJsSWJNYzFzMVFaVFpXUnAtR2xtZEZ5YXhjdXRSOHI4ZkNVMlJvWUszcWJEdGFBWmpqZG9zaGJWRnZGMHFtM0J3OWluTEZMVE9xSkV0Q29QTnJFQzEza0ZQaERRWjNBaEN6QlpkSFdMcGRuWndIWE1RVU5uczhza2w2WndRYWlUVkg3Yi10bUJFLWRWTE1sT2I1NnhwVTdCa3ZBRmxpRklNbGtzbkQ3V1licnlmakQw0gGUAkFVX3lxTE5pNjM4R2ZHalBOWTl1aGVPaWxONlMyd2lmVERYa0RZeDlDMU1IbnZMWnhNQ2VuWXY2dGRTTlFrZVFrU3RmaUJtcjZxNnlVNXc0eU4wQjR5Z29zd2FWZVRoM2FVYl9BY0xldFp3SDNjYnNSdmRwdXFYTEpxcWM5WWFrbHZCeDhZZ1c4ODE2SWJpX1RvX0dkX1VHemI3dmpJem9uWWJsNU1Ia0JFWmxobTRWMjBFdktPS0d</t>
+          <t>Td5S2ZqUmVJYkRaYnd2RF8xZjlDakRzUWFvaTlVb2REeWo4WUF2aTIxZUVncDVzY2o0Tmp3bVR5TmpRQmFSMDZzSTB1MFBCSWh5RmJ2b1d5QTNDdHlSN1hVcEJqUHdlOHZ3VENMVm8yWDMwV3N2M0phaDNFZzZGdE41OWVxbkdjU0tDNnFnTnM5Y2phV1pIYWN1RF9DNDhtd2JBd0I4WHRlMGFvZUtHdXNlWHJVYnN6eTFwVjVhODVsYW04ck9LRnJhb3NzTjEzVnfSAZoCQVVfeXFMUEV5VVRyZjl4LW9fV21rY0Y1SkJyYmluZTZHZlpld0cyakhLcHhKTXBNR1kwU0RET0VZeW1Ea2liT2JzSkNGenlOSzlkdVZwejU2X2FJVHFOUHZwRnM5YjRGUzJDM0VaMVlVR2M3N3FwZW83b3pBcnRwQjFTSy1UVVpDUWEwYTVDSmF0eExBWkdOQml5Zkp5aWtqU0hqNlloT2V0XzRPVml6dXV2WW5MVXlSMXZFYkQwMGNqZTBXNjBWTFVkd3pUblpDdHZ2RjlXRGlreDhvWXNnMV9KVGFySDFFNFBzUkpZUEh3OVFRVmFfSU1oU3V2bV9Pdm5hR21UWXBLYW9TUElFRExLRGdPTmJXQ2tSMjlFRV93?oc=5", "source": "Livemint", "published": "2026-09-27 09:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOT3N4b21hRzhJSXdJVzFVNWRNQ3RqT2l3aXFBN2RjN1JDX1Y2V2U5MXlDN2l1a1BGQ1hLcWktbEgwYU1UMUEtalJDYkc5RDZqX0FHdFVuMmpDVDhHdkhWSDVpMFpXLXpoa0ZTWDdGcTBxU1hJSUtIQzgwUXZvQTRPdUh6UnlXYUkxZTZHTmJFSnFQcVFSc0s4V2tGNUUwUTJVZktuRkUwY1c5eTI2NjA5VEgwMDExekhFYVhLRW4wRlduOU1wZ2JqV1F1emdiLVUwWHZwa3BmOXV3MmtLOVpzWlZOOXJ3b1MxY2pvR3VYRlFjYkxmNFdIWGFxNTJJYVVvcWhJRVVwb01UbU3SAZACQVVfeXFMUDJ0a2tkZUxvVXFoM0VZMW5YYm13NlNjNl9KY2l6X2NkS0VvMGw5eGhyWDRzU2ZsTlJmTVdTbmZ0Vzhqc1YyNGU2TWV2a0FLLU1vQmRRVktFOXhtcDRwVVVMbXZPNmo4Q0V4ZkNCU1M3TEZ3RzZwcVp6SlhoczYwY3NYNVN1c1BKSTJLYXBRbVh0bDN1ZWc4VnZNb1VZZERDOFlSXzFwNW1RX0d4LVVGRHUta0Q0cVR5dndQUGNYaTkxWFU4ZVloTzNfR01UMDJ5aVB2R0ptYjU5Q0RLRnBEZExqdEZJV1BDMHRiRTBBa19fa0djbno1blZZM1ZwUWx2VWREaHpQeS0yVFQtRFpQc2s?oc=5", "source": "Livemint", "published": "2026-09-27 04:22", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks To Own In September 2026", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWmN1VW9wZjRBZl96MHMzNnRmeS0tY28xWWZtR0hfa19FN2lyVjdtZUc0a0U3c1ZYNmZ3eTNiWFVIRElaRGV4VDFVYi1kYlN3ZjNNemNjVzFwWV9CQmxlR1B3X2kwVmphZGhMazZCVTE1a3E4clpQbU9GLVNXTWs5MjdNaldOQVBOOVpMWnNMUXA4VEtmc0drX3RWWk01aXVvd2xJS2JYeGppOElvRTFWbEJwdEJoYlBVaXFhTUNhMG14Y1FnSWROVk1qb241Sk1vOW1MWGJ3dXpuZ9IB3wFBVV95cUxPSXhqMzhnOGFvNkRfakZ0cUxHVkcycHlESmtYb2N6Vzc0MGVlSnNhLXUzOElWb1YwclgwRmY5MFhreTM0TkpzdjVjR3d1Qmd0Y1ZmRi1KM1dLeTU4QjRjOUdTNzlRNUR2b3FvaVNTbW5adHhMQk54YTR3YlRLclVfUmxKZmhRXzc4VG9PUVg4RFU5UWFOWmsyYWZHaFM4N1pxTHVLX3RVTVUwSzRtQzhCenRfa1REbS1CeXQ1Rm1GUXhvV3BxRndHZHRGVEV3VHM0S0Vidjk5bm1SSHJiVTFB?oc=5", "source": "simplywall.st", "published": "2026-09-26 22:56", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "\ud83d\udea6 Indian Markets Stuck In A Jam! But who's responsible for the traffic? \ud83e\udd14 A Bernstein note argues that India\u2019s large caps are stuck in a bygone economic era. But here's the BIG question: \ud83c\uddee\ud83c\uddf3 Is The Market\u2019s Fate Really In India\u2019s Hands? \ud83c\udf0d Or are global cues pul", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxORUdYckd5Y2pPQUg1MHZTaHlTT1ZXWTdmTGxwSWlMcE9NQm1vNE15dk9qS25VanFnTzk3c0FHTEpwaGcxXzhmekh2dUNLM2s5Zy1USHBjMHRfakhvYndNanZrV19NZVFMY1hjOHZsektLSVZoS2tTNkdzMEJTeExiS3ZVbDVRWTNWVjZ3MWVmSzhnZDVvT2d2YnEwZGJLRUp3QXhxTDVfSUc5TTdvTXIw?oc=5", "source": "LinkedIn", "published": "2026-09-26 13:51", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market News: Nifty 50 Outlook &amp; Prediction", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVJvTS1CRXVsT2ZzNUhBV0piRVV1UnZTeDVEcDJmRElmWHB5WkZsM2s5YzlYaXJuVU9vVjQ2dE5XVk93WTVVLUx2d19wRm9lc2YzWW9xX0F1YWJCTUJtMURwVzRxbC1vUlNDWEpLRUZibzdnbVdjdEJUeThfeHZLSXpwTktCQnlMM0tTNUhwWmplMHJKb2ptYmVn?oc=5", "source": "Liquide Blog", "published": "2026-09-26 12:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxPbm8wM0RSWWRXc1Bzc3daeEpaNnFwZW55Y1FBT19TQUdxYXdrZ2FJeDJGd1EwQk9BbFJTZ2xKNV9Gd1BadEFlZExtZWlxdUZEZHh1RkRIU1lMNEJVR3hkZ2VKWnNGWUVLa1Fha29hcWcyNVR6dEdydjluNGxlN1YybHFabnUzRWdzMTFSWThkNWRRX0NXQ055dWl2dXN3cGw2RUJxSHAyTTFWMnNOeXZ4S0xGQXFjRmhub1lHeVQyRUhUdEpFSGEwM2U1MEFnbExtV1JPRUVNRmV2dUNfZ1BiblROc2IzLVNPclpNRtIB-gFBVV95cUxOT2FRblV0ZG5vNUh2QTZGeldJa2FuRF8xSmRWYUQ4a1NLblFyUmtJNTRCdHB3NENTZUZhdi1Ha1g4aTV6cy1POUl0Njl3bzZNdE1ZRk43bWQwRXZvNGxncTdBaWg3cDNUMHcyRVp3d2ZKRmljNXZwQktjUTZnV3NpWldYMmNoV0ZJSjZONVJjNEQ3d2ZLWXlVREFsd1VFbFdob0xydFJ5dHpFdGIzeERrQU5kcXBubmVLd2RZODE2Skd0Yk92bFNnWG1qUjNnZWRSR2YwaWIxLU91ZHBzTlJVb0twSW5pUnYxb3E1WEJFTWdmQ0tzeVhaZjRR?oc=5", "source": "The New Indian Express", "published": "2026-09-26 09:15", "score": -0.128, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQWm9DM0I5TUU2aWVIdHhCam9zXzFSUEI0RzhWaEFxWDFfbDFoeUFJUEZQbHk2OXJJdlpjeVBTVjd0RDdMSjdPMjl0eTN3NXZnRmR5bTM1Qi1KS3JsNFRrZlFCcmViSW5MTmdQdDItWTU4T3lUeFFkTEU5VHBEV2FmUjlqOWdvaDhNcGZlTk9jTjJQeVZ1Zkc4Q09fUGY4LVZiWk51d2U0ZGtxRFZ4cXpMV1V1UlJOdFN3RnZyTA?oc=5", "source": "Kalkine India", "published": "2026-09-26 06:30", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure \u0915\u0947 \u0936\u0947\u092f\u0930 \u092e\u0947\u0902 7% \u0915\u0940 \u092c\u0922\u093c\u0924; \u0915\u0902\u092a\u0928\u0940 \u0915\u094b \u092a\u093e\u0935\u0930 \u0915\u0947\u092c\u0932\u094d\u0938 \u0915\u0947 \u0932\u093f\u090f \u20b993 \u0915\u0930\u094b\u0921\u093c \u0915\u093e EPC \u0911\u0930\u094d\u0921\u0930 \u092e\u093f\u0932\u0928\u0947 \u0915\u0947 \u092c\u093e\u0926\u0964", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPVXU1bkFLVlVQVmhKWjdoVDlSNFQxTTlheVZFdGtDeEVEVzVtc3Y5Qk45R1RaOV93WlZrOXF3MzFKTlE5OGR1Xy1DcnFtUTV6YTYxYXlVMHlTWXFEbnlMaFliTC1uYTZOeVhCY2ZjQW5Qd0pzcEZWUmx5NHJHZ18tSDNHbTZrT29hbFNrWXFuQzFRTW5OQ3BMRERrUldoQUVMYmRTeTBfZEctVi1DUzF1bHphN2JnNV9lbWx3MGU5MlZRbHdZYnNrR1NHUVJVekRybmZtcWNFNGQ?oc=5", "source": "Alice Blue", "published": "2026-09-26 00:50", "score": 0.34, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxOTXpFTDNOdlg4R1lYS1FPU2VpM05pUUVGSHBvdWxqLXJ4SFpPTXZ6Q25FVjh0V1lvbnR3ODJsa1Q0ZDJlbWpRZFFiSmw2MUhwVF9lUVVyVWJTQ3lTMkJHNmtHMFNOMmwyRng2TlFUVlM0WGhOdU9KaTh4QWZ4bm81SUlqcEN0dm5FRHZVQ09UdTBIVWxZajM4alAwcjRrUURkMHFPSnNWVndUNjhjcjVUb0ROQVZJTFBCMmU1bFUyNUl5c0YzZDQ0bmVSNXB3Nm9pNUhnaW9RdEJYMU9WZkVqS3FHdGRaTnPSAewBQVVfeXFMTm9mRGRDb0NZSlU0UTM4c19nUEJhMERMSFc2ZlY4Ul96bUdPUFBlSEZQZ3c0NnFXX250RkQybjhjQkxoSVc2OGNlTnNoOWcweUdOVjlzdS1sZjZvUkM1T3FKWkxTSFczOHVHQ3pMbWlJbGxDX2Itd29DZU5iTzF1ZGlpSEk2dkNaZE0tNXA0Sms5SDdsZ3VuNjhQTGxYc0lYemowWmJzbFE2VUJjb0drM1NYNktGWTBieGFoOFJEbU05ekZtODl1UGsyM1UxbF9idTdCRlppbW05c1RYZXhVaFd3eXc0NU5PN3RGeWM?oc=5", "source": "simplywall.st", "published": "2026-09-25 14:34", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "PERSISTENT Stock Price and Chart \u2014 NSE:PERSISTENT", "link": "https://news.google.com/rss/articles/CBMiYEFVX3lxTE01VG4tR1ZHRnF6bF9CZzh6bHlySkh2MFd6bGJKUVhycUhNQkh2R2syeXEzOG9tLVpSTmNrcUEtOUVWZm45QUE1ZTB1VXFYSEc0LUI0akZJc3NQTDE5SHh0cg?oc=5", "source": "TradingView", "published": "2026-09-25 14:31", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "R R Kabel board approves proposal to acquire U M Cables\u2019 optical fibre cable business; shares rally 72% YTD", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcGpkYXl6WDhuYWFNMkVobGFYaHROYTR3R2NJcWhMcmptMEpqS09jeVBMRFNsQjkxSE9QVWVZQUVXeUFweWdVeEVTNzUycGFHMmxkekJSR2F2OFl0LV9CYUg3M0VvVnJEaUlEUFNrT2RqVkpNY21PeW53SThRUzMzSzhqYm93VkNPWjVSWUJUYnFicTdONEVQY1NwdTlqTTlSbWhxUGlZMEN5aUpyWjN5aUgxckhCampqdzhoQTYtZEpkSGljNWhhVUJoM2dqNUhSMGc?oc=5", "source": "upstox.com", "published": "2026-09-25 14:04", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "India shares log longest weekly losing run since 2020 as oil prices bite", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRDlIOXFjNzhyRGVteU5DNTJCdVlRNUZEY3VObFdZNDI1MDU2SUo0NEM1N1JDTHpDMTk0YU9OM2V1eXRla1VaanBsTTlUM1lWR3VYU0g1eG5pM21hNzFWQTdabWphemRRMlc1U09MdWxVRVNLUWxjd3pIODVuY2UtcFE0dEhPTUM2MU1pbHNOQ1NnOUQtME1TTDJjSzJzOGljZTRmN0NBZ2Q0S1VodGZaSXFxZU1VTGNnanc3a0o0anM?oc=5", "source": "Reuters", "published": "2026-09-25 12:52", "score": -0.382, "label": "Negative"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxQbV84TnZBcDlZcGRjQ2YxN1Z3eC1lNHdhNTN1ZENIRnZsR21zVVQyQUFmNnpKbmQ1VWl6SEpGNi1XX01ZcXZuM09QZklRNUh3YTZwd1RJNDRpM01BRUJfS0VJSXRGVy12UllLVU5jZnd4UWMyQjlkZHJPRGsxX2RQZnY2c3RRRE0?oc=5", "source": "Univest", "published": "2026-09-25 12:22", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Two years ago Sensex hit lifetime high: What went wrong after that &amp; what\u2019s the road ahead?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPNjg3MGJpYWo0SHZZNlZLX09hOHJTTU1CZm9FYzZTejdsbWl1bmZfY2t4SVEyNTFLM01ZcVZueHJhZlVtRC1zdWo5ZXZaRkhWOUtJc193NnZOZVhXUDcxcWpzcXQ0eHlmdG1TWEQ1R3NfaElGZjc3eldBcmtIbmphT3F4VFZoMWFwOFZQZ1ctWjAzRlZNTlZOOVVrVFVGcVJkSHo2WVBleXNYWi1VU3VaMk1teVJnVGgtN3BKdXY4U1cwTXYyUXJ6Q21YWmhZbTI5QkdCUG5xaDdyUVFvMi13SGVteFl5a2lSNUhYSTN1ZFo2Vkk1X2lURTB4QXpmc253Zmc?oc=5", "source": "The Times of India", "published": "2026-09-25 11:56", "score": -0.44, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel enters optical fibre cable segment with \u20b977 crore U M Cables acquisition", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVHNrRVg1VDRadktqWU9TVnUtdlV0UGx2YVN1Wk9maFBKZkl6NXN1dEhmSGxFNVVaejRWQy05czFfT2twSjJxX1lDR2x5QTZycklWVWJBTDNGZ2lWYWFGYUN2dHUtRnEwUGxsVmw5UmhRandzdHdDUHZMUGZNbnhsUVdmbWJ5VTZ1NnlDdTM4UVJJNWlDU3QxRDJfeUZyMWF1Rl9fWmUyWmdyUHZpVXNRT0lkVjVUaHZpX25Na0RVa1lHRFh1ZFlQOUlhVUFJbmVLamVsdHZHVkt6bWJrRXY5UdIB5gFBVV95cUxONTd5ZUl2WG5FUzRqVGsyNGNWcHpEN0ItSkJvV2wweHhrVENsb1NFa3ppbm92bUFGdERMZWlva1YyMEl0dDYxcXg3clQwZ0xKRk1OY0c0cjZOYWFmamVwdnNsTm51TTIwV2lhNnFNX1pfS29Od0xQZXpWNWdFd1k5Y1Fmc2ZKRWJtRGlJUDdBM3NUS0RSMWJtdDlVaGM0NzVuZFZvTktxelNrd29GOFo2SjU5ZU1HR2VWUHZaUTBVa0l3TjZVOGZaWDZUTzRTSW52VnIyNThJb3p6b3lPU3RualRINlVGZw?oc=5", "source": "CNBC TV18", "published": "2026-09-25 11:42", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPMGh4UXhKOTVzdW1BeE5LNGFFR2Jwbzd3T3ZvV0NTYU4wekJVZmE1U0FuZ3FsTXlTakZ1Y09lZTFJRXVIOVl2Z1R2ZmJsUUFHaEZXREJUZEtCdFNjWjRKWHhZWDNBMGpMOTJnZHhIa3ZLdHpvQ0tmMEdOTy1BN1hBcm5WcFZpYUdVZmdXZkVFYUkwdnA1VFhQWlNDc2xGNzY1eGlPdjhvZGR2MlRYbnVoTVFjakVVeTd5SWxEbnc2RjlxcHdkcTRYb2tDaXhocjVD0gHTAUFVX3lxTFBiSHlyQWowSl9jdW9fNEZsWnBKV0VjVkFTcV9kNkNoNDQxUHhiZHZiREtiMjkzMGplU19TNjNqVXlVTFRTd1kzeTBwSlFCS2VDdEt2VmlOb1ZvY3ZhMW11aFZWd3Y0bWxUWUQ5WmhGN21xeE9XcnNHWUpvQ05iRER2R1NoaXIwMDJ2dm84a2NpRzRVZ1N5NWk4Tk9XOGxKb0R3aHZlNFdfTzU2MFBMQjBBeEFVSUV5cDQ5eTVWSWgwRGY2dGs3X1BoWDdQQWRhUzJiRXM?oc=5", "source": "Rediff", "published": "2026-09-25 11:22", "score": 0.612, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPbUR3cDZZTmx0T0FjVGdkU0ZOV21PRUFzdFNkR1FaT2hqcFQyZkVxS0ZKSVEydXF6OGlMbnUtakExc2NhTGI0WkE3NXVYYlpnR1NBV2l5SUxWUFhXX0VtemF1WG1pdUU3TnoyLVJCb3ZxM2ZrdjUzRW1wZFJ3M01WQmtaYnFWbUZxR1NGQ2Fwd2dJRTM1QndDMnlobXFVbjAtUnVscXUyZUtyMVZIaEdmSE9MQlFSTkpkYXhvQlBicjJTRjJ6V2VIRnM4RFNCSDNWVmFudGZNTQ?oc=5", "source": "Equitymaster", "published": "2026-09-25 11:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rebound on Value Buying After Sharp Losses", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSjR4N2QtaTVfdUc1bkpKY0JWcFZ6RzdlM21SN2M0eXNfT2hQVWt1eXZxYmlmUFVBSGhRdmxTalRGYlIyV3J2M2lmZk05WUpVcDQ3bk1IeFh5aTN5Mm1nVXFZOUJCenlPRzR6VVAtaW0zcjZMQno2QTh0MklYUFhvZW1Pa1JvRDNCS2JIa3U5Qk1SMjJRTm5zZjE4NGFIVlVFOHpwVWJHTlBtaGfSAbABQVVfeXFMTzMwT3V5UkdaUUpqeTRFOHBwOXhrSFdVNjV6QXlZc1lzN1AwUzU0RFNxYl9aWGdQSS10S1d4dnRZNlhQNjZzMW1hTmhBaFoxMmFIaWNIdjdDblFCanNIUjJXMHR2SEJyUnVUb1J4X2ZoS2FVLWh4N0tnZGJ0RGc4aXpPNnQxLXFrR3J1Z3FGczZjM181U3FTbnVySUducS1VNGUyaVByUVNyanFPdHRHSVQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-25 10:48", "score": 0.318, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxPQUxBSWtnLWFqMkRfMks5NTlUcF9sTm1lNEtSdFZDaEstMWw3ejZUX2czMHFwS3k5MEFOWHNBb2w5VElVd011VTdpZ3V4OE94Q3ZGUVhJYTJhXzlKQnRicGVnc25ZNDZDdzhmN09xTzJCNDhLM0JQOHdRZlFKTXlXLQ?oc=5", "source": "INDmoney", "published": "2026-09-25 10:31", "score": 0.572, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Sah Polymers Share Price", "link": "https://news.google.com/rss/articles/CBMia0FVX3lxTFAxM1NrSlNad3RNSzJKUGVISVgtY1lGZ3NYN3FyNTBJb0FBYlNGQjVCSTRBWXE0c1dHR1lvemdIOFFwLUQ4czVFaGplWHRnbWR4Wkc2N1pkTUlfQ29mQkFNdU9DZkg2akQ2LVRF?oc=5", "source": "upstox.com", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "Nifty Chemicals (NFTCHEMIC) Share Price", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYURIakNOVnRybktpTUJSR0ZBR1Vla0tUNHQzQmY4clE5d0o4Q1pZM3BtaGhTcjk4UWtuR2tXbmJ1S3kxOGZ4SVhYSURHRkRCN3NwUUxzaDJ0dUZZWWZ0aWhlQkZtclZ6U0hIbTNJTlpNQk9Sblp6WW1WUTVyb3ZRRHJlV1BoUUE?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.402, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today", "link": "https://news.google.com/rss/articles/CBMilgFBVV95cUxOSmhSUlhBeGVjR0VmV1paYzdJdDlLd045M2hLX1dPc0NQdkJXUmR5dUNCNGNYeGxBNnlrTVNtMkQya1JiamhQQTNfbU8zdmxndzB4TWlmSndSdmpzZ3RGU0VickFfeDg2U0x0ZmFkMWtxMndNU3FkdmMyTTE3R20wdnNpdUJoN1RNdlFKbXJHNXlqMU9KUUE?oc=5", "source": "Univest", "published": "2026-09-25 06:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNU2lpQ2pNTWhOZFRyMzhsc25Pd1Z2VjI5SkFZa2d3VDhmQVNmT2JuNjBoNWczYU5QaDZZLVhRdVc5WkNZR3RzcGhTN3JpdEJRcWllYlNWQjd3aDBwM0Z3RnNVeG45SUllbmQzX3RtTlZVVmFyRllRTHZwcmZVcFpybi16QVlYeEZoU1Q4Z3o4ZXMxekZ4UWdWYjV1b1Njc3g0dVJlVk5sbEFmRkp5VFNvb1BXeU40RFhHZV9jOXdhU2tIeXV1Sk5mYTdUaHVRamxZTHlqbkwtLVA4MW93SDVJbk5HT0hrbVYwdEZJQVJfSDJSanFzQl9lZtIB_gFBVV95cUxQZ3hlSUszOFFSZW8zSkdBSm0wY3ZNblIxRS1HRnBLVG91VVZ4blFjb2xzakhtMjNBblRzU09WR2NZeWdGT0x3ZHBiSkNKNkJoTmFGanNzX3owUE5sb0szNFhhVEpjV1I3NVFKMGU4VnRCTFBON0doMmhmUUtnZDVYTWpiNV9CZWdkZnlEWXdZVlpBRFRCdUNLVU4xQjJ2dHdJM21Va21pbGppWDBGUkpYbi1VTjVVTEEwM0Jza3ZzbEFHQnFybUJJTUVTc3lsbVNVbF93VzdqV3BWdHR6THZEYXpBeGRZbHZ5Z1hUOUFWeDVJWTRFS3htSFB0N2Jadw?oc=5", "source": "Business Standard", "published": "2026-09-25 06:34", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxQTE9BdERYOTF4QjNsVFdOSUVsVjdickVLMkJHYld6YmRCdm5PRGloTnh2OHk5VmRRQjJiTDMyTUZNalZMQXk5eGt2OHd6RmllbVhWbUpEQjhnOVJvbmtVU2w2aEs1cTd4WWljRTkyc2dmT01xZVRnb3k2TGlvS0lCT3NVcS1yclo1TERWQWszM2l1dzhDdnBoSUpOVTRQNW10RFd6ODFidlM5QWttRnkyX1RWaWhWS3RzWURldTM4MDctTWR3d2ZWSWh1a2FJX29lV3Z5NnkxWUhVYzRzZmw3NGI0V1Q0R1o3TTVVZUl3REw4TFBtNTdUZVA3Q1VxanRQYVF5Yk8xc0g1YkVUZm1mTzFR0gGXAkFVX3lxTE9HLTI5ZmFma1R5UUFlREE1U052c1BXWndUTkY4ZlpnQi1hVGs0MFNNTS1SZU1qeUM3cXduelRYbzM2WENOQXNDVUprdkVfYnJDbE90cE9CQXZ6bUJEZkkxdE9wbW52akpFZTZwWGtQaTFQei14d2hFLWJMT2VpOVotMloyZ0U1UFFLeWZNZ3NzYVozQ0lwbE50S2pJN0REOVpaNWZXX0ZOTFVmZWVkbDI2RFA0OFRtUFZxc2ZEeF83emxxMHN2LVk2M2tNNUpmemRCR2lXeUtwYlVPdHFzNGh6Z1RJVmV2aUgtVkFzajM3R2VtOU9qNlAwY29sN09XSDRRR0FXTF9zVV8tNkY5YVpPbVYyb01icw?oc=5", "source": "Livemint", "published": "2026-09-25 05:52", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE shares dip on day 2 of listing, brokerages back long-term growth story", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNVmN3NGUwRl9DSWI4bV9GWXNDZk5fRV83NEJWVDc3RGVNQkh5ZWktVjdJRnJZcE9aZUxUQ3dyZWZodFFiZzljZmppdTJ1R0lPNUtPTjdLSVdfUXJ6VmNyN1FWVElaV094SGFJMlNOU2drVGlFdUlPSGpld1g4VGpoa0QyS21vUTE5QWViVl9ETWtJdHpKbDNvek9wOHZnR0ZRQTNvNGdPSmVaV1BvRmMyQmtPSWZpZmFwYklWOGpkS2dKdF9DUDg0LUU1QzZDUkhLNHdNR0RRd9IB3AFBVV95cUxPdk8wd0R3RW9FSW1lamlhT2tiT0phLWRyT0R5bDhEUVU2aVRjNVZwMGo0SHlfZVotNHZoTGxCR2ctcGxWNml2UWZCZ1FGOEJZNDRFNElqSUtKY3I4NjUyR1RsTEpZbWI2YkNudU9GRXJURUFfRjZfSlh3VHpsaWJ0VEhRdGhhcHVMVjMxMkg0Q3pEMWY1N0thZm5KTnRINTNwWE54NWNUc1REZFhzN0JCZnVxc0J0RndhMFZxTUJlOFZ0XzhnLUpGWDR2Y3Ftd2dwb2hRalRKSk1lS3M0?oc=5", "source": "Business Standard", "published": "2026-09-25 05:32", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNS2ZIYlJtSTJ2R0tUd041X2M0a2gyT0hxbktRNi1YSFpNcXlUZlBwcW9FMGl0RkRoUXJpLXFSYmI1SUlJTkFBNTl0dlExYi1LWm0xX1hUVVFqVjhxWlJwd1Mwb29fX1U0VVFhRE01d3IxSTNpNkkzQWY2TkpJSVVKLWtlM1dFWkFnaEFuZ2hCT2RYWktac2dQLUVmemdKeHlMMHYwbEtfaEI2d2w0MEdYVGx4T2R1ZktDV1RWQ2ZfUFBDZGRTWVdmSF92OS1kTnFNUTBXeHlZd3ctMF9wMk9lNHRoVEJTUTVYSV9rR0FvdG5jZVIxdzBJdnNSS1VzbXll0gGGAkFVX3lxTFBZX2J6TDljZ3haMlBoSFNpQWJ3XzE1aVhVTXVUNUkyYUZLY2N5Z1VuV19hbzZNNDhsb2RlTjZWRmpObFNlVFR1RmtRcVM3bXZGODZXUnhJcC11VXVDM2pKWVNfdXRjaENBQUZiRjZwZmZ2SmRmRTE1Nmxac1I4RlVla0U0LVdlNGdKS2RxOHhfRUFTaUtlcDNLTFVjY2JyZzBSWFEwVXR1R25rMjZmRldrRldOazUwRmRjTmhpVUl6Q1ViWFo4bS1GaEpuWkhUelYyd0ZBOGdIM0Fxa0p0U29jZEpnR1NWcGx6TEl6ckt5NUNhS0lTVU1QR043dEZvbC0zNmpHNmc?oc=5", "source": "The Times of India", "published": "2026-09-25 03:51", "score": -0.494, "label": "Negative"}, {"symbol": "LAURUSLABS", "title": "Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSUFqNDJicXN5c19sQXd2WXNJb1BWb2UtNUpOZTI3d2JudFdlNkZmTzVQUzFKM3VXTHJlZGZKUlhCZTR6MUZob0p6Y0hERlZkcDBzYmp6OGJaMTBKRFcySjNlblpkZXNabW1kZFZLRzdkT2N2Wnl0TWtJcU54Skk2MTJMUTVFQmJnbXlzeE9jSDgxRlhQaUd1X0xibGxDWks3Y01hZkViMTdVNVJYZ3RJald5TGVvUW5sMkV2M2dxbXBiWUNDT2ZXV0xONFBVa1lPOWN0aW1ZY3JVZ9IB3wFBVV95cUxQOGJWak1PMG9YdEpvYzc3S1VhNXI1bDBheUl0TVdJMTBCdmJoM2M5NUFhQzdYb0VFM2dsRmZLOER4U3k1eFUwQmg2QTdlRGNYZ3Fod1F3RW52bWVGUU02NlpaUkVhWTBXUXd3SERZblFDR2JVR3ZZZ1FkcTVTcGU2ZWZQUEVaWlFTMmJRWDR5WHVoYWtQejV5YjRjNXQtSHBKOFdaM1Y0UVBTNTZENWU1elFHYTZmVkUzSFkwUkM2TGw4Sno0SU00WXNUMjZUenpEMXdqQ3AxdmFOeE9HNnI4?oc=5", "source": "ET Now", "published": "2026-09-25 02:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...", "link": "https://news.google.com/rss/articles/CBMiqAJBVV95cUxOQ0Z0MUFZM2ViTTdHaHJ5akJLdkNEbEVZeFFsZ25KVmN6UTE1X2xMTmtUckhBOUdZeE5OOHY5blA4WDhVZDVJbjZCeUJVWE5meUM0aWhoY01DRnRBRHJaVURNTWg2SVRPVkJhUjVUb3dkRDVQZ1B5ZzRhS1ZyUVA1NnNXOEJqbWh0TG5EWHAxZXIzcU5nYnIzQ2xZU2RWaHR1dE5KTE1sMUpTQUthdmdLbGpjcXZvY1JsWXNzcHp0b1F3c1I3ZHpmUTdqMUpmbTV3M0JNM3AzWDZETUFsOFpURk9oQlY3UXB2Rjh6cjNobFhYOTI4MXRUN3YxVXYwaXJnTklxOGU3NXNHSjl6c3RndGt4TmluUUROMVhIZ0pWc3hia3F6blRJSNIBrgJBVV95cUxOdWNfS1N2QVhiREVSTXpDajYwUE9RM1VycGxPNmRKaHU2N3N4Y2tiX2tKSlU1NEpYR0Y5Q2xOMFFhV0VRRE83WmNDUXFvUU5LNXFITElxRmNJSEFJT3dDcGNwT3Q5UHYzaFB4NHg4NlpKUXo3bGtOV1lPRllGMXUxdC13N2RoTl85V01LU3o3Yk5Oa2hzWVZxdGoweFJySlZDVXFPY3NFcXJwV0tpdkxOZDhhRXRpU3ZhOEZCMEZ5QWlBUnczdTRuMUxCcXdwb1Vtd3JWS1Q0aUxpbzhhLXh2bmRtZ05Cc2VyVWM2YjVJTzRXd18yNndmaklMQWdsWlEtdEkybzlJRng2WndzbnJWUGF2S0RBNnE2MlRCb1FGSVktd0g2TEdPdGEwMDRYZw?oc=5", "source": "Moneycontrol.com", "published": "2026-09-25 02:06", "score": 0.178, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Bond Yields To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On September 25", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxOdVk2NWY2YmFvVWRzUDF4anpscG54WjM1SVVVVldRT244LTh1aXVWbXFCWnQyQVZnbmQycU41N3JiV3p5ZTF6VlZMSUI3NUQtR0tsVDF6cS0zdjZiQ3lCM0VhTXFoSEt4aEh2YVF2cXFxY2ZfMkVZSjhuNDZyODRGQUNYRXNpeWdEZzRjd2ZaeThvb3BxdmpBdU1jZVhNWHAyUzR0eGhtTzRHYTVkdTdvYWhRcWhldEkxV3Z2bnZ2SjhqNVYzMWR4MTcxdWc4X0FkNzdjb1VhYUFFNFNOTnVMeGFtUkF5SC1ZRG4wM1Z3VUU1SE5ucnfSAf4BQVVfeXFMTzFDRFpfdFA3RTRhanpJaFljZTc3ams4V2FOMENpZWYtUC1uSEwtYWlNODhZSnhnVXBZUEc5REwtbjFDYkFtSjd3SlBwbHgzblJDQ2pyc2F2aHdwV1NnaTlxU2plcGhYNWg4cWZiZGNObUVPOENwTFRuS0dnbHdTbVNtQTZGUXlGTnVnaEhZYW0xVHhjVnpZdk1qMlQxWFNnRHM4NENlWDFtdFhQODYyNWFRb2haeThMUWdsZk55R1g4YzBWbkFGc2xvX0Q4REwxdHBjb2VidHFmMHNKRnZDXzBrQU5oZmJ5bVFuZ2dIVmhlMGJKNHhhQmFPdlNPVlE?oc=5", "source": "NDTV Profit", "published": "2026-09-25 01:28", "score": 0.807, "label": "Positive"}, {"symbol": "RRKABEL", "title": "R R Kabel executes BTA to acquire U M Cables business for \u20b977 crore", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxOekdBdkJnQy1zc05YRUg5aFF1a0lwT04xNl9vZlhFaUhGVE0yeENFRkdPYWp5eW5qNGJPQ1Z5M0tIQWJTMmVBZ2NIcG13ZTFtc3FJaE9hOG1SQVk2UENVdGNWTXktTE10MGNUVmpvNkxodGg4TS1KdHFlZGprNUpZMkRsS2x6OW1LcGtSVnJPQnFvNlpOaHZZbFlnSlZ0MGtEdjdSdzVvSQ?oc=5", "source": "scanx.trade", "published": "2026-09-24 16:21", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets", "link": "https://news.google.com/rss/articles/CBMi-wFBVV95cUxNNDY4RnFxUWdPN3hFd2xaaFZRMERxSGpxN2Z1ZjF1LWVVZXFDUnZlQzFhNDRUYkdVWW14NDRCdXZ2LUQ0YzZpNWVUQmxtTEtHV1UzaUw1eWtXYm53a2JYSzdFQ3Z0clktdUNZY2J2dE9MU2lxM012czJpUDR1R2ZkN2h3QXNIWGkwX3pEM0xNakt5RUt3Y3hrQTZPNW9yUVhDQnRCaUs5RHdjRVM5Z2RMTGc2cG10WS0ycnl6ejY3YWFsYkUyVzJBYVc2UXlvaVNpRkFKZkZmWkE2RzBxcWFMNElnR19nMFN6cmRzRDBteVpQMjlDVHlaVi1VONIBgAJBVV95cUxQbEJYN0g0YUZETXczaUtkbUdMb1c4M2lQaUszdUtyTXZxMVVYWENrRm10czlDRHQ0alpzSjBhRXMwVzVYUUo0djJYXzBQWlM4S3NZZXZtZTM4TS1zd3BVbEtHeExGNHVVcTI1eDN1VWZHTUQwRllLU0VTenctSGtMT09DTFpSSG00UF81R2ZsdGxFMFlGVFB5aTZLWGVvQ3RwWTVVWTV3Rjg0N1RKbTROQjdaVjR0RTRuRUVtLTFUTDgxdUVMOWVhOV81ZEhMbHlxVmh5Qk5NMXNCdXo3anhfSTY1SlNaSi1zSEtvemVYdjY4R2YteVlTRG1qX2wzQXFy?oc=5", "source": "Livemint", "published": "2026-09-24 16:04", "score": 0.7, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxORWVLSFhyVy1XclJaTW9wUmtOTF84WGZkclJHbmtIdW5oUXNJS2J2V2xqUjNnVmEzRDJJRko2Y1UzaVVuYnFOUlRyYTFzNFB1dTlvMXp0U3BTRS1rUV9pWXotZG5FX2xZVnI0eHRaWDhlLVZwaThPXzdCNW0tT2ZEMFp1b0FrRFVsNnZSVzVCTTd4MWZEUm9ERnJ5bTJNaGRIYlhYcmRGOE1ub1c0THBORGt4d2h6SnlBWUhFeVdSUDg?oc=5", "source": "scanx.trade", "published": "2026-09-24 14:42", "score": 0.382, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQnJ1UkZncDJJcTRVNElLd1ZKN1Nnd053YjRobGxJUEdGYUdWS0lvb0dHS2MtemJ3SUppQmZ2c0NERjFpa2szSjhMZG5BcGZiT3NNa191ZHEtaGRCNUYyU3FhMHBnXzFBUkk1d09ZNWFnNXJvZHR2VU5LTWkwMFlWU19xVnZkUkk2aFd1N1FBZm5xVVlEQmx6dVhDcG83MGZveUFrMm9pMWgydUlPMDFZOTB2RFBBT3JPdDRVYmdKTUtzbVBMTDFIbGlzdkhVMklTNi1aeVFHNjNBUU9RclRiSmtXVjRlakw2S2UzVlhlRTZvWWs2RFNoVG0wUkhrZw?oc=5", "source": "The Economic Times", "published": "2026-09-24 13:49", "score": -0.153, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxPSmdZMUhhTERFclM4bzZicU5pWTdPX3lDUFQ3NU5qcU5hNWVHU3Jrem1lS3FuYjhUcXBVOGJFLXVKc3hCSFlvZ0E4QzNJYjQtNGRHNldTU0pyWS00ci1qNUNTNFpXd2lJLTZnRnQzVGNraVBUUGNhSkJzWWRjVVNqWm9Qa004SHQ0bXIwUV9SNm4tLWxtUHl6eHFoZVpPUHQ3UXZxdUxZTHZrdnpYY3JrTHhFTUxuQ24wd1lBR092aDNFV0lPcXJWMkxITnFFZkdNTkJqRzZqeVFIZmYx?oc=5", "source": "Kalkine India", "published": "2026-09-24 13:15", "score": 0.318, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "3 Indian Export Stocks That Could Benefit From A Weaker Rupee", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQNUp4b2tjbFlmWklUVm5zT2NJRjVXMm53bE5DNjJvb2ZFd0tFZVRUWHVxbWozaEp4aVBQMGtxZkpfQ3FmYnZtbEppcGtXZ1hYYl9seFIwdlhpczRuUWg0dE05REgyUkRMdXJpaVZDc1BORHVteE1IcHptNnNRbkdTY0NEUTZKZk04cHEwWTlNTno4MjJKU05aVlVOZExfd3plejl1cUxiVXlVbVNibjctMlFyOWx3aEZmYk5VNElFYUM4WENySTZGcmFrWURmdElfRjhyTm4xelJnYWNjVGtmb1I2NmxXZnRPem56RDZ2b24xZ9IB9wFBVV95cUxNVGN5NWZ1TnFTNUt1elFVSE5Tam8xZi0zWVY4Um1SX3UyVE5xNDZPZmpWQ2VWXzBsaW1vcnVzX1NoZXk0aWJjeU5iaXpiT1dTejAwSUt6Z3FhTThnTlhsa1ZFdHpfTG1sNjIzQ3pkZ0duUXY5N3ZqZU1qckxKVlZneVRJVmxjU1VrckJtQWlBNWRsNGdZbnRxX253TU56dE9NdXA0RlRoR0dLS0VDWFQ3VXJILUlrcF9OTU1lVk1sODFsbmVIeG1ROEFLcUlhWmswVzVkUjgwRW85cUNQUXpOcS1VZnBLT2pMSlZ1c3lGQ3MyN0JKeGlB?oc=5", "source": "simplywall.st", "published": "2026-09-24 13:01", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPTmEwdzJWdUtmS1lTeHJNaEFsLUVRRTNTSU0yMko0SUJCczVmU05rb2tDckFtclNUdEJzbmN4VUw0TUY0aWwtVVlEM19wTF9BZ0xyZmw4Z0ZTam4wMmphemF0SjRoWWZTaXZOOGJES2dTWWc4MXU2djFTZFQ2ZmtnTGgtNFBvMlpVbFJUeGVCQ242RGpic3ViMFl5QmlzbE9ZMFBIQktpRXRkSWhmWVh1WWJYZjRYQ3FkcEJtOTVNUmZseW02bXQ2cDlheEVZWnItWGFrOU5aTmdDVFQ5UDJMUEI5Y2VSREJGSmRGdFY1UGY0cUJTR0FFUDNSc014endZb3U2TUN0dFdXQdIBjwJBVV95cUxPX2xOWkM1Q0VWS2w1cGpsMXpBUFVpZHZOQ05TMTBkY3BMRHUzcjVIeEdpRHBhYXhKNXUxSzRjZkI1RHpXbkRQdlpBUkdPS0JIVG5jcjQ4cGxZUnZndUIwX1VMVWlwU2c3dUZTNHR4VjZrUzg2VXd6UHFaYzdTV2xMRXQyWmFQcFdIMEJUN2pqcFliNW1tRHU2a1VNNnUwekE5ZWRTYTF6Sy1FbnBhNEQ1Zkh3Uno3QTZuTXVRcHVlNm1LVE5oVEJHLWRiMWFUeEo2ams0QU1ocjRRREF3Vkd0dXQ3ZC14cWNLNE5oM3lPMXNKelVjbmxuQjA0dURockhtcDBQS2gweGZ5NERLYVRB?oc=5", "source": "Livemint", "published": "2026-09-24 12:36", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see worst day in weeks: Why was market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNTTMxLVltQWc5MkFQOUFYNlpYUTlLRnVtOWFTM19ETVhBaDduYk9pa3VKY2lIdGNGTkpIbVVKaDNkV2Z1NlBvdUVVeC1JbTNJem02eHlvdHRvMFFkR285ZjlFWk1fbXR2Z29HSnNVVklmYnhpOVlHdUFxeUFuNmtXeTZFY21KcGFraFdXRVBfNWZRLUU3WEhhd0x5OGxkRlRCbXR5T21JNDRpWE8tSU81VGtxUXFqUzl5T2FrS1dXd0s2QkdoTkRlSWJFR2lORk1JOWpnWHhvanB4bEdTaS1aZG1sbTJfUDFManBUNNIB8gFBVV95cUxQaVFGYUROS1ExTmNWWWI1RHNoTGZfWDd4U0hPeGVCdzM4eUtkZXVMaGZSTXp3NDZEcS1POXpFa01KQlNtY3U5QWgtdl9VV2hZY2VzZGp2U1pQbE5sT1JoQkZJeFFqT3VMOENGMjFXM3dRajdZdTVJMVpIWVVubzJhbjNyakljV1BrTl9vVDh1Nnhnd3VqdDJBbThXVDY5ZjBIZXFKZ0ZHUkt6eF81SHJEbEF0YkJnVDQ4clNuSFJONkZRRTkwZWxLaS1QcEVwVmRqQURkTlpSTm14R2Z4bDV0NEhMMzVJdWZ1TzhaRUlweVQ0UQ?oc=5", "source": "hindustantimes.com", "published": "2026-09-24 10:57", "score": -0.34, "label": "Negative"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNb1U1UU5HdEFtaWZCRWdVRWxUc2pRMFZ2YXl2bUpYNE1xNzZBX01tTXNtQWc5d2ZCNTdzYUZwXzU5U2VOX19rRndvYkVDaUl3aGVqQ3lyU01qYkNtVENjRG41VW9IenA4V21EcDhLYWFrdHZPYU9yNGl2RDFSUEdRcEtObWtDS0doZlo1V3ZwOGcwcmRROTcweDNZeTZaRGdQZ084YzU0amppMUZaZERQamg3YUE3RF84TjFuLWx6T28?oc=5", "source": "Kalkine India", "published": "2026-09-24 10:15", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVTh5Q2ROa0YzRWp5NS1Kamp3NnMzYnBNRlJHcEZ1cVRnOG1aampUb2pFbERqcGNPZjN2WGZqNGd5dWNDN2R3bnhXQ016bjJoUXUxN2FqcVYxaDFrSTlwZGpSQmZIbGM3THdoMUFDX1hwZXo1OHNPTjVpNFhLWVZudVFHU2xxbmZ1aUFnWXZqM09tZzZ0TVlRWUwxakpaM3JIUkg4QlBBaG40QUQzTWxYYzNSZi1uVVZtWTJHVU1UQzhDWHB5OW9Fb2JHS3ExdVR3dExkMGJRRVRQVmZfZnM1THUyOTdWbWhDaWfSAe8BQVVfeXFMTUFnaWZmYkVLMzZkNk5ZRXF1ZF82LXluT0hoSlJNZ19kUVk4VHlzLXhabENVbTd5LThnUlJIc215aVY1T2ZwOThSS0dVNnJNTVBIdjgyQlBPQjJaTF9sQnZWeEw3Z3dVdFVMNnU4ZzBWOENQQ0dtZ1JQal84UmdMS3FvdEFJUFdMbVhXQm5tM3JYNUJhYTFFRnFtX2VIaDJMcWNPUFhpaUs1YjRSbG1lWWVTYng5VnNjbFF4Z3NqVWFHWEd3eEMxUjE5YUFQZ21qdVJJV240Q3dsYTdHQUhKTjVGcnk4UWRhd3lEdTJYeGs?oc=5", "source": "simplywall.st", "published": "2026-09-24 10:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "The battle between India\u2019s stock exchanges is heating up again", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQSllxZjNuQ0l0ZExkQlp2RmVURXBuMm5WRjUyUkZsOXNaeF90Zy1GWXMyZFAzYmlGMGFfTWlhSl9lT2JNMmVnclFGYlg3bjNZQTRUeERZRkFScXBYc0IxZnhEcUF4Q0tzcWhhQTZXaXR6NjA5Y1pTSWdDQXBPQS1HZWpMOWJHN0NzN0lLWkdiMlJWWjN3OC1Ha1VDQ1ViSE9QTmZmSHBYTVpFM1FiUEJtZ1B4Y01nd2dabTlwTw?oc=5", "source": "The Economist", "published": "2026-09-24 09:42", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPVWZGNDlpWFN6MFJFZVZMVWp4RnIxcTVXOTRMUS1oVnMyQkVmZkF4eDdQTGYxOXVKV253c2dWUVZrOFpQUEEzdUQ1Rm45bG1aX01RSzVBNjNIWEFIb0lLbFJsSWJNYzFzMVFaVFpXUnAtR2xtZEZ5YXhjdXRSOHI4ZkNVMlJvWUszcWJEdGFBWmpqZG9zaGJWRnZGMHFtM0J3OWluTEZMVE9xSkV0Q29QTnJFQzEza0ZQaERRWjNBaEN6QlpkSFdMcGRuWndIWE1RVU5uczhza2w2WndRYWlUVkg3Yi10bUJFLWRWTE1sT2I1NnhwVTdCa3ZBRmxpRklNbGtzbkQ3V1licnlmakQw0gGUAkFVX3lxTE5pNjM4R2ZHalBOWTl1aGVPaWxONlMyd2lmVERYa0RZeDlDMU1IbnZMWnhNQ2VuWXY2dGRTTlFrZVFrU3RmaUJtcjZxNnlVNXc0eU4wQjR5Z29zd2FWZVRoM2FVYl9BY0xldFp3SDNjYnNSdmRwdXFYTEpxcWM5WWFrbHZCeDhZZ1c4ODE2SWJpX1RvX0dkX1VHemI3dmpJem9uWWJsNU1Ia0JFWmxobTRWMjBFdktPS0dsZGhlVjdIaVh6dFRhU0FERjk4aE15ZmlNR19BbmlCei1FRHV2TXNwV1BJaVRHQmxSZnh5dGotNDRaUEpUZV9pMmR2STRRbkhLUHhPa2FMelZzX0VfdXJMOGVoeQ?oc=5", "source": "Livemint", "pub</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sZGhlVjdIaVh6dFRhU0FERjk4aE15ZmlNR19BbmlCei1FRHV2TXNwV1BJaVRHQmxSZnh5dGotNDRaUEpUZV9pMmR2STRRbkhLUHhPa2FMelZzX0VfdXJMOGVoeQ?oc=5", "source": "Livemint", "published": "2026-09-24 09:40", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZ3RITnlWRlVoLVRXRW9Pc1NnU042UFB5V1BVM0s0QkFvcnRjbElBRVd1ejJZQjdSTmNfM19uazFjYnZFbm9EMmhxVU0xYWtsd1dZNldfbEFJOE45dEVDMWw4TUVwSW5LdkVfSHZPVnZsRVI4eWhyVFpaQW1mRFM0UFUzZDhXaTB6anpwWDlSSk0yWjlpZ1Z4WEsxd3M3YklFREtEbi1TNXhEUmsxYUVyWXlPTHNxUXJVYUxpbV9ENkEtNURlYnlPcU5lTnBEbjRMVGE0SXdGRTd2VWvSAeABQVVfeXFMTVVqV1N6TXB3TXJhak1kUURlODRETFpFX1NBa1RRb1oyUlVNd0xRcXBHU2ozWVN4dlQ2N1Y2WUhpdTdZQk1NWWNYcDB4U2ZneFRVblBSajlpRmlzLXZWMTNCeHdIZG44a0ZMandxanFjTW5qTHpGM05QQ1Vxbnlsck51UjJhMkloS3dPaWstcTFoS3Q2NEQyRi0zQVhITkp3NzdWRnBkWG1vaVdWSll0SGlsdXRiaUxWc2FUVk9wMW1ZZ09tRlRCa3RoQjNONFhvQmdyN25tVWhBVTBEZmpuMnQ?oc=5", "source": "CNBC TV18", "published": "2026-09-24 09:08", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxNeEtEbWlBNTFIcHJzRV9zU0hnQUd4MVRma2VMWXpOdDl3SURrMGJPOXBnVnFOTm1MLVpMMFAzYUhUWDJVYnpYd1cyWG1xUjhxOVdkb0tVNkF2VnZfZktsRnRYTlNjMzBYblcyM0pHRUo4Ul8xVlFoci1JOXpSU2F2RlBkbFJaZGhTeE9yODV4aDlnSDdKbjd2c0ZKMzc0Y2JFbER0c2hDNW1pbURITlcw0gG3AUFVX3lxTE8xbVZoQm0xdm9CSmg5ZVBDMVluS0lTTUctTnpYYVU2S0RxcFhlaUY5Qndta09tY3VuZWI3MW1LRWlPNVl6QlY4OVBFcENPZEY4OU9jMThxdzM1cG56U1ZtN29HNGEtZmZ6eklRSXlNNERlUVF0dXNjVXV0dERKeFpyeHY4YUV3ZXdWYWhjcWsxM1d4TWtYOE1tUjRFQ0xKQm5aWHJhcnJfSHFha1FDeUJpSDdJaWhrNA?oc=5", "source": "NDTV", "published": "2026-09-24 09:02", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxNT1lNOEhqOHFBM0dUS21nbjEzUDVTOVY0YnkweVp1T1pQdy0zTG9LUmppQkhYTGtIZXBSTEtiVHdDNjZxWm5FM1VXYUl5Mk9WcklBS1p0NWlKY1FUWDNqUnlYcDRrTzI2dms1NVNjenlmQkJZdlIyQllHaEF5VVU5OWE1OFgzeE5jaVdSR0ZfNklZOGpsMGRyc3NXcEdsdFVGRl80QXRsZUhkSDVWbXN0TlRKNjJXSkRSc05IQnczMlpyYXJwYnV3NERXY3BQRjdJN0h6REx4LVo3S1dLQjNRQlpNOU9zX0RLaUlxNXUzRzFmTEdGakNJTHotX2cwX0hyb3lMVEZmR0PSAY4CQVVfeXFMTWdFZHhRbFpBMnQtazZaZUpQVk9Ramd2ajI4M296WDFaazhGZG1OV1RmeGRqcDJkeTNsWC1TYXNTbWtJa1RGRktmREpwbkpqNFYzUlFIYkR3ODg3RllZQTNWZ2h1ZzBLUlU0WXpYV2ZlQnN5WE9pN2JCV2sxbEZMdjcwQXcxRGE2c0lLSWdLVHJVYTRuX2gyYnV6MFlPZDhMUmpzVHpUUWk4WmJYNWtsMnRZSTdmNzBzdnhGRzNRUnN4aTdrakZ5QlJ0aHJsaGRGQlk5NFllakp1bHByRFpMbU05S2tqWFExY3lQYkVlUjlyX3hTUXpmRFQtVmdocWFJMG1aQ29LTHNvb200Rlh3?oc=5", "source": "The Times of India", "published": "2026-09-24 08:52", "score": -0.402, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "Hero Motors Ltd leads gainers in 'B' group", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQSDJtZTVDOFZES0ZIb3BKUnlmdkV5VTlSc2doTWJUZ1k3WEhzVDNxd0doUHI2aFBOUG9FRW1hbUw2bTBKb3FxYlNxZS1kM2VvaWtpcnp4ZEJpa1AxQ04yN3QySVkwS1dUZ3YzVUo3UVlIdzV2eE41ZUdJOWs4cTMtS2ZQNWdySzltWE5CVVFQZTZLdVZCaHVxTDVYTkJKLTE4ZWQ2SlpuVVAxNFFSVVJKYzlhT1FxMnYxZ0dKUDUwNNIBxAFBVV95cUxQS1NzWTc3QXZDVEZ2M1JsYlh1RFVzUjdVdHVWdVFrcWMyRS1zdVRJajBxXzdvSnVzWlZCQXRNbDJyenM5SDJwUnRMcW5BR3ZCMnlKbUY0dTdiVXZMalpuT1lsOHJoaFZtYkhkY2lIbVVXOVJ2MkRoRE1pa21xNU1LWUtYOGpEaVE4VFhqdElqLXVRZ1Q5SHNLVGJfN2VPNUtLT2F1ZnhMUU1hMjNXSTh1dzVZS1d2VE1fQ25BcmZEcVhTVGxf?oc=5", "source": "Business Standard", "published": "2026-09-24 08:46", "score": 0.557, "label": "Positive"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems Share Price today: decline and analysis", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxQcUhUNEJMQ3ZXeU5ZcFk0aUE1NndmWmVMR2E0MVJuM2RhTi1QRHhxT1lZRTZKeXp3NEkwak4yQ1RPVDBDRDlXUlJVUXQ1QjVIMURYTEtsZ2lXVW52SmR2VzZRS3FHanh2RklUTlNTWElScmtkaTdGMGx0SWIxdlF0YjlzVTZzQQ?oc=5", "source": "Univest", "published": "2026-09-24 08:35", "score": -0.382, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNYTRVYTVWR1lSdF95cG9QR1FLMk9SOTlCWVg0NzdVR21OeTdQQXJYc2UxbkUxa2I2blpPOVRYSmVCcWNaQnVxSnpvX0RGQnhZdmp6X1JXRGxXaVk0dXZnRDV0ZTJmdFNMTzUySWNXUjZ0OWN6Y2hwcHY2cWRxLS1hZVRpdHpISHpjMnl6b0s1M1J1bHR6LWNTd1otbHEzM0ZRV2RHeUNEdmY3X2t6ZnF3YkNyRHREUDA?oc=5", "source": "scanx.trade", "published": "2026-09-24 08:21", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices", "link": "https://news.google.com/rss/articles/CBMi6wFBVV95cUxNcnpYS1l4a05TYTZaQUM2enZTYmIxVThMMmd0UzZaSEczczdQSXhEU0tSSV9DdXFXdXE3SUNBem5BRV9BMUFlZF80U24xWHh1ZHM1SkRjU1p2a2NvM2NuRjdMQUswaWJkZUV6dVp1ZzVrZC1jZUdkX09JaWRSNWFOcEdOc1JFUVNRcEdfVXdYMVF4MHpnTl9zRDhLQWY2NVllQzkyMXN1Y0YzQzdSUTFoUC1nanVwcEhzNnc1NDNtbVZOSFhDVVpUM0F0ZG1VemZSZkF3eU5FSldzSEFLZGRBell3ZVA2Y01JWVhv0gHwAUFVX3lxTE1XVE1JUmZXOUd6YURZeGlua2c3dEZoZ3NQdWY4SnB2RFVOa0dnd012UlV5Mm16QmE1c1c1SHppQ2luZHZqU3lfb2llTkxTQmN3MUlpejNJOVVYb3BCaUQxZ1RSWEZBWWFwdjVlN2ZTZWVyTGZhdjVfWkNtUG50SkNhS3hNRFlFbHBhMG5DMjZXS1FGVWJnMmUtVzJueHhRa1IxdnZpaGVuU3ZJYmhUVXFGUWFNVW52ZGxYODBxWFVzMmRnNl9PMW53dGJ0Qi1EZmRaUGhzc0FLZWxnejdscjFjRDdUM0UtRWNpa1d5bm5JOA?oc=5", "source": "theweek.in", "published": "2026-09-24 07:35", "score": 0.077, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom \u2014 Ask Profit", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxPcjBhRnpQaFhkbGdfV3E0ZHlmUjFPQUlUQm9LTFU4UnFqSHduWnhNSEcwenhUQmM5LUxsdFNwUXN1S3gxZW9PN213QUx2TDhzUWpoNXJldnBQRmI4eTBIOE9JMGdqd3I3T2F1QVVYcVZSUF9jOEt6cnB3QWhmZ3F3Z202eHZkRXM4NHduSVVzLThxbTQ0aUJEeEJlTThhWHBFMkJ2OGJ5X0FXT3ZyWFR3MGlZeWEzWjJGU0hhejlZTFgxakpDdVVtbkV2VGJtOXU3aTh4Z0lPdmtneU5EQTNudGd30gHqAUFVX3lxTE5SeDJuQlhJbTcxaDUzbWNPNjNuZDFqLTNYYmEwR0o1QW43WVdkLW9FQUhpVExqaFluQjJwYWRVcG5NcE1ELTduTUxUVTJzQjhvVlN5YWJKa1AxaEFjYnIxempBeUNFbG1IeW94YVMwanoxOHAzNHlRSnFUbWJ3anJqQWVvb2xQeVRwZl9CQUwyUl9KSXhhTm16Qy00Uk5JdkhGU2Z5SGRzNkthQmRBN0J5WnE5bFNUREhuNC02SklqM01odWNqWjV1YTVsVUhXUUZMdlhkN09kWTdvbHhZUjFXV05sVTlGQkptQQ?oc=5", "source": "NDTV Profit", "published": "2026-09-24 07:25", "score": 0.296, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxOU0F5bUI3X2RaNWllcFpuSUpqZFp4Ui0xRVNpb2FSbVRfMjZieWxhWGV5R2N5MHpqeHBQcXIzT2dfTHBjZUt4Zk5aV2Y2SDNhM3VjamJBeTRhUjNjVklyZ3lWZDMxZ3hMMjNXaHFHWUFKV19ZaEp1WTBQekRXOU5ZdXc5UG1hQkIxRTJWdU9USDZqekc5QTh5VENqRW1ybVVCYUMwODlQRGJGVUZKV28tSVpXMFQ?oc=5", "source": "Kalkine India", "published": "2026-09-24 06:20", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'", "link": "https://news.google.com/rss/articles/CBMimwJBVV95cUxNblY5UUJKckZ0My1hbEZrdS1NbjFpR0Vyam1YUHcxd1BSMDdzWkpVZzVyN0ptcnZWZ0EwRElGTEdLV1pWNFd3a05HeEpBOC1UN0NCandyUjlzUVpsUXpKZElQajdHYUoyc2dvLXdMVkNQSW5lZHNFVG1aMzVJQ0tUcENOcmR3QWIyUFNWOFo1RENRX29SbEZLVmNGdVdjSVdkYVZyM1l6dUNtaE9KYjk1VmhIVTlWUlVZNUVFekwwRGZETkw1NTFzbWhSX2xVc2RTdzdCRExjMW5LZ05EbFZRODJvcXRnbmpKZGdPRGlpeGgza1BVNFA1V0xkR2ZJUEpCNWpPZnh5aXR2MW5aQ1EzTEJBdGY5Mi1UTkZF0gGgAkFVX3lxTE9GWEM2U2ttbzdkc05MdlJqN2tFU2pGUmxYbmVIeHktdHRhWVpuaWRnUE1RN01WREtsT2x1cTBBbExxTi1sRE93d3FvWDljRGJzWHNxMW9jek9KTklxUEdnbUk1a0t0YXdlMVZvbzc4Mnh0c3hUUXMzdV9VOWV3UXdqSnRQZFJNaVNRZ1RybmpKR19rS2dNdm5HVkNlUmRUTzJrbkRuYy1fR3pRLTFLUDBZcVAxMjRrdXg5ZVF2M2NDMjgwTXZ4bktqUXNidVU1dmJKWXEzUi1NLUwxUjliSG1vU2lQeWM2S1lRdkMxbW1qSGI4M1lpSHRVS1FVXzNja3B5Q3BYalFYLXV0T3d6VXlWVVdEWTdfUVRsWFV0RlVkdg?oc=5", "source": "The Economic Times", "published": "2026-09-24 04:09", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxNNmFnZnk5VzNtcVFkY1JFVlVCMFh6T3BlejFod0JXRWFjMng2alROdHU2YzRmcEVCV3VMZFdYM3hCbUFCa09PVmVkWTh1MWFaaUxhTndsdjlVb3pZZy1VZU1wWFl6WnNvUzUyZ243ZUQ2RUVIMEhVbm8tMWxWMzM0Y1N6aVlPenNvZkl5R0hmVG5JWlE2QkcxNlRDd0UwU2RSN3NscF9PR2NRVGVaRWYyVUpMeHFrYWNVcGdMNTM3MmpSVGdkc0laX1E5U2U4Q0pBM1N2cUNlQndvUGRvUHVhT2w3Qkh0UHZ4dkcwVTQwUkRMMHlY0gH6AUFVX3lxTE5jREhsTGtRRUVDMnRQMEhucHBndU15SnViUmVFb0ZxTUE1dmpUSlBMV01WYkZ6UXd4QkRncTdNZUh5VVRxNEQ1cmViQ2Z6WFViOVktS1hld09jM25FTHRYN0lJa3d2Q1NsWUxZR2VqUElmYXVFVk5wczFqMy13QUd4Ty1ER181WE5KaHE5SEhFdHZzTy15T0tnZ3pyZzhVMktvLUI2WDF2M3hTRThxVzZEeDRaU21jYUd4ZzZPbHlWRFVMN1lZVGRzcHd4bDUwTWc5d09MYks4c21iYlZKNUUyaC1GOXIzZ1ZzT3dXTWVaWm9KdVhHYzN4emc?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 03:56", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPRFR1dnlza0cxUU5PbXRVYmRRT19oaHZFS3NmTDZUdHhDUVpIaTJDVDFHYThvSXE3RzNWenBDSUlDUDVCdE51VkpDaXppUEl2M1htMGxsMkxPV3ZaS2d3YVhYVTlFUEphWm45cWVuYTZLYmJ2V0xwT2dtMFkwQXZ5bjVWOVh2UHczVnZUSFQ5NFBrUkJaQTJwRXFoSlY5ajhXaHJXOVd3enFaclR4QUpXODFjMWxjVVE?oc=5", "source": "Reuters", "published": "2026-09-24 02:46", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPUXhSRW9fbndZUTd4Q3FFZjhsaThCbS1jNzk4Z1N2TUdiU0lpcHNQcEZ0WmpqdGZHUUlIUUhNdlNseThhQ0hkVDVNazBSQTV1SmRVNTJ6SnUyVTBEQ3pfWTBubFpaREdzcjI0VTFacmFUZzI4ajJfZXZLcU0yQ05NcG9BN1ZkYWQ4M3pJVkFmRllNRXJXeU8zWXRMRkVoQ2o5aGJOamlGaXlfYll4WDBEdGdpY21SN1o4UENfRGNSZ1E5elpxVjJ1aGVWZ1BnZGpfUFMwM0VYM0t4eHpnM3BTTlBKaFZoQkFTT3M2bWhSNlExcEZkcmRUUHZMVmNzSzlPc2fSAYcCQVVfeXFMTnBRN0FXeEh4U2V5eEYydmZXb19IdldaZk5tYU8zbVV2TFV5ZjgxOGg5cGZfdHVScXprR3dCeEQ4czVEOF9zSWpoM3MzdWVrNFphaTdJZWg3SHVac0VnOVc0Si04cUdma2xrRFRLRlJSakp5N1FobmtwdUNqRVRFNWxsYnJrbVpjRHI2RTI5dmJ0Qml3eVBLa2NTXzNhUHZzckNXVHJxVGs1clVveXhUYlk1MjdQOTE3SDZTelVJb1JpSF9wWkpjMno4X0lDdkt2TzFIVE0zVEVRaUFxNG5IVFRhTGRwVURPZlBOcTZtUmlNTTJYS0gxU2RWTkh4T2RZOHB3SFQ4RHc?oc=5", "source": "Livemint", "published": "2026-09-24 02:44", "score": 0.758, "label": "Positive"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxOT0tVTzVLRFhsRHJ6QVB0WV85ZGh4RHFXTEdKY1R3Snp4T1VIcXVyQmNMOGpKeDF2aVdfckZKRGVqMzVpaDlTMDU0Q0lVemMzLUxFblYwQkIxcFFvalhLYng4bVdZbUhqTnFDSDFweU93akx6V3ViVXF5cEtCbk9QSFJQTjNobXRLQUpPTGNuSlc3UkVfNGdnQ0hWbXJldU11M3hadi1FU1o5azNRZ3pIUldvMkV3b1FQYVktMldOcWZkVFhPcHI2QUdMOXQxOEY1aGN6TG13WW1yMjlQWHNYd0p5LTFkRGZqOHhHNlJIcW9pWU1VQ1k0Yy01VDRPQdIBgwJBVV95cUxOdVk4MlI1LWY0aGw5azFlQ3UtdkF1V2lVYjJBaC1UYUtRNi1FT1lTeWpTbG1jZ2dPeGtBVnFYcTdISXFqaUxJcnpuZ29EWml0UkJEN0VfeHRONWRtcGo5dG9ZTDhOWGlvemZrUWZHRWtxUVBwcFRaRno4UmpWSDIwdHh6Si1LbFFDS1E3R3hvTTRGSFA4T256enl3RjBfb1hWNEFaTEkyOHJNRXBMVng1YnJMd01TMW51ZGhta1dRRmNnc3p4TC0xa2lsMDVOQ3VoZFZzUzRGV2IzYTVzajR1Mm11ZXZ6NkNfNjJjSG5iOVNmSkVXaWozaDNwaHVTNS1MNjRF?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 02:38", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields \u2014 Five Key Factors For Sensex, Nifty 50 On Sept 24", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxNMHRUa21iWVZtelA2Um13ZTJ6ZDhOSGNJMlcyandCLUFTT0w0V3R5eWd5SEdCZ1pyOEMwSlY3ak42dHRhUjdnREc5UzdaNmI3QnFkd2RsLUk0SmhaRGNqOS1QdWp0ZVdnOExERTduSHhXZlpFb2ZHaHVneDFmaGdpVTAwa3I4RWxTT3NxUHp5ekV2YTlVd3ltNS1FLTdKN19nUzBFaHB2a1Etd0xVb0NMVDJMaG5RcGlDMDhhLUJqOWFoTmFEdXFCbDZ0SlAwTmlheHZuWEZ5dGJJdW1LQ2dGeTVtNS15Z0tmR1B2YXZ0eDR6YlFBUFRIUlRVLTZ2ZTjSAYcCQVVfeXFMTVJoelZ4TXkyUmNUWkk2RThDUWRtT1RrS0dqQUtzTHJTM1RZX0w5ZHl3b0xicjN6Z1IxS2dQUV94YWdwRGpyME1rZmVaZnZ6SGE1bW5sUlM3N2ZBYl9lajJub1AwcjJLYUc1d3pHUG5HLWUtc1VFVlc3Z0FVNXI1anMwNzA5MkZvd1YzdTRUNHpRZTBBSWpqcm05bUp0ZmxNZklyNU9LS0l0NG9uSWZCRkhYenIzaktxa3Bic25SYzVfVVdPcko2ZG95YWhraURGZ212MDJBVHBCVWxXUWVQVzZZLTFIZmVGdkdsNHF3aTNOclNEMUEtSjNsUHFCZU5JSlA5bE1aZGs?oc=5", "source": "NDTV Profit", "published": "2026-09-24 01:42", "score": 0.844, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQTDl3ZlJyNW5xZXBBLUtBLXRfSU5kbEdSOXFWM3V2RU51eVdlanIzclZnczhweGRBR1lmWkVUNWI0SlBsbW5tWmd4SzBzNXA0Ty15d21DNVJkQ0piMXpzMDYxYkNndEtmV19UQnV6NVBKZlgzU1ltZEpEakJ5dVl3WU8xQS1DRVQxN0pxV1NuU19RaGZhTWNqSHFhRHFGUVROWDhEMkxhODZ2bmZFX1piMDl0ZzVJSVRhUU5KUC1pV0NCclR5dGxXXzR1VUNvbHMweU1xaHRIQWNIRG5HN1o4NWNlRlBlRjhRVFc2SElTNklUNEtMSXBZVmQ1YkxBOFg2eWtOOFZiMUTSAY4CQVVfeXFMTUdPNHFyRDVseGxVX1p5RDdOWFBabmJQdm1ZNmVZOVB0RGZMeERCSnFfZUMxV3FrMXBJT1liYmFZekEzWGR4cUs4eDlKOUhiNURta2xDLTM0dUFkRTJrOHNaa0djNnlJWFpQcE43OGt0SkFJNEgxSm9hd0puemtzNVgyX3dHdUtGa1VIRHJBdFllRUFmYlYwQ3Y4elV1djY2ZUo5R204dmZyZ3RwaGdZSHZrbERxQWZfRlhCUEhrZjdaelZGLXZmY2lTWm84ek9wWHYzdGRKQVFOR3pYWU94RUVERlBYOXFEeDJaUVI1and2N1hCenc4anc0NVVaRG50TF9Pa1o2di0xc3k3SDdn?oc=5", "source": "Livemint", "published": "2026-09-24 01:17", "score": 0.842, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs stock gains 1.37 percent as profit jumps 126 percent", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRGZMMkVQZFBodEJ4cHVqbng0YWJyNHJjbndja3pLdkJzamNORjlNUGNab3A1MDczV2piSTRpUG5yeklwV2ZvMWlFMGp2OVota2lsTHJoZlB6dG10UlBHeXRYNTk5NlRLVVduSzZJM0dLdFlTN2hkM29mWnhNU3lHVUlaTmlGQ25fUFo0dXhGT2cyNWlhQmllc3hiRFU3Z1RIN01VV0xHOFBTMUtoWUQxTDZUY2J0VTNxRXYyb2xhQ3c?oc=5", "source": "AD HOC NEWS", "published": "2026-09-23 22:57", "score": 0.791, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUE9BMFBTZkQ0bmQwWjZyUG4tSWp1VU1ERG50V2ptaVRoamFQX21HUDNBVmdwOG81TjVLeU1GSUZoNGIzUU5Vc0drSzhsMlZkOFl4MmstUEMyZWdYTTNING9fVnZrR0ZvS3VCYmJaVEk5aFdJRUJNWTZMMlV5Sy1iaU5ieC05WjZtaFJaQmMyaU5jTW9Oc1pmZHFsaUl3aVJ6TUJTR0s3SjYtdnE4c0NDejFJOFprT0Z0Zm1RTGFsTFlFVTVvUHo3d0lpZk16R1NmVGczYlUzZGNXb0Mwd3RQUmxKR0pRcklfUl9XRVNyMEZBZ1Fxa2FsSWtGSllrV2QwSmRSVnBOMmQ?oc=5", "source": "The Economic Times", "published": "2026-09-23 12:57", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxOUExzY0ZPTTBDblhZUWV1SjVUZWd0amE1STlQN1N6bm9VajdoT2NVb1ZvVjJrcHg2WTNBYlI1SGkwMlVOU3o4NDY2ZVpRMHRkRUhVUWVaS0N5QUdNbzRLa1I4UkRhNkVwOWpaVVNxOHhFV0NxZFhGOUx4anFCRDlDb0ptMHlzWFhvTmhMTEFvSk1ybFBSTzA1SG1KQnczZVdTX1NmUktxYURuVTBFbk0ydGhjNVBNN1d0Q1lUWkZlQVBJWWJLd0NhVml5amI0STBVcEs5WW4tN1pTajJSbU1wYm5ydUdIUjdvSW04MWVkdl85NmpZVmVVVFl1YmxZaWxBTVB5bkhUSFVaMXFu0gGSAkFVX3lxTE5LZmlZbUxuSjFGRzllWHk1R0RmZ0tla0huTUZYM25TUGxFMXpWLU5rTXc0WXdXM3lTWW1nYUNmNTI2elJWcEhZOTRhZ3A2X2JOUHZ1XzBuSmRRX2ZsNGZrQVBkVDlFSExzbHc3Z0VPYjRTekszODB5QndnS1Q3NmVvRmpfdmc4QzhRcGZScWlZZ01KUE1ZVWZmSFQ0UnpKVFllOFZxY3ZIME1LX2xaZ2o5bUxoYkR6Q0JQTlN0b3ZWU19IRHRCaTRmdFZLVXo1dG1oODdLOWJhSkQ4akVrODVaQTUxZnZtLWxUNDhyTGdxMDBkS3ExQXJwbnRPQlpxTFdReTZxNEtLWGRwNnIwTEhCcGc?oc=5", "source": "Livemint", "published": "2026-09-23 11:16", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPaHBTQzhTRUdZS2tNRmJlTDU1UXJ4bnYzUXZNY1RzZWhub0dSbFFIZDM3aGZCNFJ2V2F1QmJRX3lVelpSd2ZsTkZVTF9ncUZCZ1NYblZYUjBYNi13Z19fOVhDN19taGt4MGV1Q1NtWEY4U0lrdnVXaUtFQm9TZTFUMGlzNWdoTUdBYWZxOUtWcG1idGJwOE10NTloS1hrdV9HN3lhLXZXWUh3dzA2TVVLcHRuRFJDVXdmUC1nV084LTVEV2N4OFRVQjU1Smg4Q2ktSTBKWmRCRGtRdWdWOEc5UGh0YWpOTUlNWmVyV2l0RC10T3d1YndQalotU0NWWDBqTDhn?oc=5", "source": "Upstox", "published": "2026-09-23 10:15", "score": 0.612, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure Share Price Rises 2.68% Today", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNbjd5UVZ4d3N3ZUtybnEyZW1MZ1R4T0NrS1JsMEhETFc5d2tyclFHRnV4bzQ1RVQyUkZvNnIwOURYdjdBUzZldEpRN0FBV29YLVZOTjlFalZfemVpUzBVZ3BZSDJxSVFqSmdCMDVfNVNVXy1ZZVJpZUZORHdmNUFzazBrdGVsOGVPN1ZMRmdyQ0U1X3kzS1ZNZU1mQQ?oc=5", "source": "Univest", "published": "2026-09-23 10:02", "score": 0.34, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs Share Price: one-year high and valuation view", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYU9VS2psbTA2SEFlWWF6NVFFbVRManpTcU0wUjJIbWRQdEU2S1JUeWVXWVUtSW1RNGp3VmdEZjRGYkdVYmFtV2tZd1BQLWJfT2ZHYzhXcFhMTVgwaDlmNmZkOHhaY0JiOEVaQmZmTk5FS1luRmcxeE9ZbGV3VDlqOWR4VFhCZEE?oc=5", "source": "Univest", "published": "2026-09-23 09:19", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQa2ZFOFYwaEJuQTl6N3NjWFFvMWUyUGdxNXlZNFJHVWxtcFNEenVuTlNieHRNX3RpY0dfNnNCUk1hMU9Ndk5Sckl3TVg1Z2lJYnFORjgtY0UySTc0WW5qVmV0bU5hd0UzTVM3OVdKUFNUUHdzbEhaTTNERlV0WTdFWTBYSnpadUhucV9mejJxMnNlZ2V2UzJaOVY0dHdfNWtMVWN3U0tkVVFuSUVSMnV5NjhTUUE5a2Zrc2xieTVkZEphNmVqSEQ1MmRqMEFKM2xwU1FCVkxkZ0VsdFZYazRiMDhKcEhsejFNOXgtSGo0bFRJWThyZkZaXzJVQWpwbklBNno4NE1QSzRfT001NktmddIBlgJBVV95cUxOdy1fS2JiOHZGWTlaelh4ak5fQTR6TU9lek4tN0tIODhtWjRtRkJmS2hhZHVLTmpSMkQ2T0dXNnk1VFlTdFRjcmE1b1dCQWYtSnVQRFh0Z1hsUUljNkZVeF9GQ2pSZmplX082cHlVWEx2aVQ0dWpyZndmREdSOUJmcHBfczhYU0ZjUVVWYU96N1J0SENVQV8tR243REJnYzZwcnNzTlFnakJWcmV6eU9yTUs3NC1FWVpwRnFiZTRrUVVtM1UxQy01YnNsN1BweXNTbGpkb1l1UTNTRzNDUDEtWjBOeVJsa2QtejEtRElXcy1LNXc5bW5FY0Q4TGhXQXNWWlgxRjlXQlNEQ1R0V1B2OVZqWHluUQ?oc=5", "source": "The Times of India", "published": "2026-09-23 07:59", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks Share Price news: price rise and valuation", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNS3pobG5zQUpFLU53cFlCQWxZTFQ5S0E1dDNmbTU3V2daQUx1ZTMxMjctRHphNW5OSWVoYk9UY09CU2NxbF9GWjVCZDJzeF9OTXVTX3NUYVRjZ1U3ekZnLVFxZ01Sc3dVWlZIcnZOdXdvTzVlNTdoMlhYaVZZaWNaTEpZTkxpZw?oc=5", "source": "Univest", "published": "2026-09-23 07:26", "score": 0.0, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQThVQlhqMHhQX1dCbzk5aTVLRzAzLVhTQ0kzajBZMXRVTTNTazhRNTM3Y2d5SE1fbUhYVkJkT0hDeDlCZFhGRHEtWUxEcEhISzA4bkNGUlQ2RW44NEdPa1k5VFF5MGktRHhhZHJMRjAyeUVCVmEwWkVIQ2ROQmlhdTZTY255RFg2Rkp4NWtCTk1vaGxrUFc1VTRFSkJFY1Nnakd4VXpMNGxRVkpvMkl5VnpmakQtMWgwcV90RFpwM3BwaFFfNzhsR3IzQWhRNmpCWVVjdVM1ZExSSkxZR1N1bEpNaUp0eGV5bGIyTDQzZTZjdw?oc=5", "source": "The Economic Times", "published": "2026-09-23 06:24", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPa2tacGJLRFdET1pPVlhxQlRodHp4ZVZkREJLUU8yQlFiSmdib0hReElVbW5Qc2QtMnFqZWVDREFveHlPbDB5MHhGQjlBcTVfMS12Q1hyNGRFUjZrOHY0Ym9jSGhaSnV4YlZYZDZGV25jb1NtRV9admFLQWN1N1NETF9pUU1GbFFadFVXdzJ0dUxJelU3SFlaQUR0MlZxTWxHaDQ2SnpjRl9LczRSQ1BiX2h6SWl3ckJiek5mSDVwNm84cVVBYnRCSnFPYWRHLUlhUUlwb2cyN0tGdHRGU2lNdnVkdlNQZGJS0gHuAUFVX3lxTFBtQmV3OHlXVURIb1VpaGFmZnYtYjJnSFVyVjEtM2pvajJYV3BZQlZDOGtuOEZ4dG9hMDNkQmJVaXJPODNLdFdBMHJVdmRoTkRkR1NERk5DaWRlNXgyMUJmNDkzYXZzWVUwSzlIZ29CX3BueG8ySTU4Ymlod19HTFVJM1k2X1FDMmFpLXJPa3YtVjlSdi0tdjJ4UVc3MHZGR1ljSTJHdENmV0MwOHhJdmgyTEZBV0ZUN1JVR2gxOFhXSXBHdXlWTVYxT2RMdkhnY3UtN3FXOGd1UUtZYWRaWXVIR193bmsydVZRVnJNV0E?oc=5", "source": "simplywall.st", "published": "2026-09-23 05:56", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNUnltRmdqM0NYQ2wzZWItS3BOdjdlU1pUcFJ6aEtPV1Zub1hfcVR0MERkbjZzTWpuc3pFdFVxUFBSY3U5WEhLVjdOLV9tX2lSWG1yNjJzUzVWR2xhRFJ1NUctcDN6VlJtMGlZaGlpQWx3T3RBYWs0ZExick04cTBYd0tYY1dBcTV2MjFVTUtsWFdtY3NZMFFiVjYyM0JpSmpNUWVzSVJqRGpUMzUyRHc2dm1yZEgyRmNnQmpjbDFYaXZkV3NPaXgxM2ZFWGtoemxNWU9STmpkUVlSa3oydXk5bjJpMWFRWlNqM2J5Y2lCMTB4d0FoTGFNNdIBgAJBVV95cUxQYm1wblRHcjNRcnF0MG5Uel9qVFEycDNoSzNfQWx4WWoweVQzX3d3Ym5UTTM3cjVzUG9STkdXYmlzc1psbE10cUNKYTBGVlZPaTh4bEFkN0szUHJmS2wzYzRmazBKT2MxY29WZUxaWVhmdjVEbS1TU0NyeFlRVGFEbXk3R2R3OFJYc0s1bTZmbzJGZ1hDRWE4Z05Wa2lPT0FiWWRvaFlRWFFkaDNoYnBmazJfYVlhblBVMF8yMDlfVllVdk9BeVZKUzRVSXUwNUlxOE9LUVZENWw2LW8yNGhWX3VnaUxSZC04bDljRXJGZUE0RlgycFlabTVrRDVoYy1W?oc=5", "source": "NDTV Profit", "published": "2026-09-23 01:42", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxNNi1kLW5uekpsdjNub29Fa3NDaWEzNU91MUMxNGZMS1ZVeEZPZ2tiLWZWY1M4MW84dTRYRl93QjFISTVtSG9oUHRpLUZZcE9welgydkFGTDZPRWtBbXVkaC1xOVgtWnhuNVZNVklETHgyNFdOMEo3UWFjUWx4dzI0ZlZDbXJ3cEdKMTFWZkNoeVo1OXlpUG1iLXhIUkREVElXLWozbkxtUWtmWXFxc043VHB2R0NpU2dQVVVGZlNWeXNkbVItSGk0VGZ5M202QUVzckd5bFliQUtMbE5SZ2NURVNsZW50aFZnd1RsQkJoRGVHUklpNF9iRGxCbE5XamlvWnZyVUNIM3NrdkZiYjI1MjFB0gGXAkFVX3lxTE1waWJFallWREMwLVdIUXFpMDlzd1loMmViNEdDbzVfbTJoSUxubGpLVy1NZjU1c2taUzdsczJIaG9OSmpIVFc5bUlyRjZQdzZkWVZKeVlwMG9GTTI1N0dHV09ucTJJX0hQUS1rUGtMLXhVTkNXQjNpNDVYVTQ1TmxtMmVWWGx0UVhpTDhmSGdCNlNma19TQTZadDlPa0RjZ2RfQ1dLaXFHMVZtdjNPRzFhdGVnMFYydnNJR3VGWEJiTHVvNW11dV9SbzNiaU1fSEJLeUpVY0R3UnBZbWp3NTNZN2NwU3ZFMzVhME9XVjI0cWdvdW1DZno2ZHVkTWFwMkRDUUkwdVRsYW5XQkx6M0gwX2tJYWJacw?oc=5", "source": "Livemint", "published": "2026-09-23 01:13", "score": 0.557, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPeE5EWjI1ZEd2aG02OThzbUpNSXdERzVpYkNmNXRCdEFNLU1JUEk2RG9IanhndHM2N1oxMDAwblVrcXpSaVFfcmc0WEF6UUJqd09acWZQYXdzM2cwZFJkUVZVSkE5Tk9WWnhJV0ZXR19HN18tRFhCU2hqWXR5a3lBazR6UWN4UDJ0VEh3NGFxNE1oX3M2Sjhib0h5N0RvMGdUcU9zVm91ODRoaGl2dVJXc18xTnJObk9pS3BfX1lQWS1HWGUzR0lEbDZ1ZTZ1b1FlY0h6SnBCRdIB3AFBVV95cUxQbHN0Tmw0M3l2RFNtTzBTaEtMbzJ5WmE3cWRraUhSRTc3ejR4SUE2NDBvTEhqMTZPQmktdXJ5N3VwM2ZudzBPTU8zZU1tLUVIUFlVVDdCbGFaZGllcHA5UmEzLUpOU2RlU2c0YzlrTUk4ejU3UUxQM2hXTWlsU0p5eVh0blVNMmdpcERxXzFnZ1d2R3lzUzE2c21vOGxBWGlIMnR1Z25MQTlITTI4S3JIcU56YU5VVHVyUXVSU3JHZ3ZiVnZFLWVFbmR0S0dHTHVqOGw2QlZrZzg5bDFT?oc=5", "source": "simplywall.st", "published": "2026-09-23 00:46", "score": 0.0, "label": "Neutral"}], "errors": []}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T17:07:39", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view":</t>
+          <t>lished": "2026-09-24 09:40", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZ3RITnlWRlVoLVRXRW9Pc1NnU042UFB5V1BVM0s0QkFvcnRjbElBRVd1ejJZQjdSTmNfM19uazFjYnZFbm9EMmhxVU0xYWtsd1dZNldfbEFJOE45dEVDMWw4TUVwSW5LdkVfSHZPVnZsRVI4eWhyVFpaQW1mRFM0UFUzZDhXaTB6anpwWDlSSk0yWjlpZ1Z4WEsxd3M3YklFREtEbi1TNXhEUmsxYUVyWXlPTHNxUXJVYUxpbV9ENkEtNURlYnlPcU5lTnBEbjRMVGE0SXdGRTd2VWvSAeABQVVfeXFMTVVqV1N6TXB3TXJhak1kUURlODRETFpFX1NBa1RRb1oyUlVNd0xRcXBHU2ozWVN4dlQ2N1Y2WUhpdTdZQk1NWWNYcDB4U2ZneFRVblBSajlpRmlzLXZWMTNCeHdIZG44a0ZMandxanFjTW5qTHpGM05QQ1Vxbnlsck51UjJhMkloS3dPaWstcTFoS3Q2NEQyRi0zQVhITkp3NzdWRnBkWG1vaVdWSll0SGlsdXRiaUxWc2FUVk9wMW1ZZ09tRlRCa3RoQjNONFhvQmdyN25tVWhBVTBEZmpuMnQ?oc=5", "source": "CNBC TV18", "published": "2026-09-24 09:08", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxNeEtEbWlBNTFIcHJzRV9zU0hnQUd4MVRma2VMWXpOdDl3SURrMGJPOXBnVnFOTm1MLVpMMFAzYUhUWDJVYnpYd1cyWG1xUjhxOVdkb0tVNkF2VnZfZktsRnRYTlNjMzBYblcyM0pHRUo4Ul8xVlFoci1JOXpSU2F2RlBkbFJaZGhTeE9yODV4aDlnSDdKbjd2c0ZKMzc0Y2JFbER0c2hDNW1pbURITlcw0gG3AUFVX3lxTE8xbVZoQm0xdm9CSmg5ZVBDMVluS0lTTUctTnpYYVU2S0RxcFhlaUY5Qndta09tY3VuZWI3MW1LRWlPNVl6QlY4OVBFcENPZEY4OU9jMThxdzM1cG56U1ZtN29HNGEtZmZ6eklRSXlNNERlUVF0dXNjVXV0dERKeFpyeHY4YUV3ZXdWYWhjcWsxM1d4TWtYOE1tUjRFQ0xKQm5aWHJhcnJfSHFha1FDeUJpSDdJaWhrNA?oc=5", "source": "NDTV", "published": "2026-09-24 09:02", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxNT1lNOEhqOHFBM0dUS21nbjEzUDVTOVY0YnkweVp1T1pQdy0zTG9LUmppQkhYTGtIZXBSTEtiVHdDNjZxWm5FM1VXYUl5Mk9WcklBS1p0NWlKY1FUWDNqUnlYcDRrTzI2dms1NVNjenlmQkJZdlIyQllHaEF5VVU5OWE1OFgzeE5jaVdSR0ZfNklZOGpsMGRyc3NXcEdsdFVGRl80QXRsZUhkSDVWbXN0TlRKNjJXSkRSc05IQnczMlpyYXJwYnV3NERXY3BQRjdJN0h6REx4LVo3S1dLQjNRQlpNOU9zX0RLaUlxNXUzRzFmTEdGakNJTHotX2cwX0hyb3lMVEZmR0PSAY4CQVVfeXFMTWdFZHhRbFpBMnQtazZaZUpQVk9Ramd2ajI4M296WDFaazhGZG1OV1RmeGRqcDJkeTNsWC1TYXNTbWtJa1RGRktmREpwbkpqNFYzUlFIYkR3ODg3RllZQTNWZ2h1ZzBLUlU0WXpYV2ZlQnN5WE9pN2JCV2sxbEZMdjcwQXcxRGE2c0lLSWdLVHJVYTRuX2gyYnV6MFlPZDhMUmpzVHpUUWk4WmJYNWtsMnRZSTdmNzBzdnhGRzNRUnN4aTdrakZ5QlJ0aHJsaGRGQlk5NFllakp1bHByRFpMbU05S2tqWFExY3lQYkVlUjlyX3hTUXpmRFQtVmdocWFJMG1aQ29LTHNvb200Rlh3?oc=5", "source": "The Times of India", "published": "2026-09-24 08:52", "score": -0.402, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "Hero Motors Ltd leads gainers in 'B' group", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQSDJtZTVDOFZES0ZIb3BKUnlmdkV5VTlSc2doTWJUZ1k3WEhzVDNxd0doUHI2aFBOUG9FRW1hbUw2bTBKb3FxYlNxZS1kM2VvaWtpcnp4ZEJpa1AxQ04yN3QySVkwS1dUZ3YzVUo3UVlIdzV2eE41ZUdJOWs4cTMtS2ZQNWdySzltWE5CVVFQZTZLdVZCaHVxTDVYTkJKLTE4ZWQ2SlpuVVAxNFFSVVJKYzlhT1FxMnYxZ0dKUDUwNNIBxAFBVV95cUxQS1NzWTc3QXZDVEZ2M1JsYlh1RFVzUjdVdHVWdVFrcWMyRS1zdVRJajBxXzdvSnVzWlZCQXRNbDJyenM5SDJwUnRMcW5BR3ZCMnlKbUY0dTdiVXZMalpuT1lsOHJoaFZtYkhkY2lIbVVXOVJ2MkRoRE1pa21xNU1LWUtYOGpEaVE4VFhqdElqLXVRZ1Q5SHNLVGJfN2VPNUtLT2F1ZnhMUU1hMjNXSTh1dzVZS1d2VE1fQ25BcmZEcVhTVGxf?oc=5", "source": "Business Standard", "published": "2026-09-24 08:46", "score": 0.557, "label": "Positive"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems Share Price today: decline and analysis", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxQcUhUNEJMQ3ZXeU5ZcFk0aUE1NndmWmVMR2E0MVJuM2RhTi1QRHhxT1lZRTZKeXp3NEkwak4yQ1RPVDBDRDlXUlJVUXQ1QjVIMURYTEtsZ2lXVW52SmR2VzZRS3FHanh2RklUTlNTWElScmtkaTdGMGx0SWIxdlF0YjlzVTZzQQ?oc=5", "source": "Univest", "published": "2026-09-24 08:35", "score": -0.382, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNYTRVYTVWR1lSdF95cG9QR1FLMk9SOTlCWVg0NzdVR21OeTdQQXJYc2UxbkUxa2I2blpPOVRYSmVCcWNaQnVxSnpvX0RGQnhZdmp6X1JXRGxXaVk0dXZnRDV0ZTJmdFNMTzUySWNXUjZ0OWN6Y2hwcHY2cWRxLS1hZVRpdHpISHpjMnl6b0s1M1J1bHR6LWNTd1otbHEzM0ZRV2RHeUNEdmY3X2t6ZnF3YkNyRHREUDA?oc=5", "source": "scanx.trade", "published": "2026-09-24 08:21", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices", "link": "https://news.google.com/rss/articles/CBMi6wFBVV95cUxNcnpYS1l4a05TYTZaQUM2enZTYmIxVThMMmd0UzZaSEczczdQSXhEU0tSSV9DdXFXdXE3SUNBem5BRV9BMUFlZF80U24xWHh1ZHM1SkRjU1p2a2NvM2NuRjdMQUswaWJkZUV6dVp1ZzVrZC1jZUdkX09JaWRSNWFOcEdOc1JFUVNRcEdfVXdYMVF4MHpnTl9zRDhLQWY2NVllQzkyMXN1Y0YzQzdSUTFoUC1nanVwcEhzNnc1NDNtbVZOSFhDVVpUM0F0ZG1VemZSZkF3eU5FSldzSEFLZGRBell3ZVA2Y01JWVhv0gHwAUFVX3lxTE1XVE1JUmZXOUd6YURZeGlua2c3dEZoZ3NQdWY4SnB2RFVOa0dnd012UlV5Mm16QmE1c1c1SHppQ2luZHZqU3lfb2llTkxTQmN3MUlpejNJOVVYb3BCaUQxZ1RSWEZBWWFwdjVlN2ZTZWVyTGZhdjVfWkNtUG50SkNhS3hNRFlFbHBhMG5DMjZXS1FGVWJnMmUtVzJueHhRa1IxdnZpaGVuU3ZJYmhUVXFGUWFNVW52ZGxYODBxWFVzMmRnNl9PMW53dGJ0Qi1EZmRaUGhzc0FLZWxnejdscjFjRDdUM0UtRWNpa1d5bm5JOA?oc=5", "source": "theweek.in", "published": "2026-09-24 07:35", "score": 0.077, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom \u2014 Ask Profit", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxPcjBhRnpQaFhkbGdfV3E0ZHlmUjFPQUlUQm9LTFU4UnFqSHduWnhNSEcwenhUQmM5LUxsdFNwUXN1S3gxZW9PN213QUx2TDhzUWpoNXJldnBQRmI4eTBIOE9JMGdqd3I3T2F1QVVYcVZSUF9jOEt6cnB3QWhmZ3F3Z202eHZkRXM4NHduSVVzLThxbTQ0aUJEeEJlTThhWHBFMkJ2OGJ5X0FXT3ZyWFR3MGlZeWEzWjJGU0hhejlZTFgxakpDdVVtbkV2VGJtOXU3aTh4Z0lPdmtneU5EQTNudGd30gHqAUFVX3lxTE5SeDJuQlhJbTcxaDUzbWNPNjNuZDFqLTNYYmEwR0o1QW43WVdkLW9FQUhpVExqaFluQjJwYWRVcG5NcE1ELTduTUxUVTJzQjhvVlN5YWJKa1AxaEFjYnIxempBeUNFbG1IeW94YVMwanoxOHAzNHlRSnFUbWJ3anJqQWVvb2xQeVRwZl9CQUwyUl9KSXhhTm16Qy00Uk5JdkhGU2Z5SGRzNkthQmRBN0J5WnE5bFNUREhuNC02SklqM01odWNqWjV1YTVsVUhXUUZMdlhkN09kWTdvbHhZUjFXV05sVTlGQkptQQ?oc=5", "source": "NDTV Profit", "published": "2026-09-24 07:25", "score": 0.296, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxOU0F5bUI3X2RaNWllcFpuSUpqZFp4Ui0xRVNpb2FSbVRfMjZieWxhWGV5R2N5MHpqeHBQcXIzT2dfTHBjZUt4Zk5aV2Y2SDNhM3VjamJBeTRhUjNjVklyZ3lWZDMxZ3hMMjNXaHFHWUFKV19ZaEp1WTBQekRXOU5ZdXc5UG1hQkIxRTJWdU9USDZqekc5QTh5VENqRW1ybVVCYUMwODlQRGJGVUZKV28tSVpXMFQ?oc=5", "source": "Kalkine India", "published": "2026-09-24 06:20", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'", "link": "https://news.google.com/rss/articles/CBMimwJBVV95cUxNblY5UUJKckZ0My1hbEZrdS1NbjFpR0Vyam1YUHcxd1BSMDdzWkpVZzVyN0ptcnZWZ0EwRElGTEdLV1pWNFd3a05HeEpBOC1UN0NCandyUjlzUVpsUXpKZElQajdHYUoyc2dvLXdMVkNQSW5lZHNFVG1aMzVJQ0tUcENOcmR3QWIyUFNWOFo1RENRX29SbEZLVmNGdVdjSVdkYVZyM1l6dUNtaE9KYjk1VmhIVTlWUlVZNUVFekwwRGZETkw1NTFzbWhSX2xVc2RTdzdCRExjMW5LZ05EbFZRODJvcXRnbmpKZGdPRGlpeGgza1BVNFA1V0xkR2ZJUEpCNWpPZnh5aXR2MW5aQ1EzTEJBdGY5Mi1UTkZF0gGgAkFVX3lxTE9GWEM2U2ttbzdkc05MdlJqN2tFU2pGUmxYbmVIeHktdHRhWVpuaWRnUE1RN01WREtsT2x1cTBBbExxTi1sRE93d3FvWDljRGJzWHNxMW9jek9KTklxUEdnbUk1a0t0YXdlMVZvbzc4Mnh0c3hUUXMzdV9VOWV3UXdqSnRQZFJNaVNRZ1RybmpKR19rS2dNdm5HVkNlUmRUTzJrbkRuYy1fR3pRLTFLUDBZcVAxMjRrdXg5ZVF2M2NDMjgwTXZ4bktqUXNidVU1dmJKWXEzUi1NLUwxUjliSG1vU2lQeWM2S1lRdkMxbW1qSGI4M1lpSHRVS1FVXzNja3B5Q3BYalFYLXV0T3d6VXlWVVdEWTdfUVRsWFV0RlVkdg?oc=5", "source": "The Economic Times", "published": "2026-09-24 04:09", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxNNmFnZnk5VzNtcVFkY1JFVlVCMFh6T3BlejFod0JXRWFjMng2alROdHU2YzRmcEVCV3VMZFdYM3hCbUFCa09PVmVkWTh1MWFaaUxhTndsdjlVb3pZZy1VZU1wWFl6WnNvUzUyZ243ZUQ2RUVIMEhVbm8tMWxWMzM0Y1N6aVlPenNvZkl5R0hmVG5JWlE2QkcxNlRDd0UwU2RSN3NscF9PR2NRVGVaRWYyVUpMeHFrYWNVcGdMNTM3MmpSVGdkc0laX1E5U2U4Q0pBM1N2cUNlQndvUGRvUHVhT2w3Qkh0UHZ4dkcwVTQwUkRMMHlY0gH6AUFVX3lxTE5jREhsTGtRRUVDMnRQMEhucHBndU15SnViUmVFb0ZxTUE1dmpUSlBMV01WYkZ6UXd4QkRncTdNZUh5VVRxNEQ1cmViQ2Z6WFViOVktS1hld09jM25FTHRYN0lJa3d2Q1NsWUxZR2VqUElmYXVFVk5wczFqMy13QUd4Ty1ER181WE5KaHE5SEhFdHZzTy15T0tnZ3pyZzhVMktvLUI2WDF2M3hTRThxVzZEeDRaU21jYUd4ZzZPbHlWRFVMN1lZVGRzcHd4bDUwTWc5d09MYks4c21iYlZKNUUyaC1GOXIzZ1ZzT3dXTWVaWm9KdVhHYzN4emc?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 03:56", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPRFR1dnlza0cxUU5PbXRVYmRRT19oaHZFS3NmTDZUdHhDUVpIaTJDVDFHYThvSXE3RzNWenBDSUlDUDVCdE51VkpDaXppUEl2M1htMGxsMkxPV3ZaS2d3YVhYVTlFUEphWm45cWVuYTZLYmJ2V0xwT2dtMFkwQXZ5bjVWOVh2UHczVnZUSFQ5NFBrUkJaQTJwRXFoSlY5ajhXaHJXOVd3enFaclR4QUpXODFjMWxjVVE?oc=5", "source": "Reuters", "published": "2026-09-24 02:46", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPUXhSRW9fbndZUTd4Q3FFZjhsaThCbS1jNzk4Z1N2TUdiU0lpcHNQcEZ0WmpqdGZHUUlIUUhNdlNseThhQ0hkVDVNazBSQTV1SmRVNTJ6SnUyVTBEQ3pfWTBubFpaREdzcjI0VTFacmFUZzI4ajJfZXZLcU0yQ05NcG9BN1ZkYWQ4M3pJVkFmRllNRXJXeU8zWXRMRkVoQ2o5aGJOamlGaXlfYll4WDBEdGdpY21SN1o4UENfRGNSZ1E5elpxVjJ1aGVWZ1BnZGpfUFMwM0VYM0t4eHpnM3BTTlBKaFZoQkFTT3M2bWhSNlExcEZkcmRUUHZMVmNzSzlPc2fSAYcCQVVfeXFMTnBRN0FXeEh4U2V5eEYydmZXb19IdldaZk5tYU8zbVV2TFV5ZjgxOGg5cGZfdHVScXprR3dCeEQ4czVEOF9zSWpoM3MzdWVrNFphaTdJZWg3SHVac0VnOVc0Si04cUdma2xrRFRLRlJSakp5N1FobmtwdUNqRVRFNWxsYnJrbVpjRHI2RTI5dmJ0Qml3eVBLa2NTXzNhUHZzckNXVHJxVGs1clVveXhUYlk1MjdQOTE3SDZTelVJb1JpSF9wWkpjMno4X0lDdkt2TzFIVE0zVEVRaUFxNG5IVFRhTGRwVURPZlBOcTZtUmlNTTJYS0gxU2RWTkh4T2RZOHB3SFQ4RHc?oc=5", "source": "Livemint", "published": "2026-09-24 02:44", "score": 0.758, "label": "Positive"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxOT0tVTzVLRFhsRHJ6QVB0WV85ZGh4RHFXTEdKY1R3Snp4T1VIcXVyQmNMOGpKeDF2aVdfckZKRGVqMzVpaDlTMDU0Q0lVemMzLUxFblYwQkIxcFFvalhLYng4bVdZbUhqTnFDSDFweU93akx6V3ViVXF5cEtCbk9QSFJQTjNobXRLQUpPTGNuSlc3UkVfNGdnQ0hWbXJldU11M3hadi1FU1o5azNRZ3pIUldvMkV3b1FQYVktMldOcWZkVFhPcHI2QUdMOXQxOEY1aGN6TG13WW1yMjlQWHNYd0p5LTFkRGZqOHhHNlJIcW9pWU1VQ1k0Yy01VDRPQdIBgwJBVV95cUxOdVk4MlI1LWY0aGw5azFlQ3UtdkF1V2lVYjJBaC1UYUtRNi1FT1lTeWpTbG1jZ2dPeGtBVnFYcTdISXFqaUxJcnpuZ29EWml0UkJEN0VfeHRONWRtcGo5dG9ZTDhOWGlvemZrUWZHRWtxUVBwcFRaRno4UmpWSDIwdHh6Si1LbFFDS1E3R3hvTTRGSFA4T256enl3RjBfb1hWNEFaTEkyOHJNRXBMVng1YnJMd01TMW51ZGhta1dRRmNnc3p4TC0xa2lsMDVOQ3VoZFZzUzRGV2IzYTVzajR1Mm11ZXZ6NkNfNjJjSG5iOVNmSkVXaWozaDNwaHVTNS1MNjRF?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 02:38", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields \u2014 Five Key Factors For Sensex, Nifty 50 On Sept 24", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxNMHRUa21iWVZtelA2Um13ZTJ6ZDhOSGNJMlcyandCLUFTT0w0V3R5eWd5SEdCZ1pyOEMwSlY3ak42dHRhUjdnREc5UzdaNmI3QnFkd2RsLUk0SmhaRGNqOS1QdWp0ZVdnOExERTduSHhXZlpFb2ZHaHVneDFmaGdpVTAwa3I4RWxTT3NxUHp5ekV2YTlVd3ltNS1FLTdKN19nUzBFaHB2a1Etd0xVb0NMVDJMaG5RcGlDMDhhLUJqOWFoTmFEdXFCbDZ0SlAwTmlheHZuWEZ5dGJJdW1LQ2dGeTVtNS15Z0tmR1B2YXZ0eDR6YlFBUFRIUlRVLTZ2ZTjSAYcCQVVfeXFMTVJoelZ4TXkyUmNUWkk2RThDUWRtT1RrS0dqQUtzTHJTM1RZX0w5ZHl3b0xicjN6Z1IxS2dQUV94YWdwRGpyME1rZmVaZnZ6SGE1bW5sUlM3N2ZBYl9lajJub1AwcjJLYUc1d3pHUG5HLWUtc1VFVlc3Z0FVNXI1anMwNzA5MkZvd1YzdTRUNHpRZTBBSWpqcm05bUp0ZmxNZklyNU9LS0l0NG9uSWZCRkhYenIzaktxa3Bic25SYzVfVVdPcko2ZG95YWhraURGZ212MDJBVHBCVWxXUWVQVzZZLTFIZmVGdkdsNHF3aTNOclNEMUEtSjNsUHFCZU5JSlA5bE1aZGs?oc=5", "source": "NDTV Profit", "published": "2026-09-24 01:42", "score": 0.844, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQTDl3ZlJyNW5xZXBBLUtBLXRfSU5kbEdSOXFWM3V2RU51eVdlanIzclZnczhweGRBR1lmWkVUNWI0SlBsbW5tWmd4SzBzNXA0Ty15d21DNVJkQ0piMXpzMDYxYkNndEtmV19UQnV6NVBKZlgzU1ltZEpEakJ5dVl3WU8xQS1DRVQxN0pxV1NuU19RaGZhTWNqSHFhRHFGUVROWDhEMkxhODZ2bmZFX1piMDl0ZzVJSVRhUU5KUC1pV0NCclR5dGxXXzR1VUNvbHMweU1xaHRIQWNIRG5HN1o4NWNlRlBlRjhRVFc2SElTNklUNEtMSXBZVmQ1YkxBOFg2eWtOOFZiMUTSAY4CQVVfeXFMTUdPNHFyRDVseGxVX1p5RDdOWFBabmJQdm1ZNmVZOVB0RGZMeERCSnFfZUMxV3FrMXBJT1liYmFZekEzWGR4cUs4eDlKOUhiNURta2xDLTM0dUFkRTJrOHNaa0djNnlJWFpQcE43OGt0SkFJNEgxSm9hd0puemtzNVgyX3dHdUtGa1VIRHJBdFllRUFmYlYwQ3Y4elV1djY2ZUo5R204dmZyZ3RwaGdZSHZrbERxQWZfRlhCUEhrZjdaelZGLXZmY2lTWm84ek9wWHYzdGRKQVFOR3pYWU94RUVERlBYOXFEeDJaUVI1and2N1hCenc4anc0NVVaRG50TF9Pa1o2di0xc3k3SDdn?oc=5", "source": "Livemint", "published": "2026-09-24 01:17", "score": 0.842, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs stock gains 1.37 percent as profit jumps 126 percent", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRGZMMkVQZFBodEJ4cHVqbng0YWJyNHJjbndja3pLdkJzamNORjlNUGNab3A1MDczV2piSTRpUG5yeklwV2ZvMWlFMGp2OVota2lsTHJoZlB6dG10UlBHeXRYNTk5NlRLVVduSzZJM0dLdFlTN2hkM29mWnhNU3lHVUlaTmlGQ25fUFo0dXhGT2cyNWlhQmllc3hiRFU3Z1RIN01VV0xHOFBTMUtoWUQxTDZUY2J0VTNxRXYyb2xhQ3c?oc=5", "source": "AD HOC NEWS", "published": "2026-09-23 22:57", "score": 0.791, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUE9BMFBTZkQ0bmQwWjZyUG4tSWp1VU1ERG50V2ptaVRoamFQX21HUDNBVmdwOG81TjVLeU1GSUZoNGIzUU5Vc0drSzhsMlZkOFl4MmstUEMyZWdYTTNING9fVnZrR0ZvS3VCYmJaVEk5aFdJRUJNWTZMMlV5Sy1iaU5ieC05WjZtaFJaQmMyaU5jTW9Oc1pmZHFsaUl3aVJ6TUJTR0s3SjYtdnE4c0NDejFJOFprT0Z0Zm1RTGFsTFlFVTVvUHo3d0lpZk16R1NmVGczYlUzZGNXb0Mwd3RQUmxKR0pRcklfUl9XRVNyMEZBZ1Fxa2FsSWtGSllrV2QwSmRSVnBOMmQ?oc=5", "source": "The Economic Times", "published": "2026-09-23 12:57", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxOUExzY0ZPTTBDblhZUWV1SjVUZWd0amE1STlQN1N6bm9VajdoT2NVb1ZvVjJrcHg2WTNBYlI1SGkwMlVOU3o4NDY2ZVpRMHRkRUhVUWVaS0N5QUdNbzRLa1I4UkRhNkVwOWpaVVNxOHhFV0NxZFhGOUx4anFCRDlDb0ptMHlzWFhvTmhMTEFvSk1ybFBSTzA1SG1KQnczZVdTX1NmUktxYURuVTBFbk0ydGhjNVBNN1d0Q1lUWkZlQVBJWWJLd0NhVml5amI0STBVcEs5WW4tN1pTajJSbU1wYm5ydUdIUjdvSW04MWVkdl85NmpZVmVVVFl1YmxZaWxBTVB5bkhUSFVaMXFu0gGSAkFVX3lxTE5LZmlZbUxuSjFGRzllWHk1R0RmZ0tla0huTUZYM25TUGxFMXpWLU5rTXc0WXdXM3lTWW1nYUNmNTI2elJWcEhZOTRhZ3A2X2JOUHZ1XzBuSmRRX2ZsNGZrQVBkVDlFSExzbHc3Z0VPYjRTekszODB5QndnS1Q3NmVvRmpfdmc4QzhRcGZScWlZZ01KUE1ZVWZmSFQ0UnpKVFllOFZxY3ZIME1LX2xaZ2o5bUxoYkR6Q0JQTlN0b3ZWU19IRHRCaTRmdFZLVXo1dG1oODdLOWJhSkQ4akVrODVaQTUxZnZtLWxUNDhyTGdxMDBkS3ExQXJwbnRPQlpxTFdReTZxNEtLWGRwNnIwTEhCcGc?oc=5", "source": "Livemint", "published": "2026-09-23 11:16", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPaHBTQzhTRUdZS2tNRmJlTDU1UXJ4bnYzUXZNY1RzZWhub0dSbFFIZDM3aGZCNFJ2V2F1QmJRX3lVelpSd2ZsTkZVTF9ncUZCZ1NYblZYUjBYNi13Z19fOVhDN19taGt4MGV1Q1NtWEY4U0lrdnVXaUtFQm9TZTFUMGlzNWdoTUdBYWZxOUtWcG1idGJwOE10NTloS1hrdV9HN3lhLXZXWUh3dzA2TVVLcHRuRFJDVXdmUC1nV084LTVEV2N4OFRVQjU1Smg4Q2ktSTBKWmRCRGtRdWdWOEc5UGh0YWpOTUlNWmVyV2l0RC10T3d1YndQalotU0NWWDBqTDhn?oc=5", "source": "upstox.com", "published": "2026-09-23 10:15", "score": 0.612, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure Share Price Rises 2.68% Today", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNbjd5UVZ4d3N3ZUtybnEyZW1MZ1R4T0NrS1JsMEhETFc5d2tyclFHRnV4bzQ1RVQyUkZvNnIwOURYdjdBUzZldEpRN0FBV29YLVZOTjlFalZfemVpUzBVZ3BZSDJxSVFqSmdCMDVfNVNVXy1ZZVJpZUZORHdmNUFzazBrdGVsOGVPN1ZMRmdyQ0U1X3kzS1ZNZU1mQQ?oc=5", "source": "Univest", "published": "2026-09-23 10:02", "score": 0.34, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs Share Price: one-year high and valuation view", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYU9VS2psbTA2SEFlWWF6NVFFbVRManpTcU0wUjJIbWRQdEU2S1JUeWVXWVUtSW1RNGp3VmdEZjRGYkdVYmFtV2tZd1BQLWJfT2ZHYzhXcFhMTVgwaDlmNmZkOHhaY0JiOEVaQmZmTk5FS1luRmcxeE9ZbGV3VDlqOWR4VFhCZEE?oc=5", "source": "Univest", "published": "2026-09-23 09:19", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQa2ZFOFYwaEJuQTl6N3NjWFFvMWUyUGdxNXlZNFJHVWxtcFNEenVuTlNieHRNX3RpY0dfNnNCUk1hMU9Ndk5Sckl3TVg1Z2lJYnFORjgtY0UySTc0WW5qVmV0bU5hd0UzTVM3OVdKUFNUUHdzbEhaTTNERlV0WTdFWTBYSnpadUhucV9mejJxMnNlZ2V2UzJaOVY0dHdfNWtMVWN3U0tkVVFuSUVSMnV5NjhTUUE5a2Zrc2xieTVkZEphNmVqSEQ1MmRqMEFKM2xwU1FCVkxkZ0VsdFZYazRiMDhKcEhsejFNOXgtSGo0bFRJWThyZkZaXzJVQWpwbklBNno4NE1QSzRfT001NktmddIBlgJBVV95cUxOdy1fS2JiOHZGWTlaelh4ak5fQTR6TU9lek4tN0tIODhtWjRtRkJmS2hhZHVLTmpSMkQ2T0dXNnk1VFlTdFRjcmE1b1dCQWYtSnVQRFh0Z1hsUUljNkZVeF9GQ2pSZmplX082cHlVWEx2aVQ0dWpyZndmREdSOUJmcHBfczhYU0ZjUVVWYU96N1J0SENVQV8tR243REJnYzZwcnNzTlFnakJWcmV6eU9yTUs3NC1FWVpwRnFiZTRrUVVtM1UxQy01YnNsN1BweXNTbGpkb1l1UTNTRzNDUDEtWjBOeVJsa2QtejEtRElXcy1LNXc5bW5FY0Q4TGhXQXNWWlgxRjlXQlNEQ1R0V1B2OVZqWHluUQ?oc=5", "source": "The Times of India", "published": "2026-09-23 07:59", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks Share Price news: price rise and valuation", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNS3pobG5zQUpFLU53cFlCQWxZTFQ5S0E1dDNmbTU3V2daQUx1ZTMxMjctRHphNW5OSWVoYk9UY09CU2NxbF9GWjVCZDJzeF9OTXVTX3NUYVRjZ1U3ekZnLVFxZ01Sc3dVWlZIcnZOdXdvTzVlNTdoMlhYaVZZaWNaTEpZTkxpZw?oc=5", "source": "Univest", "published": "2026-09-23 07:26", "score": 0.0, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQThVQlhqMHhQX1dCbzk5aTVLRzAzLVhTQ0kzajBZMXRVTTNTazhRNTM3Y2d5SE1fbUhYVkJkT0hDeDlCZFhGRHEtWUxEcEhISzA4bkNGUlQ2RW44NEdPa1k5VFF5MGktRHhhZHJMRjAyeUVCVmEwWkVIQ2ROQmlhdTZTY255RFg2Rkp4NWtCTk1vaGxrUFc1VTRFSkJFY1Nnakd4VXpMNGxRVkpvMkl5VnpmakQtMWgwcV90RFpwM3BwaFFfNzhsR3IzQWhRNmpCWVVjdVM1ZExSSkxZR1N1bEpNaUp0eGV5bGIyTDQzZTZjdw?oc=5", "source": "The Economic Times", "published": "2026-09-23 06:24", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPa2tacGJLRFdET1pPVlhxQlRodHp4ZVZkREJLUU8yQlFiSmdib0hReElVbW5Qc2QtMnFqZWVDREFveHlPbDB5MHhGQjlBcTVfMS12Q1hyNGRFUjZrOHY0Ym9jSGhaSnV4YlZYZDZGV25jb1NtRV9admFLQWN1N1NETF9pUU1GbFFadFVXdzJ0dUxJelU3SFlaQUR0MlZxTWxHaDQ2SnpjRl9LczRSQ1BiX2h6SWl3ckJiek5mSDVwNm84cVVBYnRCSnFPYWRHLUlhUUlwb2cyN0tGdHRGU2lNdnVkdlNQZGJS0gHuAUFVX3lxTFBtQmV3OHlXVURIb1VpaGFmZnYtYjJnSFVyVjEtM2pvajJYV3BZQlZDOGtuOEZ4dG9hMDNkQmJVaXJPODNLdFdBMHJVdmRoTkRkR1NERk5DaWRlNXgyMUJmNDkzYXZzWVUwSzlIZ29CX3BueG8ySTU4Ymlod19HTFVJM1k2X1FDMmFpLXJPa3YtVjlSdi0tdjJ4UVc3MHZGR1ljSTJHdENmV0MwOHhJdmgyTEZBV0ZUN1JVR2gxOFhXSXBHdXlWTVYxT2RMdkhnY3UtN3FXOGd1UUtZYWRaWXVIR193bmsydVZRVnJNV0E?oc=5", "source": "simplywall.st", "published": "2026-09-23 05:56", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNUnltRmdqM0NYQ2wzZWItS3BOdjdlU1pUcFJ6aEtPV1Zub1hfcVR0MERkbjZzTWpuc3pFdFVxUFBSY3U5WEhLVjdOLV9tX2lSWG1yNjJzUzVWR2xhRFJ1NUctcDN6VlJtMGlZaGlpQWx3T3RBYWs0ZExick04cTBYd0tYY1dBcTV2MjFVTUtsWFdtY3NZMFFiVjYyM0JpSmpNUWVzSVJqRGpUMzUyRHc2dm1yZEgyRmNnQmpjbDFYaXZkV3NPaXgxM2ZFWGtoemxNWU9STmpkUVlSa3oydXk5bjJpMWFRWlNqM2J5Y2lCMTB4d0FoTGFNNdIBgAJBVV95cUxQYm1wblRHcjNRcnF0MG5Uel9qVFEycDNoSzNfQWx4WWoweVQzX3d3Ym5UTTM3cjVzUG9STkdXYmlzc1psbE10cUNKYTBGVlZPaTh4bEFkN0szUHJmS2wzYzRmazBKT2MxY29WZUxaWVhmdjVEbS1TU0NyeFlRVGFEbXk3R2R3OFJYc0s1bTZmbzJGZ1hDRWE4Z05Wa2lPT0FiWWRvaFlRWFFkaDNoYnBmazJfYVlhblBVMF8yMDlfVllVdk9BeVZKUzRVSXUwNUlxOE9LUVZENWw2LW8yNGhWX3VnaUxSZC04bDljRXJGZUE0RlgycFlabTVrRDVoYy1W?oc=5", "source": "NDTV Profit", "published": "2026-09-23 01:42", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxNNi1kLW5uekpsdjNub29Fa3NDaWEzNU91MUMxNGZMS1ZVeEZPZ2tiLWZWY1M4MW84dTRYRl93QjFISTVtSG9oUHRpLUZZcE9welgydkFGTDZPRWtBbXVkaC1xOVgtWnhuNVZNVklETHgyNFdOMEo3UWFjUWx4dzI0ZlZDbXJ3cEdKMTFWZkNoeVo1OXlpUG1iLXhIUkREVElXLWozbkxtUWtmWXFxc043VHB2R0NpU2dQVVVGZlNWeXNkbVItSGk0VGZ5M202QUVzckd5bFliQUtMbE5SZ2NURVNsZW50aFZnd1RsQkJoRGVHUklpNF9iRGxCbE5XamlvWnZyVUNIM3NrdkZiYjI1MjFB0gGXAkFVX3lxTE1waWJFallWREMwLVdIUXFpMDlzd1loMmViNEdDbzVfbTJoSUxubGpLVy1NZjU1c2taUzdsczJIaG9OSmpIVFc5bUlyRjZQdzZkWVZKeVlwMG9GTTI1N0dHV09ucTJJX0hQUS1rUGtMLXhVTkNXQjNpNDVYVTQ1TmxtMmVWWGx0UVhpTDhmSGdCNlNma19TQTZadDlPa0RjZ2RfQ1dLaXFHMVZtdjNPRzFhdGVnMFYydnNJR3VGWEJiTHVvNW11dV9SbzNiaU1fSEJLeUpVY0R3UnBZbWp3NTNZN2NwU3ZFMzVhME9XVjI0cWdvdW1DZno2ZHVkTWFwMkRDUUkwdVRsYW5XQkx6M0gwX2tJYWJacw?oc=5", "source": "Livemint", "published": "2026-09-23 01:13", "score": 0.557, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPeE5EWjI1ZEd2aG02OThzbUpNSXdERzVpYkNmNXRCdEFNLU1JUEk2RG9IanhndHM2N1oxMDAwblVrcXpSaVFfcmc0WEF6UUJqd09acWZQYXdzM2cwZFJkUVZVSkE5Tk9WWnhJV0ZXR19HN18tRFhCU2hqWXR5a3lBazR6UWN4UDJ0VEh3NGFxNE1oX3M2Sjhib0h5N0RvMGdUcU9zVm91ODRoaGl2dVJXc18xTnJObk9pS3BfX1lQWS1HWGUzR0lEbDZ1ZTZ1b1FlY0h6SnBCRdIB3AFBVV95cUxQbHN0Tmw0M3l2RFNtTzBTaEtMbzJ5WmE3cWRraUhSRTc3ejR4SUE2NDBvTEhqMTZPQmktdXJ5N3VwM2ZudzBPTU8zZU1tLUVIUFlVVDdCbGFaZGllcHA5UmEzLUpOU2RlU2c0YzlrTUk4ejU3UUxQM2hXTWlsU0p5eVh0blVNMmdpcERxXzFnZ1d2R3lzUzE2c21vOGxBWGlIMnR1Z25MQTlITTI4S3JIcU56YU5VVHVyUXVSU3JHZ3ZiVnZFLWVFbmR0S0dHTHVqOGw2QlZrZzg5bDFT?oc=5", "source": "simplywall.st", "published": "2026-09-23 00:46", "score": 0.0, "label": "Neutral"}], "errors": []}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T18:12:59", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-be</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}, "telegram_sent": "2026-09-28", "corp_actions": []}</t>
+          <t>ar", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}, "telegram_sent": "2026-09-29", "corp_actions": [], "pending_alerts": []}</t>
         </is>
       </c>
     </row>

--- a/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
+++ b/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
@@ -1498,7 +1498,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 18:13</t>
+          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 19:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 18:13</t>
+          <t>Signal 2026-09-28  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-10-29  •  Updated 29-Sep-2026 19:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10168,7 +10168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10196,7 +10196,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fetched 2026-09-29 18:13</t>
+          <t>Fetched 2026-09-29 19:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="C6" s="51" t="inlineStr">
         <is>
-          <t>Markets ride expiry-day seesaw as derivatives swings jolt Nifty</t>
+          <t>High derivatives activity lead to swings in Indian market on expiry day</t>
         </is>
       </c>
       <c r="D6" s="51" t="inlineStr">
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="E6" s="81" t="n">
-        <v>0.402</v>
+        <v>0.202</v>
       </c>
       <c r="F6" s="51" t="inlineStr">
         <is>
@@ -10356,25 +10356,25 @@
       </c>
       <c r="B8" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 11:26</t>
+          <t>2026-09-29 11:14</t>
         </is>
       </c>
       <c r="C8" s="51" t="inlineStr">
         <is>
-          <t>Stock market today, Sept 29: 227 securities hit 52-week low on NSE; Waaree Energies, Canara Bank, Britannia on list</t>
+          <t>Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%</t>
         </is>
       </c>
       <c r="D8" s="51" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>APAC Media</t>
         </is>
       </c>
       <c r="E8" s="81" t="n">
-        <v>0.103</v>
+        <v>0.226</v>
       </c>
       <c r="F8" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G8" s="82" t="inlineStr">
@@ -10391,25 +10391,25 @@
       </c>
       <c r="B9" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 11:14</t>
+          <t>2026-09-29 10:48</t>
         </is>
       </c>
       <c r="C9" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%</t>
+          <t>Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh</t>
         </is>
       </c>
       <c r="D9" s="51" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>DD India</t>
         </is>
       </c>
       <c r="E9" s="81" t="n">
-        <v>0.226</v>
+        <v>-0.34</v>
       </c>
       <c r="F9" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G9" s="82" t="inlineStr">
@@ -10426,25 +10426,25 @@
       </c>
       <c r="B10" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 10:48</t>
+          <t>2026-09-29 10:19</t>
         </is>
       </c>
       <c r="C10" s="51" t="inlineStr">
         <is>
-          <t>Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh</t>
+          <t>Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%</t>
         </is>
       </c>
       <c r="D10" s="51" t="inlineStr">
         <is>
-          <t>DD India</t>
+          <t>equitymaster.com</t>
         </is>
       </c>
       <c r="E10" s="81" t="n">
-        <v>-0.34</v>
+        <v>0.226</v>
       </c>
       <c r="F10" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G10" s="82" t="inlineStr">
@@ -10461,21 +10461,21 @@
       </c>
       <c r="B11" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 10:19</t>
+          <t>2026-09-29 10:11</t>
         </is>
       </c>
       <c r="C11" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%</t>
+          <t>Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E11" s="81" t="n">
-        <v>0.226</v>
+        <v>0.402</v>
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
@@ -10491,26 +10491,26 @@
     <row r="12">
       <c r="A12" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B12" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 10:11</t>
+          <t>2026-09-29 08:18</t>
         </is>
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026</t>
+          <t>AEROFLEX Share Price gains as market cap tops Rs 6,946 Cr</t>
         </is>
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E12" s="81" t="n">
-        <v>0.402</v>
+        <v>0.71</v>
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
@@ -10636,25 +10636,25 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 05:09</t>
+          <t>2026-09-29 05:18</t>
         </is>
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600</t>
+          <t>5 reasons why market is down today: Sensex, Nifty hit six-month lows; India VIX spikes</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="E16" s="81" t="n">
-        <v>-0.791</v>
+        <v>0.077</v>
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G16" s="82" t="inlineStr">
@@ -10671,21 +10671,21 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 05:06</t>
+          <t>2026-09-29 05:09</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for</t>
+          <t>Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E17" s="81" t="n">
-        <v>-0.459</v>
+        <v>-0.791</v>
       </c>
       <c r="F17" s="51" t="inlineStr">
         <is>
@@ -10706,25 +10706,25 @@
       </c>
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:38</t>
+          <t>2026-09-29 05:06</t>
         </is>
       </c>
       <c r="C18" s="51" t="inlineStr">
         <is>
-          <t>BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle</t>
+          <t>Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for</t>
         </is>
       </c>
       <c r="D18" s="51" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E18" s="81" t="n">
-        <v>0.71</v>
+        <v>-0.459</v>
       </c>
       <c r="F18" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G18" s="82" t="inlineStr">
@@ -10741,25 +10741,25 @@
       </c>
       <c r="B19" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:35</t>
+          <t>2026-09-29 04:38</t>
         </is>
       </c>
       <c r="C19" s="51" t="inlineStr">
         <is>
-          <t>Sensex Falls 400 Points; Nifty Slips Below 22,700</t>
+          <t>BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle</t>
         </is>
       </c>
       <c r="D19" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="E19" s="81" t="n">
-        <v>-0.318</v>
+        <v>0.71</v>
       </c>
       <c r="F19" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G19" s="82" t="inlineStr">
@@ -10781,16 +10781,16 @@
       </c>
       <c r="C20" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+          <t>Sensex Falls 400 Points; Nifty Slips Below 22,700</t>
         </is>
       </c>
       <c r="D20" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E20" s="81" t="n">
-        <v>-0.477</v>
+        <v>-0.318</v>
       </c>
       <c r="F20" s="51" t="inlineStr">
         <is>
@@ -10806,30 +10806,30 @@
     <row r="21">
       <c r="A21" s="51" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B21" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:23</t>
+          <t>2026-09-29 04:35</t>
         </is>
       </c>
       <c r="C21" s="51" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price News: Today’s Decline Analyzed</t>
+          <t>Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
         </is>
       </c>
       <c r="D21" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>equitymaster.com</t>
         </is>
       </c>
       <c r="E21" s="81" t="n">
-        <v>-0.128</v>
+        <v>-0.477</v>
       </c>
       <c r="F21" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G21" s="82" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="22">
       <c r="A22" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B22" s="51" t="inlineStr">
@@ -10851,16 +10851,16 @@
       </c>
       <c r="C22" s="51" t="inlineStr">
         <is>
-          <t>Oil rise, bond yields: Top factors behind Tuesday's stock market fall</t>
+          <t>Ather Energy Share Price News: Today’s Decline Analyzed</t>
         </is>
       </c>
       <c r="D22" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E22" s="81" t="n">
-        <v>-0.153</v>
+        <v>-0.128</v>
       </c>
       <c r="F22" s="51" t="inlineStr">
         <is>
@@ -10881,25 +10881,25 @@
       </c>
       <c r="B23" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:21</t>
+          <t>2026-09-29 04:23</t>
         </is>
       </c>
       <c r="C23" s="51" t="inlineStr">
         <is>
-          <t>No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what’s dragging the market?</t>
+          <t>Oil rise, bond yields: Top factors behind Tuesday's stock market fall</t>
         </is>
       </c>
       <c r="D23" s="51" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E23" s="81" t="n">
-        <v>-0.402</v>
+        <v>-0.153</v>
       </c>
       <c r="F23" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" s="82" t="inlineStr">
@@ -10921,20 +10921,20 @@
       </c>
       <c r="C24" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty sink further; What is keeping the market under pressure?</t>
+          <t>No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what’s dragging the market?</t>
         </is>
       </c>
       <c r="D24" s="51" t="inlineStr">
         <is>
-          <t>newsdrum.in</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="E24" s="81" t="n">
-        <v>0.128</v>
+        <v>-0.402</v>
       </c>
       <c r="F24" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G24" s="82" t="inlineStr">
@@ -10951,25 +10951,25 @@
       </c>
       <c r="B25" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:14</t>
+          <t>2026-09-29 04:21</t>
         </is>
       </c>
       <c r="C25" s="51" t="inlineStr">
         <is>
-          <t>Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street</t>
+          <t>Sensex, Nifty sink further; What is keeping the market under pressure?</t>
         </is>
       </c>
       <c r="D25" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>newsdrum.in</t>
         </is>
       </c>
       <c r="E25" s="81" t="n">
-        <v>-0.273</v>
+        <v>0.128</v>
       </c>
       <c r="F25" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G25" s="82" t="inlineStr">
@@ -10986,21 +10986,21 @@
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:02</t>
+          <t>2026-09-29 04:14</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr">
         <is>
-          <t>Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...</t>
+          <t>Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street</t>
         </is>
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E26" s="81" t="n">
-        <v>-0.421</v>
+        <v>-0.273</v>
       </c>
       <c r="F26" s="51" t="inlineStr">
         <is>
@@ -11021,25 +11021,25 @@
       </c>
       <c r="B27" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 04:01</t>
+          <t>2026-09-29 04:02</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr">
         <is>
-          <t>Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How</t>
+          <t>Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...</t>
         </is>
       </c>
       <c r="D27" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E27" s="81" t="n">
-        <v>0.214</v>
+        <v>-0.421</v>
       </c>
       <c r="F27" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G27" s="82" t="inlineStr">
@@ -11056,25 +11056,25 @@
       </c>
       <c r="B28" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 02:57</t>
+          <t>2026-09-29 04:01</t>
         </is>
       </c>
       <c r="C28" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty opening: Will stock market crash or open higher today?</t>
+          <t>Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How</t>
         </is>
       </c>
       <c r="D28" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>ndtv.com</t>
         </is>
       </c>
       <c r="E28" s="81" t="n">
-        <v>-0.273</v>
+        <v>0.214</v>
       </c>
       <c r="F28" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G28" s="82" t="inlineStr">
@@ -11091,25 +11091,25 @@
       </c>
       <c r="B29" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:36</t>
+          <t>2026-09-29 02:57</t>
         </is>
       </c>
       <c r="C29" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
+          <t>Sensex, Nifty opening: Will stock market crash or open higher today?</t>
         </is>
       </c>
       <c r="D29" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E29" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.273</v>
       </c>
       <c r="F29" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G29" s="82" t="inlineStr">
@@ -11126,21 +11126,21 @@
       </c>
       <c r="B30" s="51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:19</t>
+          <t>2026-09-29 01:36</t>
         </is>
       </c>
       <c r="C30" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
         </is>
       </c>
       <c r="D30" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E30" s="81" t="n">
-        <v>0.842</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F30" s="51" t="inlineStr">
         <is>
@@ -11161,25 +11161,25 @@
       </c>
       <c r="B31" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 19:51</t>
+          <t>2026-09-29 01:19</t>
         </is>
       </c>
       <c r="C31" s="51" t="inlineStr">
         <is>
-          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D31" s="51" t="inlineStr">
         <is>
-          <t>wionews.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E31" s="81" t="n">
-        <v>-0.34</v>
+        <v>0.842</v>
       </c>
       <c r="F31" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G31" s="82" t="inlineStr">
@@ -11196,25 +11196,25 @@
       </c>
       <c r="B32" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 17:36</t>
+          <t>2026-09-28 19:51</t>
         </is>
       </c>
       <c r="C32" s="51" t="inlineStr">
         <is>
-          <t>Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens</t>
+          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
         </is>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>WION</t>
         </is>
       </c>
       <c r="E32" s="81" t="n">
-        <v>0.026</v>
+        <v>-0.34</v>
       </c>
       <c r="F32" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G32" s="82" t="inlineStr">
@@ -11231,25 +11231,25 @@
       </c>
       <c r="B33" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42</t>
+          <t>2026-09-28 17:36</t>
         </is>
       </c>
       <c r="C33" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
+          <t>Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens</t>
         </is>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E33" s="81" t="n">
-        <v>-0.896</v>
+        <v>0.026</v>
       </c>
       <c r="F33" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G33" s="82" t="inlineStr">
@@ -11261,30 +11261,30 @@
     <row r="34">
       <c r="A34" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B34" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 13:25</t>
+          <t>2026-09-28 13:42</t>
         </is>
       </c>
       <c r="C34" s="51" t="inlineStr">
         <is>
-          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
+          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
         </is>
       </c>
       <c r="D34" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E34" s="81" t="n">
-        <v>0.652</v>
+        <v>-0.896</v>
       </c>
       <c r="F34" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G34" s="82" t="inlineStr">
@@ -11296,26 +11296,26 @@
     <row r="35">
       <c r="A35" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B35" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 13:16</t>
+          <t>2026-09-28 13:25</t>
         </is>
       </c>
       <c r="C35" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
+          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
         </is>
       </c>
       <c r="D35" s="51" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>equitymaster.com</t>
         </is>
       </c>
       <c r="E35" s="81" t="n">
-        <v>0.361</v>
+        <v>0.652</v>
       </c>
       <c r="F35" s="51" t="inlineStr">
         <is>
@@ -11331,30 +11331,30 @@
     <row r="36">
       <c r="A36" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B36" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 11:48</t>
+          <t>2026-09-28 13:16</t>
         </is>
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="E36" s="81" t="n">
-        <v>0.153</v>
+        <v>0.361</v>
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G36" s="82" t="inlineStr">
@@ -11366,30 +11366,30 @@
     <row r="37">
       <c r="A37" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B37" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:56</t>
+          <t>2026-09-28 11:48</t>
         </is>
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
+          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
         </is>
       </c>
       <c r="D37" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E37" s="81" t="n">
-        <v>-0.273</v>
+        <v>0.153</v>
       </c>
       <c r="F37" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G37" s="82" t="inlineStr">
@@ -11406,21 +11406,21 @@
       </c>
       <c r="B38" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:48</t>
+          <t>2026-09-28 10:56</t>
         </is>
       </c>
       <c r="C38" s="51" t="inlineStr">
         <is>
-          <t>Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge</t>
+          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
         </is>
       </c>
       <c r="D38" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>equitymaster.com</t>
         </is>
       </c>
       <c r="E38" s="81" t="n">
-        <v>-0.7</v>
+        <v>-0.273</v>
       </c>
       <c r="F38" s="51" t="inlineStr">
         <is>
@@ -11441,21 +11441,21 @@
       </c>
       <c r="B39" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:46</t>
+          <t>2026-09-28 10:48</t>
         </is>
       </c>
       <c r="C39" s="51" t="inlineStr">
         <is>
-          <t>Sensex Falls 1,124 Points, Nifty Slips Below 22,800</t>
+          <t>Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge</t>
         </is>
       </c>
       <c r="D39" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="E39" s="81" t="n">
-        <v>-0.318</v>
+        <v>-0.7</v>
       </c>
       <c r="F39" s="51" t="inlineStr">
         <is>
@@ -11476,21 +11476,21 @@
       </c>
       <c r="B40" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:26</t>
+          <t>2026-09-28 10:46</t>
         </is>
       </c>
       <c r="C40" s="51" t="inlineStr">
         <is>
-          <t>Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low</t>
+          <t>Sensex Falls 1,124 Points, Nifty Slips Below 22,800</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E40" s="81" t="n">
-        <v>-0.612</v>
+        <v>-0.318</v>
       </c>
       <c r="F40" s="51" t="inlineStr">
         <is>
@@ -11511,25 +11511,25 @@
       </c>
       <c r="B41" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:15</t>
+          <t>2026-09-28 10:26</t>
         </is>
       </c>
       <c r="C41" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
+          <t>Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low</t>
         </is>
       </c>
       <c r="D41" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E41" s="81" t="n">
-        <v>0.402</v>
+        <v>-0.612</v>
       </c>
       <c r="F41" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G41" s="82" t="inlineStr">
@@ -11541,30 +11541,30 @@
     <row r="42">
       <c r="A42" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B42" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:06</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="C42" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
         </is>
       </c>
       <c r="D42" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E42" s="81" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F42" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G42" s="82" t="inlineStr">
@@ -11576,26 +11576,26 @@
     <row r="43">
       <c r="A43" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B43" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:05</t>
+          <t>2026-09-28 10:06</t>
         </is>
       </c>
       <c r="C43" s="51" t="inlineStr">
         <is>
-          <t>Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top losers</t>
+          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
         </is>
       </c>
       <c r="D43" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E43" s="81" t="n">
-        <v>-0.178</v>
+        <v>0</v>
       </c>
       <c r="F43" s="51" t="inlineStr">
         <is>
@@ -11686,25 +11686,25 @@
       </c>
       <c r="B46" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 08:03</t>
+          <t>2026-09-28 08:14</t>
         </is>
       </c>
       <c r="C46" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
+          <t>Forget KOSPI, Nikkei, Nasdaq, even Pakistan's KSE surged over 100% in 2 years, leaving India's Nifty, Sensex far behind</t>
         </is>
       </c>
       <c r="D46" s="51" t="inlineStr">
         <is>
-          <t>Free Press Kashmir</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E46" s="81" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G46" s="82" t="inlineStr">
@@ -11721,25 +11721,25 @@
       </c>
       <c r="B47" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 08:03</t>
         </is>
       </c>
       <c r="C47" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?</t>
+          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
         </is>
       </c>
       <c r="D47" s="51" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>Free Press Kashmir</t>
         </is>
       </c>
       <c r="E47" s="81" t="n">
-        <v>-0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="F47" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G47" s="82" t="inlineStr">
@@ -11756,25 +11756,25 @@
       </c>
       <c r="B48" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:44</t>
+          <t>2026-09-28 07:56</t>
         </is>
       </c>
       <c r="C48" s="51" t="inlineStr">
         <is>
-          <t>Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts</t>
+          <t>Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?</t>
         </is>
       </c>
       <c r="D48" s="51" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="E48" s="81" t="n">
-        <v>0</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="F48" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G48" s="82" t="inlineStr">
@@ -11791,25 +11791,25 @@
       </c>
       <c r="B49" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:36</t>
+          <t>2026-09-28 07:44</t>
         </is>
       </c>
       <c r="C49" s="51" t="inlineStr">
         <is>
-          <t>September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets</t>
+          <t>Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts</t>
         </is>
       </c>
       <c r="D49" s="51" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>APAC Media</t>
         </is>
       </c>
       <c r="E49" s="81" t="n">
-        <v>-0.806</v>
+        <v>0</v>
       </c>
       <c r="F49" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G49" s="82" t="inlineStr">
@@ -11826,21 +11826,21 @@
       </c>
       <c r="B50" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 07:06</t>
+          <t>2026-09-28 07:36</t>
         </is>
       </c>
       <c r="C50" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800</t>
+          <t>September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets</t>
         </is>
       </c>
       <c r="D50" s="51" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E50" s="81" t="n">
-        <v>-0.402</v>
+        <v>-0.806</v>
       </c>
       <c r="F50" s="51" t="inlineStr">
         <is>
@@ -11861,21 +11861,21 @@
       </c>
       <c r="B51" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 06:47</t>
+          <t>2026-09-28 07:06</t>
         </is>
       </c>
       <c r="C51" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
+          <t>Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800</t>
         </is>
       </c>
       <c r="D51" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="E51" s="81" t="n">
-        <v>-0.791</v>
+        <v>-0.402</v>
       </c>
       <c r="F51" s="51" t="inlineStr">
         <is>
@@ -11896,21 +11896,21 @@
       </c>
       <c r="B52" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 06:40</t>
+          <t>2026-09-28 06:47</t>
         </is>
       </c>
       <c r="C52" s="51" t="inlineStr">
         <is>
-          <t>SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday’s market crash</t>
+          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
         </is>
       </c>
       <c r="D52" s="51" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E52" s="81" t="n">
-        <v>-0.595</v>
+        <v>-0.791</v>
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
@@ -11926,26 +11926,26 @@
     <row r="53">
       <c r="A53" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B53" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:52</t>
+          <t>2026-09-28 06:40</t>
         </is>
       </c>
       <c r="C53" s="51" t="inlineStr">
         <is>
-          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
+          <t>SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday’s market crash</t>
         </is>
       </c>
       <c r="D53" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E53" s="81" t="n">
-        <v>-0.382</v>
+        <v>-0.595</v>
       </c>
       <c r="F53" s="51" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
     <row r="54">
       <c r="A54" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B54" s="51" t="inlineStr">
@@ -11971,16 +11971,16 @@
       </c>
       <c r="C54" s="51" t="inlineStr">
         <is>
-          <t>India VIX spikes 14% as oil, geopolitical risks trigger market sell-off</t>
+          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
         </is>
       </c>
       <c r="D54" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E54" s="81" t="n">
-        <v>-0.273</v>
+        <v>-0.382</v>
       </c>
       <c r="F54" s="51" t="inlineStr">
         <is>
@@ -12001,25 +12001,25 @@
       </c>
       <c r="B55" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:42</t>
+          <t>2026-09-28 05:52</t>
         </is>
       </c>
       <c r="C55" s="51" t="inlineStr">
         <is>
-          <t>Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern</t>
+          <t>India VIX spikes 14% as oil, geopolitical risks trigger market sell-off</t>
         </is>
       </c>
       <c r="D55" s="51" t="inlineStr">
         <is>
-          <t>India Infoline</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E55" s="81" t="n">
-        <v>0.103</v>
+        <v>-0.273</v>
       </c>
       <c r="F55" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G55" s="82" t="inlineStr">
@@ -12031,26 +12031,26 @@
     <row r="56">
       <c r="A56" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B56" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:37</t>
+          <t>2026-09-28 05:42</t>
         </is>
       </c>
       <c r="C56" s="51" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
+          <t>Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern</t>
         </is>
       </c>
       <c r="D56" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>India Infoline</t>
         </is>
       </c>
       <c r="E56" s="81" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
@@ -12066,30 +12066,30 @@
     <row r="57">
       <c r="A57" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B57" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:18</t>
+          <t>2026-09-28 05:37</t>
         </is>
       </c>
       <c r="C57" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
         </is>
       </c>
       <c r="D57" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E57" s="81" t="n">
-        <v>-0.6909999999999999</v>
+        <v>0</v>
       </c>
       <c r="F57" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G57" s="82" t="inlineStr">
@@ -12106,21 +12106,21 @@
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 05:11</t>
+          <t>2026-09-28 05:18</t>
         </is>
       </c>
       <c r="C58" s="51" t="inlineStr">
         <is>
-          <t>Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties</t>
+          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
         </is>
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E58" s="81" t="n">
-        <v>-0.852</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="F58" s="51" t="inlineStr">
         <is>
@@ -12141,21 +12141,21 @@
       </c>
       <c r="B59" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:56</t>
+          <t>2026-09-28 05:11</t>
         </is>
       </c>
       <c r="C59" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+          <t>Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties</t>
         </is>
       </c>
       <c r="D59" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E59" s="81" t="n">
-        <v>-0.477</v>
+        <v>-0.852</v>
       </c>
       <c r="F59" s="51" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:51</t>
+          <t>2026-09-28 04:56</t>
         </is>
       </c>
       <c r="C60" s="51" t="inlineStr">
         <is>
-          <t>Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil</t>
+          <t>Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
         </is>
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>equitymaster.com</t>
         </is>
       </c>
       <c r="E60" s="81" t="n">
-        <v>-0.586</v>
+        <v>-0.477</v>
       </c>
       <c r="F60" s="51" t="inlineStr">
         <is>
@@ -12211,21 +12211,21 @@
       </c>
       <c r="B61" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:45</t>
+          <t>2026-09-28 04:51</t>
         </is>
       </c>
       <c r="C61" s="51" t="inlineStr">
         <is>
-          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
+          <t>Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil</t>
         </is>
       </c>
       <c r="D61" s="51" t="inlineStr">
         <is>
-          <t>hindustantimes.com</t>
+          <t>rediff.com</t>
         </is>
       </c>
       <c r="E61" s="81" t="n">
-        <v>-0.361</v>
+        <v>-0.586</v>
       </c>
       <c r="F61" s="51" t="inlineStr">
         <is>
@@ -12246,21 +12246,21 @@
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:42</t>
+          <t>2026-09-28 04:45</t>
         </is>
       </c>
       <c r="C62" s="51" t="inlineStr">
         <is>
-          <t>NSE stock slips below issue price of ₹1,785; down 2% on Monday</t>
+          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
         </is>
       </c>
       <c r="D62" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="E62" s="81" t="n">
-        <v>-0.34</v>
+        <v>-0.361</v>
       </c>
       <c r="F62" s="51" t="inlineStr">
         <is>
@@ -12281,21 +12281,21 @@
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:41</t>
+          <t>2026-09-28 04:42</t>
         </is>
       </c>
       <c r="C63" s="51" t="inlineStr">
         <is>
-          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
+          <t>NSE stock slips below issue price of ₹1,785; down 2% on Monday</t>
         </is>
       </c>
       <c r="D63" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E63" s="81" t="n">
-        <v>-0.758</v>
+        <v>-0.34</v>
       </c>
       <c r="F63" s="51" t="inlineStr">
         <is>
@@ -12316,25 +12316,25 @@
       </c>
       <c r="B64" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:29</t>
+          <t>2026-09-28 04:41</t>
         </is>
       </c>
       <c r="C64" s="51" t="inlineStr">
         <is>
-          <t>Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%</t>
+          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
         </is>
       </c>
       <c r="D64" s="51" t="inlineStr">
         <is>
-          <t>newsdrum.in</t>
+          <t>ndtv.com</t>
         </is>
       </c>
       <c r="E64" s="81" t="n">
-        <v>0</v>
+        <v>-0.758</v>
       </c>
       <c r="F64" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G64" s="82" t="inlineStr">
@@ -12351,25 +12351,25 @@
       </c>
       <c r="B65" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:25</t>
+          <t>2026-09-28 04:29</t>
         </is>
       </c>
       <c r="C65" s="51" t="inlineStr">
         <is>
-          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
+          <t>Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%</t>
         </is>
       </c>
       <c r="D65" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>newsdrum.in</t>
         </is>
       </c>
       <c r="E65" s="81" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="F65" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G65" s="82" t="inlineStr">
@@ -12386,21 +12386,21 @@
       </c>
       <c r="B66" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:17</t>
+          <t>2026-09-28 04:25</t>
         </is>
       </c>
       <c r="C66" s="51" t="inlineStr">
         <is>
-          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
+          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
         </is>
       </c>
       <c r="D66" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E66" s="81" t="n">
-        <v>-0.511</v>
+        <v>-0.34</v>
       </c>
       <c r="F66" s="51" t="inlineStr">
         <is>
@@ -12421,21 +12421,21 @@
       </c>
       <c r="B67" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:11</t>
+          <t>2026-09-28 04:17</t>
         </is>
       </c>
       <c r="C67" s="51" t="inlineStr">
         <is>
-          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
+          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
         </is>
       </c>
       <c r="D67" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E67" s="81" t="n">
-        <v>-0.586</v>
+        <v>-0.511</v>
       </c>
       <c r="F67" s="51" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
       </c>
       <c r="B68" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:08</t>
+          <t>2026-09-28 04:11</t>
         </is>
       </c>
       <c r="C68" s="51" t="inlineStr">
         <is>
-          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 lakh crore rout</t>
+          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
         </is>
       </c>
       <c r="D68" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E68" s="81" t="n">
-        <v>-0.649</v>
+        <v>-0.586</v>
       </c>
       <c r="F68" s="51" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
       </c>
       <c r="B69" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:07</t>
+          <t>2026-09-28 04:08</t>
         </is>
       </c>
       <c r="C69" s="51" t="inlineStr">
         <is>
-          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
+          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 lakh crore rout</t>
         </is>
       </c>
       <c r="D69" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E69" s="81" t="n">
-        <v>-0.44</v>
+        <v>-0.649</v>
       </c>
       <c r="F69" s="51" t="inlineStr">
         <is>
@@ -12521,30 +12521,30 @@
     <row r="70">
       <c r="A70" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B70" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 04:01</t>
+          <t>2026-09-28 04:07</t>
         </is>
       </c>
       <c r="C70" s="51" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines ESOP 2019 Share Allotment Explained</t>
+          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
         </is>
       </c>
       <c r="D70" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E70" s="81" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="F70" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G70" s="82" t="inlineStr">
@@ -12556,30 +12556,30 @@
     <row r="71">
       <c r="A71" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B71" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:58</t>
+          <t>2026-09-28 04:01</t>
         </is>
       </c>
       <c r="C71" s="51" t="inlineStr">
         <is>
-          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
+          <t>Kirloskar Oil Engines ESOP 2019 Share Allotment Explained</t>
         </is>
       </c>
       <c r="D71" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E71" s="81" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="F71" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G71" s="82" t="inlineStr">
@@ -12596,25 +12596,25 @@
       </c>
       <c r="B72" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:54</t>
+          <t>2026-09-28 03:58</t>
         </is>
       </c>
       <c r="C72" s="51" t="inlineStr">
         <is>
-          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
+          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
         </is>
       </c>
       <c r="D72" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E72" s="81" t="n">
-        <v>-0.494</v>
+        <v>0.296</v>
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G72" s="82" t="inlineStr">
@@ -12631,21 +12631,21 @@
       </c>
       <c r="B73" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:48</t>
+          <t>2026-09-28 03:54</t>
         </is>
       </c>
       <c r="C73" s="51" t="inlineStr">
         <is>
-          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
+          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
         </is>
       </c>
       <c r="D73" s="51" t="inlineStr">
         <is>
-          <t>hindustantimes.com</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E73" s="81" t="n">
-        <v>-0.44</v>
+        <v>-0.494</v>
       </c>
       <c r="F73" s="51" t="inlineStr">
         <is>
@@ -12666,25 +12666,25 @@
       </c>
       <c r="B74" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 03:28</t>
+          <t>2026-09-28 03:48</t>
         </is>
       </c>
       <c r="C74" s="51" t="inlineStr">
         <is>
-          <t>Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open</t>
+          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
         </is>
       </c>
       <c r="D74" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="E74" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.44</v>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G74" s="82" t="inlineStr">
@@ -12701,25 +12701,25 @@
       </c>
       <c r="B75" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 02:19</t>
+          <t>2026-09-28 03:28</t>
         </is>
       </c>
       <c r="C75" s="51" t="inlineStr">
         <is>
-          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
+          <t>Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open</t>
         </is>
       </c>
       <c r="D75" s="51" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E75" s="81" t="n">
-        <v>-0.542</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F75" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G75" s="82" t="inlineStr">
@@ -12736,25 +12736,25 @@
       </c>
       <c r="B76" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 01:58</t>
+          <t>2026-09-28 02:19</t>
         </is>
       </c>
       <c r="C76" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices — Five Key Factors For Sensex, Nifty 50 On September 28</t>
+          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
         </is>
       </c>
       <c r="D76" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E76" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.542</v>
       </c>
       <c r="F76" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G76" s="82" t="inlineStr">
@@ -12771,21 +12771,21 @@
       </c>
       <c r="B77" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 01:20</t>
+          <t>2026-09-28 01:58</t>
         </is>
       </c>
       <c r="C77" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
+          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices — Five Key Factors For Sensex, Nifty 50 On September 28</t>
         </is>
       </c>
       <c r="D77" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E77" s="81" t="n">
-        <v>0.842</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F77" s="51" t="inlineStr">
         <is>
@@ -12801,26 +12801,26 @@
     <row r="78">
       <c r="A78" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B78" s="51" t="inlineStr">
         <is>
-          <t>2026-09-28 00:30</t>
+          <t>2026-09-28 01:20</t>
         </is>
       </c>
       <c r="C78" s="51" t="inlineStr">
         <is>
-          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
         </is>
       </c>
       <c r="D78" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E78" s="81" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.842</v>
       </c>
       <c r="F78" s="51" t="inlineStr">
         <is>
@@ -12836,26 +12836,26 @@
     <row r="79">
       <c r="A79" s="51" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B79" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 17:20</t>
+          <t>2026-09-28 00:30</t>
         </is>
       </c>
       <c r="C79" s="51" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
+          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
         </is>
       </c>
       <c r="D79" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>equitymaster.com</t>
         </is>
       </c>
       <c r="E79" s="81" t="n">
-        <v>0.625</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F79" s="51" t="inlineStr">
         <is>
@@ -12871,30 +12871,30 @@
     <row r="80">
       <c r="A80" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B80" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 11:03</t>
+          <t>2026-09-27 17:20</t>
         </is>
       </c>
       <c r="C80" s="51" t="inlineStr">
         <is>
-          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
+          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
         </is>
       </c>
       <c r="D80" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E80" s="81" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="F80" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G80" s="82" t="inlineStr">
@@ -12911,25 +12911,25 @@
       </c>
       <c r="B81" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 09:48</t>
+          <t>2026-09-27 11:03</t>
         </is>
       </c>
       <c r="C81" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
+          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
         </is>
       </c>
       <c r="D81" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E81" s="81" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="F81" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G81" s="82" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="B82" s="51" t="inlineStr">
         <is>
-          <t>2026-09-27 04:22</t>
+          <t>2026-09-27 09:48</t>
         </is>
       </c>
       <c r="C82" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
+          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
         </is>
       </c>
       <c r="D82" s="51" t="inlineStr">
@@ -12960,11 +12960,11 @@
         </is>
       </c>
       <c r="E82" s="81" t="n">
-        <v>0.842</v>
+        <v>-0.44</v>
       </c>
       <c r="F82" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G82" s="82" t="inlineStr">
@@ -12976,30 +12976,30 @@
     <row r="83">
       <c r="A83" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B83" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 22:56</t>
+          <t>2026-09-27 04:22</t>
         </is>
       </c>
       <c r="C83" s="51" t="inlineStr">
         <is>
-          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
+          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
         </is>
       </c>
       <c r="D83" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E83" s="81" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="F83" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G83" s="82" t="inlineStr">
@@ -13011,30 +13011,30 @@
     <row r="84">
       <c r="A84" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B84" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 13:51</t>
+          <t>2026-09-26 22:56</t>
         </is>
       </c>
       <c r="C84" s="51" t="inlineStr">
         <is>
-          <t>🚦 Indian Markets Stuck In A Jam! But who's responsible for the traffic? 🤔 A Bernstein note argues that India’s large caps are stuck in a bygone economic era. But here's the BIG question: 🇮🇳 Is The Market’s Fate Really In India’s Hands? 🌍 Or are global cues pul</t>
+          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
         </is>
       </c>
       <c r="D84" s="51" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E84" s="81" t="n">
-        <v>-0.625</v>
+        <v>0</v>
       </c>
       <c r="F84" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G84" s="82" t="inlineStr">
@@ -13051,25 +13051,25 @@
       </c>
       <c r="B85" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 12:11</t>
+          <t>2026-09-26 13:51</t>
         </is>
       </c>
       <c r="C85" s="51" t="inlineStr">
         <is>
-          <t>Share Market News: Nifty 50 Outlook &amp; Prediction</t>
+          <t>🚦 Indian Markets Stuck In A Jam! But who's responsible for the traffic? 🤔 A Bernstein note argues that India’s large caps are stuck in a bygone economic era. But here's the BIG question: 🇮🇳 Is The Market’s Fate Really In India’s Hands? 🌍 Or are global cues pul</t>
         </is>
       </c>
       <c r="D85" s="51" t="inlineStr">
         <is>
-          <t>Liquide Blog</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E85" s="81" t="n">
-        <v>0.402</v>
+        <v>-0.625</v>
       </c>
       <c r="F85" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G85" s="82" t="inlineStr">
@@ -13086,25 +13086,25 @@
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 09:15</t>
+          <t>2026-09-26 12:11</t>
         </is>
       </c>
       <c r="C86" s="51" t="inlineStr">
         <is>
-          <t>Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide</t>
+          <t>Share Market News: Nifty 50 Outlook &amp; Prediction</t>
         </is>
       </c>
       <c r="D86" s="51" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>Liquide Blog</t>
         </is>
       </c>
       <c r="E86" s="81" t="n">
-        <v>-0.128</v>
+        <v>0.402</v>
       </c>
       <c r="F86" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G86" s="82" t="inlineStr">
@@ -13116,26 +13116,26 @@
     <row r="87">
       <c r="A87" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B87" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 06:30</t>
+          <t>2026-09-26 09:15</t>
         </is>
       </c>
       <c r="C87" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
+          <t>Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide</t>
         </is>
       </c>
       <c r="D87" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="E87" s="81" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="F87" s="51" t="inlineStr">
         <is>
@@ -13151,30 +13151,30 @@
     <row r="88">
       <c r="A88" s="51" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B88" s="51" t="inlineStr">
         <is>
-          <t>2026-09-26 00:50</t>
+          <t>2026-09-26 06:30</t>
         </is>
       </c>
       <c r="C88" s="51" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
+          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
         </is>
       </c>
       <c r="D88" s="51" t="inlineStr">
         <is>
-          <t>Alice Blue</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E88" s="81" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="F88" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G88" s="82" t="inlineStr">
@@ -13186,30 +13186,30 @@
     <row r="89">
       <c r="A89" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B89" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 14:34</t>
+          <t>2026-09-26 00:50</t>
         </is>
       </c>
       <c r="C89" s="51" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
+          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
         </is>
       </c>
       <c r="D89" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Alice Blue</t>
         </is>
       </c>
       <c r="E89" s="81" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="F89" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G89" s="82" t="inlineStr">
@@ -13221,22 +13221,22 @@
     <row r="90">
       <c r="A90" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B90" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 14:31</t>
+          <t>2026-09-25 14:34</t>
         </is>
       </c>
       <c r="C90" s="51" t="inlineStr">
         <is>
-          <t>PERSISTENT Stock Price and Chart — NSE:PERSISTENT</t>
+          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
         </is>
       </c>
       <c r="D90" s="51" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E90" s="81" t="n">
@@ -13256,30 +13256,30 @@
     <row r="91">
       <c r="A91" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B91" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 14:04</t>
+          <t>2026-09-25 14:31</t>
         </is>
       </c>
       <c r="C91" s="51" t="inlineStr">
         <is>
-          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
+          <t>PERSISTENT Stock Price and Chart — NSE:PERSISTENT</t>
         </is>
       </c>
       <c r="D91" s="51" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="E91" s="81" t="n">
-        <v>0.681</v>
+        <v>0</v>
       </c>
       <c r="F91" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G91" s="82" t="inlineStr">
@@ -13291,30 +13291,30 @@
     <row r="92">
       <c r="A92" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B92" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 12:52</t>
+          <t>2026-09-25 14:04</t>
         </is>
       </c>
       <c r="C92" s="51" t="inlineStr">
         <is>
-          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
+          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
         </is>
       </c>
       <c r="D92" s="51" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E92" s="81" t="n">
-        <v>-0.382</v>
+        <v>0.681</v>
       </c>
       <c r="F92" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G92" s="82" t="inlineStr">
@@ -13326,30 +13326,30 @@
     <row r="93">
       <c r="A93" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B93" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 12:22</t>
+          <t>2026-09-25 12:52</t>
         </is>
       </c>
       <c r="C93" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
+          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
         </is>
       </c>
       <c r="D93" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E93" s="81" t="n">
-        <v>0</v>
+        <v>-0.382</v>
       </c>
       <c r="F93" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G93" s="82" t="inlineStr">
@@ -13361,30 +13361,30 @@
     <row r="94">
       <c r="A94" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B94" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:56</t>
+          <t>2026-09-25 12:22</t>
         </is>
       </c>
       <c r="C94" s="51" t="inlineStr">
         <is>
-          <t>Two years ago Sensex hit lifetime high: What went wrong after that &amp; what’s the road ahead?</t>
+          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
         </is>
       </c>
       <c r="D94" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E94" s="81" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="F94" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G94" s="82" t="inlineStr">
@@ -13396,30 +13396,30 @@
     <row r="95">
       <c r="A95" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B95" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:42</t>
+          <t>2026-09-25 11:56</t>
         </is>
       </c>
       <c r="C95" s="51" t="inlineStr">
         <is>
-          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
+          <t>Two years ago Sensex hit lifetime high: What went wrong after that &amp; what’s the road ahead?</t>
         </is>
       </c>
       <c r="D95" s="51" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E95" s="81" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="F95" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G95" s="82" t="inlineStr">
@@ -13431,30 +13431,30 @@
     <row r="96">
       <c r="A96" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B96" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:22</t>
+          <t>2026-09-25 11:42</t>
         </is>
       </c>
       <c r="C96" s="51" t="inlineStr">
         <is>
-          <t>Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points</t>
+          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
         </is>
       </c>
       <c r="D96" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="E96" s="81" t="n">
-        <v>0.612</v>
+        <v>0</v>
       </c>
       <c r="F96" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G96" s="82" t="inlineStr">
@@ -13471,21 +13471,21 @@
       </c>
       <c r="B97" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 11:03</t>
+          <t>2026-09-25 11:22</t>
         </is>
       </c>
       <c r="C97" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%</t>
+          <t>Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points</t>
         </is>
       </c>
       <c r="D97" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>rediff.com</t>
         </is>
       </c>
       <c r="E97" s="81" t="n">
-        <v>0.402</v>
+        <v>0.612</v>
       </c>
       <c r="F97" s="51" t="inlineStr">
         <is>
@@ -13506,21 +13506,21 @@
       </c>
       <c r="B98" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 10:48</t>
+          <t>2026-09-25 11:03</t>
         </is>
       </c>
       <c r="C98" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rebound on Value Buying After Sharp Losses</t>
+          <t>Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%</t>
         </is>
       </c>
       <c r="D98" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>equitymaster.com</t>
         </is>
       </c>
       <c r="E98" s="81" t="n">
-        <v>0.318</v>
+        <v>0.402</v>
       </c>
       <c r="F98" s="51" t="inlineStr">
         <is>
@@ -13536,26 +13536,26 @@
     <row r="99">
       <c r="A99" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B99" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 10:31</t>
+          <t>2026-09-25 10:48</t>
         </is>
       </c>
       <c r="C99" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date</t>
+          <t>Sensex, Nifty Rebound on Value Buying After Sharp Losses</t>
         </is>
       </c>
       <c r="D99" s="51" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="E99" s="81" t="n">
-        <v>0.572</v>
+        <v>0.318</v>
       </c>
       <c r="F99" s="51" t="inlineStr">
         <is>
@@ -13571,30 +13571,30 @@
     <row r="100">
       <c r="A100" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B100" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 07:00</t>
+          <t>2026-09-25 10:31</t>
         </is>
       </c>
       <c r="C100" s="51" t="inlineStr">
         <is>
-          <t>Sah Polymers Share Price</t>
+          <t>Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date</t>
         </is>
       </c>
       <c r="D100" s="51" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>indmoney.com</t>
         </is>
       </c>
       <c r="E100" s="81" t="n">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="F100" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G100" s="82" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="101">
       <c r="A101" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B101" s="51" t="inlineStr">
@@ -13616,20 +13616,20 @@
       </c>
       <c r="C101" s="51" t="inlineStr">
         <is>
-          <t>Nifty Chemicals (NFTCHEMIC) Share Price</t>
+          <t>Sah Polymers Share Price</t>
         </is>
       </c>
       <c r="D101" s="51" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E101" s="81" t="n">
-        <v>0.402</v>
+        <v>0</v>
       </c>
       <c r="F101" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G101" s="82" t="inlineStr">
@@ -13641,30 +13641,30 @@
     <row r="102">
       <c r="A102" s="51" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B102" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 06:49</t>
+          <t>2026-09-25 07:00</t>
         </is>
       </c>
       <c r="C102" s="51" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today</t>
+          <t>Nifty Chemicals (NFTCHEMIC) Share Price</t>
         </is>
       </c>
       <c r="D102" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="E102" s="81" t="n">
-        <v>-0.052</v>
+        <v>0.402</v>
       </c>
       <c r="F102" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G102" s="82" t="inlineStr">
@@ -13676,26 +13676,26 @@
     <row r="103">
       <c r="A103" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B103" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 06:34</t>
+          <t>2026-09-25 06:49</t>
         </is>
       </c>
       <c r="C103" s="51" t="inlineStr">
         <is>
-          <t>Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore</t>
+          <t>Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today</t>
         </is>
       </c>
       <c r="D103" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E103" s="81" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="F103" s="51" t="inlineStr">
         <is>
@@ -13711,30 +13711,30 @@
     <row r="104">
       <c r="A104" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B104" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 05:52</t>
+          <t>2026-09-25 06:34</t>
         </is>
       </c>
       <c r="C104" s="51" t="inlineStr">
         <is>
-          <t>Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons</t>
+          <t>Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore</t>
         </is>
       </c>
       <c r="D104" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E104" s="81" t="n">
-        <v>0.727</v>
+        <v>0</v>
       </c>
       <c r="F104" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G104" s="82" t="inlineStr">
@@ -13751,21 +13751,21 @@
       </c>
       <c r="B105" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 05:32</t>
+          <t>2026-09-25 05:52</t>
         </is>
       </c>
       <c r="C105" s="51" t="inlineStr">
         <is>
-          <t>NSE shares dip on day 2 of listing, brokerages back long-term growth story</t>
+          <t>Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons</t>
         </is>
       </c>
       <c r="D105" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E105" s="81" t="n">
-        <v>0.361</v>
+        <v>0.727</v>
       </c>
       <c r="F105" s="51" t="inlineStr">
         <is>
@@ -13786,25 +13786,25 @@
       </c>
       <c r="B106" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 03:51</t>
+          <t>2026-09-25 05:32</t>
         </is>
       </c>
       <c r="C106" s="51" t="inlineStr">
         <is>
-          <t>Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050</t>
+          <t>NSE shares dip on day 2 of listing, brokerages back long-term growth story</t>
         </is>
       </c>
       <c r="D106" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E106" s="81" t="n">
-        <v>-0.494</v>
+        <v>0.361</v>
       </c>
       <c r="F106" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G106" s="82" t="inlineStr">
@@ -13816,30 +13816,30 @@
     <row r="107">
       <c r="A107" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B107" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 02:49</t>
+          <t>2026-09-25 03:51</t>
         </is>
       </c>
       <c r="C107" s="51" t="inlineStr">
         <is>
-          <t>Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others</t>
+          <t>Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050</t>
         </is>
       </c>
       <c r="D107" s="51" t="inlineStr">
         <is>
-          <t>ET Now</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E107" s="81" t="n">
-        <v>-0.052</v>
+        <v>-0.494</v>
       </c>
       <c r="F107" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G107" s="82" t="inlineStr">
@@ -13851,26 +13851,26 @@
     <row r="108">
       <c r="A108" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B108" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 02:06</t>
+          <t>2026-09-25 02:49</t>
         </is>
       </c>
       <c r="C108" s="51" t="inlineStr">
         <is>
-          <t>Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...</t>
+          <t>Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others</t>
         </is>
       </c>
       <c r="D108" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>etnownews.com</t>
         </is>
       </c>
       <c r="E108" s="81" t="n">
-        <v>0.178</v>
+        <v>-0.052</v>
       </c>
       <c r="F108" s="51" t="inlineStr">
         <is>
@@ -13886,30 +13886,30 @@
     <row r="109">
       <c r="A109" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B109" s="51" t="inlineStr">
         <is>
-          <t>2026-09-25 01:28</t>
+          <t>2026-09-25 02:06</t>
         </is>
       </c>
       <c r="C109" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Bond Yields To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On September 25</t>
+          <t>Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...</t>
         </is>
       </c>
       <c r="D109" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E109" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.178</v>
       </c>
       <c r="F109" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G109" s="82" t="inlineStr">
@@ -13921,30 +13921,30 @@
     <row r="110">
       <c r="A110" s="51" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B110" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-25 01:28</t>
         </is>
       </c>
       <c r="C110" s="51" t="inlineStr">
         <is>
-          <t>R R Kabel executes BTA to acquire U M Cables business for ₹77 crore</t>
+          <t>Stock Market Today: Gift Nifty, Bond Yields To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On September 25</t>
         </is>
       </c>
       <c r="D110" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E110" s="81" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F110" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G110" s="82" t="inlineStr">
@@ -13961,25 +13961,25 @@
       </c>
       <c r="B111" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 16:04</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
       <c r="C111" s="51" t="inlineStr">
         <is>
-          <t>Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets</t>
+          <t>R R Kabel executes BTA to acquire U M Cables business for ₹77 crore</t>
         </is>
       </c>
       <c r="D111" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E111" s="81" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F111" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G111" s="82" t="inlineStr">
@@ -13991,26 +13991,26 @@
     <row r="112">
       <c r="A112" s="51" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B112" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 14:42</t>
+          <t>2026-09-24 16:04</t>
         </is>
       </c>
       <c r="C112" s="51" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics</t>
+          <t>Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets</t>
         </is>
       </c>
       <c r="D112" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E112" s="81" t="n">
-        <v>0.382</v>
+        <v>0.7</v>
       </c>
       <c r="F112" s="51" t="inlineStr">
         <is>
@@ -14026,30 +14026,30 @@
     <row r="113">
       <c r="A113" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B113" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 13:49</t>
+          <t>2026-09-24 14:42</t>
         </is>
       </c>
       <c r="C113" s="51" t="inlineStr">
         <is>
-          <t>Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month</t>
+          <t>Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics</t>
         </is>
       </c>
       <c r="D113" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E113" s="81" t="n">
-        <v>-0.153</v>
+        <v>0.382</v>
       </c>
       <c r="F113" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G113" s="82" t="inlineStr">
@@ -14061,30 +14061,30 @@
     <row r="114">
       <c r="A114" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B114" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 13:15</t>
+          <t>2026-09-24 13:49</t>
         </is>
       </c>
       <c r="C114" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team</t>
+          <t>Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month</t>
         </is>
       </c>
       <c r="D114" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E114" s="81" t="n">
-        <v>0.318</v>
+        <v>-0.153</v>
       </c>
       <c r="F114" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G114" s="82" t="inlineStr">
@@ -14096,30 +14096,30 @@
     <row r="115">
       <c r="A115" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B115" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 13:01</t>
+          <t>2026-09-24 13:15</t>
         </is>
       </c>
       <c r="C115" s="51" t="inlineStr">
         <is>
-          <t>3 Indian Export Stocks That Could Benefit From A Weaker Rupee</t>
+          <t>E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team</t>
         </is>
       </c>
       <c r="D115" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E115" s="81" t="n">
-        <v>0.026</v>
+        <v>0.318</v>
       </c>
       <c r="F115" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G115" s="82" t="inlineStr">
@@ -14131,30 +14131,30 @@
     <row r="116">
       <c r="A116" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B116" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 12:36</t>
+          <t>2026-09-24 13:01</t>
         </is>
       </c>
       <c r="C116" s="51" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026</t>
+          <t>3 Indian Export Stocks That Could Benefit From A Weaker Rupee</t>
         </is>
       </c>
       <c r="D116" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E116" s="81" t="n">
-        <v>0.402</v>
+        <v>0.026</v>
       </c>
       <c r="F116" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G116" s="82" t="inlineStr">
@@ -14171,25 +14171,25 @@
       </c>
       <c r="B117" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-24 12:36</t>
         </is>
       </c>
       <c r="C117" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty see worst day in weeks: Why was market down today? | Business News</t>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026</t>
         </is>
       </c>
       <c r="D117" s="51" t="inlineStr">
         <is>
-          <t>hindustantimes.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E117" s="81" t="n">
-        <v>-0.34</v>
+        <v>0.402</v>
       </c>
       <c r="F117" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G117" s="82" t="inlineStr">
@@ -14201,30 +14201,30 @@
     <row r="118">
       <c r="A118" s="51" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B118" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 10:15</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="C118" s="51" t="inlineStr">
         <is>
-          <t>TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026</t>
+          <t>Sensex, Nifty see worst day in weeks: Why was market down today? | Business News</t>
         </is>
       </c>
       <c r="D118" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="E118" s="81" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F118" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G118" s="82" t="inlineStr">
@@ -14236,22 +14236,22 @@
     <row r="119">
       <c r="A119" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B119" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
+          <t>2026-09-24 10:15</t>
         </is>
       </c>
       <c r="C119" s="51" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks</t>
+          <t>TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026</t>
         </is>
       </c>
       <c r="D119" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E119" s="81" t="n">
@@ -14271,30 +14271,30 @@
     <row r="120">
       <c r="A120" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B120" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 09:42</t>
+          <t>2026-09-24 10:00</t>
         </is>
       </c>
       <c r="C120" s="51" t="inlineStr">
         <is>
-          <t>The battle between India’s stock exchanges is heating up again</t>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks</t>
         </is>
       </c>
       <c r="D120" s="51" t="inlineStr">
         <is>
-          <t>The Economist</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E120" s="81" t="n">
-        <v>-0.382</v>
+        <v>0</v>
       </c>
       <c r="F120" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G120" s="82" t="inlineStr">
@@ -14311,21 +14311,21 @@
       </c>
       <c r="B121" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 09:40</t>
+          <t>2026-09-24 09:42</t>
         </is>
       </c>
       <c r="C121" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss</t>
+          <t>The battle between India’s stock exchanges is heating up again</t>
         </is>
       </c>
       <c r="D121" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>The Economist</t>
         </is>
       </c>
       <c r="E121" s="81" t="n">
-        <v>-0.758</v>
+        <v>-0.382</v>
       </c>
       <c r="F121" s="51" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
       </c>
       <c r="B122" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 09:08</t>
+          <t>2026-09-24 09:40</t>
         </is>
       </c>
       <c r="C122" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday</t>
+          <t>Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss</t>
         </is>
       </c>
       <c r="D122" s="51" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E122" s="81" t="n">
-        <v>-0.273</v>
+        <v>-0.758</v>
       </c>
       <c r="F122" s="51" t="inlineStr">
         <is>
@@ -14381,21 +14381,21 @@
       </c>
       <c r="B123" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 09:02</t>
+          <t>2026-09-24 09:08</t>
         </is>
       </c>
       <c r="C123" s="51" t="inlineStr">
         <is>
-          <t>Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today</t>
+          <t>Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday</t>
         </is>
       </c>
       <c r="D123" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="E123" s="81" t="n">
-        <v>-0.402</v>
+        <v>-0.273</v>
       </c>
       <c r="F123" s="51" t="inlineStr">
         <is>
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B124" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:52</t>
+          <t>2026-09-24 09:02</t>
         </is>
       </c>
       <c r="C124" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall</t>
+          <t>Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today</t>
         </is>
       </c>
       <c r="D124" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>ndtv.com</t>
         </is>
       </c>
       <c r="E124" s="81" t="n">
@@ -14446,30 +14446,30 @@
     <row r="125">
       <c r="A125" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B125" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:46</t>
+          <t>2026-09-24 08:52</t>
         </is>
       </c>
       <c r="C125" s="51" t="inlineStr">
         <is>
-          <t>Hero Motors Ltd leads gainers in 'B' group</t>
+          <t>Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall</t>
         </is>
       </c>
       <c r="D125" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E125" s="81" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.402</v>
       </c>
       <c r="F125" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G125" s="82" t="inlineStr">
@@ -14481,30 +14481,30 @@
     <row r="126">
       <c r="A126" s="51" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B126" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:35</t>
+          <t>2026-09-24 08:46</t>
         </is>
       </c>
       <c r="C126" s="51" t="inlineStr">
         <is>
-          <t>TD Power Systems Share Price today: decline and analysis</t>
+          <t>Hero Motors Ltd leads gainers in 'B' group</t>
         </is>
       </c>
       <c r="D126" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E126" s="81" t="n">
-        <v>-0.382</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F126" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G126" s="82" t="inlineStr">
@@ -14516,30 +14516,30 @@
     <row r="127">
       <c r="A127" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B127" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:21</t>
+          <t>2026-09-24 08:35</t>
         </is>
       </c>
       <c r="C127" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer</t>
+          <t>TD Power Systems Share Price today: decline and analysis</t>
         </is>
       </c>
       <c r="D127" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E127" s="81" t="n">
-        <v>0</v>
+        <v>-0.382</v>
       </c>
       <c r="F127" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G127" s="82" t="inlineStr">
@@ -14551,26 +14551,26 @@
     <row r="128">
       <c r="A128" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B128" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 07:35</t>
+          <t>2026-09-24 08:21</t>
         </is>
       </c>
       <c r="C128" s="51" t="inlineStr">
         <is>
-          <t>Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices</t>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer</t>
         </is>
       </c>
       <c r="D128" s="51" t="inlineStr">
         <is>
-          <t>theweek.in</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E128" s="81" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="F128" s="51" t="inlineStr">
         <is>
@@ -14586,30 +14586,30 @@
     <row r="129">
       <c r="A129" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B129" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 07:25</t>
+          <t>2026-09-24 07:35</t>
         </is>
       </c>
       <c r="C129" s="51" t="inlineStr">
         <is>
-          <t>Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom — Ask Profit</t>
+          <t>Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices</t>
         </is>
       </c>
       <c r="D129" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>theweek.in</t>
         </is>
       </c>
       <c r="E129" s="81" t="n">
-        <v>0.296</v>
+        <v>0.077</v>
       </c>
       <c r="F129" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G129" s="82" t="inlineStr">
@@ -14621,26 +14621,26 @@
     <row r="130">
       <c r="A130" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B130" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 06:20</t>
+          <t>2026-09-24 07:25</t>
         </is>
       </c>
       <c r="C130" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest</t>
+          <t>Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom — Ask Profit</t>
         </is>
       </c>
       <c r="D130" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E130" s="81" t="n">
-        <v>0.681</v>
+        <v>0.296</v>
       </c>
       <c r="F130" s="51" t="inlineStr">
         <is>
@@ -14656,30 +14656,30 @@
     <row r="131">
       <c r="A131" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B131" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 04:09</t>
+          <t>2026-09-24 06:20</t>
         </is>
       </c>
       <c r="C131" s="51" t="inlineStr">
         <is>
-          <t>Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'</t>
+          <t>Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest</t>
         </is>
       </c>
       <c r="D131" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E131" s="81" t="n">
-        <v>-0.273</v>
+        <v>0.681</v>
       </c>
       <c r="F131" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G131" s="82" t="inlineStr">
@@ -14696,21 +14696,21 @@
       </c>
       <c r="B132" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 03:56</t>
+          <t>2026-09-24 04:09</t>
         </is>
       </c>
       <c r="C132" s="51" t="inlineStr">
         <is>
-          <t>Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash</t>
+          <t>Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'</t>
         </is>
       </c>
       <c r="D132" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E132" s="81" t="n">
-        <v>-0.44</v>
+        <v>-0.273</v>
       </c>
       <c r="F132" s="51" t="inlineStr">
         <is>
@@ -14731,21 +14731,21 @@
       </c>
       <c r="B133" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 02:46</t>
+          <t>2026-09-24 03:56</t>
         </is>
       </c>
       <c r="C133" s="51" t="inlineStr">
         <is>
-          <t>Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs</t>
+          <t>Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash</t>
         </is>
       </c>
       <c r="D133" s="51" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E133" s="81" t="n">
-        <v>-0.625</v>
+        <v>-0.44</v>
       </c>
       <c r="F133" s="51" t="inlineStr">
         <is>
@@ -14766,25 +14766,25 @@
       </c>
       <c r="B134" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 02:44</t>
+          <t>2026-09-24 02:46</t>
         </is>
       </c>
       <c r="C134" s="51" t="inlineStr">
         <is>
-          <t>US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact</t>
+          <t>Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs</t>
         </is>
       </c>
       <c r="D134" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E134" s="81" t="n">
-        <v>0.758</v>
+        <v>-0.625</v>
       </c>
       <c r="F134" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G134" s="82" t="inlineStr">
@@ -14801,21 +14801,21 @@
       </c>
       <c r="B135" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 02:38</t>
+          <t>2026-09-24 02:44</t>
         </is>
       </c>
       <c r="C135" s="51" t="inlineStr">
         <is>
-          <t>GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...</t>
+          <t>US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact</t>
         </is>
       </c>
       <c r="D135" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E135" s="81" t="n">
-        <v>0.842</v>
+        <v>0.758</v>
       </c>
       <c r="F135" s="51" t="inlineStr">
         <is>
@@ -14836,21 +14836,21 @@
       </c>
       <c r="B136" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 01:42</t>
+          <t>2026-09-24 02:38</t>
         </is>
       </c>
       <c r="C136" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields — Five Key Factors For Sensex, Nifty 50 On Sept 24</t>
+          <t>GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...</t>
         </is>
       </c>
       <c r="D136" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E136" s="81" t="n">
-        <v>0.844</v>
+        <v>0.842</v>
       </c>
       <c r="F136" s="51" t="inlineStr">
         <is>
@@ -14871,21 +14871,21 @@
       </c>
       <c r="B137" s="51" t="inlineStr">
         <is>
-          <t>2026-09-24 01:17</t>
+          <t>2026-09-24 01:42</t>
         </is>
       </c>
       <c r="C137" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals</t>
+          <t>Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields — Five Key Factors For Sensex, Nifty 50 On Sept 24</t>
         </is>
       </c>
       <c r="D137" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E137" s="81" t="n">
-        <v>0.842</v>
+        <v>0.844</v>
       </c>
       <c r="F137" s="51" t="inlineStr">
         <is>
@@ -14901,26 +14901,26 @@
     <row r="138">
       <c r="A138" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B138" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 22:57</t>
+          <t>2026-09-24 01:17</t>
         </is>
       </c>
       <c r="C138" s="51" t="inlineStr">
         <is>
-          <t>Laurus Labs stock gains 1.37 percent as profit jumps 126 percent</t>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals</t>
         </is>
       </c>
       <c r="D138" s="51" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E138" s="81" t="n">
-        <v>0.791</v>
+        <v>0.842</v>
       </c>
       <c r="F138" s="51" t="inlineStr">
         <is>
@@ -14941,25 +14941,25 @@
       </c>
       <c r="B139" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 12:57</t>
+          <t>2026-09-23 22:57</t>
         </is>
       </c>
       <c r="C139" s="51" t="inlineStr">
         <is>
-          <t>Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month</t>
+          <t>Laurus Labs stock gains 1.37 percent as profit jumps 126 percent</t>
         </is>
       </c>
       <c r="D139" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="E139" s="81" t="n">
-        <v>0</v>
+        <v>0.791</v>
       </c>
       <c r="F139" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G139" s="82" t="inlineStr">
@@ -14971,30 +14971,30 @@
     <row r="140">
       <c r="A140" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B140" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 11:16</t>
+          <t>2026-09-23 12:57</t>
         </is>
       </c>
       <c r="C140" s="51" t="inlineStr">
         <is>
-          <t>Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market</t>
+          <t>Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month</t>
         </is>
       </c>
       <c r="D140" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E140" s="81" t="n">
-        <v>0.226</v>
+        <v>0</v>
       </c>
       <c r="F140" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G140" s="82" t="inlineStr">
@@ -15011,21 +15011,21 @@
       </c>
       <c r="B141" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 10:15</t>
+          <t>2026-09-23 11:16</t>
         </is>
       </c>
       <c r="C141" s="51" t="inlineStr">
         <is>
-          <t>Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers</t>
+          <t>Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market</t>
         </is>
       </c>
       <c r="D141" s="51" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E141" s="81" t="n">
-        <v>0.612</v>
+        <v>0.226</v>
       </c>
       <c r="F141" s="51" t="inlineStr">
         <is>
@@ -15041,26 +15041,26 @@
     <row r="142">
       <c r="A142" s="51" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B142" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 10:02</t>
+          <t>2026-09-23 10:15</t>
         </is>
       </c>
       <c r="C142" s="51" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure Share Price Rises 2.68% Today</t>
+          <t>Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers</t>
         </is>
       </c>
       <c r="D142" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E142" s="81" t="n">
-        <v>0.34</v>
+        <v>0.612</v>
       </c>
       <c r="F142" s="51" t="inlineStr">
         <is>
@@ -15076,17 +15076,17 @@
     <row r="143">
       <c r="A143" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B143" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 09:19</t>
+          <t>2026-09-23 10:02</t>
         </is>
       </c>
       <c r="C143" s="51" t="inlineStr">
         <is>
-          <t>Laurus Labs Share Price: one-year high and valuation view</t>
+          <t>Diamond Power Infrastructure Share Price Rises 2.68% Today</t>
         </is>
       </c>
       <c r="D143" s="51" t="inlineStr">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="E143" s="81" t="n">
-        <v>0.202</v>
+        <v>0.34</v>
       </c>
       <c r="F143" s="51" t="inlineStr">
         <is>
@@ -15111,30 +15111,30 @@
     <row r="144">
       <c r="A144" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B144" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 07:59</t>
+          <t>2026-09-23 09:19</t>
         </is>
       </c>
       <c r="C144" s="51" t="inlineStr">
         <is>
-          <t>NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details</t>
+          <t>Laurus Labs Share Price: one-year high and valuation view</t>
         </is>
       </c>
       <c r="D144" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E144" s="81" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="F144" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G144" s="82" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="145">
       <c r="A145" s="51" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B145" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 07:26</t>
+          <t>2026-09-23 07:59</t>
         </is>
       </c>
       <c r="C145" s="51" t="inlineStr">
         <is>
-          <t>E2E Networks Share Price news: price rise and valuation</t>
+          <t>NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details</t>
         </is>
       </c>
       <c r="D145" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E145" s="81" t="n">
@@ -15181,22 +15181,22 @@
     <row r="146">
       <c r="A146" s="51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B146" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 06:24</t>
+          <t>2026-09-23 07:26</t>
         </is>
       </c>
       <c r="C146" s="51" t="inlineStr">
         <is>
-          <t>Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings</t>
+          <t>E2E Networks Share Price news: price rise and valuation</t>
         </is>
       </c>
       <c r="D146" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E146" s="81" t="n">
@@ -15216,30 +15216,30 @@
     <row r="147">
       <c r="A147" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B147" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 05:56</t>
+          <t>2026-09-23 06:24</t>
         </is>
       </c>
       <c r="C147" s="51" t="inlineStr">
         <is>
-          <t>3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%</t>
+          <t>Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings</t>
         </is>
       </c>
       <c r="D147" s="51" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E147" s="81" t="n">
-        <v>0.5570000000000001</v>
+        <v>0</v>
       </c>
       <c r="F147" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G147" s="82" t="inlineStr">
@@ -15251,26 +15251,26 @@
     <row r="148">
       <c r="A148" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B148" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 01:42</t>
+          <t>2026-09-23 05:56</t>
         </is>
       </c>
       <c r="C148" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23</t>
+          <t>3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%</t>
         </is>
       </c>
       <c r="D148" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E148" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F148" s="51" t="inlineStr">
         <is>
@@ -15291,21 +15291,21 @@
       </c>
       <c r="B149" s="51" t="inlineStr">
         <is>
-          <t>2026-09-23 01:13</t>
+          <t>2026-09-23 01:42</t>
         </is>
       </c>
       <c r="C149" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal</t>
+          <t>Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices — Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23</t>
         </is>
       </c>
       <c r="D149" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E149" s="81" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F149" s="51" t="inlineStr">
         <is>
@@ -15321,33 +15321,68 @@
     <row r="150">
       <c r="A150" s="51" t="inlineStr">
         <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B150" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-23 01:13</t>
+        </is>
+      </c>
+      <c r="C150" s="51" t="inlineStr">
+        <is>
+          <t>Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal</t>
+        </is>
+      </c>
+      <c r="D150" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E150" s="81" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F150" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G150" s="82" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="51" t="inlineStr">
+        <is>
           <t>RRKABEL</t>
         </is>
       </c>
-      <c r="B150" s="51" t="inlineStr">
+      <c r="B151" s="51" t="inlineStr">
         <is>
           <t>2026-09-23 00:46</t>
         </is>
       </c>
-      <c r="C150" s="51" t="inlineStr">
+      <c r="C151" s="51" t="inlineStr">
         <is>
           <t>Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors</t>
         </is>
       </c>
-      <c r="D150" s="51" t="inlineStr">
+      <c r="D151" s="51" t="inlineStr">
         <is>
           <t>simplywall.st</t>
         </is>
       </c>
-      <c r="E150" s="81" t="n">
+      <c r="E151" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="F150" s="51" t="inlineStr">
+      <c r="F151" s="51" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G150" s="82" t="inlineStr">
+      <c r="G151" s="82" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -15358,7 +15393,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E150">
+  <conditionalFormatting sqref="E5:E151">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1"/>
@@ -15517,6 +15552,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -15543,35 +15579,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-29": {"open": 1460.2, "close": 1407.0, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-09-28": {"open": 5100.0, "close": 5011.5, "src": "yahoo"}, "2026-09-29": {"open": 5010.0, "close": 5204.5, "src": "bhavcopy"}}, "RRKABEL": {"2026-09-28": {"open": 2530.4, "close": 2459.8, "src": "yahoo"}, "2026-09-29": {"open": 2459.8, "close": 2523.2, "src": "bhavcopy"}}, "ACUTAAS": {"2026-09-28": {"open": 3272.5, "close": 3214.4, "src": "yahoo"}, "2026-09-29": {"open": 3290.0, "close": 3304.1, "src": "bhavcopy"}}, "DIACABS": {"2026-09-28": {"open": 353.0, "close": 339.25, "src": "yahoo"}, "2026-09-29": {"open": 336.9, "close": 352.05, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-09-28": {"open": 2138.1, "close": 2141.2, "src": "yahoo"}, "2026-09-29": {"open": 2141.2, "close": 2402.0, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 18:13", "days": 7, "items": [{"symbol": "MARKET", "title": "Sensex, Nifty End Lower for Second Day; Global Tensions, FII Selling Hurt Investor Mood", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxNOC0wWWx3dmhaeFRrNDNBUU8zLUxRMDdKSXNURGVXT09GdFJQbGlOR2pOeXdmTHlVMzViVWpVcFJrSmtGbktLUWlESkNzWGJwTlNERW00Y0hWVmR5dUxIV1AzNl9YeXFIZTR1WGRRZlp3RTVyMUR5Wmw0d0xWYWg2ME9Yc2Z3NlBibjR0S1NiV1l5d080TWxvQmpPVVVRMHA2VlNUM1oycTlZcG5CSlh4amFn?oc=5", "source": "The Indian Awaaz", "published": "2026-09-29 15:41", "score": -0.637, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets ride expiry-day seesaw as derivatives swings jolt Nifty", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxOX2lHWmtSZUZtUnhORjFzUGQweW5Ca1F2VDdRdVhDaHd3OF83Q1hvY09NMU5NY1JzQ1Z3MU1hRmVHVkppOHJxTXBYeE1aOFh2MUZEejFaNV9yWVNmNFRtRDJXN0xic1JiVGtaY25JTWZVTFh0bzRCZnVud29LQ1pkR2tIeVF1amxrZElwZTNNdW5IV0drNjBXU2RvUGZNNzgxaVRrTVlHcjdRcnBjLXNkMmlXQTV0N1F3LXI3TzU1a29UTmpMQ2p2OGxR0gHPAUFVX3lxTE0wYlo3VkFBcjJTdjdPWGJiVnY5SjRFb2tSRl9iVzVmTkNDSTNQSVRrVWF3SmhfVTlwWE1UQXkzZDludUdlbnhOUHlLZmI2M19OTGprTHVFLXV0N3BBczlFV1VqemhMT1NhOHhVVGNVY0pRQ21RSGJ4eVJBTUF6NktiOWkzd19kYkF5QVd3WEU5SlNydGFqTXNiM1RDZ0l1d1BHV2tnSGdQREFUdzUyWlZVTkRqR19VRXQ1emJMVFZ5ZjZsbGhBSUtOOEhZSUl1RQ?oc=5", "source": "Business Standard", "published": "2026-09-29 14:34", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZExVZU95MGlua1BLV2ZFTG9YR0dpLXI5czY0TTVJYTV1UU5PeWFJdGtTTjV4VmdnUFJoNGJ1Tl9BYS1LR0FGY0pkNmpWOG00RzZvMTFkZXFsZWVHdjNhMXBGWFJYOC1BR0NkdkNsSnU5TzAzaU9ka2VBZV93Yk95TVhlUFJBbmpxa3dEYnlqT3g3STBOZmN6eXJJVVVuTk9PdXZ0NWNHVXJhUE83R1JuelFPSGdjOTFO?oc=5", "source": "The Federal", "published": "2026-09-29 12:51", "score": -0.226, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market today, Sept 29: 227 securities hit 52-week low on NSE; Waaree Energies, Canara Bank, Britannia on list", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPelRLOXBfN3VzSWJZNVlQM2h6enZDQmF6TnZ2Z3RUT0FsUklwX0NiUC1GaWRUYTNzLU9Kc3d0V1M5U1NPck95OFpUZE9aTnRTLUJEcGc1Y2FsVHNyZXFUS1JEWkhjRnkwS19IMWxZTXZ3QnB6WWZncXVXcEpXNjBkN3Q2cmFBZmJ1Rk5mME9jbnFzTEFWOFgtNXNETGZmekR2X2xWZlA2RUZKdnN0MXdVazNFM1hnbnVxTGR6M012NmUxN3Aza2tRVUV5dThNWjFROUtybFQxYXI4RW53VzFjS1prZzRCOXVGbHFqUHEtRVJPQ2RUZW9neERnZUw2TVJhQ1U4?oc=5", "source": "upstox.com", "published": "2026-09-29 11:26", "score": 0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMiiwFBVV95cUxOSzJsdnF0SDkzMmFPNTNaZ05vaGU2STJGWFdWNEprdEJSWV9JeUZpaW1XTWs3eGJsVGJUTVctVlFLOHpScGZEaF9wWkxEWms0TG1aOHdKY0F2Q2hmSXlMMS1XOTNtX2lLQmVFTlN1ZzFOVzhMemtQV0NJMExuR3ZObDZadHhUOUxkeTQ4?oc=5", "source": "APAC Media", "published": "2026-09-29 11:14", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjE0RnktVUk3N3FQdTJJOHFVOUhKQ01LNGVXUm4tZVNyRnJOY0JhaXNnMkliMUtRdmxZakl1ZTN2VERkdjNxVVRLUXhSV19zY2ZnOE1icGVtSVRXOHNtM3Zwa0ZmTWNPejZwdkhmd0puNzlqeTRZcjRsNTdMcjFhLUxBb1VFWjg3OExMRGFycUt6YUZXbTlsUVUzNGhhSi1HdVFDRjlfOHJjbXMwNXhTckhpa041QQ?oc=5", "source": "DD India", "published": "2026-09-29 10:48", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOd0ZfSDFRbVZ0dEJpMlltNlF3Uy1wdlRBOGpYWGdJc3k3TFNNSkJKOGxnUExZNjZ5SlNQMnVzNU1jSm1EQzVXdHJDdkx1YmdrMzBQS2oxXy1veUY5V2xnNl9KR0Q0akNFYmVnb2MtcFBMMjlFR2FvM3JNYU1YV1dvcDFIVGJaWndpTUJEc1Z5V2dQWGxKSzVsbFA0RlhyeVNtMTkwWl9qdFJHTVVnT2FxaEZDVktKdUd2TUtZS2tyWGVQNGtjSmdadVVWQTlHRUplQl96cA?oc=5", "source": "Equitymaster", "published": "2026-09-29 10:19", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026", "link": "https://news.google.com/rss/articles/CBMijgJBVV95cUxQUlR6X25LUHNTc0Z0WHFMTkd6QTFmWWYxU3NHa0lFLXI4SFpHWXRMQVpMTHFGeE5lM2ktZTloaDZYMXozNWMxY25Rdk9sZ240YlhaeENTNmRraUFDTW9IbHdEdGxuOV8tR0J4bDlIeDdCZGlEYU9jem9qOEVBWjk3YU1oNVdrZGE5NmxKWG5jSWludXFEV3Y5aENySDBaQXJmRDNtalNPVU04NXF3VUNGS0xzUFFDMko1TDE3d0F2ckFwVzlhMG95M0h5QWdSSkpnTzBqbVpPYmhIMXhlVURMM3Rwb1R6ZUdjOUExX1I5Vl8yWl84dUZiNTFRU2dFbVMxUTM4X0ZXaGhBYlpHQ0HSAZMCQVVfeXFMTlppcXBnR2F2R1p4Z1hXNjZlRUtaeU9sa3VLeHV5NXFfQWFGd08wRE5mWDN5TFJiMEU1Y29JY1BNVzdDRTRaUE1NYkp1SEFycmtIVkE5dW51Ym1WUVZYS1ZFVW5ZY0puSm9kUFlxZ0t6YnFyY2x0M0dWNFQyYW9LeUtlZk4tYXltODh1ZzI3bWJMTFRRdWFUSzNyMllQOVd1RjJHcWFab2JrWkxJMmtLNUV4OHNRcWdrS2lpZHVFVzVfMEtwWkl5OTY5WVBrMmJFSmVTZEdKZmlDbzJSd1NlUC1wQTZYR1l0d3NpU1JzX1BybEllN091c3dwOXVNaU5LYTBxLWpxOVE0MFYycC1nbjNlZ1U?oc=5", "source": "Livemint", "published": "2026-09-29 10:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rebound from near six-month lows amid crude shock", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxPbnlwRUxnX0Mtc0I1MHBlVmo5dlptQ2NnUm5ib1lSUk5EU1o4TjhNNUgtY2k3TENnYlpQSkptbEZRU1JXaFcydWNEY0F2c2FjcjZhajBmQllqU2dIckQyZDlMcWo2emcxajVEN0xjaWQtSy1NVlBaa2x0QzFlV3cyblVHemQ2X2xSWjVCZVJUNkdjak5SQ0h5NEVqSGZsZUlIQTdCUUZxR1hpUmMtYVZxeHRaRUZpWVcw0gG-AUFVX3lxTE5ySzVLbHhfdWYzTWpxYm1zLWNSUEZ4QVE3c1BhZ1ktWDM0aENCZ0Qtal85VVhCVFFFeVJqbFVwNkRxOEJaTVdyZWZPZTR0bTNDT0xyNndFS0ZlTUtwTDFzNnpQZFprT3pEazRHX0xFbFczaGhoemc1OWNkeWFqQUk0UVUtYnNiUWV6WC1iZHpJQ3U5ZWRSZnh6eWlKNlR2MTkwUmwzSE1pZzh5NzREOUtkRy1Tb2ZvY0Fpa0RickE?oc=5", "source": "Livemint", "published": "2026-09-29 06:14", "score": -0.66, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows", "link": "https://news.google.com/rss/articles/CBMingFBVV95cUxOOTVLQWt4QUFvUzdlVURzbTFiZElZQTJ4ZGxERVdHZElrLUJKRVg1cHZKNVFLY0JjckVPSVdaOU9jVlZ0U2p0RWM5RjZOOVRLN25ncUdtSEhCZWZyYlFWbDVnTEJQbndBV2ZqQWktRFdQQ1djOVlaTmhfNFBaUE9kNDVnelNwdGxtVU1OczBva1ByODZGVkFfTE9HcHlJUdIBpAFBVV95cUxQdUIxRFphQzJqZ0Jqa0kxVmpvbFBMN19SVzhCY3RPMGR4TmgtOEhLN2FNZFN0bDJxUklqbG5pTDdQcUNTRjdnRk8zZmoxUEUtaXNXRFBrWldLMHh4VlpaOWdJQ1kyMDNUU0ZmWG9qQWlLUlQ2TEFNZHZLbHdoVWFzRDB1N1V0ejN5VXlGazByTG5JeXRVeWE3Y2tOd3lpMERISm05Rw?oc=5", "source": "The Hindu", "published": "2026-09-29 05:26", "score": -0.599, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxOYXhNdG9wbEpyV1JrT2ZVSG1veDJCakIwTVJDTGNZY1RuRDlYZFlTMHpWcjBRN0lwQ1I0WnBxWWJveEJvZzkySFZ5NG1JODR2OHlFQlMwR0FEZGY1cFRCcFRobUR1RjJoeEtxdXlCd3Fac2otQXpSTFEyLTVUTktTLTBfb3c3MVl5NExiUm5aN1pOQkR2bDBWLUJJQTVBdE0xQ3BLR3l2NG1hemFCb0VuNjJiMDlkZmpvZFNUSHZBMGhSbm41OTJpT1VWY1J3aTlrMGw2QldJTDA1RndGM2ZpLXR5dFdFYUpYcUxFd3paUU1kRmZEdGhYSNIB_gFBVV95cUxNUGZ4U1VBSU1YUGdsOTVHb0dyVkNoT1lGSjBucl9LR24yUnRKajNCSHFLWWFFbDg2b05iN0pNR05KdG5ZQWo0dzFDRUp3N0hCamVpbWdMeTZMSVQ1bU1GRmY2X3hjMTRTMFFMZVJKOExiZFF5dFhkbUZkcUVjWHNma2YzcFVQZF9LT1hJaVgxYTZXSFBoTDBkT25jNDdIMzI4YldxdjJ5TmtINF8wa2tnb3d2eWtsX3FVamNKV2RmZG5KdzBKd292V0pYd3dQcDVFTGg4QjNLWWxLZ3o3MVNvS3FnT0ZJQnR3REYxSTd4TUdtenFheXQzb3FLMmZzdw?oc=5", "source": "Livemint", "published": "2026-09-29 05:23", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNYi1rRVNYUG1VMmF2VjVva1lnTmNXSGdCbU5SeG1yMkhWUkVjUUl5WjljdGhWNU1wcUhDakVQU3FsQjh5bmlRV08wX3pxMXV0U0Q0VDAweWUzQ0tNZnVsd19FLVVyb3daaTVGY2FZcGtXM25qYkxCaUk2NFB2NXc4dThpTld2ZDh6TFNzanJlYmx3OXVDNTctSW5haEtqWHBrcjJSOWROYmwxQUVEejlnUm0zYVFhTUQ4VXFSbFptWDA3LVBVVER2NzEyaFdLUkljcUltVTdhci1JejFSSEpiQ053RWtjQ2dWaTJ2blJuY3ZYVnFiN1NnT1RxYkpoNTh0Z2tLTTRR0gGOAkFVX3lxTFBSSFVsVGFrRGxxQmZjSF9Lbi14XzVaa0tIRFh0MzhJS21ONkxBTWNkUkJDXzNnRnFjMmk2dTlwNzRoem9INy1sYk12YVNkLVJ0VTUySkJnNTM1QzV6ZFFFQVlhd3c5cUlUZVpUc1hha184X2pGSE5JTEkwWW84LWlwNV9HMkNVamNaWGo0Mlp0M1N3cmRxSmZJUUw5UzN6aTd5MUlHLTRlM25uM2VScXljRXlVcjFlZk4yajZwZkxYSkx1VFp1LWtLX2dWdW51V2NSVFhxUUlUZ3lQT3pkNDctM1hldGtrX2NJQ3hkN0xXQmM3MmFkeXdweXA0M3VsdjhZbWN6ZjREclA0eFdHdw?oc=5", "source": "NDTV Profit", "published": "2026-09-29 05:09", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxORm9sbGt4LWI0Qnc2ZTIyNm5MMVFFT0FXelZ0aTQta2ExTkZxbUZ0bW55RjFMVG9yNmZVczZSWFluQmpxNkxKRnpMdmJPUFNfRDFQSk1vVUVpMGpLdkp0V1c1RDd6Q1NEZUFjQTJzT1VWaTNZTGYyOU45T0cxRWV4UUs0NER0Qm5ucWJxV0xyY2diTFJ5a2N0eWVWRElHZ081bFlNckRUNEpRbmZVYXRZaTA5TWxpUUltR3dsdEQ3VEMxMUkzZWNLZmlsTlRPWWV0dHBwQ2Q5MUlOcDNqVWhNS1RoSlhfYlg0X0hVR0k5R3VER3JjS2JBejJrWFJ0TFhYLTFLX2RBQkpaVDhtd2RJOFRn0gGXAkFVX3lxTE9YUFdsMTlDTl9lbkdfTE1VY0toUk10QmlBcWM0blRhdTBjU0RxV3Q4eWNyNDhpNmhFTGZvSFY2bHU2RVpMM0JzMGdsWFRKQWdPVTNpSkl2WXZHVHNuTXo5c2VDOHBuVXltMnVKT2c4UVprUHdodmd6QUF0ODN5MnQ4UW5sS3RCWjVTMGhZNVNNRjViWFkxek51M3hqUHd3SWJtVzVwMGx3LUNnV2xfLU5WLWk0UXZDYVFLWGtxdlprQl8xNVF0SmR5ZmZiLXFBNDd1YnBuRkJabWZNSDY4SVpseDZKZEZQV1JsbHdFdHJVMW43T0JmRGR1THNMcjVxbVFyUGZpdVN3X0lSTzRLVkE0UDBZeHlFbw?oc=5", "source": "The Times of India", "published": "2026-09-29 05:06", "score": -0.459, "label": "Negative"}, {"symbol": "MARKET", "title": "BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWFYxc2FLNFJkeU5VQ0dWdFVETE9Sb1JzT2tuVnNEWTdRaU9JNWQzX0x0VjNmZlNuem9FdGRUelVPeUhNMUpTUWlmbF9nUGJJU1NndEl4eGxYaU5IWjdzSVlpOE9TQlhmakNHbTZlRmMxbGkya1JTYmJpM3FWNnhLM0FSeDhYRndHcDJzaW50dEE4WkVyb1MtcTZvN2pyeV9sTlZ5NVBLc3M4Wl9hQ3JmUF9CSWp2N2NEVk1rWld2Zm5BbXNXdFBZ0gHOAUFVX3lxTE5YV0ZiOEdkcDVUc2tDU1Myb0RnY1VRYkFHUERHLWdyM205dmdzWUoyekhSd2FIaVltYUZVa3ZUNG1qdktXNEpPTkVxdTduMmhGNGFlckQ3UkNrS0lqYkU0dVFqRmtSVS1nUkdNVXlnN1RIdmlaNUhMVGlFWHdrMERaVFo2bnlla2w0eklGTEFzSUdCeVNmYW0wZThzQ2N0WF9wNnhIZy0tZmxwREprRUFLMFk4eDN0eWhPV0x2YmZ5WXhzVU55aExVaFJtMnNR?oc=5", "source": "BusinessLine", "published": "2026-09-29 04:38", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Falls 400 Points; Nifty Slips Below 22,700", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWW5nZzl6c0Rqemg0cG1reGtZa3NMMTJEb2xNczJsMS1xbnJscHczcXpwSnJVOFVVQTJQZ2w1T0RNZ1pXb3hoWHFFMkhTdGIxYWgtNGZvQUE1X2dzNS1LMmF5dUZnZVJDbUhqdURGTlhpMTd0NERLVl9wZnNTUEx1dTJXeXY1ZVZnOWgtZGhLUEQxMzM3bmgzWTVxVXA0TWlwbDdTdXFRRVpLQ3p6NjI2ZU5SMTZIU1hsbFhXYU4wUDZpbW1fQUtZ?oc=5", "source": "HDFC Sky", "published": "2026-09-29 04:35", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxQNjN4TURGTmhtN2ctbmhRZ0NIMUVodFU1RzZNQlB0UkxGemdVQjZiYWh4WDJGakxkN290TjNzY0JEV3RsZkEtLXlxTW0xNFRzbksyQjRtSW9nSFlCSHF5Z1JMMHJjblJLbFJhX1VjRVE2WTZ2YV9wbnhNM1ZCMG5hekNoQU5uVEpscFdaczk1c1BPcWt1VXRzbWs4WFAtYUZIQVFMbWZNcmxWNE9zN3dkanZUdDhOb3dFckZGWXZfc21sMVc1Q0pOeDRQejVMR2Ztck1hTFFwSW9qM21kYWxqM3BoXzRGZw?oc=5", "source": "Equitymaster", "published": "2026-09-29 04:35", "score": -0.477, "label": "Negative"}, {"symbol": "ATHERENERG", "title": "Ather Energy Share Price News: Today\u2019s Decline Analyzed", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxNSlI3d1lGdTBUQ1NsMmhvSDh5UVZMVndVcjQtLUJBX2VLOFhIT1hoZFFhaEZWaVhKSm85eUw5SFY3NTBrMlJ0SThWYU1Ib1R5Y0NyUGlSQzk4UDloNlhPVmRyR1JWR0hZUDdfeGZXT2toVDVseWxuZVBKVFVKdW1RNg?oc=5", "source": "Univest", "published": "2026-09-29 04:23", "score": -0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Oil rise, bond yields: Top factors behind Tuesday's stock market fall", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxNQWN6aWtsVWFkYzZta0ppZDBKT3V2WEIyYy1nWWJNMWNEYUl1T09nLXRyeTFlNWF6NTZUQ2dxQmZfYWxuTkxKbFRkQm9RUWZfMVA2R0lVMFlubHFyTi1BV0NGWnBuNGtobzJmZURPa1IwbjlGU1VwUkZNQUlOWEt1U2Y2SW40MV9ncTAySWd1bjVJMWRJTVhZczlVczRQZWMyekNLTThSXzFDM3pwR0NONHVidWVEbUhzN2h0bklZMkNEYTJqSU13bF9uUi1ISVAwemU5RGRFTi1EZkowSWE4emRB0gHnAUFVX3lxTE1aRkM0ZnlvVmp3MHNlaklqcFR1dTFSeUFtbHBBbjdMV0tkY3lTbUpPQ280dkFZUXoyaDEyT3gwVHRrRW9CVm9PanNSb1k3RGtSZlFTeWtBWWotMGwxUzBOUzNVZ19lZHA3RHdwRTlfbTMzekNDR0trRXdrZzZWUmJFVmFWdmhaTnRzWkZYdDBmZXhnMmlEcjBiN0k3Tl9yWnJLMHBPZ2lHYWhGMXMtWEtCQXFfMmpxVkYwYTc0UmFIX01WVXFoZVFncHNybGktUkxhZzRLTFJGdEE5d05KWnVaUy01ZmRmZw?oc=5", "source": "Business Standard", "published": "2026-09-29 04:23", "score": -0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what\u2019s dragging the market?", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUmk0WlNhUWFKM2hkY0tydWR0QV9jUVFvV0lQclJYVFlpcXd1Q2xYWjV6aDQ3SGZKWjdkdE9nWTFNNWFsT3NwNXpnVlNtQVowZDhOTmF5eHJkbmdZZ0R5eWh2RHlhZmlXNE03ODdxWnJtYWE0NzlLdmZCNXBVMUNLRW1Hem5EYjUwMXdvcjN5alZJbUdLSTN2RDhvamt1cm8yNWNzOURJZUctaExtNk1ocHRONWswa2ZRc2pjYnRtMXJQcV93MEtTc05yZkJIa1phUnFSSjlSaXpGZ9IB5wFBVV95cUxQUXJua0JCWWl3dVNjWmdUNFdmYTNrYjh1ZDNMS0tVRUhNSTJ6c3RRRjZaRmJnNnMya2MxbmpId0djX3QzQ29LS2EweVFmSFNjZTVfVFIxUEZlbUFEX0F6djZvMnZhUW1oUWlHV29yMno5V0ZzZjJwYnhOSkhuT1BMc1FDdTFwcGtiTTYyT3ktdnVaSjFnU1hkZVhrSE82N1c5NDJjR2Z3LUlNQ0Q5N29rVnVPRTJwUjY5NlNoVkVRMlFQRFVzUnFtYmh0NHhManBaYm5HOEYwckcyR25KR3NiZXFFbVRVZDA?oc=5", "source": "Fortune India", "published": "2026-09-29 04:21", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty sink further; What is keeping the market under pressure?", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxPT2hTUks4TnNPVTAzVG1rd2xFajdvVU5QX2VTZWplSk9zXzBWc0ZOdGVzOHlrTmVOOC1hYXV1MnZxQmdnUFUwcHZPbTVMenVma0hOOVc3ZDVwWnZScEpoQUp1d2I5XzRyMmktMHZIYWhvZVVtZ2xzakx4ekpES1h6RzlfbHFxTGRUakRTbU9yeDZFT3JLUFZPMVBLdXQ1SW90Umc3S3hIMWFTeVlReWfSAa4BQVVfeXFMT09oU1JLOE5zT1UwM1Rta3dsRWo3b1VOUF9lU2VqZUpPc18wVnNGTnRlczh5a05lTjgtYWF1dTJ2cUJnZ1BVMHB2T201THp1ZmtITjlXN2Q1cFp2UnBKaEFKdXdiOV80cjJpLTB2SGFob2VVbWdsc2pMeHpKREtYekc5X2xxcUxkVGpEU21Pcng2RU9yS1BWTzFQS3V0NUlvdFJnN0t4SDFhU3lZUXln?oc=5", "source": "newsdrum.in", "published": "2026-09-29 04:21", "score": 0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street", "link": "https://news.google.com/rss/articles/CBMihwJBVV95cUxPSUtnaHFiYjg4Q204R0luSEhzcmdiaE4ycm9QNW93XzVKMGFOVlpkLUhhbXJDeXhqWWVTWW9FTGw3N2ExV1JFaTg0YjJhV0FrMUQ0Q2lOY3RtekpOUHpHWGJsU2tJTWhzSWdrU1pxNWpaZDVCclRGWWJrSi1HX2k2WmdEREJtd0RBeUdBSlNqekVYTHVqZnBNT2s2UDhYYXBBNmh3cE9kN29vbFlvRjU1OFVaemROVDFEMTgtbnRDVE5HeGRRSUkzY1ZScTlhM1ZqTVBSRThJXzhTb1QwX0R3YnR0b2twZEtsYmJJWHAwTzE2MFR1eWlsUDhNMHpvOW1BeG1pOE92NNIBjAJBVV95cUxOQTI5THdETFZZTFQwUFpsMktSVFhjeDZZWjhqcWdldDVwa2YzOXEtRzBrMWp4UW1QU3dqSzlqeGR5UGJpYUo4MXJMVndFdHpVd1MwOF9vWEFjQ0haZEwzNHB0RWZBRDVCdFZWUmhKdnM1bHRLbkp6cHNTUC1hNVIxdGRlVEtsczRRSXZtVlhyYWpQTUVXelJyeHFOZkREMUx3dnQxTXhCdFd3RGdraUd5NGFUU3NCM2hQY0tLaEU1Ym14WDM4UmZNdFppUWVNYWJtY2c4VjhFRTd0Zm4zczBtSGxJcXBPM2FCVXI1akRfU1VGWWd5UmlGV3Z4dkZHc0hjU0VsZ2p0Ny0wUndQ?oc=5", "source": "The Economic Times", "published": "2026-09-29 04:14", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxQYUFDem9SaEJWdjhyclFJQ0NyNENLejUtdThtMHpzZlREc1dxWVNucG95Mnc5QjE4WGNZc1dMRnFUZkxmanN1T1FmTEw0ZUE4bDhCQ2lXeFU1X2FlVERFS3BEcEVncG5Ya3BGQlRrQmI1WHJkRUcya1F6bV9XU0tvaXZGXzVwN0tEMGFONklKRTV5MVc0bkN4UUYySm50SmZGZms2UHptNTVPMDZnTlJvXzNFNEUxcWRKbTlTZlNLT29rcHBWaWd6RGZLTVV0NjNJSG1kTXBpSW1SZjRJcWRCb3FhWURJTFc3ck45WURndnRTZjNTYlHSAfsBQVVfeXFMTXItZGlfbXJYZnI0OFZ2V0c1VnNhMFB6Z0Y3ZjFrckJPTVZLajJBaXRmS2JjNnJyR1RfMXNoTy1ZQUViZk9tay1yQl8tbDVIQU5TSDJBdF8za3FjMGVZbWZZcV9NdDdILV9MZTFybHRtNlpDeFlPdVh4cmd5d01McXlQVEN1N1M2VlB4ZnJFdERpbUtJX3FlMXJlQmdzcDFnekRROExiRk9RTFBncFpwbzJQanZGZThMZWx5UWlIM2g0cVY0d0tLTi1kWnU1WW8xMHBNQU1qc01GcGl2ZXRHLVN6SXk5djFxZ0J6akJVSF9MZ2RVY3BYYUtoVGM?oc=5", "source": "Moneycontrol.com", "published": "2026-09-29 04:02", "score": -0.421, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxPM0JpdnpnZHlIYlVQUnRNYVVFYUlUZFJ3YkdJWXpXSzRQaktqaTN3LTdPYXU1SkRibHhTd0dOTTJkeV9NM1FZU1JWbFVPTmVBOGwzRFNwLTZ2V0lldi1kNXR3RWpjZzNmaUJOSGlIamdJcWY5TTlvRzdIZE9xZ0NiMFRpTTRnWHJZS2JaR0FOd3M1TmltbXBhb2RZU1dXUHhPdGp0MlNVbEEwV0cybVc3cEhxclU0azJyVzV3dNIBxAFBVV95cUxNS3psTE9IOFpFRVFkLU11bGZMbjA5VFNIN04xWDZJYkxIX0RscVpJTWJ0Z1N3Sjlsb3lCNTl2RURseHQ0ZVZTeHZSQnVjOFJCUjBZLUl4OUhSN0NLTm9kUmlLbU5BaTFLSzVYSVNXNExPb0VQRm9FSTVodDkzaEVLeThKSUl4b3IzcEhwbE1vSFJESGxRRnU4SDNaVkI0N05VTmtpX3F4S0VaZnBfekd4YWk5YXF2LXRycHVlOGVGTUVmX0hJ?oc=5", "source": "NDTV", "published": "2026-09-29 04:01", "score": 0.214, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty opening: Will stock market crash or open higher today?", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOUDZsU21wOWJFXzhjakg3OUQxaHREd05uWF95VTJlS05aOXQ0Vjdqam9UcjAycERGamJKcVdrYVJ6WEt4QUhHeWJaaVlJY09vQWxqUU5FVFVjcVBheEhubUkwMWdfSV8wSFNxOXpGWWN5WGwtZHk5VjlwTGw5TEVUdmNDUk4tMmZTdVlwOVpwX1IwaEVnNjNSeW9abHNFUThiS2I1RG13YS1pVjRWYkduWXk2YXh1STNNWUdEUWpKZXpVMUs0Sm9aOUs1Vm5vWFFiLWR0TmNTNmx1bXlkd2h4b2JocnN0RkpqRUHSAe8BQVVfeXFMT0JkeUl1MmI5TEZGbmM2bGFKWnl3LWdpQk8xVlVnNXhhbHg0VTI4WUUybUxNRjdKZHBVem5GbWVqZWZsSzhacWNOa3NpaUQwa0tQV0pMSGg1cDJVRGJHNVl1UWF3YjllaDJ5WnU4NjA0dFVTRkprekFzTHBGYlkyb1VmZXd2czlibnoyRm1Scy0tcGR4TXU0aGVDZjdua3JrcXJDUXRUZENMY0pTc1ZpUEk3UFl2andIckNfZ2tNZlZBXzEtMVF0Y1YwYmhkRTNOVmp2Q0ZMd01jQWR1SVJQMVlJQk5SRVpzbHpveVQyazg?oc=5", "source": "India Today", "published": "2026-09-29 02:57", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Gold Rate To Bond Yields \u2014 Five Key Factors For Sensex, Nifty 50 On September 29", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxPX2RZNUVYaGZnM0prSjZkblNWUDAyQkJnS3hOQVFsZVVzWWY3azFvYXFOekJUajR6R0Zla0NHN3NNSlZhbFI0NmhUUW1CaEdCckFrS3gxZGFUZDhVaEdqVzlwaDNIQV9mak8tTlNWVlZxU2J2OGUzemk1akNYb2k2MDREZGNNZFJ6UmxQcGQtblVyV2RKRnJ3cl96M0kzdmE5bmU1aktMcG9oZU5nUE52RnhuSGZSbnI1dU5udm9aNVpuQzVVanlZTWVHbHhGNDRDMlllS1F2ejFGcmxuNnhlOHloNE4yUdIB7gFBVV95cUxNYkFxX1BHMHZULVZmS05DY2N4cXJjaWdnX3RsWFFaWnJjTlF0dk1ySEtERGF5bzF1RFM2SjRZYzVlUUQ5LWswYUVvSHoyb3h0dC1jZ0ZZcnhkYXpFMzJvS25LNEk1SzFKTmdGVnN4MDdQN2FMaHhmZFdQVDc1TVZWTXlSSUtRYVlPVzBER004eFpRcFFhZFpXRVM4T0FWZFFVWFZQbjNnRk9tVFFtWVBNY1FEVmNBUzZPdFNJdWVZWGRsdzB2ZnRwZUI3YWdzUTk2Ym9lT2VtcXZFZVF0NUI0bmhKNHNUdzhMZnAzZDZn?oc=5", "source": "NDTV Profit", "published": "2026-09-29 01:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQWDNNbllRRzFSTkxtZmZHNmJ0ZnJPdDhyZFh0LUVuME1CYU9hdkZsR3NubDJXN2NQUXFnUER4RVhud1FsUENqWUhMdGdjT243VGZ1RGZJWGVMV2UwRl9HTTNQSk5wVU11djAzV05oalhsYzRrdG9mUF9ya2Q1ZUc5dFFUaUtNU0RqWExWMXVLSkVFSG9pUGp2VVZjWlJqdE9QbE9hRzIxYWJURXhwYm9faDk1S0Z3X18xd1J1d2duVXExemd6aDJyOEo2OW5RLVFUTWw3ZFFhU21oNGxZRnVfWXRPcjBDNzFUYVVrN0lfRzNoNDJJcktFa2FVR3lOSEVPSl9XN0dLQVNPaGfSAZACQVVfeXFMUEQ4OS1kTDJjTHlCVHp3dEFPZmJNdGxBQWlrdmN4dlhGSm45c1duQTM1WmFGRnRuTmNrRW5FaV9OQnBtc3dmVENWU1QzZG5yRGpyVFRTLTFnTlUySlNfSTFIR0RBSXpkQkhlWjNSZGFKTkFteVliTE1Zdmd4VWpCVkZ3MlQtTWxjZWdKR2VfdEM3ellKWlhua2lIVVZGaHB3bjlYQ0ptaWpmYUtid2dnLU0xdGlnMm9jYXlBSUJ5cV9ZbGZEUEUzMWd1czk4Q3Z3UHFWVWRyb3VxZy1EbnkxVXVmOVdmMVlHaEwteUllVkdCRThlQlc0S0xyblBKa2lUbWtwdzRJSGp0T0RfVE44cG0?oc=5", "source": "Livemint", "published": "2026-09-29 01:19", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3ZwWkRNRjJrZ1RQN0tCaXBfTGZORVVIeFJ2d1FmTkJpZ3RFM2ZUNW52alVyTDVSLXNzN0hRWUE0YUZ1NXBJZWEzbWVuV2NDUFRxNmRmWXVSdnkzZ0MtLV9UMm9FeTVaM2VGckptZWt1Wnhpd2F6TmVjcEpXVEJhNXpKWkVFd0NCelczRTBidmMxam1zVjRfM1J0aDVHaVl5MWtkQ1RvS2xXNm9lMTlraE9IQXBqd9IBuwFBVV95cUxQdU1hSjhhcHpRbXBFRmlSLUVvakR5c3ZwYlpORGl2M1hiaEhqa2dDWTVIdHhmY2NsNkVUWFZKT1c4MHROTG1fbEtCYnZnM0VMOHFEXzB5cFotZEtGNHgyVDR6ZkpwM19JM1JaVmlFMElpSUw0OHRMUXNKVUlvSEswOFdQcXlLLVVZZWpDVlE5bHplYkZoNUp4bUVEV2VhaWFVZzNDN1dpRFVUMUROeGtLQ3VlZFJjUDZ5Rmd3?oc=5", "source": "wionews.com", "published": "2026-09-28 19:51", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQWkFyUEVEYlc5ejlyTldhYVVvYml2c3N0YTlnSm9yZHEyMDNHUnNKVnRNeGl5NTZ0NkRpZFJJWURHUjdEczROQVpseThQbmlJdGRLa0R2X0Vid1VKM3FncW43TkVIU0hpVE5QY29VMklwNDRQa0FXNHpoRXhWSC1kaFQyVUtzc2RZYk9BMWhpTU5XTHZ4RHRMMU81azFLVFF4THZkTjJ6ZUl5NDNLcWFibmtqOUhjeEJYQW0zY24zT0lhZnMwZElXQXpB0gHPAUFVX3lxTE9jTkdQUlc5aXV2N0dtX0UzYWlfV2ZUSEhCUGp2OHFENzhsWnJQODNmemptdW9oQ2s3Si01ZnV0N3RlazVRS3YxZWJsNDZWZEx1MXdMcFFzZy11MnItN1pWQTdYS284QWJwd2hQZXdxdDc2VkR6emZGZFdsX1pDM1d2Rk1Ka25SVTRXcnAzT3dqekpRQnBKUXBwMGpHZjlQMXBtUi1pUEJac0RYSW9LcnBTUFkwbXoyQ2tDUkN4bEs5UGpoR3NBaldjekJVMFJ4MA?oc=5", "source": "Business Standard", "published": "2026-09-28 17:36", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr", "link": "https://news.google.com/rss/articles/CBMinAJBVV95cUxOOFgyakNMWTlmbmpOdjRVeTdlckZXNks0dmhfc21YME9FaUcxWjRFUG1XdTQwblI3MS1oUFN5eThST252YWpSdkhXbWZQY1V0ZWdVTGI5c2VXNXdFbzI3aUozMDh4RVMxLUxnb0tLX1NYU09yRGxGMWlvaDFlRzQyNkd2eUsxZ1lBTVNnMWI0VkMwejI1a0pWcm91NXFJSUVDZ1VhQ2JESWo2cnpDSHNHbGlhY19Za0pNQ0E3V045bjJMR09ueDZIdkNVUGthN3lRak53QWpiN1B0WkpRb3dRUTNaX1RYVXp0LUMyZG1EUWZPZlNXUGQ0WldOLWF6MFhQalU3YzA4WUttM0x6al9xS0xSVHdOajJJa2lacNIBogJBVV95cUxPanhKS0R3c2ZjbHJ5RlhHMmxmQUVLSFlUTEtBcWFTbS11YlNxdzZqNDVRSHBISmZfblhRcnhPbXVwN0NkclB6ZHNLYUk4bTZQU0x3YUs3NXdrUVE4RzJzY0VQVjZfazRmSmtudW9lNGtqcU1aMU5lMUVVS21lWm5pa2NxWlZxLTEwN0FlNGVJVS1lTzVvV1B6R0lsZGtDOUViTEFycFdFb3FmSm1KTjJZS3dEV3FUMEc4T0FVQXdBTFlCdk9sUlRyMDA5WHA0dmo2Q2lYcTFGTTJqYkI2R1JDLXZkbEdpYTBDU0NWZE1tTmd5SkFBNWxTM24yOERhN0x0SWkwY2RzZmZkRnFqNUJjdER2cFpqYmNBYVNfT2otZks5QQ?oc=5", "source": "The Times of India", "published": "2026-09-28 13:42", "score": -0.896, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNUkhaTEo2TVV5Q3h0cjBXLWVGX3EwakNwOXJxS1dmT0Fnc2p1eXByY2d4cFlIbE1HTER1QXFqWTB0bHNLR0lfWTdWT2RTTnJKRjYwLVhPU2t1dEdVMk5NMFZfemk3TFNhdk5GWDJGRVZUdV82aHJETlJWS051R0N6bU9pSktUWjR6SXY0d3g2ejhjeFRpdkszSFJzaw?oc=5", "source": "Equitymaster", "published": "2026-09-28 13:25", "score": 0.652, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxQeEMyTGpqalIydEJBcFVFWC12WDdUZVYwbkJPVk1RTGRrWlpwTnlnMWJPMk9TM21CWWxfWkpIRU1QRWNCcVcya2JHbEFRLUZLa0Vwb29SOWt0Q01nbmRfZUhrcDd1M0hsb1pHWWViTnRUNkNYek9KZDVEcUlnemU0SEozeGo0dDQxV3BJSkRlS3JQZU91YWEtUHBERUt1cWZ0T2VZY01yVVlWRlNUR3FpWlJNeFFHYlhiekdoa2htZzlJeWw3b3BhaXFnRy0?oc=5", "source": "hrtoday.in", "published": "2026-09-28 13:16", "score": 0.361, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOZGFILWIzX0lTNkh0Rm8zMGVUTWxEVGdYN1FXR2JPUTJDeVhiNHdwaVdGM0xCOHdUYTQ4MmZqLUtVTXk5NU5va01tSzN0b0lJWjFMcmY3M0N3OEhaa1NYLUF1WkxLUk8zaGZZT1RzYzd3MWpMQjFmdTgtYm5fWG5Xb3VWenYtZEVWQTJsZDd6elFSTWd2RWtMeURUdTgzTFgxSExQSW1rMFJLVkpnVG5TSGx3YUhtM01oUHpvRWNERDEwTmw3RzN1d0M3SlZ3dThNbEVnNnBtVmJXMGgyaWI0NVUzeFJ3LWFocVNyVnBqM1BxeEdlZXVQeUJZdXRKdWwxM2hDU9IBigJBVV95cUxQUWpCNDFiSU9RRGF5Rm5PYU9FZGp3c2JWVFRVSzFWTHdrdDZUczkxMVBnLV8yN0hmQkdhbXhYM3dLeHViT0Fjd0o1MkFpT2h4d0tkR2JjS29ZZWs3T25DRV95dDVtNWlFQ2ZkbGZ1WVgxRU43aEZBZEZjLVNnZ0JnZHd4TkJUbUVMaHdEUTZERnFvQ25RT3V5MmxrRk5UaG1oQWoyTUtPMG9oaktqczhZel9nTUN0eEpfRkdxWGZHRTNHUnVRQVlUdENBVFctUnRRS3lMRFBWMVk4Y1JhVFFHMGNMWDNrNjhiclVOOThFa1JrTkxZWjB6U09fRGRZLVhrbGx1OE9MZHFMUQ?oc=5", "source": "Livemint", "published": "2026-09-28 11:48", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPX21IU01KT20tUWlfRy1IMWJ2LVBfSXBlOFdWYUZid1ZJdDRncFozNEtSb3NRdnlUTUlOTHFBNkloNjROR2daRV9EQlRObWhYYm1uYkl1dGdDck5yRXM5b1pzU3podGhMc1UybjV6SGNnd2J0dW9xWjRaLWVMWjBLYXlqN2NCRk1fSndYX3lBUU9LUGRBMlg0VnBfYWtJcHhaZlYwVTBxMHBhMWtXY3NhRko4UmUyVDZOUUFVRWN1OWs5RUhyOGxzV0VMWl9sUG11RjdudmdVNHp5M0hFQ3N1aUpoN19LZ19vVmo1MGVBQQ?oc=5", "source": "Equitymaster", "published": "2026-09-28 10:56", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxPSmh5R1BHajZwb2tLTkNjdWctZ2g4d1RVU2FVaXdvU2Q4RlYzWmhia2RFWVlCbDBQdUd1NkQ1bWJUbkQtTWQ4Rk9zYkVMTVFKSGZINVFtSkVKMzhRU19ueHF3SUszbkdSOThBNFQwa0lhN1c3LVdJajZqV01uZENnWHV5UzlqbDVfSGpVdm80WlM2STJRQ3RBN2NSc1Fqc1h2amk5aFlyRExGQjh30gGyAUFVX3lxTFBSM1VWX25QMlNMcVR3N1ZFR21rX0JhZy1FVlJ3UFF1cS1PekRTcVhTOEU0Q0VGenl6Ujl1VzUtbEFvaDNiTGVpT0lHakNiQkpOX1lYRktta2stajUxT3NqSmZzRnBzVlUxNUlvdHFlRUJIN2ZKLWJfRjJ4R0ZaZVpOazYtTFlnakVCSWFINDdfcXE4cGJUYmJXcFhWbHhZUHczOHFrb0x2QV9wa0ZtTkJzb2c?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-28 10:48", "score": -0.7, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Falls 1,124 Points, Nifty Slips Below 22,800", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkNsYXBaNkxVbEJONXRoU2VUMDhmLVp5MjJ4bm9KZXJpWWp2TV9WQWhkYndIOWJOM3AxbHljM0Z4amc2NmVKS0p1SFk2REJiUVdxT3JEcG9tQ0VPMEJSa0kxNUlOS2dGTHFVN1M0T3JxbThwSkFVMHE2NzVYck1FUDR1bmM2bE1UbGJaZVFmR3hCVDJTbERmTzFnMVBoUlg3dmRkdno3b2lmZTVGNGhQbm9YOGl6SDlBSkt4M1ZoaUlsTkVf?oc=5", "source": "HDFC Sky", "published": "2026-09-28 10:46", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaFhnckpab0xJQWs2Q0lFM2ZfamY0ZklMM19qbWRQLTFXY053NHJjdkRkMWJIWUI5aU1OVl9YNEhRWGNCU0syb0RZcXUzRE1rbDBSZGE3WWVxZmJGN2poT0VJYl9VTThlQVZVYmcwS0tyal9kcFVkRmVpT0FRODZRdFZCTzE4bjhOVXctRTR0ODBvdC1DWGVEdVY3a185cEJQdUdxRmxXbFpJQlVUdHpYNlVXS3VIdmJXQl83VFgtRnNJRHJXX3BpZkhqN0hlOXFjZ1l5ekpJTdIB3AFBVV95cUxPYTNqWi1LYzdqcXJ2c2FtWEJGUVdUd3k1YXRDTnNWVWlyUFo3am13UmVSaHd1c1FqcDFHQ0pNSXlvaVZKYnVYWGZBRzJXOTgzdkdpbHVfWjlHbnBVV3Mwcnc5eE56S0hwaFlRREl0WVIwS0Q4WjRsOGMxVm1XUWQ5YnY0dzcxOUVPbUxrUFYzcEx2T0JPZ3Z6X2tkazNjRXc3ci04MHZGZnJUalk4c0M1OG1UZ1VDQ3E1UFJ5eVVaLXdqSWs3eWVnMnRPV2ZWcHE0YUw0cGVROG03aXV0?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 10:26", "score": -0.612, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPUU44cXhTejNjWEFmX3pOMEQ5YkhwR20yQUs4NGxnNks0d09rWnU2R2pxMWdmOGQ4N2s4Nm41WW9OR1lRRzU5X240Nnp4Zm44NFJ0b1N6a052VjJpXzlmR1VIXzlobHd2OVVJYnV4Q1BfMHNZUmZ0eWNqWUNqMzNGelN0Y3o5ZXRxY3hzby05M094NmZ4aWxpakRnZlZWYlRQMnhvVGRJcGlleVFpMHlNS0VRZllGQTktc1ZUWXM3MldYVkd3THVpOUh1TVVJVDJqd2tiU1N0al9oblNQajFGUDN6RlV6UGRQU2poMTV5dDRtTEVnZ2p4bzFITjQ4SVRoNVV5Z2dZbTFyUDDSAZACQVVfeXFMTl9adnRITUZ1VzVQX29ZOGpxVXpOZ24wcFluN2JGVjFsT056LU10RmMyQ3RnM3pkQlQzSV96TXZVT1ZWdmFNU1VSZmhpMWlCaWNtejhpNWwyZ05CM3c5NjJ0VnE3MUl5R19XWXphSU50eWRpd2RZemRtMzcyZTJMcWpOUUJEZ1BwZGdyXzl6ZW9MbkRoOXZjYWw2X0tURlRyTk13ajNhUXRBbWJpaFhQd2lUd1doVXRMU0VRQVRBTU1rM0xxMFN2alRHRWlWZ3pUUzd5dGJwQTJpdUlDUjJLMjBHNVVOVTJtMFFhdVlJb2dONjJjNzU1Y0p1ZE5Cbk9XcFFRT3ZYNHZaVFY1V1lIVjE?oc=5", "source": "Livemint", "published": "2026-09-28 10:15", "score": 0.402, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks shareholders approve fund raise and borrowing powers", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxNR1MxLTBoYmdoaG5EZlRjaXpBaS1ZNmkwbjBPV29xOUNGMlFQTjdFdG5ZS0JTRExGcm1XWTJCWERCMG9SRm5FcFBwSUZuVkZ1clJ3RDdRQWQxMENXTDA4UzdRUVBZeTJNN1RIZ281SG1sYkJ1TGZZeFBpN2FIRS1ieDJPcVNXY3ZuS3VHYTgyM1VuTzMyaFZkSTAwSzhrZWI2Mm1iVHlkOUlJelFUVnM4N0I3aVFwR3hvOHc?oc=5", "source": "scanx.trade", "published": "2026-09-28 10:06", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top </t>
+          <t>-29": {"open": 1460.2, "close": 1407.0, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-09-28": {"open": 5100.0, "close": 5011.5, "src": "yahoo"}, "2026-09-29": {"open": 5010.0, "close": 5204.5, "src": "bhavcopy"}}, "RRKABEL": {"2026-09-28": {"open": 2530.4, "close": 2459.8, "src": "yahoo"}, "2026-09-29": {"open": 2459.8, "close": 2523.2, "src": "bhavcopy"}}, "ACUTAAS": {"2026-09-28": {"open": 3272.5, "close": 3214.4, "src": "yahoo"}, "2026-09-29": {"open": 3290.0, "close": 3304.1, "src": "bhavcopy"}}, "DIACABS": {"2026-09-28": {"open": 353.0, "close": 339.25, "src": "yahoo"}, "2026-09-29": {"open": 336.9, "close": 352.05, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-09-28": {"open": 2138.1, "close": 2141.2, "src": "yahoo"}, "2026-09-29": {"open": 2141.2, "close": 2402.0, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-09-29 19:38", "days": 7, "items": [{"symbol": "MARKET", "title": "Sensex, Nifty End Lower for Second Day; Global Tensions, FII Selling Hurt Investor Mood", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxNOC0wWWx3dmhaeFRrNDNBUU8zLUxRMDdKSXNURGVXT09GdFJQbGlOR2pOeXdmTHlVMzViVWpVcFJrSmtGbktLUWlESkNzWGJwTlNERW00Y0hWVmR5dUxIV1AzNl9YeXFIZTR1WGRRZlp3RTVyMUR5Wmw0d0xWYWg2ME9Yc2Z3NlBibjR0S1NiV1l5d080TWxvQmpPVVVRMHA2VlNUM1oycTlZcG5CSlh4amFn?oc=5", "source": "The Indian Awaaz", "published": "2026-09-29 15:41", "score": -0.637, "label": "Negative"}, {"symbol": "MARKET", "title": "High derivatives activity lead to swings in Indian market on expiry day", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxOX2lHWmtSZUZtUnhORjFzUGQweW5Ca1F2VDdRdVhDaHd3OF83Q1hvY09NMU5NY1JzQ1Z3MU1hRmVHVkppOHJxTXBYeE1aOFh2MUZEejFaNV9yWVNmNFRtRDJXN0xic1JiVGtaY25JTWZVTFh0bzRCZnVud29LQ1pkR2tIeVF1amxrZElwZTNNdW5IV0drNjBXU2RvUGZNNzgxaVRrTVlHcjdRcnBjLXNkMmlXQTV0N1F3LXI3TzU1a29UTmpMQ2p2OGxR0gHPAUFVX3lxTE0wYlo3VkFBcjJTdjdPWGJiVnY5SjRFb2tSRl9iVzVmTkNDSTNQSVRrVWF3SmhfVTlwWE1UQXkzZDludUdlbnhOUHlLZmI2M19OTGprTHVFLXV0N3BBczlFV1VqemhMT1NhOHhVVGNVY0pRQ21RSGJ4eVJBTUF6NktiOWkzd19kYkF5QVd3WEU5SlNydGFqTXNiM1RDZ0l1d1BHV2tnSGdQREFUdzUyWlZVTkRqR19VRXQ1emJMVFZ5ZjZsbGhBSUtOOEhZSUl1RQ?oc=5", "source": "Business Standard", "published": "2026-09-29 14:34", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZExVZU95MGlua1BLV2ZFTG9YR0dpLXI5czY0TTVJYTV1UU5PeWFJdGtTTjV4VmdnUFJoNGJ1Tl9BYS1LR0FGY0pkNmpWOG00RzZvMTFkZXFsZWVHdjNhMXBGWFJYOC1BR0NkdkNsSnU5TzAzaU9ka2VBZV93Yk95TVhlUFJBbmpxa3dEYnlqT3g3STBOZmN6eXJJVVVuTk9PdXZ0NWNHVXJhUE83R1JuelFPSGdjOTFO?oc=5", "source": "The Federal", "published": "2026-09-29 12:51", "score": -0.226, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMiiwFBVV95cUxOSzJsdnF0SDkzMmFPNTNaZ05vaGU2STJGWFdWNEprdEJSWV9JeUZpaW1XTWs3eGJsVGJUTVctVlFLOHpScGZEaF9wWkxEWms0TG1aOHdKY0F2Q2hmSXlMMS1XOTNtX2lLQmVFTlN1ZzFOVzhMemtQV0NJMExuR3ZObDZadHhUOUxkeTQ4?oc=5", "source": "APAC Media", "published": "2026-09-29 11:14", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjE0RnktVUk3N3FQdTJJOHFVOUhKQ01LNGVXUm4tZVNyRnJOY0JhaXNnMkliMUtRdmxZakl1ZTN2VERkdjNxVVRLUXhSV19zY2ZnOE1icGVtSVRXOHNtM3Zwa0ZmTWNPejZwdkhmd0puNzlqeTRZcjRsNTdMcjFhLUxBb1VFWjg3OExMRGFycUt6YUZXbTlsUVUzNGhhSi1HdVFDRjlfOHJjbXMwNXhTckhpa041QQ?oc=5", "source": "DD India", "published": "2026-09-29 10:48", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOd0ZfSDFRbVZ0dEJpMlltNlF3Uy1wdlRBOGpYWGdJc3k3TFNNSkJKOGxnUExZNjZ5SlNQMnVzNU1jSm1EQzVXdHJDdkx1YmdrMzBQS2oxXy1veUY5V2xnNl9KR0Q0akNFYmVnb2MtcFBMMjlFR2FvM3JNYU1YV1dvcDFIVGJaWndpTUJEc1Z5V2dQWGxKSzVsbFA0RlhyeVNtMTkwWl9qdFJHTVVnT2FxaEZDVktKdUd2TUtZS2tyWGVQNGtjSmdadVVWQTlHRUplQl96cA?oc=5", "source": "equitymaster.com", "published": "2026-09-29 10:19", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market prediction for tomorrow: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026", "link": "https://news.google.com/rss/articles/CBMijgJBVV95cUxQUlR6X25LUHNTc0Z0WHFMTkd6QTFmWWYxU3NHa0lFLXI4SFpHWXRMQVpMTHFGeE5lM2ktZTloaDZYMXozNWMxY25Rdk9sZ240YlhaeENTNmRraUFDTW9IbHdEdGxuOV8tR0J4bDlIeDdCZGlEYU9jem9qOEVBWjk3YU1oNVdrZGE5NmxKWG5jSWludXFEV3Y5aENySDBaQXJmRDNtalNPVU04NXF3VUNGS0xzUFFDMko1TDE3d0F2ckFwVzlhMG95M0h5QWdSSkpnTzBqbVpPYmhIMXhlVURMM3Rwb1R6ZUdjOUExX1I5Vl8yWl84dUZiNTFRU2dFbVMxUTM4X0ZXaGhBYlpHQ0HSAZMCQVVfeXFMTlppcXBnR2F2R1p4Z1hXNjZlRUtaeU9sa3VLeHV5NXFfQWFGd08wRE5mWDN5TFJiMEU1Y29JY1BNVzdDRTRaUE1NYkp1SEFycmtIVkE5dW51Ym1WUVZYS1ZFVW5ZY0puSm9kUFlxZ0t6YnFyY2x0M0dWNFQyYW9LeUtlZk4tYXltODh1ZzI3bWJMTFRRdWFUSzNyMllQOVd1RjJHcWFab2JrWkxJMmtLNUV4OHNRcWdrS2lpZHVFVzVfMEtwWkl5OTY5WVBrMmJFSmVTZEdKZmlDbzJSd1NlUC1wQTZYR1l0d3NpU1JzX1BybEllN091c3dwOXVNaU5LYTBxLWpxOVE0MFYycC1nbjNlZ1U?oc=5", "source": "Livemint", "published": "2026-09-29 10:11", "score": 0.402, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "AEROFLEX Share Price gains as market cap tops Rs 6,946 Cr", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxOZWdYU0xLYUJYR3QwY3N5RXNVb3c4cTMzbUlrcWVoRndKQVAwbmZqakRQeTB3Z3E4LUk1ckxpRGd5WURhaWNRNFlBZlVYRThLNnVfSzRGUXhTdVpnRFZMWHhNNFJ1bTljbFV2VnZPMWJfc3ZYMWQ4bHJIRGZCbE94ZElPc3lIM28?oc=5", "source": "Univest", "published": "2026-09-29 08:18", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rebound from near six-month lows amid crude shock", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxPbnlwRUxnX0Mtc0I1MHBlVmo5dlptQ2NnUm5ib1lSUk5EU1o4TjhNNUgtY2k3TENnYlpQSkptbEZRU1JXaFcydWNEY0F2c2FjcjZhajBmQllqU2dIckQyZDlMcWo2emcxajVEN0xjaWQtSy1NVlBaa2x0QzFlV3cyblVHemQ2X2xSWjVCZVJUNkdjak5SQ0h5NEVqSGZsZUlIQTdCUUZxR1hpUmMtYVZxeHRaRUZpWVcw0gG-AUFVX3lxTE5ySzVLbHhfdWYzTWpxYm1zLWNSUEZ4QVE3c1BhZ1ktWDM0aENCZ0Qtal85VVhCVFFFeVJqbFVwNkRxOEJaTVdyZWZPZTR0bTNDT0xyNndFS0ZlTUtwTDFzNnpQZFprT3pEazRHX0xFbFczaGhoemc1OWNkeWFqQUk0UVUtYnNiUWV6WC1iZHpJQ3U5ZWRSZnh6eWlKNlR2MTkwUmwzSE1pZzh5NzREOUtkRy1Tb2ZvY0Fpa0RickE?oc=5", "source": "Livemint", "published": "2026-09-29 06:14", "score": -0.66, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows", "link": "https://news.google.com/rss/articles/CBMingFBVV95cUxOOTVLQWt4QUFvUzdlVURzbTFiZElZQTJ4ZGxERVdHZElrLUJKRVg1cHZKNVFLY0JjckVPSVdaOU9jVlZ0U2p0RWM5RjZOOVRLN25ncUdtSEhCZWZyYlFWbDVnTEJQbndBV2ZqQWktRFdQQ1djOVlaTmhfNFBaUE9kNDVnelNwdGxtVU1OczBva1ByODZGVkFfTE9HcHlJUdIBpAFBVV95cUxQdUIxRFphQzJqZ0Jqa0kxVmpvbFBMN19SVzhCY3RPMGR4TmgtOEhLN2FNZFN0bDJxUklqbG5pTDdQcUNTRjdnRk8zZmoxUEUtaXNXRFBrWldLMHh4VlpaOWdJQ1kyMDNUU0ZmWG9qQWlLUlQ2TEFNZHZLbHdoVWFzRDB1N1V0ejN5VXlGazByTG5JeXRVeWE3Y2tOd3lpMERISm05Rw?oc=5", "source": "The Hindu", "published": "2026-09-29 05:26", "score": -0.599, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxOYXhNdG9wbEpyV1JrT2ZVSG1veDJCakIwTVJDTGNZY1RuRDlYZFlTMHpWcjBRN0lwQ1I0WnBxWWJveEJvZzkySFZ5NG1JODR2OHlFQlMwR0FEZGY1cFRCcFRobUR1RjJoeEtxdXlCd3Fac2otQXpSTFEyLTVUTktTLTBfb3c3MVl5NExiUm5aN1pOQkR2bDBWLUJJQTVBdE0xQ3BLR3l2NG1hemFCb0VuNjJiMDlkZmpvZFNUSHZBMGhSbm41OTJpT1VWY1J3aTlrMGw2QldJTDA1RndGM2ZpLXR5dFdFYUpYcUxFd3paUU1kRmZEdGhYSNIB_gFBVV95cUxNUGZ4U1VBSU1YUGdsOTVHb0dyVkNoT1lGSjBucl9LR24yUnRKajNCSHFLWWFFbDg2b05iN0pNR05KdG5ZQWo0dzFDRUp3N0hCamVpbWdMeTZMSVQ1bU1GRmY2X3hjMTRTMFFMZVJKOExiZFF5dFhkbUZkcUVjWHNma2YzcFVQZF9LT1hJaVgxYTZXSFBoTDBkT25jNDdIMzI4YldxdjJ5TmtINF8wa2tnb3d2eWtsX3FVamNKV2RmZG5KdzBKd292V0pYd3dQcDVFTGg4QjNLWWxLZ3o3MVNvS3FnT0ZJQnR3REYxSTd4TUdtenFheXQzb3FLMmZzdw?oc=5", "source": "Livemint", "published": "2026-09-29 05:23", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "5 reasons why market is down today: Sensex, Nifty hit six-month lows; India VIX spikes", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxQM0tPSzhJN2ZQZnYtUVVaMnV6eGVWRFdvTUtTQWd2SFpBZGRicXkwVG5qYUM4cU5lTTRVS3kwaVBPMGdIUkZCUmIyR1VZRlVLMWhMYy1OQkdnaGhNaFdlYWp6Qm1Xa0VfNzF3VFBLVTREeDVMblhWWndCR1I3QmIwaHB0Yi0zVmZOT1ROZXlYbGJISjdlM2dSOE5ObDMzbURYRUNRandYUWt3MUZoRXVFQWE3UmJpeTJtTjBVODV1bExCbjQ1UE5OVHZ6d2x6RVdSclFsV0lYQllud3BMN1E4bGsxWkFsZ9IB6wFBVV95cUxOR2UzREJ0R0ljU1dXdS0xLUFwWlVIUnhOLVEySllrWTVtRnFEXzFCc3BVcFNyTDNaTUpNSGxMUWJjalRISmU2R3VVbWdFRWhVQTBPTU9kRHB0V1RPV1BzRHhoQkN4YzVOdVpXYV9aMmVZVWxJRHZ2YUdFSVhmZnJZS1ZQY0FkUC00SExHRVF0NExfblVJYXJ4YUxvU1M1RlVoVmxMZ1NycXNyQWpMeGF2SWZ0LURlU3JrZjhCclFNY1FSaGI3cmh1MzdSeFREa3VmQXNLTHo0dF90Y2FLZFQ1VE9kWWFsbjJXUUZF?oc=5", "source": "Business Today", "published": "2026-09-29 05:18", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNYi1rRVNYUG1VMmF2VjVva1lnTmNXSGdCbU5SeG1yMkhWUkVjUUl5WjljdGhWNU1wcUhDakVQU3FsQjh5bmlRV08wX3pxMXV0U0Q0VDAweWUzQ0tNZnVsd19FLVVyb3daaTVGY2FZcGtXM25qYkxCaUk2NFB2NXc4dThpTld2ZDh6TFNzanJlYmx3OXVDNTctSW5haEtqWHBrcjJSOWROYmwxQUVEejlnUm0zYVFhTUQ4VXFSbFptWDA3LVBVVER2NzEyaFdLUkljcUltVTdhci1JejFSSEpiQ053RWtjQ2dWaTJ2blJuY3ZYVnFiN1NnT1RxYkpoNTh0Z2tLTTRR0gGOAkFVX3lxTFBSSFVsVGFrRGxxQmZjSF9Lbi14XzVaa0tIRFh0MzhJS21ONkxBTWNkUkJDXzNnRnFjMmk2dTlwNzRoem9INy1sYk12YVNkLVJ0VTUySkJnNTM1QzV6ZFFFQVlhd3c5cUlUZVpUc1hha184X2pGSE5JTEkwWW84LWlwNV9HMkNVamNaWGo0Mlp0M1N3cmRxSmZJUUw5UzN6aTd5MUlHLTRlM25uM2VScXljRXlVcjFlZk4yajZwZkxYSkx1VFp1LWtLX2dWdW51V2NSVFhxUUlUZ3lQT3pkNDctM1hldGtrX2NJQ3hkN0xXQmM3MmFkeXdweXA0M3VsdjhZbWN6ZjREclA0eFdHdw?oc=5", "source": "NDTV Profit", "published": "2026-09-29 05:09", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxORm9sbGt4LWI0Qnc2ZTIyNm5MMVFFT0FXelZ0aTQta2ExTkZxbUZ0bW55RjFMVG9yNmZVczZSWFluQmpxNkxKRnpMdmJPUFNfRDFQSk1vVUVpMGpLdkp0V1c1RDd6Q1NEZUFjQTJzT1VWaTNZTGYyOU45T0cxRWV4UUs0NER0Qm5ucWJxV0xyY2diTFJ5a2N0eWVWRElHZ081bFlNckRUNEpRbmZVYXRZaTA5TWxpUUltR3dsdEQ3VEMxMUkzZWNLZmlsTlRPWWV0dHBwQ2Q5MUlOcDNqVWhNS1RoSlhfYlg0X0hVR0k5R3VER3JjS2JBejJrWFJ0TFhYLTFLX2RBQkpaVDhtd2RJOFRn0gGXAkFVX3lxTE9YUFdsMTlDTl9lbkdfTE1VY0toUk10QmlBcWM0blRhdTBjU0RxV3Q4eWNyNDhpNmhFTGZvSFY2bHU2RVpMM0JzMGdsWFRKQWdPVTNpSkl2WXZHVHNuTXo5c2VDOHBuVXltMnVKT2c4UVprUHdodmd6QUF0ODN5MnQ4UW5sS3RCWjVTMGhZNVNNRjViWFkxek51M3hqUHd3SWJtVzVwMGx3LUNnV2xfLU5WLWk0UXZDYVFLWGtxdlprQl8xNVF0SmR5ZmZiLXFBNDd1YnBuRkJabWZNSDY4SVpseDZKZEZQV1JsbHdFdHJVMW43T0JmRGR1THNMcjVxbVFyUGZpdVN3X0lSTzRLVkE0UDBZeHlFbw?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-29 05:06", "score": -0.459, "label": "Negative"}, {"symbol": "MARKET", "title": "BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWFYxc2FLNFJkeU5VQ0dWdFVETE9Sb1JzT2tuVnNEWTdRaU9JNWQzX0x0VjNmZlNuem9FdGRUelVPeUhNMUpTUWlmbF9nUGJJU1NndEl4eGxYaU5IWjdzSVlpOE9TQlhmakNHbTZlRmMxbGkya1JTYmJpM3FWNnhLM0FSeDhYRndHcDJzaW50dEE4WkVyb1MtcTZvN2pyeV9sTlZ5NVBLc3M4Wl9hQ3JmUF9CSWp2N2NEVk1rWld2Zm5BbXNXdFBZ0gHOAUFVX3lxTE5YV0ZiOEdkcDVUc2tDU1Myb0RnY1VRYkFHUERHLWdyM205dmdzWUoyekhSd2FIaVltYUZVa3ZUNG1qdktXNEpPTkVxdTduMmhGNGFlckQ3UkNrS0lqYkU0dVFqRmtSVS1nUkdNVXlnN1RIdmlaNUhMVGlFWHdrMERaVFo2bnlla2w0eklGTEFzSUdCeVNmYW0wZThzQ2N0WF9wNnhIZy0tZmxwREprRUFLMFk4eDN0eWhPV0x2YmZ5WXhzVU55aExVaFJtMnNR?oc=5", "source": "BusinessLine", "published": "2026-09-29 04:38", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Falls 400 Points; Nifty Slips Below 22,700", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxQWW5nZzl6c0Rqemg0cG1reGtZa3NMMTJEb2xNczJsMS1xbnJscHczcXpwSnJVOFVVQTJQZ2w1T0RNZ1pXb3hoWHFFMkhTdGIxYWgtNGZvQUE1X2dzNS1LMmF5dUZnZVJDbUhqdURGTlhpMTd0NERLVl9wZnNTUEx1dTJXeXY1ZVZnOWgtZGhLUEQxMzM3bmgzWTVxVXA0TWlwbDdTdXFRRVpLQ3p6NjI2ZU5SMTZIU1hsbFhXYU4wUDZpbW1fQUtZ?oc=5", "source": "HDFC Sky", "published": "2026-09-29 04:35", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxQNjN4TURGTmhtN2ctbmhRZ0NIMUVodFU1RzZNQlB0UkxGemdVQjZiYWh4WDJGakxkN290TjNzY0JEV3RsZkEtLXlxTW0xNFRzbksyQjRtSW9nSFlCSHF5Z1JMMHJjblJLbFJhX1VjRVE2WTZ2YV9wbnhNM1ZCMG5hekNoQU5uVEpscFdaczk1c1BPcWt1VXRzbWs4WFAtYUZIQVFMbWZNcmxWNE9zN3dkanZUdDhOb3dFckZGWXZfc21sMVc1Q0pOeDRQejVMR2Ztck1hTFFwSW9qM21kYWxqM3BoXzRGZw?oc=5", "source": "equitymaster.com", "published": "2026-09-29 04:35", "score": -0.477, "label": "Negative"}, {"symbol": "ATHERENERG", "title": "Ather Energy Share Price News: Today\u2019s Decline Analyzed", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxNSlI3d1lGdTBUQ1NsMmhvSDh5UVZMVndVcjQtLUJBX2VLOFhIT1hoZFFhaEZWaVhKSm85eUw5SFY3NTBrMlJ0SThWYU1Ib1R5Y0NyUGlSQzk4UDloNlhPVmRyR1JWR0hZUDdfeGZXT2toVDVseWxuZVBKVFVKdW1RNg?oc=5", "source": "Univest", "published": "2026-09-29 04:23", "score": -0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Oil rise, bond yields: Top factors behind Tuesday's stock market fall", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxNQWN6aWtsVWFkYzZta0ppZDBKT3V2WEIyYy1nWWJNMWNEYUl1T09nLXRyeTFlNWF6NTZUQ2dxQmZfYWxuTkxKbFRkQm9RUWZfMVA2R0lVMFlubHFyTi1BV0NGWnBuNGtobzJmZURPa1IwbjlGU1VwUkZNQUlOWEt1U2Y2SW40MV9ncTAySWd1bjVJMWRJTVhZczlVczRQZWMyekNLTThSXzFDM3pwR0NONHVidWVEbUhzN2h0bklZMkNEYTJqSU13bF9uUi1ISVAwemU5RGRFTi1EZkowSWE4emRB0gHnAUFVX3lxTE1aRkM0ZnlvVmp3MHNlaklqcFR1dTFSeUFtbHBBbjdMV0tkY3lTbUpPQ280dkFZUXoyaDEyT3gwVHRrRW9CVm9PanNSb1k3RGtSZlFTeWtBWWotMGwxUzBOUzNVZ19lZHA3RHdwRTlfbTMzekNDR0trRXdrZzZWUmJFVmFWdmhaTnRzWkZYdDBmZXhnMmlEcjBiN0k3Tl9yWnJLMHBPZ2lHYWhGMXMtWEtCQXFfMmpxVkYwYTc0UmFIX01WVXFoZVFncHNybGktUkxhZzRLTFJGdEE5d05KWnVaUy01ZmRmZw?oc=5", "source": "Business Standard", "published": "2026-09-29 04:23", "score": -0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what\u2019s dragging the market?", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUmk0WlNhUWFKM2hkY0tydWR0QV9jUVFvV0lQclJYVFlpcXd1Q2xYWjV6aDQ3SGZKWjdkdE9nWTFNNWFsT3NwNXpnVlNtQVowZDhOTmF5eHJkbmdZZ0R5eWh2RHlhZmlXNE03ODdxWnJtYWE0NzlLdmZCNXBVMUNLRW1Hem5EYjUwMXdvcjN5alZJbUdLSTN2RDhvamt1cm8yNWNzOURJZUctaExtNk1ocHRONWswa2ZRc2pjYnRtMXJQcV93MEtTc05yZkJIa1phUnFSSjlSaXpGZ9IB5wFBVV95cUxQUXJua0JCWWl3dVNjWmdUNFdmYTNrYjh1ZDNMS0tVRUhNSTJ6c3RRRjZaRmJnNnMya2MxbmpId0djX3QzQ29LS2EweVFmSFNjZTVfVFIxUEZlbUFEX0F6djZvMnZhUW1oUWlHV29yMno5V0ZzZjJwYnhOSkhuT1BMc1FDdTFwcGtiTTYyT3ktdnVaSjFnU1hkZVhrSE82N1c5NDJjR2Z3LUlNQ0Q5N29rVnVPRTJwUjY5NlNoVkVRMlFQRFVzUnFtYmh0NHhManBaYm5HOEYwckcyR25KR3NiZXFFbVRVZDA?oc=5", "source": "Fortune India", "published": "2026-09-29 04:21", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty sink further; What is keeping the market under pressure?", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxPT2hTUks4TnNPVTAzVG1rd2xFajdvVU5QX2VTZWplSk9zXzBWc0ZOdGVzOHlrTmVOOC1hYXV1MnZxQmdnUFUwcHZPbTVMenVma0hOOVc3ZDVwWnZScEpoQUp1d2I5XzRyMmktMHZIYWhvZVVtZ2xzakx4ekpES1h6RzlfbHFxTGRUakRTbU9yeDZFT3JLUFZPMVBLdXQ1SW90Umc3S3hIMWFTeVlReWfSAa4BQVVfeXFMT09oU1JLOE5zT1UwM1Rta3dsRWo3b1VOUF9lU2VqZUpPc18wVnNGTnRlczh5a05lTjgtYWF1dTJ2cUJnZ1BVMHB2T201THp1ZmtITjlXN2Q1cFp2UnBKaEFKdXdiOV80cjJpLTB2SGFob2VVbWdsc2pMeHpKREtYekc5X2xxcUxkVGpEU21Pcng2RU9yS1BWTzFQS3V0NUlvdFJnN0t4SDFhU3lZUXln?oc=5", "source": "newsdrum.in", "published": "2026-09-29 04:21", "score": 0.128, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street", "link": "https://news.google.com/rss/articles/CBMihwJBVV95cUxPSUtnaHFiYjg4Q204R0luSEhzcmdiaE4ycm9QNW93XzVKMGFOVlpkLUhhbXJDeXhqWWVTWW9FTGw3N2ExV1JFaTg0YjJhV0FrMUQ0Q2lOY3RtekpOUHpHWGJsU2tJTWhzSWdrU1pxNWpaZDVCclRGWWJrSi1HX2k2WmdEREJtd0RBeUdBSlNqekVYTHVqZnBNT2s2UDhYYXBBNmh3cE9kN29vbFlvRjU1OFVaemROVDFEMTgtbnRDVE5HeGRRSUkzY1ZScTlhM1ZqTVBSRThJXzhTb1QwX0R3YnR0b2twZEtsYmJJWHAwTzE2MFR1eWlsUDhNMHpvOW1BeG1pOE92NNIBjAJBVV95cUxOQTI5THdETFZZTFQwUFpsMktSVFhjeDZZWjhqcWdldDVwa2YzOXEtRzBrMWp4UW1QU3dqSzlqeGR5UGJpYUo4MXJMVndFdHpVd1MwOF9vWEFjQ0haZEwzNHB0RWZBRDVCdFZWUmhKdnM1bHRLbkp6cHNTUC1hNVIxdGRlVEtsczRRSXZtVlhyYWpQTUVXelJyeHFOZkREMUx3dnQxTXhCdFd3RGdraUd5NGFUU3NCM2hQY0tLaEU1Ym14WDM4UmZNdFppUWVNYWJtY2c4VjhFRTd0Zm4zczBtSGxJcXBPM2FCVXI1akRfU1VGWWd5UmlGV3Z4dkZHc0hjU0VsZ2p0Ny0wUndQ?oc=5", "source": "The Economic Times", "published": "2026-09-29 04:14", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxQYUFDem9SaEJWdjhyclFJQ0NyNENLejUtdThtMHpzZlREc1dxWVNucG95Mnc5QjE4WGNZc1dMRnFUZkxmanN1T1FmTEw0ZUE4bDhCQ2lXeFU1X2FlVERFS3BEcEVncG5Ya3BGQlRrQmI1WHJkRUcya1F6bV9XU0tvaXZGXzVwN0tEMGFONklKRTV5MVc0bkN4UUYySm50SmZGZms2UHptNTVPMDZnTlJvXzNFNEUxcWRKbTlTZlNLT29rcHBWaWd6RGZLTVV0NjNJSG1kTXBpSW1SZjRJcWRCb3FhWURJTFc3ck45WURndnRTZjNTYlHSAfsBQVVfeXFMTXItZGlfbXJYZnI0OFZ2V0c1VnNhMFB6Z0Y3ZjFrckJPTVZLajJBaXRmS2JjNnJyR1RfMXNoTy1ZQUViZk9tay1yQl8tbDVIQU5TSDJBdF8za3FjMGVZbWZZcV9NdDdILV9MZTFybHRtNlpDeFlPdVh4cmd5d01McXlQVEN1N1M2VlB4ZnJFdERpbUtJX3FlMXJlQmdzcDFnekRROExiRk9RTFBncFpwbzJQanZGZThMZWx5UWlIM2g0cVY0d0tLTi1kWnU1WW8xMHBNQU1qc01GcGl2ZXRHLVN6SXk5djFxZ0J6akJVSF9MZ2RVY3BYYUtoVGM?oc=5", "source": "Moneycontrol.com", "published": "2026-09-29 04:02", "score": -0.421, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Fell 10% In 2 Years, But This Rs 1 Crore Portfolio Grew By Rs 16 Lakh. Here's How", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxPM0JpdnpnZHlIYlVQUnRNYVVFYUlUZFJ3YkdJWXpXSzRQaktqaTN3LTdPYXU1SkRibHhTd0dOTTJkeV9NM1FZU1JWbFVPTmVBOGwzRFNwLTZ2V0lldi1kNXR3RWpjZzNmaUJOSGlIamdJcWY5TTlvRzdIZE9xZ0NiMFRpTTRnWHJZS2JaR0FOd3M1TmltbXBhb2RZU1dXUHhPdGp0MlNVbEEwV0cybVc3cEhxclU0azJyVzV3dNIBxAFBVV95cUxNS3psTE9IOFpFRVFkLU11bGZMbjA5VFNIN04xWDZJYkxIX0RscVpJTWJ0Z1N3Sjlsb3lCNTl2RURseHQ0ZVZTeHZSQnVjOFJCUjBZLUl4OUhSN0NLTm9kUmlLbU5BaTFLSzVYSVNXNExPb0VQRm9FSTVodDkzaEVLeThKSUl4b3IzcEhwbE1vSFJESGxRRnU4SDNaVkI0N05VTmtpX3F4S0VaZnBfekd4YWk5YXF2LXRycHVlOGVGTUVmX0hJ?oc=5", "source": "ndtv.com", "published": "2026-09-29 04:01", "score": 0.214, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty opening: Will stock market crash or open higher today?", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOUDZsU21wOWJFXzhjakg3OUQxaHREd05uWF95VTJlS05aOXQ0Vjdqam9UcjAycERGamJKcVdrYVJ6WEt4QUhHeWJaaVlJY09vQWxqUU5FVFVjcVBheEhubUkwMWdfSV8wSFNxOXpGWWN5WGwtZHk5VjlwTGw5TEVUdmNDUk4tMmZTdVlwOVpwX1IwaEVnNjNSeW9abHNFUThiS2I1RG13YS1pVjRWYkduWXk2YXh1STNNWUdEUWpKZXpVMUs0Sm9aOUs1Vm5vWFFiLWR0TmNTNmx1bXlkd2h4b2JocnN0RkpqRUHSAe8BQVVfeXFMT0JkeUl1MmI5TEZGbmM2bGFKWnl3LWdpQk8xVlVnNXhhbHg0VTI4WUUybUxNRjdKZHBVem5GbWVqZWZsSzhacWNOa3NpaUQwa0tQV0pMSGg1cDJVRGJHNVl1UWF3YjllaDJ5WnU4NjA0dFVTRkprekFzTHBGYlkyb1VmZXd2czlibnoyRm1Scy0tcGR4TXU0aGVDZjdua3JrcXJDUXRUZENMY0pTc1ZpUEk3UFl2andIckNfZ2tNZlZBXzEtMVF0Y1YwYmhkRTNOVmp2Q0ZMd01jQWR1SVJQMVlJQk5SRVpzbHpveVQyazg?oc=5", "source": "India Today", "published": "2026-09-29 02:57", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Gold Rate To Bond Yields \u2014 Five Key Factors For Sensex, Nifty 50 On September 29", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxPX2RZNUVYaGZnM0prSjZkblNWUDAyQkJnS3hOQVFsZVVzWWY3azFvYXFOekJUajR6R0Zla0NHN3NNSlZhbFI0NmhUUW1CaEdCckFrS3gxZGFUZDhVaEdqVzlwaDNIQV9mak8tTlNWVlZxU2J2OGUzemk1akNYb2k2MDREZGNNZFJ6UmxQcGQtblVyV2RKRnJ3cl96M0kzdmE5bmU1aktMcG9oZU5nUE52RnhuSGZSbnI1dU5udm9aNVpuQzVVanlZTWVHbHhGNDRDMlllS1F2ejFGcmxuNnhlOHloNE4yUdIB7gFBVV95cUxNYkFxX1BHMHZULVZmS05DY2N4cXJjaWdnX3RsWFFaWnJjTlF0dk1ySEtERGF5bzF1RFM2SjRZYzVlUUQ5LWswYUVvSHoyb3h0dC1jZ0ZZcnhkYXpFMzJvS25LNEk1SzFKTmdGVnN4MDdQN2FMaHhmZFdQVDc1TVZWTXlSSUtRYVlPVzBER004eFpRcFFhZFpXRVM4T0FWZFFVWFZQbjNnRk9tVFFtWVBNY1FEVmNBUzZPdFNJdWVZWGRsdzB2ZnRwZUI3YWdzUTk2Ym9lT2VtcXZFZVF0NUI0bmhKNHNUdzhMZnAzZDZn?oc=5", "source": "NDTV Profit", "published": "2026-09-29 01:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQWDNNbllRRzFSTkxtZmZHNmJ0ZnJPdDhyZFh0LUVuME1CYU9hdkZsR3NubDJXN2NQUXFnUER4RVhud1FsUENqWUhMdGdjT243VGZ1RGZJWGVMV2UwRl9HTTNQSk5wVU11djAzV05oalhsYzRrdG9mUF9ya2Q1ZUc5dFFUaUtNU0RqWExWMXVLSkVFSG9pUGp2VVZjWlJqdE9QbE9hRzIxYWJURXhwYm9faDk1S0Z3X18xd1J1d2duVXExemd6aDJyOEo2OW5RLVFUTWw3ZFFhU21oNGxZRnVfWXRPcjBDNzFUYVVrN0lfRzNoNDJJcktFa2FVR3lOSEVPSl9XN0dLQVNPaGfSAZACQVVfeXFMUEQ4OS1kTDJjTHlCVHp3dEFPZmJNdGxBQWlrdmN4dlhGSm45c1duQTM1WmFGRnRuTmNrRW5FaV9OQnBtc3dmVENWU1QzZG5yRGpyVFRTLTFnTlUySlNfSTFIR0RBSXpkQkhlWjNSZGFKTkFteVliTE1Zdmd4VWpCVkZ3MlQtTWxjZWdKR2VfdEM3ellKWlhua2lIVVZGaHB3bjlYQ0ptaWpmYUtid2dnLU0xdGlnMm9jYXlBSUJ5cV9ZbGZEUEUzMWd1czk4Q3Z3UHFWVWRyb3VxZy1EbnkxVXVmOVdmMVlHaEwteUllVkdCRThlQlc0S0xyblBKa2lUbWtwdzRJSGp0T0RfVE44cG0?oc=5", "source": "Livemint", "published": "2026-09-29 01:19", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?", "link": "https://news.google.com/rss/articles/CBMitgFBVV95cUxOZ3ZwWkRNRjJrZ1RQN0tCaXBfTGZORVVIeFJ2d1FmTkJpZ3RFM2ZUNW52alVyTDVSLXNzN0hRWUE0YUZ1NXBJZWEzbWVuV2NDUFRxNmRmWXVSdnkzZ0MtLV9UMm9FeTVaM2VGckptZWt1Wnhpd2F6TmVjcEpXVEJhNXpKWkVFd0NCelczRTBidmMxam1zVjRfM1J0aDVHaVl5MWtkQ1RvS2xXNm9lMTlraE9IQXBqd9IBuwFBVV95cUxQdU1hSjhhcHpRbXBFRmlSLUVvakR5c3ZwYlpORGl2M1hiaEhqa2dDWTVIdHhmY2NsNkVUWFZKT1c4MHROTG1fbEtCYnZnM0VMOHFEXzB5cFotZEtGNHgyVDR6ZkpwM19JM1JaVmlFMElpSUw0OHRMUXNKVUlvSEswOFdQcXlLLVVZZWpDVlE5bHplYkZoNUp4bUVEV2VhaWFVZzNDN1dpRFVUMUROeGtLQ3VlZFJjUDZ5Rmd3?oc=5", "source": "WION", "published": "2026-09-28 19:51", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty falls 1.56% as Brent futures near $108, riskoff mood deepens", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQWkFyUEVEYlc5ejlyTldhYVVvYml2c3N0YTlnSm9yZHEyMDNHUnNKVnRNeGl5NTZ0NkRpZFJJWURHUjdEczROQVpseThQbmlJdGRLa0R2X0Vid1VKM3FncW43TkVIU0hpVE5QY29VMklwNDRQa0FXNHpoRXhWSC1kaFQyVUtzc2RZYk9BMWhpTU5XTHZ4RHRMMU81azFLVFF4THZkTjJ6ZUl5NDNLcWFibmtqOUhjeEJYQW0zY24zT0lhZnMwZElXQXpB0gHPAUFVX3lxTE9jTkdQUlc5aXV2N0dtX0UzYWlfV2ZUSEhCUGp2OHFENzhsWnJQODNmemptdW9oQ2s3Si01ZnV0N3RlazVRS3YxZWJsNDZWZEx1MXdMcFFzZy11MnItN1pWQTdYS284QWJwd2hQZXdxdDc2VkR6emZGZFdsX1pDM1d2Rk1Ka25SVTRXcnAzT3dqekpRQnBKUXBwMGpHZjlQMXBtUi1pUEJac0RYSW9LcnBTUFkwbXoyQ2tDUkN4bEs5UGpoR3NBaldjekJVMFJ4MA?oc=5", "source": "Business Standard", "published": "2026-09-28 17:36", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr", "link": "https://news.google.com/rss/articles/CBMinAJBVV95cUxOOFgyakNMWTlmbmpOdjRVeTdlckZXNks0dmhfc21YME9FaUcxWjRFUG1XdTQwblI3MS1oUFN5eThST252YWpSdkhXbWZQY1V0ZWdVTGI5c2VXNXdFbzI3aUozMDh4RVMxLUxnb0tLX1NYU09yRGxGMWlvaDFlRzQyNkd2eUsxZ1lBTVNnMWI0VkMwejI1a0pWcm91NXFJSUVDZ1VhQ2JESWo2cnpDSHNHbGlhY19Za0pNQ0E3V045bjJMR09ueDZIdkNVUGthN3lRak53QWpiN1B0WkpRb3dRUTNaX1RYVXp0LUMyZG1EUWZPZlNXUGQ0WldOLWF6MFhQalU3YzA4WUttM0x6al9xS0xSVHdOajJJa2lacNIBogJBVV95cUxPanhKS0R3c2ZjbHJ5RlhHMmxmQUVLSFlUTEtBcWFTbS11YlNxdzZqNDVRSHBISmZfblhRcnhPbXVwN0NkclB6ZHNLYUk4bTZQU0x3YUs3NXdrUVE4RzJzY0VQVjZfazRmSmtudW9lNGtqcU1aMU5lMUVVS21lWm5pa2NxWlZxLTEwN0FlNGVJVS1lTzVvV1B6R0lsZGtDOUViTEFycFdFb3FmSm1KTjJZS3dEV3FUMEc4T0FVQXdBTFlCdk9sUlRyMDA5WHA0dmo2Q2lYcTFGTTJqYkI2R1JDLXZkbEdpYTBDU0NWZE1tTmd5SkFBNWxTM24yOERhN0x0SWkwY2RzZmZkRnFqNUJjdER2cFpqYmNBYVNfT2otZks5QQ?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-28 13:42", "score": -0.896, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNUkhaTEo2TVV5Q3h0cjBXLWVGX3EwakNwOXJxS1dmT0Fnc2p1eXByY2d4cFlIbE1HTER1QXFqWTB0bHNLR0lfWTdWT2RTTnJKRjYwLVhPU2t1dEdVMk5NMFZfemk3TFNhdk5GWDJGRVZUdV82aHJETlJWS051R0N6bU9pSktUWjR6SXY0d3g2ejhjeFRpdkszSFJzaw?oc=5", "source": "equitymaster.com", "published": "2026-09-28 13:25", "score": 0.652, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxQeEMyTGpqalIydEJBcFVFWC12WDdUZVYwbkJPVk1RTGRrWlpwTnlnMWJPMk9TM21CWWxfWkpIRU1QRWNCcVcya2JHbEFRLUZLa0Vwb29SOWt0Q01nbmRfZUhrcDd1M0hsb1pHWWViTnRUNkNYek9KZDVEcUlnemU0SEozeGo0dDQxV3BJSkRlS3JQZU91YWEtUHBERUt1cWZ0T2VZY01yVVlWRlNUR3FpWlJNeFFHYlhiekdoa2htZzlJeWw3b3BhaXFnRy0?oc=5", "source": "hrtoday.in", "published": "2026-09-28 13:16", "score": 0.361, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOZGFILWIzX0lTNkh0Rm8zMGVUTWxEVGdYN1FXR2JPUTJDeVhiNHdwaVdGM0xCOHdUYTQ4MmZqLUtVTXk5NU5va01tSzN0b0lJWjFMcmY3M0N3OEhaa1NYLUF1WkxLUk8zaGZZT1RzYzd3MWpMQjFmdTgtYm5fWG5Xb3VWenYtZEVWQTJsZDd6elFSTWd2RWtMeURUdTgzTFgxSExQSW1rMFJLVkpnVG5TSGx3YUhtM01oUHpvRWNERDEwTmw3RzN1d0M3SlZ3dThNbEVnNnBtVmJXMGgyaWI0NVUzeFJ3LWFocVNyVnBqM1BxeEdlZXVQeUJZdXRKdWwxM2hDU9IBigJBVV95cUxQUWpCNDFiSU9RRGF5Rm5PYU9FZGp3c2JWVFRVSzFWTHdrdDZUczkxMVBnLV8yN0hmQkdhbXhYM3dLeHViT0Fjd0o1MkFpT2h4d0tkR2JjS29ZZWs3T25DRV95dDVtNWlFQ2ZkbGZ1WVgxRU43aEZBZEZjLVNnZ0JnZHd4TkJUbUVMaHdEUTZERnFvQ25RT3V5MmxrRk5UaG1oQWoyTUtPMG9oaktqczhZel9nTUN0eEpfRkdxWGZHRTNHUnVRQVlUdENBVFctUnRRS3lMRFBWMVk4Y1JhVFFHMGNMWDNrNjhiclVOOThFa1JrTkxZWjB6U09fRGRZLVhrbGx1OE9MZHFMUQ?oc=5", "source": "Livemint", "published": "2026-09-28 11:48", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPX21IU01KT20tUWlfRy1IMWJ2LVBfSXBlOFdWYUZid1ZJdDRncFozNEtSb3NRdnlUTUlOTHFBNkloNjROR2daRV9EQlRObWhYYm1uYkl1dGdDck5yRXM5b1pzU3podGhMc1UybjV6SGNnd2J0dW9xWjRaLWVMWjBLYXlqN2NCRk1fSndYX3lBUU9LUGRBMlg0VnBfYWtJcHhaZlYwVTBxMHBhMWtXY3NhRko4UmUyVDZOUUFVRWN1OWs5RUhyOGxzV0VMWl9sUG11RjdudmdVNHp5M0hFQ3N1aUpoN19LZ19vVmo1MGVBQQ?oc=5", "source": "equitymaster.com", "published": "2026-09-28 10:56", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxPSmh5R1BHajZwb2tLTkNjdWctZ2g4d1RVU2FVaXdvU2Q4RlYzWmhia2RFWVlCbDBQdUd1NkQ1bWJUbkQtTWQ4Rk9zYkVMTVFKSGZINVFtSkVKMzhRU19ueHF3SUszbkdSOThBNFQwa0lhN1c3LVdJajZqV01uZENnWHV5UzlqbDVfSGpVdm80WlM2STJRQ3RBN2NSc1Fqc1h2amk5aFlyRExGQjh30gGyAUFVX3lxTFBSM1VWX25QMlNMcVR3N1ZFR21rX0JhZy1FVlJ3UFF1cS1PekRTcVhTOEU0Q0VGenl6Ujl1VzUtbEFvaDNiTGVpT0lHakNiQkpOX1lYRktta2stajUxT3NqSmZzRnBzVlUxNUlvdHFlRUJIN2ZKLWJfRjJ4R0ZaZVpOazYtTFlnakVCSWFINDdfcXE4cGJUYmJXcFhWbHhZUHczOHFrb0x2QV9wa0ZtTkJzb2c?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-28 10:48", "score": -0.7, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Falls 1,124 Points, Nifty Slips Below 22,800", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkNsYXBaNkxVbEJONXRoU2VUMDhmLVp5MjJ4bm9KZXJpWWp2TV9WQWhkYndIOWJOM3AxbHljM0Z4amc2NmVKS0p1SFk2REJiUVdxT3JEcG9tQ0VPMEJSa0kxNUlOS2dGTHFVN1M0T3JxbThwSkFVMHE2NzVYck1FUDR1bmM2bE1UbGJaZVFmR3hCVDJTbERmTzFnMVBoUlg3dmRkdno3b2lmZTVGNGhQbm9YOGl6SDlBSkt4M1ZoaUlsTkVf?oc=5", "source": "HDFC Sky", "published": "2026-09-28 10:46", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Taking Stock: Sensex sheds 1,124 pts; Nifty ends below 22,800, sinks to 6-month low", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaFhnckpab0xJQWs2Q0lFM2ZfamY0ZklMM19qbWRQLTFXY053NHJjdkRkMWJIWUI5aU1OVl9YNEhRWGNCU0syb0RZcXUzRE1rbDBSZGE3WWVxZmJGN2poT0VJYl9VTThlQVZVYmcwS0tyal9kcFVkRmVpT0FRODZRdFZCTzE4bjhOVXctRTR0ODBvdC1DWGVEdVY3a185cEJQdUdxRmxXbFpJQlVUdHpYNlVXS3VIdmJXQl83VFgtRnNJRHJXX3BpZkhqN0hlOXFjZ1l5ekpJTdIB3AFBVV95cUxPYTNqWi1LYzdqcXJ2c2FtWEJGUVdUd3k1YXRDTnNWVWlyUFo3am13UmVSaHd1c1FqcDFHQ0pNSXlvaVZKYnVYWGZBRzJXOTgzdkdpbHVfWjlHbnBVV3Mwcnc5eE56S0hwaFlRREl0WVIwS0Q4WjRsOGMxVm1XUWQ5YnY0dzcxOUVPbUxrUFYzcEx2T0JPZ3Z6X2tkazNjRXc3ci04MHZGZnJUalk4c0M1OG1UZ1VDQ3E1UFJ5eVVaLXdqSWs3eWVnMnRPV2ZWcHE0YUw0cGVROG03aXV0?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 10:26", "score": -0.612, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPUU44cXhTejNjWEFmX3pOMEQ5YkhwR20yQUs4NGxnNks0d09rWnU2R2pxMWdmOGQ4N2s4Nm41WW9OR1lRRzU5X240Nnp4Zm44NFJ0b1N6a052VjJpXzlmR1VIXzlobHd2OVVJYnV4Q1BfMHNZUmZ0eWNqWUNqMzNGelN0Y3o5ZXRxY3hzby05M094NmZ4aWxpakRnZlZWYlRQMnhvVGRJcGlleVFpMHlNS0VRZllGQTktc1ZUWXM3MldYVkd3THVpOUh1TVVJVDJqd2tiU1N0al9oblNQajFGUDN6RlV6UGRQU2poMTV5dDRtTEVnZ2p4bzFITjQ4SVRoNVV5Z2dZbTFyUDDSAZACQVVfeXFMTl9adnRITUZ1VzVQX29ZOGpxVXpOZ24wcFluN2JGVjFsT056LU10RmMyQ3RnM3pkQlQzSV96TXZVT1ZWdmFNU1VSZmhpMWlCaWNtejhpNWwyZ05CM3c5NjJ0VnE3MUl5R19XWXphSU50eWRpd2RZemRtMzcyZTJMcWpOUUJEZ1BwZGdyXzl6ZW9MbkRoOXZjYWw2X0tURlRyTk13ajNhUXRBbWJpaFhQd2lUd1doVXRMU0VRQVRBTU1rM0xxMFN2alRHRWlWZ3pUUzd5dGJwQTJpdUlDUjJLMjBHNVVOVTJtMFFhdVlJb2dONjJjNzU1Y0p1ZE5Cbk9XcFFRT3ZYNHZaVFY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>losers", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNMmZlbEQ0Z0pQZ3FTUXJfQ3E0YkxMTFZlY3pIRjROZTIxeXE3T05xbW1iTUpkV3QwTGlqUnplMUtNZHF0Y0ZzSXBnS1luZG5UZ2h0NkpxNzhPZW52NGUyMjZPaHpveHVHZmpHM21TNmRtS3FldUdGeFRyMEk3MzhLRVkzMWI0RVhKbHFqa2JCUGh3U09IckU2bTEwbkxwenhaSC02X2NVTVBlT0FWN0hPWGFleXdzR1FwZWhBYW1kUmVMdHdha0s2REl2LWxjczAtOTBIQjMtZ3N2SnZHNDdRY3VydlJCM0XSAewBQVVfeXFMUHQ2MUh1aFVLaDBFTVZuR05mVGlpR2V2QVkzMnJFSC1DRXROZDNRSENDMHk2blF4TGR2WllXRk13YlhFRTJJT0UxN1BPbnRBcEpJZWRSc1VTU2tfcWwtNk5vTHZYdjlRZ0FjOG1OYlVuNHFyQjN5MGRicU14eEpadzRkMjVYdmNWbG1Zbmh3ZkJicGV6c3ppMlMtLWhqazd0VkpsVHEwNFlfVFlOTDd0Zjg0OWJLeFBXMGxGWlBzS3ZheDYwdDN0UWNXdl9BUGFnTnRMamNnTWJYUVNmRWJWTzJhN0U3YzU0YS1PSDI?oc=5", "source": "India Today", "published": "2026-09-28 10:05", "score": -0.178, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVkFmQXdEZjZITFVKV1BEOHlKXy1rajlNZ3NuN3N6UXdZa2lWWVFxNnhXOTJtYmZxOVpOcVVpLWE3VUhwZUhjVXBYV2VleEVpbVR4RTRsc05tTFBIcXNoME5VaVlJVFR2ZUx0Mmx6RXlHTFhKUUdFU1J2OUhXNERPU2xsa0FGTGFOcjJzQ0ZlQkIwY204X1Z3UUZTMEt6NDZRVDJMbUQzclRobkxrcFpWbGJTQXJnRFR0ZHBMdURjQjgxZw?oc=5", "source": "Kalkine India", "published": "2026-09-28 08:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Nifty, Sensex: History favours stock market comeback in October; stocks to watch", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZE5UeURMRWtrOUFNekVkT0ZOcFI1SkE4Q28tZDc1NkJvbmFaakNlQlBDWkt4RDd6b3FpazN4NjRzWGhMN0RaYXY0U05IVEY3bU1lN3RFaURJSjRUTnF5Y3o3LW1wT3RtSkx5LW5yaWpiemJ2Ym1lYjdtTmpKY2lPWk04aVhiR25wMVl5ME9HSmUtQ3RIaENZTC1pOHpOekZVUVNSSWlFaXl0N2NrS19MeVpJdUxLeEl2blBYSjNseU41V2NjTUxmeklyeTN2Y1B2eWNuQWFTS0FVX2hJNWfSAeMBQVVfeXFMUDhHbWlIakswUl8zYmdMcHhmcVlGQ1V4RkdsdHhqN19JMjZwT0dxMGtVeHBQX2gxZk8yVlFwamlzblJNbUZJZU84N0RRTWk0U1VJRmc4VUZyV2p5NnJLNjRYcExKb3NKWjg2NmlMbUhRVFNDZHdocnNsMl9RVTF3YjBkYzMzaTRqdFAzbE9jX2NKWlZWb3FGOEFPMkktYURRbUZLYTR3SUVTWG84cXo3TzItZGhlOTBoNFhfRTlXSnNfOHJPNVctVEFEcW5WSzg1bHNHR1c4MUoyODVYWnJqV3U2U3c?oc=5", "source": "Business Today", "published": "2026-09-28 08:15", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher", "link": "https://news.google.com/rss/articles/CBMiowFBVV95cUxOci1kRlliVGdLVkdiMUM4b1lqbEFvLUdDV0VITWp3NGlyb2w5N1Rmc2pZUi11cVhmNkxDUlkwZThkS1hOZ0lFaXdmYXJoa3FiT3hfeHhaNkFwdEg2b0V6NHZaZ094cG9RZGQxLTMySlZLX1J6SGRXcU1Sb2RuTng0RzFzc1lZMWNHNjY4b29HdWpzOFRWclh4S1JGUjlGelRRSzlv0gGjAUFVX3lxTE5yLWRGWWJUZ0tWR2IxQzhvWWpsQW8tR0NXRUhNanc0aXJvbDk3VGZzallSLXVxWGY2TENSWTBlOGRLWE5nSUVpd2ZhcmhrcWJPeF94eFo2QXB0SDZvRXo0dlpnT3hwb1FkZDEtMzJKVktfUnpIZFdxTVJvZG5OeDRHMXNzWVkxY0c2Njhvb0d1anM4VFZyWHhLUkZSOUZ6VFFLOW8?oc=5", "source": "Free Press Kashmir", "published": "2026-09-28 08:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHU1a2VYbkdKb1k1RENtVm56MHlVeE9EcW1DQWd4ZmRyY0g2b2JqZjkxVENveE5US2JvaWtoanpITFc5NzVFS3hzMWRxcmtPUFJ2a1NBX2xsVDJUWEZrekpKNWVLZzZ6TlRQUnVoVWZWTzZ3Q3VBWTM0WkxqRzVhM0FzWm5kNmtCa3JMUDRENUwyVU1iZDBNd1BMRkpWenlNUHpLTDFScU1rcW0zcnNBM3pWODVoMHV1WlhwNmVSSllWTHVWOW5hRE9B0gHPAUFVX3lxTE00UXRvMWNWTlhGMWphc2xibF9MLUtJQnFQRjR3UG5nbVh4M0NWMVg2MzdockRzaEdnWlpTcEtyM3dGWnRTbnFRQnRKV1JmZk9RdWY2UnpYY1VsWjRBSDVwTk10clJnNHlCSEs0a2g2TFA1alQyYUFWNXIzWDNfeXlOejBhVGJrQTJZRG13cG5XVEdVWExyM2Yyb1owX2pmUDNTWEZsenBGcUlYdWpWZ2NpSXh1dmt4blhQYUptLWFNNnBndk04NXhzdVc2ODNNVQ?oc=5", "source": "ETV Bharat", "published": "2026-09-28 07:56", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxQVWNmQ2tBRmd0NTdUbmZ2YW9kZW1wdDZrMXU4Y0gtTXZPYU9uc3JGRGJXQnhBaEY2YXk2TGhCWlhqZGU5OWs1eDlPOTJMcHp3ek5GUEYtcGQtYUdUVmpTZzVNZGlnS2UxVXhHZE9DcTYxSk9uWkFmaThOdUdzbnpmanpXUF9sSVVReXFLY29VeTg5QUZPNkszSmNGQQ?oc=5", "source": "APAC Media", "published": "2026-09-28 07:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxONU5xeDQyaGZ0M2JBemJwU0REcWJxYkZWN1hxM2d1VHZBOGh2X3gwR3plbk90RlZMLWtWZV9jek1KR2lsTDB4d09oQlJzRTNadHgyUEY4bHhFbGp6eVhOWDhqLUtQWkpIUldLLU1EbUoyU1VfYmNaOVdqWnJzREo0Mjh3bU5wTTZPN081MmVFY0liRzQzVEtZRWFVMURCaTJZX0twZzRZWVJHVV9KaEl2LUNFZzBpdmt0RFM1OXZoLXVKQmt3WmlDSGR6VHZFMWdiV2dWcklYVWxuTXdFbXc?oc=5", "source": "upstox.com", "published": "2026-09-28 07:36", "score": -0.806, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxOMzZwenBCS1ZIMUJRRXVOZTBBME0xU0N0WGJsVEVfQkVhZ1NtMEplNUNXM1A0WGRZLUVOZWlTNi10QUVQQnJRSnZDZTh0SXVlQkN5eDZ3ZWstRVQ2TlctUE82ZmxJRG1BZkw1NjZGZGYyZWJiZlZ1YktSZU5OTk5MZ1A0Q2NyV0wzZEd6c3dHaUwxcUpZa3ZBQ0g0dGViQzhfTFF4RExTb2p4azg0WjhlVTBlSUZtSG80clVYa2p2MFBuZWIwVURXMGd5dG9wVE5sWUNLbGJCb1U5SjNBcHNXZnE2dGNkUlVhVUlrNndWVTVpOG1jWVZYeFppQUdRekXSAYQCQVVfeXFMTWsza1RTaVB1QndYVDNrWE1GWUo0QkJCd09tUGxGUkx2T3pVamh4d1VTUG9FYkxpUmpRV0RlaDhxeXVMMFN1Vk9sMVRIY2xaUjNXRlhYLWN0SXFuT2V4UktnYlRvVnZzUlFQbkJFZlNsMnBCR1JZeTVvRzVUa1duQm5hb2llbUlPNmZuQ2owWUFPbDRJWUV1ZHVoZWd2ODJMUFo1V3g5RzNfRnZ4MldzV0F3UGJfV3UzZ0lxWjdIS0hfZ2JXeXh5VFVtTm1JVnNtX0d2bjAySWZZU25TZGhiUjhkVERUenU0T1VJTld2WGM4QmVOckxtMk5QcThMbnR6bjg1cGs?oc=5", "source": "CNBC TV18", "published": "2026-09-28 07:06", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxPUkRFSHF1dXJEMUtBZUdNc0FqX0g2TjZqMV9MSFRVSXdDSHRobkFERnFiamUtMDVVcks2NDVkS3JYVzNYR0dCMnFlVDVobmpEWlduX2tCODBQMThWMm96RW1BTUlHbVlxbVMwNkpuWVphWFZJS1pTUHdwYWFJbEM2ZzNZTWhYS2luLWhYR1htelNSS3E1OHpXaV85Rm5iQWVIcHFnNkpiYzFFTHB5eXktdEplbUk3czJwV2dadzlBR3MtQmtlNnl3VDBhOGc1VGs1eENMWU54STdnREtoc2NOeGpJWXMxSnp1VGEtUVJWS2c3YWPSAfsBQVVfeXFMUFBfZ0J3ZVlJNGVQMHhXZTNvaU1wUzh3dHYzOU1sS3pFX2RIS01fSmpIMDRLOExqVmxMemRwRTZjbmxNcFRHbTlScFhKUHh4TXJzSTJyR0g1cVNwRmd3WDVWck1iaDB0b3FsVzNpYy1TZUU3RExUZjdfcl9ZTms2a2VnZUQ5NW11VEdGbFU1VmEwUjRPaGNHS01sVDVTMDNpVUltUFFUc2NKRDV6bmVyZWRMcDNXTzE0cEZLc3lNVDlpTmZMd2ttaVg0Ylo2d3BYY3BJa3dUcFM5UU9yLVpHSU16MXVUOUZ1dUhmSTdjVTRfTDZGZWUwd05zQjg?oc=5", "source": "NDTV Profit", "published": "2026-09-28 06:47", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday\u2019s market crash", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNeDY4VXlDMWttUXVoM1pMNFhYeks3ZVJpaUI1eDVJZklkME5QbmdzcFpRbFMyT3JYUEV5REM1V1hPSE9JckhRcE5EU0xpOWFfZmtTdVVqM3h2TDdwLWJDWUpMb09XOHdkVURHaUx1Y1BYNW1qbWh2cUpTazhOREdqa0lmMkl5d2pSV0RqSDhUOXlmT2VCWUdxdlZMV0lOeDc4ZFJIWHk1ZXhhbUhjUlpVSmVZNEY2cVpTQUxXdjVpOFJEWDU3RGZOemRCVEJiLUVSMXNhSWE3N25TQVV1eUoxMjJjcHh3YlU?oc=5", "source": "upstox.com", "published": "2026-09-28 06:40", "score": -0.595, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: decline, valuation and peers", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE43Z0JKcUo3bkM2R2FfLWQ5TXNkQ2dpMnNldEZ1UHU3THMyeUkyTkc4TmN5V3NEUjFiNGVEQlBWd1pwQk5lZk54YWIyX0F3ZGNWQWJJc1NGY25WakxxMjQ3VWFfRHZhN291N1F6Wnd4YW55TjQ0eXJ5bXNuMA?oc=5", "source": "Univest", "published": "2026-09-28 05:52", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "India VIX spikes 14% as oil, geopolitical risks trigger market sell-off", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQc3R2Z25xanJ3ZVVqYmk4THp6a0pjWnc2UFg5VUNQLUZOaEowZW9WREszOXhBNURRYzh4ZkZNNWJaUmx2TGZjZDBVUUsyQ2VRczJUa0lvNzBLVzFZX1ZhdlV4R1Z4T3pIaWZOdWVvaDcxLXJ0Q1hxQzNaaDBURkRVN3VYT3ZUd3ZjNFNCNzJkZWtnZHgwQ2ViSWxHa1p0TUVlRXpROXVQaTNnbGtHM1dOOHkzUkJtSnBXS0YwU3JEd2J0VmdpQng2bENyOVFfTHhiTXfSAdcBQVVfeXFMUEE2WUJINWNtZDJCUTRSY1RsRHJsWUVSZi16N1F6YjBwVU1keTJZRFpUaE9rZ2FYZ2lKdU1KaldxM1ZFZkRMelphRi0xTnBxRWczdUNlU1FQTExxUE1qSnBzQkxlVGFNZUwwdExoVG91NFlEcHdOOUtJZ0xmZ0wyMnh1QjJrZzVUSWMwX0JYbHNBVVBNNXJLbkx4UG1GdmxKNExxWVdpWFVYUkoxSWRHQWRmTWh0QlNzSTVrMHlRaGVjSFowbUtkdF9GR2FUN0wtaEJWd0t5SWM?oc=5", "source": "Business Standard", "published": "2026-09-28 05:52", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxOZFhpNERkTkx4Z2RRS1k2ejBhN1IyTzR6a2g5MjJ3bkNjeDZlOWRBSmlIek1xQk1GcVIweUZvcVFEcGwwSW90RThvU0J6cng2YVpLV0tZU1dQQlhGZUtieFVuZ3BmWXY5aFFkSlRuR2p2ZW8wZF9TQmZ2RnJoNFV2Q1lMT2JGMkxLUlp3OF81dlkyWHVmQ0xyNVg5R29GVXZkR1NLUkRqTzF2ZXA1cmtlcEptcmJNR3dwRi1R?oc=5", "source": "India Infoline", "published": "2026-09-28 05:42", "score": 0.103, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUdIB8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUQ?oc=5", "source": "simplywall.st", "published": "2026-09-28 05:37", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r", "link": "https://news.google.com/rss/articles/CBMiwgJBVV95cUxPQ3drbk9QbWRHcU9uVDJLU0EydWpPdVZRVE1rTEE5bFZadHZmUVJPeG9nUjVYWnVvSTkzNzFyNFo3TWhfN1lzX0ZScEVrSnZETUJ2MmtDaE1XYjc2TXo2a1p0UWZhcHprU1lwM3V3YUNUVzlTc3l4UXdCLVExX3dLQTdRaGh5Rk0xUDQtR2lkY3Mxd29QSHNPRU5fRDFYRVBSbC03X2pFaGpnWlJ6MFZDUGlicHlPUUpXeDh4ZU94UWR5ZHNCZ0pydDdFdHZNSjgyRThId0JfSlcxVzFibmR3clVwQzllekZnLUJ1LTdZcHpsRkt1YzN0b1FBT2FkZF9zblJkRlIxdmZfdzNFSXllSDM3b19zME9xaXhlWGk0Qjd5TWwxdDJaenFsOE5iOUNOU2VKRkxYazExZVAxYWJuVVVn0gHHAkFVX3lxTE1EMGdQdWlWbVp5aUpTbEJmb0M5dWQ5X0xJYmNpTFJJVERpUDZkcVo5V1ZGeTNyR3VmYjUyUDF0bG1HVlBGQ21nNDBfU1RZRTdYTEZFTy11OXExZmNOdzRwQTFQNlBRcFZ6NVdDSFFkeWdkV1ZGdm14cXpoTTc5eFc2WkZnVTQ1SlZ3NmxCOWk1b1BWU3doODZadUV0c0tkQ0VCeERINlczUmlYWmJ2MjNoblhPeWtqa0NvU3ZRcGw4NlQ3Mk5GcTFlZDIzQlN4SWxiNE5Md0ctQVBmMklselFGekszWTlFM2JFN244eVJtOHctcnFCc0RVM0Z4OUlqVmctZ25xTDVnTTV4djlfc2U3T2pkeC0tajA2ZnVKRDk3eEJ2ZkNWSmZicmVEOXN0UHpfRkJQdlZMLTVveENMYmdJenM0UFRfRQ?oc=5", "source": "The Times of India", "published": "2026-09-28 05:18", "score": -0.691, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeDRfUkctTnR5c0x3dEhXcmFSWWREQnhLUGMxbmFRT0RpWW1CbkVpN3dkcjJTSUZOd0ZpTjF2M3U5OW1vOEdHS3BKZG03d3BhenZtX21jTEh6VVc4ZC1oazJmSGJCZTBQTVZObmVYeEJFT2ZuaVd4OF9rbWNyUGo1T1ZMZFFtY1Zpd2dSYV94Yk5uS3FRVWFueWpYaTNyVjJVdnVoRzVFaGhvc1pOcmJOb1BWN2I1VXBTTnNNWURYZ18tRXFkZHR3Mks2TEk4X1lMb19NbVU1am5jd9IB4AFBVV95cUxNbVVHcVRveFpQaExzeVVnLXV2bTRTY0dTaTNSWDhoWEdCVkRCZjdZY0I2TElNdWxlb2RYVThZcXFFM1VDQVRxbmRETlVSTGJjX1R0MWpCQTFId3Iwb0hjUXF4bHhoNjNhZlBoeFptZHVHRWdwYTIxd0N4dmZtNHNFRXhvc0h4TVFXNl9ELUhkQ1VXS2FjV19NWWZpeGJTZmc4R0VWZldxNWVlOWlzVGRHX3cwaUd4UjVuMmlDVjlVelA5Umt3dVkwTDlhOEFSWGY5V1k0anMwOFNGbU5ZNmtZUg?oc=5", "source": "The Hindu", "published": "2026-09-28 05:11", "score": -0.852, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxObFRUUjZrRFpjTE1NcXBPb2NicXQtS3RtU0wtNHVjVHV4VHRlWWtMc1RtMzYwbXN2dnl3SVRBcjJxWFphN0hXMm0yZFNFNVduQ2dDdnVweVhTR24xNW5qemFXaTl2dkxsMkFYTlNCbGM1Si1IcmZIN3ZBTmF2ajBCcERjU1RPNXlIRHdlanZ1T0VxWWlWZkZ2eEYyZFBJWUJiSUp6b2gtcEtUQjJMaHNuWHNrRkNYek0tZlRITmkteDFreTNVb2VvcmhWZnJNa3FzTnZiUy1aXzVMMzg0cGNZR3pvMUFRQQ?oc=5", "source": "Equitymaster", "published": "2026-09-28 04:56", "score": -0.477, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil", "link": "https://news.google.com/rss/articles/CBMi5AFBVV95cUxOMEwwTHh2ZHV6TVZtbjNDSEprS000QlNTUjh4X09yNWFTUmpHcW12aERXVXNSOUlSNWVrMlM1eG94ckljVXRpdDUzVHFtWUJ1M1p2TncyUDdBUWItZnppY0dSV2VZQjZiTDNLNzRBYVZnZUpIQzBPQk1BbjNEckUtdUxuU0oxMmRLYmw1cnhOV2FpUkMwNHhqazg4MGs0VTQySklGWTJwUGl5U09GS0t4alJNajVvc2lMdi1nMTJxQkNLeTg1OWUyYWlwbVJoR3F0b2NWU1pOVDFiOVhBZk9Nbk5TQUTSAecBQVVfeXFMTkhYdHl3d2FCU3RHT2JTZzJfcmhZbzNWWFZqMXFObDVBVHNsNnZsX29kak5jdG1BLUowT0REU2xTQWt0RmdoVVg5LXpzSEJobHl0U2hnNUJ6ZDU5MHlIaVVpTG1YeG5VQThDa05fTm1IczQwR3o2TjdQa2NEOVZ6dVZuU1lXN1dEN3dZWTV6ZkgxX0tYWXJNZXJLSU1nYXh2aGtrQTJJQUl1VnRJVGhjbmZpRmp5QnBjcThMTlJrbGFvb2tjUnkyT3B3MXo4VkdEdERQM3hKSmMwWWdoWk9uZGphb0M2a1Q4?oc=5", "source": "Rediff", "published": "2026-09-28 04:51", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQeTNsTy1qVmtORm03dkJ0LVQwRUVQU3ZnT0RqMEI4NG5kVUxYeU0wcmp2N1hqaFVPdXhHNDV6cGRuZUcwclFTZ2NUV1NjdzQwYlhwWEMtcmFIVXZpMWxhWnpzOUFwaF9QUTVPQXVnTmZlUVVHNlNZQTVUOWxjdHZ6UHJuVDVtZkpPVWJqd1hlLXNlUVBEMmNuUFRCUFZZb25KNGpaNmJ4RjRuRDh5ZWFvS1JheXpLSzVQWkNSODVvaHh5ZUgyWjFPTTRnYlpxbUluek0xZHdaVU91cVRrYzFHWVJfRlJVemI0RW42Q19KSdIB9AFBVV95cUxPRWZEblJNRmlJNmdQMUpNa2FMYzNDRGZrTlp2RFh5MnZvSW5HMDhlVmNPODRlRkJTYkIySVFBWGZQLVh3Y1QzWXhValo3RkpjX0pidkhKQjJaTGFGOXhsZzBfeHBadVhGcjZKZXpuSkF1ZFB4RzVwVDIyeEtqamhHX09HR2FtY3ZRcGM3bzg5X25sU01NeW85LWQ0SG9pYjMzS2VfU0pncEJLc2QweG5wbFdZbEpDU3hvenI3V1BUU2FPclVvZGNCU1NEb0ZsZU9GdmQ3Smd6ZTZ3WTJtY3BTOElrdURuLVVsZFo3ZTVLalFBY0lD?oc=5", "source": "hindustantimes.com", "published": "2026-09-28 04:45", "score": -0.361, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE stock slips below issue price of \u20b91,785; down 2% on Monday", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQSTM2eERXZ0NPUHpTR185VFYyNzFaR0lYZlMzeHB0Y2dGMjM4RlhXdWtnczBEblZtV2F3YVItUUpYbmhGTWI0YVpSdVlRejFmZUdyWmhLRUYzNFVCNkhsdWZoMlpTenVZSDBkVXNpY0Jwam9pTmtocUJhdzA1X1dyWTVJVWhVdzJZRWpiNzVFRzd1NUREdzd3bW1vQm4ydkVETWthRE1WVGpqUkZoSVZYbmtqdVNuWnhnM2ZaaHhORjRReXM50gHKAUFVX3lxTE9fUlRRS204UnpsenJGSWtxSnJiR19Dcmh2LXFMVWhQSzdDamQ4QlBSanluUDdfYUY5YkpXcURFZUZ3TU1TQVM1WFM3QnhoLWd0VFBXckt2R25razdOMEFvc0F1emhYVzIwZkY3OXc3Z2xJblJfTXo4SFZyekdPZDlHTDc5Ykp5VVlpaU9MblVhUlBhcW9Ta3h6SWpIeFZGOGs0bWh6NmNWT09yN3pjc0pzdXdqYlBjN25UajdLT3VvZEdNRlhxazh5ZWc?oc=5", "source": "Business Standard", "published": "2026-09-28 04:42", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOXdSQ1g3eFlqb0loV211WW1MSkhiWVlTNzBWd0M2a0ZFQUduVlI2bXk2eDBmYnBIZWlFeDRrbTh4TnNsM0hBSllPZTBHOTU2ZVZaQXhZOUFDczM2ZU1wdkZteFEyTXA1SFhGR1F5dGpDY3JGd0JyOEpnZEdmdWUzd3Fwczg0SzJyQ2tWaWxNSEJYSU5kdHpJbzlYQlAwWnd6bzBGaGpIS3Z3V3hlaVBWOU55X2Fyb3FLUE9DQ1pQcVlka1HSAcsBQVVfeXFMUGxERGozWEJnZFBKVXdKSTNKNUV1N2V0ODJPUEljV281NkFXYlpnWmtINFFlaUtfUDZwcUg5RHc5VlpRT3p3TlhzOHFKNkNIVXpfZi1SbXlTQV8xa25LU2FpTXJxNkRVNDJhQVRkWVFFaXFxQW1FcWVqUE1waDJKZDI1WDMtd05IQTlzdE9xNFFpdVRIRmJ3WGR5aS1Wb1Y5WWpMUTZmcWtqdnU1YnNPTUpTOHlvcmlPMkE0Ylp4Ql9idDVGcUxTZHRibnM?oc=5", "source": "NDTV", "published": "2026-09-28 04:41", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxQQl9VUVpCdDlvWEZ4OXE5V1pabEo4U0RPcVlBRXJuMVBQMzlWQ3Jidkxzc2drSUZPcEhOdG1jRmpqRXE3TDVIdEY5T3hCVXV4Ung2X19yRU1OcE8xUU1FZUwzR3ZTOVBCYWNvc1p1U0x3WF9kazVjV3h5Tk9PbElFSzN1V25BN0xDcU83cGZ1QVRTN2kwZWxjZW9VeFFZZTctcG5PWDdhbERNdzI4ZlZlLWJLYVdxUHZOQUJDWUc0MkbSAcABQVVfeXFMUEJfVVFaQnQ5b1hGeDlxOVdaWmxKOFNET3FZQUVybjFQUDM5VkNyYnZMc3Nna0lGT3BITnRtY0ZqakVxN0w1SHRGOU94QlV1eFJ4Nl9fckVNTnBPMVFNRWVMM0d2UzlQQmFjb3NadVNMd1hfZGs1Y1d4eU5PT2xJRUszdVduQTdMQ3FPN3BmdUFUUzdpMGVsY2VvVXhRWWU3LXBuT1g3YWxETXcyOGZWZS1iS2FXcVB2TkFCQ1lHNDJG?oc=5", "source": "newsdrum.in", "published": "2026-09-28 04:29", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb2JZRzNjNjBpV29mRkZobTRsNWJaVExQeWMxZmw0WjYzZnhCNktBQm5Hdmw0U3NrVGlrYm9abFZwRlZvendEZldPMlNlVGtqVFZ0ZC1rclZGci1yb3BjbVJ1YUlta1VYM3pBMl9kbXh1VjA4ZmtURl85S0Z4OTR0cDFyWXdkU1FiZ1JVdEZ4eVBPSUtJMk9RMnFJQUpxdjRiNmNHQzdmbnRwbGNjZUFJZkVXYV9yc3p3SlF2TDFkWk8tT3hnNkZPc1JTb3c1dkZ0MS12S09LWE9vaWV0SUhOOVpGUmRrZkJxbW9XQdIB8gFBVV95cUxNVVJKdDl3emc1ZEJXb2ROY3hadnZaaXlhZEtTZmZ1RjZFNFE1VVdJTnNxVFJFRWRlaTZaUGl3ckg2dzRfY2ZXTWxvS0dWVV9ibktOOGlsWjVmVDQ4YUN3aVlLaXA1anJ6YmdNRUM4UzRrZTJxWkE5UERZbmZJR2ZHQ3phMlg2bldoWDhBT2U4bVY4SnF2c1JiQkVHdXVVSGMwTVFJVG1GckhxdURSdkpMdUpfSUNQOWo5VjNxS3FEeGRNVzZiX0UzUVozR3JXMHduVzF0S2xnMVdhYVFaNEJmOHZvZGhfbkNmY2lMYlU2Y19wdw?oc=5", "source": "Livemint", "published": "2026-09-28 04:25", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?", "link": "https://news.google.com/rss/articles/CBMi7gFBVV95cUxNNDl1aHc2VHYtR3lHdGJnY2oxdXpXX0tNN29FU0dnYnZTX1hrRWFzOFBzSk5KTWc1RTFJOFdmT3VVMEFmOXNDcXhKbHdBMVUtR0kzclhZVDRLSDRHcnljSTF6UG40ak5SQmMtN2lzRG9QSkRNUzFidmRkSnc2aHRLanVnTURTNU9DcUZXU21kWVhoVUlacHhSa2lYT2tPMUJ6NUxkWjJ1V0xpYndCQU11S2djSjZ4aXpHdHpXRTZpRDlnZFZNNk9PU1hycldaa2w5Ylg1Ull2SXU2SlIwbDVrdG1RZUJaN1JpVjRUT0Jn0gHzAUFVX3lxTFBtcU5GS1BLNVRSQ1BWekxLUmhQaFFhMlZLV3RIcjk3M0RBVkpwU19mcmNLZ3I3UXQxdFY0WHBIMmw3SUtkeTdwN1RFa3RfbzB6bkNGSzJwZWtZN2dDS3E0a04zZEFid2pXVm9xejFDbUpLeG9hWGlfQ2p4NWZtakVWUmxLMEdteDBkVFFLLTlGWHVid2ZNYmh1cHdsS2R6UjFFUzlQNXdUX3VqSlRKY014bU1mcGlxZ2VGbGtxZWlDbHRZTnVZcm55NE5zaE1ra0lUVjlTNTZaQjhQbEJLOV9yWkxSSWwxZ2FacHBnaV85SzhfWQ?oc=5", "source": "India Today", "published": "2026-09-28 04:17", "score": -0.511, "label": "Negative"}, {"symbol": "MARKET", "title": "Mkt crash wipes off \u20b97.4 trn; Sensex down 1,180 pts intraday: 5 key factors", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNFNEZXdXeWxyUDZNNkJvYmhvM29nZ05JbUhkLWRmZ2VWME9TMFQyTWctZjhoeWVNQ3dGZ21NcmV2THVjUmt1TTBwTWNJTmVnRFVzVXlCekNMZnBqUDY5M3RWSWpQeVBYTXl4Zm1ndjhBcmZUV2ZVdHQ3VUFxQzN5c3NON3N3Zjh3UjZYSjR2VER1OXBWMkZOUExnTHF6OVBtTWxCM09ZVHhmdW9DZDZ2U2FxVEtGVHhIVlNsLWhkcnByMmdVaGl1OTFwQW5GZnZ1OVJvM9IB2gFBVV95cUxNWUItS2dqMFByNUlUcXdPMUdQSHZxX3VTYU1PcEdaWnFaOUo1MnhrQWQ4MTBmaWM2eDY5WURsaFpId1RnLVFJRTdadERxTDVKc0J0UkkwRDM4V0g2WDMtclZ4eEtxY3NCVTV5SV9tQnhEZUR2aHJ4N1Q3VzFLbF9Rb1ZadHN5Vk9tOEE3THlxQVViN0tfZnB1bl9aQU0xRjFZc1dqS3RKVWpLUVM3UkV4aUYzOVNaMDlBbEM3bS0ydnltemJ4TEFOZWt4OHNOcnNNdG5DaE5GVVRHUQ?oc=5", "source": "Business Standard", "published": "2026-09-28 04:11", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 lakh crore rout", "link": "https://news.google.com/rss/articles/CBMilgJBVV95cUxQZi1NX0ZnR1pnWl9lLURWQW9uazJudU5adU43UVVWdG9BV1A5WTZaN2RPZ3NSWHl5bTlCZlA4ODkzcDRoc3JWVEtyRk1NbGx4MDQ5X3NGZ2ZHVW9MWnFTV0F4U3ZSWVA5S3BtbzdtZFRLT2JVOXJjZjUtNENidWtZai1JaTJPc0VQVE9mdDE2VGhBNXByZnZ3ZEtVdm5ZRkFvUXd4UGdfZjJTcFFRcHkwcmo3d0p0Vy0yZXNkV3RXV3ZFcTRLTlBUNGRrNXNGMGVpUXFKMDJzUndJWXpqWnpGSkFIRVJ4Q0MzQUJVOHMwT0Z6X3R3aHZ0YzU3TmN1RDZVQmNzWWNZbkF1YVJ3YlV2Tndac1N3Zw?oc=5", "source": "The Economic Times", "published": "2026-09-28 04:08", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi-gFBVV95cUxNd3FFLUl4RkRuRktMczNpNmU5VmotaWdaUENGMWExNHZJOERsVFNMQ2ZiX0tDSGFXYXhxSjVUM2p4QWUzZThrTkxDNXR6ZndFMXU2NEFTNG90Wm1JVnZpNDdaRU1vSnJOUno4VGN6dDhndTdDWDhhbGVjQ25nSDBWOXFGa2xUWlEtRDQ0dVNCZ0I2TWdQcmlZWkxLcllVUXBpa1NpdjItdDBhZlNLYUU5bWhwREZoSWV2dEMxMWJMNUZza0FpQ2dKM0JSdU9fajZEdmQzOXFnZUxqd09wcW9qd1V0alZ1TGtFYWs5d1k4eGc2NVZvbXFONkNB0gH_AUFVX3lxTE5yLU5FWTlXQmdqRWY5MS1MYXRPVHV3bjNkZWlEa25SVC1INTV0QjQzOXBxVzhFbEUxME1WbU9jbTZISE1fa19JS1dwRW9KOVplQ1A4QkNWWlE2YjM5NlBCNndyN2F4T2VfVmlOVnhEQzMtSENPZ2N2clVGNTdtVnQ4SU1idWI3eThwenZWRUZ4NzNwaHJvTllHUlBpYnQ4SEEtZFlRTmJuT3dGU2ZpRTdMLUFraWlfNjl5UWFZLTBlX2VMSTdXdWV6cXNOaGFzRU5QSjBOcHBPT081Z2R1d1JWQUt5TXFieXRCbGFLcGRkWVI4OG9oRk1YQXJuQmdrRQ?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 04:07", "score": -0.44, "label": "Negative"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines ESOP 2019 Share Allotment Explained", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxPUWZWQWFhUXl0MHliZTNDMXZuOTFtUXB4UTgxU1hJTlotLVRrSjdSMXBGWU9vaXk4ZC1vaTVzbTJMb3djcjZfZi1xYkR4clBmdE42NC05V1BWbmxfZTRXN3pDS1pKNmF0UWJ5dlE0Ry1qczcwdUQ2VHM3V0hzQ196M0ZxeVBuMkNXUXR6X01mVm9HNWgtVW5XamJNcVlTdW5MVklzZlRWdFM1MG1VNDdJbFZLcUkzVENpVVRrWkk5NTJJWG5hbWtCWmJmWTNtUDB0VWhEV0xnZEExUWxxOVhjejZ2b3BwRFk4QlE?oc=5", "source": "Kalkine India", "published": "2026-09-28 04:01", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 \u2014 Five Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNWmNXeUhrY0hPcXlaYnhxdEpqRTBKbWJadHhpVGFOX21Oc1FnTVM1UDNDOWZ3dU1jd2RjNTA5VTV1SnJHM1YyNC02dGlZYnhzeDZramF1NGpBTm0xcV9DS2ZIVURQSjlrT0M2bTJfY19qc0VmRHRBdWdZdXBmcC1pUHQzSzF4OThzSzFDV2sxbVVUQnBCWjhoemhmSEhyc01oeWJJeGlSbXlaX0xiUl9qXzdBaWhHSUt3eUdKMTh3djNuZlg3dVlqYUNjMkhpX0RoazhISVpBTnJFbmFVVGtZaFlKdGY3Rzd2SkxUTtIB9AFBVV95cUxOLV9xeHRCVnRiX1FUSENXSHZ3S3NqQkRRZFA4MzZPYkd6WENNM0NZQVpMU0FQUUJnWkVROVNSbTFrMkdJaHltbkUwTExjby0wVzViS0NkSVI1NDNORG5wNkFtSXBwMlRNbXhQbllkYnE3cGpVeVF2a1RrQTJqNG5oSnVsS2pyc0dUVEtlNnM3eHJ3bmJwbXBxZC1FSG1MbnRENzNmUFluMzJwMlJzelA3M3R5Y2V6SXZreFpGYTlZWXlITE5xS0NMdDZ3M244U0NUdWQ0R1N0TWE1bEJLM0hJYzlmYWJjcWJUUHhMVUZDZlJpMExI?oc=5", "source": "NDTV Profit", "published": "2026-09-28 03:58", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxNdFJQdUVBNmhGOF9naWYwc1VCWWozTGVwOWl1b082TGI2bmppQVQ5dmxfUWo0RGhBQ29IU29vaUJ1cDZCNEJoelpMc2g0eGhldHVGdy1WeWcxVEtZcDBDNDlfRkxNZnRFMURFLUVfY1U2UG1YTk1vampZZUozYjEzU3JGbDRWNkhhVU5qVy1qcVlhdWxFa2YzX19vSjZ4NEl0dk1reVhEMXlPb1RTTzdkNENIS2RraEdzTTlBXzFteWpPMkpkUk9MdEJqaG91ZTlUSll2UEVwcjNoM0FDdFJQVUJCM0JLQTZzS0xTVkNJQ3VIYUVyV2czYWxBLXRUNzlPUkwtTHFTNUs0cGE3VWdj0gGUAkFVX3lxTE55LTJyNkZRSldBTGdKNnM1THNXOEtPQ3FZaXdOWmhNMEVtby05Y0xaZV9QSlFuNDg3TFlfZlNpb1Z1eTI1S1ZaZDJVeGwxcktWMW9pbWxRZk83ZE1scnkxWGlVOGhDQUJJNWtnTS1MWV9BcDdKRmYybmZSVEJydVdzS1dTVGdvM0c0R09GdUEzd3Zfb3pmMXdSMGUwTk5uZ0xTTlRmV2NZWTV1M0FjWmlQZ1k3aW0wZE52QmlpeTI4bzFHTEtnbjRRZWtzb1NrTnE5dU1XX1ZQV2cxazdKZlRCNmZ6UkNSaVNnVGZVZVV4R21xZ2ZfOVBzcGZ2N3l2RkI3aGpqNnNJWjdTNnFwYnNQNEt0bw?oc=5", "source": "The Times of India", "published": "2026-09-28 03:54", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxNZ0dpRTVlRDlxc1RtOW81dTVmTTREN3MwakViZzNUakNFTDJkWkt2QkstemktQmhGZHBFWjRZYXhHcVZDcU83WWpLeXpBUDZyVzBINUVFalBwaDZ4YUhwOEdXN1E4TmVTX1ExY1U2MV83T25QZFhsa1NVcDRlWmtYSHlXdWFMTEIwcVdoS2tRWWZ6V2NIVFZMMHloczRjb0JvNHhmamx0SDEzZUxtLUJDeVgtWTNTWm50SktyR01HV0d1cXI2MmU1UWNseGFDRTVLbGx6b196aE5BMzJYV2lLYkEtZW9fcTRONVHSAe8BQVVfeXFMTVh3alpWbmYySWstWjFjN3NmVG5Sb1kyV0ZjSkYtc3MxN19pMDA3VkJwRGh0Z1FYZEU4X3BTVWkwRjlLdGQzTW9DMm5Nb05oel9SdVZrYmxRT2VIZk1nblpwMUZlWDR5ZlVnY25oU3BwaHVybk5ibEt1VXk5dS00QlBqV2ZLY01WWXN2TWNvWnc3YzRfNXBTVTJtR0w4MHRlNHBWbmcwS2tpWEkyRnlvRFFHSUtsdXdZZ010MVFsSXBEcEwyNTlNM3daV2l3Q2s2ZGVERFJNNGg5NE1iZzNJRnloY3FVYU1BRWUyaWNsRlE?oc=5", "source": "hindustantimes.com", "published": "2026-09-28 03:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQU1VkYW85T1l4Mzh4SDJFZDBhZC1GczBiSUw3TmdJYUxvTW1TRXpUd3BTOVZwY1FzODlGUkxyNFlXSklFNzBRWUZ4WEpGdUZDWWRIZ21vM05wMHBnQ2N3UTk1VENDZTVYeHJsSEIwUG15RmpnRi0yOUdBaFRTdFg4Rkp6LXBSbzVmQjRQU0V1NXdCdVRmby13QXZqb2Zzb25Fd0FsR18yZW0yZlZBd1VibQ?oc=5", "source": "HDFC Sky", "published": "2026-09-28 03:28", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxNQmUtcnhXbVNOQ0lacFk2Z1JXa0JON1VtZTRsYnZVMDlKdjh0dXhobk9tajVtRVdUbE5RV2MxUy1MbUpkNkc4UXNvalZoZXltbUNScGEyanBReERmbTRuQnB2d2M2dkU3NkJ0anMybXdHWV9QWElRVG9WcDhNSzE4eTV4VWs4WWluaGpYR1NZZTNuYVFPNWZwUk1YcXNOR0NrN0REb2V5eENFRjFaTVNpeWtJdw?oc=5", "source": "Reuters", "published": "2026-09-28 02:19", "score": -0.542, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices \u2014 Five Key Factors For Sensex, Nifty 50 On September 28", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQYTlhOERzdTdrb3FJNkRCaFpyd3p3dGE0QjFQNW5ndE9qQ0VTM3gwOURRS3hlYkxQOXh5UnUzYlVfMmxYZmtkcHVpZUpZZnhsNy05RWRKWi1FdHR2ZWVIa2F3MmxBTjBCeC1rNDBQQzhSYkVKSGdyV2pxa21xcnd3dk82Z2JOU3FMV3pKNzcyQjFreUdPZDlaNWh5WGVLUE1OSzV1VE9Qc3k1el9pOFdKYzBKVEMyRmZRMU9icTFpZTdQOFB5UEFCLXEybjl4MFFJam9tMFV4aXV5cjQ5bWR1Mnh3SUdXYzhtVUk5VU1uQWlMTHFwdlhr0gH_AUFVX3lxTE9yT1pHVWp1N19wOTVOLWdVWEloQV9BS0lKeDhwaWcwTGNqSnpxUVFIRkg3Y05tRUc4MUNDOF9CVm1EZjYzdnlsX0UwVkRDaEVKQ1ZNcVJteXhQQnpjR2JsMGh0QkhNcmt2eUxOdlRxTjVaMlFZWGtVSkU3Z2xfU1BLNjRrYzZ5eFE2V202Y2RKaVV4LXdqb2FNZHVDYlM5WmFyNWVSWnRKVDNab2h5VUhBaDlmbUVJWFNiOU9qYUNrVTJybWpyZkY3OHBiRUl0MTNBRjBNQ0lfYjljbkFCUE5oS3hDaEVILXd1TDNDRFVaOVR0enZ3VzBZZkJzQktabw?oc=5", "source": "NDTV Profit", "published": "2026-09-28 01:58", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOd3lLLTBUWlJpdVVESnptNXpwZnVmVk5zbTU4LWV3eTZyT1R0MzRfVFpFYzltdWhnSTI5Uko3M2dpSzY0NGJwZzFfbzZXM0ZOcV96T2hHaWQxR284Vi10dHRxeUVCQUJrV1lCclJZREI0NlpSdHp4Q0R2V1paVFlVWllhWkVCQWdaTlhiUjN4bENkS25yU0tJczFLVE9vUE1rY2hvc1FTSl9QZ1RkX1Q5ZVNfLUx2LWpmN2lQQ1pNMDNUS3NJenhycjRsNUNjbnZRMFNZNllsUU9WeU1xTk43NUY3OThtVFJadFJUSWhuNnZEMUh4VGdicDdNdFI5QkV4U20wY9IBigJBVV95cUxNVE84MHlqVDk1czZmeWtPckg1UUh1bF9OQU44MFlsSkdUeU14X2xZYXozODFYb0JtaGMwSDFVNzRpczZZb0MtY29aYTBsdl9fRFgzQkhhNG5Id2hYcE55WjhMYUU5N1hWRjg1RjJ6NGpuVmIyaURHQnI5d1RsVUxxRWZ2M0Q4NjlLQ1ZENVdyLWtSUkNrZG9MbVBwTnVENFc1UndfTzhlby1NdktITDZBbldMMlZua0xGbnVRTUFucy1GYVRaZUpPbEN4VlhTTGFlbElpVXBiZnNPeWpqQzVjbHhwYnFXUHBzWUM5WU1UVmh4ajlKbHpDRHdBR1F1bWNhNEhfZk1DNGRWZw?oc=5", "source": "Livemint", "published": "2026-09-28 01:20", "score": 0.842, "label": "Positive"}, {"symbol": "E2E", "title": "Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxORnluOHJzdFp4bmJaUl9hdWY5Ql9WeFd4cnF2ZnVZdkRIbGpTWlRzSlBxX1lBb3VEcFVTclJjQ0lVVkFKcGZTUFhLVDlDVkJkZDRnY3VQQkdlWFFOS2M1VVNNa1B1dmpueVBIRFNyRGhKVmRpd0IyV3NmTHNrdTZpZ3BKN3lSMjFnbGNyYnFtelZWWXgxWF9KYW5WSkoyQnA1R0dqTHBscWRHVVg2eDhveGtabHVVUjNoNTJCYjlsbGh4Mjk5cjgySUcwano1THJpbUY0X0swTG1POTA4a0ZSOEZFMVFJakg4RjI4aENIaVdZWWpSNWU5QnVDYkJyeTZlMXc?oc=5", "source": "Equitymaster", "published": "2026-09-28 00:30", "score": 0.557, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxQNmdxX3hPMzJrejF0R0pvaUNBbDFacW44MXRuLXZ1bF9yVnlwTXFwWGlOZUh0U19XOTJhYkZ1cHJ6VkJSMkk0QVAzcENpdkNJWVRWMDhkYXJ0NUdxRjVnaVhiS2VPWExCMWdaQlBmVzQ4a0lhNlNjNnV5Nk9xcV9zOWMyc24wTFdBY3lCbFdQdXlsaWFNdnVxblZYWVhBcm5wQW11NzdmV01JeVBsQV93eXJuU0ZaTmM?oc=5", "source": "scanx.trade", "published": "2026-09-27 17:20", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Ahead of Market: 10 things that will decide stock market action on Monday", "link": "https://news.google.com/rss/articles/CBMi3wFBVV95cUxOOHlGS3FhbzhQTUM5VG9rOXZjZXBTZ2Q2X1VJWjVOZXVEM1hET3BtSktCcmlhLXpIX3JUeWtBWlRNX1l4dWk0aGJiNFRuRVlzaDhfVUpzeF9jNzNUT0VpcFVSZWlGNkR5Mm5qeEU4ODR1RUpZcldoc2t3TkFweE8xLTF2YTROOGpkZ3lkWGRFQkpaY0xTRFB1akhkbG01QjZ1eXVBWlpjZHdnMGR2a0ZNODZuQWZ2cThKTG5nb3V1WUxxS3BCRHllVkhKM1hQTWVpQzd2WFU2b2x5TEdYcG5N0gHkAUFVX3lxTE9uUFVOSFVOazh5cm5jb1RDcVU5YzMwUjBJTV9yR1JmeHhaeTB1WmNIUS1faENuVTFJZEVxSEpheGpGcGMycjEwenhnekROSnR5OVI5V1l0TkJsTHp0V0g3MkF1TzNpMmZCUm54dXFiS3lJVWhGTkRnMklIT1pucDc1U0hrSkFoN1dkci1UM1UwVDdoNXNiZFNPWU9iUk1kSTV0RFBTTVl1UkJxc0t4OUIzcXRWWUJMbXcyZF9zZXp0c0ZEcUdBeXFKTFdxbzJWSzl6ZUFZTHI1aDZtdWFOOWhBbUQzbQ?oc=5", "source": "The Economic Times", "published": "2026-09-27 11:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show \u2014 3 reasons", "link": "https://news.google.com/rss/articles/CBMilAJBVV95cUxNekdIczJ6NEZleldrYUtRZ0pEMFlMaHFDcWdFeVVhVnJROWRBWTVFeURzYXM3NVY2eTUtZmNMOVg2VVF6eUZOZFpzc</t>
+          <t>1V1lIVjE?oc=5", "source": "Livemint", "published": "2026-09-28 10:15", "score": 0.402, "label": "Positive"}, {"symbol": "E2E", "title": "E2E Networks shareholders approve fund raise and borrowing powers", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxNR1MxLTBoYmdoaG5EZlRjaXpBaS1ZNmkwbjBPV29xOUNGMlFQTjdFdG5ZS0JTRExGcm1XWTJCWERCMG9SRm5FcFBwSUZuVkZ1clJ3RDdRQWQxMENXTDA4UzdRUVBZeTJNN1RIZ281SG1sYkJ1TGZZeFBpN2FIRS1ieDJPcVNXY3ZuS3VHYTgyM1VuTzMyaFZkSTAwSzhrZWI2Mm1iVHlkOUlJelFUVnM4N0I3aVFwR3hvOHc?oc=5", "source": "scanx.trade", "published": "2026-09-28 10:06", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVkFmQXdEZjZITFVKV1BEOHlKXy1rajlNZ3NuN3N6UXdZa2lWWVFxNnhXOTJtYmZxOVpOcVVpLWE3VUhwZUhjVXBYV2VleEVpbVR4RTRsc05tTFBIcXNoME5VaVlJVFR2ZUx0Mmx6RXlHTFhKUUdFU1J2OUhXNERPU2xsa0FGTGFOcjJzQ0ZlQkIwY204X1Z3UUZTMEt6NDZRVDJMbUQzclRobkxrcFpWbGJTQXJnRFR0ZHBMdURjQjgxZw?oc=5", "source": "Kalkine India", "published": "2026-09-28 08:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Nifty, Sensex: History favours stock market comeback in October; stocks to watch", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZE5UeURMRWtrOUFNekVkT0ZOcFI1SkE4Q28tZDc1NkJvbmFaakNlQlBDWkt4RDd6b3FpazN4NjRzWGhMN0RaYXY0U05IVEY3bU1lN3RFaURJSjRUTnF5Y3o3LW1wT3RtSkx5LW5yaWpiemJ2Ym1lYjdtTmpKY2lPWk04aVhiR25wMVl5ME9HSmUtQ3RIaENZTC1pOHpOekZVUVNSSWlFaXl0N2NrS19MeVpJdUxLeEl2blBYSjNseU41V2NjTUxmeklyeTN2Y1B2eWNuQWFTS0FVX2hJNWfSAeMBQVVfeXFMUDhHbWlIakswUl8zYmdMcHhmcVlGQ1V4RkdsdHhqN19JMjZwT0dxMGtVeHBQX2gxZk8yVlFwamlzblJNbUZJZU84N0RRTWk0U1VJRmc4VUZyV2p5NnJLNjRYcExKb3NKWjg2NmlMbUhRVFNDZHdocnNsMl9RVTF3YjBkYzMzaTRqdFAzbE9jX2NKWlZWb3FGOEFPMkktYURRbUZLYTR3SUVTWG84cXo3TzItZGhlOTBoNFhfRTlXSnNfOHJPNVctVEFEcW5WSzg1bHNHR1c4MUoyODVYWnJqV3U2U3c?oc=5", "source": "Business Today", "published": "2026-09-28 08:15", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Forget KOSPI, Nikkei, Nasdaq, even Pakistan's KSE surged over 100% in 2 years, leaving India's Nifty, Sensex far behind", "link": "https://news.google.com/rss/articles/CBMijgJBVV95cUxNSmhrMDZOaXFuaWJrcGtTQzNoUThUUm1XRWRhMEUtM0hGdVJvZUFiMWtzLUF3M1YwOVBzX29kYzBsNFI0Z0VJdXVleGxyY3RVVGNyMG9OM1drVXVqVzZpa2RZcWM5UFdpUmVwODRyQkdYa0ZLV3ZacnAtWWZUVnJhY095eE5GYmZJb1lSQlVIcDB2clZ4ZVprczQzTW1HWGtvXzFFNHhJTWZfaGZldFlUVUJBVF9YSFBpbEtwSThLUXJLSnR1Y0xDSThMTERuU29IaXpDakpmNHQza091LWhheXhja1BZWl9MSWpHMkF1QVhJa3gtbm1sNmZrMUtUSUdaVUFLUVgwai1XR3VxZ3fSAZMCQVVfeXFMTlJadTVlRDFjZzRJU1JtX2xtakFSNW44cUpLTDRtcFNUdmdWWnpNMlRZTG5qaG9wTGVpUHdJa2NSZnRXU3hsZ1NnekQ3d25hMlE3SkJvM05MQUVSUHdWTnZCcE9FemlJUG52ZlQzWWlFZXI1U3AxU3VRMTJNcER6bExfbDZTYlRZM3MwS0tCSWxiUVhNMjdMVmdvNXBkbjhJSENJeVBfOGNDY0M3Wk9mVFRiWTNrcWY0bXc0UWNSRkxiQ2x5UXVpV2hpM2dHdGtzcEtRODRoWkxBZ1NjeGN6YmVudkMyWFFRZGhLZ1FvMFhHclhFSkVKN2dCdjhQVXR0RzBtUUpEdUhUdWdVeFgtRmYxNG8?oc=5", "source": "Livemint", "published": "2026-09-28 08:14", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher", "link": "https://news.google.com/rss/articles/CBMiowFBVV95cUxOci1kRlliVGdLVkdiMUM4b1lqbEFvLUdDV0VITWp3NGlyb2w5N1Rmc2pZUi11cVhmNkxDUlkwZThkS1hOZ0lFaXdmYXJoa3FiT3hfeHhaNkFwdEg2b0V6NHZaZ094cG9RZGQxLTMySlZLX1J6SGRXcU1Sb2RuTng0RzFzc1lZMWNHNjY4b29HdWpzOFRWclh4S1JGUjlGelRRSzlv0gGjAUFVX3lxTE5yLWRGWWJUZ0tWR2IxQzhvWWpsQW8tR0NXRUhNanc0aXJvbDk3VGZzallSLXVxWGY2TENSWTBlOGRLWE5nSUVpd2ZhcmhrcWJPeF94eFo2QXB0SDZvRXo0dlpnT3hwb1FkZDEtMzJKVktfUnpIZFdxTVJvZG5OeDRHMXNzWVkxY0c2Njhvb0d1anM4VFZyWHhLUkZSOUZ6VFFLOW8?oc=5", "source": "Free Press Kashmir", "published": "2026-09-28 08:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Rs 6 lakh Crore; Why Did Sensex, Nifty Plunge?", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHU1a2VYbkdKb1k1RENtVm56MHlVeE9EcW1DQWd4ZmRyY0g2b2JqZjkxVENveE5US2JvaWtoanpITFc5NzVFS3hzMWRxcmtPUFJ2a1NBX2xsVDJUWEZrekpKNWVLZzZ6TlRQUnVoVWZWTzZ3Q3VBWTM0WkxqRzVhM0FzWm5kNmtCa3JMUDRENUwyVU1iZDBNd1BMRkpWenlNUHpLTDFScU1rcW0zcnNBM3pWODVoMHV1WlhwNmVSSllWTHVWOW5hRE9B0gHPAUFVX3lxTE00UXRvMWNWTlhGMWphc2xibF9MLUtJQnFQRjR3UG5nbVh4M0NWMVg2MzdockRzaEdnWlpTcEtyM3dGWnRTbnFRQnRKV1JmZk9RdWY2UnpYY1VsWjRBSDVwTk10clJnNHlCSEs0a2g2TFA1alQyYUFWNXIzWDNfeXlOejBhVGJrQTJZRG13cG5XVEdVWExyM2Yyb1owX2pmUDNTWEZsenBGcUlYdWpWZ2NpSXh1dmt4blhQYUptLWFNNnBndk04NXhzdVc2ODNNVQ?oc=5", "source": "ETV Bharat", "published": "2026-09-28 07:56", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Bloodbath Today: Stock Market Crashes Over 1,000 Pts", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxQVWNmQ2tBRmd0NTdUbmZ2YW9kZW1wdDZrMXU4Y0gtTXZPYU9uc3JGRGJXQnhBaEY2YXk2TGhCWlhqZGU5OWs1eDlPOTJMcHp3ek5GUEYtcGQtYUdUVmpTZzVNZGlnS2UxVXhHZE9DcTYxSk9uWkFmaThOdUdzbnpmanpXUF9sSVVReXFLY29VeTg5QUZPNkszSmNGQQ?oc=5", "source": "APAC Media", "published": "2026-09-28 07:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "September Slump: SENSEX, NIFTY crash 5% as FII selling and crude oil spike rattle markets", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxONU5xeDQyaGZ0M2JBemJwU0REcWJxYkZWN1hxM2d1VHZBOGh2X3gwR3plbk90RlZMLWtWZV9jek1KR2lsTDB4d09oQlJzRTNadHgyUEY4bHhFbGp6eVhOWDhqLUtQWkpIUldLLU1EbUoyU1VfYmNaOVdqWnJzREo0Mjh3bU5wTTZPN081MmVFY0liRzQzVEtZRWFVMURCaTJZX0twZzRZWVJHVV9KaEl2LUNFZzBpdmt0RFM1OXZoLXVKQmt3WmlDSGR6VHZFMWdiV2dWcklYVWxuTXdFbXc?oc=5", "source": "Upstox", "published": "2026-09-28 07:36", "score": -0.806, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Key factors behind Sensex falling 1,100 points and Nifty dropping below 22,800", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxOMzZwenBCS1ZIMUJRRXVOZTBBME0xU0N0WGJsVEVfQkVhZ1NtMEplNUNXM1A0WGRZLUVOZWlTNi10QUVQQnJRSnZDZTh0SXVlQkN5eDZ3ZWstRVQ2TlctUE82ZmxJRG1BZkw1NjZGZGYyZWJiZlZ1YktSZU5OTk5MZ1A0Q2NyV0wzZEd6c3dHaUwxcUpZa3ZBQ0g0dGViQzhfTFF4RExTb2p4azg0WjhlVTBlSUZtSG80clVYa2p2MFBuZWIwVURXMGd5dG9wVE5sWUNLbGJCb1U5SjNBcHNXZnE2dGNkUlVhVUlrNndWVTVpOG1jWVZYeFppQUdRekXSAYQCQVVfeXFMTWsza1RTaVB1QndYVDNrWE1GWUo0QkJCd09tUGxGUkx2T3pVamh4d1VTUG9FYkxpUmpRV0RlaDhxeXVMMFN1Vk9sMVRIY2xaUjNXRlhYLWN0SXFuT2V4UktnYlRvVnZzUlFQbkJFZlNsMnBCR1JZeTVvRzVUa1duQm5hb2llbUlPNmZuQ2owWUFPbDRJWUV1ZHVoZWd2ODJMUFo1V3g5RzNfRnZ4MldzV0F3UGJfV3UzZ0lxWjdIS0hfZ2JXeXh5VFVtTm1JVnNtX0d2bjAySWZZU25TZGhiUjhkVERUenU0T1VJTld2WGM4QmVOckxtMk5QcThMbnR6bjg1cGs?oc=5", "source": "CNBC TV18", "published": "2026-09-28 07:06", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxPUkRFSHF1dXJEMUtBZUdNc0FqX0g2TjZqMV9MSFRVSXdDSHRobkFERnFiamUtMDVVcks2NDVkS3JYVzNYR0dCMnFlVDVobmpEWlduX2tCODBQMThWMm96RW1BTUlHbVlxbVMwNkpuWVphWFZJS1pTUHdwYWFJbEM2ZzNZTWhYS2luLWhYR1htelNSS3E1OHpXaV85Rm5iQWVIcHFnNkpiYzFFTHB5eXktdEplbUk3czJwV2dadzlBR3MtQmtlNnl3VDBhOGc1VGs1eENMWU54STdnREtoc2NOeGpJWXMxSnp1VGEtUVJWS2c3YWPSAfsBQVVfeXFMUFBfZ0J3ZVlJNGVQMHhXZTNvaU1wUzh3dHYzOU1sS3pFX2RIS01fSmpIMDRLOExqVmxMemRwRTZjbmxNcFRHbTlScFhKUHh4TXJzSTJyR0g1cVNwRmd3WDVWck1iaDB0b3FsVzNpYy1TZUU3RExUZjdfcl9ZTms2a2VnZUQ5NW11VEdGbFU1VmEwUjRPaGNHS01sVDVTMDNpVUltUFFUc2NKRDV6bmVyZWRMcDNXTzE0cEZLc3lNVDlpTmZMd2ttaVg0Ylo2d3BYY3BJa3dUcFM5UU9yLVpHSU16MXVUOUZ1dUhmSTdjVTRfTDZGZWUwd05zQjg?oc=5", "source": "NDTV Profit", "published": "2026-09-28 06:47", "score": -0.791, "label": "Negative"}, {"symbol": "MARKET", "title": "SENSEX, NIFTY50 plunge, NIFTY Bank drops over 1,000 pts; 5 factors behind Monday\u2019s market crash", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxNeDY4VXlDMWttUXVoM1pMNFhYeks3ZVJpaUI1eDVJZklkME5QbmdzcFpRbFMyT3JYUEV5REM1V1hPSE9JckhRcE5EU0xpOWFfZmtTdVVqM3h2TDdwLWJDWUpMb09XOHdkVURHaUx1Y1BYNW1qbWh2cUpTazhOREdqa0lmMkl5d2pSV0RqSDhUOXlmT2VCWUdxdlZMV0lOeDc4ZFJIWHk1ZXhhbUhjUlpVSmVZNEY2cVpTQUxXdjVpOFJEWDU3RGZOemRCVEJiLUVSMXNhSWE3N25TQVV1eUoxMjJjcHh3YlU?oc=5", "source": "Upstox", "published": "2026-09-28 06:40", "score": -0.595, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel Share Price Today: decline, valuation and peers", "link": "https://news.google.com/rss/articles/CBMie0FVX3lxTE43Z0JKcUo3bkM2R2FfLWQ5TXNkQ2dpMnNldEZ1UHU3THMyeUkyTkc4TmN5V3NEUjFiNGVEQlBWd1pwQk5lZk54YWIyX0F3ZGNWQWJJc1NGY25WakxxMjQ3VWFfRHZhN291N1F6Wnd4YW55TjQ0eXJ5bXNuMA?oc=5", "source": "Univest", "published": "2026-09-28 05:52", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "India VIX spikes 14% as oil, geopolitical risks trigger market sell-off", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQc3R2Z25xanJ3ZVVqYmk4THp6a0pjWnc2UFg5VUNQLUZOaEowZW9WREszOXhBNURRYzh4ZkZNNWJaUmx2TGZjZDBVUUsyQ2VRczJUa0lvNzBLVzFZX1ZhdlV4R1Z4T3pIaWZOdWVvaDcxLXJ0Q1hxQzNaaDBURkRVN3VYT3ZUd3ZjNFNCNzJkZWtnZHgwQ2ViSWxHa1p0TUVlRXpROXVQaTNnbGtHM1dOOHkzUkJtSnBXS0YwU3JEd2J0VmdpQng2bENyOVFfTHhiTXfSAdcBQVVfeXFMUEE2WUJINWNtZDJCUTRSY1RsRHJsWUVSZi16N1F6YjBwVU1keTJZRFpUaE9rZ2FYZ2lKdU1KaldxM1ZFZkRMelphRi0xTnBxRWczdUNlU1FQTExxUE1qSnBzQkxlVGFNZUwwdExoVG91NFlEcHdOOUtJZ0xmZ0wyMnh1QjJrZzVUSWMwX0JYbHNBVVBNNXJLbkx4UG1GdmxKNExxWVdpWFVYUkoxSWRHQWRmTWh0QlNzSTVrMHlRaGVjSFowbUtkdF9GR2FUN0wtaEJWd0t5SWM?oc=5", "source": "Business Standard", "published": "2026-09-28 05:52", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Nifty Sensex drops 1% each as Iran US Conflict and FII Outflows raise concern", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxOZFhpNERkTkx4Z2RRS1k2ejBhN1IyTzR6a2g5MjJ3bkNjeDZlOWRBSmlIek1xQk1GcVIweUZvcVFEcGwwSW90RThvU0J6cng2YVpLV0tZU1dQQlhGZUtieFVuZ3BmWXY5aFFkSlRuR2p2ZW8wZF9TQmZ2RnJoNFV2Q1lMT2JGMkxLUlp3OF81dlkyWHVmQ0xyNVg5R29GVXZkR1NLUkRqTzF2ZXA1cmtlcEptcmJNR3dwRi1R?oc=5", "source": "India Infoline", "published": "2026-09-28 05:42", "score": 0.103, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUdIB8gFBVV95cUxPWGNSN0pnWVRzSXBrbG1na09BWUhrN3VFQTc1QVRPTVBnUlZMOXNJRmZYVHIxWEJEODNEbGdPQ1BDSkhPMFhMWTRpWkNqMnp3Mzg5WEszNVEwcXd0Z0d4Y3kzTFd1WnpVbGZLR1VFMjNJR3FzTDRsYWJxd0U3SHlkWGpCUVlHZXhfWnJDc2w1ZzJuTGRKMDljRjNHbV9CamprN2lUTWxwREpxV2JHcXJBUW1Mak9WS3RvNUxrWnJEakM1eXh2OHRPMkVscklPcHY2UF96Wll2c1IwUnRQZjhxWUNBUUowYlBfMzYyVktNOTFBUQ?oc=5", "source": "simplywall.st", "published": "2026-09-28 05:37", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r", "link": "https://news.google.com/rss/articles/CBMiwgJBVV95cUxPQ3drbk9QbWRHcU9uVDJLU0EydWpPdVZRVE1rTEE5bFZadHZmUVJPeG9nUjVYWnVvSTkzNzFyNFo3TWhfN1lzX0ZScEVrSnZETUJ2MmtDaE1XYjc2TXo2a1p0UWZhcHprU1lwM3V3YUNUVzlTc3l4UXdCLVExX3dLQTdRaGh5Rk0xUDQtR2lkY3Mxd29QSHNPRU5fRDFYRVBSbC03X2pFaGpnWlJ6MFZDUGlicHlPUUpXeDh4ZU94UWR5ZHNCZ0pydDdFdHZNSjgyRThId0JfSlcxVzFibmR3clVwQzllekZnLUJ1LTdZcHpsRkt1YzN0b1FBT2FkZF9zblJkRlIxdmZfdzNFSXllSDM3b19zME9xaXhlWGk0Qjd5TWwxdDJaenFsOE5iOUNOU2VKRkxYazExZVAxYWJuVVVn0gHHAkFVX3lxTE1EMGdQdWlWbVp5aUpTbEJmb0M5dWQ5X0xJYmNpTFJJVERpUDZkcVo5V1ZGeTNyR3VmYjUyUDF0bG1HVlBGQ21nNDBfU1RZRTdYTEZFTy11OXExZmNOdzRwQTFQNlBRcFZ6NVdDSFFkeWdkV1ZGdm14cXpoTTc5eFc2WkZnVTQ1SlZ3NmxCOWk1b1BWU3doODZadUV0c0tkQ0VCeERINlczUmlYWmJ2MjNoblhPeWtqa0NvU3ZRcGw4NlQ3Mk5GcTFlZDIzQlN4SWxiNE5Md0ctQVBmMklselFGekszWTlFM2JFN244eVJtOHctcnFCc0RVM0Z4OUlqVmctZ25xTDVnTTV4djlfc2U3T2pkeC0tajA2ZnVKRDk3eEJ2ZkNWSmZicmVEOXN0UHpfRkJQdlZMLTVveENMYmdJenM0UFRfRQ?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-28 05:18", "score": -0.691, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex tanks 730 points amid surging crude oil prices, geopolitical uncertainties", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeDRfUkctTnR5c0x3dEhXcmFSWWREQnhLUGMxbmFRT0RpWW1CbkVpN3dkcjJTSUZOd0ZpTjF2M3U5OW1vOEdHS3BKZG03d3BhenZtX21jTEh6VVc4ZC1oazJmSGJCZTBQTVZObmVYeEJFT2ZuaVd4OF9rbWNyUGo1T1ZMZFFtY1Zpd2dSYV94Yk5uS3FRVWFueWpYaTNyVjJVdnVoRzVFaGhvc1pOcmJOb1BWN2I1VXBTTnNNWURYZ18tRXFkZHR3Mks2TEk4X1lMb19NbVU1am5jd9IB4AFBVV95cUxNbVVHcVRveFpQaExzeVVnLXV2bTRTY0dTaTNSWDhoWEdCVkRCZjdZY0I2TElNdWxlb2RYVThZcXFFM1VDQVRxbmRETlVSTGJjX1R0MWpCQTFId3Iwb0hjUXF4bHhoNjNhZlBoeFptZHVHRWdwYTIxd0N4dmZtNHNFRXhvc0h4TVFXNl9ELUhkQ1VXS2FjV19NWWZpeGJTZmc4R0VWZldxNWVlOWlzVGRHX3cwaUd4UjVuMmlDVjlVelA5Umt3dVkwTDlhOEFSWGY5V1k0anMwOFNGbU5ZNmtZUg?oc=5", "source": "The Hindu", "published": "2026-09-28 05:11", "score": -0.852, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 903 Points | Nifty Below 22,900 | Bajaj Finance &amp; Kotak Mahindra Top Losers", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxObFRUUjZrRFpjTE1NcXBPb2NicXQtS3RtU0wtNHVjVHV4VHRlWWtMc1RtMzYwbXN2dnl3SVRBcjJxWFphN0hXMm0yZFNFNVduQ2dDdnVweVhTR24xNW5qemFXaTl2dkxsMkFYTlNCbGM1Si1IcmZIN3ZBTmF2ajBCcERjU1RPNXlIRHdlanZ1T0VxWWlWZkZ2eEYyZFBJWUJiSUp6b2gtcEtUQjJMaHNuWHNrRkNYek0tZlRITmkteDFreTNVb2VvcmhWZnJNa3FzTnZiUy1aXzVMMzg0cGNZR3pvMUFRQQ?oc=5", "source": "equitymaster.com", "published": "2026-09-28 04:56", "score": -0.477, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Tumble Amid Geopolitical Worries, Surging Crude Oil", "link": "https://news.google.com/rss/articles/CBMi5AFBVV95cUxOMEwwTHh2ZHV6TVZtbjNDSEprS000QlNTUjh4X09yNWFTUmpHcW12aERXVXNSOUlSNWVrMlM1eG94ckljVXRpdDUzVHFtWUJ1M1p2TncyUDdBUWItZnppY0dSV2VZQjZiTDNLNzRBYVZnZUpIQzBPQk1BbjNEckUtdUxuU0oxMmRLYmw1cnhOV2FpUkMwNHhqazg4MGs0VTQySklGWTJwUGl5U09GS0t4alJNajVvc2lMdi1nMTJxQkNLeTg1OWUyYWlwbVJoR3F0b2NWU1pOVDFiOVhBZk9Nbk5TQUTSAecBQVVfeXFMTkhYdHl3d2FCU3RHT2JTZzJfcmhZbzNWWFZqMXFObDVBVHNsNnZsX29kak5jdG1BLUowT0REU2xTQWt0RmdoVVg5LXpzSEJobHl0U2hnNUJ6ZDU5MHlIaVVpTG1YeG5VQThDa05fTm1IczQwR3o2TjdQa2NEOVZ6dVZuU1lXN1dEN3dZWTV6ZkgxX0tYWXJNZXJLSU1nYXh2aGtrQTJJQUl1VnRJVGhjbmZpRmp5QnBjcThMTlJrbGFvb2tjUnkyT3B3MXo4VkdEdERQM3hKSmMwWWdoWk9uZGphb0M2a1Q4?oc=5", "source": "rediff.com", "published": "2026-09-28 04:51", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQeTNsTy1qVmtORm03dkJ0LVQwRUVQU3ZnT0RqMEI4NG5kVUxYeU0wcmp2N1hqaFVPdXhHNDV6cGRuZUcwclFTZ2NUV1NjdzQwYlhwWEMtcmFIVXZpMWxhWnpzOUFwaF9QUTVPQXVnTmZlUVVHNlNZQTVUOWxjdHZ6UHJuVDVtZkpPVWJqd1hlLXNlUVBEMmNuUFRCUFZZb25KNGpaNmJ4RjRuRDh5ZWFvS1JheXpLSzVQWkNSODVvaHh5ZUgyWjFPTTRnYlpxbUluek0xZHdaVU91cVRrYzFHWVJfRlJVemI0RW42Q19KSdIB9AFBVV95cUxPRWZEblJNRmlJNmdQMUpNa2FMYzNDRGZrTlp2RFh5MnZvSW5HMDhlVmNPODRlRkJTYkIySVFBWGZQLVh3Y1QzWXhValo3RkpjX0pidkhKQjJaTGFGOXhsZzBfeHBadVhGcjZKZXpuSkF1ZFB4RzVwVDIyeEtqamhHX09HR2FtY3ZRcGM3bzg5X25sU01NeW85LWQ0SG9pYjMzS2VfU0pncEJLc2QweG5wbFdZbEpDU3hvenI3V1BUU2FPclVvZGNCU1NEb0ZsZU9GdmQ3Smd6ZTZ3WTJtY3BTOElrdURuLVVsZFo3ZTVLalFBY0lD?oc=5", "source": "Hindustan Times", "published": "2026-09-28 04:45", "score": -0.361, "label": "Negative"}, {"symbol": "MARKET", "title": "NSE stock slips below issue price of \u20b91,785; down 2% on Monday", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQSTM2eERXZ0NPUHpTR185VFYyNzFaR0lYZlMzeHB0Y2dGMjM4RlhXdWtnczBEblZtV2F3YVItUUpYbmhGTWI0YVpSdVlRejFmZUdyWmhLRUYzNFVCNkhsdWZoMlpTenVZSDBkVXNpY0Jwam9pTmtocUJhdzA1X1dyWTVJVWhVdzJZRWpiNzVFRzd1NUREdzd3bW1vQm4ydkVETWthRE1WVGpqUkZoSVZYbmtqdVNuWnhnM2ZaaHhORjRReXM50gHKAUFVX3lxTE9fUlRRS204UnpsenJGSWtxSnJiR19Dcmh2LXFMVWhQSzdDamQ4QlBSanluUDdfYUY5YkpXcURFZUZ3TU1TQVM1WFM3QnhoLWd0VFBXckt2R25razdOMEFvc0F1emhYVzIwZkY3OXc3Z2xJblJfTXo4SFZyekdPZDlHTDc5Ykp5VVlpaU9MblVhUlBhcW9Ta3h6SWpIeFZGOGs0bWh6NmNWT09yN3pjc0pzdXdqYlBjN25UajdLT3VvZEdNRlhxazh5ZWc?oc=5", "source": "Business Standard", "published": "2026-09-28 04:42", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOXdSQ1g3eFlqb0loV211WW1MSkhiWVlTNzBWd0M2a0ZFQUduVlI2bXk2eDBmYnBIZWlFeDRrbTh4TnNsM0hBSllPZTBHOTU2ZVZaQXhZOUFDczM2ZU1wdkZteFEyTXA1SFhGR1F5dGpDY3JGd0JyOEpnZEdmdWUzd3Fwczg0SzJyQ2tWaWxNSEJYSU5kdHpJbzlYQlAwWnd6bzBGaGpIS3Z3V3hlaVBWOU55X2Fyb3FLUE9DQ1pQcVlka1HSAcsBQVVfeXFMUGxERGozWEJnZFBKVXdKSTNKNUV1N2V0ODJPUEljV281NkFXYlpnWmtINFFlaUtfUDZwcUg5RHc5VlpRT3p3TlhzOHFKNkNIVXpfZi1SbXlTQV8xa25LU2FpTXJxNkRVNDJhQVRkWVFFaXFxQW1FcWVqUE1waDJKZDI1WDMtd05IQTlzdE9xNFFpdVRIRmJ3WGR5aS1Wb1Y5WWpMUTZmcWtqdnU1YnNPTUpTOHlvcmlPMkE0Ylp4Ql9idDVGcUxTZHRibnM?oc=5", "source": "ndtv.com", "published": "2026-09-28 04:41", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Why are Sensex, Nifty falling today as crude climbs above $106? Hindalco down over 2%", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxQQl9VUVpCdDlvWEZ4OXE5V1pabEo4U0RPcVlBRXJuMVBQMzlWQ3Jidkxzc2drSUZPcEhOdG1jRmpqRXE3TDVIdEY5T3hCVXV4Ung2X19yRU1OcE8xUU1FZUwzR3ZTOVBCYWNvc1p1U0x3WF9kazVjV3h5Tk9PbElFSzN1V25BN0xDcU83cGZ1QVRTN2kwZWxjZW9VeFFZZTctcG5PWDdhbERNdzI4ZlZlLWJLYVdxUHZOQUJDWUc0MkbSAcABQVVfeXFMUEJfVVFaQnQ5b1hGeDlxOVdaWmxKOFNET3FZQUVybjFQUDM5VkNyYnZMc3Nna0lGT3BITnRtY0ZqakVxN0w1SHRGOU94QlV1eFJ4Nl9fckVNTnBPMVFNRWVMM0d2UzlQQmFjb3NadVNMd1hfZGs1Y1d4eU5PT2xJRUszdVduQTdMQ3FPN3BmdUFUUzdpMGVsY2VvVXhRWWU3LXBuT1g3YWxETXcyOGZWZS1iS2FXcVB2TkFCQ1lHNDJG?oc=5", "source": "newsdrum.in", "published": "2026-09-28 04:29", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb2JZRzNjNjBpV29mRkZobTRsNWJaVExQeWMxZmw0WjYzZnhCNktBQm5Hdmw0U3NrVGlrYm9abFZwRlZvendEZldPMlNlVGtqVFZ0ZC1rclZGci1yb3BjbVJ1YUlta1VYM3pBMl9kbXh1VjA4ZmtURl85S0Z4OTR0cDFyWXdkU1FiZ1JVdEZ4eVBPSUtJMk9RMnFJQUpxdjRiNmNHQzdmbnRwbGNjZUFJZkVXYV9yc3p3SlF2TDFkWk8tT3hnNkZPc1JTb3c1dkZ0MS12S09LWE9vaWV0SUhOOVpGUmRrZkJxbW9XQdIB8gFBVV95cUxNVVJKdDl3emc1ZEJXb2ROY3hadnZaaXlhZEtTZmZ1RjZFNFE1VVdJTnNxVFJFRWRlaTZaUGl3ckg2dzRfY2ZXTWxvS0dWVV9ibktOOGlsWjVmVDQ4YUN3aVlLaXA1anJ6YmdNRUM4UzRrZTJxWkE5UERZbmZJR2ZHQ3phMlg2bldoWDhBT2U4bVY4SnF2c1JiQkVHdXVVSGMwTVFJVG1GckhxdURSdkpMdUpfSUNQOWo5VjNxS3FEeGRNVzZiX0UzUVozR3JXMHduVzF0S2xnMVdhYVFaNEJmOHZvZGhfbkNmY2lMYlU2Y19wdw?oc=5", "source": "Livemint", "published": "2026-09-28 04:25", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?", "link": "https://news.google.com/rss/articles/CBMi7gFBVV95cUxNNDl1aHc2VHYtR3lHdGJnY2oxdXpXX0tNN29FU0dnYnZTX1hrRWFzOFBzSk5KTWc1RTFJOFdmT3VVMEFmOXNDcXhKbHdBMVUtR0kzclhZVDRLSDRHcnljSTF6UG40ak5SQmMtN2lzRG9QSkRNUzFidmRkSnc2aHRLanVnTURTNU9DcUZXU21kWVhoVUlacHhSa2lYT2tPMUJ6NUxkWjJ1V0xpYndCQU11S2djSjZ4aXpHdHpXRTZpRDlnZFZNNk9PU1hycldaa2w5Ylg1Ull2SXU2SlIwbDVrdG1RZUJaN1JpVjRUT0Jn0gHzAUFVX3lxTFBtcU5GS1BLNVRSQ1BWekxLUmhQaFFhMlZLV3RIcjk3M0RBVkpwU19mcmNLZ3I3UXQxdFY0WHBIMmw3SUtkeTdwN1RFa3RfbzB6bkNGSzJwZWtZN2dDS3E0a04zZEFid2pXVm9xejFDbUpLeG9hWGlfQ2p4NWZtakVWUmxLMEdteDBkVFFLLTlGWHVid2ZNYmh1cHdsS2R6UjFFUzlQNXdUX3VqSlRKY014bU1mcGlxZ2VGbGtxZWlDbHRZTnVZcm55NE5zaE1ra0lUVjlTNTZaQjhQbEJLOV9yWkxSSWwxZ2FacHBnaV85SzhfWQ?oc=5", "source": "India Today", "published": "2026-09-28 04:17", "score": -0.511, "label": "Negative"}, {"symbol": "MARKET", "title": "Mkt crash wipes off \u20b97.4 trn; Sensex down 1,180 pts intraday: 5 key factors", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNFNEZXdXeWxyUDZNNkJvYmhvM29nZ05JbUhkLWRmZ2VWME9TMFQyTWctZjhoeWVNQ3dGZ21NcmV2THVjUmt1TTBwTWNJTmVnRFVzVXlCekNMZnBqUDY5M3RWSWpQeVBYTXl4Zm1ndjhBcmZUV2ZVdHQ3VUFxQzN5c3NON3N3Zjh3UjZYSjR2VER1OXBWMkZOUExnTHF6OVBtTWxCM09ZVHhmdW9DZDZ2U2FxVEtGVHhIVlNsLWhkcnByMmdVaGl1OTFwQW5GZnZ1OVJvM9IB2gFBVV95cUxNWUItS2dqMFByNUlUcXdPMUdQSHZxX3VTYU1PcEdaWnFaOUo1MnhrQWQ4MTBmaWM2eDY5WURsaFpId1RnLVFJRTdadERxTDVKc0J0UkkwRDM4V0g2WDMtclZ4eEtxY3NCVTV5SV9tQnhEZUR2aHJ4N1Q3VzFLbF9Rb1ZadHN5Vk9tOEE3THlxQVViN0tfZnB1bl9aQU0xRjFZc1dqS3RKVWpLUVM3UkV4aUYzOVNaMDlBbEM3bS0ydnltemJ4TEFOZWt4OHNOcnNNdG5DaE5GVVRHUQ?oc=5", "source": "Business Standard", "published": "2026-09-28 04:11", "score": -0.586, "label": "Negative"}, {"symbol": "MARKET", "title": "Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 lakh crore rout", "link": "https://news.google.com/rss/articles/CBMilgJBVV95cUxQZi1NX0ZnR1pnWl9lLURWQW9uazJudU5adU43UVVWdG9BV1A5WTZaN2RPZ3NSWHl5bTlCZlA4ODkzcDRoc3JWVEtyRk1NbGx4MDQ5X3NGZ2ZHVW9MWnFTV0F4U3ZSWVA5S3BtbzdtZFRLT2JVOXJjZjUtNENidWtZai1JaTJPc0VQVE9mdDE2VGhBNXByZnZ3ZEtVdm5ZRkFvUXd4UGdfZjJTcFFRcHkwcmo3d0p0Vy0yZXNkV3RXV3ZFcTRLTlBUNGRrNXNGMGVpUXFKMDJzUndJWXpqWnpGSkFIRVJ4Q0MzQUJVOHMwT0Z6X3R3aHZ0YzU3TmN1RDZVQmNzWWNZbkF1YVJ3YlV2Tndac1N3Zw?oc=5", "source": "The Economic Times", "published": "2026-09-28 04:08", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi-gFBVV95cUxNd3FFLUl4RkRuRktMczNpNmU5VmotaWdaUENGMWExNHZJOERsVFNMQ2ZiX0tDSGFXYXhxSjVUM2p4QWUzZThrTkxDNXR6ZndFMXU2NEFTNG90Wm1JVnZpNDdaRU1vSnJOUno4VGN6dDhndTdDWDhhbGVjQ25nSDBWOXFGa2xUWlEtRDQ0dVNCZ0I2TWdQcmlZWkxLcllVUXBpa1NpdjItdDBhZlNLYUU5bWhwREZoSWV2dEMxMWJMNUZza0FpQ2dKM0JSdU9fajZEdmQzOXFnZUxqd09wcW9qd1V0alZ1TGtFYWs5d1k4eGc2NVZvbXFONkNB0gH_AUFVX3lxTE5yLU5FWTlXQmdqRWY5MS1MYXRPVHV3bjNkZWlEa25SVC1INTV0QjQzOXBxVzhFbEUxME1WbU9jbTZISE1fa19JS1dwRW9KOVplQ1A4QkNWWlE2YjM5NlBCNndyN2F4T2VfVmlOVnhEQzMtSENPZ2N2clVGNTdtVnQ4SU1idWI3eThwenZWRUZ4NzNwaHJvTllHUlBpYnQ4SEEtZFlRTmJuT3dGU2ZpRTdMLUFraWlfNjl5UWFZLTBlX2VMSTdXdWV6cXNOaGFzRU5QSjBOcHBPT081Z2R1d1JWQUt5TXFieXRCbGFLcGRkWVI4OG9oRk1YQXJuQmdrRQ?oc=5", "source": "Moneycontrol.com", "published": "2026-09-28 04:07", "score": -0.44, "label": "Negative"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines ESOP 2019 Share Allotment Explained", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxPUWZWQWFhUXl0MHliZTNDMXZuOTFtUXB4UTgxU1hJTlotLVRrSjdSMXBGWU9vaXk4ZC1vaTVzbTJMb3djcjZfZi1xYkR4clBmdE42NC05V1BWbmxfZTRXN3pDS1pKNmF0UWJ5dlE0Ry1qczcwdUQ2VHM3V0hzQ196M0ZxeVBuMkNXUXR6X01mVm9HNWgtVW5XamJNcVlTdW5MVklzZlRWdFM1MG1VNDdJbFZLcUkzVENpVVRrWkk5NTJJWG5hbWtCWmJmWTNtUDB0VWhEV0xnZEExUWxxOVhjejZ2b3BwRFk4QlE?oc=5", "source": "Kalkine India", "published": "2026-09-28 04:01", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 \u2014 Five Reasons Behind Sell-Off", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNWmNXeUhrY0hPcXlaYnhxdEpqRTBKbWJadHhpVGFOX21Oc1FnTVM1UDNDOWZ3dU1jd2RjNTA5VTV1SnJHM1YyNC02dGlZYnhzeDZramF1NGpBTm0xcV9DS2ZIVURQSjlrT0M2bTJfY19qc0VmRHRBdWdZdXBmcC1pUHQzSzF4OThzSzFDV2sxbVVUQnBCWjhoemhmSEhyc01oeWJJeGlSbXlaX0xiUl9qXzdBaWhHSUt3eUdKMTh3djNuZlg3dVlqYUNjMkhpX0RoazhISVpBTnJFbmFVVGtZaFlKdGY3Rzd2SkxUTtIB9AFBVV95cUxOLV9xeHRCVnRiX1FUSENXSHZ3S3NqQkRRZFA4MzZPYkd6WENNM0NZQVpMU0FQUUJnWkVROVNSbTFrMkdJaHltbkUwTExjby0wVzViS0NkSVI1NDNORG5wNkFtSXBwMlRNbXhQbllkYnE3cGpVeVF2a1RrQTJqNG5oSnVsS2pyc0dUVEtlNnM3eHJ3bmJwbXBxZC1FSG1MbnRENzNmUFluMzJwMlJzelA3M3R5Y2V6SXZreFpGYTlZWXlITE5xS0NMdDZ3M244U0NUdWQ0R1N0TWE1bEJLM0hJYzlmYWJjcWJUUHhMVUZDZlJpMExI?oc=5", "source": "NDTV Profit", "published": "2026-09-28 03:58", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxNdFJQdUVBNmhGOF9naWYwc1VCWWozTGVwOWl1b082TGI2bmppQVQ5dmxfUWo0RGhBQ29IU29vaUJ1cDZCNEJoelpMc2g0eGhldHVGdy1WeWcxVEtZcDBDNDlfRkxNZnRFMURFLUVfY1U2UG1YTk1vampZZUozYjEzU3JGbDRWNkhhVU5qVy1qcVlhdWxFa2YzX19vSjZ4NEl0dk1reVhEMXlPb1RTTzdkNENIS2RraEdzTTlBXzFteWpPMkpkUk9MdEJqaG91ZTlUSll2UEVwcjNoM0FDdFJQVUJCM0JLQTZzS0xTVkNJQ3VIYUVyV2czYWxBLXRUNzlPUkwtTHFTNUs0cGE3VWdj0gGUAkFVX3lxTE55LTJyNkZRSldBTGdKNnM1THNXOEtPQ3FZaXdOWmhNMEVtby05Y0xaZV9QSlFuNDg3TFlfZlNpb1Z1eTI1S1ZaZDJVeGwxcktWMW9pbWxRZk83ZE1scnkxWGlVOGhDQUJJNWtnTS1MWV9BcDdKRmYybmZSVEJydVdzS1dTVGdvM0c0R09GdUEzd3Zfb3pmMXdSMGUwTk5uZ0xTTlRmV2NZWTV1M0FjWmlQZ1k3aW0wZE52QmlpeTI4bzFHTEtnbjRRZWtzb1NrTnE5dU1XX1ZQV2cxazdKZlRCNmZ6UkNSaVNnVGZVZVV4R21xZ2ZfOVBzcGZ2N3l2RkI3aGpqNnNJWjdTNnFwYnNQNEt0bw?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-28 03:54", "score": -0.494, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxNZ0dpRTVlRDlxc1RtOW81dTVmTTREN3MwakViZzNUakNFTDJkWkt2QkstemktQmhGZHBFWjRZYXhHcVZDcU83WWpLeXpBUDZyVzBINUVFalBwaDZ4YUhwOEdXN1E4TmVTX1ExY1U2MV83T25QZFhsa1NVcDRlWmtYSHlXdWFMTEIwcVdoS2tRWWZ6V2NIVFZMMHloczRjb0JvNHhmamx0SDEzZUxtLUJDeVgtWTNTWm50SktyR01HV0d1cXI2MmU1UWNseGFDRTVLbGx6b196aE5BMzJYV2lLYkEtZW9fcTRONVHSAe8BQVVfeXFMTVh3alpWbmYySWstWjFjN3NmVG5Sb1kyV0ZjSkYtc3MxN19pMDA3VkJwRGh0Z1FYZEU4X3BTVWkwRjlLdGQzTW9DMm5Nb05oel9SdVZrYmxRT2VIZk1nblpwMUZlWDR5ZlVnY25oU3BwaHVybk5ibEt1VXk5dS00QlBqV2ZLY01WWXN2TWNvWnc3YzRfNXBTVTJtR0w4MHRlNHBWbmcwS2tpWEkyRnlvRFFHSUtsdXdZZ010MVFsSXBEcEwyNTlNM3daV2l3Q2s2ZGVERFJNNGg5NE1iZzNJRnloY3FVYU1BRWUyaWNsRlE?oc=5", "source": "Hindustan Times", "published": "2026-09-28 03:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Gift Nifty Down 0.52%; Sensex, Nifty Set for Weak Open", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQU1VkYW85T1l4Mzh4SDJFZDBhZC1GczBiSUw3TmdJYUxvTW1TRXpUd3BTOVZwY1FzODlGUkxyNFlXSklFNzBRWUZ4WEpGdUZDWWRIZ21vM05wMHBnQ2N3UTk1VENDZTVYeHJsSEIwUG15RmpnRi0yOUdBaFRTdFg4Rkp6LXBSbzVmQjRQU0V1NXdCdVRmby13QXZqb2Zzb25Fd0FsR18yZW0yZlZBd1VibQ?oc=5", "source": "HDFC Sky", "published": "2026-09-28 03:28", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxNQmUtcnhXbVNOQ0lacFk2Z1JXa0JON1VtZTRsYnZVMDlKdjh0dXhobk9tajVtRVdUbE5RV2MxUy1MbUpkNkc4UXNvalZoZXltbUNScGEyanBReERmbTRuQnB2d2M2dkU3NkJ0anMybXdHWV9QWElRVG9WcDhNSzE4eTV4VWs4WWluaGpYR1NZZTNuYVFPNWZwUk1YcXNOR0NrN0REb2V5eENFRjFaTVNpeWtJdw?oc=5", "source": "Reuters", "published": "2026-09-28 02:19", "score": -0.542, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices \u2014 Five Key Factors For Sensex, Nifty 50 On September 28", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQYTlhOERzdTdrb3FJNkRCaFpyd3p3dGE0QjFQNW5ndE9qQ0VTM3gwOURRS3hlYkxQOXh5UnUzYlVfMmxYZmtkcHVpZUpZZnhsNy05RWRKWi1FdHR2ZWVIa2F3MmxBTjBCeC1rNDBQQzhSYkVKSGdyV2pxa21xcnd3dk82Z2JOU3FMV3pKNzcyQjFreUdPZDlaNWh5WGVLUE1OSzV1VE9Qc3k1el9pOFdKYzBKVEMyRmZRMU9icTFpZTdQOFB5UEFCLXEybjl4MFFJam9tMFV4aXV5cjQ5bWR1Mnh3SUdXYzhtVUk5VU1uQWlMTHFwdlhr0gH_AUFVX3lxTE9yT1pHVWp1N19wOTVOLWdVWEloQV9BS0lKeDhwaWcwTGNqSnpxUVFIRkg3Y05tRUc4MUNDOF9CVm1EZjYzdnlsX0UwVkRDaEVKQ1ZNcVJteXhQQnpjR2JsMGh0QkhNcmt2eUxOdlRxTjVaMlFZWGtVSkU3Z2xfU1BLNjRrYzZ5eFE2V202Y2RKaVV4LXdqb2FNZHVDYlM5WmFyNWVSWnRKVDNab2h5VUhBaDlmbUVJWFNiOU9qYUNrVTJybWpyZkY3OHBiRUl0MTNBRjBNQ0lfYjljbkFCUE5oS3hDaEVILXd1TDNDRFVaOVR0enZ3VzBZZkJzQktabw?oc=5", "source": "NDTV Profit", "published": "2026-09-28 01:58", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxOd3lLLTBUWlJpdVVESnptNXpwZnVmVk5zbTU4LWV3eTZyT1R0MzRfVFpFYzltdWhnSTI5Uko3M2dpSzY0NGJwZzFfbzZXM0ZOcV96T2hHaWQxR284Vi10dHRxeUVCQUJrV1lCclJZREI0NlpSdHp4Q0R2V1paVFlVWllhWkVCQWdaTlhiUjN4bENkS25yU0tJczFLVE9vUE1rY2hvc1FTSl9QZ1RkX1Q5ZVNfLUx2LWpmN2lQQ1pNMDNUS3NJenhycjRsNUNjbnZRMFNZNllsUU9WeU1xTk43NUY3OThtVFJadFJUSWhuNnZEMUh4VGdicDdNdFI5QkV4U20wY9IBigJBVV95cUxNVE84MHlqVDk1czZmeWtPckg1UUh1bF9OQU44MFlsSkdUeU14X2xZYXozODFYb0JtaGMwSDFVNzRpczZZb0MtY29aYTBsdl9fRFgzQkhhNG5Id2hYcE55WjhMYUU5N1hWRjg1RjJ6NGpuVmIyaURHQnI5d1RsVUxxRWZ2M0Q4NjlLQ1ZENVdyLWtSUkNrZG9MbVBwTnVENFc1UndfTzhlby1NdktITDZBbldMMlZua0xGbnVRTUFucy1GYVRaZUpPbEN4VlhTTGFlbElpVXBiZnNPeWpqQzVjbHhwYnFXUHBzWUM5WU1UVmh4ajlKbHpDRHdBR1F1bWNhNEhfZk1DNGRWZw?oc=5", "source": "Livemint", "published": "2026-09-28 01:20", "score": 0.842, "label": "Positive"}, {"symbol": "E2E", "title": "Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxORnluOHJzdFp4bmJaUl9hdWY5Ql9WeFd4cnF2ZnVZdkRIbGpTWlRzSlBxX1lBb3VEcFVTclJjQ0lVVkFKcGZTUFhLVDlDVkJkZDRnY3VQQkdlWFFOS2M1VVNNa1B1dmpueVBIRFNyRGhKVmRpd0IyV3NmTHNrdTZpZ3BKN3lSMjFnbGNyYnFtelZWWXgxWF9KYW5WSkoyQnA1R0dqTHBscWRHVVg2eDhveGtabHVVUjNoNTJCYjlsbGh4Mjk5cjgySUcwano1THJpbUY0X0swTG1POTA4a0ZSOEZFMVFJakg4RjI4aENIaVdZWWpSNWU5QnVDYkJyeTZlMXc?oc=5", "source": "equitymaster.com", "published": "2026-09-28 00:30", "score": 0.557, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxQNmdxX3hPMzJrejF0R0pvaUNBbDFacW44MXRuLXZ1bF9yVnlwTXFwWGlOZUh0U19XOTJhYkZ1cHJ6VkJSMkk0QVAzcENpdkNJWVRWMDhkYXJ0NUdxRjVnaVhiS2VPWExCMWdaQlBmVzQ4a0lhNlNjNnV5Nk9xcV9zOWMyc24wTFdBY3lCbFdQdXlsaWFNdnVxblZYWVhBcm5wQW11NzdmV01JeVBsQV93eXJuU0ZaTmM?oc=5", "source": "scanx.trade", "published": "2026-09-27 17:20", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Ahead of Market: 10 things that will decide stock market action on Monday", "link": "https://news.google.com/rss/articles/CBMi3wFBVV95cUxOOHlGS3FhbzhQTUM5VG9rOXZjZXBTZ2Q2X1VJWjVOZXVEM1hET3BtSktCcmlhLXpIX3JUeWtBWlRNX1l4dWk0aGJiNFRuRVlzaDhfVUpzeF9jNzNUT0VpcFVSZWlGNkR5Mm5qeEU4ODR1RUpZ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Td5S2ZqUmVJYkRaYnd2RF8xZjlDakRzUWFvaTlVb2REeWo4WUF2aTIxZUVncDVzY2o0Tmp3bVR5TmpRQmFSMDZzSTB1MFBCSWh5RmJ2b1d5QTNDdHlSN1hVcEJqUHdlOHZ3VENMVm8yWDMwV3N2M0phaDNFZzZGdE41OWVxbkdjU0tDNnFnTnM5Y2phV1pIYWN1RF9DNDhtd2JBd0I4WHRlMGFvZUtHdXNlWHJVYnN6eTFwVjVhODVsYW04ck9LRnJhb3NzTjEzVnfSAZoCQVVfeXFMUEV5VVRyZjl4LW9fV21rY0Y1SkJyYmluZTZHZlpld0cyakhLcHhKTXBNR1kwU0RET0VZeW1Ea2liT2JzSkNGenlOSzlkdVZwejU2X2FJVHFOUHZwRnM5YjRGUzJDM0VaMVlVR2M3N3FwZW83b3pBcnRwQjFTSy1UVVpDUWEwYTVDSmF0eExBWkdOQml5Zkp5aWtqU0hqNlloT2V0XzRPVml6dXV2WW5MVXlSMXZFYkQwMGNqZTBXNjBWTFVkd3pUblpDdHZ2RjlXRGlreDhvWXNnMV9KVGFySDFFNFBzUkpZUEh3OVFRVmFfSU1oU3V2bV9Pdm5hR21UWXBLYW9TUElFRExLRGdPTmJXQ2tSMjlFRV93?oc=5", "source": "Livemint", "published": "2026-09-27 09:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOT3N4b21hRzhJSXdJVzFVNWRNQ3RqT2l3aXFBN2RjN1JDX1Y2V2U5MXlDN2l1a1BGQ1hLcWktbEgwYU1UMUEtalJDYkc5RDZqX0FHdFVuMmpDVDhHdkhWSDVpMFpXLXpoa0ZTWDdGcTBxU1hJSUtIQzgwUXZvQTRPdUh6UnlXYUkxZTZHTmJFSnFQcVFSc0s4V2tGNUUwUTJVZktuRkUwY1c5eTI2NjA5VEgwMDExekhFYVhLRW4wRlduOU1wZ2JqV1F1emdiLVUwWHZwa3BmOXV3MmtLOVpzWlZOOXJ3b1MxY2pvR3VYRlFjYkxmNFdIWGFxNTJJYVVvcWhJRVVwb01UbU3SAZACQVVfeXFMUDJ0a2tkZUxvVXFoM0VZMW5YYm13NlNjNl9KY2l6X2NkS0VvMGw5eGhyWDRzU2ZsTlJmTVdTbmZ0Vzhqc1YyNGU2TWV2a0FLLU1vQmRRVktFOXhtcDRwVVVMbXZPNmo4Q0V4ZkNCU1M3TEZ3RzZwcVp6SlhoczYwY3NYNVN1c1BKSTJLYXBRbVh0bDN1ZWc4VnZNb1VZZERDOFlSXzFwNW1RX0d4LVVGRHUta0Q0cVR5dndQUGNYaTkxWFU4ZVloTzNfR01UMDJ5aVB2R0ptYjU5Q0RLRnBEZExqdEZJV1BDMHRiRTBBa19fa0djbno1blZZM1ZwUWx2VWREaHpQeS0yVFQtRFpQc2s?oc=5", "source": "Livemint", "published": "2026-09-27 04:22", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks To Own In September 2026", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWmN1VW9wZjRBZl96MHMzNnRmeS0tY28xWWZtR0hfa19FN2lyVjdtZUc0a0U3c1ZYNmZ3eTNiWFVIRElaRGV4VDFVYi1kYlN3ZjNNemNjVzFwWV9CQmxlR1B3X2kwVmphZGhMazZCVTE1a3E4clpQbU9GLVNXTWs5MjdNaldOQVBOOVpMWnNMUXA4VEtmc0drX3RWWk01aXVvd2xJS2JYeGppOElvRTFWbEJwdEJoYlBVaXFhTUNhMG14Y1FnSWROVk1qb241Sk1vOW1MWGJ3dXpuZ9IB3wFBVV95cUxPSXhqMzhnOGFvNkRfakZ0cUxHVkcycHlESmtYb2N6Vzc0MGVlSnNhLXUzOElWb1YwclgwRmY5MFhreTM0TkpzdjVjR3d1Qmd0Y1ZmRi1KM1dLeTU4QjRjOUdTNzlRNUR2b3FvaVNTbW5adHhMQk54YTR3YlRLclVfUmxKZmhRXzc4VG9PUVg4RFU5UWFOWmsyYWZHaFM4N1pxTHVLX3RVTVUwSzRtQzhCenRfa1REbS1CeXQ1Rm1GUXhvV3BxRndHZHRGVEV3VHM0S0Vidjk5bm1SSHJiVTFB?oc=5", "source": "simplywall.st", "published": "2026-09-26 22:56", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "\ud83d\udea6 Indian Markets Stuck In A Jam! But who's responsible for the traffic? \ud83e\udd14 A Bernstein note argues that India\u2019s large caps are stuck in a bygone economic era. But here's the BIG question: \ud83c\uddee\ud83c\uddf3 Is The Market\u2019s Fate Really In India\u2019s Hands? \ud83c\udf0d Or are global cues pul", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxORUdYckd5Y2pPQUg1MHZTaHlTT1ZXWTdmTGxwSWlMcE9NQm1vNE15dk9qS25VanFnTzk3c0FHTEpwaGcxXzhmekh2dUNLM2s5Zy1USHBjMHRfakhvYndNanZrV19NZVFMY1hjOHZsektLSVZoS2tTNkdzMEJTeExiS3ZVbDVRWTNWVjZ3MWVmSzhnZDVvT2d2YnEwZGJLRUp3QXhxTDVfSUc5TTdvTXIw?oc=5", "source": "LinkedIn", "published": "2026-09-26 13:51", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market News: Nifty 50 Outlook &amp; Prediction", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVJvTS1CRXVsT2ZzNUhBV0piRVV1UnZTeDVEcDJmRElmWHB5WkZsM2s5YzlYaXJuVU9vVjQ2dE5XVk93WTVVLUx2d19wRm9lc2YzWW9xX0F1YWJCTUJtMURwVzRxbC1vUlNDWEpLRUZibzdnbVdjdEJUeThfeHZLSXpwTktCQnlMM0tTNUhwWmplMHJKb2ptYmVn?oc=5", "source": "Liquide Blog", "published": "2026-09-26 12:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxPbm8wM0RSWWRXc1Bzc3daeEpaNnFwZW55Y1FBT19TQUdxYXdrZ2FJeDJGd1EwQk9BbFJTZ2xKNV9Gd1BadEFlZExtZWlxdUZEZHh1RkRIU1lMNEJVR3hkZ2VKWnNGWUVLa1Fha29hcWcyNVR6dEdydjluNGxlN1YybHFabnUzRWdzMTFSWThkNWRRX0NXQ055dWl2dXN3cGw2RUJxSHAyTTFWMnNOeXZ4S0xGQXFjRmhub1lHeVQyRUhUdEpFSGEwM2U1MEFnbExtV1JPRUVNRmV2dUNfZ1BiblROc2IzLVNPclpNRtIB-gFBVV95cUxOT2FRblV0ZG5vNUh2QTZGeldJa2FuRF8xSmRWYUQ4a1NLblFyUmtJNTRCdHB3NENTZUZhdi1Ha1g4aTV6cy1POUl0Njl3bzZNdE1ZRk43bWQwRXZvNGxncTdBaWg3cDNUMHcyRVp3d2ZKRmljNXZwQktjUTZnV3NpWldYMmNoV0ZJSjZONVJjNEQ3d2ZLWXlVREFsd1VFbFdob0xydFJ5dHpFdGIzeERrQU5kcXBubmVLd2RZODE2Skd0Yk92bFNnWG1qUjNnZWRSR2YwaWIxLU91ZHBzTlJVb0twSW5pUnYxb3E1WEJFTWdmQ0tzeVhaZjRR?oc=5", "source": "The New Indian Express", "published": "2026-09-26 09:15", "score": -0.128, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQWm9DM0I5TUU2aWVIdHhCam9zXzFSUEI0RzhWaEFxWDFfbDFoeUFJUEZQbHk2OXJJdlpjeVBTVjd0RDdMSjdPMjl0eTN3NXZnRmR5bTM1Qi1KS3JsNFRrZlFCcmViSW5MTmdQdDItWTU4T3lUeFFkTEU5VHBEV2FmUjlqOWdvaDhNcGZlTk9jTjJQeVZ1Zkc4Q09fUGY4LVZiWk51d2U0ZGtxRFZ4cXpMV1V1UlJOdFN3RnZyTA?oc=5", "source": "Kalkine India", "published": "2026-09-26 06:30", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure \u0915\u0947 \u0936\u0947\u092f\u0930 \u092e\u0947\u0902 7% \u0915\u0940 \u092c\u0922\u093c\u0924; \u0915\u0902\u092a\u0928\u0940 \u0915\u094b \u092a\u093e\u0935\u0930 \u0915\u0947\u092c\u0932\u094d\u0938 \u0915\u0947 \u0932\u093f\u090f \u20b993 \u0915\u0930\u094b\u0921\u093c \u0915\u093e EPC \u0911\u0930\u094d\u0921\u0930 \u092e\u093f\u0932\u0928\u0947 \u0915\u0947 \u092c\u093e\u0926\u0964", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPVXU1bkFLVlVQVmhKWjdoVDlSNFQxTTlheVZFdGtDeEVEVzVtc3Y5Qk45R1RaOV93WlZrOXF3MzFKTlE5OGR1Xy1DcnFtUTV6YTYxYXlVMHlTWXFEbnlMaFliTC1uYTZOeVhCY2ZjQW5Qd0pzcEZWUmx5NHJHZ18tSDNHbTZrT29hbFNrWXFuQzFRTW5OQ3BMRERrUldoQUVMYmRTeTBfZEctVi1DUzF1bHphN2JnNV9lbWx3MGU5MlZRbHdZYnNrR1NHUVJVekRybmZtcWNFNGQ?oc=5", "source": "Alice Blue", "published": "2026-09-26 00:50", "score": 0.34, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxOTXpFTDNOdlg4R1lYS1FPU2VpM05pUUVGSHBvdWxqLXJ4SFpPTXZ6Q25FVjh0V1lvbnR3ODJsa1Q0ZDJlbWpRZFFiSmw2MUhwVF9lUVVyVWJTQ3lTMkJHNmtHMFNOMmwyRng2TlFUVlM0WGhOdU9KaTh4QWZ4bm81SUlqcEN0dm5FRHZVQ09UdTBIVWxZajM4alAwcjRrUURkMHFPSnNWVndUNjhjcjVUb0ROQVZJTFBCMmU1bFUyNUl5c0YzZDQ0bmVSNXB3Nm9pNUhnaW9RdEJYMU9WZkVqS3FHdGRaTnPSAewBQVVfeXFMTm9mRGRDb0NZSlU0UTM4c19nUEJhMERMSFc2ZlY4Ul96bUdPUFBlSEZQZ3c0NnFXX250RkQybjhjQkxoSVc2OGNlTnNoOWcweUdOVjlzdS1sZjZvUkM1T3FKWkxTSFczOHVHQ3pMbWlJbGxDX2Itd29DZU5iTzF1ZGlpSEk2dkNaZE0tNXA0Sms5SDdsZ3VuNjhQTGxYc0lYemowWmJzbFE2VUJjb0drM1NYNktGWTBieGFoOFJEbU05ekZtODl1UGsyM1UxbF9idTdCRlppbW05c1RYZXhVaFd3eXc0NU5PN3RGeWM?oc=5", "source": "simplywall.st", "published": "2026-09-25 14:34", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "PERSISTENT Stock Price and Chart \u2014 NSE:PERSISTENT", "link": "https://news.google.com/rss/articles/CBMiYEFVX3lxTE01VG4tR1ZHRnF6bF9CZzh6bHlySkh2MFd6bGJKUVhycUhNQkh2R2syeXEzOG9tLVpSTmNrcUEtOUVWZm45QUE1ZTB1VXFYSEc0LUI0akZJc3NQTDE5SHh0cg?oc=5", "source": "TradingView", "published": "2026-09-25 14:31", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "R R Kabel board approves proposal to acquire U M Cables\u2019 optical fibre cable business; shares rally 72% YTD", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcGpkYXl6WDhuYWFNMkVobGFYaHROYTR3R2NJcWhMcmptMEpqS09jeVBMRFNsQjkxSE9QVWVZQUVXeUFweWdVeEVTNzUycGFHMmxkekJSR2F2OFl0LV9CYUg3M0VvVnJEaUlEUFNrT2RqVkpNY21PeW53SThRUzMzSzhqYm93VkNPWjVSWUJUYnFicTdONEVQY1NwdTlqTTlSbWhxUGlZMEN5aUpyWjN5aUgxckhCampqdzhoQTYtZEpkSGljNWhhVUJoM2dqNUhSMGc?oc=5", "source": "upstox.com", "published": "2026-09-25 14:04", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "India shares log longest weekly losing run since 2020 as oil prices bite", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRDlIOXFjNzhyRGVteU5DNTJCdVlRNUZEY3VObFdZNDI1MDU2SUo0NEM1N1JDTHpDMTk0YU9OM2V1eXRla1VaanBsTTlUM1lWR3VYU0g1eG5pM21hNzFWQTdabWphemRRMlc1U09MdWxVRVNLUWxjd3pIODVuY2UtcFE0dEhPTUM2MU1pbHNOQ1NnOUQtME1TTDJjSzJzOGljZTRmN0NBZ2Q0S1VodGZaSXFxZU1VTGNnanc3a0o0anM?oc=5", "source": "Reuters", "published": "2026-09-25 12:52", "score": -0.382, "label": "Negative"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxQbV84TnZBcDlZcGRjQ2YxN1Z3eC1lNHdhNTN1ZENIRnZsR21zVVQyQUFmNnpKbmQ1VWl6SEpGNi1XX01ZcXZuM09QZklRNUh3YTZwd1RJNDRpM01BRUJfS0VJSXRGVy12UllLVU5jZnd4UWMyQjlkZHJPRGsxX2RQZnY2c3RRRE0?oc=5", "source": "Univest", "published": "2026-09-25 12:22", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Two years ago Sensex hit lifetime high: What went wrong after that &amp; what\u2019s the road ahead?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPNjg3MGJpYWo0SHZZNlZLX09hOHJTTU1CZm9FYzZTejdsbWl1bmZfY2t4SVEyNTFLM01ZcVZueHJhZlVtRC1zdWo5ZXZaRkhWOUtJc193NnZOZVhXUDcxcWpzcXQ0eHlmdG1TWEQ1R3NfaElGZjc3eldBcmtIbmphT3F4VFZoMWFwOFZQZ1ctWjAzRlZNTlZOOVVrVFVGcVJkSHo2WVBleXNYWi1VU3VaMk1teVJnVGgtN3BKdXY4U1cwTXYyUXJ6Q21YWmhZbTI5QkdCUG5xaDdyUVFvMi13SGVteFl5a2lSNUhYSTN1ZFo2Vkk1X2lURTB4QXpmc253Zmc?oc=5", "source": "The Times of India", "published": "2026-09-25 11:56", "score": -0.44, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel enters optical fibre cable segment with \u20b977 crore U M Cables acquisition", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVHNrRVg1VDRadktqWU9TVnUtdlV0UGx2YVN1Wk9maFBKZkl6NXN1dEhmSGxFNVVaejRWQy05czFfT2twSjJxX1lDR2x5QTZycklWVWJBTDNGZ2lWYWFGYUN2dHUtRnEwUGxsVmw5UmhRandzdHdDUHZMUGZNbnhsUVdmbWJ5VTZ1NnlDdTM4UVJJNWlDU3QxRDJfeUZyMWF1Rl9fWmUyWmdyUHZpVXNRT0lkVjVUaHZpX25Na0RVa1lHRFh1ZFlQOUlhVUFJbmVLamVsdHZHVkt6bWJrRXY5UdIB5gFBVV95cUxONTd5ZUl2WG5FUzRqVGsyNGNWcHpEN0ItSkJvV2wweHhrVENsb1NFa3ppbm92bUFGdERMZWlva1YyMEl0dDYxcXg3clQwZ0xKRk1OY0c0cjZOYWFmamVwdnNsTm51TTIwV2lhNnFNX1pfS29Od0xQZXpWNWdFd1k5Y1Fmc2ZKRWJtRGlJUDdBM3NUS0RSMWJtdDlVaGM0NzVuZFZvTktxelNrd29GOFo2SjU5ZU1HR2VWUHZaUTBVa0l3TjZVOGZaWDZUTzRTSW52VnIyNThJb3p6b3lPU3RualRINlVGZw?oc=5", "source": "CNBC TV18", "published": "2026-09-25 11:42", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPMGh4UXhKOTVzdW1BeE5LNGFFR2Jwbzd3T3ZvV0NTYU4wekJVZmE1U0FuZ3FsTXlTakZ1Y09lZTFJRXVIOVl2Z1R2ZmJsUUFHaEZXREJUZEtCdFNjWjRKWHhZWDNBMGpMOTJnZHhIa3ZLdHpvQ0tmMEdOTy1BN1hBcm5WcFZpYUdVZmdXZkVFYUkwdnA1VFhQWlNDc2xGNzY1eGlPdjhvZGR2MlRYbnVoTVFjakVVeTd5SWxEbnc2RjlxcHdkcTRYb2tDaXhocjVD0gHTAUFVX3lxTFBiSHlyQWowSl9jdW9fNEZsWnBKV0VjVkFTcV9kNkNoNDQxUHhiZHZiREtiMjkzMGplU19TNjNqVXlVTFRTd1kzeTBwSlFCS2VDdEt2VmlOb1ZvY3ZhMW11aFZWd3Y0bWxUWUQ5WmhGN21xeE9XcnNHWUpvQ05iRER2R1NoaXIwMDJ2dm84a2NpRzRVZ1N5NWk4Tk9XOGxKb0R3aHZlNFdfTzU2MFBMQjBBeEFVSUV5cDQ5eTVWSWgwRGY2dGs3X1BoWDdQQWRhUzJiRXM?oc=5", "source": "Rediff", "published": "2026-09-25 11:22", "score": 0.612, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPbUR3cDZZTmx0T0FjVGdkU0ZOV21PRUFzdFNkR1FaT2hqcFQyZkVxS0ZKSVEydXF6OGlMbnUtakExc2NhTGI0WkE3NXVYYlpnR1NBV2l5SUxWUFhXX0VtemF1WG1pdUU3TnoyLVJCb3ZxM2ZrdjUzRW1wZFJ3M01WQmtaYnFWbUZxR1NGQ2Fwd2dJRTM1QndDMnlobXFVbjAtUnVscXUyZUtyMVZIaEdmSE9MQlFSTkpkYXhvQlBicjJTRjJ6V2VIRnM4RFNCSDNWVmFudGZNTQ?oc=5", "source": "Equitymaster", "published": "2026-09-25 11:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rebound on Value Buying After Sharp Losses", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSjR4N2QtaTVfdUc1bkpKY0JWcFZ6RzdlM21SN2M0eXNfT2hQVWt1eXZxYmlmUFVBSGhRdmxTalRGYlIyV3J2M2lmZk05WUpVcDQ3bk1IeFh5aTN5Mm1nVXFZOUJCenlPRzR6VVAtaW0zcjZMQno2QTh0MklYUFhvZW1Pa1JvRDNCS2JIa3U5Qk1SMjJRTm5zZjE4NGFIVlVFOHpwVWJHTlBtaGfSAbABQVVfeXFMTzMwT3V5UkdaUUpqeTRFOHBwOXhrSFdVNjV6QXlZc1lzN1AwUzU0RFNxYl9aWGdQSS10S1d4dnRZNlhQNjZzMW1hTmhBaFoxMmFIaWNIdjdDblFCanNIUjJXMHR2SEJyUnVUb1J4X2ZoS2FVLWh4N0tnZGJ0RGc4aXpPNnQxLXFrR3J1Z3FGczZjM181U3FTbnVySUducS1VNGUyaVByUVNyanFPdHRHSVQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-25 10:48", "score": 0.318, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxPQUxBSWtnLWFqMkRfMks5NTlUcF9sTm1lNEtSdFZDaEstMWw3ejZUX2czMHFwS3k5MEFOWHNBb2w5VElVd011VTdpZ3V4OE94Q3ZGUVhJYTJhXzlKQnRicGVnc25ZNDZDdzhmN09xTzJCNDhLM0JQOHdRZlFKTXlXLQ?oc=5", "source": "INDmoney", "published": "2026-09-25 10:31", "score": 0.572, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Sah Polymers Share Price", "link": "https://news.google.com/rss/articles/CBMia0FVX3lxTFAxM1NrSlNad3RNSzJKUGVISVgtY1lGZ3NYN3FyNTBJb0FBYlNGQjVCSTRBWXE0c1dHR1lvemdIOFFwLUQ4czVFaGplWHRnbWR4Wkc2N1pkTUlfQ29mQkFNdU9DZkg2akQ2LVRF?oc=5", "source": "upstox.com", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "Nifty Chemicals (NFTCHEMIC) Share Price", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYURIakNOVnRybktpTUJSR0ZBR1Vla0tUNHQzQmY4clE5d0o4Q1pZM3BtaGhTcjk4UWtuR2tXbmJ1S3kxOGZ4SVhYSURHRkRCN3NwUUxzaDJ0dUZZWWZ0aWhlQkZtclZ6U0hIbTNJTlpNQk9Sblp6WW1WUTVyb3ZRRHJlV1BoUUE?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.402, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today", "link": "https://news.google.com/rss/articles/CBMilgFBVV95cUxOSmhSUlhBeGVjR0VmV1paYzdJdDlLd045M2hLX1dPc0NQdkJXUmR5dUNCNGNYeGxBNnlrTVNtMkQya1JiamhQQTNfbU8zdmxndzB4TWlmSndSdmpzZ3RGU0VickFfeDg2U0x0ZmFkMWtxMndNU3FkdmMyTTE3R20wdnNpdUJoN1RNdlFKbXJHNXlqMU9KUUE?oc=5", "source": "Univest", "published": "2026-09-25 06:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNU2lpQ2pNTWhOZFRyMzhsc25Pd1Z2VjI5SkFZa2d3VDhmQVNmT2JuNjBoNWczYU5QaDZZLVhRdVc5WkNZR3RzcGhTN3JpdEJRcWllYlNWQjd3aDBwM0Z3RnNVeG45SUllbmQzX3RtTlZVVmFyRllRTHZwcmZVcFpybi16QVlYeEZoU1Q4Z3o4ZXMxekZ4UWdWYjV1b1Njc3g0dVJlVk5sbEFmRkp5VFNvb1BXeU40RFhHZV9jOXdhU2tIeXV1Sk5mYTdUaHVRamxZTHlqbkwtLVA4MW93SDVJbk5HT0hrbVYwdEZJQVJfSDJSanFzQl9lZtIB_gFBVV95cUxQZ3hlSUszOFFSZW8zSkdBSm0wY3ZNblIxRS1HRnBLVG91VVZ4blFjb2xzakhtMjNBblRzU09WR2NZeWdGT0x3ZHBiSkNKNkJoTmFGanNzX3owUE5sb0szNFhhVEpjV1I3NVFKMGU4VnRCTFBON0doMmhmUUtnZDVYTWpiNV9CZWdkZnlEWXdZVlpBRFRCdUNLVU4xQjJ2dHdJM21Va21pbGppWDBGUkpYbi1VTjVVTEEwM0Jza3ZzbEFHQnFybUJJTUVTc3lsbVNVbF93VzdqV3BWdHR6THZEYXpBeGRZbHZ5Z1hUOUFWeDVJWTRFS3htSFB0N2Jadw?oc=5", "source": "Business Standard", "published": "2026-09-25 06:34", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxQTE9BdERYOTF4QjNsVFdOSUVsVjdickVLMkJHYld6YmRCdm5PRGloTnh2OHk5VmRRQjJiTDMyTUZNalZMQXk5eGt2OHd6RmllbVhWbUpEQjhnOVJvbmtVU2w2aEs1cTd4WWljRTkyc2dmT01xZVRnb3k2TGlvS0lCT3NVcS1yclo1TERWQWszM2l1dzhDdnBoSUpOVTRQNW10RFd6ODFidlM5QWttRnkyX1RWaWhWS3RzWURldTM4MDctTWR3d2ZWSWh1a2FJX29lV3Z5NnkxWUhVYzRzZmw3NGI0V1Q0R1o3TTVVZUl3REw4TFBtNTdUZVA3Q1VxanRQYVF5Yk8xc0g1YkVUZm1mTzFR0gGXAkFVX3lxTE9HLTI5ZmFma1R5UUFlREE1U052c1BXWndUTkY4ZlpnQi1hVGs0MFNNTS1SZU1qeUM3cXduelRYbzM2WENOQXNDVUprdkVfYnJDbE90cE9CQXZ6bUJEZkkxdE9wbW52akpFZTZwWGtQaTFQei14d2hFLWJMT2VpOVotMloyZ0U1UFFLeWZNZ3NzYVozQ0lwbE50S2pJN0REOVpaNWZXX0ZOTFVmZWVkbDI2RFA0OFRtUFZxc2ZEeF83emxxMHN2LVk2M2tNNUpmemRCR2lXeUtwYlVPdHFzNGh6Z1RJVmV2aUgtVkFzajM3R2VtOU9qNlAwY29sN09XSDRRR0FXTF9zVV8tNkY5YVpPbVYyb01icw?oc=5", "source": "Livemint", "published": "2026-09-25 05:52", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE shares dip on day 2 of listing, brokerages back long-term growth story", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNVmN3NGUwRl9DSWI4bV9GWXNDZk5fRV83NEJWVDc3RGVNQkh5ZWktVjdJRnJZcE9aZUxUQ3dyZWZodFFiZzljZmppdTJ1R0lPNUtPTjdLSVdfUXJ6VmNyN1FWVElaV094SGFJMlNOU2drVGlFdUlPSGpld1g4VGpoa0QyS21vUTE5QWViVl9ETWtJdHpKbDNvek9wOHZnR0ZRQTNvNGdPSmVaV1BvRmMyQmtPSWZpZmFwYklWOGpkS2dKdF9DUDg0LUU1QzZDUkhLNHdNR0RRd9IB3AFBVV95cUxPdk8wd0R3RW9FSW1lamlhT2tiT0phLWRyT0R5bDhEUVU2aVRjNVZwMGo0SHlfZVotNHZoTGxCR2ctcGxWNml2UWZCZ1FGOEJZNDRFNElqSUtKY3I4NjUyR1RsTEpZbWI2YkNudU9GRXJURUFfRjZfSlh3VHpsaWJ0VEhRdGhhcHVMVjMxMkg0Q3pEMWY1N0thZm5KTnRINTNwWE54NWNUc1REZFhzN0JCZnVxc0J0RndhMFZxTUJlOFZ0XzhnLUpGWDR2Y3Ftd2dwb2hRalRKSk1lS3M0?oc=5", "source": "Business Standard", "published": "2026-09-25 05:32", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNS2ZIYlJtSTJ2R0tUd041X2M0a2gyT0hxbktRNi1YSFpNcXlUZlBwcW9FMGl0RkRoUXJpLXFSYmI1SUlJTkFBNTl0dlExYi1LWm0xX1hUVVFqVjhxWlJwd1Mwb29fX1U0VVFhRE01d3IxSTNpNkkzQWY2TkpJSVVKLWtlM1dFWkFnaEFuZ2hCT2RYWktac2dQLUVmemdKeHlMMHYwbEtfaEI2d2w0MEdYVGx4T2R1ZktDV1RWQ2ZfUFBDZGRTWVdmSF92OS1kTnFNUTBXeHlZd3ctMF9wMk9lNHRoVEJTUTVYSV9rR0FvdG5jZVIxdzBJdnNSS1VzbXll0gGGAkFVX3lxTFBZX2J6TDljZ3haMlBoSFNpQWJ3XzE1aVhVTXVUNUkyYUZLY2N5Z1VuV19hbzZNNDhsb2RlTjZWRmpObFNlVFR1RmtRcVM3bXZGODZXUnhJcC11VXVDM2pKWVNfdXRjaENBQUZiRjZwZmZ2SmRmRTE1Nmxac1I4RlVla0U0LVdlNGdKS2RxOHhfRUFTaUtlcDNLTFVjY2JyZzBSWFEwVXR1R25rMjZmRldrRldOazUwRmRjTmhpVUl6Q1ViWFo4bS1GaEpuWkhUelYyd0ZBOGdIM0Fxa0p0U29jZEpnR1NWcGx6TEl6ckt5NUNhS0lTVU1QR043dEZvbC0zNmpHNmc?oc=5", "source": "The Times of India", "published": "2026-09-25 03:51", "score": -0.494, "label": "Negative"}, {"symbol": "LAURUSLABS", "title": "Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSUFqNDJicXN5c19sQXd2WXNJb1BWb2UtNUpOZTI3d2JudFdlNkZmTzVQUzFKM3VXTHJlZGZKUlhCZTR6MUZob0p6Y0hERlZkcDBzYmp6OGJaMTBKRFcySjNlblpkZXNabW1kZFZLRzdkT2N2Wnl0TWtJcU54Skk2MTJMUTVFQmJnbXlzeE9jSDgxRlhQaUd1X0xibGxDWks3Y01hZkViMTdVNVJYZ3RJald5TGVvUW5sMkV2M2dxbXBiWUNDT2ZXV0xONFBVa1lPOWN0aW1ZY3JVZ9IB3wFBVV95cUxQOGJWak1PMG9YdEpvYzc3S1VhNXI1bDBheUl0TVdJMTBCdmJoM2M5NUFhQzdYb0VFM2dsRmZLOER4U3k1eFUwQmg2QTdlRGNYZ3Fod1F3RW52bWVGUU02NlpaUkVhWTBXUXd3SERZblFDR2JVR3ZZZ1FkcTVTcGU2ZWZQUEVaWlFTMmJRWDR5WHVoYWtQejV5YjRjNXQtSHBKOFdaM1Y0UVBTNTZENWU1elFHYTZmVkUzSFkwUkM2TGw4Sno0SU00WXNUMjZUenpEMXdqQ3AxdmFOeE9HNnI4?oc=5", "source": "ET Now", "published": "2026-09-25 02:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...", "link": "https://news.google.com/rss/articles/CBMiqAJBVV95cUxOQ0Z0MUFZM2ViTTdHaHJ5akJLdkNEbEVZeFFsZ25KVmN6UTE1X2xMTmtUckhBOUdZeE5OOHY5blA4WDhVZDVJbjZCeUJVWE5meUM0aWhoY01DRnRBRHJaVURNTWg2SVRPVkJhUjVUb3dkRDVQZ1B5ZzRhS1ZyUVA1NnNXOEJqbWh0TG5EWHAxZXIzcU5nYnIzQ2xZU2RWaHR1dE5KTE1sMUpTQUthdmdLbGpjcXZvY1JsWXNzcHp0b1F3c1I3ZHpmUTdqMUpmbTV3M0JNM3AzWDZETUFsOFpURk9oQlY3UXB2Rjh6cjNobFhYOTI4MXRUN3YxVXYwaXJnTklxOGU3NXNHSjl6c3RndGt4TmluUUROMVhIZ0pWc3hia3F6blRJSNIBrgJBVV95cUxOdWNfS1N2QVhiREVSTXpDajYwUE9RM1VycGxPNmRKaHU2N3N4Y2tiX2tKSlU1NEpYR0Y5Q2xOMFFhV0VRRE83WmNDUXFvUU5LNXFITElxRmNJSEFJT3dDcGNwT3Q5UHYzaFB4NHg4NlpKUXo3bGtOV1lPRllGMXUxdC13N2RoTl85V01LU3o3Yk5Oa2hzWVZxdGoweFJySlZDVXFPY3NFcXJwV0tpdkxOZDhhRXRpU3ZhOEZCMEZ5QWlBUnczdTRuMUxCcXdwb1Vtd3JWS1Q0aUxpbzhhLXh2bmRtZ05Cc2VyVWM2YjVJTzRXd18yNndmaklMQWdsWlEtdEkybzlJRng2WndzbnJWUGF2S0RBNnE2MlRCb1FGSVktd0g2TEdPdGEwMDRYZw?oc=5", "source": "Moneycontrol.com", "published": "2026-09-25 02:06", "score": 0.178, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Bond Yields To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On September 25", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxOdVk2NWY2YmFvVWRzUDF4anpscG54WjM1SVVVVldRT244LTh1aXVWbXFCWnQyQVZnbmQycU41N3JiV3p5ZTF6VlZMSUI3NUQtR0tsVDF6cS0zdjZiQ3lCM0VhTXFoSEt4aEh2YVF2cXFxY2ZfMkVZSjhuNDZyODRGQUNYRXNpeWdEZzRjd2ZaeThvb3BxdmpBdU1jZVhNWHAyUzR0eGhtTzRHYTVkdTdvYWhRcWhldEkxV3Z2bnZ2SjhqNVYzMWR4MTcxdWc4X0FkNzdjb1VhYUFFNFNOTnVMeGFtUkF5SC1ZRG4wM1Z3VUU1SE5ucnfSAf4BQVVfeXFMTzFDRFpfdFA3RTRhanpJaFljZTc3ams4V2FOMENpZWYtUC1uSEwtYWlNODhZSnhnVXBZUEc5REwtbjFDYkFtSjd3SlBwbHgzblJDQ2pyc2F2aHdwV1NnaTlxU2plcGhYNWg4cWZiZGNObUVPOENwTFRuS0dnbHdTbVNtQTZGUXlGTnVnaEhZYW0xVHhjVnpZdk1qMlQxWFNnRHM4NENlWDFtdFhQODYyNWFRb2haeThMUWdsZk55R1g4YzBWbkFGc2xvX0Q4REwxdHBjb2VidHFmMHNKRnZDXzBrQU5oZmJ5bVFuZ2dIVmhlMGJKNHhhQmFPdlNPVlE?oc=5", "source": "NDTV Profit", "published": "2026-09-25 01:28", "score": 0.807, "label": "Positive"}, {"symbol": "RRKABEL", "title": "R R Kabel executes BTA to acquire U M Cables business for \u20b977 crore", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxOekdBdkJnQy1zc05YRUg5aFF1a0lwT04xNl9vZlhFaUhGVE0yeENFRkdPYWp5eW5qNGJPQ1Z5M0tIQWJTMmVBZ2NIcG13ZTFtc3FJaE9hOG1SQVk2UENVdGNWTXktTE10MGNUVmpvNkxodGg4TS1KdHFlZGprNUpZMkRsS2x6OW1LcGtSVnJPQnFvNlpOaHZZbFlnSlZ0MGtEdjdSdzVvSQ?oc=5", "source": "scanx.trade", "published": "2026-09-24 16:21", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets", "link": "https://news.google.com/rss/articles/CBMi-wFBVV95cUxNNDY4RnFxUWdPN3hFd2xaaFZRMERxSGpxN2Z1ZjF1LWVVZXFDUnZlQzFhNDRUYkdVWW14NDRCdXZ2LUQ0YzZpNWVUQmxtTEtHV1UzaUw1eWtXYm53a2JYSzdFQ3Z0clktdUNZY2J2dE9MU2lxM012czJpUDR1R2ZkN2h3QXNIWGkwX3pEM0xNakt5RUt3Y3hrQTZPNW9yUVhDQnRCaUs5RHdjRVM5Z2RMTGc2cG10WS0ycnl6ejY3YWFsYkUyVzJBYVc2UXlvaVNpRkFKZkZmWkE2RzBxcWFMNElnR19nMFN6cmRzRDBteVpQMjlDVHlaVi1VONIBgAJBVV95cUxQbEJYN0g0YUZETXczaUtkbUdMb1c4M2lQaUszdUtyTXZxMVVYWENrRm10czlDRHQ0alpzSjBhRXMwVzVYUUo0djJYXzBQWlM4S3NZZXZtZTM4TS1zd3BVbEtHeExGNHVVcTI1eDN1VWZHTUQwRllLU0VTenctSGtMT09DTFpSSG00UF81R2ZsdGxFMFlGVFB5aTZLWGVvQ3RwWTVVWTV3Rjg0N1RKbTROQjdaVjR0RTRuRUVtLTFUTDgxdUVMOWVhOV81ZEhMbHlxVmh5Qk5NMXNCdXo3anhfSTY1SlNaSi1zSEtvemVYdjY4R2YteVlTRG1qX2wzQXFy?oc=5", "source": "Livemint", "published": "2026-09-24 16:04", "score": 0.7, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxORWVLSFhyVy1XclJaTW9wUmtOTF84WGZkclJHbmtIdW5oUXNJS2J2V2xqUjNnVmEzRDJJRko2Y1UzaVVuYnFOUlRyYTFzNFB1dTlvMXp0U3BTRS1rUV9pWXotZG5FX2xZVnI0eHRaWDhlLVZwaThPXzdCNW0tT2ZEMFp1b0FrRFVsNnZSVzVCTTd4MWZEUm9ERnJ5bTJNaGRIYlhYcmRGOE1ub1c0THBORGt4d2h6SnlBWUhFeVdSUDg?oc=5", "source": "scanx.trade", "published": "2026-09-24 14:42", "score": 0.382, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQnJ1UkZncDJJcTRVNElLd1ZKN1Nnd053YjRobGxJUEdGYUdWS0lvb0dHS2MtemJ3SUppQmZ2c0NERjFpa2szSjhMZG5BcGZiT3NNa191ZHEtaGRCNUYyU3FhMHBnXzFBUkk1d09ZNWFnNXJvZHR2VU5LTWkwMFlWU19xVnZkUkk2aFd1N1FBZm5xVVlEQmx6dVhDcG83MGZveUFrMm9pMWgydUlPMDFZOTB2RFBBT3JPdDRVYmdKTUtzbVBMTDFIbGlzdkhVMklTNi1aeVFHNjNBUU9RclRiSmtXVjRlakw2S2UzVlhlRTZvWWs2RFNoVG0wUkhrZw?oc=5", "source": "The Economic Times", "published": "2026-09-24 13:49", "score": -0.153, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxPSmdZMUhhTERFclM4bzZicU5pWTdPX3lDUFQ3NU5qcU5hNWVHU3Jrem1lS3FuYjhUcXBVOGJFLXVKc3hCSFlvZ0E4QzNJYjQtNGRHNldTU0pyWS00ci1qNUNTNFpXd2lJLTZnRnQzVGNraVBUUGNhSkJzWWRjVVNqWm9Qa004SHQ0bXIwUV9SNm4tLWxtUHl6eHFoZVpPUHQ3UXZxdUxZTHZrdnpYY3JrTHhFTUxuQ24wd1lBR092aDNFV0lPcXJWMkxITnFFZkdNTkJqRzZqeVFIZmYx?oc=5", "source": "Kalkine India", "published": "2026-09-24 13:15", "score": 0.318, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "3 Indian Export Stocks That Could Benefit From A Weaker Rupee", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQNUp4b2tjbFlmWklUVm5zT2NJRjVXMm53bE5DNjJvb2ZFd0tFZVRUWHVxbWozaEp4aVBQMGtxZkpfQ3FmYnZtbEppcGtXZ1hYYl9seFIwdlhpczRuUWg0dE05REgyUkRMdXJpaVZDc1BORHVteE1IcHptNnNRbkdTY0NEUTZKZk04cHEwWTlNTno4MjJKU05aVlVOZExfd3plejl1cUxiVXlVbVNibjctMlFyOWx3aEZmYk5VNElFYUM4WENySTZGcmFrWURmdElfRjhyTm4xelJnYWNjVGtmb1I2NmxXZnRPem56RDZ2b24xZ9IB9wFBVV95cUxNVGN5NWZ1TnFTNUt1elFVSE5Tam8xZi0zWVY4Um1SX3UyVE5xNDZPZmpWQ2VWXzBsaW1vcnVzX1NoZXk0aWJjeU5iaXpiT1dTejAwSUt6Z3FhTThnTlhsa1ZFdHpfTG1sNjIzQ3pkZ0duUXY5N3ZqZU1qckxKVlZneVRJVmxjU1VrckJtQWlBNWRsNGdZbnRxX253TU56dE9NdXA0RlRoR0dLS0VDWFQ3VXJILUlrcF9OTU1lVk1sODFsbmVIeG1ROEFLcUlhWmswVzVkUjgwRW85cUNQUXpOcS1VZnBLT2pMSlZ1c3lGQ3MyN0JKeGlB?oc=5", "source": "simplywall.st", "published": "2026-09-24 13:01", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPTmEwdzJWdUtmS1lTeHJNaEFsLUVRRTNTSU0yMko0SUJCczVmU05rb2tDckFtclNUdEJzbmN4VUw0TUY0aWwtVVlEM19wTF9BZ0xyZmw4Z0ZTam4wMmphemF0SjRoWWZTaXZOOGJES2dTWWc4MXU2djFTZFQ2ZmtnTGgtNFBvMlpVbFJUeGVCQ242RGpic3ViMFl5QmlzbE9ZMFBIQktpRXRkSWhmWVh1WWJYZjRYQ3FkcEJtOTVNUmZseW02bXQ2cDlheEVZWnItWGFrOU5aTmdDVFQ5UDJMUEI5Y2VSREJGSmRGdFY1UGY0cUJTR0FFUDNSc014endZb3U2TUN0dFdXQdIBjwJBVV95cUxPX2xOWkM1Q0VWS2w1cGpsMXpBUFVpZHZOQ05TMTBkY3BMRHUzcjVIeEdpRHBhYXhKNXUxSzRjZkI1RHpXbkRQdlpBUkdPS0JIVG5jcjQ4cGxZUnZndUIwX1VMVWlwU2c3dUZTNHR4VjZrUzg2VXd6UHFaYzdTV2xMRXQyWmFQcFdIMEJUN2pqcFliNW1tRHU2a1VNNnUwekE5ZWRTYTF6Sy1FbnBhNEQ1Zkh3Uno3QTZuTXVRcHVlNm1LVE5oVEJHLWRiMWFUeEo2ams0QU1ocjRRREF3Vkd0dXQ3ZC14cWNLNE5oM3lPMXNKelVjbmxuQjA0dURockhtcDBQS2gweGZ5NERLYVRB?oc=5", "source": "Livemint", "published": "2026-09-24 12:36", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see worst day in weeks: Why was market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNTTMxLVltQWc5MkFQOUFYNlpYUTlLRnVtOWFTM19ETVhBaDduYk9pa3VKY2lIdGNGTkpIbVVKaDNkV2Z1NlBvdUVVeC1JbTNJem02eHlvdHRvMFFkR285ZjlFWk1fbXR2Z29HSnNVVklmYnhpOVlHdUFxeUFuNmtXeTZFY21KcGFraFdXRVBfNWZRLUU3WEhhd0x5OGxkRlRCbXR5T21JNDRpWE8tSU81VGtxUXFqUzl5T2FrS1dXd0s2QkdoTkRlSWJFR2lORk1JOWpnWHhvanB4bEdTaS1aZG1sbTJfUDFManBUNNIB8gFBVV95cUxQaVFGYUROS1ExTmNWWWI1RHNoTGZfWDd4U0hPeGVCdzM4eUtkZXVMaGZSTXp3NDZEcS1POXpFa01KQlNtY3U5QWgtdl9VV2hZY2VzZGp2U1pQbE5sT1JoQkZJeFFqT3VMOENGMjFXM3dRajdZdTVJMVpIWVVubzJhbjNyakljV1BrTl9vVDh1Nnhnd3VqdDJBbThXVDY5ZjBIZXFKZ0ZHUkt6eF81SHJEbEF0YkJnVDQ4clNuSFJONkZRRTkwZWxLaS1QcEVwVmRqQURkTlpSTm14R2Z4bDV0NEhMMzVJdWZ1TzhaRUlweVQ0UQ?oc=5", "source": "hindustantimes.com", "published": "2026-09-24 10:57", "score": -0.34, "label": "Negative"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNb1U1UU5HdEFtaWZCRWdVRWxUc2pRMFZ2YXl2bUpYNE1xNzZBX01tTXNtQWc5d2ZCNTdzYUZwXzU5U2VOX19rRndvYkVDaUl3aGVqQ3lyU01qYkNtVENjRG41VW9IenA4V21EcDhLYWFrdHZPYU9yNGl2RDFSUEdRcEtObWtDS0doZlo1V3ZwOGcwcmRROTcweDNZeTZaRGdQZ084YzU0amppMUZaZERQamg3YUE3RF84TjFuLWx6T28?oc=5", "source": "Kalkine India", "published": "2026-09-24 10:15", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVTh5Q2ROa0YzRWp5NS1Kamp3NnMzYnBNRlJHcEZ1cVRnOG1aampUb2pFbERqcGNPZjN2WGZqNGd5dWNDN2R3bnhXQ016bjJoUXUxN2FqcVYxaDFrSTlwZGpSQmZIbGM3THdoMUFDX1hwZXo1OHNPTjVpNFhLWVZudVFHU2xxbmZ1aUFnWXZqM09tZzZ0TVlRWUwxakpaM3JIUkg4QlBBaG40QUQzTWxYYzNSZi1uVVZtWTJHVU1UQzhDWHB5OW9Fb2JHS3ExdVR3dExkMGJRRVRQVmZfZnM1THUyOTdWbWhDaWfSAe8BQVVfeXFMTUFnaWZmYkVLMzZkNk5ZRXF1ZF82LXluT0hoSlJNZ19kUVk4VHlzLXhabENVbTd5LThnUlJIc215aVY1T2ZwOThSS0dVNnJNTVBIdjgyQlBPQjJaTF9sQnZWeEw3Z3dVdFVMNnU4ZzBWOENQQ0dtZ1JQal84UmdMS3FvdEFJUFdMbVhXQm5tM3JYNUJhYTFFRnFtX2VIaDJMcWNPUFhpaUs1YjRSbG1lWWVTYng5VnNjbFF4Z3NqVWFHWEd3eEMxUjE5YUFQZ21qdVJJV240Q3dsYTdHQUhKTjVGcnk4UWRhd3lEdTJYeGs?oc=5", "source": "simplywall.st", "published": "2026-09-24 10:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "The battle between India\u2019s stock exchanges is heating up again", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQSllxZjNuQ0l0ZExkQlp2RmVURXBuMm5WRjUyUkZsOXNaeF90Zy1GWXMyZFAzYmlGMGFfTWlhSl9lT2JNMmVnclFGYlg3bjNZQTRUeERZRkFScXBYc0IxZnhEcUF4Q0tzcWhhQTZXaXR6NjA5Y1pTSWdDQXBPQS1HZWpMOWJHN0NzN0lLWkdiMlJWWjN3OC1Ha1VDQ1ViSE9QTmZmSHBYTVpFM1FiUEJtZ1B4Y01nd2dabTlwTw?oc=5", "source": "The Economist", "published": "2026-09-24 09:42", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty crash today: What led to 'Thursday Tank' - Top impact made by these news; check biggest losers, m-cap loss", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPVWZGNDlpWFN6MFJFZVZMVWp4RnIxcTVXOTRMUS1oVnMyQkVmZkF4eDdQTGYxOXVKV253c2dWUVZrOFpQUEEzdUQ1Rm45bG1aX01RSzVBNjNIWEFIb0lLbFJsSWJNYzFzMVFaVFpXUnAtR2xtZEZ5YXhjdXRSOHI4ZkNVMlJvWUszcWJEdGFBWmpqZG9zaGJWRnZGMHFtM0J3OWluTEZMVE9xSkV0Q29QTnJFQzEza0ZQaERRWjNBaEN6QlpkSFdMcGRuWndIWE1RVU5uczhza2w2WndRYWlUVkg3Yi10bUJFLWRWTE1sT2I1NnhwVTdCa3ZBRmxpRklNbGtzbkQ3V1licnlmakQw0gGUAkFVX3lxTE5pNjM4R2ZHalBOWTl1aGVPaWxONlMyd2lmVERYa0RZeDlDMU1IbnZMWnhNQ2VuWXY2dGRTTlFrZVFrU3RmaUJtcjZxNnlVNXc0eU4wQjR5Z29zd2FWZVRoM2FVYl9BY0xldFp3SDNjYnNSdmRwdXFYTEpxcWM5WWFrbHZCeDhZZ1c4ODE2SWJpX1RvX0dkX1VHemI3dmpJem9uWWJsNU1Ia0JFWmxobTRWMjBFdktPS0dsZGhlVjdIaVh6dFRhU0FERjk4aE15ZmlNR19BbmlCei1FRHV2TXNwV1BJaVRHQmxSZnh5dGotNDRaUEpUZV9pMmR2STRRbkhLUHhPa2FMelZzX0VfdXJMOGVoeQ?oc=5", "source": "Livemint", "pub</t>
+          <t>cldoc2t3TkFweE8xLTF2YTROOGpkZ3lkWGRFQkpaY0xTRFB1akhkbG01QjZ1eXVBWlpjZHdnMGR2a0ZNODZuQWZ2cThKTG5nb3V1WUxxS3BCRHllVkhKM1hQTWVpQzd2WFU2b2x5TEdYcG5N0gHkAUFVX3lxTE9uUFVOSFVOazh5cm5jb1RDcVU5YzMwUjBJTV9yR1JmeHhaeTB1WmNIUS1faENuVTFJZEVxSEpheGpGcGMycjEwenhnekROSnR5OVI5V1l0TkJsTHp0V0g3MkF1TzNpMmZCUm54dXFiS3lJVWhGTkRnMklIT1pucDc1U0hrSkFoN1dkci1UM1UwVDdoNXNiZFNPWU9iUk1kSTV0RFBTTVl1UkJxc0t4OUIzcXRWWUJMbXcyZF9zZXp0c0ZEcUdBeXFKTFdxbzJWSzl6ZUFZTHI1aDZtdWFOOWhBbUQzbQ?oc=5", "source": "The Economic Times", "published": "2026-09-27 11:03", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show \u2014 3 reasons", "link": "https://news.google.com/rss/articles/CBMilAJBVV95cUxNekdIczJ6NEZleldrYUtRZ0pEMFlMaHFDcWdFeVVhVnJROWRBWTVFeURzYXM3NVY2eTUtZmNMOVg2VVF6eUZOZFpzcTd5S2ZqUmVJYkRaYnd2RF8xZjlDakRzUWFvaTlVb2REeWo4WUF2aTIxZUVncDVzY2o0Tmp3bVR5TmpRQmFSMDZzSTB1MFBCSWh5RmJ2b1d5QTNDdHlSN1hVcEJqUHdlOHZ3VENMVm8yWDMwV3N2M0phaDNFZzZGdE41OWVxbkdjU0tDNnFnTnM5Y2phV1pIYWN1RF9DNDhtd2JBd0I4WHRlMGFvZUtHdXNlWHJVYnN6eTFwVjVhODVsYW04ck9LRnJhb3NzTjEzVnfSAZoCQVVfeXFMUEV5VVRyZjl4LW9fV21rY0Y1SkJyYmluZTZHZlpld0cyakhLcHhKTXBNR1kwU0RET0VZeW1Ea2liT2JzSkNGenlOSzlkdVZwejU2X2FJVHFOUHZwRnM5YjRGUzJDM0VaMVlVR2M3N3FwZW83b3pBcnRwQjFTSy1UVVpDUWEwYTVDSmF0eExBWkdOQml5Zkp5aWtqU0hqNlloT2V0XzRPVml6dXV2WW5MVXlSMXZFYkQwMGNqZTBXNjBWTFVkd3pUblpDdHZ2RjlXRGlreDhvWXNnMV9KVGFySDFFNFBzUkpZUEh3OVFRVmFfSU1oU3V2bV9Pdm5hR21UWXBLYW9TUElFRExLRGdPTmJXQ2tSMjlFRV93?oc=5", "source": "Livemint", "published": "2026-09-27 09:48", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOT3N4b21hRzhJSXdJVzFVNWRNQ3RqT2l3aXFBN2RjN1JDX1Y2V2U5MXlDN2l1a1BGQ1hLcWktbEgwYU1UMUEtalJDYkc5RDZqX0FHdFVuMmpDVDhHdkhWSDVpMFpXLXpoa0ZTWDdGcTBxU1hJSUtIQzgwUXZvQTRPdUh6UnlXYUkxZTZHTmJFSnFQcVFSc0s4V2tGNUUwUTJVZktuRkUwY1c5eTI2NjA5VEgwMDExekhFYVhLRW4wRlduOU1wZ2JqV1F1emdiLVUwWHZwa3BmOXV3MmtLOVpzWlZOOXJ3b1MxY2pvR3VYRlFjYkxmNFdIWGFxNTJJYVVvcWhJRVVwb01UbU3SAZACQVVfeXFMUDJ0a2tkZUxvVXFoM0VZMW5YYm13NlNjNl9KY2l6X2NkS0VvMGw5eGhyWDRzU2ZsTlJmTVdTbmZ0Vzhqc1YyNGU2TWV2a0FLLU1vQmRRVktFOXhtcDRwVVVMbXZPNmo4Q0V4ZkNCU1M3TEZ3RzZwcVp6SlhoczYwY3NYNVN1c1BKSTJLYXBRbVh0bDN1ZWc4VnZNb1VZZERDOFlSXzFwNW1RX0d4LVVGRHUta0Q0cVR5dndQUGNYaTkxWFU4ZVloTzNfR01UMDJ5aVB2R0ptYjU5Q0RLRnBEZExqdEZJV1BDMHRiRTBBa19fa0djbno1blZZM1ZwUWx2VWREaHpQeS0yVFQtRFpQc2s?oc=5", "source": "Livemint", "published": "2026-09-27 04:22", "score": 0.842, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Stocks To Own In September 2026", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWmN1VW9wZjRBZl96MHMzNnRmeS0tY28xWWZtR0hfa19FN2lyVjdtZUc0a0U3c1ZYNmZ3eTNiWFVIRElaRGV4VDFVYi1kYlN3ZjNNemNjVzFwWV9CQmxlR1B3X2kwVmphZGhMazZCVTE1a3E4clpQbU9GLVNXTWs5MjdNaldOQVBOOVpMWnNMUXA4VEtmc0drX3RWWk01aXVvd2xJS2JYeGppOElvRTFWbEJwdEJoYlBVaXFhTUNhMG14Y1FnSWROVk1qb241Sk1vOW1MWGJ3dXpuZ9IB3wFBVV95cUxPSXhqMzhnOGFvNkRfakZ0cUxHVkcycHlESmtYb2N6Vzc0MGVlSnNhLXUzOElWb1YwclgwRmY5MFhreTM0TkpzdjVjR3d1Qmd0Y1ZmRi1KM1dLeTU4QjRjOUdTNzlRNUR2b3FvaVNTbW5adHhMQk54YTR3YlRLclVfUmxKZmhRXzc4VG9PUVg4RFU5UWFOWmsyYWZHaFM4N1pxTHVLX3RVTVUwSzRtQzhCenRfa1REbS1CeXQ1Rm1GUXhvV3BxRndHZHRGVEV3VHM0S0Vidjk5bm1SSHJiVTFB?oc=5", "source": "simplywall.st", "published": "2026-09-26 22:56", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "\ud83d\udea6 Indian Markets Stuck In A Jam! But who's responsible for the traffic? \ud83e\udd14 A Bernstein note argues that India\u2019s large caps are stuck in a bygone economic era. But here's the BIG question: \ud83c\uddee\ud83c\uddf3 Is The Market\u2019s Fate Really In India\u2019s Hands? \ud83c\udf0d Or are global cues pul", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxORUdYckd5Y2pPQUg1MHZTaHlTT1ZXWTdmTGxwSWlMcE9NQm1vNE15dk9qS25VanFnTzk3c0FHTEpwaGcxXzhmekh2dUNLM2s5Zy1USHBjMHRfakhvYndNanZrV19NZVFMY1hjOHZsektLSVZoS2tTNkdzMEJTeExiS3ZVbDVRWTNWVjZ3MWVmSzhnZDVvT2d2YnEwZGJLRUp3QXhxTDVfSUc5TTdvTXIw?oc=5", "source": "LinkedIn", "published": "2026-09-26 13:51", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market News: Nifty 50 Outlook &amp; Prediction", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVJvTS1CRXVsT2ZzNUhBV0piRVV1UnZTeDVEcDJmRElmWHB5WkZsM2s5YzlYaXJuVU9vVjQ2dE5XVk93WTVVLUx2d19wRm9lc2YzWW9xX0F1YWJCTUJtMURwVzRxbC1vUlNDWEpLRUZibzdnbVdjdEJUeThfeHZLSXpwTktCQnlMM0tTNUhwWmplMHJKb2ptYmVn?oc=5", "source": "Liquide Blog", "published": "2026-09-26 12:11", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Weekly Review| Indian markets under pressure: Oil, outflows and global yields extend the seven-week slide", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxPbm8wM0RSWWRXc1Bzc3daeEpaNnFwZW55Y1FBT19TQUdxYXdrZ2FJeDJGd1EwQk9BbFJTZ2xKNV9Gd1BadEFlZExtZWlxdUZEZHh1RkRIU1lMNEJVR3hkZ2VKWnNGWUVLa1Fha29hcWcyNVR6dEdydjluNGxlN1YybHFabnUzRWdzMTFSWThkNWRRX0NXQ055dWl2dXN3cGw2RUJxSHAyTTFWMnNOeXZ4S0xGQXFjRmhub1lHeVQyRUhUdEpFSGEwM2U1MEFnbExtV1JPRUVNRmV2dUNfZ1BiblROc2IzLVNPclpNRtIB-gFBVV95cUxOT2FRblV0ZG5vNUh2QTZGeldJa2FuRF8xSmRWYUQ4a1NLblFyUmtJNTRCdHB3NENTZUZhdi1Ha1g4aTV6cy1POUl0Njl3bzZNdE1ZRk43bWQwRXZvNGxncTdBaWg3cDNUMHcyRVp3d2ZKRmljNXZwQktjUTZnV3NpWldYMmNoV0ZJSjZONVJjNEQ3d2ZLWXlVREFsd1VFbFdob0xydFJ5dHpFdGIzeERrQU5kcXBubmVLd2RZODE2Skd0Yk92bFNnWG1qUjNnZWRSR2YwaWIxLU91ZHBzTlJVb0twSW5pUnYxb3E1WEJFTWdmQ0tzeVhaZjRR?oc=5", "source": "The New Indian Express", "published": "2026-09-26 09:15", "score": -0.128, "label": "Neutral"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQWm9DM0I5TUU2aWVIdHhCam9zXzFSUEI0RzhWaEFxWDFfbDFoeUFJUEZQbHk2OXJJdlpjeVBTVjd0RDdMSjdPMjl0eTN3NXZnRmR5bTM1Qi1KS3JsNFRrZlFCcmViSW5MTmdQdDItWTU4T3lUeFFkTEU5VHBEV2FmUjlqOWdvaDhNcGZlTk9jTjJQeVZ1Zkc4Q09fUGY4LVZiWk51d2U0ZGtxRFZ4cXpMV1V1UlJOdFN3RnZyTA?oc=5", "source": "Kalkine India", "published": "2026-09-26 06:30", "score": 0.0, "label": "Neutral"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure \u0915\u0947 \u0936\u0947\u092f\u0930 \u092e\u0947\u0902 7% \u0915\u0940 \u092c\u0922\u093c\u0924; \u0915\u0902\u092a\u0928\u0940 \u0915\u094b \u092a\u093e\u0935\u0930 \u0915\u0947\u092c\u0932\u094d\u0938 \u0915\u0947 \u0932\u093f\u090f \u20b993 \u0915\u0930\u094b\u0921\u093c \u0915\u093e EPC \u0911\u0930\u094d\u0921\u0930 \u092e\u093f\u0932\u0928\u0947 \u0915\u0947 \u092c\u093e\u0926\u0964", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPVXU1bkFLVlVQVmhKWjdoVDlSNFQxTTlheVZFdGtDeEVEVzVtc3Y5Qk45R1RaOV93WlZrOXF3MzFKTlE5OGR1Xy1DcnFtUTV6YTYxYXlVMHlTWXFEbnlMaFliTC1uYTZOeVhCY2ZjQW5Qd0pzcEZWUmx5NHJHZ18tSDNHbTZrT29hbFNrWXFuQzFRTW5OQ3BMRERrUldoQUVMYmRTeTBfZEctVi1DUzF1bHphN2JnNV9lbWx3MGU5MlZRbHdZYnNrR1NHUVJVekRybmZtcWNFNGQ?oc=5", "source": "Alice Blue", "published": "2026-09-26 00:50", "score": 0.34, "label": "Positive"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxOTXpFTDNOdlg4R1lYS1FPU2VpM05pUUVGSHBvdWxqLXJ4SFpPTXZ6Q25FVjh0V1lvbnR3ODJsa1Q0ZDJlbWpRZFFiSmw2MUhwVF9lUVVyVWJTQ3lTMkJHNmtHMFNOMmwyRng2TlFUVlM0WGhOdU9KaTh4QWZ4bm81SUlqcEN0dm5FRHZVQ09UdTBIVWxZajM4alAwcjRrUURkMHFPSnNWVndUNjhjcjVUb0ROQVZJTFBCMmU1bFUyNUl5c0YzZDQ0bmVSNXB3Nm9pNUhnaW9RdEJYMU9WZkVqS3FHdGRaTnPSAewBQVVfeXFMTm9mRGRDb0NZSlU0UTM4c19nUEJhMERMSFc2ZlY4Ul96bUdPUFBlSEZQZ3c0NnFXX250RkQybjhjQkxoSVc2OGNlTnNoOWcweUdOVjlzdS1sZjZvUkM1T3FKWkxTSFczOHVHQ3pMbWlJbGxDX2Itd29DZU5iTzF1ZGlpSEk2dkNaZE0tNXA0Sms5SDdsZ3VuNjhQTGxYc0lYemowWmJzbFE2VUJjb0drM1NYNktGWTBieGFoOFJEbU05ekZtODl1UGsyM1UxbF9idTdCRlppbW05c1RYZXhVaFd3eXc0NU5PN3RGeWM?oc=5", "source": "simplywall.st", "published": "2026-09-25 14:34", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "PERSISTENT Stock Price and Chart \u2014 NSE:PERSISTENT", "link": "https://news.google.com/rss/articles/CBMiYEFVX3lxTE01VG4tR1ZHRnF6bF9CZzh6bHlySkh2MFd6bGJKUVhycUhNQkh2R2syeXEzOG9tLVpSTmNrcUEtOUVWZm45QUE1ZTB1VXFYSEc0LUI0akZJc3NQTDE5SHh0cg?oc=5", "source": "TradingView", "published": "2026-09-25 14:31", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "R R Kabel board approves proposal to acquire U M Cables\u2019 optical fibre cable business; shares rally 72% YTD", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcGpkYXl6WDhuYWFNMkVobGFYaHROYTR3R2NJcWhMcmptMEpqS09jeVBMRFNsQjkxSE9QVWVZQUVXeUFweWdVeEVTNzUycGFHMmxkekJSR2F2OFl0LV9CYUg3M0VvVnJEaUlEUFNrT2RqVkpNY21PeW53SThRUzMzSzhqYm93VkNPWjVSWUJUYnFicTdONEVQY1NwdTlqTTlSbWhxUGlZMEN5aUpyWjN5aUgxckhCampqdzhoQTYtZEpkSGljNWhhVUJoM2dqNUhSMGc?oc=5", "source": "Upstox", "published": "2026-09-25 14:04", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "India shares log longest weekly losing run since 2020 as oil prices bite", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRDlIOXFjNzhyRGVteU5DNTJCdVlRNUZEY3VObFdZNDI1MDU2SUo0NEM1N1JDTHpDMTk0YU9OM2V1eXRla1VaanBsTTlUM1lWR3VYU0g1eG5pM21hNzFWQTdabWphemRRMlc1U09MdWxVRVNLUWxjd3pIODVuY2UtcFE0dEhPTUM2MU1pbHNOQ1NnOUQtME1TTDJjSzJzOGljZTRmN0NBZ2Q0S1VodGZaSXFxZU1VTGNnanc3a0o0anM?oc=5", "source": "Reuters", "published": "2026-09-25 12:52", "score": -0.382, "label": "Negative"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxQbV84TnZBcDlZcGRjQ2YxN1Z3eC1lNHdhNTN1ZENIRnZsR21zVVQyQUFmNnpKbmQ1VWl6SEpGNi1XX01ZcXZuM09QZklRNUh3YTZwd1RJNDRpM01BRUJfS0VJSXRGVy12UllLVU5jZnd4UWMyQjlkZHJPRGsxX2RQZnY2c3RRRE0?oc=5", "source": "Univest", "published": "2026-09-25 12:22", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Two years ago Sensex hit lifetime high: What went wrong after that &amp; what\u2019s the road ahead?", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPNjg3MGJpYWo0SHZZNlZLX09hOHJTTU1CZm9FYzZTejdsbWl1bmZfY2t4SVEyNTFLM01ZcVZueHJhZlVtRC1zdWo5ZXZaRkhWOUtJc193NnZOZVhXUDcxcWpzcXQ0eHlmdG1TWEQ1R3NfaElGZjc3eldBcmtIbmphT3F4VFZoMWFwOFZQZ1ctWjAzRlZNTlZOOVVrVFVGcVJkSHo2WVBleXNYWi1VU3VaMk1teVJnVGgtN3BKdXY4U1cwTXYyUXJ6Q21YWmhZbTI5QkdCUG5xaDdyUVFvMi13SGVteFl5a2lSNUhYSTN1ZFo2Vkk1X2lURTB4QXpmc253Zmc?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-25 11:56", "score": -0.44, "label": "Negative"}, {"symbol": "RRKABEL", "title": "RR Kabel enters optical fibre cable segment with \u20b977 crore U M Cables acquisition", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVHNrRVg1VDRadktqWU9TVnUtdlV0UGx2YVN1Wk9maFBKZkl6NXN1dEhmSGxFNVVaejRWQy05czFfT2twSjJxX1lDR2x5QTZycklWVWJBTDNGZ2lWYWFGYUN2dHUtRnEwUGxsVmw5UmhRandzdHdDUHZMUGZNbnhsUVdmbWJ5VTZ1NnlDdTM4UVJJNWlDU3QxRDJfeUZyMWF1Rl9fWmUyWmdyUHZpVXNRT0lkVjVUaHZpX25Na0RVa1lHRFh1ZFlQOUlhVUFJbmVLamVsdHZHVkt6bWJrRXY5UdIB5gFBVV95cUxONTd5ZUl2WG5FUzRqVGsyNGNWcHpEN0ItSkJvV2wweHhrVENsb1NFa3ppbm92bUFGdERMZWlva1YyMEl0dDYxcXg3clQwZ0xKRk1OY0c0cjZOYWFmamVwdnNsTm51TTIwV2lhNnFNX1pfS29Od0xQZXpWNWdFd1k5Y1Fmc2ZKRWJtRGlJUDdBM3NUS0RSMWJtdDlVaGM0NzVuZFZvTktxelNrd29GOFo2SjU5ZU1HR2VWUHZaUTBVa0l3TjZVOGZaWDZUTzRTSW52VnIyNThJb3p6b3lPU3RualRINlVGZw?oc=5", "source": "CNBC TV18", "published": "2026-09-25 11:42", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Value Buying Drives Indian Stock Market Rebound; Sensex Climbs 315 Points", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPMGh4UXhKOTVzdW1BeE5LNGFFR2Jwbzd3T3ZvV0NTYU4wekJVZmE1U0FuZ3FsTXlTakZ1Y09lZTFJRXVIOVl2Z1R2ZmJsUUFHaEZXREJUZEtCdFNjWjRKWHhZWDNBMGpMOTJnZHhIa3ZLdHpvQ0tmMEdOTy1BN1hBcm5WcFZpYUdVZmdXZkVFYUkwdnA1VFhQWlNDc2xGNzY1eGlPdjhvZGR2MlRYbnVoTVFjakVVeTd5SWxEbnc2RjlxcHdkcTRYb2tDaXhocjVD0gHTAUFVX3lxTFBiSHlyQWowSl9jdW9fNEZsWnBKV0VjVkFTcV9kNkNoNDQxUHhiZHZiREtiMjkzMGplU19TNjNqVXlVTFRTd1kzeTBwSlFCS2VDdEt2VmlOb1ZvY3ZhMW11aFZWd3Y0bWxUWUQ5WmhGN21xeE9XcnNHWUpvQ05iRER2R1NoaXIwMDJ2dm84a2NpRzRVZ1N5NWk4Tk9XOGxKb0R3aHZlNFdfTzU2MFBMQjBBeEFVSUV5cDQ5eTVWSWgwRGY2dGs3X1BoWDdQQWRhUzJiRXM?oc=5", "source": "rediff.com", "published": "2026-09-25 11:22", "score": 0.612, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 315 Points Higher | Nifty Above 23,100 | Whirlpool of India Up 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPbUR3cDZZTmx0T0FjVGdkU0ZOV21PRUFzdFNkR1FaT2hqcFQyZkVxS0ZKSVEydXF6OGlMbnUtakExc2NhTGI0WkE3NXVYYlpnR1NBV2l5SUxWUFhXX0VtemF1WG1pdUU3TnoyLVJCb3ZxM2ZrdjUzRW1wZFJ3M01WQmtaYnFWbUZxR1NGQ2Fwd2dJRTM1QndDMnlobXFVbjAtUnVscXUyZUtyMVZIaEdmSE9MQlFSTkpkYXhvQlBicjJTRjJ6V2VIRnM4RFNCSDNWVmFudGZNTQ?oc=5", "source": "equitymaster.com", "published": "2026-09-25 11:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rebound on Value Buying After Sharp Losses", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSjR4N2QtaTVfdUc1bkpKY0JWcFZ6RzdlM21SN2M0eXNfT2hQVWt1eXZxYmlmUFVBSGhRdmxTalRGYlIyV3J2M2lmZk05WUpVcDQ3bk1IeFh5aTN5Mm1nVXFZOUJCenlPRzR6VVAtaW0zcjZMQno2QTh0MklYUFhvZW1Pa1JvRDNCS2JIa3U5Qk1SMjJRTm5zZjE4NGFIVlVFOHpwVWJHTlBtaGfSAbABQVVfeXFMTzMwT3V5UkdaUUpqeTRFOHBwOXhrSFdVNjV6QXlZc1lzN1AwUzU0RFNxYl9aWGdQSS10S1d4dnRZNlhQNjZzMW1hTmhBaFoxMmFIaWNIdjdDblFCanNIUjJXMHR2SEJyUnVUb1J4X2ZoS2FVLWh4N0tnZGJ0RGc4aXpPNnQxLXFrR3J1Z3FGczZjM181U3FTbnVySUducS1VNGUyaVByUVNyanFPdHRHSVQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-09-25 10:48", "score": 0.318, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date", "link": "https://news.google.com/rss/articles/CBMigAFBVV95cUxPQUxBSWtnLWFqMkRfMks5NTlUcF9sTm1lNEtSdFZDaEstMWw3ejZUX2czMHFwS3k5MEFOWHNBb2w5VElVd011VTdpZ3V4OE94Q3ZGUVhJYTJhXzlKQnRicGVnc25ZNDZDdzhmN09xTzJCNDhLM0JQOHdRZlFKTXlXLQ?oc=5", "source": "indmoney.com", "published": "2026-09-25 10:31", "score": 0.572, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Sah Polymers Share Price", "link": "https://news.google.com/rss/articles/CBMia0FVX3lxTFAxM1NrSlNad3RNSzJKUGVISVgtY1lGZ3NYN3FyNTBJb0FBYlNGQjVCSTRBWXE0c1dHR1lvemdIOFFwLUQ4czVFaGplWHRnbWR4Wkc2N1pkTUlfQ29mQkFNdU9DZkg2akQ2LVRF?oc=5", "source": "Upstox", "published": "2026-09-25 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "Nifty Chemicals (NFTCHEMIC) Share Price", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYURIakNOVnRybktpTUJSR0ZBR1Vla0tUNHQzQmY4clE5d0o4Q1pZM3BtaGhTcjk4UWtuR2tXbmJ1S3kxOGZ4SVhYSURHRkRCN3NwUUxzaDJ0dUZZWWZ0aWhlQkZtclZ6U0hIbTNJTlpNQk9Sblp6WW1WUTVyb3ZRRHJlV1BoUUE?oc=5", "source": "Business Today", "published": "2026-09-25 07:00", "score": 0.402, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today", "link": "https://news.google.com/rss/articles/CBMilgFBVV95cUxOSmhSUlhBeGVjR0VmV1paYzdJdDlLd045M2hLX1dPc0NQdkJXUmR5dUNCNGNYeGxBNnlrTVNtMkQya1JiamhQQTNfbU8zdmxndzB4TWlmSndSdmpzZ3RGU0VickFfeDg2U0x0ZmFkMWtxMndNU3FkdmMyTTE3R20wdnNpdUJoN1RNdlFKbXJHNXlqMU9KUUE?oc=5", "source": "Univest", "published": "2026-09-25 06:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNU2lpQ2pNTWhOZFRyMzhsc25Pd1Z2VjI5SkFZa2d3VDhmQVNmT2JuNjBoNWczYU5QaDZZLVhRdVc5WkNZR3RzcGhTN3JpdEJRcWllYlNWQjd3aDBwM0Z3RnNVeG45SUllbmQzX3RtTlZVVmFyRllRTHZwcmZVcFpybi16QVlYeEZoU1Q4Z3o4ZXMxekZ4UWdWYjV1b1Njc3g0dVJlVk5sbEFmRkp5VFNvb1BXeU40RFhHZV9jOXdhU2tIeXV1Sk5mYTdUaHVRamxZTHlqbkwtLVA4MW93SDVJbk5HT0hrbVYwdEZJQVJfSDJSanFzQl9lZtIB_gFBVV95cUxQZ3hlSUszOFFSZW8zSkdBSm0wY3ZNblIxRS1HRnBLVG91VVZ4blFjb2xzakhtMjNBblRzU09WR2NZeWdGT0x3ZHBiSkNKNkJoTmFGanNzX3owUE5sb0szNFhhVEpjV1I3NVFKMGU4VnRCTFBON0doMmhmUUtnZDVYTWpiNV9CZWdkZnlEWXdZVlpBRFRCdUNLVU4xQjJ2dHdJM21Va21pbGppWDBGUkpYbi1VTjVVTEEwM0Jza3ZzbEFHQnFybUJJTUVTc3lsbVNVbF93VzdqV3BWdHR6THZEYXpBeGRZbHZ5Z1hUOUFWeDVJWTRFS3htSFB0N2Jadw?oc=5", "source": "Business Standard", "published": "2026-09-25 06:34", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxQTE9BdERYOTF4QjNsVFdOSUVsVjdickVLMkJHYld6YmRCdm5PRGloTnh2OHk5VmRRQjJiTDMyTUZNalZMQXk5eGt2OHd6RmllbVhWbUpEQjhnOVJvbmtVU2w2aEs1cTd4WWljRTkyc2dmT01xZVRnb3k2TGlvS0lCT3NVcS1yclo1TERWQWszM2l1dzhDdnBoSUpOVTRQNW10RFd6ODFidlM5QWttRnkyX1RWaWhWS3RzWURldTM4MDctTWR3d2ZWSWh1a2FJX29lV3Z5NnkxWUhVYzRzZmw3NGI0V1Q0R1o3TTVVZUl3REw4TFBtNTdUZVA3Q1VxanRQYVF5Yk8xc0g1YkVUZm1mTzFR0gGXAkFVX3lxTE9HLTI5ZmFma1R5UUFlREE1U052c1BXWndUTkY4ZlpnQi1hVGs0MFNNTS1SZU1qeUM3cXduelRYbzM2WENOQXNDVUprdkVfYnJDbE90cE9CQXZ6bUJEZkkxdE9wbW52akpFZTZwWGtQaTFQei14d2hFLWJMT2VpOVotMloyZ0U1UFFLeWZNZ3NzYVozQ0lwbE50S2pJN0REOVpaNWZXX0ZOTFVmZWVkbDI2RFA0OFRtUFZxc2ZEeF83emxxMHN2LVk2M2tNNUpmemRCR2lXeUtwYlVPdHFzNGh6Z1RJVmV2aUgtVkFzajM3R2VtOU9qNlAwY29sN09XSDRRR0FXTF9zVV8tNkY5YVpPbVYyb01icw?oc=5", "source": "Livemint", "published": "2026-09-25 05:52", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE shares dip on day 2 of listing, brokerages back long-term growth story", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNVmN3NGUwRl9DSWI4bV9GWXNDZk5fRV83NEJWVDc3RGVNQkh5ZWktVjdJRnJZcE9aZUxUQ3dyZWZodFFiZzljZmppdTJ1R0lPNUtPTjdLSVdfUXJ6VmNyN1FWVElaV094SGFJMlNOU2drVGlFdUlPSGpld1g4VGpoa0QyS21vUTE5QWViVl9ETWtJdHpKbDNvek9wOHZnR0ZRQTNvNGdPSmVaV1BvRmMyQmtPSWZpZmFwYklWOGpkS2dKdF9DUDg0LUU1QzZDUkhLNHdNR0RRd9IB3AFBVV95cUxPdk8wd0R3RW9FSW1lamlhT2tiT0phLWRyT0R5bDhEUVU2aVRjNVZwMGo0SHlfZVotNHZoTGxCR2ctcGxWNml2UWZCZ1FGOEJZNDRFNElqSUtKY3I4NjUyR1RsTEpZbWI2YkNudU9GRXJURUFfRjZfSlh3VHpsaWJ0VEhRdGhhcHVMVjMxMkg0Q3pEMWY1N0thZm5KTnRINTNwWE54NWNUc1REZFhzN0JCZnVxc0J0RndhMFZxTUJlOFZ0XzhnLUpGWDR2Y3Ftd2dwb2hRalRKSk1lS3M0?oc=5", "source": "Business Standard", "published": "2026-09-25 05:32", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNS2ZIYlJtSTJ2R0tUd041X2M0a2gyT0hxbktRNi1YSFpNcXlUZlBwcW9FMGl0RkRoUXJpLXFSYmI1SUlJTkFBNTl0dlExYi1LWm0xX1hUVVFqVjhxWlJwd1Mwb29fX1U0VVFhRE01d3IxSTNpNkkzQWY2TkpJSVVKLWtlM1dFWkFnaEFuZ2hCT2RYWktac2dQLUVmemdKeHlMMHYwbEtfaEI2d2w0MEdYVGx4T2R1ZktDV1RWQ2ZfUFBDZGRTWVdmSF92OS1kTnFNUTBXeHlZd3ctMF9wMk9lNHRoVEJTUTVYSV9rR0FvdG5jZVIxdzBJdnNSS1VzbXll0gGGAkFVX3lxTFBZX2J6TDljZ3haMlBoSFNpQWJ3XzE1aVhVTXVUNUkyYUZLY2N5Z1VuV19hbzZNNDhsb2RlTjZWRmpObFNlVFR1RmtRcVM3bXZGODZXUnhJcC11VXVDM2pKWVNfdXRjaENBQUZiRjZwZmZ2SmRmRTE1Nmxac1I4RlVla0U0LVdlNGdKS2RxOHhfRUFTaUtlcDNLTFVjY2JyZzBSWFEwVXR1R25rMjZmRldrRldOazUwRmRjTmhpVUl6Q1ViWFo4bS1GaEpuWkhUelYyd0ZBOGdIM0Fxa0p0U29jZEpnR1NWcGx6TEl6ckt5NUNhS0lTVU1QR043dEZvbC0zNmpHNmc?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-25 03:51", "score": -0.494, "label": "Negative"}, {"symbol": "LAURUSLABS", "title": "Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSUFqNDJicXN5c19sQXd2WXNJb1BWb2UtNUpOZTI3d2JudFdlNkZmTzVQUzFKM3VXTHJlZGZKUlhCZTR6MUZob0p6Y0hERlZkcDBzYmp6OGJaMTBKRFcySjNlblpkZXNabW1kZFZLRzdkT2N2Wnl0TWtJcU54Skk2MTJMUTVFQmJnbXlzeE9jSDgxRlhQaUd1X0xibGxDWks3Y01hZkViMTdVNVJYZ3RJald5TGVvUW5sMkV2M2dxbXBiWUNDT2ZXV0xONFBVa1lPOWN0aW1ZY3JVZ9IB3wFBVV95cUxQOGJWak1PMG9YdEpvYzc3S1VhNXI1bDBheUl0TVdJMTBCdmJoM2M5NUFhQzdYb0VFM2dsRmZLOER4U3k1eFUwQmg2QTdlRGNYZ3Fod1F3RW52bWVGUU02NlpaUkVhWTBXUXd3SERZblFDR2JVR3ZZZ1FkcTVTcGU2ZWZQUEVaWlFTMmJRWDR5WHVoYWtQejV5YjRjNXQtSHBKOFdaM1Y0UVBTNTZENWU1elFHYTZmVkUzSFkwUkM2TGw4Sno0SU00WXNUMjZUenpEMXdqQ3AxdmFOeE9HNnI4?oc=5", "source": "etnownews.com", "published": "2026-09-25 02:49", "score": -0.052, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...", "link": "https://news.google.com/rss/articles/CBMiqAJBVV95cUxOQ0Z0MUFZM2ViTTdHaHJ5akJLdkNEbEVZeFFsZ25KVmN6UTE1X2xMTmtUckhBOUdZeE5OOHY5blA4WDhVZDVJbjZCeUJVWE5meUM0aWhoY01DRnRBRHJaVURNTWg2SVRPVkJhUjVUb3dkRDVQZ1B5ZzRhS1ZyUVA1NnNXOEJqbWh0TG5EWHAxZXIzcU5nYnIzQ2xZU2RWaHR1dE5KTE1sMUpTQUthdmdLbGpjcXZvY1JsWXNzcHp0b1F3c1I3ZHpmUTdqMUpmbTV3M0JNM3AzWDZETUFsOFpURk9oQlY3UXB2Rjh6cjNobFhYOTI4MXRUN3YxVXYwaXJnTklxOGU3NXNHSjl6c3RndGt4TmluUUROMVhIZ0pWc3hia3F6blRJSNIBrgJBVV95cUxOdWNfS1N2QVhiREVSTXpDajYwUE9RM1VycGxPNmRKaHU2N3N4Y2tiX2tKSlU1NEpYR0Y5Q2xOMFFhV0VRRE83WmNDUXFvUU5LNXFITElxRmNJSEFJT3dDcGNwT3Q5UHYzaFB4NHg4NlpKUXo3bGtOV1lPRllGMXUxdC13N2RoTl85V01LU3o3Yk5Oa2hzWVZxdGoweFJySlZDVXFPY3NFcXJwV0tpdkxOZDhhRXRpU3ZhOEZCMEZ5QWlBUnczdTRuMUxCcXdwb1Vtd3JWS1Q0aUxpbzhhLXh2bmRtZ05Cc2VyVWM2YjVJTzRXd18yNndmaklMQWdsWlEtdEkybzlJRng2WndzbnJWUGF2S0RBNnE2MlRCb1FGSVktd0g2TEdPdGEwMDRYZw?oc=5", "source": "Moneycontrol.com", "published": "2026-09-25 02:06", "score": 0.178, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Bond Yields To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On September 25", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxOdVk2NWY2YmFvVWRzUDF4anpscG54WjM1SVVVVldRT244LTh1aXVWbXFCWnQyQVZnbmQycU41N3JiV3p5ZTF6VlZMSUI3NUQtR0tsVDF6cS0zdjZiQ3lCM0VhTXFoSEt4aEh2YVF2cXFxY2ZfMkVZSjhuNDZyODRGQUNYRXNpeWdEZzRjd2ZaeThvb3BxdmpBdU1jZVhNWHAyUzR0eGhtTzRHYTVkdTdvYWhRcWhldEkxV3Z2bnZ2SjhqNVYzMWR4MTcxdWc4X0FkNzdjb1VhYUFFNFNOTnVMeGFtUkF5SC1ZRG4wM1Z3VUU1SE5ucnfSAf4BQVVfeXFMTzFDRFpfdFA3RTRhanpJaFljZTc3ams4V2FOMENpZWYtUC1uSEwtYWlNODhZSnhnVXBZUEc5REwtbjFDYkFtSjd3SlBwbHgzblJDQ2pyc2F2aHdwV1NnaTlxU2plcGhYNWg4cWZiZGNObUVPOENwTFRuS0dnbHdTbVNtQTZGUXlGTnVnaEhZYW0xVHhjVnpZdk1qMlQxWFNnRHM4NENlWDFtdFhQODYyNWFRb2haeThMUWdsZk55R1g4YzBWbkFGc2xvX0Q4REwxdHBjb2VidHFmMHNKRnZDXzBrQU5oZmJ5bVFuZ2dIVmhlMGJKNHhhQmFPdlNPVlE?oc=5", "source": "NDTV Profit", "published": "2026-09-25 01:28", "score": 0.807, "label": "Positive"}, {"symbol": "RRKABEL", "title": "R R Kabel executes BTA to acquire U M Cables business for \u20b977 crore", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxOekdBdkJnQy1zc05YRUg5aFF1a0lwT04xNl9vZlhFaUhGVE0yeENFRkdPYWp5eW5qNGJPQ1Z5M0tIQWJTMmVBZ2NIcG13ZTFtc3FJaE9hOG1SQVk2UENVdGNWTXktTE10MGNUVmpvNkxodGg4TS1KdHFlZGprNUpZMkRsS2x6OW1LcGtSVnJPQnFvNlpOaHZZbFlnSlZ0MGtEdjdSdzVvSQ?oc=5", "source": "scanx.trade", "published": "2026-09-24 16:21", "score": 0.0, "label": "Neutral"}, {"symbol": "RRKABEL", "title": "Top breakout stocks to buy today: ITC Hotels, RR Kabel, MCX, Texrail, UBL by Sumeet Bagadia | Targets", "link": "https://news.google.com/rss/articles/CBMi-wFBVV95cUxNNDY4RnFxUWdPN3hFd2xaaFZRMERxSGpxN2Z1ZjF1LWVVZXFDUnZlQzFhNDRUYkdVWW14NDRCdXZ2LUQ0YzZpNWVUQmxtTEtHV1UzaUw1eWtXYm53a2JYSzdFQ3Z0clktdUNZY2J2dE9MU2lxM012czJpUDR1R2ZkN2h3QXNIWGkwX3pEM0xNakt5RUt3Y3hrQTZPNW9yUVhDQnRCaUs5RHdjRVM5Z2RMTGc2cG10WS0ycnl6ejY3YWFsYkUyVzJBYVc2UXlvaVNpRkFKZkZmWkE2RzBxcWFMNElnR19nMFN6cmRzRDBteVpQMjlDVHlaVi1VONIBgAJBVV95cUxQbEJYN0g0YUZETXczaUtkbUdMb1c4M2lQaUszdUtyTXZxMVVYWENrRm10czlDRHQ0alpzSjBhRXMwVzVYUUo0djJYXzBQWlM4S3NZZXZtZTM4TS1zd3BVbEtHeExGNHVVcTI1eDN1VWZHTUQwRllLU0VTenctSGtMT09DTFpSSG00UF81R2ZsdGxFMFlGVFB5aTZLWGVvQ3RwWTVVWTV3Rjg0N1RKbTROQjdaVjR0RTRuRUVtLTFUTDgxdUVMOWVhOV81ZEhMbHlxVmh5Qk5NMXNCdXo3anhfSTY1SlNaSi1zSEtvemVYdjY4R2YteVlTRG1qX2wzQXFy?oc=5", "source": "Livemint", "published": "2026-09-24 16:04", "score": 0.7, "label": "Positive"}, {"symbol": "ACUTAAS", "title": "Acutaas Chemicals approves acquisition of step-down subsidiary Enchem Ami Organics", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxORWVLSFhyVy1XclJaTW9wUmtOTF84WGZkclJHbmtIdW5oUXNJS2J2V2xqUjNnVmEzRDJJRko2Y1UzaVVuYnFOUlRyYTFzNFB1dTlvMXp0U3BTRS1rUV9pWXotZG5FX2xZVnI0eHRaWDhlLVZwaThPXzdCNW0tT2ZEMFp1b0FrRFVsNnZSVzVCTTd4MWZEUm9ERnJ5bTJNaGRIYlhYcmRGOE1ub1c0THBORGt4d2h6SnlBWUhFeVdSUDg?oc=5", "source": "scanx.trade", "published": "2026-09-24 14:42", "score": 0.382, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Allied Blenders among 7 stocks that hit 52-week highs and rallied up to 17% in a month", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQnJ1UkZncDJJcTRVNElLd1ZKN1Nnd053YjRobGxJUEdGYUdWS0lvb0dHS2MtemJ3SUppQmZ2c0NERjFpa2szSjhMZG5BcGZiT3NNa191ZHEtaGRCNUYyU3FhMHBnXzFBUkk1d09ZNWFnNXJvZHR2VU5LTWkwMFlWU19xVnZkUkk2aFd1N1FBZm5xVVlEQmx6dVhDcG83MGZveUFrMm9pMWgydUlPMDFZOTB2RFBBT3JPdDRVYmdKTUtzbVBMTDFIbGlzdkhVMklTNi1aeVFHNjNBUU9RclRiSmtXVjRlakw2S2UzVlhlRTZvWWs2RFNoVG0wUkhrZw?oc=5", "source": "The Economic Times", "published": "2026-09-24 13:49", "score": -0.153, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks (NSE:E2E) Appoints Anand Ganapathy as Chief Revenue Officer to Strengthen Leadership Team", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxPSmdZMUhhTERFclM4bzZicU5pWTdPX3lDUFQ3NU5qcU5hNWVHU3Jrem1lS3FuYjhUcXBVOGJFLXVKc3hCSFlvZ0E4QzNJYjQtNGRHNldTU0pyWS00ci1qNUNTNFpXd2lJLTZnRnQzVGNraVBUUGNhSkJzWWRjVVNqWm9Qa004SHQ0bXIwUV9SNm4tLWxtUHl6eHFoZVpPUHQ3UXZxdUxZTHZrdnpYY3JrTHhFTUxuQ24wd1lBR092aDNFV0lPcXJWMkxITnFFZkdNTkJqRzZqeVFIZmYx?oc=5", "source": "Kalkine India", "published": "2026-09-24 13:15", "score": 0.318, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "3 Indian Export Stocks That Could Benefit From A Weaker Rupee", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQNUp4b2tjbFlmWklUVm5zT2NJRjVXMm53bE5DNjJvb2ZFd0tFZVRUWHVxbWozaEp4aVBQMGtxZkpfQ3FmYnZtbEppcGtXZ1hYYl9seFIwdlhpczRuUWg0dE05REgyUkRMdXJpaVZDc1BORHVteE1IcHptNnNRbkdTY0NEUTZKZk04cHEwWTlNTno4MjJKU05aVlVOZExfd3plejl1cUxiVXlVbVNibjctMlFyOWx3aEZmYk5VNElFYUM4WENySTZGcmFrWURmdElfRjhyTm4xelJnYWNjVGtmb1I2NmxXZnRPem56RDZ2b24xZ9IB9wFBVV95cUxNVGN5NWZ1TnFTNUt1elFVSE5Tam8xZi0zWVY4Um1SX3UyVE5xNDZPZmpWQ2VWXzBsaW1vcnVzX1NoZXk0aWJjeU5iaXpiT1dTejAwSUt6Z3FhTThnTlhsa1ZFdHpfTG1sNjIzQ3pkZ0duUXY5N3ZqZU1qckxKVlZneVRJVmxjU1VrckJtQWlBNWRsNGdZbnRxX253TU56dE9NdXA0RlRoR0dLS0VDWFQ3VXJILUlrcF9OTU1lVk1sODFsbmVIeG1ROEFLcUlhWmswVzVkUjgwRW85cUNQUXpOcS1VZnBLT2pMSlZ1c3lGQ3MyN0JKeGlB?oc=5", "source": "simplywall.st", "published": "2026-09-24 13:01", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market prediction for today: Sensex, Nifty outlook for Friday | Kospi, Taiwan cues to watch | 25 Sept 2026", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPTmEwdzJWdUtmS1lTeHJNaEFsLUVRRTNTSU0yMko0SUJCczVmU05rb2tDckFtclNUdEJzbmN4VUw0TUY0aWwtVVlEM19wTF9BZ0xyZmw4Z0ZTam4wMmphemF0SjRoWWZTaXZOOGJES2dTWWc4MXU2djFTZFQ2ZmtnTGgtNFBvMlpVbFJUeGVCQ242RGpic3ViMFl5QmlzbE9ZMFBIQktpRXRkSWhmWVh1WWJYZjRYQ3FkcEJtOTVNUmZseW02bXQ2cDlheEVZWnItWGFrOU5aTmdDVFQ5UDJMUEI5Y2VSREJGSmRGdFY1UGY0cUJTR0FFUDNSc014endZb3U2TUN0dFdXQdIBjwJBVV95cUxPX2xOWkM1Q0VWS2w1cGpsMXpBUFVpZHZOQ05TMTBkY3BMRHUzcjVIeEdpRHBhYXhKNXUxSzRjZkI1RHpXbkRQdlpBUkdPS0JIVG5jcjQ4cGxZUnZndUIwX1VMVWlwU2c3dUZTNHR4VjZrUzg2VXd6UHFaYzdTV2xMRXQyWmFQcFdIMEJUN2pqcFliNW1tRHU2a1VNNnUwekE5ZWRTYTF6Sy1FbnBhNEQ1Zkh3Uno3QTZuTXVRcHVlNm1LVE5oVEJHLWRiMWFUeEo2ams0QU1ocjRRREF3Vkd0dXQ3ZC14cWNLNE5oM3lPMXNKelVjbmxuQjA0dURockhtcDBQS2gweGZ5NERLYVRB?oc=5", "source": "Livemint", "published": "2026-09-24 12:36", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see worst day in weeks: Why was market down today? | Business News", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxNTTMxLVltQWc5MkFQOUFYNlpYUTlLRnVtOWFTM19ETVhBaDduYk9pa3VKY2lIdGNGTkpIbVVKaDNkV2Z1NlBvdUVVeC1JbTNJem02eHlvdHRvMFFkR285ZjlFWk1fbXR2Z29HSnNVVklmYnhpOVlHdUFxeUFuNmtXeTZFY21KcGFraFdXRVBfNWZRLUU3WEhhd0x5OGxkRlRCbXR5T21JNDRpWE8tSU81VGtxUXFqUzl5T2FrS1dXd0s2QkdoTkRlSWJFR2lORk1JOWpnWHhvanB4bEdTaS1aZG1sbTJfUDFManBUNNIB8gFBVV95cUxQaVFGYUROS1ExTmNWWWI1RHNoTGZfWDd4U0hPeGVCdzM4eUtkZXVMaGZSTXp3NDZEcS1POXpFa01KQlNtY3U5QWgtdl9VV2hZY2VzZGp2U1pQbE5sT1JoQkZJeFFqT3VMOENGMjFXM3dRajdZdTVJMVpIWVVubzJhbjNyakljV1BrTl9vVDh1Nnhnd3VqdDJBbThXVDY5ZjBIZXFKZ0ZHUkt6eF81SHJEbEF0YkJnVDQ4clNuSFJONkZRRTkwZWxLaS1QcEVwVmRqQURkTlpSTm14R2Z4bDV0NEhMMzVJdWZ1TzhaRUlweVQ0UQ?oc=5", "source": "Hindustan Times", "published": "2026-09-24 10:57", "score": -0.34, "label": "Negative"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems TDPOWERSYS Goldman Sachs Analyst Meet Sep 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNb1U1UU5HdEFtaWZCRWdVRWxUc2pRMFZ2YXl2bUpYNE1xNzZBX01tTXNtQWc5d2ZCNTdzYUZwXzU5U2VOX19rRndvYkVDaUl3aGVqQ3lyU01qYkNtVENjRG41VW9IenA4V21EcDhLYWFrdHZPYU9yNGl2RDFSUEdRcEtObWtDS0doZlo1V3ZwOGcwcmRROTcweDNZeTZaRGdQZ084YzU0amppMUZaZERQamg3YUE3RF84TjFuLWx6T28?oc=5", "source": "Kalkine India", "published": "2026-09-24 10:15", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOVTh5Q2ROa0YzRWp5NS1Kamp3NnMzYnBNRlJHcEZ1cVRnOG1aampUb2pFbERqcGNPZjN2WGZqNGd5dWNDN2R3bnhXQ016bjJoUXUxN2FqcVYxaDFrSTlwZGpSQmZIbGM3THdoMUFDX1hwZXo1OHNPTjVpNFhLWVZudVFHU2xxbmZ1aUFnWXZqM09tZzZ0TVlRWUwxakpaM3JIUkg4QlBBaG40QUQzTWxYYzNSZi1uVVZtWTJHVU1UQzhDWHB5OW9Fb2JHS3ExdVR3dExkMGJRRVRQVmZfZnM1THUyOTdWbWhDaWfSAe8BQVVfeXFMTUFnaWZmYkVLMzZkNk5ZRXF1ZF82LXluT0hoSlJNZ19kUVk4VHlzLXhabENVbTd5LThnUlJIc215aVY1T2ZwOThSS0dVNnJNTVBIdjgyQlBPQjJaTF9sQnZWeEw3Z3dVdFVMNnU4ZzBWOENQQ0dtZ1JQal84UmdMS3FvdEFJUFdMbVhXQm5tM3JYNUJhYTFFRnFtX2VIaDJMcWNPUFhpaUs1YjRSbG1lWWVTYng5VnNjbFF4Z3NqVWFHWEd3eEMxUjE5YUFQZ21qdVJJV240Q3dsYTdHQUhKTjVGcnk4UWRhd3lEdTJYeGs?oc=5", "source": "simplywall.st", "published": "2026-09-24 10:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "The battle between India\u2019s stock exchanges is heating up again", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxQSllxZjNuQ0l0ZExkQlp2RmVURXBuMm5WRjUyUkZsOXNaeF90Zy1GWXMyZFAzYmlGMGFfTWlhSl9lT2JNMmVnclFGYlg3bjNZQTRUeERZRkFScXBYc0IxZnhEcUF4Q0tzcWhhQTZXaXR6NjA5Y1pTSWdDQXBPQS1HZWpMOWJHN0NzN0lLWkdiMlJWWjN3OC1Ha1VDQ1ViSE9QTmZmSHBYTVpFM1FiUEJtZ1B4Y01nd2dabTlwTw?oc=5", "source": "The Economist", "published": "2026-09-24 09:42", "score": -0.382, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty crash today: What led to 'Thursda</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lished": "2026-09-24 09:40", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZ3RITnlWRlVoLVRXRW9Pc1NnU042UFB5V1BVM0s0QkFvcnRjbElBRVd1ejJZQjdSTmNfM19uazFjYnZFbm9EMmhxVU0xYWtsd1dZNldfbEFJOE45dEVDMWw4TUVwSW5LdkVfSHZPVnZsRVI4eWhyVFpaQW1mRFM0UFUzZDhXaTB6anpwWDlSSk0yWjlpZ1Z4WEsxd3M3YklFREtEbi1TNXhEUmsxYUVyWXlPTHNxUXJVYUxpbV9ENkEtNURlYnlPcU5lTnBEbjRMVGE0SXdGRTd2VWvSAeABQVVfeXFMTVVqV1N6TXB3TXJhak1kUURlODRETFpFX1NBa1RRb1oyUlVNd0xRcXBHU2ozWVN4dlQ2N1Y2WUhpdTdZQk1NWWNYcDB4U2ZneFRVblBSajlpRmlzLXZWMTNCeHdIZG44a0ZMandxanFjTW5qTHpGM05QQ1Vxbnlsck51UjJhMkloS3dPaWstcTFoS3Q2NEQyRi0zQVhITkp3NzdWRnBkWG1vaVdWSll0SGlsdXRiaUxWc2FUVk9wMW1ZZ09tRlRCa3RoQjNONFhvQmdyN25tVWhBVTBEZmpuMnQ?oc=5", "source": "CNBC TV18", "published": "2026-09-24 09:08", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxNeEtEbWlBNTFIcHJzRV9zU0hnQUd4MVRma2VMWXpOdDl3SURrMGJPOXBnVnFOTm1MLVpMMFAzYUhUWDJVYnpYd1cyWG1xUjhxOVdkb0tVNkF2VnZfZktsRnRYTlNjMzBYblcyM0pHRUo4Ul8xVlFoci1JOXpSU2F2RlBkbFJaZGhTeE9yODV4aDlnSDdKbjd2c0ZKMzc0Y2JFbER0c2hDNW1pbURITlcw0gG3AUFVX3lxTE8xbVZoQm0xdm9CSmg5ZVBDMVluS0lTTUctTnpYYVU2S0RxcFhlaUY5Qndta09tY3VuZWI3MW1LRWlPNVl6QlY4OVBFcENPZEY4OU9jMThxdzM1cG56U1ZtN29HNGEtZmZ6eklRSXlNNERlUVF0dXNjVXV0dERKeFpyeHY4YUV3ZXdWYWhjcWsxM1d4TWtYOE1tUjRFQ0xKQm5aWHJhcnJfSHFha1FDeUJpSDdJaWhrNA?oc=5", "source": "NDTV", "published": "2026-09-24 09:02", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxNT1lNOEhqOHFBM0dUS21nbjEzUDVTOVY0YnkweVp1T1pQdy0zTG9LUmppQkhYTGtIZXBSTEtiVHdDNjZxWm5FM1VXYUl5Mk9WcklBS1p0NWlKY1FUWDNqUnlYcDRrTzI2dms1NVNjenlmQkJZdlIyQllHaEF5VVU5OWE1OFgzeE5jaVdSR0ZfNklZOGpsMGRyc3NXcEdsdFVGRl80QXRsZUhkSDVWbXN0TlRKNjJXSkRSc05IQnczMlpyYXJwYnV3NERXY3BQRjdJN0h6REx4LVo3S1dLQjNRQlpNOU9zX0RLaUlxNXUzRzFmTEdGakNJTHotX2cwX0hyb3lMVEZmR0PSAY4CQVVfeXFMTWdFZHhRbFpBMnQtazZaZUpQVk9Ramd2ajI4M296WDFaazhGZG1OV1RmeGRqcDJkeTNsWC1TYXNTbWtJa1RGRktmREpwbkpqNFYzUlFIYkR3ODg3RllZQTNWZ2h1ZzBLUlU0WXpYV2ZlQnN5WE9pN2JCV2sxbEZMdjcwQXcxRGE2c0lLSWdLVHJVYTRuX2gyYnV6MFlPZDhMUmpzVHpUUWk4WmJYNWtsMnRZSTdmNzBzdnhGRzNRUnN4aTdrakZ5QlJ0aHJsaGRGQlk5NFllakp1bHByRFpMbU05S2tqWFExY3lQYkVlUjlyX3hTUXpmRFQtVmdocWFJMG1aQ29LTHNvb200Rlh3?oc=5", "source": "The Times of India", "published": "2026-09-24 08:52", "score": -0.402, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "Hero Motors Ltd leads gainers in 'B' group", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQSDJtZTVDOFZES0ZIb3BKUnlmdkV5VTlSc2doTWJUZ1k3WEhzVDNxd0doUHI2aFBOUG9FRW1hbUw2bTBKb3FxYlNxZS1kM2VvaWtpcnp4ZEJpa1AxQ04yN3QySVkwS1dUZ3YzVUo3UVlIdzV2eE41ZUdJOWs4cTMtS2ZQNWdySzltWE5CVVFQZTZLdVZCaHVxTDVYTkJKLTE4ZWQ2SlpuVVAxNFFSVVJKYzlhT1FxMnYxZ0dKUDUwNNIBxAFBVV95cUxQS1NzWTc3QXZDVEZ2M1JsYlh1RFVzUjdVdHVWdVFrcWMyRS1zdVRJajBxXzdvSnVzWlZCQXRNbDJyenM5SDJwUnRMcW5BR3ZCMnlKbUY0dTdiVXZMalpuT1lsOHJoaFZtYkhkY2lIbVVXOVJ2MkRoRE1pa21xNU1LWUtYOGpEaVE4VFhqdElqLXVRZ1Q5SHNLVGJfN2VPNUtLT2F1ZnhMUU1hMjNXSTh1dzVZS1d2VE1fQ25BcmZEcVhTVGxf?oc=5", "source": "Business Standard", "published": "2026-09-24 08:46", "score": 0.557, "label": "Positive"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems Share Price today: decline and analysis", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxQcUhUNEJMQ3ZXeU5ZcFk0aUE1NndmWmVMR2E0MVJuM2RhTi1QRHhxT1lZRTZKeXp3NEkwak4yQ1RPVDBDRDlXUlJVUXQ1QjVIMURYTEtsZ2lXVW52SmR2VzZRS3FHanh2RklUTlNTWElScmtkaTdGMGx0SWIxdlF0YjlzVTZzQQ?oc=5", "source": "Univest", "published": "2026-09-24 08:35", "score": -0.382, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNYTRVYTVWR1lSdF95cG9QR1FLMk9SOTlCWVg0NzdVR21OeTdQQXJYc2UxbkUxa2I2blpPOVRYSmVCcWNaQnVxSnpvX0RGQnhZdmp6X1JXRGxXaVk0dXZnRDV0ZTJmdFNMTzUySWNXUjZ0OWN6Y2hwcHY2cWRxLS1hZVRpdHpISHpjMnl6b0s1M1J1bHR6LWNTd1otbHEzM0ZRV2RHeUNEdmY3X2t6ZnF3YkNyRHREUDA?oc=5", "source": "scanx.trade", "published": "2026-09-24 08:21", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices", "link": "https://news.google.com/rss/articles/CBMi6wFBVV95cUxNcnpYS1l4a05TYTZaQUM2enZTYmIxVThMMmd0UzZaSEczczdQSXhEU0tSSV9DdXFXdXE3SUNBem5BRV9BMUFlZF80U24xWHh1ZHM1SkRjU1p2a2NvM2NuRjdMQUswaWJkZUV6dVp1ZzVrZC1jZUdkX09JaWRSNWFOcEdOc1JFUVNRcEdfVXdYMVF4MHpnTl9zRDhLQWY2NVllQzkyMXN1Y0YzQzdSUTFoUC1nanVwcEhzNnc1NDNtbVZOSFhDVVpUM0F0ZG1VemZSZkF3eU5FSldzSEFLZGRBell3ZVA2Y01JWVhv0gHwAUFVX3lxTE1XVE1JUmZXOUd6YURZeGlua2c3dEZoZ3NQdWY4SnB2RFVOa0dnd012UlV5Mm16QmE1c1c1SHppQ2luZHZqU3lfb2llTkxTQmN3MUlpejNJOVVYb3BCaUQxZ1RSWEZBWWFwdjVlN2ZTZWVyTGZhdjVfWkNtUG50SkNhS3hNRFlFbHBhMG5DMjZXS1FGVWJnMmUtVzJueHhRa1IxdnZpaGVuU3ZJYmhUVXFGUWFNVW52ZGxYODBxWFVzMmRnNl9PMW53dGJ0Qi1EZmRaUGhzc0FLZWxnejdscjFjRDdUM0UtRWNpa1d5bm5JOA?oc=5", "source": "theweek.in", "published": "2026-09-24 07:35", "score": 0.077, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom \u2014 Ask Profit", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxPcjBhRnpQaFhkbGdfV3E0ZHlmUjFPQUlUQm9LTFU4UnFqSHduWnhNSEcwenhUQmM5LUxsdFNwUXN1S3gxZW9PN213QUx2TDhzUWpoNXJldnBQRmI4eTBIOE9JMGdqd3I3T2F1QVVYcVZSUF9jOEt6cnB3QWhmZ3F3Z202eHZkRXM4NHduSVVzLThxbTQ0aUJEeEJlTThhWHBFMkJ2OGJ5X0FXT3ZyWFR3MGlZeWEzWjJGU0hhejlZTFgxakpDdVVtbkV2VGJtOXU3aTh4Z0lPdmtneU5EQTNudGd30gHqAUFVX3lxTE5SeDJuQlhJbTcxaDUzbWNPNjNuZDFqLTNYYmEwR0o1QW43WVdkLW9FQUhpVExqaFluQjJwYWRVcG5NcE1ELTduTUxUVTJzQjhvVlN5YWJKa1AxaEFjYnIxempBeUNFbG1IeW94YVMwanoxOHAzNHlRSnFUbWJ3anJqQWVvb2xQeVRwZl9CQUwyUl9KSXhhTm16Qy00Uk5JdkhGU2Z5SGRzNkthQmRBN0J5WnE5bFNUREhuNC02SklqM01odWNqWjV1YTVsVUhXUUZMdlhkN09kWTdvbHhZUjFXV05sVTlGQkptQQ?oc=5", "source": "NDTV Profit", "published": "2026-09-24 07:25", "score": 0.296, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxOU0F5bUI3X2RaNWllcFpuSUpqZFp4Ui0xRVNpb2FSbVRfMjZieWxhWGV5R2N5MHpqeHBQcXIzT2dfTHBjZUt4Zk5aV2Y2SDNhM3VjamJBeTRhUjNjVklyZ3lWZDMxZ3hMMjNXaHFHWUFKV19ZaEp1WTBQekRXOU5ZdXc5UG1hQkIxRTJWdU9USDZqekc5QTh5VENqRW1ybVVCYUMwODlQRGJGVUZKV28tSVpXMFQ?oc=5", "source": "Kalkine India", "published": "2026-09-24 06:20", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'", "link": "https://news.google.com/rss/articles/CBMimwJBVV95cUxNblY5UUJKckZ0My1hbEZrdS1NbjFpR0Vyam1YUHcxd1BSMDdzWkpVZzVyN0ptcnZWZ0EwRElGTEdLV1pWNFd3a05HeEpBOC1UN0NCandyUjlzUVpsUXpKZElQajdHYUoyc2dvLXdMVkNQSW5lZHNFVG1aMzVJQ0tUcENOcmR3QWIyUFNWOFo1RENRX29SbEZLVmNGdVdjSVdkYVZyM1l6dUNtaE9KYjk1VmhIVTlWUlVZNUVFekwwRGZETkw1NTFzbWhSX2xVc2RTdzdCRExjMW5LZ05EbFZRODJvcXRnbmpKZGdPRGlpeGgza1BVNFA1V0xkR2ZJUEpCNWpPZnh5aXR2MW5aQ1EzTEJBdGY5Mi1UTkZF0gGgAkFVX3lxTE9GWEM2U2ttbzdkc05MdlJqN2tFU2pGUmxYbmVIeHktdHRhWVpuaWRnUE1RN01WREtsT2x1cTBBbExxTi1sRE93d3FvWDljRGJzWHNxMW9jek9KTklxUEdnbUk1a0t0YXdlMVZvbzc4Mnh0c3hUUXMzdV9VOWV3UXdqSnRQZFJNaVNRZ1RybmpKR19rS2dNdm5HVkNlUmRUTzJrbkRuYy1fR3pRLTFLUDBZcVAxMjRrdXg5ZVF2M2NDMjgwTXZ4bktqUXNidVU1dmJKWXEzUi1NLUwxUjliSG1vU2lQeWM2S1lRdkMxbW1qSGI4M1lpSHRVS1FVXzNja3B5Q3BYalFYLXV0T3d6VXlWVVdEWTdfUVRsWFV0RlVkdg?oc=5", "source": "The Economic Times", "published": "2026-09-24 04:09", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxNNmFnZnk5VzNtcVFkY1JFVlVCMFh6T3BlejFod0JXRWFjMng2alROdHU2YzRmcEVCV3VMZFdYM3hCbUFCa09PVmVkWTh1MWFaaUxhTndsdjlVb3pZZy1VZU1wWFl6WnNvUzUyZ243ZUQ2RUVIMEhVbm8tMWxWMzM0Y1N6aVlPenNvZkl5R0hmVG5JWlE2QkcxNlRDd0UwU2RSN3NscF9PR2NRVGVaRWYyVUpMeHFrYWNVcGdMNTM3MmpSVGdkc0laX1E5U2U4Q0pBM1N2cUNlQndvUGRvUHVhT2w3Qkh0UHZ4dkcwVTQwUkRMMHlY0gH6AUFVX3lxTE5jREhsTGtRRUVDMnRQMEhucHBndU15SnViUmVFb0ZxTUE1dmpUSlBMV01WYkZ6UXd4QkRncTdNZUh5VVRxNEQ1cmViQ2Z6WFViOVktS1hld09jM25FTHRYN0lJa3d2Q1NsWUxZR2VqUElmYXVFVk5wczFqMy13QUd4Ty1ER181WE5KaHE5SEhFdHZzTy15T0tnZ3pyZzhVMktvLUI2WDF2M3hTRThxVzZEeDRaU21jYUd4ZzZPbHlWRFVMN1lZVGRzcHd4bDUwTWc5d09MYks4c21iYlZKNUUyaC1GOXIzZ1ZzT3dXTWVaWm9KdVhHYzN4emc?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 03:56", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPRFR1dnlza0cxUU5PbXRVYmRRT19oaHZFS3NmTDZUdHhDUVpIaTJDVDFHYThvSXE3RzNWenBDSUlDUDVCdE51VkpDaXppUEl2M1htMGxsMkxPV3ZaS2d3YVhYVTlFUEphWm45cWVuYTZLYmJ2V0xwT2dtMFkwQXZ5bjVWOVh2UHczVnZUSFQ5NFBrUkJaQTJwRXFoSlY5ajhXaHJXOVd3enFaclR4QUpXODFjMWxjVVE?oc=5", "source": "Reuters", "published": "2026-09-24 02:46", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPUXhSRW9fbndZUTd4Q3FFZjhsaThCbS1jNzk4Z1N2TUdiU0lpcHNQcEZ0WmpqdGZHUUlIUUhNdlNseThhQ0hkVDVNazBSQTV1SmRVNTJ6SnUyVTBEQ3pfWTBubFpaREdzcjI0VTFacmFUZzI4ajJfZXZLcU0yQ05NcG9BN1ZkYWQ4M3pJVkFmRllNRXJXeU8zWXRMRkVoQ2o5aGJOamlGaXlfYll4WDBEdGdpY21SN1o4UENfRGNSZ1E5elpxVjJ1aGVWZ1BnZGpfUFMwM0VYM0t4eHpnM3BTTlBKaFZoQkFTT3M2bWhSNlExcEZkcmRUUHZMVmNzSzlPc2fSAYcCQVVfeXFMTnBRN0FXeEh4U2V5eEYydmZXb19IdldaZk5tYU8zbVV2TFV5ZjgxOGg5cGZfdHVScXprR3dCeEQ4czVEOF9zSWpoM3MzdWVrNFphaTdJZWg3SHVac0VnOVc0Si04cUdma2xrRFRLRlJSakp5N1FobmtwdUNqRVRFNWxsYnJrbVpjRHI2RTI5dmJ0Qml3eVBLa2NTXzNhUHZzckNXVHJxVGs1clVveXhUYlk1MjdQOTE3SDZTelVJb1JpSF9wWkpjMno4X0lDdkt2TzFIVE0zVEVRaUFxNG5IVFRhTGRwVURPZlBOcTZtUmlNTTJYS0gxU2RWTkh4T2RZOHB3SFQ4RHc?oc=5", "source": "Livemint", "published": "2026-09-24 02:44", "score": 0.758, "label": "Positive"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxOT0tVTzVLRFhsRHJ6QVB0WV85ZGh4RHFXTEdKY1R3Snp4T1VIcXVyQmNMOGpKeDF2aVdfckZKRGVqMzVpaDlTMDU0Q0lVemMzLUxFblYwQkIxcFFvalhLYng4bVdZbUhqTnFDSDFweU93akx6V3ViVXF5cEtCbk9QSFJQTjNobXRLQUpPTGNuSlc3UkVfNGdnQ0hWbXJldU11M3hadi1FU1o5azNRZ3pIUldvMkV3b1FQYVktMldOcWZkVFhPcHI2QUdMOXQxOEY1aGN6TG13WW1yMjlQWHNYd0p5LTFkRGZqOHhHNlJIcW9pWU1VQ1k0Yy01VDRPQdIBgwJBVV95cUxOdVk4MlI1LWY0aGw5azFlQ3UtdkF1V2lVYjJBaC1UYUtRNi1FT1lTeWpTbG1jZ2dPeGtBVnFYcTdISXFqaUxJcnpuZ29EWml0UkJEN0VfeHRONWRtcGo5dG9ZTDhOWGlvemZrUWZHRWtxUVBwcFRaRno4UmpWSDIwdHh6Si1LbFFDS1E3R3hvTTRGSFA4T256enl3RjBfb1hWNEFaTEkyOHJNRXBMVng1YnJMd01TMW51ZGhta1dRRmNnc3p4TC0xa2lsMDVOQ3VoZFZzUzRGV2IzYTVzajR1Mm11ZXZ6NkNfNjJjSG5iOVNmSkVXaWozaDNwaHVTNS1MNjRF?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 02:38", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields \u2014 Five Key Factors For Sensex, Nifty 50 On Sept 24", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxNMHRUa21iWVZtelA2Um13ZTJ6ZDhOSGNJMlcyandCLUFTT0w0V3R5eWd5SEdCZ1pyOEMwSlY3ak42dHRhUjdnREc5UzdaNmI3QnFkd2RsLUk0SmhaRGNqOS1QdWp0ZVdnOExERTduSHhXZlpFb2ZHaHVneDFmaGdpVTAwa3I4RWxTT3NxUHp5ekV2YTlVd3ltNS1FLTdKN19nUzBFaHB2a1Etd0xVb0NMVDJMaG5RcGlDMDhhLUJqOWFoTmFEdXFCbDZ0SlAwTmlheHZuWEZ5dGJJdW1LQ2dGeTVtNS15Z0tmR1B2YXZ0eDR6YlFBUFRIUlRVLTZ2ZTjSAYcCQVVfeXFMTVJoelZ4TXkyUmNUWkk2RThDUWRtT1RrS0dqQUtzTHJTM1RZX0w5ZHl3b0xicjN6Z1IxS2dQUV94YWdwRGpyME1rZmVaZnZ6SGE1bW5sUlM3N2ZBYl9lajJub1AwcjJLYUc1d3pHUG5HLWUtc1VFVlc3Z0FVNXI1anMwNzA5MkZvd1YzdTRUNHpRZTBBSWpqcm05bUp0ZmxNZklyNU9LS0l0NG9uSWZCRkhYenIzaktxa3Bic25SYzVfVVdPcko2ZG95YWhraURGZ212MDJBVHBCVWxXUWVQVzZZLTFIZmVGdkdsNHF3aTNOclNEMUEtSjNsUHFCZU5JSlA5bE1aZGs?oc=5", "source": "NDTV Profit", "published": "2026-09-24 01:42", "score": 0.844, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQTDl3ZlJyNW5xZXBBLUtBLXRfSU5kbEdSOXFWM3V2RU51eVdlanIzclZnczhweGRBR1lmWkVUNWI0SlBsbW5tWmd4SzBzNXA0Ty15d21DNVJkQ0piMXpzMDYxYkNndEtmV19UQnV6NVBKZlgzU1ltZEpEakJ5dVl3WU8xQS1DRVQxN0pxV1NuU19RaGZhTWNqSHFhRHFGUVROWDhEMkxhODZ2bmZFX1piMDl0ZzVJSVRhUU5KUC1pV0NCclR5dGxXXzR1VUNvbHMweU1xaHRIQWNIRG5HN1o4NWNlRlBlRjhRVFc2SElTNklUNEtMSXBZVmQ1YkxBOFg2eWtOOFZiMUTSAY4CQVVfeXFMTUdPNHFyRDVseGxVX1p5RDdOWFBabmJQdm1ZNmVZOVB0RGZMeERCSnFfZUMxV3FrMXBJT1liYmFZekEzWGR4cUs4eDlKOUhiNURta2xDLTM0dUFkRTJrOHNaa0djNnlJWFpQcE43OGt0SkFJNEgxSm9hd0puemtzNVgyX3dHdUtGa1VIRHJBdFllRUFmYlYwQ3Y4elV1djY2ZUo5R204dmZyZ3RwaGdZSHZrbERxQWZfRlhCUEhrZjdaelZGLXZmY2lTWm84ek9wWHYzdGRKQVFOR3pYWU94RUVERlBYOXFEeDJaUVI1and2N1hCenc4anc0NVVaRG50TF9Pa1o2di0xc3k3SDdn?oc=5", "source": "Livemint", "published": "2026-09-24 01:17", "score": 0.842, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs stock gains 1.37 percent as profit jumps 126 percent", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRGZMMkVQZFBodEJ4cHVqbng0YWJyNHJjbndja3pLdkJzamNORjlNUGNab3A1MDczV2piSTRpUG5yeklwV2ZvMWlFMGp2OVota2lsTHJoZlB6dG10UlBHeXRYNTk5NlRLVVduSzZJM0dLdFlTN2hkM29mWnhNU3lHVUlaTmlGQ25fUFo0dXhGT2cyNWlhQmllc3hiRFU3Z1RIN01VV0xHOFBTMUtoWUQxTDZUY2J0VTNxRXYyb2xhQ3c?oc=5", "source": "AD HOC NEWS", "published": "2026-09-23 22:57", "score": 0.791, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUE9BMFBTZkQ0bmQwWjZyUG4tSWp1VU1ERG50V2ptaVRoamFQX21HUDNBVmdwOG81TjVLeU1GSUZoNGIzUU5Vc0drSzhsMlZkOFl4MmstUEMyZWdYTTNING9fVnZrR0ZvS3VCYmJaVEk5aFdJRUJNWTZMMlV5Sy1iaU5ieC05WjZtaFJaQmMyaU5jTW9Oc1pmZHFsaUl3aVJ6TUJTR0s3SjYtdnE4c0NDejFJOFprT0Z0Zm1RTGFsTFlFVTVvUHo3d0lpZk16R1NmVGczYlUzZGNXb0Mwd3RQUmxKR0pRcklfUl9XRVNyMEZBZ1Fxa2FsSWtGSllrV2QwSmRSVnBOMmQ?oc=5", "source": "The Economic Times", "published": "2026-09-23 12:57", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxOUExzY0ZPTTBDblhZUWV1SjVUZWd0amE1STlQN1N6bm9VajdoT2NVb1ZvVjJrcHg2WTNBYlI1SGkwMlVOU3o4NDY2ZVpRMHRkRUhVUWVaS0N5QUdNbzRLa1I4UkRhNkVwOWpaVVNxOHhFV0NxZFhGOUx4anFCRDlDb0ptMHlzWFhvTmhMTEFvSk1ybFBSTzA1SG1KQnczZVdTX1NmUktxYURuVTBFbk0ydGhjNVBNN1d0Q1lUWkZlQVBJWWJLd0NhVml5amI0STBVcEs5WW4tN1pTajJSbU1wYm5ydUdIUjdvSW04MWVkdl85NmpZVmVVVFl1YmxZaWxBTVB5bkhUSFVaMXFu0gGSAkFVX3lxTE5LZmlZbUxuSjFGRzllWHk1R0RmZ0tla0huTUZYM25TUGxFMXpWLU5rTXc0WXdXM3lTWW1nYUNmNTI2elJWcEhZOTRhZ3A2X2JOUHZ1XzBuSmRRX2ZsNGZrQVBkVDlFSExzbHc3Z0VPYjRTekszODB5QndnS1Q3NmVvRmpfdmc4QzhRcGZScWlZZ01KUE1ZVWZmSFQ0UnpKVFllOFZxY3ZIME1LX2xaZ2o5bUxoYkR6Q0JQTlN0b3ZWU19IRHRCaTRmdFZLVXo1dG1oODdLOWJhSkQ4akVrODVaQTUxZnZtLWxUNDhyTGdxMDBkS3ExQXJwbnRPQlpxTFdReTZxNEtLWGRwNnIwTEhCcGc?oc=5", "source": "Livemint", "published": "2026-09-23 11:16", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPaHBTQzhTRUdZS2tNRmJlTDU1UXJ4bnYzUXZNY1RzZWhub0dSbFFIZDM3aGZCNFJ2V2F1QmJRX3lVelpSd2ZsTkZVTF9ncUZCZ1NYblZYUjBYNi13Z19fOVhDN19taGt4MGV1Q1NtWEY4U0lrdnVXaUtFQm9TZTFUMGlzNWdoTUdBYWZxOUtWcG1idGJwOE10NTloS1hrdV9HN3lhLXZXWUh3dzA2TVVLcHRuRFJDVXdmUC1nV084LTVEV2N4OFRVQjU1Smg4Q2ktSTBKWmRCRGtRdWdWOEc5UGh0YWpOTUlNWmVyV2l0RC10T3d1YndQalotU0NWWDBqTDhn?oc=5", "source": "upstox.com", "published": "2026-09-23 10:15", "score": 0.612, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure Share Price Rises 2.68% Today", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNbjd5UVZ4d3N3ZUtybnEyZW1MZ1R4T0NrS1JsMEhETFc5d2tyclFHRnV4bzQ1RVQyUkZvNnIwOURYdjdBUzZldEpRN0FBV29YLVZOTjlFalZfemVpUzBVZ3BZSDJxSVFqSmdCMDVfNVNVXy1ZZVJpZUZORHdmNUFzazBrdGVsOGVPN1ZMRmdyQ0U1X3kzS1ZNZU1mQQ?oc=5", "source": "Univest", "published": "2026-09-23 10:02", "score": 0.34, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs Share Price: one-year high and valuation view", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYU9VS2psbTA2SEFlWWF6NVFFbVRManpTcU0wUjJIbWRQdEU2S1JUeWVXWVUtSW1RNGp3VmdEZjRGYkdVYmFtV2tZd1BQLWJfT2ZHYzhXcFhMTVgwaDlmNmZkOHhaY0JiOEVaQmZmTk5FS1luRmcxeE9ZbGV3VDlqOWR4VFhCZEE?oc=5", "source": "Univest", "published": "2026-09-23 09:19", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQa2ZFOFYwaEJuQTl6N3NjWFFvMWUyUGdxNXlZNFJHVWxtcFNEenVuTlNieHRNX3RpY0dfNnNCUk1hMU9Ndk5Sckl3TVg1Z2lJYnFORjgtY0UySTc0WW5qVmV0bU5hd0UzTVM3OVdKUFNUUHdzbEhaTTNERlV0WTdFWTBYSnpadUhucV9mejJxMnNlZ2V2UzJaOVY0dHdfNWtMVWN3U0tkVVFuSUVSMnV5NjhTUUE5a2Zrc2xieTVkZEphNmVqSEQ1MmRqMEFKM2xwU1FCVkxkZ0VsdFZYazRiMDhKcEhsejFNOXgtSGo0bFRJWThyZkZaXzJVQWpwbklBNno4NE1QSzRfT001NktmddIBlgJBVV95cUxOdy1fS2JiOHZGWTlaelh4ak5fQTR6TU9lek4tN0tIODhtWjRtRkJmS2hhZHVLTmpSMkQ2T0dXNnk1VFlTdFRjcmE1b1dCQWYtSnVQRFh0Z1hsUUljNkZVeF9GQ2pSZmplX082cHlVWEx2aVQ0dWpyZndmREdSOUJmcHBfczhYU0ZjUVVWYU96N1J0SENVQV8tR243REJnYzZwcnNzTlFnakJWcmV6eU9yTUs3NC1FWVpwRnFiZTRrUVVtM1UxQy01YnNsN1BweXNTbGpkb1l1UTNTRzNDUDEtWjBOeVJsa2QtejEtRElXcy1LNXc5bW5FY0Q4TGhXQXNWWlgxRjlXQlNEQ1R0V1B2OVZqWHluUQ?oc=5", "source": "The Times of India", "published": "2026-09-23 07:59", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks Share Price news: price rise and valuation", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNS3pobG5zQUpFLU53cFlCQWxZTFQ5S0E1dDNmbTU3V2daQUx1ZTMxMjctRHphNW5OSWVoYk9UY09CU2NxbF9GWjVCZDJzeF9OTXVTX3NUYVRjZ1U3ekZnLVFxZ01Sc3dVWlZIcnZOdXdvTzVlNTdoMlhYaVZZaWNaTEpZTkxpZw?oc=5", "source": "Univest", "published": "2026-09-23 07:26", "score": 0.0, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQThVQlhqMHhQX1dCbzk5aTVLRzAzLVhTQ0kzajBZMXRVTTNTazhRNTM3Y2d5SE1fbUhYVkJkT0hDeDlCZFhGRHEtWUxEcEhISzA4bkNGUlQ2RW44NEdPa1k5VFF5MGktRHhhZHJMRjAyeUVCVmEwWkVIQ2ROQmlhdTZTY255RFg2Rkp4NWtCTk1vaGxrUFc1VTRFSkJFY1Nnakd4VXpMNGxRVkpvMkl5VnpmakQtMWgwcV90RFpwM3BwaFFfNzhsR3IzQWhRNmpCWVVjdVM1ZExSSkxZR1N1bEpNaUp0eGV5bGIyTDQzZTZjdw?oc=5", "source": "The Economic Times", "published": "2026-09-23 06:24", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPa2tacGJLRFdET1pPVlhxQlRodHp4ZVZkREJLUU8yQlFiSmdib0hReElVbW5Qc2QtMnFqZWVDREFveHlPbDB5MHhGQjlBcTVfMS12Q1hyNGRFUjZrOHY0Ym9jSGhaSnV4YlZYZDZGV25jb1NtRV9admFLQWN1N1NETF9pUU1GbFFadFVXdzJ0dUxJelU3SFlaQUR0MlZxTWxHaDQ2SnpjRl9LczRSQ1BiX2h6SWl3ckJiek5mSDVwNm84cVVBYnRCSnFPYWRHLUlhUUlwb2cyN0tGdHRGU2lNdnVkdlNQZGJS0gHuAUFVX3lxTFBtQmV3OHlXVURIb1VpaGFmZnYtYjJnSFVyVjEtM2pvajJYV3BZQlZDOGtuOEZ4dG9hMDNkQmJVaXJPODNLdFdBMHJVdmRoTkRkR1NERk5DaWRlNXgyMUJmNDkzYXZzWVUwSzlIZ29CX3BueG8ySTU4Ymlod19HTFVJM1k2X1FDMmFpLXJPa3YtVjlSdi0tdjJ4UVc3MHZGR1ljSTJHdENmV0MwOHhJdmgyTEZBV0ZUN1JVR2gxOFhXSXBHdXlWTVYxT2RMdkhnY3UtN3FXOGd1UUtZYWRaWXVIR193bmsydVZRVnJNV0E?oc=5", "source": "simplywall.st", "published": "2026-09-23 05:56", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNUnltRmdqM0NYQ2wzZWItS3BOdjdlU1pUcFJ6aEtPV1Zub1hfcVR0MERkbjZzTWpuc3pFdFVxUFBSY3U5WEhLVjdOLV9tX2lSWG1yNjJzUzVWR2xhRFJ1NUctcDN6VlJtMGlZaGlpQWx3T3RBYWs0ZExick04cTBYd0tYY1dBcTV2MjFVTUtsWFdtY3NZMFFiVjYyM0JpSmpNUWVzSVJqRGpUMzUyRHc2dm1yZEgyRmNnQmpjbDFYaXZkV3NPaXgxM2ZFWGtoemxNWU9STmpkUVlSa3oydXk5bjJpMWFRWlNqM2J5Y2lCMTB4d0FoTGFNNdIBgAJBVV95cUxQYm1wblRHcjNRcnF0MG5Uel9qVFEycDNoSzNfQWx4WWoweVQzX3d3Ym5UTTM3cjVzUG9STkdXYmlzc1psbE10cUNKYTBGVlZPaTh4bEFkN0szUHJmS2wzYzRmazBKT2MxY29WZUxaWVhmdjVEbS1TU0NyeFlRVGFEbXk3R2R3OFJYc0s1bTZmbzJGZ1hDRWE4Z05Wa2lPT0FiWWRvaFlRWFFkaDNoYnBmazJfYVlhblBVMF8yMDlfVllVdk9BeVZKUzRVSXUwNUlxOE9LUVZENWw2LW8yNGhWX3VnaUxSZC04bDljRXJGZUE0RlgycFlabTVrRDVoYy1W?oc=5", "source": "NDTV Profit", "published": "2026-09-23 01:42", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxNNi1kLW5uekpsdjNub29Fa3NDaWEzNU91MUMxNGZMS1ZVeEZPZ2tiLWZWY1M4MW84dTRYRl93QjFISTVtSG9oUHRpLUZZcE9welgydkFGTDZPRWtBbXVkaC1xOVgtWnhuNVZNVklETHgyNFdOMEo3UWFjUWx4dzI0ZlZDbXJ3cEdKMTFWZkNoeVo1OXlpUG1iLXhIUkREVElXLWozbkxtUWtmWXFxc043VHB2R0NpU2dQVVVGZlNWeXNkbVItSGk0VGZ5M202QUVzckd5bFliQUtMbE5SZ2NURVNsZW50aFZnd1RsQkJoRGVHUklpNF9iRGxCbE5XamlvWnZyVUNIM3NrdkZiYjI1MjFB0gGXAkFVX3lxTE1waWJFallWREMwLVdIUXFpMDlzd1loMmViNEdDbzVfbTJoSUxubGpLVy1NZjU1c2taUzdsczJIaG9OSmpIVFc5bUlyRjZQdzZkWVZKeVlwMG9GTTI1N0dHV09ucTJJX0hQUS1rUGtMLXhVTkNXQjNpNDVYVTQ1TmxtMmVWWGx0UVhpTDhmSGdCNlNma19TQTZadDlPa0RjZ2RfQ1dLaXFHMVZtdjNPRzFhdGVnMFYydnNJR3VGWEJiTHVvNW11dV9SbzNiaU1fSEJLeUpVY0R3UnBZbWp3NTNZN2NwU3ZFMzVhME9XVjI0cWdvdW1DZno2ZHVkTWFwMkRDUUkwdVRsYW5XQkx6M0gwX2tJYWJacw?oc=5", "source": "Livemint", "published": "2026-09-23 01:13", "score": 0.557, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPeE5EWjI1ZEd2aG02OThzbUpNSXdERzVpYkNmNXRCdEFNLU1JUEk2RG9IanhndHM2N1oxMDAwblVrcXpSaVFfcmc0WEF6UUJqd09acWZQYXdzM2cwZFJkUVZVSkE5Tk9WWnhJV0ZXR19HN18tRFhCU2hqWXR5a3lBazR6UWN4UDJ0VEh3NGFxNE1oX3M2Sjhib0h5N0RvMGdUcU9zVm91ODRoaGl2dVJXc18xTnJObk9pS3BfX1lQWS1HWGUzR0lEbDZ1ZTZ1b1FlY0h6SnBCRdIB3AFBVV95cUxQbHN0Tmw0M3l2RFNtTzBTaEtMbzJ5WmE3cWRraUhSRTc3ejR4SUE2NDBvTEhqMTZPQmktdXJ5N3VwM2ZudzBPTU8zZU1tLUVIUFlVVDdCbGFaZGllcHA5UmEzLUpOU2RlU2c0YzlrTUk4ejU3UUxQM2hXTWlsU0p5eVh0blVNMmdpcERxXzFnZ1d2R3lzUzE2c21vOGxBWGlIMnR1Z25MQTlITTI4S3JIcU56YU5VVHVyUXVSU3JHZ3ZiVnZFLWVFbmR0S0dHTHVqOGw2QlZrZzg5bDFT?oc=5", "source": "simplywall.st", "published": "2026-09-23 00:46", "score": 0.0, "label": "Neutral"}], "errors": []}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T18:12:59", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-be</t>
+          <t>y Tank' - Top impact made by these news; check biggest losers, m-cap loss", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPVWZGNDlpWFN6MFJFZVZMVWp4RnIxcTVXOTRMUS1oVnMyQkVmZkF4eDdQTGYxOXVKV253c2dWUVZrOFpQUEEzdUQ1Rm45bG1aX01RSzVBNjNIWEFIb0lLbFJsSWJNYzFzMVFaVFpXUnAtR2xtZEZ5YXhjdXRSOHI4ZkNVMlJvWUszcWJEdGFBWmpqZG9zaGJWRnZGMHFtM0J3OWluTEZMVE9xSkV0Q29QTnJFQzEza0ZQaERRWjNBaEN6QlpkSFdMcGRuWndIWE1RVU5uczhza2w2WndRYWlUVkg3Yi10bUJFLWRWTE1sT2I1NnhwVTdCa3ZBRmxpRklNbGtzbkQ3V1licnlmakQw0gGUAkFVX3lxTE5pNjM4R2ZHalBOWTl1aGVPaWxONlMyd2lmVERYa0RZeDlDMU1IbnZMWnhNQ2VuWXY2dGRTTlFrZVFrU3RmaUJtcjZxNnlVNXc0eU4wQjR5Z29zd2FWZVRoM2FVYl9BY0xldFp3SDNjYnNSdmRwdXFYTEpxcWM5WWFrbHZCeDhZZ1c4ODE2SWJpX1RvX0dkX1VHemI3dmpJem9uWWJsNU1Ia0JFWmxobTRWMjBFdktPS0dsZGhlVjdIaVh6dFRhU0FERjk4aE15ZmlNR19BbmlCei1FRHV2TXNwV1BJaVRHQmxSZnh5dGotNDRaUEpUZV9pMmR2STRRbkhLUHhPa2FMelZzX0VfdXJMOGVoeQ?oc=5", "source": "Livemint", "published": "2026-09-24 09:40", "score": -0.758, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Crash: Five reasons why Nifty fell 400 points, Sensex tanked 1,200 points on Thursday", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZ3RITnlWRlVoLVRXRW9Pc1NnU042UFB5V1BVM0s0QkFvcnRjbElBRVd1ejJZQjdSTmNfM19uazFjYnZFbm9EMmhxVU0xYWtsd1dZNldfbEFJOE45dEVDMWw4TUVwSW5LdkVfSHZPVnZsRVI4eWhyVFpaQW1mRFM0UFUzZDhXaTB6anpwWDlSSk0yWjlpZ1Z4WEsxd3M3YklFREtEbi1TNXhEUmsxYUVyWXlPTHNxUXJVYUxpbV9ENkEtNURlYnlPcU5lTnBEbjRMVGE0SXdGRTd2VWvSAeABQVVfeXFMTVVqV1N6TXB3TXJhak1kUURlODRETFpFX1NBa1RRb1oyUlVNd0xRcXBHU2ozWVN4dlQ2N1Y2WUhpdTdZQk1NWWNYcDB4U2ZneFRVblBSajlpRmlzLXZWMTNCeHdIZG44a0ZMandxanFjTW5qTHpGM05QQ1Vxbnlsck51UjJhMkloS3dPaWstcTFoS3Q2NEQyRi0zQVhITkp3NzdWRnBkWG1vaVdWSll0SGlsdXRiaUxWc2FUVk9wMW1ZZ09tRlRCa3RoQjNONFhvQmdyN25tVWhBVTBEZmpuMnQ?oc=5", "source": "CNBC TV18", "published": "2026-09-24 09:08", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets Hit 3-Month Low, 5 Reasons Behind Sensex Crashing 1,250 Points Today", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxNeEtEbWlBNTFIcHJzRV9zU0hnQUd4MVRma2VMWXpOdDl3SURrMGJPOXBnVnFOTm1MLVpMMFAzYUhUWDJVYnpYd1cyWG1xUjhxOVdkb0tVNkF2VnZfZktsRnRYTlNjMzBYblcyM0pHRUo4Ul8xVlFoci1JOXpSU2F2RlBkbFJaZGhTeE9yODV4aDlnSDdKbjd2c0ZKMzc0Y2JFbER0c2hDNW1pbURITlcw0gG3AUFVX3lxTE8xbVZoQm0xdm9CSmg5ZVBDMVluS0lTTUctTnpYYVU2S0RxcFhlaUY5Qndta09tY3VuZWI3MW1LRWlPNVl6QlY4OVBFcENPZEY4OU9jMThxdzM1cG56U1ZtN29HNGEtZmZ6eklRSXlNNERlUVF0dXNjVXV0dERKeFpyeHY4YUV3ZXdWYWhjcWsxM1d4TWtYOE1tUjRFQ0xKQm5aWHJhcnJfSHFha1FDeUJpSDdJaWhrNA?oc=5", "source": "ndtv.com", "published": "2026-09-24 09:02", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex ends over 1,200 points, Nifty goes below 23,100 - top reasons for fall", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxNT1lNOEhqOHFBM0dUS21nbjEzUDVTOVY0YnkweVp1T1pQdy0zTG9LUmppQkhYTGtIZXBSTEtiVHdDNjZxWm5FM1VXYUl5Mk9WcklBS1p0NWlKY1FUWDNqUnlYcDRrTzI2dms1NVNjenlmQkJZdlIyQllHaEF5VVU5OWE1OFgzeE5jaVdSR0ZfNklZOGpsMGRyc3NXcEdsdFVGRl80QXRsZUhkSDVWbXN0TlRKNjJXSkRSc05IQnczMlpyYXJwYnV3NERXY3BQRjdJN0h6REx4LVo3S1dLQjNRQlpNOU9zX0RLaUlxNXUzRzFmTEdGakNJTHotX2cwX0hyb3lMVEZmR0PSAY4CQVVfeXFMTWdFZHhRbFpBMnQtazZaZUpQVk9Ramd2ajI4M296WDFaazhGZG1OV1RmeGRqcDJkeTNsWC1TYXNTbWtJa1RGRktmREpwbkpqNFYzUlFIYkR3ODg3RllZQTNWZ2h1ZzBLUlU0WXpYV2ZlQnN5WE9pN2JCV2sxbEZMdjcwQXcxRGE2c0lLSWdLVHJVYTRuX2gyYnV6MFlPZDhMUmpzVHpUUWk4WmJYNWtsMnRZSTdmNzBzdnhGRzNRUnN4aTdrakZ5QlJ0aHJsaGRGQlk5NFllakp1bHByRFpMbU05S2tqWFExY3lQYkVlUjlyX3hTUXpmRFQtVmdocWFJMG1aQ29LTHNvb200Rlh3?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-24 08:52", "score": -0.402, "label": "Negative"}, {"symbol": "AEROFLEX", "title": "Hero Motors Ltd leads gainers in 'B' group", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQSDJtZTVDOFZES0ZIb3BKUnlmdkV5VTlSc2doTWJUZ1k3WEhzVDNxd0doUHI2aFBOUG9FRW1hbUw2bTBKb3FxYlNxZS1kM2VvaWtpcnp4ZEJpa1AxQ04yN3QySVkwS1dUZ3YzVUo3UVlIdzV2eE41ZUdJOWs4cTMtS2ZQNWdySzltWE5CVVFQZTZLdVZCaHVxTDVYTkJKLTE4ZWQ2SlpuVVAxNFFSVVJKYzlhT1FxMnYxZ0dKUDUwNNIBxAFBVV95cUxQS1NzWTc3QXZDVEZ2M1JsYlh1RFVzUjdVdHVWdVFrcWMyRS1zdVRJajBxXzdvSnVzWlZCQXRNbDJyenM5SDJwUnRMcW5BR3ZCMnlKbUY0dTdiVXZMalpuT1lsOHJoaFZtYkhkY2lIbVVXOVJ2MkRoRE1pa21xNU1LWUtYOGpEaVE4VFhqdElqLXVRZ1Q5SHNLVGJfN2VPNUtLT2F1ZnhMUU1hMjNXSTh1dzVZS1d2VE1fQ25BcmZEcVhTVGxf?oc=5", "source": "Business Standard", "published": "2026-09-24 08:46", "score": 0.557, "label": "Positive"}, {"symbol": "TDPOWERSYS", "title": "TD Power Systems Share Price today: decline and analysis", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxQcUhUNEJMQ3ZXeU5ZcFk0aUE1NndmWmVMR2E0MVJuM2RhTi1QRHhxT1lZRTZKeXp3NEkwak4yQ1RPVDBDRDlXUlJVUXQ1QjVIMURYTEtsZ2lXVW52SmR2VzZRS3FHanh2RklUTlNTWElScmtkaTdGMGx0SWIxdlF0YjlzVTZzQQ?oc=5", "source": "Univest", "published": "2026-09-24 08:35", "score": -0.382, "label": "Negative"}, {"symbol": "E2E", "title": "E2E Networks appoints Anand Ganapathy as Chief Revenue Officer", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNYTRVYTVWR1lSdF95cG9QR1FLMk9SOTlCWVg0NzdVR21OeTdQQXJYc2UxbkUxa2I2blpPOVRYSmVCcWNaQnVxSnpvX0RGQnhZdmp6X1JXRGxXaVk0dXZnRDV0ZTJmdFNMTzUySWNXUjZ0OWN6Y2hwcHY2cWRxLS1hZVRpdHpISHpjMnl6b0s1M1J1bHR6LWNTd1otbHEzM0ZRV2RHeUNEdmY3X2t6ZnF3YkNyRHREUDA?oc=5", "source": "scanx.trade", "published": "2026-09-24 08:21", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market crashing today? 4 factors behind the sharp fall in the Nifty and Sensex indices", "link": "https://news.google.com/rss/articles/CBMi6wFBVV95cUxNcnpYS1l4a05TYTZaQUM2enZTYmIxVThMMmd0UzZaSEczczdQSXhEU0tSSV9DdXFXdXE3SUNBem5BRV9BMUFlZF80U24xWHh1ZHM1SkRjU1p2a2NvM2NuRjdMQUswaWJkZUV6dVp1ZzVrZC1jZUdkX09JaWRSNWFOcEdOc1JFUVNRcEdfVXdYMVF4MHpnTl9zRDhLQWY2NVllQzkyMXN1Y0YzQzdSUTFoUC1nanVwcEhzNnc1NDNtbVZOSFhDVVpUM0F0ZG1VemZSZkF3eU5FSldzSEFLZGRBell3ZVA2Y01JWVhv0gHwAUFVX3lxTE1XVE1JUmZXOUd6YURZeGlua2c3dEZoZ3NQdWY4SnB2RFVOa0dnd012UlV5Mm16QmE1c1c1SHppQ2luZHZqU3lfb2llTkxTQmN3MUlpejNJOVVYb3BCaUQxZ1RSWEZBWWFwdjVlN2ZTZWVyTGZhdjVfWkNtUG50SkNhS3hNRFlFbHBhMG5DMjZXS1FGVWJnMmUtVzJueHhRa1IxdnZpaGVuU3ZJYmhUVXFGUWFNVW52ZGxYODBxWFVzMmRnNl9PMW53dGJ0Qi1EZmRaUGhzc0FLZWxnejdscjFjRDdUM0UtRWNpa1d5bm5JOA?oc=5", "source": "theweek.in", "published": "2026-09-24 07:35", "score": 0.077, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom \u2014 Ask Profit", "link": "https://news.google.com/rss/articles/CBMi4gFBVV95cUxPcjBhRnpQaFhkbGdfV3E0ZHlmUjFPQUlUQm9LTFU4UnFqSHduWnhNSEcwenhUQmM5LUxsdFNwUXN1S3gxZW9PN213QUx2TDhzUWpoNXJldnBQRmI4eTBIOE9JMGdqd3I3T2F1QVVYcVZSUF9jOEt6cnB3QWhmZ3F3Z202eHZkRXM4NHduSVVzLThxbTQ0aUJEeEJlTThhWHBFMkJ2OGJ5X0FXT3ZyWFR3MGlZeWEzWjJGU0hhejlZTFgxakpDdVVtbkV2VGJtOXU3aTh4Z0lPdmtneU5EQTNudGd30gHqAUFVX3lxTE5SeDJuQlhJbTcxaDUzbWNPNjNuZDFqLTNYYmEwR0o1QW43WVdkLW9FQUhpVExqaFluQjJwYWRVcG5NcE1ELTduTUxUVTJzQjhvVlN5YWJKa1AxaEFjYnIxempBeUNFbG1IeW94YVMwanoxOHAzNHlRSnFUbWJ3anJqQWVvb2xQeVRwZl9CQUwyUl9KSXhhTm16Qy00Uk5JdkhGU2Z5SGRzNkthQmRBN0J5WnE5bFNUREhuNC02SklqM01odWNqWjV1YTVsVUhXUUZMdlhkN09kWTdvbHhZUjFXV05sVTlGQkptQQ?oc=5", "source": "NDTV Profit", "published": "2026-09-24 07:25", "score": 0.296, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxOU0F5bUI3X2RaNWllcFpuSUpqZFp4Ui0xRVNpb2FSbVRfMjZieWxhWGV5R2N5MHpqeHBQcXIzT2dfTHBjZUt4Zk5aV2Y2SDNhM3VjamJBeTRhUjNjVklyZ3lWZDMxZ3hMMjNXaHFHWUFKV19ZaEp1WTBQekRXOU5ZdXc5UG1hQkIxRTJWdU9USDZqekc5QTh5VENqRW1ybVVCYUMwODlQRGJGVUZKV28tSVpXMFQ?oc=5", "source": "Kalkine India", "published": "2026-09-24 06:20", "score": 0.681, "label": "Positive"}, {"symbol": "MARKET", "title": "Why did market crash today? Sensex plummets 1,248 points, Nifty ends below 23,100. 5 factors behind today'", "link": "https://news.google.com/rss/articles/CBMimwJBVV95cUxNblY5UUJKckZ0My1hbEZrdS1NbjFpR0Vyam1YUHcxd1BSMDdzWkpVZzVyN0ptcnZWZ0EwRElGTEdLV1pWNFd3a05HeEpBOC1UN0NCandyUjlzUVpsUXpKZElQajdHYUoyc2dvLXdMVkNQSW5lZHNFVG1aMzVJQ0tUcENOcmR3QWIyUFNWOFo1RENRX29SbEZLVmNGdVdjSVdkYVZyM1l6dUNtaE9KYjk1VmhIVTlWUlVZNUVFekwwRGZETkw1NTFzbWhSX2xVc2RTdzdCRExjMW5LZ05EbFZRODJvcXRnbmpKZGdPRGlpeGgza1BVNFA1V0xkR2ZJUEpCNWpPZnh5aXR2MW5aQ1EzTEJBdGY5Mi1UTkZF0gGgAkFVX3lxTE9GWEM2U2ttbzdkc05MdlJqN2tFU2pGUmxYbmVIeHktdHRhWVpuaWRnUE1RN01WREtsT2x1cTBBbExxTi1sRE93d3FvWDljRGJzWHNxMW9jek9KTklxUEdnbUk1a0t0YXdlMVZvbzc4Mnh0c3hUUXMzdV9VOWV3UXdqSnRQZFJNaVNRZ1RybmpKR19rS2dNdm5HVkNlUmRUTzJrbkRuYy1fR3pRLTFLUDBZcVAxMjRrdXg5ZVF2M2NDMjgwTXZ4bktqUXNidVU1dmJKWXEzUi1NLUwxUjliSG1vU2lQeWM2S1lRdkMxbW1qSGI4M1lpSHRVS1FVXzNja3B5Q3BYalFYLXV0T3d6VXlWVVdEWTdfUVRsWFV0RlVkdg?oc=5", "source": "The Economic Times", "published": "2026-09-24 04:09", "score": -0.273, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 1,250 pts lower, Nifty ends below 23,100: 7 key factors behind market crash", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxNNmFnZnk5VzNtcVFkY1JFVlVCMFh6T3BlejFod0JXRWFjMng2alROdHU2YzRmcEVCV3VMZFdYM3hCbUFCa09PVmVkWTh1MWFaaUxhTndsdjlVb3pZZy1VZU1wWFl6WnNvUzUyZ243ZUQ2RUVIMEhVbm8tMWxWMzM0Y1N6aVlPenNvZkl5R0hmVG5JWlE2QkcxNlRDd0UwU2RSN3NscF9PR2NRVGVaRWYyVUpMeHFrYWNVcGdMNTM3MmpSVGdkc0laX1E5U2U4Q0pBM1N2cUNlQndvUGRvUHVhT2w3Qkh0UHZ4dkcwVTQwUkRMMHlY0gH6AUFVX3lxTE5jREhsTGtRRUVDMnRQMEhucHBndU15SnViUmVFb0ZxTUE1dmpUSlBMV01WYkZ6UXd4QkRncTdNZUh5VVRxNEQ1cmViQ2Z6WFViOVktS1hld09jM25FTHRYN0lJa3d2Q1NsWUxZR2VqUElmYXVFVk5wczFqMy13QUd4Ty1ER181WE5KaHE5SEhFdHZzTy15T0tnZ3pyZzhVMktvLUI2WDF2M3hTRThxVzZEeDRaU21jYUd4ZzZPbHlWRFVMN1lZVGRzcHd4bDUwTWc5d09MYks4c21iYlZKNUUyaC1GOXIzZ1ZzT3dXTWVaWm9KdVhHYzN4emc?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 03:56", "score": -0.44, "label": "Negative"}, {"symbol": "MARKET", "title": "Indian shares post worst day in 10 weeks on oil spike, proposed insurance curbs", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPRFR1dnlza0cxUU5PbXRVYmRRT19oaHZFS3NmTDZUdHhDUVpIaTJDVDFHYThvSXE3RzNWenBDSUlDUDVCdE51VkpDaXppUEl2M1htMGxsMkxPV3ZaS2d3YVhYVTlFUEphWm45cWVuYTZLYmJ2V0xwT2dtMFkwQXZ5bjVWOVh2UHczVnZUSFQ5NFBrUkJaQTJwRXFoSlY5ajhXaHJXOVd3enFaclR4QUpXODFjMWxjVVE?oc=5", "source": "Reuters", "published": "2026-09-24 02:46", "score": -0.625, "label": "Negative"}, {"symbol": "MARKET", "title": "US Dollar jumps to near two-month high. What could it mean for Indian stock markets - Sensex, Nifty impact", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPUXhSRW9fbndZUTd4Q3FFZjhsaThCbS1jNzk4Z1N2TUdiU0lpcHNQcEZ0WmpqdGZHUUlIUUhNdlNseThhQ0hkVDVNazBSQTV1SmRVNTJ6SnUyVTBEQ3pfWTBubFpaREdzcjI0VTFacmFUZzI4ajJfZXZLcU0yQ05NcG9BN1ZkYWQ4M3pJVkFmRllNRXJXeU8zWXRMRkVoQ2o5aGJOamlGaXlfYll4WDBEdGdpY21SN1o4UENfRGNSZ1E5elpxVjJ1aGVWZ1BnZGpfUFMwM0VYM0t4eHpnM3BTTlBKaFZoQkFTT3M2bWhSNlExcEZkcmRUUHZMVmNzSzlPc2fSAYcCQVVfeXFMTnBRN0FXeEh4U2V5eEYydmZXb19IdldaZk5tYU8zbVV2TFV5ZjgxOGg5cGZfdHVScXprR3dCeEQ4czVEOF9zSWpoM3MzdWVrNFphaTdJZWg3SHVac0VnOVc0Si04cUdma2xrRFRLRlJSakp5N1FobmtwdUNqRVRFNWxsYnJrbVpjRHI2RTI5dmJ0Qml3eVBLa2NTXzNhUHZzckNXVHJxVGs1clVveXhUYlk1MjdQOTE3SDZTelVJb1JpSF9wWkpjMno4X0lDdkt2TzFIVE0zVEVRaUFxNG5IVFRhTGRwVURPZlBOcTZtUmlNTTJYS0gxU2RWTkh4T2RZOHB3SFQ4RHc?oc=5", "source": "Livemint", "published": "2026-09-24 02:44", "score": 0.758, "label": "Positive"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes nearly 200 pts, signals gap-down start for Sensex, Nifty; US selloff, rising yields...", "link": "https://news.google.com/rss/articles/CBMi_gFBVV95cUxOT0tVTzVLRFhsRHJ6QVB0WV85ZGh4RHFXTEdKY1R3Snp4T1VIcXVyQmNMOGpKeDF2aVdfckZKRGVqMzVpaDlTMDU0Q0lVemMzLUxFblYwQkIxcFFvalhLYng4bVdZbUhqTnFDSDFweU93akx6V3ViVXF5cEtCbk9QSFJQTjNobXRLQUpPTGNuSlc3UkVfNGdnQ0hWbXJldU11M3hadi1FU1o5azNRZ3pIUldvMkV3b1FQYVktMldOcWZkVFhPcHI2QUdMOXQxOEY1aGN6TG13WW1yMjlQWHNYd0p5LTFkRGZqOHhHNlJIcW9pWU1VQ1k0Yy01VDRPQdIBgwJBVV95cUxOdVk4MlI1LWY0aGw5azFlQ3UtdkF1V2lVYjJBaC1UYUtRNi1FT1lTeWpTbG1jZ2dPeGtBVnFYcTdISXFqaUxJcnpuZ29EWml0UkJEN0VfeHRONWRtcGo5dG9ZTDhOWGlvemZrUWZHRWtxUVBwcFRaRno4UmpWSDIwdHh6Si1LbFFDS1E3R3hvTTRGSFA4T256enl3RjBfb1hWNEFaTEkyOHJNRXBMVng1YnJMd01TMW51ZGhta1dRRmNnc3p4TC0xa2lsMDVOQ3VoZFZzUzRGV2IzYTVzajR1Mm11ZXZ6NkNfNjJjSG5iOVNmSkVXaWozaDNwaHVTNS1MNjRF?oc=5", "source": "Moneycontrol.com", "published": "2026-09-24 02:38", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Oil Prices To US Treasury Yields \u2014 Five Key Factors For Sensex, Nifty 50 On Sept 24", "link": "https://news.google.com/rss/articles/CBMi_wFBVV95cUxNMHRUa21iWVZtelA2Um13ZTJ6ZDhOSGNJMlcyandCLUFTT0w0V3R5eWd5SEdCZ1pyOEMwSlY3ak42dHRhUjdnREc5UzdaNmI3QnFkd2RsLUk0SmhaRGNqOS1QdWp0ZVdnOExERTduSHhXZlpFb2ZHaHVneDFmaGdpVTAwa3I4RWxTT3NxUHp5ekV2YTlVd3ltNS1FLTdKN19nUzBFaHB2a1Etd0xVb0NMVDJMaG5RcGlDMDhhLUJqOWFoTmFEdXFCbDZ0SlAwTmlheHZuWEZ5dGJJdW1LQ2dGeTVtNS15Z0tmR1B2YXZ0eDR6YlFBUFRIUlRVLTZ2ZTjSAYcCQVVfeXFMTVJoelZ4TXkyUmNUWkk2RThDUWRtT1RrS0dqQUtzTHJTM1RZX0w5ZHl3b0xicjN6Z1IxS2dQUV94YWdwRGpyME1rZmVaZnZ6SGE1bW5sUlM3N2ZBYl9lajJub1AwcjJLYUc1d3pHUG5HLWUtc1VFVlc3Z0FVNXI1anMwNzA5MkZvd1YzdTRUNHpRZTBBSWpqcm05bUp0ZmxNZklyNU9LS0l0NG9uSWZCRkhYenIzaktxa3Bic25SYzVfVVdPcko2ZG95YWhraURGZ212MDJBVHBCVWxXUWVQVzZZLTFIZmVGdkdsNHF3aTNOclNEMUEtSjNsUHFCZU5JSlA5bE1aZGs?oc=5", "source": "NDTV Profit", "published": "2026-09-24 01:42", "score": 0.844, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: Stock market outlook for Thursday, 24 Sept - GIFT Nifty, Nikkei, Taiwan signals", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQTDl3ZlJyNW5xZXBBLUtBLXRfSU5kbEdSOXFWM3V2RU51eVdlanIzclZnczhweGRBR1lmWkVUNWI0SlBsbW5tWmd4SzBzNXA0Ty15d21DNVJkQ0piMXpzMDYxYkNndEtmV19UQnV6NVBKZlgzU1ltZEpEakJ5dVl3WU8xQS1DRVQxN0pxV1NuU19RaGZhTWNqSHFhRHFGUVROWDhEMkxhODZ2bmZFX1piMDl0ZzVJSVRhUU5KUC1pV0NCclR5dGxXXzR1VUNvbHMweU1xaHRIQWNIRG5HN1o4NWNlRlBlRjhRVFc2SElTNklUNEtMSXBZVmQ1YkxBOFg2eWtOOFZiMUTSAY4CQVVfeXFMTUdPNHFyRDVseGxVX1p5RDdOWFBabmJQdm1ZNmVZOVB0RGZMeERCSnFfZUMxV3FrMXBJT1liYmFZekEzWGR4cUs4eDlKOUhiNURta2xDLTM0dUFkRTJrOHNaa0djNnlJWFpQcE43OGt0SkFJNEgxSm9hd0puemtzNVgyX3dHdUtGa1VIRHJBdFllRUFmYlYwQ3Y4elV1djY2ZUo5R204dmZyZ3RwaGdZSHZrbERxQWZfRlhCUEhrZjdaelZGLXZmY2lTWm84ek9wWHYzdGRKQVFOR3pYWU94RUVERlBYOXFEeDJaUVI1and2N1hCenc4anc0NVVaRG50TF9Pa1o2di0xc3k3SDdn?oc=5", "source": "Livemint", "published": "2026-09-24 01:17", "score": 0.842, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs stock gains 1.37 percent as profit jumps 126 percent", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRGZMMkVQZFBodEJ4cHVqbng0YWJyNHJjbndja3pLdkJzamNORjlNUGNab3A1MDczV2piSTRpUG5yeklwV2ZvMWlFMGp2OVota2lsTHJoZlB6dG10UlBHeXRYNTk5NlRLVVduSzZJM0dLdFlTN2hkM29mWnhNU3lHVUlaTmlGQ25fUFo0dXhGT2cyNWlhQmllc3hiRFU3Z1RIN01VV0xHOFBTMUtoWUQxTDZUY2J0VTNxRXYyb2xhQ3c?oc=5", "source": "AD HOC NEWS", "published": "2026-09-23 22:57", "score": 0.791, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - Anlon Healthcare among 7 healthcare stocks hitting 52-week highs; rallied up to 105% in a month", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUE9BMFBTZkQ0bmQwWjZyUG4tSWp1VU1ERG50V2ptaVRoamFQX21HUDNBVmdwOG81TjVLeU1GSUZoNGIzUU5Vc0drSzhsMlZkOFl4MmstUEMyZWdYTTNING9fVnZrR0ZvS3VCYmJaVEk5aFdJRUJNWTZMMlV5Sy1iaU5ieC05WjZtaFJaQmMyaU5jTW9Oc1pmZHFsaUl3aVJ6TUJTR0s3SjYtdnE4c0NDejFJOFprT0Z0Zm1RTGFsTFlFVTVvUHo3d0lpZk16R1NmVGczYlUzZGNXb0Mwd3RQUmxKR0pRcklfUl9XRVNyMEZBZ1Fxa2FsSWtGSllrV2QwSmRSVnBOMmQ?oc=5", "source": "The Economic Times", "published": "2026-09-23 12:57", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex slips over 11,000 points from record high in 10 months; 3 triggers that may fuel the Indian stock market", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxOUExzY0ZPTTBDblhZUWV1SjVUZWd0amE1STlQN1N6bm9VajdoT2NVb1ZvVjJrcHg2WTNBYlI1SGkwMlVOU3o4NDY2ZVpRMHRkRUhVUWVaS0N5QUdNbzRLa1I4UkRhNkVwOWpaVVNxOHhFV0NxZFhGOUx4anFCRDlDb0ptMHlzWFhvTmhMTEFvSk1ybFBSTzA1SG1KQnczZVdTX1NmUktxYURuVTBFbk0ydGhjNVBNN1d0Q1lUWkZlQVBJWWJLd0NhVml5amI0STBVcEs5WW4tN1pTajJSbU1wYm5ydUdIUjdvSW04MWVkdl85NmpZVmVVVFl1YmxZaWxBTVB5bkhUSFVaMXFu0gGSAkFVX3lxTE5LZmlZbUxuSjFGRzllWHk1R0RmZ0tla0huTUZYM25TUGxFMXpWLU5rTXc0WXdXM3lTWW1nYUNmNTI2elJWcEhZOTRhZ3A2X2JOUHZ1XzBuSmRRX2ZsNGZrQVBkVDlFSExzbHc3Z0VPYjRTekszODB5QndnS1Q3NmVvRmpfdmc4QzhRcGZScWlZZ01KUE1ZVWZmSFQ0UnpKVFllOFZxY3ZIME1LX2xaZ2o5bUxoYkR6Q0JQTlN0b3ZWU19IRHRCaTRmdFZLVXo1dG1oODdLOWJhSkQ4akVrODVaQTUxZnZtLWxUNDhyTGdxMDBkS3ExQXJwbnRPQlpxTFdReTZxNEtLWGRwNnIwTEhCcGc?oc=5", "source": "Livemint", "published": "2026-09-23 11:16", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap, Sept 23: SENSEX, NIFTY50 gain as metal stocks rally, crude oil price ease; Bajaj Fin, Hindalco top gainers", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPaHBTQzhTRUdZS2tNRmJlTDU1UXJ4bnYzUXZNY1RzZWhub0dSbFFIZDM3aGZCNFJ2V2F1QmJRX3lVelpSd2ZsTkZVTF9ncUZCZ1NYblZYUjBYNi13Z19fOVhDN19taGt4MGV1Q1NtWEY4U0lrdnVXaUtFQm9TZTFUMGlzNWdoTUdBYWZxOUtWcG1idGJwOE10NTloS1hrdV9HN3lhLXZXWUh3dzA2TVVLcHRuRFJDVXdmUC1nV084LTVEV2N4OFRVQjU1Smg4Q2ktSTBKWmRCRGtRdWdWOEc5UGh0YWpOTUlNWmVyV2l0RC10T3d1YndQalotU0NWWDBqTDhn?oc=5", "source": "Upstox", "published": "2026-09-23 10:15", "score": 0.612, "label": "Positive"}, {"symbol": "DIACABS", "title": "Diamond Power Infrastructure Share Price Rises 2.68% Today", "link": "https://news.google.com/rss/articles/CBMimwFBVV95cUxNbjd5UVZ4d3N3ZUtybnEyZW1MZ1R4T0NrS1JsMEhETFc5d2tyclFHRnV4bzQ1RVQyUkZvNnIwOURYdjdBUzZldEpRN0FBV29YLVZOTjlFalZfemVpUzBVZ3BZSDJxSVFqSmdCMDVfNVNVXy1ZZVJpZUZORHdmNUFzazBrdGVsOGVPN1ZMRmdyQ0U1X3kzS1ZNZU1mQQ?oc=5", "source": "Univest", "published": "2026-09-23 10:02", "score": 0.34, "label": "Positive"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs Share Price: one-year high and valuation view", "link": "https://news.google.com/rss/articles/CBMihwFBVV95cUxPYU9VS2psbTA2SEFlWWF6NVFFbVRManpTcU0wUjJIbWRQdEU2S1JUeWVXWVUtSW1RNGp3VmdEZjRGYkdVYmFtV2tZd1BQLWJfT2ZHYzhXcFhMTVgwaDlmNmZkOHhaY0JiOEVaQmZmTk5FS1luRmcxeE9ZbGV3VDlqOWR4VFhCZEE?oc=5", "source": "Univest", "published": "2026-09-23 09:19", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "NSE IPO listing: National Stock Exchange of India to debut on September 24; check GMP &amp; other details", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQa2ZFOFYwaEJuQTl6N3NjWFFvMWUyUGdxNXlZNFJHVWxtcFNEenVuTlNieHRNX3RpY0dfNnNCUk1hMU9Ndk5Sckl3TVg1Z2lJYnFORjgtY0UySTc0WW5qVmV0bU5hd0UzTVM3OVdKUFNUUHdzbEhaTTNERlV0WTdFWTBYSnpadUhucV9mejJxMnNlZ2V2UzJaOVY0dHdfNWtMVWN3U0tkVVFuSUVSMnV5NjhTUUE5a2Zrc2xieTVkZEphNmVqSEQ1MmRqMEFKM2xwU1FCVkxkZ0VsdFZYazRiMDhKcEhsejFNOXgtSGo0bFRJWThyZkZaXzJVQWpwbklBNno4NE1QSzRfT001NktmddIBlgJBVV95cUxOdy1fS2JiOHZGWTlaelh4ak5fQTR6TU9lek4tN0tIODhtWjRtRkJmS2hhZHVLTmpSMkQ2T0dXNnk1VFlTdFRjcmE1b1dCQWYtSnVQRFh0Z1hsUUljNkZVeF9GQ2pSZmplX082cHlVWEx2aVQ0dWpyZndmREdSOUJmcHBfczhYU0ZjUVVWYU96N1J0SENVQV8tR243REJnYzZwcnNzTlFnakJWcmV6eU9yTUs3NC1FWVpwRnFiZTRrUVVtM1UxQy01YnNsN1BweXNTbGpkb1l1UTNTRzNDUDEtWjBOeVJsa2QtejEtRElXcy1LNXc5bW5FY0Q4TGhXQXNWWlgxRjlXQlNEQ1R0V1B2OVZqWHluUQ?oc=5", "source": "timesofindia.indiatimes.com", "published": "2026-09-23 07:59", "score": 0.0, "label": "Neutral"}, {"symbol": "E2E", "title": "E2E Networks Share Price news: price rise and valuation", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNS3pobG5zQUpFLU53cFlCQWxZTFQ5S0E1dDNmbTU3V2daQUx1ZTMxMjctRHphNW5OSWVoYk9UY09CU2NxbF9GWjVCZDJzeF9OTXVTX3NUYVRjZ1U3ekZnLVFxZ01Sc3dVWlZIcnZOdXdvTzVlNTdoMlhYaVZZaWNaTEpZTkxpZw?oc=5", "source": "Univest", "published": "2026-09-23 07:26", "score": 0.0, "label": "Neutral"}, {"symbol": "LAURUSLABS", "title": "Laurus Labs - 10 midcap stocks that soared up to 105% in 6 months; check FII and MF holdings", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQThVQlhqMHhQX1dCbzk5aTVLRzAzLVhTQ0kzajBZMXRVTTNTazhRNTM3Y2d5SE1fbUhYVkJkT0hDeDlCZFhGRHEtWUxEcEhISzA4bkNGUlQ2RW44NEdPa1k5VFF5MGktRHhhZHJMRjAyeUVCVmEwWkVIQ2ROQmlhdTZTY255RFg2Rkp4NWtCTk1vaGxrUFc1VTRFSkJFY1Nnakd4VXpMNGxRVkpvMkl5VnpmakQtMWgwcV90RFpwM3BwaFFfNzhsR3IzQWhRNmpCWVVjdVM1ZExSSkxZR1N1bEpNaUp0eGV5bGIyTDQzZTZjdw?oc=5", "source": "The Economic Times", "published": "2026-09-23 06:24", "score": 0.0, "label": "Neutral"}, {"symbol": "KIRLOSENG", "title": "3 Indian Nuclear Energy Stocks With Revenue Growth Up To 16%", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPa2tacGJLRFdET1pPVlhxQlRodHp4ZVZkREJLUU8yQlFiSmdib0hReElVbW5Qc2QtMnFqZWVDREFveHlPbDB5MHhGQjlBcTVfMS12Q1hyNGRFUjZrOHY0Ym9jSGhaSnV4YlZYZDZGV25jb1NtRV9admFLQWN1N1NETF9pUU1GbFFadFVXdzJ0dUxJelU3SFlaQUR0MlZxTWxHaDQ2SnpjRl9LczRSQ1BiX2h6SWl3ckJiek5mSDVwNm84cVVBYnRCSnFPYWRHLUlhUUlwb2cyN0tGdHRGU2lNdnVkdlNQZGJS0gHuAUFVX3lxTFBtQmV3OHlXVURIb1VpaGFmZnYtYjJnSFVyVjEtM2pvajJYV3BZQlZDOGtuOEZ4dG9hMDNkQmJVaXJPODNLdFdBMHJVdmRoTkRkR1NERk5DaWRlNXgyMUJmNDkzYXZzWVUwSzlIZ29CX3BueG8ySTU4Ymlod19HTFVJM1k2X1FDMmFpLXJPa3YtVjlSdi0tdjJ4UVc3MHZGR1ljSTJHdENmV0MwOHhJdmgyTEZBV0ZUN1JVR2gxOFhXSXBHdXlWTVYxT2RMdkhnY3UtN3FXOGd1UUtZYWRaWXVIR193bmsydVZRVnJNV0E?oc=5", "source": "simplywall.st", "published": "2026-09-23 05:56", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, US-Iran Talks To Oil Prices \u2014 Five Key Factors That May Drive Sensex, Nifty 50 On Sept 23", "link": "https://news.google.com/rss/articles/CBMi-AFBVV95cUxNUnltRmdqM0NYQ2wzZWItS3BOdjdlU1pUcFJ6aEtPV1Zub1hfcVR0MERkbjZzTWpuc3pFdFVxUFBSY3U5WEhLVjdOLV9tX2lSWG1yNjJzUzVWR2xhRFJ1NUctcDN6VlJtMGlZaGlpQWx3T3RBYWs0ZExick04cTBYd0tYY1dBcTV2MjFVTUtsWFdtY3NZMFFiVjYyM0JpSmpNUWVzSVJqRGpUMzUyRHc2dm1yZEgyRmNnQmpjbDFYaXZkV3NPaXgxM2ZFWGtoemxNWU9STmpkUVlSa3oydXk5bjJpMWFRWlNqM2J5Y2lCMTB4d0FoTGFNNdIBgAJBVV95cUxQYm1wblRHcjNRcnF0MG5Uel9qVFEycDNoSzNfQWx4WWoweVQzX3d3Ym5UTTM3cjVzUG9STkdXYmlzc1psbE10cUNKYTBGVlZPaTh4bEFkN0szUHJmS2wzYzRmazBKT2MxY29WZUxaWVhmdjVEbS1TU0NyeFlRVGFEbXk3R2R3OFJYc0s1bTZmbzJGZ1hDRWE4Z05Wa2lPT0FiWWRvaFlRWFFkaDNoYnBmazJfYVlhblBVMF8yMDlfVllVdk9BeVZKUzRVSXUwNUlxOE9LUVZENWw2LW8yNGhWX3VnaUxSZC04bDljRXJGZUE0RlgycFlabTVrRDVoYy1W?oc=5", "source": "NDTV Profit", "published": "2026-09-23 01:42", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty 50 prediction today: How Asian markets, crude will impact Indian markets? Gift Nifty, Kospi, Taiwan signal", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxNNi1kLW5uekpsdjNub29Fa3NDaWEzNU91MUMxNGZMS1ZVeEZPZ2tiLWZWY1M4MW84dTRYRl93QjFISTVtSG9oUHRpLUZZcE9welgydkFGTDZPRWtBbXVkaC1xOVgtWnhuNVZNVklETHgyNFdOMEo3UWFjUWx4dzI0ZlZDbXJ3cEdKMTFWZkNoeVo1OXlpUG1iLXhIUkREVElXLWozbkxtUWtmWXFxc043VHB2R0NpU2dQVVVGZlNWeXNkbVItSGk0VGZ5M202QUVzckd5bFliQUtMbE5SZ2NURVNsZW50aFZnd1RsQkJoRGVHUklpNF9iRGxCbE5XamlvWnZyVUNIM3NrdkZiYjI1MjFB0gGXAkFVX3lxTE1waWJFallWREMwLVdIUXFpMDlzd1loMmViNEdDbzVfbTJoSUxubGpLVy1NZjU1c2taUzdsczJIaG9OSmpIVFc5bUlyRjZQdzZkWVZKeVlwMG9GTTI1N0dHV09ucTJJX0hQUS1rUGtMLXhVTkNXQjNpNDVYVTQ1TmxtMmVWWGx0UVhpTDhmSGdCNlNma19TQTZadDlPa0RjZ2RfQ1dLaXFHMVZtdjNPRzFhdGVnMFYydnNJR3VGWEJiTHVvNW11dV9SbzNiaU1fSEJLeUpVY0R3UnBZbWp3NTNZN2NwU3ZFMzVhME9XVjI0cWdvdW1DZno2ZHVkTWFwMkRDUUkwdVRsYW5XQkx6M0gwX2tJYWJacw?oc=5", "source": "Livemint", "published": "2026-09-23 01:13", "score": 0.557, "label": "Positive"}, {"symbol": "RRKABEL", "title": "Here's Why R R Kabel (NSE:RRKABEL) Has Caught The Eye Of Investors", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxPeE5EWjI1ZEd2aG02OThzbUpNSXdERzVpYkNmNXRCdEFNLU1JUEk2RG9IanhndHM2N1oxMDAwblVrcXpSaVFfcmc0WEF6UUJqd09acWZQYXdzM2cwZFJkUVZVSkE5Tk9WWnhJV0ZXR19HN18tRFhCU2hqWXR5a3lBazR6UWN4UDJ0VEh3NGFxNE1oX3M2Sjhib0h5N0RvMGdUcU9zVm91ODRoaGl2dVJXc18xTnJObk9pS3BfX1lQWS1HWGUzR0lEbDZ1ZTZ1b1FlY0h6SnBCRdIB3AFBVV95cUxQbHN0Tmw0M3l2RFNtTzBTaEtMbzJ5WmE3cWRraUhSRTc3ejR4SUE2NDBvTEhqMTZPQmktdXJ5N3VwM2ZudzBPTU8zZU1tLUVIUFlVVDdCbGFaZGllcHA5UmEzLUpOU2RlU2c0YzlrTUk4ejU3UUxQM2hXTWlsU0p5eVh0blVNMmdpcERxXzFnZ1d2R3lzUzE2c21vOGxBWGlIMnR1Z25MQTlITTI4S3JIcU56YU5VVHVyUXVSU3JHZ3ZiVnZFLWVFbmR0S0dHTHVqOGw2QlZrZzg5bDFT?oc=5", "source": "simplywall.st", "published": "2026-09-23 00:46", "score": 0.0, "label": "Neutral"}], "errors": []}, "created": "2026-09-28T13:27:26", "last_updated": "2026-09-29T19:38:35", "research": {"method": "notes", "generated": "2026-09-28 13:27", "title": "Stock by stock", "stocks": {"TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD Power Systems", "view": "Bullish", "view_score": 1.5, "tone": "bull", "summary": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "why": "Guidance raised, shallow pullback. Check for a fundraise.", "points": [{"text": "The stock is 10% below its high, a shallow pullback within a strong uptrend.", "kind": "context", "source": "", "url": ""}, {"text": "Q1 FY27 revenue rose about 72% YoY.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "It raised its FY27 revenue guidance to \u20b92,600 crore.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3Afyers.in"}, {"text": "A board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending.", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}, {"text": "Valuation is stretched (P/E around 70).", "kind": "risk", "source": "5paisa", "url": "https://www.google.com/search?q=TD%20Power%20Systems%20site%3A5paisa.com"}], "short_view": "Bullish"}, "AEROFLEX": {"symbol": "AEROFLEX", "name": "Aeroflex Industries", "view": "Bullish, high risk", "view_score": 1.25, "tone": "bull", "summary": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "why": "Strong growth, expensive, volatile, thin liquidity", "points": [{"text": "Q1 FY27 revenue grew 72.4% and PAT rose 162%.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "Liquid-cooling skid capacity was raised 50%, with further expansion planned.", "kind": "catalyst", "source": "sahi", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20site%3Asahi.com"}, {"text": "P/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day).", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}, {"text": "That makes it the most fragile in a falling market.", "kind": "risk", "source": "share", "url": "https://www.google.com/search?q=Aeroflex%20Industries%20share"}], "short_view": "Bullish, risky"}, "ATHERENERG": {"symbol": "ATHERENERG", "name": "Ather Energy", "view": "Bullish, mid-pullback", "view_score": 1.25, "tone": "bull", "summary": "Q1 revenue grew 89% and the loss narrowed 71%.", "why": "Strong catalysts and brokers, but still pulling back", "points": [{"text": "Q1 revenue grew 89% and the loss narrowed 71%.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "It was also added to the MSCI India Domestic Small Cap Index.", "kind": "catalyst", "source": "indmoney", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Aindmoney.com"}, {"text": "Hero MotoCorp is lifting its stake to about 32.8%.", "kind": "catalyst", "source": "freepressjournal", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Afreepressjournal.in"}, {"text": "A global broker raised its target to \u20b91,926.", "kind": "catalyst", "source": "hdfcsky", "url": "https://www.google.com/search?q=Ather%20Energy%20site%3Ahdfcsky.com"}, {"text": "The stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run.", "kind": "context", "source": "", "url": ""}, {"text": "High oil prices are a tailwind for the EV theme.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Bullish"}, "RRKABEL": {"symbol": "RRKABEL", "name": "RR Kabel", "view": "Moderately bullish", "view_score": 1.0, "tone": "mod-bull", "summary": "Q1 PAT jumped 129% and EBITDA doubled.", "why": "Strong Q1, moderate volatility", "points": [{"text": "Q1 PAT jumped 129% and EBITDA doubled.", "kind": "catalyst", "source": "5paisa", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3A5paisa.com"}, {"text": "CLSA initiated at Outperform with a \u20b92,850 target.", "kind": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=RR%20Kabel%20site%3Afyers.in"}, {"text": "The stock is 16% off its high, so it is consolidating.", "kind": "context", "source": "", "url": ""}, {"text": "Volatility is moderate (44%), which is better than most here.", "kind": "catalyst", "source": "", "url": ""}], "short_view": "Moderately bullish"}, "E2E": {"symbol": "E2E", "name": "E2E Networks", "view": "Speculative, neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "why": "Big revenue jump, P/E near 400", "points": [{"text": "Q1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.", "kind": "catalyst", "source": "angelone", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aangelone.in"}, {"text": "P/E is about 398 and the stock fell 11.8% in the month to 18 Sep.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It has bounced since.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=E2E%20Networks%20site%3Aanandrathi.com"}, {"text": "It is an AI-theme stock with thin liquidity and gap risk in both directions.", "kind": "risk", "source": "", "url": ""}], "short_view": "Speculative"}, "ACUTAAS": {"symbol": "ACUTAAS", "name": "Acutaas Chemicals", "view": "Neutral", "view_score": 0.0, "tone": "neutral", "summary": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "why": "No catalyst, sideways trend", "points": [{"text": "It received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.", "ki</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ar", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}, "telegram_sent": "2026-09-29", "corp_actions": [], "pending_alerts": []}</t>
+          <t>nd": "catalyst", "source": "fyers", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Afyers.in"}, {"text": "Quarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar).", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is negative.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Acutaas%20Chemicals%20site%3Aanandrathi.com"}, {"text": "The price has moved sideways since June.", "kind": "risk", "source": "", "url": ""}, {"text": "There is no clear trigger for a 21-day move.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral"}, "DIACABS": {"symbol": "DIACABS", "name": "Diamond Power Infra", "view": "Neutral to bearish short term", "view_score": -1.0, "tone": "mod-bear", "summary": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "why": "Extended, weak balance sheet", "points": [{"text": "It hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Aanandrathi.com"}, {"text": "Book value per share was negative in the July data.", "kind": "risk", "source": "bajajfinserv", "url": "https://www.google.com/search?q=Diamond%20Power%20Infra%20site%3Abajajfinserv.in"}, {"text": "It is now 14% off that high.", "kind": "risk", "source": "", "url": ""}, {"text": "The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.", "kind": "context", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "Kirloskar Oil Engines", "view": "Neutral to bearish", "view_score": -1.0, "tone": "mod-bear", "summary": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "why": "Margins and momentum fading", "points": [{"text": "June-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Kirloskar%20Oil%20Engines%20site%3Aanandrathi.com"}, {"text": "The 6-1 return is \u221211% and the stock is 16.5% below its high.", "kind": "risk", "source": "", "url": ""}, {"text": "Momentum is fading.", "kind": "risk", "source": "", "url": ""}], "short_view": "Neutral to bearish"}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "Thangamayil Jewellery", "view": "Bearish", "view_score": -2.0, "tone": "bear", "summary": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "why": "Downtrend, avoid", "points": [{"text": "It hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep.", "kind": "context", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It is now about 31% below the peak.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "Q1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Thangamayil%20Jewellery%20site%3Aanandrathi.com"}, {"text": "It has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.", "kind": "risk", "source": "", "url": ""}], "short_view": "Bearish"}, "LAURUSLABS": {"symbol": "LAURUSLABS", "name": "Laurus Labs", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "why": "Relative strength near highs, lowest volatility, defensive sector", "points": [{"text": "Its close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).", "kind": "catalyst", "source": "", "url": ""}, {"text": "FY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.", "kind": "catalyst", "source": "torusdigital", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Atorusdigital.com"}, {"text": "It is up about 94% in six months and holding near highs while the index falls.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "Pharma is also defensive in a risk-off tape.", "kind": "catalyst", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}, {"text": "P/E is high, so it can still pull back.", "kind": "risk", "source": "anandrathi", "url": "https://www.google.com/search?q=Laurus%20Labs%20site%3Aanandrathi.com"}], "short_view": "Bullish"}}, "shortlist": ["LAURUSLABS", "TDPOWERSYS", "ATHERENERG", "RRKABEL", "AEROFLEX", "E2E", "ACUTAAS", "DIACABS", "KIRLOSENG", "THANGAMAYL"], "missing": []}, "research_notes": "Stock by stock\n\n1. TD Power Systems (TDPOWERSYS): bullish\n\nThe stock is 10% below its high, a shallow pullback within a strong uptrend.\nQ1 FY27 revenue rose about 72% YoY.\n5paisa\nIt raised its FY27 revenue guidance to \u20b92,600 crore.\nfyers\nA board meeting on 14 Aug was set to consider raising funds, so check whether a dilutive QIP is pending. Valuation is stretched (P/E around 70).\n5paisa\n\n2. Aeroflex Industries (AEROFLEX): bullish, high risk\n\nQ1 FY27 revenue grew 72.4% and PAT rose 162%. Liquid-cooling skid capacity was raised 50%, with further expansion planned.\nsahi\nP/E is about 102, volatility is the highest of the ten (67%), and liquidity is thin (\u20b953 cr/day). That makes it the most fragile in a falling market.\nshare\n\n3. Ather Energy (ATHERENERG): bullish, mid-pullback\n\nQ1 revenue grew 89% and the loss narrowed 71%. It was also added to the MSCI India Domestic Small Cap Index.\nindmoney\nHero MotoCorp is lifting its stake to about 32.8%.\nfreepressjournal\nA global broker raised its target to \u20b91,926.\nhdfcsky\nThe stock has slid about 16% from its early-September high, so the story is intact but the price is digesting a big run. High oil prices are a tailwind for the EV theme.\n\n4. RR Kabel (RRKABEL): moderately bullish\n\nQ1 PAT jumped 129% and EBITDA doubled.\n5paisa\nCLSA initiated at Outperform with a \u20b92,850 target.\nfyers\nThe stock is 16% off its high, so it is consolidating. Volatility is moderate (44%), which is better than most here.\n\n5. E2E Networks (E2E): speculative, neutral to bullish\n\nQ1 revenue was \u20b9156.76 crore vs \u20b936.11 crore a year earlier, with a profit of \u20b943.88 crore, on GPU cluster expansion.\nangelone\nP/E is about 398 and the stock fell 11.8% in the month to 18 Sep. It has bounced since.\nanandrathi\nIt is an AI-theme stock with thin liquidity and gap risk in both directions.\n\n6. Acutaas Chemicals (ACUTAAS): neutral\n\nIt received PLI approval for an electrolyte additives plan and commissioned a high-potency API pilot plant.\nfyers\nQuarterly revenue and profit were lower sequentially (\u20b9327 cr and \u20b976 cr in Jun vs \u20b9436 cr and \u20b9137 cr in Mar). The 6-1 return is negative.\nanandrathi\nThe price has moved sideways since June. There is no clear trigger for a 21-day move.\n\n7. Diamond Power Infra (DIACABS): neutral to bearish short term\n\nIt hit a 52-week high of about \u20b9395 on 17 Sep, up 202% in six months, with a P/E near 128.\nanandrathi\nBook value per share was negative in the July data.\nbajajfinserv\nIt is now 14% off that high. The T&amp;D order-book story is real, but the valuation and balance sheet make it a momentum-only trade.\n\n8. Kirloskar Oil Engines (KIRLOSENG): neutral to bearish\n\nJune-quarter revenue was \u20b91,482 cr vs \u20b91,284 cr a year ago, but EBITDA slipped to \u20b9176 cr from \u20b9184 cr, so margins are compressing.\nanandrathi\nThe 6-1 return is \u221211% and the stock is 16.5% below its high. Momentum is fading.\n\n9. Thangamayil Jewellery (THANGAMAYL): bearish\n\nIt hit a high of \u20b97,429 and traded near \u20b95,085 on 22 Sep. It is now about 31% below the peak.\nanandrathi\nQ1 EBITDA (\u20b9145 cr) fell from \u20b9214 cr in the March quarter.\nanandrathi\nIt has the weakest chart in the batch: a clear downtrend, a negative 6-1 return, and a gold-price-sensitive business.\n\n10. Laurus Labs (LAURUSLABS): strongest, bullish\n\nIts close is only 1.1% below its 12-month high, and its volatility is the lowest of the ten (28%).\nFY26 profit after tax was \u20b9740 crore vs \u20b9380 crore the year before.\ntorusdigital\nIt is up about 94% in six months and holding near highs while the index falls. Pharma is also defensive in a risk-off tape. P/E is high, so it can still pull back.\nanandrathi\nSwing-trade shortlist (21-session hold)\nRank\tStock\tView\tWhy\n1\tLAURUSLABS\tBullish\tRelative strength near highs, lowest volatility, defensive sector\n2\tTDPOWERSYS\tBullish\tGuidance raised, shallow pullback. Check for a fundraise.\n3\tATHERENERG\tBullish\tStrong catalysts and brokers, but still pulling back\n4\tRRKABEL\tModerately bullish\tStrong Q1, moderate volatility\n5\tAEROFLEX\tBullish, risky\tStrong growth, expensive, volatile, thin liquidity\n6\tE2E\tSpeculative\tBig revenue jump, P/E near 400\n7\tACUTAAS\tNeutral\tNo catalyst, sideways trend\n8\tDIACABS\tNeutral to bearish\tExtended, weak balance sheet\n9\tKIRLOSENG\tNeutral to bearish\tMargins and momentum fading\n10\tTHANGAMAYL\tBearish\tDowntrend, avoid\n", "fundamentals": {"TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 85.44379, "fwd_pe": 48.537815, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22649.634816, "pb": 21.047108, "rev_growth": 0.721, "earn_growth": 0.72}, "AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 102.0676, "fwd_pe": 51.85859, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 6793.8619392, "pb": 15.18935, "rev_growth": 0.724, "earn_growth": 1.582}, "ATHERENERG": {"name": "ATHER ENERGY LIMITED", "pe": null, "fwd_pe": 516.02814, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 57631.3819136, "pb": 21.641281, "rev_growth": 0.888, "earn_growth": null}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 39.837044, "fwd_pe": 27.495428, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 15576.7537664, "pb": 11.000529, "rev_growth": 0.712, "earn_growth": 0.861}, "RRKABEL": {"name": "R R KABEL LIMITED", "pe": 45.891792, "fwd_pe": 31.331299, "sector": "Industrials", "industry": "Electrical Equipment &amp; Parts", "mcap_cr": 27821.6933376, "pb": 10.807082, "rev_growth": 0.539, "earn_growth": 1.285}, "ACUTAAS": {"name": "ACUTAAS CHEMICALS LIMITED", "pe": 68.217316, "fwd_pe": 43.793648, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 26316.652544, "pb": 15.918781, "rev_growth": 0.591, "earn_growth": 0.671}, "DIACABS": {"name": "DIAMOND POWER INFRA LTD", "pe": 89.51187, "fwd_pe": null, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 20289.560576, "pb": -29.587477, "rev_growth": 1.272, "earn_growth": 2.083}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 57.251335, "fwd_pe": 37.53199, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 31168.6397952, "pb": 8.596884, "rev_growth": 0.134, "earn_growth": -0.199}, "E2E": {"name": "E2E NETWORKS LIMITED", "pe": 237.98479, "fwd_pe": null, "sector": "Technology", "industry": "Software - Infrastructure", "mcap_cr": 12859.6099072, "pb": 7.4469357, "rev_growth": 3.341, "earn_growth": null}, "LAURUSLABS": {"name": "LAURUS LABS LIMITED", "pe": 99.195854, "fwd_pe": 69.47338, "sector": "Healthcare", "industry": "Drug Manufacturers - Specialty &amp; Generic", "mcap_cr": 108640.567296, "pb": 20.480774, "rev_growth": 0.291, "earn_growth": 1.252}}, "telegram_sent": "2026-09-29", "corp_actions": [], "pending_alerts": []}</t>
         </is>
       </c>
     </row>

--- a/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
+++ b/data/batches/2026-09-28/SwingScope_2026-09-28_tracker.xlsx
@@ -1504,7 +1504,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 2 of 21  •  Holding  •  Exit ~2026-10-29  •  Updated 30-Sep-2026 16:22</t>
+          <t>Signal 2026-09-28  •  Day 2 of 21  •  Holding  •  Exit ~2026-10-29  •  Updated 30-Sep-2026 18:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2391,7 +2391,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-09-28  •  Day 2 of 21  •  Holding  •  Exit ~2026-10-29  •  Updated 30-Sep-2026 16:22</t>
+          <t>Signal 2026-09-28  •  Day 2 of 21  •  Holding  •  Exit ~2026-10-29  •  Updated 30-Sep-2026 18:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10206,7 +10206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10234,7 +10234,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fetched 2026-09-30 16:22</t>
+          <t>Fetched 2026-09-30 18:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D5" s="52" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>apacnewsnetwork.com</t>
         </is>
       </c>
       <c r="E5" s="82" t="n">
@@ -10324,21 +10324,21 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 14:54</t>
+          <t>2026-09-30 15:56</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty extend losses for third session as oil, FII selling weigh</t>
+          <t>Ahead of Market: 10 things that will decide stock market action on Thursday</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>The Indian Awaaz</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E6" s="82" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="F6" s="52" t="inlineStr">
         <is>
@@ -10359,25 +10359,25 @@
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 11:20</t>
+          <t>2026-09-30 14:54</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty fall for third day on crude prices, FII outflows</t>
+          <t>Sensex, Nifty extend losses for third session as oil, FII selling weigh</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>theindianawaaz.com</t>
         </is>
       </c>
       <c r="E7" s="82" t="n">
-        <v>-0.527</v>
+        <v>0.153</v>
       </c>
       <c r="F7" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G7" s="83" t="inlineStr">
@@ -10394,25 +10394,25 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 11:00</t>
+          <t>2026-09-30 12:22</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>Stock market prediction for tomorrow: Sensex, Nifty outlook for Thursday | Kospi, Taiwan cues to watch | 1 Oct 2026</t>
+          <t>Stock markets fall for 3rd day; Sensex drops 48 pts on fag-end selling in metal, pharma shares</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>bfsi.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="E8" s="82" t="n">
-        <v>0.402</v>
+        <v>-0.34</v>
       </c>
       <c r="F8" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G8" s="83" t="inlineStr">
@@ -10429,21 +10429,21 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 11:00</t>
+          <t>2026-09-30 11:20</t>
         </is>
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>Indian markets end September on a weak note amid global headwinds</t>
+          <t>Sensex, Nifty fall for third day on crude prices, FII outflows</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="E9" s="82" t="n">
-        <v>-0.382</v>
+        <v>-0.527</v>
       </c>
       <c r="F9" s="52" t="inlineStr">
         <is>
@@ -10464,17 +10464,17 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 10:44</t>
+          <t>2026-09-30 11:00</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>Sensex Today Ends Flat | Nifty Below 22,650 | Kirloskar Brothers Down 4%</t>
+          <t>Stock market prediction for tomorrow: Sensex, Nifty outlook for Thursday | Kospi, Taiwan cues to watch | 1 Oct 2026</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E10" s="82" t="n">
@@ -10499,21 +10499,21 @@
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 10:40</t>
+          <t>2026-09-30 11:00</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>India benchmark shares log worst month since March as oil, global rate hikes spark outflows</t>
+          <t>Indian markets end September on a weak note amid global headwinds</t>
         </is>
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>newindianexpress.com</t>
         </is>
       </c>
       <c r="E11" s="82" t="n">
-        <v>-0.494</v>
+        <v>-0.382</v>
       </c>
       <c r="F11" s="52" t="inlineStr">
         <is>
@@ -10534,21 +10534,21 @@
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 10:20</t>
+          <t>2026-09-30 10:44</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>Taking Stock: Sensex, Nifty end flat amid volatility; metal, pharma stocks drag</t>
+          <t>Sensex Today Ends Flat | Nifty Below 22,650 | Kirloskar Brothers Down 4%</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E12" s="82" t="n">
-        <v>0.202</v>
+        <v>0.402</v>
       </c>
       <c r="F12" s="52" t="inlineStr">
         <is>
@@ -10569,21 +10569,21 @@
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 09:41</t>
+          <t>2026-09-30 10:20</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty remains volatile: Where should investors put their money? Experts decode portfolio allocation</t>
+          <t>Taking Stock: Sensex, Nifty end flat amid volatility; metal, pharma stocks drag</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E13" s="82" t="n">
-        <v>0.402</v>
+        <v>0.202</v>
       </c>
       <c r="F13" s="52" t="inlineStr">
         <is>
@@ -10599,26 +10599,26 @@
     <row r="14">
       <c r="A14" s="52" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 09:26</t>
+          <t>2026-09-30 09:41</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>E2E Networks - 14 smallcap stocks defy market selloff, rally up to 105% in 3 month</t>
+          <t>Sensex, Nifty remains volatile: Where should investors put their money? Experts decode portfolio allocation</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E14" s="82" t="n">
-        <v>0.459</v>
+        <v>0.402</v>
       </c>
       <c r="F14" s="52" t="inlineStr">
         <is>
@@ -10634,30 +10634,30 @@
     <row r="15">
       <c r="A15" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 07:48</t>
+          <t>2026-09-30 09:26</t>
         </is>
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty: Here's what happened after 9MCY loss, shows 15-year history</t>
+          <t>E2E Networks - 14 smallcap stocks defy market selloff, rally up to 105% in 3 month</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E15" s="82" t="n">
-        <v>-0.026</v>
+        <v>0.459</v>
       </c>
       <c r="F15" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G15" s="83" t="inlineStr">
@@ -10674,25 +10674,25 @@
       </c>
       <c r="B16" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 05:30</t>
+          <t>2026-09-30 07:48</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>Stock Market Today, 30 September 2026: Sensex Recovers From Early Dip, Nifty Holds 22,700 as Banks Lead</t>
+          <t>Sensex, Nifty: Here's what happened after 9MCY loss, shows 15-year history</t>
         </is>
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E16" s="82" t="n">
-        <v>0.402</v>
+        <v>-0.026</v>
       </c>
       <c r="F16" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G16" s="83" t="inlineStr">
@@ -10704,17 +10704,17 @@
     <row r="17">
       <c r="A17" s="52" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 05:11</t>
+          <t>2026-09-30 05:30</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>TD Power Systems Share Price Rise Streak and Fundamentals</t>
+          <t>Stock Market Today, 30 September 2026: Sensex Recovers From Early Dip, Nifty Holds 22,700 as Banks Lead</t>
         </is>
       </c>
       <c r="D17" s="52" t="inlineStr">
@@ -10723,11 +10723,11 @@
         </is>
       </c>
       <c r="E17" s="82" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F17" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G17" s="83" t="inlineStr">
@@ -10739,30 +10739,30 @@
     <row r="18">
       <c r="A18" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 04:44</t>
+          <t>2026-09-30 05:11</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rise as Iran-US Peace Hopes Lift Markets</t>
+          <t>TD Power Systems Share Price Rise Streak and Fundamentals</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E18" s="82" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="F18" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G18" s="83" t="inlineStr">
@@ -10784,20 +10784,20 @@
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>Sensex Today Trades 203 Points Higher | Nifty Below 22,700 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+          <t>Sensex, Nifty Rise as Iran-US Peace Hopes Lift Markets</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>hdfcsky.com</t>
         </is>
       </c>
       <c r="E19" s="82" t="n">
-        <v>0.026</v>
+        <v>0.84</v>
       </c>
       <c r="F19" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G19" s="83" t="inlineStr">
@@ -10814,25 +10814,25 @@
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 04:17</t>
+          <t>2026-09-30 04:44</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>Stock markets rebound in early trade after days of losses: Sensex jumps 190 points, Nifty up 22 points</t>
+          <t>Sensex Today Trades 203 Points Higher | Nifty Below 22,700 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
         <is>
-          <t>Telegraph India</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E20" s="82" t="n">
-        <v>0.44</v>
+        <v>0.026</v>
       </c>
       <c r="F20" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G20" s="83" t="inlineStr">
@@ -10849,25 +10849,25 @@
       </c>
       <c r="B21" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 04:10</t>
+          <t>2026-09-30 04:39</t>
         </is>
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty set to post worst 9-month show in 15 years</t>
+          <t>October stock market holidays 2026: Will NSE, BSE be open on Gandhi Jayanti? Check full trading holiday...</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E21" s="82" t="n">
-        <v>-0.34</v>
+        <v>0.649</v>
       </c>
       <c r="F21" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G21" s="83" t="inlineStr">
@@ -10884,25 +10884,25 @@
       </c>
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 03:18</t>
+          <t>2026-09-30 04:10</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>Stock market today: Sensex, Nifty to open higher or lower?</t>
+          <t>Sensex, Nifty set to post worst 9-month show in 15 years</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E22" s="82" t="n">
-        <v>0.226</v>
+        <v>-0.34</v>
       </c>
       <c r="F22" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G22" s="83" t="inlineStr">
@@ -10919,21 +10919,21 @@
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 03:01</t>
+          <t>2026-09-30 03:18</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>These top 3 developments from US stock markets have a direct impact on Sensex, Nifty, Bank Nifty, Nifty IT</t>
+          <t>Stock market today: Sensex, Nifty to open higher or lower?</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E23" s="82" t="n">
-        <v>0.836</v>
+        <v>0.226</v>
       </c>
       <c r="F23" s="52" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 01:50</t>
+          <t>2026-09-30 03:01</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>Nifty rejig kicks in: BSE joins as Wipro exits; what investors need to know</t>
+          <t>These top 3 developments from US stock markets have a direct impact on Sensex, Nifty, Bank Nifty, Nifty IT</t>
         </is>
       </c>
       <c r="D24" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E24" s="82" t="n">
-        <v>0.402</v>
+        <v>0.836</v>
       </c>
       <c r="F24" s="52" t="inlineStr">
         <is>
@@ -10989,21 +10989,21 @@
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 01:46</t>
+          <t>2026-09-30 02:24</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>Nifty 50 set to log worst September in 8 years as market sell-off deepens</t>
+          <t>India benchmark shares log worst month since March as oil, global rate hikes spark outflows</t>
         </is>
       </c>
       <c r="D25" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E25" s="82" t="n">
-        <v>-0.34</v>
+        <v>-0.494</v>
       </c>
       <c r="F25" s="52" t="inlineStr">
         <is>
@@ -11024,21 +11024,21 @@
       </c>
       <c r="B26" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 01:30</t>
+          <t>2026-09-30 01:50</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors That May Drive Sensex, Nifty 50 On Sept 30</t>
+          <t>Nifty rejig kicks in: BSE joins as Wipro exits; what investors need to know</t>
         </is>
       </c>
       <c r="D26" s="52" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E26" s="82" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.402</v>
       </c>
       <c r="F26" s="52" t="inlineStr">
         <is>
@@ -11059,25 +11059,25 @@
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>2026-09-30 01:22</t>
+          <t>2026-09-30 01:46</t>
         </is>
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>Stock market outlook today 30 Sept: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>Nifty 50 set to log worst September in 8 years as market sell-off deepens</t>
         </is>
       </c>
       <c r="D27" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E27" s="82" t="n">
-        <v>0.842</v>
+        <v>-0.34</v>
       </c>
       <c r="F27" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G27" s="83" t="inlineStr">
@@ -11089,30 +11089,30 @@
     <row r="28">
       <c r="A28" s="52" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B28" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 21:57</t>
+          <t>2026-09-30 01:30</t>
         </is>
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Indian Nuclear Power Stocks To Watch</t>
+          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors That May Drive Sensex, Nifty 50 On Sept 30</t>
         </is>
       </c>
       <c r="D28" s="52" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E28" s="82" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F28" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G28" s="83" t="inlineStr">
@@ -11129,25 +11129,25 @@
       </c>
       <c r="B29" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 19:45</t>
+          <t>2026-09-30 01:22</t>
         </is>
       </c>
       <c r="C29" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty End Lower for Second Day; Global Tensions, FII Selling Hurt Investor Mood</t>
+          <t>Stock market outlook today 30 Sept: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D29" s="52" t="inlineStr">
         <is>
-          <t>The Indian Awaaz</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E29" s="82" t="n">
-        <v>-0.637</v>
+        <v>0.842</v>
       </c>
       <c r="F29" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G29" s="83" t="inlineStr">
@@ -11159,30 +11159,30 @@
     <row r="30">
       <c r="A30" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B30" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 14:34</t>
+          <t>2026-09-29 21:57</t>
         </is>
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>High derivatives activity lead to swings in Indian market on expiry day</t>
+          <t>Kirloskar Oil Engines And 2 Indian Nuclear Power Stocks To Watch</t>
         </is>
       </c>
       <c r="D30" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E30" s="82" t="n">
-        <v>0.202</v>
+        <v>0</v>
       </c>
       <c r="F30" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G30" s="83" t="inlineStr">
@@ -11199,25 +11199,25 @@
       </c>
       <c r="B31" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 12:51</t>
+          <t>2026-09-29 14:34</t>
         </is>
       </c>
       <c r="C31" s="52" t="inlineStr">
         <is>
-          <t>Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil</t>
+          <t>High derivatives activity lead to swings in Indian market on expiry day</t>
         </is>
       </c>
       <c r="D31" s="52" t="inlineStr">
         <is>
-          <t>The Federal</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E31" s="82" t="n">
-        <v>-0.226</v>
+        <v>0.202</v>
       </c>
       <c r="F31" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G31" s="83" t="inlineStr">
@@ -11234,25 +11234,25 @@
       </c>
       <c r="B32" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 11:14</t>
+          <t>2026-09-29 12:51</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%</t>
+          <t>Stock market closing: Sensex, Nifty end lower; Sept losses mount on FII selling, oil</t>
         </is>
       </c>
       <c r="D32" s="52" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>The Federal</t>
         </is>
       </c>
       <c r="E32" s="82" t="n">
-        <v>0.226</v>
+        <v>-0.226</v>
       </c>
       <c r="F32" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G32" s="83" t="inlineStr">
@@ -11269,25 +11269,25 @@
       </c>
       <c r="B33" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 10:48</t>
+          <t>2026-09-29 11:14</t>
         </is>
       </c>
       <c r="C33" s="52" t="inlineStr">
         <is>
-          <t>Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh</t>
+          <t>Stock Market Today: Sensex, Nifty Decline Amid High Oil Prices; Tata Chemicals Down 4.5%</t>
         </is>
       </c>
       <c r="D33" s="52" t="inlineStr">
         <is>
-          <t>DD India</t>
+          <t>apacnewsnetwork.com</t>
         </is>
       </c>
       <c r="E33" s="82" t="n">
-        <v>-0.34</v>
+        <v>0.226</v>
       </c>
       <c r="F33" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G33" s="83" t="inlineStr">
@@ -11304,25 +11304,25 @@
       </c>
       <c r="B34" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 10:19</t>
+          <t>2026-09-29 10:48</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%</t>
+          <t>Stock markets fall for second day as elevated oil prices, foreign fund outflows weigh</t>
         </is>
       </c>
       <c r="D34" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>ddindia.co.in</t>
         </is>
       </c>
       <c r="E34" s="82" t="n">
-        <v>0.226</v>
+        <v>-0.34</v>
       </c>
       <c r="F34" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G34" s="83" t="inlineStr">
@@ -11339,21 +11339,21 @@
       </c>
       <c r="B35" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 10:11</t>
+          <t>2026-09-29 10:19</t>
         </is>
       </c>
       <c r="C35" s="52" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026</t>
+          <t>Sensex Today Ends 242 Points Lower | Nifty Below 22,750 | Tata Chemicals Down 4.5%</t>
         </is>
       </c>
       <c r="D35" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E35" s="82" t="n">
-        <v>0.402</v>
+        <v>0.226</v>
       </c>
       <c r="F35" s="52" t="inlineStr">
         <is>
@@ -11369,30 +11369,30 @@
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B36" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 09:39</t>
+          <t>2026-09-29 10:11</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
         <is>
-          <t>TD POWER Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Wednesday | Kospi, Taiwan cues to watch | 30 Sept 2026</t>
         </is>
       </c>
       <c r="D36" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E36" s="82" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F36" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G36" s="83" t="inlineStr">
@@ -11404,30 +11404,30 @@
     <row r="37">
       <c r="A37" s="52" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B37" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 08:18</t>
+          <t>2026-09-29 09:39</t>
         </is>
       </c>
       <c r="C37" s="52" t="inlineStr">
         <is>
-          <t>AEROFLEX Share Price gains as market cap tops Rs 6,946 Cr</t>
+          <t>TD POWER Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
         </is>
       </c>
       <c r="D37" s="52" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E37" s="82" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="F37" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G37" s="83" t="inlineStr">
@@ -11439,30 +11439,30 @@
     <row r="38">
       <c r="A38" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B38" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 07:39</t>
+          <t>2026-09-29 08:18</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>Stocks down again — but what are the outliers in India’s share market slide?</t>
+          <t>AEROFLEX Share Price gains as market cap tops Rs 6,946 Cr</t>
         </is>
       </c>
       <c r="D38" s="52" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E38" s="82" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="F38" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G38" s="83" t="inlineStr">
@@ -11479,21 +11479,21 @@
       </c>
       <c r="B39" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 07:26</t>
+          <t>2026-09-29 07:39</t>
         </is>
       </c>
       <c r="C39" s="52" t="inlineStr">
         <is>
-          <t>Stock Market Today: Sensex Falls Over 1,100 Points, Nifty Below 22,800</t>
+          <t>Stocks down again — but what are the outliers in India’s share market slide?</t>
         </is>
       </c>
       <c r="D39" s="52" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="E39" s="82" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="F39" s="52" t="inlineStr">
         <is>
@@ -11514,25 +11514,25 @@
       </c>
       <c r="B40" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 07:21</t>
+          <t>2026-09-29 07:26</t>
         </is>
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>D-Street’s September blues: SENSEX, NIFTY plunge 6%; FIIs, crude, IPOs and the asset-allocation call</t>
+          <t>Stock Market Today: Sensex Falls Over 1,100 Points, Nifty Below 22,800</t>
         </is>
       </c>
       <c r="D40" s="52" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E40" s="82" t="n">
-        <v>-0.581</v>
+        <v>0.026</v>
       </c>
       <c r="F40" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G40" s="83" t="inlineStr">
@@ -11549,21 +11549,21 @@
       </c>
       <c r="B41" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 06:14</t>
+          <t>2026-09-29 07:21</t>
         </is>
       </c>
       <c r="C41" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty rebound from near six-month lows amid crude shock</t>
+          <t>D-Street’s September blues: SENSEX, NIFTY plunge 6%; FIIs, crude, IPOs and the asset-allocation call</t>
         </is>
       </c>
       <c r="D41" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E41" s="82" t="n">
-        <v>-0.66</v>
+        <v>-0.581</v>
       </c>
       <c r="F41" s="52" t="inlineStr">
         <is>
@@ -11584,25 +11584,25 @@
       </c>
       <c r="B42" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 05:55</t>
+          <t>2026-09-29 06:14</t>
         </is>
       </c>
       <c r="C42" s="52" t="inlineStr">
         <is>
-          <t>Indian Stock Market Sell-Off: Why Nifty and Bank Nifty Are Falling and What Retail Investors Should Do Now</t>
+          <t>Sensex, Nifty rebound from near six-month lows amid crude shock</t>
         </is>
       </c>
       <c r="D42" s="52" t="inlineStr">
         <is>
-          <t>SMEStreet</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E42" s="82" t="n">
-        <v>0.586</v>
+        <v>-0.66</v>
       </c>
       <c r="F42" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G42" s="83" t="inlineStr">
@@ -11619,25 +11619,25 @@
       </c>
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 05:26</t>
+          <t>2026-09-29 05:55</t>
         </is>
       </c>
       <c r="C43" s="52" t="inlineStr">
         <is>
-          <t>Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows</t>
+          <t>Indian Stock Market Sell-Off: Why Nifty and Bank Nifty Are Falling and What Retail Investors Should Do Now</t>
         </is>
       </c>
       <c r="D43" s="52" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>SMEStreet</t>
         </is>
       </c>
       <c r="E43" s="82" t="n">
-        <v>-0.599</v>
+        <v>0.586</v>
       </c>
       <c r="F43" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G43" s="83" t="inlineStr">
@@ -11654,25 +11654,25 @@
       </c>
       <c r="B44" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 05:23</t>
+          <t>2026-09-29 05:53</t>
         </is>
       </c>
       <c r="C44" s="52" t="inlineStr">
         <is>
-          <t>Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons</t>
+          <t>Sensex rises 500 pts from day's low, Nifty reclaims 22,700: Key reasons behind sharp market recovery</t>
         </is>
       </c>
       <c r="D44" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E44" s="82" t="n">
-        <v>-0.382</v>
+        <v>0.153</v>
       </c>
       <c r="F44" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G44" s="83" t="inlineStr">
@@ -11689,25 +11689,25 @@
       </c>
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 05:18</t>
+          <t>2026-09-29 05:26</t>
         </is>
       </c>
       <c r="C45" s="52" t="inlineStr">
         <is>
-          <t>5 reasons why market is down today: Sensex, Nifty hit six-month lows; India VIX spikes</t>
+          <t>Stock markets tumble in early trade dragged by elevated crude oil prices, foreign fund outflows</t>
         </is>
       </c>
       <c r="D45" s="52" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E45" s="82" t="n">
-        <v>0.077</v>
+        <v>-0.599</v>
       </c>
       <c r="F45" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G45" s="83" t="inlineStr">
@@ -11724,21 +11724,21 @@
       </c>
       <c r="B46" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 05:09</t>
+          <t>2026-09-29 05:23</t>
         </is>
       </c>
       <c r="C46" s="52" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600</t>
+          <t>Stock market crash: Why Sensex crashed 1800 points, Nifty lost 550 points in 2 days? Top 5 reasons</t>
         </is>
       </c>
       <c r="D46" s="52" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E46" s="82" t="n">
-        <v>-0.791</v>
+        <v>-0.382</v>
       </c>
       <c r="F46" s="52" t="inlineStr">
         <is>
@@ -11759,25 +11759,25 @@
       </c>
       <c r="B47" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 05:06</t>
+          <t>2026-09-29 05:18</t>
         </is>
       </c>
       <c r="C47" s="52" t="inlineStr">
         <is>
-          <t>Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for</t>
+          <t>5 reasons why market is down today: Sensex, Nifty hit six-month lows; India VIX spikes</t>
         </is>
       </c>
       <c r="D47" s="52" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="E47" s="82" t="n">
-        <v>-0.459</v>
+        <v>0.077</v>
       </c>
       <c r="F47" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G47" s="83" t="inlineStr">
@@ -11794,25 +11794,25 @@
       </c>
       <c r="B48" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:58</t>
+          <t>2026-09-29 05:09</t>
         </is>
       </c>
       <c r="C48" s="52" t="inlineStr">
         <is>
-          <t>Stock Markets Today: Sensex, Nifty Fall as Crude Oil Prices Surge, Foreign Funds Exit</t>
+          <t>Stock Market Crash: Investors Lose Rs 5.9 Lakh Crore In 90 Minutes As Sensex Tumbles Over 700 Points, Nifty Breaches 22,600</t>
         </is>
       </c>
       <c r="D48" s="52" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E48" s="82" t="n">
-        <v>-0.052</v>
+        <v>-0.791</v>
       </c>
       <c r="F48" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G48" s="83" t="inlineStr">
@@ -11829,25 +11829,25 @@
       </c>
       <c r="B49" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:38</t>
+          <t>2026-09-29 05:06</t>
         </is>
       </c>
       <c r="C49" s="52" t="inlineStr">
         <is>
-          <t>BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle</t>
+          <t>Stock market crash today: BSE Sensex continues to be in bear grip; Nifty50 below 22,600 - top reasons for</t>
         </is>
       </c>
       <c r="D49" s="52" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E49" s="82" t="n">
-        <v>0.71</v>
+        <v>-0.459</v>
       </c>
       <c r="F49" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G49" s="83" t="inlineStr">
@@ -11864,25 +11864,25 @@
       </c>
       <c r="B50" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:35</t>
+          <t>2026-09-29 04:58</t>
         </is>
       </c>
       <c r="C50" s="52" t="inlineStr">
         <is>
-          <t>Sensex Falls 400 Points; Nifty Slips Below 22,700</t>
+          <t>Stock Markets Today: Sensex, Nifty Fall as Crude Oil Prices Surge, Foreign Funds Exit</t>
         </is>
       </c>
       <c r="D50" s="52" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="E50" s="82" t="n">
-        <v>-0.318</v>
+        <v>-0.052</v>
       </c>
       <c r="F50" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G50" s="83" t="inlineStr">
@@ -11899,25 +11899,25 @@
       </c>
       <c r="B51" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:35</t>
+          <t>2026-09-29 04:38</t>
         </is>
       </c>
       <c r="C51" s="52" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
+          <t>BSE shares surge over 3%, stock to replace Wipro in Nifty 50 reshuffle</t>
         </is>
       </c>
       <c r="D51" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="E51" s="82" t="n">
-        <v>-0.477</v>
+        <v>0.71</v>
       </c>
       <c r="F51" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G51" s="83" t="inlineStr">
@@ -11929,30 +11929,30 @@
     <row r="52">
       <c r="A52" s="52" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B52" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:23</t>
+          <t>2026-09-29 04:35</t>
         </is>
       </c>
       <c r="C52" s="52" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price News: Today’s Decline Analyzed</t>
+          <t>Sensex Falls 400 Points; Nifty Slips Below 22,700</t>
         </is>
       </c>
       <c r="D52" s="52" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>hdfcsky.com</t>
         </is>
       </c>
       <c r="E52" s="82" t="n">
-        <v>-0.128</v>
+        <v>-0.318</v>
       </c>
       <c r="F52" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G52" s="83" t="inlineStr">
@@ -11969,25 +11969,25 @@
       </c>
       <c r="B53" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:23</t>
+          <t>2026-09-29 04:35</t>
         </is>
       </c>
       <c r="C53" s="52" t="inlineStr">
         <is>
-          <t>Oil rise, bond yields: Top factors behind Tuesday's stock market fall</t>
+          <t>Sensex Today Tanks 695 Points | Nifty Below 22,600 | Bajaj Finance &amp; Kotak Mahindra Top Losers</t>
         </is>
       </c>
       <c r="D53" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E53" s="82" t="n">
-        <v>-0.153</v>
+        <v>-0.477</v>
       </c>
       <c r="F53" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G53" s="83" t="inlineStr">
@@ -11999,30 +11999,30 @@
     <row r="54">
       <c r="A54" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B54" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:21</t>
+          <t>2026-09-29 04:23</t>
         </is>
       </c>
       <c r="C54" s="52" t="inlineStr">
         <is>
-          <t>No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what’s dragging the markets down?</t>
+          <t>Ather Energy Share Price News: Today’s Decline Analyzed</t>
         </is>
       </c>
       <c r="D54" s="52" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E54" s="82" t="n">
-        <v>-0.402</v>
+        <v>-0.128</v>
       </c>
       <c r="F54" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G54" s="83" t="inlineStr">
@@ -12039,21 +12039,21 @@
       </c>
       <c r="B55" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:21</t>
+          <t>2026-09-29 04:23</t>
         </is>
       </c>
       <c r="C55" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty sink further; What is keeping the market under pressure?</t>
+          <t>Oil rise, bond yields: Top factors behind Tuesday's stock market fall</t>
         </is>
       </c>
       <c r="D55" s="52" t="inlineStr">
         <is>
-          <t>newsdrum.in</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E55" s="82" t="n">
-        <v>0.128</v>
+        <v>-0.153</v>
       </c>
       <c r="F55" s="52" t="inlineStr">
         <is>
@@ -12079,20 +12079,20 @@
       </c>
       <c r="C56" s="52" t="inlineStr">
         <is>
-          <t>Why Is Share Market Falling Today? Know Key Factors Behind Sensex, Nifty Decline On September 29</t>
+          <t>No respite after Monday blues: Sensex slumps 568 points, Nifty below 22,650; what’s dragging the markets down?</t>
         </is>
       </c>
       <c r="D56" s="52" t="inlineStr">
         <is>
-          <t>News18</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="E56" s="82" t="n">
-        <v>-0.128</v>
+        <v>-0.402</v>
       </c>
       <c r="F56" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G56" s="83" t="inlineStr">
@@ -12109,25 +12109,25 @@
       </c>
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:14</t>
+          <t>2026-09-29 04:21</t>
         </is>
       </c>
       <c r="C57" s="52" t="inlineStr">
         <is>
-          <t>Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street</t>
+          <t>Sensex, Nifty sink further; What is keeping the market under pressure?</t>
         </is>
       </c>
       <c r="D57" s="52" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>newsdrum.in</t>
         </is>
       </c>
       <c r="E57" s="82" t="n">
-        <v>-0.273</v>
+        <v>0.128</v>
       </c>
       <c r="F57" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G57" s="83" t="inlineStr">
@@ -12144,25 +12144,25 @@
       </c>
       <c r="B58" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 04:02</t>
+          <t>2026-09-29 04:21</t>
         </is>
       </c>
       <c r="C58" s="52" t="inlineStr">
         <is>
-          <t>Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...</t>
+          <t>Why Is Share Market Falling Today? Know Key Factors Behind Sensex, Nifty Decline On September 29</t>
         </is>
       </c>
       <c r="D58" s="52" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>News18</t>
         </is>
       </c>
       <c r="E58" s="82" t="n">
-        <v>-0.421</v>
+        <v>-0.128</v>
       </c>
       <c r="F58" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G58" s="83" t="inlineStr">
@@ -12179,17 +12179,17 @@
       </c>
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 02:57</t>
+          <t>2026-09-29 04:14</t>
         </is>
       </c>
       <c r="C59" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty opening: Will stock market crash or open higher today?</t>
+          <t>Why is market falling today? Sensex slumps 700 points, Nifty below 22,600. 8 key factors rattling D-Street</t>
         </is>
       </c>
       <c r="D59" s="52" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E59" s="82" t="n">
@@ -12214,25 +12214,25 @@
       </c>
       <c r="B60" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 01:36</t>
+          <t>2026-09-29 04:02</t>
         </is>
       </c>
       <c r="C60" s="52" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
+          <t>Sensex settles 250 pts lower, Nifty ends below 22,750: Surging crude prices among key factors behind...</t>
         </is>
       </c>
       <c r="D60" s="52" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E60" s="82" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.421</v>
       </c>
       <c r="F60" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G60" s="83" t="inlineStr">
@@ -12249,25 +12249,25 @@
       </c>
       <c r="B61" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 01:19</t>
+          <t>2026-09-29 02:57</t>
         </is>
       </c>
       <c r="C61" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>Sensex, Nifty opening: Will stock market crash or open higher today?</t>
         </is>
       </c>
       <c r="D61" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E61" s="82" t="n">
-        <v>0.842</v>
+        <v>-0.273</v>
       </c>
       <c r="F61" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G61" s="83" t="inlineStr">
@@ -12279,26 +12279,26 @@
     <row r="62">
       <c r="A62" s="52" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B62" s="52" t="inlineStr">
         <is>
-          <t>2026-09-29 00:10</t>
+          <t>2026-09-29 01:36</t>
         </is>
       </c>
       <c r="C62" s="52" t="inlineStr">
         <is>
-          <t>3 Indian Nuclear Stocks With Earnings Growth Over 17%</t>
+          <t>Stock Market Today: Gift Nifty, Gold Rate To Bond Yields — Five Key Factors For Sensex, Nifty 50 On September 29</t>
         </is>
       </c>
       <c r="D62" s="52" t="inlineStr">
         <is>
-          <t>Simply Wall St.</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E62" s="82" t="n">
-        <v>0.888</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F62" s="52" t="inlineStr">
         <is>
@@ -12319,25 +12319,25 @@
       </c>
       <c r="B63" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 19:51</t>
+          <t>2026-09-29 01:19</t>
         </is>
       </c>
       <c r="C63" s="52" t="inlineStr">
         <is>
-          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Tuesday, 29 Sept - GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D63" s="52" t="inlineStr">
         <is>
-          <t>WION</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E63" s="82" t="n">
-        <v>-0.34</v>
+        <v>0.842</v>
       </c>
       <c r="F63" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G63" s="83" t="inlineStr">
@@ -12349,30 +12349,30 @@
     <row r="64">
       <c r="A64" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B64" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42</t>
+          <t>2026-09-29 00:10</t>
         </is>
       </c>
       <c r="C64" s="52" t="inlineStr">
         <is>
-          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
+          <t>3 Indian Nuclear Stocks With Earnings Growth Over 17%</t>
         </is>
       </c>
       <c r="D64" s="52" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Simply Wall St.</t>
         </is>
       </c>
       <c r="E64" s="82" t="n">
-        <v>-0.896</v>
+        <v>0.888</v>
       </c>
       <c r="F64" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G64" s="83" t="inlineStr">
@@ -12384,30 +12384,30 @@
     <row r="65">
       <c r="A65" s="52" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B65" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 13:25</t>
+          <t>2026-09-28 19:51</t>
         </is>
       </c>
       <c r="C65" s="52" t="inlineStr">
         <is>
-          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
+          <t>Indian stock market crashes, 7.4 lakh crore wiped out: What is driving the fall?</t>
         </is>
       </c>
       <c r="D65" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>WION</t>
         </is>
       </c>
       <c r="E65" s="82" t="n">
-        <v>0.652</v>
+        <v>-0.34</v>
       </c>
       <c r="F65" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G65" s="83" t="inlineStr">
@@ -12419,30 +12419,30 @@
     <row r="66">
       <c r="A66" s="52" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B66" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 13:16</t>
+          <t>2026-09-28 13:42</t>
         </is>
       </c>
       <c r="C66" s="52" t="inlineStr">
         <is>
-          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
+          <t>Stock market crash takes Sensex to 6-month low; index tanks 5% in a month as investors lose Rs 17 lakh cr</t>
         </is>
       </c>
       <c r="D66" s="52" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E66" s="82" t="n">
-        <v>0.361</v>
+        <v>-0.896</v>
       </c>
       <c r="F66" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G66" s="83" t="inlineStr">
@@ -12454,30 +12454,30 @@
     <row r="67">
       <c r="A67" s="52" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B67" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 11:48</t>
+          <t>2026-09-28 13:25</t>
         </is>
       </c>
       <c r="C67" s="52" t="inlineStr">
         <is>
-          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
+          <t>JINDAL SUPREME (INDIA) LTD. Stock/Share price , NSE/BSE Forecast News and Live Quotes</t>
         </is>
       </c>
       <c r="D67" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E67" s="82" t="n">
-        <v>0.153</v>
+        <v>0.652</v>
       </c>
       <c r="F67" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G67" s="83" t="inlineStr">
@@ -12489,30 +12489,30 @@
     <row r="68">
       <c r="A68" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B68" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 10:56</t>
+          <t>2026-09-28 13:16</t>
         </is>
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
+          <t>E2E Networks appoints Anand Ganapathy as Chief Revenue Officer to accelerate next phase of growth and GTM engine</t>
         </is>
       </c>
       <c r="D68" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="E68" s="82" t="n">
-        <v>-0.273</v>
+        <v>0.361</v>
       </c>
       <c r="F68" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G68" s="83" t="inlineStr">
@@ -12524,30 +12524,30 @@
     <row r="69">
       <c r="A69" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B69" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 10:48</t>
+          <t>2026-09-28 11:48</t>
         </is>
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge</t>
+          <t>Top 2 stocks to buy or sell tomorrow: Laurus Labs, Indus Towers by Chandan Taparia - Check stop-loss, targets</t>
         </is>
       </c>
       <c r="D69" s="52" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E69" s="82" t="n">
-        <v>-0.7</v>
+        <v>0.153</v>
       </c>
       <c r="F69" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G69" s="83" t="inlineStr">
@@ -12564,25 +12564,25 @@
       </c>
       <c r="B70" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 10:15</t>
+          <t>2026-09-28 10:56</t>
         </is>
       </c>
       <c r="C70" s="52" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
+          <t>Sensex Today Tanks 1,124 Points | Nifty Below 22,800 | 6 Reasons Why Indian Share Markets Are Falling</t>
         </is>
       </c>
       <c r="D70" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E70" s="82" t="n">
-        <v>0.402</v>
+        <v>-0.273</v>
       </c>
       <c r="F70" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G70" s="83" t="inlineStr">
@@ -12594,30 +12594,30 @@
     <row r="71">
       <c r="A71" s="52" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 10:06</t>
+          <t>2026-09-28 10:48</t>
         </is>
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
+          <t>Sensex Tanks 1,124 Pts to 6-Month Low Amid Crude Surge</t>
         </is>
       </c>
       <c r="D71" s="52" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="E71" s="82" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="F71" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G71" s="83" t="inlineStr">
@@ -12634,25 +12634,25 @@
       </c>
       <c r="B72" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 10:05</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="C72" s="52" t="inlineStr">
         <is>
-          <t>Sensex ends over 1,100 points lower, Nifty below 23,000; Reliance, SBI among top losers</t>
+          <t>Stock market prediction for today: Sensex, Nifty outlook for Tuesday | Kospi, Taiwan cues to watch | 29 Sept 2026</t>
         </is>
       </c>
       <c r="D72" s="52" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E72" s="82" t="n">
-        <v>-0.178</v>
+        <v>0.402</v>
       </c>
       <c r="F72" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G72" s="83" t="inlineStr">
@@ -12669,17 +12669,17 @@
       </c>
       <c r="B73" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 08:20</t>
+          <t>2026-09-28 10:06</t>
         </is>
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?</t>
+          <t>E2E Networks shareholders approve fund raise and borrowing powers</t>
         </is>
       </c>
       <c r="D73" s="52" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E73" s="82" t="n">
@@ -12699,30 +12699,30 @@
     <row r="74">
       <c r="A74" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B74" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 08:14</t>
+          <t>2026-09-28 08:20</t>
         </is>
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>Forget KOSPI, Nikkei, Nasdaq, even Pakistan's KSE surged over 100% in 2 years, leaving India's Nifty, Sensex far behind</t>
+          <t>E2E Networks (NSE:E2E): Why Has the Trading Window Been Shut from October 1, 2026?</t>
         </is>
       </c>
       <c r="D74" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E74" s="82" t="n">
-        <v>0.202</v>
+        <v>0</v>
       </c>
       <c r="F74" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G74" s="83" t="inlineStr">
@@ -12739,25 +12739,25 @@
       </c>
       <c r="B75" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 08:02</t>
+          <t>2026-09-28 08:14</t>
         </is>
       </c>
       <c r="C75" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Tumble as US-Iran Tensions Push Oil Higher</t>
+          <t>Forget KOSPI, Nikkei, Nasdaq, even Pakistan's KSE surged over 100% in 2 years, leaving India's Nifty, Sensex far behind</t>
         </is>
       </c>
       <c r="D75" s="52" t="inlineStr">
         <is>
-          <t>Free Press Kashmir</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E75" s="82" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="F75" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G75" s="83" t="inlineStr">
@@ -12839,30 +12839,30 @@
     <row r="78">
       <c r="A78" s="52" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B78" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 07:00</t>
+          <t>2026-09-28 06:47</t>
         </is>
       </c>
       <c r="C78" s="52" t="inlineStr">
         <is>
-          <t>Market News: Share Market Today, NIFTY, BSE/NSE LIVE, Sensex Today, Latest Share Market News Live Updates</t>
+          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
         </is>
       </c>
       <c r="D78" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E78" s="82" t="n">
-        <v>0.532</v>
+        <v>-0.791</v>
       </c>
       <c r="F78" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G78" s="83" t="inlineStr">
@@ -12874,26 +12874,26 @@
     <row r="79">
       <c r="A79" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B79" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 06:47</t>
+          <t>2026-09-28 05:52</t>
         </is>
       </c>
       <c r="C79" s="52" t="inlineStr">
         <is>
-          <t>Stock Market Crash: Investors Lose Nearly Rs 9 Lakh Crore As Sensex Tanks 1,180 Points; Nifty Below 22,800</t>
+          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
         </is>
       </c>
       <c r="D79" s="52" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E79" s="82" t="n">
-        <v>-0.791</v>
+        <v>-0.382</v>
       </c>
       <c r="F79" s="52" t="inlineStr">
         <is>
@@ -12909,30 +12909,30 @@
     <row r="80">
       <c r="A80" s="52" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B80" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 05:52</t>
+          <t>2026-09-28 05:37</t>
         </is>
       </c>
       <c r="C80" s="52" t="inlineStr">
         <is>
-          <t>RR Kabel Share Price Today: decline, valuation and peers</t>
+          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
         </is>
       </c>
       <c r="D80" s="52" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E80" s="82" t="n">
-        <v>-0.382</v>
+        <v>0</v>
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G80" s="83" t="inlineStr">
@@ -12944,30 +12944,30 @@
     <row r="81">
       <c r="A81" s="52" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B81" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 05:37</t>
+          <t>2026-09-28 05:18</t>
         </is>
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Other Indian Nuclear Power Stocks To Watch</t>
+          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
         </is>
       </c>
       <c r="D81" s="52" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E81" s="82" t="n">
-        <v>0</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="F81" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G81" s="83" t="inlineStr">
@@ -12984,21 +12984,21 @@
       </c>
       <c r="B82" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 05:18</t>
+          <t>2026-09-28 04:45</t>
         </is>
       </c>
       <c r="C82" s="52" t="inlineStr">
         <is>
-          <t>Stock market crash today: BSE Sensex crashes over 1,100 points, investors lose Rs 8.92 lakh crore - top r</t>
+          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
         </is>
       </c>
       <c r="D82" s="52" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="E82" s="82" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.361</v>
       </c>
       <c r="F82" s="52" t="inlineStr">
         <is>
@@ -13019,21 +13019,21 @@
       </c>
       <c r="B83" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:45</t>
+          <t>2026-09-28 04:41</t>
         </is>
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>Sensex ends over 1,100 points, Nifty also sharply low: Why went wrong with stock market down today? | Business News</t>
+          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
         </is>
       </c>
       <c r="D83" s="52" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="E83" s="82" t="n">
-        <v>-0.361</v>
+        <v>-0.758</v>
       </c>
       <c r="F83" s="52" t="inlineStr">
         <is>
@@ -13054,21 +13054,21 @@
       </c>
       <c r="B84" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:41</t>
+          <t>2026-09-28 04:25</t>
         </is>
       </c>
       <c r="C84" s="52" t="inlineStr">
         <is>
-          <t>Investors Lose Rs 5 Lakh Crore In An Hour: 5 Reasons Behind Market Crash Today</t>
+          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
         </is>
       </c>
       <c r="D84" s="52" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E84" s="82" t="n">
-        <v>-0.758</v>
+        <v>-0.34</v>
       </c>
       <c r="F84" s="52" t="inlineStr">
         <is>
@@ -13089,21 +13089,21 @@
       </c>
       <c r="B85" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:25</t>
+          <t>2026-09-28 04:17</t>
         </is>
       </c>
       <c r="C85" s="52" t="inlineStr">
         <is>
-          <t>Why is market down today: Sensex, Nifty fall in Monday trade - Top 3 factors behind plunge</t>
+          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
         </is>
       </c>
       <c r="D85" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E85" s="82" t="n">
-        <v>-0.34</v>
+        <v>-0.511</v>
       </c>
       <c r="F85" s="52" t="inlineStr">
         <is>
@@ -13124,21 +13124,21 @@
       </c>
       <c r="B86" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:17</t>
+          <t>2026-09-28 04:11</t>
         </is>
       </c>
       <c r="C86" s="52" t="inlineStr">
         <is>
-          <t>Sensex crashes over 1,100 points, investors lose Rs 6 lakh crore: Why are markets falling?</t>
+          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
         </is>
       </c>
       <c r="D86" s="52" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E86" s="82" t="n">
-        <v>-0.511</v>
+        <v>-0.586</v>
       </c>
       <c r="F86" s="52" t="inlineStr">
         <is>
@@ -13159,21 +13159,21 @@
       </c>
       <c r="B87" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:11</t>
+          <t>2026-09-28 04:08</t>
         </is>
       </c>
       <c r="C87" s="52" t="inlineStr">
         <is>
-          <t>Mkt crash wipes off ₹7.4 trn; Sensex down 1,180 pts intraday: 5 key factors</t>
+          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l</t>
         </is>
       </c>
       <c r="D87" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E87" s="82" t="n">
-        <v>-0.586</v>
+        <v>-0.649</v>
       </c>
       <c r="F87" s="52" t="inlineStr">
         <is>
@@ -13194,21 +13194,21 @@
       </c>
       <c r="B88" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:08</t>
+          <t>2026-09-28 04:07</t>
         </is>
       </c>
       <c r="C88" s="52" t="inlineStr">
         <is>
-          <t>Why did stock market crash today? Sensex tumbles 1,124 points, Nifty below 22,800; 6 factors behind Rs 8 l</t>
+          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
         </is>
       </c>
       <c r="D88" s="52" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E88" s="82" t="n">
-        <v>-0.649</v>
+        <v>-0.44</v>
       </c>
       <c r="F88" s="52" t="inlineStr">
         <is>
@@ -13224,30 +13224,30 @@
     <row r="89">
       <c r="A89" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B89" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:07</t>
+          <t>2026-09-28 04:01</t>
         </is>
       </c>
       <c r="C89" s="52" t="inlineStr">
         <is>
-          <t>Monday mayhem: Sensex settles 1,100 pts lower, Nifty ends below 22,800; key factors behind market crash</t>
+          <t>Kirloskar Oil Engines ESOP 2019 Share Allotment Explained</t>
         </is>
       </c>
       <c r="D89" s="52" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E89" s="82" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="F89" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G89" s="83" t="inlineStr">
@@ -13259,30 +13259,30 @@
     <row r="90">
       <c r="A90" s="52" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B90" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 04:01</t>
+          <t>2026-09-28 03:58</t>
         </is>
       </c>
       <c r="C90" s="52" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines ESOP 2019 Share Allotment Explained</t>
+          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
         </is>
       </c>
       <c r="D90" s="52" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E90" s="82" t="n">
-        <v>0</v>
+        <v>0.296</v>
       </c>
       <c r="F90" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G90" s="83" t="inlineStr">
@@ -13299,25 +13299,25 @@
       </c>
       <c r="B91" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 03:58</t>
+          <t>2026-09-28 03:54</t>
         </is>
       </c>
       <c r="C91" s="52" t="inlineStr">
         <is>
-          <t>Sensex Tanks 1,000 Points To Breach Support Level, Nifty Below 22,800 — Five Reasons Behind Sell-Off</t>
+          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
         </is>
       </c>
       <c r="D91" s="52" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E91" s="82" t="n">
-        <v>0.296</v>
+        <v>-0.494</v>
       </c>
       <c r="F91" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G91" s="83" t="inlineStr">
@@ -13334,21 +13334,21 @@
       </c>
       <c r="B92" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 03:54</t>
+          <t>2026-09-28 03:48</t>
         </is>
       </c>
       <c r="C92" s="52" t="inlineStr">
         <is>
-          <t>Stock market live updates today: BSE Sensex tumbles over 1,000 points, NSE Nifty50 trades below 22,900</t>
+          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
         </is>
       </c>
       <c r="D92" s="52" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="E92" s="82" t="n">
-        <v>-0.494</v>
+        <v>-0.44</v>
       </c>
       <c r="F92" s="52" t="inlineStr">
         <is>
@@ -13369,21 +13369,21 @@
       </c>
       <c r="B93" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 03:48</t>
+          <t>2026-09-28 02:19</t>
         </is>
       </c>
       <c r="C93" s="52" t="inlineStr">
         <is>
-          <t>Sensex over 900 points down after longest weekly losing streak in years; crude soars above $106 | Business News</t>
+          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
         </is>
       </c>
       <c r="D93" s="52" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E93" s="82" t="n">
-        <v>-0.44</v>
+        <v>-0.542</v>
       </c>
       <c r="F93" s="52" t="inlineStr">
         <is>
@@ -13404,25 +13404,25 @@
       </c>
       <c r="B94" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 02:19</t>
+          <t>2026-09-28 01:20</t>
         </is>
       </c>
       <c r="C94" s="52" t="inlineStr">
         <is>
-          <t>Indian shares slide to near six-month low as US-Iran deadlock lifts oil prices</t>
+          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
         </is>
       </c>
       <c r="D94" s="52" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E94" s="82" t="n">
-        <v>-0.542</v>
+        <v>0.842</v>
       </c>
       <c r="F94" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G94" s="83" t="inlineStr">
@@ -13434,26 +13434,26 @@
     <row r="95">
       <c r="A95" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B95" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 01:20</t>
+          <t>2026-09-28 00:30</t>
         </is>
       </c>
       <c r="C95" s="52" t="inlineStr">
         <is>
-          <t>Sensex, Nifty 50 prediction today: Stock market outlook for Monday, 28 Sept - GIFT Nifty, Kospi, Nikkei signals</t>
+          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
         </is>
       </c>
       <c r="D95" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E95" s="82" t="n">
-        <v>0.842</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F95" s="52" t="inlineStr">
         <is>
@@ -13469,26 +13469,26 @@
     <row r="96">
       <c r="A96" s="52" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B96" s="52" t="inlineStr">
         <is>
-          <t>2026-09-28 00:30</t>
+          <t>2026-09-27 17:20</t>
         </is>
       </c>
       <c r="C96" s="52" t="inlineStr">
         <is>
-          <t>Which AI Infrastructure Stock is Better: E2E Networks vs ESDS Software Solutions vs Netweb Technologies?</t>
+          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
         </is>
       </c>
       <c r="D96" s="52" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E96" s="82" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="F96" s="52" t="inlineStr">
         <is>
@@ -13504,30 +13504,30 @@
     <row r="97">
       <c r="A97" s="52" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B97" s="52" t="inlineStr">
         <is>
-          <t>2026-09-27 17:20</t>
+          <t>2026-09-27 11:03</t>
         </is>
       </c>
       <c r="C97" s="52" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals posts 70% profit surge in Q1 FY27 on pharma demand</t>
+          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
         </is>
       </c>
       <c r="D97" s="52" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E97" s="82" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="F97" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G97" s="83" t="inlineStr">
@@ -13544,25 +13544,25 @@
       </c>
       <c r="B98" s="52" t="inlineStr">
         <is>
-          <t>2026-09-27 11:03</t>
+          <t>2026-09-27 09:48</t>
         </is>
       </c>
       <c r="C98" s="52" t="inlineStr">
         <is>
-          <t>Ahead of Market: 10 things that will decide stock market action on Monday</t>
+          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
         </is>
       </c>
       <c r="D98" s="52" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E98" s="82" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="F98" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G98" s="83" t="inlineStr">
@@ -13579,12 +13579,12 @@
       </c>
       <c r="B99" s="52" t="inlineStr">
         <is>
-          <t>2026-09-27 09:48</t>
+          <t>2026-09-27 04:22</t>
         </is>
       </c>
       <c r="C99" s="52" t="inlineStr">
         <is>
-          <t>Stock market prediction: Experts see more pain ahead but see bottom in Oct 2026 amid Nifty, Sensex poor show — 3 reasons</t>
+          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
         </is>
       </c>
       <c r="D99" s="52" t="inlineStr">
@@ -13593,11 +13593,11 @@
         </is>
       </c>
       <c r="E99" s="82" t="n">
-        <v>-0.44</v>
+        <v>0.842</v>
       </c>
       <c r="F99" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G99" s="83" t="inlineStr">
@@ -13609,30 +13609,30 @@
     <row r="100">
       <c r="A100" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B100" s="52" t="inlineStr">
         <is>
-          <t>2026-09-27 04:22</t>
+          <t>2026-09-26 22:56</t>
         </is>
       </c>
       <c r="C100" s="52" t="inlineStr">
         <is>
-          <t>Stock market prediction for today: Sensex, Nifty Monday, 28 Sept triggers | GIFT Nifty, Nikkei, Taiwan, Kospi cues</t>
+          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
         </is>
       </c>
       <c r="D100" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E100" s="82" t="n">
-        <v>0.842</v>
+        <v>0</v>
       </c>
       <c r="F100" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G100" s="83" t="inlineStr">
@@ -13644,22 +13644,22 @@
     <row r="101">
       <c r="A101" s="52" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B101" s="52" t="inlineStr">
         <is>
-          <t>2026-09-26 22:56</t>
+          <t>2026-09-26 06:30</t>
         </is>
       </c>
       <c r="C101" s="52" t="inlineStr">
         <is>
-          <t>3 Indian Nuclear Stocks To Own In September 2026</t>
+          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
         </is>
       </c>
       <c r="D101" s="52" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E101" s="82" t="n">
@@ -13679,30 +13679,30 @@
     <row r="102">
       <c r="A102" s="52" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B102" s="52" t="inlineStr">
         <is>
-          <t>2026-09-26 06:30</t>
+          <t>2026-09-26 00:50</t>
         </is>
       </c>
       <c r="C102" s="52" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery THANGAMAYL Trading Window Closure Q2 FY27</t>
+          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
         </is>
       </c>
       <c r="D102" s="52" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Alice Blue</t>
         </is>
       </c>
       <c r="E102" s="82" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="F102" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G102" s="83" t="inlineStr">
@@ -13714,30 +13714,30 @@
     <row r="103">
       <c r="A103" s="52" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B103" s="52" t="inlineStr">
         <is>
-          <t>2026-09-26 00:50</t>
+          <t>2026-09-25 14:34</t>
         </is>
       </c>
       <c r="C103" s="52" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure के शेयर में 7% की बढ़त; कंपनी को पावर केबल्स के लिए ₹93 करोड़ का EPC ऑर्डर मिलने के बाद।</t>
+          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
         </is>
       </c>
       <c r="D103" s="52" t="inlineStr">
         <is>
-          <t>Alice Blue</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="E103" s="82" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="F103" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G103" s="83" t="inlineStr">
@@ -13749,30 +13749,30 @@
     <row r="104">
       <c r="A104" s="52" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B104" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 14:34</t>
+          <t>2026-09-25 14:04</t>
         </is>
       </c>
       <c r="C104" s="52" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Engines And 2 Indian Nuclear Stocks To Watch</t>
+          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
         </is>
       </c>
       <c r="D104" s="52" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E104" s="82" t="n">
-        <v>0</v>
+        <v>0.681</v>
       </c>
       <c r="F104" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G104" s="83" t="inlineStr">
@@ -13784,30 +13784,30 @@
     <row r="105">
       <c r="A105" s="52" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B105" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 14:04</t>
+          <t>2026-09-25 12:52</t>
         </is>
       </c>
       <c r="C105" s="52" t="inlineStr">
         <is>
-          <t>R R Kabel board approves proposal to acquire U M Cables’ optical fibre cable business; shares rally 72% YTD</t>
+          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
         </is>
       </c>
       <c r="D105" s="52" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="E105" s="82" t="n">
-        <v>0.681</v>
+        <v>-0.382</v>
       </c>
       <c r="F105" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G105" s="83" t="inlineStr">
@@ -13819,30 +13819,30 @@
     <row r="106">
       <c r="A106" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B106" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 12:52</t>
+          <t>2026-09-25 12:22</t>
         </is>
       </c>
       <c r="C106" s="52" t="inlineStr">
         <is>
-          <t>India shares log longest weekly losing run since 2020 as oil prices bite</t>
+          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
         </is>
       </c>
       <c r="D106" s="52" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E106" s="82" t="n">
-        <v>-0.382</v>
+        <v>0</v>
       </c>
       <c r="F106" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G106" s="83" t="inlineStr">
@@ -13854,30 +13854,30 @@
     <row r="107">
       <c r="A107" s="52" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B107" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 12:22</t>
+          <t>2026-09-25 11:56</t>
         </is>
       </c>
       <c r="C107" s="52" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery Share: Bull Case vs Bear Case for 2026</t>
+          <t>Two years ago Sensex hit lifetime high: What went wrong after that &amp; what’s the road ahead?</t>
         </is>
       </c>
       <c r="D107" s="52" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E107" s="82" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="F107" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G107" s="83" t="inlineStr">
@@ -13889,30 +13889,30 @@
     <row r="108">
       <c r="A108" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B108" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 11:56</t>
+          <t>2026-09-25 11:42</t>
         </is>
       </c>
       <c r="C108" s="52" t="inlineStr">
         <is>
-          <t>Two years ago Sensex hit lifetime high: What went wrong after that &amp; what’s the road ahead?</t>
+          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
         </is>
       </c>
       <c r="D108" s="52" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="E108" s="82" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="F108" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G108" s="83" t="inlineStr">
@@ -13924,30 +13924,30 @@
     <row r="109">
       <c r="A109" s="52" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B109" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 11:42</t>
+          <t>2026-09-25 10:31</t>
         </is>
       </c>
       <c r="C109" s="52" t="inlineStr">
         <is>
-          <t>RR Kabel enters optical fibre cable segment with ₹77 crore U M Cables acquisition</t>
+          <t>Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date</t>
         </is>
       </c>
       <c r="D109" s="52" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>indmoney.com</t>
         </is>
       </c>
       <c r="E109" s="82" t="n">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="F109" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G109" s="83" t="inlineStr">
@@ -13959,30 +13959,30 @@
     <row r="110">
       <c r="A110" s="52" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B110" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 10:31</t>
+          <t>2026-09-25 07:00</t>
         </is>
       </c>
       <c r="C110" s="52" t="inlineStr">
         <is>
-          <t>Thangamayil Jewellery Ltd Dividend History, Yield &amp; Record Date</t>
+          <t>Sah Polymers Share Price</t>
         </is>
       </c>
       <c r="D110" s="52" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E110" s="82" t="n">
-        <v>0.572</v>
+        <v>0</v>
       </c>
       <c r="F110" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G110" s="83" t="inlineStr">
@@ -13994,7 +13994,7 @@
     <row r="111">
       <c r="A111" s="52" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B111" s="52" t="inlineStr">
@@ -14004,20 +14004,20 @@
       </c>
       <c r="C111" s="52" t="inlineStr">
         <is>
-          <t>Sah Polymers Share Price</t>
+          <t>Nifty Chemicals (NFTCHEMIC) Share Price</t>
         </is>
       </c>
       <c r="D111" s="52" t="inlineStr">
         <is>
-          <t>upstox.com</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="E111" s="82" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F111" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G111" s="83" t="inlineStr">
@@ -14029,7 +14029,7 @@
     <row r="112">
       <c r="A112" s="52" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B112" s="52" t="inlineStr">
@@ -14039,20 +14039,20 @@
       </c>
       <c r="C112" s="52" t="inlineStr">
         <is>
-          <t>Nifty Chemicals (NFTCHEMIC) Share Price</t>
+          <t>LAURUSLABS Outlook for the Week (September 28, 2026 – October 02, 2026)</t>
         </is>
       </c>
       <c r="D112" s="52" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="E112" s="82" t="n">
-        <v>0.402</v>
+        <v>0</v>
       </c>
       <c r="F112" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G112" s="83" t="inlineStr">
@@ -14064,26 +14064,26 @@
     <row r="113">
       <c r="A113" s="52" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B113" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 07:00</t>
+          <t>2026-09-25 06:49</t>
         </is>
       </c>
       <c r="C113" s="52" t="inlineStr">
         <is>
-          <t>LAURUSLABS Outlook for the Week (September 28, 2026 – October 02, 2026)</t>
+          <t>Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today</t>
         </is>
       </c>
       <c r="D113" s="52" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E113" s="82" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="F113" s="52" t="inlineStr">
         <is>
@@ -14099,26 +14099,26 @@
     <row r="114">
       <c r="A114" s="52" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B114" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 06:49</t>
+          <t>2026-09-25 06:34</t>
         </is>
       </c>
       <c r="C114" s="52" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure (DIACABS-BE) Share Price Falls 3.54% Today</t>
+          <t>Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore</t>
         </is>
       </c>
       <c r="D114" s="52" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E114" s="82" t="n">
-        <v>-0.052</v>
+        <v>0</v>
       </c>
       <c r="F114" s="52" t="inlineStr">
         <is>
@@ -14134,30 +14134,30 @@
     <row r="115">
       <c r="A115" s="52" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B115" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 06:34</t>
+          <t>2026-09-25 05:52</t>
         </is>
       </c>
       <c r="C115" s="52" t="inlineStr">
         <is>
-          <t>Usha Martin sells optical fibre manufacturing business to R R Kabel for Rs 77 crore</t>
+          <t>Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons</t>
         </is>
       </c>
       <c r="D115" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E115" s="82" t="n">
-        <v>0</v>
+        <v>0.727</v>
       </c>
       <c r="F115" s="52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G115" s="83" t="inlineStr">
@@ -14174,21 +14174,21 @@
       </c>
       <c r="B116" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 05:52</t>
+          <t>2026-09-25 05:32</t>
         </is>
       </c>
       <c r="C116" s="52" t="inlineStr">
         <is>
-          <t>Decoded: Sensex lost nearly 3300 points, Nifty dip 1000 since announcement of blockbuster GDP of India | Top 3 reasons</t>
+          <t>NSE shares dip on day 2 of listing, brokerages back long-term growth story</t>
         </is>
       </c>
       <c r="D116" s="52" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E116" s="82" t="n">
-        <v>0.727</v>
+        <v>0.361</v>
       </c>
       <c r="F116" s="52" t="inlineStr">
         <is>
@@ -14209,25 +14209,25 @@
       </c>
       <c r="B117" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 05:32</t>
+          <t>2026-09-25 03:51</t>
         </is>
       </c>
       <c r="C117" s="52" t="inlineStr">
         <is>
-          <t>NSE shares dip on day 2 of listing, brokerages back long-term growth story</t>
+          <t>Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050</t>
         </is>
       </c>
       <c r="D117" s="52" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E117" s="82" t="n">
-        <v>0.361</v>
+        <v>-0.494</v>
       </c>
       <c r="F117" s="52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G117" s="83" t="inlineStr">
@@ -14239,30 +14239,30 @@
     <row r="118">
       <c r="A118" s="52" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B118" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 03:51</t>
+          <t>2026-09-25 02:49</t>
         </is>
       </c>
       <c r="C118" s="52" t="inlineStr">
         <is>
-          <t>Stock market today: BSE Sensex tumbles in afternoon trade, NSE Nifty50 trades below 23,050</t>
+          <t>Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others</t>
         </is>
       </c>
       <c r="D118" s="52" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>ET Now</t>
         </is>
       </c>
       <c r="E118" s="82" t="n">
-        <v>-0.494</v>
+        <v>-0.052</v>
       </c>
       <c r="F118" s="52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G118" s="83" t="inlineStr">
@@ -14274,26 +14274,26 @@
     <row r="119">
       <c r="A119" s="52" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B119" s="52" t="inlineStr">
         <is>
-          <t>2026-09-25 02:49</t>
+          <t>2026-09-25 02:06</t>
         </is>
       </c>
       <c r="C119" s="52" t="inlineStr">
         <is>
-          <t>Stocks to BUY, SELL or HOLD Today, Sept 25: Adani Power, NSE, PB Fintech, Laurus Labs and others</t>
+          <t>Trade Spotlight: How should you trade HBL Engineering, Arvind, Inventurus Knowledge Solutions, RR Kabel,...</t>
         </is>
      